--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dc549f2659ed9bd7/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61849" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{019C507C-1DE4-4613-B8AC-898FBE42BC86}"/>
+  <xr:revisionPtr revIDLastSave="61852" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7A0598E-9562-466C-B47A-374C156B2E0C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10053,9 +10053,6 @@
     <t xml:space="preserve">68496217 1 pantalla hasta el 06 de septiembre </t>
   </si>
   <si>
-    <t>63867856 1 pantalla hasta el 06 de septiembre</t>
-  </si>
-  <si>
     <t>Trac060826</t>
   </si>
   <si>
@@ -12367,6 +12364,9 @@
   </si>
   <si>
     <t>N005 1 pantalla hasta el 12 de octubre 120926-1420v</t>
+  </si>
+  <si>
+    <t>N005 1 pantalla hasta el 12 de octubre 120926-1445r</t>
   </si>
 </sst>
 </file>
@@ -30369,7 +30369,7 @@
   <sheetData>
     <row r="1" spans="1:11" s="30" customFormat="1">
       <c r="A1" s="30" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="B1" s="30">
         <v>60389752</v>
@@ -30381,7 +30381,7 @@
         <v>2030</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="F1" s="30" t="s">
         <v>2099</v>
@@ -30401,12 +30401,12 @@
         <v>2146</v>
       </c>
       <c r="D2" s="148" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="148" customFormat="1">
       <c r="A3" s="148" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="B3" s="148" t="s">
         <v>2703</v>
@@ -30420,7 +30420,7 @@
     </row>
     <row r="4" spans="1:11" s="30" customFormat="1">
       <c r="A4" s="30" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="B4" s="30">
         <v>60389752</v>
@@ -30432,7 +30432,7 @@
         <v>2028</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="F4" s="30" t="s">
         <v>2099</v>
@@ -30452,7 +30452,7 @@
         <v>2160</v>
       </c>
       <c r="D5" s="148" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="148" customFormat="1">
@@ -30483,7 +30483,7 @@
         <v>2911</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="F7" s="30" t="s">
         <v>2104</v>
@@ -30508,7 +30508,7 @@
     </row>
     <row r="9" spans="1:11" s="148" customFormat="1">
       <c r="A9" s="148" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="B9" s="148" t="s">
         <v>1213</v>
@@ -30525,7 +30525,7 @@
     </row>
     <row r="10" spans="1:11" s="429" customFormat="1">
       <c r="A10" s="429" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B10" s="429">
         <v>60389752</v>
@@ -30562,7 +30562,7 @@
         <v>2165</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>3276</v>
+        <v>3275</v>
       </c>
       <c r="F13" s="30" t="s">
         <v>2164</v>
@@ -30574,7 +30574,7 @@
     </row>
     <row r="14" spans="1:11" s="148" customFormat="1">
       <c r="A14" s="226" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="B14" s="226" t="s">
         <v>1691</v>
@@ -30588,7 +30588,7 @@
     </row>
     <row r="15" spans="1:11" s="148" customFormat="1">
       <c r="A15" s="226" t="s">
-        <v>3606</v>
+        <v>3605</v>
       </c>
       <c r="B15" s="422">
         <v>62439069</v>
@@ -30611,10 +30611,10 @@
         <v>1541</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>3277</v>
+        <v>3276</v>
       </c>
       <c r="F16" s="32" t="s">
         <v>1542</v>
@@ -30623,21 +30623,21 @@
         <v>198</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="I16" s="32" t="s">
-        <v>3437</v>
+        <v>3436</v>
       </c>
       <c r="J16" s="32" t="s">
+        <v>3358</v>
+      </c>
+      <c r="K16" s="30" t="s">
         <v>3359</v>
-      </c>
-      <c r="K16" s="30" t="s">
-        <v>3360</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="164" customFormat="1">
       <c r="A17" s="253" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="B17" s="253" t="s">
         <v>1405</v>
@@ -30680,10 +30680,10 @@
         <v>1504</v>
       </c>
       <c r="D19" s="145" t="s">
-        <v>3675</v>
+        <v>3674</v>
       </c>
       <c r="E19" s="145" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="F19" s="145" t="s">
         <v>1371</v>
@@ -30698,7 +30698,7 @@
     </row>
     <row r="20" spans="1:11" s="298" customFormat="1">
       <c r="A20" s="164" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="B20" s="164">
         <v>68444421</v>
@@ -30707,7 +30707,7 @@
         <v>1697</v>
       </c>
       <c r="D20" s="253" t="s">
-        <v>3084</v>
+        <v>3083</v>
       </c>
       <c r="E20" s="253" t="s">
         <v>1698</v>
@@ -30720,7 +30720,7 @@
         <v>1702</v>
       </c>
       <c r="D21" s="164" t="s">
-        <v>3676</v>
+        <v>3675</v>
       </c>
       <c r="E21" s="164" t="s">
         <v>1703</v>
@@ -30728,7 +30728,7 @@
     </row>
     <row r="22" spans="1:11" s="30" customFormat="1">
       <c r="A22" s="32" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
       <c r="B22" s="32">
         <v>60389752</v>
@@ -30740,7 +30740,7 @@
         <v>2143</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="F22" s="30" t="s">
         <v>2098</v>
@@ -30769,7 +30769,7 @@
         <v>2139</v>
       </c>
       <c r="D24" s="148" t="s">
-        <v>3678</v>
+        <v>3677</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="30" customFormat="1">
@@ -30786,7 +30786,7 @@
         <v>1538</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
       <c r="F25" s="30" t="s">
         <v>1371</v>
@@ -30834,7 +30834,7 @@
     </row>
     <row r="28" spans="1:11" s="30" customFormat="1">
       <c r="A28" s="30" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="B28" s="30">
         <v>60389752</v>
@@ -30846,7 +30846,7 @@
         <v>2025</v>
       </c>
       <c r="E28" s="30" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="F28" s="305" t="s">
         <v>2176</v>
@@ -30871,7 +30871,7 @@
     </row>
     <row r="30" spans="1:11" s="164" customFormat="1">
       <c r="A30" s="164" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
       <c r="B30" s="164">
         <v>62782770</v>
@@ -30880,24 +30880,24 @@
         <v>2397</v>
       </c>
       <c r="D30" s="164" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="30" customFormat="1">
       <c r="A31" s="30" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>3150</v>
+        <v>3149</v>
       </c>
       <c r="C31" s="252" t="s">
         <v>1916</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="E31" s="30" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="F31" s="30" t="s">
         <v>2047</v>
@@ -30906,16 +30906,16 @@
         <v>198</v>
       </c>
       <c r="H31" s="30" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="I31" s="192" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="J31" s="427" t="s">
-        <v>3174</v>
-      </c>
-      <c r="K31" s="217" t="s">
-        <v>2918</v>
+        <v>3173</v>
+      </c>
+      <c r="K31" s="145" t="s">
+        <v>3689</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="163" customFormat="1">
@@ -30961,7 +30961,7 @@
         <v>2111</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
       <c r="F34" s="30" t="s">
         <v>2102</v>
@@ -31012,10 +31012,10 @@
         <v>2023</v>
       </c>
       <c r="D37" s="30" t="s">
-        <v>3296</v>
+        <v>3295</v>
       </c>
       <c r="E37" s="30" t="s">
-        <v>3027</v>
+        <v>3026</v>
       </c>
       <c r="F37" s="30" t="s">
         <v>2092</v>
@@ -31024,21 +31024,21 @@
         <v>198</v>
       </c>
       <c r="H37" s="30" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="I37" s="30" t="s">
-        <v>3330</v>
+        <v>3329</v>
       </c>
       <c r="J37" s="30" t="s">
-        <v>3677</v>
+        <v>3676</v>
       </c>
       <c r="K37" s="30" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="147" customFormat="1">
       <c r="A38" s="147" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="B38" s="147" t="s">
         <v>2701</v>
@@ -31070,16 +31070,16 @@
         <v>2526</v>
       </c>
       <c r="B40" s="32" t="s">
-        <v>3306</v>
+        <v>3305</v>
       </c>
       <c r="C40" s="252" t="s">
         <v>1678</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>3648</v>
+        <v>3647</v>
       </c>
       <c r="E40" s="30" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
       <c r="F40" s="30" t="s">
         <v>2107</v>
@@ -31088,21 +31088,21 @@
         <v>198</v>
       </c>
       <c r="H40" s="30" t="s">
-        <v>3235</v>
+        <v>3234</v>
       </c>
       <c r="I40" s="32" t="s">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="J40" s="32" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
       <c r="K40" s="145" t="s">
-        <v>3649</v>
+        <v>3648</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="163" customFormat="1">
       <c r="A41" s="163" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="B41" s="163">
         <v>68381893</v>
@@ -31134,7 +31134,7 @@
     </row>
     <row r="43" spans="1:11" s="30" customFormat="1">
       <c r="A43" s="30" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B43" s="30">
         <v>60389752</v>
@@ -31146,7 +31146,7 @@
         <v>2051</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="F43" s="30" t="s">
         <v>2140</v>
@@ -31157,7 +31157,7 @@
     </row>
     <row r="44" spans="1:11" s="164" customFormat="1">
       <c r="A44" s="164" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="B44" s="164">
         <v>68381893</v>
@@ -31174,7 +31174,7 @@
     </row>
     <row r="45" spans="1:11" s="163" customFormat="1">
       <c r="A45" s="163" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="B45" s="163">
         <v>64079861</v>
@@ -31203,7 +31203,7 @@
         <v>2905</v>
       </c>
       <c r="E46" s="30" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="F46" s="30" t="s">
         <v>2124</v>
@@ -31249,16 +31249,16 @@
         <v>1512</v>
       </c>
       <c r="B49" s="30" t="s">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="C49" s="134" t="s">
         <v>2014</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
       <c r="E49" s="30" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="F49" s="30" t="s">
         <v>2110</v>
@@ -31267,16 +31267,16 @@
         <v>198</v>
       </c>
       <c r="H49" s="30" t="s">
-        <v>3259</v>
+        <v>3258</v>
       </c>
       <c r="I49" s="30" t="s">
-        <v>3317</v>
+        <v>3316</v>
       </c>
       <c r="J49" s="435" t="s">
         <v>2880</v>
       </c>
       <c r="K49" s="32" t="s">
-        <v>3423</v>
+        <v>3422</v>
       </c>
     </row>
     <row r="50" spans="1:11" s="164" customFormat="1">
@@ -31304,7 +31304,7 @@
         <v>2022</v>
       </c>
       <c r="D51" s="164" t="s">
-        <v>3221</v>
+        <v>3220</v>
       </c>
     </row>
     <row r="52" spans="1:11" s="139" customFormat="1">
@@ -31318,10 +31318,10 @@
         <v>1374</v>
       </c>
       <c r="D52" s="139" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="E52" s="139" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
       <c r="F52" s="139" t="s">
         <v>2108</v>
@@ -31330,16 +31330,16 @@
         <v>198</v>
       </c>
       <c r="H52" s="140" t="s">
-        <v>3264</v>
+        <v>3263</v>
       </c>
       <c r="I52" s="140" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
       <c r="J52" s="30" t="s">
-        <v>3393</v>
+        <v>3392</v>
       </c>
       <c r="K52" s="270" t="s">
-        <v>3137</v>
+        <v>3136</v>
       </c>
     </row>
     <row r="53" spans="1:11" s="164" customFormat="1">
@@ -31380,7 +31380,7 @@
     </row>
     <row r="55" spans="1:11" s="30" customFormat="1">
       <c r="A55" s="30" t="s">
-        <v>3659</v>
+        <v>3658</v>
       </c>
       <c r="B55" s="30">
         <v>61130088</v>
@@ -31392,7 +31392,7 @@
         <v>2018</v>
       </c>
       <c r="E55" s="30" t="s">
-        <v>3276</v>
+        <v>3275</v>
       </c>
       <c r="F55" s="30" t="s">
         <v>2125</v>
@@ -31409,10 +31409,10 @@
         <v>60433915</v>
       </c>
       <c r="C56" s="405" t="s">
-        <v>3287</v>
+        <v>3286</v>
       </c>
       <c r="D56" s="375" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="E56" s="164"/>
     </row>
@@ -31421,13 +31421,13 @@
         <v>2526</v>
       </c>
       <c r="B57" s="163" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="C57" s="405" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="D57" s="375" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="E57" s="164"/>
     </row>
@@ -31445,7 +31445,7 @@
         <v>2844</v>
       </c>
       <c r="E58" s="30" t="s">
-        <v>3350</v>
+        <v>3349</v>
       </c>
       <c r="F58" s="30" t="s">
         <v>2137</v>
@@ -31454,16 +31454,16 @@
         <v>198</v>
       </c>
       <c r="H58" s="30" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="I58" s="30" t="s">
-        <v>3304</v>
+        <v>3303</v>
       </c>
       <c r="J58" s="30" t="s">
-        <v>3397</v>
+        <v>3396</v>
       </c>
       <c r="K58" s="217" t="s">
-        <v>3028</v>
+        <v>3027</v>
       </c>
     </row>
     <row r="59" spans="1:11" s="393" customFormat="1">
@@ -31478,7 +31478,7 @@
         <v>158</v>
       </c>
       <c r="B61" s="30" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="C61" s="134" t="s">
         <v>2091</v>
@@ -31487,7 +31487,7 @@
         <v>2908</v>
       </c>
       <c r="E61" s="30" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="F61" s="30" t="s">
         <v>2092</v>
@@ -31496,21 +31496,21 @@
         <v>198</v>
       </c>
       <c r="H61" s="30" t="s">
-        <v>3569</v>
+        <v>3568</v>
       </c>
       <c r="I61" s="30" t="s">
-        <v>3324</v>
+        <v>3323</v>
       </c>
       <c r="J61" s="30" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
       <c r="K61" s="30" t="s">
-        <v>3523</v>
+        <v>3522</v>
       </c>
     </row>
     <row r="62" spans="1:11" s="147" customFormat="1">
       <c r="A62" s="147" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
       <c r="B62" s="147">
         <v>60196388</v>
@@ -31519,7 +31519,7 @@
         <v>1483</v>
       </c>
       <c r="D62" s="376" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="E62" s="148" t="s">
         <v>1391</v>
@@ -31527,7 +31527,7 @@
     </row>
     <row r="63" spans="1:11" s="163" customFormat="1">
       <c r="A63" s="163" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="B63" s="163">
         <v>62960567</v>
@@ -31536,7 +31536,7 @@
         <v>2076</v>
       </c>
       <c r="D63" s="375" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="E63" s="164"/>
     </row>
@@ -31551,10 +31551,10 @@
         <v>1677</v>
       </c>
       <c r="D64" s="30" t="s">
-        <v>3436</v>
+        <v>3435</v>
       </c>
       <c r="E64" s="30" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="F64" s="30" t="s">
         <v>2109</v>
@@ -31563,16 +31563,16 @@
         <v>198</v>
       </c>
       <c r="H64" s="32" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="I64" s="32" t="s">
-        <v>3609</v>
+        <v>3608</v>
       </c>
       <c r="J64" s="30" t="s">
-        <v>3486</v>
+        <v>3485</v>
       </c>
       <c r="K64" s="30" t="s">
-        <v>3305</v>
+        <v>3304</v>
       </c>
     </row>
     <row r="65" spans="1:11" s="164" customFormat="1">
@@ -31594,7 +31594,7 @@
     </row>
     <row r="66" spans="1:11" s="164" customFormat="1">
       <c r="A66" s="253" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
       <c r="B66" s="164">
         <v>62090364</v>
@@ -31611,7 +31611,7 @@
     </row>
     <row r="67" spans="1:11" s="30" customFormat="1">
       <c r="A67" s="254" t="s">
-        <v>3617</v>
+        <v>3616</v>
       </c>
       <c r="B67" s="285" t="s">
         <v>1924</v>
@@ -31620,10 +31620,10 @@
         <v>1681</v>
       </c>
       <c r="D67" s="30" t="s">
-        <v>3104</v>
+        <v>3103</v>
       </c>
       <c r="E67" s="30" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="F67" s="30" t="s">
         <v>2113</v>
@@ -31632,21 +31632,21 @@
         <v>198</v>
       </c>
       <c r="H67" s="30" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="I67" s="30" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="J67" s="30" t="s">
-        <v>3647</v>
+        <v>3646</v>
       </c>
       <c r="K67" s="30" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
     </row>
     <row r="68" spans="1:11" s="147" customFormat="1">
       <c r="A68" s="147" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
       <c r="B68" s="147">
         <v>68741448</v>
@@ -31655,7 +31655,7 @@
         <v>1892</v>
       </c>
       <c r="D68" s="376" t="s">
-        <v>3257</v>
+        <v>3256</v>
       </c>
       <c r="E68" s="148"/>
     </row>
@@ -31670,7 +31670,7 @@
         <v>2112</v>
       </c>
       <c r="D69" s="148" t="s">
-        <v>2983</v>
+        <v>2982</v>
       </c>
     </row>
     <row r="70" spans="1:11" s="30" customFormat="1">
@@ -31678,16 +31678,16 @@
         <v>467</v>
       </c>
       <c r="B70" s="32" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="C70" s="252" t="s">
         <v>1680</v>
       </c>
       <c r="D70" s="30" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="E70" s="30" t="s">
-        <v>3351</v>
+        <v>3350</v>
       </c>
       <c r="F70" s="30" t="s">
         <v>2151</v>
@@ -31696,13 +31696,13 @@
         <v>198</v>
       </c>
       <c r="H70" s="32" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
       <c r="I70" s="30" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="J70" s="32" t="s">
-        <v>3428</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="71" spans="1:11" s="164" customFormat="1">
@@ -31716,12 +31716,12 @@
         <v>1978</v>
       </c>
       <c r="D71" s="164" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
     </row>
     <row r="72" spans="1:11" s="163" customFormat="1">
       <c r="A72" s="269" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="B72" s="269" t="s">
         <v>1465</v>
@@ -31736,7 +31736,7 @@
     </row>
     <row r="73" spans="1:11" s="30" customFormat="1">
       <c r="A73" s="30" t="s">
-        <v>3438</v>
+        <v>3437</v>
       </c>
       <c r="B73" s="30">
         <v>60389752</v>
@@ -31748,7 +31748,7 @@
         <v>2856</v>
       </c>
       <c r="E73" s="30" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="F73" s="30" t="s">
         <v>2046</v>
@@ -31759,7 +31759,7 @@
     </row>
     <row r="74" spans="1:11" s="147" customFormat="1">
       <c r="A74" s="147" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="B74" s="147">
         <v>64226974</v>
@@ -31783,7 +31783,7 @@
         <v>1962</v>
       </c>
       <c r="D75" s="148" t="s">
-        <v>3332</v>
+        <v>3331</v>
       </c>
       <c r="E75" s="148"/>
     </row>
@@ -31798,10 +31798,10 @@
         <v>1891</v>
       </c>
       <c r="D76" s="30" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
       <c r="E76" s="30" t="s">
-        <v>3227</v>
+        <v>3226</v>
       </c>
       <c r="F76" s="30" t="s">
         <v>2124</v>
@@ -31810,16 +31810,16 @@
         <v>198</v>
       </c>
       <c r="H76" s="30" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
       <c r="I76" s="30" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="J76" s="30" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="K76" s="30" t="s">
-        <v>3404</v>
+        <v>3403</v>
       </c>
     </row>
     <row r="77" spans="1:11" s="152" customFormat="1">
@@ -31835,16 +31835,16 @@
         <v>143</v>
       </c>
       <c r="B79" s="30" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="C79" s="134" t="s">
         <v>2021</v>
       </c>
       <c r="D79" s="30" t="s">
-        <v>3080</v>
+        <v>3079</v>
       </c>
       <c r="E79" s="30" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="F79" s="30" t="s">
         <v>2103</v>
@@ -31853,16 +31853,16 @@
         <v>198</v>
       </c>
       <c r="H79" s="32" t="s">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="I79" s="32" t="s">
-        <v>3301</v>
+        <v>3300</v>
       </c>
       <c r="J79" s="30" t="s">
-        <v>3667</v>
+        <v>3666</v>
       </c>
       <c r="K79" s="30" t="s">
-        <v>3340</v>
+        <v>3339</v>
       </c>
     </row>
     <row r="80" spans="1:11" s="147" customFormat="1">
@@ -31882,7 +31882,7 @@
     </row>
     <row r="81" spans="1:11" s="147" customFormat="1">
       <c r="A81" s="149" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="B81" s="147">
         <v>64720128</v>
@@ -31899,10 +31899,10 @@
     </row>
     <row r="82" spans="1:11" s="30" customFormat="1">
       <c r="A82" s="30" t="s">
-        <v>3311</v>
+        <v>3310</v>
       </c>
       <c r="B82" s="30" t="s">
-        <v>3310</v>
+        <v>3309</v>
       </c>
       <c r="C82" s="22" t="s">
         <v>1917</v>
@@ -31911,7 +31911,7 @@
         <v>2887</v>
       </c>
       <c r="E82" s="30" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="F82" s="30" t="s">
         <v>1918</v>
@@ -31920,16 +31920,16 @@
         <v>198</v>
       </c>
       <c r="H82" s="30" t="s">
-        <v>3616</v>
+        <v>3615</v>
       </c>
       <c r="I82" s="30" t="s">
-        <v>3453</v>
+        <v>3452</v>
       </c>
       <c r="J82" s="30" t="s">
-        <v>3604</v>
+        <v>3603</v>
       </c>
       <c r="K82" s="217" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
     </row>
     <row r="83" spans="1:11" s="148" customFormat="1">
@@ -31971,7 +31971,7 @@
         <v>694</v>
       </c>
       <c r="D85" s="30" t="s">
-        <v>3454</v>
+        <v>3453</v>
       </c>
       <c r="E85" s="30" t="s">
         <v>1807</v>
@@ -31983,16 +31983,16 @@
         <v>493</v>
       </c>
       <c r="H85" s="30" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
       <c r="I85" s="442" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="J85" s="30" t="s">
-        <v>3596</v>
+        <v>3595</v>
       </c>
       <c r="K85" s="215" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
     </row>
     <row r="86" spans="1:11" s="147" customFormat="1">
@@ -32015,7 +32015,7 @@
     </row>
     <row r="87" spans="1:11" s="147" customFormat="1">
       <c r="A87" s="147" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B87" s="147" t="s">
         <v>913</v>
@@ -32033,16 +32033,16 @@
     </row>
     <row r="88" spans="1:11" s="30" customFormat="1">
       <c r="A88" s="145" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
       <c r="B88" s="30" t="s">
-        <v>3681</v>
+        <v>3680</v>
       </c>
       <c r="C88" s="153" t="s">
         <v>695</v>
       </c>
       <c r="D88" s="30" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="E88" s="30" t="s">
         <v>1091</v>
@@ -32054,16 +32054,16 @@
         <v>1539</v>
       </c>
       <c r="H88" s="30" t="s">
-        <v>3030</v>
+        <v>3029</v>
       </c>
       <c r="I88" s="30" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="J88" s="32" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="K88" s="30" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
     </row>
     <row r="89" spans="1:11" s="147" customFormat="1">
@@ -32086,7 +32086,7 @@
     </row>
     <row r="90" spans="1:11" s="148" customFormat="1">
       <c r="A90" s="226" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B90" s="148">
         <v>67381873</v>
@@ -32104,7 +32104,7 @@
     </row>
     <row r="91" spans="1:11" s="106" customFormat="1">
       <c r="A91" s="250" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="B91" s="32" t="s">
         <v>1411</v>
@@ -32113,7 +32113,7 @@
         <v>46</v>
       </c>
       <c r="D91" s="106" t="s">
-        <v>3308</v>
+        <v>3307</v>
       </c>
       <c r="E91" s="106" t="s">
         <v>1133</v>
@@ -32125,16 +32125,16 @@
         <v>66</v>
       </c>
       <c r="H91" s="30" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="I91" s="31" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="J91" s="32" t="s">
-        <v>3136</v>
+        <v>3135</v>
       </c>
       <c r="K91" s="30" t="s">
-        <v>3429</v>
+        <v>3428</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="411" customFormat="1">
@@ -32165,7 +32165,7 @@
         <v>1734</v>
       </c>
       <c r="D93" s="148" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
     </row>
     <row r="94" spans="1:11" s="32" customFormat="1">
@@ -32182,7 +32182,7 @@
         <v>1372</v>
       </c>
       <c r="E94" s="32" t="s">
-        <v>3581</v>
+        <v>3580</v>
       </c>
       <c r="F94" s="32" t="s">
         <v>1373</v>
@@ -32215,7 +32215,7 @@
         <v>1390</v>
       </c>
       <c r="D96" s="148" t="s">
-        <v>3682</v>
+        <v>3681</v>
       </c>
       <c r="E96" s="148" t="s">
         <v>1389</v>
@@ -32226,16 +32226,16 @@
         <v>1430</v>
       </c>
       <c r="B97" s="30" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="C97" s="153" t="s">
         <v>2011</v>
       </c>
       <c r="D97" s="30" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="E97" s="30" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="F97" s="30" t="s">
         <v>1918</v>
@@ -32244,16 +32244,16 @@
         <v>198</v>
       </c>
       <c r="H97" s="32" t="s">
-        <v>3627</v>
+        <v>3626</v>
       </c>
       <c r="I97" s="30" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="J97" s="30" t="s">
-        <v>3476</v>
+        <v>3475</v>
       </c>
       <c r="K97" s="439" t="s">
-        <v>3650</v>
+        <v>3649</v>
       </c>
     </row>
     <row r="98" spans="1:13" s="393" customFormat="1">
@@ -32266,19 +32266,19 @@
     </row>
     <row r="100" spans="1:13" s="30" customFormat="1">
       <c r="A100" s="145" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
       <c r="B100" s="30" t="s">
-        <v>3687</v>
+        <v>3686</v>
       </c>
       <c r="C100" s="252" t="s">
         <v>2886</v>
       </c>
       <c r="D100" s="30" t="s">
-        <v>3479</v>
+        <v>3478</v>
       </c>
       <c r="E100" s="30" t="s">
-        <v>3230</v>
+        <v>3229</v>
       </c>
       <c r="F100" s="30" t="s">
         <v>1918</v>
@@ -32287,16 +32287,16 @@
         <v>198</v>
       </c>
       <c r="H100" s="30" t="s">
-        <v>3618</v>
+        <v>3617</v>
       </c>
       <c r="I100" s="145" t="s">
+        <v>3687</v>
+      </c>
+      <c r="J100" s="30" t="s">
+        <v>3657</v>
+      </c>
+      <c r="K100" s="145" t="s">
         <v>3688</v>
-      </c>
-      <c r="J100" s="30" t="s">
-        <v>3658</v>
-      </c>
-      <c r="K100" s="145" t="s">
-        <v>3689</v>
       </c>
     </row>
     <row r="101" spans="1:13" s="393" customFormat="1">
@@ -32309,19 +32309,19 @@
     </row>
     <row r="103" spans="1:13" s="30" customFormat="1">
       <c r="A103" s="30" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B103" s="30" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="C103" s="252" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
       <c r="D103" s="30" t="s">
+        <v>3324</v>
+      </c>
+      <c r="E103" s="30" t="s">
         <v>3325</v>
-      </c>
-      <c r="E103" s="30" t="s">
-        <v>3326</v>
       </c>
       <c r="F103" s="30" t="s">
         <v>1918</v>
@@ -32330,16 +32330,16 @@
         <v>198</v>
       </c>
       <c r="H103" s="30" t="s">
-        <v>3327</v>
+        <v>3326</v>
       </c>
       <c r="I103" s="30" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="J103" s="30" t="s">
-        <v>3392</v>
+        <v>3391</v>
       </c>
       <c r="K103" s="30" t="s">
-        <v>3354</v>
+        <v>3353</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -32374,22 +32374,22 @@
     </row>
     <row r="106" spans="1:13" s="30" customFormat="1">
       <c r="A106" s="30" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="B106" s="30">
         <v>62724019</v>
       </c>
       <c r="C106" s="252" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="D106" s="30" t="s">
+        <v>3157</v>
+      </c>
+      <c r="E106" s="30" t="s">
+        <v>3159</v>
+      </c>
+      <c r="F106" s="30" t="s">
         <v>3158</v>
-      </c>
-      <c r="E106" s="30" t="s">
-        <v>3160</v>
-      </c>
-      <c r="F106" s="30" t="s">
-        <v>3159</v>
       </c>
       <c r="G106" s="30" t="s">
         <v>59</v>
@@ -32408,7 +32408,7 @@
         <v>157</v>
       </c>
       <c r="B112" s="285" t="s">
-        <v>3177</v>
+        <v>3176</v>
       </c>
       <c r="C112" s="134" t="s">
         <v>2008</v>
@@ -32451,7 +32451,7 @@
         <v>1998</v>
       </c>
       <c r="E127" s="30" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="F127" t="s">
         <v>1996</v>
@@ -32471,7 +32471,7 @@
         <v>1968</v>
       </c>
       <c r="E128" s="30" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -32485,10 +32485,10 @@
         <v>2763</v>
       </c>
       <c r="D129" s="378" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="E129" s="30" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -32505,7 +32505,7 @@
         <v>2638</v>
       </c>
       <c r="E130" s="30" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -32522,7 +32522,7 @@
         <v>1974</v>
       </c>
       <c r="E131" s="30" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="133" spans="1:6" s="121" customFormat="1" ht="23.5">
@@ -32544,7 +32544,7 @@
         <v>2380</v>
       </c>
       <c r="E134" s="30" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="F134" t="s">
         <v>1349</v>
@@ -32564,7 +32564,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>3659</v>
+        <v>3658</v>
       </c>
       <c r="B139">
         <v>64720128</v>
@@ -32593,7 +32593,7 @@
         <v>1985</v>
       </c>
       <c r="D140" s="378" t="s">
-        <v>3294</v>
+        <v>3293</v>
       </c>
       <c r="E140" s="30" t="s">
         <v>1984</v>
@@ -32624,7 +32624,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="C143" s="1" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -32668,7 +32668,7 @@
         <v>2385</v>
       </c>
       <c r="E153" s="30" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -32676,16 +32676,16 @@
         <v>1512</v>
       </c>
       <c r="B154" t="s">
-        <v>3505</v>
+        <v>3504</v>
       </c>
       <c r="C154" t="s">
         <v>2250</v>
       </c>
       <c r="D154" s="378" t="s">
-        <v>3504</v>
+        <v>3503</v>
       </c>
       <c r="E154" s="30" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -32702,7 +32702,7 @@
         <v>2639</v>
       </c>
       <c r="E155" s="30" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -32716,10 +32716,10 @@
         <v>2260</v>
       </c>
       <c r="D156" s="378" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="E156" s="30" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -32736,7 +32736,7 @@
         <v>2527</v>
       </c>
       <c r="E157" s="30" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -32753,7 +32753,7 @@
         <v>2679</v>
       </c>
       <c r="E158" s="30" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -32767,15 +32767,15 @@
         <v>2549</v>
       </c>
       <c r="D159" s="378" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="E159" s="30" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="B160">
         <v>65133588</v>
@@ -32787,12 +32787,12 @@
         <v>2550</v>
       </c>
       <c r="E160" s="30" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="4" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>1147</v>
@@ -32801,10 +32801,10 @@
         <v>2640</v>
       </c>
       <c r="D161" s="378" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="E161" s="30" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -32818,10 +32818,10 @@
         <v>2552</v>
       </c>
       <c r="D162" s="378" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="E162" s="30" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -32832,18 +32832,18 @@
         <v>12369714760</v>
       </c>
       <c r="C163" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="D163" s="378" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="E163" s="30" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="4" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>2192</v>
@@ -32855,12 +32855,12 @@
         <v>2528</v>
       </c>
       <c r="E164" s="30" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="B165">
         <v>66315726</v>
@@ -32872,7 +32872,7 @@
         <v>2299</v>
       </c>
       <c r="E165" s="30" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -32889,24 +32889,24 @@
         <v>2299</v>
       </c>
       <c r="E166" s="30" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="B167">
         <v>68818154</v>
       </c>
       <c r="C167" t="s">
-        <v>3508</v>
+        <v>3507</v>
       </c>
       <c r="D167" s="378" t="s">
         <v>2641</v>
       </c>
       <c r="E167" s="30" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -32920,10 +32920,10 @@
         <v>2765</v>
       </c>
       <c r="D168" s="378" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="E168" s="30" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -32940,7 +32940,7 @@
         <v>2801</v>
       </c>
       <c r="E169" s="30" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -32957,7 +32957,7 @@
         <v>2525</v>
       </c>
       <c r="E170" s="30" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -32974,12 +32974,12 @@
         <v>2340</v>
       </c>
       <c r="E171" s="30" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="B172">
         <v>66935922</v>
@@ -32988,10 +32988,10 @@
         <v>2352</v>
       </c>
       <c r="D172" s="378" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="E172" s="30" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -33005,10 +33005,10 @@
         <v>2353</v>
       </c>
       <c r="D173" s="378" t="s">
-        <v>3333</v>
+        <v>3332</v>
       </c>
       <c r="E173" s="30" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -33022,10 +33022,10 @@
         <v>2354</v>
       </c>
       <c r="D174" s="378" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="E174" s="30" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -33039,15 +33039,15 @@
         <v>2804</v>
       </c>
       <c r="D175" s="378" t="s">
-        <v>3376</v>
+        <v>3375</v>
       </c>
       <c r="E175" s="30" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="B176">
         <v>66935922</v>
@@ -33056,10 +33056,10 @@
         <v>2805</v>
       </c>
       <c r="D176" s="220" t="s">
-        <v>3410</v>
+        <v>3409</v>
       </c>
       <c r="E176" s="30" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -33070,13 +33070,13 @@
         <v>63503223</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="D177" s="220" t="s">
         <v>2876</v>
       </c>
       <c r="E177" s="30" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -33093,12 +33093,12 @@
         <v>2824</v>
       </c>
       <c r="E178" s="30" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="B179">
         <v>68570552</v>
@@ -33107,15 +33107,15 @@
         <v>2807</v>
       </c>
       <c r="D179" s="220" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="E179" s="30" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="B180">
         <v>69964218</v>
@@ -33124,15 +33124,15 @@
         <v>2829</v>
       </c>
       <c r="D180" s="378" t="s">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="E180" s="30" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B181">
         <v>63950696</v>
@@ -33144,12 +33144,12 @@
         <v>2830</v>
       </c>
       <c r="E181" s="30" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="4" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B182" t="s">
         <v>2861</v>
@@ -33161,7 +33161,7 @@
         <v>2830</v>
       </c>
       <c r="E182" s="30" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -33178,7 +33178,7 @@
         <v>2912</v>
       </c>
       <c r="E183" s="30" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -33186,7 +33186,7 @@
         <v>2903</v>
       </c>
       <c r="B184" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="C184" t="s">
         <v>2901</v>
@@ -33195,12 +33195,12 @@
         <v>2913</v>
       </c>
       <c r="E184" s="30" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="49" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="B185">
         <v>68201775</v>
@@ -33212,12 +33212,12 @@
         <v>2916</v>
       </c>
       <c r="E185" s="30" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="B186">
         <v>60240509</v>
@@ -33226,10 +33226,10 @@
         <v>2868</v>
       </c>
       <c r="D186" s="378" t="s">
+        <v>3610</v>
+      </c>
+      <c r="E186" s="30" t="s">
         <v>3611</v>
-      </c>
-      <c r="E186" s="30" t="s">
-        <v>3612</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -33243,10 +33243,10 @@
         <v>2869</v>
       </c>
       <c r="D187" s="378" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="E187" s="30" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -33263,7 +33263,7 @@
         <v>2876</v>
       </c>
       <c r="E188" s="30" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -33280,7 +33280,7 @@
         <v>2876</v>
       </c>
       <c r="E189" s="30" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -33297,12 +33297,12 @@
         <v>2876</v>
       </c>
       <c r="E190" s="30" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="4" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>1873</v>
@@ -33314,12 +33314,12 @@
         <v>2876</v>
       </c>
       <c r="E191" s="30" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="49" t="s">
-        <v>3233</v>
+        <v>3232</v>
       </c>
       <c r="B192">
         <v>64046277</v>
@@ -33331,7 +33331,7 @@
         <v>2915</v>
       </c>
       <c r="E192" s="30" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -33348,7 +33348,7 @@
         <v>2876</v>
       </c>
       <c r="E193" s="30" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -33365,18 +33365,18 @@
         <v>2876</v>
       </c>
       <c r="E194" s="30" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="C195" s="56" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="D195" t="s">
-        <v>3529</v>
+        <v>3528</v>
       </c>
       <c r="E195" s="30" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
     </row>
     <row r="197" spans="1:5" s="396" customFormat="1" ht="23.5">
@@ -33398,49 +33398,49 @@
         <v>2902</v>
       </c>
       <c r="D198" s="378" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="E198" s="30" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" t="s">
+        <v>3605</v>
+      </c>
+      <c r="B199" t="s">
         <v>3606</v>
-      </c>
-      <c r="B199" t="s">
-        <v>3607</v>
       </c>
       <c r="C199" t="s">
         <v>2893</v>
       </c>
       <c r="D199" s="378" t="s">
-        <v>3605</v>
+        <v>3604</v>
       </c>
       <c r="E199" s="30" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="B200">
         <v>63617941</v>
       </c>
       <c r="C200" s="22" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="D200" s="378" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="E200" s="30" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="B201">
         <v>65633205</v>
@@ -33449,10 +33449,10 @@
         <v>2894</v>
       </c>
       <c r="D201" s="378" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="E201" s="30" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -33466,10 +33466,10 @@
         <v>2895</v>
       </c>
       <c r="D202" s="378" t="s">
-        <v>2958</v>
+        <v>2957</v>
       </c>
       <c r="E202" s="30" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -33480,13 +33480,13 @@
         <v>69329372</v>
       </c>
       <c r="C203" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="D203" s="378" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="E203" s="30" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -33500,10 +33500,10 @@
         <v>2896</v>
       </c>
       <c r="D204" s="378" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
       <c r="E204" s="30" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -33517,10 +33517,10 @@
         <v>2897</v>
       </c>
       <c r="D205" s="378" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="E205" s="30" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -33528,16 +33528,16 @@
         <v>2787</v>
       </c>
       <c r="B206" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="C206" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="D206" s="378" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="E206" s="30" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -33548,30 +33548,30 @@
         <v>65344753</v>
       </c>
       <c r="C207" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="D207" s="378" t="s">
+        <v>3385</v>
+      </c>
+      <c r="E207" s="30" t="s">
         <v>3386</v>
-      </c>
-      <c r="E207" s="30" t="s">
-        <v>3387</v>
       </c>
     </row>
     <row r="208" spans="1:5">
       <c r="A208" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="B208">
         <v>66496809</v>
       </c>
       <c r="C208" s="455" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="D208" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="E208" s="30" t="s">
-        <v>3674</v>
+        <v>3673</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -33582,30 +33582,30 @@
         <v>65583706</v>
       </c>
       <c r="C209" s="455" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="D209" s="378" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="E209" s="30" t="s">
-        <v>3674</v>
+        <v>3673</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210" t="s">
-        <v>3556</v>
+        <v>3555</v>
       </c>
       <c r="B210">
         <v>65574051</v>
       </c>
       <c r="C210" s="455" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="D210" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="E210" s="30" t="s">
-        <v>3674</v>
+        <v>3673</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -33613,16 +33613,16 @@
         <v>2835</v>
       </c>
       <c r="B211" t="s">
-        <v>3083</v>
+        <v>3082</v>
       </c>
       <c r="C211" s="455" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="D211" s="378" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="E211" s="30" t="s">
-        <v>3674</v>
+        <v>3673</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -33633,13 +33633,13 @@
         <v>64881871</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="D212" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="E212" s="30" t="s">
-        <v>3674</v>
+        <v>3673</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -33650,30 +33650,30 @@
         <v>68069608</v>
       </c>
       <c r="C213" s="22" t="s">
-        <v>3107</v>
+        <v>3106</v>
       </c>
       <c r="D213" s="378" t="s">
+        <v>3108</v>
+      </c>
+      <c r="E213" s="30" t="s">
         <v>3109</v>
-      </c>
-      <c r="E213" s="30" t="s">
-        <v>3110</v>
       </c>
     </row>
     <row r="214" spans="1:5">
       <c r="A214" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="B214">
         <v>63258169</v>
       </c>
       <c r="C214" s="22" t="s">
-        <v>3129</v>
+        <v>3128</v>
       </c>
       <c r="D214" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="E214" s="30" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -33684,13 +33684,13 @@
         <v>69243886</v>
       </c>
       <c r="C215" s="22" t="s">
-        <v>3130</v>
+        <v>3129</v>
       </c>
       <c r="D215" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="E215" s="30" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -33701,13 +33701,13 @@
         <v>67752170</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="D216" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="E216" s="30" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -33718,13 +33718,13 @@
         <v>64457890</v>
       </c>
       <c r="C217" t="s">
+        <v>3130</v>
+      </c>
+      <c r="D217" s="378" t="s">
         <v>3131</v>
       </c>
-      <c r="D217" s="378" t="s">
-        <v>3132</v>
-      </c>
       <c r="E217" s="30" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
     </row>
     <row r="231" spans="3:4">
@@ -33855,10 +33855,10 @@
     </row>
     <row r="259" spans="1:6">
       <c r="C259" s="1" t="s">
+        <v>2936</v>
+      </c>
+      <c r="D259" s="1" t="s">
         <v>2937</v>
-      </c>
-      <c r="D259" s="1" t="s">
-        <v>2938</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -33866,7 +33866,7 @@
         <v>1679</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="261" spans="1:6">
@@ -36496,7 +36496,7 @@
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>3102</v>
+        <v>3101</v>
       </c>
     </row>
     <row r="18" spans="4:4">
@@ -36553,7 +36553,7 @@
     </row>
     <row r="6" spans="1:9" s="76" customFormat="1">
       <c r="A6" s="76" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="B6" s="76">
         <v>64966680</v>
@@ -36568,7 +36568,7 @@
         <v>678</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="G6" s="222" t="s">
         <v>1455</v>
@@ -36588,13 +36588,13 @@
         <v>1861</v>
       </c>
       <c r="D7" s="183" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F7" s="183" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="G7" s="183" t="s">
         <v>1455</v>
@@ -36605,7 +36605,7 @@
     </row>
     <row r="8" spans="1:9" s="183" customFormat="1">
       <c r="A8" s="193" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B8" s="193">
         <v>62747874</v>
@@ -36620,7 +36620,7 @@
         <v>362</v>
       </c>
       <c r="F8" s="183" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="G8" s="183" t="s">
         <v>1455</v>
@@ -36646,7 +36646,7 @@
         <v>362</v>
       </c>
       <c r="F9" s="183" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="G9" s="183" t="s">
         <v>1455</v>
@@ -36672,7 +36672,7 @@
         <v>362</v>
       </c>
       <c r="F10" s="183" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="G10" s="183" t="s">
         <v>1455</v>
@@ -36698,7 +36698,7 @@
         <v>362</v>
       </c>
       <c r="F11" s="183" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="G11" s="183" t="s">
         <v>1455</v>
@@ -36721,7 +36721,7 @@
         <v>2558</v>
       </c>
       <c r="E13" s="195" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="F13" s="195" t="s">
         <v>1440</v>
@@ -36748,7 +36748,7 @@
         <v>1862</v>
       </c>
       <c r="E14" s="193" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="F14" s="193" t="s">
         <v>1440</v>
@@ -36775,7 +36775,7 @@
         <v>2839</v>
       </c>
       <c r="E15" s="193" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="F15" s="193" t="s">
         <v>1440</v>
@@ -36790,7 +36790,7 @@
     </row>
     <row r="16" spans="1:9" s="183" customFormat="1">
       <c r="A16" s="183" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="B16" s="183">
         <v>63666666</v>
@@ -36802,7 +36802,7 @@
         <v>2343</v>
       </c>
       <c r="E16" s="193" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="F16" s="193" t="s">
         <v>1440</v>
@@ -36829,7 +36829,7 @@
         <v>1521</v>
       </c>
       <c r="E17" s="193" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="F17" s="193" t="s">
         <v>1440</v>
@@ -36856,7 +36856,7 @@
         <v>2181</v>
       </c>
       <c r="E18" s="193" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="F18" s="193" t="s">
         <v>1440</v>
@@ -36871,7 +36871,7 @@
     </row>
     <row r="20" spans="1:9" s="76" customFormat="1">
       <c r="A20" s="195" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="B20" s="195">
         <v>67539485</v>
@@ -36886,7 +36886,7 @@
         <v>362</v>
       </c>
       <c r="F20" s="195" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="G20" s="76" t="s">
         <v>422</v>
@@ -36900,7 +36900,7 @@
     </row>
     <row r="21" spans="1:9" s="183" customFormat="1">
       <c r="A21" s="183" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="B21" s="183">
         <v>62723048</v>
@@ -36915,7 +36915,7 @@
         <v>362</v>
       </c>
       <c r="F21" s="193" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="G21" s="183" t="s">
         <v>422</v>
@@ -36944,7 +36944,7 @@
         <v>362</v>
       </c>
       <c r="F22" s="193" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="G22" s="183" t="s">
         <v>422</v>
@@ -36958,7 +36958,7 @@
     </row>
     <row r="23" spans="1:9" s="183" customFormat="1">
       <c r="A23" s="183" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="B23" s="183">
         <v>60389752</v>
@@ -36973,7 +36973,7 @@
         <v>362</v>
       </c>
       <c r="F23" s="193" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="G23" s="183" t="s">
         <v>422</v>
@@ -37002,7 +37002,7 @@
         <v>362</v>
       </c>
       <c r="F24" s="193" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="G24" s="183" t="s">
         <v>422</v>
@@ -37031,7 +37031,7 @@
         <v>362</v>
       </c>
       <c r="F25" s="193" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="G25" s="183" t="s">
         <v>422</v>
@@ -37048,7 +37048,7 @@
         <v>362</v>
       </c>
       <c r="F27" s="446" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="G27" s="393" t="s">
         <v>422</v>
@@ -37067,7 +37067,7 @@
         <v>362</v>
       </c>
       <c r="F28" s="446" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="G28" s="393" t="s">
         <v>422</v>
@@ -37084,7 +37084,7 @@
         <v>362</v>
       </c>
       <c r="F29" s="446" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="G29" s="393" t="s">
         <v>422</v>
@@ -37098,7 +37098,7 @@
     </row>
     <row r="30" spans="1:9" s="393" customFormat="1">
       <c r="A30" s="393" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B30" s="393">
         <v>63950696</v>
@@ -37113,7 +37113,7 @@
         <v>362</v>
       </c>
       <c r="F30" s="446" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="G30" s="393" t="s">
         <v>422</v>
@@ -37133,7 +37133,7 @@
     </row>
     <row r="32" spans="1:9" s="393" customFormat="1">
       <c r="A32" s="452" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
       <c r="B32" s="446">
         <v>64967407</v>
@@ -37148,7 +37148,7 @@
         <v>362</v>
       </c>
       <c r="F32" s="446" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="G32" s="393" t="s">
         <v>422</v>
@@ -37179,7 +37179,7 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B36">
         <v>69563253</v>
@@ -37228,7 +37228,7 @@
     </row>
     <row r="41" spans="1:9" s="76" customFormat="1">
       <c r="A41" s="76" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="B41" s="76">
         <v>60389752</v>
@@ -37243,7 +37243,7 @@
         <v>362</v>
       </c>
       <c r="F41" s="76" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="G41" s="76" t="s">
         <v>1456</v>
@@ -37270,7 +37270,7 @@
         <v>362</v>
       </c>
       <c r="F42" s="183" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="G42" s="183" t="s">
         <v>378</v>
@@ -37284,22 +37284,22 @@
     </row>
     <row r="43" spans="1:9" s="183" customFormat="1">
       <c r="A43" s="183" t="s">
-        <v>3637</v>
+        <v>3636</v>
       </c>
       <c r="B43" s="183">
         <v>65234700</v>
       </c>
       <c r="C43" s="194" t="s">
+        <v>3550</v>
+      </c>
+      <c r="D43" s="183" t="s">
         <v>3551</v>
-      </c>
-      <c r="D43" s="183" t="s">
-        <v>3552</v>
       </c>
       <c r="E43" s="443">
         <v>46243</v>
       </c>
       <c r="F43" s="183" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="G43" s="183" t="s">
         <v>378</v>
@@ -37328,7 +37328,7 @@
         <v>362</v>
       </c>
       <c r="F44" s="183" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="G44" s="183" t="s">
         <v>378</v>
@@ -37357,7 +37357,7 @@
         <v>362</v>
       </c>
       <c r="F45" s="183" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="G45" s="183" t="s">
         <v>378</v>
@@ -37371,7 +37371,7 @@
     </row>
     <row r="46" spans="1:9" s="183" customFormat="1">
       <c r="A46" s="183" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="B46" s="183">
         <v>68241069</v>
@@ -37386,7 +37386,7 @@
         <v>362</v>
       </c>
       <c r="F46" s="183" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="G46" s="183" t="s">
         <v>378</v>
@@ -37415,7 +37415,7 @@
         <v>2523</v>
       </c>
       <c r="F48" s="195" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
       <c r="G48" s="76" t="s">
         <v>1455</v>
@@ -37442,7 +37442,7 @@
         <v>2523</v>
       </c>
       <c r="F49" s="193" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
       <c r="G49" s="183" t="s">
         <v>1455</v>
@@ -37454,7 +37454,7 @@
     </row>
     <row r="50" spans="1:9" s="183" customFormat="1">
       <c r="A50" s="193" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="B50" s="193">
         <v>63226030</v>
@@ -37469,7 +37469,7 @@
         <v>2523</v>
       </c>
       <c r="F50" s="193" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
       <c r="G50" s="183" t="s">
         <v>1455</v>
@@ -37481,7 +37481,7 @@
     </row>
     <row r="51" spans="1:9" s="183" customFormat="1">
       <c r="A51" s="193" t="s">
-        <v>3584</v>
+        <v>3583</v>
       </c>
       <c r="B51" s="193">
         <v>69111188</v>
@@ -37496,7 +37496,7 @@
         <v>2523</v>
       </c>
       <c r="F51" s="193" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
       <c r="G51" s="183" t="s">
         <v>1455</v>
@@ -37523,7 +37523,7 @@
         <v>2523</v>
       </c>
       <c r="F52" s="193" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
       <c r="G52" s="183" t="s">
         <v>1455</v>
@@ -37550,7 +37550,7 @@
         <v>2523</v>
       </c>
       <c r="F53" s="193" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
       <c r="G53" s="183" t="s">
         <v>1455</v>
@@ -37571,13 +37571,13 @@
         <v>1680</v>
       </c>
       <c r="D55" s="195" t="s">
-        <v>3149</v>
+        <v>3148</v>
       </c>
       <c r="E55" s="76" t="s">
         <v>2523</v>
       </c>
       <c r="F55" s="195" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
       <c r="G55" s="76" t="s">
         <v>1455</v>
@@ -37604,7 +37604,7 @@
         <v>2523</v>
       </c>
       <c r="F56" s="193" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
       <c r="G56" s="183" t="s">
         <v>1455</v>
@@ -37625,13 +37625,13 @@
         <v>2652</v>
       </c>
       <c r="D57" s="193" t="s">
-        <v>3342</v>
+        <v>3341</v>
       </c>
       <c r="E57" s="183" t="s">
         <v>2523</v>
       </c>
       <c r="F57" s="193" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
       <c r="G57" s="183" t="s">
         <v>1455</v>
@@ -37658,7 +37658,7 @@
         <v>2523</v>
       </c>
       <c r="F58" s="193" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
       <c r="G58" s="183" t="s">
         <v>1455</v>
@@ -37685,7 +37685,7 @@
         <v>2523</v>
       </c>
       <c r="F59" s="193" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
       <c r="G59" s="183" t="s">
         <v>1455</v>
@@ -37703,16 +37703,16 @@
         <v>63062167</v>
       </c>
       <c r="C60" s="193" t="s">
-        <v>3459</v>
+        <v>3458</v>
       </c>
       <c r="D60" s="193" t="s">
-        <v>3494</v>
+        <v>3493</v>
       </c>
       <c r="E60" s="183" t="s">
         <v>2523</v>
       </c>
       <c r="F60" s="193" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
       <c r="G60" s="183" t="s">
         <v>1455</v>
@@ -37738,7 +37738,7 @@
         <v>2523</v>
       </c>
       <c r="F62" s="195" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
       <c r="G62" s="76" t="s">
         <v>1455</v>
@@ -37765,7 +37765,7 @@
         <v>2523</v>
       </c>
       <c r="F63" s="193" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
       <c r="G63" s="183" t="s">
         <v>1455</v>
@@ -37777,7 +37777,7 @@
     </row>
     <row r="64" spans="1:9" s="183" customFormat="1">
       <c r="A64" s="183" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="B64" s="183">
         <v>64403333</v>
@@ -37792,7 +37792,7 @@
         <v>2523</v>
       </c>
       <c r="F64" s="193" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
       <c r="G64" s="183" t="s">
         <v>1455</v>
@@ -37804,7 +37804,7 @@
     </row>
     <row r="65" spans="1:9" s="183" customFormat="1">
       <c r="A65" s="193" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="B65" s="193">
         <v>68030850</v>
@@ -37819,7 +37819,7 @@
         <v>2523</v>
       </c>
       <c r="F65" s="193" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
       <c r="G65" s="183" t="s">
         <v>1455</v>
@@ -37831,7 +37831,7 @@
     </row>
     <row r="66" spans="1:9" s="183" customFormat="1">
       <c r="A66" s="183" t="s">
-        <v>3659</v>
+        <v>3658</v>
       </c>
       <c r="B66" s="183">
         <v>65003516</v>
@@ -37846,7 +37846,7 @@
         <v>2523</v>
       </c>
       <c r="F66" s="193" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
       <c r="G66" s="183" t="s">
         <v>1455</v>
@@ -37873,7 +37873,7 @@
         <v>2523</v>
       </c>
       <c r="F67" s="193" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
       <c r="G67" s="183" t="s">
         <v>1455</v>
@@ -37885,7 +37885,7 @@
     </row>
     <row r="69" spans="1:9" s="76" customFormat="1">
       <c r="A69" s="76" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="B69" s="76">
         <v>64147946</v>
@@ -37897,7 +37897,7 @@
         <v>2486</v>
       </c>
       <c r="E69" s="76" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="F69" s="195" t="s">
         <v>2487</v>
@@ -37912,7 +37912,7 @@
     </row>
     <row r="70" spans="1:9" s="183" customFormat="1">
       <c r="A70" s="193" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
       <c r="B70" s="193">
         <v>62646186</v>
@@ -37924,7 +37924,7 @@
         <v>2491</v>
       </c>
       <c r="E70" s="183" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="F70" s="193" t="s">
         <v>2487</v>
@@ -37951,7 +37951,7 @@
         <v>2316</v>
       </c>
       <c r="E71" s="183" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="F71" s="193" t="s">
         <v>2487</v>
@@ -37978,7 +37978,7 @@
         <v>2789</v>
       </c>
       <c r="E72" s="183" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="F72" s="183" t="s">
         <v>2487</v>
@@ -38004,7 +38004,7 @@
         <v>2075</v>
       </c>
       <c r="E73" s="183" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="F73" s="183" t="s">
         <v>2487</v>
@@ -38030,7 +38030,7 @@
         <v>2482</v>
       </c>
       <c r="E74" s="183" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="F74" s="183" t="s">
         <v>2487</v>
@@ -38056,7 +38056,7 @@
         <v>1740</v>
       </c>
       <c r="E76" s="76" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="F76" s="195" t="s">
         <v>2485</v>
@@ -38068,7 +38068,7 @@
     </row>
     <row r="77" spans="1:9" s="183" customFormat="1">
       <c r="A77" s="193" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="B77" s="193">
         <v>66082581</v>
@@ -38080,7 +38080,7 @@
         <v>2358</v>
       </c>
       <c r="E77" s="183" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="F77" s="193" t="s">
         <v>2485</v>
@@ -38104,7 +38104,7 @@
         <v>1248</v>
       </c>
       <c r="E78" s="183" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="F78" s="193" t="s">
         <v>2485</v>
@@ -38128,7 +38128,7 @@
         <v>2393</v>
       </c>
       <c r="E79" s="183" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="F79" s="193" t="s">
         <v>2485</v>
@@ -38152,7 +38152,7 @@
         <v>2314</v>
       </c>
       <c r="E80" s="183" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="F80" s="193" t="s">
         <v>2485</v>
@@ -38164,7 +38164,7 @@
     </row>
     <row r="81" spans="1:9" s="183" customFormat="1">
       <c r="A81" s="55" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="B81" s="183" t="s">
         <v>1451</v>
@@ -38176,7 +38176,7 @@
         <v>2534</v>
       </c>
       <c r="E81" s="183" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="F81" s="193" t="s">
         <v>2485</v>
@@ -38188,7 +38188,7 @@
     </row>
     <row r="83" spans="1:9" s="76" customFormat="1">
       <c r="A83" s="76" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="B83" s="76">
         <v>63574980</v>
@@ -38203,7 +38203,7 @@
         <v>1354</v>
       </c>
       <c r="F83" s="195" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="G83" s="76" t="s">
         <v>1455</v>
@@ -38229,7 +38229,7 @@
         <v>1354</v>
       </c>
       <c r="F84" s="183" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="G84" s="183" t="s">
         <v>1455</v>
@@ -38246,7 +38246,7 @@
         <v>68483411</v>
       </c>
       <c r="C85" s="183" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="D85" s="183" t="s">
         <v>2179</v>
@@ -38255,7 +38255,7 @@
         <v>1354</v>
       </c>
       <c r="F85" s="183" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="G85" s="183" t="s">
         <v>1455</v>
@@ -38269,19 +38269,19 @@
         <v>2541</v>
       </c>
       <c r="B86" s="183" t="s">
-        <v>3300</v>
+        <v>3299</v>
       </c>
       <c r="C86" s="194" t="s">
         <v>2714</v>
       </c>
       <c r="D86" s="183" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
       <c r="E86" s="183" t="s">
         <v>1354</v>
       </c>
       <c r="F86" s="183" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="G86" s="183" t="s">
         <v>1455</v>
@@ -38292,7 +38292,7 @@
     </row>
     <row r="87" spans="1:9" s="183" customFormat="1">
       <c r="A87" s="183" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B87" s="183">
         <v>69904406</v>
@@ -38301,13 +38301,13 @@
         <v>2715</v>
       </c>
       <c r="D87" s="183" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
       <c r="E87" s="183" t="s">
         <v>1354</v>
       </c>
       <c r="F87" s="183" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="G87" s="183" t="s">
         <v>1455</v>
@@ -38318,7 +38318,7 @@
     </row>
     <row r="88" spans="1:9" s="183" customFormat="1">
       <c r="A88" s="183" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="B88" s="183" t="s">
         <v>2733</v>
@@ -38333,7 +38333,7 @@
         <v>1354</v>
       </c>
       <c r="F88" s="183" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="G88" s="183" t="s">
         <v>1455</v>
@@ -38359,7 +38359,7 @@
         <v>1670</v>
       </c>
       <c r="F90" s="195" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="G90" s="76" t="s">
         <v>1455</v>
@@ -38383,7 +38383,7 @@
         <v>1670</v>
       </c>
       <c r="F91" s="193" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="G91" s="183" t="s">
         <v>1455</v>
@@ -38407,7 +38407,7 @@
         <v>1670</v>
       </c>
       <c r="F92" s="193" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="G92" s="183" t="s">
         <v>1455</v>
@@ -38431,7 +38431,7 @@
         <v>1670</v>
       </c>
       <c r="F93" s="193" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="G93" s="183" t="s">
         <v>1455</v>
@@ -38455,7 +38455,7 @@
         <v>1670</v>
       </c>
       <c r="F94" s="193" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="G94" s="183" t="s">
         <v>1455</v>
@@ -38479,7 +38479,7 @@
         <v>1670</v>
       </c>
       <c r="F95" s="193" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="G95" s="183" t="s">
         <v>1455</v>
@@ -38488,7 +38488,7 @@
     </row>
     <row r="97" spans="1:9" s="76" customFormat="1">
       <c r="A97" s="195" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="B97" s="195">
         <v>64476521</v>
@@ -38503,7 +38503,7 @@
         <v>2523</v>
       </c>
       <c r="F97" s="195" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="G97" s="76" t="s">
         <v>1455</v>
@@ -38515,7 +38515,7 @@
     </row>
     <row r="98" spans="1:9" s="183" customFormat="1">
       <c r="A98" s="193" t="s">
-        <v>3511</v>
+        <v>3510</v>
       </c>
       <c r="B98" s="193">
         <v>60389752</v>
@@ -38524,13 +38524,13 @@
         <v>2695</v>
       </c>
       <c r="D98" s="193" t="s">
-        <v>3510</v>
+        <v>3509</v>
       </c>
       <c r="E98" s="183" t="s">
         <v>2523</v>
       </c>
       <c r="F98" s="193" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="G98" s="183" t="s">
         <v>1455</v>
@@ -38557,7 +38557,7 @@
         <v>2523</v>
       </c>
       <c r="F99" s="193" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="G99" s="183" t="s">
         <v>1455</v>
@@ -38569,7 +38569,7 @@
     </row>
     <row r="100" spans="1:9" s="183" customFormat="1">
       <c r="A100" s="193" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="B100" s="193">
         <v>60389752</v>
@@ -38584,7 +38584,7 @@
         <v>2523</v>
       </c>
       <c r="F100" s="193" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="G100" s="183" t="s">
         <v>1455</v>
@@ -38611,7 +38611,7 @@
         <v>2523</v>
       </c>
       <c r="F101" s="193" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="G101" s="183" t="s">
         <v>1455</v>
@@ -38623,7 +38623,7 @@
     </row>
     <row r="102" spans="1:9" s="183" customFormat="1">
       <c r="A102" s="193" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B102" s="193">
         <v>67381873</v>
@@ -38632,13 +38632,13 @@
         <v>2312</v>
       </c>
       <c r="D102" s="193" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="E102" s="183" t="s">
         <v>2523</v>
       </c>
       <c r="F102" s="193" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="G102" s="183" t="s">
         <v>1455</v>
@@ -38650,7 +38650,7 @@
     </row>
     <row r="104" spans="1:9" s="76" customFormat="1">
       <c r="A104" s="195" t="s">
-        <v>3135</v>
+        <v>3134</v>
       </c>
       <c r="B104" s="195">
         <v>66082581</v>
@@ -38662,7 +38662,7 @@
         <v>2325</v>
       </c>
       <c r="E104" s="76" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="F104" s="195" t="s">
         <v>422</v>
@@ -38677,7 +38677,7 @@
     </row>
     <row r="105" spans="1:9" s="183" customFormat="1">
       <c r="A105" s="193" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="B105" s="193" t="s">
         <v>2753</v>
@@ -38689,7 +38689,7 @@
         <v>2330</v>
       </c>
       <c r="E105" s="183" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="F105" s="193" t="s">
         <v>422</v>
@@ -38704,7 +38704,7 @@
     </row>
     <row r="106" spans="1:9" s="183" customFormat="1">
       <c r="A106" s="193" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="B106" s="193">
         <v>62723048</v>
@@ -38713,10 +38713,10 @@
         <v>2331</v>
       </c>
       <c r="D106" s="193" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="E106" s="183" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="F106" s="193" t="s">
         <v>422</v>
@@ -38737,13 +38737,13 @@
         <v>69017426</v>
       </c>
       <c r="C107" s="194" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="D107" s="193" t="s">
         <v>2497</v>
       </c>
       <c r="E107" s="183" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="F107" s="193" t="s">
         <v>422</v>
@@ -38770,7 +38770,7 @@
         <v>2334</v>
       </c>
       <c r="E108" s="183" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="F108" s="193" t="s">
         <v>422</v>
@@ -38791,13 +38791,13 @@
         <v>62723048</v>
       </c>
       <c r="C109" s="194" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="D109" s="193" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="E109" s="183" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="F109" s="193" t="s">
         <v>422</v>
@@ -38818,16 +38818,16 @@
         <v>68310153</v>
       </c>
       <c r="C111" s="195" t="s">
+        <v>3126</v>
+      </c>
+      <c r="D111" s="195" t="s">
         <v>3127</v>
-      </c>
-      <c r="D111" s="195" t="s">
-        <v>3128</v>
       </c>
       <c r="E111" s="76" t="s">
         <v>362</v>
       </c>
       <c r="F111" s="195" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="G111" s="76" t="s">
         <v>1354</v>
@@ -38841,7 +38841,7 @@
     </row>
     <row r="112" spans="1:9" s="183" customFormat="1">
       <c r="A112" s="193" t="s">
-        <v>3134</v>
+        <v>3133</v>
       </c>
       <c r="B112" s="193">
         <v>63910392</v>
@@ -38854,7 +38854,7 @@
         <v>362</v>
       </c>
       <c r="F112" s="193" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="G112" s="183" t="s">
         <v>1354</v>
@@ -38874,16 +38874,16 @@
         <v>68853797</v>
       </c>
       <c r="C113" s="193" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="D113" s="193" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="E113" s="183" t="s">
         <v>2523</v>
       </c>
       <c r="F113" s="193" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="G113" s="183" t="s">
         <v>1354</v>
@@ -38903,16 +38903,16 @@
         <v>62360487</v>
       </c>
       <c r="C114" s="194" t="s">
+        <v>3459</v>
+      </c>
+      <c r="D114" s="183" t="s">
         <v>3460</v>
-      </c>
-      <c r="D114" s="183" t="s">
-        <v>3461</v>
       </c>
       <c r="E114" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F114" s="193" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="G114" s="183" t="s">
         <v>1354</v>
@@ -38932,16 +38932,16 @@
         <v>62085821</v>
       </c>
       <c r="C115" s="193" t="s">
+        <v>3461</v>
+      </c>
+      <c r="D115" s="193" t="s">
         <v>3462</v>
-      </c>
-      <c r="D115" s="193" t="s">
-        <v>3463</v>
       </c>
       <c r="E115" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F115" s="193" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="G115" s="183" t="s">
         <v>1354</v>
@@ -38961,16 +38961,16 @@
         <v>64403333</v>
       </c>
       <c r="C116" s="193" t="s">
+        <v>3463</v>
+      </c>
+      <c r="D116" s="193" t="s">
         <v>3464</v>
-      </c>
-      <c r="D116" s="193" t="s">
-        <v>3465</v>
       </c>
       <c r="E116" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F116" s="193" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="G116" s="183" t="s">
         <v>1354</v>
@@ -38987,7 +38987,7 @@
         <v>1354</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="G118" s="444" t="s">
         <v>1455</v>
@@ -39002,7 +39002,7 @@
         <v>1354</v>
       </c>
       <c r="F119" s="302" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="G119" s="7" t="s">
         <v>1455</v>
@@ -39020,16 +39020,16 @@
         <v>64543204</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>3074</v>
+        <v>3073</v>
       </c>
       <c r="D120" s="7" t="s">
-        <v>3073</v>
+        <v>3072</v>
       </c>
       <c r="E120" s="7" t="s">
         <v>1354</v>
       </c>
       <c r="F120" s="302" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="G120" s="7" t="s">
         <v>1455</v>
@@ -39044,7 +39044,7 @@
         <v>1354</v>
       </c>
       <c r="F121" s="302" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="G121" s="7" t="s">
         <v>1455</v>
@@ -39071,7 +39071,7 @@
         <v>1354</v>
       </c>
       <c r="F122" s="302" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="G122" s="7" t="s">
         <v>1455</v>
@@ -39086,7 +39086,7 @@
         <v>1354</v>
       </c>
       <c r="F123" s="302" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="G123" s="7" t="s">
         <v>1455</v>
@@ -39110,7 +39110,7 @@
         <v>2347</v>
       </c>
       <c r="E125" s="76" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="F125" s="76" t="s">
         <v>422</v>
@@ -39136,7 +39136,7 @@
         <v>2349</v>
       </c>
       <c r="E126" s="183" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="F126" s="193" t="s">
         <v>422</v>
@@ -39163,7 +39163,7 @@
         <v>2351</v>
       </c>
       <c r="E127" s="183" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="F127" s="193" t="s">
         <v>422</v>
@@ -39178,19 +39178,19 @@
     </row>
     <row r="128" spans="1:9" s="183" customFormat="1">
       <c r="A128" s="183" t="s">
-        <v>3555</v>
+        <v>3554</v>
       </c>
       <c r="B128" s="183">
         <v>64403333</v>
       </c>
       <c r="C128" s="183" t="s">
+        <v>3465</v>
+      </c>
+      <c r="D128" s="183" t="s">
         <v>3466</v>
       </c>
-      <c r="D128" s="183" t="s">
-        <v>3467</v>
-      </c>
       <c r="E128" s="183" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="F128" s="193" t="s">
         <v>422</v>
@@ -39217,7 +39217,7 @@
         <v>377</v>
       </c>
       <c r="E129" s="183" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="F129" s="193" t="s">
         <v>422</v>
@@ -39244,7 +39244,7 @@
         <v>1666</v>
       </c>
       <c r="E130" s="183" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="F130" s="193" t="s">
         <v>422</v>
@@ -39274,7 +39274,7 @@
         <v>678</v>
       </c>
       <c r="F132" s="76" t="s">
-        <v>3331</v>
+        <v>3330</v>
       </c>
       <c r="G132" s="76" t="s">
         <v>422</v>
@@ -39303,7 +39303,7 @@
         <v>362</v>
       </c>
       <c r="F133" s="183" t="s">
-        <v>3331</v>
+        <v>3330</v>
       </c>
       <c r="G133" s="183" t="s">
         <v>422</v>
@@ -39332,7 +39332,7 @@
         <v>362</v>
       </c>
       <c r="F134" s="183" t="s">
-        <v>3331</v>
+        <v>3330</v>
       </c>
       <c r="G134" s="183" t="s">
         <v>422</v>
@@ -39358,7 +39358,7 @@
         <v>362</v>
       </c>
       <c r="F135" s="183" t="s">
-        <v>3331</v>
+        <v>3330</v>
       </c>
       <c r="G135" s="183" t="s">
         <v>422</v>
@@ -39372,7 +39372,7 @@
     </row>
     <row r="136" spans="1:9" s="183" customFormat="1">
       <c r="A136" s="183" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="B136" s="183">
         <v>66230961</v>
@@ -39387,7 +39387,7 @@
         <v>362</v>
       </c>
       <c r="F136" s="183" t="s">
-        <v>3331</v>
+        <v>3330</v>
       </c>
       <c r="G136" s="183" t="s">
         <v>422</v>
@@ -39401,7 +39401,7 @@
     </row>
     <row r="137" spans="1:9" s="183" customFormat="1">
       <c r="A137" s="183" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="B137" s="183">
         <v>69888391</v>
@@ -39416,7 +39416,7 @@
         <v>362</v>
       </c>
       <c r="F137" s="183" t="s">
-        <v>3331</v>
+        <v>3330</v>
       </c>
       <c r="G137" s="183" t="s">
         <v>422</v>
@@ -39445,7 +39445,7 @@
         <v>2405</v>
       </c>
       <c r="F139" s="195" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="G139" s="76" t="s">
         <v>1455</v>
@@ -39463,7 +39463,7 @@
         <v>64226974</v>
       </c>
       <c r="C140" s="183" t="s">
-        <v>3625</v>
+        <v>3624</v>
       </c>
       <c r="D140" s="193" t="s">
         <v>377</v>
@@ -39472,7 +39472,7 @@
         <v>2405</v>
       </c>
       <c r="F140" s="193" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="G140" s="183" t="s">
         <v>1455</v>
@@ -39499,7 +39499,7 @@
         <v>2405</v>
       </c>
       <c r="F141" s="193" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="G141" s="183" t="s">
         <v>1455</v>
@@ -39526,7 +39526,7 @@
         <v>2405</v>
       </c>
       <c r="F142" s="193" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="G142" s="183" t="s">
         <v>1455</v>
@@ -39538,7 +39538,7 @@
     </row>
     <row r="143" spans="1:9" s="183" customFormat="1">
       <c r="A143" s="55" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
       <c r="B143" s="183">
         <v>62385671</v>
@@ -39553,7 +39553,7 @@
         <v>2405</v>
       </c>
       <c r="F143" s="193" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="G143" s="183" t="s">
         <v>1455</v>
@@ -39580,7 +39580,7 @@
         <v>2405</v>
       </c>
       <c r="F144" s="193" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="G144" s="183" t="s">
         <v>1455</v>
@@ -39598,16 +39598,16 @@
         <v>2186</v>
       </c>
       <c r="C146" s="195" t="s">
-        <v>3381</v>
+        <v>3380</v>
       </c>
       <c r="D146" s="195" t="s">
-        <v>3380</v>
+        <v>3379</v>
       </c>
       <c r="E146" s="76" t="s">
         <v>2405</v>
       </c>
       <c r="F146" s="195" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="G146" s="76" t="s">
         <v>1455</v>
@@ -39625,16 +39625,16 @@
         <v>66319486</v>
       </c>
       <c r="C147" s="193" t="s">
-        <v>3468</v>
+        <v>3467</v>
       </c>
       <c r="D147" s="193" t="s">
-        <v>3512</v>
+        <v>3511</v>
       </c>
       <c r="E147" s="183" t="s">
         <v>2405</v>
       </c>
       <c r="F147" s="193" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="G147" s="183" t="s">
         <v>1455</v>
@@ -39661,7 +39661,7 @@
         <v>2405</v>
       </c>
       <c r="F148" s="193" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="G148" s="183" t="s">
         <v>1455</v>
@@ -39673,7 +39673,7 @@
     </row>
     <row r="149" spans="1:9" s="183" customFormat="1">
       <c r="A149" s="183" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="B149" s="183">
         <v>64403333</v>
@@ -39688,7 +39688,7 @@
         <v>2405</v>
       </c>
       <c r="F149" s="193" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="G149" s="183" t="s">
         <v>1455</v>
@@ -39715,7 +39715,7 @@
         <v>2405</v>
       </c>
       <c r="F150" s="193" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="G150" s="183" t="s">
         <v>1455</v>
@@ -39742,7 +39742,7 @@
         <v>2405</v>
       </c>
       <c r="F151" s="193" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="G151" s="183" t="s">
         <v>1455</v>
@@ -39769,7 +39769,7 @@
         <v>2523</v>
       </c>
       <c r="F153" s="195" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="G153" s="76" t="s">
         <v>1455</v>
@@ -39781,13 +39781,13 @@
     </row>
     <row r="154" spans="1:9" s="183" customFormat="1">
       <c r="A154" s="193" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="B154" s="193">
         <v>67697112</v>
       </c>
       <c r="C154" s="193" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="D154" s="193" t="s">
         <v>1316</v>
@@ -39796,7 +39796,7 @@
         <v>2523</v>
       </c>
       <c r="F154" s="193" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="G154" s="183" t="s">
         <v>1455</v>
@@ -39808,7 +39808,7 @@
     </row>
     <row r="155" spans="1:9" s="183" customFormat="1">
       <c r="A155" s="183" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="B155" s="183">
         <v>62560788</v>
@@ -39823,7 +39823,7 @@
         <v>2523</v>
       </c>
       <c r="F155" s="193" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="G155" s="183" t="s">
         <v>1455</v>
@@ -39835,7 +39835,7 @@
     </row>
     <row r="156" spans="1:9" s="183" customFormat="1">
       <c r="A156" s="193" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B156" s="193">
         <v>64403333</v>
@@ -39850,7 +39850,7 @@
         <v>2523</v>
       </c>
       <c r="F156" s="193" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="G156" s="183" t="s">
         <v>1455</v>
@@ -39862,22 +39862,22 @@
     </row>
     <row r="157" spans="1:9" s="183" customFormat="1">
       <c r="A157" s="193" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B157" s="193">
         <v>60125401</v>
       </c>
       <c r="C157" s="194" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
       <c r="D157" s="193" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="E157" s="183" t="s">
         <v>2523</v>
       </c>
       <c r="F157" s="193" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="G157" s="183" t="s">
         <v>1455</v>
@@ -39904,7 +39904,7 @@
         <v>2523</v>
       </c>
       <c r="F158" s="193" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="G158" s="183" t="s">
         <v>1455</v>
@@ -39931,7 +39931,7 @@
         <v>362</v>
       </c>
       <c r="F160" s="195" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="G160" s="76" t="s">
         <v>2411</v>
@@ -39945,22 +39945,22 @@
     </row>
     <row r="161" spans="1:9" s="183" customFormat="1">
       <c r="A161" s="193" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="B161" s="193">
         <v>65963732</v>
       </c>
       <c r="C161" s="194" t="s">
+        <v>3450</v>
+      </c>
+      <c r="D161" s="193" t="s">
         <v>3451</v>
-      </c>
-      <c r="D161" s="193" t="s">
-        <v>3452</v>
       </c>
       <c r="E161" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F161" s="193" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="G161" s="183" t="s">
         <v>2411</v>
@@ -39974,7 +39974,7 @@
     </row>
     <row r="162" spans="1:9" s="183" customFormat="1">
       <c r="A162" s="183" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="B162" s="183">
         <v>60071688</v>
@@ -39983,13 +39983,13 @@
         <v>2394</v>
       </c>
       <c r="D162" s="183" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="E162" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F162" s="193" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="G162" s="183" t="s">
         <v>2411</v>
@@ -40018,7 +40018,7 @@
         <v>362</v>
       </c>
       <c r="F163" s="193" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="G163" s="183" t="s">
         <v>2411</v>
@@ -40047,7 +40047,7 @@
         <v>362</v>
       </c>
       <c r="F164" s="193" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="G164" s="183" t="s">
         <v>2411</v>
@@ -40061,22 +40061,22 @@
     </row>
     <row r="165" spans="1:9" s="183" customFormat="1">
       <c r="A165" s="183" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="B165" s="183">
         <v>64403333</v>
       </c>
       <c r="C165" s="194" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="D165" s="416" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="E165" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F165" s="193" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="G165" s="183" t="s">
         <v>2411</v>
@@ -40092,16 +40092,16 @@
       <c r="A167" s="195"/>
       <c r="B167" s="195"/>
       <c r="C167" s="195" t="s">
+        <v>3599</v>
+      </c>
+      <c r="D167" s="195" t="s">
         <v>3600</v>
-      </c>
-      <c r="D167" s="195" t="s">
-        <v>3601</v>
       </c>
       <c r="E167" s="76" t="s">
         <v>362</v>
       </c>
       <c r="F167" s="195" t="s">
-        <v>3602</v>
+        <v>3601</v>
       </c>
       <c r="G167" s="76" t="s">
         <v>2411</v>
@@ -40121,7 +40121,7 @@
         <v>69563253</v>
       </c>
       <c r="C168" s="193" t="s">
-        <v>3603</v>
+        <v>3602</v>
       </c>
       <c r="D168" s="193" t="s">
         <v>1693</v>
@@ -40142,10 +40142,10 @@
         <v>1959</v>
       </c>
       <c r="C169" s="194" t="s">
+        <v>3578</v>
+      </c>
+      <c r="D169" s="193" t="s">
         <v>3579</v>
-      </c>
-      <c r="D169" s="193" t="s">
-        <v>3580</v>
       </c>
       <c r="E169" s="443">
         <v>46304</v>
@@ -40163,7 +40163,7 @@
         <v>62751201</v>
       </c>
       <c r="C170" s="194" t="s">
-        <v>3608</v>
+        <v>3607</v>
       </c>
       <c r="D170" s="183" t="s">
         <v>1367</v>
@@ -40184,10 +40184,10 @@
         <v>68030850</v>
       </c>
       <c r="C171" s="193" t="s">
+        <v>3581</v>
+      </c>
+      <c r="D171" s="193" t="s">
         <v>3582</v>
-      </c>
-      <c r="D171" s="193" t="s">
-        <v>3583</v>
       </c>
       <c r="E171" s="443">
         <v>46243</v>
@@ -40222,16 +40222,16 @@
       <c r="A174" s="195"/>
       <c r="B174" s="195"/>
       <c r="C174" s="195" t="s">
+        <v>3638</v>
+      </c>
+      <c r="D174" s="195" t="s">
         <v>3639</v>
       </c>
-      <c r="D174" s="195" t="s">
+      <c r="E174" s="76" t="s">
         <v>3640</v>
       </c>
-      <c r="E174" s="76" t="s">
+      <c r="F174" s="195" t="s">
         <v>3641</v>
-      </c>
-      <c r="F174" s="195" t="s">
-        <v>3642</v>
       </c>
       <c r="G174" s="76" t="s">
         <v>1455</v>
@@ -40270,10 +40270,10 @@
         <v>61548403</v>
       </c>
       <c r="C176" s="194" t="s">
+        <v>3642</v>
+      </c>
+      <c r="D176" s="193" t="s">
         <v>3643</v>
-      </c>
-      <c r="D176" s="193" t="s">
-        <v>3644</v>
       </c>
       <c r="E176" s="443">
         <v>46304</v>
@@ -40333,27 +40333,27 @@
     </row>
     <row r="183" spans="1:9" s="221" customFormat="1" ht="15.5">
       <c r="C183" s="221" t="s">
-        <v>3546</v>
+        <v>3545</v>
       </c>
     </row>
     <row r="184" spans="1:9" s="76" customFormat="1">
       <c r="C184" s="195" t="s">
+        <v>3671</v>
+      </c>
+      <c r="D184" s="195" t="s">
         <v>3672</v>
-      </c>
-      <c r="D184" s="195" t="s">
-        <v>3673</v>
       </c>
       <c r="E184" s="445">
         <v>46243</v>
       </c>
       <c r="F184" s="76" t="s">
+        <v>3546</v>
+      </c>
+      <c r="G184" s="195" t="s">
+        <v>3597</v>
+      </c>
+      <c r="H184" s="76" t="s">
         <v>3547</v>
-      </c>
-      <c r="G184" s="195" t="s">
-        <v>3598</v>
-      </c>
-      <c r="H184" s="76" t="s">
-        <v>3548</v>
       </c>
       <c r="I184" s="195"/>
     </row>
@@ -40403,7 +40403,7 @@
         <v>316</v>
       </c>
       <c r="D194" s="438" t="s">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="E194" s="30"/>
       <c r="F194"/>
@@ -40429,7 +40429,7 @@
         <v>439</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="E196" s="30"/>
       <c r="F196"/>
@@ -40440,7 +40440,7 @@
         <v>26</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>3462</v>
+        <v>3461</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -40448,7 +40448,7 @@
         <v>1337</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -40456,7 +40456,7 @@
         <v>1677</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>3466</v>
+        <v>3465</v>
       </c>
       <c r="F199" s="399"/>
     </row>
@@ -40465,7 +40465,7 @@
         <v>1318</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>3468</v>
+        <v>3467</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -40473,7 +40473,7 @@
         <v>406</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="202" spans="1:9">
@@ -40481,7 +40481,7 @@
         <v>709</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>3582</v>
+        <v>3581</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -40489,7 +40489,7 @@
         <v>281</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
     </row>
     <row r="204" spans="1:9">
@@ -40497,7 +40497,7 @@
         <v>2413</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
     </row>
     <row r="205" spans="1:9">
@@ -40507,7 +40507,7 @@
         <v>465</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>3603</v>
+        <v>3602</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -40515,7 +40515,7 @@
         <v>219</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>3608</v>
+        <v>3607</v>
       </c>
     </row>
     <row r="207" spans="1:9">
@@ -40523,7 +40523,7 @@
         <v>427</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>3625</v>
+        <v>3624</v>
       </c>
     </row>
     <row r="208" spans="1:9">
@@ -40531,7 +40531,7 @@
         <v>1058</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>3639</v>
+        <v>3638</v>
       </c>
     </row>
     <row r="223" spans="1:9">
@@ -41865,10 +41865,10 @@
         <v>706</v>
       </c>
       <c r="H3" t="s">
-        <v>3660</v>
+        <v>3659</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>3166</v>
+        <v>3165</v>
       </c>
       <c r="J3"/>
     </row>
@@ -41895,10 +41895,10 @@
         <v>515</v>
       </c>
       <c r="H4" t="s">
-        <v>3472</v>
+        <v>3471</v>
       </c>
       <c r="I4" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
       <c r="J4"/>
     </row>
@@ -41907,7 +41907,7 @@
         <v>2903</v>
       </c>
       <c r="B5" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>480</v>
@@ -41916,7 +41916,7 @@
         <v>1537</v>
       </c>
       <c r="E5" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="F5" t="s">
         <v>2195</v>
@@ -41925,10 +41925,10 @@
         <v>515</v>
       </c>
       <c r="H5" s="220" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
       <c r="I5" s="220" t="s">
-        <v>3316</v>
+        <v>3315</v>
       </c>
       <c r="J5" t="s">
         <v>1408</v>
@@ -41941,19 +41941,19 @@
         <v>427</v>
       </c>
       <c r="D6" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>3488</v>
+        <v>3487</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="G6" t="s">
         <v>436</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
       <c r="I6" s="97"/>
       <c r="J6"/>
@@ -41986,13 +41986,13 @@
         <v>143</v>
       </c>
       <c r="B8" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>2086</v>
       </c>
       <c r="D8" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="E8" t="s">
         <v>2360</v>
@@ -42004,10 +42004,10 @@
         <v>250</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>3307</v>
+        <v>3306</v>
       </c>
       <c r="I8" t="s">
-        <v>3437</v>
+        <v>3436</v>
       </c>
       <c r="J8"/>
     </row>
@@ -42037,7 +42037,7 @@
         <v>2803</v>
       </c>
       <c r="I9" s="276" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -42104,28 +42104,28 @@
         <v>67663098</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
       <c r="D16" t="s">
-        <v>2922</v>
+        <v>2921</v>
       </c>
       <c r="E16" t="s">
+        <v>2959</v>
+      </c>
+      <c r="F16" t="s">
         <v>2960</v>
-      </c>
-      <c r="F16" t="s">
-        <v>2961</v>
       </c>
       <c r="G16" t="s">
         <v>121</v>
       </c>
       <c r="H16" s="276" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="I16" s="276" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
     </row>
     <row r="19" customFormat="1"/>
@@ -42204,7 +42204,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="10" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="B5" s="10">
         <v>67992849</v>
@@ -42257,7 +42257,7 @@
         <v>2814</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>3170</v>
+        <v>3169</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -42271,7 +42271,7 @@
         <v>1742</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1715</v>
@@ -42283,10 +42283,10 @@
         <v>517</v>
       </c>
       <c r="H7" t="s">
-        <v>3329</v>
+        <v>3328</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>3358</v>
+        <v>3357</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -42302,7 +42302,7 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="10" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="B11" s="10">
         <v>64403333</v>
@@ -42334,7 +42334,7 @@
         <v>2173</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>3372</v>
+        <v>3371</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>966</v>
@@ -42346,10 +42346,10 @@
         <v>517</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>3373</v>
+        <v>3372</v>
       </c>
       <c r="I12" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -42365,7 +42365,7 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="10" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="B15" s="10">
         <v>68543713</v>
@@ -42374,7 +42374,7 @@
         <v>2234</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>966</v>
@@ -42386,10 +42386,10 @@
         <v>517</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>3211</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -42438,7 +42438,7 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="10" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="B18" s="10">
         <v>60345107</v>
@@ -42447,7 +42447,7 @@
         <v>2368</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>3434</v>
+        <v>3433</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>966</v>
@@ -42459,10 +42459,10 @@
         <v>517</v>
       </c>
       <c r="H18" s="436" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -42488,10 +42488,10 @@
         <v>517</v>
       </c>
       <c r="H19" s="276" t="s">
-        <v>3141</v>
+        <v>3140</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>3629</v>
+        <v>3628</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="190" customFormat="1" ht="26">
@@ -42507,13 +42507,13 @@
         <v>2664</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>2457</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>3559</v>
+        <v>3558</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>966</v>
@@ -42525,15 +42525,15 @@
         <v>517</v>
       </c>
       <c r="H22" s="276" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>3664</v>
+        <v>3663</v>
       </c>
       <c r="B23" s="10">
         <v>64720128</v>
@@ -42554,10 +42554,10 @@
         <v>517</v>
       </c>
       <c r="H23" s="10" t="s">
+        <v>3664</v>
+      </c>
+      <c r="I23" s="10" t="s">
         <v>3665</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>3666</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -42571,7 +42571,7 @@
         <v>2475</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>966</v>
@@ -42583,10 +42583,10 @@
         <v>517</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -42596,7 +42596,7 @@
         <v>2488</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>966</v>
@@ -42715,13 +42715,13 @@
         <v>2503</v>
       </c>
       <c r="B4" t="s">
-        <v>3271</v>
+        <v>3270</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1883</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>3270</v>
+        <v>3269</v>
       </c>
       <c r="E4" t="s">
         <v>1884</v>
@@ -42733,13 +42733,13 @@
         <v>970</v>
       </c>
       <c r="H4" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>3295</v>
+        <v>3294</v>
       </c>
       <c r="J4" t="s">
-        <v>3353</v>
+        <v>3352</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -42788,7 +42788,7 @@
         <v>970</v>
       </c>
       <c r="H6" t="s">
-        <v>3314</v>
+        <v>3313</v>
       </c>
       <c r="J6" s="49" t="s">
         <v>2257</v>
@@ -42800,7 +42800,7 @@
         <v>2322</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>2323</v>
@@ -42812,13 +42812,13 @@
         <v>970</v>
       </c>
       <c r="H7" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>3396</v>
+        <v>3395</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -42826,63 +42826,63 @@
         <v>2483</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>2987</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>2986</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>2988</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>2987</v>
-      </c>
-      <c r="E8" s="10" t="s">
+      <c r="F8" s="10" t="s">
         <v>2989</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>2990</v>
       </c>
       <c r="G8" t="s">
         <v>970</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>3366</v>
+        <v>3365</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="10" t="s">
+        <v>3213</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>3214</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>3215</v>
-      </c>
       <c r="C9" s="22" t="s">
+        <v>3211</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>2986</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>3212</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>2987</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>3213</v>
-      </c>
       <c r="F9" s="10" t="s">
-        <v>2990</v>
+        <v>2989</v>
       </c>
       <c r="G9" t="s">
         <v>970</v>
       </c>
       <c r="H9" s="10" t="s">
+        <v>3215</v>
+      </c>
+      <c r="I9" s="10" t="s">
         <v>3216</v>
       </c>
-      <c r="I9" s="10" t="s">
-        <v>3217</v>
-      </c>
       <c r="J9" t="s">
-        <v>3266</v>
+        <v>3265</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -42890,16 +42890,16 @@
         <v>1444</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>3371</v>
+        <v>3370</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>3368</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>3369</v>
       </c>
-      <c r="D10" s="10" t="s">
-        <v>3370</v>
-      </c>
       <c r="E10" s="10" t="s">
-        <v>3285</v>
+        <v>3284</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>2324</v>
@@ -42908,13 +42908,13 @@
         <v>970</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>3478</v>
+        <v>3477</v>
       </c>
       <c r="J10" t="s">
-        <v>3530</v>
+        <v>3529</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -43076,7 +43076,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="10" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="B10" s="10">
         <v>64676716</v>
@@ -43085,7 +43085,7 @@
         <v>1806</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>3178</v>
+        <v>3177</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>2662</v>
@@ -43126,7 +43126,7 @@
         <v>65124748</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>3053</v>
+        <v>3052</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>2686</v>
@@ -43147,7 +43147,7 @@
         <v>63132287</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>2686</v>
@@ -43323,7 +43323,7 @@
     <row r="1" spans="1:10" s="415" customFormat="1" ht="42.5" customHeight="1">
       <c r="A1" s="414"/>
       <c r="B1" s="414" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="C1" s="414"/>
     </row>
@@ -43332,28 +43332,28 @@
         <v>147</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>3126</v>
+        <v>3125</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>3273</v>
+      </c>
+      <c r="E4" t="s">
+        <v>3068</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>3274</v>
       </c>
-      <c r="E4" t="s">
-        <v>3069</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>3275</v>
-      </c>
       <c r="G4" s="10" t="s">
-        <v>3081</v>
+        <v>3080</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>3385</v>
+        <v>3384</v>
       </c>
     </row>
   </sheetData>
@@ -43699,7 +43699,7 @@
         <v>2606</v>
       </c>
       <c r="C5" s="327" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="327" customFormat="1">
@@ -43707,10 +43707,10 @@
         <v>2585</v>
       </c>
       <c r="B6" s="327" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="C6" s="327" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
     </row>
     <row r="7" spans="1:13" s="327" customFormat="1">
@@ -43785,10 +43785,10 @@
         <v>2615</v>
       </c>
       <c r="H14" s="333" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
       <c r="I14" s="333" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="L14" s="333"/>
       <c r="M14" s="333"/>
@@ -43816,10 +43816,10 @@
         <v>2616</v>
       </c>
       <c r="H15" s="334" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
       <c r="I15" s="334" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="L15" s="334"/>
       <c r="M15" s="334"/>
@@ -43847,7 +43847,7 @@
         <v>2617</v>
       </c>
       <c r="H16" s="334" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
       <c r="I16" s="334" t="s">
         <v>1354</v>
@@ -43860,7 +43860,7 @@
         <v>2590</v>
       </c>
       <c r="B17" s="401" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="C17" s="401"/>
       <c r="D17" s="401"/>
@@ -43877,7 +43877,7 @@
         <v>2585</v>
       </c>
       <c r="B18" s="401" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
       <c r="C18" s="401"/>
       <c r="D18" s="401"/>
@@ -43894,7 +43894,7 @@
         <v>2586</v>
       </c>
       <c r="B19" s="401" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
       <c r="C19" s="401"/>
       <c r="D19" s="401"/>
@@ -44749,7 +44749,7 @@
         <v>51</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>3343</v>
+        <v>3342</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>1170</v>
@@ -44761,10 +44761,10 @@
         <v>159</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>3560</v>
+        <v>3559</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
       <c r="N6" s="4" t="s">
         <v>26</v>
@@ -44796,7 +44796,7 @@
         <v>2297</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="L7" s="3"/>
     </row>
@@ -44826,7 +44826,7 @@
         <v>2786</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
     </row>
     <row r="9" spans="1:14" s="4" customFormat="1">
@@ -44843,19 +44843,19 @@
         <v>2185</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>3572</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>3573</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>3574</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>159</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>3532</v>
+        <v>3531</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>3486</v>
+        <v>3485</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>819</v>
@@ -44863,7 +44863,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="4" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="B10" s="4">
         <v>67916500</v>
@@ -44884,10 +44884,10 @@
         <v>244</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>3660</v>
+        <v>3659</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -44904,19 +44904,19 @@
         <v>1527</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>3483</v>
+        <v>3482</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>244</v>
       </c>
       <c r="H11" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -44942,10 +44942,10 @@
         <v>244</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -44953,7 +44953,7 @@
         <v>2562</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>2933</v>
+        <v>2932</v>
       </c>
       <c r="C13" s="22" t="s">
         <v>1231</v>
@@ -44971,10 +44971,10 @@
         <v>244</v>
       </c>
       <c r="H13" s="220" t="s">
-        <v>3481</v>
+        <v>3480</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="4" customFormat="1">
@@ -45000,25 +45000,25 @@
         <v>244</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="I14" s="220" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="105" t="s">
+        <v>2931</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>2932</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>2933</v>
       </c>
       <c r="C15" s="22" t="s">
         <v>340</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>1547</v>
@@ -45030,10 +45030,10 @@
         <v>891</v>
       </c>
       <c r="H15" t="s">
-        <v>3390</v>
+        <v>3389</v>
       </c>
       <c r="I15" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>498</v>
@@ -45050,7 +45050,7 @@
         <v>2646</v>
       </c>
       <c r="D16" t="s">
-        <v>2919</v>
+        <v>2918</v>
       </c>
       <c r="E16" t="s">
         <v>2648</v>
@@ -45062,10 +45062,10 @@
         <v>159</v>
       </c>
       <c r="H16" s="49" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
       <c r="I16" t="s">
-        <v>3561</v>
+        <v>3560</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>809</v>
@@ -45073,7 +45073,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="B17">
         <v>65325884</v>
@@ -45096,7 +45096,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="4" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>2134</v>
@@ -45108,24 +45108,24 @@
         <v>2246</v>
       </c>
       <c r="E18" s="4" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>3032</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>3033</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>244</v>
       </c>
       <c r="H18" s="49" t="s">
-        <v>3228</v>
+        <v>3227</v>
       </c>
       <c r="I18" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="4" customFormat="1">
       <c r="A19" s="4" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="B19" s="4">
         <v>64403333</v>
@@ -45137,10 +45137,10 @@
         <v>2647</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>1240</v>
@@ -45150,7 +45150,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="4" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="B20">
         <v>64403333</v>
@@ -45199,7 +45199,7 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="4" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="B22" s="4">
         <v>64403333</v>
@@ -45222,7 +45222,7 @@
     </row>
     <row r="23" spans="1:12" s="4" customFormat="1">
       <c r="A23" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="B23">
         <v>63247837</v>
@@ -45231,7 +45231,7 @@
         <v>2655</v>
       </c>
       <c r="D23" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="E23" t="s">
         <v>2658</v>
@@ -45243,10 +45243,10 @@
         <v>159</v>
       </c>
       <c r="H23" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="L23" s="6"/>
     </row>
@@ -45261,10 +45261,10 @@
         <v>1649</v>
       </c>
       <c r="D24" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>3256</v>
+        <v>3255</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>2516</v>
@@ -45275,19 +45275,19 @@
     </row>
     <row r="25" spans="1:12" s="4" customFormat="1">
       <c r="A25" s="4" t="s">
-        <v>3606</v>
+        <v>3605</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>3620</v>
+        <v>3619</v>
       </c>
       <c r="C25" s="21" t="s">
         <v>1339</v>
       </c>
       <c r="D25" t="s">
-        <v>3619</v>
+        <v>3618</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>2519</v>
@@ -45296,10 +45296,10 @@
         <v>244</v>
       </c>
       <c r="H25" s="359" t="s">
+        <v>3620</v>
+      </c>
+      <c r="I25" s="359" t="s">
         <v>3621</v>
-      </c>
-      <c r="I25" s="359" t="s">
-        <v>3622</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="4" customFormat="1">
@@ -45325,10 +45325,10 @@
         <v>159</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>3039</v>
+        <v>3038</v>
       </c>
       <c r="I27" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="L27" s="4" t="s">
         <v>817</v>
@@ -45336,7 +45336,7 @@
     </row>
     <row r="28" spans="1:12" s="4" customFormat="1">
       <c r="A28" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>2510</v>
@@ -45348,7 +45348,7 @@
         <v>2052</v>
       </c>
       <c r="E28" t="s">
-        <v>3267</v>
+        <v>3266</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>2519</v>
@@ -45360,7 +45360,7 @@
         <v>2704</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>3645</v>
+        <v>3644</v>
       </c>
       <c r="K28"/>
     </row>
@@ -45375,41 +45375,41 @@
         <v>350</v>
       </c>
       <c r="D29" s="75" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="E29" t="s">
-        <v>3558</v>
+        <v>3557</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="G29" s="75" t="s">
         <v>250</v>
       </c>
       <c r="H29" s="49" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I29" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="J29" s="4"/>
       <c r="L29" s="135"/>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="C30" s="22" t="s">
         <v>402</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>3222</v>
+        <v>3221</v>
       </c>
       <c r="E30" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>1354</v>
@@ -45418,7 +45418,7 @@
         <v>159</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>3226</v>
+        <v>3225</v>
       </c>
       <c r="I30" s="55" t="s">
         <v>2813</v>
@@ -45426,7 +45426,7 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>3555</v>
+        <v>3554</v>
       </c>
       <c r="B31" s="4">
         <v>69409351</v>
@@ -45447,10 +45447,10 @@
         <v>159</v>
       </c>
       <c r="H31" t="s">
-        <v>3389</v>
+        <v>3388</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>3313</v>
+        <v>3312</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -45476,7 +45476,7 @@
         <v>159</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
       <c r="I32" s="49" t="s">
         <v>2800</v>
@@ -45508,7 +45508,7 @@
         <v>2888</v>
       </c>
       <c r="I33" t="s">
-        <v>3167</v>
+        <v>3166</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -45516,13 +45516,13 @@
         <v>1444</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>3683</v>
+        <v>3682</v>
       </c>
       <c r="C34" s="21" t="s">
         <v>2642</v>
       </c>
       <c r="D34" t="s">
-        <v>3337</v>
+        <v>3336</v>
       </c>
       <c r="E34" t="s">
         <v>2648</v>
@@ -45534,10 +45534,10 @@
         <v>159</v>
       </c>
       <c r="H34" t="s">
-        <v>3348</v>
+        <v>3347</v>
       </c>
       <c r="I34" t="s">
-        <v>3477</v>
+        <v>3476</v>
       </c>
       <c r="J34" s="4"/>
     </row>
@@ -45546,13 +45546,13 @@
         <v>147</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>3100</v>
+        <v>3099</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>2643</v>
       </c>
       <c r="D35" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
       <c r="E35" t="s">
         <v>2648</v>
@@ -45564,24 +45564,24 @@
         <v>2649</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="I35" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="B36" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="C36" s="22" t="s">
         <v>2644</v>
       </c>
       <c r="D36" t="s">
-        <v>3586</v>
+        <v>3585</v>
       </c>
       <c r="E36" t="s">
         <v>2648</v>
@@ -45593,10 +45593,10 @@
         <v>159</v>
       </c>
       <c r="H36" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="I36" t="s">
-        <v>3377</v>
+        <v>3376</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -45610,7 +45610,7 @@
         <v>2656</v>
       </c>
       <c r="D37" t="s">
-        <v>3016</v>
+        <v>3015</v>
       </c>
       <c r="E37" t="s">
         <v>2658</v>
@@ -45622,10 +45622,10 @@
         <v>159</v>
       </c>
       <c r="H37" t="s">
-        <v>3017</v>
+        <v>3016</v>
       </c>
       <c r="I37" t="s">
-        <v>3087</v>
+        <v>3086</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -45633,7 +45633,7 @@
         <v>157</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>3240</v>
+        <v>3239</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>2657</v>
@@ -45651,10 +45651,10 @@
         <v>159</v>
       </c>
       <c r="H38" s="97" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="I38" t="s">
-        <v>3433</v>
+        <v>3432</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -45667,10 +45667,10 @@
         <v>1364</v>
       </c>
       <c r="E41" s="97" t="s">
+        <v>3490</v>
+      </c>
+      <c r="F41" s="105" t="s">
         <v>3491</v>
-      </c>
-      <c r="F41" s="105" t="s">
-        <v>3492</v>
       </c>
       <c r="G41" s="105" t="s">
         <v>159</v>
@@ -45688,10 +45688,10 @@
         <v>2120</v>
       </c>
       <c r="E42" s="97" t="s">
+        <v>3490</v>
+      </c>
+      <c r="F42" s="105" t="s">
         <v>3491</v>
-      </c>
-      <c r="F42" s="105" t="s">
-        <v>3492</v>
       </c>
       <c r="G42" s="105" t="s">
         <v>159</v>
@@ -45707,7 +45707,7 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="4" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="B45" t="s">
         <v>2556</v>
@@ -45737,7 +45737,7 @@
         <v>2877</v>
       </c>
       <c r="K45" t="s">
-        <v>3082</v>
+        <v>3081</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="4" customFormat="1">
@@ -46128,13 +46128,13 @@
         <v>157</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="C2" s="277" t="s">
         <v>254</v>
       </c>
       <c r="D2" s="106" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>1309</v>
@@ -46146,16 +46146,16 @@
         <v>62</v>
       </c>
       <c r="H2" s="301" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
       <c r="I2" s="106" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="J2" s="450" t="s">
-        <v>3679</v>
+        <v>3678</v>
       </c>
       <c r="K2" s="30" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="M2" s="159"/>
     </row>
@@ -46170,7 +46170,7 @@
         <v>1192</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>3339</v>
+        <v>3338</v>
       </c>
       <c r="E4" s="32" t="s">
         <v>2442</v>
@@ -46182,25 +46182,25 @@
         <v>270</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="I4" s="30" t="s">
-        <v>3398</v>
+        <v>3397</v>
       </c>
       <c r="J4" s="139" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="K4" s="139" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
       <c r="M4" s="39"/>
     </row>
     <row r="5" spans="1:13" s="30" customFormat="1">
       <c r="A5" s="30" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>1124</v>
@@ -46218,16 +46218,16 @@
         <v>65</v>
       </c>
       <c r="H5" s="453" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="J5" s="30" t="s">
-        <v>3509</v>
+        <v>3508</v>
       </c>
       <c r="K5" s="30" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="M5" s="36"/>
     </row>
@@ -46242,7 +46242,7 @@
         <v>2818</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>3670</v>
+        <v>3669</v>
       </c>
       <c r="E6" s="140" t="s">
         <v>2778</v>
@@ -46254,22 +46254,22 @@
         <v>65</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="K6" s="30" t="s">
-        <v>3375</v>
+        <v>3374</v>
       </c>
       <c r="M6" s="36"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="107" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>1222</v>
@@ -46278,28 +46278,28 @@
         <v>1097</v>
       </c>
       <c r="D7" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
       <c r="E7" s="107" t="s">
+        <v>3494</v>
+      </c>
+      <c r="F7" s="30" t="s">
         <v>3495</v>
-      </c>
-      <c r="F7" s="30" t="s">
-        <v>3496</v>
       </c>
       <c r="G7" s="106" t="s">
         <v>724</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>3391</v>
+        <v>3390</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="J7" s="30" t="s">
         <v>2720</v>
       </c>
       <c r="K7" s="30" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="M7" s="36"/>
     </row>
@@ -46314,7 +46314,7 @@
         <v>990</v>
       </c>
       <c r="D8" s="139" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="E8" s="107" t="s">
         <v>1167</v>
@@ -46326,16 +46326,16 @@
         <v>65</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="I8" s="32" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="J8" s="107" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="K8" s="139" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
       <c r="M8" s="36"/>
     </row>
@@ -46362,16 +46362,16 @@
         <v>65</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="I9" s="107" t="s">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>3444</v>
+        <v>3443</v>
       </c>
       <c r="K9" s="107" t="s">
-        <v>3168</v>
+        <v>3167</v>
       </c>
       <c r="M9" s="36"/>
     </row>
@@ -46398,22 +46398,22 @@
         <v>65</v>
       </c>
       <c r="H10" s="107" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="I10" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
       <c r="J10" s="219" t="s">
-        <v>3661</v>
+        <v>3660</v>
       </c>
       <c r="K10" s="107" t="s">
-        <v>3196</v>
+        <v>3195</v>
       </c>
       <c r="M10" s="34"/>
     </row>
     <row r="11" spans="1:13" s="30" customFormat="1">
       <c r="A11" s="107" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="B11" s="107">
         <v>62657225</v>
@@ -46434,16 +46434,16 @@
         <v>605</v>
       </c>
       <c r="H11" s="139" t="s">
-        <v>3314</v>
+        <v>3313</v>
       </c>
       <c r="I11" s="30" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="J11" s="107" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="K11" s="107" t="s">
-        <v>3437</v>
+        <v>3436</v>
       </c>
       <c r="M11" s="36"/>
     </row>
@@ -46458,7 +46458,7 @@
         <v>72</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
       <c r="E12" s="106" t="s">
         <v>912</v>
@@ -46470,22 +46470,22 @@
         <v>245</v>
       </c>
       <c r="H12" s="106" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="I12" s="106" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="J12" s="106" t="s">
-        <v>3669</v>
+        <v>3668</v>
       </c>
       <c r="K12" s="107" t="s">
-        <v>3432</v>
+        <v>3431</v>
       </c>
       <c r="M12" s="151"/>
     </row>
     <row r="13" spans="1:13" s="107" customFormat="1">
       <c r="A13" s="140" t="s">
-        <v>3606</v>
+        <v>3605</v>
       </c>
       <c r="B13" s="107" t="s">
         <v>2850</v>
@@ -46494,7 +46494,7 @@
         <v>923</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>3297</v>
+        <v>3296</v>
       </c>
       <c r="E13" s="140" t="s">
         <v>2819</v>
@@ -46506,16 +46506,16 @@
         <v>65</v>
       </c>
       <c r="H13" s="30" t="s">
-        <v>3298</v>
+        <v>3297</v>
       </c>
       <c r="I13" s="30" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="J13" s="107" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="K13" t="s">
-        <v>3473</v>
+        <v>3472</v>
       </c>
       <c r="M13" s="36"/>
     </row>
@@ -46542,13 +46542,13 @@
         <v>65</v>
       </c>
       <c r="H14" s="107" t="s">
-        <v>3533</v>
+        <v>3532</v>
       </c>
       <c r="I14" s="417" t="s">
         <v>2298</v>
       </c>
       <c r="J14" s="32" t="s">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="M14" s="36"/>
     </row>
@@ -46575,16 +46575,16 @@
         <v>66</v>
       </c>
       <c r="H15" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="I15" s="49" t="s">
-        <v>3671</v>
+        <v>3670</v>
       </c>
       <c r="J15" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="K15" s="107" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="M15" s="36"/>
     </row>
@@ -46639,13 +46639,13 @@
         <v>2863</v>
       </c>
       <c r="I17" s="30" t="s">
-        <v>3258</v>
+        <v>3257</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="K17" s="430" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="M17" s="34"/>
     </row>
@@ -46672,22 +46672,22 @@
         <v>66</v>
       </c>
       <c r="H18" s="30" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
       <c r="I18" t="s">
-        <v>3361</v>
+        <v>3360</v>
       </c>
       <c r="J18" t="s">
-        <v>3390</v>
+        <v>3389</v>
       </c>
       <c r="K18" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="M18" s="36"/>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="4" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>1548</v>
@@ -46696,7 +46696,7 @@
         <v>1709</v>
       </c>
       <c r="D19" s="134" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
       <c r="E19" t="s">
         <v>1712</v>
@@ -46708,16 +46708,16 @@
         <v>66</v>
       </c>
       <c r="H19" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
       <c r="I19" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="J19" s="220" t="s">
-        <v>3388</v>
+        <v>3387</v>
       </c>
       <c r="K19" t="s">
-        <v>3207</v>
+        <v>3206</v>
       </c>
       <c r="M19" s="36"/>
     </row>
@@ -46732,7 +46732,7 @@
         <v>2536</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="E20" s="107" t="s">
         <v>2460</v>
@@ -46744,31 +46744,31 @@
         <v>65</v>
       </c>
       <c r="H20" s="454" t="s">
-        <v>3668</v>
+        <v>3667</v>
       </c>
       <c r="I20" t="s">
+        <v>3186</v>
+      </c>
+      <c r="J20" t="s">
         <v>3187</v>
       </c>
-      <c r="J20" t="s">
-        <v>3188</v>
-      </c>
       <c r="K20" t="s">
-        <v>3225</v>
+        <v>3224</v>
       </c>
       <c r="M20" s="36"/>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="B21" t="s">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="C21" s="22" t="s">
         <v>1140</v>
       </c>
       <c r="D21" t="s">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="E21" s="140" t="s">
         <v>1608</v>
@@ -46780,19 +46780,19 @@
         <v>65</v>
       </c>
       <c r="H21" t="s">
-        <v>3550</v>
+        <v>3549</v>
       </c>
       <c r="I21" t="s">
+        <v>3552</v>
+      </c>
+      <c r="J21" t="s">
         <v>3553</v>
-      </c>
-      <c r="J21" t="s">
-        <v>3554</v>
       </c>
       <c r="M21" s="36"/>
     </row>
     <row r="22" spans="1:13" s="30" customFormat="1">
       <c r="A22" s="30" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="B22" s="30" t="s">
         <v>2136</v>
@@ -46801,58 +46801,58 @@
         <v>2781</v>
       </c>
       <c r="D22" s="107" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
       <c r="E22" s="30" t="s">
+        <v>3569</v>
+      </c>
+      <c r="F22" s="30" t="s">
         <v>3570</v>
-      </c>
-      <c r="F22" s="30" t="s">
-        <v>3571</v>
       </c>
       <c r="G22" s="32" t="s">
         <v>65</v>
       </c>
       <c r="H22" s="30" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
       <c r="I22" s="30" t="s">
+        <v>3576</v>
+      </c>
+      <c r="J22" s="30" t="s">
         <v>3577</v>
-      </c>
-      <c r="J22" s="30" t="s">
-        <v>3578</v>
       </c>
       <c r="M22" s="36"/>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="B23" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
       <c r="C23" s="22" t="s">
         <v>1922</v>
       </c>
       <c r="D23" t="s">
-        <v>3651</v>
+        <v>3650</v>
       </c>
       <c r="E23" s="30" t="s">
+        <v>3569</v>
+      </c>
+      <c r="F23" s="30" t="s">
         <v>3570</v>
-      </c>
-      <c r="F23" s="30" t="s">
-        <v>3571</v>
       </c>
       <c r="G23" t="s">
         <v>66</v>
       </c>
       <c r="H23" s="97" t="s">
+        <v>3651</v>
+      </c>
+      <c r="I23" s="97" t="s">
         <v>3652</v>
       </c>
-      <c r="I23" s="97" t="s">
+      <c r="J23" s="97" t="s">
         <v>3653</v>
-      </c>
-      <c r="J23" s="97" t="s">
-        <v>3654</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -46945,7 +46945,7 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="B33">
         <v>60389752</v>
@@ -46968,7 +46968,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
       <c r="B34">
         <v>60389752</v>
@@ -46977,13 +46977,13 @@
         <v>2201</v>
       </c>
       <c r="D34" s="32" t="s">
-        <v>3439</v>
+        <v>3438</v>
       </c>
       <c r="E34" s="30" t="s">
+        <v>3569</v>
+      </c>
+      <c r="F34" s="30" t="s">
         <v>3570</v>
-      </c>
-      <c r="F34" s="30" t="s">
-        <v>3571</v>
       </c>
       <c r="G34" t="s">
         <v>3</v>
@@ -46992,7 +46992,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="B35">
         <v>60389752</v>
@@ -47040,7 +47040,7 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="30" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="B37" s="30">
         <v>64403333</v>
@@ -47102,10 +47102,10 @@
         <v>2170</v>
       </c>
       <c r="E39" s="140" t="s">
+        <v>3011</v>
+      </c>
+      <c r="F39" s="140" t="s">
         <v>3012</v>
-      </c>
-      <c r="F39" s="140" t="s">
-        <v>3013</v>
       </c>
       <c r="G39" s="106" t="s">
         <v>724</v>
@@ -47174,7 +47174,7 @@
         <v>2564</v>
       </c>
       <c r="E45" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="F45" s="30" t="s">
         <v>2565</v>
@@ -47183,13 +47183,13 @@
         <v>369</v>
       </c>
       <c r="H45" t="s">
-        <v>3336</v>
+        <v>3335</v>
       </c>
       <c r="I45" s="30" t="s">
-        <v>3535</v>
+        <v>3534</v>
       </c>
       <c r="J45" t="s">
-        <v>3103</v>
+        <v>3102</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -47241,10 +47241,10 @@
     </row>
     <row r="66" spans="1:38">
       <c r="C66" s="7" t="s">
-        <v>3685</v>
+        <v>3684</v>
       </c>
       <c r="D66" t="s">
-        <v>3439</v>
+        <v>3438</v>
       </c>
       <c r="E66" t="s">
         <v>2458</v>
@@ -47335,7 +47335,7 @@
         <v>1108</v>
       </c>
       <c r="D74" s="97" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
       <c r="E74" s="107" t="s">
         <v>1109</v>
@@ -47625,7 +47625,7 @@
         <v>1143</v>
       </c>
       <c r="D93" t="s">
-        <v>3564</v>
+        <v>3563</v>
       </c>
       <c r="E93" s="140" t="s">
         <v>1145</v>
@@ -47649,7 +47649,7 @@
         <v>1404</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>3565</v>
+        <v>3564</v>
       </c>
       <c r="E94" s="267" t="s">
         <v>1522</v>
@@ -47683,7 +47683,7 @@
         <v>358</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>3685</v>
+        <v>3684</v>
       </c>
     </row>
     <row r="105" spans="2:5">
@@ -47909,7 +47909,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>3567</v>
+        <v>3566</v>
       </c>
       <c r="C12" s="237" t="s">
         <v>1956</v>
@@ -48040,7 +48040,7 @@
         <v>6.83</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -48049,7 +48049,7 @@
       </c>
       <c r="B24" s="87"/>
       <c r="F24" s="2" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -48125,27 +48125,27 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="87" t="s">
-        <v>3631</v>
+        <v>3630</v>
       </c>
       <c r="C40" t="s">
-        <v>3634</v>
+        <v>3633</v>
       </c>
       <c r="F40" s="45"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="89" t="s">
-        <v>3632</v>
+        <v>3631</v>
       </c>
       <c r="C41" t="s">
-        <v>3635</v>
+        <v>3634</v>
       </c>
     </row>
     <row r="42" spans="2:6" ht="15" thickBot="1">
       <c r="B42" s="86" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
       <c r="C42" t="s">
-        <v>3636</v>
+        <v>3635</v>
       </c>
     </row>
     <row r="43" spans="2:6">
@@ -48299,7 +48299,7 @@
         <v>143</v>
       </c>
       <c r="B6" s="248" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="C6" s="247" t="s">
         <v>1301</v>
@@ -48308,22 +48308,22 @@
         <v>2057</v>
       </c>
       <c r="E6" s="248" t="s">
+        <v>3483</v>
+      </c>
+      <c r="F6" s="248" t="s">
         <v>3484</v>
-      </c>
-      <c r="F6" s="248" t="s">
-        <v>3485</v>
       </c>
       <c r="G6" s="248" t="s">
         <v>357</v>
       </c>
       <c r="H6" s="248" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="I6" s="245" t="s">
-        <v>3036</v>
+        <v>3035</v>
       </c>
       <c r="J6" s="296" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="K6" s="248" t="s">
         <v>475</v>
@@ -48351,19 +48351,19 @@
         <v>1044</v>
       </c>
       <c r="F8" s="266" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="G8" s="266" t="s">
         <v>690</v>
       </c>
       <c r="H8" s="296" t="s">
-        <v>3482</v>
+        <v>3481</v>
       </c>
       <c r="I8" s="296" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="J8" s="441" t="s">
-        <v>3624</v>
+        <v>3623</v>
       </c>
       <c r="K8" s="266" t="s">
         <v>710</v>
@@ -48386,7 +48386,7 @@
         <v>1241</v>
       </c>
       <c r="F9" s="106" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="G9" s="106" t="s">
         <v>250</v>
@@ -48395,7 +48395,7 @@
         <v>2900</v>
       </c>
       <c r="I9" s="213" t="s">
-        <v>3645</v>
+        <v>3644</v>
       </c>
       <c r="J9" s="106" t="s">
         <v>2245</v>
@@ -48418,7 +48418,7 @@
         <v>2766</v>
       </c>
       <c r="F10" s="264" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
       <c r="G10" s="264" t="s">
         <v>952</v>
@@ -48450,13 +48450,13 @@
         <v>690</v>
       </c>
       <c r="H11" s="265" t="s">
-        <v>3169</v>
+        <v>3168</v>
       </c>
       <c r="I11" s="296" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
       <c r="J11" s="265" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="K11" s="246" t="s">
         <v>1216</v>
@@ -48467,7 +48467,7 @@
         <v>2562</v>
       </c>
       <c r="B12" s="263" t="s">
-        <v>3474</v>
+        <v>3473</v>
       </c>
       <c r="C12" s="194" t="s">
         <v>491</v>
@@ -48485,13 +48485,13 @@
         <v>690</v>
       </c>
       <c r="H12" s="145" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
       <c r="I12" s="432" t="s">
-        <v>3662</v>
+        <v>3661</v>
       </c>
       <c r="J12" s="270" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="K12" s="183" t="s">
         <v>1217</v>
@@ -48525,10 +48525,10 @@
     </row>
     <row r="14" spans="1:11" s="224" customFormat="1">
       <c r="A14" s="224" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="B14" s="224" t="s">
-        <v>3563</v>
+        <v>3562</v>
       </c>
       <c r="C14" s="431" t="s">
         <v>335</v>
@@ -48537,22 +48537,22 @@
         <v>2440</v>
       </c>
       <c r="E14" s="224" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="F14" s="224" t="s">
-        <v>3237</v>
+        <v>3236</v>
       </c>
       <c r="G14" s="224" t="s">
         <v>690</v>
       </c>
       <c r="H14" s="224" t="s">
+        <v>3243</v>
+      </c>
+      <c r="I14" s="215" t="s">
+        <v>3454</v>
+      </c>
+      <c r="J14" s="224" t="s">
         <v>3244</v>
-      </c>
-      <c r="I14" s="215" t="s">
-        <v>3455</v>
-      </c>
-      <c r="J14" s="224" t="s">
-        <v>3245</v>
       </c>
       <c r="K14" s="224" t="s">
         <v>1330</v>
@@ -48572,7 +48572,7 @@
         <v>1993</v>
       </c>
       <c r="E15" s="216" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="F15" s="216" t="s">
         <v>1448</v>
@@ -48581,13 +48581,13 @@
         <v>690</v>
       </c>
       <c r="H15" s="437" t="s">
-        <v>3180</v>
+        <v>3179</v>
       </c>
       <c r="I15" s="215" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="J15" s="263" t="s">
-        <v>3315</v>
+        <v>3314</v>
       </c>
       <c r="K15" s="183" t="s">
         <v>1218</v>
@@ -48598,13 +48598,13 @@
         <v>1430</v>
       </c>
       <c r="B16" s="265" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="C16" s="271" t="s">
         <v>1318</v>
       </c>
       <c r="D16" s="260" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="E16" s="260" t="s">
         <v>2827</v>
@@ -48616,13 +48616,13 @@
         <v>690</v>
       </c>
       <c r="H16" s="265" t="s">
-        <v>3427</v>
+        <v>3426</v>
       </c>
       <c r="I16" s="272" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="J16" s="265" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="K16" s="260" t="s">
         <v>1454</v>
@@ -48715,7 +48715,7 @@
         <v>690</v>
       </c>
       <c r="I20" s="49" t="s">
-        <v>3680</v>
+        <v>3679</v>
       </c>
       <c r="J20" s="49"/>
       <c r="K20" s="265" t="s">
@@ -48745,13 +48745,13 @@
         <v>690</v>
       </c>
       <c r="H21" s="260" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="I21" s="299" t="s">
-        <v>3522</v>
+        <v>3521</v>
       </c>
       <c r="J21" s="49" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="K21" s="265" t="s">
         <v>1785</v>
@@ -48759,7 +48759,7 @@
     </row>
     <row r="22" spans="1:11" s="260" customFormat="1">
       <c r="A22" s="49" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="B22" s="260" t="s">
         <v>2427</v>
@@ -48780,13 +48780,13 @@
         <v>690</v>
       </c>
       <c r="H22" s="260" t="s">
-        <v>3328</v>
+        <v>3327</v>
       </c>
       <c r="I22" s="260" t="s">
-        <v>3684</v>
+        <v>3683</v>
       </c>
       <c r="J22" s="260" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
       <c r="K22" s="260" t="s">
         <v>1830</v>
@@ -48818,10 +48818,10 @@
         <v>2837</v>
       </c>
       <c r="I24" s="265" t="s">
-        <v>3041</v>
+        <v>3040</v>
       </c>
       <c r="J24" s="265" t="s">
-        <v>3585</v>
+        <v>3584</v>
       </c>
       <c r="K24" s="260" t="s">
         <v>1832</v>
@@ -48864,10 +48864,10 @@
         <v>637</v>
       </c>
       <c r="D27" s="256" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
       <c r="E27" s="272" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="F27" s="272" t="s">
         <v>1730</v>
@@ -48876,13 +48876,13 @@
         <v>250</v>
       </c>
       <c r="H27" s="49" t="s">
-        <v>3228</v>
+        <v>3227</v>
       </c>
       <c r="I27" s="265" t="s">
-        <v>3456</v>
+        <v>3455</v>
       </c>
       <c r="J27" s="265" t="s">
-        <v>3349</v>
+        <v>3348</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="260" customFormat="1">
@@ -48890,7 +48890,7 @@
         <v>844</v>
       </c>
       <c r="D29" s="265" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="E29" s="260" t="s">
         <v>1808</v>
@@ -49272,13 +49272,13 @@
         <v>2846</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>3513</v>
+        <v>3512</v>
       </c>
       <c r="I2" s="455" t="s">
-        <v>3686</v>
+        <v>3685</v>
       </c>
       <c r="J2" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="L2" s="36" t="s">
         <v>1186</v>
@@ -49304,7 +49304,7 @@
         <v>298</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>3514</v>
+        <v>3513</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>708</v>
@@ -49330,25 +49330,25 @@
         <v>313</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>3085</v>
+        <v>3084</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>323</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>3040</v>
+        <v>3039</v>
       </c>
       <c r="H4" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="J4" t="s">
-        <v>3086</v>
+        <v>3085</v>
       </c>
       <c r="L4" s="127" t="s">
         <v>322</v>
@@ -49374,7 +49374,7 @@
         <v>424</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="H5" s="49" t="s">
         <v>2812</v>
@@ -49398,25 +49398,25 @@
         <v>327</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>166</v>
       </c>
       <c r="G6" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="I6" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="J6" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
       <c r="L6" s="67" t="s">
         <v>423</v>
@@ -49424,7 +49424,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="4" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
       <c r="B7" s="4">
         <v>69561522</v>
@@ -49433,25 +49433,25 @@
         <v>434</v>
       </c>
       <c r="D7" t="s">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="E7" t="s">
-        <v>3378</v>
+        <v>3377</v>
       </c>
       <c r="F7" t="s">
         <v>151</v>
       </c>
       <c r="G7" s="49" t="s">
-        <v>3680</v>
+        <v>3679</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>3663</v>
+        <v>3662</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>3265</v>
+        <v>3264</v>
       </c>
       <c r="J7" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="L7" s="83" t="s">
         <v>435</v>
@@ -49459,10 +49459,10 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="4" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>658</v>
@@ -49480,10 +49480,10 @@
         <v>2706</v>
       </c>
       <c r="H8" t="s">
-        <v>3352</v>
+        <v>3351</v>
       </c>
       <c r="I8" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="J8" s="49" t="s">
         <v>2845</v>
@@ -49510,16 +49510,16 @@
         <v>151</v>
       </c>
       <c r="G9" t="s">
-        <v>3314</v>
+        <v>3313</v>
       </c>
       <c r="H9" s="220" t="s">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="I9" s="453" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="J9" s="220" t="s">
-        <v>3291</v>
+        <v>3290</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -49533,7 +49533,7 @@
         <v>2228</v>
       </c>
       <c r="D10" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="E10" t="s">
         <v>2199</v>
@@ -49542,13 +49542,13 @@
         <v>1838</v>
       </c>
       <c r="G10" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
       <c r="H10" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="I10" t="s">
-        <v>3521</v>
+        <v>3520</v>
       </c>
       <c r="J10" s="49" t="s">
         <v>2917</v>
@@ -49591,7 +49591,7 @@
         <v>1494</v>
       </c>
       <c r="E12" t="s">
-        <v>3344</v>
+        <v>3343</v>
       </c>
       <c r="F12" t="s">
         <v>614</v>
@@ -49622,16 +49622,16 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="B14" t="s">
-        <v>3458</v>
+        <v>3457</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>281</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="E14" t="s">
         <v>2163</v>
@@ -49640,16 +49640,16 @@
         <v>1838</v>
       </c>
       <c r="G14" s="97" t="s">
+        <v>3497</v>
+      </c>
+      <c r="H14" s="97" t="s">
         <v>3498</v>
       </c>
-      <c r="H14" s="97" t="s">
-        <v>3499</v>
-      </c>
       <c r="I14" t="s">
-        <v>3656</v>
+        <v>3655</v>
       </c>
       <c r="J14" t="s">
-        <v>3562</v>
+        <v>3561</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -49917,7 +49917,7 @@
     </row>
     <row r="2" spans="1:14" ht="43.15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="C2" s="51"/>
       <c r="D2" s="52" t="s">
@@ -49929,7 +49929,7 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="B4">
         <v>62445630</v>
@@ -49941,7 +49941,7 @@
         <v>2738</v>
       </c>
       <c r="E4" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -49966,7 +49966,7 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="B9" t="s">
         <v>1570</v>
@@ -49978,7 +49978,7 @@
         <v>1569</v>
       </c>
       <c r="E9" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="F9" t="s">
         <v>1752</v>
@@ -49998,7 +49998,7 @@
         <v>2243</v>
       </c>
       <c r="E10" s="284" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="F10" t="s">
         <v>1701</v>
@@ -50006,7 +50006,7 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="30" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="B11" s="178">
         <v>68241069</v>
@@ -50018,7 +50018,7 @@
         <v>2080</v>
       </c>
       <c r="E11" t="s">
-        <v>3224</v>
+        <v>3223</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -50035,7 +50035,7 @@
         <v>2747</v>
       </c>
       <c r="E12" t="s">
-        <v>3630</v>
+        <v>3629</v>
       </c>
       <c r="F12" t="s">
         <v>1701</v>
@@ -50043,7 +50043,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="B13">
         <v>62271547</v>
@@ -50055,15 +50055,15 @@
         <v>2433</v>
       </c>
       <c r="E13" t="s">
+        <v>3069</v>
+      </c>
+      <c r="F13" t="s">
         <v>3070</v>
-      </c>
-      <c r="F13" t="s">
-        <v>3071</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="B14">
         <v>62445630</v>
@@ -50072,7 +50072,7 @@
         <v>1957</v>
       </c>
       <c r="D14" t="s">
-        <v>3346</v>
+        <v>3345</v>
       </c>
       <c r="E14" t="s">
         <v>2707</v>
@@ -50083,7 +50083,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="B15">
         <v>62806425</v>
@@ -50095,7 +50095,7 @@
         <v>1755</v>
       </c>
       <c r="E15" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="F15" t="s">
         <v>2750</v>
@@ -50112,10 +50112,10 @@
         <v>2795</v>
       </c>
       <c r="D16" s="30" t="s">
+        <v>3230</v>
+      </c>
+      <c r="E16" t="s">
         <v>3231</v>
-      </c>
-      <c r="E16" t="s">
-        <v>3232</v>
       </c>
       <c r="F16" t="s">
         <v>2750</v>
@@ -50123,19 +50123,19 @@
     </row>
     <row r="17" spans="1:8" s="30" customFormat="1">
       <c r="A17" s="30" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="B17" s="30">
         <v>68582631</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="D17" s="30" t="s">
+        <v>3246</v>
+      </c>
+      <c r="E17" t="s">
         <v>3247</v>
-      </c>
-      <c r="E17" t="s">
-        <v>3248</v>
       </c>
       <c r="F17" t="s">
         <v>2750</v>
@@ -50158,7 +50158,7 @@
         <v>2799</v>
       </c>
       <c r="E18" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="F18" t="s">
         <v>2750</v>
@@ -50178,10 +50178,10 @@
         <v>2843</v>
       </c>
       <c r="E19" t="s">
-        <v>3395</v>
+        <v>3394</v>
       </c>
       <c r="F19" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -50201,7 +50201,7 @@
         <v>1529</v>
       </c>
       <c r="F21" t="s">
-        <v>3531</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -50237,7 +50237,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="B26">
         <v>68927207</v>
@@ -50249,13 +50249,13 @@
         <v>2724</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>3204</v>
+      </c>
+      <c r="F26" t="s">
         <v>3205</v>
       </c>
-      <c r="F26" t="s">
-        <v>3206</v>
-      </c>
       <c r="G26" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -50272,13 +50272,13 @@
         <v>421</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>3205</v>
+        <v>3204</v>
       </c>
       <c r="F27" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="G27" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -50289,16 +50289,16 @@
         <v>1477</v>
       </c>
       <c r="D29" t="s">
+        <v>3500</v>
+      </c>
+      <c r="E29" t="s">
+        <v>3445</v>
+      </c>
+      <c r="F29" t="s">
+        <v>3219</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>3501</v>
-      </c>
-      <c r="E29" t="s">
-        <v>3446</v>
-      </c>
-      <c r="F29" t="s">
-        <v>3220</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>3502</v>
       </c>
       <c r="H29" t="s">
         <v>407</v>
@@ -50306,7 +50306,7 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="B30">
         <v>63926844</v>
@@ -50318,10 +50318,10 @@
         <v>2749</v>
       </c>
       <c r="E30" t="s">
+        <v>3218</v>
+      </c>
+      <c r="F30" t="s">
         <v>3219</v>
-      </c>
-      <c r="F30" t="s">
-        <v>3220</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -50335,10 +50335,10 @@
         <v>1576</v>
       </c>
       <c r="D31" t="s">
+        <v>3469</v>
+      </c>
+      <c r="E31" t="s">
         <v>3470</v>
-      </c>
-      <c r="E31" t="s">
-        <v>3471</v>
       </c>
       <c r="F31" t="s">
         <v>1326</v>
@@ -50447,10 +50447,10 @@
         <v>2555</v>
       </c>
       <c r="D47" s="30" t="s">
+        <v>2954</v>
+      </c>
+      <c r="F47" s="402" t="s">
         <v>2955</v>
-      </c>
-      <c r="F47" s="402" t="s">
-        <v>2956</v>
       </c>
       <c r="G47" s="30" t="s">
         <v>407</v>
@@ -50546,7 +50546,7 @@
     </row>
     <row r="60" spans="1:5" s="397" customFormat="1" ht="18">
       <c r="C60" s="397" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -50563,7 +50563,7 @@
         <v>2560</v>
       </c>
       <c r="E61" s="30" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
     </row>
     <row r="69" spans="1:12" s="76" customFormat="1">
@@ -52382,7 +52382,7 @@
     </row>
     <row r="252" spans="1:6" s="426" customFormat="1" ht="21">
       <c r="C252" s="426" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
     </row>
     <row r="253" spans="1:6">
@@ -52399,30 +52399,30 @@
         <v>2277</v>
       </c>
       <c r="E253" t="s">
+        <v>3170</v>
+      </c>
+      <c r="F253" t="s">
         <v>3171</v>
-      </c>
-      <c r="F253" t="s">
-        <v>3172</v>
       </c>
     </row>
     <row r="254" spans="1:6">
       <c r="A254" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
       <c r="B254">
         <v>64738222</v>
       </c>
       <c r="C254" s="22" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="D254" t="s">
-        <v>3088</v>
+        <v>3087</v>
       </c>
       <c r="E254" t="s">
+        <v>3170</v>
+      </c>
+      <c r="F254" t="s">
         <v>3171</v>
-      </c>
-      <c r="F254" t="s">
-        <v>3172</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -52433,16 +52433,16 @@
         <v>60433915</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="D255" s="252" t="s">
         <v>2691</v>
       </c>
       <c r="E255" t="s">
+        <v>3170</v>
+      </c>
+      <c r="F255" t="s">
         <v>3171</v>
-      </c>
-      <c r="F255" t="s">
-        <v>3172</v>
       </c>
     </row>
     <row r="256" spans="1:6">
@@ -57196,7 +57196,7 @@
         <v>2738</v>
       </c>
       <c r="E537" s="76" t="s">
-        <v>3365</v>
+        <v>3364</v>
       </c>
       <c r="F537" s="76"/>
       <c r="G537" s="76"/>

--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dc549f2659ed9bd7/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61852" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7A0598E-9562-466C-B47A-374C156B2E0C}"/>
+  <xr:revisionPtr revIDLastSave="61856" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{000B680A-8759-4C8C-86D6-D34046075004}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10098,9 +10098,6 @@
     <t>Max005</t>
   </si>
   <si>
-    <t>65118654 1 pantalla hasta el 08 de septiembre</t>
-  </si>
-  <si>
     <t>Hfas080826</t>
   </si>
   <si>
@@ -10380,9 +10377,6 @@
     <t>15.15 hasta 17 de septiembre</t>
   </si>
   <si>
-    <t>63393953 1 pantalla hasta el 10 de septiembre</t>
-  </si>
-  <si>
     <t>Tea150826</t>
   </si>
   <si>
@@ -12367,6 +12361,12 @@
   </si>
   <si>
     <t>N005 1 pantalla hasta el 12 de octubre 120926-1445r</t>
+  </si>
+  <si>
+    <t>63393953 1 pantalla hasta el 12 de septiembre</t>
+  </si>
+  <si>
+    <t>N005 1 pantalla hasta el 12 de octubre 120926-15-03c</t>
   </si>
 </sst>
 </file>
@@ -30369,7 +30369,7 @@
   <sheetData>
     <row r="1" spans="1:11" s="30" customFormat="1">
       <c r="A1" s="30" t="s">
-        <v>3311</v>
+        <v>3309</v>
       </c>
       <c r="B1" s="30">
         <v>60389752</v>
@@ -30381,7 +30381,7 @@
         <v>2030</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="F1" s="30" t="s">
         <v>2099</v>
@@ -30401,12 +30401,12 @@
         <v>2146</v>
       </c>
       <c r="D2" s="148" t="s">
-        <v>3196</v>
+        <v>3194</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="148" customFormat="1">
       <c r="A3" s="148" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="B3" s="148" t="s">
         <v>2703</v>
@@ -30420,7 +30420,7 @@
     </row>
     <row r="4" spans="1:11" s="30" customFormat="1">
       <c r="A4" s="30" t="s">
-        <v>3311</v>
+        <v>3309</v>
       </c>
       <c r="B4" s="30">
         <v>60389752</v>
@@ -30432,7 +30432,7 @@
         <v>2028</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>3112</v>
+        <v>3110</v>
       </c>
       <c r="F4" s="30" t="s">
         <v>2099</v>
@@ -30452,7 +30452,7 @@
         <v>2160</v>
       </c>
       <c r="D5" s="148" t="s">
-        <v>3317</v>
+        <v>3315</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="148" customFormat="1">
@@ -30483,7 +30483,7 @@
         <v>2911</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>3181</v>
+        <v>3179</v>
       </c>
       <c r="F7" s="30" t="s">
         <v>2104</v>
@@ -30508,7 +30508,7 @@
     </row>
     <row r="9" spans="1:11" s="148" customFormat="1">
       <c r="A9" s="148" t="s">
-        <v>3429</v>
+        <v>3427</v>
       </c>
       <c r="B9" s="148" t="s">
         <v>1213</v>
@@ -30525,7 +30525,7 @@
     </row>
     <row r="10" spans="1:11" s="429" customFormat="1">
       <c r="A10" s="429" t="s">
-        <v>3282</v>
+        <v>3280</v>
       </c>
       <c r="B10" s="429">
         <v>60389752</v>
@@ -30562,7 +30562,7 @@
         <v>2165</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>3275</v>
+        <v>3273</v>
       </c>
       <c r="F13" s="30" t="s">
         <v>2164</v>
@@ -30574,7 +30574,7 @@
     </row>
     <row r="14" spans="1:11" s="148" customFormat="1">
       <c r="A14" s="226" t="s">
-        <v>3033</v>
+        <v>3031</v>
       </c>
       <c r="B14" s="226" t="s">
         <v>1691</v>
@@ -30588,7 +30588,7 @@
     </row>
     <row r="15" spans="1:11" s="148" customFormat="1">
       <c r="A15" s="226" t="s">
-        <v>3605</v>
+        <v>3603</v>
       </c>
       <c r="B15" s="422">
         <v>62439069</v>
@@ -30611,10 +30611,10 @@
         <v>1541</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>3183</v>
+        <v>3181</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>3276</v>
+        <v>3274</v>
       </c>
       <c r="F16" s="32" t="s">
         <v>1542</v>
@@ -30623,21 +30623,21 @@
         <v>198</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>3184</v>
+        <v>3182</v>
       </c>
       <c r="I16" s="32" t="s">
-        <v>3436</v>
+        <v>3434</v>
       </c>
       <c r="J16" s="32" t="s">
-        <v>3358</v>
+        <v>3356</v>
       </c>
       <c r="K16" s="30" t="s">
-        <v>3359</v>
+        <v>3357</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="164" customFormat="1">
       <c r="A17" s="253" t="s">
-        <v>3556</v>
+        <v>3554</v>
       </c>
       <c r="B17" s="253" t="s">
         <v>1405</v>
@@ -30680,10 +30680,10 @@
         <v>1504</v>
       </c>
       <c r="D19" s="145" t="s">
-        <v>3674</v>
+        <v>3672</v>
       </c>
       <c r="E19" s="145" t="s">
-        <v>3163</v>
+        <v>3161</v>
       </c>
       <c r="F19" s="145" t="s">
         <v>1371</v>
@@ -30698,7 +30698,7 @@
     </row>
     <row r="20" spans="1:11" s="298" customFormat="1">
       <c r="A20" s="164" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="B20" s="164">
         <v>68444421</v>
@@ -30707,7 +30707,7 @@
         <v>1697</v>
       </c>
       <c r="D20" s="253" t="s">
-        <v>3083</v>
+        <v>3081</v>
       </c>
       <c r="E20" s="253" t="s">
         <v>1698</v>
@@ -30720,7 +30720,7 @@
         <v>1702</v>
       </c>
       <c r="D21" s="164" t="s">
-        <v>3675</v>
+        <v>3673</v>
       </c>
       <c r="E21" s="164" t="s">
         <v>1703</v>
@@ -30728,7 +30728,7 @@
     </row>
     <row r="22" spans="1:11" s="30" customFormat="1">
       <c r="A22" s="32" t="s">
-        <v>3088</v>
+        <v>3086</v>
       </c>
       <c r="B22" s="32">
         <v>60389752</v>
@@ -30740,7 +30740,7 @@
         <v>2143</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="F22" s="30" t="s">
         <v>2098</v>
@@ -30769,7 +30769,7 @@
         <v>2139</v>
       </c>
       <c r="D24" s="148" t="s">
-        <v>3677</v>
+        <v>3675</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="30" customFormat="1">
@@ -30786,7 +30786,7 @@
         <v>1538</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>3162</v>
+        <v>3160</v>
       </c>
       <c r="F25" s="30" t="s">
         <v>1371</v>
@@ -30834,7 +30834,7 @@
     </row>
     <row r="28" spans="1:11" s="30" customFormat="1">
       <c r="A28" s="30" t="s">
-        <v>3429</v>
+        <v>3427</v>
       </c>
       <c r="B28" s="30">
         <v>60389752</v>
@@ -30846,7 +30846,7 @@
         <v>2025</v>
       </c>
       <c r="E28" s="30" t="s">
-        <v>3406</v>
+        <v>3404</v>
       </c>
       <c r="F28" s="305" t="s">
         <v>2176</v>
@@ -30871,7 +30871,7 @@
     </row>
     <row r="30" spans="1:11" s="164" customFormat="1">
       <c r="A30" s="164" t="s">
-        <v>3654</v>
+        <v>3652</v>
       </c>
       <c r="B30" s="164">
         <v>62782770</v>
@@ -30880,24 +30880,24 @@
         <v>2397</v>
       </c>
       <c r="D30" s="164" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="30" customFormat="1">
       <c r="A31" s="30" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>3149</v>
+        <v>3147</v>
       </c>
       <c r="C31" s="252" t="s">
         <v>1916</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>3150</v>
+        <v>3148</v>
       </c>
       <c r="E31" s="30" t="s">
-        <v>3055</v>
+        <v>3053</v>
       </c>
       <c r="F31" s="30" t="s">
         <v>2047</v>
@@ -30906,16 +30906,16 @@
         <v>198</v>
       </c>
       <c r="H31" s="30" t="s">
-        <v>3151</v>
+        <v>3149</v>
       </c>
       <c r="I31" s="192" t="s">
-        <v>3271</v>
+        <v>3269</v>
       </c>
       <c r="J31" s="427" t="s">
-        <v>3173</v>
+        <v>3171</v>
       </c>
       <c r="K31" s="145" t="s">
-        <v>3689</v>
+        <v>3687</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="163" customFormat="1">
@@ -30961,7 +30961,7 @@
         <v>2111</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="F34" s="30" t="s">
         <v>2102</v>
@@ -31012,10 +31012,10 @@
         <v>2023</v>
       </c>
       <c r="D37" s="30" t="s">
-        <v>3295</v>
+        <v>3293</v>
       </c>
       <c r="E37" s="30" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="F37" s="30" t="s">
         <v>2092</v>
@@ -31027,18 +31027,18 @@
         <v>2926</v>
       </c>
       <c r="I37" s="30" t="s">
-        <v>3329</v>
+        <v>3327</v>
       </c>
       <c r="J37" s="30" t="s">
-        <v>3676</v>
+        <v>3674</v>
       </c>
       <c r="K37" s="30" t="s">
-        <v>3525</v>
+        <v>3523</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="147" customFormat="1">
       <c r="A38" s="147" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="B38" s="147" t="s">
         <v>2701</v>
@@ -31070,16 +31070,16 @@
         <v>2526</v>
       </c>
       <c r="B40" s="32" t="s">
-        <v>3305</v>
+        <v>3303</v>
       </c>
       <c r="C40" s="252" t="s">
         <v>1678</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>3647</v>
+        <v>3645</v>
       </c>
       <c r="E40" s="30" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="F40" s="30" t="s">
         <v>2107</v>
@@ -31088,21 +31088,21 @@
         <v>198</v>
       </c>
       <c r="H40" s="30" t="s">
-        <v>3234</v>
+        <v>3232</v>
       </c>
       <c r="I40" s="32" t="s">
-        <v>3260</v>
+        <v>3258</v>
       </c>
       <c r="J40" s="32" t="s">
-        <v>3291</v>
+        <v>3289</v>
       </c>
       <c r="K40" s="145" t="s">
-        <v>3648</v>
+        <v>3646</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="163" customFormat="1">
       <c r="A41" s="163" t="s">
-        <v>3104</v>
+        <v>3102</v>
       </c>
       <c r="B41" s="163">
         <v>68381893</v>
@@ -31134,7 +31134,7 @@
     </row>
     <row r="43" spans="1:11" s="30" customFormat="1">
       <c r="A43" s="30" t="s">
-        <v>3282</v>
+        <v>3280</v>
       </c>
       <c r="B43" s="30">
         <v>60389752</v>
@@ -31146,7 +31146,7 @@
         <v>2051</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>3115</v>
+        <v>3113</v>
       </c>
       <c r="F43" s="30" t="s">
         <v>2140</v>
@@ -31157,7 +31157,7 @@
     </row>
     <row r="44" spans="1:11" s="164" customFormat="1">
       <c r="A44" s="164" t="s">
-        <v>3104</v>
+        <v>3102</v>
       </c>
       <c r="B44" s="164">
         <v>68381893</v>
@@ -31174,7 +31174,7 @@
     </row>
     <row r="45" spans="1:11" s="163" customFormat="1">
       <c r="A45" s="163" t="s">
-        <v>3539</v>
+        <v>3537</v>
       </c>
       <c r="B45" s="163">
         <v>64079861</v>
@@ -31203,7 +31203,7 @@
         <v>2905</v>
       </c>
       <c r="E46" s="30" t="s">
-        <v>3496</v>
+        <v>3494</v>
       </c>
       <c r="F46" s="30" t="s">
         <v>2124</v>
@@ -31249,16 +31249,16 @@
         <v>1512</v>
       </c>
       <c r="B49" s="30" t="s">
-        <v>3548</v>
+        <v>3546</v>
       </c>
       <c r="C49" s="134" t="s">
         <v>2014</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>3423</v>
+        <v>3421</v>
       </c>
       <c r="E49" s="30" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="F49" s="30" t="s">
         <v>2110</v>
@@ -31267,16 +31267,16 @@
         <v>198</v>
       </c>
       <c r="H49" s="30" t="s">
-        <v>3258</v>
+        <v>3256</v>
       </c>
       <c r="I49" s="30" t="s">
-        <v>3316</v>
+        <v>3314</v>
       </c>
       <c r="J49" s="435" t="s">
         <v>2880</v>
       </c>
       <c r="K49" s="32" t="s">
-        <v>3422</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="50" spans="1:11" s="164" customFormat="1">
@@ -31304,7 +31304,7 @@
         <v>2022</v>
       </c>
       <c r="D51" s="164" t="s">
-        <v>3220</v>
+        <v>3218</v>
       </c>
     </row>
     <row r="52" spans="1:11" s="139" customFormat="1">
@@ -31321,7 +31321,7 @@
         <v>2920</v>
       </c>
       <c r="E52" s="139" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="F52" s="139" t="s">
         <v>2108</v>
@@ -31330,16 +31330,16 @@
         <v>198</v>
       </c>
       <c r="H52" s="140" t="s">
-        <v>3263</v>
+        <v>3261</v>
       </c>
       <c r="I52" s="140" t="s">
-        <v>3519</v>
+        <v>3517</v>
       </c>
       <c r="J52" s="30" t="s">
-        <v>3392</v>
+        <v>3390</v>
       </c>
       <c r="K52" s="270" t="s">
-        <v>3136</v>
+        <v>3134</v>
       </c>
     </row>
     <row r="53" spans="1:11" s="164" customFormat="1">
@@ -31380,7 +31380,7 @@
     </row>
     <row r="55" spans="1:11" s="30" customFormat="1">
       <c r="A55" s="30" t="s">
-        <v>3658</v>
+        <v>3656</v>
       </c>
       <c r="B55" s="30">
         <v>61130088</v>
@@ -31392,7 +31392,7 @@
         <v>2018</v>
       </c>
       <c r="E55" s="30" t="s">
-        <v>3275</v>
+        <v>3273</v>
       </c>
       <c r="F55" s="30" t="s">
         <v>2125</v>
@@ -31409,10 +31409,10 @@
         <v>60433915</v>
       </c>
       <c r="C56" s="405" t="s">
+        <v>3284</v>
+      </c>
+      <c r="D56" s="375" t="s">
         <v>3286</v>
-      </c>
-      <c r="D56" s="375" t="s">
-        <v>3288</v>
       </c>
       <c r="E56" s="164"/>
     </row>
@@ -31421,13 +31421,13 @@
         <v>2526</v>
       </c>
       <c r="B57" s="163" t="s">
-        <v>3292</v>
+        <v>3290</v>
       </c>
       <c r="C57" s="405" t="s">
+        <v>3285</v>
+      </c>
+      <c r="D57" s="375" t="s">
         <v>3287</v>
-      </c>
-      <c r="D57" s="375" t="s">
-        <v>3289</v>
       </c>
       <c r="E57" s="164"/>
     </row>
@@ -31445,7 +31445,7 @@
         <v>2844</v>
       </c>
       <c r="E58" s="30" t="s">
-        <v>3349</v>
+        <v>3347</v>
       </c>
       <c r="F58" s="30" t="s">
         <v>2137</v>
@@ -31454,16 +31454,16 @@
         <v>198</v>
       </c>
       <c r="H58" s="30" t="s">
-        <v>3441</v>
+        <v>3439</v>
       </c>
       <c r="I58" s="30" t="s">
-        <v>3303</v>
+        <v>3301</v>
       </c>
       <c r="J58" s="30" t="s">
-        <v>3396</v>
+        <v>3394</v>
       </c>
       <c r="K58" s="217" t="s">
-        <v>3027</v>
+        <v>3688</v>
       </c>
     </row>
     <row r="59" spans="1:11" s="393" customFormat="1">
@@ -31478,7 +31478,7 @@
         <v>158</v>
       </c>
       <c r="B61" s="30" t="s">
-        <v>3279</v>
+        <v>3277</v>
       </c>
       <c r="C61" s="134" t="s">
         <v>2091</v>
@@ -31487,7 +31487,7 @@
         <v>2908</v>
       </c>
       <c r="E61" s="30" t="s">
-        <v>3182</v>
+        <v>3180</v>
       </c>
       <c r="F61" s="30" t="s">
         <v>2092</v>
@@ -31496,21 +31496,21 @@
         <v>198</v>
       </c>
       <c r="H61" s="30" t="s">
-        <v>3568</v>
+        <v>3566</v>
       </c>
       <c r="I61" s="30" t="s">
-        <v>3323</v>
+        <v>3321</v>
       </c>
       <c r="J61" s="30" t="s">
-        <v>3430</v>
+        <v>3428</v>
       </c>
       <c r="K61" s="30" t="s">
-        <v>3522</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="62" spans="1:11" s="147" customFormat="1">
       <c r="A62" s="147" t="s">
-        <v>3277</v>
+        <v>3275</v>
       </c>
       <c r="B62" s="147">
         <v>60196388</v>
@@ -31519,7 +31519,7 @@
         <v>1483</v>
       </c>
       <c r="D62" s="376" t="s">
-        <v>3280</v>
+        <v>3278</v>
       </c>
       <c r="E62" s="148" t="s">
         <v>1391</v>
@@ -31527,7 +31527,7 @@
     </row>
     <row r="63" spans="1:11" s="163" customFormat="1">
       <c r="A63" s="163" t="s">
-        <v>3311</v>
+        <v>3309</v>
       </c>
       <c r="B63" s="163">
         <v>62960567</v>
@@ -31536,7 +31536,7 @@
         <v>2076</v>
       </c>
       <c r="D63" s="375" t="s">
-        <v>3235</v>
+        <v>3233</v>
       </c>
       <c r="E63" s="164"/>
     </row>
@@ -31551,10 +31551,10 @@
         <v>1677</v>
       </c>
       <c r="D64" s="30" t="s">
-        <v>3435</v>
+        <v>3433</v>
       </c>
       <c r="E64" s="30" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
       <c r="F64" s="30" t="s">
         <v>2109</v>
@@ -31563,16 +31563,16 @@
         <v>198</v>
       </c>
       <c r="H64" s="32" t="s">
-        <v>3536</v>
+        <v>3534</v>
       </c>
       <c r="I64" s="32" t="s">
-        <v>3608</v>
+        <v>3606</v>
       </c>
       <c r="J64" s="30" t="s">
-        <v>3485</v>
+        <v>3483</v>
       </c>
       <c r="K64" s="30" t="s">
-        <v>3304</v>
+        <v>3302</v>
       </c>
     </row>
     <row r="65" spans="1:11" s="164" customFormat="1">
@@ -31594,7 +31594,7 @@
     </row>
     <row r="66" spans="1:11" s="164" customFormat="1">
       <c r="A66" s="253" t="s">
-        <v>3088</v>
+        <v>3086</v>
       </c>
       <c r="B66" s="164">
         <v>62090364</v>
@@ -31611,7 +31611,7 @@
     </row>
     <row r="67" spans="1:11" s="30" customFormat="1">
       <c r="A67" s="254" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
       <c r="B67" s="285" t="s">
         <v>1924</v>
@@ -31620,10 +31620,10 @@
         <v>1681</v>
       </c>
       <c r="D67" s="30" t="s">
-        <v>3103</v>
+        <v>3101</v>
       </c>
       <c r="E67" s="30" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="F67" s="30" t="s">
         <v>2113</v>
@@ -31632,21 +31632,21 @@
         <v>198</v>
       </c>
       <c r="H67" s="30" t="s">
-        <v>3518</v>
+        <v>3516</v>
       </c>
       <c r="I67" s="30" t="s">
-        <v>3594</v>
+        <v>3592</v>
       </c>
       <c r="J67" s="30" t="s">
-        <v>3646</v>
+        <v>3644</v>
       </c>
       <c r="K67" s="30" t="s">
-        <v>3111</v>
+        <v>3109</v>
       </c>
     </row>
     <row r="68" spans="1:11" s="147" customFormat="1">
       <c r="A68" s="147" t="s">
-        <v>3277</v>
+        <v>3275</v>
       </c>
       <c r="B68" s="147">
         <v>68741448</v>
@@ -31655,7 +31655,7 @@
         <v>1892</v>
       </c>
       <c r="D68" s="376" t="s">
-        <v>3256</v>
+        <v>3254</v>
       </c>
       <c r="E68" s="148"/>
     </row>
@@ -31670,7 +31670,7 @@
         <v>2112</v>
       </c>
       <c r="D69" s="148" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
     </row>
     <row r="70" spans="1:11" s="30" customFormat="1">
@@ -31678,16 +31678,16 @@
         <v>467</v>
       </c>
       <c r="B70" s="32" t="s">
-        <v>3533</v>
+        <v>3531</v>
       </c>
       <c r="C70" s="252" t="s">
         <v>1680</v>
       </c>
       <c r="D70" s="30" t="s">
-        <v>3401</v>
+        <v>3399</v>
       </c>
       <c r="E70" s="30" t="s">
-        <v>3350</v>
+        <v>3348</v>
       </c>
       <c r="F70" s="30" t="s">
         <v>2151</v>
@@ -31696,13 +31696,13 @@
         <v>198</v>
       </c>
       <c r="H70" s="32" t="s">
-        <v>3144</v>
+        <v>3142</v>
       </c>
       <c r="I70" s="30" t="s">
-        <v>3402</v>
+        <v>3400</v>
       </c>
       <c r="J70" s="32" t="s">
-        <v>3427</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="71" spans="1:11" s="164" customFormat="1">
@@ -31716,12 +31716,12 @@
         <v>1978</v>
       </c>
       <c r="D71" s="164" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
     </row>
     <row r="72" spans="1:11" s="163" customFormat="1">
       <c r="A72" s="269" t="s">
-        <v>3043</v>
+        <v>3041</v>
       </c>
       <c r="B72" s="269" t="s">
         <v>1465</v>
@@ -31736,7 +31736,7 @@
     </row>
     <row r="73" spans="1:11" s="30" customFormat="1">
       <c r="A73" s="30" t="s">
-        <v>3437</v>
+        <v>3435</v>
       </c>
       <c r="B73" s="30">
         <v>60389752</v>
@@ -31748,7 +31748,7 @@
         <v>2856</v>
       </c>
       <c r="E73" s="30" t="s">
-        <v>3540</v>
+        <v>3538</v>
       </c>
       <c r="F73" s="30" t="s">
         <v>2046</v>
@@ -31759,7 +31759,7 @@
     </row>
     <row r="74" spans="1:11" s="147" customFormat="1">
       <c r="A74" s="147" t="s">
-        <v>3033</v>
+        <v>3031</v>
       </c>
       <c r="B74" s="147">
         <v>64226974</v>
@@ -31783,7 +31783,7 @@
         <v>1962</v>
       </c>
       <c r="D75" s="148" t="s">
-        <v>3331</v>
+        <v>3329</v>
       </c>
       <c r="E75" s="148"/>
     </row>
@@ -31798,10 +31798,10 @@
         <v>1891</v>
       </c>
       <c r="D76" s="30" t="s">
-        <v>3048</v>
+        <v>3046</v>
       </c>
       <c r="E76" s="30" t="s">
-        <v>3226</v>
+        <v>3224</v>
       </c>
       <c r="F76" s="30" t="s">
         <v>2124</v>
@@ -31810,16 +31810,16 @@
         <v>198</v>
       </c>
       <c r="H76" s="30" t="s">
+        <v>3047</v>
+      </c>
+      <c r="I76" s="30" t="s">
         <v>3049</v>
       </c>
-      <c r="I76" s="30" t="s">
-        <v>3051</v>
-      </c>
       <c r="J76" s="30" t="s">
-        <v>3337</v>
+        <v>3335</v>
       </c>
       <c r="K76" s="30" t="s">
-        <v>3403</v>
+        <v>3401</v>
       </c>
     </row>
     <row r="77" spans="1:11" s="152" customFormat="1">
@@ -31835,16 +31835,16 @@
         <v>143</v>
       </c>
       <c r="B79" s="30" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="C79" s="134" t="s">
         <v>2021</v>
       </c>
       <c r="D79" s="30" t="s">
-        <v>3079</v>
+        <v>3077</v>
       </c>
       <c r="E79" s="30" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="F79" s="30" t="s">
         <v>2103</v>
@@ -31853,16 +31853,16 @@
         <v>198</v>
       </c>
       <c r="H79" s="32" t="s">
-        <v>3100</v>
+        <v>3098</v>
       </c>
       <c r="I79" s="32" t="s">
-        <v>3300</v>
+        <v>3298</v>
       </c>
       <c r="J79" s="30" t="s">
-        <v>3666</v>
+        <v>3664</v>
       </c>
       <c r="K79" s="30" t="s">
-        <v>3339</v>
+        <v>3337</v>
       </c>
     </row>
     <row r="80" spans="1:11" s="147" customFormat="1">
@@ -31882,7 +31882,7 @@
     </row>
     <row r="81" spans="1:11" s="147" customFormat="1">
       <c r="A81" s="149" t="s">
-        <v>3278</v>
+        <v>3276</v>
       </c>
       <c r="B81" s="147">
         <v>64720128</v>
@@ -31899,10 +31899,10 @@
     </row>
     <row r="82" spans="1:11" s="30" customFormat="1">
       <c r="A82" s="30" t="s">
-        <v>3310</v>
+        <v>3308</v>
       </c>
       <c r="B82" s="30" t="s">
-        <v>3309</v>
+        <v>3307</v>
       </c>
       <c r="C82" s="22" t="s">
         <v>1917</v>
@@ -31911,7 +31911,7 @@
         <v>2887</v>
       </c>
       <c r="E82" s="30" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="F82" s="30" t="s">
         <v>1918</v>
@@ -31920,16 +31920,16 @@
         <v>198</v>
       </c>
       <c r="H82" s="30" t="s">
-        <v>3615</v>
+        <v>3613</v>
       </c>
       <c r="I82" s="30" t="s">
-        <v>3452</v>
+        <v>3450</v>
       </c>
       <c r="J82" s="30" t="s">
-        <v>3603</v>
-      </c>
-      <c r="K82" s="217" t="s">
-        <v>2933</v>
+        <v>3601</v>
+      </c>
+      <c r="K82" s="145" t="s">
+        <v>3689</v>
       </c>
     </row>
     <row r="83" spans="1:11" s="148" customFormat="1">
@@ -31971,7 +31971,7 @@
         <v>694</v>
       </c>
       <c r="D85" s="30" t="s">
-        <v>3453</v>
+        <v>3451</v>
       </c>
       <c r="E85" s="30" t="s">
         <v>1807</v>
@@ -31983,16 +31983,16 @@
         <v>493</v>
       </c>
       <c r="H85" s="30" t="s">
-        <v>3575</v>
+        <v>3573</v>
       </c>
       <c r="I85" s="442" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="J85" s="30" t="s">
-        <v>3595</v>
+        <v>3593</v>
       </c>
       <c r="K85" s="215" t="s">
-        <v>3175</v>
+        <v>3173</v>
       </c>
     </row>
     <row r="86" spans="1:11" s="147" customFormat="1">
@@ -32015,7 +32015,7 @@
     </row>
     <row r="87" spans="1:11" s="147" customFormat="1">
       <c r="A87" s="147" t="s">
-        <v>3282</v>
+        <v>3280</v>
       </c>
       <c r="B87" s="147" t="s">
         <v>913</v>
@@ -32033,16 +32033,16 @@
     </row>
     <row r="88" spans="1:11" s="30" customFormat="1">
       <c r="A88" s="145" t="s">
-        <v>3654</v>
+        <v>3652</v>
       </c>
       <c r="B88" s="30" t="s">
-        <v>3680</v>
+        <v>3678</v>
       </c>
       <c r="C88" s="153" t="s">
         <v>695</v>
       </c>
       <c r="D88" s="30" t="s">
-        <v>3028</v>
+        <v>3026</v>
       </c>
       <c r="E88" s="30" t="s">
         <v>1091</v>
@@ -32054,16 +32054,16 @@
         <v>1539</v>
       </c>
       <c r="H88" s="30" t="s">
-        <v>3029</v>
+        <v>3027</v>
       </c>
       <c r="I88" s="30" t="s">
-        <v>3063</v>
+        <v>3061</v>
       </c>
       <c r="J88" s="32" t="s">
-        <v>3153</v>
+        <v>3151</v>
       </c>
       <c r="K88" s="30" t="s">
-        <v>3152</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="89" spans="1:11" s="147" customFormat="1">
@@ -32086,7 +32086,7 @@
     </row>
     <row r="90" spans="1:11" s="148" customFormat="1">
       <c r="A90" s="226" t="s">
-        <v>3282</v>
+        <v>3280</v>
       </c>
       <c r="B90" s="148">
         <v>67381873</v>
@@ -32104,7 +32104,7 @@
     </row>
     <row r="91" spans="1:11" s="106" customFormat="1">
       <c r="A91" s="250" t="s">
-        <v>3043</v>
+        <v>3041</v>
       </c>
       <c r="B91" s="32" t="s">
         <v>1411</v>
@@ -32113,7 +32113,7 @@
         <v>46</v>
       </c>
       <c r="D91" s="106" t="s">
-        <v>3307</v>
+        <v>3305</v>
       </c>
       <c r="E91" s="106" t="s">
         <v>1133</v>
@@ -32125,16 +32125,16 @@
         <v>66</v>
       </c>
       <c r="H91" s="30" t="s">
-        <v>3308</v>
+        <v>3306</v>
       </c>
       <c r="I91" s="31" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="J91" s="32" t="s">
-        <v>3135</v>
+        <v>3133</v>
       </c>
       <c r="K91" s="30" t="s">
-        <v>3428</v>
+        <v>3426</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="411" customFormat="1">
@@ -32165,7 +32165,7 @@
         <v>1734</v>
       </c>
       <c r="D93" s="148" t="s">
-        <v>3407</v>
+        <v>3405</v>
       </c>
     </row>
     <row r="94" spans="1:11" s="32" customFormat="1">
@@ -32182,7 +32182,7 @@
         <v>1372</v>
       </c>
       <c r="E94" s="32" t="s">
-        <v>3580</v>
+        <v>3578</v>
       </c>
       <c r="F94" s="32" t="s">
         <v>1373</v>
@@ -32215,7 +32215,7 @@
         <v>1390</v>
       </c>
       <c r="D96" s="148" t="s">
-        <v>3681</v>
+        <v>3679</v>
       </c>
       <c r="E96" s="148" t="s">
         <v>1389</v>
@@ -32226,16 +32226,16 @@
         <v>1430</v>
       </c>
       <c r="B97" s="30" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="C97" s="153" t="s">
         <v>2011</v>
       </c>
       <c r="D97" s="30" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="E97" s="30" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="F97" s="30" t="s">
         <v>1918</v>
@@ -32244,16 +32244,16 @@
         <v>198</v>
       </c>
       <c r="H97" s="32" t="s">
-        <v>3626</v>
+        <v>3624</v>
       </c>
       <c r="I97" s="30" t="s">
-        <v>3092</v>
+        <v>3090</v>
       </c>
       <c r="J97" s="30" t="s">
-        <v>3475</v>
+        <v>3473</v>
       </c>
       <c r="K97" s="439" t="s">
-        <v>3649</v>
+        <v>3647</v>
       </c>
     </row>
     <row r="98" spans="1:13" s="393" customFormat="1">
@@ -32266,19 +32266,19 @@
     </row>
     <row r="100" spans="1:13" s="30" customFormat="1">
       <c r="A100" s="145" t="s">
-        <v>3654</v>
+        <v>3652</v>
       </c>
       <c r="B100" s="30" t="s">
-        <v>3686</v>
+        <v>3684</v>
       </c>
       <c r="C100" s="252" t="s">
         <v>2886</v>
       </c>
       <c r="D100" s="30" t="s">
-        <v>3478</v>
+        <v>3476</v>
       </c>
       <c r="E100" s="30" t="s">
-        <v>3229</v>
+        <v>3227</v>
       </c>
       <c r="F100" s="30" t="s">
         <v>1918</v>
@@ -32287,16 +32287,16 @@
         <v>198</v>
       </c>
       <c r="H100" s="30" t="s">
-        <v>3617</v>
+        <v>3615</v>
       </c>
       <c r="I100" s="145" t="s">
-        <v>3687</v>
+        <v>3685</v>
       </c>
       <c r="J100" s="30" t="s">
-        <v>3657</v>
+        <v>3655</v>
       </c>
       <c r="K100" s="145" t="s">
-        <v>3688</v>
+        <v>3686</v>
       </c>
     </row>
     <row r="101" spans="1:13" s="393" customFormat="1">
@@ -32309,19 +32309,19 @@
     </row>
     <row r="103" spans="1:13" s="30" customFormat="1">
       <c r="A103" s="30" t="s">
-        <v>3282</v>
+        <v>3280</v>
       </c>
       <c r="B103" s="30" t="s">
-        <v>3404</v>
+        <v>3402</v>
       </c>
       <c r="C103" s="252" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="D103" s="30" t="s">
-        <v>3324</v>
+        <v>3322</v>
       </c>
       <c r="E103" s="30" t="s">
-        <v>3325</v>
+        <v>3323</v>
       </c>
       <c r="F103" s="30" t="s">
         <v>1918</v>
@@ -32330,16 +32330,16 @@
         <v>198</v>
       </c>
       <c r="H103" s="30" t="s">
-        <v>3326</v>
+        <v>3324</v>
       </c>
       <c r="I103" s="30" t="s">
-        <v>3405</v>
+        <v>3403</v>
       </c>
       <c r="J103" s="30" t="s">
-        <v>3391</v>
+        <v>3389</v>
       </c>
       <c r="K103" s="30" t="s">
-        <v>3353</v>
+        <v>3351</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -32374,22 +32374,22 @@
     </row>
     <row r="106" spans="1:13" s="30" customFormat="1">
       <c r="A106" s="30" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="B106" s="30">
         <v>62724019</v>
       </c>
       <c r="C106" s="252" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
       <c r="D106" s="30" t="s">
+        <v>3155</v>
+      </c>
+      <c r="E106" s="30" t="s">
         <v>3157</v>
       </c>
-      <c r="E106" s="30" t="s">
-        <v>3159</v>
-      </c>
       <c r="F106" s="30" t="s">
-        <v>3158</v>
+        <v>3156</v>
       </c>
       <c r="G106" s="30" t="s">
         <v>59</v>
@@ -32408,7 +32408,7 @@
         <v>157</v>
       </c>
       <c r="B112" s="285" t="s">
-        <v>3176</v>
+        <v>3174</v>
       </c>
       <c r="C112" s="134" t="s">
         <v>2008</v>
@@ -32451,7 +32451,7 @@
         <v>1998</v>
       </c>
       <c r="E127" s="30" t="s">
-        <v>3250</v>
+        <v>3248</v>
       </c>
       <c r="F127" t="s">
         <v>1996</v>
@@ -32471,7 +32471,7 @@
         <v>1968</v>
       </c>
       <c r="E128" s="30" t="s">
-        <v>3250</v>
+        <v>3248</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -32485,10 +32485,10 @@
         <v>2763</v>
       </c>
       <c r="D129" s="378" t="s">
-        <v>3321</v>
+        <v>3319</v>
       </c>
       <c r="E129" s="30" t="s">
-        <v>3250</v>
+        <v>3248</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -32505,7 +32505,7 @@
         <v>2638</v>
       </c>
       <c r="E130" s="30" t="s">
-        <v>3250</v>
+        <v>3248</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -32522,7 +32522,7 @@
         <v>1974</v>
       </c>
       <c r="E131" s="30" t="s">
-        <v>3250</v>
+        <v>3248</v>
       </c>
     </row>
     <row r="133" spans="1:6" s="121" customFormat="1" ht="23.5">
@@ -32544,7 +32544,7 @@
         <v>2380</v>
       </c>
       <c r="E134" s="30" t="s">
-        <v>3268</v>
+        <v>3266</v>
       </c>
       <c r="F134" t="s">
         <v>1349</v>
@@ -32564,7 +32564,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>3658</v>
+        <v>3656</v>
       </c>
       <c r="B139">
         <v>64720128</v>
@@ -32593,7 +32593,7 @@
         <v>1985</v>
       </c>
       <c r="D140" s="378" t="s">
-        <v>3293</v>
+        <v>3291</v>
       </c>
       <c r="E140" s="30" t="s">
         <v>1984</v>
@@ -32624,7 +32624,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="C143" s="1" t="s">
-        <v>3334</v>
+        <v>3332</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -32668,7 +32668,7 @@
         <v>2385</v>
       </c>
       <c r="E153" s="30" t="s">
-        <v>3251</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -32676,16 +32676,16 @@
         <v>1512</v>
       </c>
       <c r="B154" t="s">
-        <v>3504</v>
+        <v>3502</v>
       </c>
       <c r="C154" t="s">
         <v>2250</v>
       </c>
       <c r="D154" s="378" t="s">
-        <v>3503</v>
+        <v>3501</v>
       </c>
       <c r="E154" s="30" t="s">
-        <v>3251</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -32702,7 +32702,7 @@
         <v>2639</v>
       </c>
       <c r="E155" s="30" t="s">
-        <v>3367</v>
+        <v>3365</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -32716,10 +32716,10 @@
         <v>2260</v>
       </c>
       <c r="D156" s="378" t="s">
-        <v>3056</v>
+        <v>3054</v>
       </c>
       <c r="E156" s="30" t="s">
-        <v>3367</v>
+        <v>3365</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -32736,7 +32736,7 @@
         <v>2527</v>
       </c>
       <c r="E157" s="30" t="s">
-        <v>3367</v>
+        <v>3365</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -32753,7 +32753,7 @@
         <v>2679</v>
       </c>
       <c r="E158" s="30" t="s">
-        <v>3367</v>
+        <v>3365</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -32767,15 +32767,15 @@
         <v>2549</v>
       </c>
       <c r="D159" s="378" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="E159" s="30" t="s">
-        <v>3367</v>
+        <v>3365</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" t="s">
-        <v>3429</v>
+        <v>3427</v>
       </c>
       <c r="B160">
         <v>65133588</v>
@@ -32787,12 +32787,12 @@
         <v>2550</v>
       </c>
       <c r="E160" s="30" t="s">
-        <v>3367</v>
+        <v>3365</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="4" t="s">
-        <v>3311</v>
+        <v>3309</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>1147</v>
@@ -32801,10 +32801,10 @@
         <v>2640</v>
       </c>
       <c r="D161" s="378" t="s">
-        <v>3190</v>
+        <v>3188</v>
       </c>
       <c r="E161" s="30" t="s">
-        <v>3367</v>
+        <v>3365</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -32818,10 +32818,10 @@
         <v>2552</v>
       </c>
       <c r="D162" s="378" t="s">
-        <v>3318</v>
+        <v>3316</v>
       </c>
       <c r="E162" s="30" t="s">
-        <v>3367</v>
+        <v>3365</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -32832,18 +32832,18 @@
         <v>12369714760</v>
       </c>
       <c r="C163" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="D163" s="378" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="E163" s="30" t="s">
-        <v>3367</v>
+        <v>3365</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="4" t="s">
-        <v>3278</v>
+        <v>3276</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>2192</v>
@@ -32855,12 +32855,12 @@
         <v>2528</v>
       </c>
       <c r="E164" s="30" t="s">
-        <v>3593</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>3556</v>
+        <v>3554</v>
       </c>
       <c r="B165">
         <v>66315726</v>
@@ -32872,7 +32872,7 @@
         <v>2299</v>
       </c>
       <c r="E165" s="30" t="s">
-        <v>3593</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -32889,24 +32889,24 @@
         <v>2299</v>
       </c>
       <c r="E166" s="30" t="s">
-        <v>3593</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>3556</v>
+        <v>3554</v>
       </c>
       <c r="B167">
         <v>68818154</v>
       </c>
       <c r="C167" t="s">
-        <v>3507</v>
+        <v>3505</v>
       </c>
       <c r="D167" s="378" t="s">
         <v>2641</v>
       </c>
       <c r="E167" s="30" t="s">
-        <v>3593</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -32920,10 +32920,10 @@
         <v>2765</v>
       </c>
       <c r="D168" s="378" t="s">
-        <v>3354</v>
+        <v>3352</v>
       </c>
       <c r="E168" s="30" t="s">
-        <v>3147</v>
+        <v>3145</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -32940,7 +32940,7 @@
         <v>2801</v>
       </c>
       <c r="E169" s="30" t="s">
-        <v>3147</v>
+        <v>3145</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -32957,7 +32957,7 @@
         <v>2525</v>
       </c>
       <c r="E170" s="30" t="s">
-        <v>3147</v>
+        <v>3145</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -32974,12 +32974,12 @@
         <v>2340</v>
       </c>
       <c r="E171" s="30" t="s">
-        <v>3147</v>
+        <v>3145</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="B172">
         <v>66935922</v>
@@ -32988,10 +32988,10 @@
         <v>2352</v>
       </c>
       <c r="D172" s="378" t="s">
-        <v>3408</v>
+        <v>3406</v>
       </c>
       <c r="E172" s="30" t="s">
-        <v>3189</v>
+        <v>3187</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -33005,10 +33005,10 @@
         <v>2353</v>
       </c>
       <c r="D173" s="378" t="s">
-        <v>3332</v>
+        <v>3330</v>
       </c>
       <c r="E173" s="30" t="s">
-        <v>3189</v>
+        <v>3187</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -33022,10 +33022,10 @@
         <v>2354</v>
       </c>
       <c r="D174" s="378" t="s">
-        <v>3363</v>
+        <v>3361</v>
       </c>
       <c r="E174" s="30" t="s">
-        <v>3189</v>
+        <v>3187</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -33039,15 +33039,15 @@
         <v>2804</v>
       </c>
       <c r="D175" s="378" t="s">
-        <v>3375</v>
+        <v>3373</v>
       </c>
       <c r="E175" s="30" t="s">
-        <v>3268</v>
+        <v>3266</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" t="s">
-        <v>3429</v>
+        <v>3427</v>
       </c>
       <c r="B176">
         <v>66935922</v>
@@ -33056,10 +33056,10 @@
         <v>2805</v>
       </c>
       <c r="D176" s="220" t="s">
-        <v>3409</v>
+        <v>3407</v>
       </c>
       <c r="E176" s="30" t="s">
-        <v>3268</v>
+        <v>3266</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -33070,13 +33070,13 @@
         <v>63503223</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>3319</v>
+        <v>3317</v>
       </c>
       <c r="D177" s="220" t="s">
         <v>2876</v>
       </c>
       <c r="E177" s="30" t="s">
-        <v>3268</v>
+        <v>3266</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -33093,12 +33093,12 @@
         <v>2824</v>
       </c>
       <c r="E178" s="30" t="s">
-        <v>3268</v>
+        <v>3266</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" t="s">
-        <v>3311</v>
+        <v>3309</v>
       </c>
       <c r="B179">
         <v>68570552</v>
@@ -33107,15 +33107,15 @@
         <v>2807</v>
       </c>
       <c r="D179" s="220" t="s">
-        <v>3410</v>
+        <v>3408</v>
       </c>
       <c r="E179" s="30" t="s">
-        <v>3268</v>
+        <v>3266</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" t="s">
-        <v>3311</v>
+        <v>3309</v>
       </c>
       <c r="B180">
         <v>69964218</v>
@@ -33124,15 +33124,15 @@
         <v>2829</v>
       </c>
       <c r="D180" s="378" t="s">
-        <v>3411</v>
+        <v>3409</v>
       </c>
       <c r="E180" s="30" t="s">
-        <v>3322</v>
+        <v>3320</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" t="s">
-        <v>3282</v>
+        <v>3280</v>
       </c>
       <c r="B181">
         <v>63950696</v>
@@ -33144,12 +33144,12 @@
         <v>2830</v>
       </c>
       <c r="E181" s="30" t="s">
-        <v>3322</v>
+        <v>3320</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="4" t="s">
-        <v>3282</v>
+        <v>3280</v>
       </c>
       <c r="B182" t="s">
         <v>2861</v>
@@ -33161,7 +33161,7 @@
         <v>2830</v>
       </c>
       <c r="E182" s="30" t="s">
-        <v>3322</v>
+        <v>3320</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -33178,7 +33178,7 @@
         <v>2912</v>
       </c>
       <c r="E183" s="30" t="s">
-        <v>3322</v>
+        <v>3320</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -33195,7 +33195,7 @@
         <v>2913</v>
       </c>
       <c r="E184" s="30" t="s">
-        <v>3322</v>
+        <v>3320</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -33212,12 +33212,12 @@
         <v>2916</v>
       </c>
       <c r="E185" s="30" t="s">
-        <v>3399</v>
+        <v>3397</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" t="s">
-        <v>3612</v>
+        <v>3610</v>
       </c>
       <c r="B186">
         <v>60240509</v>
@@ -33226,10 +33226,10 @@
         <v>2868</v>
       </c>
       <c r="D186" s="378" t="s">
-        <v>3610</v>
+        <v>3608</v>
       </c>
       <c r="E186" s="30" t="s">
-        <v>3611</v>
+        <v>3609</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -33243,10 +33243,10 @@
         <v>2869</v>
       </c>
       <c r="D187" s="378" t="s">
-        <v>3542</v>
+        <v>3540</v>
       </c>
       <c r="E187" s="30" t="s">
-        <v>3399</v>
+        <v>3397</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -33263,7 +33263,7 @@
         <v>2876</v>
       </c>
       <c r="E188" s="30" t="s">
-        <v>3399</v>
+        <v>3397</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -33280,7 +33280,7 @@
         <v>2876</v>
       </c>
       <c r="E189" s="30" t="s">
-        <v>3399</v>
+        <v>3397</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -33297,12 +33297,12 @@
         <v>2876</v>
       </c>
       <c r="E190" s="30" t="s">
-        <v>3399</v>
+        <v>3397</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="4" t="s">
-        <v>3282</v>
+        <v>3280</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>1873</v>
@@ -33314,12 +33314,12 @@
         <v>2876</v>
       </c>
       <c r="E191" s="30" t="s">
-        <v>3399</v>
+        <v>3397</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="49" t="s">
-        <v>3232</v>
+        <v>3230</v>
       </c>
       <c r="B192">
         <v>64046277</v>
@@ -33331,7 +33331,7 @@
         <v>2915</v>
       </c>
       <c r="E192" s="30" t="s">
-        <v>3399</v>
+        <v>3397</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -33348,7 +33348,7 @@
         <v>2876</v>
       </c>
       <c r="E193" s="30" t="s">
-        <v>3399</v>
+        <v>3397</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -33365,18 +33365,18 @@
         <v>2876</v>
       </c>
       <c r="E194" s="30" t="s">
-        <v>3399</v>
+        <v>3397</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="C195" s="56" t="s">
-        <v>3346</v>
+        <v>3344</v>
       </c>
       <c r="D195" t="s">
-        <v>3528</v>
+        <v>3526</v>
       </c>
       <c r="E195" s="30" t="s">
-        <v>3251</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="197" spans="1:5" s="396" customFormat="1" ht="23.5">
@@ -33398,49 +33398,49 @@
         <v>2902</v>
       </c>
       <c r="D198" s="378" t="s">
-        <v>3541</v>
+        <v>3539</v>
       </c>
       <c r="E198" s="30" t="s">
-        <v>3386</v>
+        <v>3384</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" t="s">
-        <v>3605</v>
+        <v>3603</v>
       </c>
       <c r="B199" t="s">
-        <v>3606</v>
+        <v>3604</v>
       </c>
       <c r="C199" t="s">
         <v>2893</v>
       </c>
       <c r="D199" s="378" t="s">
-        <v>3604</v>
+        <v>3602</v>
       </c>
       <c r="E199" s="30" t="s">
-        <v>3386</v>
+        <v>3384</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" t="s">
-        <v>3311</v>
+        <v>3309</v>
       </c>
       <c r="B200">
         <v>63617941</v>
       </c>
       <c r="C200" s="22" t="s">
-        <v>3412</v>
+        <v>3410</v>
       </c>
       <c r="D200" s="378" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="E200" s="30" t="s">
-        <v>3386</v>
+        <v>3384</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" t="s">
-        <v>3124</v>
+        <v>3122</v>
       </c>
       <c r="B201">
         <v>65633205</v>
@@ -33449,10 +33449,10 @@
         <v>2894</v>
       </c>
       <c r="D201" s="378" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="E201" s="30" t="s">
-        <v>3386</v>
+        <v>3384</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -33466,10 +33466,10 @@
         <v>2895</v>
       </c>
       <c r="D202" s="378" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="E202" s="30" t="s">
-        <v>3386</v>
+        <v>3384</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -33480,13 +33480,13 @@
         <v>69329372</v>
       </c>
       <c r="C203" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
       <c r="D203" s="378" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="E203" s="30" t="s">
-        <v>3386</v>
+        <v>3384</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -33500,10 +33500,10 @@
         <v>2896</v>
       </c>
       <c r="D204" s="378" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="E204" s="30" t="s">
-        <v>3386</v>
+        <v>3384</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -33517,10 +33517,10 @@
         <v>2897</v>
       </c>
       <c r="D205" s="378" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="E205" s="30" t="s">
-        <v>3386</v>
+        <v>3384</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -33528,16 +33528,16 @@
         <v>2787</v>
       </c>
       <c r="B206" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="C206" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
       <c r="D206" s="378" t="s">
-        <v>2983</v>
+        <v>2982</v>
       </c>
       <c r="E206" s="30" t="s">
-        <v>3386</v>
+        <v>3384</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -33548,30 +33548,30 @@
         <v>65344753</v>
       </c>
       <c r="C207" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="D207" s="378" t="s">
-        <v>3385</v>
+        <v>3383</v>
       </c>
       <c r="E207" s="30" t="s">
-        <v>3386</v>
+        <v>3384</v>
       </c>
     </row>
     <row r="208" spans="1:5">
       <c r="A208" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="B208">
         <v>66496809</v>
       </c>
       <c r="C208" s="455" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="D208" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="E208" s="30" t="s">
-        <v>3673</v>
+        <v>3671</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -33582,30 +33582,30 @@
         <v>65583706</v>
       </c>
       <c r="C209" s="455" t="s">
+        <v>3055</v>
+      </c>
+      <c r="D209" s="378" t="s">
         <v>3057</v>
       </c>
-      <c r="D209" s="378" t="s">
-        <v>3059</v>
-      </c>
       <c r="E209" s="30" t="s">
-        <v>3673</v>
+        <v>3671</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210" t="s">
-        <v>3555</v>
+        <v>3553</v>
       </c>
       <c r="B210">
         <v>65574051</v>
       </c>
       <c r="C210" s="455" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="D210" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="E210" s="30" t="s">
-        <v>3673</v>
+        <v>3671</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -33613,16 +33613,16 @@
         <v>2835</v>
       </c>
       <c r="B211" t="s">
-        <v>3082</v>
+        <v>3080</v>
       </c>
       <c r="C211" s="455" t="s">
+        <v>3056</v>
+      </c>
+      <c r="D211" s="378" t="s">
         <v>3058</v>
       </c>
-      <c r="D211" s="378" t="s">
-        <v>3060</v>
-      </c>
       <c r="E211" s="30" t="s">
-        <v>3673</v>
+        <v>3671</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -33633,13 +33633,13 @@
         <v>64881871</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>3320</v>
+        <v>3318</v>
       </c>
       <c r="D212" t="s">
-        <v>3283</v>
+        <v>3281</v>
       </c>
       <c r="E212" s="30" t="s">
-        <v>3673</v>
+        <v>3671</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -33650,30 +33650,30 @@
         <v>68069608</v>
       </c>
       <c r="C213" s="22" t="s">
+        <v>3104</v>
+      </c>
+      <c r="D213" s="378" t="s">
         <v>3106</v>
       </c>
-      <c r="D213" s="378" t="s">
-        <v>3108</v>
-      </c>
       <c r="E213" s="30" t="s">
-        <v>3109</v>
+        <v>3107</v>
       </c>
     </row>
     <row r="214" spans="1:5">
       <c r="A214" t="s">
-        <v>3043</v>
+        <v>3041</v>
       </c>
       <c r="B214">
         <v>63258169</v>
       </c>
       <c r="C214" s="22" t="s">
-        <v>3128</v>
+        <v>3126</v>
       </c>
       <c r="D214" t="s">
-        <v>3178</v>
+        <v>3176</v>
       </c>
       <c r="E214" s="30" t="s">
-        <v>3109</v>
+        <v>3107</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -33684,13 +33684,13 @@
         <v>69243886</v>
       </c>
       <c r="C215" s="22" t="s">
-        <v>3129</v>
+        <v>3127</v>
       </c>
       <c r="D215" t="s">
-        <v>3121</v>
+        <v>3119</v>
       </c>
       <c r="E215" s="30" t="s">
-        <v>3109</v>
+        <v>3107</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -33701,13 +33701,13 @@
         <v>67752170</v>
       </c>
       <c r="C216" s="3" t="s">
+        <v>3105</v>
+      </c>
+      <c r="D216" t="s">
+        <v>3120</v>
+      </c>
+      <c r="E216" s="30" t="s">
         <v>3107</v>
-      </c>
-      <c r="D216" t="s">
-        <v>3122</v>
-      </c>
-      <c r="E216" s="30" t="s">
-        <v>3109</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -33718,13 +33718,13 @@
         <v>64457890</v>
       </c>
       <c r="C217" t="s">
-        <v>3130</v>
+        <v>3128</v>
       </c>
       <c r="D217" s="378" t="s">
-        <v>3131</v>
+        <v>3129</v>
       </c>
       <c r="E217" s="30" t="s">
-        <v>3109</v>
+        <v>3107</v>
       </c>
     </row>
     <row r="231" spans="3:4">
@@ -33855,10 +33855,10 @@
     </row>
     <row r="259" spans="1:6">
       <c r="C259" s="1" t="s">
+        <v>2935</v>
+      </c>
+      <c r="D259" s="1" t="s">
         <v>2936</v>
-      </c>
-      <c r="D259" s="1" t="s">
-        <v>2937</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -33866,7 +33866,7 @@
         <v>1679</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
     </row>
     <row r="261" spans="1:6">
@@ -36496,7 +36496,7 @@
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>3101</v>
+        <v>3099</v>
       </c>
     </row>
     <row r="18" spans="4:4">
@@ -36553,7 +36553,7 @@
     </row>
     <row r="6" spans="1:9" s="76" customFormat="1">
       <c r="A6" s="76" t="s">
-        <v>3104</v>
+        <v>3102</v>
       </c>
       <c r="B6" s="76">
         <v>64966680</v>
@@ -36568,7 +36568,7 @@
         <v>678</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>3419</v>
+        <v>3417</v>
       </c>
       <c r="G6" s="222" t="s">
         <v>1455</v>
@@ -36588,13 +36588,13 @@
         <v>1861</v>
       </c>
       <c r="D7" s="183" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F7" s="183" t="s">
-        <v>3419</v>
+        <v>3417</v>
       </c>
       <c r="G7" s="183" t="s">
         <v>1455</v>
@@ -36605,7 +36605,7 @@
     </row>
     <row r="8" spans="1:9" s="183" customFormat="1">
       <c r="A8" s="193" t="s">
-        <v>3282</v>
+        <v>3280</v>
       </c>
       <c r="B8" s="193">
         <v>62747874</v>
@@ -36620,7 +36620,7 @@
         <v>362</v>
       </c>
       <c r="F8" s="183" t="s">
-        <v>3419</v>
+        <v>3417</v>
       </c>
       <c r="G8" s="183" t="s">
         <v>1455</v>
@@ -36646,7 +36646,7 @@
         <v>362</v>
       </c>
       <c r="F9" s="183" t="s">
-        <v>3419</v>
+        <v>3417</v>
       </c>
       <c r="G9" s="183" t="s">
         <v>1455</v>
@@ -36672,7 +36672,7 @@
         <v>362</v>
       </c>
       <c r="F10" s="183" t="s">
-        <v>3419</v>
+        <v>3417</v>
       </c>
       <c r="G10" s="183" t="s">
         <v>1455</v>
@@ -36698,7 +36698,7 @@
         <v>362</v>
       </c>
       <c r="F11" s="183" t="s">
-        <v>3419</v>
+        <v>3417</v>
       </c>
       <c r="G11" s="183" t="s">
         <v>1455</v>
@@ -36721,7 +36721,7 @@
         <v>2558</v>
       </c>
       <c r="E13" s="195" t="s">
-        <v>3420</v>
+        <v>3418</v>
       </c>
       <c r="F13" s="195" t="s">
         <v>1440</v>
@@ -36748,7 +36748,7 @@
         <v>1862</v>
       </c>
       <c r="E14" s="193" t="s">
-        <v>3420</v>
+        <v>3418</v>
       </c>
       <c r="F14" s="193" t="s">
         <v>1440</v>
@@ -36775,7 +36775,7 @@
         <v>2839</v>
       </c>
       <c r="E15" s="193" t="s">
-        <v>3420</v>
+        <v>3418</v>
       </c>
       <c r="F15" s="193" t="s">
         <v>1440</v>
@@ -36790,7 +36790,7 @@
     </row>
     <row r="16" spans="1:9" s="183" customFormat="1">
       <c r="A16" s="183" t="s">
-        <v>3104</v>
+        <v>3102</v>
       </c>
       <c r="B16" s="183">
         <v>63666666</v>
@@ -36802,7 +36802,7 @@
         <v>2343</v>
       </c>
       <c r="E16" s="193" t="s">
-        <v>3420</v>
+        <v>3418</v>
       </c>
       <c r="F16" s="193" t="s">
         <v>1440</v>
@@ -36829,7 +36829,7 @@
         <v>1521</v>
       </c>
       <c r="E17" s="193" t="s">
-        <v>3420</v>
+        <v>3418</v>
       </c>
       <c r="F17" s="193" t="s">
         <v>1440</v>
@@ -36856,7 +36856,7 @@
         <v>2181</v>
       </c>
       <c r="E18" s="193" t="s">
-        <v>3420</v>
+        <v>3418</v>
       </c>
       <c r="F18" s="193" t="s">
         <v>1440</v>
@@ -36871,7 +36871,7 @@
     </row>
     <row r="20" spans="1:9" s="76" customFormat="1">
       <c r="A20" s="195" t="s">
-        <v>3104</v>
+        <v>3102</v>
       </c>
       <c r="B20" s="195">
         <v>67539485</v>
@@ -36886,7 +36886,7 @@
         <v>362</v>
       </c>
       <c r="F20" s="195" t="s">
-        <v>3420</v>
+        <v>3418</v>
       </c>
       <c r="G20" s="76" t="s">
         <v>422</v>
@@ -36915,7 +36915,7 @@
         <v>362</v>
       </c>
       <c r="F21" s="193" t="s">
-        <v>3420</v>
+        <v>3418</v>
       </c>
       <c r="G21" s="183" t="s">
         <v>422</v>
@@ -36944,7 +36944,7 @@
         <v>362</v>
       </c>
       <c r="F22" s="193" t="s">
-        <v>3420</v>
+        <v>3418</v>
       </c>
       <c r="G22" s="183" t="s">
         <v>422</v>
@@ -36958,7 +36958,7 @@
     </row>
     <row r="23" spans="1:9" s="183" customFormat="1">
       <c r="A23" s="183" t="s">
-        <v>3278</v>
+        <v>3276</v>
       </c>
       <c r="B23" s="183">
         <v>60389752</v>
@@ -36973,7 +36973,7 @@
         <v>362</v>
       </c>
       <c r="F23" s="193" t="s">
-        <v>3420</v>
+        <v>3418</v>
       </c>
       <c r="G23" s="183" t="s">
         <v>422</v>
@@ -37002,7 +37002,7 @@
         <v>362</v>
       </c>
       <c r="F24" s="193" t="s">
-        <v>3420</v>
+        <v>3418</v>
       </c>
       <c r="G24" s="183" t="s">
         <v>422</v>
@@ -37031,7 +37031,7 @@
         <v>362</v>
       </c>
       <c r="F25" s="193" t="s">
-        <v>3420</v>
+        <v>3418</v>
       </c>
       <c r="G25" s="183" t="s">
         <v>422</v>
@@ -37048,7 +37048,7 @@
         <v>362</v>
       </c>
       <c r="F27" s="446" t="s">
-        <v>3535</v>
+        <v>3533</v>
       </c>
       <c r="G27" s="393" t="s">
         <v>422</v>
@@ -37067,7 +37067,7 @@
         <v>362</v>
       </c>
       <c r="F28" s="446" t="s">
-        <v>3535</v>
+        <v>3533</v>
       </c>
       <c r="G28" s="393" t="s">
         <v>422</v>
@@ -37084,7 +37084,7 @@
         <v>362</v>
       </c>
       <c r="F29" s="446" t="s">
-        <v>3535</v>
+        <v>3533</v>
       </c>
       <c r="G29" s="393" t="s">
         <v>422</v>
@@ -37098,7 +37098,7 @@
     </row>
     <row r="30" spans="1:9" s="393" customFormat="1">
       <c r="A30" s="393" t="s">
-        <v>3282</v>
+        <v>3280</v>
       </c>
       <c r="B30" s="393">
         <v>63950696</v>
@@ -37113,7 +37113,7 @@
         <v>362</v>
       </c>
       <c r="F30" s="446" t="s">
-        <v>3535</v>
+        <v>3533</v>
       </c>
       <c r="G30" s="393" t="s">
         <v>422</v>
@@ -37133,7 +37133,7 @@
     </row>
     <row r="32" spans="1:9" s="393" customFormat="1">
       <c r="A32" s="452" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="B32" s="446">
         <v>64967407</v>
@@ -37148,7 +37148,7 @@
         <v>362</v>
       </c>
       <c r="F32" s="446" t="s">
-        <v>3535</v>
+        <v>3533</v>
       </c>
       <c r="G32" s="393" t="s">
         <v>422</v>
@@ -37179,7 +37179,7 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>3161</v>
+        <v>3159</v>
       </c>
       <c r="B36">
         <v>69563253</v>
@@ -37228,7 +37228,7 @@
     </row>
     <row r="41" spans="1:9" s="76" customFormat="1">
       <c r="A41" s="76" t="s">
-        <v>3382</v>
+        <v>3380</v>
       </c>
       <c r="B41" s="76">
         <v>60389752</v>
@@ -37243,7 +37243,7 @@
         <v>362</v>
       </c>
       <c r="F41" s="76" t="s">
-        <v>3524</v>
+        <v>3522</v>
       </c>
       <c r="G41" s="76" t="s">
         <v>1456</v>
@@ -37270,7 +37270,7 @@
         <v>362</v>
       </c>
       <c r="F42" s="183" t="s">
-        <v>3524</v>
+        <v>3522</v>
       </c>
       <c r="G42" s="183" t="s">
         <v>378</v>
@@ -37284,22 +37284,22 @@
     </row>
     <row r="43" spans="1:9" s="183" customFormat="1">
       <c r="A43" s="183" t="s">
-        <v>3636</v>
+        <v>3634</v>
       </c>
       <c r="B43" s="183">
         <v>65234700</v>
       </c>
       <c r="C43" s="194" t="s">
-        <v>3550</v>
+        <v>3548</v>
       </c>
       <c r="D43" s="183" t="s">
-        <v>3551</v>
+        <v>3549</v>
       </c>
       <c r="E43" s="443">
         <v>46243</v>
       </c>
       <c r="F43" s="183" t="s">
-        <v>3524</v>
+        <v>3522</v>
       </c>
       <c r="G43" s="183" t="s">
         <v>378</v>
@@ -37328,7 +37328,7 @@
         <v>362</v>
       </c>
       <c r="F44" s="183" t="s">
-        <v>3524</v>
+        <v>3522</v>
       </c>
       <c r="G44" s="183" t="s">
         <v>378</v>
@@ -37357,7 +37357,7 @@
         <v>362</v>
       </c>
       <c r="F45" s="183" t="s">
-        <v>3524</v>
+        <v>3522</v>
       </c>
       <c r="G45" s="183" t="s">
         <v>378</v>
@@ -37371,7 +37371,7 @@
     </row>
     <row r="46" spans="1:9" s="183" customFormat="1">
       <c r="A46" s="183" t="s">
-        <v>3311</v>
+        <v>3309</v>
       </c>
       <c r="B46" s="183">
         <v>68241069</v>
@@ -37386,7 +37386,7 @@
         <v>362</v>
       </c>
       <c r="F46" s="183" t="s">
-        <v>3524</v>
+        <v>3522</v>
       </c>
       <c r="G46" s="183" t="s">
         <v>378</v>
@@ -37415,7 +37415,7 @@
         <v>2523</v>
       </c>
       <c r="F48" s="195" t="s">
-        <v>3609</v>
+        <v>3607</v>
       </c>
       <c r="G48" s="76" t="s">
         <v>1455</v>
@@ -37442,7 +37442,7 @@
         <v>2523</v>
       </c>
       <c r="F49" s="193" t="s">
-        <v>3609</v>
+        <v>3607</v>
       </c>
       <c r="G49" s="183" t="s">
         <v>1455</v>
@@ -37454,7 +37454,7 @@
     </row>
     <row r="50" spans="1:9" s="183" customFormat="1">
       <c r="A50" s="193" t="s">
-        <v>3104</v>
+        <v>3102</v>
       </c>
       <c r="B50" s="193">
         <v>63226030</v>
@@ -37469,7 +37469,7 @@
         <v>2523</v>
       </c>
       <c r="F50" s="193" t="s">
-        <v>3609</v>
+        <v>3607</v>
       </c>
       <c r="G50" s="183" t="s">
         <v>1455</v>
@@ -37481,7 +37481,7 @@
     </row>
     <row r="51" spans="1:9" s="183" customFormat="1">
       <c r="A51" s="193" t="s">
-        <v>3583</v>
+        <v>3581</v>
       </c>
       <c r="B51" s="193">
         <v>69111188</v>
@@ -37496,7 +37496,7 @@
         <v>2523</v>
       </c>
       <c r="F51" s="193" t="s">
-        <v>3609</v>
+        <v>3607</v>
       </c>
       <c r="G51" s="183" t="s">
         <v>1455</v>
@@ -37523,7 +37523,7 @@
         <v>2523</v>
       </c>
       <c r="F52" s="193" t="s">
-        <v>3609</v>
+        <v>3607</v>
       </c>
       <c r="G52" s="183" t="s">
         <v>1455</v>
@@ -37550,7 +37550,7 @@
         <v>2523</v>
       </c>
       <c r="F53" s="193" t="s">
-        <v>3609</v>
+        <v>3607</v>
       </c>
       <c r="G53" s="183" t="s">
         <v>1455</v>
@@ -37571,13 +37571,13 @@
         <v>1680</v>
       </c>
       <c r="D55" s="195" t="s">
-        <v>3148</v>
+        <v>3146</v>
       </c>
       <c r="E55" s="76" t="s">
         <v>2523</v>
       </c>
       <c r="F55" s="195" t="s">
-        <v>3645</v>
+        <v>3643</v>
       </c>
       <c r="G55" s="76" t="s">
         <v>1455</v>
@@ -37604,7 +37604,7 @@
         <v>2523</v>
       </c>
       <c r="F56" s="193" t="s">
-        <v>3645</v>
+        <v>3643</v>
       </c>
       <c r="G56" s="183" t="s">
         <v>1455</v>
@@ -37625,13 +37625,13 @@
         <v>2652</v>
       </c>
       <c r="D57" s="193" t="s">
-        <v>3341</v>
+        <v>3339</v>
       </c>
       <c r="E57" s="183" t="s">
         <v>2523</v>
       </c>
       <c r="F57" s="193" t="s">
-        <v>3645</v>
+        <v>3643</v>
       </c>
       <c r="G57" s="183" t="s">
         <v>1455</v>
@@ -37658,7 +37658,7 @@
         <v>2523</v>
       </c>
       <c r="F58" s="193" t="s">
-        <v>3645</v>
+        <v>3643</v>
       </c>
       <c r="G58" s="183" t="s">
         <v>1455</v>
@@ -37685,7 +37685,7 @@
         <v>2523</v>
       </c>
       <c r="F59" s="193" t="s">
-        <v>3645</v>
+        <v>3643</v>
       </c>
       <c r="G59" s="183" t="s">
         <v>1455</v>
@@ -37703,16 +37703,16 @@
         <v>63062167</v>
       </c>
       <c r="C60" s="193" t="s">
-        <v>3458</v>
+        <v>3456</v>
       </c>
       <c r="D60" s="193" t="s">
-        <v>3493</v>
+        <v>3491</v>
       </c>
       <c r="E60" s="183" t="s">
         <v>2523</v>
       </c>
       <c r="F60" s="193" t="s">
-        <v>3645</v>
+        <v>3643</v>
       </c>
       <c r="G60" s="183" t="s">
         <v>1455</v>
@@ -37738,7 +37738,7 @@
         <v>2523</v>
       </c>
       <c r="F62" s="195" t="s">
-        <v>3645</v>
+        <v>3643</v>
       </c>
       <c r="G62" s="76" t="s">
         <v>1455</v>
@@ -37765,7 +37765,7 @@
         <v>2523</v>
       </c>
       <c r="F63" s="193" t="s">
-        <v>3645</v>
+        <v>3643</v>
       </c>
       <c r="G63" s="183" t="s">
         <v>1455</v>
@@ -37777,7 +37777,7 @@
     </row>
     <row r="64" spans="1:9" s="183" customFormat="1">
       <c r="A64" s="183" t="s">
-        <v>3556</v>
+        <v>3554</v>
       </c>
       <c r="B64" s="183">
         <v>64403333</v>
@@ -37792,7 +37792,7 @@
         <v>2523</v>
       </c>
       <c r="F64" s="193" t="s">
-        <v>3645</v>
+        <v>3643</v>
       </c>
       <c r="G64" s="183" t="s">
         <v>1455</v>
@@ -37804,7 +37804,7 @@
     </row>
     <row r="65" spans="1:9" s="183" customFormat="1">
       <c r="A65" s="193" t="s">
-        <v>3413</v>
+        <v>3411</v>
       </c>
       <c r="B65" s="193">
         <v>68030850</v>
@@ -37819,7 +37819,7 @@
         <v>2523</v>
       </c>
       <c r="F65" s="193" t="s">
-        <v>3645</v>
+        <v>3643</v>
       </c>
       <c r="G65" s="183" t="s">
         <v>1455</v>
@@ -37831,7 +37831,7 @@
     </row>
     <row r="66" spans="1:9" s="183" customFormat="1">
       <c r="A66" s="183" t="s">
-        <v>3658</v>
+        <v>3656</v>
       </c>
       <c r="B66" s="183">
         <v>65003516</v>
@@ -37846,7 +37846,7 @@
         <v>2523</v>
       </c>
       <c r="F66" s="193" t="s">
-        <v>3645</v>
+        <v>3643</v>
       </c>
       <c r="G66" s="183" t="s">
         <v>1455</v>
@@ -37873,7 +37873,7 @@
         <v>2523</v>
       </c>
       <c r="F67" s="193" t="s">
-        <v>3645</v>
+        <v>3643</v>
       </c>
       <c r="G67" s="183" t="s">
         <v>1455</v>
@@ -37885,7 +37885,7 @@
     </row>
     <row r="69" spans="1:9" s="76" customFormat="1">
       <c r="A69" s="76" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="B69" s="76">
         <v>64147946</v>
@@ -37897,7 +37897,7 @@
         <v>2486</v>
       </c>
       <c r="E69" s="76" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="F69" s="195" t="s">
         <v>2487</v>
@@ -37912,7 +37912,7 @@
     </row>
     <row r="70" spans="1:9" s="183" customFormat="1">
       <c r="A70" s="193" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="B70" s="193">
         <v>62646186</v>
@@ -37924,7 +37924,7 @@
         <v>2491</v>
       </c>
       <c r="E70" s="183" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="F70" s="193" t="s">
         <v>2487</v>
@@ -37951,7 +37951,7 @@
         <v>2316</v>
       </c>
       <c r="E71" s="183" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="F71" s="193" t="s">
         <v>2487</v>
@@ -37978,7 +37978,7 @@
         <v>2789</v>
       </c>
       <c r="E72" s="183" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="F72" s="183" t="s">
         <v>2487</v>
@@ -38004,7 +38004,7 @@
         <v>2075</v>
       </c>
       <c r="E73" s="183" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="F73" s="183" t="s">
         <v>2487</v>
@@ -38030,7 +38030,7 @@
         <v>2482</v>
       </c>
       <c r="E74" s="183" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="F74" s="183" t="s">
         <v>2487</v>
@@ -38056,7 +38056,7 @@
         <v>1740</v>
       </c>
       <c r="E76" s="76" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="F76" s="195" t="s">
         <v>2485</v>
@@ -38080,7 +38080,7 @@
         <v>2358</v>
       </c>
       <c r="E77" s="183" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="F77" s="193" t="s">
         <v>2485</v>
@@ -38104,7 +38104,7 @@
         <v>1248</v>
       </c>
       <c r="E78" s="183" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="F78" s="193" t="s">
         <v>2485</v>
@@ -38128,7 +38128,7 @@
         <v>2393</v>
       </c>
       <c r="E79" s="183" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="F79" s="193" t="s">
         <v>2485</v>
@@ -38152,7 +38152,7 @@
         <v>2314</v>
       </c>
       <c r="E80" s="183" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="F80" s="193" t="s">
         <v>2485</v>
@@ -38176,7 +38176,7 @@
         <v>2534</v>
       </c>
       <c r="E81" s="183" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="F81" s="193" t="s">
         <v>2485</v>
@@ -38188,7 +38188,7 @@
     </row>
     <row r="83" spans="1:9" s="76" customFormat="1">
       <c r="A83" s="76" t="s">
-        <v>3429</v>
+        <v>3427</v>
       </c>
       <c r="B83" s="76">
         <v>63574980</v>
@@ -38203,7 +38203,7 @@
         <v>1354</v>
       </c>
       <c r="F83" s="195" t="s">
-        <v>3094</v>
+        <v>3092</v>
       </c>
       <c r="G83" s="76" t="s">
         <v>1455</v>
@@ -38229,7 +38229,7 @@
         <v>1354</v>
       </c>
       <c r="F84" s="183" t="s">
-        <v>3094</v>
+        <v>3092</v>
       </c>
       <c r="G84" s="183" t="s">
         <v>1455</v>
@@ -38246,7 +38246,7 @@
         <v>68483411</v>
       </c>
       <c r="C85" s="183" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="D85" s="183" t="s">
         <v>2179</v>
@@ -38255,7 +38255,7 @@
         <v>1354</v>
       </c>
       <c r="F85" s="183" t="s">
-        <v>3094</v>
+        <v>3092</v>
       </c>
       <c r="G85" s="183" t="s">
         <v>1455</v>
@@ -38269,19 +38269,19 @@
         <v>2541</v>
       </c>
       <c r="B86" s="183" t="s">
-        <v>3299</v>
+        <v>3297</v>
       </c>
       <c r="C86" s="194" t="s">
         <v>2714</v>
       </c>
       <c r="D86" s="183" t="s">
-        <v>3298</v>
+        <v>3296</v>
       </c>
       <c r="E86" s="183" t="s">
         <v>1354</v>
       </c>
       <c r="F86" s="183" t="s">
-        <v>3094</v>
+        <v>3092</v>
       </c>
       <c r="G86" s="183" t="s">
         <v>1455</v>
@@ -38292,7 +38292,7 @@
     </row>
     <row r="87" spans="1:9" s="183" customFormat="1">
       <c r="A87" s="183" t="s">
-        <v>3282</v>
+        <v>3280</v>
       </c>
       <c r="B87" s="183">
         <v>69904406</v>
@@ -38301,13 +38301,13 @@
         <v>2715</v>
       </c>
       <c r="D87" s="183" t="s">
-        <v>3421</v>
+        <v>3419</v>
       </c>
       <c r="E87" s="183" t="s">
         <v>1354</v>
       </c>
       <c r="F87" s="183" t="s">
-        <v>3094</v>
+        <v>3092</v>
       </c>
       <c r="G87" s="183" t="s">
         <v>1455</v>
@@ -38318,7 +38318,7 @@
     </row>
     <row r="88" spans="1:9" s="183" customFormat="1">
       <c r="A88" s="183" t="s">
-        <v>3043</v>
+        <v>3041</v>
       </c>
       <c r="B88" s="183" t="s">
         <v>2733</v>
@@ -38333,7 +38333,7 @@
         <v>1354</v>
       </c>
       <c r="F88" s="183" t="s">
-        <v>3094</v>
+        <v>3092</v>
       </c>
       <c r="G88" s="183" t="s">
         <v>1455</v>
@@ -38359,7 +38359,7 @@
         <v>1670</v>
       </c>
       <c r="F90" s="195" t="s">
-        <v>3095</v>
+        <v>3093</v>
       </c>
       <c r="G90" s="76" t="s">
         <v>1455</v>
@@ -38383,7 +38383,7 @@
         <v>1670</v>
       </c>
       <c r="F91" s="193" t="s">
-        <v>3095</v>
+        <v>3093</v>
       </c>
       <c r="G91" s="183" t="s">
         <v>1455</v>
@@ -38407,7 +38407,7 @@
         <v>1670</v>
       </c>
       <c r="F92" s="193" t="s">
-        <v>3095</v>
+        <v>3093</v>
       </c>
       <c r="G92" s="183" t="s">
         <v>1455</v>
@@ -38431,7 +38431,7 @@
         <v>1670</v>
       </c>
       <c r="F93" s="193" t="s">
-        <v>3095</v>
+        <v>3093</v>
       </c>
       <c r="G93" s="183" t="s">
         <v>1455</v>
@@ -38455,7 +38455,7 @@
         <v>1670</v>
       </c>
       <c r="F94" s="193" t="s">
-        <v>3095</v>
+        <v>3093</v>
       </c>
       <c r="G94" s="183" t="s">
         <v>1455</v>
@@ -38479,7 +38479,7 @@
         <v>1670</v>
       </c>
       <c r="F95" s="193" t="s">
-        <v>3095</v>
+        <v>3093</v>
       </c>
       <c r="G95" s="183" t="s">
         <v>1455</v>
@@ -38488,7 +38488,7 @@
     </row>
     <row r="97" spans="1:9" s="76" customFormat="1">
       <c r="A97" s="195" t="s">
-        <v>3627</v>
+        <v>3625</v>
       </c>
       <c r="B97" s="195">
         <v>64476521</v>
@@ -38503,7 +38503,7 @@
         <v>2523</v>
       </c>
       <c r="F97" s="195" t="s">
-        <v>3096</v>
+        <v>3094</v>
       </c>
       <c r="G97" s="76" t="s">
         <v>1455</v>
@@ -38515,7 +38515,7 @@
     </row>
     <row r="98" spans="1:9" s="183" customFormat="1">
       <c r="A98" s="193" t="s">
-        <v>3510</v>
+        <v>3508</v>
       </c>
       <c r="B98" s="193">
         <v>60389752</v>
@@ -38524,13 +38524,13 @@
         <v>2695</v>
       </c>
       <c r="D98" s="193" t="s">
-        <v>3509</v>
+        <v>3507</v>
       </c>
       <c r="E98" s="183" t="s">
         <v>2523</v>
       </c>
       <c r="F98" s="193" t="s">
-        <v>3096</v>
+        <v>3094</v>
       </c>
       <c r="G98" s="183" t="s">
         <v>1455</v>
@@ -38557,7 +38557,7 @@
         <v>2523</v>
       </c>
       <c r="F99" s="193" t="s">
-        <v>3096</v>
+        <v>3094</v>
       </c>
       <c r="G99" s="183" t="s">
         <v>1455</v>
@@ -38569,7 +38569,7 @@
     </row>
     <row r="100" spans="1:9" s="183" customFormat="1">
       <c r="A100" s="193" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="B100" s="193">
         <v>60389752</v>
@@ -38584,7 +38584,7 @@
         <v>2523</v>
       </c>
       <c r="F100" s="193" t="s">
-        <v>3096</v>
+        <v>3094</v>
       </c>
       <c r="G100" s="183" t="s">
         <v>1455</v>
@@ -38611,7 +38611,7 @@
         <v>2523</v>
       </c>
       <c r="F101" s="193" t="s">
-        <v>3096</v>
+        <v>3094</v>
       </c>
       <c r="G101" s="183" t="s">
         <v>1455</v>
@@ -38623,7 +38623,7 @@
     </row>
     <row r="102" spans="1:9" s="183" customFormat="1">
       <c r="A102" s="193" t="s">
-        <v>3282</v>
+        <v>3280</v>
       </c>
       <c r="B102" s="193">
         <v>67381873</v>
@@ -38632,13 +38632,13 @@
         <v>2312</v>
       </c>
       <c r="D102" s="193" t="s">
-        <v>3425</v>
+        <v>3423</v>
       </c>
       <c r="E102" s="183" t="s">
         <v>2523</v>
       </c>
       <c r="F102" s="193" t="s">
-        <v>3096</v>
+        <v>3094</v>
       </c>
       <c r="G102" s="183" t="s">
         <v>1455</v>
@@ -38650,7 +38650,7 @@
     </row>
     <row r="104" spans="1:9" s="76" customFormat="1">
       <c r="A104" s="195" t="s">
-        <v>3134</v>
+        <v>3132</v>
       </c>
       <c r="B104" s="195">
         <v>66082581</v>
@@ -38662,7 +38662,7 @@
         <v>2325</v>
       </c>
       <c r="E104" s="76" t="s">
-        <v>3096</v>
+        <v>3094</v>
       </c>
       <c r="F104" s="195" t="s">
         <v>422</v>
@@ -38677,7 +38677,7 @@
     </row>
     <row r="105" spans="1:9" s="183" customFormat="1">
       <c r="A105" s="193" t="s">
-        <v>3104</v>
+        <v>3102</v>
       </c>
       <c r="B105" s="193" t="s">
         <v>2753</v>
@@ -38689,7 +38689,7 @@
         <v>2330</v>
       </c>
       <c r="E105" s="183" t="s">
-        <v>3096</v>
+        <v>3094</v>
       </c>
       <c r="F105" s="193" t="s">
         <v>422</v>
@@ -38704,7 +38704,7 @@
     </row>
     <row r="106" spans="1:9" s="183" customFormat="1">
       <c r="A106" s="193" t="s">
-        <v>3448</v>
+        <v>3446</v>
       </c>
       <c r="B106" s="193">
         <v>62723048</v>
@@ -38713,10 +38713,10 @@
         <v>2331</v>
       </c>
       <c r="D106" s="193" t="s">
-        <v>3447</v>
+        <v>3445</v>
       </c>
       <c r="E106" s="183" t="s">
-        <v>3096</v>
+        <v>3094</v>
       </c>
       <c r="F106" s="193" t="s">
         <v>422</v>
@@ -38737,13 +38737,13 @@
         <v>69017426</v>
       </c>
       <c r="C107" s="194" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="D107" s="193" t="s">
         <v>2497</v>
       </c>
       <c r="E107" s="183" t="s">
-        <v>3096</v>
+        <v>3094</v>
       </c>
       <c r="F107" s="193" t="s">
         <v>422</v>
@@ -38770,7 +38770,7 @@
         <v>2334</v>
       </c>
       <c r="E108" s="183" t="s">
-        <v>3096</v>
+        <v>3094</v>
       </c>
       <c r="F108" s="193" t="s">
         <v>422</v>
@@ -38791,13 +38791,13 @@
         <v>62723048</v>
       </c>
       <c r="C109" s="194" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="D109" s="193" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="E109" s="183" t="s">
-        <v>3096</v>
+        <v>3094</v>
       </c>
       <c r="F109" s="193" t="s">
         <v>422</v>
@@ -38818,16 +38818,16 @@
         <v>68310153</v>
       </c>
       <c r="C111" s="195" t="s">
-        <v>3126</v>
+        <v>3124</v>
       </c>
       <c r="D111" s="195" t="s">
-        <v>3127</v>
+        <v>3125</v>
       </c>
       <c r="E111" s="76" t="s">
         <v>362</v>
       </c>
       <c r="F111" s="195" t="s">
-        <v>3132</v>
+        <v>3130</v>
       </c>
       <c r="G111" s="76" t="s">
         <v>1354</v>
@@ -38841,7 +38841,7 @@
     </row>
     <row r="112" spans="1:9" s="183" customFormat="1">
       <c r="A112" s="193" t="s">
-        <v>3133</v>
+        <v>3131</v>
       </c>
       <c r="B112" s="193">
         <v>63910392</v>
@@ -38854,7 +38854,7 @@
         <v>362</v>
       </c>
       <c r="F112" s="193" t="s">
-        <v>3132</v>
+        <v>3130</v>
       </c>
       <c r="G112" s="183" t="s">
         <v>1354</v>
@@ -38874,16 +38874,16 @@
         <v>68853797</v>
       </c>
       <c r="C113" s="193" t="s">
-        <v>3192</v>
+        <v>3190</v>
       </c>
       <c r="D113" s="193" t="s">
-        <v>3062</v>
+        <v>3060</v>
       </c>
       <c r="E113" s="183" t="s">
         <v>2523</v>
       </c>
       <c r="F113" s="193" t="s">
-        <v>3132</v>
+        <v>3130</v>
       </c>
       <c r="G113" s="183" t="s">
         <v>1354</v>
@@ -38903,16 +38903,16 @@
         <v>62360487</v>
       </c>
       <c r="C114" s="194" t="s">
-        <v>3459</v>
+        <v>3457</v>
       </c>
       <c r="D114" s="183" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="E114" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F114" s="193" t="s">
-        <v>3132</v>
+        <v>3130</v>
       </c>
       <c r="G114" s="183" t="s">
         <v>1354</v>
@@ -38932,16 +38932,16 @@
         <v>62085821</v>
       </c>
       <c r="C115" s="193" t="s">
-        <v>3461</v>
+        <v>3459</v>
       </c>
       <c r="D115" s="193" t="s">
-        <v>3462</v>
+        <v>3460</v>
       </c>
       <c r="E115" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F115" s="193" t="s">
-        <v>3132</v>
+        <v>3130</v>
       </c>
       <c r="G115" s="183" t="s">
         <v>1354</v>
@@ -38961,16 +38961,16 @@
         <v>64403333</v>
       </c>
       <c r="C116" s="193" t="s">
-        <v>3463</v>
+        <v>3461</v>
       </c>
       <c r="D116" s="193" t="s">
-        <v>3464</v>
+        <v>3462</v>
       </c>
       <c r="E116" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F116" s="193" t="s">
-        <v>3132</v>
+        <v>3130</v>
       </c>
       <c r="G116" s="183" t="s">
         <v>1354</v>
@@ -38987,7 +38987,7 @@
         <v>1354</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>3537</v>
+        <v>3535</v>
       </c>
       <c r="G118" s="444" t="s">
         <v>1455</v>
@@ -39002,7 +39002,7 @@
         <v>1354</v>
       </c>
       <c r="F119" s="302" t="s">
-        <v>3537</v>
+        <v>3535</v>
       </c>
       <c r="G119" s="7" t="s">
         <v>1455</v>
@@ -39020,16 +39020,16 @@
         <v>64543204</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>3073</v>
+        <v>3071</v>
       </c>
       <c r="D120" s="7" t="s">
-        <v>3072</v>
+        <v>3070</v>
       </c>
       <c r="E120" s="7" t="s">
         <v>1354</v>
       </c>
       <c r="F120" s="302" t="s">
-        <v>3537</v>
+        <v>3535</v>
       </c>
       <c r="G120" s="7" t="s">
         <v>1455</v>
@@ -39044,7 +39044,7 @@
         <v>1354</v>
       </c>
       <c r="F121" s="302" t="s">
-        <v>3537</v>
+        <v>3535</v>
       </c>
       <c r="G121" s="7" t="s">
         <v>1455</v>
@@ -39071,7 +39071,7 @@
         <v>1354</v>
       </c>
       <c r="F122" s="302" t="s">
-        <v>3537</v>
+        <v>3535</v>
       </c>
       <c r="G122" s="7" t="s">
         <v>1455</v>
@@ -39086,7 +39086,7 @@
         <v>1354</v>
       </c>
       <c r="F123" s="302" t="s">
-        <v>3537</v>
+        <v>3535</v>
       </c>
       <c r="G123" s="7" t="s">
         <v>1455</v>
@@ -39110,7 +39110,7 @@
         <v>2347</v>
       </c>
       <c r="E125" s="76" t="s">
-        <v>3208</v>
+        <v>3206</v>
       </c>
       <c r="F125" s="76" t="s">
         <v>422</v>
@@ -39136,7 +39136,7 @@
         <v>2349</v>
       </c>
       <c r="E126" s="183" t="s">
-        <v>3208</v>
+        <v>3206</v>
       </c>
       <c r="F126" s="193" t="s">
         <v>422</v>
@@ -39163,7 +39163,7 @@
         <v>2351</v>
       </c>
       <c r="E127" s="183" t="s">
-        <v>3208</v>
+        <v>3206</v>
       </c>
       <c r="F127" s="193" t="s">
         <v>422</v>
@@ -39178,19 +39178,19 @@
     </row>
     <row r="128" spans="1:9" s="183" customFormat="1">
       <c r="A128" s="183" t="s">
-        <v>3554</v>
+        <v>3552</v>
       </c>
       <c r="B128" s="183">
         <v>64403333</v>
       </c>
       <c r="C128" s="183" t="s">
-        <v>3465</v>
+        <v>3463</v>
       </c>
       <c r="D128" s="183" t="s">
-        <v>3466</v>
+        <v>3464</v>
       </c>
       <c r="E128" s="183" t="s">
-        <v>3208</v>
+        <v>3206</v>
       </c>
       <c r="F128" s="193" t="s">
         <v>422</v>
@@ -39217,7 +39217,7 @@
         <v>377</v>
       </c>
       <c r="E129" s="183" t="s">
-        <v>3208</v>
+        <v>3206</v>
       </c>
       <c r="F129" s="193" t="s">
         <v>422</v>
@@ -39244,7 +39244,7 @@
         <v>1666</v>
       </c>
       <c r="E130" s="183" t="s">
-        <v>3208</v>
+        <v>3206</v>
       </c>
       <c r="F130" s="193" t="s">
         <v>422</v>
@@ -39274,7 +39274,7 @@
         <v>678</v>
       </c>
       <c r="F132" s="76" t="s">
-        <v>3330</v>
+        <v>3328</v>
       </c>
       <c r="G132" s="76" t="s">
         <v>422</v>
@@ -39303,7 +39303,7 @@
         <v>362</v>
       </c>
       <c r="F133" s="183" t="s">
-        <v>3330</v>
+        <v>3328</v>
       </c>
       <c r="G133" s="183" t="s">
         <v>422</v>
@@ -39332,7 +39332,7 @@
         <v>362</v>
       </c>
       <c r="F134" s="183" t="s">
-        <v>3330</v>
+        <v>3328</v>
       </c>
       <c r="G134" s="183" t="s">
         <v>422</v>
@@ -39358,7 +39358,7 @@
         <v>362</v>
       </c>
       <c r="F135" s="183" t="s">
-        <v>3330</v>
+        <v>3328</v>
       </c>
       <c r="G135" s="183" t="s">
         <v>422</v>
@@ -39372,7 +39372,7 @@
     </row>
     <row r="136" spans="1:9" s="183" customFormat="1">
       <c r="A136" s="183" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="B136" s="183">
         <v>66230961</v>
@@ -39387,7 +39387,7 @@
         <v>362</v>
       </c>
       <c r="F136" s="183" t="s">
-        <v>3330</v>
+        <v>3328</v>
       </c>
       <c r="G136" s="183" t="s">
         <v>422</v>
@@ -39401,7 +39401,7 @@
     </row>
     <row r="137" spans="1:9" s="183" customFormat="1">
       <c r="A137" s="183" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="B137" s="183">
         <v>69888391</v>
@@ -39416,7 +39416,7 @@
         <v>362</v>
       </c>
       <c r="F137" s="183" t="s">
-        <v>3330</v>
+        <v>3328</v>
       </c>
       <c r="G137" s="183" t="s">
         <v>422</v>
@@ -39445,7 +39445,7 @@
         <v>2405</v>
       </c>
       <c r="F139" s="195" t="s">
-        <v>3378</v>
+        <v>3376</v>
       </c>
       <c r="G139" s="76" t="s">
         <v>1455</v>
@@ -39463,7 +39463,7 @@
         <v>64226974</v>
       </c>
       <c r="C140" s="183" t="s">
-        <v>3624</v>
+        <v>3622</v>
       </c>
       <c r="D140" s="193" t="s">
         <v>377</v>
@@ -39472,7 +39472,7 @@
         <v>2405</v>
       </c>
       <c r="F140" s="193" t="s">
-        <v>3378</v>
+        <v>3376</v>
       </c>
       <c r="G140" s="183" t="s">
         <v>1455</v>
@@ -39499,7 +39499,7 @@
         <v>2405</v>
       </c>
       <c r="F141" s="193" t="s">
-        <v>3378</v>
+        <v>3376</v>
       </c>
       <c r="G141" s="183" t="s">
         <v>1455</v>
@@ -39526,7 +39526,7 @@
         <v>2405</v>
       </c>
       <c r="F142" s="193" t="s">
-        <v>3378</v>
+        <v>3376</v>
       </c>
       <c r="G142" s="183" t="s">
         <v>1455</v>
@@ -39538,7 +39538,7 @@
     </row>
     <row r="143" spans="1:9" s="183" customFormat="1">
       <c r="A143" s="55" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="B143" s="183">
         <v>62385671</v>
@@ -39553,7 +39553,7 @@
         <v>2405</v>
       </c>
       <c r="F143" s="193" t="s">
-        <v>3378</v>
+        <v>3376</v>
       </c>
       <c r="G143" s="183" t="s">
         <v>1455</v>
@@ -39580,7 +39580,7 @@
         <v>2405</v>
       </c>
       <c r="F144" s="193" t="s">
-        <v>3378</v>
+        <v>3376</v>
       </c>
       <c r="G144" s="183" t="s">
         <v>1455</v>
@@ -39598,16 +39598,16 @@
         <v>2186</v>
       </c>
       <c r="C146" s="195" t="s">
-        <v>3380</v>
+        <v>3378</v>
       </c>
       <c r="D146" s="195" t="s">
-        <v>3379</v>
+        <v>3377</v>
       </c>
       <c r="E146" s="76" t="s">
         <v>2405</v>
       </c>
       <c r="F146" s="195" t="s">
-        <v>3378</v>
+        <v>3376</v>
       </c>
       <c r="G146" s="76" t="s">
         <v>1455</v>
@@ -39625,16 +39625,16 @@
         <v>66319486</v>
       </c>
       <c r="C147" s="193" t="s">
-        <v>3467</v>
+        <v>3465</v>
       </c>
       <c r="D147" s="193" t="s">
-        <v>3511</v>
+        <v>3509</v>
       </c>
       <c r="E147" s="183" t="s">
         <v>2405</v>
       </c>
       <c r="F147" s="193" t="s">
-        <v>3378</v>
+        <v>3376</v>
       </c>
       <c r="G147" s="183" t="s">
         <v>1455</v>
@@ -39661,7 +39661,7 @@
         <v>2405</v>
       </c>
       <c r="F148" s="193" t="s">
-        <v>3378</v>
+        <v>3376</v>
       </c>
       <c r="G148" s="183" t="s">
         <v>1455</v>
@@ -39673,7 +39673,7 @@
     </row>
     <row r="149" spans="1:9" s="183" customFormat="1">
       <c r="A149" s="183" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="B149" s="183">
         <v>64403333</v>
@@ -39688,7 +39688,7 @@
         <v>2405</v>
       </c>
       <c r="F149" s="193" t="s">
-        <v>3378</v>
+        <v>3376</v>
       </c>
       <c r="G149" s="183" t="s">
         <v>1455</v>
@@ -39715,7 +39715,7 @@
         <v>2405</v>
       </c>
       <c r="F150" s="193" t="s">
-        <v>3378</v>
+        <v>3376</v>
       </c>
       <c r="G150" s="183" t="s">
         <v>1455</v>
@@ -39742,7 +39742,7 @@
         <v>2405</v>
       </c>
       <c r="F151" s="193" t="s">
-        <v>3378</v>
+        <v>3376</v>
       </c>
       <c r="G151" s="183" t="s">
         <v>1455</v>
@@ -39769,7 +39769,7 @@
         <v>2523</v>
       </c>
       <c r="F153" s="195" t="s">
-        <v>3381</v>
+        <v>3379</v>
       </c>
       <c r="G153" s="76" t="s">
         <v>1455</v>
@@ -39781,13 +39781,13 @@
     </row>
     <row r="154" spans="1:9" s="183" customFormat="1">
       <c r="A154" s="193" t="s">
-        <v>3311</v>
+        <v>3309</v>
       </c>
       <c r="B154" s="193">
         <v>67697112</v>
       </c>
       <c r="C154" s="193" t="s">
-        <v>3492</v>
+        <v>3490</v>
       </c>
       <c r="D154" s="193" t="s">
         <v>1316</v>
@@ -39796,7 +39796,7 @@
         <v>2523</v>
       </c>
       <c r="F154" s="193" t="s">
-        <v>3381</v>
+        <v>3379</v>
       </c>
       <c r="G154" s="183" t="s">
         <v>1455</v>
@@ -39808,7 +39808,7 @@
     </row>
     <row r="155" spans="1:9" s="183" customFormat="1">
       <c r="A155" s="183" t="s">
-        <v>3539</v>
+        <v>3537</v>
       </c>
       <c r="B155" s="183">
         <v>62560788</v>
@@ -39823,7 +39823,7 @@
         <v>2523</v>
       </c>
       <c r="F155" s="193" t="s">
-        <v>3381</v>
+        <v>3379</v>
       </c>
       <c r="G155" s="183" t="s">
         <v>1455</v>
@@ -39835,7 +39835,7 @@
     </row>
     <row r="156" spans="1:9" s="183" customFormat="1">
       <c r="A156" s="193" t="s">
-        <v>3282</v>
+        <v>3280</v>
       </c>
       <c r="B156" s="193">
         <v>64403333</v>
@@ -39850,7 +39850,7 @@
         <v>2523</v>
       </c>
       <c r="F156" s="193" t="s">
-        <v>3381</v>
+        <v>3379</v>
       </c>
       <c r="G156" s="183" t="s">
         <v>1455</v>
@@ -39862,22 +39862,22 @@
     </row>
     <row r="157" spans="1:9" s="183" customFormat="1">
       <c r="A157" s="193" t="s">
-        <v>3075</v>
+        <v>3073</v>
       </c>
       <c r="B157" s="193">
         <v>60125401</v>
       </c>
       <c r="C157" s="194" t="s">
+        <v>3072</v>
+      </c>
+      <c r="D157" s="193" t="s">
         <v>3074</v>
-      </c>
-      <c r="D157" s="193" t="s">
-        <v>3076</v>
       </c>
       <c r="E157" s="183" t="s">
         <v>2523</v>
       </c>
       <c r="F157" s="193" t="s">
-        <v>3381</v>
+        <v>3379</v>
       </c>
       <c r="G157" s="183" t="s">
         <v>1455</v>
@@ -39904,7 +39904,7 @@
         <v>2523</v>
       </c>
       <c r="F158" s="193" t="s">
-        <v>3381</v>
+        <v>3379</v>
       </c>
       <c r="G158" s="183" t="s">
         <v>1455</v>
@@ -39931,7 +39931,7 @@
         <v>362</v>
       </c>
       <c r="F160" s="195" t="s">
-        <v>3418</v>
+        <v>3416</v>
       </c>
       <c r="G160" s="76" t="s">
         <v>2411</v>
@@ -39945,22 +39945,22 @@
     </row>
     <row r="161" spans="1:9" s="183" customFormat="1">
       <c r="A161" s="193" t="s">
-        <v>3429</v>
+        <v>3427</v>
       </c>
       <c r="B161" s="193">
         <v>65963732</v>
       </c>
       <c r="C161" s="194" t="s">
-        <v>3450</v>
+        <v>3448</v>
       </c>
       <c r="D161" s="193" t="s">
-        <v>3451</v>
+        <v>3449</v>
       </c>
       <c r="E161" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F161" s="193" t="s">
-        <v>3418</v>
+        <v>3416</v>
       </c>
       <c r="G161" s="183" t="s">
         <v>2411</v>
@@ -39974,7 +39974,7 @@
     </row>
     <row r="162" spans="1:9" s="183" customFormat="1">
       <c r="A162" s="183" t="s">
-        <v>3429</v>
+        <v>3427</v>
       </c>
       <c r="B162" s="183">
         <v>60071688</v>
@@ -39983,13 +39983,13 @@
         <v>2394</v>
       </c>
       <c r="D162" s="183" t="s">
-        <v>3444</v>
+        <v>3442</v>
       </c>
       <c r="E162" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F162" s="193" t="s">
-        <v>3418</v>
+        <v>3416</v>
       </c>
       <c r="G162" s="183" t="s">
         <v>2411</v>
@@ -40018,7 +40018,7 @@
         <v>362</v>
       </c>
       <c r="F163" s="193" t="s">
-        <v>3418</v>
+        <v>3416</v>
       </c>
       <c r="G163" s="183" t="s">
         <v>2411</v>
@@ -40047,7 +40047,7 @@
         <v>362</v>
       </c>
       <c r="F164" s="193" t="s">
-        <v>3418</v>
+        <v>3416</v>
       </c>
       <c r="G164" s="183" t="s">
         <v>2411</v>
@@ -40061,22 +40061,22 @@
     </row>
     <row r="165" spans="1:9" s="183" customFormat="1">
       <c r="A165" s="183" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="B165" s="183">
         <v>64403333</v>
       </c>
       <c r="C165" s="194" t="s">
-        <v>3077</v>
+        <v>3075</v>
       </c>
       <c r="D165" s="416" t="s">
-        <v>3076</v>
+        <v>3074</v>
       </c>
       <c r="E165" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F165" s="193" t="s">
-        <v>3418</v>
+        <v>3416</v>
       </c>
       <c r="G165" s="183" t="s">
         <v>2411</v>
@@ -40092,16 +40092,16 @@
       <c r="A167" s="195"/>
       <c r="B167" s="195"/>
       <c r="C167" s="195" t="s">
-        <v>3599</v>
+        <v>3597</v>
       </c>
       <c r="D167" s="195" t="s">
-        <v>3600</v>
+        <v>3598</v>
       </c>
       <c r="E167" s="76" t="s">
         <v>362</v>
       </c>
       <c r="F167" s="195" t="s">
-        <v>3601</v>
+        <v>3599</v>
       </c>
       <c r="G167" s="76" t="s">
         <v>2411</v>
@@ -40121,7 +40121,7 @@
         <v>69563253</v>
       </c>
       <c r="C168" s="193" t="s">
-        <v>3602</v>
+        <v>3600</v>
       </c>
       <c r="D168" s="193" t="s">
         <v>1693</v>
@@ -40142,10 +40142,10 @@
         <v>1959</v>
       </c>
       <c r="C169" s="194" t="s">
-        <v>3578</v>
+        <v>3576</v>
       </c>
       <c r="D169" s="193" t="s">
-        <v>3579</v>
+        <v>3577</v>
       </c>
       <c r="E169" s="443">
         <v>46304</v>
@@ -40163,7 +40163,7 @@
         <v>62751201</v>
       </c>
       <c r="C170" s="194" t="s">
-        <v>3607</v>
+        <v>3605</v>
       </c>
       <c r="D170" s="183" t="s">
         <v>1367</v>
@@ -40184,10 +40184,10 @@
         <v>68030850</v>
       </c>
       <c r="C171" s="193" t="s">
-        <v>3581</v>
+        <v>3579</v>
       </c>
       <c r="D171" s="193" t="s">
-        <v>3582</v>
+        <v>3580</v>
       </c>
       <c r="E171" s="443">
         <v>46243</v>
@@ -40222,16 +40222,16 @@
       <c r="A174" s="195"/>
       <c r="B174" s="195"/>
       <c r="C174" s="195" t="s">
+        <v>3636</v>
+      </c>
+      <c r="D174" s="195" t="s">
+        <v>3637</v>
+      </c>
+      <c r="E174" s="76" t="s">
         <v>3638</v>
       </c>
-      <c r="D174" s="195" t="s">
+      <c r="F174" s="195" t="s">
         <v>3639</v>
-      </c>
-      <c r="E174" s="76" t="s">
-        <v>3640</v>
-      </c>
-      <c r="F174" s="195" t="s">
-        <v>3641</v>
       </c>
       <c r="G174" s="76" t="s">
         <v>1455</v>
@@ -40270,10 +40270,10 @@
         <v>61548403</v>
       </c>
       <c r="C176" s="194" t="s">
-        <v>3642</v>
+        <v>3640</v>
       </c>
       <c r="D176" s="193" t="s">
-        <v>3643</v>
+        <v>3641</v>
       </c>
       <c r="E176" s="443">
         <v>46304</v>
@@ -40333,27 +40333,27 @@
     </row>
     <row r="183" spans="1:9" s="221" customFormat="1" ht="15.5">
       <c r="C183" s="221" t="s">
-        <v>3545</v>
+        <v>3543</v>
       </c>
     </row>
     <row r="184" spans="1:9" s="76" customFormat="1">
       <c r="C184" s="195" t="s">
-        <v>3671</v>
+        <v>3669</v>
       </c>
       <c r="D184" s="195" t="s">
-        <v>3672</v>
+        <v>3670</v>
       </c>
       <c r="E184" s="445">
         <v>46243</v>
       </c>
       <c r="F184" s="76" t="s">
-        <v>3546</v>
+        <v>3544</v>
       </c>
       <c r="G184" s="195" t="s">
-        <v>3597</v>
+        <v>3595</v>
       </c>
       <c r="H184" s="76" t="s">
-        <v>3547</v>
+        <v>3545</v>
       </c>
       <c r="I184" s="195"/>
     </row>
@@ -40403,7 +40403,7 @@
         <v>316</v>
       </c>
       <c r="D194" s="438" t="s">
-        <v>3642</v>
+        <v>3640</v>
       </c>
       <c r="E194" s="30"/>
       <c r="F194"/>
@@ -40429,7 +40429,7 @@
         <v>439</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>3459</v>
+        <v>3457</v>
       </c>
       <c r="E196" s="30"/>
       <c r="F196"/>
@@ -40440,7 +40440,7 @@
         <v>26</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>3461</v>
+        <v>3459</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -40448,7 +40448,7 @@
         <v>1337</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>3463</v>
+        <v>3461</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -40456,7 +40456,7 @@
         <v>1677</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>3465</v>
+        <v>3463</v>
       </c>
       <c r="F199" s="399"/>
     </row>
@@ -40465,7 +40465,7 @@
         <v>1318</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>3467</v>
+        <v>3465</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -40473,7 +40473,7 @@
         <v>406</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>3578</v>
+        <v>3576</v>
       </c>
     </row>
     <row r="202" spans="1:9">
@@ -40481,7 +40481,7 @@
         <v>709</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>3581</v>
+        <v>3579</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -40489,7 +40489,7 @@
         <v>281</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>3598</v>
+        <v>3596</v>
       </c>
     </row>
     <row r="204" spans="1:9">
@@ -40497,7 +40497,7 @@
         <v>2413</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>3599</v>
+        <v>3597</v>
       </c>
     </row>
     <row r="205" spans="1:9">
@@ -40507,7 +40507,7 @@
         <v>465</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>3602</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -40515,7 +40515,7 @@
         <v>219</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>3607</v>
+        <v>3605</v>
       </c>
     </row>
     <row r="207" spans="1:9">
@@ -40523,7 +40523,7 @@
         <v>427</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>3624</v>
+        <v>3622</v>
       </c>
     </row>
     <row r="208" spans="1:9">
@@ -40531,7 +40531,7 @@
         <v>1058</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>3638</v>
+        <v>3636</v>
       </c>
     </row>
     <row r="223" spans="1:9">
@@ -41865,10 +41865,10 @@
         <v>706</v>
       </c>
       <c r="H3" t="s">
-        <v>3659</v>
+        <v>3657</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>3165</v>
+        <v>3163</v>
       </c>
       <c r="J3"/>
     </row>
@@ -41895,10 +41895,10 @@
         <v>515</v>
       </c>
       <c r="H4" t="s">
-        <v>3471</v>
+        <v>3469</v>
       </c>
       <c r="I4" t="s">
-        <v>3066</v>
+        <v>3064</v>
       </c>
       <c r="J4"/>
     </row>
@@ -41907,7 +41907,7 @@
         <v>2903</v>
       </c>
       <c r="B5" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>480</v>
@@ -41916,7 +41916,7 @@
         <v>1537</v>
       </c>
       <c r="E5" t="s">
-        <v>3197</v>
+        <v>3195</v>
       </c>
       <c r="F5" t="s">
         <v>2195</v>
@@ -41925,10 +41925,10 @@
         <v>515</v>
       </c>
       <c r="H5" s="220" t="s">
-        <v>3479</v>
+        <v>3477</v>
       </c>
       <c r="I5" s="220" t="s">
-        <v>3315</v>
+        <v>3313</v>
       </c>
       <c r="J5" t="s">
         <v>1408</v>
@@ -41941,19 +41941,19 @@
         <v>427</v>
       </c>
       <c r="D6" t="s">
-        <v>3489</v>
+        <v>3487</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>3487</v>
+        <v>3485</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="G6" t="s">
         <v>436</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>3262</v>
+        <v>3260</v>
       </c>
       <c r="I6" s="97"/>
       <c r="J6"/>
@@ -41986,13 +41986,13 @@
         <v>143</v>
       </c>
       <c r="B8" t="s">
-        <v>3047</v>
+        <v>3045</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>2086</v>
       </c>
       <c r="D8" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="E8" t="s">
         <v>2360</v>
@@ -42004,10 +42004,10 @@
         <v>250</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>3306</v>
+        <v>3304</v>
       </c>
       <c r="I8" t="s">
-        <v>3436</v>
+        <v>3434</v>
       </c>
       <c r="J8"/>
     </row>
@@ -42110,22 +42110,22 @@
         <v>2921</v>
       </c>
       <c r="E16" t="s">
+        <v>2958</v>
+      </c>
+      <c r="F16" t="s">
         <v>2959</v>
-      </c>
-      <c r="F16" t="s">
-        <v>2960</v>
       </c>
       <c r="G16" t="s">
         <v>121</v>
       </c>
       <c r="H16" s="276" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="I16" s="276" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>3044</v>
+        <v>3042</v>
       </c>
     </row>
     <row r="19" customFormat="1"/>
@@ -42204,7 +42204,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="10" t="s">
-        <v>3556</v>
+        <v>3554</v>
       </c>
       <c r="B5" s="10">
         <v>67992849</v>
@@ -42257,7 +42257,7 @@
         <v>2814</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>3169</v>
+        <v>3167</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -42271,7 +42271,7 @@
         <v>1742</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>3356</v>
+        <v>3354</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1715</v>
@@ -42283,10 +42283,10 @@
         <v>517</v>
       </c>
       <c r="H7" t="s">
-        <v>3328</v>
+        <v>3326</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>3357</v>
+        <v>3355</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -42302,7 +42302,7 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="10" t="s">
-        <v>3429</v>
+        <v>3427</v>
       </c>
       <c r="B11" s="10">
         <v>64403333</v>
@@ -42334,7 +42334,7 @@
         <v>2173</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>3371</v>
+        <v>3369</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>966</v>
@@ -42346,10 +42346,10 @@
         <v>517</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>3372</v>
+        <v>3370</v>
       </c>
       <c r="I12" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -42365,7 +42365,7 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="10" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="B15" s="10">
         <v>68543713</v>
@@ -42374,7 +42374,7 @@
         <v>2234</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>3200</v>
+        <v>3198</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>966</v>
@@ -42386,10 +42386,10 @@
         <v>517</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>3201</v>
+        <v>3199</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>3210</v>
+        <v>3208</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -42438,7 +42438,7 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="10" t="s">
-        <v>3429</v>
+        <v>3427</v>
       </c>
       <c r="B18" s="10">
         <v>60345107</v>
@@ -42447,7 +42447,7 @@
         <v>2368</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>3433</v>
+        <v>3431</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>966</v>
@@ -42459,10 +42459,10 @@
         <v>517</v>
       </c>
       <c r="H18" s="436" t="s">
-        <v>3398</v>
+        <v>3396</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>3505</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -42488,10 +42488,10 @@
         <v>517</v>
       </c>
       <c r="H19" s="276" t="s">
-        <v>3140</v>
+        <v>3138</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>3628</v>
+        <v>3626</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="190" customFormat="1" ht="26">
@@ -42507,13 +42507,13 @@
         <v>2664</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>3587</v>
+        <v>3585</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>2457</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>3558</v>
+        <v>3556</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>966</v>
@@ -42525,15 +42525,15 @@
         <v>517</v>
       </c>
       <c r="H22" s="276" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>3355</v>
+        <v>3353</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>3663</v>
+        <v>3661</v>
       </c>
       <c r="B23" s="10">
         <v>64720128</v>
@@ -42554,10 +42554,10 @@
         <v>517</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>3664</v>
+        <v>3662</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>3665</v>
+        <v>3663</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -42571,7 +42571,7 @@
         <v>2475</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>3301</v>
+        <v>3299</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>966</v>
@@ -42583,10 +42583,10 @@
         <v>517</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>3625</v>
+        <v>3623</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>3146</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -42596,7 +42596,7 @@
         <v>2488</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>3199</v>
+        <v>3197</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>966</v>
@@ -42715,13 +42715,13 @@
         <v>2503</v>
       </c>
       <c r="B4" t="s">
-        <v>3270</v>
+        <v>3268</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1883</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>3269</v>
+        <v>3267</v>
       </c>
       <c r="E4" t="s">
         <v>1884</v>
@@ -42733,13 +42733,13 @@
         <v>970</v>
       </c>
       <c r="H4" t="s">
-        <v>3285</v>
+        <v>3283</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>3294</v>
+        <v>3292</v>
       </c>
       <c r="J4" t="s">
-        <v>3352</v>
+        <v>3350</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -42788,7 +42788,7 @@
         <v>970</v>
       </c>
       <c r="H6" t="s">
-        <v>3313</v>
+        <v>3311</v>
       </c>
       <c r="J6" s="49" t="s">
         <v>2257</v>
@@ -42800,7 +42800,7 @@
         <v>2322</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>3656</v>
+        <v>3654</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>2323</v>
@@ -42812,13 +42812,13 @@
         <v>970</v>
       </c>
       <c r="H7" t="s">
-        <v>3249</v>
+        <v>3247</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>3395</v>
+        <v>3393</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>3191</v>
+        <v>3189</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -42826,63 +42826,63 @@
         <v>2483</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>2990</v>
+        <v>2989</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>2986</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>2985</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>2987</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>2986</v>
-      </c>
-      <c r="E8" s="10" t="s">
+      <c r="F8" s="10" t="s">
         <v>2988</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>2989</v>
       </c>
       <c r="G8" t="s">
         <v>970</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>3198</v>
+        <v>3196</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>3365</v>
+        <v>3363</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>3209</v>
+        <v>3207</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="10" t="s">
-        <v>3213</v>
+        <v>3211</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>3214</v>
+        <v>3212</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>3211</v>
+        <v>3209</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>3212</v>
+        <v>3210</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="G9" t="s">
         <v>970</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>3215</v>
+        <v>3213</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>3216</v>
+        <v>3214</v>
       </c>
       <c r="J9" t="s">
-        <v>3265</v>
+        <v>3263</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -42890,16 +42890,16 @@
         <v>1444</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>3370</v>
+        <v>3368</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>3368</v>
+        <v>3366</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>3369</v>
+        <v>3367</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>3284</v>
+        <v>3282</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>2324</v>
@@ -42908,13 +42908,13 @@
         <v>970</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>3474</v>
+        <v>3472</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>3477</v>
+        <v>3475</v>
       </c>
       <c r="J10" t="s">
-        <v>3529</v>
+        <v>3527</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -43076,7 +43076,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="10" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="B10" s="10">
         <v>64676716</v>
@@ -43085,7 +43085,7 @@
         <v>1806</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>3177</v>
+        <v>3175</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>2662</v>
@@ -43126,7 +43126,7 @@
         <v>65124748</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>3052</v>
+        <v>3050</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>2686</v>
@@ -43147,7 +43147,7 @@
         <v>63132287</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>3078</v>
+        <v>3076</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>2686</v>
@@ -43323,7 +43323,7 @@
     <row r="1" spans="1:10" s="415" customFormat="1" ht="42.5" customHeight="1">
       <c r="A1" s="414"/>
       <c r="B1" s="414" t="s">
-        <v>3067</v>
+        <v>3065</v>
       </c>
       <c r="C1" s="414"/>
     </row>
@@ -43332,28 +43332,28 @@
         <v>147</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>3125</v>
+        <v>3123</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3273</v>
+        <v>3271</v>
       </c>
       <c r="E4" t="s">
-        <v>3068</v>
+        <v>3066</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>3274</v>
+        <v>3272</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>3080</v>
+        <v>3078</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>3254</v>
+        <v>3252</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>3267</v>
+        <v>3265</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>3384</v>
+        <v>3382</v>
       </c>
     </row>
   </sheetData>
@@ -43699,7 +43699,7 @@
         <v>2606</v>
       </c>
       <c r="C5" s="327" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="327" customFormat="1">
@@ -43707,10 +43707,10 @@
         <v>2585</v>
       </c>
       <c r="B6" s="327" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
       <c r="C6" s="327" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="7" spans="1:13" s="327" customFormat="1">
@@ -43785,10 +43785,10 @@
         <v>2615</v>
       </c>
       <c r="H14" s="333" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
       <c r="I14" s="333" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
       <c r="L14" s="333"/>
       <c r="M14" s="333"/>
@@ -43816,10 +43816,10 @@
         <v>2616</v>
       </c>
       <c r="H15" s="334" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
       <c r="I15" s="334" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="L15" s="334"/>
       <c r="M15" s="334"/>
@@ -43847,7 +43847,7 @@
         <v>2617</v>
       </c>
       <c r="H16" s="334" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
       <c r="I16" s="334" t="s">
         <v>1354</v>
@@ -43860,7 +43860,7 @@
         <v>2590</v>
       </c>
       <c r="B17" s="401" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="C17" s="401"/>
       <c r="D17" s="401"/>
@@ -43877,7 +43877,7 @@
         <v>2585</v>
       </c>
       <c r="B18" s="401" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="C18" s="401"/>
       <c r="D18" s="401"/>
@@ -43894,7 +43894,7 @@
         <v>2586</v>
       </c>
       <c r="B19" s="401" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
       <c r="C19" s="401"/>
       <c r="D19" s="401"/>
@@ -44749,7 +44749,7 @@
         <v>51</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>3342</v>
+        <v>3340</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>1170</v>
@@ -44761,10 +44761,10 @@
         <v>159</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>3559</v>
+        <v>3557</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>3571</v>
+        <v>3569</v>
       </c>
       <c r="N6" s="4" t="s">
         <v>26</v>
@@ -44796,7 +44796,7 @@
         <v>2297</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>3361</v>
+        <v>3359</v>
       </c>
       <c r="L7" s="3"/>
     </row>
@@ -44826,7 +44826,7 @@
         <v>2786</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>3340</v>
+        <v>3338</v>
       </c>
     </row>
     <row r="9" spans="1:14" s="4" customFormat="1">
@@ -44843,19 +44843,19 @@
         <v>2185</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>3572</v>
+        <v>3570</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>3573</v>
+        <v>3571</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>159</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>3531</v>
+        <v>3529</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>3485</v>
+        <v>3483</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>819</v>
@@ -44863,7 +44863,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="4" t="s">
-        <v>3033</v>
+        <v>3031</v>
       </c>
       <c r="B10" s="4">
         <v>67916500</v>
@@ -44884,10 +44884,10 @@
         <v>244</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>3659</v>
+        <v>3657</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>3414</v>
+        <v>3412</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -44904,19 +44904,19 @@
         <v>1527</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>3482</v>
+        <v>3480</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>3032</v>
+        <v>3030</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>244</v>
       </c>
       <c r="H11" t="s">
-        <v>3036</v>
+        <v>3034</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>3042</v>
+        <v>3040</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -44942,10 +44942,10 @@
         <v>244</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>3064</v>
+        <v>3062</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>3116</v>
+        <v>3114</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -44971,10 +44971,10 @@
         <v>244</v>
       </c>
       <c r="H13" s="220" t="s">
-        <v>3480</v>
+        <v>3478</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>3054</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="4" customFormat="1">
@@ -45000,10 +45000,10 @@
         <v>244</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="I14" s="220" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="L14" s="3"/>
     </row>
@@ -45030,10 +45030,10 @@
         <v>891</v>
       </c>
       <c r="H15" t="s">
-        <v>3389</v>
+        <v>3387</v>
       </c>
       <c r="I15" t="s">
-        <v>3164</v>
+        <v>3162</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>498</v>
@@ -45062,10 +45062,10 @@
         <v>159</v>
       </c>
       <c r="H16" s="49" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="I16" t="s">
-        <v>3560</v>
+        <v>3558</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>809</v>
@@ -45073,7 +45073,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>3556</v>
+        <v>3554</v>
       </c>
       <c r="B17">
         <v>65325884</v>
@@ -45096,7 +45096,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="4" t="s">
-        <v>3654</v>
+        <v>3652</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>2134</v>
@@ -45108,24 +45108,24 @@
         <v>2246</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>3031</v>
+        <v>3029</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>3032</v>
+        <v>3030</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>244</v>
       </c>
       <c r="H18" s="49" t="s">
-        <v>3227</v>
+        <v>3225</v>
       </c>
       <c r="I18" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="4" customFormat="1">
       <c r="A19" s="4" t="s">
-        <v>3104</v>
+        <v>3102</v>
       </c>
       <c r="B19" s="4">
         <v>64403333</v>
@@ -45137,10 +45137,10 @@
         <v>2647</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>3589</v>
+        <v>3587</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>3573</v>
+        <v>3571</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>1240</v>
@@ -45150,7 +45150,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="4" t="s">
-        <v>3556</v>
+        <v>3554</v>
       </c>
       <c r="B20">
         <v>64403333</v>
@@ -45199,7 +45199,7 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="4" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="B22" s="4">
         <v>64403333</v>
@@ -45222,7 +45222,7 @@
     </row>
     <row r="23" spans="1:12" s="4" customFormat="1">
       <c r="A23" t="s">
-        <v>3556</v>
+        <v>3554</v>
       </c>
       <c r="B23">
         <v>63247837</v>
@@ -45231,7 +45231,7 @@
         <v>2655</v>
       </c>
       <c r="D23" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="E23" t="s">
         <v>2658</v>
@@ -45243,10 +45243,10 @@
         <v>159</v>
       </c>
       <c r="H23" t="s">
-        <v>3439</v>
+        <v>3437</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>3523</v>
+        <v>3521</v>
       </c>
       <c r="L23" s="6"/>
     </row>
@@ -45261,10 +45261,10 @@
         <v>1649</v>
       </c>
       <c r="D24" t="s">
+        <v>3251</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>3253</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>3255</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>2516</v>
@@ -45275,19 +45275,19 @@
     </row>
     <row r="25" spans="1:12" s="4" customFormat="1">
       <c r="A25" s="4" t="s">
-        <v>3605</v>
+        <v>3603</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>3619</v>
+        <v>3617</v>
       </c>
       <c r="C25" s="21" t="s">
         <v>1339</v>
       </c>
       <c r="D25" t="s">
-        <v>3618</v>
+        <v>3616</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>3156</v>
+        <v>3154</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>2519</v>
@@ -45296,10 +45296,10 @@
         <v>244</v>
       </c>
       <c r="H25" s="359" t="s">
-        <v>3620</v>
+        <v>3618</v>
       </c>
       <c r="I25" s="359" t="s">
-        <v>3621</v>
+        <v>3619</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="4" customFormat="1">
@@ -45325,10 +45325,10 @@
         <v>159</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>3038</v>
+        <v>3036</v>
       </c>
       <c r="I27" t="s">
-        <v>3393</v>
+        <v>3391</v>
       </c>
       <c r="L27" s="4" t="s">
         <v>817</v>
@@ -45336,7 +45336,7 @@
     </row>
     <row r="28" spans="1:12" s="4" customFormat="1">
       <c r="A28" t="s">
-        <v>3043</v>
+        <v>3041</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>2510</v>
@@ -45348,7 +45348,7 @@
         <v>2052</v>
       </c>
       <c r="E28" t="s">
-        <v>3266</v>
+        <v>3264</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>2519</v>
@@ -45360,7 +45360,7 @@
         <v>2704</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>3644</v>
+        <v>3642</v>
       </c>
       <c r="K28"/>
     </row>
@@ -45375,41 +45375,41 @@
         <v>350</v>
       </c>
       <c r="D29" s="75" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
       <c r="E29" t="s">
-        <v>3557</v>
+        <v>3555</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>3032</v>
+        <v>3030</v>
       </c>
       <c r="G29" s="75" t="s">
         <v>250</v>
       </c>
       <c r="H29" s="49" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="I29" t="s">
-        <v>3499</v>
+        <v>3497</v>
       </c>
       <c r="J29" s="4"/>
       <c r="L29" s="135"/>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>3104</v>
+        <v>3102</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>3222</v>
+        <v>3220</v>
       </c>
       <c r="C30" s="22" t="s">
         <v>402</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>3221</v>
+        <v>3219</v>
       </c>
       <c r="E30" t="s">
-        <v>3415</v>
+        <v>3413</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>1354</v>
@@ -45418,7 +45418,7 @@
         <v>159</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>3225</v>
+        <v>3223</v>
       </c>
       <c r="I30" s="55" t="s">
         <v>2813</v>
@@ -45426,7 +45426,7 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>3554</v>
+        <v>3552</v>
       </c>
       <c r="B31" s="4">
         <v>69409351</v>
@@ -45447,10 +45447,10 @@
         <v>159</v>
       </c>
       <c r="H31" t="s">
-        <v>3388</v>
+        <v>3386</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>3312</v>
+        <v>3310</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -45476,7 +45476,7 @@
         <v>159</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>3137</v>
+        <v>3135</v>
       </c>
       <c r="I32" s="49" t="s">
         <v>2800</v>
@@ -45508,7 +45508,7 @@
         <v>2888</v>
       </c>
       <c r="I33" t="s">
-        <v>3166</v>
+        <v>3164</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -45516,13 +45516,13 @@
         <v>1444</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>3682</v>
+        <v>3680</v>
       </c>
       <c r="C34" s="21" t="s">
         <v>2642</v>
       </c>
       <c r="D34" t="s">
-        <v>3336</v>
+        <v>3334</v>
       </c>
       <c r="E34" t="s">
         <v>2648</v>
@@ -45534,10 +45534,10 @@
         <v>159</v>
       </c>
       <c r="H34" t="s">
-        <v>3347</v>
+        <v>3345</v>
       </c>
       <c r="I34" t="s">
-        <v>3476</v>
+        <v>3474</v>
       </c>
       <c r="J34" s="4"/>
     </row>
@@ -45546,13 +45546,13 @@
         <v>147</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>3099</v>
+        <v>3097</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>2643</v>
       </c>
       <c r="D35" t="s">
-        <v>3098</v>
+        <v>3096</v>
       </c>
       <c r="E35" t="s">
         <v>2648</v>
@@ -45564,24 +45564,24 @@
         <v>2649</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>3142</v>
+        <v>3140</v>
       </c>
       <c r="I35" t="s">
-        <v>3154</v>
+        <v>3152</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>3556</v>
+        <v>3554</v>
       </c>
       <c r="B36" t="s">
-        <v>3586</v>
+        <v>3584</v>
       </c>
       <c r="C36" s="22" t="s">
         <v>2644</v>
       </c>
       <c r="D36" t="s">
-        <v>3585</v>
+        <v>3583</v>
       </c>
       <c r="E36" t="s">
         <v>2648</v>
@@ -45593,10 +45593,10 @@
         <v>159</v>
       </c>
       <c r="H36" t="s">
-        <v>3588</v>
+        <v>3586</v>
       </c>
       <c r="I36" t="s">
-        <v>3376</v>
+        <v>3374</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -45610,7 +45610,7 @@
         <v>2656</v>
       </c>
       <c r="D37" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="E37" t="s">
         <v>2658</v>
@@ -45622,10 +45622,10 @@
         <v>159</v>
       </c>
       <c r="H37" t="s">
-        <v>3016</v>
+        <v>3015</v>
       </c>
       <c r="I37" t="s">
-        <v>3086</v>
+        <v>3084</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -45633,7 +45633,7 @@
         <v>157</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>3239</v>
+        <v>3237</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>2657</v>
@@ -45651,10 +45651,10 @@
         <v>159</v>
       </c>
       <c r="H38" s="97" t="s">
-        <v>3333</v>
+        <v>3331</v>
       </c>
       <c r="I38" t="s">
-        <v>3432</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -45667,10 +45667,10 @@
         <v>1364</v>
       </c>
       <c r="E41" s="97" t="s">
-        <v>3490</v>
+        <v>3488</v>
       </c>
       <c r="F41" s="105" t="s">
-        <v>3491</v>
+        <v>3489</v>
       </c>
       <c r="G41" s="105" t="s">
         <v>159</v>
@@ -45688,10 +45688,10 @@
         <v>2120</v>
       </c>
       <c r="E42" s="97" t="s">
-        <v>3490</v>
+        <v>3488</v>
       </c>
       <c r="F42" s="105" t="s">
-        <v>3491</v>
+        <v>3489</v>
       </c>
       <c r="G42" s="105" t="s">
         <v>159</v>
@@ -45707,7 +45707,7 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="4" t="s">
-        <v>3429</v>
+        <v>3427</v>
       </c>
       <c r="B45" t="s">
         <v>2556</v>
@@ -45737,7 +45737,7 @@
         <v>2877</v>
       </c>
       <c r="K45" t="s">
-        <v>3081</v>
+        <v>3079</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="4" customFormat="1">
@@ -46128,13 +46128,13 @@
         <v>157</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>3242</v>
+        <v>3240</v>
       </c>
       <c r="C2" s="277" t="s">
         <v>254</v>
       </c>
       <c r="D2" s="106" t="s">
-        <v>3241</v>
+        <v>3239</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>1309</v>
@@ -46146,16 +46146,16 @@
         <v>62</v>
       </c>
       <c r="H2" s="301" t="s">
-        <v>3281</v>
+        <v>3279</v>
       </c>
       <c r="I2" s="106" t="s">
-        <v>3252</v>
+        <v>3250</v>
       </c>
       <c r="J2" s="450" t="s">
-        <v>3678</v>
+        <v>3676</v>
       </c>
       <c r="K2" s="30" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="M2" s="159"/>
     </row>
@@ -46170,7 +46170,7 @@
         <v>1192</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>3338</v>
+        <v>3336</v>
       </c>
       <c r="E4" s="32" t="s">
         <v>2442</v>
@@ -46182,25 +46182,25 @@
         <v>270</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>3515</v>
+        <v>3513</v>
       </c>
       <c r="I4" s="30" t="s">
-        <v>3397</v>
+        <v>3395</v>
       </c>
       <c r="J4" s="139" t="s">
-        <v>3037</v>
+        <v>3035</v>
       </c>
       <c r="K4" s="139" t="s">
-        <v>3590</v>
+        <v>3588</v>
       </c>
       <c r="M4" s="39"/>
     </row>
     <row r="5" spans="1:13" s="30" customFormat="1">
       <c r="A5" s="30" t="s">
-        <v>3429</v>
+        <v>3427</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>3434</v>
+        <v>3432</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>1124</v>
@@ -46218,16 +46218,16 @@
         <v>65</v>
       </c>
       <c r="H5" s="453" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>3105</v>
+        <v>3103</v>
       </c>
       <c r="J5" s="30" t="s">
-        <v>3508</v>
+        <v>3506</v>
       </c>
       <c r="K5" s="30" t="s">
-        <v>3416</v>
+        <v>3414</v>
       </c>
       <c r="M5" s="36"/>
     </row>
@@ -46242,7 +46242,7 @@
         <v>2818</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>3669</v>
+        <v>3667</v>
       </c>
       <c r="E6" s="140" t="s">
         <v>2778</v>
@@ -46254,22 +46254,22 @@
         <v>65</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>3141</v>
+        <v>3139</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>3245</v>
+        <v>3243</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>3248</v>
+        <v>3246</v>
       </c>
       <c r="K6" s="30" t="s">
-        <v>3374</v>
+        <v>3372</v>
       </c>
       <c r="M6" s="36"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="107" t="s">
-        <v>3311</v>
+        <v>3309</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>1222</v>
@@ -46278,28 +46278,28 @@
         <v>1097</v>
       </c>
       <c r="D7" t="s">
-        <v>3516</v>
+        <v>3514</v>
       </c>
       <c r="E7" s="107" t="s">
-        <v>3494</v>
+        <v>3492</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>3495</v>
+        <v>3493</v>
       </c>
       <c r="G7" s="106" t="s">
         <v>724</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>3390</v>
+        <v>3388</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>3117</v>
+        <v>3115</v>
       </c>
       <c r="J7" s="30" t="s">
         <v>2720</v>
       </c>
       <c r="K7" s="30" t="s">
-        <v>3143</v>
+        <v>3141</v>
       </c>
       <c r="M7" s="36"/>
     </row>
@@ -46314,7 +46314,7 @@
         <v>990</v>
       </c>
       <c r="D8" s="139" t="s">
-        <v>3613</v>
+        <v>3611</v>
       </c>
       <c r="E8" s="107" t="s">
         <v>1167</v>
@@ -46326,16 +46326,16 @@
         <v>65</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>3041</v>
+        <v>3039</v>
       </c>
       <c r="I8" s="32" t="s">
-        <v>3207</v>
+        <v>3205</v>
       </c>
       <c r="J8" s="107" t="s">
-        <v>3053</v>
+        <v>3051</v>
       </c>
       <c r="K8" s="139" t="s">
-        <v>3565</v>
+        <v>3563</v>
       </c>
       <c r="M8" s="36"/>
     </row>
@@ -46362,16 +46362,16 @@
         <v>65</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>3164</v>
+        <v>3162</v>
       </c>
       <c r="I9" s="107" t="s">
-        <v>3194</v>
+        <v>3192</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>3443</v>
+        <v>3441</v>
       </c>
       <c r="K9" s="107" t="s">
-        <v>3167</v>
+        <v>3165</v>
       </c>
       <c r="M9" s="36"/>
     </row>
@@ -46398,22 +46398,22 @@
         <v>65</v>
       </c>
       <c r="H10" s="107" t="s">
-        <v>3440</v>
+        <v>3438</v>
       </c>
       <c r="I10" t="s">
-        <v>3526</v>
+        <v>3524</v>
       </c>
       <c r="J10" s="219" t="s">
-        <v>3660</v>
+        <v>3658</v>
       </c>
       <c r="K10" s="107" t="s">
-        <v>3195</v>
+        <v>3193</v>
       </c>
       <c r="M10" s="34"/>
     </row>
     <row r="11" spans="1:13" s="30" customFormat="1">
       <c r="A11" s="107" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="B11" s="107">
         <v>62657225</v>
@@ -46434,16 +46434,16 @@
         <v>605</v>
       </c>
       <c r="H11" s="139" t="s">
-        <v>3313</v>
+        <v>3311</v>
       </c>
       <c r="I11" s="30" t="s">
-        <v>3034</v>
+        <v>3032</v>
       </c>
       <c r="J11" s="107" t="s">
-        <v>3138</v>
+        <v>3136</v>
       </c>
       <c r="K11" s="107" t="s">
-        <v>3436</v>
+        <v>3434</v>
       </c>
       <c r="M11" s="36"/>
     </row>
@@ -46458,7 +46458,7 @@
         <v>72</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
       <c r="E12" s="106" t="s">
         <v>912</v>
@@ -46470,22 +46470,22 @@
         <v>245</v>
       </c>
       <c r="H12" s="106" t="s">
-        <v>3030</v>
+        <v>3028</v>
       </c>
       <c r="I12" s="106" t="s">
-        <v>3017</v>
+        <v>3016</v>
       </c>
       <c r="J12" s="106" t="s">
-        <v>3668</v>
+        <v>3666</v>
       </c>
       <c r="K12" s="107" t="s">
-        <v>3431</v>
+        <v>3429</v>
       </c>
       <c r="M12" s="151"/>
     </row>
     <row r="13" spans="1:13" s="107" customFormat="1">
       <c r="A13" s="140" t="s">
-        <v>3605</v>
+        <v>3603</v>
       </c>
       <c r="B13" s="107" t="s">
         <v>2850</v>
@@ -46494,7 +46494,7 @@
         <v>923</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>3296</v>
+        <v>3294</v>
       </c>
       <c r="E13" s="140" t="s">
         <v>2819</v>
@@ -46506,16 +46506,16 @@
         <v>65</v>
       </c>
       <c r="H13" s="30" t="s">
-        <v>3297</v>
+        <v>3295</v>
       </c>
       <c r="I13" s="30" t="s">
-        <v>3400</v>
+        <v>3398</v>
       </c>
       <c r="J13" s="107" t="s">
-        <v>3446</v>
+        <v>3444</v>
       </c>
       <c r="K13" t="s">
-        <v>3472</v>
+        <v>3470</v>
       </c>
       <c r="M13" s="36"/>
     </row>
@@ -46542,13 +46542,13 @@
         <v>65</v>
       </c>
       <c r="H14" s="107" t="s">
-        <v>3532</v>
+        <v>3530</v>
       </c>
       <c r="I14" s="417" t="s">
         <v>2298</v>
       </c>
       <c r="J14" s="32" t="s">
-        <v>3361</v>
+        <v>3359</v>
       </c>
       <c r="M14" s="36"/>
     </row>
@@ -46575,16 +46575,16 @@
         <v>66</v>
       </c>
       <c r="H15" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="I15" s="49" t="s">
-        <v>3670</v>
+        <v>3668</v>
       </c>
       <c r="J15" t="s">
-        <v>3417</v>
+        <v>3415</v>
       </c>
       <c r="K15" s="107" t="s">
-        <v>3155</v>
+        <v>3153</v>
       </c>
       <c r="M15" s="36"/>
     </row>
@@ -46639,13 +46639,13 @@
         <v>2863</v>
       </c>
       <c r="I17" s="30" t="s">
-        <v>3257</v>
+        <v>3255</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>3113</v>
+        <v>3111</v>
       </c>
       <c r="K17" s="430" t="s">
-        <v>2958</v>
+        <v>2957</v>
       </c>
       <c r="M17" s="34"/>
     </row>
@@ -46672,22 +46672,22 @@
         <v>66</v>
       </c>
       <c r="H18" s="30" t="s">
-        <v>3240</v>
+        <v>3238</v>
       </c>
       <c r="I18" t="s">
-        <v>3360</v>
+        <v>3358</v>
       </c>
       <c r="J18" t="s">
-        <v>3389</v>
+        <v>3387</v>
       </c>
       <c r="K18" t="s">
-        <v>3071</v>
+        <v>3069</v>
       </c>
       <c r="M18" s="36"/>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="4" t="s">
-        <v>3088</v>
+        <v>3086</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>1548</v>
@@ -46696,7 +46696,7 @@
         <v>1709</v>
       </c>
       <c r="D19" s="134" t="s">
-        <v>3614</v>
+        <v>3612</v>
       </c>
       <c r="E19" t="s">
         <v>1712</v>
@@ -46708,16 +46708,16 @@
         <v>66</v>
       </c>
       <c r="H19" t="s">
-        <v>3261</v>
+        <v>3259</v>
       </c>
       <c r="I19" t="s">
-        <v>3061</v>
+        <v>3059</v>
       </c>
       <c r="J19" s="220" t="s">
-        <v>3387</v>
+        <v>3385</v>
       </c>
       <c r="K19" t="s">
-        <v>3206</v>
+        <v>3204</v>
       </c>
       <c r="M19" s="36"/>
     </row>
@@ -46732,7 +46732,7 @@
         <v>2536</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>3185</v>
+        <v>3183</v>
       </c>
       <c r="E20" s="107" t="s">
         <v>2460</v>
@@ -46744,31 +46744,31 @@
         <v>65</v>
       </c>
       <c r="H20" s="454" t="s">
-        <v>3667</v>
+        <v>3665</v>
       </c>
       <c r="I20" t="s">
-        <v>3186</v>
+        <v>3184</v>
       </c>
       <c r="J20" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="K20" t="s">
-        <v>3224</v>
+        <v>3222</v>
       </c>
       <c r="M20" s="36"/>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>3539</v>
+        <v>3537</v>
       </c>
       <c r="B21" t="s">
-        <v>3544</v>
+        <v>3542</v>
       </c>
       <c r="C21" s="22" t="s">
         <v>1140</v>
       </c>
       <c r="D21" t="s">
-        <v>3543</v>
+        <v>3541</v>
       </c>
       <c r="E21" s="140" t="s">
         <v>1608</v>
@@ -46780,19 +46780,19 @@
         <v>65</v>
       </c>
       <c r="H21" t="s">
-        <v>3549</v>
+        <v>3547</v>
       </c>
       <c r="I21" t="s">
-        <v>3552</v>
+        <v>3550</v>
       </c>
       <c r="J21" t="s">
-        <v>3553</v>
+        <v>3551</v>
       </c>
       <c r="M21" s="36"/>
     </row>
     <row r="22" spans="1:13" s="30" customFormat="1">
       <c r="A22" s="30" t="s">
-        <v>3556</v>
+        <v>3554</v>
       </c>
       <c r="B22" s="30" t="s">
         <v>2136</v>
@@ -46801,58 +46801,58 @@
         <v>2781</v>
       </c>
       <c r="D22" s="107" t="s">
-        <v>3596</v>
+        <v>3594</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>3569</v>
+        <v>3567</v>
       </c>
       <c r="F22" s="30" t="s">
-        <v>3570</v>
+        <v>3568</v>
       </c>
       <c r="G22" s="32" t="s">
         <v>65</v>
       </c>
       <c r="H22" s="30" t="s">
+        <v>3572</v>
+      </c>
+      <c r="I22" s="30" t="s">
         <v>3574</v>
       </c>
-      <c r="I22" s="30" t="s">
-        <v>3576</v>
-      </c>
       <c r="J22" s="30" t="s">
-        <v>3577</v>
+        <v>3575</v>
       </c>
       <c r="M22" s="36"/>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>3556</v>
+        <v>3554</v>
       </c>
       <c r="B23" t="s">
-        <v>3591</v>
+        <v>3589</v>
       </c>
       <c r="C23" s="22" t="s">
         <v>1922</v>
       </c>
       <c r="D23" t="s">
-        <v>3650</v>
+        <v>3648</v>
       </c>
       <c r="E23" s="30" t="s">
-        <v>3569</v>
+        <v>3567</v>
       </c>
       <c r="F23" s="30" t="s">
-        <v>3570</v>
+        <v>3568</v>
       </c>
       <c r="G23" t="s">
         <v>66</v>
       </c>
       <c r="H23" s="97" t="s">
+        <v>3649</v>
+      </c>
+      <c r="I23" s="97" t="s">
+        <v>3650</v>
+      </c>
+      <c r="J23" s="97" t="s">
         <v>3651</v>
-      </c>
-      <c r="I23" s="97" t="s">
-        <v>3652</v>
-      </c>
-      <c r="J23" s="97" t="s">
-        <v>3653</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -46945,7 +46945,7 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" t="s">
-        <v>3043</v>
+        <v>3041</v>
       </c>
       <c r="B33">
         <v>60389752</v>
@@ -46968,7 +46968,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" t="s">
-        <v>3654</v>
+        <v>3652</v>
       </c>
       <c r="B34">
         <v>60389752</v>
@@ -46977,13 +46977,13 @@
         <v>2201</v>
       </c>
       <c r="D34" s="32" t="s">
-        <v>3438</v>
+        <v>3436</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>3569</v>
+        <v>3567</v>
       </c>
       <c r="F34" s="30" t="s">
-        <v>3570</v>
+        <v>3568</v>
       </c>
       <c r="G34" t="s">
         <v>3</v>
@@ -46992,7 +46992,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>3539</v>
+        <v>3537</v>
       </c>
       <c r="B35">
         <v>60389752</v>
@@ -47040,7 +47040,7 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="30" t="s">
-        <v>3539</v>
+        <v>3537</v>
       </c>
       <c r="B37" s="30">
         <v>64403333</v>
@@ -47102,10 +47102,10 @@
         <v>2170</v>
       </c>
       <c r="E39" s="140" t="s">
+        <v>3010</v>
+      </c>
+      <c r="F39" s="140" t="s">
         <v>3011</v>
-      </c>
-      <c r="F39" s="140" t="s">
-        <v>3012</v>
       </c>
       <c r="G39" s="106" t="s">
         <v>724</v>
@@ -47174,7 +47174,7 @@
         <v>2564</v>
       </c>
       <c r="E45" t="s">
-        <v>3449</v>
+        <v>3447</v>
       </c>
       <c r="F45" s="30" t="s">
         <v>2565</v>
@@ -47183,13 +47183,13 @@
         <v>369</v>
       </c>
       <c r="H45" t="s">
-        <v>3335</v>
+        <v>3333</v>
       </c>
       <c r="I45" s="30" t="s">
-        <v>3534</v>
+        <v>3532</v>
       </c>
       <c r="J45" t="s">
-        <v>3102</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -47241,10 +47241,10 @@
     </row>
     <row r="66" spans="1:38">
       <c r="C66" s="7" t="s">
-        <v>3684</v>
+        <v>3682</v>
       </c>
       <c r="D66" t="s">
-        <v>3438</v>
+        <v>3436</v>
       </c>
       <c r="E66" t="s">
         <v>2458</v>
@@ -47335,7 +47335,7 @@
         <v>1108</v>
       </c>
       <c r="D74" s="97" t="s">
-        <v>3567</v>
+        <v>3565</v>
       </c>
       <c r="E74" s="107" t="s">
         <v>1109</v>
@@ -47625,7 +47625,7 @@
         <v>1143</v>
       </c>
       <c r="D93" t="s">
-        <v>3563</v>
+        <v>3561</v>
       </c>
       <c r="E93" s="140" t="s">
         <v>1145</v>
@@ -47649,7 +47649,7 @@
         <v>1404</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>3564</v>
+        <v>3562</v>
       </c>
       <c r="E94" s="267" t="s">
         <v>1522</v>
@@ -47683,7 +47683,7 @@
         <v>358</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>3684</v>
+        <v>3682</v>
       </c>
     </row>
     <row r="105" spans="2:5">
@@ -47909,7 +47909,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>3566</v>
+        <v>3564</v>
       </c>
       <c r="C12" s="237" t="s">
         <v>1956</v>
@@ -48040,7 +48040,7 @@
         <v>6.83</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -48049,7 +48049,7 @@
       </c>
       <c r="B24" s="87"/>
       <c r="F24" s="2" t="s">
-        <v>3193</v>
+        <v>3191</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -48125,27 +48125,27 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="87" t="s">
-        <v>3630</v>
+        <v>3628</v>
       </c>
       <c r="C40" t="s">
-        <v>3633</v>
+        <v>3631</v>
       </c>
       <c r="F40" s="45"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="89" t="s">
-        <v>3631</v>
+        <v>3629</v>
       </c>
       <c r="C41" t="s">
-        <v>3634</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="42" spans="2:6" ht="15" thickBot="1">
       <c r="B42" s="86" t="s">
-        <v>3632</v>
+        <v>3630</v>
       </c>
       <c r="C42" t="s">
-        <v>3635</v>
+        <v>3633</v>
       </c>
     </row>
     <row r="43" spans="2:6">
@@ -48299,7 +48299,7 @@
         <v>143</v>
       </c>
       <c r="B6" s="248" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="C6" s="247" t="s">
         <v>1301</v>
@@ -48308,22 +48308,22 @@
         <v>2057</v>
       </c>
       <c r="E6" s="248" t="s">
-        <v>3483</v>
+        <v>3481</v>
       </c>
       <c r="F6" s="248" t="s">
-        <v>3484</v>
+        <v>3482</v>
       </c>
       <c r="G6" s="248" t="s">
         <v>357</v>
       </c>
       <c r="H6" s="248" t="s">
-        <v>3442</v>
+        <v>3440</v>
       </c>
       <c r="I6" s="245" t="s">
-        <v>3035</v>
+        <v>3033</v>
       </c>
       <c r="J6" s="296" t="s">
-        <v>3091</v>
+        <v>3089</v>
       </c>
       <c r="K6" s="248" t="s">
         <v>475</v>
@@ -48351,19 +48351,19 @@
         <v>1044</v>
       </c>
       <c r="F8" s="266" t="s">
-        <v>3486</v>
+        <v>3484</v>
       </c>
       <c r="G8" s="266" t="s">
         <v>690</v>
       </c>
       <c r="H8" s="296" t="s">
-        <v>3481</v>
+        <v>3479</v>
       </c>
       <c r="I8" s="296" t="s">
-        <v>3202</v>
+        <v>3200</v>
       </c>
       <c r="J8" s="441" t="s">
-        <v>3623</v>
+        <v>3621</v>
       </c>
       <c r="K8" s="266" t="s">
         <v>710</v>
@@ -48386,7 +48386,7 @@
         <v>1241</v>
       </c>
       <c r="F9" s="106" t="s">
-        <v>3362</v>
+        <v>3360</v>
       </c>
       <c r="G9" s="106" t="s">
         <v>250</v>
@@ -48395,7 +48395,7 @@
         <v>2900</v>
       </c>
       <c r="I9" s="213" t="s">
-        <v>3644</v>
+        <v>3642</v>
       </c>
       <c r="J9" s="106" t="s">
         <v>2245</v>
@@ -48418,7 +48418,7 @@
         <v>2766</v>
       </c>
       <c r="F10" s="264" t="s">
-        <v>3592</v>
+        <v>3590</v>
       </c>
       <c r="G10" s="264" t="s">
         <v>952</v>
@@ -48450,13 +48450,13 @@
         <v>690</v>
       </c>
       <c r="H11" s="265" t="s">
-        <v>3168</v>
+        <v>3166</v>
       </c>
       <c r="I11" s="296" t="s">
-        <v>3160</v>
+        <v>3158</v>
       </c>
       <c r="J11" s="265" t="s">
-        <v>3065</v>
+        <v>3063</v>
       </c>
       <c r="K11" s="246" t="s">
         <v>1216</v>
@@ -48467,7 +48467,7 @@
         <v>2562</v>
       </c>
       <c r="B12" s="263" t="s">
-        <v>3473</v>
+        <v>3471</v>
       </c>
       <c r="C12" s="194" t="s">
         <v>491</v>
@@ -48485,13 +48485,13 @@
         <v>690</v>
       </c>
       <c r="H12" s="145" t="s">
-        <v>3622</v>
+        <v>3620</v>
       </c>
       <c r="I12" s="432" t="s">
-        <v>3661</v>
+        <v>3659</v>
       </c>
       <c r="J12" s="270" t="s">
-        <v>3097</v>
+        <v>3095</v>
       </c>
       <c r="K12" s="183" t="s">
         <v>1217</v>
@@ -48525,10 +48525,10 @@
     </row>
     <row r="14" spans="1:11" s="224" customFormat="1">
       <c r="A14" s="224" t="s">
-        <v>3539</v>
+        <v>3537</v>
       </c>
       <c r="B14" s="224" t="s">
-        <v>3562</v>
+        <v>3560</v>
       </c>
       <c r="C14" s="431" t="s">
         <v>335</v>
@@ -48537,22 +48537,22 @@
         <v>2440</v>
       </c>
       <c r="E14" s="224" t="s">
-        <v>3237</v>
+        <v>3235</v>
       </c>
       <c r="F14" s="224" t="s">
-        <v>3236</v>
+        <v>3234</v>
       </c>
       <c r="G14" s="224" t="s">
         <v>690</v>
       </c>
       <c r="H14" s="224" t="s">
-        <v>3243</v>
+        <v>3241</v>
       </c>
       <c r="I14" s="215" t="s">
-        <v>3454</v>
+        <v>3452</v>
       </c>
       <c r="J14" s="224" t="s">
-        <v>3244</v>
+        <v>3242</v>
       </c>
       <c r="K14" s="224" t="s">
         <v>1330</v>
@@ -48572,7 +48572,7 @@
         <v>1993</v>
       </c>
       <c r="E15" s="216" t="s">
-        <v>3514</v>
+        <v>3512</v>
       </c>
       <c r="F15" s="216" t="s">
         <v>1448</v>
@@ -48581,13 +48581,13 @@
         <v>690</v>
       </c>
       <c r="H15" s="437" t="s">
-        <v>3179</v>
+        <v>3177</v>
       </c>
       <c r="I15" s="215" t="s">
-        <v>3139</v>
+        <v>3137</v>
       </c>
       <c r="J15" s="263" t="s">
-        <v>3314</v>
+        <v>3312</v>
       </c>
       <c r="K15" s="183" t="s">
         <v>1218</v>
@@ -48598,13 +48598,13 @@
         <v>1430</v>
       </c>
       <c r="B16" s="265" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="C16" s="271" t="s">
         <v>1318</v>
       </c>
       <c r="D16" s="260" t="s">
-        <v>3110</v>
+        <v>3108</v>
       </c>
       <c r="E16" s="260" t="s">
         <v>2827</v>
@@ -48616,13 +48616,13 @@
         <v>690</v>
       </c>
       <c r="H16" s="265" t="s">
-        <v>3426</v>
+        <v>3424</v>
       </c>
       <c r="I16" s="272" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="J16" s="265" t="s">
-        <v>3383</v>
+        <v>3381</v>
       </c>
       <c r="K16" s="260" t="s">
         <v>1454</v>
@@ -48715,7 +48715,7 @@
         <v>690</v>
       </c>
       <c r="I20" s="49" t="s">
-        <v>3679</v>
+        <v>3677</v>
       </c>
       <c r="J20" s="49"/>
       <c r="K20" s="265" t="s">
@@ -48745,13 +48745,13 @@
         <v>690</v>
       </c>
       <c r="H21" s="260" t="s">
-        <v>3114</v>
+        <v>3112</v>
       </c>
       <c r="I21" s="299" t="s">
-        <v>3521</v>
+        <v>3519</v>
       </c>
       <c r="J21" s="49" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="K21" s="265" t="s">
         <v>1785</v>
@@ -48759,7 +48759,7 @@
     </row>
     <row r="22" spans="1:11" s="260" customFormat="1">
       <c r="A22" s="49" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
       <c r="B22" s="260" t="s">
         <v>2427</v>
@@ -48780,13 +48780,13 @@
         <v>690</v>
       </c>
       <c r="H22" s="260" t="s">
-        <v>3327</v>
+        <v>3325</v>
       </c>
       <c r="I22" s="260" t="s">
-        <v>3683</v>
+        <v>3681</v>
       </c>
       <c r="J22" s="260" t="s">
-        <v>3259</v>
+        <v>3257</v>
       </c>
       <c r="K22" s="260" t="s">
         <v>1830</v>
@@ -48818,10 +48818,10 @@
         <v>2837</v>
       </c>
       <c r="I24" s="265" t="s">
-        <v>3040</v>
+        <v>3038</v>
       </c>
       <c r="J24" s="265" t="s">
-        <v>3584</v>
+        <v>3582</v>
       </c>
       <c r="K24" s="260" t="s">
         <v>1832</v>
@@ -48864,10 +48864,10 @@
         <v>637</v>
       </c>
       <c r="D27" s="256" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="E27" s="272" t="s">
-        <v>3637</v>
+        <v>3635</v>
       </c>
       <c r="F27" s="272" t="s">
         <v>1730</v>
@@ -48876,13 +48876,13 @@
         <v>250</v>
       </c>
       <c r="H27" s="49" t="s">
-        <v>3227</v>
+        <v>3225</v>
       </c>
       <c r="I27" s="265" t="s">
-        <v>3455</v>
+        <v>3453</v>
       </c>
       <c r="J27" s="265" t="s">
-        <v>3348</v>
+        <v>3346</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="260" customFormat="1">
@@ -48890,7 +48890,7 @@
         <v>844</v>
       </c>
       <c r="D29" s="265" t="s">
-        <v>3180</v>
+        <v>3178</v>
       </c>
       <c r="E29" s="260" t="s">
         <v>1808</v>
@@ -49272,13 +49272,13 @@
         <v>2846</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>3512</v>
+        <v>3510</v>
       </c>
       <c r="I2" s="455" t="s">
-        <v>3685</v>
+        <v>3683</v>
       </c>
       <c r="J2" t="s">
-        <v>3093</v>
+        <v>3091</v>
       </c>
       <c r="L2" s="36" t="s">
         <v>1186</v>
@@ -49304,7 +49304,7 @@
         <v>298</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>3513</v>
+        <v>3511</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>708</v>
@@ -49330,25 +49330,25 @@
         <v>313</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>3084</v>
+        <v>3082</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>3174</v>
+        <v>3172</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>323</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="H4" t="s">
-        <v>3233</v>
+        <v>3231</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>3092</v>
+        <v>3090</v>
       </c>
       <c r="J4" t="s">
-        <v>3085</v>
+        <v>3083</v>
       </c>
       <c r="L4" s="127" t="s">
         <v>322</v>
@@ -49374,7 +49374,7 @@
         <v>424</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>3238</v>
+        <v>3236</v>
       </c>
       <c r="H5" s="49" t="s">
         <v>2812</v>
@@ -49398,25 +49398,25 @@
         <v>327</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>166</v>
       </c>
       <c r="G6" t="s">
-        <v>3468</v>
+        <v>3466</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>3118</v>
+        <v>3116</v>
       </c>
       <c r="I6" t="s">
-        <v>3517</v>
+        <v>3515</v>
       </c>
       <c r="J6" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="L6" s="67" t="s">
         <v>423</v>
@@ -49424,7 +49424,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="4" t="s">
-        <v>3424</v>
+        <v>3422</v>
       </c>
       <c r="B7" s="4">
         <v>69561522</v>
@@ -49433,25 +49433,25 @@
         <v>434</v>
       </c>
       <c r="D7" t="s">
-        <v>3344</v>
+        <v>3342</v>
       </c>
       <c r="E7" t="s">
-        <v>3377</v>
+        <v>3375</v>
       </c>
       <c r="F7" t="s">
         <v>151</v>
       </c>
       <c r="G7" s="49" t="s">
-        <v>3679</v>
+        <v>3677</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>3662</v>
+        <v>3660</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>3264</v>
+        <v>3262</v>
       </c>
       <c r="J7" t="s">
-        <v>3373</v>
+        <v>3371</v>
       </c>
       <c r="L7" s="83" t="s">
         <v>435</v>
@@ -49459,10 +49459,10 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="4" t="s">
-        <v>3033</v>
+        <v>3031</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>3120</v>
+        <v>3118</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>658</v>
@@ -49480,10 +49480,10 @@
         <v>2706</v>
       </c>
       <c r="H8" t="s">
-        <v>3351</v>
+        <v>3349</v>
       </c>
       <c r="I8" t="s">
-        <v>3155</v>
+        <v>3153</v>
       </c>
       <c r="J8" s="49" t="s">
         <v>2845</v>
@@ -49510,16 +49510,16 @@
         <v>151</v>
       </c>
       <c r="G9" t="s">
-        <v>3313</v>
+        <v>3311</v>
       </c>
       <c r="H9" s="220" t="s">
-        <v>3302</v>
+        <v>3300</v>
       </c>
       <c r="I9" s="453" t="s">
-        <v>3119</v>
+        <v>3117</v>
       </c>
       <c r="J9" s="220" t="s">
-        <v>3290</v>
+        <v>3288</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -49533,7 +49533,7 @@
         <v>2228</v>
       </c>
       <c r="D10" t="s">
-        <v>3188</v>
+        <v>3186</v>
       </c>
       <c r="E10" t="s">
         <v>2199</v>
@@ -49542,13 +49542,13 @@
         <v>1838</v>
       </c>
       <c r="G10" t="s">
-        <v>3488</v>
+        <v>3486</v>
       </c>
       <c r="H10" t="s">
-        <v>3050</v>
+        <v>3048</v>
       </c>
       <c r="I10" t="s">
-        <v>3520</v>
+        <v>3518</v>
       </c>
       <c r="J10" s="49" t="s">
         <v>2917</v>
@@ -49591,7 +49591,7 @@
         <v>1494</v>
       </c>
       <c r="E12" t="s">
-        <v>3343</v>
+        <v>3341</v>
       </c>
       <c r="F12" t="s">
         <v>614</v>
@@ -49622,16 +49622,16 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>3448</v>
+        <v>3446</v>
       </c>
       <c r="B14" t="s">
-        <v>3457</v>
+        <v>3455</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>281</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>3456</v>
+        <v>3454</v>
       </c>
       <c r="E14" t="s">
         <v>2163</v>
@@ -49640,16 +49640,16 @@
         <v>1838</v>
       </c>
       <c r="G14" s="97" t="s">
-        <v>3497</v>
+        <v>3495</v>
       </c>
       <c r="H14" s="97" t="s">
-        <v>3498</v>
+        <v>3496</v>
       </c>
       <c r="I14" t="s">
-        <v>3655</v>
+        <v>3653</v>
       </c>
       <c r="J14" t="s">
-        <v>3561</v>
+        <v>3559</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -49917,7 +49917,7 @@
     </row>
     <row r="2" spans="1:14" ht="43.15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>3203</v>
+        <v>3201</v>
       </c>
       <c r="C2" s="51"/>
       <c r="D2" s="52" t="s">
@@ -49929,7 +49929,7 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="B4">
         <v>62445630</v>
@@ -49941,7 +49941,7 @@
         <v>2738</v>
       </c>
       <c r="E4" t="s">
-        <v>3366</v>
+        <v>3364</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -49966,7 +49966,7 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>3043</v>
+        <v>3041</v>
       </c>
       <c r="B9" t="s">
         <v>1570</v>
@@ -49978,7 +49978,7 @@
         <v>1569</v>
       </c>
       <c r="E9" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="F9" t="s">
         <v>1752</v>
@@ -49998,7 +49998,7 @@
         <v>2243</v>
       </c>
       <c r="E10" s="284" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="F10" t="s">
         <v>1701</v>
@@ -50006,7 +50006,7 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="30" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="B11" s="178">
         <v>68241069</v>
@@ -50018,7 +50018,7 @@
         <v>2080</v>
       </c>
       <c r="E11" t="s">
-        <v>3223</v>
+        <v>3221</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -50035,7 +50035,7 @@
         <v>2747</v>
       </c>
       <c r="E12" t="s">
-        <v>3629</v>
+        <v>3627</v>
       </c>
       <c r="F12" t="s">
         <v>1701</v>
@@ -50043,7 +50043,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>3538</v>
+        <v>3536</v>
       </c>
       <c r="B13">
         <v>62271547</v>
@@ -50055,15 +50055,15 @@
         <v>2433</v>
       </c>
       <c r="E13" t="s">
-        <v>3069</v>
+        <v>3067</v>
       </c>
       <c r="F13" t="s">
-        <v>3070</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="B14">
         <v>62445630</v>
@@ -50072,7 +50072,7 @@
         <v>1957</v>
       </c>
       <c r="D14" t="s">
-        <v>3345</v>
+        <v>3343</v>
       </c>
       <c r="E14" t="s">
         <v>2707</v>
@@ -50083,7 +50083,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>3311</v>
+        <v>3309</v>
       </c>
       <c r="B15">
         <v>62806425</v>
@@ -50112,10 +50112,10 @@
         <v>2795</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>3230</v>
+        <v>3228</v>
       </c>
       <c r="E16" t="s">
-        <v>3231</v>
+        <v>3229</v>
       </c>
       <c r="F16" t="s">
         <v>2750</v>
@@ -50123,19 +50123,19 @@
     </row>
     <row r="17" spans="1:8" s="30" customFormat="1">
       <c r="A17" s="30" t="s">
-        <v>3033</v>
+        <v>3031</v>
       </c>
       <c r="B17" s="30">
         <v>68582631</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>3101</v>
+        <v>3099</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>3246</v>
+        <v>3244</v>
       </c>
       <c r="E17" t="s">
-        <v>3247</v>
+        <v>3245</v>
       </c>
       <c r="F17" t="s">
         <v>2750</v>
@@ -50158,7 +50158,7 @@
         <v>2799</v>
       </c>
       <c r="E18" t="s">
-        <v>3247</v>
+        <v>3245</v>
       </c>
       <c r="F18" t="s">
         <v>2750</v>
@@ -50178,10 +50178,10 @@
         <v>2843</v>
       </c>
       <c r="E19" t="s">
-        <v>3394</v>
+        <v>3392</v>
       </c>
       <c r="F19" t="s">
-        <v>3070</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -50201,7 +50201,7 @@
         <v>1529</v>
       </c>
       <c r="F21" t="s">
-        <v>3530</v>
+        <v>3528</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -50237,7 +50237,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>3104</v>
+        <v>3102</v>
       </c>
       <c r="B26">
         <v>68927207</v>
@@ -50249,13 +50249,13 @@
         <v>2724</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>3204</v>
+        <v>3202</v>
       </c>
       <c r="F26" t="s">
-        <v>3205</v>
+        <v>3203</v>
       </c>
       <c r="G26" t="s">
-        <v>3217</v>
+        <v>3215</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -50272,13 +50272,13 @@
         <v>421</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>3204</v>
+        <v>3202</v>
       </c>
       <c r="F27" t="s">
-        <v>3237</v>
+        <v>3235</v>
       </c>
       <c r="G27" t="s">
-        <v>3272</v>
+        <v>3270</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -50289,16 +50289,16 @@
         <v>1477</v>
       </c>
       <c r="D29" t="s">
-        <v>3500</v>
+        <v>3498</v>
       </c>
       <c r="E29" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="F29" t="s">
-        <v>3219</v>
+        <v>3217</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>3501</v>
+        <v>3499</v>
       </c>
       <c r="H29" t="s">
         <v>407</v>
@@ -50306,7 +50306,7 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>3104</v>
+        <v>3102</v>
       </c>
       <c r="B30">
         <v>63926844</v>
@@ -50318,10 +50318,10 @@
         <v>2749</v>
       </c>
       <c r="E30" t="s">
-        <v>3218</v>
+        <v>3216</v>
       </c>
       <c r="F30" t="s">
-        <v>3219</v>
+        <v>3217</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -50335,10 +50335,10 @@
         <v>1576</v>
       </c>
       <c r="D31" t="s">
-        <v>3469</v>
+        <v>3467</v>
       </c>
       <c r="E31" t="s">
-        <v>3470</v>
+        <v>3468</v>
       </c>
       <c r="F31" t="s">
         <v>1326</v>
@@ -50447,10 +50447,10 @@
         <v>2555</v>
       </c>
       <c r="D47" s="30" t="s">
+        <v>2953</v>
+      </c>
+      <c r="F47" s="402" t="s">
         <v>2954</v>
-      </c>
-      <c r="F47" s="402" t="s">
-        <v>2955</v>
       </c>
       <c r="G47" s="30" t="s">
         <v>407</v>
@@ -52382,7 +52382,7 @@
     </row>
     <row r="252" spans="1:6" s="426" customFormat="1" ht="21">
       <c r="C252" s="426" t="s">
-        <v>3172</v>
+        <v>3170</v>
       </c>
     </row>
     <row r="253" spans="1:6">
@@ -52399,30 +52399,30 @@
         <v>2277</v>
       </c>
       <c r="E253" t="s">
-        <v>3170</v>
+        <v>3168</v>
       </c>
       <c r="F253" t="s">
-        <v>3171</v>
+        <v>3169</v>
       </c>
     </row>
     <row r="254" spans="1:6">
       <c r="A254" t="s">
-        <v>3088</v>
+        <v>3086</v>
       </c>
       <c r="B254">
         <v>64738222</v>
       </c>
       <c r="C254" s="22" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="D254" t="s">
-        <v>3087</v>
+        <v>3085</v>
       </c>
       <c r="E254" t="s">
-        <v>3170</v>
+        <v>3168</v>
       </c>
       <c r="F254" t="s">
-        <v>3171</v>
+        <v>3169</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -52433,16 +52433,16 @@
         <v>60433915</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>3089</v>
+        <v>3087</v>
       </c>
       <c r="D255" s="252" t="s">
         <v>2691</v>
       </c>
       <c r="E255" t="s">
-        <v>3170</v>
+        <v>3168</v>
       </c>
       <c r="F255" t="s">
-        <v>3171</v>
+        <v>3169</v>
       </c>
     </row>
     <row r="256" spans="1:6">
@@ -57196,7 +57196,7 @@
         <v>2738</v>
       </c>
       <c r="E537" s="76" t="s">
-        <v>3364</v>
+        <v>3362</v>
       </c>
       <c r="F537" s="76"/>
       <c r="G537" s="76"/>

--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dc549f2659ed9bd7/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62617" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA47CDD2-7438-4AA8-983E-AB211D68EA89}"/>
+  <xr:revisionPtr revIDLastSave="62647" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{373D19BC-DF15-431C-991A-38E9010CD0BF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1297,7 +1297,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6166" uniqueCount="3670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6170" uniqueCount="3668">
   <si>
     <t>shopfreefire.1.21.2@gmail.com</t>
   </si>
@@ -9885,12 +9885,6 @@
     <t>serranoanthony5890+ashley.colsonn.ie@outlook.com</t>
   </si>
   <si>
-    <t>Pas080626</t>
-  </si>
-  <si>
-    <t>Yra060826</t>
-  </si>
-  <si>
     <t xml:space="preserve">68496217 1 pantalla hasta el 06 de septiembre </t>
   </si>
   <si>
@@ -9915,18 +9909,12 @@
     <t>hasta 07denoviembre</t>
   </si>
   <si>
-    <t>68676175 1 pantalla hasta el 13 de septiembre (Aimethhg)</t>
-  </si>
-  <si>
     <t>invitacion de provedoor</t>
   </si>
   <si>
     <t>w51904635162</t>
   </si>
   <si>
-    <t>08 de septiembre</t>
-  </si>
-  <si>
     <t>Gdaa080826</t>
   </si>
   <si>
@@ -10032,9 +10020,6 @@
     <t>stevensabigail7804+prakito.th@outlook.com</t>
   </si>
   <si>
-    <t>gonzalesdean5791+izi_zi1.br@outlook.com</t>
-  </si>
-  <si>
     <t>Tra130826</t>
   </si>
   <si>
@@ -10065,9 +10050,6 @@
     <t>63040442 Orlando por Yai 1 pantalla hasta el 20 de septiembre</t>
   </si>
   <si>
-    <t>Rt140826</t>
-  </si>
-  <si>
     <t>hasta 12deagosto 2027</t>
   </si>
   <si>
@@ -10167,9 +10149,6 @@
     <t>15 gifcard hasta 18 de septiembre</t>
   </si>
   <si>
-    <t>Hfs160826</t>
-  </si>
-  <si>
     <t>yalaluz4+danielle.nanfra.au@gmail.com</t>
   </si>
   <si>
@@ -10626,9 +10605,6 @@
     <t>hasta 24denoviembre</t>
   </si>
   <si>
-    <t>quincenal 09 de septiembre</t>
-  </si>
-  <si>
     <t>63606961 1 pantalla hasta el 23 de septiembre (Marisol)</t>
   </si>
   <si>
@@ -11040,9 +11016,6 @@
     <t>62884444 1 pantalla hasta el 29 de septiembre</t>
   </si>
   <si>
-    <t>Yrd310826</t>
-  </si>
-  <si>
     <t>69105664 1 pantalla hasta el 29 de septiembre (Andres)</t>
   </si>
   <si>
@@ -12307,6 +12280,27 @@
   </si>
   <si>
     <t>N005 180926-1410d</t>
+  </si>
+  <si>
+    <t>Ydd180926</t>
+  </si>
+  <si>
+    <t>Yra180926</t>
+  </si>
+  <si>
+    <t>Ytr180926</t>
+  </si>
+  <si>
+    <t>parklaura1458+netkheopss.es@outlook.com</t>
+  </si>
+  <si>
+    <t>te180926</t>
+  </si>
+  <si>
+    <t>hs180926</t>
+  </si>
+  <si>
+    <t>N005 1 pantalla hasta el 18 de octubre 180926-1611g</t>
   </si>
 </sst>
 </file>
@@ -30195,7 +30189,7 @@
   <sheetData>
     <row r="1" spans="1:11" s="30" customFormat="1">
       <c r="A1" s="30" t="s">
-        <v>3184</v>
+        <v>3176</v>
       </c>
       <c r="B1" s="30">
         <v>60389752</v>
@@ -30207,7 +30201,7 @@
         <v>2012</v>
       </c>
       <c r="E1" s="459" t="s">
-        <v>3665</v>
+        <v>3656</v>
       </c>
       <c r="F1" s="30" t="s">
         <v>2078</v>
@@ -30227,12 +30221,12 @@
         <v>2124</v>
       </c>
       <c r="D2" s="148" t="s">
-        <v>3074</v>
+        <v>3067</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="148" customFormat="1">
       <c r="A3" s="148" t="s">
-        <v>2908</v>
+        <v>2904</v>
       </c>
       <c r="B3" s="148" t="s">
         <v>2659</v>
@@ -30246,7 +30240,7 @@
     </row>
     <row r="4" spans="1:11" s="30" customFormat="1">
       <c r="A4" s="30" t="s">
-        <v>3184</v>
+        <v>3176</v>
       </c>
       <c r="B4" s="30">
         <v>60389752</v>
@@ -30258,7 +30252,7 @@
         <v>2010</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>3000</v>
+        <v>2993</v>
       </c>
       <c r="F4" s="30" t="s">
         <v>2078</v>
@@ -30278,7 +30272,7 @@
         <v>2138</v>
       </c>
       <c r="D5" s="148" t="s">
-        <v>3190</v>
+        <v>3182</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="148" customFormat="1">
@@ -30309,7 +30303,7 @@
         <v>2859</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>3061</v>
+        <v>3054</v>
       </c>
       <c r="F7" s="30" t="s">
         <v>2083</v>
@@ -30320,7 +30314,7 @@
     </row>
     <row r="8" spans="1:11" s="148" customFormat="1">
       <c r="A8" s="225" t="s">
-        <v>2931</v>
+        <v>2925</v>
       </c>
       <c r="B8" s="148">
         <v>66003234</v>
@@ -30329,12 +30323,12 @@
         <v>2244</v>
       </c>
       <c r="D8" s="148" t="s">
-        <v>3590</v>
+        <v>3581</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="148" customFormat="1">
       <c r="A9" s="148" t="s">
-        <v>3301</v>
+        <v>3292</v>
       </c>
       <c r="B9" s="148" t="s">
         <v>1203</v>
@@ -30351,7 +30345,7 @@
     </row>
     <row r="10" spans="1:11" s="423" customFormat="1">
       <c r="A10" s="423" t="s">
-        <v>3157</v>
+        <v>3149</v>
       </c>
       <c r="B10" s="423">
         <v>60389752</v>
@@ -30388,7 +30382,7 @@
         <v>2143</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>3150</v>
+        <v>3142</v>
       </c>
       <c r="F13" s="30" t="s">
         <v>2142</v>
@@ -30400,7 +30394,7 @@
     </row>
     <row r="14" spans="1:11" s="148" customFormat="1">
       <c r="A14" s="225" t="s">
-        <v>3612</v>
+        <v>3603</v>
       </c>
       <c r="B14" s="225" t="s">
         <v>1675</v>
@@ -30414,7 +30408,7 @@
     </row>
     <row r="15" spans="1:11" s="148" customFormat="1">
       <c r="A15" s="225" t="s">
-        <v>3470</v>
+        <v>3461</v>
       </c>
       <c r="B15" s="416">
         <v>62439069</v>
@@ -30428,7 +30422,7 @@
     </row>
     <row r="16" spans="1:11" s="32" customFormat="1">
       <c r="A16" s="30" t="s">
-        <v>3512</v>
+        <v>3503</v>
       </c>
       <c r="B16" s="284" t="s">
         <v>2198</v>
@@ -30437,10 +30431,10 @@
         <v>1526</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>3063</v>
+        <v>3056</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>3151</v>
+        <v>3143</v>
       </c>
       <c r="F16" s="32" t="s">
         <v>1527</v>
@@ -30449,21 +30443,21 @@
         <v>198</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>3064</v>
+        <v>3057</v>
       </c>
       <c r="I16" s="32" t="s">
-        <v>3308</v>
+        <v>3299</v>
       </c>
       <c r="J16" s="32" t="s">
-        <v>3230</v>
+        <v>3222</v>
       </c>
       <c r="K16" s="30" t="s">
-        <v>3231</v>
+        <v>3223</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="164" customFormat="1">
       <c r="A17" s="252" t="s">
-        <v>3424</v>
+        <v>3415</v>
       </c>
       <c r="B17" s="252" t="s">
         <v>1394</v>
@@ -30506,10 +30500,10 @@
         <v>1491</v>
       </c>
       <c r="D19" s="145" t="s">
-        <v>3531</v>
+        <v>3522</v>
       </c>
       <c r="E19" s="145" t="s">
-        <v>3045</v>
+        <v>3038</v>
       </c>
       <c r="F19" s="145" t="s">
         <v>1361</v>
@@ -30524,7 +30518,7 @@
     </row>
     <row r="20" spans="1:11" s="297" customFormat="1">
       <c r="A20" s="164" t="s">
-        <v>2931</v>
+        <v>2925</v>
       </c>
       <c r="B20" s="164">
         <v>68444421</v>
@@ -30533,7 +30527,7 @@
         <v>1681</v>
       </c>
       <c r="D20" s="252" t="s">
-        <v>2978</v>
+        <v>2971</v>
       </c>
       <c r="E20" s="252" t="s">
         <v>1682</v>
@@ -30541,7 +30535,7 @@
     </row>
     <row r="21" spans="1:11" s="297" customFormat="1">
       <c r="A21" s="252" t="s">
-        <v>3541</v>
+        <v>3532</v>
       </c>
       <c r="B21" s="252">
         <v>62169673</v>
@@ -30550,7 +30544,7 @@
         <v>1686</v>
       </c>
       <c r="D21" s="164" t="s">
-        <v>3532</v>
+        <v>3523</v>
       </c>
       <c r="E21" s="164" t="s">
         <v>1687</v>
@@ -30558,7 +30552,7 @@
     </row>
     <row r="22" spans="1:11" s="30" customFormat="1">
       <c r="A22" s="32" t="s">
-        <v>2983</v>
+        <v>2976</v>
       </c>
       <c r="B22" s="32">
         <v>60389752</v>
@@ -30570,7 +30564,7 @@
         <v>2121</v>
       </c>
       <c r="E22" s="459" t="s">
-        <v>3665</v>
+        <v>3656</v>
       </c>
       <c r="F22" s="30" t="s">
         <v>2077</v>
@@ -30581,7 +30575,7 @@
     </row>
     <row r="23" spans="1:11" s="148" customFormat="1">
       <c r="A23" s="225" t="s">
-        <v>3153</v>
+        <v>3145</v>
       </c>
       <c r="B23" s="148">
         <v>64858241</v>
@@ -30595,7 +30589,7 @@
     </row>
     <row r="24" spans="1:11" s="148" customFormat="1">
       <c r="A24" s="149" t="s">
-        <v>3153</v>
+        <v>3145</v>
       </c>
       <c r="B24" s="149">
         <v>68934853</v>
@@ -30604,12 +30598,12 @@
         <v>2117</v>
       </c>
       <c r="D24" s="148" t="s">
-        <v>3534</v>
+        <v>3525</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="30" customFormat="1">
       <c r="A25" s="30" t="s">
-        <v>2931</v>
+        <v>2925</v>
       </c>
       <c r="B25" s="30">
         <v>63166786</v>
@@ -30621,7 +30615,7 @@
         <v>1523</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>3044</v>
+        <v>3037</v>
       </c>
       <c r="F25" s="30" t="s">
         <v>1361</v>
@@ -30635,7 +30629,7 @@
     </row>
     <row r="26" spans="1:11" s="225" customFormat="1">
       <c r="A26" s="225" t="s">
-        <v>2983</v>
+        <v>2976</v>
       </c>
       <c r="B26" s="225" t="s">
         <v>1925</v>
@@ -30669,7 +30663,7 @@
     </row>
     <row r="28" spans="1:11" s="30" customFormat="1">
       <c r="A28" s="30" t="s">
-        <v>3301</v>
+        <v>3292</v>
       </c>
       <c r="B28" s="30">
         <v>60389752</v>
@@ -30681,7 +30675,7 @@
         <v>2007</v>
       </c>
       <c r="E28" s="30" t="s">
-        <v>3278</v>
+        <v>3269</v>
       </c>
       <c r="F28" s="303" t="s">
         <v>2153</v>
@@ -30706,7 +30700,7 @@
     </row>
     <row r="30" spans="1:11" s="164" customFormat="1">
       <c r="A30" s="164" t="s">
-        <v>3512</v>
+        <v>3503</v>
       </c>
       <c r="B30" s="164">
         <v>62782770</v>
@@ -30715,24 +30709,24 @@
         <v>2360</v>
       </c>
       <c r="D30" s="164" t="s">
-        <v>2880</v>
+        <v>2876</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="30" customFormat="1">
       <c r="A31" s="30" t="s">
-        <v>2908</v>
+        <v>2904</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>3032</v>
+        <v>3025</v>
       </c>
       <c r="C31" s="251" t="s">
         <v>1900</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>3033</v>
+        <v>3026</v>
       </c>
       <c r="E31" s="454" t="s">
-        <v>2955</v>
+        <v>2949</v>
       </c>
       <c r="F31" s="30" t="s">
         <v>2028</v>
@@ -30741,21 +30735,21 @@
         <v>198</v>
       </c>
       <c r="H31" s="30" t="s">
-        <v>3034</v>
+        <v>3027</v>
       </c>
       <c r="I31" s="192" t="s">
-        <v>3146</v>
+        <v>3138</v>
       </c>
       <c r="J31" s="421" t="s">
-        <v>3055</v>
+        <v>3048</v>
       </c>
       <c r="K31" s="30" t="s">
-        <v>3565</v>
+        <v>3556</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="163" customFormat="1">
       <c r="A32" s="163" t="s">
-        <v>2931</v>
+        <v>2925</v>
       </c>
       <c r="B32" s="163">
         <v>63487773</v>
@@ -30796,7 +30790,7 @@
         <v>2090</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>3566</v>
+        <v>3557</v>
       </c>
       <c r="F34" s="30" t="s">
         <v>2081</v>
@@ -30807,7 +30801,7 @@
     </row>
     <row r="35" spans="1:11" s="148" customFormat="1">
       <c r="A35" s="148" t="s">
-        <v>2983</v>
+        <v>2976</v>
       </c>
       <c r="B35" s="148">
         <v>69692470</v>
@@ -30816,7 +30810,7 @@
         <v>1984</v>
       </c>
       <c r="D35" s="148" t="s">
-        <v>3616</v>
+        <v>3607</v>
       </c>
       <c r="E35" s="148" t="s">
         <v>1986</v>
@@ -30847,10 +30841,10 @@
         <v>2005</v>
       </c>
       <c r="D37" s="30" t="s">
-        <v>3170</v>
+        <v>3162</v>
       </c>
       <c r="E37" s="459" t="s">
-        <v>3666</v>
+        <v>3657</v>
       </c>
       <c r="F37" s="30" t="s">
         <v>2071</v>
@@ -30858,22 +30852,22 @@
       <c r="G37" s="30" t="s">
         <v>198</v>
       </c>
-      <c r="H37" s="217" t="s">
-        <v>2872</v>
+      <c r="H37" s="145" t="s">
+        <v>3667</v>
       </c>
       <c r="I37" s="30" t="s">
-        <v>3202</v>
+        <v>3194</v>
       </c>
       <c r="J37" s="30" t="s">
-        <v>3533</v>
+        <v>3524</v>
       </c>
       <c r="K37" s="30" t="s">
-        <v>3396</v>
+        <v>3387</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="147" customFormat="1">
       <c r="A38" s="147" t="s">
-        <v>2908</v>
+        <v>2904</v>
       </c>
       <c r="B38" s="147" t="s">
         <v>2657</v>
@@ -30905,16 +30899,16 @@
         <v>2489</v>
       </c>
       <c r="B40" s="32" t="s">
-        <v>3180</v>
+        <v>3172</v>
       </c>
       <c r="C40" s="251" t="s">
         <v>1662</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>3508</v>
+        <v>3499</v>
       </c>
       <c r="E40" s="30" t="s">
-        <v>3566</v>
+        <v>3557</v>
       </c>
       <c r="F40" s="30" t="s">
         <v>2086</v>
@@ -30923,21 +30917,21 @@
         <v>198</v>
       </c>
       <c r="H40" s="30" t="s">
-        <v>3663</v>
+        <v>3654</v>
       </c>
       <c r="I40" s="32" t="s">
-        <v>3136</v>
+        <v>3128</v>
       </c>
       <c r="J40" s="32" t="s">
-        <v>3166</v>
+        <v>3158</v>
       </c>
       <c r="K40" s="145" t="s">
-        <v>3509</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="163" customFormat="1">
       <c r="A41" s="163" t="s">
-        <v>3649</v>
+        <v>3640</v>
       </c>
       <c r="B41" s="163">
         <v>68381893</v>
@@ -30969,7 +30963,7 @@
     </row>
     <row r="43" spans="1:11" s="30" customFormat="1">
       <c r="A43" s="30" t="s">
-        <v>3157</v>
+        <v>3149</v>
       </c>
       <c r="B43" s="30">
         <v>60389752</v>
@@ -30981,7 +30975,7 @@
         <v>2032</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>3001</v>
+        <v>2994</v>
       </c>
       <c r="F43" s="30" t="s">
         <v>2118</v>
@@ -30992,7 +30986,7 @@
     </row>
     <row r="44" spans="1:11" s="164" customFormat="1">
       <c r="A44" s="164" t="s">
-        <v>3649</v>
+        <v>3640</v>
       </c>
       <c r="B44" s="164">
         <v>68381893</v>
@@ -31009,7 +31003,7 @@
     </row>
     <row r="45" spans="1:11" s="163" customFormat="1">
       <c r="A45" s="163" t="s">
-        <v>3408</v>
+        <v>3399</v>
       </c>
       <c r="B45" s="163">
         <v>64079861</v>
@@ -31038,7 +31032,7 @@
         <v>2853</v>
       </c>
       <c r="E46" s="30" t="s">
-        <v>3368</v>
+        <v>3359</v>
       </c>
       <c r="F46" s="30" t="s">
         <v>2102</v>
@@ -31050,7 +31044,7 @@
     </row>
     <row r="47" spans="1:11" s="164" customFormat="1">
       <c r="A47" s="164" t="s">
-        <v>3153</v>
+        <v>3145</v>
       </c>
       <c r="B47" s="164">
         <v>63183787</v>
@@ -31084,16 +31078,16 @@
         <v>1498</v>
       </c>
       <c r="B49" s="30" t="s">
-        <v>3416</v>
+        <v>3407</v>
       </c>
       <c r="C49" s="134" t="s">
         <v>1996</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>3295</v>
+        <v>3286</v>
       </c>
       <c r="E49" s="30" t="s">
-        <v>3567</v>
+        <v>3558</v>
       </c>
       <c r="F49" s="30" t="s">
         <v>2089</v>
@@ -31102,16 +31096,16 @@
         <v>198</v>
       </c>
       <c r="H49" s="30" t="s">
-        <v>3134</v>
+        <v>3126</v>
       </c>
       <c r="I49" s="30" t="s">
-        <v>3189</v>
+        <v>3181</v>
       </c>
       <c r="J49" s="30" t="s">
-        <v>3619</v>
+        <v>3610</v>
       </c>
       <c r="K49" s="32" t="s">
-        <v>3294</v>
+        <v>3285</v>
       </c>
     </row>
     <row r="50" spans="1:11" s="164" customFormat="1">
@@ -31139,12 +31133,12 @@
         <v>2004</v>
       </c>
       <c r="D51" s="164" t="s">
-        <v>3098</v>
+        <v>3091</v>
       </c>
     </row>
     <row r="52" spans="1:11" s="139" customFormat="1">
       <c r="A52" s="140" t="s">
-        <v>2931</v>
+        <v>2925</v>
       </c>
       <c r="B52" s="413" t="s">
         <v>1440</v>
@@ -31153,10 +31147,10 @@
         <v>1364</v>
       </c>
       <c r="D52" s="139" t="s">
-        <v>2867</v>
+        <v>2865</v>
       </c>
       <c r="E52" s="139" t="s">
-        <v>3566</v>
+        <v>3557</v>
       </c>
       <c r="F52" s="139" t="s">
         <v>2087</v>
@@ -31165,16 +31159,16 @@
         <v>198</v>
       </c>
       <c r="H52" s="140" t="s">
-        <v>3599</v>
+        <v>3590</v>
       </c>
       <c r="I52" s="140" t="s">
-        <v>3390</v>
+        <v>3381</v>
       </c>
       <c r="J52" s="30" t="s">
-        <v>3264</v>
+        <v>3255</v>
       </c>
       <c r="K52" s="269" t="s">
-        <v>3021</v>
+        <v>3014</v>
       </c>
     </row>
     <row r="53" spans="1:11" s="164" customFormat="1">
@@ -31215,7 +31209,7 @@
     </row>
     <row r="55" spans="1:11" s="30" customFormat="1">
       <c r="A55" s="30" t="s">
-        <v>3516</v>
+        <v>3507</v>
       </c>
       <c r="B55" s="30">
         <v>61130088</v>
@@ -31227,7 +31221,7 @@
         <v>2000</v>
       </c>
       <c r="E55" s="30" t="s">
-        <v>3150</v>
+        <v>3142</v>
       </c>
       <c r="F55" s="30" t="s">
         <v>2103</v>
@@ -31244,10 +31238,10 @@
         <v>60433915</v>
       </c>
       <c r="C56" s="400" t="s">
-        <v>3161</v>
+        <v>3153</v>
       </c>
       <c r="D56" s="370" t="s">
-        <v>3163</v>
+        <v>3155</v>
       </c>
       <c r="E56" s="164"/>
     </row>
@@ -31256,19 +31250,19 @@
         <v>2489</v>
       </c>
       <c r="B57" s="163" t="s">
-        <v>3167</v>
+        <v>3159</v>
       </c>
       <c r="C57" s="400" t="s">
-        <v>3162</v>
+        <v>3154</v>
       </c>
       <c r="D57" s="370" t="s">
-        <v>3164</v>
+        <v>3156</v>
       </c>
       <c r="E57" s="164"/>
     </row>
     <row r="58" spans="1:11" s="30" customFormat="1">
       <c r="A58" s="459" t="s">
-        <v>3153</v>
+        <v>3145</v>
       </c>
       <c r="B58" s="412" t="s">
         <v>2069</v>
@@ -31280,7 +31274,7 @@
         <v>2798</v>
       </c>
       <c r="E58" s="30" t="s">
-        <v>3222</v>
+        <v>3214</v>
       </c>
       <c r="F58" s="30" t="s">
         <v>2115</v>
@@ -31289,16 +31283,16 @@
         <v>198</v>
       </c>
       <c r="H58" s="30" t="s">
-        <v>3313</v>
+        <v>3304</v>
       </c>
       <c r="I58" s="30" t="s">
-        <v>3178</v>
+        <v>3170</v>
       </c>
       <c r="J58" s="30" t="s">
-        <v>3268</v>
+        <v>3259</v>
       </c>
       <c r="K58" s="30" t="s">
-        <v>3587</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="59" spans="1:11" s="388" customFormat="1">
@@ -31313,7 +31307,7 @@
         <v>158</v>
       </c>
       <c r="B61" s="30" t="s">
-        <v>3154</v>
+        <v>3146</v>
       </c>
       <c r="C61" s="134" t="s">
         <v>2070</v>
@@ -31322,7 +31316,7 @@
         <v>2856</v>
       </c>
       <c r="E61" s="30" t="s">
-        <v>3062</v>
+        <v>3055</v>
       </c>
       <c r="F61" s="30" t="s">
         <v>2071</v>
@@ -31331,21 +31325,21 @@
         <v>198</v>
       </c>
       <c r="H61" s="30" t="s">
-        <v>3435</v>
+        <v>3426</v>
       </c>
       <c r="I61" s="30" t="s">
-        <v>3196</v>
+        <v>3188</v>
       </c>
       <c r="J61" s="30" t="s">
-        <v>3302</v>
+        <v>3293</v>
       </c>
       <c r="K61" s="30" t="s">
-        <v>3393</v>
+        <v>3384</v>
       </c>
     </row>
     <row r="62" spans="1:11" s="147" customFormat="1">
       <c r="A62" s="147" t="s">
-        <v>3152</v>
+        <v>3144</v>
       </c>
       <c r="B62" s="147">
         <v>60196388</v>
@@ -31354,7 +31348,7 @@
         <v>1470</v>
       </c>
       <c r="D62" s="371" t="s">
-        <v>3155</v>
+        <v>3147</v>
       </c>
       <c r="E62" s="148" t="s">
         <v>1380</v>
@@ -31362,7 +31356,7 @@
     </row>
     <row r="63" spans="1:11" s="163" customFormat="1">
       <c r="A63" s="163" t="s">
-        <v>3184</v>
+        <v>3176</v>
       </c>
       <c r="B63" s="163">
         <v>62960567</v>
@@ -31371,13 +31365,13 @@
         <v>2055</v>
       </c>
       <c r="D63" s="370" t="s">
-        <v>3111</v>
+        <v>3103</v>
       </c>
       <c r="E63" s="164"/>
     </row>
     <row r="64" spans="1:11" s="30" customFormat="1">
       <c r="A64" s="32" t="s">
-        <v>3153</v>
+        <v>3145</v>
       </c>
       <c r="B64" s="32" t="s">
         <v>2122</v>
@@ -31386,10 +31380,10 @@
         <v>1661</v>
       </c>
       <c r="D64" s="30" t="s">
-        <v>3307</v>
+        <v>3298</v>
       </c>
       <c r="E64" s="30" t="s">
-        <v>3566</v>
+        <v>3557</v>
       </c>
       <c r="F64" s="30" t="s">
         <v>2088</v>
@@ -31398,16 +31392,16 @@
         <v>198</v>
       </c>
       <c r="H64" s="32" t="s">
-        <v>3406</v>
+        <v>3397</v>
       </c>
       <c r="I64" s="32" t="s">
-        <v>3473</v>
+        <v>3464</v>
       </c>
       <c r="J64" s="30" t="s">
-        <v>3357</v>
+        <v>3348</v>
       </c>
       <c r="K64" s="30" t="s">
-        <v>3179</v>
+        <v>3171</v>
       </c>
     </row>
     <row r="65" spans="1:11" s="164" customFormat="1">
@@ -31429,7 +31423,7 @@
     </row>
     <row r="66" spans="1:11" s="164" customFormat="1">
       <c r="A66" s="252" t="s">
-        <v>2983</v>
+        <v>2976</v>
       </c>
       <c r="B66" s="164">
         <v>62090364</v>
@@ -31446,7 +31440,7 @@
     </row>
     <row r="67" spans="1:11" s="30" customFormat="1">
       <c r="A67" s="253" t="s">
-        <v>3481</v>
+        <v>3472</v>
       </c>
       <c r="B67" s="284" t="s">
         <v>1908</v>
@@ -31455,10 +31449,10 @@
         <v>1665</v>
       </c>
       <c r="D67" s="30" t="s">
-        <v>2992</v>
+        <v>2985</v>
       </c>
       <c r="E67" s="30" t="s">
-        <v>3620</v>
+        <v>3611</v>
       </c>
       <c r="F67" s="30" t="s">
         <v>2092</v>
@@ -31467,21 +31461,21 @@
         <v>198</v>
       </c>
       <c r="H67" s="30" t="s">
-        <v>3389</v>
+        <v>3380</v>
       </c>
       <c r="I67" s="30" t="s">
-        <v>3461</v>
+        <v>3452</v>
       </c>
       <c r="J67" s="30" t="s">
-        <v>3507</v>
+        <v>3498</v>
       </c>
       <c r="K67" s="30" t="s">
-        <v>2999</v>
+        <v>2992</v>
       </c>
     </row>
     <row r="68" spans="1:11" s="147" customFormat="1">
       <c r="A68" s="147" t="s">
-        <v>3152</v>
+        <v>3144</v>
       </c>
       <c r="B68" s="147">
         <v>68741448</v>
@@ -31490,13 +31484,13 @@
         <v>1876</v>
       </c>
       <c r="D68" s="371" t="s">
-        <v>3132</v>
+        <v>3124</v>
       </c>
       <c r="E68" s="148"/>
     </row>
     <row r="69" spans="1:11" s="148" customFormat="1">
       <c r="A69" s="225" t="s">
-        <v>3254</v>
+        <v>3245</v>
       </c>
       <c r="B69" s="148">
         <v>63018763</v>
@@ -31505,7 +31499,7 @@
         <v>2091</v>
       </c>
       <c r="D69" s="148" t="s">
-        <v>3629</v>
+        <v>3620</v>
       </c>
     </row>
     <row r="70" spans="1:11" s="30" customFormat="1">
@@ -31513,16 +31507,16 @@
         <v>467</v>
       </c>
       <c r="B70" s="32" t="s">
-        <v>3404</v>
+        <v>3395</v>
       </c>
       <c r="C70" s="251" t="s">
         <v>1664</v>
       </c>
       <c r="D70" s="30" t="s">
-        <v>3273</v>
+        <v>3264</v>
       </c>
       <c r="E70" s="30" t="s">
-        <v>3223</v>
+        <v>3215</v>
       </c>
       <c r="F70" s="30" t="s">
         <v>2129</v>
@@ -31531,13 +31525,13 @@
         <v>198</v>
       </c>
       <c r="H70" s="32" t="s">
-        <v>3618</v>
+        <v>3609</v>
       </c>
       <c r="I70" s="217" t="s">
-        <v>3274</v>
+        <v>3265</v>
       </c>
       <c r="J70" s="432" t="s">
-        <v>3299</v>
+        <v>3290</v>
       </c>
     </row>
     <row r="71" spans="1:11" s="164" customFormat="1">
@@ -31551,12 +31545,12 @@
         <v>1962</v>
       </c>
       <c r="D71" s="164" t="s">
-        <v>2899</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="72" spans="1:11" s="163" customFormat="1">
       <c r="A72" s="268" t="s">
-        <v>3608</v>
+        <v>3599</v>
       </c>
       <c r="B72" s="268" t="s">
         <v>1452</v>
@@ -31571,7 +31565,7 @@
     </row>
     <row r="73" spans="1:11" s="30" customFormat="1">
       <c r="A73" s="30" t="s">
-        <v>3309</v>
+        <v>3300</v>
       </c>
       <c r="B73" s="30">
         <v>60389752</v>
@@ -31583,7 +31577,7 @@
         <v>2809</v>
       </c>
       <c r="E73" s="30" t="s">
-        <v>3409</v>
+        <v>3400</v>
       </c>
       <c r="F73" s="30" t="s">
         <v>2027</v>
@@ -31594,7 +31588,7 @@
     </row>
     <row r="74" spans="1:11" s="147" customFormat="1">
       <c r="A74" s="147" t="s">
-        <v>3612</v>
+        <v>3603</v>
       </c>
       <c r="B74" s="147">
         <v>64226974</v>
@@ -31618,7 +31612,7 @@
         <v>1946</v>
       </c>
       <c r="D75" s="148" t="s">
-        <v>3204</v>
+        <v>3196</v>
       </c>
       <c r="E75" s="148"/>
     </row>
@@ -31633,10 +31627,10 @@
         <v>1875</v>
       </c>
       <c r="D76" s="30" t="s">
-        <v>2951</v>
+        <v>2945</v>
       </c>
       <c r="E76" s="30" t="s">
-        <v>3104</v>
+        <v>3097</v>
       </c>
       <c r="F76" s="30" t="s">
         <v>2102</v>
@@ -31645,16 +31639,16 @@
         <v>198</v>
       </c>
       <c r="H76" s="30" t="s">
-        <v>3568</v>
+        <v>3559</v>
       </c>
       <c r="I76" s="30" t="s">
-        <v>3617</v>
+        <v>3608</v>
       </c>
       <c r="J76" s="30" t="s">
-        <v>3210</v>
+        <v>3202</v>
       </c>
       <c r="K76" s="217" t="s">
-        <v>3275</v>
+        <v>3266</v>
       </c>
     </row>
     <row r="77" spans="1:11" s="152" customFormat="1">
@@ -31670,16 +31664,16 @@
         <v>143</v>
       </c>
       <c r="B79" s="30" t="s">
-        <v>2920</v>
+        <v>2915</v>
       </c>
       <c r="C79" s="134" t="s">
         <v>2003</v>
       </c>
       <c r="D79" s="30" t="s">
-        <v>2975</v>
+        <v>2968</v>
       </c>
       <c r="E79" s="459" t="s">
-        <v>3665</v>
+        <v>3656</v>
       </c>
       <c r="F79" s="30" t="s">
         <v>2082</v>
@@ -31688,21 +31682,21 @@
         <v>198</v>
       </c>
       <c r="H79" s="432" t="s">
-        <v>2989</v>
+        <v>2982</v>
       </c>
       <c r="I79" s="32" t="s">
-        <v>3175</v>
+        <v>3167</v>
       </c>
       <c r="J79" s="30" t="s">
-        <v>3524</v>
+        <v>3515</v>
       </c>
       <c r="K79" s="30" t="s">
-        <v>3212</v>
+        <v>3204</v>
       </c>
     </row>
     <row r="80" spans="1:11" s="147" customFormat="1">
       <c r="A80" s="149" t="s">
-        <v>2931</v>
+        <v>2925</v>
       </c>
       <c r="B80" s="147">
         <v>60533053</v>
@@ -31717,7 +31711,7 @@
     </row>
     <row r="81" spans="1:11" s="147" customFormat="1">
       <c r="A81" s="149" t="s">
-        <v>3153</v>
+        <v>3145</v>
       </c>
       <c r="B81" s="147">
         <v>64720128</v>
@@ -31734,10 +31728,10 @@
     </row>
     <row r="82" spans="1:11" s="30" customFormat="1">
       <c r="A82" s="145" t="s">
-        <v>3612</v>
+        <v>3603</v>
       </c>
       <c r="B82" s="30" t="s">
-        <v>3669</v>
+        <v>3660</v>
       </c>
       <c r="C82" s="22" t="s">
         <v>1901</v>
@@ -31746,7 +31740,7 @@
         <v>2838</v>
       </c>
       <c r="E82" s="30" t="s">
-        <v>2948</v>
+        <v>2942</v>
       </c>
       <c r="F82" s="30" t="s">
         <v>1902</v>
@@ -31755,16 +31749,16 @@
         <v>198</v>
       </c>
       <c r="H82" s="30" t="s">
-        <v>3480</v>
+        <v>3471</v>
       </c>
       <c r="I82" s="30" t="s">
-        <v>3324</v>
+        <v>3315</v>
       </c>
       <c r="J82" s="30" t="s">
-        <v>3601</v>
+        <v>3592</v>
       </c>
       <c r="K82" s="30" t="s">
-        <v>3545</v>
+        <v>3536</v>
       </c>
     </row>
     <row r="83" spans="1:11" s="148" customFormat="1">
@@ -31772,13 +31766,13 @@
         <v>1516</v>
       </c>
       <c r="B83" s="225" t="s">
-        <v>3057</v>
+        <v>3050</v>
       </c>
       <c r="C83" s="398" t="s">
         <v>1959</v>
       </c>
       <c r="D83" s="148" t="s">
-        <v>3667</v>
+        <v>3658</v>
       </c>
     </row>
     <row r="84" spans="1:11" s="280" customFormat="1">
@@ -31806,7 +31800,7 @@
         <v>693</v>
       </c>
       <c r="D85" s="30" t="s">
-        <v>3325</v>
+        <v>3316</v>
       </c>
       <c r="E85" s="30" t="s">
         <v>1791</v>
@@ -31818,16 +31812,16 @@
         <v>493</v>
       </c>
       <c r="H85" s="30" t="s">
-        <v>3442</v>
+        <v>3433</v>
       </c>
       <c r="I85" s="432" t="s">
-        <v>2885</v>
+        <v>2881</v>
       </c>
       <c r="J85" s="30" t="s">
-        <v>3462</v>
+        <v>3453</v>
       </c>
       <c r="K85" s="215" t="s">
-        <v>3643</v>
+        <v>3634</v>
       </c>
     </row>
     <row r="86" spans="1:11" s="147" customFormat="1">
@@ -31850,7 +31844,7 @@
     </row>
     <row r="87" spans="1:11" s="147" customFormat="1">
       <c r="A87" s="147" t="s">
-        <v>3157</v>
+        <v>3149</v>
       </c>
       <c r="B87" s="147" t="s">
         <v>909</v>
@@ -31868,16 +31862,16 @@
     </row>
     <row r="88" spans="1:11" s="30" customFormat="1">
       <c r="A88" s="145" t="s">
-        <v>3512</v>
+        <v>3503</v>
       </c>
       <c r="B88" s="30" t="s">
-        <v>3535</v>
+        <v>3526</v>
       </c>
       <c r="C88" s="153" t="s">
         <v>694</v>
       </c>
       <c r="D88" s="30" t="s">
-        <v>2941</v>
+        <v>2935</v>
       </c>
       <c r="E88" s="30" t="s">
         <v>1085</v>
@@ -31889,21 +31883,21 @@
         <v>1524</v>
       </c>
       <c r="H88" s="217" t="s">
-        <v>2942</v>
+        <v>2936</v>
       </c>
       <c r="I88" s="217" t="s">
-        <v>2962</v>
+        <v>2955</v>
       </c>
       <c r="J88" s="32" t="s">
-        <v>3036</v>
+        <v>3029</v>
       </c>
       <c r="K88" s="30" t="s">
-        <v>3035</v>
+        <v>3028</v>
       </c>
     </row>
     <row r="89" spans="1:11" s="147" customFormat="1">
       <c r="A89" s="149" t="s">
-        <v>2983</v>
+        <v>2976</v>
       </c>
       <c r="B89" s="147">
         <v>64844119</v>
@@ -31921,7 +31915,7 @@
     </row>
     <row r="90" spans="1:11" s="148" customFormat="1">
       <c r="A90" s="225" t="s">
-        <v>3157</v>
+        <v>3149</v>
       </c>
       <c r="B90" s="148">
         <v>67381873</v>
@@ -31939,7 +31933,7 @@
     </row>
     <row r="91" spans="1:11" s="106" customFormat="1">
       <c r="A91" s="249" t="s">
-        <v>3608</v>
+        <v>3599</v>
       </c>
       <c r="B91" s="32" t="s">
         <v>1400</v>
@@ -31948,7 +31942,7 @@
         <v>46</v>
       </c>
       <c r="D91" s="106" t="s">
-        <v>3182</v>
+        <v>3174</v>
       </c>
       <c r="E91" s="106" t="s">
         <v>1123</v>
@@ -31960,16 +31954,16 @@
         <v>66</v>
       </c>
       <c r="H91" s="30" t="s">
-        <v>3183</v>
+        <v>3175</v>
       </c>
       <c r="I91" s="31" t="s">
-        <v>2921</v>
+        <v>2916</v>
       </c>
       <c r="J91" s="32" t="s">
-        <v>3020</v>
+        <v>3013</v>
       </c>
       <c r="K91" s="30" t="s">
-        <v>3300</v>
+        <v>3291</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="406" customFormat="1">
@@ -32000,7 +31994,7 @@
         <v>1718</v>
       </c>
       <c r="D93" s="148" t="s">
-        <v>3279</v>
+        <v>3270</v>
       </c>
     </row>
     <row r="94" spans="1:11" s="32" customFormat="1">
@@ -32017,7 +32011,7 @@
         <v>1362</v>
       </c>
       <c r="E94" s="32" t="s">
-        <v>3447</v>
+        <v>3438</v>
       </c>
       <c r="F94" s="32" t="s">
         <v>1363</v>
@@ -32029,7 +32023,7 @@
     </row>
     <row r="95" spans="1:11" s="148" customFormat="1">
       <c r="A95" s="148" t="s">
-        <v>3521</v>
+        <v>3512</v>
       </c>
       <c r="B95" s="148" t="s">
         <v>2648</v>
@@ -32046,7 +32040,7 @@
     </row>
     <row r="96" spans="1:11" s="148" customFormat="1">
       <c r="A96" s="148" t="s">
-        <v>3512</v>
+        <v>3503</v>
       </c>
       <c r="B96" s="148">
         <v>65633205</v>
@@ -32055,7 +32049,7 @@
         <v>1379</v>
       </c>
       <c r="D96" s="148" t="s">
-        <v>3536</v>
+        <v>3527</v>
       </c>
       <c r="E96" s="148" t="s">
         <v>1378</v>
@@ -32066,16 +32060,16 @@
         <v>1419</v>
       </c>
       <c r="B97" s="30" t="s">
-        <v>2919</v>
+        <v>2914</v>
       </c>
       <c r="C97" s="153" t="s">
         <v>1993</v>
       </c>
       <c r="D97" s="30" t="s">
-        <v>2918</v>
+        <v>2913</v>
       </c>
       <c r="E97" s="30" t="s">
-        <v>2948</v>
+        <v>2942</v>
       </c>
       <c r="F97" s="30" t="s">
         <v>1902</v>
@@ -32084,16 +32078,16 @@
         <v>198</v>
       </c>
       <c r="H97" s="32" t="s">
-        <v>3487</v>
+        <v>3478</v>
       </c>
       <c r="I97" s="30" t="s">
-        <v>3647</v>
+        <v>3638</v>
       </c>
       <c r="J97" s="30" t="s">
-        <v>3347</v>
+        <v>3338</v>
       </c>
       <c r="K97" s="430" t="s">
-        <v>3510</v>
+        <v>3501</v>
       </c>
     </row>
     <row r="98" spans="1:13" s="388" customFormat="1">
@@ -32106,19 +32100,19 @@
     </row>
     <row r="100" spans="1:13" s="30" customFormat="1">
       <c r="A100" s="30" t="s">
-        <v>3254</v>
+        <v>3245</v>
       </c>
       <c r="B100" s="30" t="s">
-        <v>3660</v>
+        <v>3651</v>
       </c>
       <c r="C100" s="251" t="s">
         <v>2837</v>
       </c>
       <c r="D100" s="30" t="s">
-        <v>3350</v>
+        <v>3341</v>
       </c>
       <c r="E100" s="30" t="s">
-        <v>3106</v>
+        <v>3099</v>
       </c>
       <c r="F100" s="30" t="s">
         <v>1902</v>
@@ -32127,16 +32121,16 @@
         <v>198</v>
       </c>
       <c r="H100" s="30" t="s">
-        <v>3482</v>
+        <v>3473</v>
       </c>
       <c r="I100" s="30" t="s">
-        <v>3637</v>
+        <v>3628</v>
       </c>
       <c r="J100" s="30" t="s">
-        <v>3515</v>
+        <v>3506</v>
       </c>
       <c r="K100" s="30" t="s">
-        <v>3571</v>
+        <v>3562</v>
       </c>
     </row>
     <row r="101" spans="1:13" s="388" customFormat="1">
@@ -32149,19 +32143,19 @@
     </row>
     <row r="103" spans="1:13" s="30" customFormat="1">
       <c r="A103" s="30" t="s">
-        <v>3157</v>
+        <v>3149</v>
       </c>
       <c r="B103" s="30" t="s">
-        <v>3276</v>
+        <v>3267</v>
       </c>
       <c r="C103" s="251" t="s">
-        <v>2883</v>
+        <v>2879</v>
       </c>
       <c r="D103" s="30" t="s">
-        <v>3197</v>
+        <v>3189</v>
       </c>
       <c r="E103" s="30" t="s">
-        <v>3198</v>
+        <v>3190</v>
       </c>
       <c r="F103" s="30" t="s">
         <v>1902</v>
@@ -32170,16 +32164,16 @@
         <v>198</v>
       </c>
       <c r="H103" s="30" t="s">
-        <v>3199</v>
+        <v>3191</v>
       </c>
       <c r="I103" s="30" t="s">
-        <v>3277</v>
+        <v>3268</v>
       </c>
       <c r="J103" s="30" t="s">
-        <v>3263</v>
+        <v>3254</v>
       </c>
       <c r="K103" s="30" t="s">
-        <v>3225</v>
+        <v>3217</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -32214,22 +32208,22 @@
     </row>
     <row r="106" spans="1:13" s="30" customFormat="1">
       <c r="A106" s="30" t="s">
-        <v>2908</v>
+        <v>2904</v>
       </c>
       <c r="B106" s="30">
         <v>62724019</v>
       </c>
       <c r="C106" s="251" t="s">
-        <v>2882</v>
+        <v>2878</v>
       </c>
       <c r="D106" s="30" t="s">
-        <v>3040</v>
+        <v>3033</v>
       </c>
       <c r="E106" s="30" t="s">
-        <v>3042</v>
+        <v>3035</v>
       </c>
       <c r="F106" s="30" t="s">
-        <v>3041</v>
+        <v>3034</v>
       </c>
       <c r="G106" s="30" t="s">
         <v>59</v>
@@ -32281,7 +32275,7 @@
         <v>1982</v>
       </c>
       <c r="E127" s="30" t="s">
-        <v>3126</v>
+        <v>3118</v>
       </c>
       <c r="F127" t="s">
         <v>1980</v>
@@ -32301,7 +32295,7 @@
         <v>1952</v>
       </c>
       <c r="E128" s="30" t="s">
-        <v>3126</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -32315,15 +32309,15 @@
         <v>2719</v>
       </c>
       <c r="D129" s="373" t="s">
-        <v>3194</v>
+        <v>3186</v>
       </c>
       <c r="E129" s="30" t="s">
-        <v>3126</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="4" t="s">
-        <v>3153</v>
+        <v>3145</v>
       </c>
       <c r="B130">
         <v>67046608</v>
@@ -32335,7 +32329,7 @@
         <v>2596</v>
       </c>
       <c r="E130" s="30" t="s">
-        <v>3126</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -32352,7 +32346,7 @@
         <v>1958</v>
       </c>
       <c r="E131" s="30" t="s">
-        <v>3126</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="133" spans="1:6" s="121" customFormat="1" ht="23.5">
@@ -32374,7 +32368,7 @@
         <v>2347</v>
       </c>
       <c r="E134" s="30" t="s">
-        <v>3143</v>
+        <v>3135</v>
       </c>
       <c r="F134" t="s">
         <v>1339</v>
@@ -32394,7 +32388,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>3516</v>
+        <v>3507</v>
       </c>
       <c r="B139">
         <v>64720128</v>
@@ -32423,7 +32417,7 @@
         <v>1969</v>
       </c>
       <c r="D140" s="373" t="s">
-        <v>3168</v>
+        <v>3160</v>
       </c>
       <c r="E140" s="30" t="s">
         <v>1968</v>
@@ -32454,7 +32448,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="C143" s="1" t="s">
-        <v>3207</v>
+        <v>3199</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -32498,7 +32492,7 @@
         <v>2352</v>
       </c>
       <c r="E153" s="30" t="s">
-        <v>3127</v>
+        <v>3119</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -32506,21 +32500,21 @@
         <v>1498</v>
       </c>
       <c r="B154" t="s">
-        <v>3375</v>
+        <v>3366</v>
       </c>
       <c r="C154" t="s">
         <v>2225</v>
       </c>
       <c r="D154" s="373" t="s">
-        <v>3374</v>
+        <v>3365</v>
       </c>
       <c r="E154" s="30" t="s">
-        <v>3127</v>
+        <v>3119</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" t="s">
-        <v>3153</v>
+        <v>3145</v>
       </c>
       <c r="B155">
         <v>60183566</v>
@@ -32532,24 +32526,24 @@
         <v>2597</v>
       </c>
       <c r="E155" s="30" t="s">
-        <v>3239</v>
+        <v>3231</v>
       </c>
     </row>
     <row r="156" spans="1:5">
-      <c r="A156" s="49" t="s">
-        <v>2789</v>
-      </c>
-      <c r="B156">
-        <v>62491046</v>
+      <c r="A156" s="97" t="s">
+        <v>3603</v>
+      </c>
+      <c r="B156" t="s">
+        <v>1164</v>
       </c>
       <c r="C156" t="s">
         <v>2235</v>
       </c>
       <c r="D156" s="373" t="s">
-        <v>2956</v>
+        <v>3661</v>
       </c>
       <c r="E156" s="30" t="s">
-        <v>3239</v>
+        <v>3231</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -32566,7 +32560,7 @@
         <v>2490</v>
       </c>
       <c r="E157" s="30" t="s">
-        <v>3239</v>
+        <v>3231</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -32583,7 +32577,7 @@
         <v>2637</v>
       </c>
       <c r="E158" s="30" t="s">
-        <v>3239</v>
+        <v>3231</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -32597,15 +32591,15 @@
         <v>2510</v>
       </c>
       <c r="D159" s="373" t="s">
-        <v>3377</v>
+        <v>3368</v>
       </c>
       <c r="E159" s="30" t="s">
-        <v>3239</v>
+        <v>3231</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" t="s">
-        <v>3301</v>
+        <v>3292</v>
       </c>
       <c r="B160">
         <v>65133588</v>
@@ -32617,12 +32611,12 @@
         <v>2511</v>
       </c>
       <c r="E160" s="30" t="s">
-        <v>3239</v>
+        <v>3231</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="4" t="s">
-        <v>3184</v>
+        <v>3176</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>1137</v>
@@ -32631,10 +32625,10 @@
         <v>2598</v>
       </c>
       <c r="D161" s="373" t="s">
-        <v>3070</v>
+        <v>3063</v>
       </c>
       <c r="E161" s="30" t="s">
-        <v>3239</v>
+        <v>3231</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -32648,32 +32642,32 @@
         <v>2513</v>
       </c>
       <c r="D162" s="373" t="s">
-        <v>3191</v>
+        <v>3183</v>
       </c>
       <c r="E162" s="30" t="s">
-        <v>3239</v>
+        <v>3231</v>
       </c>
     </row>
     <row r="163" spans="1:5">
-      <c r="A163" s="49" t="s">
-        <v>143</v>
-      </c>
-      <c r="B163">
-        <v>12369714760</v>
-      </c>
-      <c r="C163" t="s">
-        <v>2911</v>
+      <c r="A163" s="97" t="s">
+        <v>3603</v>
+      </c>
+      <c r="B163" s="460" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C163" s="460" t="s">
+        <v>3664</v>
       </c>
       <c r="D163" s="373" t="s">
-        <v>2922</v>
+        <v>3665</v>
       </c>
       <c r="E163" s="30" t="s">
-        <v>3239</v>
+        <v>3231</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="4" t="s">
-        <v>3153</v>
+        <v>3145</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>2168</v>
@@ -32685,12 +32679,12 @@
         <v>2491</v>
       </c>
       <c r="E164" s="30" t="s">
-        <v>3460</v>
+        <v>3451</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>3424</v>
+        <v>3415</v>
       </c>
       <c r="B165">
         <v>66315726</v>
@@ -32702,12 +32696,12 @@
         <v>2273</v>
       </c>
       <c r="E165" s="30" t="s">
-        <v>3460</v>
+        <v>3451</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" t="s">
-        <v>3254</v>
+        <v>3245</v>
       </c>
       <c r="B166">
         <v>64568369</v>
@@ -32719,24 +32713,24 @@
         <v>2273</v>
       </c>
       <c r="E166" s="30" t="s">
-        <v>3460</v>
+        <v>3451</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>3424</v>
+        <v>3415</v>
       </c>
       <c r="B167">
         <v>68818154</v>
       </c>
       <c r="C167" t="s">
-        <v>3378</v>
+        <v>3369</v>
       </c>
       <c r="D167" s="373" t="s">
         <v>2599</v>
       </c>
       <c r="E167" s="30" t="s">
-        <v>3460</v>
+        <v>3451</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -32750,10 +32744,10 @@
         <v>2721</v>
       </c>
       <c r="D168" s="373" t="s">
-        <v>3226</v>
+        <v>3218</v>
       </c>
       <c r="E168" s="30" t="s">
-        <v>3030</v>
+        <v>3023</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -32770,7 +32764,7 @@
         <v>2757</v>
       </c>
       <c r="E169" s="30" t="s">
-        <v>3030</v>
+        <v>3023</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -32787,7 +32781,7 @@
         <v>2488</v>
       </c>
       <c r="E170" s="30" t="s">
-        <v>3030</v>
+        <v>3023</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -32804,12 +32798,12 @@
         <v>2312</v>
       </c>
       <c r="E171" s="30" t="s">
-        <v>3030</v>
+        <v>3023</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" t="s">
-        <v>2908</v>
+        <v>2904</v>
       </c>
       <c r="B172">
         <v>66935922</v>
@@ -32818,10 +32812,10 @@
         <v>2324</v>
       </c>
       <c r="D172" s="373" t="s">
-        <v>3280</v>
+        <v>3271</v>
       </c>
       <c r="E172" s="30" t="s">
-        <v>3069</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -32835,10 +32829,10 @@
         <v>2325</v>
       </c>
       <c r="D173" s="373" t="s">
-        <v>3205</v>
+        <v>3197</v>
       </c>
       <c r="E173" s="30" t="s">
-        <v>3069</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -32852,32 +32846,29 @@
         <v>2326</v>
       </c>
       <c r="D174" s="373" t="s">
-        <v>3235</v>
+        <v>3227</v>
       </c>
       <c r="E174" s="30" t="s">
-        <v>3069</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="175" spans="1:5">
-      <c r="A175" s="49" t="s">
-        <v>147</v>
-      </c>
-      <c r="B175">
-        <v>67178677</v>
+      <c r="A175" s="97" t="s">
+        <v>1164</v>
       </c>
       <c r="C175" t="s">
         <v>2759</v>
       </c>
       <c r="D175" s="373" t="s">
-        <v>3247</v>
+        <v>3662</v>
       </c>
       <c r="E175" s="30" t="s">
-        <v>3143</v>
+        <v>3135</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" t="s">
-        <v>3301</v>
+        <v>3292</v>
       </c>
       <c r="B176">
         <v>66935922</v>
@@ -32886,27 +32877,27 @@
         <v>2760</v>
       </c>
       <c r="D176" s="220" t="s">
-        <v>3281</v>
+        <v>3272</v>
       </c>
       <c r="E176" s="30" t="s">
-        <v>3143</v>
+        <v>3135</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" t="s">
-        <v>3153</v>
+        <v>3145</v>
       </c>
       <c r="B177">
         <v>64455322</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>3192</v>
+        <v>3184</v>
       </c>
       <c r="D177" s="220" t="s">
-        <v>3562</v>
+        <v>3553</v>
       </c>
       <c r="E177" s="30" t="s">
-        <v>3143</v>
+        <v>3135</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -32923,12 +32914,12 @@
         <v>2779</v>
       </c>
       <c r="E178" s="30" t="s">
-        <v>3143</v>
+        <v>3135</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" t="s">
-        <v>3184</v>
+        <v>3176</v>
       </c>
       <c r="B179">
         <v>68570552</v>
@@ -32937,15 +32928,15 @@
         <v>2762</v>
       </c>
       <c r="D179" s="220" t="s">
-        <v>3282</v>
+        <v>3273</v>
       </c>
       <c r="E179" s="30" t="s">
-        <v>3143</v>
+        <v>3135</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" t="s">
-        <v>3184</v>
+        <v>3176</v>
       </c>
       <c r="B180">
         <v>69964218</v>
@@ -32954,15 +32945,15 @@
         <v>2784</v>
       </c>
       <c r="D180" s="373" t="s">
-        <v>3283</v>
+        <v>3274</v>
       </c>
       <c r="E180" s="30" t="s">
-        <v>3195</v>
+        <v>3187</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" t="s">
-        <v>3157</v>
+        <v>3149</v>
       </c>
       <c r="B181">
         <v>63950696</v>
@@ -32974,12 +32965,12 @@
         <v>2785</v>
       </c>
       <c r="E181" s="30" t="s">
-        <v>3195</v>
+        <v>3187</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="4" t="s">
-        <v>3157</v>
+        <v>3149</v>
       </c>
       <c r="B182" t="s">
         <v>2814</v>
@@ -32991,7 +32982,7 @@
         <v>2785</v>
       </c>
       <c r="E182" s="30" t="s">
-        <v>3195</v>
+        <v>3187</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -33008,12 +32999,12 @@
         <v>2860</v>
       </c>
       <c r="E183" s="30" t="s">
-        <v>3195</v>
+        <v>3187</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" t="s">
-        <v>3153</v>
+        <v>3145</v>
       </c>
       <c r="B184">
         <v>63755362</v>
@@ -33022,32 +33013,32 @@
         <v>2849</v>
       </c>
       <c r="D184" s="373" t="s">
-        <v>3606</v>
+        <v>3597</v>
       </c>
       <c r="E184" s="30" t="s">
-        <v>3195</v>
+        <v>3187</v>
       </c>
     </row>
     <row r="185" spans="1:5">
-      <c r="A185" s="49" t="s">
-        <v>2875</v>
-      </c>
-      <c r="B185">
-        <v>68201775</v>
+      <c r="A185" s="97" t="s">
+        <v>3603</v>
+      </c>
+      <c r="B185" t="s">
+        <v>1164</v>
       </c>
       <c r="C185" t="s">
         <v>2819</v>
       </c>
       <c r="D185" s="373" t="s">
-        <v>2863</v>
+        <v>3663</v>
       </c>
       <c r="E185" s="30" t="s">
-        <v>3271</v>
+        <v>3262</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" t="s">
-        <v>3477</v>
+        <v>3468</v>
       </c>
       <c r="B186">
         <v>60240509</v>
@@ -33056,10 +33047,10 @@
         <v>2820</v>
       </c>
       <c r="D186" s="373" t="s">
-        <v>3475</v>
+        <v>3466</v>
       </c>
       <c r="E186" s="30" t="s">
-        <v>3476</v>
+        <v>3467</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -33073,10 +33064,10 @@
         <v>2821</v>
       </c>
       <c r="D187" s="373" t="s">
-        <v>3411</v>
+        <v>3402</v>
       </c>
       <c r="E187" s="30" t="s">
-        <v>3271</v>
+        <v>3262</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -33093,7 +33084,7 @@
         <v>2828</v>
       </c>
       <c r="E188" s="30" t="s">
-        <v>3271</v>
+        <v>3262</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -33110,7 +33101,7 @@
         <v>2828</v>
       </c>
       <c r="E189" s="30" t="s">
-        <v>3271</v>
+        <v>3262</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -33127,12 +33118,12 @@
         <v>2828</v>
       </c>
       <c r="E190" s="30" t="s">
-        <v>3271</v>
+        <v>3262</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="4" t="s">
-        <v>3157</v>
+        <v>3149</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>1857</v>
@@ -33144,29 +33135,29 @@
         <v>2828</v>
       </c>
       <c r="E191" s="30" t="s">
-        <v>3271</v>
+        <v>3262</v>
       </c>
     </row>
     <row r="192" spans="1:5">
-      <c r="A192" s="49" t="s">
-        <v>3109</v>
-      </c>
-      <c r="B192">
-        <v>64046277</v>
+      <c r="A192" s="97" t="s">
+        <v>3603</v>
+      </c>
+      <c r="B192" t="s">
+        <v>1164</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>2861</v>
       </c>
       <c r="D192" s="373" t="s">
-        <v>2862</v>
+        <v>3666</v>
       </c>
       <c r="E192" s="30" t="s">
-        <v>3271</v>
+        <v>3262</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" t="s">
-        <v>3254</v>
+        <v>3245</v>
       </c>
       <c r="B193">
         <v>69575383</v>
@@ -33175,10 +33166,10 @@
         <v>2826</v>
       </c>
       <c r="D193" s="373" t="s">
-        <v>3639</v>
+        <v>3630</v>
       </c>
       <c r="E193" s="30" t="s">
-        <v>3271</v>
+        <v>3262</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -33195,18 +33186,18 @@
         <v>2828</v>
       </c>
       <c r="E194" s="30" t="s">
-        <v>3271</v>
+        <v>3262</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="C195" s="56" t="s">
-        <v>3219</v>
+        <v>3211</v>
       </c>
       <c r="D195" t="s">
-        <v>3399</v>
+        <v>3390</v>
       </c>
       <c r="E195" s="30" t="s">
-        <v>3127</v>
+        <v>3119</v>
       </c>
     </row>
     <row r="197" spans="1:5" s="391" customFormat="1" ht="23.5">
@@ -33228,49 +33219,49 @@
         <v>2850</v>
       </c>
       <c r="D198" s="373" t="s">
-        <v>3410</v>
+        <v>3401</v>
       </c>
       <c r="E198" s="30" t="s">
-        <v>3258</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" t="s">
-        <v>3470</v>
+        <v>3461</v>
       </c>
       <c r="B199" t="s">
-        <v>3471</v>
+        <v>3462</v>
       </c>
       <c r="C199" t="s">
         <v>2843</v>
       </c>
       <c r="D199" s="373" t="s">
-        <v>3469</v>
+        <v>3460</v>
       </c>
       <c r="E199" s="30" t="s">
-        <v>3258</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" t="s">
-        <v>3184</v>
+        <v>3176</v>
       </c>
       <c r="B200">
         <v>63617941</v>
       </c>
       <c r="C200" s="22" t="s">
-        <v>3284</v>
+        <v>3275</v>
       </c>
       <c r="D200" s="373" t="s">
-        <v>2906</v>
+        <v>2902</v>
       </c>
       <c r="E200" s="30" t="s">
-        <v>3258</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" t="s">
-        <v>3009</v>
+        <v>3002</v>
       </c>
       <c r="B201">
         <v>65633205</v>
@@ -33279,15 +33270,15 @@
         <v>2844</v>
       </c>
       <c r="D201" s="373" t="s">
-        <v>3008</v>
+        <v>3001</v>
       </c>
       <c r="E201" s="30" t="s">
-        <v>3258</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="202" spans="1:5">
       <c r="A202" t="s">
-        <v>3153</v>
+        <v>3145</v>
       </c>
       <c r="B202">
         <v>62279384</v>
@@ -33296,78 +33287,78 @@
         <v>2845</v>
       </c>
       <c r="D202" s="373" t="s">
-        <v>3552</v>
+        <v>3543</v>
       </c>
       <c r="E202" s="30" t="s">
-        <v>3258</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="203" spans="1:5">
       <c r="A203" t="s">
-        <v>2931</v>
+        <v>2925</v>
       </c>
       <c r="B203">
         <v>67911756</v>
       </c>
       <c r="C203" t="s">
-        <v>2905</v>
+        <v>2901</v>
       </c>
       <c r="D203" s="373" t="s">
-        <v>3576</v>
+        <v>3567</v>
       </c>
       <c r="E203" s="30" t="s">
-        <v>3258</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="30" t="s">
-        <v>3153</v>
+        <v>3145</v>
       </c>
       <c r="B204" t="s">
-        <v>3561</v>
+        <v>3552</v>
       </c>
       <c r="C204" t="s">
         <v>2846</v>
       </c>
       <c r="D204" s="373" t="s">
-        <v>3560</v>
+        <v>3551</v>
       </c>
       <c r="E204" s="30" t="s">
-        <v>3258</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="205" spans="1:5">
       <c r="A205" t="s">
-        <v>2931</v>
+        <v>2925</v>
       </c>
       <c r="B205">
         <v>64982293</v>
       </c>
       <c r="C205" t="s">
-        <v>3551</v>
+        <v>3542</v>
       </c>
       <c r="D205" s="373" t="s">
-        <v>3633</v>
+        <v>3624</v>
       </c>
       <c r="E205" s="30" t="s">
-        <v>3258</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="206" spans="1:5">
       <c r="A206" t="s">
-        <v>3153</v>
+        <v>3145</v>
       </c>
       <c r="B206" t="s">
-        <v>2914</v>
+        <v>2909</v>
       </c>
       <c r="C206" t="s">
-        <v>2910</v>
+        <v>2906</v>
       </c>
       <c r="D206" s="373" t="s">
-        <v>2912</v>
+        <v>2907</v>
       </c>
       <c r="E206" s="30" t="s">
-        <v>3258</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -33378,30 +33369,30 @@
         <v>65344753</v>
       </c>
       <c r="C207" t="s">
-        <v>2913</v>
+        <v>2908</v>
       </c>
       <c r="D207" s="373" t="s">
-        <v>3257</v>
+        <v>3248</v>
       </c>
       <c r="E207" s="30" t="s">
-        <v>3258</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="208" spans="1:5">
       <c r="A208" t="s">
-        <v>2931</v>
+        <v>2925</v>
       </c>
       <c r="B208">
         <v>66496809</v>
       </c>
       <c r="C208" t="s">
-        <v>2928</v>
+        <v>2922</v>
       </c>
       <c r="D208" t="s">
-        <v>2930</v>
+        <v>2924</v>
       </c>
       <c r="E208" s="30" t="s">
-        <v>3530</v>
+        <v>3521</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -33412,30 +33403,30 @@
         <v>65583706</v>
       </c>
       <c r="C209" t="s">
-        <v>2957</v>
+        <v>2950</v>
       </c>
       <c r="D209" s="373" t="s">
-        <v>2959</v>
+        <v>2952</v>
       </c>
       <c r="E209" s="30" t="s">
-        <v>3530</v>
+        <v>3521</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210" t="s">
-        <v>3423</v>
+        <v>3414</v>
       </c>
       <c r="B210">
         <v>65574051</v>
       </c>
       <c r="C210" t="s">
-        <v>2929</v>
+        <v>2923</v>
       </c>
       <c r="D210" t="s">
-        <v>2932</v>
+        <v>2926</v>
       </c>
       <c r="E210" s="30" t="s">
-        <v>3530</v>
+        <v>3521</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -33443,16 +33434,16 @@
         <v>2789</v>
       </c>
       <c r="B211" t="s">
-        <v>2977</v>
+        <v>2970</v>
       </c>
       <c r="C211" t="s">
-        <v>2958</v>
+        <v>2951</v>
       </c>
       <c r="D211" s="373" t="s">
-        <v>2960</v>
+        <v>2953</v>
       </c>
       <c r="E211" s="30" t="s">
-        <v>3530</v>
+        <v>3521</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -33463,13 +33454,13 @@
         <v>64881871</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>3193</v>
+        <v>3185</v>
       </c>
       <c r="D212" t="s">
-        <v>3158</v>
+        <v>3150</v>
       </c>
       <c r="E212" s="30" t="s">
-        <v>3530</v>
+        <v>3521</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -33480,30 +33471,30 @@
         <v>68069608</v>
       </c>
       <c r="C213" s="22" t="s">
-        <v>2995</v>
+        <v>2988</v>
       </c>
       <c r="D213" s="373" t="s">
-        <v>2997</v>
+        <v>2990</v>
       </c>
       <c r="E213" s="30" t="s">
-        <v>3621</v>
+        <v>3612</v>
       </c>
     </row>
     <row r="214" spans="1:5">
       <c r="A214" t="s">
-        <v>2947</v>
+        <v>2941</v>
       </c>
       <c r="B214">
         <v>63258169</v>
       </c>
       <c r="C214" s="22" t="s">
-        <v>3013</v>
+        <v>3006</v>
       </c>
       <c r="D214" t="s">
-        <v>3059</v>
+        <v>3052</v>
       </c>
       <c r="E214" s="30" t="s">
-        <v>3621</v>
+        <v>3612</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -33514,13 +33505,13 @@
         <v>69243886</v>
       </c>
       <c r="C215" s="22" t="s">
-        <v>3014</v>
+        <v>3007</v>
       </c>
       <c r="D215" t="s">
-        <v>3006</v>
+        <v>2999</v>
       </c>
       <c r="E215" s="30" t="s">
-        <v>3621</v>
+        <v>3612</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -33531,13 +33522,13 @@
         <v>67752170</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>2996</v>
+        <v>2989</v>
       </c>
       <c r="D216" t="s">
-        <v>3007</v>
+        <v>3000</v>
       </c>
       <c r="E216" s="30" t="s">
-        <v>3621</v>
+        <v>3612</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -33548,13 +33539,13 @@
         <v>64457890</v>
       </c>
       <c r="C217" t="s">
-        <v>3015</v>
+        <v>3008</v>
       </c>
       <c r="D217" s="373" t="s">
-        <v>3016</v>
+        <v>3009</v>
       </c>
       <c r="E217" s="30" t="s">
-        <v>3621</v>
+        <v>3612</v>
       </c>
     </row>
     <row r="231" spans="3:4">
@@ -33685,10 +33676,10 @@
     </row>
     <row r="259" spans="1:6">
       <c r="C259" s="1" t="s">
-        <v>2881</v>
+        <v>2877</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>2882</v>
+        <v>2878</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -33696,7 +33687,7 @@
         <v>1663</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>2883</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="261" spans="1:6">
@@ -36326,7 +36317,7 @@
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>2990</v>
+        <v>2983</v>
       </c>
     </row>
     <row r="18" spans="4:4">
@@ -36413,7 +36404,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="76" t="s">
-        <v>2993</v>
+        <v>2986</v>
       </c>
       <c r="B6" s="76">
         <v>64966680</v>
@@ -36428,7 +36419,7 @@
         <v>678</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>3291</v>
+        <v>3282</v>
       </c>
       <c r="G6" s="363" t="s">
         <v>1442</v>
@@ -36449,13 +36440,13 @@
         <v>1845</v>
       </c>
       <c r="D7" s="183" t="s">
-        <v>2926</v>
+        <v>2920</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F7" s="183" t="s">
-        <v>3291</v>
+        <v>3282</v>
       </c>
       <c r="G7" s="183" t="s">
         <v>1442</v>
@@ -36467,7 +36458,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="193" t="s">
-        <v>3157</v>
+        <v>3149</v>
       </c>
       <c r="B8" s="193">
         <v>62747874</v>
@@ -36482,7 +36473,7 @@
         <v>362</v>
       </c>
       <c r="F8" s="183" t="s">
-        <v>3291</v>
+        <v>3282</v>
       </c>
       <c r="G8" s="183" t="s">
         <v>1442</v>
@@ -36509,7 +36500,7 @@
         <v>362</v>
       </c>
       <c r="F9" s="183" t="s">
-        <v>3291</v>
+        <v>3282</v>
       </c>
       <c r="G9" s="183" t="s">
         <v>1442</v>
@@ -36536,7 +36527,7 @@
         <v>362</v>
       </c>
       <c r="F10" s="183" t="s">
-        <v>3291</v>
+        <v>3282</v>
       </c>
       <c r="G10" s="183" t="s">
         <v>1442</v>
@@ -36563,7 +36554,7 @@
         <v>362</v>
       </c>
       <c r="F11" s="183" t="s">
-        <v>3291</v>
+        <v>3282</v>
       </c>
       <c r="G11" s="183" t="s">
         <v>1442</v>
@@ -36587,7 +36578,7 @@
         <v>2518</v>
       </c>
       <c r="E13" s="195" t="s">
-        <v>3292</v>
+        <v>3283</v>
       </c>
       <c r="F13" s="195" t="s">
         <v>1429</v>
@@ -36613,7 +36604,7 @@
         <v>1846</v>
       </c>
       <c r="E14" s="193" t="s">
-        <v>3292</v>
+        <v>3283</v>
       </c>
       <c r="F14" s="193" t="s">
         <v>1429</v>
@@ -36639,7 +36630,7 @@
         <v>2793</v>
       </c>
       <c r="E15" s="193" t="s">
-        <v>3292</v>
+        <v>3283</v>
       </c>
       <c r="F15" s="193" t="s">
         <v>1429</v>
@@ -36653,7 +36644,7 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="183" t="s">
-        <v>2993</v>
+        <v>2986</v>
       </c>
       <c r="B16" s="183">
         <v>63666666</v>
@@ -36665,7 +36656,7 @@
         <v>2315</v>
       </c>
       <c r="E16" s="193" t="s">
-        <v>3292</v>
+        <v>3283</v>
       </c>
       <c r="F16" s="193" t="s">
         <v>1429</v>
@@ -36679,7 +36670,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="193" t="s">
-        <v>3512</v>
+        <v>3503</v>
       </c>
       <c r="B17" s="193">
         <v>64403333</v>
@@ -36691,7 +36682,7 @@
         <v>1507</v>
       </c>
       <c r="E17" s="193" t="s">
-        <v>3292</v>
+        <v>3283</v>
       </c>
       <c r="F17" s="193" t="s">
         <v>1429</v>
@@ -36717,7 +36708,7 @@
         <v>2157</v>
       </c>
       <c r="E18" s="193" t="s">
-        <v>3292</v>
+        <v>3283</v>
       </c>
       <c r="F18" s="193" t="s">
         <v>1429</v>
@@ -36731,7 +36722,7 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="195" t="s">
-        <v>2993</v>
+        <v>2986</v>
       </c>
       <c r="B20" s="195">
         <v>67539485</v>
@@ -36746,7 +36737,7 @@
         <v>362</v>
       </c>
       <c r="F20" s="195" t="s">
-        <v>3292</v>
+        <v>3283</v>
       </c>
       <c r="G20" s="76" t="s">
         <v>422</v>
@@ -36760,7 +36751,7 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="183" t="s">
-        <v>2870</v>
+        <v>2868</v>
       </c>
       <c r="B21" s="183">
         <v>62723048</v>
@@ -36775,7 +36766,7 @@
         <v>362</v>
       </c>
       <c r="F21" s="193" t="s">
-        <v>3292</v>
+        <v>3283</v>
       </c>
       <c r="G21" s="183" t="s">
         <v>422</v>
@@ -36804,7 +36795,7 @@
         <v>362</v>
       </c>
       <c r="F22" s="193" t="s">
-        <v>3292</v>
+        <v>3283</v>
       </c>
       <c r="G22" s="183" t="s">
         <v>422</v>
@@ -36818,7 +36809,7 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="183" t="s">
-        <v>3153</v>
+        <v>3145</v>
       </c>
       <c r="B23" s="183">
         <v>60389752</v>
@@ -36833,7 +36824,7 @@
         <v>362</v>
       </c>
       <c r="F23" s="193" t="s">
-        <v>3292</v>
+        <v>3283</v>
       </c>
       <c r="G23" s="183" t="s">
         <v>422</v>
@@ -36862,7 +36853,7 @@
         <v>362</v>
       </c>
       <c r="F24" s="193" t="s">
-        <v>3292</v>
+        <v>3283</v>
       </c>
       <c r="G24" s="183" t="s">
         <v>422</v>
@@ -36891,7 +36882,7 @@
         <v>362</v>
       </c>
       <c r="F25" s="193" t="s">
-        <v>3292</v>
+        <v>3283</v>
       </c>
       <c r="G25" s="183" t="s">
         <v>422</v>
@@ -36905,7 +36896,7 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="76" t="s">
-        <v>3254</v>
+        <v>3245</v>
       </c>
       <c r="B27" s="76">
         <v>60389752</v>
@@ -36920,7 +36911,7 @@
         <v>362</v>
       </c>
       <c r="F27" s="76" t="s">
-        <v>3395</v>
+        <v>3386</v>
       </c>
       <c r="G27" s="76" t="s">
         <v>1443</v>
@@ -36947,7 +36938,7 @@
         <v>362</v>
       </c>
       <c r="F28" s="183" t="s">
-        <v>3395</v>
+        <v>3386</v>
       </c>
       <c r="G28" s="183" t="s">
         <v>378</v>
@@ -36961,22 +36952,22 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="183" t="s">
-        <v>3497</v>
+        <v>3488</v>
       </c>
       <c r="B29" s="183">
         <v>65234700</v>
       </c>
       <c r="C29" s="194" t="s">
-        <v>3418</v>
+        <v>3409</v>
       </c>
       <c r="D29" s="183" t="s">
-        <v>3419</v>
+        <v>3410</v>
       </c>
       <c r="E29" s="433">
         <v>46243</v>
       </c>
       <c r="F29" s="183" t="s">
-        <v>3395</v>
+        <v>3386</v>
       </c>
       <c r="G29" s="183" t="s">
         <v>378</v>
@@ -37005,7 +36996,7 @@
         <v>362</v>
       </c>
       <c r="F30" s="183" t="s">
-        <v>3395</v>
+        <v>3386</v>
       </c>
       <c r="G30" s="183" t="s">
         <v>378</v>
@@ -37034,7 +37025,7 @@
         <v>362</v>
       </c>
       <c r="F31" s="183" t="s">
-        <v>3395</v>
+        <v>3386</v>
       </c>
       <c r="G31" s="183" t="s">
         <v>378</v>
@@ -37048,7 +37039,7 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="183" t="s">
-        <v>3184</v>
+        <v>3176</v>
       </c>
       <c r="B32" s="183">
         <v>68241069</v>
@@ -37063,7 +37054,7 @@
         <v>362</v>
       </c>
       <c r="F32" s="183" t="s">
-        <v>3395</v>
+        <v>3386</v>
       </c>
       <c r="G32" s="183" t="s">
         <v>378</v>
@@ -37086,13 +37077,13 @@
         <v>1665</v>
       </c>
       <c r="D34" s="195" t="s">
-        <v>3582</v>
+        <v>3573</v>
       </c>
       <c r="E34" s="76" t="s">
         <v>2486</v>
       </c>
       <c r="F34" s="195" t="s">
-        <v>3474</v>
+        <v>3465</v>
       </c>
       <c r="G34" s="76" t="s">
         <v>1442</v>
@@ -37103,7 +37094,7 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="193" t="s">
-        <v>3153</v>
+        <v>3145</v>
       </c>
       <c r="B35" s="193">
         <v>63465332</v>
@@ -37118,7 +37109,7 @@
         <v>2486</v>
       </c>
       <c r="F35" s="193" t="s">
-        <v>3474</v>
+        <v>3465</v>
       </c>
       <c r="G35" s="183" t="s">
         <v>1442</v>
@@ -37129,7 +37120,7 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="193" t="s">
-        <v>2993</v>
+        <v>2986</v>
       </c>
       <c r="B36" s="193">
         <v>63226030</v>
@@ -37144,7 +37135,7 @@
         <v>2486</v>
       </c>
       <c r="F36" s="193" t="s">
-        <v>3474</v>
+        <v>3465</v>
       </c>
       <c r="G36" s="183" t="s">
         <v>1442</v>
@@ -37155,7 +37146,7 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="193" t="s">
-        <v>3450</v>
+        <v>3441</v>
       </c>
       <c r="B37" s="193">
         <v>69111188</v>
@@ -37170,7 +37161,7 @@
         <v>2486</v>
       </c>
       <c r="F37" s="193" t="s">
-        <v>3474</v>
+        <v>3465</v>
       </c>
       <c r="G37" s="183" t="s">
         <v>1442</v>
@@ -37196,7 +37187,7 @@
         <v>2486</v>
       </c>
       <c r="F38" s="193" t="s">
-        <v>3474</v>
+        <v>3465</v>
       </c>
       <c r="G38" s="183" t="s">
         <v>1442</v>
@@ -37222,7 +37213,7 @@
         <v>2486</v>
       </c>
       <c r="F39" s="193" t="s">
-        <v>3474</v>
+        <v>3465</v>
       </c>
       <c r="G39" s="183" t="s">
         <v>1442</v>
@@ -37235,16 +37226,16 @@
       <c r="A41" s="195"/>
       <c r="B41" s="195"/>
       <c r="C41" s="195" t="s">
-        <v>3465</v>
+        <v>3456</v>
       </c>
       <c r="D41" s="195" t="s">
-        <v>3466</v>
+        <v>3457</v>
       </c>
       <c r="E41" s="76" t="s">
         <v>362</v>
       </c>
       <c r="F41" s="195" t="s">
-        <v>3467</v>
+        <v>3458</v>
       </c>
       <c r="G41" s="76" t="s">
         <v>2374</v>
@@ -37264,7 +37255,7 @@
         <v>69563253</v>
       </c>
       <c r="C42" s="193" t="s">
-        <v>3468</v>
+        <v>3459</v>
       </c>
       <c r="D42" s="193" t="s">
         <v>1677</v>
@@ -37278,16 +37269,16 @@
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="234" t="s">
-        <v>2971</v>
+        <v>2964</v>
       </c>
       <c r="B43" s="193" t="s">
         <v>1943</v>
       </c>
       <c r="C43" s="194" t="s">
-        <v>3445</v>
+        <v>3436</v>
       </c>
       <c r="D43" s="193" t="s">
-        <v>3446</v>
+        <v>3437</v>
       </c>
       <c r="E43" s="433">
         <v>46304</v>
@@ -37304,7 +37295,7 @@
         <v>62751201</v>
       </c>
       <c r="C44" s="194" t="s">
-        <v>3472</v>
+        <v>3463</v>
       </c>
       <c r="D44" s="183" t="s">
         <v>1357</v>
@@ -37324,10 +37315,10 @@
         <v>68030850</v>
       </c>
       <c r="C45" s="193" t="s">
-        <v>3448</v>
+        <v>3439</v>
       </c>
       <c r="D45" s="193" t="s">
-        <v>3449</v>
+        <v>3440</v>
       </c>
       <c r="E45" s="433">
         <v>46243</v>
@@ -37360,16 +37351,16 @@
       <c r="A48" s="195"/>
       <c r="B48" s="195"/>
       <c r="C48" s="195" t="s">
-        <v>3499</v>
+        <v>3490</v>
       </c>
       <c r="D48" s="195" t="s">
-        <v>3500</v>
+        <v>3491</v>
       </c>
       <c r="E48" s="76" t="s">
-        <v>3501</v>
+        <v>3492</v>
       </c>
       <c r="F48" s="195" t="s">
-        <v>3502</v>
+        <v>3493</v>
       </c>
       <c r="G48" s="76" t="s">
         <v>1442</v>
@@ -37406,10 +37397,10 @@
         <v>61548403</v>
       </c>
       <c r="C50" s="194" t="s">
-        <v>3503</v>
+        <v>3494</v>
       </c>
       <c r="D50" s="193" t="s">
-        <v>3504</v>
+        <v>3495</v>
       </c>
       <c r="E50" s="433">
         <v>46304</v>
@@ -37422,7 +37413,7 @@
       <c r="C51" s="456"/>
       <c r="D51" s="456"/>
       <c r="E51" s="433" t="s">
-        <v>3581</v>
+        <v>3572</v>
       </c>
       <c r="F51" s="193"/>
       <c r="G51" s="183"/>
@@ -37442,7 +37433,7 @@
         <v>936</v>
       </c>
       <c r="E52" s="433" t="s">
-        <v>3581</v>
+        <v>3572</v>
       </c>
       <c r="F52" s="193"/>
       <c r="G52" s="183"/>
@@ -37450,19 +37441,19 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="183" t="s">
-        <v>2947</v>
+        <v>2941</v>
       </c>
       <c r="B53" s="183">
         <v>64543204</v>
       </c>
       <c r="C53" s="194" t="s">
-        <v>2969</v>
+        <v>2962</v>
       </c>
       <c r="D53" s="183" t="s">
-        <v>2968</v>
+        <v>2961</v>
       </c>
       <c r="E53" s="433" t="s">
-        <v>3581</v>
+        <v>3572</v>
       </c>
       <c r="F53" s="193"/>
       <c r="G53" s="183"/>
@@ -37479,13 +37470,13 @@
         <v>1664</v>
       </c>
       <c r="D55" s="195" t="s">
-        <v>3031</v>
+        <v>3024</v>
       </c>
       <c r="E55" s="76" t="s">
         <v>2486</v>
       </c>
       <c r="F55" s="195" t="s">
-        <v>3506</v>
+        <v>3497</v>
       </c>
       <c r="G55" s="76" t="s">
         <v>1442</v>
@@ -37511,7 +37502,7 @@
         <v>2486</v>
       </c>
       <c r="F56" s="193" t="s">
-        <v>3506</v>
+        <v>3497</v>
       </c>
       <c r="G56" s="183" t="s">
         <v>1442</v>
@@ -37531,13 +37522,13 @@
         <v>2610</v>
       </c>
       <c r="D57" s="193" t="s">
-        <v>3214</v>
+        <v>3206</v>
       </c>
       <c r="E57" s="183" t="s">
         <v>2486</v>
       </c>
       <c r="F57" s="193" t="s">
-        <v>3506</v>
+        <v>3497</v>
       </c>
       <c r="G57" s="183" t="s">
         <v>1442</v>
@@ -37563,7 +37554,7 @@
         <v>2486</v>
       </c>
       <c r="F58" s="193" t="s">
-        <v>3506</v>
+        <v>3497</v>
       </c>
       <c r="G58" s="183" t="s">
         <v>1442</v>
@@ -37574,7 +37565,7 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="193" t="s">
-        <v>2983</v>
+        <v>2976</v>
       </c>
       <c r="B59" s="193">
         <v>65174343</v>
@@ -37589,7 +37580,7 @@
         <v>2486</v>
       </c>
       <c r="F59" s="193" t="s">
-        <v>3506</v>
+        <v>3497</v>
       </c>
       <c r="G59" s="183" t="s">
         <v>1442</v>
@@ -37606,16 +37597,16 @@
         <v>63062167</v>
       </c>
       <c r="C60" s="193" t="s">
-        <v>3330</v>
+        <v>3321</v>
       </c>
       <c r="D60" s="193" t="s">
-        <v>3365</v>
+        <v>3356</v>
       </c>
       <c r="E60" s="183" t="s">
         <v>2486</v>
       </c>
       <c r="F60" s="193" t="s">
-        <v>3506</v>
+        <v>3497</v>
       </c>
       <c r="G60" s="183" t="s">
         <v>1442</v>
@@ -37641,7 +37632,7 @@
         <v>2486</v>
       </c>
       <c r="F62" s="195" t="s">
-        <v>3506</v>
+        <v>3497</v>
       </c>
       <c r="G62" s="76" t="s">
         <v>1442</v>
@@ -37667,7 +37658,7 @@
         <v>2486</v>
       </c>
       <c r="F63" s="193" t="s">
-        <v>3506</v>
+        <v>3497</v>
       </c>
       <c r="G63" s="183" t="s">
         <v>1442</v>
@@ -37678,7 +37669,7 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="183" t="s">
-        <v>3424</v>
+        <v>3415</v>
       </c>
       <c r="B64" s="183">
         <v>64403333</v>
@@ -37693,7 +37684,7 @@
         <v>2486</v>
       </c>
       <c r="F64" s="193" t="s">
-        <v>3506</v>
+        <v>3497</v>
       </c>
       <c r="G64" s="183" t="s">
         <v>1442</v>
@@ -37704,7 +37695,7 @@
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="193" t="s">
-        <v>3285</v>
+        <v>3276</v>
       </c>
       <c r="B65" s="193">
         <v>68030850</v>
@@ -37719,7 +37710,7 @@
         <v>2486</v>
       </c>
       <c r="F65" s="193" t="s">
-        <v>3506</v>
+        <v>3497</v>
       </c>
       <c r="G65" s="183" t="s">
         <v>1442</v>
@@ -37730,7 +37721,7 @@
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="183" t="s">
-        <v>3516</v>
+        <v>3507</v>
       </c>
       <c r="B66" s="183">
         <v>65003516</v>
@@ -37745,7 +37736,7 @@
         <v>2486</v>
       </c>
       <c r="F66" s="193" t="s">
-        <v>3506</v>
+        <v>3497</v>
       </c>
       <c r="G66" s="183" t="s">
         <v>1442</v>
@@ -37771,7 +37762,7 @@
         <v>2486</v>
       </c>
       <c r="F67" s="193" t="s">
-        <v>3506</v>
+        <v>3497</v>
       </c>
       <c r="G67" s="183" t="s">
         <v>1442</v>
@@ -37782,7 +37773,7 @@
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="76" t="s">
-        <v>2908</v>
+        <v>2904</v>
       </c>
       <c r="B69" s="76">
         <v>64147946</v>
@@ -37794,7 +37785,7 @@
         <v>2449</v>
       </c>
       <c r="E69" s="76" t="s">
-        <v>3555</v>
+        <v>3546</v>
       </c>
       <c r="F69" s="195" t="s">
         <v>2450</v>
@@ -37808,7 +37799,7 @@
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="193" t="s">
-        <v>2904</v>
+        <v>2900</v>
       </c>
       <c r="B70" s="193">
         <v>62646186</v>
@@ -37820,7 +37811,7 @@
         <v>2454</v>
       </c>
       <c r="E70" s="183" t="s">
-        <v>3555</v>
+        <v>3546</v>
       </c>
       <c r="F70" s="193" t="s">
         <v>2450</v>
@@ -37846,7 +37837,7 @@
         <v>2289</v>
       </c>
       <c r="E71" s="183" t="s">
-        <v>3555</v>
+        <v>3546</v>
       </c>
       <c r="F71" s="193" t="s">
         <v>2450</v>
@@ -37872,7 +37863,7 @@
         <v>2745</v>
       </c>
       <c r="E72" s="183" t="s">
-        <v>3555</v>
+        <v>3546</v>
       </c>
       <c r="F72" s="183" t="s">
         <v>2450</v>
@@ -37899,7 +37890,7 @@
         <v>2054</v>
       </c>
       <c r="E73" s="183" t="s">
-        <v>3555</v>
+        <v>3546</v>
       </c>
       <c r="F73" s="183" t="s">
         <v>2450</v>
@@ -37926,7 +37917,7 @@
         <v>2445</v>
       </c>
       <c r="E74" s="183" t="s">
-        <v>3555</v>
+        <v>3546</v>
       </c>
       <c r="F74" s="183" t="s">
         <v>2450</v>
@@ -37953,7 +37944,7 @@
         <v>1724</v>
       </c>
       <c r="E76" s="76" t="s">
-        <v>3555</v>
+        <v>3546</v>
       </c>
       <c r="F76" s="195" t="s">
         <v>2448</v>
@@ -37965,7 +37956,7 @@
     </row>
     <row r="77" spans="1:9">
       <c r="A77" s="193" t="s">
-        <v>2870</v>
+        <v>2868</v>
       </c>
       <c r="B77" s="193">
         <v>66082581</v>
@@ -37977,7 +37968,7 @@
         <v>2329</v>
       </c>
       <c r="E77" s="183" t="s">
-        <v>3555</v>
+        <v>3546</v>
       </c>
       <c r="F77" s="193" t="s">
         <v>2448</v>
@@ -38001,7 +37992,7 @@
         <v>1238</v>
       </c>
       <c r="E78" s="183" t="s">
-        <v>3555</v>
+        <v>3546</v>
       </c>
       <c r="F78" s="193" t="s">
         <v>2448</v>
@@ -38013,7 +38004,7 @@
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="183" t="s">
-        <v>3635</v>
+        <v>3626</v>
       </c>
       <c r="B79" s="183">
         <v>62820256</v>
@@ -38025,7 +38016,7 @@
         <v>2357</v>
       </c>
       <c r="E79" s="183" t="s">
-        <v>3555</v>
+        <v>3546</v>
       </c>
       <c r="F79" s="193" t="s">
         <v>2448</v>
@@ -38037,19 +38028,19 @@
     </row>
     <row r="80" spans="1:9">
       <c r="A80" s="183" t="s">
-        <v>3043</v>
+        <v>3036</v>
       </c>
       <c r="B80" s="183">
         <v>69563253</v>
       </c>
       <c r="C80" s="194" t="s">
-        <v>3556</v>
+        <v>3547</v>
       </c>
       <c r="D80" s="183" t="s">
         <v>1005</v>
       </c>
       <c r="E80" s="183" t="s">
-        <v>3557</v>
+        <v>3548</v>
       </c>
       <c r="F80" s="193" t="s">
         <v>2448</v>
@@ -38061,7 +38052,7 @@
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="183" t="s">
-        <v>3586</v>
+        <v>3577</v>
       </c>
       <c r="B81" s="183">
         <v>63233935</v>
@@ -38070,10 +38061,10 @@
         <v>2376</v>
       </c>
       <c r="D81" s="183" t="s">
-        <v>3583</v>
+        <v>3574</v>
       </c>
       <c r="E81" s="183" t="s">
-        <v>3555</v>
+        <v>3546</v>
       </c>
       <c r="F81" s="193" t="s">
         <v>2448</v>
@@ -38085,7 +38076,7 @@
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="76" t="s">
-        <v>3301</v>
+        <v>3292</v>
       </c>
       <c r="B83" s="76">
         <v>63574980</v>
@@ -38100,7 +38091,7 @@
         <v>1344</v>
       </c>
       <c r="F83" s="195" t="s">
-        <v>3627</v>
+        <v>3618</v>
       </c>
       <c r="G83" s="76" t="s">
         <v>1442</v>
@@ -38127,7 +38118,7 @@
         <v>1344</v>
       </c>
       <c r="F84" s="183" t="s">
-        <v>3627</v>
+        <v>3618</v>
       </c>
       <c r="G84" s="183" t="s">
         <v>1442</v>
@@ -38145,7 +38136,7 @@
         <v>68483411</v>
       </c>
       <c r="C85" s="183" t="s">
-        <v>2907</v>
+        <v>2903</v>
       </c>
       <c r="D85" s="183" t="s">
         <v>2155</v>
@@ -38154,7 +38145,7 @@
         <v>1344</v>
       </c>
       <c r="F85" s="183" t="s">
-        <v>3627</v>
+        <v>3618</v>
       </c>
       <c r="G85" s="183" t="s">
         <v>1442</v>
@@ -38169,19 +38160,19 @@
         <v>2503</v>
       </c>
       <c r="B86" s="183" t="s">
-        <v>3174</v>
+        <v>3166</v>
       </c>
       <c r="C86" s="194" t="s">
         <v>2670</v>
       </c>
       <c r="D86" s="183" t="s">
-        <v>3173</v>
+        <v>3165</v>
       </c>
       <c r="E86" s="183" t="s">
         <v>1344</v>
       </c>
       <c r="F86" s="183" t="s">
-        <v>3627</v>
+        <v>3618</v>
       </c>
       <c r="G86" s="183" t="s">
         <v>1442</v>
@@ -38193,7 +38184,7 @@
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="183" t="s">
-        <v>3157</v>
+        <v>3149</v>
       </c>
       <c r="B87" s="183">
         <v>69904406</v>
@@ -38202,13 +38193,13 @@
         <v>2671</v>
       </c>
       <c r="D87" s="183" t="s">
-        <v>3293</v>
+        <v>3284</v>
       </c>
       <c r="E87" s="183" t="s">
         <v>1344</v>
       </c>
       <c r="F87" s="183" t="s">
-        <v>3627</v>
+        <v>3618</v>
       </c>
       <c r="G87" s="183" t="s">
         <v>1442</v>
@@ -38220,7 +38211,7 @@
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="183" t="s">
-        <v>2947</v>
+        <v>2941</v>
       </c>
       <c r="B88" s="183" t="s">
         <v>2689</v>
@@ -38235,7 +38226,7 @@
         <v>1344</v>
       </c>
       <c r="F88" s="183" t="s">
-        <v>3627</v>
+        <v>3618</v>
       </c>
       <c r="G88" s="183" t="s">
         <v>1442</v>
@@ -38262,7 +38253,7 @@
         <v>1654</v>
       </c>
       <c r="F90" s="195" t="s">
-        <v>3628</v>
+        <v>3619</v>
       </c>
       <c r="G90" s="76" t="s">
         <v>1442</v>
@@ -38286,7 +38277,7 @@
         <v>1654</v>
       </c>
       <c r="F91" s="193" t="s">
-        <v>3628</v>
+        <v>3619</v>
       </c>
       <c r="G91" s="183" t="s">
         <v>1442</v>
@@ -38310,7 +38301,7 @@
         <v>1654</v>
       </c>
       <c r="F92" s="193" t="s">
-        <v>3628</v>
+        <v>3619</v>
       </c>
       <c r="G92" s="183" t="s">
         <v>1442</v>
@@ -38334,7 +38325,7 @@
         <v>1654</v>
       </c>
       <c r="F93" s="193" t="s">
-        <v>3628</v>
+        <v>3619</v>
       </c>
       <c r="G93" s="183" t="s">
         <v>1442</v>
@@ -38343,7 +38334,7 @@
     </row>
     <row r="94" spans="1:9">
       <c r="A94" s="183" t="s">
-        <v>2983</v>
+        <v>2976</v>
       </c>
       <c r="B94" s="183">
         <v>64403333</v>
@@ -38358,7 +38349,7 @@
         <v>1654</v>
       </c>
       <c r="F94" s="193" t="s">
-        <v>3628</v>
+        <v>3619</v>
       </c>
       <c r="G94" s="183" t="s">
         <v>1442</v>
@@ -38382,7 +38373,7 @@
         <v>1654</v>
       </c>
       <c r="F95" s="193" t="s">
-        <v>3628</v>
+        <v>3619</v>
       </c>
       <c r="G95" s="183" t="s">
         <v>1442</v>
@@ -38391,7 +38382,7 @@
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="195" t="s">
-        <v>3488</v>
+        <v>3479</v>
       </c>
       <c r="B97" s="195">
         <v>64476521</v>
@@ -38406,7 +38397,7 @@
         <v>2486</v>
       </c>
       <c r="F97" s="195" t="s">
-        <v>3651</v>
+        <v>3642</v>
       </c>
       <c r="G97" s="76" t="s">
         <v>1442</v>
@@ -38417,7 +38408,7 @@
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="193" t="s">
-        <v>3381</v>
+        <v>3372</v>
       </c>
       <c r="B98" s="193">
         <v>60389752</v>
@@ -38426,13 +38417,13 @@
         <v>2651</v>
       </c>
       <c r="D98" s="193" t="s">
-        <v>3380</v>
+        <v>3371</v>
       </c>
       <c r="E98" s="183" t="s">
         <v>2486</v>
       </c>
       <c r="F98" s="193" t="s">
-        <v>3651</v>
+        <v>3642</v>
       </c>
       <c r="G98" s="183" t="s">
         <v>1442</v>
@@ -38443,7 +38434,7 @@
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="183" t="s">
-        <v>3603</v>
+        <v>3594</v>
       </c>
       <c r="B99" s="183">
         <v>60389752</v>
@@ -38458,7 +38449,7 @@
         <v>2486</v>
       </c>
       <c r="F99" s="193" t="s">
-        <v>3651</v>
+        <v>3642</v>
       </c>
       <c r="G99" s="183" t="s">
         <v>1442</v>
@@ -38469,7 +38460,7 @@
     </row>
     <row r="100" spans="1:9">
       <c r="A100" s="193" t="s">
-        <v>2908</v>
+        <v>2904</v>
       </c>
       <c r="B100" s="193">
         <v>60389752</v>
@@ -38484,7 +38475,7 @@
         <v>2486</v>
       </c>
       <c r="F100" s="193" t="s">
-        <v>3651</v>
+        <v>3642</v>
       </c>
       <c r="G100" s="183" t="s">
         <v>1442</v>
@@ -38495,7 +38486,7 @@
     </row>
     <row r="101" spans="1:9">
       <c r="A101" s="183" t="s">
-        <v>2931</v>
+        <v>2925</v>
       </c>
       <c r="B101" s="183">
         <v>60533053</v>
@@ -38510,7 +38501,7 @@
         <v>2486</v>
       </c>
       <c r="F101" s="193" t="s">
-        <v>3651</v>
+        <v>3642</v>
       </c>
       <c r="G101" s="183" t="s">
         <v>1442</v>
@@ -38521,7 +38512,7 @@
     </row>
     <row r="102" spans="1:9">
       <c r="A102" s="193" t="s">
-        <v>3157</v>
+        <v>3149</v>
       </c>
       <c r="B102" s="193">
         <v>67381873</v>
@@ -38530,13 +38521,13 @@
         <v>2286</v>
       </c>
       <c r="D102" s="193" t="s">
-        <v>3297</v>
+        <v>3288</v>
       </c>
       <c r="E102" s="183" t="s">
         <v>2486</v>
       </c>
       <c r="F102" s="193" t="s">
-        <v>3651</v>
+        <v>3642</v>
       </c>
       <c r="G102" s="183" t="s">
         <v>1442</v>
@@ -38547,7 +38538,7 @@
     </row>
     <row r="104" spans="1:9">
       <c r="A104" s="195" t="s">
-        <v>3019</v>
+        <v>3012</v>
       </c>
       <c r="B104" s="195">
         <v>66082581</v>
@@ -38559,7 +38550,7 @@
         <v>2297</v>
       </c>
       <c r="E104" s="76" t="s">
-        <v>3651</v>
+        <v>3642</v>
       </c>
       <c r="F104" s="195" t="s">
         <v>422</v>
@@ -38573,7 +38564,7 @@
     </row>
     <row r="105" spans="1:9">
       <c r="A105" s="193" t="s">
-        <v>2993</v>
+        <v>2986</v>
       </c>
       <c r="B105" s="193" t="s">
         <v>2709</v>
@@ -38585,7 +38576,7 @@
         <v>2302</v>
       </c>
       <c r="E105" s="183" t="s">
-        <v>3651</v>
+        <v>3642</v>
       </c>
       <c r="F105" s="193" t="s">
         <v>422</v>
@@ -38599,7 +38590,7 @@
     </row>
     <row r="106" spans="1:9">
       <c r="A106" s="193" t="s">
-        <v>3320</v>
+        <v>3311</v>
       </c>
       <c r="B106" s="193">
         <v>62723048</v>
@@ -38608,10 +38599,10 @@
         <v>2303</v>
       </c>
       <c r="D106" s="193" t="s">
-        <v>3319</v>
+        <v>3310</v>
       </c>
       <c r="E106" s="183" t="s">
-        <v>3651</v>
+        <v>3642</v>
       </c>
       <c r="F106" s="193" t="s">
         <v>422</v>
@@ -38631,13 +38622,13 @@
         <v>69017426</v>
       </c>
       <c r="C107" s="194" t="s">
-        <v>2927</v>
+        <v>2921</v>
       </c>
       <c r="D107" s="193" t="s">
         <v>2460</v>
       </c>
       <c r="E107" s="183" t="s">
-        <v>3651</v>
+        <v>3642</v>
       </c>
       <c r="F107" s="193" t="s">
         <v>422</v>
@@ -38663,7 +38654,7 @@
         <v>2306</v>
       </c>
       <c r="E108" s="183" t="s">
-        <v>3651</v>
+        <v>3642</v>
       </c>
       <c r="F108" s="193" t="s">
         <v>422</v>
@@ -38683,13 +38674,13 @@
         <v>62723048</v>
       </c>
       <c r="C109" s="194" t="s">
-        <v>2938</v>
+        <v>2932</v>
       </c>
       <c r="D109" s="193" t="s">
-        <v>2937</v>
+        <v>2931</v>
       </c>
       <c r="E109" s="183" t="s">
-        <v>3651</v>
+        <v>3642</v>
       </c>
       <c r="F109" s="193" t="s">
         <v>422</v>
@@ -38709,16 +38700,16 @@
         <v>68310153</v>
       </c>
       <c r="C111" s="195" t="s">
-        <v>3011</v>
+        <v>3004</v>
       </c>
       <c r="D111" s="195" t="s">
-        <v>3012</v>
+        <v>3005</v>
       </c>
       <c r="E111" s="76" t="s">
         <v>362</v>
       </c>
       <c r="F111" s="195" t="s">
-        <v>3017</v>
+        <v>3010</v>
       </c>
       <c r="G111" s="76" t="s">
         <v>1344</v>
@@ -38732,7 +38723,7 @@
     </row>
     <row r="112" spans="1:9">
       <c r="A112" s="193" t="s">
-        <v>3018</v>
+        <v>3011</v>
       </c>
       <c r="B112" s="193">
         <v>63910392</v>
@@ -38745,7 +38736,7 @@
         <v>362</v>
       </c>
       <c r="F112" s="193" t="s">
-        <v>3017</v>
+        <v>3010</v>
       </c>
       <c r="G112" s="183" t="s">
         <v>1344</v>
@@ -38774,7 +38765,7 @@
         <v>2486</v>
       </c>
       <c r="F113" s="193" t="s">
-        <v>3017</v>
+        <v>3010</v>
       </c>
       <c r="G113" s="183" t="s">
         <v>1344</v>
@@ -38794,16 +38785,16 @@
         <v>62360487</v>
       </c>
       <c r="C114" s="194" t="s">
-        <v>3331</v>
+        <v>3322</v>
       </c>
       <c r="D114" s="183" t="s">
-        <v>3332</v>
+        <v>3323</v>
       </c>
       <c r="E114" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F114" s="193" t="s">
-        <v>3017</v>
+        <v>3010</v>
       </c>
       <c r="G114" s="183" t="s">
         <v>1344</v>
@@ -38823,16 +38814,16 @@
         <v>62085821</v>
       </c>
       <c r="C115" s="193" t="s">
-        <v>3333</v>
+        <v>3324</v>
       </c>
       <c r="D115" s="193" t="s">
-        <v>3334</v>
+        <v>3325</v>
       </c>
       <c r="E115" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F115" s="193" t="s">
-        <v>3017</v>
+        <v>3010</v>
       </c>
       <c r="G115" s="183" t="s">
         <v>1344</v>
@@ -38852,16 +38843,16 @@
         <v>64403333</v>
       </c>
       <c r="C116" s="193" t="s">
-        <v>3335</v>
+        <v>3326</v>
       </c>
       <c r="D116" s="193" t="s">
-        <v>3336</v>
+        <v>3327</v>
       </c>
       <c r="E116" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F116" s="193" t="s">
-        <v>3017</v>
+        <v>3010</v>
       </c>
       <c r="G116" s="183" t="s">
         <v>1344</v>
@@ -38893,7 +38884,7 @@
         <v>2319</v>
       </c>
       <c r="E118" s="76" t="s">
-        <v>3086</v>
+        <v>3079</v>
       </c>
       <c r="F118" s="76" t="s">
         <v>422</v>
@@ -38920,7 +38911,7 @@
         <v>2321</v>
       </c>
       <c r="E119" s="183" t="s">
-        <v>3086</v>
+        <v>3079</v>
       </c>
       <c r="F119" s="193" t="s">
         <v>422</v>
@@ -38946,7 +38937,7 @@
         <v>2323</v>
       </c>
       <c r="E120" s="183" t="s">
-        <v>3086</v>
+        <v>3079</v>
       </c>
       <c r="F120" s="193" t="s">
         <v>422</v>
@@ -38960,19 +38951,19 @@
     </row>
     <row r="121" spans="1:9">
       <c r="A121" s="183" t="s">
-        <v>3422</v>
+        <v>3413</v>
       </c>
       <c r="B121" s="183">
         <v>64403333</v>
       </c>
       <c r="C121" s="183" t="s">
-        <v>3337</v>
+        <v>3328</v>
       </c>
       <c r="D121" s="183" t="s">
-        <v>3338</v>
+        <v>3329</v>
       </c>
       <c r="E121" s="183" t="s">
-        <v>3086</v>
+        <v>3079</v>
       </c>
       <c r="F121" s="193" t="s">
         <v>422</v>
@@ -38998,7 +38989,7 @@
         <v>377</v>
       </c>
       <c r="E122" s="183" t="s">
-        <v>3086</v>
+        <v>3079</v>
       </c>
       <c r="F122" s="193" t="s">
         <v>422</v>
@@ -39024,7 +39015,7 @@
         <v>1650</v>
       </c>
       <c r="E123" s="183" t="s">
-        <v>3086</v>
+        <v>3079</v>
       </c>
       <c r="F123" s="193" t="s">
         <v>422</v>
@@ -39053,7 +39044,7 @@
         <v>678</v>
       </c>
       <c r="F125" s="76" t="s">
-        <v>3203</v>
+        <v>3195</v>
       </c>
       <c r="G125" s="76" t="s">
         <v>422</v>
@@ -39082,7 +39073,7 @@
         <v>362</v>
       </c>
       <c r="F126" s="183" t="s">
-        <v>3203</v>
+        <v>3195</v>
       </c>
       <c r="G126" s="183" t="s">
         <v>422</v>
@@ -39111,7 +39102,7 @@
         <v>362</v>
       </c>
       <c r="F127" s="183" t="s">
-        <v>3203</v>
+        <v>3195</v>
       </c>
       <c r="G127" s="183" t="s">
         <v>422</v>
@@ -39138,7 +39129,7 @@
         <v>362</v>
       </c>
       <c r="F128" s="183" t="s">
-        <v>3203</v>
+        <v>3195</v>
       </c>
       <c r="G128" s="183" t="s">
         <v>422</v>
@@ -39152,7 +39143,7 @@
     </row>
     <row r="129" spans="1:9">
       <c r="A129" s="183" t="s">
-        <v>2891</v>
+        <v>2887</v>
       </c>
       <c r="B129" s="183">
         <v>66230961</v>
@@ -39167,7 +39158,7 @@
         <v>362</v>
       </c>
       <c r="F129" s="183" t="s">
-        <v>3203</v>
+        <v>3195</v>
       </c>
       <c r="G129" s="183" t="s">
         <v>422</v>
@@ -39181,7 +39172,7 @@
     </row>
     <row r="130" spans="1:9">
       <c r="A130" s="183" t="s">
-        <v>2908</v>
+        <v>2904</v>
       </c>
       <c r="B130" s="183">
         <v>69888391</v>
@@ -39196,7 +39187,7 @@
         <v>362</v>
       </c>
       <c r="F130" s="183" t="s">
-        <v>3203</v>
+        <v>3195</v>
       </c>
       <c r="G130" s="183" t="s">
         <v>422</v>
@@ -39225,7 +39216,7 @@
         <v>2368</v>
       </c>
       <c r="F132" s="195" t="s">
-        <v>3250</v>
+        <v>3241</v>
       </c>
       <c r="G132" s="76" t="s">
         <v>1442</v>
@@ -39242,7 +39233,7 @@
         <v>64226974</v>
       </c>
       <c r="C133" s="183" t="s">
-        <v>3485</v>
+        <v>3476</v>
       </c>
       <c r="D133" s="193" t="s">
         <v>377</v>
@@ -39251,7 +39242,7 @@
         <v>2368</v>
       </c>
       <c r="F133" s="193" t="s">
-        <v>3250</v>
+        <v>3241</v>
       </c>
       <c r="G133" s="183" t="s">
         <v>1442</v>
@@ -39277,7 +39268,7 @@
         <v>2368</v>
       </c>
       <c r="F134" s="193" t="s">
-        <v>3250</v>
+        <v>3241</v>
       </c>
       <c r="G134" s="183" t="s">
         <v>1442</v>
@@ -39303,7 +39294,7 @@
         <v>2368</v>
       </c>
       <c r="F135" s="193" t="s">
-        <v>3250</v>
+        <v>3241</v>
       </c>
       <c r="G135" s="183" t="s">
         <v>1442</v>
@@ -39329,7 +39320,7 @@
         <v>2368</v>
       </c>
       <c r="F136" s="193" t="s">
-        <v>3250</v>
+        <v>3241</v>
       </c>
       <c r="G136" s="183" t="s">
         <v>1442</v>
@@ -39355,7 +39346,7 @@
         <v>2368</v>
       </c>
       <c r="F137" s="193" t="s">
-        <v>3250</v>
+        <v>3241</v>
       </c>
       <c r="G137" s="183" t="s">
         <v>1442</v>
@@ -39366,22 +39357,22 @@
     </row>
     <row r="139" spans="1:9">
       <c r="A139" s="195" t="s">
-        <v>3153</v>
+        <v>3145</v>
       </c>
       <c r="B139" s="195" t="s">
         <v>2162</v>
       </c>
       <c r="C139" s="195" t="s">
-        <v>3252</v>
+        <v>3243</v>
       </c>
       <c r="D139" s="195" t="s">
-        <v>3251</v>
+        <v>3242</v>
       </c>
       <c r="E139" s="76" t="s">
         <v>2368</v>
       </c>
       <c r="F139" s="195" t="s">
-        <v>3250</v>
+        <v>3241</v>
       </c>
       <c r="G139" s="76" t="s">
         <v>1442</v>
@@ -39398,16 +39389,16 @@
         <v>66319486</v>
       </c>
       <c r="C140" s="193" t="s">
-        <v>3339</v>
+        <v>3330</v>
       </c>
       <c r="D140" s="193" t="s">
-        <v>3382</v>
+        <v>3373</v>
       </c>
       <c r="E140" s="183" t="s">
         <v>2368</v>
       </c>
       <c r="F140" s="193" t="s">
-        <v>3250</v>
+        <v>3241</v>
       </c>
       <c r="G140" s="183" t="s">
         <v>1442</v>
@@ -39418,7 +39409,7 @@
     </row>
     <row r="141" spans="1:9">
       <c r="A141" s="183" t="s">
-        <v>3254</v>
+        <v>3245</v>
       </c>
       <c r="B141" s="183">
         <v>60389752</v>
@@ -39433,7 +39424,7 @@
         <v>2368</v>
       </c>
       <c r="F141" s="193" t="s">
-        <v>3250</v>
+        <v>3241</v>
       </c>
       <c r="G141" s="183" t="s">
         <v>1442</v>
@@ -39447,7 +39438,7 @@
         <v>2368</v>
       </c>
       <c r="F142" s="193" t="s">
-        <v>3250</v>
+        <v>3241</v>
       </c>
       <c r="G142" s="183" t="s">
         <v>1442</v>
@@ -39473,7 +39464,7 @@
         <v>2368</v>
       </c>
       <c r="F143" s="193" t="s">
-        <v>3250</v>
+        <v>3241</v>
       </c>
       <c r="G143" s="183" t="s">
         <v>1442</v>
@@ -39499,7 +39490,7 @@
         <v>2368</v>
       </c>
       <c r="F144" s="193" t="s">
-        <v>3250</v>
+        <v>3241</v>
       </c>
       <c r="G144" s="183" t="s">
         <v>1442</v>
@@ -39525,7 +39516,7 @@
         <v>2486</v>
       </c>
       <c r="F146" s="195" t="s">
-        <v>3253</v>
+        <v>3244</v>
       </c>
       <c r="G146" s="76" t="s">
         <v>1442</v>
@@ -39536,13 +39527,13 @@
     </row>
     <row r="147" spans="1:9">
       <c r="A147" s="193" t="s">
-        <v>3184</v>
+        <v>3176</v>
       </c>
       <c r="B147" s="193">
         <v>67697112</v>
       </c>
       <c r="C147" s="193" t="s">
-        <v>3364</v>
+        <v>3355</v>
       </c>
       <c r="D147" s="193" t="s">
         <v>1306</v>
@@ -39551,7 +39542,7 @@
         <v>2486</v>
       </c>
       <c r="F147" s="193" t="s">
-        <v>3253</v>
+        <v>3244</v>
       </c>
       <c r="G147" s="183" t="s">
         <v>1442</v>
@@ -39562,7 +39553,7 @@
     </row>
     <row r="148" spans="1:9">
       <c r="A148" s="183" t="s">
-        <v>3408</v>
+        <v>3399</v>
       </c>
       <c r="B148" s="183">
         <v>62560788</v>
@@ -39577,7 +39568,7 @@
         <v>2486</v>
       </c>
       <c r="F148" s="193" t="s">
-        <v>3253</v>
+        <v>3244</v>
       </c>
       <c r="G148" s="183" t="s">
         <v>1442</v>
@@ -39588,7 +39579,7 @@
     </row>
     <row r="149" spans="1:9">
       <c r="A149" s="193" t="s">
-        <v>3157</v>
+        <v>3149</v>
       </c>
       <c r="B149" s="193">
         <v>64403333</v>
@@ -39603,7 +39594,7 @@
         <v>2486</v>
       </c>
       <c r="F149" s="193" t="s">
-        <v>3253</v>
+        <v>3244</v>
       </c>
       <c r="G149" s="183" t="s">
         <v>1442</v>
@@ -39614,22 +39605,22 @@
     </row>
     <row r="150" spans="1:9">
       <c r="A150" s="193" t="s">
-        <v>2971</v>
+        <v>2964</v>
       </c>
       <c r="B150" s="193">
         <v>60125401</v>
       </c>
       <c r="C150" s="194" t="s">
-        <v>2970</v>
+        <v>2963</v>
       </c>
       <c r="D150" s="193" t="s">
-        <v>2972</v>
+        <v>2965</v>
       </c>
       <c r="E150" s="183" t="s">
         <v>2486</v>
       </c>
       <c r="F150" s="193" t="s">
-        <v>3253</v>
+        <v>3244</v>
       </c>
       <c r="G150" s="183" t="s">
         <v>1442</v>
@@ -39655,7 +39646,7 @@
         <v>2486</v>
       </c>
       <c r="F151" s="193" t="s">
-        <v>3253</v>
+        <v>3244</v>
       </c>
       <c r="G151" s="183" t="s">
         <v>1442</v>
@@ -39681,7 +39672,7 @@
         <v>362</v>
       </c>
       <c r="F153" s="195" t="s">
-        <v>3290</v>
+        <v>3281</v>
       </c>
       <c r="G153" s="76" t="s">
         <v>2374</v>
@@ -39695,22 +39686,22 @@
     </row>
     <row r="154" spans="1:9">
       <c r="A154" s="193" t="s">
-        <v>3301</v>
+        <v>3292</v>
       </c>
       <c r="B154" s="193">
         <v>65963732</v>
       </c>
       <c r="C154" s="194" t="s">
-        <v>3322</v>
+        <v>3313</v>
       </c>
       <c r="D154" s="193" t="s">
-        <v>3323</v>
+        <v>3314</v>
       </c>
       <c r="E154" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F154" s="193" t="s">
-        <v>3290</v>
+        <v>3281</v>
       </c>
       <c r="G154" s="183" t="s">
         <v>2374</v>
@@ -39724,7 +39715,7 @@
     </row>
     <row r="155" spans="1:9">
       <c r="A155" s="183" t="s">
-        <v>3301</v>
+        <v>3292</v>
       </c>
       <c r="B155" s="183">
         <v>60071688</v>
@@ -39733,13 +39724,13 @@
         <v>2358</v>
       </c>
       <c r="D155" s="183" t="s">
-        <v>3316</v>
+        <v>3307</v>
       </c>
       <c r="E155" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F155" s="193" t="s">
-        <v>3290</v>
+        <v>3281</v>
       </c>
       <c r="G155" s="183" t="s">
         <v>2374</v>
@@ -39768,7 +39759,7 @@
         <v>362</v>
       </c>
       <c r="F156" s="193" t="s">
-        <v>3290</v>
+        <v>3281</v>
       </c>
       <c r="G156" s="183" t="s">
         <v>2374</v>
@@ -39797,7 +39788,7 @@
         <v>362</v>
       </c>
       <c r="F157" s="193" t="s">
-        <v>3290</v>
+        <v>3281</v>
       </c>
       <c r="G157" s="183" t="s">
         <v>2374</v>
@@ -39811,22 +39802,22 @@
     </row>
     <row r="158" spans="1:9">
       <c r="A158" s="183" t="s">
-        <v>2908</v>
+        <v>2904</v>
       </c>
       <c r="B158" s="183">
         <v>64403333</v>
       </c>
       <c r="C158" s="194" t="s">
-        <v>2973</v>
+        <v>2966</v>
       </c>
       <c r="D158" s="444" t="s">
-        <v>2972</v>
+        <v>2965</v>
       </c>
       <c r="E158" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F158" s="193" t="s">
-        <v>3290</v>
+        <v>3281</v>
       </c>
       <c r="G158" s="183" t="s">
         <v>2374</v>
@@ -39857,7 +39848,7 @@
       <c r="A183" s="221"/>
       <c r="B183" s="221"/>
       <c r="C183" s="221" t="s">
-        <v>3414</v>
+        <v>3405</v>
       </c>
       <c r="D183" s="221"/>
       <c r="E183" s="221"/>
@@ -39865,25 +39856,25 @@
     </row>
     <row r="184" spans="1:9">
       <c r="A184" s="76" t="s">
-        <v>2983</v>
+        <v>2976</v>
       </c>
       <c r="B184" s="76">
         <v>67836337</v>
       </c>
       <c r="C184" s="195" t="s">
-        <v>3528</v>
+        <v>3519</v>
       </c>
       <c r="D184" s="195" t="s">
-        <v>3529</v>
+        <v>3520</v>
       </c>
       <c r="E184" s="434">
         <v>46243</v>
       </c>
       <c r="F184" s="76" t="s">
-        <v>3415</v>
+        <v>3406</v>
       </c>
       <c r="G184" s="195" t="s">
-        <v>3584</v>
+        <v>3575</v>
       </c>
       <c r="H184" s="76" t="s">
         <v>1980</v>
@@ -39891,19 +39882,19 @@
     </row>
     <row r="185" spans="1:9">
       <c r="A185" s="193" t="s">
-        <v>3586</v>
+        <v>3577</v>
       </c>
       <c r="B185" s="193">
         <v>60196388</v>
       </c>
       <c r="C185" s="193" t="s">
-        <v>3585</v>
+        <v>3576</v>
       </c>
       <c r="D185" s="447" t="s">
-        <v>3529</v>
+        <v>3520</v>
       </c>
       <c r="E185" s="433" t="s">
-        <v>3581</v>
+        <v>3572</v>
       </c>
       <c r="F185" s="193"/>
       <c r="G185" s="183"/>
@@ -39911,19 +39902,19 @@
     </row>
     <row r="186" spans="1:9">
       <c r="A186" s="183" t="s">
-        <v>2993</v>
+        <v>2986</v>
       </c>
       <c r="B186" s="183">
         <v>64403333</v>
       </c>
       <c r="C186" s="191" t="s">
-        <v>3602</v>
+        <v>3593</v>
       </c>
       <c r="D186" s="183" t="s">
-        <v>3592</v>
+        <v>3583</v>
       </c>
       <c r="E186" s="433" t="s">
-        <v>3581</v>
+        <v>3572</v>
       </c>
       <c r="F186" s="193"/>
       <c r="G186" s="183"/>
@@ -39931,19 +39922,19 @@
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="193" t="s">
-        <v>3625</v>
+        <v>3616</v>
       </c>
       <c r="B187" s="193">
         <v>68071614</v>
       </c>
       <c r="C187" s="193" t="s">
-        <v>3622</v>
+        <v>3613</v>
       </c>
       <c r="D187" s="193" t="s">
-        <v>3623</v>
+        <v>3614</v>
       </c>
       <c r="E187" s="433" t="s">
-        <v>3624</v>
+        <v>3615</v>
       </c>
       <c r="F187" s="193"/>
       <c r="G187" s="183"/>
@@ -39957,13 +39948,13 @@
         <v>63950696</v>
       </c>
       <c r="C188" s="457" t="s">
-        <v>3652</v>
+        <v>3643</v>
       </c>
       <c r="D188" s="457" t="s">
         <v>2805</v>
       </c>
       <c r="E188" s="433" t="s">
-        <v>3653</v>
+        <v>3644</v>
       </c>
       <c r="F188" s="458"/>
       <c r="G188" s="448"/>
@@ -40015,7 +40006,7 @@
         <v>316</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>3503</v>
+        <v>3494</v>
       </c>
       <c r="E194" s="30"/>
       <c r="F194"/>
@@ -40041,7 +40032,7 @@
         <v>439</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>3556</v>
+        <v>3547</v>
       </c>
       <c r="E196" s="30"/>
       <c r="F196"/>
@@ -40052,7 +40043,7 @@
         <v>26</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>3622</v>
+        <v>3613</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -40060,7 +40051,7 @@
         <v>1327</v>
       </c>
       <c r="D198" s="429" t="s">
-        <v>3652</v>
+        <v>3643</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -40068,7 +40059,7 @@
         <v>1661</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>3337</v>
+        <v>3328</v>
       </c>
       <c r="F199" s="394"/>
     </row>
@@ -40077,7 +40068,7 @@
         <v>1308</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>3339</v>
+        <v>3330</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -40085,7 +40076,7 @@
         <v>406</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>3445</v>
+        <v>3436</v>
       </c>
     </row>
     <row r="202" spans="1:9">
@@ -40093,7 +40084,7 @@
         <v>708</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>3448</v>
+        <v>3439</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -40101,7 +40092,7 @@
         <v>281</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>3464</v>
+        <v>3455</v>
       </c>
     </row>
     <row r="204" spans="1:9">
@@ -40109,7 +40100,7 @@
         <v>2376</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>3465</v>
+        <v>3456</v>
       </c>
     </row>
     <row r="205" spans="1:9">
@@ -40119,7 +40110,7 @@
         <v>465</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>3468</v>
+        <v>3459</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -40127,7 +40118,7 @@
         <v>219</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>3472</v>
+        <v>3463</v>
       </c>
     </row>
     <row r="207" spans="1:9">
@@ -40135,7 +40126,7 @@
         <v>427</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>3485</v>
+        <v>3476</v>
       </c>
     </row>
     <row r="208" spans="1:9">
@@ -40143,7 +40134,7 @@
         <v>1052</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>3499</v>
+        <v>3490</v>
       </c>
     </row>
     <row r="223" spans="1:9">
@@ -41358,7 +41349,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>3153</v>
+        <v>3145</v>
       </c>
       <c r="B3">
         <v>62349088</v>
@@ -41379,10 +41370,10 @@
         <v>705</v>
       </c>
       <c r="H3" t="s">
-        <v>3517</v>
+        <v>3508</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>3047</v>
+        <v>3040</v>
       </c>
       <c r="J3"/>
     </row>
@@ -41409,10 +41400,10 @@
         <v>515</v>
       </c>
       <c r="H4" t="s">
-        <v>3343</v>
+        <v>3334</v>
       </c>
       <c r="I4" t="s">
-        <v>3646</v>
+        <v>3637</v>
       </c>
       <c r="J4"/>
     </row>
@@ -41421,7 +41412,7 @@
         <v>2851</v>
       </c>
       <c r="B5" t="s">
-        <v>2884</v>
+        <v>2880</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>480</v>
@@ -41430,7 +41421,7 @@
         <v>1522</v>
       </c>
       <c r="E5" t="s">
-        <v>3075</v>
+        <v>3068</v>
       </c>
       <c r="F5" t="s">
         <v>2171</v>
@@ -41439,10 +41430,10 @@
         <v>515</v>
       </c>
       <c r="H5" s="220" t="s">
-        <v>3351</v>
+        <v>3342</v>
       </c>
       <c r="I5" s="220" t="s">
-        <v>3188</v>
+        <v>3180</v>
       </c>
       <c r="J5" t="s">
         <v>1397</v>
@@ -41450,31 +41441,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>3516</v>
+        <v>3507</v>
       </c>
       <c r="B6" t="s">
-        <v>3548</v>
+        <v>3539</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>427</v>
       </c>
       <c r="D6" t="s">
-        <v>3361</v>
+        <v>3352</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>3359</v>
+        <v>3350</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>2890</v>
+        <v>2886</v>
       </c>
       <c r="G6" t="s">
         <v>436</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>3138</v>
+        <v>3130</v>
       </c>
       <c r="I6" t="s">
-        <v>3659</v>
+        <v>3650</v>
       </c>
       <c r="J6"/>
     </row>
@@ -41506,13 +41497,13 @@
         <v>143</v>
       </c>
       <c r="B8" t="s">
-        <v>2950</v>
+        <v>2944</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>2065</v>
       </c>
       <c r="D8" t="s">
-        <v>2949</v>
+        <v>2943</v>
       </c>
       <c r="E8" t="s">
         <v>2331</v>
@@ -41524,10 +41515,10 @@
         <v>250</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>3181</v>
+        <v>3173</v>
       </c>
       <c r="I8" t="s">
-        <v>3308</v>
+        <v>3299</v>
       </c>
       <c r="J8"/>
     </row>
@@ -41557,7 +41548,7 @@
         <v>2758</v>
       </c>
       <c r="I9" s="275" t="s">
-        <v>2866</v>
+        <v>2864</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -41618,16 +41609,16 @@
     </row>
     <row r="16" spans="1:10">
       <c r="C16" s="8" t="s">
-        <v>2869</v>
+        <v>2867</v>
       </c>
       <c r="D16" t="s">
-        <v>2868</v>
+        <v>2866</v>
       </c>
       <c r="E16" t="s">
-        <v>2900</v>
+        <v>2896</v>
       </c>
       <c r="F16" t="s">
-        <v>2901</v>
+        <v>2897</v>
       </c>
       <c r="G16" t="s">
         <v>121</v>
@@ -41709,7 +41700,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="10" t="s">
-        <v>3424</v>
+        <v>3415</v>
       </c>
       <c r="B5" s="10">
         <v>67992849</v>
@@ -41730,7 +41721,7 @@
         <v>517</v>
       </c>
       <c r="H5" s="220" t="s">
-        <v>3543</v>
+        <v>3534</v>
       </c>
       <c r="I5" s="278" t="s">
         <v>2158</v>
@@ -41762,12 +41753,12 @@
         <v>2769</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>3051</v>
+        <v>3044</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="10" t="s">
-        <v>3512</v>
+        <v>3503</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>2411</v>
@@ -41776,7 +41767,7 @@
         <v>1726</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>3228</v>
+        <v>3220</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1699</v>
@@ -41788,10 +41779,10 @@
         <v>517</v>
       </c>
       <c r="H7" t="s">
-        <v>3201</v>
+        <v>3193</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>3229</v>
+        <v>3221</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -41807,7 +41798,7 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="10" t="s">
-        <v>3301</v>
+        <v>3292</v>
       </c>
       <c r="B11" s="10">
         <v>64403333</v>
@@ -41839,7 +41830,7 @@
         <v>2151</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>3243</v>
+        <v>3235</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>961</v>
@@ -41851,10 +41842,10 @@
         <v>517</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>3244</v>
+        <v>3236</v>
       </c>
       <c r="I12" t="s">
-        <v>3398</v>
+        <v>3389</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -41870,7 +41861,7 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="10" t="s">
-        <v>2891</v>
+        <v>2887</v>
       </c>
       <c r="B15" s="10">
         <v>68543713</v>
@@ -41879,7 +41870,7 @@
         <v>2210</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>3078</v>
+        <v>3071</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>961</v>
@@ -41891,10 +41882,10 @@
         <v>517</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>3079</v>
+        <v>3072</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>3088</v>
+        <v>3081</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -41920,7 +41911,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="10" t="s">
-        <v>3512</v>
+        <v>3503</v>
       </c>
       <c r="B17" s="10">
         <v>64403333</v>
@@ -41943,7 +41934,7 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="10" t="s">
-        <v>3301</v>
+        <v>3292</v>
       </c>
       <c r="B18" s="10">
         <v>60345107</v>
@@ -41952,7 +41943,7 @@
         <v>2339</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>3305</v>
+        <v>3296</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>961</v>
@@ -41964,10 +41955,10 @@
         <v>517</v>
       </c>
       <c r="H18" s="428" t="s">
-        <v>3270</v>
+        <v>3261</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>3376</v>
+        <v>3367</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -41993,10 +41984,10 @@
         <v>517</v>
       </c>
       <c r="H19" s="275" t="s">
-        <v>3025</v>
+        <v>3018</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>3489</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="190" customFormat="1" ht="26">
@@ -42012,13 +42003,13 @@
         <v>2622</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>3454</v>
+        <v>3445</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>2420</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>3426</v>
+        <v>3417</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>961</v>
@@ -42030,15 +42021,15 @@
         <v>517</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>3544</v>
+        <v>3535</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>3227</v>
+        <v>3219</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>3521</v>
+        <v>3512</v>
       </c>
       <c r="B23" s="10">
         <v>64720128</v>
@@ -42059,10 +42050,10 @@
         <v>517</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>3522</v>
+        <v>3513</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>3523</v>
+        <v>3514</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -42076,7 +42067,7 @@
         <v>2438</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>3176</v>
+        <v>3168</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>961</v>
@@ -42088,10 +42079,10 @@
         <v>517</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>3486</v>
+        <v>3477</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>3029</v>
+        <v>3022</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -42101,7 +42092,7 @@
         <v>2451</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>3077</v>
+        <v>3070</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>961</v>
@@ -42220,13 +42211,13 @@
         <v>2466</v>
       </c>
       <c r="B4" t="s">
-        <v>3145</v>
+        <v>3137</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1867</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>3144</v>
+        <v>3136</v>
       </c>
       <c r="E4" t="s">
         <v>1868</v>
@@ -42238,13 +42229,13 @@
         <v>965</v>
       </c>
       <c r="H4" t="s">
-        <v>3160</v>
+        <v>3152</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>3169</v>
+        <v>3161</v>
       </c>
       <c r="J4" t="s">
-        <v>3224</v>
+        <v>3216</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -42293,7 +42284,7 @@
         <v>965</v>
       </c>
       <c r="H6" t="s">
-        <v>3186</v>
+        <v>3178</v>
       </c>
       <c r="J6" s="49" t="s">
         <v>2232</v>
@@ -42304,13 +42295,13 @@
         <v>2619</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>2917</v>
+        <v>2912</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>2294</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>3514</v>
+        <v>3505</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>2295</v>
@@ -42322,25 +42313,25 @@
         <v>965</v>
       </c>
       <c r="H7" t="s">
-        <v>3125</v>
+        <v>3117</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>3267</v>
+        <v>3258</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>3071</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="278"/>
       <c r="C8" s="3" t="s">
-        <v>3595</v>
+        <v>3586</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>3596</v>
+        <v>3587</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>3597</v>
+        <v>3588</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>1742</v>
@@ -42349,45 +42340,45 @@
         <v>965</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>3076</v>
+        <v>3069</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>3237</v>
+        <v>3229</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>3087</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="10" t="s">
-        <v>3091</v>
+        <v>3084</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>3092</v>
+        <v>3085</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>3089</v>
+        <v>3082</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>2915</v>
+        <v>2910</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>3090</v>
+        <v>3083</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>2916</v>
+        <v>2911</v>
       </c>
       <c r="G9" t="s">
         <v>965</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>3093</v>
+        <v>3086</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>3094</v>
+        <v>3087</v>
       </c>
       <c r="J9" t="s">
-        <v>3140</v>
+        <v>3132</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -42395,16 +42386,16 @@
         <v>1432</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>3242</v>
+        <v>3234</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>3240</v>
+        <v>3232</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>3241</v>
+        <v>3233</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>3159</v>
+        <v>3151</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>2296</v>
@@ -42413,13 +42404,13 @@
         <v>965</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>3346</v>
+        <v>3337</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>3349</v>
+        <v>3340</v>
       </c>
       <c r="J10" t="s">
-        <v>3400</v>
+        <v>3391</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -42430,7 +42421,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="C15" s="429" t="s">
-        <v>3595</v>
+        <v>3586</v>
       </c>
     </row>
   </sheetData>
@@ -42571,10 +42562,10 @@
         <v>60240509</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>3572</v>
+        <v>3563</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>3573</v>
+        <v>3564</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>2620</v>
@@ -42586,7 +42577,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="10" t="s">
-        <v>2908</v>
+        <v>2904</v>
       </c>
       <c r="B10" s="10">
         <v>64676716</v>
@@ -42595,7 +42586,7 @@
         <v>1790</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>3058</v>
+        <v>3051</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>2620</v>
@@ -42636,7 +42627,7 @@
         <v>60052700</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>2952</v>
+        <v>2946</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>2643</v>
@@ -42657,7 +42648,7 @@
         <v>63132287</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>2974</v>
+        <v>2967</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>2643</v>
@@ -42834,7 +42825,7 @@
     <row r="1" spans="1:10" s="410" customFormat="1" ht="42.5" customHeight="1">
       <c r="A1" s="409"/>
       <c r="B1" s="409" t="s">
-        <v>2963</v>
+        <v>2956</v>
       </c>
       <c r="C1" s="409"/>
     </row>
@@ -42843,28 +42834,28 @@
         <v>147</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>3010</v>
+        <v>3003</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3148</v>
+        <v>3140</v>
       </c>
       <c r="E4" t="s">
-        <v>2964</v>
+        <v>2957</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>3149</v>
+        <v>3141</v>
       </c>
       <c r="G4" s="275" t="s">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>3130</v>
+        <v>3122</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>3142</v>
+        <v>3134</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>3256</v>
+        <v>3247</v>
       </c>
     </row>
   </sheetData>
@@ -43210,7 +43201,7 @@
         <v>2566</v>
       </c>
       <c r="C5" s="325" t="s">
-        <v>2890</v>
+        <v>2886</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="325" customFormat="1">
@@ -43218,10 +43209,10 @@
         <v>2545</v>
       </c>
       <c r="B6" s="325" t="s">
-        <v>2889</v>
+        <v>2885</v>
       </c>
       <c r="C6" s="325" t="s">
-        <v>2889</v>
+        <v>2885</v>
       </c>
     </row>
     <row r="7" spans="1:13" s="325" customFormat="1">
@@ -43296,10 +43287,10 @@
         <v>2575</v>
       </c>
       <c r="H14" s="331" t="s">
-        <v>2892</v>
+        <v>2888</v>
       </c>
       <c r="I14" s="331" t="s">
-        <v>2895</v>
+        <v>2891</v>
       </c>
       <c r="L14" s="331"/>
       <c r="M14" s="331"/>
@@ -43327,10 +43318,10 @@
         <v>2576</v>
       </c>
       <c r="H15" s="332" t="s">
-        <v>2893</v>
+        <v>2889</v>
       </c>
       <c r="I15" s="332" t="s">
-        <v>2896</v>
+        <v>2892</v>
       </c>
       <c r="L15" s="332"/>
       <c r="M15" s="332"/>
@@ -43358,7 +43349,7 @@
         <v>2577</v>
       </c>
       <c r="H16" s="332" t="s">
-        <v>2894</v>
+        <v>2890</v>
       </c>
       <c r="I16" s="332" t="s">
         <v>1344</v>
@@ -43371,7 +43362,7 @@
         <v>2550</v>
       </c>
       <c r="B17" s="396" t="s">
-        <v>2886</v>
+        <v>2882</v>
       </c>
       <c r="C17" s="396"/>
       <c r="D17" s="396"/>
@@ -43388,7 +43379,7 @@
         <v>2545</v>
       </c>
       <c r="B18" s="396" t="s">
-        <v>2887</v>
+        <v>2883</v>
       </c>
       <c r="C18" s="396"/>
       <c r="D18" s="396"/>
@@ -43405,7 +43396,7 @@
         <v>2546</v>
       </c>
       <c r="B19" s="396" t="s">
-        <v>2888</v>
+        <v>2884</v>
       </c>
       <c r="C19" s="396"/>
       <c r="D19" s="396"/>
@@ -44260,7 +44251,7 @@
         <v>51</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>3215</v>
+        <v>3207</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>1160</v>
@@ -44272,10 +44263,10 @@
         <v>159</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>3427</v>
+        <v>3418</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>3438</v>
+        <v>3429</v>
       </c>
       <c r="N6" s="4" t="s">
         <v>26</v>
@@ -44307,13 +44298,13 @@
         <v>2271</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>3233</v>
+        <v>3225</v>
       </c>
       <c r="L7" s="3"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>3635</v>
+        <v>3626</v>
       </c>
       <c r="B8" t="s">
         <v>452</v>
@@ -44337,7 +44328,7 @@
         <v>2742</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>3213</v>
+        <v>3205</v>
       </c>
     </row>
     <row r="9" spans="1:14" s="4" customFormat="1">
@@ -44354,19 +44345,19 @@
         <v>2161</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>3439</v>
+        <v>3430</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>3440</v>
+        <v>3431</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>159</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>3402</v>
+        <v>3393</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>3357</v>
+        <v>3348</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>815</v>
@@ -44374,7 +44365,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="4" t="s">
-        <v>3612</v>
+        <v>3603</v>
       </c>
       <c r="B10" s="4">
         <v>67916500</v>
@@ -44395,10 +44386,10 @@
         <v>244</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>3517</v>
+        <v>3508</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>3286</v>
+        <v>3277</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -44415,19 +44406,19 @@
         <v>1513</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>3354</v>
+        <v>3345</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>2945</v>
+        <v>2939</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>244</v>
       </c>
       <c r="H11" t="s">
-        <v>3641</v>
+        <v>3632</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>3609</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -44453,18 +44444,18 @@
         <v>244</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>3644</v>
+        <v>3635</v>
       </c>
       <c r="I12" s="306" t="s">
-        <v>3002</v>
+        <v>2995</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="4" t="s">
-        <v>2983</v>
+        <v>2976</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>3661</v>
+        <v>3652</v>
       </c>
       <c r="C13" s="22" t="s">
         <v>1221</v>
@@ -44482,10 +44473,10 @@
         <v>244</v>
       </c>
       <c r="H13" s="220" t="s">
-        <v>3352</v>
+        <v>3343</v>
       </c>
       <c r="I13" s="306" t="s">
-        <v>2954</v>
+        <v>2948</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="4" customFormat="1">
@@ -44511,25 +44502,25 @@
         <v>244</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>3553</v>
+        <v>3544</v>
       </c>
       <c r="I14" s="220" t="s">
-        <v>3600</v>
+        <v>3591</v>
       </c>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="105" t="s">
-        <v>2877</v>
+        <v>2873</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>2878</v>
+        <v>2874</v>
       </c>
       <c r="C15" s="22" t="s">
         <v>340</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>2876</v>
+        <v>2872</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>1532</v>
@@ -44541,10 +44532,10 @@
         <v>887</v>
       </c>
       <c r="H15" t="s">
-        <v>3261</v>
+        <v>3252</v>
       </c>
       <c r="I15" t="s">
-        <v>3046</v>
+        <v>3039</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>498</v>
@@ -44561,7 +44552,7 @@
         <v>2604</v>
       </c>
       <c r="D16" t="s">
-        <v>2865</v>
+        <v>2863</v>
       </c>
       <c r="E16" t="s">
         <v>2606</v>
@@ -44573,10 +44564,10 @@
         <v>159</v>
       </c>
       <c r="H16" t="s">
-        <v>3559</v>
+        <v>3550</v>
       </c>
       <c r="I16" t="s">
-        <v>3428</v>
+        <v>3419</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>805</v>
@@ -44584,7 +44575,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>3424</v>
+        <v>3415</v>
       </c>
       <c r="B17">
         <v>65325884</v>
@@ -44607,7 +44598,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="4" t="s">
-        <v>3512</v>
+        <v>3503</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>2112</v>
@@ -44619,24 +44610,24 @@
         <v>2221</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>2944</v>
+        <v>2938</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>2945</v>
+        <v>2939</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>244</v>
       </c>
       <c r="H18" s="49" t="s">
-        <v>3105</v>
+        <v>3098</v>
       </c>
       <c r="I18" t="s">
-        <v>3634</v>
+        <v>3625</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="4" customFormat="1">
       <c r="A19" s="4" t="s">
-        <v>2993</v>
+        <v>2986</v>
       </c>
       <c r="B19" s="4">
         <v>64403333</v>
@@ -44648,10 +44639,10 @@
         <v>2605</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>3456</v>
+        <v>3447</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>3440</v>
+        <v>3431</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>1230</v>
@@ -44661,7 +44652,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="4" t="s">
-        <v>3424</v>
+        <v>3415</v>
       </c>
       <c r="B20">
         <v>64403333</v>
@@ -44687,7 +44678,7 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="4" t="s">
-        <v>2931</v>
+        <v>2925</v>
       </c>
       <c r="B21" s="4">
         <v>64403333</v>
@@ -44710,7 +44701,7 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="4" t="s">
-        <v>2908</v>
+        <v>2904</v>
       </c>
       <c r="B22" s="4">
         <v>64403333</v>
@@ -44733,7 +44724,7 @@
     </row>
     <row r="23" spans="1:12" s="4" customFormat="1">
       <c r="A23" t="s">
-        <v>3424</v>
+        <v>3415</v>
       </c>
       <c r="B23">
         <v>63247837</v>
@@ -44742,7 +44733,7 @@
         <v>2613</v>
       </c>
       <c r="D23" t="s">
-        <v>3373</v>
+        <v>3364</v>
       </c>
       <c r="E23" t="s">
         <v>2616</v>
@@ -44754,10 +44745,10 @@
         <v>159</v>
       </c>
       <c r="H23" t="s">
-        <v>3311</v>
+        <v>3302</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>3394</v>
+        <v>3385</v>
       </c>
       <c r="L23" s="6"/>
     </row>
@@ -44772,10 +44763,10 @@
         <v>1634</v>
       </c>
       <c r="D24" t="s">
-        <v>3129</v>
+        <v>3121</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>3131</v>
+        <v>3123</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>2479</v>
@@ -44786,19 +44777,19 @@
     </row>
     <row r="25" spans="1:12" s="4" customFormat="1">
       <c r="A25" s="4" t="s">
-        <v>3470</v>
+        <v>3461</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>3484</v>
+        <v>3475</v>
       </c>
       <c r="C25" s="21" t="s">
         <v>1329</v>
       </c>
       <c r="D25" t="s">
-        <v>3483</v>
+        <v>3474</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>3039</v>
+        <v>3032</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>2482</v>
@@ -44807,10 +44798,10 @@
         <v>244</v>
       </c>
       <c r="H25" s="220" t="s">
-        <v>3638</v>
+        <v>3629</v>
       </c>
       <c r="I25" s="220" t="s">
-        <v>3547</v>
+        <v>3538</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="4" customFormat="1">
@@ -44836,10 +44827,10 @@
         <v>159</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>3569</v>
+        <v>3560</v>
       </c>
       <c r="I27" t="s">
-        <v>3265</v>
+        <v>3256</v>
       </c>
       <c r="L27" s="4" t="s">
         <v>813</v>
@@ -44847,7 +44838,7 @@
     </row>
     <row r="28" spans="1:12" s="4" customFormat="1">
       <c r="A28" t="s">
-        <v>3608</v>
+        <v>3599</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>2473</v>
@@ -44859,7 +44850,7 @@
         <v>2033</v>
       </c>
       <c r="E28" t="s">
-        <v>3141</v>
+        <v>3133</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>2482</v>
@@ -44871,7 +44862,7 @@
         <v>2660</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>3505</v>
+        <v>3496</v>
       </c>
       <c r="K28"/>
     </row>
@@ -44886,41 +44877,41 @@
         <v>350</v>
       </c>
       <c r="D29" s="75" t="s">
-        <v>2902</v>
+        <v>2898</v>
       </c>
       <c r="E29" t="s">
-        <v>3425</v>
+        <v>3416</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>2945</v>
+        <v>2939</v>
       </c>
       <c r="G29" s="75" t="s">
         <v>250</v>
       </c>
       <c r="H29" s="49" t="s">
-        <v>2903</v>
+        <v>2899</v>
       </c>
       <c r="I29" t="s">
-        <v>3370</v>
+        <v>3361</v>
       </c>
       <c r="J29" s="4"/>
       <c r="L29" s="135"/>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>2993</v>
+        <v>2986</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>3100</v>
+        <v>3093</v>
       </c>
       <c r="C30" s="22" t="s">
         <v>402</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>3099</v>
+        <v>3092</v>
       </c>
       <c r="E30" t="s">
-        <v>3287</v>
+        <v>3278</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>1344</v>
@@ -44929,7 +44920,7 @@
         <v>159</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>3103</v>
+        <v>3096</v>
       </c>
       <c r="I30" s="55" t="s">
         <v>2768</v>
@@ -44937,7 +44928,7 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>3422</v>
+        <v>3413</v>
       </c>
       <c r="B31" s="4">
         <v>69409351</v>
@@ -44958,10 +44949,10 @@
         <v>159</v>
       </c>
       <c r="H31" t="s">
-        <v>3260</v>
+        <v>3251</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>3185</v>
+        <v>3177</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -44987,7 +44978,7 @@
         <v>159</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>3022</v>
+        <v>3015</v>
       </c>
       <c r="I32" s="49" t="s">
         <v>2756</v>
@@ -44998,13 +44989,13 @@
         <v>2619</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>3589</v>
+        <v>3580</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>2603</v>
       </c>
       <c r="D33" t="s">
-        <v>3588</v>
+        <v>3579</v>
       </c>
       <c r="E33" t="s">
         <v>2606</v>
@@ -45016,7 +45007,7 @@
         <v>2607</v>
       </c>
       <c r="H33" s="49" t="s">
-        <v>3048</v>
+        <v>3041</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -45024,13 +45015,13 @@
         <v>1432</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>3537</v>
+        <v>3528</v>
       </c>
       <c r="C34" s="21" t="s">
         <v>2600</v>
       </c>
       <c r="D34" t="s">
-        <v>3209</v>
+        <v>3201</v>
       </c>
       <c r="E34" t="s">
         <v>2606</v>
@@ -45042,25 +45033,25 @@
         <v>159</v>
       </c>
       <c r="H34" t="s">
-        <v>3220</v>
+        <v>3212</v>
       </c>
       <c r="I34" t="s">
-        <v>3348</v>
+        <v>3339</v>
       </c>
       <c r="J34" s="4"/>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>2983</v>
+        <v>2976</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>2988</v>
+        <v>2981</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>2601</v>
       </c>
       <c r="D35" t="s">
-        <v>2987</v>
+        <v>2980</v>
       </c>
       <c r="E35" t="s">
         <v>2606</v>
@@ -45072,24 +45063,24 @@
         <v>2607</v>
       </c>
       <c r="H35" s="306" t="s">
-        <v>3026</v>
+        <v>3019</v>
       </c>
       <c r="I35" t="s">
-        <v>3037</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>3424</v>
+        <v>3415</v>
       </c>
       <c r="B36" t="s">
-        <v>3453</v>
+        <v>3444</v>
       </c>
       <c r="C36" s="22" t="s">
         <v>2602</v>
       </c>
       <c r="D36" t="s">
-        <v>3452</v>
+        <v>3443</v>
       </c>
       <c r="E36" t="s">
         <v>2606</v>
@@ -45101,10 +45092,10 @@
         <v>159</v>
       </c>
       <c r="H36" t="s">
-        <v>3455</v>
+        <v>3446</v>
       </c>
       <c r="I36" t="s">
-        <v>3248</v>
+        <v>3239</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -45118,7 +45109,7 @@
         <v>2614</v>
       </c>
       <c r="D37" t="s">
-        <v>2936</v>
+        <v>2930</v>
       </c>
       <c r="E37" t="s">
         <v>2616</v>
@@ -45130,10 +45121,10 @@
         <v>159</v>
       </c>
       <c r="H37" t="s">
-        <v>3656</v>
+        <v>3647</v>
       </c>
       <c r="I37" t="s">
-        <v>2981</v>
+        <v>2974</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -45141,7 +45132,7 @@
         <v>157</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>3115</v>
+        <v>3107</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>2615</v>
@@ -45159,10 +45150,10 @@
         <v>159</v>
       </c>
       <c r="H38" s="97" t="s">
-        <v>3206</v>
+        <v>3198</v>
       </c>
       <c r="I38" t="s">
-        <v>3304</v>
+        <v>3295</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -45175,10 +45166,10 @@
         <v>1354</v>
       </c>
       <c r="E41" s="97" t="s">
-        <v>3362</v>
+        <v>3353</v>
       </c>
       <c r="F41" s="105" t="s">
-        <v>3363</v>
+        <v>3354</v>
       </c>
       <c r="G41" s="105" t="s">
         <v>159</v>
@@ -45196,10 +45187,10 @@
         <v>2098</v>
       </c>
       <c r="E42" s="97" t="s">
-        <v>3362</v>
+        <v>3353</v>
       </c>
       <c r="F42" s="105" t="s">
-        <v>3363</v>
+        <v>3354</v>
       </c>
       <c r="G42" s="105" t="s">
         <v>159</v>
@@ -45215,7 +45206,7 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="4" t="s">
-        <v>3301</v>
+        <v>3292</v>
       </c>
       <c r="B45" t="s">
         <v>2517</v>
@@ -45245,7 +45236,7 @@
         <v>2829</v>
       </c>
       <c r="K45" t="s">
-        <v>3654</v>
+        <v>3645</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="4" customFormat="1">
@@ -45636,13 +45627,13 @@
         <v>157</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>3118</v>
+        <v>3110</v>
       </c>
       <c r="C2" s="276" t="s">
         <v>254</v>
       </c>
       <c r="D2" s="106" t="s">
-        <v>3117</v>
+        <v>3109</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>1299</v>
@@ -45654,16 +45645,16 @@
         <v>62</v>
       </c>
       <c r="H2" s="300" t="s">
-        <v>3156</v>
+        <v>3148</v>
       </c>
       <c r="I2" s="106" t="s">
-        <v>3128</v>
+        <v>3120</v>
       </c>
       <c r="J2" s="107" t="s">
-        <v>3630</v>
+        <v>3621</v>
       </c>
       <c r="K2" s="30" t="s">
-        <v>2940</v>
+        <v>2934</v>
       </c>
       <c r="M2" s="159"/>
     </row>
@@ -45678,7 +45669,7 @@
         <v>1182</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>3211</v>
+        <v>3203</v>
       </c>
       <c r="E4" s="32" t="s">
         <v>2405</v>
@@ -45690,25 +45681,25 @@
         <v>270</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>3386</v>
+        <v>3377</v>
       </c>
       <c r="I4" s="30" t="s">
-        <v>3269</v>
+        <v>3260</v>
       </c>
       <c r="J4" s="139" t="s">
-        <v>3642</v>
+        <v>3633</v>
       </c>
       <c r="K4" s="139" t="s">
-        <v>3457</v>
+        <v>3448</v>
       </c>
       <c r="M4" s="39"/>
     </row>
     <row r="5" spans="1:13" s="30" customFormat="1">
       <c r="A5" s="30" t="s">
-        <v>3301</v>
+        <v>3292</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>3306</v>
+        <v>3297</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>1114</v>
@@ -45726,22 +45717,22 @@
         <v>65</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>3604</v>
+        <v>3595</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>2994</v>
+        <v>2987</v>
       </c>
       <c r="J5" s="30" t="s">
-        <v>3379</v>
+        <v>3370</v>
       </c>
       <c r="K5" s="30" t="s">
-        <v>3288</v>
+        <v>3279</v>
       </c>
       <c r="M5" s="36"/>
     </row>
     <row r="6" spans="1:13" s="30" customFormat="1">
       <c r="A6" s="107" t="s">
-        <v>3153</v>
+        <v>3145</v>
       </c>
       <c r="B6" s="30" t="s">
         <v>2187</v>
@@ -45750,7 +45741,7 @@
         <v>2773</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>3527</v>
+        <v>3518</v>
       </c>
       <c r="E6" s="140" t="s">
         <v>2734</v>
@@ -45762,22 +45753,22 @@
         <v>65</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>3598</v>
+        <v>3589</v>
       </c>
       <c r="I6" s="432" t="s">
-        <v>3121</v>
+        <v>3113</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="K6" s="30" t="s">
-        <v>3246</v>
+        <v>3238</v>
       </c>
       <c r="M6" s="36"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="107" t="s">
-        <v>3184</v>
+        <v>3176</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>1212</v>
@@ -45786,28 +45777,28 @@
         <v>1091</v>
       </c>
       <c r="D7" t="s">
-        <v>3387</v>
+        <v>3378</v>
       </c>
       <c r="E7" s="107" t="s">
-        <v>3366</v>
+        <v>3357</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>3367</v>
+        <v>3358</v>
       </c>
       <c r="G7" s="106" t="s">
         <v>720</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>3262</v>
+        <v>3253</v>
       </c>
       <c r="I7" s="217" t="s">
-        <v>3003</v>
+        <v>2996</v>
       </c>
       <c r="J7" s="217" t="s">
         <v>2676</v>
       </c>
       <c r="K7" s="30" t="s">
-        <v>3027</v>
+        <v>3020</v>
       </c>
       <c r="M7" s="36"/>
     </row>
@@ -45822,7 +45813,7 @@
         <v>985</v>
       </c>
       <c r="D8" s="139" t="s">
-        <v>3478</v>
+        <v>3469</v>
       </c>
       <c r="E8" s="107" t="s">
         <v>1157</v>
@@ -45834,22 +45825,22 @@
         <v>65</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>3610</v>
+        <v>3601</v>
       </c>
       <c r="I8" s="32" t="s">
-        <v>3085</v>
+        <v>3078</v>
       </c>
       <c r="J8" s="449" t="s">
-        <v>2953</v>
+        <v>2947</v>
       </c>
       <c r="K8" s="139" t="s">
-        <v>3433</v>
+        <v>3424</v>
       </c>
       <c r="M8" s="36"/>
     </row>
     <row r="9" spans="1:13" s="107" customFormat="1">
       <c r="A9" s="302" t="s">
-        <v>3254</v>
+        <v>3245</v>
       </c>
       <c r="B9" s="32" t="s">
         <v>1676</v>
@@ -45870,22 +45861,22 @@
         <v>65</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>3046</v>
+        <v>3039</v>
       </c>
       <c r="I9" s="107" t="s">
-        <v>3626</v>
+        <v>3617</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>3315</v>
+        <v>3306</v>
       </c>
       <c r="K9" s="107" t="s">
-        <v>3049</v>
+        <v>3042</v>
       </c>
       <c r="M9" s="36"/>
     </row>
     <row r="10" spans="1:13" s="30" customFormat="1">
       <c r="A10" s="30" t="s">
-        <v>3254</v>
+        <v>3245</v>
       </c>
       <c r="B10" s="30">
         <v>69575383</v>
@@ -45906,16 +45897,16 @@
         <v>65</v>
       </c>
       <c r="H10" s="107" t="s">
-        <v>3312</v>
+        <v>3303</v>
       </c>
       <c r="I10" t="s">
-        <v>3397</v>
+        <v>3388</v>
       </c>
       <c r="J10" s="219" t="s">
-        <v>3518</v>
+        <v>3509</v>
       </c>
       <c r="K10" s="107" t="s">
-        <v>3073</v>
+        <v>3066</v>
       </c>
       <c r="M10" s="34"/>
     </row>
@@ -45942,16 +45933,16 @@
         <v>605</v>
       </c>
       <c r="H11" s="139" t="s">
-        <v>3186</v>
+        <v>3178</v>
       </c>
       <c r="I11" s="30" t="s">
-        <v>3613</v>
+        <v>3604</v>
       </c>
       <c r="J11" s="107" t="s">
-        <v>3023</v>
+        <v>3016</v>
       </c>
       <c r="K11" s="107" t="s">
-        <v>3308</v>
+        <v>3299</v>
       </c>
       <c r="M11" s="36"/>
     </row>
@@ -45966,7 +45957,7 @@
         <v>72</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>2879</v>
+        <v>2875</v>
       </c>
       <c r="E12" s="106" t="s">
         <v>908</v>
@@ -45978,22 +45969,22 @@
         <v>245</v>
       </c>
       <c r="H12" s="450" t="s">
-        <v>2943</v>
+        <v>2937</v>
       </c>
       <c r="I12" s="106" t="s">
-        <v>3593</v>
+        <v>3584</v>
       </c>
       <c r="J12" s="106" t="s">
-        <v>3526</v>
+        <v>3517</v>
       </c>
       <c r="K12" s="107" t="s">
-        <v>3303</v>
+        <v>3294</v>
       </c>
       <c r="M12" s="151"/>
     </row>
     <row r="13" spans="1:13" s="107" customFormat="1">
       <c r="A13" s="140" t="s">
-        <v>3470</v>
+        <v>3461</v>
       </c>
       <c r="B13" s="107" t="s">
         <v>2804</v>
@@ -46002,7 +45993,7 @@
         <v>919</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>3171</v>
+        <v>3163</v>
       </c>
       <c r="E13" s="140" t="s">
         <v>2774</v>
@@ -46014,16 +46005,16 @@
         <v>65</v>
       </c>
       <c r="H13" s="30" t="s">
-        <v>3172</v>
+        <v>3164</v>
       </c>
       <c r="I13" s="30" t="s">
-        <v>3272</v>
+        <v>3263</v>
       </c>
       <c r="J13" s="107" t="s">
-        <v>3318</v>
+        <v>3309</v>
       </c>
       <c r="K13" t="s">
-        <v>3344</v>
+        <v>3335</v>
       </c>
       <c r="M13" s="36"/>
     </row>
@@ -46050,13 +46041,13 @@
         <v>65</v>
       </c>
       <c r="H14" s="107" t="s">
-        <v>3403</v>
+        <v>3394</v>
       </c>
       <c r="I14" s="411" t="s">
         <v>2272</v>
       </c>
       <c r="J14" s="32" t="s">
-        <v>3233</v>
+        <v>3225</v>
       </c>
       <c r="M14" s="36"/>
     </row>
@@ -46083,16 +46074,16 @@
         <v>66</v>
       </c>
       <c r="H15" t="s">
-        <v>3554</v>
+        <v>3545</v>
       </c>
       <c r="I15" t="s">
-        <v>3558</v>
+        <v>3549</v>
       </c>
       <c r="J15" t="s">
-        <v>3289</v>
+        <v>3280</v>
       </c>
       <c r="K15" s="107" t="s">
-        <v>3038</v>
+        <v>3031</v>
       </c>
       <c r="M15" s="36"/>
     </row>
@@ -46144,16 +46135,16 @@
         <v>66</v>
       </c>
       <c r="H17" t="s">
-        <v>3615</v>
+        <v>3606</v>
       </c>
       <c r="I17" s="30" t="s">
-        <v>3133</v>
+        <v>3125</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>3668</v>
+        <v>3659</v>
       </c>
       <c r="K17" s="220" t="s">
-        <v>3607</v>
+        <v>3598</v>
       </c>
       <c r="M17" s="34"/>
     </row>
@@ -46180,22 +46171,22 @@
         <v>66</v>
       </c>
       <c r="H18" s="30" t="s">
-        <v>3116</v>
+        <v>3108</v>
       </c>
       <c r="I18" t="s">
-        <v>3232</v>
+        <v>3224</v>
       </c>
       <c r="J18" t="s">
-        <v>3261</v>
+        <v>3252</v>
       </c>
       <c r="K18" s="49" t="s">
-        <v>2967</v>
+        <v>2960</v>
       </c>
       <c r="M18" s="36"/>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="4" t="s">
-        <v>2983</v>
+        <v>2976</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>1533</v>
@@ -46204,7 +46195,7 @@
         <v>1693</v>
       </c>
       <c r="D19" s="134" t="s">
-        <v>3479</v>
+        <v>3470</v>
       </c>
       <c r="E19" t="s">
         <v>1696</v>
@@ -46216,16 +46207,16 @@
         <v>66</v>
       </c>
       <c r="H19" t="s">
-        <v>3137</v>
+        <v>3129</v>
       </c>
       <c r="I19" s="49" t="s">
-        <v>2961</v>
+        <v>2954</v>
       </c>
       <c r="J19" s="220" t="s">
-        <v>3259</v>
+        <v>3250</v>
       </c>
       <c r="K19" t="s">
-        <v>3084</v>
+        <v>3077</v>
       </c>
       <c r="M19" s="36"/>
     </row>
@@ -46240,7 +46231,7 @@
         <v>2498</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>3065</v>
+        <v>3058</v>
       </c>
       <c r="E20" s="107" t="s">
         <v>2423</v>
@@ -46252,31 +46243,31 @@
         <v>65</v>
       </c>
       <c r="H20" s="438" t="s">
-        <v>3525</v>
+        <v>3516</v>
       </c>
       <c r="I20" t="s">
-        <v>3066</v>
+        <v>3059</v>
       </c>
       <c r="J20" t="s">
-        <v>3067</v>
+        <v>3060</v>
       </c>
       <c r="K20" t="s">
-        <v>3102</v>
+        <v>3095</v>
       </c>
       <c r="M20" s="36"/>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>3408</v>
+        <v>3399</v>
       </c>
       <c r="B21" t="s">
-        <v>3413</v>
+        <v>3404</v>
       </c>
       <c r="C21" s="22" t="s">
         <v>1130</v>
       </c>
       <c r="D21" t="s">
-        <v>3412</v>
+        <v>3403</v>
       </c>
       <c r="E21" s="140" t="s">
         <v>1593</v>
@@ -46288,19 +46279,19 @@
         <v>65</v>
       </c>
       <c r="H21" t="s">
-        <v>3417</v>
+        <v>3408</v>
       </c>
       <c r="I21" t="s">
-        <v>3420</v>
+        <v>3411</v>
       </c>
       <c r="J21" t="s">
-        <v>3421</v>
+        <v>3412</v>
       </c>
       <c r="M21" s="36"/>
     </row>
     <row r="22" spans="1:13" s="30" customFormat="1">
       <c r="A22" s="30" t="s">
-        <v>3424</v>
+        <v>3415</v>
       </c>
       <c r="B22" s="30" t="s">
         <v>2114</v>
@@ -46309,58 +46300,58 @@
         <v>2737</v>
       </c>
       <c r="D22" s="107" t="s">
-        <v>3463</v>
+        <v>3454</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>3436</v>
+        <v>3427</v>
       </c>
       <c r="F22" s="30" t="s">
-        <v>3437</v>
+        <v>3428</v>
       </c>
       <c r="G22" s="32" t="s">
         <v>65</v>
       </c>
       <c r="H22" s="30" t="s">
-        <v>3441</v>
+        <v>3432</v>
       </c>
       <c r="I22" s="30" t="s">
-        <v>3443</v>
+        <v>3434</v>
       </c>
       <c r="J22" s="30" t="s">
-        <v>3444</v>
+        <v>3435</v>
       </c>
       <c r="M22" s="36"/>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>3424</v>
+        <v>3415</v>
       </c>
       <c r="B23" t="s">
-        <v>3458</v>
+        <v>3449</v>
       </c>
       <c r="C23" s="22" t="s">
         <v>1906</v>
       </c>
       <c r="D23" t="s">
-        <v>3511</v>
+        <v>3502</v>
       </c>
       <c r="E23" s="30" t="s">
-        <v>3436</v>
+        <v>3427</v>
       </c>
       <c r="F23" s="30" t="s">
-        <v>3437</v>
+        <v>3428</v>
       </c>
       <c r="G23" t="s">
         <v>66</v>
       </c>
       <c r="H23" t="s">
-        <v>3550</v>
+        <v>3541</v>
       </c>
       <c r="I23" t="s">
-        <v>3549</v>
+        <v>3540</v>
       </c>
       <c r="J23" t="s">
-        <v>3542</v>
+        <v>3533</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -46429,7 +46420,7 @@
     </row>
     <row r="32" spans="1:13" s="107" customFormat="1">
       <c r="A32" s="32" t="s">
-        <v>2931</v>
+        <v>2925</v>
       </c>
       <c r="B32" s="32">
         <v>64403333</v>
@@ -46453,7 +46444,7 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" t="s">
-        <v>2947</v>
+        <v>2941</v>
       </c>
       <c r="B33">
         <v>60389752</v>
@@ -46476,7 +46467,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" t="s">
-        <v>3512</v>
+        <v>3503</v>
       </c>
       <c r="B34">
         <v>60389752</v>
@@ -46485,13 +46476,13 @@
         <v>2177</v>
       </c>
       <c r="D34" s="32" t="s">
-        <v>3310</v>
+        <v>3301</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>3436</v>
+        <v>3427</v>
       </c>
       <c r="F34" s="30" t="s">
-        <v>3437</v>
+        <v>3428</v>
       </c>
       <c r="G34" t="s">
         <v>3</v>
@@ -46500,7 +46491,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>3408</v>
+        <v>3399</v>
       </c>
       <c r="B35">
         <v>60389752</v>
@@ -46524,7 +46515,7 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" t="s">
-        <v>3153</v>
+        <v>3145</v>
       </c>
       <c r="B36">
         <v>60389752</v>
@@ -46548,7 +46539,7 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="30" t="s">
-        <v>3408</v>
+        <v>3399</v>
       </c>
       <c r="B37" s="30">
         <v>64403333</v>
@@ -46573,7 +46564,7 @@
     </row>
     <row r="38" spans="1:13" s="30" customFormat="1">
       <c r="A38" s="30" t="s">
-        <v>3512</v>
+        <v>3503</v>
       </c>
       <c r="B38" s="30">
         <v>60389752</v>
@@ -46610,10 +46601,10 @@
         <v>2148</v>
       </c>
       <c r="E39" t="s">
-        <v>3436</v>
+        <v>3427</v>
       </c>
       <c r="F39" t="s">
-        <v>3437</v>
+        <v>3428</v>
       </c>
       <c r="G39" t="s">
         <v>3</v>
@@ -46682,7 +46673,7 @@
         <v>2524</v>
       </c>
       <c r="E45" t="s">
-        <v>3321</v>
+        <v>3312</v>
       </c>
       <c r="F45" s="30" t="s">
         <v>2525</v>
@@ -46691,13 +46682,13 @@
         <v>369</v>
       </c>
       <c r="H45" t="s">
-        <v>3208</v>
+        <v>3200</v>
       </c>
       <c r="I45" s="30" t="s">
-        <v>3405</v>
+        <v>3396</v>
       </c>
       <c r="J45" t="s">
-        <v>2991</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -46749,10 +46740,10 @@
     </row>
     <row r="66" spans="1:38">
       <c r="C66" s="7" t="s">
-        <v>3539</v>
+        <v>3530</v>
       </c>
       <c r="D66" t="s">
-        <v>3310</v>
+        <v>3301</v>
       </c>
       <c r="E66" t="s">
         <v>2421</v>
@@ -46800,16 +46791,16 @@
     </row>
     <row r="70" spans="1:38">
       <c r="C70" s="8" t="s">
-        <v>3657</v>
+        <v>3648</v>
       </c>
       <c r="D70" t="s">
-        <v>3658</v>
+        <v>3649</v>
       </c>
       <c r="E70" s="140" t="s">
-        <v>2933</v>
+        <v>2927</v>
       </c>
       <c r="F70" s="140" t="s">
-        <v>2934</v>
+        <v>2928</v>
       </c>
       <c r="G70" s="106" t="s">
         <v>720</v>
@@ -47144,7 +47135,7 @@
         <v>1133</v>
       </c>
       <c r="D93" t="s">
-        <v>3431</v>
+        <v>3422</v>
       </c>
       <c r="E93" s="140" t="s">
         <v>1135</v>
@@ -47168,7 +47159,7 @@
         <v>1393</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>3432</v>
+        <v>3423</v>
       </c>
       <c r="E94" s="266" t="s">
         <v>1508</v>
@@ -47202,7 +47193,7 @@
         <v>358</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>3539</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="105" spans="2:5">
@@ -47428,7 +47419,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>3434</v>
+        <v>3425</v>
       </c>
       <c r="C12" s="236" t="s">
         <v>1940</v>
@@ -47559,7 +47550,7 @@
         <v>6.83</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>2909</v>
+        <v>2905</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -47568,7 +47559,7 @@
       </c>
       <c r="B24" s="87"/>
       <c r="F24" s="2" t="s">
-        <v>3072</v>
+        <v>3065</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -47644,27 +47635,27 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="87" t="s">
-        <v>3491</v>
+        <v>3482</v>
       </c>
       <c r="C40" t="s">
-        <v>3494</v>
+        <v>3485</v>
       </c>
       <c r="F40" s="45"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="89" t="s">
-        <v>3492</v>
+        <v>3483</v>
       </c>
       <c r="C41" t="s">
-        <v>3495</v>
+        <v>3486</v>
       </c>
     </row>
     <row r="42" spans="2:6" ht="15" thickBot="1">
       <c r="B42" s="86" t="s">
-        <v>3493</v>
+        <v>3484</v>
       </c>
       <c r="C42" t="s">
-        <v>3496</v>
+        <v>3487</v>
       </c>
     </row>
     <row r="43" spans="2:6">
@@ -47818,7 +47809,7 @@
         <v>143</v>
       </c>
       <c r="B6" s="247" t="s">
-        <v>2939</v>
+        <v>2933</v>
       </c>
       <c r="C6" s="246" t="s">
         <v>1291</v>
@@ -47827,22 +47818,22 @@
         <v>2038</v>
       </c>
       <c r="E6" s="247" t="s">
-        <v>3355</v>
+        <v>3346</v>
       </c>
       <c r="F6" s="247" t="s">
-        <v>3356</v>
+        <v>3347</v>
       </c>
       <c r="G6" s="247" t="s">
         <v>357</v>
       </c>
       <c r="H6" s="247" t="s">
-        <v>3314</v>
+        <v>3305</v>
       </c>
       <c r="I6" s="244" t="s">
-        <v>3614</v>
+        <v>3605</v>
       </c>
       <c r="J6" s="455" t="s">
-        <v>2986</v>
+        <v>2979</v>
       </c>
       <c r="K6" s="247" t="s">
         <v>475</v>
@@ -47865,19 +47856,19 @@
         <v>1038</v>
       </c>
       <c r="F7" s="265" t="s">
-        <v>3358</v>
+        <v>3349</v>
       </c>
       <c r="G7" s="265" t="s">
         <v>690</v>
       </c>
       <c r="H7" s="295" t="s">
-        <v>3353</v>
+        <v>3344</v>
       </c>
       <c r="I7" s="295" t="s">
-        <v>3080</v>
+        <v>3073</v>
       </c>
       <c r="J7" s="295" t="s">
-        <v>3563</v>
+        <v>3554</v>
       </c>
       <c r="K7" s="265" t="s">
         <v>709</v>
@@ -47900,19 +47891,19 @@
         <v>1231</v>
       </c>
       <c r="F8" s="265" t="s">
-        <v>3234</v>
+        <v>3226</v>
       </c>
       <c r="G8" s="265" t="s">
         <v>250</v>
       </c>
       <c r="H8" s="319" t="s">
-        <v>3575</v>
+        <v>3566</v>
       </c>
       <c r="I8" s="265" t="s">
-        <v>3505</v>
+        <v>3496</v>
       </c>
       <c r="J8" s="265" t="s">
-        <v>3574</v>
+        <v>3565</v>
       </c>
       <c r="K8" s="259"/>
       <c r="L8" s="259"/>
@@ -47934,7 +47925,7 @@
         <v>2722</v>
       </c>
       <c r="F9" s="263" t="s">
-        <v>3459</v>
+        <v>3450</v>
       </c>
       <c r="G9" s="263" t="s">
         <v>948</v>
@@ -47945,7 +47936,7 @@
     </row>
     <row r="10" spans="1:12" s="245" customFormat="1">
       <c r="A10" s="298" t="s">
-        <v>2931</v>
+        <v>2925</v>
       </c>
       <c r="B10" s="241" t="s">
         <v>2627</v>
@@ -47966,13 +47957,13 @@
         <v>690</v>
       </c>
       <c r="H10" s="264" t="s">
-        <v>3050</v>
+        <v>3043</v>
       </c>
       <c r="I10" s="455" t="s">
-        <v>3650</v>
+        <v>3641</v>
       </c>
       <c r="J10" s="264" t="s">
-        <v>3645</v>
+        <v>3636</v>
       </c>
       <c r="K10" s="245" t="s">
         <v>1206</v>
@@ -47983,7 +47974,7 @@
         <v>2522</v>
       </c>
       <c r="B11" s="262" t="s">
-        <v>3345</v>
+        <v>3336</v>
       </c>
       <c r="C11" s="194" t="s">
         <v>491</v>
@@ -48001,13 +47992,13 @@
         <v>690</v>
       </c>
       <c r="H11" s="215" t="s">
-        <v>3546</v>
+        <v>3537</v>
       </c>
       <c r="I11" s="425" t="s">
-        <v>3519</v>
+        <v>3510</v>
       </c>
       <c r="J11" s="269" t="s">
-        <v>3662</v>
+        <v>3653</v>
       </c>
       <c r="K11" s="183" t="s">
         <v>1207</v>
@@ -48041,10 +48032,10 @@
     </row>
     <row r="13" spans="1:12" s="223" customFormat="1">
       <c r="A13" s="223" t="s">
-        <v>3408</v>
+        <v>3399</v>
       </c>
       <c r="B13" s="223" t="s">
-        <v>3430</v>
+        <v>3421</v>
       </c>
       <c r="C13" s="424" t="s">
         <v>335</v>
@@ -48053,22 +48044,22 @@
         <v>2403</v>
       </c>
       <c r="E13" s="223" t="s">
-        <v>3113</v>
+        <v>3105</v>
       </c>
       <c r="F13" s="223" t="s">
-        <v>3112</v>
+        <v>3104</v>
       </c>
       <c r="G13" s="223" t="s">
         <v>690</v>
       </c>
       <c r="H13" s="223" t="s">
-        <v>3119</v>
+        <v>3111</v>
       </c>
       <c r="I13" s="215" t="s">
-        <v>3326</v>
+        <v>3317</v>
       </c>
       <c r="J13" s="223" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="K13" s="223" t="s">
         <v>1320</v>
@@ -48088,7 +48079,7 @@
         <v>1977</v>
       </c>
       <c r="E14" s="216" t="s">
-        <v>3385</v>
+        <v>3376</v>
       </c>
       <c r="F14" s="216" t="s">
         <v>1436</v>
@@ -48097,13 +48088,13 @@
         <v>690</v>
       </c>
       <c r="H14" s="272" t="s">
-        <v>3564</v>
+        <v>3555</v>
       </c>
       <c r="I14" s="215" t="s">
-        <v>3024</v>
+        <v>3017</v>
       </c>
       <c r="J14" s="262" t="s">
-        <v>3187</v>
+        <v>3179</v>
       </c>
       <c r="K14" s="183" t="s">
         <v>1208</v>
@@ -48114,13 +48105,13 @@
         <v>1419</v>
       </c>
       <c r="B15" s="264" t="s">
-        <v>3028</v>
+        <v>3021</v>
       </c>
       <c r="C15" s="270" t="s">
         <v>1308</v>
       </c>
       <c r="D15" s="259" t="s">
-        <v>2998</v>
+        <v>2991</v>
       </c>
       <c r="E15" s="259" t="s">
         <v>2782</v>
@@ -48132,13 +48123,13 @@
         <v>690</v>
       </c>
       <c r="H15" s="264" t="s">
-        <v>3298</v>
+        <v>3289</v>
       </c>
       <c r="I15" s="439" t="s">
-        <v>3578</v>
+        <v>3569</v>
       </c>
       <c r="J15" s="264" t="s">
-        <v>3255</v>
+        <v>3246</v>
       </c>
       <c r="K15" s="259" t="s">
         <v>1441</v>
@@ -48196,7 +48187,7 @@
     </row>
     <row r="18" spans="1:11" s="259" customFormat="1">
       <c r="A18" s="271" t="s">
-        <v>3153</v>
+        <v>3145</v>
       </c>
       <c r="B18" s="259" t="s">
         <v>2345</v>
@@ -48205,7 +48196,7 @@
         <v>831</v>
       </c>
       <c r="D18" s="264" t="s">
-        <v>3579</v>
+        <v>3570</v>
       </c>
       <c r="E18" s="264" t="s">
         <v>1792</v>
@@ -48217,13 +48208,13 @@
         <v>690</v>
       </c>
       <c r="H18" s="259" t="s">
-        <v>3648</v>
+        <v>3639</v>
       </c>
       <c r="I18" s="298" t="s">
-        <v>3392</v>
+        <v>3383</v>
       </c>
       <c r="J18" s="259" t="s">
-        <v>3631</v>
+        <v>3622</v>
       </c>
       <c r="K18" s="264" t="s">
         <v>1769</v>
@@ -48231,7 +48222,7 @@
     </row>
     <row r="19" spans="1:11" s="259" customFormat="1">
       <c r="A19" s="259" t="s">
-        <v>3516</v>
+        <v>3507</v>
       </c>
       <c r="B19" s="259" t="s">
         <v>2390</v>
@@ -48252,13 +48243,13 @@
         <v>690</v>
       </c>
       <c r="H19" s="259" t="s">
-        <v>3200</v>
+        <v>3192</v>
       </c>
       <c r="I19" s="259" t="s">
-        <v>3538</v>
+        <v>3529</v>
       </c>
       <c r="J19" s="259" t="s">
-        <v>3135</v>
+        <v>3127</v>
       </c>
       <c r="K19" s="259" t="s">
         <v>1814</v>
@@ -48269,7 +48260,7 @@
         <v>2619</v>
       </c>
       <c r="B20" s="304" t="s">
-        <v>3577</v>
+        <v>3568</v>
       </c>
       <c r="C20" s="259" t="s">
         <v>1815</v>
@@ -48290,10 +48281,10 @@
         <v>2791</v>
       </c>
       <c r="I20" s="264" t="s">
-        <v>3611</v>
+        <v>3602</v>
       </c>
       <c r="J20" s="264" t="s">
-        <v>3451</v>
+        <v>3442</v>
       </c>
       <c r="K20" s="259" t="s">
         <v>1816</v>
@@ -48336,10 +48327,10 @@
         <v>637</v>
       </c>
       <c r="D22" s="255" t="s">
-        <v>3580</v>
+        <v>3571</v>
       </c>
       <c r="E22" s="271" t="s">
-        <v>3498</v>
+        <v>3489</v>
       </c>
       <c r="F22" s="271" t="s">
         <v>1714</v>
@@ -48348,13 +48339,13 @@
         <v>250</v>
       </c>
       <c r="H22" s="259" t="s">
-        <v>3591</v>
+        <v>3582</v>
       </c>
       <c r="I22" s="264" t="s">
-        <v>3327</v>
+        <v>3318</v>
       </c>
       <c r="J22" s="264" t="s">
-        <v>3221</v>
+        <v>3213</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="97" customFormat="1">
@@ -48575,7 +48566,7 @@
         <v>840</v>
       </c>
       <c r="D45" s="264" t="s">
-        <v>3060</v>
+        <v>3053</v>
       </c>
       <c r="E45" s="259" t="s">
         <v>1792</v>
@@ -48778,13 +48769,13 @@
         <v>2800</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>3383</v>
+        <v>3374</v>
       </c>
       <c r="I2" t="s">
-        <v>3540</v>
+        <v>3531</v>
       </c>
       <c r="J2" t="s">
-        <v>3636</v>
+        <v>3627</v>
       </c>
       <c r="L2" s="36" t="s">
         <v>1176</v>
@@ -48810,7 +48801,7 @@
         <v>298</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>3384</v>
+        <v>3375</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>707</v>
@@ -48836,25 +48827,25 @@
         <v>313</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>2979</v>
+        <v>2972</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>3056</v>
+        <v>3049</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>323</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>3570</v>
+        <v>3561</v>
       </c>
       <c r="H4" t="s">
-        <v>3110</v>
+        <v>3102</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>3647</v>
+        <v>3638</v>
       </c>
       <c r="J4" t="s">
-        <v>2980</v>
+        <v>2973</v>
       </c>
       <c r="L4" s="127" t="s">
         <v>322</v>
@@ -48880,7 +48871,7 @@
         <v>424</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>3114</v>
+        <v>3106</v>
       </c>
       <c r="H5" s="49" t="s">
         <v>2767</v>
@@ -48895,7 +48886,7 @@
     </row>
     <row r="6" spans="1:12" s="4" customFormat="1">
       <c r="A6" s="4" t="s">
-        <v>3625</v>
+        <v>3616</v>
       </c>
       <c r="B6" s="4">
         <v>65436260</v>
@@ -48904,25 +48895,25 @@
         <v>327</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>2924</v>
+        <v>2918</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>2923</v>
+        <v>2917</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>166</v>
       </c>
       <c r="G6" t="s">
-        <v>3340</v>
+        <v>3331</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>3004</v>
+        <v>2997</v>
       </c>
       <c r="I6" t="s">
-        <v>3388</v>
+        <v>3379</v>
       </c>
       <c r="J6" s="49" t="s">
-        <v>2925</v>
+        <v>2919</v>
       </c>
       <c r="L6" s="67" t="s">
         <v>423</v>
@@ -48930,7 +48921,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="4" t="s">
-        <v>3296</v>
+        <v>3287</v>
       </c>
       <c r="B7" s="4">
         <v>69561522</v>
@@ -48939,25 +48930,25 @@
         <v>434</v>
       </c>
       <c r="D7" t="s">
-        <v>3217</v>
+        <v>3209</v>
       </c>
       <c r="E7" t="s">
-        <v>3249</v>
+        <v>3240</v>
       </c>
       <c r="F7" t="s">
         <v>151</v>
       </c>
       <c r="G7" t="s">
-        <v>3632</v>
+        <v>3623</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>3520</v>
+        <v>3511</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>3139</v>
+        <v>3131</v>
       </c>
       <c r="J7" t="s">
-        <v>3245</v>
+        <v>3237</v>
       </c>
       <c r="L7" s="83" t="s">
         <v>435</v>
@@ -48965,10 +48956,10 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="306" t="s">
-        <v>2946</v>
+        <v>2940</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>3005</v>
+        <v>2998</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>658</v>
@@ -48986,10 +48977,10 @@
         <v>2662</v>
       </c>
       <c r="H8" t="s">
-        <v>3605</v>
+        <v>3596</v>
       </c>
       <c r="I8" t="s">
-        <v>3038</v>
+        <v>3031</v>
       </c>
       <c r="J8" s="49" t="s">
         <v>2799</v>
@@ -49016,16 +49007,16 @@
         <v>151</v>
       </c>
       <c r="G9" t="s">
-        <v>3186</v>
+        <v>3178</v>
       </c>
       <c r="H9" s="220" t="s">
-        <v>3177</v>
+        <v>3169</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>3640</v>
+        <v>3631</v>
       </c>
       <c r="J9" s="220" t="s">
-        <v>3165</v>
+        <v>3157</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -49039,7 +49030,7 @@
         <v>2204</v>
       </c>
       <c r="D10" t="s">
-        <v>3068</v>
+        <v>3061</v>
       </c>
       <c r="E10" t="s">
         <v>2175</v>
@@ -49048,16 +49039,16 @@
         <v>1822</v>
       </c>
       <c r="G10" t="s">
-        <v>3360</v>
+        <v>3351</v>
       </c>
       <c r="H10" s="49" t="s">
-        <v>3594</v>
+        <v>3585</v>
       </c>
       <c r="I10" t="s">
-        <v>3391</v>
+        <v>3382</v>
       </c>
       <c r="J10" s="49" t="s">
-        <v>2864</v>
+        <v>2862</v>
       </c>
       <c r="L10" s="36" t="s">
         <v>2205</v>
@@ -49097,7 +49088,7 @@
         <v>1481</v>
       </c>
       <c r="E12" t="s">
-        <v>3216</v>
+        <v>3208</v>
       </c>
       <c r="F12" t="s">
         <v>614</v>
@@ -49128,16 +49119,16 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
+        <v>3311</v>
+      </c>
+      <c r="B14" t="s">
         <v>3320</v>
-      </c>
-      <c r="B14" t="s">
-        <v>3329</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>281</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>3328</v>
+        <v>3319</v>
       </c>
       <c r="E14" t="s">
         <v>2141</v>
@@ -49146,16 +49137,16 @@
         <v>1822</v>
       </c>
       <c r="G14" s="97" t="s">
-        <v>3369</v>
+        <v>3360</v>
       </c>
       <c r="H14" t="s">
-        <v>3655</v>
+        <v>3646</v>
       </c>
       <c r="I14" t="s">
-        <v>3513</v>
+        <v>3504</v>
       </c>
       <c r="J14" t="s">
-        <v>3429</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -49423,7 +49414,7 @@
     </row>
     <row r="2" spans="1:14" ht="43.15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>3081</v>
+        <v>3074</v>
       </c>
       <c r="C2" s="51"/>
       <c r="D2" s="52" t="s">
@@ -49435,7 +49426,7 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>2908</v>
+        <v>2904</v>
       </c>
       <c r="B4">
         <v>62445630</v>
@@ -49447,7 +49438,7 @@
         <v>2694</v>
       </c>
       <c r="E4" t="s">
-        <v>3238</v>
+        <v>3230</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -49472,7 +49463,7 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>2947</v>
+        <v>2941</v>
       </c>
       <c r="B9" t="s">
         <v>1555</v>
@@ -49484,7 +49475,7 @@
         <v>1554</v>
       </c>
       <c r="E9" s="283" t="s">
-        <v>2935</v>
+        <v>2929</v>
       </c>
       <c r="F9" t="s">
         <v>1736</v>
@@ -49492,7 +49483,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="460" t="s">
-        <v>3254</v>
+        <v>3245</v>
       </c>
       <c r="B10">
         <v>63000545</v>
@@ -49504,7 +49495,7 @@
         <v>2219</v>
       </c>
       <c r="E10" s="460" t="s">
-        <v>3664</v>
+        <v>3655</v>
       </c>
       <c r="F10" t="s">
         <v>1685</v>
@@ -49512,7 +49503,7 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="30" t="s">
-        <v>2931</v>
+        <v>2925</v>
       </c>
       <c r="B11" s="178">
         <v>68241069</v>
@@ -49524,7 +49515,7 @@
         <v>2059</v>
       </c>
       <c r="E11" t="s">
-        <v>3101</v>
+        <v>3094</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -49541,7 +49532,7 @@
         <v>2703</v>
       </c>
       <c r="E12" t="s">
-        <v>3490</v>
+        <v>3481</v>
       </c>
       <c r="F12" t="s">
         <v>1685</v>
@@ -49549,7 +49540,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>3407</v>
+        <v>3398</v>
       </c>
       <c r="B13">
         <v>62271547</v>
@@ -49561,15 +49552,15 @@
         <v>2396</v>
       </c>
       <c r="E13" t="s">
-        <v>2965</v>
+        <v>2958</v>
       </c>
       <c r="F13" t="s">
-        <v>2966</v>
+        <v>2959</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>2908</v>
+        <v>2904</v>
       </c>
       <c r="B14">
         <v>62445630</v>
@@ -49578,7 +49569,7 @@
         <v>1941</v>
       </c>
       <c r="D14" t="s">
-        <v>3218</v>
+        <v>3210</v>
       </c>
       <c r="E14" t="s">
         <v>2663</v>
@@ -49589,7 +49580,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>3184</v>
+        <v>3176</v>
       </c>
       <c r="B15">
         <v>62806425</v>
@@ -49601,7 +49592,7 @@
         <v>1739</v>
       </c>
       <c r="E15" t="s">
-        <v>2871</v>
+        <v>2869</v>
       </c>
       <c r="F15" t="s">
         <v>2706</v>
@@ -49618,10 +49609,10 @@
         <v>2751</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>3107</v>
+        <v>3100</v>
       </c>
       <c r="E16" t="s">
-        <v>3108</v>
+        <v>3101</v>
       </c>
       <c r="F16" t="s">
         <v>2706</v>
@@ -49629,19 +49620,19 @@
     </row>
     <row r="17" spans="1:8" s="30" customFormat="1">
       <c r="A17" s="217" t="s">
-        <v>2946</v>
+        <v>2940</v>
       </c>
       <c r="B17" s="30">
         <v>68582631</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>2990</v>
+        <v>2983</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>3122</v>
+        <v>3114</v>
       </c>
       <c r="E17" t="s">
-        <v>3123</v>
+        <v>3115</v>
       </c>
       <c r="F17" t="s">
         <v>2706</v>
@@ -49664,7 +49655,7 @@
         <v>2755</v>
       </c>
       <c r="E18" t="s">
-        <v>3123</v>
+        <v>3115</v>
       </c>
       <c r="F18" t="s">
         <v>2706</v>
@@ -49684,10 +49675,10 @@
         <v>2797</v>
       </c>
       <c r="E19" t="s">
-        <v>3266</v>
+        <v>3257</v>
       </c>
       <c r="F19" t="s">
-        <v>2966</v>
+        <v>2959</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -49707,7 +49698,7 @@
         <v>1515</v>
       </c>
       <c r="F21" t="s">
-        <v>3401</v>
+        <v>3392</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -49743,7 +49734,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>2993</v>
+        <v>2986</v>
       </c>
       <c r="B26">
         <v>68927207</v>
@@ -49755,13 +49746,13 @@
         <v>2680</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>3082</v>
+        <v>3075</v>
       </c>
       <c r="F26" t="s">
-        <v>3083</v>
+        <v>3076</v>
       </c>
       <c r="G26" t="s">
-        <v>3095</v>
+        <v>3088</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -49778,13 +49769,13 @@
         <v>421</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>3082</v>
+        <v>3075</v>
       </c>
       <c r="F27" t="s">
-        <v>3113</v>
+        <v>3105</v>
       </c>
       <c r="G27" t="s">
-        <v>3147</v>
+        <v>3139</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -49795,16 +49786,16 @@
         <v>1464</v>
       </c>
       <c r="D29" t="s">
-        <v>3371</v>
+        <v>3362</v>
       </c>
       <c r="E29" t="s">
-        <v>3317</v>
+        <v>3308</v>
       </c>
       <c r="F29" t="s">
-        <v>3097</v>
+        <v>3090</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>3372</v>
+        <v>3363</v>
       </c>
       <c r="H29" t="s">
         <v>407</v>
@@ -49812,7 +49803,7 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>2993</v>
+        <v>2986</v>
       </c>
       <c r="B30">
         <v>63926844</v>
@@ -49824,10 +49815,10 @@
         <v>2705</v>
       </c>
       <c r="E30" t="s">
-        <v>3096</v>
+        <v>3089</v>
       </c>
       <c r="F30" t="s">
-        <v>3097</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -49841,10 +49832,10 @@
         <v>1561</v>
       </c>
       <c r="D31" t="s">
-        <v>3341</v>
+        <v>3332</v>
       </c>
       <c r="E31" t="s">
-        <v>3342</v>
+        <v>3333</v>
       </c>
       <c r="F31" t="s">
         <v>1316</v>
@@ -49953,10 +49944,10 @@
         <v>2516</v>
       </c>
       <c r="D47" s="30" t="s">
-        <v>2897</v>
+        <v>2893</v>
       </c>
       <c r="F47" s="397" t="s">
-        <v>2898</v>
+        <v>2894</v>
       </c>
       <c r="G47" s="30" t="s">
         <v>407</v>
@@ -50052,7 +50043,7 @@
     </row>
     <row r="60" spans="1:5" s="392" customFormat="1" ht="18">
       <c r="C60" s="392" t="s">
-        <v>2873</v>
+        <v>2870</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -50069,7 +50060,7 @@
         <v>2520</v>
       </c>
       <c r="E61" s="30" t="s">
-        <v>2874</v>
+        <v>2871</v>
       </c>
     </row>
     <row r="69" spans="1:12" s="76" customFormat="1">
@@ -51888,7 +51879,7 @@
     </row>
     <row r="252" spans="1:6" s="420" customFormat="1" ht="21">
       <c r="C252" s="420" t="s">
-        <v>3054</v>
+        <v>3047</v>
       </c>
     </row>
     <row r="253" spans="1:6">
@@ -51905,30 +51896,30 @@
         <v>2251</v>
       </c>
       <c r="E253" t="s">
-        <v>3052</v>
+        <v>3045</v>
       </c>
       <c r="F253" t="s">
-        <v>3053</v>
+        <v>3046</v>
       </c>
     </row>
     <row r="254" spans="1:6">
       <c r="A254" t="s">
-        <v>2983</v>
+        <v>2976</v>
       </c>
       <c r="B254">
         <v>64738222</v>
       </c>
       <c r="C254" s="22" t="s">
-        <v>2985</v>
+        <v>2978</v>
       </c>
       <c r="D254" t="s">
-        <v>2982</v>
+        <v>2975</v>
       </c>
       <c r="E254" t="s">
-        <v>3052</v>
+        <v>3045</v>
       </c>
       <c r="F254" t="s">
-        <v>3053</v>
+        <v>3046</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -51939,16 +51930,16 @@
         <v>60433915</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>2984</v>
+        <v>2977</v>
       </c>
       <c r="D255" s="251" t="s">
         <v>2647</v>
       </c>
       <c r="E255" t="s">
-        <v>3052</v>
+        <v>3045</v>
       </c>
       <c r="F255" t="s">
-        <v>3053</v>
+        <v>3046</v>
       </c>
     </row>
     <row r="256" spans="1:6">
@@ -56702,7 +56693,7 @@
         <v>2694</v>
       </c>
       <c r="E537" s="76" t="s">
-        <v>3236</v>
+        <v>3228</v>
       </c>
       <c r="F537" s="76"/>
       <c r="G537" s="76"/>

--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dc549f2659ed9bd7/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62647" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{373D19BC-DF15-431C-991A-38E9010CD0BF}"/>
+  <xr:revisionPtr revIDLastSave="62658" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA0EABD0-C36F-4A85-93C8-DF9330DBF1AB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,7 +67,6 @@
     <author>tc={63325648-98C5-43A5-B0A0-BE3F1931179F}</author>
     <author>tc={D74A6BC7-C936-4D18-B207-7662524F2FF1}</author>
     <author>tc={A3C653E5-B008-4D78-A9B3-C292CBCE6481}</author>
-    <author>tc={76A385E1-B49D-4CB9-9F2C-60615C4FA65C}</author>
     <author>tc={263CFA38-6940-48E3-8C6D-4FD90BA5C72C}</author>
     <author>tc={2DA6ACCC-7F6B-4F63-9F66-2022723D557F}</author>
     <author>tc={2C80CEB1-D520-47E4-8891-F2B7A2059B85}</author>
@@ -157,15 +156,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/180826-2044</t>
       </text>
     </comment>
-    <comment ref="J70" authorId="8" shapeId="0" xr:uid="{76A385E1-B49D-4CB9-9F2C-60615C4FA65C}">
-      <text>
-        <t>[Comentario encadenado]
-Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
-Comentario:
-    https://netflix-server-a9i0.onrender.com/cliente/60957473-jose</t>
-      </text>
-    </comment>
-    <comment ref="I76" authorId="9" shapeId="0" xr:uid="{263CFA38-6940-48E3-8C6D-4FD90BA5C72C}">
+    <comment ref="I76" authorId="8" shapeId="0" xr:uid="{263CFA38-6940-48E3-8C6D-4FD90BA5C72C}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -173,7 +164,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/150826-2208</t>
       </text>
     </comment>
-    <comment ref="J79" authorId="10" shapeId="0" xr:uid="{2DA6ACCC-7F6B-4F63-9F66-2022723D557F}">
+    <comment ref="J79" authorId="9" shapeId="0" xr:uid="{2DA6ACCC-7F6B-4F63-9F66-2022723D557F}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -181,7 +172,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/68582631-melanie</t>
       </text>
     </comment>
-    <comment ref="J88" authorId="11" shapeId="0" xr:uid="{2C80CEB1-D520-47E4-8891-F2B7A2059B85}">
+    <comment ref="J88" authorId="10" shapeId="0" xr:uid="{2C80CEB1-D520-47E4-8891-F2B7A2059B85}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -189,7 +180,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/200826-2043</t>
       </text>
     </comment>
-    <comment ref="K88" authorId="12" shapeId="0" xr:uid="{A1BAE17A-7373-4E96-9A79-0A588580086C}">
+    <comment ref="K88" authorId="11" shapeId="0" xr:uid="{A1BAE17A-7373-4E96-9A79-0A588580086C}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -197,7 +188,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/69645877-yimara</t>
       </text>
     </comment>
-    <comment ref="H91" authorId="13" shapeId="0" xr:uid="{6CB69787-04DC-427D-92C4-EA68685283A6}">
+    <comment ref="H91" authorId="12" shapeId="0" xr:uid="{6CB69787-04DC-427D-92C4-EA68685283A6}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -205,7 +196,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/68131498-melanie</t>
       </text>
     </comment>
-    <comment ref="J97" authorId="14" shapeId="0" xr:uid="{D6ECFDFD-E9B9-4F9B-B2EF-5C67AA00056B}">
+    <comment ref="J97" authorId="13" shapeId="0" xr:uid="{D6ECFDFD-E9B9-4F9B-B2EF-5C67AA00056B}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -213,7 +204,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/68259581-kenneth</t>
       </text>
     </comment>
-    <comment ref="H103" authorId="15" shapeId="0" xr:uid="{5775AADF-97AE-4D86-A7DF-2817E0EA08FF}">
+    <comment ref="H103" authorId="14" shapeId="0" xr:uid="{5775AADF-97AE-4D86-A7DF-2817E0EA08FF}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -10107,9 +10098,6 @@
     <t>Tea150826</t>
   </si>
   <si>
-    <t xml:space="preserve">64891979-made 1 pantalla hasta el 15 de septiembre </t>
-  </si>
-  <si>
     <t xml:space="preserve">63017550 1 pantalla hasta el 14 de septiembre </t>
   </si>
   <si>
@@ -10164,9 +10152,6 @@
     <t>65583706 1 pantalla hasta el 16 de septiembre (Anthony)</t>
   </si>
   <si>
-    <t>60432412 pantalla hasta el 16 de septiembre 110n005</t>
-  </si>
-  <si>
     <t>chat gpt dispositivos</t>
   </si>
   <si>
@@ -11094,9 +11079,6 @@
     <t>Hfd010926</t>
   </si>
   <si>
-    <t>QUINCENAL 68762307v 1 pantalla hasta el 16 de septiembre (Natasha)</t>
-  </si>
-  <si>
     <t>QUINCENAL 62140561b 1 pantalla hasta el 16 de septiembre (Itziar)</t>
   </si>
   <si>
@@ -11169,9 +11151,6 @@
     <t>62814795 1 pantalla hasta el 01 de octubre (Antonio)</t>
   </si>
   <si>
-    <t xml:space="preserve">quincenal 60957473-jose 1 pantalla hasta el 17 de septiembre </t>
-  </si>
-  <si>
     <t>64457890-fello 1 pantalla hasta el 01 de octubre</t>
   </si>
   <si>
@@ -12301,6 +12280,18 @@
   </si>
   <si>
     <t>N005 1 pantalla hasta el 18 de octubre 180926-1611g</t>
+  </si>
+  <si>
+    <t>N004 1 pantalla hasta el 18 de octubre 180926-1626y</t>
+  </si>
+  <si>
+    <t>N006 1 pantalla hasta el 18 de octubre 180926-1628d</t>
+  </si>
+  <si>
+    <t>N004 1 pantalla hasta el 18 de octubre 180926-1644d</t>
+  </si>
+  <si>
+    <t>N006 1 pantalla hasta el 18 de octubre 180926-1645x</t>
   </si>
 </sst>
 </file>
@@ -30037,15 +30028,6 @@
       </x:ext>
     </extLst>
   </threadedComment>
-  <threadedComment ref="J70" dT="2026-08-17T21:13:15.44" personId="{0912E1D7-9EEC-46AD-AFB7-0C0A7E0E5337}" id="{76A385E1-B49D-4CB9-9F2C-60615C4FA65C}">
-    <text>https://netflix-server-a9i0.onrender.com/cliente/60957473-jose</text>
-    <extLst>
-      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>4113612618</xltc2:checksum>
-        <xltc2:hyperlink startIndex="0" length="49" url="https://netflix-server-a9i0.onrender.com/cliente/"/>
-      </x:ext>
-    </extLst>
-  </threadedComment>
   <threadedComment ref="I76" dT="2026-08-16T04:09:02.31" personId="{0912E1D7-9EEC-46AD-AFB7-0C0A7E0E5337}" id="{263CFA38-6940-48E3-8C6D-4FD90BA5C72C}">
     <text>https://netflix-server-a9i0.onrender.com/cliente/150826-2208</text>
     <extLst>
@@ -30189,7 +30171,7 @@
   <sheetData>
     <row r="1" spans="1:11" s="30" customFormat="1">
       <c r="A1" s="30" t="s">
-        <v>3176</v>
+        <v>3174</v>
       </c>
       <c r="B1" s="30">
         <v>60389752</v>
@@ -30201,7 +30183,7 @@
         <v>2012</v>
       </c>
       <c r="E1" s="459" t="s">
-        <v>3656</v>
+        <v>3652</v>
       </c>
       <c r="F1" s="30" t="s">
         <v>2078</v>
@@ -30221,7 +30203,7 @@
         <v>2124</v>
       </c>
       <c r="D2" s="148" t="s">
-        <v>3067</v>
+        <v>3065</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="148" customFormat="1">
@@ -30240,7 +30222,7 @@
     </row>
     <row r="4" spans="1:11" s="30" customFormat="1">
       <c r="A4" s="30" t="s">
-        <v>3176</v>
+        <v>3174</v>
       </c>
       <c r="B4" s="30">
         <v>60389752</v>
@@ -30252,7 +30234,7 @@
         <v>2010</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
       <c r="F4" s="30" t="s">
         <v>2078</v>
@@ -30272,7 +30254,7 @@
         <v>2138</v>
       </c>
       <c r="D5" s="148" t="s">
-        <v>3182</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="148" customFormat="1">
@@ -30303,7 +30285,7 @@
         <v>2859</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>3054</v>
+        <v>3052</v>
       </c>
       <c r="F7" s="30" t="s">
         <v>2083</v>
@@ -30323,12 +30305,12 @@
         <v>2244</v>
       </c>
       <c r="D8" s="148" t="s">
-        <v>3581</v>
+        <v>3577</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="148" customFormat="1">
       <c r="A9" s="148" t="s">
-        <v>3292</v>
+        <v>3288</v>
       </c>
       <c r="B9" s="148" t="s">
         <v>1203</v>
@@ -30345,7 +30327,7 @@
     </row>
     <row r="10" spans="1:11" s="423" customFormat="1">
       <c r="A10" s="423" t="s">
-        <v>3149</v>
+        <v>3147</v>
       </c>
       <c r="B10" s="423">
         <v>60389752</v>
@@ -30382,7 +30364,7 @@
         <v>2143</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>3142</v>
+        <v>3140</v>
       </c>
       <c r="F13" s="30" t="s">
         <v>2142</v>
@@ -30394,7 +30376,7 @@
     </row>
     <row r="14" spans="1:11" s="148" customFormat="1">
       <c r="A14" s="225" t="s">
-        <v>3603</v>
+        <v>3599</v>
       </c>
       <c r="B14" s="225" t="s">
         <v>1675</v>
@@ -30408,7 +30390,7 @@
     </row>
     <row r="15" spans="1:11" s="148" customFormat="1">
       <c r="A15" s="225" t="s">
-        <v>3461</v>
+        <v>3457</v>
       </c>
       <c r="B15" s="416">
         <v>62439069</v>
@@ -30422,7 +30404,7 @@
     </row>
     <row r="16" spans="1:11" s="32" customFormat="1">
       <c r="A16" s="30" t="s">
-        <v>3503</v>
+        <v>3499</v>
       </c>
       <c r="B16" s="284" t="s">
         <v>2198</v>
@@ -30431,10 +30413,10 @@
         <v>1526</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>3056</v>
+        <v>3054</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>3143</v>
+        <v>3141</v>
       </c>
       <c r="F16" s="32" t="s">
         <v>1527</v>
@@ -30443,21 +30425,21 @@
         <v>198</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>3057</v>
+        <v>3055</v>
       </c>
       <c r="I16" s="32" t="s">
-        <v>3299</v>
+        <v>3295</v>
       </c>
       <c r="J16" s="32" t="s">
-        <v>3222</v>
+        <v>3220</v>
       </c>
       <c r="K16" s="30" t="s">
-        <v>3223</v>
+        <v>3221</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="164" customFormat="1">
       <c r="A17" s="252" t="s">
-        <v>3415</v>
+        <v>3411</v>
       </c>
       <c r="B17" s="252" t="s">
         <v>1394</v>
@@ -30500,10 +30482,10 @@
         <v>1491</v>
       </c>
       <c r="D19" s="145" t="s">
-        <v>3522</v>
+        <v>3518</v>
       </c>
       <c r="E19" s="145" t="s">
-        <v>3038</v>
+        <v>3036</v>
       </c>
       <c r="F19" s="145" t="s">
         <v>1361</v>
@@ -30527,7 +30509,7 @@
         <v>1681</v>
       </c>
       <c r="D20" s="252" t="s">
-        <v>2971</v>
+        <v>2969</v>
       </c>
       <c r="E20" s="252" t="s">
         <v>1682</v>
@@ -30535,7 +30517,7 @@
     </row>
     <row r="21" spans="1:11" s="297" customFormat="1">
       <c r="A21" s="252" t="s">
-        <v>3532</v>
+        <v>3528</v>
       </c>
       <c r="B21" s="252">
         <v>62169673</v>
@@ -30544,7 +30526,7 @@
         <v>1686</v>
       </c>
       <c r="D21" s="164" t="s">
-        <v>3523</v>
+        <v>3519</v>
       </c>
       <c r="E21" s="164" t="s">
         <v>1687</v>
@@ -30552,7 +30534,7 @@
     </row>
     <row r="22" spans="1:11" s="30" customFormat="1">
       <c r="A22" s="32" t="s">
-        <v>2976</v>
+        <v>2974</v>
       </c>
       <c r="B22" s="32">
         <v>60389752</v>
@@ -30564,7 +30546,7 @@
         <v>2121</v>
       </c>
       <c r="E22" s="459" t="s">
-        <v>3656</v>
+        <v>3652</v>
       </c>
       <c r="F22" s="30" t="s">
         <v>2077</v>
@@ -30575,7 +30557,7 @@
     </row>
     <row r="23" spans="1:11" s="148" customFormat="1">
       <c r="A23" s="225" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="B23" s="148">
         <v>64858241</v>
@@ -30589,7 +30571,7 @@
     </row>
     <row r="24" spans="1:11" s="148" customFormat="1">
       <c r="A24" s="149" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="B24" s="149">
         <v>68934853</v>
@@ -30598,7 +30580,7 @@
         <v>2117</v>
       </c>
       <c r="D24" s="148" t="s">
-        <v>3525</v>
+        <v>3521</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="30" customFormat="1">
@@ -30615,7 +30597,7 @@
         <v>1523</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>3037</v>
+        <v>3035</v>
       </c>
       <c r="F25" s="30" t="s">
         <v>1361</v>
@@ -30629,7 +30611,7 @@
     </row>
     <row r="26" spans="1:11" s="225" customFormat="1">
       <c r="A26" s="225" t="s">
-        <v>2976</v>
+        <v>2974</v>
       </c>
       <c r="B26" s="225" t="s">
         <v>1925</v>
@@ -30663,7 +30645,7 @@
     </row>
     <row r="28" spans="1:11" s="30" customFormat="1">
       <c r="A28" s="30" t="s">
-        <v>3292</v>
+        <v>3288</v>
       </c>
       <c r="B28" s="30">
         <v>60389752</v>
@@ -30675,7 +30657,7 @@
         <v>2007</v>
       </c>
       <c r="E28" s="30" t="s">
-        <v>3269</v>
+        <v>3266</v>
       </c>
       <c r="F28" s="303" t="s">
         <v>2153</v>
@@ -30700,7 +30682,7 @@
     </row>
     <row r="30" spans="1:11" s="164" customFormat="1">
       <c r="A30" s="164" t="s">
-        <v>3503</v>
+        <v>3499</v>
       </c>
       <c r="B30" s="164">
         <v>62782770</v>
@@ -30717,16 +30699,16 @@
         <v>2904</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>3025</v>
+        <v>3023</v>
       </c>
       <c r="C31" s="251" t="s">
         <v>1900</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>3026</v>
+        <v>3024</v>
       </c>
       <c r="E31" s="454" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
       <c r="F31" s="30" t="s">
         <v>2028</v>
@@ -30735,16 +30717,16 @@
         <v>198</v>
       </c>
       <c r="H31" s="30" t="s">
-        <v>3027</v>
+        <v>3025</v>
       </c>
       <c r="I31" s="192" t="s">
-        <v>3138</v>
+        <v>3136</v>
       </c>
       <c r="J31" s="421" t="s">
-        <v>3048</v>
+        <v>3046</v>
       </c>
       <c r="K31" s="30" t="s">
-        <v>3556</v>
+        <v>3552</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="163" customFormat="1">
@@ -30790,7 +30772,7 @@
         <v>2090</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>3557</v>
+        <v>3553</v>
       </c>
       <c r="F34" s="30" t="s">
         <v>2081</v>
@@ -30801,7 +30783,7 @@
     </row>
     <row r="35" spans="1:11" s="148" customFormat="1">
       <c r="A35" s="148" t="s">
-        <v>2976</v>
+        <v>2974</v>
       </c>
       <c r="B35" s="148">
         <v>69692470</v>
@@ -30810,7 +30792,7 @@
         <v>1984</v>
       </c>
       <c r="D35" s="148" t="s">
-        <v>3607</v>
+        <v>3603</v>
       </c>
       <c r="E35" s="148" t="s">
         <v>1986</v>
@@ -30841,10 +30823,10 @@
         <v>2005</v>
       </c>
       <c r="D37" s="30" t="s">
-        <v>3162</v>
+        <v>3160</v>
       </c>
       <c r="E37" s="459" t="s">
-        <v>3657</v>
+        <v>3653</v>
       </c>
       <c r="F37" s="30" t="s">
         <v>2071</v>
@@ -30853,16 +30835,16 @@
         <v>198</v>
       </c>
       <c r="H37" s="145" t="s">
-        <v>3667</v>
+        <v>3663</v>
       </c>
       <c r="I37" s="30" t="s">
-        <v>3194</v>
+        <v>3192</v>
       </c>
       <c r="J37" s="30" t="s">
-        <v>3524</v>
+        <v>3520</v>
       </c>
       <c r="K37" s="30" t="s">
-        <v>3387</v>
+        <v>3383</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="147" customFormat="1">
@@ -30899,16 +30881,16 @@
         <v>2489</v>
       </c>
       <c r="B40" s="32" t="s">
-        <v>3172</v>
+        <v>3170</v>
       </c>
       <c r="C40" s="251" t="s">
         <v>1662</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>3499</v>
+        <v>3495</v>
       </c>
       <c r="E40" s="30" t="s">
-        <v>3557</v>
+        <v>3553</v>
       </c>
       <c r="F40" s="30" t="s">
         <v>2086</v>
@@ -30917,21 +30899,21 @@
         <v>198</v>
       </c>
       <c r="H40" s="30" t="s">
-        <v>3654</v>
+        <v>3650</v>
       </c>
       <c r="I40" s="32" t="s">
-        <v>3128</v>
+        <v>3126</v>
       </c>
       <c r="J40" s="32" t="s">
-        <v>3158</v>
+        <v>3156</v>
       </c>
       <c r="K40" s="145" t="s">
-        <v>3500</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="163" customFormat="1">
       <c r="A41" s="163" t="s">
-        <v>3640</v>
+        <v>3636</v>
       </c>
       <c r="B41" s="163">
         <v>68381893</v>
@@ -30963,7 +30945,7 @@
     </row>
     <row r="43" spans="1:11" s="30" customFormat="1">
       <c r="A43" s="30" t="s">
-        <v>3149</v>
+        <v>3147</v>
       </c>
       <c r="B43" s="30">
         <v>60389752</v>
@@ -30975,7 +30957,7 @@
         <v>2032</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>2994</v>
+        <v>2992</v>
       </c>
       <c r="F43" s="30" t="s">
         <v>2118</v>
@@ -30986,7 +30968,7 @@
     </row>
     <row r="44" spans="1:11" s="164" customFormat="1">
       <c r="A44" s="164" t="s">
-        <v>3640</v>
+        <v>3636</v>
       </c>
       <c r="B44" s="164">
         <v>68381893</v>
@@ -31003,7 +30985,7 @@
     </row>
     <row r="45" spans="1:11" s="163" customFormat="1">
       <c r="A45" s="163" t="s">
-        <v>3399</v>
+        <v>3395</v>
       </c>
       <c r="B45" s="163">
         <v>64079861</v>
@@ -31032,7 +31014,7 @@
         <v>2853</v>
       </c>
       <c r="E46" s="30" t="s">
-        <v>3359</v>
+        <v>3355</v>
       </c>
       <c r="F46" s="30" t="s">
         <v>2102</v>
@@ -31044,7 +31026,7 @@
     </row>
     <row r="47" spans="1:11" s="164" customFormat="1">
       <c r="A47" s="164" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="B47" s="164">
         <v>63183787</v>
@@ -31078,16 +31060,16 @@
         <v>1498</v>
       </c>
       <c r="B49" s="30" t="s">
-        <v>3407</v>
+        <v>3403</v>
       </c>
       <c r="C49" s="134" t="s">
         <v>1996</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>3286</v>
+        <v>3283</v>
       </c>
       <c r="E49" s="30" t="s">
-        <v>3558</v>
+        <v>3554</v>
       </c>
       <c r="F49" s="30" t="s">
         <v>2089</v>
@@ -31096,16 +31078,16 @@
         <v>198</v>
       </c>
       <c r="H49" s="30" t="s">
-        <v>3126</v>
+        <v>3124</v>
       </c>
       <c r="I49" s="30" t="s">
-        <v>3181</v>
+        <v>3179</v>
       </c>
       <c r="J49" s="30" t="s">
-        <v>3610</v>
+        <v>3606</v>
       </c>
       <c r="K49" s="32" t="s">
-        <v>3285</v>
+        <v>3282</v>
       </c>
     </row>
     <row r="50" spans="1:11" s="164" customFormat="1">
@@ -31133,7 +31115,7 @@
         <v>2004</v>
       </c>
       <c r="D51" s="164" t="s">
-        <v>3091</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="52" spans="1:11" s="139" customFormat="1">
@@ -31150,7 +31132,7 @@
         <v>2865</v>
       </c>
       <c r="E52" s="139" t="s">
-        <v>3557</v>
+        <v>3553</v>
       </c>
       <c r="F52" s="139" t="s">
         <v>2087</v>
@@ -31159,16 +31141,16 @@
         <v>198</v>
       </c>
       <c r="H52" s="140" t="s">
-        <v>3590</v>
+        <v>3586</v>
       </c>
       <c r="I52" s="140" t="s">
-        <v>3381</v>
+        <v>3377</v>
       </c>
       <c r="J52" s="30" t="s">
-        <v>3255</v>
+        <v>3253</v>
       </c>
       <c r="K52" s="269" t="s">
-        <v>3014</v>
+        <v>3012</v>
       </c>
     </row>
     <row r="53" spans="1:11" s="164" customFormat="1">
@@ -31209,7 +31191,7 @@
     </row>
     <row r="55" spans="1:11" s="30" customFormat="1">
       <c r="A55" s="30" t="s">
-        <v>3507</v>
+        <v>3503</v>
       </c>
       <c r="B55" s="30">
         <v>61130088</v>
@@ -31221,7 +31203,7 @@
         <v>2000</v>
       </c>
       <c r="E55" s="30" t="s">
-        <v>3142</v>
+        <v>3140</v>
       </c>
       <c r="F55" s="30" t="s">
         <v>2103</v>
@@ -31238,10 +31220,10 @@
         <v>60433915</v>
       </c>
       <c r="C56" s="400" t="s">
+        <v>3151</v>
+      </c>
+      <c r="D56" s="370" t="s">
         <v>3153</v>
-      </c>
-      <c r="D56" s="370" t="s">
-        <v>3155</v>
       </c>
       <c r="E56" s="164"/>
     </row>
@@ -31250,19 +31232,19 @@
         <v>2489</v>
       </c>
       <c r="B57" s="163" t="s">
-        <v>3159</v>
+        <v>3157</v>
       </c>
       <c r="C57" s="400" t="s">
+        <v>3152</v>
+      </c>
+      <c r="D57" s="370" t="s">
         <v>3154</v>
-      </c>
-      <c r="D57" s="370" t="s">
-        <v>3156</v>
       </c>
       <c r="E57" s="164"/>
     </row>
     <row r="58" spans="1:11" s="30" customFormat="1">
       <c r="A58" s="459" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="B58" s="412" t="s">
         <v>2069</v>
@@ -31274,7 +31256,7 @@
         <v>2798</v>
       </c>
       <c r="E58" s="30" t="s">
-        <v>3214</v>
+        <v>3212</v>
       </c>
       <c r="F58" s="30" t="s">
         <v>2115</v>
@@ -31283,16 +31265,16 @@
         <v>198</v>
       </c>
       <c r="H58" s="30" t="s">
-        <v>3304</v>
+        <v>3300</v>
       </c>
       <c r="I58" s="30" t="s">
-        <v>3170</v>
+        <v>3168</v>
       </c>
       <c r="J58" s="30" t="s">
-        <v>3259</v>
+        <v>3257</v>
       </c>
       <c r="K58" s="30" t="s">
-        <v>3578</v>
+        <v>3574</v>
       </c>
     </row>
     <row r="59" spans="1:11" s="388" customFormat="1">
@@ -31307,7 +31289,7 @@
         <v>158</v>
       </c>
       <c r="B61" s="30" t="s">
-        <v>3146</v>
+        <v>3144</v>
       </c>
       <c r="C61" s="134" t="s">
         <v>2070</v>
@@ -31316,7 +31298,7 @@
         <v>2856</v>
       </c>
       <c r="E61" s="30" t="s">
-        <v>3055</v>
+        <v>3053</v>
       </c>
       <c r="F61" s="30" t="s">
         <v>2071</v>
@@ -31325,21 +31307,21 @@
         <v>198</v>
       </c>
       <c r="H61" s="30" t="s">
-        <v>3426</v>
+        <v>3422</v>
       </c>
       <c r="I61" s="30" t="s">
-        <v>3188</v>
+        <v>3186</v>
       </c>
       <c r="J61" s="30" t="s">
-        <v>3293</v>
+        <v>3289</v>
       </c>
       <c r="K61" s="30" t="s">
-        <v>3384</v>
+        <v>3380</v>
       </c>
     </row>
     <row r="62" spans="1:11" s="147" customFormat="1">
       <c r="A62" s="147" t="s">
-        <v>3144</v>
+        <v>3142</v>
       </c>
       <c r="B62" s="147">
         <v>60196388</v>
@@ -31348,7 +31330,7 @@
         <v>1470</v>
       </c>
       <c r="D62" s="371" t="s">
-        <v>3147</v>
+        <v>3145</v>
       </c>
       <c r="E62" s="148" t="s">
         <v>1380</v>
@@ -31356,7 +31338,7 @@
     </row>
     <row r="63" spans="1:11" s="163" customFormat="1">
       <c r="A63" s="163" t="s">
-        <v>3176</v>
+        <v>3174</v>
       </c>
       <c r="B63" s="163">
         <v>62960567</v>
@@ -31365,13 +31347,13 @@
         <v>2055</v>
       </c>
       <c r="D63" s="370" t="s">
-        <v>3103</v>
+        <v>3101</v>
       </c>
       <c r="E63" s="164"/>
     </row>
     <row r="64" spans="1:11" s="30" customFormat="1">
       <c r="A64" s="32" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="B64" s="32" t="s">
         <v>2122</v>
@@ -31380,10 +31362,10 @@
         <v>1661</v>
       </c>
       <c r="D64" s="30" t="s">
-        <v>3298</v>
+        <v>3294</v>
       </c>
       <c r="E64" s="30" t="s">
-        <v>3557</v>
+        <v>3553</v>
       </c>
       <c r="F64" s="30" t="s">
         <v>2088</v>
@@ -31392,16 +31374,16 @@
         <v>198</v>
       </c>
       <c r="H64" s="32" t="s">
-        <v>3397</v>
+        <v>3393</v>
       </c>
       <c r="I64" s="32" t="s">
-        <v>3464</v>
+        <v>3460</v>
       </c>
       <c r="J64" s="30" t="s">
-        <v>3348</v>
+        <v>3344</v>
       </c>
       <c r="K64" s="30" t="s">
-        <v>3171</v>
+        <v>3169</v>
       </c>
     </row>
     <row r="65" spans="1:11" s="164" customFormat="1">
@@ -31423,7 +31405,7 @@
     </row>
     <row r="66" spans="1:11" s="164" customFormat="1">
       <c r="A66" s="252" t="s">
-        <v>2976</v>
+        <v>2974</v>
       </c>
       <c r="B66" s="164">
         <v>62090364</v>
@@ -31440,7 +31422,7 @@
     </row>
     <row r="67" spans="1:11" s="30" customFormat="1">
       <c r="A67" s="253" t="s">
-        <v>3472</v>
+        <v>3468</v>
       </c>
       <c r="B67" s="284" t="s">
         <v>1908</v>
@@ -31449,10 +31431,10 @@
         <v>1665</v>
       </c>
       <c r="D67" s="30" t="s">
-        <v>2985</v>
+        <v>2983</v>
       </c>
       <c r="E67" s="30" t="s">
-        <v>3611</v>
+        <v>3607</v>
       </c>
       <c r="F67" s="30" t="s">
         <v>2092</v>
@@ -31461,21 +31443,21 @@
         <v>198</v>
       </c>
       <c r="H67" s="30" t="s">
-        <v>3380</v>
+        <v>3376</v>
       </c>
       <c r="I67" s="30" t="s">
-        <v>3452</v>
+        <v>3448</v>
       </c>
       <c r="J67" s="30" t="s">
-        <v>3498</v>
+        <v>3494</v>
       </c>
       <c r="K67" s="30" t="s">
-        <v>2992</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="68" spans="1:11" s="147" customFormat="1">
       <c r="A68" s="147" t="s">
-        <v>3144</v>
+        <v>3142</v>
       </c>
       <c r="B68" s="147">
         <v>68741448</v>
@@ -31484,13 +31466,13 @@
         <v>1876</v>
       </c>
       <c r="D68" s="371" t="s">
-        <v>3124</v>
+        <v>3122</v>
       </c>
       <c r="E68" s="148"/>
     </row>
     <row r="69" spans="1:11" s="148" customFormat="1">
       <c r="A69" s="225" t="s">
-        <v>3245</v>
+        <v>3243</v>
       </c>
       <c r="B69" s="148">
         <v>63018763</v>
@@ -31499,7 +31481,7 @@
         <v>2091</v>
       </c>
       <c r="D69" s="148" t="s">
-        <v>3620</v>
+        <v>3616</v>
       </c>
     </row>
     <row r="70" spans="1:11" s="30" customFormat="1">
@@ -31507,16 +31489,16 @@
         <v>467</v>
       </c>
       <c r="B70" s="32" t="s">
-        <v>3395</v>
+        <v>3391</v>
       </c>
       <c r="C70" s="251" t="s">
         <v>1664</v>
       </c>
       <c r="D70" s="30" t="s">
-        <v>3264</v>
+        <v>3262</v>
       </c>
       <c r="E70" s="30" t="s">
-        <v>3215</v>
+        <v>3213</v>
       </c>
       <c r="F70" s="30" t="s">
         <v>2129</v>
@@ -31525,13 +31507,13 @@
         <v>198</v>
       </c>
       <c r="H70" s="32" t="s">
-        <v>3609</v>
-      </c>
-      <c r="I70" s="217" t="s">
-        <v>3265</v>
-      </c>
-      <c r="J70" s="432" t="s">
-        <v>3290</v>
+        <v>3605</v>
+      </c>
+      <c r="I70" s="145" t="s">
+        <v>3664</v>
+      </c>
+      <c r="J70" s="145" t="s">
+        <v>3665</v>
       </c>
     </row>
     <row r="71" spans="1:11" s="164" customFormat="1">
@@ -31550,7 +31532,7 @@
     </row>
     <row r="72" spans="1:11" s="163" customFormat="1">
       <c r="A72" s="268" t="s">
-        <v>3599</v>
+        <v>3595</v>
       </c>
       <c r="B72" s="268" t="s">
         <v>1452</v>
@@ -31565,7 +31547,7 @@
     </row>
     <row r="73" spans="1:11" s="30" customFormat="1">
       <c r="A73" s="30" t="s">
-        <v>3300</v>
+        <v>3296</v>
       </c>
       <c r="B73" s="30">
         <v>60389752</v>
@@ -31577,7 +31559,7 @@
         <v>2809</v>
       </c>
       <c r="E73" s="30" t="s">
-        <v>3400</v>
+        <v>3396</v>
       </c>
       <c r="F73" s="30" t="s">
         <v>2027</v>
@@ -31588,7 +31570,7 @@
     </row>
     <row r="74" spans="1:11" s="147" customFormat="1">
       <c r="A74" s="147" t="s">
-        <v>3603</v>
+        <v>3599</v>
       </c>
       <c r="B74" s="147">
         <v>64226974</v>
@@ -31612,7 +31594,7 @@
         <v>1946</v>
       </c>
       <c r="D75" s="148" t="s">
-        <v>3196</v>
+        <v>3194</v>
       </c>
       <c r="E75" s="148"/>
     </row>
@@ -31627,10 +31609,10 @@
         <v>1875</v>
       </c>
       <c r="D76" s="30" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="E76" s="30" t="s">
-        <v>3097</v>
+        <v>3095</v>
       </c>
       <c r="F76" s="30" t="s">
         <v>2102</v>
@@ -31639,16 +31621,16 @@
         <v>198</v>
       </c>
       <c r="H76" s="30" t="s">
-        <v>3559</v>
+        <v>3555</v>
       </c>
       <c r="I76" s="30" t="s">
-        <v>3608</v>
+        <v>3604</v>
       </c>
       <c r="J76" s="30" t="s">
-        <v>3202</v>
+        <v>3200</v>
       </c>
       <c r="K76" s="217" t="s">
-        <v>3266</v>
+        <v>3263</v>
       </c>
     </row>
     <row r="77" spans="1:11" s="152" customFormat="1">
@@ -31670,10 +31652,10 @@
         <v>2003</v>
       </c>
       <c r="D79" s="30" t="s">
-        <v>2968</v>
+        <v>2966</v>
       </c>
       <c r="E79" s="459" t="s">
-        <v>3656</v>
+        <v>3652</v>
       </c>
       <c r="F79" s="30" t="s">
         <v>2082</v>
@@ -31682,16 +31664,16 @@
         <v>198</v>
       </c>
       <c r="H79" s="432" t="s">
-        <v>2982</v>
+        <v>2980</v>
       </c>
       <c r="I79" s="32" t="s">
-        <v>3167</v>
+        <v>3165</v>
       </c>
       <c r="J79" s="30" t="s">
-        <v>3515</v>
+        <v>3511</v>
       </c>
       <c r="K79" s="30" t="s">
-        <v>3204</v>
+        <v>3202</v>
       </c>
     </row>
     <row r="80" spans="1:11" s="147" customFormat="1">
@@ -31711,7 +31693,7 @@
     </row>
     <row r="81" spans="1:11" s="147" customFormat="1">
       <c r="A81" s="149" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="B81" s="147">
         <v>64720128</v>
@@ -31728,10 +31710,10 @@
     </row>
     <row r="82" spans="1:11" s="30" customFormat="1">
       <c r="A82" s="145" t="s">
-        <v>3603</v>
+        <v>3599</v>
       </c>
       <c r="B82" s="30" t="s">
-        <v>3660</v>
+        <v>3656</v>
       </c>
       <c r="C82" s="22" t="s">
         <v>1901</v>
@@ -31740,7 +31722,7 @@
         <v>2838</v>
       </c>
       <c r="E82" s="30" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="F82" s="30" t="s">
         <v>1902</v>
@@ -31749,16 +31731,16 @@
         <v>198</v>
       </c>
       <c r="H82" s="30" t="s">
-        <v>3471</v>
+        <v>3467</v>
       </c>
       <c r="I82" s="30" t="s">
-        <v>3315</v>
+        <v>3311</v>
       </c>
       <c r="J82" s="30" t="s">
-        <v>3592</v>
+        <v>3588</v>
       </c>
       <c r="K82" s="30" t="s">
-        <v>3536</v>
+        <v>3532</v>
       </c>
     </row>
     <row r="83" spans="1:11" s="148" customFormat="1">
@@ -31766,13 +31748,13 @@
         <v>1516</v>
       </c>
       <c r="B83" s="225" t="s">
-        <v>3050</v>
+        <v>3048</v>
       </c>
       <c r="C83" s="398" t="s">
         <v>1959</v>
       </c>
       <c r="D83" s="148" t="s">
-        <v>3658</v>
+        <v>3654</v>
       </c>
     </row>
     <row r="84" spans="1:11" s="280" customFormat="1">
@@ -31800,7 +31782,7 @@
         <v>693</v>
       </c>
       <c r="D85" s="30" t="s">
-        <v>3316</v>
+        <v>3312</v>
       </c>
       <c r="E85" s="30" t="s">
         <v>1791</v>
@@ -31812,16 +31794,16 @@
         <v>493</v>
       </c>
       <c r="H85" s="30" t="s">
-        <v>3433</v>
+        <v>3429</v>
       </c>
       <c r="I85" s="432" t="s">
         <v>2881</v>
       </c>
       <c r="J85" s="30" t="s">
-        <v>3453</v>
+        <v>3449</v>
       </c>
       <c r="K85" s="215" t="s">
-        <v>3634</v>
+        <v>3630</v>
       </c>
     </row>
     <row r="86" spans="1:11" s="147" customFormat="1">
@@ -31844,7 +31826,7 @@
     </row>
     <row r="87" spans="1:11" s="147" customFormat="1">
       <c r="A87" s="147" t="s">
-        <v>3149</v>
+        <v>3147</v>
       </c>
       <c r="B87" s="147" t="s">
         <v>909</v>
@@ -31862,10 +31844,10 @@
     </row>
     <row r="88" spans="1:11" s="30" customFormat="1">
       <c r="A88" s="145" t="s">
-        <v>3503</v>
+        <v>3499</v>
       </c>
       <c r="B88" s="30" t="s">
-        <v>3526</v>
+        <v>3522</v>
       </c>
       <c r="C88" s="153" t="s">
         <v>694</v>
@@ -31882,22 +31864,22 @@
       <c r="G88" s="30" t="s">
         <v>1524</v>
       </c>
-      <c r="H88" s="217" t="s">
-        <v>2936</v>
-      </c>
-      <c r="I88" s="217" t="s">
-        <v>2955</v>
+      <c r="H88" s="145" t="s">
+        <v>3666</v>
+      </c>
+      <c r="I88" s="145" t="s">
+        <v>3667</v>
       </c>
       <c r="J88" s="32" t="s">
-        <v>3029</v>
+        <v>3027</v>
       </c>
       <c r="K88" s="30" t="s">
-        <v>3028</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="89" spans="1:11" s="147" customFormat="1">
       <c r="A89" s="149" t="s">
-        <v>2976</v>
+        <v>2974</v>
       </c>
       <c r="B89" s="147">
         <v>64844119</v>
@@ -31915,7 +31897,7 @@
     </row>
     <row r="90" spans="1:11" s="148" customFormat="1">
       <c r="A90" s="225" t="s">
-        <v>3149</v>
+        <v>3147</v>
       </c>
       <c r="B90" s="148">
         <v>67381873</v>
@@ -31933,7 +31915,7 @@
     </row>
     <row r="91" spans="1:11" s="106" customFormat="1">
       <c r="A91" s="249" t="s">
-        <v>3599</v>
+        <v>3595</v>
       </c>
       <c r="B91" s="32" t="s">
         <v>1400</v>
@@ -31942,7 +31924,7 @@
         <v>46</v>
       </c>
       <c r="D91" s="106" t="s">
-        <v>3174</v>
+        <v>3172</v>
       </c>
       <c r="E91" s="106" t="s">
         <v>1123</v>
@@ -31954,16 +31936,16 @@
         <v>66</v>
       </c>
       <c r="H91" s="30" t="s">
-        <v>3175</v>
+        <v>3173</v>
       </c>
       <c r="I91" s="31" t="s">
         <v>2916</v>
       </c>
       <c r="J91" s="32" t="s">
-        <v>3013</v>
+        <v>3011</v>
       </c>
       <c r="K91" s="30" t="s">
-        <v>3291</v>
+        <v>3287</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="406" customFormat="1">
@@ -31994,7 +31976,7 @@
         <v>1718</v>
       </c>
       <c r="D93" s="148" t="s">
-        <v>3270</v>
+        <v>3267</v>
       </c>
     </row>
     <row r="94" spans="1:11" s="32" customFormat="1">
@@ -32011,7 +31993,7 @@
         <v>1362</v>
       </c>
       <c r="E94" s="32" t="s">
-        <v>3438</v>
+        <v>3434</v>
       </c>
       <c r="F94" s="32" t="s">
         <v>1363</v>
@@ -32023,7 +32005,7 @@
     </row>
     <row r="95" spans="1:11" s="148" customFormat="1">
       <c r="A95" s="148" t="s">
-        <v>3512</v>
+        <v>3508</v>
       </c>
       <c r="B95" s="148" t="s">
         <v>2648</v>
@@ -32040,7 +32022,7 @@
     </row>
     <row r="96" spans="1:11" s="148" customFormat="1">
       <c r="A96" s="148" t="s">
-        <v>3503</v>
+        <v>3499</v>
       </c>
       <c r="B96" s="148">
         <v>65633205</v>
@@ -32049,7 +32031,7 @@
         <v>1379</v>
       </c>
       <c r="D96" s="148" t="s">
-        <v>3527</v>
+        <v>3523</v>
       </c>
       <c r="E96" s="148" t="s">
         <v>1378</v>
@@ -32069,7 +32051,7 @@
         <v>2913</v>
       </c>
       <c r="E97" s="30" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="F97" s="30" t="s">
         <v>1902</v>
@@ -32078,16 +32060,16 @@
         <v>198</v>
       </c>
       <c r="H97" s="32" t="s">
-        <v>3478</v>
+        <v>3474</v>
       </c>
       <c r="I97" s="30" t="s">
-        <v>3638</v>
+        <v>3634</v>
       </c>
       <c r="J97" s="30" t="s">
-        <v>3338</v>
+        <v>3334</v>
       </c>
       <c r="K97" s="430" t="s">
-        <v>3501</v>
+        <v>3497</v>
       </c>
     </row>
     <row r="98" spans="1:13" s="388" customFormat="1">
@@ -32100,19 +32082,19 @@
     </row>
     <row r="100" spans="1:13" s="30" customFormat="1">
       <c r="A100" s="30" t="s">
-        <v>3245</v>
+        <v>3243</v>
       </c>
       <c r="B100" s="30" t="s">
-        <v>3651</v>
+        <v>3647</v>
       </c>
       <c r="C100" s="251" t="s">
         <v>2837</v>
       </c>
       <c r="D100" s="30" t="s">
-        <v>3341</v>
+        <v>3337</v>
       </c>
       <c r="E100" s="30" t="s">
-        <v>3099</v>
+        <v>3097</v>
       </c>
       <c r="F100" s="30" t="s">
         <v>1902</v>
@@ -32121,16 +32103,16 @@
         <v>198</v>
       </c>
       <c r="H100" s="30" t="s">
-        <v>3473</v>
+        <v>3469</v>
       </c>
       <c r="I100" s="30" t="s">
-        <v>3628</v>
+        <v>3624</v>
       </c>
       <c r="J100" s="30" t="s">
-        <v>3506</v>
+        <v>3502</v>
       </c>
       <c r="K100" s="30" t="s">
-        <v>3562</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="101" spans="1:13" s="388" customFormat="1">
@@ -32143,19 +32125,19 @@
     </row>
     <row r="103" spans="1:13" s="30" customFormat="1">
       <c r="A103" s="30" t="s">
-        <v>3149</v>
+        <v>3147</v>
       </c>
       <c r="B103" s="30" t="s">
-        <v>3267</v>
+        <v>3264</v>
       </c>
       <c r="C103" s="251" t="s">
         <v>2879</v>
       </c>
       <c r="D103" s="30" t="s">
-        <v>3189</v>
+        <v>3187</v>
       </c>
       <c r="E103" s="30" t="s">
-        <v>3190</v>
+        <v>3188</v>
       </c>
       <c r="F103" s="30" t="s">
         <v>1902</v>
@@ -32164,16 +32146,16 @@
         <v>198</v>
       </c>
       <c r="H103" s="30" t="s">
-        <v>3191</v>
+        <v>3189</v>
       </c>
       <c r="I103" s="30" t="s">
-        <v>3268</v>
+        <v>3265</v>
       </c>
       <c r="J103" s="30" t="s">
-        <v>3254</v>
+        <v>3252</v>
       </c>
       <c r="K103" s="30" t="s">
-        <v>3217</v>
+        <v>3215</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -32217,13 +32199,13 @@
         <v>2878</v>
       </c>
       <c r="D106" s="30" t="s">
+        <v>3031</v>
+      </c>
+      <c r="E106" s="30" t="s">
         <v>3033</v>
       </c>
-      <c r="E106" s="30" t="s">
-        <v>3035</v>
-      </c>
       <c r="F106" s="30" t="s">
-        <v>3034</v>
+        <v>3032</v>
       </c>
       <c r="G106" s="30" t="s">
         <v>59</v>
@@ -32275,7 +32257,7 @@
         <v>1982</v>
       </c>
       <c r="E127" s="30" t="s">
-        <v>3118</v>
+        <v>3116</v>
       </c>
       <c r="F127" t="s">
         <v>1980</v>
@@ -32295,7 +32277,7 @@
         <v>1952</v>
       </c>
       <c r="E128" s="30" t="s">
-        <v>3118</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -32309,15 +32291,15 @@
         <v>2719</v>
       </c>
       <c r="D129" s="373" t="s">
-        <v>3186</v>
+        <v>3184</v>
       </c>
       <c r="E129" s="30" t="s">
-        <v>3118</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="4" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="B130">
         <v>67046608</v>
@@ -32329,7 +32311,7 @@
         <v>2596</v>
       </c>
       <c r="E130" s="30" t="s">
-        <v>3118</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -32346,7 +32328,7 @@
         <v>1958</v>
       </c>
       <c r="E131" s="30" t="s">
-        <v>3118</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="133" spans="1:6" s="121" customFormat="1" ht="23.5">
@@ -32368,7 +32350,7 @@
         <v>2347</v>
       </c>
       <c r="E134" s="30" t="s">
-        <v>3135</v>
+        <v>3133</v>
       </c>
       <c r="F134" t="s">
         <v>1339</v>
@@ -32388,7 +32370,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>3507</v>
+        <v>3503</v>
       </c>
       <c r="B139">
         <v>64720128</v>
@@ -32417,7 +32399,7 @@
         <v>1969</v>
       </c>
       <c r="D140" s="373" t="s">
-        <v>3160</v>
+        <v>3158</v>
       </c>
       <c r="E140" s="30" t="s">
         <v>1968</v>
@@ -32448,7 +32430,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="C143" s="1" t="s">
-        <v>3199</v>
+        <v>3197</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -32492,7 +32474,7 @@
         <v>2352</v>
       </c>
       <c r="E153" s="30" t="s">
-        <v>3119</v>
+        <v>3117</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -32500,21 +32482,21 @@
         <v>1498</v>
       </c>
       <c r="B154" t="s">
-        <v>3366</v>
+        <v>3362</v>
       </c>
       <c r="C154" t="s">
         <v>2225</v>
       </c>
       <c r="D154" s="373" t="s">
-        <v>3365</v>
+        <v>3361</v>
       </c>
       <c r="E154" s="30" t="s">
-        <v>3119</v>
+        <v>3117</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="B155">
         <v>60183566</v>
@@ -32526,12 +32508,12 @@
         <v>2597</v>
       </c>
       <c r="E155" s="30" t="s">
-        <v>3231</v>
+        <v>3229</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="97" t="s">
-        <v>3603</v>
+        <v>3599</v>
       </c>
       <c r="B156" t="s">
         <v>1164</v>
@@ -32540,10 +32522,10 @@
         <v>2235</v>
       </c>
       <c r="D156" s="373" t="s">
-        <v>3661</v>
+        <v>3657</v>
       </c>
       <c r="E156" s="30" t="s">
-        <v>3231</v>
+        <v>3229</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -32560,7 +32542,7 @@
         <v>2490</v>
       </c>
       <c r="E157" s="30" t="s">
-        <v>3231</v>
+        <v>3229</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -32577,7 +32559,7 @@
         <v>2637</v>
       </c>
       <c r="E158" s="30" t="s">
-        <v>3231</v>
+        <v>3229</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -32591,15 +32573,15 @@
         <v>2510</v>
       </c>
       <c r="D159" s="373" t="s">
-        <v>3368</v>
+        <v>3364</v>
       </c>
       <c r="E159" s="30" t="s">
-        <v>3231</v>
+        <v>3229</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" t="s">
-        <v>3292</v>
+        <v>3288</v>
       </c>
       <c r="B160">
         <v>65133588</v>
@@ -32611,12 +32593,12 @@
         <v>2511</v>
       </c>
       <c r="E160" s="30" t="s">
-        <v>3231</v>
+        <v>3229</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="4" t="s">
-        <v>3176</v>
+        <v>3174</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>1137</v>
@@ -32625,10 +32607,10 @@
         <v>2598</v>
       </c>
       <c r="D161" s="373" t="s">
-        <v>3063</v>
+        <v>3061</v>
       </c>
       <c r="E161" s="30" t="s">
-        <v>3231</v>
+        <v>3229</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -32642,32 +32624,32 @@
         <v>2513</v>
       </c>
       <c r="D162" s="373" t="s">
-        <v>3183</v>
+        <v>3181</v>
       </c>
       <c r="E162" s="30" t="s">
-        <v>3231</v>
+        <v>3229</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="97" t="s">
-        <v>3603</v>
+        <v>3599</v>
       </c>
       <c r="B163" s="460" t="s">
         <v>1164</v>
       </c>
       <c r="C163" s="460" t="s">
-        <v>3664</v>
+        <v>3660</v>
       </c>
       <c r="D163" s="373" t="s">
-        <v>3665</v>
+        <v>3661</v>
       </c>
       <c r="E163" s="30" t="s">
-        <v>3231</v>
+        <v>3229</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="4" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>2168</v>
@@ -32679,12 +32661,12 @@
         <v>2491</v>
       </c>
       <c r="E164" s="30" t="s">
-        <v>3451</v>
+        <v>3447</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>3415</v>
+        <v>3411</v>
       </c>
       <c r="B165">
         <v>66315726</v>
@@ -32696,12 +32678,12 @@
         <v>2273</v>
       </c>
       <c r="E165" s="30" t="s">
-        <v>3451</v>
+        <v>3447</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" t="s">
-        <v>3245</v>
+        <v>3243</v>
       </c>
       <c r="B166">
         <v>64568369</v>
@@ -32713,24 +32695,24 @@
         <v>2273</v>
       </c>
       <c r="E166" s="30" t="s">
-        <v>3451</v>
+        <v>3447</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>3415</v>
+        <v>3411</v>
       </c>
       <c r="B167">
         <v>68818154</v>
       </c>
       <c r="C167" t="s">
-        <v>3369</v>
+        <v>3365</v>
       </c>
       <c r="D167" s="373" t="s">
         <v>2599</v>
       </c>
       <c r="E167" s="30" t="s">
-        <v>3451</v>
+        <v>3447</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -32744,10 +32726,10 @@
         <v>2721</v>
       </c>
       <c r="D168" s="373" t="s">
-        <v>3218</v>
+        <v>3216</v>
       </c>
       <c r="E168" s="30" t="s">
-        <v>3023</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -32764,7 +32746,7 @@
         <v>2757</v>
       </c>
       <c r="E169" s="30" t="s">
-        <v>3023</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -32781,7 +32763,7 @@
         <v>2488</v>
       </c>
       <c r="E170" s="30" t="s">
-        <v>3023</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -32798,7 +32780,7 @@
         <v>2312</v>
       </c>
       <c r="E171" s="30" t="s">
-        <v>3023</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -32812,10 +32794,10 @@
         <v>2324</v>
       </c>
       <c r="D172" s="373" t="s">
-        <v>3271</v>
+        <v>3268</v>
       </c>
       <c r="E172" s="30" t="s">
-        <v>3062</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -32829,10 +32811,10 @@
         <v>2325</v>
       </c>
       <c r="D173" s="373" t="s">
-        <v>3197</v>
+        <v>3195</v>
       </c>
       <c r="E173" s="30" t="s">
-        <v>3062</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -32846,10 +32828,10 @@
         <v>2326</v>
       </c>
       <c r="D174" s="373" t="s">
-        <v>3227</v>
+        <v>3225</v>
       </c>
       <c r="E174" s="30" t="s">
-        <v>3062</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -32860,15 +32842,15 @@
         <v>2759</v>
       </c>
       <c r="D175" s="373" t="s">
-        <v>3662</v>
+        <v>3658</v>
       </c>
       <c r="E175" s="30" t="s">
-        <v>3135</v>
+        <v>3133</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" t="s">
-        <v>3292</v>
+        <v>3288</v>
       </c>
       <c r="B176">
         <v>66935922</v>
@@ -32877,27 +32859,27 @@
         <v>2760</v>
       </c>
       <c r="D176" s="220" t="s">
-        <v>3272</v>
+        <v>3269</v>
       </c>
       <c r="E176" s="30" t="s">
-        <v>3135</v>
+        <v>3133</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="B177">
         <v>64455322</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>3184</v>
+        <v>3182</v>
       </c>
       <c r="D177" s="220" t="s">
-        <v>3553</v>
+        <v>3549</v>
       </c>
       <c r="E177" s="30" t="s">
-        <v>3135</v>
+        <v>3133</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -32914,12 +32896,12 @@
         <v>2779</v>
       </c>
       <c r="E178" s="30" t="s">
-        <v>3135</v>
+        <v>3133</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" t="s">
-        <v>3176</v>
+        <v>3174</v>
       </c>
       <c r="B179">
         <v>68570552</v>
@@ -32928,15 +32910,15 @@
         <v>2762</v>
       </c>
       <c r="D179" s="220" t="s">
-        <v>3273</v>
+        <v>3270</v>
       </c>
       <c r="E179" s="30" t="s">
-        <v>3135</v>
+        <v>3133</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" t="s">
-        <v>3176</v>
+        <v>3174</v>
       </c>
       <c r="B180">
         <v>69964218</v>
@@ -32945,15 +32927,15 @@
         <v>2784</v>
       </c>
       <c r="D180" s="373" t="s">
-        <v>3274</v>
+        <v>3271</v>
       </c>
       <c r="E180" s="30" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" t="s">
-        <v>3149</v>
+        <v>3147</v>
       </c>
       <c r="B181">
         <v>63950696</v>
@@ -32965,12 +32947,12 @@
         <v>2785</v>
       </c>
       <c r="E181" s="30" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="4" t="s">
-        <v>3149</v>
+        <v>3147</v>
       </c>
       <c r="B182" t="s">
         <v>2814</v>
@@ -32982,7 +32964,7 @@
         <v>2785</v>
       </c>
       <c r="E182" s="30" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -32999,12 +32981,12 @@
         <v>2860</v>
       </c>
       <c r="E183" s="30" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="B184">
         <v>63755362</v>
@@ -33013,15 +32995,15 @@
         <v>2849</v>
       </c>
       <c r="D184" s="373" t="s">
-        <v>3597</v>
+        <v>3593</v>
       </c>
       <c r="E184" s="30" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="97" t="s">
-        <v>3603</v>
+        <v>3599</v>
       </c>
       <c r="B185" t="s">
         <v>1164</v>
@@ -33030,15 +33012,15 @@
         <v>2819</v>
       </c>
       <c r="D185" s="373" t="s">
-        <v>3663</v>
+        <v>3659</v>
       </c>
       <c r="E185" s="30" t="s">
-        <v>3262</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" t="s">
-        <v>3468</v>
+        <v>3464</v>
       </c>
       <c r="B186">
         <v>60240509</v>
@@ -33047,10 +33029,10 @@
         <v>2820</v>
       </c>
       <c r="D186" s="373" t="s">
-        <v>3466</v>
+        <v>3462</v>
       </c>
       <c r="E186" s="30" t="s">
-        <v>3467</v>
+        <v>3463</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -33064,10 +33046,10 @@
         <v>2821</v>
       </c>
       <c r="D187" s="373" t="s">
-        <v>3402</v>
+        <v>3398</v>
       </c>
       <c r="E187" s="30" t="s">
-        <v>3262</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -33084,7 +33066,7 @@
         <v>2828</v>
       </c>
       <c r="E188" s="30" t="s">
-        <v>3262</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -33101,7 +33083,7 @@
         <v>2828</v>
       </c>
       <c r="E189" s="30" t="s">
-        <v>3262</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -33118,12 +33100,12 @@
         <v>2828</v>
       </c>
       <c r="E190" s="30" t="s">
-        <v>3262</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="4" t="s">
-        <v>3149</v>
+        <v>3147</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>1857</v>
@@ -33135,12 +33117,12 @@
         <v>2828</v>
       </c>
       <c r="E191" s="30" t="s">
-        <v>3262</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="97" t="s">
-        <v>3603</v>
+        <v>3599</v>
       </c>
       <c r="B192" t="s">
         <v>1164</v>
@@ -33149,15 +33131,15 @@
         <v>2861</v>
       </c>
       <c r="D192" s="373" t="s">
-        <v>3666</v>
+        <v>3662</v>
       </c>
       <c r="E192" s="30" t="s">
-        <v>3262</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" t="s">
-        <v>3245</v>
+        <v>3243</v>
       </c>
       <c r="B193">
         <v>69575383</v>
@@ -33166,10 +33148,10 @@
         <v>2826</v>
       </c>
       <c r="D193" s="373" t="s">
-        <v>3630</v>
+        <v>3626</v>
       </c>
       <c r="E193" s="30" t="s">
-        <v>3262</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -33186,18 +33168,18 @@
         <v>2828</v>
       </c>
       <c r="E194" s="30" t="s">
-        <v>3262</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="C195" s="56" t="s">
-        <v>3211</v>
+        <v>3209</v>
       </c>
       <c r="D195" t="s">
-        <v>3390</v>
+        <v>3386</v>
       </c>
       <c r="E195" s="30" t="s">
-        <v>3119</v>
+        <v>3117</v>
       </c>
     </row>
     <row r="197" spans="1:5" s="391" customFormat="1" ht="23.5">
@@ -33219,49 +33201,49 @@
         <v>2850</v>
       </c>
       <c r="D198" s="373" t="s">
-        <v>3401</v>
+        <v>3397</v>
       </c>
       <c r="E198" s="30" t="s">
-        <v>3249</v>
+        <v>3247</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" t="s">
-        <v>3461</v>
+        <v>3457</v>
       </c>
       <c r="B199" t="s">
-        <v>3462</v>
+        <v>3458</v>
       </c>
       <c r="C199" t="s">
         <v>2843</v>
       </c>
       <c r="D199" s="373" t="s">
-        <v>3460</v>
+        <v>3456</v>
       </c>
       <c r="E199" s="30" t="s">
-        <v>3249</v>
+        <v>3247</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" t="s">
-        <v>3176</v>
+        <v>3174</v>
       </c>
       <c r="B200">
         <v>63617941</v>
       </c>
       <c r="C200" s="22" t="s">
-        <v>3275</v>
+        <v>3272</v>
       </c>
       <c r="D200" s="373" t="s">
         <v>2902</v>
       </c>
       <c r="E200" s="30" t="s">
-        <v>3249</v>
+        <v>3247</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" t="s">
-        <v>3002</v>
+        <v>3000</v>
       </c>
       <c r="B201">
         <v>65633205</v>
@@ -33270,15 +33252,15 @@
         <v>2844</v>
       </c>
       <c r="D201" s="373" t="s">
-        <v>3001</v>
+        <v>2999</v>
       </c>
       <c r="E201" s="30" t="s">
-        <v>3249</v>
+        <v>3247</v>
       </c>
     </row>
     <row r="202" spans="1:5">
       <c r="A202" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="B202">
         <v>62279384</v>
@@ -33287,10 +33269,10 @@
         <v>2845</v>
       </c>
       <c r="D202" s="373" t="s">
-        <v>3543</v>
+        <v>3539</v>
       </c>
       <c r="E202" s="30" t="s">
-        <v>3249</v>
+        <v>3247</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -33304,27 +33286,27 @@
         <v>2901</v>
       </c>
       <c r="D203" s="373" t="s">
-        <v>3567</v>
+        <v>3563</v>
       </c>
       <c r="E203" s="30" t="s">
-        <v>3249</v>
+        <v>3247</v>
       </c>
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="30" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="B204" t="s">
-        <v>3552</v>
+        <v>3548</v>
       </c>
       <c r="C204" t="s">
         <v>2846</v>
       </c>
       <c r="D204" s="373" t="s">
-        <v>3551</v>
+        <v>3547</v>
       </c>
       <c r="E204" s="30" t="s">
-        <v>3249</v>
+        <v>3247</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -33335,18 +33317,18 @@
         <v>64982293</v>
       </c>
       <c r="C205" t="s">
-        <v>3542</v>
+        <v>3538</v>
       </c>
       <c r="D205" s="373" t="s">
-        <v>3624</v>
+        <v>3620</v>
       </c>
       <c r="E205" s="30" t="s">
-        <v>3249</v>
+        <v>3247</v>
       </c>
     </row>
     <row r="206" spans="1:5">
       <c r="A206" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="B206" t="s">
         <v>2909</v>
@@ -33358,7 +33340,7 @@
         <v>2907</v>
       </c>
       <c r="E206" s="30" t="s">
-        <v>3249</v>
+        <v>3247</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -33372,10 +33354,10 @@
         <v>2908</v>
       </c>
       <c r="D207" s="373" t="s">
-        <v>3248</v>
+        <v>3246</v>
       </c>
       <c r="E207" s="30" t="s">
-        <v>3249</v>
+        <v>3247</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -33392,7 +33374,7 @@
         <v>2924</v>
       </c>
       <c r="E208" s="30" t="s">
-        <v>3521</v>
+        <v>3517</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -33403,18 +33385,18 @@
         <v>65583706</v>
       </c>
       <c r="C209" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
       <c r="D209" s="373" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
       <c r="E209" s="30" t="s">
-        <v>3521</v>
+        <v>3517</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210" t="s">
-        <v>3414</v>
+        <v>3410</v>
       </c>
       <c r="B210">
         <v>65574051</v>
@@ -33426,7 +33408,7 @@
         <v>2926</v>
       </c>
       <c r="E210" s="30" t="s">
-        <v>3521</v>
+        <v>3517</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -33434,16 +33416,16 @@
         <v>2789</v>
       </c>
       <c r="B211" t="s">
-        <v>2970</v>
+        <v>2968</v>
       </c>
       <c r="C211" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
       <c r="D211" s="373" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="E211" s="30" t="s">
-        <v>3521</v>
+        <v>3517</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -33454,13 +33436,13 @@
         <v>64881871</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>3185</v>
+        <v>3183</v>
       </c>
       <c r="D212" t="s">
-        <v>3150</v>
+        <v>3148</v>
       </c>
       <c r="E212" s="30" t="s">
-        <v>3521</v>
+        <v>3517</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -33471,30 +33453,30 @@
         <v>68069608</v>
       </c>
       <c r="C213" s="22" t="s">
+        <v>2986</v>
+      </c>
+      <c r="D213" s="373" t="s">
         <v>2988</v>
       </c>
-      <c r="D213" s="373" t="s">
-        <v>2990</v>
-      </c>
       <c r="E213" s="30" t="s">
-        <v>3612</v>
+        <v>3608</v>
       </c>
     </row>
     <row r="214" spans="1:5">
       <c r="A214" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="B214">
         <v>63258169</v>
       </c>
       <c r="C214" s="22" t="s">
-        <v>3006</v>
+        <v>3004</v>
       </c>
       <c r="D214" t="s">
-        <v>3052</v>
+        <v>3050</v>
       </c>
       <c r="E214" s="30" t="s">
-        <v>3612</v>
+        <v>3608</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -33505,13 +33487,13 @@
         <v>69243886</v>
       </c>
       <c r="C215" s="22" t="s">
-        <v>3007</v>
+        <v>3005</v>
       </c>
       <c r="D215" t="s">
-        <v>2999</v>
+        <v>2997</v>
       </c>
       <c r="E215" s="30" t="s">
-        <v>3612</v>
+        <v>3608</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -33522,13 +33504,13 @@
         <v>67752170</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>2989</v>
+        <v>2987</v>
       </c>
       <c r="D216" t="s">
-        <v>3000</v>
+        <v>2998</v>
       </c>
       <c r="E216" s="30" t="s">
-        <v>3612</v>
+        <v>3608</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -33539,13 +33521,13 @@
         <v>64457890</v>
       </c>
       <c r="C217" t="s">
-        <v>3008</v>
+        <v>3006</v>
       </c>
       <c r="D217" s="373" t="s">
-        <v>3009</v>
+        <v>3007</v>
       </c>
       <c r="E217" s="30" t="s">
-        <v>3612</v>
+        <v>3608</v>
       </c>
     </row>
     <row r="231" spans="3:4">
@@ -36317,7 +36299,7 @@
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>2983</v>
+        <v>2981</v>
       </c>
     </row>
     <row r="18" spans="4:4">
@@ -36404,7 +36386,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="76" t="s">
-        <v>2986</v>
+        <v>2984</v>
       </c>
       <c r="B6" s="76">
         <v>64966680</v>
@@ -36419,7 +36401,7 @@
         <v>678</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>3282</v>
+        <v>3279</v>
       </c>
       <c r="G6" s="363" t="s">
         <v>1442</v>
@@ -36446,7 +36428,7 @@
         <v>362</v>
       </c>
       <c r="F7" s="183" t="s">
-        <v>3282</v>
+        <v>3279</v>
       </c>
       <c r="G7" s="183" t="s">
         <v>1442</v>
@@ -36458,7 +36440,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="193" t="s">
-        <v>3149</v>
+        <v>3147</v>
       </c>
       <c r="B8" s="193">
         <v>62747874</v>
@@ -36473,7 +36455,7 @@
         <v>362</v>
       </c>
       <c r="F8" s="183" t="s">
-        <v>3282</v>
+        <v>3279</v>
       </c>
       <c r="G8" s="183" t="s">
         <v>1442</v>
@@ -36500,7 +36482,7 @@
         <v>362</v>
       </c>
       <c r="F9" s="183" t="s">
-        <v>3282</v>
+        <v>3279</v>
       </c>
       <c r="G9" s="183" t="s">
         <v>1442</v>
@@ -36527,7 +36509,7 @@
         <v>362</v>
       </c>
       <c r="F10" s="183" t="s">
-        <v>3282</v>
+        <v>3279</v>
       </c>
       <c r="G10" s="183" t="s">
         <v>1442</v>
@@ -36554,7 +36536,7 @@
         <v>362</v>
       </c>
       <c r="F11" s="183" t="s">
-        <v>3282</v>
+        <v>3279</v>
       </c>
       <c r="G11" s="183" t="s">
         <v>1442</v>
@@ -36578,7 +36560,7 @@
         <v>2518</v>
       </c>
       <c r="E13" s="195" t="s">
-        <v>3283</v>
+        <v>3280</v>
       </c>
       <c r="F13" s="195" t="s">
         <v>1429</v>
@@ -36604,7 +36586,7 @@
         <v>1846</v>
       </c>
       <c r="E14" s="193" t="s">
-        <v>3283</v>
+        <v>3280</v>
       </c>
       <c r="F14" s="193" t="s">
         <v>1429</v>
@@ -36630,7 +36612,7 @@
         <v>2793</v>
       </c>
       <c r="E15" s="193" t="s">
-        <v>3283</v>
+        <v>3280</v>
       </c>
       <c r="F15" s="193" t="s">
         <v>1429</v>
@@ -36644,7 +36626,7 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="183" t="s">
-        <v>2986</v>
+        <v>2984</v>
       </c>
       <c r="B16" s="183">
         <v>63666666</v>
@@ -36656,7 +36638,7 @@
         <v>2315</v>
       </c>
       <c r="E16" s="193" t="s">
-        <v>3283</v>
+        <v>3280</v>
       </c>
       <c r="F16" s="193" t="s">
         <v>1429</v>
@@ -36670,7 +36652,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="193" t="s">
-        <v>3503</v>
+        <v>3499</v>
       </c>
       <c r="B17" s="193">
         <v>64403333</v>
@@ -36682,7 +36664,7 @@
         <v>1507</v>
       </c>
       <c r="E17" s="193" t="s">
-        <v>3283</v>
+        <v>3280</v>
       </c>
       <c r="F17" s="193" t="s">
         <v>1429</v>
@@ -36708,7 +36690,7 @@
         <v>2157</v>
       </c>
       <c r="E18" s="193" t="s">
-        <v>3283</v>
+        <v>3280</v>
       </c>
       <c r="F18" s="193" t="s">
         <v>1429</v>
@@ -36722,7 +36704,7 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="195" t="s">
-        <v>2986</v>
+        <v>2984</v>
       </c>
       <c r="B20" s="195">
         <v>67539485</v>
@@ -36737,7 +36719,7 @@
         <v>362</v>
       </c>
       <c r="F20" s="195" t="s">
-        <v>3283</v>
+        <v>3280</v>
       </c>
       <c r="G20" s="76" t="s">
         <v>422</v>
@@ -36766,7 +36748,7 @@
         <v>362</v>
       </c>
       <c r="F21" s="193" t="s">
-        <v>3283</v>
+        <v>3280</v>
       </c>
       <c r="G21" s="183" t="s">
         <v>422</v>
@@ -36795,7 +36777,7 @@
         <v>362</v>
       </c>
       <c r="F22" s="193" t="s">
-        <v>3283</v>
+        <v>3280</v>
       </c>
       <c r="G22" s="183" t="s">
         <v>422</v>
@@ -36809,7 +36791,7 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="183" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="B23" s="183">
         <v>60389752</v>
@@ -36824,7 +36806,7 @@
         <v>362</v>
       </c>
       <c r="F23" s="193" t="s">
-        <v>3283</v>
+        <v>3280</v>
       </c>
       <c r="G23" s="183" t="s">
         <v>422</v>
@@ -36853,7 +36835,7 @@
         <v>362</v>
       </c>
       <c r="F24" s="193" t="s">
-        <v>3283</v>
+        <v>3280</v>
       </c>
       <c r="G24" s="183" t="s">
         <v>422</v>
@@ -36882,7 +36864,7 @@
         <v>362</v>
       </c>
       <c r="F25" s="193" t="s">
-        <v>3283</v>
+        <v>3280</v>
       </c>
       <c r="G25" s="183" t="s">
         <v>422</v>
@@ -36896,7 +36878,7 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="76" t="s">
-        <v>3245</v>
+        <v>3243</v>
       </c>
       <c r="B27" s="76">
         <v>60389752</v>
@@ -36911,7 +36893,7 @@
         <v>362</v>
       </c>
       <c r="F27" s="76" t="s">
-        <v>3386</v>
+        <v>3382</v>
       </c>
       <c r="G27" s="76" t="s">
         <v>1443</v>
@@ -36938,7 +36920,7 @@
         <v>362</v>
       </c>
       <c r="F28" s="183" t="s">
-        <v>3386</v>
+        <v>3382</v>
       </c>
       <c r="G28" s="183" t="s">
         <v>378</v>
@@ -36952,22 +36934,22 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="183" t="s">
-        <v>3488</v>
+        <v>3484</v>
       </c>
       <c r="B29" s="183">
         <v>65234700</v>
       </c>
       <c r="C29" s="194" t="s">
-        <v>3409</v>
+        <v>3405</v>
       </c>
       <c r="D29" s="183" t="s">
-        <v>3410</v>
+        <v>3406</v>
       </c>
       <c r="E29" s="433">
         <v>46243</v>
       </c>
       <c r="F29" s="183" t="s">
-        <v>3386</v>
+        <v>3382</v>
       </c>
       <c r="G29" s="183" t="s">
         <v>378</v>
@@ -36996,7 +36978,7 @@
         <v>362</v>
       </c>
       <c r="F30" s="183" t="s">
-        <v>3386</v>
+        <v>3382</v>
       </c>
       <c r="G30" s="183" t="s">
         <v>378</v>
@@ -37025,7 +37007,7 @@
         <v>362</v>
       </c>
       <c r="F31" s="183" t="s">
-        <v>3386</v>
+        <v>3382</v>
       </c>
       <c r="G31" s="183" t="s">
         <v>378</v>
@@ -37039,7 +37021,7 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="183" t="s">
-        <v>3176</v>
+        <v>3174</v>
       </c>
       <c r="B32" s="183">
         <v>68241069</v>
@@ -37054,7 +37036,7 @@
         <v>362</v>
       </c>
       <c r="F32" s="183" t="s">
-        <v>3386</v>
+        <v>3382</v>
       </c>
       <c r="G32" s="183" t="s">
         <v>378</v>
@@ -37077,13 +37059,13 @@
         <v>1665</v>
       </c>
       <c r="D34" s="195" t="s">
-        <v>3573</v>
+        <v>3569</v>
       </c>
       <c r="E34" s="76" t="s">
         <v>2486</v>
       </c>
       <c r="F34" s="195" t="s">
-        <v>3465</v>
+        <v>3461</v>
       </c>
       <c r="G34" s="76" t="s">
         <v>1442</v>
@@ -37094,7 +37076,7 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="193" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="B35" s="193">
         <v>63465332</v>
@@ -37109,7 +37091,7 @@
         <v>2486</v>
       </c>
       <c r="F35" s="193" t="s">
-        <v>3465</v>
+        <v>3461</v>
       </c>
       <c r="G35" s="183" t="s">
         <v>1442</v>
@@ -37120,7 +37102,7 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="193" t="s">
-        <v>2986</v>
+        <v>2984</v>
       </c>
       <c r="B36" s="193">
         <v>63226030</v>
@@ -37135,7 +37117,7 @@
         <v>2486</v>
       </c>
       <c r="F36" s="193" t="s">
-        <v>3465</v>
+        <v>3461</v>
       </c>
       <c r="G36" s="183" t="s">
         <v>1442</v>
@@ -37146,7 +37128,7 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="193" t="s">
-        <v>3441</v>
+        <v>3437</v>
       </c>
       <c r="B37" s="193">
         <v>69111188</v>
@@ -37161,7 +37143,7 @@
         <v>2486</v>
       </c>
       <c r="F37" s="193" t="s">
-        <v>3465</v>
+        <v>3461</v>
       </c>
       <c r="G37" s="183" t="s">
         <v>1442</v>
@@ -37187,7 +37169,7 @@
         <v>2486</v>
       </c>
       <c r="F38" s="193" t="s">
-        <v>3465</v>
+        <v>3461</v>
       </c>
       <c r="G38" s="183" t="s">
         <v>1442</v>
@@ -37213,7 +37195,7 @@
         <v>2486</v>
       </c>
       <c r="F39" s="193" t="s">
-        <v>3465</v>
+        <v>3461</v>
       </c>
       <c r="G39" s="183" t="s">
         <v>1442</v>
@@ -37226,16 +37208,16 @@
       <c r="A41" s="195"/>
       <c r="B41" s="195"/>
       <c r="C41" s="195" t="s">
-        <v>3456</v>
+        <v>3452</v>
       </c>
       <c r="D41" s="195" t="s">
-        <v>3457</v>
+        <v>3453</v>
       </c>
       <c r="E41" s="76" t="s">
         <v>362</v>
       </c>
       <c r="F41" s="195" t="s">
-        <v>3458</v>
+        <v>3454</v>
       </c>
       <c r="G41" s="76" t="s">
         <v>2374</v>
@@ -37255,7 +37237,7 @@
         <v>69563253</v>
       </c>
       <c r="C42" s="193" t="s">
-        <v>3459</v>
+        <v>3455</v>
       </c>
       <c r="D42" s="193" t="s">
         <v>1677</v>
@@ -37269,16 +37251,16 @@
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="234" t="s">
-        <v>2964</v>
+        <v>2962</v>
       </c>
       <c r="B43" s="193" t="s">
         <v>1943</v>
       </c>
       <c r="C43" s="194" t="s">
-        <v>3436</v>
+        <v>3432</v>
       </c>
       <c r="D43" s="193" t="s">
-        <v>3437</v>
+        <v>3433</v>
       </c>
       <c r="E43" s="433">
         <v>46304</v>
@@ -37295,7 +37277,7 @@
         <v>62751201</v>
       </c>
       <c r="C44" s="194" t="s">
-        <v>3463</v>
+        <v>3459</v>
       </c>
       <c r="D44" s="183" t="s">
         <v>1357</v>
@@ -37315,10 +37297,10 @@
         <v>68030850</v>
       </c>
       <c r="C45" s="193" t="s">
-        <v>3439</v>
+        <v>3435</v>
       </c>
       <c r="D45" s="193" t="s">
-        <v>3440</v>
+        <v>3436</v>
       </c>
       <c r="E45" s="433">
         <v>46243</v>
@@ -37351,16 +37333,16 @@
       <c r="A48" s="195"/>
       <c r="B48" s="195"/>
       <c r="C48" s="195" t="s">
-        <v>3490</v>
+        <v>3486</v>
       </c>
       <c r="D48" s="195" t="s">
-        <v>3491</v>
+        <v>3487</v>
       </c>
       <c r="E48" s="76" t="s">
-        <v>3492</v>
+        <v>3488</v>
       </c>
       <c r="F48" s="195" t="s">
-        <v>3493</v>
+        <v>3489</v>
       </c>
       <c r="G48" s="76" t="s">
         <v>1442</v>
@@ -37397,10 +37379,10 @@
         <v>61548403</v>
       </c>
       <c r="C50" s="194" t="s">
-        <v>3494</v>
+        <v>3490</v>
       </c>
       <c r="D50" s="193" t="s">
-        <v>3495</v>
+        <v>3491</v>
       </c>
       <c r="E50" s="433">
         <v>46304</v>
@@ -37413,7 +37395,7 @@
       <c r="C51" s="456"/>
       <c r="D51" s="456"/>
       <c r="E51" s="433" t="s">
-        <v>3572</v>
+        <v>3568</v>
       </c>
       <c r="F51" s="193"/>
       <c r="G51" s="183"/>
@@ -37433,7 +37415,7 @@
         <v>936</v>
       </c>
       <c r="E52" s="433" t="s">
-        <v>3572</v>
+        <v>3568</v>
       </c>
       <c r="F52" s="193"/>
       <c r="G52" s="183"/>
@@ -37441,19 +37423,19 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="183" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="B53" s="183">
         <v>64543204</v>
       </c>
       <c r="C53" s="194" t="s">
-        <v>2962</v>
+        <v>2960</v>
       </c>
       <c r="D53" s="183" t="s">
-        <v>2961</v>
+        <v>2959</v>
       </c>
       <c r="E53" s="433" t="s">
-        <v>3572</v>
+        <v>3568</v>
       </c>
       <c r="F53" s="193"/>
       <c r="G53" s="183"/>
@@ -37470,13 +37452,13 @@
         <v>1664</v>
       </c>
       <c r="D55" s="195" t="s">
-        <v>3024</v>
+        <v>3022</v>
       </c>
       <c r="E55" s="76" t="s">
         <v>2486</v>
       </c>
       <c r="F55" s="195" t="s">
-        <v>3497</v>
+        <v>3493</v>
       </c>
       <c r="G55" s="76" t="s">
         <v>1442</v>
@@ -37502,7 +37484,7 @@
         <v>2486</v>
       </c>
       <c r="F56" s="193" t="s">
-        <v>3497</v>
+        <v>3493</v>
       </c>
       <c r="G56" s="183" t="s">
         <v>1442</v>
@@ -37522,13 +37504,13 @@
         <v>2610</v>
       </c>
       <c r="D57" s="193" t="s">
-        <v>3206</v>
+        <v>3204</v>
       </c>
       <c r="E57" s="183" t="s">
         <v>2486</v>
       </c>
       <c r="F57" s="193" t="s">
-        <v>3497</v>
+        <v>3493</v>
       </c>
       <c r="G57" s="183" t="s">
         <v>1442</v>
@@ -37554,7 +37536,7 @@
         <v>2486</v>
       </c>
       <c r="F58" s="193" t="s">
-        <v>3497</v>
+        <v>3493</v>
       </c>
       <c r="G58" s="183" t="s">
         <v>1442</v>
@@ -37565,7 +37547,7 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="193" t="s">
-        <v>2976</v>
+        <v>2974</v>
       </c>
       <c r="B59" s="193">
         <v>65174343</v>
@@ -37580,7 +37562,7 @@
         <v>2486</v>
       </c>
       <c r="F59" s="193" t="s">
-        <v>3497</v>
+        <v>3493</v>
       </c>
       <c r="G59" s="183" t="s">
         <v>1442</v>
@@ -37597,16 +37579,16 @@
         <v>63062167</v>
       </c>
       <c r="C60" s="193" t="s">
-        <v>3321</v>
+        <v>3317</v>
       </c>
       <c r="D60" s="193" t="s">
-        <v>3356</v>
+        <v>3352</v>
       </c>
       <c r="E60" s="183" t="s">
         <v>2486</v>
       </c>
       <c r="F60" s="193" t="s">
-        <v>3497</v>
+        <v>3493</v>
       </c>
       <c r="G60" s="183" t="s">
         <v>1442</v>
@@ -37632,7 +37614,7 @@
         <v>2486</v>
       </c>
       <c r="F62" s="195" t="s">
-        <v>3497</v>
+        <v>3493</v>
       </c>
       <c r="G62" s="76" t="s">
         <v>1442</v>
@@ -37658,7 +37640,7 @@
         <v>2486</v>
       </c>
       <c r="F63" s="193" t="s">
-        <v>3497</v>
+        <v>3493</v>
       </c>
       <c r="G63" s="183" t="s">
         <v>1442</v>
@@ -37669,7 +37651,7 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="183" t="s">
-        <v>3415</v>
+        <v>3411</v>
       </c>
       <c r="B64" s="183">
         <v>64403333</v>
@@ -37684,7 +37666,7 @@
         <v>2486</v>
       </c>
       <c r="F64" s="193" t="s">
-        <v>3497</v>
+        <v>3493</v>
       </c>
       <c r="G64" s="183" t="s">
         <v>1442</v>
@@ -37695,7 +37677,7 @@
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="193" t="s">
-        <v>3276</v>
+        <v>3273</v>
       </c>
       <c r="B65" s="193">
         <v>68030850</v>
@@ -37710,7 +37692,7 @@
         <v>2486</v>
       </c>
       <c r="F65" s="193" t="s">
-        <v>3497</v>
+        <v>3493</v>
       </c>
       <c r="G65" s="183" t="s">
         <v>1442</v>
@@ -37721,7 +37703,7 @@
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="183" t="s">
-        <v>3507</v>
+        <v>3503</v>
       </c>
       <c r="B66" s="183">
         <v>65003516</v>
@@ -37736,7 +37718,7 @@
         <v>2486</v>
       </c>
       <c r="F66" s="193" t="s">
-        <v>3497</v>
+        <v>3493</v>
       </c>
       <c r="G66" s="183" t="s">
         <v>1442</v>
@@ -37762,7 +37744,7 @@
         <v>2486</v>
       </c>
       <c r="F67" s="193" t="s">
-        <v>3497</v>
+        <v>3493</v>
       </c>
       <c r="G67" s="183" t="s">
         <v>1442</v>
@@ -37785,7 +37767,7 @@
         <v>2449</v>
       </c>
       <c r="E69" s="76" t="s">
-        <v>3546</v>
+        <v>3542</v>
       </c>
       <c r="F69" s="195" t="s">
         <v>2450</v>
@@ -37811,7 +37793,7 @@
         <v>2454</v>
       </c>
       <c r="E70" s="183" t="s">
-        <v>3546</v>
+        <v>3542</v>
       </c>
       <c r="F70" s="193" t="s">
         <v>2450</v>
@@ -37837,7 +37819,7 @@
         <v>2289</v>
       </c>
       <c r="E71" s="183" t="s">
-        <v>3546</v>
+        <v>3542</v>
       </c>
       <c r="F71" s="193" t="s">
         <v>2450</v>
@@ -37863,7 +37845,7 @@
         <v>2745</v>
       </c>
       <c r="E72" s="183" t="s">
-        <v>3546</v>
+        <v>3542</v>
       </c>
       <c r="F72" s="183" t="s">
         <v>2450</v>
@@ -37890,7 +37872,7 @@
         <v>2054</v>
       </c>
       <c r="E73" s="183" t="s">
-        <v>3546</v>
+        <v>3542</v>
       </c>
       <c r="F73" s="183" t="s">
         <v>2450</v>
@@ -37917,7 +37899,7 @@
         <v>2445</v>
       </c>
       <c r="E74" s="183" t="s">
-        <v>3546</v>
+        <v>3542</v>
       </c>
       <c r="F74" s="183" t="s">
         <v>2450</v>
@@ -37944,7 +37926,7 @@
         <v>1724</v>
       </c>
       <c r="E76" s="76" t="s">
-        <v>3546</v>
+        <v>3542</v>
       </c>
       <c r="F76" s="195" t="s">
         <v>2448</v>
@@ -37968,7 +37950,7 @@
         <v>2329</v>
       </c>
       <c r="E77" s="183" t="s">
-        <v>3546</v>
+        <v>3542</v>
       </c>
       <c r="F77" s="193" t="s">
         <v>2448</v>
@@ -37992,7 +37974,7 @@
         <v>1238</v>
       </c>
       <c r="E78" s="183" t="s">
-        <v>3546</v>
+        <v>3542</v>
       </c>
       <c r="F78" s="193" t="s">
         <v>2448</v>
@@ -38004,7 +37986,7 @@
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="183" t="s">
-        <v>3626</v>
+        <v>3622</v>
       </c>
       <c r="B79" s="183">
         <v>62820256</v>
@@ -38016,7 +37998,7 @@
         <v>2357</v>
       </c>
       <c r="E79" s="183" t="s">
-        <v>3546</v>
+        <v>3542</v>
       </c>
       <c r="F79" s="193" t="s">
         <v>2448</v>
@@ -38028,19 +38010,19 @@
     </row>
     <row r="80" spans="1:9">
       <c r="A80" s="183" t="s">
-        <v>3036</v>
+        <v>3034</v>
       </c>
       <c r="B80" s="183">
         <v>69563253</v>
       </c>
       <c r="C80" s="194" t="s">
-        <v>3547</v>
+        <v>3543</v>
       </c>
       <c r="D80" s="183" t="s">
         <v>1005</v>
       </c>
       <c r="E80" s="183" t="s">
-        <v>3548</v>
+        <v>3544</v>
       </c>
       <c r="F80" s="193" t="s">
         <v>2448</v>
@@ -38052,7 +38034,7 @@
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="183" t="s">
-        <v>3577</v>
+        <v>3573</v>
       </c>
       <c r="B81" s="183">
         <v>63233935</v>
@@ -38061,10 +38043,10 @@
         <v>2376</v>
       </c>
       <c r="D81" s="183" t="s">
-        <v>3574</v>
+        <v>3570</v>
       </c>
       <c r="E81" s="183" t="s">
-        <v>3546</v>
+        <v>3542</v>
       </c>
       <c r="F81" s="193" t="s">
         <v>2448</v>
@@ -38076,7 +38058,7 @@
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="76" t="s">
-        <v>3292</v>
+        <v>3288</v>
       </c>
       <c r="B83" s="76">
         <v>63574980</v>
@@ -38091,7 +38073,7 @@
         <v>1344</v>
       </c>
       <c r="F83" s="195" t="s">
-        <v>3618</v>
+        <v>3614</v>
       </c>
       <c r="G83" s="76" t="s">
         <v>1442</v>
@@ -38118,7 +38100,7 @@
         <v>1344</v>
       </c>
       <c r="F84" s="183" t="s">
-        <v>3618</v>
+        <v>3614</v>
       </c>
       <c r="G84" s="183" t="s">
         <v>1442</v>
@@ -38145,7 +38127,7 @@
         <v>1344</v>
       </c>
       <c r="F85" s="183" t="s">
-        <v>3618</v>
+        <v>3614</v>
       </c>
       <c r="G85" s="183" t="s">
         <v>1442</v>
@@ -38160,19 +38142,19 @@
         <v>2503</v>
       </c>
       <c r="B86" s="183" t="s">
-        <v>3166</v>
+        <v>3164</v>
       </c>
       <c r="C86" s="194" t="s">
         <v>2670</v>
       </c>
       <c r="D86" s="183" t="s">
-        <v>3165</v>
+        <v>3163</v>
       </c>
       <c r="E86" s="183" t="s">
         <v>1344</v>
       </c>
       <c r="F86" s="183" t="s">
-        <v>3618</v>
+        <v>3614</v>
       </c>
       <c r="G86" s="183" t="s">
         <v>1442</v>
@@ -38184,7 +38166,7 @@
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="183" t="s">
-        <v>3149</v>
+        <v>3147</v>
       </c>
       <c r="B87" s="183">
         <v>69904406</v>
@@ -38193,13 +38175,13 @@
         <v>2671</v>
       </c>
       <c r="D87" s="183" t="s">
-        <v>3284</v>
+        <v>3281</v>
       </c>
       <c r="E87" s="183" t="s">
         <v>1344</v>
       </c>
       <c r="F87" s="183" t="s">
-        <v>3618</v>
+        <v>3614</v>
       </c>
       <c r="G87" s="183" t="s">
         <v>1442</v>
@@ -38211,7 +38193,7 @@
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="183" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="B88" s="183" t="s">
         <v>2689</v>
@@ -38226,7 +38208,7 @@
         <v>1344</v>
       </c>
       <c r="F88" s="183" t="s">
-        <v>3618</v>
+        <v>3614</v>
       </c>
       <c r="G88" s="183" t="s">
         <v>1442</v>
@@ -38253,7 +38235,7 @@
         <v>1654</v>
       </c>
       <c r="F90" s="195" t="s">
-        <v>3619</v>
+        <v>3615</v>
       </c>
       <c r="G90" s="76" t="s">
         <v>1442</v>
@@ -38277,7 +38259,7 @@
         <v>1654</v>
       </c>
       <c r="F91" s="193" t="s">
-        <v>3619</v>
+        <v>3615</v>
       </c>
       <c r="G91" s="183" t="s">
         <v>1442</v>
@@ -38301,7 +38283,7 @@
         <v>1654</v>
       </c>
       <c r="F92" s="193" t="s">
-        <v>3619</v>
+        <v>3615</v>
       </c>
       <c r="G92" s="183" t="s">
         <v>1442</v>
@@ -38325,7 +38307,7 @@
         <v>1654</v>
       </c>
       <c r="F93" s="193" t="s">
-        <v>3619</v>
+        <v>3615</v>
       </c>
       <c r="G93" s="183" t="s">
         <v>1442</v>
@@ -38334,7 +38316,7 @@
     </row>
     <row r="94" spans="1:9">
       <c r="A94" s="183" t="s">
-        <v>2976</v>
+        <v>2974</v>
       </c>
       <c r="B94" s="183">
         <v>64403333</v>
@@ -38349,7 +38331,7 @@
         <v>1654</v>
       </c>
       <c r="F94" s="193" t="s">
-        <v>3619</v>
+        <v>3615</v>
       </c>
       <c r="G94" s="183" t="s">
         <v>1442</v>
@@ -38373,7 +38355,7 @@
         <v>1654</v>
       </c>
       <c r="F95" s="193" t="s">
-        <v>3619</v>
+        <v>3615</v>
       </c>
       <c r="G95" s="183" t="s">
         <v>1442</v>
@@ -38382,7 +38364,7 @@
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="195" t="s">
-        <v>3479</v>
+        <v>3475</v>
       </c>
       <c r="B97" s="195">
         <v>64476521</v>
@@ -38397,7 +38379,7 @@
         <v>2486</v>
       </c>
       <c r="F97" s="195" t="s">
-        <v>3642</v>
+        <v>3638</v>
       </c>
       <c r="G97" s="76" t="s">
         <v>1442</v>
@@ -38408,7 +38390,7 @@
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="193" t="s">
-        <v>3372</v>
+        <v>3368</v>
       </c>
       <c r="B98" s="193">
         <v>60389752</v>
@@ -38417,13 +38399,13 @@
         <v>2651</v>
       </c>
       <c r="D98" s="193" t="s">
-        <v>3371</v>
+        <v>3367</v>
       </c>
       <c r="E98" s="183" t="s">
         <v>2486</v>
       </c>
       <c r="F98" s="193" t="s">
-        <v>3642</v>
+        <v>3638</v>
       </c>
       <c r="G98" s="183" t="s">
         <v>1442</v>
@@ -38434,7 +38416,7 @@
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="183" t="s">
-        <v>3594</v>
+        <v>3590</v>
       </c>
       <c r="B99" s="183">
         <v>60389752</v>
@@ -38449,7 +38431,7 @@
         <v>2486</v>
       </c>
       <c r="F99" s="193" t="s">
-        <v>3642</v>
+        <v>3638</v>
       </c>
       <c r="G99" s="183" t="s">
         <v>1442</v>
@@ -38475,7 +38457,7 @@
         <v>2486</v>
       </c>
       <c r="F100" s="193" t="s">
-        <v>3642</v>
+        <v>3638</v>
       </c>
       <c r="G100" s="183" t="s">
         <v>1442</v>
@@ -38501,7 +38483,7 @@
         <v>2486</v>
       </c>
       <c r="F101" s="193" t="s">
-        <v>3642</v>
+        <v>3638</v>
       </c>
       <c r="G101" s="183" t="s">
         <v>1442</v>
@@ -38512,7 +38494,7 @@
     </row>
     <row r="102" spans="1:9">
       <c r="A102" s="193" t="s">
-        <v>3149</v>
+        <v>3147</v>
       </c>
       <c r="B102" s="193">
         <v>67381873</v>
@@ -38521,13 +38503,13 @@
         <v>2286</v>
       </c>
       <c r="D102" s="193" t="s">
-        <v>3288</v>
+        <v>3285</v>
       </c>
       <c r="E102" s="183" t="s">
         <v>2486</v>
       </c>
       <c r="F102" s="193" t="s">
-        <v>3642</v>
+        <v>3638</v>
       </c>
       <c r="G102" s="183" t="s">
         <v>1442</v>
@@ -38538,7 +38520,7 @@
     </row>
     <row r="104" spans="1:9">
       <c r="A104" s="195" t="s">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="B104" s="195">
         <v>66082581</v>
@@ -38550,7 +38532,7 @@
         <v>2297</v>
       </c>
       <c r="E104" s="76" t="s">
-        <v>3642</v>
+        <v>3638</v>
       </c>
       <c r="F104" s="195" t="s">
         <v>422</v>
@@ -38564,7 +38546,7 @@
     </row>
     <row r="105" spans="1:9">
       <c r="A105" s="193" t="s">
-        <v>2986</v>
+        <v>2984</v>
       </c>
       <c r="B105" s="193" t="s">
         <v>2709</v>
@@ -38576,7 +38558,7 @@
         <v>2302</v>
       </c>
       <c r="E105" s="183" t="s">
-        <v>3642</v>
+        <v>3638</v>
       </c>
       <c r="F105" s="193" t="s">
         <v>422</v>
@@ -38590,7 +38572,7 @@
     </row>
     <row r="106" spans="1:9">
       <c r="A106" s="193" t="s">
-        <v>3311</v>
+        <v>3307</v>
       </c>
       <c r="B106" s="193">
         <v>62723048</v>
@@ -38599,10 +38581,10 @@
         <v>2303</v>
       </c>
       <c r="D106" s="193" t="s">
-        <v>3310</v>
+        <v>3306</v>
       </c>
       <c r="E106" s="183" t="s">
-        <v>3642</v>
+        <v>3638</v>
       </c>
       <c r="F106" s="193" t="s">
         <v>422</v>
@@ -38628,7 +38610,7 @@
         <v>2460</v>
       </c>
       <c r="E107" s="183" t="s">
-        <v>3642</v>
+        <v>3638</v>
       </c>
       <c r="F107" s="193" t="s">
         <v>422</v>
@@ -38654,7 +38636,7 @@
         <v>2306</v>
       </c>
       <c r="E108" s="183" t="s">
-        <v>3642</v>
+        <v>3638</v>
       </c>
       <c r="F108" s="193" t="s">
         <v>422</v>
@@ -38680,7 +38662,7 @@
         <v>2931</v>
       </c>
       <c r="E109" s="183" t="s">
-        <v>3642</v>
+        <v>3638</v>
       </c>
       <c r="F109" s="193" t="s">
         <v>422</v>
@@ -38700,16 +38682,16 @@
         <v>68310153</v>
       </c>
       <c r="C111" s="195" t="s">
-        <v>3004</v>
+        <v>3002</v>
       </c>
       <c r="D111" s="195" t="s">
-        <v>3005</v>
+        <v>3003</v>
       </c>
       <c r="E111" s="76" t="s">
         <v>362</v>
       </c>
       <c r="F111" s="195" t="s">
-        <v>3010</v>
+        <v>3008</v>
       </c>
       <c r="G111" s="76" t="s">
         <v>1344</v>
@@ -38723,7 +38705,7 @@
     </row>
     <row r="112" spans="1:9">
       <c r="A112" s="193" t="s">
-        <v>3011</v>
+        <v>3009</v>
       </c>
       <c r="B112" s="193">
         <v>63910392</v>
@@ -38736,7 +38718,7 @@
         <v>362</v>
       </c>
       <c r="F112" s="193" t="s">
-        <v>3010</v>
+        <v>3008</v>
       </c>
       <c r="G112" s="183" t="s">
         <v>1344</v>
@@ -38765,7 +38747,7 @@
         <v>2486</v>
       </c>
       <c r="F113" s="193" t="s">
-        <v>3010</v>
+        <v>3008</v>
       </c>
       <c r="G113" s="183" t="s">
         <v>1344</v>
@@ -38785,16 +38767,16 @@
         <v>62360487</v>
       </c>
       <c r="C114" s="194" t="s">
-        <v>3322</v>
+        <v>3318</v>
       </c>
       <c r="D114" s="183" t="s">
-        <v>3323</v>
+        <v>3319</v>
       </c>
       <c r="E114" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F114" s="193" t="s">
-        <v>3010</v>
+        <v>3008</v>
       </c>
       <c r="G114" s="183" t="s">
         <v>1344</v>
@@ -38814,16 +38796,16 @@
         <v>62085821</v>
       </c>
       <c r="C115" s="193" t="s">
-        <v>3324</v>
+        <v>3320</v>
       </c>
       <c r="D115" s="193" t="s">
-        <v>3325</v>
+        <v>3321</v>
       </c>
       <c r="E115" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F115" s="193" t="s">
-        <v>3010</v>
+        <v>3008</v>
       </c>
       <c r="G115" s="183" t="s">
         <v>1344</v>
@@ -38843,16 +38825,16 @@
         <v>64403333</v>
       </c>
       <c r="C116" s="193" t="s">
-        <v>3326</v>
+        <v>3322</v>
       </c>
       <c r="D116" s="193" t="s">
-        <v>3327</v>
+        <v>3323</v>
       </c>
       <c r="E116" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F116" s="193" t="s">
-        <v>3010</v>
+        <v>3008</v>
       </c>
       <c r="G116" s="183" t="s">
         <v>1344</v>
@@ -38884,7 +38866,7 @@
         <v>2319</v>
       </c>
       <c r="E118" s="76" t="s">
-        <v>3079</v>
+        <v>3077</v>
       </c>
       <c r="F118" s="76" t="s">
         <v>422</v>
@@ -38911,7 +38893,7 @@
         <v>2321</v>
       </c>
       <c r="E119" s="183" t="s">
-        <v>3079</v>
+        <v>3077</v>
       </c>
       <c r="F119" s="193" t="s">
         <v>422</v>
@@ -38937,7 +38919,7 @@
         <v>2323</v>
       </c>
       <c r="E120" s="183" t="s">
-        <v>3079</v>
+        <v>3077</v>
       </c>
       <c r="F120" s="193" t="s">
         <v>422</v>
@@ -38951,19 +38933,19 @@
     </row>
     <row r="121" spans="1:9">
       <c r="A121" s="183" t="s">
-        <v>3413</v>
+        <v>3409</v>
       </c>
       <c r="B121" s="183">
         <v>64403333</v>
       </c>
       <c r="C121" s="183" t="s">
-        <v>3328</v>
+        <v>3324</v>
       </c>
       <c r="D121" s="183" t="s">
-        <v>3329</v>
+        <v>3325</v>
       </c>
       <c r="E121" s="183" t="s">
-        <v>3079</v>
+        <v>3077</v>
       </c>
       <c r="F121" s="193" t="s">
         <v>422</v>
@@ -38989,7 +38971,7 @@
         <v>377</v>
       </c>
       <c r="E122" s="183" t="s">
-        <v>3079</v>
+        <v>3077</v>
       </c>
       <c r="F122" s="193" t="s">
         <v>422</v>
@@ -39015,7 +38997,7 @@
         <v>1650</v>
       </c>
       <c r="E123" s="183" t="s">
-        <v>3079</v>
+        <v>3077</v>
       </c>
       <c r="F123" s="193" t="s">
         <v>422</v>
@@ -39044,7 +39026,7 @@
         <v>678</v>
       </c>
       <c r="F125" s="76" t="s">
-        <v>3195</v>
+        <v>3193</v>
       </c>
       <c r="G125" s="76" t="s">
         <v>422</v>
@@ -39073,7 +39055,7 @@
         <v>362</v>
       </c>
       <c r="F126" s="183" t="s">
-        <v>3195</v>
+        <v>3193</v>
       </c>
       <c r="G126" s="183" t="s">
         <v>422</v>
@@ -39102,7 +39084,7 @@
         <v>362</v>
       </c>
       <c r="F127" s="183" t="s">
-        <v>3195</v>
+        <v>3193</v>
       </c>
       <c r="G127" s="183" t="s">
         <v>422</v>
@@ -39129,7 +39111,7 @@
         <v>362</v>
       </c>
       <c r="F128" s="183" t="s">
-        <v>3195</v>
+        <v>3193</v>
       </c>
       <c r="G128" s="183" t="s">
         <v>422</v>
@@ -39158,7 +39140,7 @@
         <v>362</v>
       </c>
       <c r="F129" s="183" t="s">
-        <v>3195</v>
+        <v>3193</v>
       </c>
       <c r="G129" s="183" t="s">
         <v>422</v>
@@ -39187,7 +39169,7 @@
         <v>362</v>
       </c>
       <c r="F130" s="183" t="s">
-        <v>3195</v>
+        <v>3193</v>
       </c>
       <c r="G130" s="183" t="s">
         <v>422</v>
@@ -39216,7 +39198,7 @@
         <v>2368</v>
       </c>
       <c r="F132" s="195" t="s">
-        <v>3241</v>
+        <v>3239</v>
       </c>
       <c r="G132" s="76" t="s">
         <v>1442</v>
@@ -39233,7 +39215,7 @@
         <v>64226974</v>
       </c>
       <c r="C133" s="183" t="s">
-        <v>3476</v>
+        <v>3472</v>
       </c>
       <c r="D133" s="193" t="s">
         <v>377</v>
@@ -39242,7 +39224,7 @@
         <v>2368</v>
       </c>
       <c r="F133" s="193" t="s">
-        <v>3241</v>
+        <v>3239</v>
       </c>
       <c r="G133" s="183" t="s">
         <v>1442</v>
@@ -39268,7 +39250,7 @@
         <v>2368</v>
       </c>
       <c r="F134" s="193" t="s">
-        <v>3241</v>
+        <v>3239</v>
       </c>
       <c r="G134" s="183" t="s">
         <v>1442</v>
@@ -39294,7 +39276,7 @@
         <v>2368</v>
       </c>
       <c r="F135" s="193" t="s">
-        <v>3241</v>
+        <v>3239</v>
       </c>
       <c r="G135" s="183" t="s">
         <v>1442</v>
@@ -39320,7 +39302,7 @@
         <v>2368</v>
       </c>
       <c r="F136" s="193" t="s">
-        <v>3241</v>
+        <v>3239</v>
       </c>
       <c r="G136" s="183" t="s">
         <v>1442</v>
@@ -39346,7 +39328,7 @@
         <v>2368</v>
       </c>
       <c r="F137" s="193" t="s">
-        <v>3241</v>
+        <v>3239</v>
       </c>
       <c r="G137" s="183" t="s">
         <v>1442</v>
@@ -39357,22 +39339,22 @@
     </row>
     <row r="139" spans="1:9">
       <c r="A139" s="195" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="B139" s="195" t="s">
         <v>2162</v>
       </c>
       <c r="C139" s="195" t="s">
-        <v>3243</v>
+        <v>3241</v>
       </c>
       <c r="D139" s="195" t="s">
-        <v>3242</v>
+        <v>3240</v>
       </c>
       <c r="E139" s="76" t="s">
         <v>2368</v>
       </c>
       <c r="F139" s="195" t="s">
-        <v>3241</v>
+        <v>3239</v>
       </c>
       <c r="G139" s="76" t="s">
         <v>1442</v>
@@ -39389,16 +39371,16 @@
         <v>66319486</v>
       </c>
       <c r="C140" s="193" t="s">
-        <v>3330</v>
+        <v>3326</v>
       </c>
       <c r="D140" s="193" t="s">
-        <v>3373</v>
+        <v>3369</v>
       </c>
       <c r="E140" s="183" t="s">
         <v>2368</v>
       </c>
       <c r="F140" s="193" t="s">
-        <v>3241</v>
+        <v>3239</v>
       </c>
       <c r="G140" s="183" t="s">
         <v>1442</v>
@@ -39409,7 +39391,7 @@
     </row>
     <row r="141" spans="1:9">
       <c r="A141" s="183" t="s">
-        <v>3245</v>
+        <v>3243</v>
       </c>
       <c r="B141" s="183">
         <v>60389752</v>
@@ -39424,7 +39406,7 @@
         <v>2368</v>
       </c>
       <c r="F141" s="193" t="s">
-        <v>3241</v>
+        <v>3239</v>
       </c>
       <c r="G141" s="183" t="s">
         <v>1442</v>
@@ -39438,7 +39420,7 @@
         <v>2368</v>
       </c>
       <c r="F142" s="193" t="s">
-        <v>3241</v>
+        <v>3239</v>
       </c>
       <c r="G142" s="183" t="s">
         <v>1442</v>
@@ -39464,7 +39446,7 @@
         <v>2368</v>
       </c>
       <c r="F143" s="193" t="s">
-        <v>3241</v>
+        <v>3239</v>
       </c>
       <c r="G143" s="183" t="s">
         <v>1442</v>
@@ -39490,7 +39472,7 @@
         <v>2368</v>
       </c>
       <c r="F144" s="193" t="s">
-        <v>3241</v>
+        <v>3239</v>
       </c>
       <c r="G144" s="183" t="s">
         <v>1442</v>
@@ -39516,7 +39498,7 @@
         <v>2486</v>
       </c>
       <c r="F146" s="195" t="s">
-        <v>3244</v>
+        <v>3242</v>
       </c>
       <c r="G146" s="76" t="s">
         <v>1442</v>
@@ -39527,13 +39509,13 @@
     </row>
     <row r="147" spans="1:9">
       <c r="A147" s="193" t="s">
-        <v>3176</v>
+        <v>3174</v>
       </c>
       <c r="B147" s="193">
         <v>67697112</v>
       </c>
       <c r="C147" s="193" t="s">
-        <v>3355</v>
+        <v>3351</v>
       </c>
       <c r="D147" s="193" t="s">
         <v>1306</v>
@@ -39542,7 +39524,7 @@
         <v>2486</v>
       </c>
       <c r="F147" s="193" t="s">
-        <v>3244</v>
+        <v>3242</v>
       </c>
       <c r="G147" s="183" t="s">
         <v>1442</v>
@@ -39553,7 +39535,7 @@
     </row>
     <row r="148" spans="1:9">
       <c r="A148" s="183" t="s">
-        <v>3399</v>
+        <v>3395</v>
       </c>
       <c r="B148" s="183">
         <v>62560788</v>
@@ -39568,7 +39550,7 @@
         <v>2486</v>
       </c>
       <c r="F148" s="193" t="s">
-        <v>3244</v>
+        <v>3242</v>
       </c>
       <c r="G148" s="183" t="s">
         <v>1442</v>
@@ -39579,7 +39561,7 @@
     </row>
     <row r="149" spans="1:9">
       <c r="A149" s="193" t="s">
-        <v>3149</v>
+        <v>3147</v>
       </c>
       <c r="B149" s="193">
         <v>64403333</v>
@@ -39594,7 +39576,7 @@
         <v>2486</v>
       </c>
       <c r="F149" s="193" t="s">
-        <v>3244</v>
+        <v>3242</v>
       </c>
       <c r="G149" s="183" t="s">
         <v>1442</v>
@@ -39605,22 +39587,22 @@
     </row>
     <row r="150" spans="1:9">
       <c r="A150" s="193" t="s">
-        <v>2964</v>
+        <v>2962</v>
       </c>
       <c r="B150" s="193">
         <v>60125401</v>
       </c>
       <c r="C150" s="194" t="s">
+        <v>2961</v>
+      </c>
+      <c r="D150" s="193" t="s">
         <v>2963</v>
-      </c>
-      <c r="D150" s="193" t="s">
-        <v>2965</v>
       </c>
       <c r="E150" s="183" t="s">
         <v>2486</v>
       </c>
       <c r="F150" s="193" t="s">
-        <v>3244</v>
+        <v>3242</v>
       </c>
       <c r="G150" s="183" t="s">
         <v>1442</v>
@@ -39646,7 +39628,7 @@
         <v>2486</v>
       </c>
       <c r="F151" s="193" t="s">
-        <v>3244</v>
+        <v>3242</v>
       </c>
       <c r="G151" s="183" t="s">
         <v>1442</v>
@@ -39672,7 +39654,7 @@
         <v>362</v>
       </c>
       <c r="F153" s="195" t="s">
-        <v>3281</v>
+        <v>3278</v>
       </c>
       <c r="G153" s="76" t="s">
         <v>2374</v>
@@ -39686,22 +39668,22 @@
     </row>
     <row r="154" spans="1:9">
       <c r="A154" s="193" t="s">
-        <v>3292</v>
+        <v>3288</v>
       </c>
       <c r="B154" s="193">
         <v>65963732</v>
       </c>
       <c r="C154" s="194" t="s">
-        <v>3313</v>
+        <v>3309</v>
       </c>
       <c r="D154" s="193" t="s">
-        <v>3314</v>
+        <v>3310</v>
       </c>
       <c r="E154" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F154" s="193" t="s">
-        <v>3281</v>
+        <v>3278</v>
       </c>
       <c r="G154" s="183" t="s">
         <v>2374</v>
@@ -39715,7 +39697,7 @@
     </row>
     <row r="155" spans="1:9">
       <c r="A155" s="183" t="s">
-        <v>3292</v>
+        <v>3288</v>
       </c>
       <c r="B155" s="183">
         <v>60071688</v>
@@ -39724,13 +39706,13 @@
         <v>2358</v>
       </c>
       <c r="D155" s="183" t="s">
-        <v>3307</v>
+        <v>3303</v>
       </c>
       <c r="E155" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F155" s="193" t="s">
-        <v>3281</v>
+        <v>3278</v>
       </c>
       <c r="G155" s="183" t="s">
         <v>2374</v>
@@ -39759,7 +39741,7 @@
         <v>362</v>
       </c>
       <c r="F156" s="193" t="s">
-        <v>3281</v>
+        <v>3278</v>
       </c>
       <c r="G156" s="183" t="s">
         <v>2374</v>
@@ -39788,7 +39770,7 @@
         <v>362</v>
       </c>
       <c r="F157" s="193" t="s">
-        <v>3281</v>
+        <v>3278</v>
       </c>
       <c r="G157" s="183" t="s">
         <v>2374</v>
@@ -39808,16 +39790,16 @@
         <v>64403333</v>
       </c>
       <c r="C158" s="194" t="s">
-        <v>2966</v>
+        <v>2964</v>
       </c>
       <c r="D158" s="444" t="s">
-        <v>2965</v>
+        <v>2963</v>
       </c>
       <c r="E158" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F158" s="193" t="s">
-        <v>3281</v>
+        <v>3278</v>
       </c>
       <c r="G158" s="183" t="s">
         <v>2374</v>
@@ -39848,7 +39830,7 @@
       <c r="A183" s="221"/>
       <c r="B183" s="221"/>
       <c r="C183" s="221" t="s">
-        <v>3405</v>
+        <v>3401</v>
       </c>
       <c r="D183" s="221"/>
       <c r="E183" s="221"/>
@@ -39856,25 +39838,25 @@
     </row>
     <row r="184" spans="1:9">
       <c r="A184" s="76" t="s">
-        <v>2976</v>
+        <v>2974</v>
       </c>
       <c r="B184" s="76">
         <v>67836337</v>
       </c>
       <c r="C184" s="195" t="s">
-        <v>3519</v>
+        <v>3515</v>
       </c>
       <c r="D184" s="195" t="s">
-        <v>3520</v>
+        <v>3516</v>
       </c>
       <c r="E184" s="434">
         <v>46243</v>
       </c>
       <c r="F184" s="76" t="s">
-        <v>3406</v>
+        <v>3402</v>
       </c>
       <c r="G184" s="195" t="s">
-        <v>3575</v>
+        <v>3571</v>
       </c>
       <c r="H184" s="76" t="s">
         <v>1980</v>
@@ -39882,19 +39864,19 @@
     </row>
     <row r="185" spans="1:9">
       <c r="A185" s="193" t="s">
-        <v>3577</v>
+        <v>3573</v>
       </c>
       <c r="B185" s="193">
         <v>60196388</v>
       </c>
       <c r="C185" s="193" t="s">
-        <v>3576</v>
+        <v>3572</v>
       </c>
       <c r="D185" s="447" t="s">
-        <v>3520</v>
+        <v>3516</v>
       </c>
       <c r="E185" s="433" t="s">
-        <v>3572</v>
+        <v>3568</v>
       </c>
       <c r="F185" s="193"/>
       <c r="G185" s="183"/>
@@ -39902,19 +39884,19 @@
     </row>
     <row r="186" spans="1:9">
       <c r="A186" s="183" t="s">
-        <v>2986</v>
+        <v>2984</v>
       </c>
       <c r="B186" s="183">
         <v>64403333</v>
       </c>
       <c r="C186" s="191" t="s">
-        <v>3593</v>
+        <v>3589</v>
       </c>
       <c r="D186" s="183" t="s">
-        <v>3583</v>
+        <v>3579</v>
       </c>
       <c r="E186" s="433" t="s">
-        <v>3572</v>
+        <v>3568</v>
       </c>
       <c r="F186" s="193"/>
       <c r="G186" s="183"/>
@@ -39922,19 +39904,19 @@
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="193" t="s">
-        <v>3616</v>
+        <v>3612</v>
       </c>
       <c r="B187" s="193">
         <v>68071614</v>
       </c>
       <c r="C187" s="193" t="s">
-        <v>3613</v>
+        <v>3609</v>
       </c>
       <c r="D187" s="193" t="s">
-        <v>3614</v>
+        <v>3610</v>
       </c>
       <c r="E187" s="433" t="s">
-        <v>3615</v>
+        <v>3611</v>
       </c>
       <c r="F187" s="193"/>
       <c r="G187" s="183"/>
@@ -39948,13 +39930,13 @@
         <v>63950696</v>
       </c>
       <c r="C188" s="457" t="s">
-        <v>3643</v>
+        <v>3639</v>
       </c>
       <c r="D188" s="457" t="s">
         <v>2805</v>
       </c>
       <c r="E188" s="433" t="s">
-        <v>3644</v>
+        <v>3640</v>
       </c>
       <c r="F188" s="458"/>
       <c r="G188" s="448"/>
@@ -40006,7 +39988,7 @@
         <v>316</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>3494</v>
+        <v>3490</v>
       </c>
       <c r="E194" s="30"/>
       <c r="F194"/>
@@ -40032,7 +40014,7 @@
         <v>439</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>3547</v>
+        <v>3543</v>
       </c>
       <c r="E196" s="30"/>
       <c r="F196"/>
@@ -40043,7 +40025,7 @@
         <v>26</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>3613</v>
+        <v>3609</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -40051,7 +40033,7 @@
         <v>1327</v>
       </c>
       <c r="D198" s="429" t="s">
-        <v>3643</v>
+        <v>3639</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -40059,7 +40041,7 @@
         <v>1661</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>3328</v>
+        <v>3324</v>
       </c>
       <c r="F199" s="394"/>
     </row>
@@ -40068,7 +40050,7 @@
         <v>1308</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>3330</v>
+        <v>3326</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -40076,7 +40058,7 @@
         <v>406</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>3436</v>
+        <v>3432</v>
       </c>
     </row>
     <row r="202" spans="1:9">
@@ -40084,7 +40066,7 @@
         <v>708</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>3439</v>
+        <v>3435</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -40092,7 +40074,7 @@
         <v>281</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>3455</v>
+        <v>3451</v>
       </c>
     </row>
     <row r="204" spans="1:9">
@@ -40100,7 +40082,7 @@
         <v>2376</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>3456</v>
+        <v>3452</v>
       </c>
     </row>
     <row r="205" spans="1:9">
@@ -40110,7 +40092,7 @@
         <v>465</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>3459</v>
+        <v>3455</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -40118,7 +40100,7 @@
         <v>219</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>3463</v>
+        <v>3459</v>
       </c>
     </row>
     <row r="207" spans="1:9">
@@ -40126,7 +40108,7 @@
         <v>427</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>3476</v>
+        <v>3472</v>
       </c>
     </row>
     <row r="208" spans="1:9">
@@ -40134,7 +40116,7 @@
         <v>1052</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>3490</v>
+        <v>3486</v>
       </c>
     </row>
     <row r="223" spans="1:9">
@@ -41349,7 +41331,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="B3">
         <v>62349088</v>
@@ -41370,10 +41352,10 @@
         <v>705</v>
       </c>
       <c r="H3" t="s">
-        <v>3508</v>
+        <v>3504</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>3040</v>
+        <v>3038</v>
       </c>
       <c r="J3"/>
     </row>
@@ -41400,10 +41382,10 @@
         <v>515</v>
       </c>
       <c r="H4" t="s">
-        <v>3334</v>
+        <v>3330</v>
       </c>
       <c r="I4" t="s">
-        <v>3637</v>
+        <v>3633</v>
       </c>
       <c r="J4"/>
     </row>
@@ -41421,7 +41403,7 @@
         <v>1522</v>
       </c>
       <c r="E5" t="s">
-        <v>3068</v>
+        <v>3066</v>
       </c>
       <c r="F5" t="s">
         <v>2171</v>
@@ -41430,10 +41412,10 @@
         <v>515</v>
       </c>
       <c r="H5" s="220" t="s">
-        <v>3342</v>
+        <v>3338</v>
       </c>
       <c r="I5" s="220" t="s">
-        <v>3180</v>
+        <v>3178</v>
       </c>
       <c r="J5" t="s">
         <v>1397</v>
@@ -41441,19 +41423,19 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>3507</v>
+        <v>3503</v>
       </c>
       <c r="B6" t="s">
-        <v>3539</v>
+        <v>3535</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>427</v>
       </c>
       <c r="D6" t="s">
-        <v>3352</v>
+        <v>3348</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>3350</v>
+        <v>3346</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>2886</v>
@@ -41462,10 +41444,10 @@
         <v>436</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>3130</v>
+        <v>3128</v>
       </c>
       <c r="I6" t="s">
-        <v>3650</v>
+        <v>3646</v>
       </c>
       <c r="J6"/>
     </row>
@@ -41497,13 +41479,13 @@
         <v>143</v>
       </c>
       <c r="B8" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>2065</v>
       </c>
       <c r="D8" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
       <c r="E8" t="s">
         <v>2331</v>
@@ -41515,10 +41497,10 @@
         <v>250</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>3173</v>
+        <v>3171</v>
       </c>
       <c r="I8" t="s">
-        <v>3299</v>
+        <v>3295</v>
       </c>
       <c r="J8"/>
     </row>
@@ -41700,7 +41682,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="10" t="s">
-        <v>3415</v>
+        <v>3411</v>
       </c>
       <c r="B5" s="10">
         <v>67992849</v>
@@ -41721,7 +41703,7 @@
         <v>517</v>
       </c>
       <c r="H5" s="220" t="s">
-        <v>3534</v>
+        <v>3530</v>
       </c>
       <c r="I5" s="278" t="s">
         <v>2158</v>
@@ -41753,12 +41735,12 @@
         <v>2769</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>3044</v>
+        <v>3042</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="10" t="s">
-        <v>3503</v>
+        <v>3499</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>2411</v>
@@ -41767,7 +41749,7 @@
         <v>1726</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>3220</v>
+        <v>3218</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1699</v>
@@ -41779,10 +41761,10 @@
         <v>517</v>
       </c>
       <c r="H7" t="s">
-        <v>3193</v>
+        <v>3191</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>3221</v>
+        <v>3219</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -41798,7 +41780,7 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="10" t="s">
-        <v>3292</v>
+        <v>3288</v>
       </c>
       <c r="B11" s="10">
         <v>64403333</v>
@@ -41830,7 +41812,7 @@
         <v>2151</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>3235</v>
+        <v>3233</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>961</v>
@@ -41842,10 +41824,10 @@
         <v>517</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>3236</v>
+        <v>3234</v>
       </c>
       <c r="I12" t="s">
-        <v>3389</v>
+        <v>3385</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -41870,7 +41852,7 @@
         <v>2210</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>3071</v>
+        <v>3069</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>961</v>
@@ -41882,10 +41864,10 @@
         <v>517</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>3072</v>
+        <v>3070</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>3081</v>
+        <v>3079</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -41911,7 +41893,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="10" t="s">
-        <v>3503</v>
+        <v>3499</v>
       </c>
       <c r="B17" s="10">
         <v>64403333</v>
@@ -41934,7 +41916,7 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="10" t="s">
-        <v>3292</v>
+        <v>3288</v>
       </c>
       <c r="B18" s="10">
         <v>60345107</v>
@@ -41943,7 +41925,7 @@
         <v>2339</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>3296</v>
+        <v>3292</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>961</v>
@@ -41955,10 +41937,10 @@
         <v>517</v>
       </c>
       <c r="H18" s="428" t="s">
-        <v>3261</v>
+        <v>3259</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>3367</v>
+        <v>3363</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -41984,10 +41966,10 @@
         <v>517</v>
       </c>
       <c r="H19" s="275" t="s">
-        <v>3018</v>
+        <v>3016</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>3480</v>
+        <v>3476</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="190" customFormat="1" ht="26">
@@ -42003,13 +41985,13 @@
         <v>2622</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>3445</v>
+        <v>3441</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>2420</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>3417</v>
+        <v>3413</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>961</v>
@@ -42021,15 +42003,15 @@
         <v>517</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>3535</v>
+        <v>3531</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>3219</v>
+        <v>3217</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>3512</v>
+        <v>3508</v>
       </c>
       <c r="B23" s="10">
         <v>64720128</v>
@@ -42050,10 +42032,10 @@
         <v>517</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>3513</v>
+        <v>3509</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>3514</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -42067,7 +42049,7 @@
         <v>2438</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>3168</v>
+        <v>3166</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>961</v>
@@ -42079,10 +42061,10 @@
         <v>517</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>3477</v>
+        <v>3473</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>3022</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -42092,7 +42074,7 @@
         <v>2451</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>3070</v>
+        <v>3068</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>961</v>
@@ -42211,13 +42193,13 @@
         <v>2466</v>
       </c>
       <c r="B4" t="s">
-        <v>3137</v>
+        <v>3135</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1867</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>3136</v>
+        <v>3134</v>
       </c>
       <c r="E4" t="s">
         <v>1868</v>
@@ -42229,13 +42211,13 @@
         <v>965</v>
       </c>
       <c r="H4" t="s">
-        <v>3152</v>
+        <v>3150</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>3161</v>
+        <v>3159</v>
       </c>
       <c r="J4" t="s">
-        <v>3216</v>
+        <v>3214</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -42284,7 +42266,7 @@
         <v>965</v>
       </c>
       <c r="H6" t="s">
-        <v>3178</v>
+        <v>3176</v>
       </c>
       <c r="J6" s="49" t="s">
         <v>2232</v>
@@ -42301,7 +42283,7 @@
         <v>2294</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>3505</v>
+        <v>3501</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>2295</v>
@@ -42313,25 +42295,25 @@
         <v>965</v>
       </c>
       <c r="H7" t="s">
-        <v>3117</v>
+        <v>3115</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>3258</v>
+        <v>3256</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>3064</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="278"/>
       <c r="C8" s="3" t="s">
-        <v>3586</v>
+        <v>3582</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>3587</v>
+        <v>3583</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>3588</v>
+        <v>3584</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>1742</v>
@@ -42340,30 +42322,30 @@
         <v>965</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>3069</v>
+        <v>3067</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>3229</v>
+        <v>3227</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>3080</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="10" t="s">
-        <v>3084</v>
+        <v>3082</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>3085</v>
+        <v>3083</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>3082</v>
+        <v>3080</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>2910</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>3083</v>
+        <v>3081</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>2911</v>
@@ -42372,13 +42354,13 @@
         <v>965</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>3086</v>
+        <v>3084</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>3087</v>
+        <v>3085</v>
       </c>
       <c r="J9" t="s">
-        <v>3132</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -42386,16 +42368,16 @@
         <v>1432</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>3234</v>
+        <v>3232</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>3232</v>
+        <v>3230</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>3233</v>
+        <v>3231</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>3151</v>
+        <v>3149</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>2296</v>
@@ -42404,13 +42386,13 @@
         <v>965</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>3337</v>
+        <v>3333</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>3340</v>
+        <v>3336</v>
       </c>
       <c r="J10" t="s">
-        <v>3391</v>
+        <v>3387</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -42421,7 +42403,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="C15" s="429" t="s">
-        <v>3586</v>
+        <v>3582</v>
       </c>
     </row>
   </sheetData>
@@ -42562,10 +42544,10 @@
         <v>60240509</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>3563</v>
+        <v>3559</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>3564</v>
+        <v>3560</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>2620</v>
@@ -42586,7 +42568,7 @@
         <v>1790</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>3051</v>
+        <v>3049</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>2620</v>
@@ -42627,7 +42609,7 @@
         <v>60052700</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>2643</v>
@@ -42648,7 +42630,7 @@
         <v>63132287</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>2967</v>
+        <v>2965</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>2643</v>
@@ -42825,7 +42807,7 @@
     <row r="1" spans="1:10" s="410" customFormat="1" ht="42.5" customHeight="1">
       <c r="A1" s="409"/>
       <c r="B1" s="409" t="s">
-        <v>2956</v>
+        <v>2954</v>
       </c>
       <c r="C1" s="409"/>
     </row>
@@ -42834,28 +42816,28 @@
         <v>147</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>3003</v>
+        <v>3001</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3140</v>
+        <v>3138</v>
       </c>
       <c r="E4" t="s">
-        <v>2957</v>
+        <v>2955</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>3141</v>
+        <v>3139</v>
       </c>
       <c r="G4" s="275" t="s">
-        <v>2969</v>
+        <v>2967</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>3122</v>
+        <v>3120</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>3134</v>
+        <v>3132</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>3247</v>
+        <v>3245</v>
       </c>
     </row>
   </sheetData>
@@ -44251,7 +44233,7 @@
         <v>51</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>3207</v>
+        <v>3205</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>1160</v>
@@ -44263,10 +44245,10 @@
         <v>159</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>3418</v>
+        <v>3414</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>3429</v>
+        <v>3425</v>
       </c>
       <c r="N6" s="4" t="s">
         <v>26</v>
@@ -44298,13 +44280,13 @@
         <v>2271</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>3225</v>
+        <v>3223</v>
       </c>
       <c r="L7" s="3"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>3626</v>
+        <v>3622</v>
       </c>
       <c r="B8" t="s">
         <v>452</v>
@@ -44328,7 +44310,7 @@
         <v>2742</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>3205</v>
+        <v>3203</v>
       </c>
     </row>
     <row r="9" spans="1:14" s="4" customFormat="1">
@@ -44345,19 +44327,19 @@
         <v>2161</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>3430</v>
+        <v>3426</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>3431</v>
+        <v>3427</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>159</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>3393</v>
+        <v>3389</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>3348</v>
+        <v>3344</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>815</v>
@@ -44365,7 +44347,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="4" t="s">
-        <v>3603</v>
+        <v>3599</v>
       </c>
       <c r="B10" s="4">
         <v>67916500</v>
@@ -44386,10 +44368,10 @@
         <v>244</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>3508</v>
+        <v>3504</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>3277</v>
+        <v>3274</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -44406,19 +44388,19 @@
         <v>1513</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>3345</v>
+        <v>3341</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>244</v>
       </c>
       <c r="H11" t="s">
-        <v>3632</v>
+        <v>3628</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>3600</v>
+        <v>3596</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -44444,18 +44426,18 @@
         <v>244</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>3635</v>
+        <v>3631</v>
       </c>
       <c r="I12" s="306" t="s">
-        <v>2995</v>
+        <v>2993</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="4" t="s">
-        <v>2976</v>
+        <v>2974</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>3652</v>
+        <v>3648</v>
       </c>
       <c r="C13" s="22" t="s">
         <v>1221</v>
@@ -44473,10 +44455,10 @@
         <v>244</v>
       </c>
       <c r="H13" s="220" t="s">
-        <v>3343</v>
+        <v>3339</v>
       </c>
       <c r="I13" s="306" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="4" customFormat="1">
@@ -44502,10 +44484,10 @@
         <v>244</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>3544</v>
+        <v>3540</v>
       </c>
       <c r="I14" s="220" t="s">
-        <v>3591</v>
+        <v>3587</v>
       </c>
       <c r="L14" s="3"/>
     </row>
@@ -44532,10 +44514,10 @@
         <v>887</v>
       </c>
       <c r="H15" t="s">
-        <v>3252</v>
+        <v>3250</v>
       </c>
       <c r="I15" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>498</v>
@@ -44564,10 +44546,10 @@
         <v>159</v>
       </c>
       <c r="H16" t="s">
-        <v>3550</v>
+        <v>3546</v>
       </c>
       <c r="I16" t="s">
-        <v>3419</v>
+        <v>3415</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>805</v>
@@ -44575,7 +44557,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>3415</v>
+        <v>3411</v>
       </c>
       <c r="B17">
         <v>65325884</v>
@@ -44598,7 +44580,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="4" t="s">
-        <v>3503</v>
+        <v>3499</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>2112</v>
@@ -44610,24 +44592,24 @@
         <v>2221</v>
       </c>
       <c r="E18" s="4" t="s">
+        <v>2937</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>2938</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>2939</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>244</v>
       </c>
       <c r="H18" s="49" t="s">
-        <v>3098</v>
+        <v>3096</v>
       </c>
       <c r="I18" t="s">
-        <v>3625</v>
+        <v>3621</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="4" customFormat="1">
       <c r="A19" s="4" t="s">
-        <v>2986</v>
+        <v>2984</v>
       </c>
       <c r="B19" s="4">
         <v>64403333</v>
@@ -44639,10 +44621,10 @@
         <v>2605</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>3447</v>
+        <v>3443</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>3431</v>
+        <v>3427</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>1230</v>
@@ -44652,7 +44634,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="4" t="s">
-        <v>3415</v>
+        <v>3411</v>
       </c>
       <c r="B20">
         <v>64403333</v>
@@ -44724,7 +44706,7 @@
     </row>
     <row r="23" spans="1:12" s="4" customFormat="1">
       <c r="A23" t="s">
-        <v>3415</v>
+        <v>3411</v>
       </c>
       <c r="B23">
         <v>63247837</v>
@@ -44733,7 +44715,7 @@
         <v>2613</v>
       </c>
       <c r="D23" t="s">
-        <v>3364</v>
+        <v>3360</v>
       </c>
       <c r="E23" t="s">
         <v>2616</v>
@@ -44745,10 +44727,10 @@
         <v>159</v>
       </c>
       <c r="H23" t="s">
-        <v>3302</v>
+        <v>3298</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>3385</v>
+        <v>3381</v>
       </c>
       <c r="L23" s="6"/>
     </row>
@@ -44763,10 +44745,10 @@
         <v>1634</v>
       </c>
       <c r="D24" t="s">
+        <v>3119</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>3121</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>3123</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>2479</v>
@@ -44777,19 +44759,19 @@
     </row>
     <row r="25" spans="1:12" s="4" customFormat="1">
       <c r="A25" s="4" t="s">
-        <v>3461</v>
+        <v>3457</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>3475</v>
+        <v>3471</v>
       </c>
       <c r="C25" s="21" t="s">
         <v>1329</v>
       </c>
       <c r="D25" t="s">
-        <v>3474</v>
+        <v>3470</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>3032</v>
+        <v>3030</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>2482</v>
@@ -44798,10 +44780,10 @@
         <v>244</v>
       </c>
       <c r="H25" s="220" t="s">
-        <v>3629</v>
+        <v>3625</v>
       </c>
       <c r="I25" s="220" t="s">
-        <v>3538</v>
+        <v>3534</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="4" customFormat="1">
@@ -44827,10 +44809,10 @@
         <v>159</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>3560</v>
+        <v>3556</v>
       </c>
       <c r="I27" t="s">
-        <v>3256</v>
+        <v>3254</v>
       </c>
       <c r="L27" s="4" t="s">
         <v>813</v>
@@ -44838,7 +44820,7 @@
     </row>
     <row r="28" spans="1:12" s="4" customFormat="1">
       <c r="A28" t="s">
-        <v>3599</v>
+        <v>3595</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>2473</v>
@@ -44850,7 +44832,7 @@
         <v>2033</v>
       </c>
       <c r="E28" t="s">
-        <v>3133</v>
+        <v>3131</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>2482</v>
@@ -44862,7 +44844,7 @@
         <v>2660</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>3496</v>
+        <v>3492</v>
       </c>
       <c r="K28"/>
     </row>
@@ -44880,10 +44862,10 @@
         <v>2898</v>
       </c>
       <c r="E29" t="s">
-        <v>3416</v>
+        <v>3412</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
       <c r="G29" s="75" t="s">
         <v>250</v>
@@ -44892,26 +44874,26 @@
         <v>2899</v>
       </c>
       <c r="I29" t="s">
-        <v>3361</v>
+        <v>3357</v>
       </c>
       <c r="J29" s="4"/>
       <c r="L29" s="135"/>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>2986</v>
+        <v>2984</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>3093</v>
+        <v>3091</v>
       </c>
       <c r="C30" s="22" t="s">
         <v>402</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>3092</v>
+        <v>3090</v>
       </c>
       <c r="E30" t="s">
-        <v>3278</v>
+        <v>3275</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>1344</v>
@@ -44920,7 +44902,7 @@
         <v>159</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>3096</v>
+        <v>3094</v>
       </c>
       <c r="I30" s="55" t="s">
         <v>2768</v>
@@ -44928,7 +44910,7 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>3413</v>
+        <v>3409</v>
       </c>
       <c r="B31" s="4">
         <v>69409351</v>
@@ -44949,10 +44931,10 @@
         <v>159</v>
       </c>
       <c r="H31" t="s">
-        <v>3251</v>
+        <v>3249</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>3177</v>
+        <v>3175</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -44978,7 +44960,7 @@
         <v>159</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>3015</v>
+        <v>3013</v>
       </c>
       <c r="I32" s="49" t="s">
         <v>2756</v>
@@ -44989,13 +44971,13 @@
         <v>2619</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>3580</v>
+        <v>3576</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>2603</v>
       </c>
       <c r="D33" t="s">
-        <v>3579</v>
+        <v>3575</v>
       </c>
       <c r="E33" t="s">
         <v>2606</v>
@@ -45007,7 +44989,7 @@
         <v>2607</v>
       </c>
       <c r="H33" s="49" t="s">
-        <v>3041</v>
+        <v>3039</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -45015,13 +44997,13 @@
         <v>1432</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>3528</v>
+        <v>3524</v>
       </c>
       <c r="C34" s="21" t="s">
         <v>2600</v>
       </c>
       <c r="D34" t="s">
-        <v>3201</v>
+        <v>3199</v>
       </c>
       <c r="E34" t="s">
         <v>2606</v>
@@ -45033,25 +45015,25 @@
         <v>159</v>
       </c>
       <c r="H34" t="s">
-        <v>3212</v>
+        <v>3210</v>
       </c>
       <c r="I34" t="s">
-        <v>3339</v>
+        <v>3335</v>
       </c>
       <c r="J34" s="4"/>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>2976</v>
+        <v>2974</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>2981</v>
+        <v>2979</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>2601</v>
       </c>
       <c r="D35" t="s">
-        <v>2980</v>
+        <v>2978</v>
       </c>
       <c r="E35" t="s">
         <v>2606</v>
@@ -45063,24 +45045,24 @@
         <v>2607</v>
       </c>
       <c r="H35" s="306" t="s">
-        <v>3019</v>
+        <v>3017</v>
       </c>
       <c r="I35" t="s">
-        <v>3030</v>
+        <v>3028</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>3415</v>
+        <v>3411</v>
       </c>
       <c r="B36" t="s">
-        <v>3444</v>
+        <v>3440</v>
       </c>
       <c r="C36" s="22" t="s">
         <v>2602</v>
       </c>
       <c r="D36" t="s">
-        <v>3443</v>
+        <v>3439</v>
       </c>
       <c r="E36" t="s">
         <v>2606</v>
@@ -45092,10 +45074,10 @@
         <v>159</v>
       </c>
       <c r="H36" t="s">
-        <v>3446</v>
+        <v>3442</v>
       </c>
       <c r="I36" t="s">
-        <v>3239</v>
+        <v>3237</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -45121,10 +45103,10 @@
         <v>159</v>
       </c>
       <c r="H37" t="s">
-        <v>3647</v>
+        <v>3643</v>
       </c>
       <c r="I37" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -45132,7 +45114,7 @@
         <v>157</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>3107</v>
+        <v>3105</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>2615</v>
@@ -45150,10 +45132,10 @@
         <v>159</v>
       </c>
       <c r="H38" s="97" t="s">
-        <v>3198</v>
+        <v>3196</v>
       </c>
       <c r="I38" t="s">
-        <v>3295</v>
+        <v>3291</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -45166,10 +45148,10 @@
         <v>1354</v>
       </c>
       <c r="E41" s="97" t="s">
-        <v>3353</v>
+        <v>3349</v>
       </c>
       <c r="F41" s="105" t="s">
-        <v>3354</v>
+        <v>3350</v>
       </c>
       <c r="G41" s="105" t="s">
         <v>159</v>
@@ -45187,10 +45169,10 @@
         <v>2098</v>
       </c>
       <c r="E42" s="97" t="s">
-        <v>3353</v>
+        <v>3349</v>
       </c>
       <c r="F42" s="105" t="s">
-        <v>3354</v>
+        <v>3350</v>
       </c>
       <c r="G42" s="105" t="s">
         <v>159</v>
@@ -45206,7 +45188,7 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="4" t="s">
-        <v>3292</v>
+        <v>3288</v>
       </c>
       <c r="B45" t="s">
         <v>2517</v>
@@ -45236,7 +45218,7 @@
         <v>2829</v>
       </c>
       <c r="K45" t="s">
-        <v>3645</v>
+        <v>3641</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="4" customFormat="1">
@@ -45627,13 +45609,13 @@
         <v>157</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>3110</v>
+        <v>3108</v>
       </c>
       <c r="C2" s="276" t="s">
         <v>254</v>
       </c>
       <c r="D2" s="106" t="s">
-        <v>3109</v>
+        <v>3107</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>1299</v>
@@ -45645,13 +45627,13 @@
         <v>62</v>
       </c>
       <c r="H2" s="300" t="s">
-        <v>3148</v>
+        <v>3146</v>
       </c>
       <c r="I2" s="106" t="s">
-        <v>3120</v>
+        <v>3118</v>
       </c>
       <c r="J2" s="107" t="s">
-        <v>3621</v>
+        <v>3617</v>
       </c>
       <c r="K2" s="30" t="s">
         <v>2934</v>
@@ -45669,7 +45651,7 @@
         <v>1182</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>3203</v>
+        <v>3201</v>
       </c>
       <c r="E4" s="32" t="s">
         <v>2405</v>
@@ -45681,25 +45663,25 @@
         <v>270</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>3377</v>
+        <v>3373</v>
       </c>
       <c r="I4" s="30" t="s">
-        <v>3260</v>
+        <v>3258</v>
       </c>
       <c r="J4" s="139" t="s">
-        <v>3633</v>
+        <v>3629</v>
       </c>
       <c r="K4" s="139" t="s">
-        <v>3448</v>
+        <v>3444</v>
       </c>
       <c r="M4" s="39"/>
     </row>
     <row r="5" spans="1:13" s="30" customFormat="1">
       <c r="A5" s="30" t="s">
-        <v>3292</v>
+        <v>3288</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>3297</v>
+        <v>3293</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>1114</v>
@@ -45717,22 +45699,22 @@
         <v>65</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>3595</v>
+        <v>3591</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="J5" s="30" t="s">
-        <v>3370</v>
+        <v>3366</v>
       </c>
       <c r="K5" s="30" t="s">
-        <v>3279</v>
+        <v>3276</v>
       </c>
       <c r="M5" s="36"/>
     </row>
     <row r="6" spans="1:13" s="30" customFormat="1">
       <c r="A6" s="107" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="B6" s="30" t="s">
         <v>2187</v>
@@ -45741,7 +45723,7 @@
         <v>2773</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>3518</v>
+        <v>3514</v>
       </c>
       <c r="E6" s="140" t="s">
         <v>2734</v>
@@ -45753,22 +45735,22 @@
         <v>65</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>3589</v>
+        <v>3585</v>
       </c>
       <c r="I6" s="432" t="s">
-        <v>3113</v>
+        <v>3111</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>3116</v>
+        <v>3114</v>
       </c>
       <c r="K6" s="30" t="s">
-        <v>3238</v>
+        <v>3236</v>
       </c>
       <c r="M6" s="36"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="107" t="s">
-        <v>3176</v>
+        <v>3174</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>1212</v>
@@ -45777,28 +45759,28 @@
         <v>1091</v>
       </c>
       <c r="D7" t="s">
-        <v>3378</v>
+        <v>3374</v>
       </c>
       <c r="E7" s="107" t="s">
-        <v>3357</v>
+        <v>3353</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>3358</v>
+        <v>3354</v>
       </c>
       <c r="G7" s="106" t="s">
         <v>720</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>3253</v>
+        <v>3251</v>
       </c>
       <c r="I7" s="217" t="s">
-        <v>2996</v>
+        <v>2994</v>
       </c>
       <c r="J7" s="217" t="s">
         <v>2676</v>
       </c>
       <c r="K7" s="30" t="s">
-        <v>3020</v>
+        <v>3018</v>
       </c>
       <c r="M7" s="36"/>
     </row>
@@ -45813,7 +45795,7 @@
         <v>985</v>
       </c>
       <c r="D8" s="139" t="s">
-        <v>3469</v>
+        <v>3465</v>
       </c>
       <c r="E8" s="107" t="s">
         <v>1157</v>
@@ -45825,22 +45807,22 @@
         <v>65</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>3601</v>
+        <v>3597</v>
       </c>
       <c r="I8" s="32" t="s">
-        <v>3078</v>
+        <v>3076</v>
       </c>
       <c r="J8" s="449" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="K8" s="139" t="s">
-        <v>3424</v>
+        <v>3420</v>
       </c>
       <c r="M8" s="36"/>
     </row>
     <row r="9" spans="1:13" s="107" customFormat="1">
       <c r="A9" s="302" t="s">
-        <v>3245</v>
+        <v>3243</v>
       </c>
       <c r="B9" s="32" t="s">
         <v>1676</v>
@@ -45861,22 +45843,22 @@
         <v>65</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="I9" s="107" t="s">
-        <v>3617</v>
+        <v>3613</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>3306</v>
+        <v>3302</v>
       </c>
       <c r="K9" s="107" t="s">
-        <v>3042</v>
+        <v>3040</v>
       </c>
       <c r="M9" s="36"/>
     </row>
     <row r="10" spans="1:13" s="30" customFormat="1">
       <c r="A10" s="30" t="s">
-        <v>3245</v>
+        <v>3243</v>
       </c>
       <c r="B10" s="30">
         <v>69575383</v>
@@ -45897,16 +45879,16 @@
         <v>65</v>
       </c>
       <c r="H10" s="107" t="s">
-        <v>3303</v>
+        <v>3299</v>
       </c>
       <c r="I10" t="s">
-        <v>3388</v>
+        <v>3384</v>
       </c>
       <c r="J10" s="219" t="s">
-        <v>3509</v>
+        <v>3505</v>
       </c>
       <c r="K10" s="107" t="s">
-        <v>3066</v>
+        <v>3064</v>
       </c>
       <c r="M10" s="34"/>
     </row>
@@ -45933,16 +45915,16 @@
         <v>605</v>
       </c>
       <c r="H11" s="139" t="s">
-        <v>3178</v>
+        <v>3176</v>
       </c>
       <c r="I11" s="30" t="s">
-        <v>3604</v>
+        <v>3600</v>
       </c>
       <c r="J11" s="107" t="s">
-        <v>3016</v>
+        <v>3014</v>
       </c>
       <c r="K11" s="107" t="s">
-        <v>3299</v>
+        <v>3295</v>
       </c>
       <c r="M11" s="36"/>
     </row>
@@ -45969,22 +45951,22 @@
         <v>245</v>
       </c>
       <c r="H12" s="450" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
       <c r="I12" s="106" t="s">
-        <v>3584</v>
+        <v>3580</v>
       </c>
       <c r="J12" s="106" t="s">
-        <v>3517</v>
+        <v>3513</v>
       </c>
       <c r="K12" s="107" t="s">
-        <v>3294</v>
+        <v>3290</v>
       </c>
       <c r="M12" s="151"/>
     </row>
     <row r="13" spans="1:13" s="107" customFormat="1">
       <c r="A13" s="140" t="s">
-        <v>3461</v>
+        <v>3457</v>
       </c>
       <c r="B13" s="107" t="s">
         <v>2804</v>
@@ -45993,7 +45975,7 @@
         <v>919</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>3163</v>
+        <v>3161</v>
       </c>
       <c r="E13" s="140" t="s">
         <v>2774</v>
@@ -46005,16 +45987,16 @@
         <v>65</v>
       </c>
       <c r="H13" s="30" t="s">
-        <v>3164</v>
+        <v>3162</v>
       </c>
       <c r="I13" s="30" t="s">
-        <v>3263</v>
+        <v>3261</v>
       </c>
       <c r="J13" s="107" t="s">
-        <v>3309</v>
+        <v>3305</v>
       </c>
       <c r="K13" t="s">
-        <v>3335</v>
+        <v>3331</v>
       </c>
       <c r="M13" s="36"/>
     </row>
@@ -46041,13 +46023,13 @@
         <v>65</v>
       </c>
       <c r="H14" s="107" t="s">
-        <v>3394</v>
+        <v>3390</v>
       </c>
       <c r="I14" s="411" t="s">
         <v>2272</v>
       </c>
       <c r="J14" s="32" t="s">
-        <v>3225</v>
+        <v>3223</v>
       </c>
       <c r="M14" s="36"/>
     </row>
@@ -46074,16 +46056,16 @@
         <v>66</v>
       </c>
       <c r="H15" t="s">
+        <v>3541</v>
+      </c>
+      <c r="I15" t="s">
         <v>3545</v>
       </c>
-      <c r="I15" t="s">
-        <v>3549</v>
-      </c>
       <c r="J15" t="s">
-        <v>3280</v>
+        <v>3277</v>
       </c>
       <c r="K15" s="107" t="s">
-        <v>3031</v>
+        <v>3029</v>
       </c>
       <c r="M15" s="36"/>
     </row>
@@ -46135,16 +46117,16 @@
         <v>66</v>
       </c>
       <c r="H17" t="s">
-        <v>3606</v>
+        <v>3602</v>
       </c>
       <c r="I17" s="30" t="s">
-        <v>3125</v>
+        <v>3123</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>3659</v>
+        <v>3655</v>
       </c>
       <c r="K17" s="220" t="s">
-        <v>3598</v>
+        <v>3594</v>
       </c>
       <c r="M17" s="34"/>
     </row>
@@ -46171,22 +46153,22 @@
         <v>66</v>
       </c>
       <c r="H18" s="30" t="s">
-        <v>3108</v>
+        <v>3106</v>
       </c>
       <c r="I18" t="s">
-        <v>3224</v>
+        <v>3222</v>
       </c>
       <c r="J18" t="s">
-        <v>3252</v>
+        <v>3250</v>
       </c>
       <c r="K18" s="49" t="s">
-        <v>2960</v>
+        <v>2958</v>
       </c>
       <c r="M18" s="36"/>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="4" t="s">
-        <v>2976</v>
+        <v>2974</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>1533</v>
@@ -46195,7 +46177,7 @@
         <v>1693</v>
       </c>
       <c r="D19" s="134" t="s">
-        <v>3470</v>
+        <v>3466</v>
       </c>
       <c r="E19" t="s">
         <v>1696</v>
@@ -46207,16 +46189,16 @@
         <v>66</v>
       </c>
       <c r="H19" t="s">
-        <v>3129</v>
+        <v>3127</v>
       </c>
       <c r="I19" s="49" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="J19" s="220" t="s">
-        <v>3250</v>
+        <v>3248</v>
       </c>
       <c r="K19" t="s">
-        <v>3077</v>
+        <v>3075</v>
       </c>
       <c r="M19" s="36"/>
     </row>
@@ -46231,7 +46213,7 @@
         <v>2498</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>3058</v>
+        <v>3056</v>
       </c>
       <c r="E20" s="107" t="s">
         <v>2423</v>
@@ -46243,31 +46225,31 @@
         <v>65</v>
       </c>
       <c r="H20" s="438" t="s">
-        <v>3516</v>
+        <v>3512</v>
       </c>
       <c r="I20" t="s">
-        <v>3059</v>
+        <v>3057</v>
       </c>
       <c r="J20" t="s">
-        <v>3060</v>
+        <v>3058</v>
       </c>
       <c r="K20" t="s">
-        <v>3095</v>
+        <v>3093</v>
       </c>
       <c r="M20" s="36"/>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>3399</v>
+        <v>3395</v>
       </c>
       <c r="B21" t="s">
-        <v>3404</v>
+        <v>3400</v>
       </c>
       <c r="C21" s="22" t="s">
         <v>1130</v>
       </c>
       <c r="D21" t="s">
-        <v>3403</v>
+        <v>3399</v>
       </c>
       <c r="E21" s="140" t="s">
         <v>1593</v>
@@ -46279,19 +46261,19 @@
         <v>65</v>
       </c>
       <c r="H21" t="s">
+        <v>3404</v>
+      </c>
+      <c r="I21" t="s">
+        <v>3407</v>
+      </c>
+      <c r="J21" t="s">
         <v>3408</v>
-      </c>
-      <c r="I21" t="s">
-        <v>3411</v>
-      </c>
-      <c r="J21" t="s">
-        <v>3412</v>
       </c>
       <c r="M21" s="36"/>
     </row>
     <row r="22" spans="1:13" s="30" customFormat="1">
       <c r="A22" s="30" t="s">
-        <v>3415</v>
+        <v>3411</v>
       </c>
       <c r="B22" s="30" t="s">
         <v>2114</v>
@@ -46300,58 +46282,58 @@
         <v>2737</v>
       </c>
       <c r="D22" s="107" t="s">
-        <v>3454</v>
+        <v>3450</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>3427</v>
+        <v>3423</v>
       </c>
       <c r="F22" s="30" t="s">
-        <v>3428</v>
+        <v>3424</v>
       </c>
       <c r="G22" s="32" t="s">
         <v>65</v>
       </c>
       <c r="H22" s="30" t="s">
-        <v>3432</v>
+        <v>3428</v>
       </c>
       <c r="I22" s="30" t="s">
-        <v>3434</v>
+        <v>3430</v>
       </c>
       <c r="J22" s="30" t="s">
-        <v>3435</v>
+        <v>3431</v>
       </c>
       <c r="M22" s="36"/>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>3415</v>
+        <v>3411</v>
       </c>
       <c r="B23" t="s">
-        <v>3449</v>
+        <v>3445</v>
       </c>
       <c r="C23" s="22" t="s">
         <v>1906</v>
       </c>
       <c r="D23" t="s">
-        <v>3502</v>
+        <v>3498</v>
       </c>
       <c r="E23" s="30" t="s">
-        <v>3427</v>
+        <v>3423</v>
       </c>
       <c r="F23" s="30" t="s">
-        <v>3428</v>
+        <v>3424</v>
       </c>
       <c r="G23" t="s">
         <v>66</v>
       </c>
       <c r="H23" t="s">
-        <v>3541</v>
+        <v>3537</v>
       </c>
       <c r="I23" t="s">
-        <v>3540</v>
+        <v>3536</v>
       </c>
       <c r="J23" t="s">
-        <v>3533</v>
+        <v>3529</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -46444,7 +46426,7 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="B33">
         <v>60389752</v>
@@ -46467,7 +46449,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" t="s">
-        <v>3503</v>
+        <v>3499</v>
       </c>
       <c r="B34">
         <v>60389752</v>
@@ -46476,13 +46458,13 @@
         <v>2177</v>
       </c>
       <c r="D34" s="32" t="s">
-        <v>3301</v>
+        <v>3297</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>3427</v>
+        <v>3423</v>
       </c>
       <c r="F34" s="30" t="s">
-        <v>3428</v>
+        <v>3424</v>
       </c>
       <c r="G34" t="s">
         <v>3</v>
@@ -46491,7 +46473,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>3399</v>
+        <v>3395</v>
       </c>
       <c r="B35">
         <v>60389752</v>
@@ -46515,7 +46497,7 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="B36">
         <v>60389752</v>
@@ -46539,7 +46521,7 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="30" t="s">
-        <v>3399</v>
+        <v>3395</v>
       </c>
       <c r="B37" s="30">
         <v>64403333</v>
@@ -46564,7 +46546,7 @@
     </row>
     <row r="38" spans="1:13" s="30" customFormat="1">
       <c r="A38" s="30" t="s">
-        <v>3503</v>
+        <v>3499</v>
       </c>
       <c r="B38" s="30">
         <v>60389752</v>
@@ -46601,10 +46583,10 @@
         <v>2148</v>
       </c>
       <c r="E39" t="s">
-        <v>3427</v>
+        <v>3423</v>
       </c>
       <c r="F39" t="s">
-        <v>3428</v>
+        <v>3424</v>
       </c>
       <c r="G39" t="s">
         <v>3</v>
@@ -46673,7 +46655,7 @@
         <v>2524</v>
       </c>
       <c r="E45" t="s">
-        <v>3312</v>
+        <v>3308</v>
       </c>
       <c r="F45" s="30" t="s">
         <v>2525</v>
@@ -46682,13 +46664,13 @@
         <v>369</v>
       </c>
       <c r="H45" t="s">
-        <v>3200</v>
+        <v>3198</v>
       </c>
       <c r="I45" s="30" t="s">
-        <v>3396</v>
+        <v>3392</v>
       </c>
       <c r="J45" t="s">
-        <v>2984</v>
+        <v>2982</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -46740,10 +46722,10 @@
     </row>
     <row r="66" spans="1:38">
       <c r="C66" s="7" t="s">
-        <v>3530</v>
+        <v>3526</v>
       </c>
       <c r="D66" t="s">
-        <v>3301</v>
+        <v>3297</v>
       </c>
       <c r="E66" t="s">
         <v>2421</v>
@@ -46791,10 +46773,10 @@
     </row>
     <row r="70" spans="1:38">
       <c r="C70" s="8" t="s">
-        <v>3648</v>
+        <v>3644</v>
       </c>
       <c r="D70" t="s">
-        <v>3649</v>
+        <v>3645</v>
       </c>
       <c r="E70" s="140" t="s">
         <v>2927</v>
@@ -47135,7 +47117,7 @@
         <v>1133</v>
       </c>
       <c r="D93" t="s">
-        <v>3422</v>
+        <v>3418</v>
       </c>
       <c r="E93" s="140" t="s">
         <v>1135</v>
@@ -47159,7 +47141,7 @@
         <v>1393</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>3423</v>
+        <v>3419</v>
       </c>
       <c r="E94" s="266" t="s">
         <v>1508</v>
@@ -47193,7 +47175,7 @@
         <v>358</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>3530</v>
+        <v>3526</v>
       </c>
     </row>
     <row r="105" spans="2:5">
@@ -47419,7 +47401,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>3425</v>
+        <v>3421</v>
       </c>
       <c r="C12" s="236" t="s">
         <v>1940</v>
@@ -47559,7 +47541,7 @@
       </c>
       <c r="B24" s="87"/>
       <c r="F24" s="2" t="s">
-        <v>3065</v>
+        <v>3063</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -47635,27 +47617,27 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="87" t="s">
-        <v>3482</v>
+        <v>3478</v>
       </c>
       <c r="C40" t="s">
-        <v>3485</v>
+        <v>3481</v>
       </c>
       <c r="F40" s="45"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="89" t="s">
-        <v>3483</v>
+        <v>3479</v>
       </c>
       <c r="C41" t="s">
-        <v>3486</v>
+        <v>3482</v>
       </c>
     </row>
     <row r="42" spans="2:6" ht="15" thickBot="1">
       <c r="B42" s="86" t="s">
-        <v>3484</v>
+        <v>3480</v>
       </c>
       <c r="C42" t="s">
-        <v>3487</v>
+        <v>3483</v>
       </c>
     </row>
     <row r="43" spans="2:6">
@@ -47818,22 +47800,22 @@
         <v>2038</v>
       </c>
       <c r="E6" s="247" t="s">
-        <v>3346</v>
+        <v>3342</v>
       </c>
       <c r="F6" s="247" t="s">
-        <v>3347</v>
+        <v>3343</v>
       </c>
       <c r="G6" s="247" t="s">
         <v>357</v>
       </c>
       <c r="H6" s="247" t="s">
-        <v>3305</v>
+        <v>3301</v>
       </c>
       <c r="I6" s="244" t="s">
-        <v>3605</v>
+        <v>3601</v>
       </c>
       <c r="J6" s="455" t="s">
-        <v>2979</v>
+        <v>2977</v>
       </c>
       <c r="K6" s="247" t="s">
         <v>475</v>
@@ -47856,19 +47838,19 @@
         <v>1038</v>
       </c>
       <c r="F7" s="265" t="s">
-        <v>3349</v>
+        <v>3345</v>
       </c>
       <c r="G7" s="265" t="s">
         <v>690</v>
       </c>
       <c r="H7" s="295" t="s">
-        <v>3344</v>
+        <v>3340</v>
       </c>
       <c r="I7" s="295" t="s">
-        <v>3073</v>
+        <v>3071</v>
       </c>
       <c r="J7" s="295" t="s">
-        <v>3554</v>
+        <v>3550</v>
       </c>
       <c r="K7" s="265" t="s">
         <v>709</v>
@@ -47891,19 +47873,19 @@
         <v>1231</v>
       </c>
       <c r="F8" s="265" t="s">
-        <v>3226</v>
+        <v>3224</v>
       </c>
       <c r="G8" s="265" t="s">
         <v>250</v>
       </c>
       <c r="H8" s="319" t="s">
-        <v>3566</v>
+        <v>3562</v>
       </c>
       <c r="I8" s="265" t="s">
-        <v>3496</v>
+        <v>3492</v>
       </c>
       <c r="J8" s="265" t="s">
-        <v>3565</v>
+        <v>3561</v>
       </c>
       <c r="K8" s="259"/>
       <c r="L8" s="259"/>
@@ -47925,7 +47907,7 @@
         <v>2722</v>
       </c>
       <c r="F9" s="263" t="s">
-        <v>3450</v>
+        <v>3446</v>
       </c>
       <c r="G9" s="263" t="s">
         <v>948</v>
@@ -47957,13 +47939,13 @@
         <v>690</v>
       </c>
       <c r="H10" s="264" t="s">
-        <v>3043</v>
+        <v>3041</v>
       </c>
       <c r="I10" s="455" t="s">
-        <v>3641</v>
+        <v>3637</v>
       </c>
       <c r="J10" s="264" t="s">
-        <v>3636</v>
+        <v>3632</v>
       </c>
       <c r="K10" s="245" t="s">
         <v>1206</v>
@@ -47974,7 +47956,7 @@
         <v>2522</v>
       </c>
       <c r="B11" s="262" t="s">
-        <v>3336</v>
+        <v>3332</v>
       </c>
       <c r="C11" s="194" t="s">
         <v>491</v>
@@ -47992,13 +47974,13 @@
         <v>690</v>
       </c>
       <c r="H11" s="215" t="s">
-        <v>3537</v>
+        <v>3533</v>
       </c>
       <c r="I11" s="425" t="s">
-        <v>3510</v>
+        <v>3506</v>
       </c>
       <c r="J11" s="269" t="s">
-        <v>3653</v>
+        <v>3649</v>
       </c>
       <c r="K11" s="183" t="s">
         <v>1207</v>
@@ -48032,10 +48014,10 @@
     </row>
     <row r="13" spans="1:12" s="223" customFormat="1">
       <c r="A13" s="223" t="s">
-        <v>3399</v>
+        <v>3395</v>
       </c>
       <c r="B13" s="223" t="s">
-        <v>3421</v>
+        <v>3417</v>
       </c>
       <c r="C13" s="424" t="s">
         <v>335</v>
@@ -48044,22 +48026,22 @@
         <v>2403</v>
       </c>
       <c r="E13" s="223" t="s">
-        <v>3105</v>
+        <v>3103</v>
       </c>
       <c r="F13" s="223" t="s">
-        <v>3104</v>
+        <v>3102</v>
       </c>
       <c r="G13" s="223" t="s">
         <v>690</v>
       </c>
       <c r="H13" s="223" t="s">
-        <v>3111</v>
+        <v>3109</v>
       </c>
       <c r="I13" s="215" t="s">
-        <v>3317</v>
+        <v>3313</v>
       </c>
       <c r="J13" s="223" t="s">
-        <v>3112</v>
+        <v>3110</v>
       </c>
       <c r="K13" s="223" t="s">
         <v>1320</v>
@@ -48079,7 +48061,7 @@
         <v>1977</v>
       </c>
       <c r="E14" s="216" t="s">
-        <v>3376</v>
+        <v>3372</v>
       </c>
       <c r="F14" s="216" t="s">
         <v>1436</v>
@@ -48088,13 +48070,13 @@
         <v>690</v>
       </c>
       <c r="H14" s="272" t="s">
-        <v>3555</v>
+        <v>3551</v>
       </c>
       <c r="I14" s="215" t="s">
-        <v>3017</v>
+        <v>3015</v>
       </c>
       <c r="J14" s="262" t="s">
-        <v>3179</v>
+        <v>3177</v>
       </c>
       <c r="K14" s="183" t="s">
         <v>1208</v>
@@ -48105,13 +48087,13 @@
         <v>1419</v>
       </c>
       <c r="B15" s="264" t="s">
-        <v>3021</v>
+        <v>3019</v>
       </c>
       <c r="C15" s="270" t="s">
         <v>1308</v>
       </c>
       <c r="D15" s="259" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
       <c r="E15" s="259" t="s">
         <v>2782</v>
@@ -48123,13 +48105,13 @@
         <v>690</v>
       </c>
       <c r="H15" s="264" t="s">
-        <v>3289</v>
+        <v>3286</v>
       </c>
       <c r="I15" s="439" t="s">
-        <v>3569</v>
+        <v>3565</v>
       </c>
       <c r="J15" s="264" t="s">
-        <v>3246</v>
+        <v>3244</v>
       </c>
       <c r="K15" s="259" t="s">
         <v>1441</v>
@@ -48187,7 +48169,7 @@
     </row>
     <row r="18" spans="1:11" s="259" customFormat="1">
       <c r="A18" s="271" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="B18" s="259" t="s">
         <v>2345</v>
@@ -48196,7 +48178,7 @@
         <v>831</v>
       </c>
       <c r="D18" s="264" t="s">
-        <v>3570</v>
+        <v>3566</v>
       </c>
       <c r="E18" s="264" t="s">
         <v>1792</v>
@@ -48208,13 +48190,13 @@
         <v>690</v>
       </c>
       <c r="H18" s="259" t="s">
-        <v>3639</v>
+        <v>3635</v>
       </c>
       <c r="I18" s="298" t="s">
-        <v>3383</v>
+        <v>3379</v>
       </c>
       <c r="J18" s="259" t="s">
-        <v>3622</v>
+        <v>3618</v>
       </c>
       <c r="K18" s="264" t="s">
         <v>1769</v>
@@ -48222,7 +48204,7 @@
     </row>
     <row r="19" spans="1:11" s="259" customFormat="1">
       <c r="A19" s="259" t="s">
-        <v>3507</v>
+        <v>3503</v>
       </c>
       <c r="B19" s="259" t="s">
         <v>2390</v>
@@ -48243,13 +48225,13 @@
         <v>690</v>
       </c>
       <c r="H19" s="259" t="s">
-        <v>3192</v>
+        <v>3190</v>
       </c>
       <c r="I19" s="259" t="s">
-        <v>3529</v>
+        <v>3525</v>
       </c>
       <c r="J19" s="259" t="s">
-        <v>3127</v>
+        <v>3125</v>
       </c>
       <c r="K19" s="259" t="s">
         <v>1814</v>
@@ -48260,7 +48242,7 @@
         <v>2619</v>
       </c>
       <c r="B20" s="304" t="s">
-        <v>3568</v>
+        <v>3564</v>
       </c>
       <c r="C20" s="259" t="s">
         <v>1815</v>
@@ -48281,10 +48263,10 @@
         <v>2791</v>
       </c>
       <c r="I20" s="264" t="s">
-        <v>3602</v>
+        <v>3598</v>
       </c>
       <c r="J20" s="264" t="s">
-        <v>3442</v>
+        <v>3438</v>
       </c>
       <c r="K20" s="259" t="s">
         <v>1816</v>
@@ -48327,10 +48309,10 @@
         <v>637</v>
       </c>
       <c r="D22" s="255" t="s">
-        <v>3571</v>
+        <v>3567</v>
       </c>
       <c r="E22" s="271" t="s">
-        <v>3489</v>
+        <v>3485</v>
       </c>
       <c r="F22" s="271" t="s">
         <v>1714</v>
@@ -48339,13 +48321,13 @@
         <v>250</v>
       </c>
       <c r="H22" s="259" t="s">
-        <v>3582</v>
+        <v>3578</v>
       </c>
       <c r="I22" s="264" t="s">
-        <v>3318</v>
+        <v>3314</v>
       </c>
       <c r="J22" s="264" t="s">
-        <v>3213</v>
+        <v>3211</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="97" customFormat="1">
@@ -48566,7 +48548,7 @@
         <v>840</v>
       </c>
       <c r="D45" s="264" t="s">
-        <v>3053</v>
+        <v>3051</v>
       </c>
       <c r="E45" s="259" t="s">
         <v>1792</v>
@@ -48769,13 +48751,13 @@
         <v>2800</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>3374</v>
+        <v>3370</v>
       </c>
       <c r="I2" t="s">
-        <v>3531</v>
+        <v>3527</v>
       </c>
       <c r="J2" t="s">
-        <v>3627</v>
+        <v>3623</v>
       </c>
       <c r="L2" s="36" t="s">
         <v>1176</v>
@@ -48801,7 +48783,7 @@
         <v>298</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>3375</v>
+        <v>3371</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>707</v>
@@ -48827,25 +48809,25 @@
         <v>313</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>2972</v>
+        <v>2970</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>3049</v>
+        <v>3047</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>323</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>3561</v>
+        <v>3557</v>
       </c>
       <c r="H4" t="s">
-        <v>3102</v>
+        <v>3100</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>3638</v>
+        <v>3634</v>
       </c>
       <c r="J4" t="s">
-        <v>2973</v>
+        <v>2971</v>
       </c>
       <c r="L4" s="127" t="s">
         <v>322</v>
@@ -48871,7 +48853,7 @@
         <v>424</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>3106</v>
+        <v>3104</v>
       </c>
       <c r="H5" s="49" t="s">
         <v>2767</v>
@@ -48886,7 +48868,7 @@
     </row>
     <row r="6" spans="1:12" s="4" customFormat="1">
       <c r="A6" s="4" t="s">
-        <v>3616</v>
+        <v>3612</v>
       </c>
       <c r="B6" s="4">
         <v>65436260</v>
@@ -48904,13 +48886,13 @@
         <v>166</v>
       </c>
       <c r="G6" t="s">
-        <v>3331</v>
+        <v>3327</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>2997</v>
+        <v>2995</v>
       </c>
       <c r="I6" t="s">
-        <v>3379</v>
+        <v>3375</v>
       </c>
       <c r="J6" s="49" t="s">
         <v>2919</v>
@@ -48921,7 +48903,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="4" t="s">
-        <v>3287</v>
+        <v>3284</v>
       </c>
       <c r="B7" s="4">
         <v>69561522</v>
@@ -48930,25 +48912,25 @@
         <v>434</v>
       </c>
       <c r="D7" t="s">
-        <v>3209</v>
+        <v>3207</v>
       </c>
       <c r="E7" t="s">
-        <v>3240</v>
+        <v>3238</v>
       </c>
       <c r="F7" t="s">
         <v>151</v>
       </c>
       <c r="G7" t="s">
-        <v>3623</v>
+        <v>3619</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>3511</v>
+        <v>3507</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>3131</v>
+        <v>3129</v>
       </c>
       <c r="J7" t="s">
-        <v>3237</v>
+        <v>3235</v>
       </c>
       <c r="L7" s="83" t="s">
         <v>435</v>
@@ -48956,10 +48938,10 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="306" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>2998</v>
+        <v>2996</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>658</v>
@@ -48977,10 +48959,10 @@
         <v>2662</v>
       </c>
       <c r="H8" t="s">
-        <v>3596</v>
+        <v>3592</v>
       </c>
       <c r="I8" t="s">
-        <v>3031</v>
+        <v>3029</v>
       </c>
       <c r="J8" s="49" t="s">
         <v>2799</v>
@@ -49007,16 +48989,16 @@
         <v>151</v>
       </c>
       <c r="G9" t="s">
-        <v>3178</v>
+        <v>3176</v>
       </c>
       <c r="H9" s="220" t="s">
-        <v>3169</v>
+        <v>3167</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>3631</v>
+        <v>3627</v>
       </c>
       <c r="J9" s="220" t="s">
-        <v>3157</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -49030,7 +49012,7 @@
         <v>2204</v>
       </c>
       <c r="D10" t="s">
-        <v>3061</v>
+        <v>3059</v>
       </c>
       <c r="E10" t="s">
         <v>2175</v>
@@ -49039,13 +49021,13 @@
         <v>1822</v>
       </c>
       <c r="G10" t="s">
-        <v>3351</v>
+        <v>3347</v>
       </c>
       <c r="H10" s="49" t="s">
-        <v>3585</v>
+        <v>3581</v>
       </c>
       <c r="I10" t="s">
-        <v>3382</v>
+        <v>3378</v>
       </c>
       <c r="J10" s="49" t="s">
         <v>2862</v>
@@ -49088,7 +49070,7 @@
         <v>1481</v>
       </c>
       <c r="E12" t="s">
-        <v>3208</v>
+        <v>3206</v>
       </c>
       <c r="F12" t="s">
         <v>614</v>
@@ -49119,16 +49101,16 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>3311</v>
+        <v>3307</v>
       </c>
       <c r="B14" t="s">
-        <v>3320</v>
+        <v>3316</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>281</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>3319</v>
+        <v>3315</v>
       </c>
       <c r="E14" t="s">
         <v>2141</v>
@@ -49137,16 +49119,16 @@
         <v>1822</v>
       </c>
       <c r="G14" s="97" t="s">
-        <v>3360</v>
+        <v>3356</v>
       </c>
       <c r="H14" t="s">
-        <v>3646</v>
+        <v>3642</v>
       </c>
       <c r="I14" t="s">
-        <v>3504</v>
+        <v>3500</v>
       </c>
       <c r="J14" t="s">
-        <v>3420</v>
+        <v>3416</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -49414,7 +49396,7 @@
     </row>
     <row r="2" spans="1:14" ht="43.15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>3074</v>
+        <v>3072</v>
       </c>
       <c r="C2" s="51"/>
       <c r="D2" s="52" t="s">
@@ -49438,7 +49420,7 @@
         <v>2694</v>
       </c>
       <c r="E4" t="s">
-        <v>3230</v>
+        <v>3228</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -49463,7 +49445,7 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="B9" t="s">
         <v>1555</v>
@@ -49483,7 +49465,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="460" t="s">
-        <v>3245</v>
+        <v>3243</v>
       </c>
       <c r="B10">
         <v>63000545</v>
@@ -49495,7 +49477,7 @@
         <v>2219</v>
       </c>
       <c r="E10" s="460" t="s">
-        <v>3655</v>
+        <v>3651</v>
       </c>
       <c r="F10" t="s">
         <v>1685</v>
@@ -49515,7 +49497,7 @@
         <v>2059</v>
       </c>
       <c r="E11" t="s">
-        <v>3094</v>
+        <v>3092</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -49532,7 +49514,7 @@
         <v>2703</v>
       </c>
       <c r="E12" t="s">
-        <v>3481</v>
+        <v>3477</v>
       </c>
       <c r="F12" t="s">
         <v>1685</v>
@@ -49540,7 +49522,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>3398</v>
+        <v>3394</v>
       </c>
       <c r="B13">
         <v>62271547</v>
@@ -49552,10 +49534,10 @@
         <v>2396</v>
       </c>
       <c r="E13" t="s">
-        <v>2958</v>
+        <v>2956</v>
       </c>
       <c r="F13" t="s">
-        <v>2959</v>
+        <v>2957</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -49569,7 +49551,7 @@
         <v>1941</v>
       </c>
       <c r="D14" t="s">
-        <v>3210</v>
+        <v>3208</v>
       </c>
       <c r="E14" t="s">
         <v>2663</v>
@@ -49580,7 +49562,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>3176</v>
+        <v>3174</v>
       </c>
       <c r="B15">
         <v>62806425</v>
@@ -49609,10 +49591,10 @@
         <v>2751</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>3100</v>
+        <v>3098</v>
       </c>
       <c r="E16" t="s">
-        <v>3101</v>
+        <v>3099</v>
       </c>
       <c r="F16" t="s">
         <v>2706</v>
@@ -49620,19 +49602,19 @@
     </row>
     <row r="17" spans="1:8" s="30" customFormat="1">
       <c r="A17" s="217" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="B17" s="30">
         <v>68582631</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>2983</v>
+        <v>2981</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>3114</v>
+        <v>3112</v>
       </c>
       <c r="E17" t="s">
-        <v>3115</v>
+        <v>3113</v>
       </c>
       <c r="F17" t="s">
         <v>2706</v>
@@ -49655,7 +49637,7 @@
         <v>2755</v>
       </c>
       <c r="E18" t="s">
-        <v>3115</v>
+        <v>3113</v>
       </c>
       <c r="F18" t="s">
         <v>2706</v>
@@ -49675,10 +49657,10 @@
         <v>2797</v>
       </c>
       <c r="E19" t="s">
-        <v>3257</v>
+        <v>3255</v>
       </c>
       <c r="F19" t="s">
-        <v>2959</v>
+        <v>2957</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -49698,7 +49680,7 @@
         <v>1515</v>
       </c>
       <c r="F21" t="s">
-        <v>3392</v>
+        <v>3388</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -49734,7 +49716,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>2986</v>
+        <v>2984</v>
       </c>
       <c r="B26">
         <v>68927207</v>
@@ -49746,13 +49728,13 @@
         <v>2680</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>3075</v>
+        <v>3073</v>
       </c>
       <c r="F26" t="s">
-        <v>3076</v>
+        <v>3074</v>
       </c>
       <c r="G26" t="s">
-        <v>3088</v>
+        <v>3086</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -49769,13 +49751,13 @@
         <v>421</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>3075</v>
+        <v>3073</v>
       </c>
       <c r="F27" t="s">
-        <v>3105</v>
+        <v>3103</v>
       </c>
       <c r="G27" t="s">
-        <v>3139</v>
+        <v>3137</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -49786,16 +49768,16 @@
         <v>1464</v>
       </c>
       <c r="D29" t="s">
-        <v>3362</v>
+        <v>3358</v>
       </c>
       <c r="E29" t="s">
-        <v>3308</v>
+        <v>3304</v>
       </c>
       <c r="F29" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>3363</v>
+        <v>3359</v>
       </c>
       <c r="H29" t="s">
         <v>407</v>
@@ -49803,7 +49785,7 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>2986</v>
+        <v>2984</v>
       </c>
       <c r="B30">
         <v>63926844</v>
@@ -49815,10 +49797,10 @@
         <v>2705</v>
       </c>
       <c r="E30" t="s">
-        <v>3089</v>
+        <v>3087</v>
       </c>
       <c r="F30" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -49832,10 +49814,10 @@
         <v>1561</v>
       </c>
       <c r="D31" t="s">
-        <v>3332</v>
+        <v>3328</v>
       </c>
       <c r="E31" t="s">
-        <v>3333</v>
+        <v>3329</v>
       </c>
       <c r="F31" t="s">
         <v>1316</v>
@@ -51879,7 +51861,7 @@
     </row>
     <row r="252" spans="1:6" s="420" customFormat="1" ht="21">
       <c r="C252" s="420" t="s">
-        <v>3047</v>
+        <v>3045</v>
       </c>
     </row>
     <row r="253" spans="1:6">
@@ -51896,30 +51878,30 @@
         <v>2251</v>
       </c>
       <c r="E253" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="F253" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
     </row>
     <row r="254" spans="1:6">
       <c r="A254" t="s">
-        <v>2976</v>
+        <v>2974</v>
       </c>
       <c r="B254">
         <v>64738222</v>
       </c>
       <c r="C254" s="22" t="s">
-        <v>2978</v>
+        <v>2976</v>
       </c>
       <c r="D254" t="s">
-        <v>2975</v>
+        <v>2973</v>
       </c>
       <c r="E254" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="F254" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -51930,16 +51912,16 @@
         <v>60433915</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>2977</v>
+        <v>2975</v>
       </c>
       <c r="D255" s="251" t="s">
         <v>2647</v>
       </c>
       <c r="E255" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="F255" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
     </row>
     <row r="256" spans="1:6">
@@ -56693,7 +56675,7 @@
         <v>2694</v>
       </c>
       <c r="E537" s="76" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="F537" s="76"/>
       <c r="G537" s="76"/>

--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dc549f2659ed9bd7/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62658" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA0EABD0-C36F-4A85-93C8-DF9330DBF1AB}"/>
+  <xr:revisionPtr revIDLastSave="62660" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3146162-E274-404E-A62D-5F1053FB0101}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9933,9 +9933,6 @@
     <t>60643090 (Yassir)</t>
   </si>
   <si>
-    <t>66388635 1 pantalla hasta el 09 de septiembre (Chelita)</t>
-  </si>
-  <si>
     <t>andresnba95</t>
   </si>
   <si>
@@ -12292,6 +12289,9 @@
   </si>
   <si>
     <t>N006 1 pantalla hasta el 18 de octubre 180926-1645x</t>
+  </si>
+  <si>
+    <t>N005 1 pantalla hasta el 18 de octubre 180926-1657s</t>
   </si>
 </sst>
 </file>
@@ -30171,7 +30171,7 @@
   <sheetData>
     <row r="1" spans="1:11" s="30" customFormat="1">
       <c r="A1" s="30" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="B1" s="30">
         <v>60389752</v>
@@ -30183,7 +30183,7 @@
         <v>2012</v>
       </c>
       <c r="E1" s="459" t="s">
-        <v>3652</v>
+        <v>3651</v>
       </c>
       <c r="F1" s="30" t="s">
         <v>2078</v>
@@ -30203,12 +30203,12 @@
         <v>2124</v>
       </c>
       <c r="D2" s="148" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="148" customFormat="1">
       <c r="A3" s="148" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="B3" s="148" t="s">
         <v>2659</v>
@@ -30222,7 +30222,7 @@
     </row>
     <row r="4" spans="1:11" s="30" customFormat="1">
       <c r="A4" s="30" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="B4" s="30">
         <v>60389752</v>
@@ -30234,7 +30234,7 @@
         <v>2010</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="F4" s="30" t="s">
         <v>2078</v>
@@ -30254,7 +30254,7 @@
         <v>2138</v>
       </c>
       <c r="D5" s="148" t="s">
-        <v>3180</v>
+        <v>3179</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="148" customFormat="1">
@@ -30285,7 +30285,7 @@
         <v>2859</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="F7" s="30" t="s">
         <v>2083</v>
@@ -30296,7 +30296,7 @@
     </row>
     <row r="8" spans="1:11" s="148" customFormat="1">
       <c r="A8" s="225" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="B8" s="148">
         <v>66003234</v>
@@ -30305,12 +30305,12 @@
         <v>2244</v>
       </c>
       <c r="D8" s="148" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="148" customFormat="1">
       <c r="A9" s="148" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="B9" s="148" t="s">
         <v>1203</v>
@@ -30327,7 +30327,7 @@
     </row>
     <row r="10" spans="1:11" s="423" customFormat="1">
       <c r="A10" s="423" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="B10" s="423">
         <v>60389752</v>
@@ -30364,7 +30364,7 @@
         <v>2143</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="F13" s="30" t="s">
         <v>2142</v>
@@ -30376,7 +30376,7 @@
     </row>
     <row r="14" spans="1:11" s="148" customFormat="1">
       <c r="A14" s="225" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
       <c r="B14" s="225" t="s">
         <v>1675</v>
@@ -30390,7 +30390,7 @@
     </row>
     <row r="15" spans="1:11" s="148" customFormat="1">
       <c r="A15" s="225" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="B15" s="416">
         <v>62439069</v>
@@ -30404,7 +30404,7 @@
     </row>
     <row r="16" spans="1:11" s="32" customFormat="1">
       <c r="A16" s="30" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="B16" s="284" t="s">
         <v>2198</v>
@@ -30413,10 +30413,10 @@
         <v>1526</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>3141</v>
+        <v>3140</v>
       </c>
       <c r="F16" s="32" t="s">
         <v>1527</v>
@@ -30425,21 +30425,21 @@
         <v>198</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="I16" s="32" t="s">
-        <v>3295</v>
+        <v>3294</v>
       </c>
       <c r="J16" s="32" t="s">
+        <v>3219</v>
+      </c>
+      <c r="K16" s="30" t="s">
         <v>3220</v>
-      </c>
-      <c r="K16" s="30" t="s">
-        <v>3221</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="164" customFormat="1">
       <c r="A17" s="252" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="B17" s="252" t="s">
         <v>1394</v>
@@ -30482,10 +30482,10 @@
         <v>1491</v>
       </c>
       <c r="D19" s="145" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="E19" s="145" t="s">
-        <v>3036</v>
+        <v>3035</v>
       </c>
       <c r="F19" s="145" t="s">
         <v>1361</v>
@@ -30500,7 +30500,7 @@
     </row>
     <row r="20" spans="1:11" s="297" customFormat="1">
       <c r="A20" s="164" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="B20" s="164">
         <v>68444421</v>
@@ -30509,7 +30509,7 @@
         <v>1681</v>
       </c>
       <c r="D20" s="252" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="E20" s="252" t="s">
         <v>1682</v>
@@ -30517,7 +30517,7 @@
     </row>
     <row r="21" spans="1:11" s="297" customFormat="1">
       <c r="A21" s="252" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="B21" s="252">
         <v>62169673</v>
@@ -30526,7 +30526,7 @@
         <v>1686</v>
       </c>
       <c r="D21" s="164" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="E21" s="164" t="s">
         <v>1687</v>
@@ -30534,7 +30534,7 @@
     </row>
     <row r="22" spans="1:11" s="30" customFormat="1">
       <c r="A22" s="32" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="B22" s="32">
         <v>60389752</v>
@@ -30546,7 +30546,7 @@
         <v>2121</v>
       </c>
       <c r="E22" s="459" t="s">
-        <v>3652</v>
+        <v>3651</v>
       </c>
       <c r="F22" s="30" t="s">
         <v>2077</v>
@@ -30557,7 +30557,7 @@
     </row>
     <row r="23" spans="1:11" s="148" customFormat="1">
       <c r="A23" s="225" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="B23" s="148">
         <v>64858241</v>
@@ -30571,7 +30571,7 @@
     </row>
     <row r="24" spans="1:11" s="148" customFormat="1">
       <c r="A24" s="149" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="B24" s="149">
         <v>68934853</v>
@@ -30580,12 +30580,12 @@
         <v>2117</v>
       </c>
       <c r="D24" s="148" t="s">
-        <v>3521</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="30" customFormat="1">
       <c r="A25" s="30" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="B25" s="30">
         <v>63166786</v>
@@ -30597,7 +30597,7 @@
         <v>1523</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="F25" s="30" t="s">
         <v>1361</v>
@@ -30611,7 +30611,7 @@
     </row>
     <row r="26" spans="1:11" s="225" customFormat="1">
       <c r="A26" s="225" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="B26" s="225" t="s">
         <v>1925</v>
@@ -30645,7 +30645,7 @@
     </row>
     <row r="28" spans="1:11" s="30" customFormat="1">
       <c r="A28" s="30" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="B28" s="30">
         <v>60389752</v>
@@ -30657,7 +30657,7 @@
         <v>2007</v>
       </c>
       <c r="E28" s="30" t="s">
-        <v>3266</v>
+        <v>3265</v>
       </c>
       <c r="F28" s="303" t="s">
         <v>2153</v>
@@ -30682,7 +30682,7 @@
     </row>
     <row r="30" spans="1:11" s="164" customFormat="1">
       <c r="A30" s="164" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="B30" s="164">
         <v>62782770</v>
@@ -30696,19 +30696,19 @@
     </row>
     <row r="31" spans="1:11" s="30" customFormat="1">
       <c r="A31" s="30" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="C31" s="251" t="s">
         <v>1900</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="E31" s="454" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="F31" s="30" t="s">
         <v>2028</v>
@@ -30717,21 +30717,21 @@
         <v>198</v>
       </c>
       <c r="H31" s="30" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="I31" s="192" t="s">
-        <v>3136</v>
+        <v>3135</v>
       </c>
       <c r="J31" s="421" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="K31" s="30" t="s">
-        <v>3552</v>
+        <v>3551</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="163" customFormat="1">
       <c r="A32" s="163" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="B32" s="163">
         <v>63487773</v>
@@ -30772,7 +30772,7 @@
         <v>2090</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="F34" s="30" t="s">
         <v>2081</v>
@@ -30783,7 +30783,7 @@
     </row>
     <row r="35" spans="1:11" s="148" customFormat="1">
       <c r="A35" s="148" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="B35" s="148">
         <v>69692470</v>
@@ -30792,7 +30792,7 @@
         <v>1984</v>
       </c>
       <c r="D35" s="148" t="s">
-        <v>3603</v>
+        <v>3602</v>
       </c>
       <c r="E35" s="148" t="s">
         <v>1986</v>
@@ -30823,10 +30823,10 @@
         <v>2005</v>
       </c>
       <c r="D37" s="30" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
       <c r="E37" s="459" t="s">
-        <v>3653</v>
+        <v>3652</v>
       </c>
       <c r="F37" s="30" t="s">
         <v>2071</v>
@@ -30835,21 +30835,21 @@
         <v>198</v>
       </c>
       <c r="H37" s="145" t="s">
-        <v>3663</v>
+        <v>3662</v>
       </c>
       <c r="I37" s="30" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="J37" s="30" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
       <c r="K37" s="30" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="147" customFormat="1">
       <c r="A38" s="147" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="B38" s="147" t="s">
         <v>2657</v>
@@ -30881,16 +30881,16 @@
         <v>2489</v>
       </c>
       <c r="B40" s="32" t="s">
-        <v>3170</v>
+        <v>3169</v>
       </c>
       <c r="C40" s="251" t="s">
         <v>1662</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
       <c r="E40" s="30" t="s">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="F40" s="30" t="s">
         <v>2086</v>
@@ -30899,21 +30899,21 @@
         <v>198</v>
       </c>
       <c r="H40" s="30" t="s">
-        <v>3650</v>
+        <v>3649</v>
       </c>
       <c r="I40" s="32" t="s">
-        <v>3126</v>
+        <v>3125</v>
       </c>
       <c r="J40" s="32" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="K40" s="145" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="163" customFormat="1">
       <c r="A41" s="163" t="s">
-        <v>3636</v>
+        <v>3635</v>
       </c>
       <c r="B41" s="163">
         <v>68381893</v>
@@ -30945,7 +30945,7 @@
     </row>
     <row r="43" spans="1:11" s="30" customFormat="1">
       <c r="A43" s="30" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="B43" s="30">
         <v>60389752</v>
@@ -30957,7 +30957,7 @@
         <v>2032</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="F43" s="30" t="s">
         <v>2118</v>
@@ -30968,7 +30968,7 @@
     </row>
     <row r="44" spans="1:11" s="164" customFormat="1">
       <c r="A44" s="164" t="s">
-        <v>3636</v>
+        <v>3635</v>
       </c>
       <c r="B44" s="164">
         <v>68381893</v>
@@ -30985,7 +30985,7 @@
     </row>
     <row r="45" spans="1:11" s="163" customFormat="1">
       <c r="A45" s="163" t="s">
-        <v>3395</v>
+        <v>3394</v>
       </c>
       <c r="B45" s="163">
         <v>64079861</v>
@@ -31014,7 +31014,7 @@
         <v>2853</v>
       </c>
       <c r="E46" s="30" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="F46" s="30" t="s">
         <v>2102</v>
@@ -31026,7 +31026,7 @@
     </row>
     <row r="47" spans="1:11" s="164" customFormat="1">
       <c r="A47" s="164" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="B47" s="164">
         <v>63183787</v>
@@ -31060,16 +31060,16 @@
         <v>1498</v>
       </c>
       <c r="B49" s="30" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="C49" s="134" t="s">
         <v>1996</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="E49" s="30" t="s">
-        <v>3554</v>
+        <v>3553</v>
       </c>
       <c r="F49" s="30" t="s">
         <v>2089</v>
@@ -31078,16 +31078,16 @@
         <v>198</v>
       </c>
       <c r="H49" s="30" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="I49" s="30" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="J49" s="30" t="s">
-        <v>3606</v>
+        <v>3605</v>
       </c>
       <c r="K49" s="32" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
     </row>
     <row r="50" spans="1:11" s="164" customFormat="1">
@@ -31115,12 +31115,12 @@
         <v>2004</v>
       </c>
       <c r="D51" s="164" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
     </row>
     <row r="52" spans="1:11" s="139" customFormat="1">
       <c r="A52" s="140" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="B52" s="413" t="s">
         <v>1440</v>
@@ -31132,7 +31132,7 @@
         <v>2865</v>
       </c>
       <c r="E52" s="139" t="s">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="F52" s="139" t="s">
         <v>2087</v>
@@ -31141,16 +31141,16 @@
         <v>198</v>
       </c>
       <c r="H52" s="140" t="s">
-        <v>3586</v>
+        <v>3585</v>
       </c>
       <c r="I52" s="140" t="s">
-        <v>3377</v>
+        <v>3376</v>
       </c>
       <c r="J52" s="30" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="K52" s="269" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
     </row>
     <row r="53" spans="1:11" s="164" customFormat="1">
@@ -31191,7 +31191,7 @@
     </row>
     <row r="55" spans="1:11" s="30" customFormat="1">
       <c r="A55" s="30" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="B55" s="30">
         <v>61130088</v>
@@ -31203,7 +31203,7 @@
         <v>2000</v>
       </c>
       <c r="E55" s="30" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="F55" s="30" t="s">
         <v>2103</v>
@@ -31220,10 +31220,10 @@
         <v>60433915</v>
       </c>
       <c r="C56" s="400" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="D56" s="370" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="E56" s="164"/>
     </row>
@@ -31232,19 +31232,19 @@
         <v>2489</v>
       </c>
       <c r="B57" s="163" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="C57" s="400" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="D57" s="370" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="E57" s="164"/>
     </row>
     <row r="58" spans="1:11" s="30" customFormat="1">
       <c r="A58" s="459" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="B58" s="412" t="s">
         <v>2069</v>
@@ -31256,7 +31256,7 @@
         <v>2798</v>
       </c>
       <c r="E58" s="30" t="s">
-        <v>3212</v>
+        <v>3211</v>
       </c>
       <c r="F58" s="30" t="s">
         <v>2115</v>
@@ -31265,16 +31265,16 @@
         <v>198</v>
       </c>
       <c r="H58" s="30" t="s">
-        <v>3300</v>
+        <v>3299</v>
       </c>
       <c r="I58" s="30" t="s">
-        <v>3168</v>
+        <v>3167</v>
       </c>
       <c r="J58" s="30" t="s">
-        <v>3257</v>
+        <v>3256</v>
       </c>
       <c r="K58" s="30" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
     </row>
     <row r="59" spans="1:11" s="388" customFormat="1">
@@ -31289,7 +31289,7 @@
         <v>158</v>
       </c>
       <c r="B61" s="30" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="C61" s="134" t="s">
         <v>2070</v>
@@ -31298,7 +31298,7 @@
         <v>2856</v>
       </c>
       <c r="E61" s="30" t="s">
-        <v>3053</v>
+        <v>3052</v>
       </c>
       <c r="F61" s="30" t="s">
         <v>2071</v>
@@ -31307,21 +31307,21 @@
         <v>198</v>
       </c>
       <c r="H61" s="30" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
       <c r="I61" s="30" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="J61" s="30" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="K61" s="30" t="s">
-        <v>3380</v>
+        <v>3379</v>
       </c>
     </row>
     <row r="62" spans="1:11" s="147" customFormat="1">
       <c r="A62" s="147" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B62" s="147">
         <v>60196388</v>
@@ -31330,7 +31330,7 @@
         <v>1470</v>
       </c>
       <c r="D62" s="371" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
       <c r="E62" s="148" t="s">
         <v>1380</v>
@@ -31338,7 +31338,7 @@
     </row>
     <row r="63" spans="1:11" s="163" customFormat="1">
       <c r="A63" s="163" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="B63" s="163">
         <v>62960567</v>
@@ -31347,13 +31347,13 @@
         <v>2055</v>
       </c>
       <c r="D63" s="370" t="s">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="E63" s="164"/>
     </row>
     <row r="64" spans="1:11" s="30" customFormat="1">
       <c r="A64" s="32" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="B64" s="32" t="s">
         <v>2122</v>
@@ -31362,10 +31362,10 @@
         <v>1661</v>
       </c>
       <c r="D64" s="30" t="s">
-        <v>3294</v>
+        <v>3293</v>
       </c>
       <c r="E64" s="30" t="s">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="F64" s="30" t="s">
         <v>2088</v>
@@ -31374,16 +31374,16 @@
         <v>198</v>
       </c>
       <c r="H64" s="32" t="s">
-        <v>3393</v>
+        <v>3392</v>
       </c>
       <c r="I64" s="32" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="J64" s="30" t="s">
-        <v>3344</v>
+        <v>3343</v>
       </c>
       <c r="K64" s="30" t="s">
-        <v>3169</v>
+        <v>3168</v>
       </c>
     </row>
     <row r="65" spans="1:11" s="164" customFormat="1">
@@ -31405,7 +31405,7 @@
     </row>
     <row r="66" spans="1:11" s="164" customFormat="1">
       <c r="A66" s="252" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="B66" s="164">
         <v>62090364</v>
@@ -31422,7 +31422,7 @@
     </row>
     <row r="67" spans="1:11" s="30" customFormat="1">
       <c r="A67" s="253" t="s">
-        <v>3468</v>
+        <v>3467</v>
       </c>
       <c r="B67" s="284" t="s">
         <v>1908</v>
@@ -31431,10 +31431,10 @@
         <v>1665</v>
       </c>
       <c r="D67" s="30" t="s">
-        <v>2983</v>
+        <v>2982</v>
       </c>
       <c r="E67" s="30" t="s">
-        <v>3607</v>
+        <v>3606</v>
       </c>
       <c r="F67" s="30" t="s">
         <v>2092</v>
@@ -31443,21 +31443,21 @@
         <v>198</v>
       </c>
       <c r="H67" s="30" t="s">
-        <v>3376</v>
+        <v>3375</v>
       </c>
       <c r="I67" s="30" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="J67" s="30" t="s">
-        <v>3494</v>
+        <v>3493</v>
       </c>
       <c r="K67" s="30" t="s">
-        <v>2990</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="68" spans="1:11" s="147" customFormat="1">
       <c r="A68" s="147" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B68" s="147">
         <v>68741448</v>
@@ -31466,13 +31466,13 @@
         <v>1876</v>
       </c>
       <c r="D68" s="371" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="E68" s="148"/>
     </row>
     <row r="69" spans="1:11" s="148" customFormat="1">
       <c r="A69" s="225" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="B69" s="148">
         <v>63018763</v>
@@ -31481,7 +31481,7 @@
         <v>2091</v>
       </c>
       <c r="D69" s="148" t="s">
-        <v>3616</v>
+        <v>3615</v>
       </c>
     </row>
     <row r="70" spans="1:11" s="30" customFormat="1">
@@ -31489,16 +31489,16 @@
         <v>467</v>
       </c>
       <c r="B70" s="32" t="s">
-        <v>3391</v>
+        <v>3390</v>
       </c>
       <c r="C70" s="251" t="s">
         <v>1664</v>
       </c>
       <c r="D70" s="30" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
       <c r="E70" s="30" t="s">
-        <v>3213</v>
+        <v>3212</v>
       </c>
       <c r="F70" s="30" t="s">
         <v>2129</v>
@@ -31507,13 +31507,13 @@
         <v>198</v>
       </c>
       <c r="H70" s="32" t="s">
-        <v>3605</v>
+        <v>3604</v>
       </c>
       <c r="I70" s="145" t="s">
+        <v>3663</v>
+      </c>
+      <c r="J70" s="145" t="s">
         <v>3664</v>
-      </c>
-      <c r="J70" s="145" t="s">
-        <v>3665</v>
       </c>
     </row>
     <row r="71" spans="1:11" s="164" customFormat="1">
@@ -31527,12 +31527,12 @@
         <v>1962</v>
       </c>
       <c r="D71" s="164" t="s">
-        <v>2895</v>
+        <v>2894</v>
       </c>
     </row>
     <row r="72" spans="1:11" s="163" customFormat="1">
       <c r="A72" s="268" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="B72" s="268" t="s">
         <v>1452</v>
@@ -31547,7 +31547,7 @@
     </row>
     <row r="73" spans="1:11" s="30" customFormat="1">
       <c r="A73" s="30" t="s">
-        <v>3296</v>
+        <v>3295</v>
       </c>
       <c r="B73" s="30">
         <v>60389752</v>
@@ -31559,7 +31559,7 @@
         <v>2809</v>
       </c>
       <c r="E73" s="30" t="s">
-        <v>3396</v>
+        <v>3395</v>
       </c>
       <c r="F73" s="30" t="s">
         <v>2027</v>
@@ -31570,7 +31570,7 @@
     </row>
     <row r="74" spans="1:11" s="147" customFormat="1">
       <c r="A74" s="147" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
       <c r="B74" s="147">
         <v>64226974</v>
@@ -31594,7 +31594,7 @@
         <v>1946</v>
       </c>
       <c r="D75" s="148" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="E75" s="148"/>
     </row>
@@ -31609,10 +31609,10 @@
         <v>1875</v>
       </c>
       <c r="D76" s="30" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
       <c r="E76" s="30" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="F76" s="30" t="s">
         <v>2102</v>
@@ -31621,16 +31621,16 @@
         <v>198</v>
       </c>
       <c r="H76" s="30" t="s">
-        <v>3555</v>
+        <v>3554</v>
       </c>
       <c r="I76" s="30" t="s">
-        <v>3604</v>
+        <v>3603</v>
       </c>
       <c r="J76" s="30" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="K76" s="217" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
     </row>
     <row r="77" spans="1:11" s="152" customFormat="1">
@@ -31646,16 +31646,16 @@
         <v>143</v>
       </c>
       <c r="B79" s="30" t="s">
-        <v>2915</v>
+        <v>2914</v>
       </c>
       <c r="C79" s="134" t="s">
         <v>2003</v>
       </c>
       <c r="D79" s="30" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="E79" s="459" t="s">
-        <v>3652</v>
+        <v>3651</v>
       </c>
       <c r="F79" s="30" t="s">
         <v>2082</v>
@@ -31664,21 +31664,21 @@
         <v>198</v>
       </c>
       <c r="H79" s="432" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
       <c r="I79" s="32" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="J79" s="30" t="s">
-        <v>3511</v>
+        <v>3510</v>
       </c>
       <c r="K79" s="30" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
     </row>
     <row r="80" spans="1:11" s="147" customFormat="1">
       <c r="A80" s="149" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="B80" s="147">
         <v>60533053</v>
@@ -31693,7 +31693,7 @@
     </row>
     <row r="81" spans="1:11" s="147" customFormat="1">
       <c r="A81" s="149" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="B81" s="147">
         <v>64720128</v>
@@ -31710,10 +31710,10 @@
     </row>
     <row r="82" spans="1:11" s="30" customFormat="1">
       <c r="A82" s="145" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
       <c r="B82" s="30" t="s">
-        <v>3656</v>
+        <v>3655</v>
       </c>
       <c r="C82" s="22" t="s">
         <v>1901</v>
@@ -31722,7 +31722,7 @@
         <v>2838</v>
       </c>
       <c r="E82" s="30" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="F82" s="30" t="s">
         <v>1902</v>
@@ -31731,16 +31731,16 @@
         <v>198</v>
       </c>
       <c r="H82" s="30" t="s">
-        <v>3467</v>
+        <v>3466</v>
       </c>
       <c r="I82" s="30" t="s">
-        <v>3311</v>
+        <v>3310</v>
       </c>
       <c r="J82" s="30" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="K82" s="30" t="s">
-        <v>3532</v>
+        <v>3531</v>
       </c>
     </row>
     <row r="83" spans="1:11" s="148" customFormat="1">
@@ -31748,13 +31748,13 @@
         <v>1516</v>
       </c>
       <c r="B83" s="225" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="C83" s="398" t="s">
         <v>1959</v>
       </c>
       <c r="D83" s="148" t="s">
-        <v>3654</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="84" spans="1:11" s="280" customFormat="1">
@@ -31782,7 +31782,7 @@
         <v>693</v>
       </c>
       <c r="D85" s="30" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="E85" s="30" t="s">
         <v>1791</v>
@@ -31794,16 +31794,16 @@
         <v>493</v>
       </c>
       <c r="H85" s="30" t="s">
-        <v>3429</v>
-      </c>
-      <c r="I85" s="432" t="s">
-        <v>2881</v>
+        <v>3428</v>
+      </c>
+      <c r="I85" s="439" t="s">
+        <v>3667</v>
       </c>
       <c r="J85" s="30" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="K85" s="215" t="s">
-        <v>3630</v>
+        <v>3629</v>
       </c>
     </row>
     <row r="86" spans="1:11" s="147" customFormat="1">
@@ -31826,7 +31826,7 @@
     </row>
     <row r="87" spans="1:11" s="147" customFormat="1">
       <c r="A87" s="147" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="B87" s="147" t="s">
         <v>909</v>
@@ -31844,16 +31844,16 @@
     </row>
     <row r="88" spans="1:11" s="30" customFormat="1">
       <c r="A88" s="145" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="B88" s="30" t="s">
-        <v>3522</v>
+        <v>3521</v>
       </c>
       <c r="C88" s="153" t="s">
         <v>694</v>
       </c>
       <c r="D88" s="30" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
       <c r="E88" s="30" t="s">
         <v>1085</v>
@@ -31865,21 +31865,21 @@
         <v>1524</v>
       </c>
       <c r="H88" s="145" t="s">
+        <v>3665</v>
+      </c>
+      <c r="I88" s="145" t="s">
         <v>3666</v>
       </c>
-      <c r="I88" s="145" t="s">
-        <v>3667</v>
-      </c>
       <c r="J88" s="32" t="s">
-        <v>3027</v>
+        <v>3026</v>
       </c>
       <c r="K88" s="30" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
     </row>
     <row r="89" spans="1:11" s="147" customFormat="1">
       <c r="A89" s="149" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="B89" s="147">
         <v>64844119</v>
@@ -31897,7 +31897,7 @@
     </row>
     <row r="90" spans="1:11" s="148" customFormat="1">
       <c r="A90" s="225" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="B90" s="148">
         <v>67381873</v>
@@ -31915,7 +31915,7 @@
     </row>
     <row r="91" spans="1:11" s="106" customFormat="1">
       <c r="A91" s="249" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="B91" s="32" t="s">
         <v>1400</v>
@@ -31924,7 +31924,7 @@
         <v>46</v>
       </c>
       <c r="D91" s="106" t="s">
-        <v>3172</v>
+        <v>3171</v>
       </c>
       <c r="E91" s="106" t="s">
         <v>1123</v>
@@ -31936,16 +31936,16 @@
         <v>66</v>
       </c>
       <c r="H91" s="30" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
       <c r="I91" s="31" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="J91" s="32" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="K91" s="30" t="s">
-        <v>3287</v>
+        <v>3286</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="406" customFormat="1">
@@ -31976,7 +31976,7 @@
         <v>1718</v>
       </c>
       <c r="D93" s="148" t="s">
-        <v>3267</v>
+        <v>3266</v>
       </c>
     </row>
     <row r="94" spans="1:11" s="32" customFormat="1">
@@ -31993,7 +31993,7 @@
         <v>1362</v>
       </c>
       <c r="E94" s="32" t="s">
-        <v>3434</v>
+        <v>3433</v>
       </c>
       <c r="F94" s="32" t="s">
         <v>1363</v>
@@ -32005,7 +32005,7 @@
     </row>
     <row r="95" spans="1:11" s="148" customFormat="1">
       <c r="A95" s="148" t="s">
-        <v>3508</v>
+        <v>3507</v>
       </c>
       <c r="B95" s="148" t="s">
         <v>2648</v>
@@ -32022,7 +32022,7 @@
     </row>
     <row r="96" spans="1:11" s="148" customFormat="1">
       <c r="A96" s="148" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="B96" s="148">
         <v>65633205</v>
@@ -32031,7 +32031,7 @@
         <v>1379</v>
       </c>
       <c r="D96" s="148" t="s">
-        <v>3523</v>
+        <v>3522</v>
       </c>
       <c r="E96" s="148" t="s">
         <v>1378</v>
@@ -32042,16 +32042,16 @@
         <v>1419</v>
       </c>
       <c r="B97" s="30" t="s">
-        <v>2914</v>
+        <v>2913</v>
       </c>
       <c r="C97" s="153" t="s">
         <v>1993</v>
       </c>
       <c r="D97" s="30" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
       <c r="E97" s="30" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="F97" s="30" t="s">
         <v>1902</v>
@@ -32060,16 +32060,16 @@
         <v>198</v>
       </c>
       <c r="H97" s="32" t="s">
-        <v>3474</v>
+        <v>3473</v>
       </c>
       <c r="I97" s="30" t="s">
-        <v>3634</v>
+        <v>3633</v>
       </c>
       <c r="J97" s="30" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="K97" s="430" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="98" spans="1:13" s="388" customFormat="1">
@@ -32082,19 +32082,19 @@
     </row>
     <row r="100" spans="1:13" s="30" customFormat="1">
       <c r="A100" s="30" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="B100" s="30" t="s">
-        <v>3647</v>
+        <v>3646</v>
       </c>
       <c r="C100" s="251" t="s">
         <v>2837</v>
       </c>
       <c r="D100" s="30" t="s">
-        <v>3337</v>
+        <v>3336</v>
       </c>
       <c r="E100" s="30" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="F100" s="30" t="s">
         <v>1902</v>
@@ -32103,16 +32103,16 @@
         <v>198</v>
       </c>
       <c r="H100" s="30" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="I100" s="30" t="s">
-        <v>3624</v>
+        <v>3623</v>
       </c>
       <c r="J100" s="30" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="K100" s="30" t="s">
-        <v>3558</v>
+        <v>3557</v>
       </c>
     </row>
     <row r="101" spans="1:13" s="388" customFormat="1">
@@ -32125,19 +32125,19 @@
     </row>
     <row r="103" spans="1:13" s="30" customFormat="1">
       <c r="A103" s="30" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="B103" s="30" t="s">
-        <v>3264</v>
+        <v>3263</v>
       </c>
       <c r="C103" s="251" t="s">
         <v>2879</v>
       </c>
       <c r="D103" s="30" t="s">
+        <v>3186</v>
+      </c>
+      <c r="E103" s="30" t="s">
         <v>3187</v>
-      </c>
-      <c r="E103" s="30" t="s">
-        <v>3188</v>
       </c>
       <c r="F103" s="30" t="s">
         <v>1902</v>
@@ -32146,16 +32146,16 @@
         <v>198</v>
       </c>
       <c r="H103" s="30" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="I103" s="30" t="s">
-        <v>3265</v>
+        <v>3264</v>
       </c>
       <c r="J103" s="30" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="K103" s="30" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -32190,7 +32190,7 @@
     </row>
     <row r="106" spans="1:13" s="30" customFormat="1">
       <c r="A106" s="30" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="B106" s="30">
         <v>62724019</v>
@@ -32199,13 +32199,13 @@
         <v>2878</v>
       </c>
       <c r="D106" s="30" t="s">
+        <v>3030</v>
+      </c>
+      <c r="E106" s="30" t="s">
+        <v>3032</v>
+      </c>
+      <c r="F106" s="30" t="s">
         <v>3031</v>
-      </c>
-      <c r="E106" s="30" t="s">
-        <v>3033</v>
-      </c>
-      <c r="F106" s="30" t="s">
-        <v>3032</v>
       </c>
       <c r="G106" s="30" t="s">
         <v>59</v>
@@ -32257,7 +32257,7 @@
         <v>1982</v>
       </c>
       <c r="E127" s="30" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="F127" t="s">
         <v>1980</v>
@@ -32277,7 +32277,7 @@
         <v>1952</v>
       </c>
       <c r="E128" s="30" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -32291,15 +32291,15 @@
         <v>2719</v>
       </c>
       <c r="D129" s="373" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
       <c r="E129" s="30" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="4" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="B130">
         <v>67046608</v>
@@ -32311,7 +32311,7 @@
         <v>2596</v>
       </c>
       <c r="E130" s="30" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -32328,7 +32328,7 @@
         <v>1958</v>
       </c>
       <c r="E131" s="30" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
     </row>
     <row r="133" spans="1:6" s="121" customFormat="1" ht="23.5">
@@ -32350,7 +32350,7 @@
         <v>2347</v>
       </c>
       <c r="E134" s="30" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="F134" t="s">
         <v>1339</v>
@@ -32370,7 +32370,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="B139">
         <v>64720128</v>
@@ -32399,7 +32399,7 @@
         <v>1969</v>
       </c>
       <c r="D140" s="373" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="E140" s="30" t="s">
         <v>1968</v>
@@ -32430,7 +32430,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="C143" s="1" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -32474,7 +32474,7 @@
         <v>2352</v>
       </c>
       <c r="E153" s="30" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -32482,21 +32482,21 @@
         <v>1498</v>
       </c>
       <c r="B154" t="s">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="C154" t="s">
         <v>2225</v>
       </c>
       <c r="D154" s="373" t="s">
-        <v>3361</v>
+        <v>3360</v>
       </c>
       <c r="E154" s="30" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="B155">
         <v>60183566</v>
@@ -32508,12 +32508,12 @@
         <v>2597</v>
       </c>
       <c r="E155" s="30" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="97" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
       <c r="B156" t="s">
         <v>1164</v>
@@ -32522,10 +32522,10 @@
         <v>2235</v>
       </c>
       <c r="D156" s="373" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
       <c r="E156" s="30" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -32542,7 +32542,7 @@
         <v>2490</v>
       </c>
       <c r="E157" s="30" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -32559,7 +32559,7 @@
         <v>2637</v>
       </c>
       <c r="E158" s="30" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -32573,15 +32573,15 @@
         <v>2510</v>
       </c>
       <c r="D159" s="373" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="E159" s="30" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="B160">
         <v>65133588</v>
@@ -32593,12 +32593,12 @@
         <v>2511</v>
       </c>
       <c r="E160" s="30" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="4" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>1137</v>
@@ -32607,10 +32607,10 @@
         <v>2598</v>
       </c>
       <c r="D161" s="373" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="E161" s="30" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -32624,32 +32624,32 @@
         <v>2513</v>
       </c>
       <c r="D162" s="373" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="E162" s="30" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="97" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
       <c r="B163" s="460" t="s">
         <v>1164</v>
       </c>
       <c r="C163" s="460" t="s">
+        <v>3659</v>
+      </c>
+      <c r="D163" s="373" t="s">
         <v>3660</v>
       </c>
-      <c r="D163" s="373" t="s">
-        <v>3661</v>
-      </c>
       <c r="E163" s="30" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="4" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>2168</v>
@@ -32661,12 +32661,12 @@
         <v>2491</v>
       </c>
       <c r="E164" s="30" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="B165">
         <v>66315726</v>
@@ -32678,12 +32678,12 @@
         <v>2273</v>
       </c>
       <c r="E165" s="30" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="B166">
         <v>64568369</v>
@@ -32695,24 +32695,24 @@
         <v>2273</v>
       </c>
       <c r="E166" s="30" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="B167">
         <v>68818154</v>
       </c>
       <c r="C167" t="s">
-        <v>3365</v>
+        <v>3364</v>
       </c>
       <c r="D167" s="373" t="s">
         <v>2599</v>
       </c>
       <c r="E167" s="30" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -32726,10 +32726,10 @@
         <v>2721</v>
       </c>
       <c r="D168" s="373" t="s">
-        <v>3216</v>
+        <v>3215</v>
       </c>
       <c r="E168" s="30" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -32746,7 +32746,7 @@
         <v>2757</v>
       </c>
       <c r="E169" s="30" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -32763,7 +32763,7 @@
         <v>2488</v>
       </c>
       <c r="E170" s="30" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -32780,12 +32780,12 @@
         <v>2312</v>
       </c>
       <c r="E171" s="30" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="B172">
         <v>66935922</v>
@@ -32794,10 +32794,10 @@
         <v>2324</v>
       </c>
       <c r="D172" s="373" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
       <c r="E172" s="30" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -32811,10 +32811,10 @@
         <v>2325</v>
       </c>
       <c r="D173" s="373" t="s">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="E173" s="30" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -32828,10 +32828,10 @@
         <v>2326</v>
       </c>
       <c r="D174" s="373" t="s">
-        <v>3225</v>
+        <v>3224</v>
       </c>
       <c r="E174" s="30" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -32842,15 +32842,15 @@
         <v>2759</v>
       </c>
       <c r="D175" s="373" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="E175" s="30" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="B176">
         <v>66935922</v>
@@ -32859,27 +32859,27 @@
         <v>2760</v>
       </c>
       <c r="D176" s="220" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="E176" s="30" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="B177">
         <v>64455322</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="D177" s="220" t="s">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="E177" s="30" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -32896,12 +32896,12 @@
         <v>2779</v>
       </c>
       <c r="E178" s="30" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="B179">
         <v>68570552</v>
@@ -32910,15 +32910,15 @@
         <v>2762</v>
       </c>
       <c r="D179" s="220" t="s">
-        <v>3270</v>
+        <v>3269</v>
       </c>
       <c r="E179" s="30" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="B180">
         <v>69964218</v>
@@ -32927,15 +32927,15 @@
         <v>2784</v>
       </c>
       <c r="D180" s="373" t="s">
-        <v>3271</v>
+        <v>3270</v>
       </c>
       <c r="E180" s="30" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="B181">
         <v>63950696</v>
@@ -32947,12 +32947,12 @@
         <v>2785</v>
       </c>
       <c r="E181" s="30" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="4" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="B182" t="s">
         <v>2814</v>
@@ -32964,7 +32964,7 @@
         <v>2785</v>
       </c>
       <c r="E182" s="30" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -32981,12 +32981,12 @@
         <v>2860</v>
       </c>
       <c r="E183" s="30" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="B184">
         <v>63755362</v>
@@ -32995,15 +32995,15 @@
         <v>2849</v>
       </c>
       <c r="D184" s="373" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
       <c r="E184" s="30" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="97" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
       <c r="B185" t="s">
         <v>1164</v>
@@ -33012,15 +33012,15 @@
         <v>2819</v>
       </c>
       <c r="D185" s="373" t="s">
-        <v>3659</v>
+        <v>3658</v>
       </c>
       <c r="E185" s="30" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="B186">
         <v>60240509</v>
@@ -33029,10 +33029,10 @@
         <v>2820</v>
       </c>
       <c r="D186" s="373" t="s">
+        <v>3461</v>
+      </c>
+      <c r="E186" s="30" t="s">
         <v>3462</v>
-      </c>
-      <c r="E186" s="30" t="s">
-        <v>3463</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -33046,10 +33046,10 @@
         <v>2821</v>
       </c>
       <c r="D187" s="373" t="s">
-        <v>3398</v>
+        <v>3397</v>
       </c>
       <c r="E187" s="30" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -33066,7 +33066,7 @@
         <v>2828</v>
       </c>
       <c r="E188" s="30" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -33083,7 +33083,7 @@
         <v>2828</v>
       </c>
       <c r="E189" s="30" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -33100,12 +33100,12 @@
         <v>2828</v>
       </c>
       <c r="E190" s="30" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="4" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>1857</v>
@@ -33117,12 +33117,12 @@
         <v>2828</v>
       </c>
       <c r="E191" s="30" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="97" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
       <c r="B192" t="s">
         <v>1164</v>
@@ -33131,15 +33131,15 @@
         <v>2861</v>
       </c>
       <c r="D192" s="373" t="s">
-        <v>3662</v>
+        <v>3661</v>
       </c>
       <c r="E192" s="30" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="B193">
         <v>69575383</v>
@@ -33148,10 +33148,10 @@
         <v>2826</v>
       </c>
       <c r="D193" s="373" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
       <c r="E193" s="30" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -33168,18 +33168,18 @@
         <v>2828</v>
       </c>
       <c r="E194" s="30" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="C195" s="56" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="D195" t="s">
-        <v>3386</v>
+        <v>3385</v>
       </c>
       <c r="E195" s="30" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="197" spans="1:5" s="391" customFormat="1" ht="23.5">
@@ -33201,49 +33201,49 @@
         <v>2850</v>
       </c>
       <c r="D198" s="373" t="s">
-        <v>3397</v>
+        <v>3396</v>
       </c>
       <c r="E198" s="30" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" t="s">
+        <v>3456</v>
+      </c>
+      <c r="B199" t="s">
         <v>3457</v>
-      </c>
-      <c r="B199" t="s">
-        <v>3458</v>
       </c>
       <c r="C199" t="s">
         <v>2843</v>
       </c>
       <c r="D199" s="373" t="s">
-        <v>3456</v>
+        <v>3455</v>
       </c>
       <c r="E199" s="30" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="B200">
         <v>63617941</v>
       </c>
       <c r="C200" s="22" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="D200" s="373" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="E200" s="30" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
       <c r="B201">
         <v>65633205</v>
@@ -33252,15 +33252,15 @@
         <v>2844</v>
       </c>
       <c r="D201" s="373" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="E201" s="30" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="202" spans="1:5">
       <c r="A202" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="B202">
         <v>62279384</v>
@@ -33269,78 +33269,78 @@
         <v>2845</v>
       </c>
       <c r="D202" s="373" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="E202" s="30" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="203" spans="1:5">
       <c r="A203" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="B203">
         <v>67911756</v>
       </c>
       <c r="C203" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="D203" s="373" t="s">
-        <v>3563</v>
+        <v>3562</v>
       </c>
       <c r="E203" s="30" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="30" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="B204" t="s">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="C204" t="s">
         <v>2846</v>
       </c>
       <c r="D204" s="373" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
       <c r="E204" s="30" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="205" spans="1:5">
       <c r="A205" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="B205">
         <v>64982293</v>
       </c>
       <c r="C205" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="D205" s="373" t="s">
-        <v>3620</v>
+        <v>3619</v>
       </c>
       <c r="E205" s="30" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="206" spans="1:5">
       <c r="A206" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="B206" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
       <c r="C206" t="s">
+        <v>2905</v>
+      </c>
+      <c r="D206" s="373" t="s">
         <v>2906</v>
       </c>
-      <c r="D206" s="373" t="s">
-        <v>2907</v>
-      </c>
       <c r="E206" s="30" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -33351,30 +33351,30 @@
         <v>65344753</v>
       </c>
       <c r="C207" t="s">
-        <v>2908</v>
+        <v>2907</v>
       </c>
       <c r="D207" s="373" t="s">
+        <v>3245</v>
+      </c>
+      <c r="E207" s="30" t="s">
         <v>3246</v>
-      </c>
-      <c r="E207" s="30" t="s">
-        <v>3247</v>
       </c>
     </row>
     <row r="208" spans="1:5">
       <c r="A208" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="B208">
         <v>66496809</v>
       </c>
       <c r="C208" t="s">
-        <v>2922</v>
+        <v>2921</v>
       </c>
       <c r="D208" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="E208" s="30" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -33385,30 +33385,30 @@
         <v>65583706</v>
       </c>
       <c r="C209" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
       <c r="D209" s="373" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
       <c r="E209" s="30" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210" t="s">
-        <v>3410</v>
+        <v>3409</v>
       </c>
       <c r="B210">
         <v>65574051</v>
       </c>
       <c r="C210" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
       <c r="D210" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="E210" s="30" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -33416,16 +33416,16 @@
         <v>2789</v>
       </c>
       <c r="B211" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
       <c r="C211" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
       <c r="D211" s="373" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
       <c r="E211" s="30" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -33436,13 +33436,13 @@
         <v>64881871</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="D212" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
       <c r="E212" s="30" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -33453,30 +33453,30 @@
         <v>68069608</v>
       </c>
       <c r="C213" s="22" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="D213" s="373" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="E213" s="30" t="s">
-        <v>3608</v>
+        <v>3607</v>
       </c>
     </row>
     <row r="214" spans="1:5">
       <c r="A214" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="B214">
         <v>63258169</v>
       </c>
       <c r="C214" s="22" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="D214" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
       <c r="E214" s="30" t="s">
-        <v>3608</v>
+        <v>3607</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -33487,13 +33487,13 @@
         <v>69243886</v>
       </c>
       <c r="C215" s="22" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="D215" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="E215" s="30" t="s">
-        <v>3608</v>
+        <v>3607</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -33504,13 +33504,13 @@
         <v>67752170</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>2987</v>
+        <v>2986</v>
       </c>
       <c r="D216" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="E216" s="30" t="s">
-        <v>3608</v>
+        <v>3607</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -33521,13 +33521,13 @@
         <v>64457890</v>
       </c>
       <c r="C217" t="s">
+        <v>3005</v>
+      </c>
+      <c r="D217" s="373" t="s">
         <v>3006</v>
       </c>
-      <c r="D217" s="373" t="s">
-        <v>3007</v>
-      </c>
       <c r="E217" s="30" t="s">
-        <v>3608</v>
+        <v>3607</v>
       </c>
     </row>
     <row r="231" spans="3:4">
@@ -36299,7 +36299,7 @@
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
     </row>
     <row r="18" spans="4:4">
@@ -36386,7 +36386,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="76" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="B6" s="76">
         <v>64966680</v>
@@ -36401,7 +36401,7 @@
         <v>678</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="G6" s="363" t="s">
         <v>1442</v>
@@ -36422,13 +36422,13 @@
         <v>1845</v>
       </c>
       <c r="D7" s="183" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F7" s="183" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="G7" s="183" t="s">
         <v>1442</v>
@@ -36440,7 +36440,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="193" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="B8" s="193">
         <v>62747874</v>
@@ -36455,7 +36455,7 @@
         <v>362</v>
       </c>
       <c r="F8" s="183" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="G8" s="183" t="s">
         <v>1442</v>
@@ -36482,7 +36482,7 @@
         <v>362</v>
       </c>
       <c r="F9" s="183" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="G9" s="183" t="s">
         <v>1442</v>
@@ -36509,7 +36509,7 @@
         <v>362</v>
       </c>
       <c r="F10" s="183" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="G10" s="183" t="s">
         <v>1442</v>
@@ -36536,7 +36536,7 @@
         <v>362</v>
       </c>
       <c r="F11" s="183" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="G11" s="183" t="s">
         <v>1442</v>
@@ -36560,7 +36560,7 @@
         <v>2518</v>
       </c>
       <c r="E13" s="195" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="F13" s="195" t="s">
         <v>1429</v>
@@ -36586,7 +36586,7 @@
         <v>1846</v>
       </c>
       <c r="E14" s="193" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="F14" s="193" t="s">
         <v>1429</v>
@@ -36612,7 +36612,7 @@
         <v>2793</v>
       </c>
       <c r="E15" s="193" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="F15" s="193" t="s">
         <v>1429</v>
@@ -36626,7 +36626,7 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="183" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="B16" s="183">
         <v>63666666</v>
@@ -36638,7 +36638,7 @@
         <v>2315</v>
       </c>
       <c r="E16" s="193" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="F16" s="193" t="s">
         <v>1429</v>
@@ -36652,7 +36652,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="193" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="B17" s="193">
         <v>64403333</v>
@@ -36664,7 +36664,7 @@
         <v>1507</v>
       </c>
       <c r="E17" s="193" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="F17" s="193" t="s">
         <v>1429</v>
@@ -36690,7 +36690,7 @@
         <v>2157</v>
       </c>
       <c r="E18" s="193" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="F18" s="193" t="s">
         <v>1429</v>
@@ -36704,7 +36704,7 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="195" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="B20" s="195">
         <v>67539485</v>
@@ -36719,7 +36719,7 @@
         <v>362</v>
       </c>
       <c r="F20" s="195" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="G20" s="76" t="s">
         <v>422</v>
@@ -36748,7 +36748,7 @@
         <v>362</v>
       </c>
       <c r="F21" s="193" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="G21" s="183" t="s">
         <v>422</v>
@@ -36777,7 +36777,7 @@
         <v>362</v>
       </c>
       <c r="F22" s="193" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="G22" s="183" t="s">
         <v>422</v>
@@ -36791,7 +36791,7 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="183" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="B23" s="183">
         <v>60389752</v>
@@ -36806,7 +36806,7 @@
         <v>362</v>
       </c>
       <c r="F23" s="193" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="G23" s="183" t="s">
         <v>422</v>
@@ -36835,7 +36835,7 @@
         <v>362</v>
       </c>
       <c r="F24" s="193" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="G24" s="183" t="s">
         <v>422</v>
@@ -36864,7 +36864,7 @@
         <v>362</v>
       </c>
       <c r="F25" s="193" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="G25" s="183" t="s">
         <v>422</v>
@@ -36878,7 +36878,7 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="76" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="B27" s="76">
         <v>60389752</v>
@@ -36893,7 +36893,7 @@
         <v>362</v>
       </c>
       <c r="F27" s="76" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="G27" s="76" t="s">
         <v>1443</v>
@@ -36920,7 +36920,7 @@
         <v>362</v>
       </c>
       <c r="F28" s="183" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="G28" s="183" t="s">
         <v>378</v>
@@ -36934,22 +36934,22 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="183" t="s">
-        <v>3484</v>
+        <v>3483</v>
       </c>
       <c r="B29" s="183">
         <v>65234700</v>
       </c>
       <c r="C29" s="194" t="s">
+        <v>3404</v>
+      </c>
+      <c r="D29" s="183" t="s">
         <v>3405</v>
-      </c>
-      <c r="D29" s="183" t="s">
-        <v>3406</v>
       </c>
       <c r="E29" s="433">
         <v>46243</v>
       </c>
       <c r="F29" s="183" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="G29" s="183" t="s">
         <v>378</v>
@@ -36978,7 +36978,7 @@
         <v>362</v>
       </c>
       <c r="F30" s="183" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="G30" s="183" t="s">
         <v>378</v>
@@ -37007,7 +37007,7 @@
         <v>362</v>
       </c>
       <c r="F31" s="183" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="G31" s="183" t="s">
         <v>378</v>
@@ -37021,7 +37021,7 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="183" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="B32" s="183">
         <v>68241069</v>
@@ -37036,7 +37036,7 @@
         <v>362</v>
       </c>
       <c r="F32" s="183" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="G32" s="183" t="s">
         <v>378</v>
@@ -37059,13 +37059,13 @@
         <v>1665</v>
       </c>
       <c r="D34" s="195" t="s">
-        <v>3569</v>
+        <v>3568</v>
       </c>
       <c r="E34" s="76" t="s">
         <v>2486</v>
       </c>
       <c r="F34" s="195" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="G34" s="76" t="s">
         <v>1442</v>
@@ -37076,7 +37076,7 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="193" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="B35" s="193">
         <v>63465332</v>
@@ -37091,7 +37091,7 @@
         <v>2486</v>
       </c>
       <c r="F35" s="193" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="G35" s="183" t="s">
         <v>1442</v>
@@ -37102,7 +37102,7 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="193" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="B36" s="193">
         <v>63226030</v>
@@ -37117,7 +37117,7 @@
         <v>2486</v>
       </c>
       <c r="F36" s="193" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="G36" s="183" t="s">
         <v>1442</v>
@@ -37128,7 +37128,7 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="193" t="s">
-        <v>3437</v>
+        <v>3436</v>
       </c>
       <c r="B37" s="193">
         <v>69111188</v>
@@ -37143,7 +37143,7 @@
         <v>2486</v>
       </c>
       <c r="F37" s="193" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="G37" s="183" t="s">
         <v>1442</v>
@@ -37169,7 +37169,7 @@
         <v>2486</v>
       </c>
       <c r="F38" s="193" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="G38" s="183" t="s">
         <v>1442</v>
@@ -37195,7 +37195,7 @@
         <v>2486</v>
       </c>
       <c r="F39" s="193" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="G39" s="183" t="s">
         <v>1442</v>
@@ -37208,16 +37208,16 @@
       <c r="A41" s="195"/>
       <c r="B41" s="195"/>
       <c r="C41" s="195" t="s">
+        <v>3451</v>
+      </c>
+      <c r="D41" s="195" t="s">
         <v>3452</v>
-      </c>
-      <c r="D41" s="195" t="s">
-        <v>3453</v>
       </c>
       <c r="E41" s="76" t="s">
         <v>362</v>
       </c>
       <c r="F41" s="195" t="s">
-        <v>3454</v>
+        <v>3453</v>
       </c>
       <c r="G41" s="76" t="s">
         <v>2374</v>
@@ -37237,7 +37237,7 @@
         <v>69563253</v>
       </c>
       <c r="C42" s="193" t="s">
-        <v>3455</v>
+        <v>3454</v>
       </c>
       <c r="D42" s="193" t="s">
         <v>1677</v>
@@ -37251,16 +37251,16 @@
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="234" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
       <c r="B43" s="193" t="s">
         <v>1943</v>
       </c>
       <c r="C43" s="194" t="s">
+        <v>3431</v>
+      </c>
+      <c r="D43" s="193" t="s">
         <v>3432</v>
-      </c>
-      <c r="D43" s="193" t="s">
-        <v>3433</v>
       </c>
       <c r="E43" s="433">
         <v>46304</v>
@@ -37277,7 +37277,7 @@
         <v>62751201</v>
       </c>
       <c r="C44" s="194" t="s">
-        <v>3459</v>
+        <v>3458</v>
       </c>
       <c r="D44" s="183" t="s">
         <v>1357</v>
@@ -37297,10 +37297,10 @@
         <v>68030850</v>
       </c>
       <c r="C45" s="193" t="s">
+        <v>3434</v>
+      </c>
+      <c r="D45" s="193" t="s">
         <v>3435</v>
-      </c>
-      <c r="D45" s="193" t="s">
-        <v>3436</v>
       </c>
       <c r="E45" s="433">
         <v>46243</v>
@@ -37333,16 +37333,16 @@
       <c r="A48" s="195"/>
       <c r="B48" s="195"/>
       <c r="C48" s="195" t="s">
+        <v>3485</v>
+      </c>
+      <c r="D48" s="195" t="s">
         <v>3486</v>
       </c>
-      <c r="D48" s="195" t="s">
+      <c r="E48" s="76" t="s">
         <v>3487</v>
       </c>
-      <c r="E48" s="76" t="s">
+      <c r="F48" s="195" t="s">
         <v>3488</v>
-      </c>
-      <c r="F48" s="195" t="s">
-        <v>3489</v>
       </c>
       <c r="G48" s="76" t="s">
         <v>1442</v>
@@ -37379,10 +37379,10 @@
         <v>61548403</v>
       </c>
       <c r="C50" s="194" t="s">
+        <v>3489</v>
+      </c>
+      <c r="D50" s="193" t="s">
         <v>3490</v>
-      </c>
-      <c r="D50" s="193" t="s">
-        <v>3491</v>
       </c>
       <c r="E50" s="433">
         <v>46304</v>
@@ -37395,7 +37395,7 @@
       <c r="C51" s="456"/>
       <c r="D51" s="456"/>
       <c r="E51" s="433" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
       <c r="F51" s="193"/>
       <c r="G51" s="183"/>
@@ -37415,7 +37415,7 @@
         <v>936</v>
       </c>
       <c r="E52" s="433" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
       <c r="F52" s="193"/>
       <c r="G52" s="183"/>
@@ -37423,19 +37423,19 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="183" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="B53" s="183">
         <v>64543204</v>
       </c>
       <c r="C53" s="194" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="D53" s="183" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="E53" s="433" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
       <c r="F53" s="193"/>
       <c r="G53" s="183"/>
@@ -37452,13 +37452,13 @@
         <v>1664</v>
       </c>
       <c r="D55" s="195" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="E55" s="76" t="s">
         <v>2486</v>
       </c>
       <c r="F55" s="195" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="G55" s="76" t="s">
         <v>1442</v>
@@ -37484,7 +37484,7 @@
         <v>2486</v>
       </c>
       <c r="F56" s="193" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="G56" s="183" t="s">
         <v>1442</v>
@@ -37504,13 +37504,13 @@
         <v>2610</v>
       </c>
       <c r="D57" s="193" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="E57" s="183" t="s">
         <v>2486</v>
       </c>
       <c r="F57" s="193" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="G57" s="183" t="s">
         <v>1442</v>
@@ -37536,7 +37536,7 @@
         <v>2486</v>
       </c>
       <c r="F58" s="193" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="G58" s="183" t="s">
         <v>1442</v>
@@ -37547,7 +37547,7 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="193" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="B59" s="193">
         <v>65174343</v>
@@ -37562,7 +37562,7 @@
         <v>2486</v>
       </c>
       <c r="F59" s="193" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="G59" s="183" t="s">
         <v>1442</v>
@@ -37579,16 +37579,16 @@
         <v>63062167</v>
       </c>
       <c r="C60" s="193" t="s">
-        <v>3317</v>
+        <v>3316</v>
       </c>
       <c r="D60" s="193" t="s">
-        <v>3352</v>
+        <v>3351</v>
       </c>
       <c r="E60" s="183" t="s">
         <v>2486</v>
       </c>
       <c r="F60" s="193" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="G60" s="183" t="s">
         <v>1442</v>
@@ -37614,7 +37614,7 @@
         <v>2486</v>
       </c>
       <c r="F62" s="195" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="G62" s="76" t="s">
         <v>1442</v>
@@ -37640,7 +37640,7 @@
         <v>2486</v>
       </c>
       <c r="F63" s="193" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="G63" s="183" t="s">
         <v>1442</v>
@@ -37651,7 +37651,7 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="183" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="B64" s="183">
         <v>64403333</v>
@@ -37666,7 +37666,7 @@
         <v>2486</v>
       </c>
       <c r="F64" s="193" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="G64" s="183" t="s">
         <v>1442</v>
@@ -37677,7 +37677,7 @@
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="193" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
       <c r="B65" s="193">
         <v>68030850</v>
@@ -37692,7 +37692,7 @@
         <v>2486</v>
       </c>
       <c r="F65" s="193" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="G65" s="183" t="s">
         <v>1442</v>
@@ -37703,7 +37703,7 @@
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="183" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="B66" s="183">
         <v>65003516</v>
@@ -37718,7 +37718,7 @@
         <v>2486</v>
       </c>
       <c r="F66" s="193" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="G66" s="183" t="s">
         <v>1442</v>
@@ -37744,7 +37744,7 @@
         <v>2486</v>
       </c>
       <c r="F67" s="193" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="G67" s="183" t="s">
         <v>1442</v>
@@ -37755,7 +37755,7 @@
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="76" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="B69" s="76">
         <v>64147946</v>
@@ -37767,7 +37767,7 @@
         <v>2449</v>
       </c>
       <c r="E69" s="76" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="F69" s="195" t="s">
         <v>2450</v>
@@ -37781,7 +37781,7 @@
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="193" t="s">
-        <v>2900</v>
+        <v>2899</v>
       </c>
       <c r="B70" s="193">
         <v>62646186</v>
@@ -37793,7 +37793,7 @@
         <v>2454</v>
       </c>
       <c r="E70" s="183" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="F70" s="193" t="s">
         <v>2450</v>
@@ -37819,7 +37819,7 @@
         <v>2289</v>
       </c>
       <c r="E71" s="183" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="F71" s="193" t="s">
         <v>2450</v>
@@ -37845,7 +37845,7 @@
         <v>2745</v>
       </c>
       <c r="E72" s="183" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="F72" s="183" t="s">
         <v>2450</v>
@@ -37872,7 +37872,7 @@
         <v>2054</v>
       </c>
       <c r="E73" s="183" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="F73" s="183" t="s">
         <v>2450</v>
@@ -37899,7 +37899,7 @@
         <v>2445</v>
       </c>
       <c r="E74" s="183" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="F74" s="183" t="s">
         <v>2450</v>
@@ -37926,7 +37926,7 @@
         <v>1724</v>
       </c>
       <c r="E76" s="76" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="F76" s="195" t="s">
         <v>2448</v>
@@ -37950,7 +37950,7 @@
         <v>2329</v>
       </c>
       <c r="E77" s="183" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="F77" s="193" t="s">
         <v>2448</v>
@@ -37974,7 +37974,7 @@
         <v>1238</v>
       </c>
       <c r="E78" s="183" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="F78" s="193" t="s">
         <v>2448</v>
@@ -37986,7 +37986,7 @@
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="183" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="B79" s="183">
         <v>62820256</v>
@@ -37998,7 +37998,7 @@
         <v>2357</v>
       </c>
       <c r="E79" s="183" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="F79" s="193" t="s">
         <v>2448</v>
@@ -38010,19 +38010,19 @@
     </row>
     <row r="80" spans="1:9">
       <c r="A80" s="183" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="B80" s="183">
         <v>69563253</v>
       </c>
       <c r="C80" s="194" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D80" s="183" t="s">
         <v>1005</v>
       </c>
       <c r="E80" s="183" t="s">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="F80" s="193" t="s">
         <v>2448</v>
@@ -38034,7 +38034,7 @@
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="183" t="s">
-        <v>3573</v>
+        <v>3572</v>
       </c>
       <c r="B81" s="183">
         <v>63233935</v>
@@ -38043,10 +38043,10 @@
         <v>2376</v>
       </c>
       <c r="D81" s="183" t="s">
-        <v>3570</v>
+        <v>3569</v>
       </c>
       <c r="E81" s="183" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="F81" s="193" t="s">
         <v>2448</v>
@@ -38058,7 +38058,7 @@
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="76" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="B83" s="76">
         <v>63574980</v>
@@ -38073,7 +38073,7 @@
         <v>1344</v>
       </c>
       <c r="F83" s="195" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="G83" s="76" t="s">
         <v>1442</v>
@@ -38100,7 +38100,7 @@
         <v>1344</v>
       </c>
       <c r="F84" s="183" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="G84" s="183" t="s">
         <v>1442</v>
@@ -38118,7 +38118,7 @@
         <v>68483411</v>
       </c>
       <c r="C85" s="183" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="D85" s="183" t="s">
         <v>2155</v>
@@ -38127,7 +38127,7 @@
         <v>1344</v>
       </c>
       <c r="F85" s="183" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="G85" s="183" t="s">
         <v>1442</v>
@@ -38142,19 +38142,19 @@
         <v>2503</v>
       </c>
       <c r="B86" s="183" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="C86" s="194" t="s">
         <v>2670</v>
       </c>
       <c r="D86" s="183" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
       <c r="E86" s="183" t="s">
         <v>1344</v>
       </c>
       <c r="F86" s="183" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="G86" s="183" t="s">
         <v>1442</v>
@@ -38166,7 +38166,7 @@
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="183" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="B87" s="183">
         <v>69904406</v>
@@ -38175,13 +38175,13 @@
         <v>2671</v>
       </c>
       <c r="D87" s="183" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="E87" s="183" t="s">
         <v>1344</v>
       </c>
       <c r="F87" s="183" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="G87" s="183" t="s">
         <v>1442</v>
@@ -38193,7 +38193,7 @@
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="183" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="B88" s="183" t="s">
         <v>2689</v>
@@ -38208,7 +38208,7 @@
         <v>1344</v>
       </c>
       <c r="F88" s="183" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="G88" s="183" t="s">
         <v>1442</v>
@@ -38235,7 +38235,7 @@
         <v>1654</v>
       </c>
       <c r="F90" s="195" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
       <c r="G90" s="76" t="s">
         <v>1442</v>
@@ -38259,7 +38259,7 @@
         <v>1654</v>
       </c>
       <c r="F91" s="193" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
       <c r="G91" s="183" t="s">
         <v>1442</v>
@@ -38283,7 +38283,7 @@
         <v>1654</v>
       </c>
       <c r="F92" s="193" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
       <c r="G92" s="183" t="s">
         <v>1442</v>
@@ -38307,7 +38307,7 @@
         <v>1654</v>
       </c>
       <c r="F93" s="193" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
       <c r="G93" s="183" t="s">
         <v>1442</v>
@@ -38316,7 +38316,7 @@
     </row>
     <row r="94" spans="1:9">
       <c r="A94" s="183" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="B94" s="183">
         <v>64403333</v>
@@ -38331,7 +38331,7 @@
         <v>1654</v>
       </c>
       <c r="F94" s="193" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
       <c r="G94" s="183" t="s">
         <v>1442</v>
@@ -38355,7 +38355,7 @@
         <v>1654</v>
       </c>
       <c r="F95" s="193" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
       <c r="G95" s="183" t="s">
         <v>1442</v>
@@ -38364,7 +38364,7 @@
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="195" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="B97" s="195">
         <v>64476521</v>
@@ -38379,7 +38379,7 @@
         <v>2486</v>
       </c>
       <c r="F97" s="195" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="G97" s="76" t="s">
         <v>1442</v>
@@ -38390,7 +38390,7 @@
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="193" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
       <c r="B98" s="193">
         <v>60389752</v>
@@ -38399,13 +38399,13 @@
         <v>2651</v>
       </c>
       <c r="D98" s="193" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="E98" s="183" t="s">
         <v>2486</v>
       </c>
       <c r="F98" s="193" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="G98" s="183" t="s">
         <v>1442</v>
@@ -38416,7 +38416,7 @@
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="183" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
       <c r="B99" s="183">
         <v>60389752</v>
@@ -38431,7 +38431,7 @@
         <v>2486</v>
       </c>
       <c r="F99" s="193" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="G99" s="183" t="s">
         <v>1442</v>
@@ -38442,7 +38442,7 @@
     </row>
     <row r="100" spans="1:9">
       <c r="A100" s="193" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="B100" s="193">
         <v>60389752</v>
@@ -38457,7 +38457,7 @@
         <v>2486</v>
       </c>
       <c r="F100" s="193" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="G100" s="183" t="s">
         <v>1442</v>
@@ -38468,7 +38468,7 @@
     </row>
     <row r="101" spans="1:9">
       <c r="A101" s="183" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="B101" s="183">
         <v>60533053</v>
@@ -38483,7 +38483,7 @@
         <v>2486</v>
       </c>
       <c r="F101" s="193" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="G101" s="183" t="s">
         <v>1442</v>
@@ -38494,7 +38494,7 @@
     </row>
     <row r="102" spans="1:9">
       <c r="A102" s="193" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="B102" s="193">
         <v>67381873</v>
@@ -38503,13 +38503,13 @@
         <v>2286</v>
       </c>
       <c r="D102" s="193" t="s">
-        <v>3285</v>
+        <v>3284</v>
       </c>
       <c r="E102" s="183" t="s">
         <v>2486</v>
       </c>
       <c r="F102" s="193" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="G102" s="183" t="s">
         <v>1442</v>
@@ -38520,7 +38520,7 @@
     </row>
     <row r="104" spans="1:9">
       <c r="A104" s="195" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="B104" s="195">
         <v>66082581</v>
@@ -38532,7 +38532,7 @@
         <v>2297</v>
       </c>
       <c r="E104" s="76" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="F104" s="195" t="s">
         <v>422</v>
@@ -38546,7 +38546,7 @@
     </row>
     <row r="105" spans="1:9">
       <c r="A105" s="193" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="B105" s="193" t="s">
         <v>2709</v>
@@ -38558,7 +38558,7 @@
         <v>2302</v>
       </c>
       <c r="E105" s="183" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="F105" s="193" t="s">
         <v>422</v>
@@ -38572,7 +38572,7 @@
     </row>
     <row r="106" spans="1:9">
       <c r="A106" s="193" t="s">
-        <v>3307</v>
+        <v>3306</v>
       </c>
       <c r="B106" s="193">
         <v>62723048</v>
@@ -38581,10 +38581,10 @@
         <v>2303</v>
       </c>
       <c r="D106" s="193" t="s">
-        <v>3306</v>
+        <v>3305</v>
       </c>
       <c r="E106" s="183" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="F106" s="193" t="s">
         <v>422</v>
@@ -38604,13 +38604,13 @@
         <v>69017426</v>
       </c>
       <c r="C107" s="194" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="D107" s="193" t="s">
         <v>2460</v>
       </c>
       <c r="E107" s="183" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="F107" s="193" t="s">
         <v>422</v>
@@ -38636,7 +38636,7 @@
         <v>2306</v>
       </c>
       <c r="E108" s="183" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="F108" s="193" t="s">
         <v>422</v>
@@ -38656,13 +38656,13 @@
         <v>62723048</v>
       </c>
       <c r="C109" s="194" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="D109" s="193" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="E109" s="183" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="F109" s="193" t="s">
         <v>422</v>
@@ -38682,16 +38682,16 @@
         <v>68310153</v>
       </c>
       <c r="C111" s="195" t="s">
+        <v>3001</v>
+      </c>
+      <c r="D111" s="195" t="s">
         <v>3002</v>
-      </c>
-      <c r="D111" s="195" t="s">
-        <v>3003</v>
       </c>
       <c r="E111" s="76" t="s">
         <v>362</v>
       </c>
       <c r="F111" s="195" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="G111" s="76" t="s">
         <v>1344</v>
@@ -38705,7 +38705,7 @@
     </row>
     <row r="112" spans="1:9">
       <c r="A112" s="193" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="B112" s="193">
         <v>63910392</v>
@@ -38718,7 +38718,7 @@
         <v>362</v>
       </c>
       <c r="F112" s="193" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="G112" s="183" t="s">
         <v>1344</v>
@@ -38747,7 +38747,7 @@
         <v>2486</v>
       </c>
       <c r="F113" s="193" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="G113" s="183" t="s">
         <v>1344</v>
@@ -38767,16 +38767,16 @@
         <v>62360487</v>
       </c>
       <c r="C114" s="194" t="s">
+        <v>3317</v>
+      </c>
+      <c r="D114" s="183" t="s">
         <v>3318</v>
-      </c>
-      <c r="D114" s="183" t="s">
-        <v>3319</v>
       </c>
       <c r="E114" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F114" s="193" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="G114" s="183" t="s">
         <v>1344</v>
@@ -38796,16 +38796,16 @@
         <v>62085821</v>
       </c>
       <c r="C115" s="193" t="s">
+        <v>3319</v>
+      </c>
+      <c r="D115" s="193" t="s">
         <v>3320</v>
-      </c>
-      <c r="D115" s="193" t="s">
-        <v>3321</v>
       </c>
       <c r="E115" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F115" s="193" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="G115" s="183" t="s">
         <v>1344</v>
@@ -38825,16 +38825,16 @@
         <v>64403333</v>
       </c>
       <c r="C116" s="193" t="s">
+        <v>3321</v>
+      </c>
+      <c r="D116" s="193" t="s">
         <v>3322</v>
-      </c>
-      <c r="D116" s="193" t="s">
-        <v>3323</v>
       </c>
       <c r="E116" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F116" s="193" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="G116" s="183" t="s">
         <v>1344</v>
@@ -38866,7 +38866,7 @@
         <v>2319</v>
       </c>
       <c r="E118" s="76" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="F118" s="76" t="s">
         <v>422</v>
@@ -38893,7 +38893,7 @@
         <v>2321</v>
       </c>
       <c r="E119" s="183" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="F119" s="193" t="s">
         <v>422</v>
@@ -38919,7 +38919,7 @@
         <v>2323</v>
       </c>
       <c r="E120" s="183" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="F120" s="193" t="s">
         <v>422</v>
@@ -38933,19 +38933,19 @@
     </row>
     <row r="121" spans="1:9">
       <c r="A121" s="183" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="B121" s="183">
         <v>64403333</v>
       </c>
       <c r="C121" s="183" t="s">
+        <v>3323</v>
+      </c>
+      <c r="D121" s="183" t="s">
         <v>3324</v>
       </c>
-      <c r="D121" s="183" t="s">
-        <v>3325</v>
-      </c>
       <c r="E121" s="183" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="F121" s="193" t="s">
         <v>422</v>
@@ -38971,7 +38971,7 @@
         <v>377</v>
       </c>
       <c r="E122" s="183" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="F122" s="193" t="s">
         <v>422</v>
@@ -38997,7 +38997,7 @@
         <v>1650</v>
       </c>
       <c r="E123" s="183" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="F123" s="193" t="s">
         <v>422</v>
@@ -39026,7 +39026,7 @@
         <v>678</v>
       </c>
       <c r="F125" s="76" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="G125" s="76" t="s">
         <v>422</v>
@@ -39055,7 +39055,7 @@
         <v>362</v>
       </c>
       <c r="F126" s="183" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="G126" s="183" t="s">
         <v>422</v>
@@ -39084,7 +39084,7 @@
         <v>362</v>
       </c>
       <c r="F127" s="183" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="G127" s="183" t="s">
         <v>422</v>
@@ -39111,7 +39111,7 @@
         <v>362</v>
       </c>
       <c r="F128" s="183" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="G128" s="183" t="s">
         <v>422</v>
@@ -39125,7 +39125,7 @@
     </row>
     <row r="129" spans="1:9">
       <c r="A129" s="183" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="B129" s="183">
         <v>66230961</v>
@@ -39140,7 +39140,7 @@
         <v>362</v>
       </c>
       <c r="F129" s="183" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="G129" s="183" t="s">
         <v>422</v>
@@ -39154,7 +39154,7 @@
     </row>
     <row r="130" spans="1:9">
       <c r="A130" s="183" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="B130" s="183">
         <v>69888391</v>
@@ -39169,7 +39169,7 @@
         <v>362</v>
       </c>
       <c r="F130" s="183" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="G130" s="183" t="s">
         <v>422</v>
@@ -39198,7 +39198,7 @@
         <v>2368</v>
       </c>
       <c r="F132" s="195" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="G132" s="76" t="s">
         <v>1442</v>
@@ -39215,7 +39215,7 @@
         <v>64226974</v>
       </c>
       <c r="C133" s="183" t="s">
-        <v>3472</v>
+        <v>3471</v>
       </c>
       <c r="D133" s="193" t="s">
         <v>377</v>
@@ -39224,7 +39224,7 @@
         <v>2368</v>
       </c>
       <c r="F133" s="193" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="G133" s="183" t="s">
         <v>1442</v>
@@ -39250,7 +39250,7 @@
         <v>2368</v>
       </c>
       <c r="F134" s="193" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="G134" s="183" t="s">
         <v>1442</v>
@@ -39276,7 +39276,7 @@
         <v>2368</v>
       </c>
       <c r="F135" s="193" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="G135" s="183" t="s">
         <v>1442</v>
@@ -39302,7 +39302,7 @@
         <v>2368</v>
       </c>
       <c r="F136" s="193" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="G136" s="183" t="s">
         <v>1442</v>
@@ -39328,7 +39328,7 @@
         <v>2368</v>
       </c>
       <c r="F137" s="193" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="G137" s="183" t="s">
         <v>1442</v>
@@ -39339,22 +39339,22 @@
     </row>
     <row r="139" spans="1:9">
       <c r="A139" s="195" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="B139" s="195" t="s">
         <v>2162</v>
       </c>
       <c r="C139" s="195" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
       <c r="D139" s="195" t="s">
-        <v>3240</v>
+        <v>3239</v>
       </c>
       <c r="E139" s="76" t="s">
         <v>2368</v>
       </c>
       <c r="F139" s="195" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="G139" s="76" t="s">
         <v>1442</v>
@@ -39371,16 +39371,16 @@
         <v>66319486</v>
       </c>
       <c r="C140" s="193" t="s">
-        <v>3326</v>
+        <v>3325</v>
       </c>
       <c r="D140" s="193" t="s">
-        <v>3369</v>
+        <v>3368</v>
       </c>
       <c r="E140" s="183" t="s">
         <v>2368</v>
       </c>
       <c r="F140" s="193" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="G140" s="183" t="s">
         <v>1442</v>
@@ -39391,7 +39391,7 @@
     </row>
     <row r="141" spans="1:9">
       <c r="A141" s="183" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="B141" s="183">
         <v>60389752</v>
@@ -39406,7 +39406,7 @@
         <v>2368</v>
       </c>
       <c r="F141" s="193" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="G141" s="183" t="s">
         <v>1442</v>
@@ -39420,7 +39420,7 @@
         <v>2368</v>
       </c>
       <c r="F142" s="193" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="G142" s="183" t="s">
         <v>1442</v>
@@ -39446,7 +39446,7 @@
         <v>2368</v>
       </c>
       <c r="F143" s="193" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="G143" s="183" t="s">
         <v>1442</v>
@@ -39472,7 +39472,7 @@
         <v>2368</v>
       </c>
       <c r="F144" s="193" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="G144" s="183" t="s">
         <v>1442</v>
@@ -39498,7 +39498,7 @@
         <v>2486</v>
       </c>
       <c r="F146" s="195" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="G146" s="76" t="s">
         <v>1442</v>
@@ -39509,13 +39509,13 @@
     </row>
     <row r="147" spans="1:9">
       <c r="A147" s="193" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="B147" s="193">
         <v>67697112</v>
       </c>
       <c r="C147" s="193" t="s">
-        <v>3351</v>
+        <v>3350</v>
       </c>
       <c r="D147" s="193" t="s">
         <v>1306</v>
@@ -39524,7 +39524,7 @@
         <v>2486</v>
       </c>
       <c r="F147" s="193" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="G147" s="183" t="s">
         <v>1442</v>
@@ -39535,7 +39535,7 @@
     </row>
     <row r="148" spans="1:9">
       <c r="A148" s="183" t="s">
-        <v>3395</v>
+        <v>3394</v>
       </c>
       <c r="B148" s="183">
         <v>62560788</v>
@@ -39550,7 +39550,7 @@
         <v>2486</v>
       </c>
       <c r="F148" s="193" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="G148" s="183" t="s">
         <v>1442</v>
@@ -39561,7 +39561,7 @@
     </row>
     <row r="149" spans="1:9">
       <c r="A149" s="193" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="B149" s="193">
         <v>64403333</v>
@@ -39576,7 +39576,7 @@
         <v>2486</v>
       </c>
       <c r="F149" s="193" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="G149" s="183" t="s">
         <v>1442</v>
@@ -39587,22 +39587,22 @@
     </row>
     <row r="150" spans="1:9">
       <c r="A150" s="193" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
       <c r="B150" s="193">
         <v>60125401</v>
       </c>
       <c r="C150" s="194" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="D150" s="193" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="E150" s="183" t="s">
         <v>2486</v>
       </c>
       <c r="F150" s="193" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="G150" s="183" t="s">
         <v>1442</v>
@@ -39628,7 +39628,7 @@
         <v>2486</v>
       </c>
       <c r="F151" s="193" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="G151" s="183" t="s">
         <v>1442</v>
@@ -39654,7 +39654,7 @@
         <v>362</v>
       </c>
       <c r="F153" s="195" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
       <c r="G153" s="76" t="s">
         <v>2374</v>
@@ -39668,22 +39668,22 @@
     </row>
     <row r="154" spans="1:9">
       <c r="A154" s="193" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="B154" s="193">
         <v>65963732</v>
       </c>
       <c r="C154" s="194" t="s">
+        <v>3308</v>
+      </c>
+      <c r="D154" s="193" t="s">
         <v>3309</v>
-      </c>
-      <c r="D154" s="193" t="s">
-        <v>3310</v>
       </c>
       <c r="E154" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F154" s="193" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
       <c r="G154" s="183" t="s">
         <v>2374</v>
@@ -39697,7 +39697,7 @@
     </row>
     <row r="155" spans="1:9">
       <c r="A155" s="183" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="B155" s="183">
         <v>60071688</v>
@@ -39706,13 +39706,13 @@
         <v>2358</v>
       </c>
       <c r="D155" s="183" t="s">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="E155" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F155" s="193" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
       <c r="G155" s="183" t="s">
         <v>2374</v>
@@ -39741,7 +39741,7 @@
         <v>362</v>
       </c>
       <c r="F156" s="193" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
       <c r="G156" s="183" t="s">
         <v>2374</v>
@@ -39770,7 +39770,7 @@
         <v>362</v>
       </c>
       <c r="F157" s="193" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
       <c r="G157" s="183" t="s">
         <v>2374</v>
@@ -39784,22 +39784,22 @@
     </row>
     <row r="158" spans="1:9">
       <c r="A158" s="183" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="B158" s="183">
         <v>64403333</v>
       </c>
       <c r="C158" s="194" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="D158" s="444" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="E158" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F158" s="193" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
       <c r="G158" s="183" t="s">
         <v>2374</v>
@@ -39830,7 +39830,7 @@
       <c r="A183" s="221"/>
       <c r="B183" s="221"/>
       <c r="C183" s="221" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="D183" s="221"/>
       <c r="E183" s="221"/>
@@ -39838,25 +39838,25 @@
     </row>
     <row r="184" spans="1:9">
       <c r="A184" s="76" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="B184" s="76">
         <v>67836337</v>
       </c>
       <c r="C184" s="195" t="s">
+        <v>3514</v>
+      </c>
+      <c r="D184" s="195" t="s">
         <v>3515</v>
-      </c>
-      <c r="D184" s="195" t="s">
-        <v>3516</v>
       </c>
       <c r="E184" s="434">
         <v>46243</v>
       </c>
       <c r="F184" s="76" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="G184" s="195" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="H184" s="76" t="s">
         <v>1980</v>
@@ -39864,19 +39864,19 @@
     </row>
     <row r="185" spans="1:9">
       <c r="A185" s="193" t="s">
-        <v>3573</v>
+        <v>3572</v>
       </c>
       <c r="B185" s="193">
         <v>60196388</v>
       </c>
       <c r="C185" s="193" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
       <c r="D185" s="447" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="E185" s="433" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
       <c r="F185" s="193"/>
       <c r="G185" s="183"/>
@@ -39884,19 +39884,19 @@
     </row>
     <row r="186" spans="1:9">
       <c r="A186" s="183" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="B186" s="183">
         <v>64403333</v>
       </c>
       <c r="C186" s="191" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="D186" s="183" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
       <c r="E186" s="433" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
       <c r="F186" s="193"/>
       <c r="G186" s="183"/>
@@ -39904,19 +39904,19 @@
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="193" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="B187" s="193">
         <v>68071614</v>
       </c>
       <c r="C187" s="193" t="s">
+        <v>3608</v>
+      </c>
+      <c r="D187" s="193" t="s">
         <v>3609</v>
       </c>
-      <c r="D187" s="193" t="s">
+      <c r="E187" s="433" t="s">
         <v>3610</v>
-      </c>
-      <c r="E187" s="433" t="s">
-        <v>3611</v>
       </c>
       <c r="F187" s="193"/>
       <c r="G187" s="183"/>
@@ -39930,13 +39930,13 @@
         <v>63950696</v>
       </c>
       <c r="C188" s="457" t="s">
-        <v>3639</v>
+        <v>3638</v>
       </c>
       <c r="D188" s="457" t="s">
         <v>2805</v>
       </c>
       <c r="E188" s="433" t="s">
-        <v>3640</v>
+        <v>3639</v>
       </c>
       <c r="F188" s="458"/>
       <c r="G188" s="448"/>
@@ -39988,7 +39988,7 @@
         <v>316</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
       <c r="E194" s="30"/>
       <c r="F194"/>
@@ -40014,7 +40014,7 @@
         <v>439</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="E196" s="30"/>
       <c r="F196"/>
@@ -40025,7 +40025,7 @@
         <v>26</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>3609</v>
+        <v>3608</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -40033,7 +40033,7 @@
         <v>1327</v>
       </c>
       <c r="D198" s="429" t="s">
-        <v>3639</v>
+        <v>3638</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -40041,7 +40041,7 @@
         <v>1661</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>3324</v>
+        <v>3323</v>
       </c>
       <c r="F199" s="394"/>
     </row>
@@ -40050,7 +40050,7 @@
         <v>1308</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>3326</v>
+        <v>3325</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -40058,7 +40058,7 @@
         <v>406</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>3432</v>
+        <v>3431</v>
       </c>
     </row>
     <row r="202" spans="1:9">
@@ -40066,7 +40066,7 @@
         <v>708</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -40074,7 +40074,7 @@
         <v>281</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>3451</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="204" spans="1:9">
@@ -40082,7 +40082,7 @@
         <v>2376</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>3452</v>
+        <v>3451</v>
       </c>
     </row>
     <row r="205" spans="1:9">
@@ -40092,7 +40092,7 @@
         <v>465</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>3455</v>
+        <v>3454</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -40100,7 +40100,7 @@
         <v>219</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>3459</v>
+        <v>3458</v>
       </c>
     </row>
     <row r="207" spans="1:9">
@@ -40108,7 +40108,7 @@
         <v>427</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>3472</v>
+        <v>3471</v>
       </c>
     </row>
     <row r="208" spans="1:9">
@@ -40116,7 +40116,7 @@
         <v>1052</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>3486</v>
+        <v>3485</v>
       </c>
     </row>
     <row r="223" spans="1:9">
@@ -41331,7 +41331,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="B3">
         <v>62349088</v>
@@ -41352,10 +41352,10 @@
         <v>705</v>
       </c>
       <c r="H3" t="s">
-        <v>3504</v>
+        <v>3503</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="J3"/>
     </row>
@@ -41382,10 +41382,10 @@
         <v>515</v>
       </c>
       <c r="H4" t="s">
-        <v>3330</v>
+        <v>3329</v>
       </c>
       <c r="I4" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
       <c r="J4"/>
     </row>
@@ -41403,7 +41403,7 @@
         <v>1522</v>
       </c>
       <c r="E5" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="F5" t="s">
         <v>2171</v>
@@ -41412,10 +41412,10 @@
         <v>515</v>
       </c>
       <c r="H5" s="220" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="I5" s="220" t="s">
-        <v>3178</v>
+        <v>3177</v>
       </c>
       <c r="J5" t="s">
         <v>1397</v>
@@ -41423,31 +41423,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="B6" t="s">
-        <v>3535</v>
+        <v>3534</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>427</v>
       </c>
       <c r="D6" t="s">
-        <v>3348</v>
+        <v>3347</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>3346</v>
+        <v>3345</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>2886</v>
+        <v>2885</v>
       </c>
       <c r="G6" t="s">
         <v>436</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>3128</v>
+        <v>3127</v>
       </c>
       <c r="I6" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
       <c r="J6"/>
     </row>
@@ -41479,13 +41479,13 @@
         <v>143</v>
       </c>
       <c r="B8" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>2065</v>
       </c>
       <c r="D8" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="E8" t="s">
         <v>2331</v>
@@ -41497,10 +41497,10 @@
         <v>250</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>3171</v>
+        <v>3170</v>
       </c>
       <c r="I8" t="s">
-        <v>3295</v>
+        <v>3294</v>
       </c>
       <c r="J8"/>
     </row>
@@ -41597,10 +41597,10 @@
         <v>2866</v>
       </c>
       <c r="E16" t="s">
+        <v>2895</v>
+      </c>
+      <c r="F16" t="s">
         <v>2896</v>
-      </c>
-      <c r="F16" t="s">
-        <v>2897</v>
       </c>
       <c r="G16" t="s">
         <v>121</v>
@@ -41682,7 +41682,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="10" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="B5" s="10">
         <v>67992849</v>
@@ -41703,7 +41703,7 @@
         <v>517</v>
       </c>
       <c r="H5" s="220" t="s">
-        <v>3530</v>
+        <v>3529</v>
       </c>
       <c r="I5" s="278" t="s">
         <v>2158</v>
@@ -41735,12 +41735,12 @@
         <v>2769</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="10" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>2411</v>
@@ -41749,7 +41749,7 @@
         <v>1726</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1699</v>
@@ -41761,10 +41761,10 @@
         <v>517</v>
       </c>
       <c r="H7" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -41780,7 +41780,7 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="10" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="B11" s="10">
         <v>64403333</v>
@@ -41812,7 +41812,7 @@
         <v>2151</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>3233</v>
+        <v>3232</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>961</v>
@@ -41824,10 +41824,10 @@
         <v>517</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="I12" t="s">
-        <v>3385</v>
+        <v>3384</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -41843,7 +41843,7 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="10" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="B15" s="10">
         <v>68543713</v>
@@ -41852,7 +41852,7 @@
         <v>2210</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>961</v>
@@ -41864,10 +41864,10 @@
         <v>517</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -41893,7 +41893,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="10" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="B17" s="10">
         <v>64403333</v>
@@ -41916,7 +41916,7 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="10" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="B18" s="10">
         <v>60345107</v>
@@ -41925,7 +41925,7 @@
         <v>2339</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>961</v>
@@ -41937,10 +41937,10 @@
         <v>517</v>
       </c>
       <c r="H18" s="428" t="s">
-        <v>3259</v>
+        <v>3258</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -41966,10 +41966,10 @@
         <v>517</v>
       </c>
       <c r="H19" s="275" t="s">
-        <v>3016</v>
+        <v>3015</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>3476</v>
+        <v>3475</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="190" customFormat="1" ht="26">
@@ -41985,13 +41985,13 @@
         <v>2622</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>2420</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>961</v>
@@ -42003,15 +42003,15 @@
         <v>517</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>3531</v>
+        <v>3530</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>3217</v>
+        <v>3216</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>3508</v>
+        <v>3507</v>
       </c>
       <c r="B23" s="10">
         <v>64720128</v>
@@ -42032,10 +42032,10 @@
         <v>517</v>
       </c>
       <c r="H23" s="10" t="s">
+        <v>3508</v>
+      </c>
+      <c r="I23" s="10" t="s">
         <v>3509</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>3510</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -42049,7 +42049,7 @@
         <v>2438</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>3166</v>
+        <v>3165</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>961</v>
@@ -42061,10 +42061,10 @@
         <v>517</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>3473</v>
+        <v>3472</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -42074,7 +42074,7 @@
         <v>2451</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>961</v>
@@ -42193,13 +42193,13 @@
         <v>2466</v>
       </c>
       <c r="B4" t="s">
-        <v>3135</v>
+        <v>3134</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1867</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>3134</v>
+        <v>3133</v>
       </c>
       <c r="E4" t="s">
         <v>1868</v>
@@ -42211,13 +42211,13 @@
         <v>965</v>
       </c>
       <c r="H4" t="s">
-        <v>3150</v>
+        <v>3149</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>3159</v>
+        <v>3158</v>
       </c>
       <c r="J4" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -42266,7 +42266,7 @@
         <v>965</v>
       </c>
       <c r="H6" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
       <c r="J6" s="49" t="s">
         <v>2232</v>
@@ -42277,13 +42277,13 @@
         <v>2619</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>2294</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>2295</v>
@@ -42295,25 +42295,25 @@
         <v>965</v>
       </c>
       <c r="H7" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>3256</v>
+        <v>3255</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="278"/>
       <c r="C8" s="3" t="s">
+        <v>3581</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>3582</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="10" t="s">
         <v>3583</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>3584</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>1742</v>
@@ -42322,45 +42322,45 @@
         <v>965</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>3227</v>
+        <v>3226</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="10" t="s">
+        <v>3081</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>3082</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>3083</v>
-      </c>
       <c r="C9" s="22" t="s">
+        <v>3079</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>2909</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>3080</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="F9" s="10" t="s">
         <v>2910</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>3081</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>2911</v>
       </c>
       <c r="G9" t="s">
         <v>965</v>
       </c>
       <c r="H9" s="10" t="s">
+        <v>3083</v>
+      </c>
+      <c r="I9" s="10" t="s">
         <v>3084</v>
       </c>
-      <c r="I9" s="10" t="s">
-        <v>3085</v>
-      </c>
       <c r="J9" t="s">
-        <v>3130</v>
+        <v>3129</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -42368,16 +42368,16 @@
         <v>1432</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>3232</v>
+        <v>3231</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>3229</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>3230</v>
       </c>
-      <c r="D10" s="10" t="s">
-        <v>3231</v>
-      </c>
       <c r="E10" s="10" t="s">
-        <v>3149</v>
+        <v>3148</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>2296</v>
@@ -42386,13 +42386,13 @@
         <v>965</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>3333</v>
+        <v>3332</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>3336</v>
+        <v>3335</v>
       </c>
       <c r="J10" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -42403,7 +42403,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="C15" s="429" t="s">
-        <v>3582</v>
+        <v>3581</v>
       </c>
     </row>
   </sheetData>
@@ -42544,10 +42544,10 @@
         <v>60240509</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>3558</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>3559</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>3560</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>2620</v>
@@ -42559,7 +42559,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="10" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="B10" s="10">
         <v>64676716</v>
@@ -42568,7 +42568,7 @@
         <v>1790</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>2620</v>
@@ -42609,7 +42609,7 @@
         <v>60052700</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>2643</v>
@@ -42630,7 +42630,7 @@
         <v>63132287</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>2643</v>
@@ -42807,7 +42807,7 @@
     <row r="1" spans="1:10" s="410" customFormat="1" ht="42.5" customHeight="1">
       <c r="A1" s="409"/>
       <c r="B1" s="409" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="C1" s="409"/>
     </row>
@@ -42816,28 +42816,28 @@
         <v>147</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>3137</v>
+      </c>
+      <c r="E4" t="s">
+        <v>2954</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>3138</v>
       </c>
-      <c r="E4" t="s">
-        <v>2955</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>3139</v>
-      </c>
       <c r="G4" s="275" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
     </row>
   </sheetData>
@@ -43183,7 +43183,7 @@
         <v>2566</v>
       </c>
       <c r="C5" s="325" t="s">
-        <v>2886</v>
+        <v>2885</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="325" customFormat="1">
@@ -43191,10 +43191,10 @@
         <v>2545</v>
       </c>
       <c r="B6" s="325" t="s">
-        <v>2885</v>
+        <v>2884</v>
       </c>
       <c r="C6" s="325" t="s">
-        <v>2885</v>
+        <v>2884</v>
       </c>
     </row>
     <row r="7" spans="1:13" s="325" customFormat="1">
@@ -43269,10 +43269,10 @@
         <v>2575</v>
       </c>
       <c r="H14" s="331" t="s">
-        <v>2888</v>
+        <v>2887</v>
       </c>
       <c r="I14" s="331" t="s">
-        <v>2891</v>
+        <v>2890</v>
       </c>
       <c r="L14" s="331"/>
       <c r="M14" s="331"/>
@@ -43300,10 +43300,10 @@
         <v>2576</v>
       </c>
       <c r="H15" s="332" t="s">
-        <v>2889</v>
+        <v>2888</v>
       </c>
       <c r="I15" s="332" t="s">
-        <v>2892</v>
+        <v>2891</v>
       </c>
       <c r="L15" s="332"/>
       <c r="M15" s="332"/>
@@ -43331,7 +43331,7 @@
         <v>2577</v>
       </c>
       <c r="H16" s="332" t="s">
-        <v>2890</v>
+        <v>2889</v>
       </c>
       <c r="I16" s="332" t="s">
         <v>1344</v>
@@ -43344,7 +43344,7 @@
         <v>2550</v>
       </c>
       <c r="B17" s="396" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="C17" s="396"/>
       <c r="D17" s="396"/>
@@ -43361,7 +43361,7 @@
         <v>2545</v>
       </c>
       <c r="B18" s="396" t="s">
-        <v>2883</v>
+        <v>2882</v>
       </c>
       <c r="C18" s="396"/>
       <c r="D18" s="396"/>
@@ -43378,7 +43378,7 @@
         <v>2546</v>
       </c>
       <c r="B19" s="396" t="s">
-        <v>2884</v>
+        <v>2883</v>
       </c>
       <c r="C19" s="396"/>
       <c r="D19" s="396"/>
@@ -44233,7 +44233,7 @@
         <v>51</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>3205</v>
+        <v>3204</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>1160</v>
@@ -44245,10 +44245,10 @@
         <v>159</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
       <c r="N6" s="4" t="s">
         <v>26</v>
@@ -44280,13 +44280,13 @@
         <v>2271</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="L7" s="3"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="B8" t="s">
         <v>452</v>
@@ -44310,7 +44310,7 @@
         <v>2742</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
     </row>
     <row r="9" spans="1:14" s="4" customFormat="1">
@@ -44327,19 +44327,19 @@
         <v>2161</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>3425</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>3426</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>3427</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>159</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>3389</v>
+        <v>3388</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>3344</v>
+        <v>3343</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>815</v>
@@ -44347,7 +44347,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="4" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
       <c r="B10" s="4">
         <v>67916500</v>
@@ -44368,10 +44368,10 @@
         <v>244</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>3504</v>
+        <v>3503</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>3274</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -44388,19 +44388,19 @@
         <v>1513</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>244</v>
       </c>
       <c r="H11" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>3596</v>
+        <v>3595</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -44426,18 +44426,18 @@
         <v>244</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>3631</v>
+        <v>3630</v>
       </c>
       <c r="I12" s="306" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="4" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>3648</v>
+        <v>3647</v>
       </c>
       <c r="C13" s="22" t="s">
         <v>1221</v>
@@ -44455,10 +44455,10 @@
         <v>244</v>
       </c>
       <c r="H13" s="220" t="s">
-        <v>3339</v>
+        <v>3338</v>
       </c>
       <c r="I13" s="306" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="4" customFormat="1">
@@ -44484,10 +44484,10 @@
         <v>244</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="I14" s="220" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="L14" s="3"/>
     </row>
@@ -44514,10 +44514,10 @@
         <v>887</v>
       </c>
       <c r="H15" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="I15" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>498</v>
@@ -44546,10 +44546,10 @@
         <v>159</v>
       </c>
       <c r="H16" t="s">
-        <v>3546</v>
+        <v>3545</v>
       </c>
       <c r="I16" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>805</v>
@@ -44557,7 +44557,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="B17">
         <v>65325884</v>
@@ -44580,7 +44580,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="4" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>2112</v>
@@ -44592,24 +44592,24 @@
         <v>2221</v>
       </c>
       <c r="E18" s="4" t="s">
+        <v>2936</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>2937</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>2938</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>244</v>
       </c>
       <c r="H18" s="49" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="I18" t="s">
-        <v>3621</v>
+        <v>3620</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="4" customFormat="1">
       <c r="A19" s="4" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="B19" s="4">
         <v>64403333</v>
@@ -44621,10 +44621,10 @@
         <v>2605</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>3427</v>
+        <v>3426</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>1230</v>
@@ -44634,7 +44634,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="4" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="B20">
         <v>64403333</v>
@@ -44660,7 +44660,7 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="4" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="B21" s="4">
         <v>64403333</v>
@@ -44683,7 +44683,7 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="4" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="B22" s="4">
         <v>64403333</v>
@@ -44706,7 +44706,7 @@
     </row>
     <row r="23" spans="1:12" s="4" customFormat="1">
       <c r="A23" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="B23">
         <v>63247837</v>
@@ -44715,7 +44715,7 @@
         <v>2613</v>
       </c>
       <c r="D23" t="s">
-        <v>3360</v>
+        <v>3359</v>
       </c>
       <c r="E23" t="s">
         <v>2616</v>
@@ -44727,10 +44727,10 @@
         <v>159</v>
       </c>
       <c r="H23" t="s">
-        <v>3298</v>
+        <v>3297</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>3381</v>
+        <v>3380</v>
       </c>
       <c r="L23" s="6"/>
     </row>
@@ -44745,10 +44745,10 @@
         <v>1634</v>
       </c>
       <c r="D24" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>2479</v>
@@ -44759,19 +44759,19 @@
     </row>
     <row r="25" spans="1:12" s="4" customFormat="1">
       <c r="A25" s="4" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="C25" s="21" t="s">
         <v>1329</v>
       </c>
       <c r="D25" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>3030</v>
+        <v>3029</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>2482</v>
@@ -44780,10 +44780,10 @@
         <v>244</v>
       </c>
       <c r="H25" s="220" t="s">
-        <v>3625</v>
+        <v>3624</v>
       </c>
       <c r="I25" s="220" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="4" customFormat="1">
@@ -44809,10 +44809,10 @@
         <v>159</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>3556</v>
+        <v>3555</v>
       </c>
       <c r="I27" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="L27" s="4" t="s">
         <v>813</v>
@@ -44820,7 +44820,7 @@
     </row>
     <row r="28" spans="1:12" s="4" customFormat="1">
       <c r="A28" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>2473</v>
@@ -44832,7 +44832,7 @@
         <v>2033</v>
       </c>
       <c r="E28" t="s">
-        <v>3131</v>
+        <v>3130</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>2482</v>
@@ -44844,7 +44844,7 @@
         <v>2660</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
       <c r="K28"/>
     </row>
@@ -44859,41 +44859,41 @@
         <v>350</v>
       </c>
       <c r="D29" s="75" t="s">
-        <v>2898</v>
+        <v>2897</v>
       </c>
       <c r="E29" t="s">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="G29" s="75" t="s">
         <v>250</v>
       </c>
       <c r="H29" s="49" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
       <c r="I29" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
       <c r="J29" s="4"/>
       <c r="L29" s="135"/>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="C30" s="22" t="s">
         <v>402</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="E30" t="s">
-        <v>3275</v>
+        <v>3274</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>1344</v>
@@ -44902,7 +44902,7 @@
         <v>159</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="I30" s="55" t="s">
         <v>2768</v>
@@ -44910,7 +44910,7 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="B31" s="4">
         <v>69409351</v>
@@ -44931,10 +44931,10 @@
         <v>159</v>
       </c>
       <c r="H31" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -44960,7 +44960,7 @@
         <v>159</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="I32" s="49" t="s">
         <v>2756</v>
@@ -44971,13 +44971,13 @@
         <v>2619</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>2603</v>
       </c>
       <c r="D33" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
       <c r="E33" t="s">
         <v>2606</v>
@@ -44989,7 +44989,7 @@
         <v>2607</v>
       </c>
       <c r="H33" s="49" t="s">
-        <v>3039</v>
+        <v>3038</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -44997,13 +44997,13 @@
         <v>1432</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="C34" s="21" t="s">
         <v>2600</v>
       </c>
       <c r="D34" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="E34" t="s">
         <v>2606</v>
@@ -45015,25 +45015,25 @@
         <v>159</v>
       </c>
       <c r="H34" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
       <c r="I34" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="J34" s="4"/>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>2601</v>
       </c>
       <c r="D35" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="E35" t="s">
         <v>2606</v>
@@ -45045,24 +45045,24 @@
         <v>2607</v>
       </c>
       <c r="H35" s="306" t="s">
-        <v>3017</v>
+        <v>3016</v>
       </c>
       <c r="I35" t="s">
-        <v>3028</v>
+        <v>3027</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="B36" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
       <c r="C36" s="22" t="s">
         <v>2602</v>
       </c>
       <c r="D36" t="s">
-        <v>3439</v>
+        <v>3438</v>
       </c>
       <c r="E36" t="s">
         <v>2606</v>
@@ -45074,10 +45074,10 @@
         <v>159</v>
       </c>
       <c r="H36" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="I36" t="s">
-        <v>3237</v>
+        <v>3236</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -45091,7 +45091,7 @@
         <v>2614</v>
       </c>
       <c r="D37" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="E37" t="s">
         <v>2616</v>
@@ -45103,10 +45103,10 @@
         <v>159</v>
       </c>
       <c r="H37" t="s">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="I37" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -45114,7 +45114,7 @@
         <v>157</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>2615</v>
@@ -45132,10 +45132,10 @@
         <v>159</v>
       </c>
       <c r="H38" s="97" t="s">
-        <v>3196</v>
+        <v>3195</v>
       </c>
       <c r="I38" t="s">
-        <v>3291</v>
+        <v>3290</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -45148,10 +45148,10 @@
         <v>1354</v>
       </c>
       <c r="E41" s="97" t="s">
+        <v>3348</v>
+      </c>
+      <c r="F41" s="105" t="s">
         <v>3349</v>
-      </c>
-      <c r="F41" s="105" t="s">
-        <v>3350</v>
       </c>
       <c r="G41" s="105" t="s">
         <v>159</v>
@@ -45169,10 +45169,10 @@
         <v>2098</v>
       </c>
       <c r="E42" s="97" t="s">
+        <v>3348</v>
+      </c>
+      <c r="F42" s="105" t="s">
         <v>3349</v>
-      </c>
-      <c r="F42" s="105" t="s">
-        <v>3350</v>
       </c>
       <c r="G42" s="105" t="s">
         <v>159</v>
@@ -45188,7 +45188,7 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="4" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="B45" t="s">
         <v>2517</v>
@@ -45218,7 +45218,7 @@
         <v>2829</v>
       </c>
       <c r="K45" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="4" customFormat="1">
@@ -45609,13 +45609,13 @@
         <v>157</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="C2" s="276" t="s">
         <v>254</v>
       </c>
       <c r="D2" s="106" t="s">
-        <v>3107</v>
+        <v>3106</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>1299</v>
@@ -45627,16 +45627,16 @@
         <v>62</v>
       </c>
       <c r="H2" s="300" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="I2" s="106" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="J2" s="107" t="s">
-        <v>3617</v>
+        <v>3616</v>
       </c>
       <c r="K2" s="30" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
       <c r="M2" s="159"/>
     </row>
@@ -45651,7 +45651,7 @@
         <v>1182</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="E4" s="32" t="s">
         <v>2405</v>
@@ -45663,25 +45663,25 @@
         <v>270</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>3373</v>
+        <v>3372</v>
       </c>
       <c r="I4" s="30" t="s">
-        <v>3258</v>
+        <v>3257</v>
       </c>
       <c r="J4" s="139" t="s">
-        <v>3629</v>
+        <v>3628</v>
       </c>
       <c r="K4" s="139" t="s">
-        <v>3444</v>
+        <v>3443</v>
       </c>
       <c r="M4" s="39"/>
     </row>
     <row r="5" spans="1:13" s="30" customFormat="1">
       <c r="A5" s="30" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>1114</v>
@@ -45699,22 +45699,22 @@
         <v>65</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="J5" s="30" t="s">
-        <v>3366</v>
+        <v>3365</v>
       </c>
       <c r="K5" s="30" t="s">
-        <v>3276</v>
+        <v>3275</v>
       </c>
       <c r="M5" s="36"/>
     </row>
     <row r="6" spans="1:13" s="30" customFormat="1">
       <c r="A6" s="107" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="B6" s="30" t="s">
         <v>2187</v>
@@ -45723,7 +45723,7 @@
         <v>2773</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>3514</v>
+        <v>3513</v>
       </c>
       <c r="E6" s="140" t="s">
         <v>2734</v>
@@ -45735,22 +45735,22 @@
         <v>65</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>3585</v>
+        <v>3584</v>
       </c>
       <c r="I6" s="432" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="K6" s="30" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="M6" s="36"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="107" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>1212</v>
@@ -45759,28 +45759,28 @@
         <v>1091</v>
       </c>
       <c r="D7" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="E7" s="107" t="s">
+        <v>3352</v>
+      </c>
+      <c r="F7" s="30" t="s">
         <v>3353</v>
-      </c>
-      <c r="F7" s="30" t="s">
-        <v>3354</v>
       </c>
       <c r="G7" s="106" t="s">
         <v>720</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="I7" s="217" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="J7" s="217" t="s">
         <v>2676</v>
       </c>
       <c r="K7" s="30" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="M7" s="36"/>
     </row>
@@ -45795,7 +45795,7 @@
         <v>985</v>
       </c>
       <c r="D8" s="139" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
       <c r="E8" s="107" t="s">
         <v>1157</v>
@@ -45807,22 +45807,22 @@
         <v>65</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
       <c r="I8" s="32" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="J8" s="449" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="K8" s="139" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="M8" s="36"/>
     </row>
     <row r="9" spans="1:13" s="107" customFormat="1">
       <c r="A9" s="302" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="B9" s="32" t="s">
         <v>1676</v>
@@ -45843,22 +45843,22 @@
         <v>65</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="I9" s="107" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="K9" s="107" t="s">
-        <v>3040</v>
+        <v>3039</v>
       </c>
       <c r="M9" s="36"/>
     </row>
     <row r="10" spans="1:13" s="30" customFormat="1">
       <c r="A10" s="30" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="B10" s="30">
         <v>69575383</v>
@@ -45879,16 +45879,16 @@
         <v>65</v>
       </c>
       <c r="H10" s="107" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
       <c r="I10" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="J10" s="219" t="s">
-        <v>3505</v>
+        <v>3504</v>
       </c>
       <c r="K10" s="107" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="M10" s="34"/>
     </row>
@@ -45915,16 +45915,16 @@
         <v>605</v>
       </c>
       <c r="H11" s="139" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
       <c r="I11" s="30" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
       <c r="J11" s="107" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="K11" s="107" t="s">
-        <v>3295</v>
+        <v>3294</v>
       </c>
       <c r="M11" s="36"/>
     </row>
@@ -45951,22 +45951,22 @@
         <v>245</v>
       </c>
       <c r="H12" s="450" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="I12" s="106" t="s">
-        <v>3580</v>
+        <v>3579</v>
       </c>
       <c r="J12" s="106" t="s">
-        <v>3513</v>
+        <v>3512</v>
       </c>
       <c r="K12" s="107" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="M12" s="151"/>
     </row>
     <row r="13" spans="1:13" s="107" customFormat="1">
       <c r="A13" s="140" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="B13" s="107" t="s">
         <v>2804</v>
@@ -45975,7 +45975,7 @@
         <v>919</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
       <c r="E13" s="140" t="s">
         <v>2774</v>
@@ -45987,16 +45987,16 @@
         <v>65</v>
       </c>
       <c r="H13" s="30" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="I13" s="30" t="s">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="J13" s="107" t="s">
-        <v>3305</v>
+        <v>3304</v>
       </c>
       <c r="K13" t="s">
-        <v>3331</v>
+        <v>3330</v>
       </c>
       <c r="M13" s="36"/>
     </row>
@@ -46023,13 +46023,13 @@
         <v>65</v>
       </c>
       <c r="H14" s="107" t="s">
-        <v>3390</v>
+        <v>3389</v>
       </c>
       <c r="I14" s="411" t="s">
         <v>2272</v>
       </c>
       <c r="J14" s="32" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="M14" s="36"/>
     </row>
@@ -46056,16 +46056,16 @@
         <v>66</v>
       </c>
       <c r="H15" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="I15" t="s">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="J15" t="s">
-        <v>3277</v>
+        <v>3276</v>
       </c>
       <c r="K15" s="107" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="M15" s="36"/>
     </row>
@@ -46117,16 +46117,16 @@
         <v>66</v>
       </c>
       <c r="H17" t="s">
-        <v>3602</v>
+        <v>3601</v>
       </c>
       <c r="I17" s="30" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
       <c r="K17" s="220" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
       <c r="M17" s="34"/>
     </row>
@@ -46153,22 +46153,22 @@
         <v>66</v>
       </c>
       <c r="H18" s="30" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="I18" t="s">
-        <v>3222</v>
+        <v>3221</v>
       </c>
       <c r="J18" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="K18" s="49" t="s">
-        <v>2958</v>
+        <v>2957</v>
       </c>
       <c r="M18" s="36"/>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="4" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>1533</v>
@@ -46177,7 +46177,7 @@
         <v>1693</v>
       </c>
       <c r="D19" s="134" t="s">
-        <v>3466</v>
+        <v>3465</v>
       </c>
       <c r="E19" t="s">
         <v>1696</v>
@@ -46189,16 +46189,16 @@
         <v>66</v>
       </c>
       <c r="H19" t="s">
-        <v>3127</v>
+        <v>3126</v>
       </c>
       <c r="I19" s="49" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="J19" s="220" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="K19" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
       <c r="M19" s="36"/>
     </row>
@@ -46213,7 +46213,7 @@
         <v>2498</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="E20" s="107" t="s">
         <v>2423</v>
@@ -46225,31 +46225,31 @@
         <v>65</v>
       </c>
       <c r="H20" s="438" t="s">
-        <v>3512</v>
+        <v>3511</v>
       </c>
       <c r="I20" t="s">
+        <v>3056</v>
+      </c>
+      <c r="J20" t="s">
         <v>3057</v>
       </c>
-      <c r="J20" t="s">
-        <v>3058</v>
-      </c>
       <c r="K20" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="M20" s="36"/>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>3395</v>
+        <v>3394</v>
       </c>
       <c r="B21" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="C21" s="22" t="s">
         <v>1130</v>
       </c>
       <c r="D21" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="E21" s="140" t="s">
         <v>1593</v>
@@ -46261,19 +46261,19 @@
         <v>65</v>
       </c>
       <c r="H21" t="s">
-        <v>3404</v>
+        <v>3403</v>
       </c>
       <c r="I21" t="s">
+        <v>3406</v>
+      </c>
+      <c r="J21" t="s">
         <v>3407</v>
-      </c>
-      <c r="J21" t="s">
-        <v>3408</v>
       </c>
       <c r="M21" s="36"/>
     </row>
     <row r="22" spans="1:13" s="30" customFormat="1">
       <c r="A22" s="30" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="B22" s="30" t="s">
         <v>2114</v>
@@ -46282,58 +46282,58 @@
         <v>2737</v>
       </c>
       <c r="D22" s="107" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="E22" s="30" t="s">
+        <v>3422</v>
+      </c>
+      <c r="F22" s="30" t="s">
         <v>3423</v>
-      </c>
-      <c r="F22" s="30" t="s">
-        <v>3424</v>
       </c>
       <c r="G22" s="32" t="s">
         <v>65</v>
       </c>
       <c r="H22" s="30" t="s">
-        <v>3428</v>
+        <v>3427</v>
       </c>
       <c r="I22" s="30" t="s">
+        <v>3429</v>
+      </c>
+      <c r="J22" s="30" t="s">
         <v>3430</v>
-      </c>
-      <c r="J22" s="30" t="s">
-        <v>3431</v>
       </c>
       <c r="M22" s="36"/>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="B23" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="C23" s="22" t="s">
         <v>1906</v>
       </c>
       <c r="D23" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="E23" s="30" t="s">
+        <v>3422</v>
+      </c>
+      <c r="F23" s="30" t="s">
         <v>3423</v>
-      </c>
-      <c r="F23" s="30" t="s">
-        <v>3424</v>
       </c>
       <c r="G23" t="s">
         <v>66</v>
       </c>
       <c r="H23" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="I23" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="J23" t="s">
-        <v>3529</v>
+        <v>3528</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -46402,7 +46402,7 @@
     </row>
     <row r="32" spans="1:13" s="107" customFormat="1">
       <c r="A32" s="32" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="B32" s="32">
         <v>64403333</v>
@@ -46426,7 +46426,7 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="B33">
         <v>60389752</v>
@@ -46449,7 +46449,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="B34">
         <v>60389752</v>
@@ -46458,13 +46458,13 @@
         <v>2177</v>
       </c>
       <c r="D34" s="32" t="s">
-        <v>3297</v>
+        <v>3296</v>
       </c>
       <c r="E34" s="30" t="s">
+        <v>3422</v>
+      </c>
+      <c r="F34" s="30" t="s">
         <v>3423</v>
-      </c>
-      <c r="F34" s="30" t="s">
-        <v>3424</v>
       </c>
       <c r="G34" t="s">
         <v>3</v>
@@ -46473,7 +46473,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>3395</v>
+        <v>3394</v>
       </c>
       <c r="B35">
         <v>60389752</v>
@@ -46497,7 +46497,7 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="B36">
         <v>60389752</v>
@@ -46521,7 +46521,7 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="30" t="s">
-        <v>3395</v>
+        <v>3394</v>
       </c>
       <c r="B37" s="30">
         <v>64403333</v>
@@ -46546,7 +46546,7 @@
     </row>
     <row r="38" spans="1:13" s="30" customFormat="1">
       <c r="A38" s="30" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="B38" s="30">
         <v>60389752</v>
@@ -46583,10 +46583,10 @@
         <v>2148</v>
       </c>
       <c r="E39" t="s">
+        <v>3422</v>
+      </c>
+      <c r="F39" t="s">
         <v>3423</v>
-      </c>
-      <c r="F39" t="s">
-        <v>3424</v>
       </c>
       <c r="G39" t="s">
         <v>3</v>
@@ -46655,7 +46655,7 @@
         <v>2524</v>
       </c>
       <c r="E45" t="s">
-        <v>3308</v>
+        <v>3307</v>
       </c>
       <c r="F45" s="30" t="s">
         <v>2525</v>
@@ -46664,13 +46664,13 @@
         <v>369</v>
       </c>
       <c r="H45" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="I45" s="30" t="s">
-        <v>3392</v>
+        <v>3391</v>
       </c>
       <c r="J45" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -46722,10 +46722,10 @@
     </row>
     <row r="66" spans="1:38">
       <c r="C66" s="7" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
       <c r="D66" t="s">
-        <v>3297</v>
+        <v>3296</v>
       </c>
       <c r="E66" t="s">
         <v>2421</v>
@@ -46773,16 +46773,16 @@
     </row>
     <row r="70" spans="1:38">
       <c r="C70" s="8" t="s">
+        <v>3643</v>
+      </c>
+      <c r="D70" t="s">
         <v>3644</v>
       </c>
-      <c r="D70" t="s">
-        <v>3645</v>
-      </c>
       <c r="E70" s="140" t="s">
+        <v>2926</v>
+      </c>
+      <c r="F70" s="140" t="s">
         <v>2927</v>
-      </c>
-      <c r="F70" s="140" t="s">
-        <v>2928</v>
       </c>
       <c r="G70" s="106" t="s">
         <v>720</v>
@@ -47117,7 +47117,7 @@
         <v>1133</v>
       </c>
       <c r="D93" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="E93" s="140" t="s">
         <v>1135</v>
@@ -47141,7 +47141,7 @@
         <v>1393</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="E94" s="266" t="s">
         <v>1508</v>
@@ -47175,7 +47175,7 @@
         <v>358</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
     </row>
     <row r="105" spans="2:5">
@@ -47401,7 +47401,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="C12" s="236" t="s">
         <v>1940</v>
@@ -47532,7 +47532,7 @@
         <v>6.83</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -47541,7 +47541,7 @@
       </c>
       <c r="B24" s="87"/>
       <c r="F24" s="2" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -47617,27 +47617,27 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="87" t="s">
-        <v>3478</v>
+        <v>3477</v>
       </c>
       <c r="C40" t="s">
-        <v>3481</v>
+        <v>3480</v>
       </c>
       <c r="F40" s="45"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="89" t="s">
-        <v>3479</v>
+        <v>3478</v>
       </c>
       <c r="C41" t="s">
-        <v>3482</v>
+        <v>3481</v>
       </c>
     </row>
     <row r="42" spans="2:6" ht="15" thickBot="1">
       <c r="B42" s="86" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
       <c r="C42" t="s">
-        <v>3483</v>
+        <v>3482</v>
       </c>
     </row>
     <row r="43" spans="2:6">
@@ -47791,7 +47791,7 @@
         <v>143</v>
       </c>
       <c r="B6" s="247" t="s">
-        <v>2933</v>
+        <v>2932</v>
       </c>
       <c r="C6" s="246" t="s">
         <v>1291</v>
@@ -47800,22 +47800,22 @@
         <v>2038</v>
       </c>
       <c r="E6" s="247" t="s">
+        <v>3341</v>
+      </c>
+      <c r="F6" s="247" t="s">
         <v>3342</v>
-      </c>
-      <c r="F6" s="247" t="s">
-        <v>3343</v>
       </c>
       <c r="G6" s="247" t="s">
         <v>357</v>
       </c>
       <c r="H6" s="247" t="s">
-        <v>3301</v>
+        <v>3300</v>
       </c>
       <c r="I6" s="244" t="s">
-        <v>3601</v>
+        <v>3600</v>
       </c>
       <c r="J6" s="455" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="K6" s="247" t="s">
         <v>475</v>
@@ -47838,19 +47838,19 @@
         <v>1038</v>
       </c>
       <c r="F7" s="265" t="s">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="G7" s="265" t="s">
         <v>690</v>
       </c>
       <c r="H7" s="295" t="s">
-        <v>3340</v>
+        <v>3339</v>
       </c>
       <c r="I7" s="295" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="J7" s="295" t="s">
-        <v>3550</v>
+        <v>3549</v>
       </c>
       <c r="K7" s="265" t="s">
         <v>709</v>
@@ -47873,19 +47873,19 @@
         <v>1231</v>
       </c>
       <c r="F8" s="265" t="s">
-        <v>3224</v>
+        <v>3223</v>
       </c>
       <c r="G8" s="265" t="s">
         <v>250</v>
       </c>
       <c r="H8" s="319" t="s">
-        <v>3562</v>
+        <v>3561</v>
       </c>
       <c r="I8" s="265" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
       <c r="J8" s="265" t="s">
-        <v>3561</v>
+        <v>3560</v>
       </c>
       <c r="K8" s="259"/>
       <c r="L8" s="259"/>
@@ -47907,7 +47907,7 @@
         <v>2722</v>
       </c>
       <c r="F9" s="263" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="G9" s="263" t="s">
         <v>948</v>
@@ -47918,7 +47918,7 @@
     </row>
     <row r="10" spans="1:12" s="245" customFormat="1">
       <c r="A10" s="298" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="B10" s="241" t="s">
         <v>2627</v>
@@ -47939,13 +47939,13 @@
         <v>690</v>
       </c>
       <c r="H10" s="264" t="s">
-        <v>3041</v>
+        <v>3040</v>
       </c>
       <c r="I10" s="455" t="s">
-        <v>3637</v>
+        <v>3636</v>
       </c>
       <c r="J10" s="264" t="s">
-        <v>3632</v>
+        <v>3631</v>
       </c>
       <c r="K10" s="245" t="s">
         <v>1206</v>
@@ -47956,7 +47956,7 @@
         <v>2522</v>
       </c>
       <c r="B11" s="262" t="s">
-        <v>3332</v>
+        <v>3331</v>
       </c>
       <c r="C11" s="194" t="s">
         <v>491</v>
@@ -47974,13 +47974,13 @@
         <v>690</v>
       </c>
       <c r="H11" s="215" t="s">
-        <v>3533</v>
+        <v>3532</v>
       </c>
       <c r="I11" s="425" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="J11" s="269" t="s">
-        <v>3649</v>
+        <v>3648</v>
       </c>
       <c r="K11" s="183" t="s">
         <v>1207</v>
@@ -48014,10 +48014,10 @@
     </row>
     <row r="13" spans="1:12" s="223" customFormat="1">
       <c r="A13" s="223" t="s">
-        <v>3395</v>
+        <v>3394</v>
       </c>
       <c r="B13" s="223" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="C13" s="424" t="s">
         <v>335</v>
@@ -48026,22 +48026,22 @@
         <v>2403</v>
       </c>
       <c r="E13" s="223" t="s">
-        <v>3103</v>
+        <v>3102</v>
       </c>
       <c r="F13" s="223" t="s">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="G13" s="223" t="s">
         <v>690</v>
       </c>
       <c r="H13" s="223" t="s">
+        <v>3108</v>
+      </c>
+      <c r="I13" s="215" t="s">
+        <v>3312</v>
+      </c>
+      <c r="J13" s="223" t="s">
         <v>3109</v>
-      </c>
-      <c r="I13" s="215" t="s">
-        <v>3313</v>
-      </c>
-      <c r="J13" s="223" t="s">
-        <v>3110</v>
       </c>
       <c r="K13" s="223" t="s">
         <v>1320</v>
@@ -48061,7 +48061,7 @@
         <v>1977</v>
       </c>
       <c r="E14" s="216" t="s">
-        <v>3372</v>
+        <v>3371</v>
       </c>
       <c r="F14" s="216" t="s">
         <v>1436</v>
@@ -48070,13 +48070,13 @@
         <v>690</v>
       </c>
       <c r="H14" s="272" t="s">
-        <v>3551</v>
+        <v>3550</v>
       </c>
       <c r="I14" s="215" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="J14" s="262" t="s">
-        <v>3177</v>
+        <v>3176</v>
       </c>
       <c r="K14" s="183" t="s">
         <v>1208</v>
@@ -48087,13 +48087,13 @@
         <v>1419</v>
       </c>
       <c r="B15" s="264" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="C15" s="270" t="s">
         <v>1308</v>
       </c>
       <c r="D15" s="259" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="E15" s="259" t="s">
         <v>2782</v>
@@ -48105,13 +48105,13 @@
         <v>690</v>
       </c>
       <c r="H15" s="264" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
       <c r="I15" s="439" t="s">
-        <v>3565</v>
+        <v>3564</v>
       </c>
       <c r="J15" s="264" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="K15" s="259" t="s">
         <v>1441</v>
@@ -48169,7 +48169,7 @@
     </row>
     <row r="18" spans="1:11" s="259" customFormat="1">
       <c r="A18" s="271" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="B18" s="259" t="s">
         <v>2345</v>
@@ -48178,7 +48178,7 @@
         <v>831</v>
       </c>
       <c r="D18" s="264" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
       <c r="E18" s="264" t="s">
         <v>1792</v>
@@ -48190,13 +48190,13 @@
         <v>690</v>
       </c>
       <c r="H18" s="259" t="s">
-        <v>3635</v>
+        <v>3634</v>
       </c>
       <c r="I18" s="298" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="J18" s="259" t="s">
-        <v>3618</v>
+        <v>3617</v>
       </c>
       <c r="K18" s="264" t="s">
         <v>1769</v>
@@ -48204,7 +48204,7 @@
     </row>
     <row r="19" spans="1:11" s="259" customFormat="1">
       <c r="A19" s="259" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="B19" s="259" t="s">
         <v>2390</v>
@@ -48225,13 +48225,13 @@
         <v>690</v>
       </c>
       <c r="H19" s="259" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="I19" s="259" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="J19" s="259" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="K19" s="259" t="s">
         <v>1814</v>
@@ -48242,7 +48242,7 @@
         <v>2619</v>
       </c>
       <c r="B20" s="304" t="s">
-        <v>3564</v>
+        <v>3563</v>
       </c>
       <c r="C20" s="259" t="s">
         <v>1815</v>
@@ -48263,10 +48263,10 @@
         <v>2791</v>
       </c>
       <c r="I20" s="264" t="s">
-        <v>3598</v>
+        <v>3597</v>
       </c>
       <c r="J20" s="264" t="s">
-        <v>3438</v>
+        <v>3437</v>
       </c>
       <c r="K20" s="259" t="s">
         <v>1816</v>
@@ -48309,10 +48309,10 @@
         <v>637</v>
       </c>
       <c r="D22" s="255" t="s">
-        <v>3567</v>
+        <v>3566</v>
       </c>
       <c r="E22" s="271" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
       <c r="F22" s="271" t="s">
         <v>1714</v>
@@ -48321,13 +48321,13 @@
         <v>250</v>
       </c>
       <c r="H22" s="259" t="s">
-        <v>3578</v>
+        <v>3577</v>
       </c>
       <c r="I22" s="264" t="s">
-        <v>3314</v>
+        <v>3313</v>
       </c>
       <c r="J22" s="264" t="s">
-        <v>3211</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="97" customFormat="1">
@@ -48548,7 +48548,7 @@
         <v>840</v>
       </c>
       <c r="D45" s="264" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="E45" s="259" t="s">
         <v>1792</v>
@@ -48751,13 +48751,13 @@
         <v>2800</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>3370</v>
+        <v>3369</v>
       </c>
       <c r="I2" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
       <c r="J2" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
       <c r="L2" s="36" t="s">
         <v>1176</v>
@@ -48783,7 +48783,7 @@
         <v>298</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>3371</v>
+        <v>3370</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>707</v>
@@ -48809,25 +48809,25 @@
         <v>313</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>323</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="H4" t="s">
-        <v>3100</v>
+        <v>3099</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>3634</v>
+        <v>3633</v>
       </c>
       <c r="J4" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="L4" s="127" t="s">
         <v>322</v>
@@ -48853,7 +48853,7 @@
         <v>424</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>3104</v>
+        <v>3103</v>
       </c>
       <c r="H5" s="49" t="s">
         <v>2767</v>
@@ -48868,7 +48868,7 @@
     </row>
     <row r="6" spans="1:12" s="4" customFormat="1">
       <c r="A6" s="4" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="B6" s="4">
         <v>65436260</v>
@@ -48877,25 +48877,25 @@
         <v>327</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>2918</v>
+        <v>2917</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>2917</v>
+        <v>2916</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>166</v>
       </c>
       <c r="G6" t="s">
-        <v>3327</v>
+        <v>3326</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="I6" t="s">
-        <v>3375</v>
+        <v>3374</v>
       </c>
       <c r="J6" s="49" t="s">
-        <v>2919</v>
+        <v>2918</v>
       </c>
       <c r="L6" s="67" t="s">
         <v>423</v>
@@ -48903,7 +48903,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="4" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="B7" s="4">
         <v>69561522</v>
@@ -48912,25 +48912,25 @@
         <v>434</v>
       </c>
       <c r="D7" t="s">
-        <v>3207</v>
+        <v>3206</v>
       </c>
       <c r="E7" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="F7" t="s">
         <v>151</v>
       </c>
       <c r="G7" t="s">
-        <v>3619</v>
+        <v>3618</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>3129</v>
+        <v>3128</v>
       </c>
       <c r="J7" t="s">
-        <v>3235</v>
+        <v>3234</v>
       </c>
       <c r="L7" s="83" t="s">
         <v>435</v>
@@ -48938,10 +48938,10 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="306" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>658</v>
@@ -48959,10 +48959,10 @@
         <v>2662</v>
       </c>
       <c r="H8" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
       <c r="I8" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="J8" s="49" t="s">
         <v>2799</v>
@@ -48989,16 +48989,16 @@
         <v>151</v>
       </c>
       <c r="G9" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
       <c r="H9" s="220" t="s">
-        <v>3167</v>
+        <v>3166</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>3627</v>
+        <v>3626</v>
       </c>
       <c r="J9" s="220" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -49012,7 +49012,7 @@
         <v>2204</v>
       </c>
       <c r="D10" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="E10" t="s">
         <v>2175</v>
@@ -49021,13 +49021,13 @@
         <v>1822</v>
       </c>
       <c r="G10" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="H10" s="49" t="s">
-        <v>3581</v>
+        <v>3580</v>
       </c>
       <c r="I10" t="s">
-        <v>3378</v>
+        <v>3377</v>
       </c>
       <c r="J10" s="49" t="s">
         <v>2862</v>
@@ -49070,7 +49070,7 @@
         <v>1481</v>
       </c>
       <c r="E12" t="s">
-        <v>3206</v>
+        <v>3205</v>
       </c>
       <c r="F12" t="s">
         <v>614</v>
@@ -49101,16 +49101,16 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>3307</v>
+        <v>3306</v>
       </c>
       <c r="B14" t="s">
-        <v>3316</v>
+        <v>3315</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>281</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>3315</v>
+        <v>3314</v>
       </c>
       <c r="E14" t="s">
         <v>2141</v>
@@ -49119,16 +49119,16 @@
         <v>1822</v>
       </c>
       <c r="G14" s="97" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
       <c r="H14" t="s">
-        <v>3642</v>
+        <v>3641</v>
       </c>
       <c r="I14" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="J14" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -49396,7 +49396,7 @@
     </row>
     <row r="2" spans="1:14" ht="43.15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="C2" s="51"/>
       <c r="D2" s="52" t="s">
@@ -49408,7 +49408,7 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="B4">
         <v>62445630</v>
@@ -49420,7 +49420,7 @@
         <v>2694</v>
       </c>
       <c r="E4" t="s">
-        <v>3228</v>
+        <v>3227</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -49445,7 +49445,7 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="B9" t="s">
         <v>1555</v>
@@ -49457,7 +49457,7 @@
         <v>1554</v>
       </c>
       <c r="E9" s="283" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="F9" t="s">
         <v>1736</v>
@@ -49465,7 +49465,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="460" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="B10">
         <v>63000545</v>
@@ -49477,7 +49477,7 @@
         <v>2219</v>
       </c>
       <c r="E10" s="460" t="s">
-        <v>3651</v>
+        <v>3650</v>
       </c>
       <c r="F10" t="s">
         <v>1685</v>
@@ -49485,7 +49485,7 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="30" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="B11" s="178">
         <v>68241069</v>
@@ -49497,7 +49497,7 @@
         <v>2059</v>
       </c>
       <c r="E11" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -49514,7 +49514,7 @@
         <v>2703</v>
       </c>
       <c r="E12" t="s">
-        <v>3477</v>
+        <v>3476</v>
       </c>
       <c r="F12" t="s">
         <v>1685</v>
@@ -49522,7 +49522,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="B13">
         <v>62271547</v>
@@ -49534,15 +49534,15 @@
         <v>2396</v>
       </c>
       <c r="E13" t="s">
+        <v>2955</v>
+      </c>
+      <c r="F13" t="s">
         <v>2956</v>
-      </c>
-      <c r="F13" t="s">
-        <v>2957</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="B14">
         <v>62445630</v>
@@ -49551,7 +49551,7 @@
         <v>1941</v>
       </c>
       <c r="D14" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="E14" t="s">
         <v>2663</v>
@@ -49562,7 +49562,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="B15">
         <v>62806425</v>
@@ -49591,10 +49591,10 @@
         <v>2751</v>
       </c>
       <c r="D16" s="30" t="s">
+        <v>3097</v>
+      </c>
+      <c r="E16" t="s">
         <v>3098</v>
-      </c>
-      <c r="E16" t="s">
-        <v>3099</v>
       </c>
       <c r="F16" t="s">
         <v>2706</v>
@@ -49602,19 +49602,19 @@
     </row>
     <row r="17" spans="1:8" s="30" customFormat="1">
       <c r="A17" s="217" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
       <c r="B17" s="30">
         <v>68582631</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="D17" s="30" t="s">
+        <v>3111</v>
+      </c>
+      <c r="E17" t="s">
         <v>3112</v>
-      </c>
-      <c r="E17" t="s">
-        <v>3113</v>
       </c>
       <c r="F17" t="s">
         <v>2706</v>
@@ -49637,7 +49637,7 @@
         <v>2755</v>
       </c>
       <c r="E18" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="F18" t="s">
         <v>2706</v>
@@ -49657,10 +49657,10 @@
         <v>2797</v>
       </c>
       <c r="E19" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="F19" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -49680,7 +49680,7 @@
         <v>1515</v>
       </c>
       <c r="F21" t="s">
-        <v>3388</v>
+        <v>3387</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -49716,7 +49716,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="B26">
         <v>68927207</v>
@@ -49728,13 +49728,13 @@
         <v>2680</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>3072</v>
+      </c>
+      <c r="F26" t="s">
         <v>3073</v>
       </c>
-      <c r="F26" t="s">
-        <v>3074</v>
-      </c>
       <c r="G26" t="s">
-        <v>3086</v>
+        <v>3085</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -49751,13 +49751,13 @@
         <v>421</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>3073</v>
+        <v>3072</v>
       </c>
       <c r="F27" t="s">
-        <v>3103</v>
+        <v>3102</v>
       </c>
       <c r="G27" t="s">
-        <v>3137</v>
+        <v>3136</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -49768,16 +49768,16 @@
         <v>1464</v>
       </c>
       <c r="D29" t="s">
+        <v>3357</v>
+      </c>
+      <c r="E29" t="s">
+        <v>3303</v>
+      </c>
+      <c r="F29" t="s">
+        <v>3087</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>3358</v>
-      </c>
-      <c r="E29" t="s">
-        <v>3304</v>
-      </c>
-      <c r="F29" t="s">
-        <v>3088</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>3359</v>
       </c>
       <c r="H29" t="s">
         <v>407</v>
@@ -49785,7 +49785,7 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="B30">
         <v>63926844</v>
@@ -49797,10 +49797,10 @@
         <v>2705</v>
       </c>
       <c r="E30" t="s">
+        <v>3086</v>
+      </c>
+      <c r="F30" t="s">
         <v>3087</v>
-      </c>
-      <c r="F30" t="s">
-        <v>3088</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -49814,10 +49814,10 @@
         <v>1561</v>
       </c>
       <c r="D31" t="s">
+        <v>3327</v>
+      </c>
+      <c r="E31" t="s">
         <v>3328</v>
-      </c>
-      <c r="E31" t="s">
-        <v>3329</v>
       </c>
       <c r="F31" t="s">
         <v>1316</v>
@@ -49926,10 +49926,10 @@
         <v>2516</v>
       </c>
       <c r="D47" s="30" t="s">
+        <v>2892</v>
+      </c>
+      <c r="F47" s="397" t="s">
         <v>2893</v>
-      </c>
-      <c r="F47" s="397" t="s">
-        <v>2894</v>
       </c>
       <c r="G47" s="30" t="s">
         <v>407</v>
@@ -51861,7 +51861,7 @@
     </row>
     <row r="252" spans="1:6" s="420" customFormat="1" ht="21">
       <c r="C252" s="420" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
     </row>
     <row r="253" spans="1:6">
@@ -51878,30 +51878,30 @@
         <v>2251</v>
       </c>
       <c r="E253" t="s">
+        <v>3042</v>
+      </c>
+      <c r="F253" t="s">
         <v>3043</v>
-      </c>
-      <c r="F253" t="s">
-        <v>3044</v>
       </c>
     </row>
     <row r="254" spans="1:6">
       <c r="A254" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="B254">
         <v>64738222</v>
       </c>
       <c r="C254" s="22" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="D254" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="E254" t="s">
+        <v>3042</v>
+      </c>
+      <c r="F254" t="s">
         <v>3043</v>
-      </c>
-      <c r="F254" t="s">
-        <v>3044</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -51912,16 +51912,16 @@
         <v>60433915</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="D255" s="251" t="s">
         <v>2647</v>
       </c>
       <c r="E255" t="s">
+        <v>3042</v>
+      </c>
+      <c r="F255" t="s">
         <v>3043</v>
-      </c>
-      <c r="F255" t="s">
-        <v>3044</v>
       </c>
     </row>
     <row r="256" spans="1:6">
@@ -56675,7 +56675,7 @@
         <v>2694</v>
       </c>
       <c r="E537" s="76" t="s">
-        <v>3226</v>
+        <v>3225</v>
       </c>
       <c r="F537" s="76"/>
       <c r="G537" s="76"/>

--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dc549f2659ed9bd7/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63135" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A523650B-8008-4BB4-B352-F76210D0216D}"/>
+  <xr:revisionPtr revIDLastSave="63137" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6EEF9C8-AE95-4A94-8615-A4672F96FF46}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10089,9 +10089,6 @@
     <t>Trda190826</t>
   </si>
   <si>
-    <t>66310836 1 pantalla hasta el 19 de septiembre (Argelis) 180826-2044</t>
-  </si>
-  <si>
     <t>63989201 (Luis)</t>
   </si>
   <si>
@@ -12301,6 +12298,9 @@
   </si>
   <si>
     <t>N005 1 pantalla hasta el 23 de octubre 220926-2350e</t>
+  </si>
+  <si>
+    <t>N005 1 pantalla hasta el 23 de octubre 220926-2359f</t>
   </si>
 </sst>
 </file>
@@ -30268,7 +30268,7 @@
   <sheetData>
     <row r="1" spans="1:11" s="30" customFormat="1">
       <c r="A1" s="30" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1" s="30">
         <v>60389752</v>
@@ -30280,7 +30280,7 @@
         <v>2007</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="F1" s="30" t="s">
         <v>2073</v>
@@ -30300,7 +30300,7 @@
         <v>2119</v>
       </c>
       <c r="D2" s="148" t="s">
-        <v>2983</v>
+        <v>2982</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="148" customFormat="1">
@@ -30319,7 +30319,7 @@
     </row>
     <row r="4" spans="1:11" s="30" customFormat="1">
       <c r="A4" s="30" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B4" s="30">
         <v>60389752</v>
@@ -30331,7 +30331,7 @@
         <v>2005</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>3631</v>
+        <v>3630</v>
       </c>
       <c r="F4" s="30" t="s">
         <v>2073</v>
@@ -30351,7 +30351,7 @@
         <v>2133</v>
       </c>
       <c r="D5" s="148" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="148" customFormat="1">
@@ -30382,7 +30382,7 @@
         <v>2828</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="F7" s="30" t="s">
         <v>2078</v>
@@ -30402,12 +30402,12 @@
         <v>2234</v>
       </c>
       <c r="D8" s="148" t="s">
-        <v>3482</v>
+        <v>3481</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="148" customFormat="1">
       <c r="A9" s="148" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="B9" s="148" t="s">
         <v>1200</v>
@@ -30424,7 +30424,7 @@
     </row>
     <row r="10" spans="1:11" s="422" customFormat="1">
       <c r="A10" s="422" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="B10" s="422">
         <v>60389752</v>
@@ -30449,7 +30449,7 @@
     <row r="12" spans="1:11" s="369" customFormat="1"/>
     <row r="13" spans="1:11" s="30" customFormat="1">
       <c r="A13" s="30" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="B13" s="30">
         <v>69184177</v>
@@ -30458,10 +30458,10 @@
         <v>1771</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>3583</v>
+        <v>3582</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="F13" s="30" t="s">
         <v>2137</v>
@@ -30473,7 +30473,7 @@
     </row>
     <row r="14" spans="1:11" s="148" customFormat="1">
       <c r="A14" s="225" t="s">
-        <v>3504</v>
+        <v>3503</v>
       </c>
       <c r="B14" s="225" t="s">
         <v>1671</v>
@@ -30487,7 +30487,7 @@
     </row>
     <row r="15" spans="1:11" s="148" customFormat="1">
       <c r="A15" s="225" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="B15" s="416">
         <v>62439069</v>
@@ -30501,7 +30501,7 @@
     </row>
     <row r="16" spans="1:11" s="32" customFormat="1">
       <c r="A16" s="30" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="B16" s="284" t="s">
         <v>2190</v>
@@ -30510,10 +30510,10 @@
         <v>1523</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="F16" s="32" t="s">
         <v>1524</v>
@@ -30522,21 +30522,21 @@
         <v>198</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="I16" s="32" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="J16" s="32" t="s">
+        <v>3135</v>
+      </c>
+      <c r="K16" s="30" t="s">
         <v>3136</v>
-      </c>
-      <c r="K16" s="30" t="s">
-        <v>3137</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="164" customFormat="1">
       <c r="A17" s="252" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="B17" s="252" t="s">
         <v>1391</v>
@@ -30553,7 +30553,7 @@
     </row>
     <row r="18" spans="1:11" s="164" customFormat="1">
       <c r="A18" s="252" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
       <c r="B18" s="252">
         <v>64341760</v>
@@ -30579,10 +30579,10 @@
         <v>1488</v>
       </c>
       <c r="D19" s="145" t="s">
-        <v>3427</v>
+        <v>3426</v>
       </c>
       <c r="E19" s="145" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="F19" s="145" t="s">
         <v>1358</v>
@@ -30614,7 +30614,7 @@
     </row>
     <row r="21" spans="1:11" s="297" customFormat="1">
       <c r="A21" s="252" t="s">
-        <v>3436</v>
+        <v>3435</v>
       </c>
       <c r="B21" s="252">
         <v>62169673</v>
@@ -30623,7 +30623,7 @@
         <v>1682</v>
       </c>
       <c r="D21" s="164" t="s">
-        <v>3428</v>
+        <v>3427</v>
       </c>
       <c r="E21" s="164" t="s">
         <v>1683</v>
@@ -30643,7 +30643,7 @@
         <v>2116</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="F22" s="30" t="s">
         <v>2072</v>
@@ -30654,7 +30654,7 @@
     </row>
     <row r="23" spans="1:11" s="148" customFormat="1">
       <c r="A23" s="225" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B23" s="148">
         <v>64858241</v>
@@ -30668,7 +30668,7 @@
     </row>
     <row r="24" spans="1:11" s="148" customFormat="1">
       <c r="A24" s="149" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B24" s="149">
         <v>68934853</v>
@@ -30677,7 +30677,7 @@
         <v>2112</v>
       </c>
       <c r="D24" s="148" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="30" customFormat="1">
@@ -30694,7 +30694,7 @@
         <v>1520</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="F25" s="30" t="s">
         <v>1358</v>
@@ -30742,7 +30742,7 @@
     </row>
     <row r="28" spans="1:11" s="30" customFormat="1">
       <c r="A28" s="30" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="B28" s="30">
         <v>60389752</v>
@@ -30754,7 +30754,7 @@
         <v>2002</v>
       </c>
       <c r="E28" s="30" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="F28" s="303" t="s">
         <v>2146</v>
@@ -30779,7 +30779,7 @@
     </row>
     <row r="30" spans="1:11" s="164" customFormat="1">
       <c r="A30" s="164" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="B30" s="164">
         <v>62782770</v>
@@ -30793,19 +30793,19 @@
     </row>
     <row r="31" spans="1:11" s="30" customFormat="1">
       <c r="A31" s="461" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="B31" s="461" t="s">
-        <v>3671</v>
+        <v>3670</v>
       </c>
       <c r="C31" s="251" t="s">
         <v>1896</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
       <c r="E31" s="30" t="s">
-        <v>3582</v>
+        <v>3581</v>
       </c>
       <c r="F31" s="30" t="s">
         <v>2023</v>
@@ -30814,16 +30814,16 @@
         <v>198</v>
       </c>
       <c r="H31" s="145" t="s">
-        <v>3673</v>
+        <v>3672</v>
       </c>
       <c r="I31" s="192" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="J31" s="458" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="K31" s="30" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="163" customFormat="1">
@@ -30869,7 +30869,7 @@
         <v>2085</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="F34" s="30" t="s">
         <v>2076</v>
@@ -30889,7 +30889,7 @@
         <v>1979</v>
       </c>
       <c r="D35" s="148" t="s">
-        <v>3508</v>
+        <v>3507</v>
       </c>
       <c r="E35" s="148" t="s">
         <v>1981</v>
@@ -30911,7 +30911,7 @@
     </row>
     <row r="37" spans="1:11" s="30" customFormat="1">
       <c r="A37" s="30" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
       <c r="B37" s="30" t="s">
         <v>2704</v>
@@ -30920,10 +30920,10 @@
         <v>2000</v>
       </c>
       <c r="D37" s="30" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="E37" s="30" t="s">
-        <v>3558</v>
+        <v>3557</v>
       </c>
       <c r="F37" s="30" t="s">
         <v>2066</v>
@@ -30932,16 +30932,16 @@
         <v>198</v>
       </c>
       <c r="H37" s="145" t="s">
-        <v>3565</v>
+        <v>3564</v>
       </c>
       <c r="I37" s="30" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="J37" s="30" t="s">
-        <v>3429</v>
+        <v>3428</v>
       </c>
       <c r="K37" s="30" t="s">
-        <v>3294</v>
+        <v>3293</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="147" customFormat="1">
@@ -30978,16 +30978,16 @@
         <v>2469</v>
       </c>
       <c r="B40" s="32" t="s">
-        <v>3088</v>
+        <v>3087</v>
       </c>
       <c r="C40" s="251" t="s">
         <v>1658</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="E40" s="30" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="F40" s="30" t="s">
         <v>2081</v>
@@ -30996,21 +30996,21 @@
         <v>198</v>
       </c>
       <c r="H40" s="30" t="s">
-        <v>3555</v>
+        <v>3554</v>
       </c>
       <c r="I40" s="32" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="J40" s="32" t="s">
-        <v>3074</v>
+        <v>3073</v>
       </c>
       <c r="K40" s="145" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="163" customFormat="1">
       <c r="A41" s="163" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="B41" s="163">
         <v>68381893</v>
@@ -31042,7 +31042,7 @@
     </row>
     <row r="43" spans="1:11" s="30" customFormat="1">
       <c r="A43" s="30" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="B43" s="30">
         <v>60389752</v>
@@ -31054,7 +31054,7 @@
         <v>2027</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>3632</v>
+        <v>3631</v>
       </c>
       <c r="F43" s="30" t="s">
         <v>2113</v>
@@ -31065,7 +31065,7 @@
     </row>
     <row r="44" spans="1:11" s="164" customFormat="1">
       <c r="A44" s="164" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="B44" s="164">
         <v>68381893</v>
@@ -31082,7 +31082,7 @@
     </row>
     <row r="45" spans="1:11" s="163" customFormat="1">
       <c r="A45" s="163" t="s">
-        <v>3306</v>
+        <v>3305</v>
       </c>
       <c r="B45" s="163">
         <v>64079861</v>
@@ -31111,7 +31111,7 @@
         <v>2822</v>
       </c>
       <c r="E46" s="30" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
       <c r="F46" s="30" t="s">
         <v>2097</v>
@@ -31123,7 +31123,7 @@
     </row>
     <row r="47" spans="1:11" s="164" customFormat="1">
       <c r="A47" s="164" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B47" s="164">
         <v>63183787</v>
@@ -31157,16 +31157,16 @@
         <v>1495</v>
       </c>
       <c r="B49" s="30" t="s">
-        <v>3314</v>
+        <v>3313</v>
       </c>
       <c r="C49" s="134" t="s">
         <v>1991</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
       <c r="E49" s="30" t="s">
-        <v>3462</v>
+        <v>3461</v>
       </c>
       <c r="F49" s="30" t="s">
         <v>2084</v>
@@ -31175,16 +31175,16 @@
         <v>198</v>
       </c>
       <c r="H49" s="30" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="I49" s="30" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="J49" s="30" t="s">
-        <v>3511</v>
+        <v>3510</v>
       </c>
       <c r="K49" s="32" t="s">
-        <v>3196</v>
+        <v>3195</v>
       </c>
     </row>
     <row r="50" spans="1:12" s="164" customFormat="1">
@@ -31212,7 +31212,7 @@
         <v>1999</v>
       </c>
       <c r="D51" s="164" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
     </row>
     <row r="52" spans="1:12" s="139" customFormat="1">
@@ -31229,7 +31229,7 @@
         <v>2834</v>
       </c>
       <c r="E52" s="139" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="F52" s="139" t="s">
         <v>2082</v>
@@ -31238,16 +31238,16 @@
         <v>198</v>
       </c>
       <c r="H52" s="140" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="I52" s="140" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="J52" s="30" t="s">
-        <v>3168</v>
+        <v>3167</v>
       </c>
       <c r="K52" s="269" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
     </row>
     <row r="53" spans="1:12" s="164" customFormat="1">
@@ -31288,7 +31288,7 @@
     </row>
     <row r="55" spans="1:12" s="30" customFormat="1">
       <c r="A55" s="30" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="B55" s="30">
         <v>61130088</v>
@@ -31300,7 +31300,7 @@
         <v>1995</v>
       </c>
       <c r="E55" s="30" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="F55" s="30" t="s">
         <v>2098</v>
@@ -31317,10 +31317,10 @@
         <v>60433915</v>
       </c>
       <c r="C56" s="400" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="D56" s="370" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="E56" s="164"/>
     </row>
@@ -31329,19 +31329,19 @@
         <v>2469</v>
       </c>
       <c r="B57" s="163" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
       <c r="C57" s="400" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="D57" s="370" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="E57" s="164"/>
     </row>
     <row r="58" spans="1:12" s="30" customFormat="1">
       <c r="A58" s="30" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B58" s="412" t="s">
         <v>2064</v>
@@ -31353,7 +31353,7 @@
         <v>2768</v>
       </c>
       <c r="E58" s="30" t="s">
-        <v>3609</v>
+        <v>3608</v>
       </c>
       <c r="F58" s="30" t="s">
         <v>2110</v>
@@ -31362,30 +31362,30 @@
         <v>198</v>
       </c>
       <c r="H58" s="30" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
       <c r="I58" s="30" t="s">
-        <v>3086</v>
+        <v>3085</v>
       </c>
       <c r="J58" s="30" t="s">
-        <v>3172</v>
+        <v>3171</v>
       </c>
       <c r="K58" s="30" t="s">
-        <v>3479</v>
+        <v>3478</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" s="147" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="B59" s="147">
         <v>67539485</v>
       </c>
       <c r="C59" s="399" t="s">
-        <v>3607</v>
+        <v>3606</v>
       </c>
       <c r="D59" s="371" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
       <c r="E59" s="148"/>
       <c r="F59" s="147"/>
@@ -31398,16 +31398,16 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" s="147" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="B60" s="147">
         <v>68853797</v>
       </c>
       <c r="C60" s="399" t="s">
-        <v>3608</v>
+        <v>3607</v>
       </c>
       <c r="D60" s="371" t="s">
-        <v>3611</v>
+        <v>3610</v>
       </c>
       <c r="E60" s="147"/>
       <c r="F60" s="147"/>
@@ -31423,7 +31423,7 @@
         <v>158</v>
       </c>
       <c r="B61" s="30" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="C61" s="134" t="s">
         <v>2065</v>
@@ -31432,7 +31432,7 @@
         <v>2825</v>
       </c>
       <c r="E61" s="30" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="F61" s="30" t="s">
         <v>2066</v>
@@ -31441,21 +31441,21 @@
         <v>198</v>
       </c>
       <c r="H61" s="30" t="s">
-        <v>3332</v>
+        <v>3331</v>
       </c>
       <c r="I61" s="30" t="s">
-        <v>3104</v>
+        <v>3103</v>
       </c>
       <c r="J61" s="30" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="K61" s="30" t="s">
-        <v>3291</v>
+        <v>3290</v>
       </c>
     </row>
     <row r="62" spans="1:12" s="147" customFormat="1">
       <c r="A62" s="147" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="B62" s="147">
         <v>60196388</v>
@@ -31464,7 +31464,7 @@
         <v>1467</v>
       </c>
       <c r="D62" s="371" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="E62" s="148" t="s">
         <v>1377</v>
@@ -31472,7 +31472,7 @@
     </row>
     <row r="63" spans="1:12" s="163" customFormat="1">
       <c r="A63" s="163" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B63" s="163">
         <v>62960567</v>
@@ -31481,13 +31481,13 @@
         <v>2050</v>
       </c>
       <c r="D63" s="370" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="E63" s="164"/>
     </row>
     <row r="64" spans="1:12" s="30" customFormat="1">
       <c r="A64" s="32" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B64" s="32" t="s">
         <v>2117</v>
@@ -31496,10 +31496,10 @@
         <v>1657</v>
       </c>
       <c r="D64" s="30" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="E64" s="30" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="F64" s="30" t="s">
         <v>2083</v>
@@ -31508,16 +31508,16 @@
         <v>198</v>
       </c>
       <c r="H64" s="32" t="s">
-        <v>3304</v>
+        <v>3303</v>
       </c>
       <c r="I64" s="32" t="s">
-        <v>3370</v>
+        <v>3369</v>
       </c>
       <c r="J64" s="30" t="s">
-        <v>3258</v>
+        <v>3257</v>
       </c>
       <c r="K64" s="30" t="s">
-        <v>3087</v>
+        <v>3086</v>
       </c>
     </row>
     <row r="65" spans="1:11" s="164" customFormat="1">
@@ -31556,7 +31556,7 @@
     </row>
     <row r="67" spans="1:11" s="30" customFormat="1">
       <c r="A67" s="253" t="s">
-        <v>3378</v>
+        <v>3377</v>
       </c>
       <c r="B67" s="284" t="s">
         <v>1904</v>
@@ -31568,7 +31568,7 @@
         <v>2929</v>
       </c>
       <c r="E67" s="30" t="s">
-        <v>3512</v>
+        <v>3511</v>
       </c>
       <c r="F67" s="30" t="s">
         <v>2087</v>
@@ -31577,21 +31577,21 @@
         <v>198</v>
       </c>
       <c r="H67" s="30" t="s">
-        <v>3578</v>
+        <v>3577</v>
       </c>
       <c r="I67" s="30" t="s">
-        <v>3358</v>
+        <v>3357</v>
       </c>
       <c r="J67" s="30" t="s">
-        <v>3404</v>
-      </c>
-      <c r="K67" s="217" t="s">
-        <v>2936</v>
+        <v>3403</v>
+      </c>
+      <c r="K67" s="145" t="s">
+        <v>3673</v>
       </c>
     </row>
     <row r="68" spans="1:11" s="147" customFormat="1">
       <c r="A68" s="147" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="B68" s="147">
         <v>68741448</v>
@@ -31600,13 +31600,13 @@
         <v>1872</v>
       </c>
       <c r="D68" s="371" t="s">
-        <v>3040</v>
+        <v>3039</v>
       </c>
       <c r="E68" s="148"/>
     </row>
     <row r="69" spans="1:11" s="148" customFormat="1">
       <c r="A69" s="225" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="B69" s="148">
         <v>63018763</v>
@@ -31615,7 +31615,7 @@
         <v>2086</v>
       </c>
       <c r="D69" s="148" t="s">
-        <v>3521</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="70" spans="1:11" s="30" customFormat="1">
@@ -31623,16 +31623,16 @@
         <v>467</v>
       </c>
       <c r="B70" s="32" t="s">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="C70" s="251" t="s">
         <v>1660</v>
       </c>
       <c r="D70" s="30" t="s">
-        <v>3177</v>
+        <v>3176</v>
       </c>
       <c r="E70" s="30" t="s">
-        <v>3129</v>
+        <v>3128</v>
       </c>
       <c r="F70" s="30" t="s">
         <v>2124</v>
@@ -31641,13 +31641,13 @@
         <v>198</v>
       </c>
       <c r="H70" s="32" t="s">
-        <v>3510</v>
+        <v>3509</v>
       </c>
       <c r="I70" s="145" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
       <c r="J70" s="30" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
     </row>
     <row r="71" spans="1:11" s="164" customFormat="1">
@@ -31666,7 +31666,7 @@
     </row>
     <row r="72" spans="1:11" s="163" customFormat="1">
       <c r="A72" s="268" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="B72" s="268" t="s">
         <v>1449</v>
@@ -31681,7 +31681,7 @@
     </row>
     <row r="73" spans="1:11" s="30" customFormat="1">
       <c r="A73" s="30" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
       <c r="B73" s="30">
         <v>60389752</v>
@@ -31693,7 +31693,7 @@
         <v>2779</v>
       </c>
       <c r="E73" s="30" t="s">
-        <v>3307</v>
+        <v>3306</v>
       </c>
       <c r="F73" s="30" t="s">
         <v>2022</v>
@@ -31704,7 +31704,7 @@
     </row>
     <row r="74" spans="1:11" s="147" customFormat="1">
       <c r="A74" s="147" t="s">
-        <v>3504</v>
+        <v>3503</v>
       </c>
       <c r="B74" s="147">
         <v>64226974</v>
@@ -31728,7 +31728,7 @@
         <v>1941</v>
       </c>
       <c r="D75" s="148" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="E75" s="148"/>
     </row>
@@ -31746,7 +31746,7 @@
         <v>2900</v>
       </c>
       <c r="E76" s="30" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="F76" s="30" t="s">
         <v>2097</v>
@@ -31755,16 +31755,16 @@
         <v>198</v>
       </c>
       <c r="H76" s="30" t="s">
-        <v>3463</v>
+        <v>3462</v>
       </c>
       <c r="I76" s="30" t="s">
-        <v>3509</v>
+        <v>3508</v>
       </c>
       <c r="J76" s="30" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="K76" s="217" t="s">
-        <v>3178</v>
+        <v>3177</v>
       </c>
     </row>
     <row r="77" spans="1:11" s="152" customFormat="1">
@@ -31789,7 +31789,7 @@
         <v>2914</v>
       </c>
       <c r="E79" s="30" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="F79" s="30" t="s">
         <v>2077</v>
@@ -31801,13 +31801,13 @@
         <v>2926</v>
       </c>
       <c r="I79" s="32" t="s">
-        <v>3083</v>
+        <v>3082</v>
       </c>
       <c r="J79" s="30" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="K79" s="30" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="80" spans="1:11" s="147" customFormat="1">
@@ -31827,7 +31827,7 @@
     </row>
     <row r="81" spans="1:11" s="147" customFormat="1">
       <c r="A81" s="149" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B81" s="147">
         <v>64720128</v>
@@ -31844,10 +31844,10 @@
     </row>
     <row r="82" spans="1:11" s="30" customFormat="1">
       <c r="A82" s="145" t="s">
-        <v>3504</v>
+        <v>3503</v>
       </c>
       <c r="B82" s="30" t="s">
-        <v>3561</v>
+        <v>3560</v>
       </c>
       <c r="C82" s="22" t="s">
         <v>1897</v>
@@ -31865,16 +31865,16 @@
         <v>198</v>
       </c>
       <c r="H82" s="30" t="s">
-        <v>3377</v>
+        <v>3376</v>
       </c>
       <c r="I82" s="217" t="s">
-        <v>3225</v>
+        <v>3224</v>
       </c>
       <c r="J82" s="30" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="K82" s="30" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
     </row>
     <row r="83" spans="1:11" s="148" customFormat="1">
@@ -31882,13 +31882,13 @@
         <v>1513</v>
       </c>
       <c r="B83" s="225" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
       <c r="C83" s="398" t="s">
         <v>1954</v>
       </c>
       <c r="D83" s="148" t="s">
-        <v>3559</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="84" spans="1:11" s="280" customFormat="1">
@@ -31916,7 +31916,7 @@
         <v>693</v>
       </c>
       <c r="D85" s="30" t="s">
-        <v>3226</v>
+        <v>3225</v>
       </c>
       <c r="E85" s="30" t="s">
         <v>1787</v>
@@ -31928,16 +31928,16 @@
         <v>493</v>
       </c>
       <c r="H85" s="30" t="s">
-        <v>3339</v>
+        <v>3338</v>
       </c>
       <c r="I85" s="32" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
       <c r="J85" s="30" t="s">
-        <v>3359</v>
+        <v>3358</v>
       </c>
       <c r="K85" s="215" t="s">
-        <v>3535</v>
+        <v>3534</v>
       </c>
     </row>
     <row r="86" spans="1:11" s="147" customFormat="1">
@@ -31960,7 +31960,7 @@
     </row>
     <row r="87" spans="1:11" s="147" customFormat="1">
       <c r="A87" s="147" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="B87" s="147" t="s">
         <v>909</v>
@@ -31978,10 +31978,10 @@
     </row>
     <row r="88" spans="1:11" s="30" customFormat="1">
       <c r="A88" s="30" t="s">
-        <v>3601</v>
+        <v>3600</v>
       </c>
       <c r="B88" s="30" t="s">
-        <v>3581</v>
+        <v>3580</v>
       </c>
       <c r="C88" s="153" t="s">
         <v>694</v>
@@ -31999,16 +31999,16 @@
         <v>1521</v>
       </c>
       <c r="H88" s="30" t="s">
-        <v>3602</v>
+        <v>3601</v>
       </c>
       <c r="I88" s="145" t="s">
-        <v>3567</v>
+        <v>3566</v>
       </c>
       <c r="J88" s="431" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
       <c r="K88" s="30" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
     </row>
     <row r="89" spans="1:11" s="147" customFormat="1">
@@ -32031,7 +32031,7 @@
     </row>
     <row r="90" spans="1:11" s="148" customFormat="1">
       <c r="A90" s="225" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="B90" s="148">
         <v>67381873</v>
@@ -32049,7 +32049,7 @@
     </row>
     <row r="91" spans="1:11" s="106" customFormat="1">
       <c r="A91" s="249" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="B91" s="32" t="s">
         <v>1397</v>
@@ -32058,7 +32058,7 @@
         <v>46</v>
       </c>
       <c r="D91" s="106" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="E91" s="106" t="s">
         <v>1120</v>
@@ -32070,16 +32070,16 @@
         <v>66</v>
       </c>
       <c r="H91" s="30" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="I91" s="31" t="s">
-        <v>3585</v>
+        <v>3584</v>
       </c>
       <c r="J91" s="431" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="K91" s="30" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="406" customFormat="1">
@@ -32110,7 +32110,7 @@
         <v>1714</v>
       </c>
       <c r="D93" s="148" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
     </row>
     <row r="94" spans="1:11" s="32" customFormat="1">
@@ -32127,7 +32127,7 @@
         <v>1359</v>
       </c>
       <c r="E94" s="32" t="s">
-        <v>3344</v>
+        <v>3343</v>
       </c>
       <c r="F94" s="32" t="s">
         <v>1360</v>
@@ -32139,7 +32139,7 @@
     </row>
     <row r="95" spans="1:11" s="148" customFormat="1">
       <c r="A95" s="148" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="B95" s="148" t="s">
         <v>2623</v>
@@ -32156,7 +32156,7 @@
     </row>
     <row r="96" spans="1:11" s="148" customFormat="1">
       <c r="A96" s="148" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="B96" s="148">
         <v>65633205</v>
@@ -32165,7 +32165,7 @@
         <v>1376</v>
       </c>
       <c r="D96" s="148" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
       <c r="E96" s="148" t="s">
         <v>1375</v>
@@ -32173,7 +32173,7 @@
     </row>
     <row r="97" spans="1:13" s="30" customFormat="1">
       <c r="A97" s="460" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="B97" s="30" t="s">
         <v>2881</v>
@@ -32194,16 +32194,16 @@
         <v>198</v>
       </c>
       <c r="H97" s="32" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="I97" s="30" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="J97" s="30" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="K97" s="429" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
     </row>
     <row r="98" spans="1:13" s="388" customFormat="1">
@@ -32216,19 +32216,19 @@
     </row>
     <row r="100" spans="1:13" s="30" customFormat="1">
       <c r="A100" s="30" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="B100" s="30" t="s">
-        <v>3552</v>
+        <v>3551</v>
       </c>
       <c r="C100" s="251" t="s">
         <v>2807</v>
       </c>
       <c r="D100" s="30" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="E100" s="30" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="F100" s="30" t="s">
         <v>1898</v>
@@ -32237,16 +32237,16 @@
         <v>198</v>
       </c>
       <c r="H100" s="30" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="I100" s="30" t="s">
-        <v>3529</v>
+        <v>3528</v>
       </c>
       <c r="J100" s="30" t="s">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="K100" s="30" t="s">
-        <v>3466</v>
+        <v>3465</v>
       </c>
     </row>
     <row r="101" spans="1:13" s="388" customFormat="1">
@@ -32259,19 +32259,19 @@
     </row>
     <row r="103" spans="1:13" s="30" customFormat="1">
       <c r="A103" s="30" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="B103" s="30" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="C103" s="251" t="s">
         <v>2847</v>
       </c>
       <c r="D103" s="30" t="s">
+        <v>3104</v>
+      </c>
+      <c r="E103" s="30" t="s">
         <v>3105</v>
-      </c>
-      <c r="E103" s="30" t="s">
-        <v>3106</v>
       </c>
       <c r="F103" s="30" t="s">
         <v>1898</v>
@@ -32280,16 +32280,16 @@
         <v>198</v>
       </c>
       <c r="H103" s="30" t="s">
-        <v>3107</v>
+        <v>3106</v>
       </c>
       <c r="I103" s="30" t="s">
-        <v>3180</v>
+        <v>3179</v>
       </c>
       <c r="J103" s="30" t="s">
-        <v>3167</v>
+        <v>3166</v>
       </c>
       <c r="K103" s="30" t="s">
-        <v>3131</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -32333,13 +32333,13 @@
         <v>2846</v>
       </c>
       <c r="D106" s="30" t="s">
+        <v>2955</v>
+      </c>
+      <c r="E106" s="453" t="s">
+        <v>2957</v>
+      </c>
+      <c r="F106" s="30" t="s">
         <v>2956</v>
-      </c>
-      <c r="E106" s="453" t="s">
-        <v>2958</v>
-      </c>
-      <c r="F106" s="30" t="s">
-        <v>2957</v>
       </c>
       <c r="G106" s="30" t="s">
         <v>59</v>
@@ -32391,7 +32391,7 @@
         <v>1977</v>
       </c>
       <c r="E127" s="30" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="F127" t="s">
         <v>1975</v>
@@ -32411,7 +32411,7 @@
         <v>1947</v>
       </c>
       <c r="E128" s="30" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -32425,15 +32425,15 @@
         <v>2692</v>
       </c>
       <c r="D129" s="373" t="s">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="E129" s="30" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="4" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B130">
         <v>67046608</v>
@@ -32445,7 +32445,7 @@
         <v>2573</v>
       </c>
       <c r="E130" s="30" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -32462,7 +32462,7 @@
         <v>1953</v>
       </c>
       <c r="E131" s="30" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
     </row>
     <row r="133" spans="1:6" s="121" customFormat="1" ht="23.5">
@@ -32484,7 +32484,7 @@
         <v>2334</v>
       </c>
       <c r="E134" s="30" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="F134" t="s">
         <v>1336</v>
@@ -32504,7 +32504,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="B139">
         <v>64720128</v>
@@ -32533,7 +32533,7 @@
         <v>1964</v>
       </c>
       <c r="D140" s="373" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="E140" s="30" t="s">
         <v>1963</v>
@@ -32558,7 +32558,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="C143" s="1" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -32602,7 +32602,7 @@
         <v>2339</v>
       </c>
       <c r="E153" s="30" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -32610,21 +32610,21 @@
         <v>1495</v>
       </c>
       <c r="B154" t="s">
-        <v>3274</v>
+        <v>3273</v>
       </c>
       <c r="C154" t="s">
         <v>2216</v>
       </c>
       <c r="D154" s="373" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
       <c r="E154" s="30" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B155">
         <v>60183566</v>
@@ -32636,12 +32636,12 @@
         <v>2574</v>
       </c>
       <c r="E155" s="30" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="B156">
         <v>63145336</v>
@@ -32650,10 +32650,10 @@
         <v>2225</v>
       </c>
       <c r="D156" s="373" t="s">
-        <v>3562</v>
+        <v>3561</v>
       </c>
       <c r="E156" s="30" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -32670,12 +32670,12 @@
         <v>2470</v>
       </c>
       <c r="E157" s="30" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="B158">
         <v>64982293</v>
@@ -32684,10 +32684,10 @@
         <v>2227</v>
       </c>
       <c r="D158" s="373" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="E158" s="30" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -32701,15 +32701,15 @@
         <v>2488</v>
       </c>
       <c r="D159" s="373" t="s">
-        <v>3276</v>
+        <v>3275</v>
       </c>
       <c r="E159" s="30" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="B160">
         <v>65133588</v>
@@ -32721,12 +32721,12 @@
         <v>2489</v>
       </c>
       <c r="E160" s="30" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="4" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>1134</v>
@@ -32735,10 +32735,10 @@
         <v>2575</v>
       </c>
       <c r="D161" s="373" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="E161" s="30" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -32752,32 +32752,32 @@
         <v>2491</v>
       </c>
       <c r="D162" s="373" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
       <c r="E162" s="30" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="B163">
         <v>67570116</v>
       </c>
       <c r="C163" t="s">
-        <v>3564</v>
+        <v>3563</v>
       </c>
       <c r="D163" s="373" t="s">
-        <v>3598</v>
+        <v>3597</v>
       </c>
       <c r="E163" s="30" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="4" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>2160</v>
@@ -32789,12 +32789,12 @@
         <v>2471</v>
       </c>
       <c r="E164" s="30" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="B165">
         <v>66315726</v>
@@ -32806,12 +32806,12 @@
         <v>2263</v>
       </c>
       <c r="E165" s="30" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="B166">
         <v>64568369</v>
@@ -32823,24 +32823,24 @@
         <v>2263</v>
       </c>
       <c r="E166" s="30" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="B167">
         <v>68818154</v>
       </c>
       <c r="C167" t="s">
-        <v>3277</v>
+        <v>3276</v>
       </c>
       <c r="D167" s="373" t="s">
         <v>2576</v>
       </c>
       <c r="E167" s="30" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -32854,10 +32854,10 @@
         <v>2694</v>
       </c>
       <c r="D168" s="373" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
       <c r="E168" s="30" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -32874,7 +32874,7 @@
         <v>2728</v>
       </c>
       <c r="E169" s="30" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -32891,7 +32891,7 @@
         <v>2468</v>
       </c>
       <c r="E170" s="30" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -32908,7 +32908,7 @@
         <v>2301</v>
       </c>
       <c r="E171" s="30" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -32919,10 +32919,10 @@
         <v>2313</v>
       </c>
       <c r="D172" s="373" t="s">
-        <v>3661</v>
+        <v>3660</v>
       </c>
       <c r="E172" s="30" t="s">
-        <v>3659</v>
+        <v>3658</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -32936,10 +32936,10 @@
         <v>2314</v>
       </c>
       <c r="D173" s="373" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="E173" s="30" t="s">
-        <v>3659</v>
+        <v>3658</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -32953,15 +32953,15 @@
         <v>2315</v>
       </c>
       <c r="D174" s="373" t="s">
-        <v>3141</v>
+        <v>3140</v>
       </c>
       <c r="E174" s="30" t="s">
-        <v>3659</v>
+        <v>3658</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" t="s">
-        <v>3504</v>
+        <v>3503</v>
       </c>
       <c r="B175">
         <v>67178677</v>
@@ -32970,15 +32970,15 @@
         <v>2730</v>
       </c>
       <c r="D175" s="373" t="s">
-        <v>3563</v>
+        <v>3562</v>
       </c>
       <c r="E175" s="30" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="B176">
         <v>66935922</v>
@@ -32987,27 +32987,27 @@
         <v>2731</v>
       </c>
       <c r="D176" s="220" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="E176" s="30" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B177">
         <v>64455322</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>3100</v>
+        <v>3099</v>
       </c>
       <c r="D177" s="220" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="E177" s="30" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -33024,12 +33024,12 @@
         <v>2750</v>
       </c>
       <c r="E178" s="30" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B179">
         <v>68570552</v>
@@ -33038,15 +33038,15 @@
         <v>2733</v>
       </c>
       <c r="D179" s="220" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
       <c r="E179" s="30" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B180">
         <v>69964218</v>
@@ -33055,15 +33055,15 @@
         <v>2755</v>
       </c>
       <c r="D180" s="373" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="E180" s="30" t="s">
-        <v>3103</v>
+        <v>3102</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="B181">
         <v>63950696</v>
@@ -33075,12 +33075,12 @@
         <v>2756</v>
       </c>
       <c r="E181" s="30" t="s">
-        <v>3103</v>
+        <v>3102</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="4" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="B182" t="s">
         <v>2784</v>
@@ -33092,7 +33092,7 @@
         <v>2756</v>
       </c>
       <c r="E182" s="30" t="s">
-        <v>3103</v>
+        <v>3102</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -33109,12 +33109,12 @@
         <v>2829</v>
       </c>
       <c r="E183" s="30" t="s">
-        <v>3103</v>
+        <v>3102</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B184">
         <v>63755362</v>
@@ -33123,15 +33123,15 @@
         <v>2819</v>
       </c>
       <c r="D184" s="373" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="E184" s="30" t="s">
-        <v>3103</v>
+        <v>3102</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="B185">
         <v>61248427</v>
@@ -33140,15 +33140,15 @@
         <v>2789</v>
       </c>
       <c r="D185" s="373" t="s">
-        <v>3584</v>
+        <v>3583</v>
       </c>
       <c r="E185" s="30" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="B186">
         <v>60240509</v>
@@ -33157,10 +33157,10 @@
         <v>2790</v>
       </c>
       <c r="D186" s="373" t="s">
+        <v>3371</v>
+      </c>
+      <c r="E186" s="30" t="s">
         <v>3372</v>
-      </c>
-      <c r="E186" s="30" t="s">
-        <v>3373</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -33174,10 +33174,10 @@
         <v>2791</v>
       </c>
       <c r="D187" s="373" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="E187" s="30" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -33194,7 +33194,7 @@
         <v>2798</v>
       </c>
       <c r="E188" s="30" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -33211,7 +33211,7 @@
         <v>2798</v>
       </c>
       <c r="E189" s="30" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -33228,12 +33228,12 @@
         <v>2798</v>
       </c>
       <c r="E190" s="30" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="4" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>1853</v>
@@ -33245,7 +33245,7 @@
         <v>2798</v>
       </c>
       <c r="E191" s="30" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -33259,15 +33259,15 @@
         <v>2830</v>
       </c>
       <c r="D192" s="373" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="E192" s="30" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="B193">
         <v>69575383</v>
@@ -33276,10 +33276,10 @@
         <v>2796</v>
       </c>
       <c r="D193" s="373" t="s">
-        <v>3531</v>
+        <v>3530</v>
       </c>
       <c r="E193" s="30" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -33296,18 +33296,18 @@
         <v>2798</v>
       </c>
       <c r="E194" s="30" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="C195" s="56" t="s">
-        <v>3126</v>
+        <v>3125</v>
       </c>
       <c r="D195" t="s">
-        <v>3297</v>
+        <v>3296</v>
       </c>
       <c r="E195" s="30" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
     </row>
     <row r="197" spans="1:5" s="391" customFormat="1" ht="23.5">
@@ -33329,44 +33329,44 @@
         <v>2820</v>
       </c>
       <c r="D198" s="373" t="s">
-        <v>3308</v>
+        <v>3307</v>
       </c>
       <c r="E198" s="30" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" t="s">
+        <v>3366</v>
+      </c>
+      <c r="B199" t="s">
         <v>3367</v>
-      </c>
-      <c r="B199" t="s">
-        <v>3368</v>
       </c>
       <c r="C199" t="s">
         <v>2813</v>
       </c>
       <c r="D199" s="373" t="s">
-        <v>3366</v>
+        <v>3365</v>
       </c>
       <c r="E199" s="30" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B200">
         <v>63617941</v>
       </c>
       <c r="C200" s="22" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="D200" s="373" t="s">
         <v>2869</v>
       </c>
       <c r="E200" s="30" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -33380,15 +33380,15 @@
         <v>2814</v>
       </c>
       <c r="D201" s="373" t="s">
-        <v>3606</v>
+        <v>3605</v>
       </c>
       <c r="E201" s="30" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="202" spans="1:5">
       <c r="A202" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B202">
         <v>62279384</v>
@@ -33397,10 +33397,10 @@
         <v>2815</v>
       </c>
       <c r="D202" s="373" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="E202" s="30" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -33414,27 +33414,27 @@
         <v>2868</v>
       </c>
       <c r="D203" s="373" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="E203" s="30" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="30" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B204" t="s">
-        <v>3456</v>
+        <v>3455</v>
       </c>
       <c r="C204" t="s">
         <v>2816</v>
       </c>
       <c r="D204" s="373" t="s">
-        <v>3455</v>
+        <v>3454</v>
       </c>
       <c r="E204" s="30" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -33445,18 +33445,18 @@
         <v>64982293</v>
       </c>
       <c r="C205" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="D205" s="373" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="E205" s="30" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="206" spans="1:5">
       <c r="A206" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B206" t="s">
         <v>2876</v>
@@ -33468,7 +33468,7 @@
         <v>2874</v>
       </c>
       <c r="E206" s="30" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -33482,10 +33482,10 @@
         <v>2875</v>
       </c>
       <c r="D207" s="373" t="s">
+        <v>3160</v>
+      </c>
+      <c r="E207" s="30" t="s">
         <v>3161</v>
-      </c>
-      <c r="E207" s="30" t="s">
-        <v>3162</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -33502,12 +33502,12 @@
         <v>2889</v>
       </c>
       <c r="E208" s="30" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="105" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="B209" t="s">
         <v>1161</v>
@@ -33516,15 +33516,15 @@
         <v>2901</v>
       </c>
       <c r="D209" s="373" t="s">
-        <v>3662</v>
+        <v>3661</v>
       </c>
       <c r="E209" s="30" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="B210">
         <v>65574051</v>
@@ -33533,15 +33533,15 @@
         <v>2888</v>
       </c>
       <c r="D210" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
       <c r="E210" s="30" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="97" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="B211" t="s">
         <v>1161</v>
@@ -33550,10 +33550,10 @@
         <v>2902</v>
       </c>
       <c r="D211" s="373" t="s">
-        <v>3663</v>
+        <v>3662</v>
       </c>
       <c r="E211" s="30" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -33564,13 +33564,13 @@
         <v>64881871</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="D212" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="E212" s="30" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -33587,21 +33587,21 @@
         <v>2934</v>
       </c>
       <c r="E213" s="30" t="s">
-        <v>3513</v>
+        <v>3512</v>
       </c>
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="97" t="s">
-        <v>3586</v>
+        <v>3585</v>
       </c>
       <c r="C214" s="22" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="D214" t="s">
-        <v>3672</v>
+        <v>3671</v>
       </c>
       <c r="E214" s="30" t="s">
-        <v>3513</v>
+        <v>3512</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -33609,16 +33609,16 @@
         <v>1434</v>
       </c>
       <c r="B215" t="s">
-        <v>3604</v>
+        <v>3603</v>
       </c>
       <c r="C215" s="22" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
       <c r="D215" t="s">
-        <v>3603</v>
+        <v>3602</v>
       </c>
       <c r="E215" s="30" t="s">
-        <v>3513</v>
+        <v>3512</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -33632,10 +33632,10 @@
         <v>2933</v>
       </c>
       <c r="D216" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="E216" s="30" t="s">
-        <v>3513</v>
+        <v>3512</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -33646,13 +33646,13 @@
         <v>64457890</v>
       </c>
       <c r="C217" t="s">
+        <v>2943</v>
+      </c>
+      <c r="D217" s="373" t="s">
         <v>2944</v>
       </c>
-      <c r="D217" s="373" t="s">
-        <v>2945</v>
-      </c>
       <c r="E217" s="30" t="s">
-        <v>3513</v>
+        <v>3512</v>
       </c>
     </row>
     <row r="231" spans="3:4">
@@ -36528,7 +36528,7 @@
         <v>678</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="G6" s="363" t="s">
         <v>1439</v>
@@ -36549,13 +36549,13 @@
         <v>1841</v>
       </c>
       <c r="D7" s="183" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F7" s="183" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="G7" s="183" t="s">
         <v>1439</v>
@@ -36567,7 +36567,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="193" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="B8" s="193">
         <v>62747874</v>
@@ -36582,7 +36582,7 @@
         <v>362</v>
       </c>
       <c r="F8" s="183" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="G8" s="183" t="s">
         <v>1439</v>
@@ -36609,7 +36609,7 @@
         <v>362</v>
       </c>
       <c r="F9" s="183" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="G9" s="183" t="s">
         <v>1439</v>
@@ -36636,7 +36636,7 @@
         <v>362</v>
       </c>
       <c r="F10" s="183" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="G10" s="183" t="s">
         <v>1439</v>
@@ -36663,7 +36663,7 @@
         <v>362</v>
       </c>
       <c r="F11" s="183" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="G11" s="183" t="s">
         <v>1439</v>
@@ -36687,7 +36687,7 @@
         <v>2496</v>
       </c>
       <c r="E13" s="195" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="F13" s="195" t="s">
         <v>1426</v>
@@ -36713,7 +36713,7 @@
         <v>1842</v>
       </c>
       <c r="E14" s="193" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="F14" s="193" t="s">
         <v>1426</v>
@@ -36739,7 +36739,7 @@
         <v>2763</v>
       </c>
       <c r="E15" s="193" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="F15" s="193" t="s">
         <v>1426</v>
@@ -36765,7 +36765,7 @@
         <v>2304</v>
       </c>
       <c r="E16" s="193" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="F16" s="193" t="s">
         <v>1426</v>
@@ -36779,7 +36779,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="193" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="B17" s="193">
         <v>64403333</v>
@@ -36791,7 +36791,7 @@
         <v>1504</v>
       </c>
       <c r="E17" s="193" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="F17" s="193" t="s">
         <v>1426</v>
@@ -36817,7 +36817,7 @@
         <v>2150</v>
       </c>
       <c r="E18" s="193" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="F18" s="193" t="s">
         <v>1426</v>
@@ -36846,7 +36846,7 @@
         <v>362</v>
       </c>
       <c r="F20" s="195" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="G20" s="76" t="s">
         <v>422</v>
@@ -36875,7 +36875,7 @@
         <v>362</v>
       </c>
       <c r="F21" s="193" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="G21" s="183" t="s">
         <v>422</v>
@@ -36904,7 +36904,7 @@
         <v>362</v>
       </c>
       <c r="F22" s="193" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="G22" s="183" t="s">
         <v>422</v>
@@ -36918,7 +36918,7 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="183" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B23" s="183">
         <v>60389752</v>
@@ -36933,7 +36933,7 @@
         <v>362</v>
       </c>
       <c r="F23" s="193" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="G23" s="183" t="s">
         <v>422</v>
@@ -36962,7 +36962,7 @@
         <v>362</v>
       </c>
       <c r="F24" s="193" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="G24" s="183" t="s">
         <v>422</v>
@@ -36991,7 +36991,7 @@
         <v>362</v>
       </c>
       <c r="F25" s="193" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="G25" s="183" t="s">
         <v>422</v>
@@ -37005,7 +37005,7 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="76" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="B27" s="76">
         <v>60389752</v>
@@ -37020,7 +37020,7 @@
         <v>362</v>
       </c>
       <c r="F27" s="76" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="G27" s="76" t="s">
         <v>1440</v>
@@ -37047,7 +37047,7 @@
         <v>362</v>
       </c>
       <c r="F28" s="183" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="G28" s="183" t="s">
         <v>378</v>
@@ -37061,22 +37061,22 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="183" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="B29" s="183">
         <v>65234700</v>
       </c>
       <c r="C29" s="194" t="s">
+        <v>3315</v>
+      </c>
+      <c r="D29" s="183" t="s">
         <v>3316</v>
-      </c>
-      <c r="D29" s="183" t="s">
-        <v>3317</v>
       </c>
       <c r="E29" s="432">
         <v>46243</v>
       </c>
       <c r="F29" s="183" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="G29" s="183" t="s">
         <v>378</v>
@@ -37105,7 +37105,7 @@
         <v>362</v>
       </c>
       <c r="F30" s="183" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="G30" s="183" t="s">
         <v>378</v>
@@ -37134,7 +37134,7 @@
         <v>362</v>
       </c>
       <c r="F31" s="183" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="G31" s="183" t="s">
         <v>378</v>
@@ -37148,7 +37148,7 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="183" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B32" s="183">
         <v>68241069</v>
@@ -37163,7 +37163,7 @@
         <v>362</v>
       </c>
       <c r="F32" s="183" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="G32" s="183" t="s">
         <v>378</v>
@@ -37177,7 +37177,7 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="195" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="B34" s="195">
         <v>66466729</v>
@@ -37186,13 +37186,13 @@
         <v>1661</v>
       </c>
       <c r="D34" s="195" t="s">
-        <v>3474</v>
+        <v>3473</v>
       </c>
       <c r="E34" s="76" t="s">
         <v>2466</v>
       </c>
       <c r="F34" s="195" t="s">
-        <v>3371</v>
+        <v>3370</v>
       </c>
       <c r="G34" s="76" t="s">
         <v>1439</v>
@@ -37203,7 +37203,7 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="193" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B35" s="193">
         <v>63465332</v>
@@ -37218,7 +37218,7 @@
         <v>2466</v>
       </c>
       <c r="F35" s="193" t="s">
-        <v>3371</v>
+        <v>3370</v>
       </c>
       <c r="G35" s="183" t="s">
         <v>1439</v>
@@ -37244,7 +37244,7 @@
         <v>2466</v>
       </c>
       <c r="F36" s="193" t="s">
-        <v>3371</v>
+        <v>3370</v>
       </c>
       <c r="G36" s="183" t="s">
         <v>1439</v>
@@ -37255,7 +37255,7 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="193" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="B37" s="193">
         <v>69111188</v>
@@ -37270,7 +37270,7 @@
         <v>2466</v>
       </c>
       <c r="F37" s="193" t="s">
-        <v>3371</v>
+        <v>3370</v>
       </c>
       <c r="G37" s="183" t="s">
         <v>1439</v>
@@ -37296,7 +37296,7 @@
         <v>2466</v>
       </c>
       <c r="F38" s="193" t="s">
-        <v>3371</v>
+        <v>3370</v>
       </c>
       <c r="G38" s="183" t="s">
         <v>1439</v>
@@ -37322,7 +37322,7 @@
         <v>2466</v>
       </c>
       <c r="F39" s="193" t="s">
-        <v>3371</v>
+        <v>3370</v>
       </c>
       <c r="G39" s="183" t="s">
         <v>1439</v>
@@ -37335,16 +37335,16 @@
       <c r="A41" s="195"/>
       <c r="B41" s="195"/>
       <c r="C41" s="195" t="s">
+        <v>3361</v>
+      </c>
+      <c r="D41" s="195" t="s">
         <v>3362</v>
-      </c>
-      <c r="D41" s="195" t="s">
-        <v>3363</v>
       </c>
       <c r="E41" s="76" t="s">
         <v>362</v>
       </c>
       <c r="F41" s="195" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="G41" s="76" t="s">
         <v>2361</v>
@@ -37364,7 +37364,7 @@
         <v>69563253</v>
       </c>
       <c r="C42" s="193" t="s">
-        <v>3365</v>
+        <v>3364</v>
       </c>
       <c r="D42" s="193" t="s">
         <v>1673</v>
@@ -37384,10 +37384,10 @@
         <v>1938</v>
       </c>
       <c r="C43" s="194" t="s">
+        <v>3341</v>
+      </c>
+      <c r="D43" s="193" t="s">
         <v>3342</v>
-      </c>
-      <c r="D43" s="193" t="s">
-        <v>3343</v>
       </c>
       <c r="E43" s="432">
         <v>46304</v>
@@ -37404,7 +37404,7 @@
         <v>62751201</v>
       </c>
       <c r="C44" s="194" t="s">
-        <v>3369</v>
+        <v>3368</v>
       </c>
       <c r="D44" s="183" t="s">
         <v>1354</v>
@@ -37424,10 +37424,10 @@
         <v>68030850</v>
       </c>
       <c r="C45" s="193" t="s">
+        <v>3344</v>
+      </c>
+      <c r="D45" s="193" t="s">
         <v>3345</v>
-      </c>
-      <c r="D45" s="193" t="s">
-        <v>3346</v>
       </c>
       <c r="E45" s="432">
         <v>46243</v>
@@ -37460,16 +37460,16 @@
       <c r="A48" s="195"/>
       <c r="B48" s="195"/>
       <c r="C48" s="195" t="s">
+        <v>3395</v>
+      </c>
+      <c r="D48" s="195" t="s">
         <v>3396</v>
       </c>
-      <c r="D48" s="195" t="s">
+      <c r="E48" s="76" t="s">
         <v>3397</v>
       </c>
-      <c r="E48" s="76" t="s">
+      <c r="F48" s="195" t="s">
         <v>3398</v>
-      </c>
-      <c r="F48" s="195" t="s">
-        <v>3399</v>
       </c>
       <c r="G48" s="76" t="s">
         <v>1439</v>
@@ -37506,10 +37506,10 @@
         <v>61548403</v>
       </c>
       <c r="C50" s="194" t="s">
+        <v>3399</v>
+      </c>
+      <c r="D50" s="193" t="s">
         <v>3400</v>
-      </c>
-      <c r="D50" s="193" t="s">
-        <v>3401</v>
       </c>
       <c r="E50" s="432">
         <v>46304</v>
@@ -37522,7 +37522,7 @@
       <c r="C51" s="449"/>
       <c r="D51" s="449"/>
       <c r="E51" s="432" t="s">
-        <v>3473</v>
+        <v>3472</v>
       </c>
       <c r="F51" s="193"/>
       <c r="G51" s="183"/>
@@ -37532,7 +37532,7 @@
       <c r="C52" s="452"/>
       <c r="D52" s="183"/>
       <c r="E52" s="432" t="s">
-        <v>3473</v>
+        <v>3472</v>
       </c>
       <c r="F52" s="193"/>
       <c r="G52" s="183"/>
@@ -37552,7 +37552,7 @@
         <v>2908</v>
       </c>
       <c r="E53" s="432" t="s">
-        <v>3473</v>
+        <v>3472</v>
       </c>
       <c r="F53" s="193"/>
       <c r="G53" s="183"/>
@@ -37565,13 +37565,13 @@
         <v>1660</v>
       </c>
       <c r="D55" s="195" t="s">
-        <v>3627</v>
+        <v>3626</v>
       </c>
       <c r="E55" s="76" t="s">
         <v>2466</v>
       </c>
       <c r="F55" s="195" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="G55" s="76" t="s">
         <v>1439</v>
@@ -37597,7 +37597,7 @@
         <v>2466</v>
       </c>
       <c r="F56" s="193" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="G56" s="183" t="s">
         <v>1439</v>
@@ -37617,13 +37617,13 @@
         <v>2587</v>
       </c>
       <c r="D57" s="193" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="E57" s="183" t="s">
         <v>2466</v>
       </c>
       <c r="F57" s="193" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="G57" s="183" t="s">
         <v>1439</v>
@@ -37649,7 +37649,7 @@
         <v>2466</v>
       </c>
       <c r="F58" s="193" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="G58" s="183" t="s">
         <v>1439</v>
@@ -37675,7 +37675,7 @@
         <v>2466</v>
       </c>
       <c r="F59" s="193" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="G59" s="183" t="s">
         <v>1439</v>
@@ -37686,22 +37686,22 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="183" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="B60" s="183">
         <v>63247837</v>
       </c>
       <c r="C60" s="193" t="s">
-        <v>3231</v>
+        <v>3230</v>
       </c>
       <c r="D60" s="193" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="E60" s="183" t="s">
         <v>2466</v>
       </c>
       <c r="F60" s="193" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="G60" s="183" t="s">
         <v>1439</v>
@@ -37727,7 +37727,7 @@
         <v>2466</v>
       </c>
       <c r="F62" s="195" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="G62" s="76" t="s">
         <v>1439</v>
@@ -37753,7 +37753,7 @@
         <v>2466</v>
       </c>
       <c r="F63" s="193" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="G63" s="183" t="s">
         <v>1439</v>
@@ -37764,7 +37764,7 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="183" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="B64" s="183">
         <v>64403333</v>
@@ -37779,7 +37779,7 @@
         <v>2466</v>
       </c>
       <c r="F64" s="193" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="G64" s="183" t="s">
         <v>1439</v>
@@ -37790,7 +37790,7 @@
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="193" t="s">
-        <v>3187</v>
+        <v>3186</v>
       </c>
       <c r="B65" s="193">
         <v>68030850</v>
@@ -37805,7 +37805,7 @@
         <v>2466</v>
       </c>
       <c r="F65" s="193" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="G65" s="183" t="s">
         <v>1439</v>
@@ -37816,7 +37816,7 @@
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="183" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="B66" s="183">
         <v>65003516</v>
@@ -37831,7 +37831,7 @@
         <v>2466</v>
       </c>
       <c r="F66" s="193" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="G66" s="183" t="s">
         <v>1439</v>
@@ -37857,7 +37857,7 @@
         <v>2466</v>
       </c>
       <c r="F67" s="193" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="G67" s="183" t="s">
         <v>1439</v>
@@ -37880,7 +37880,7 @@
         <v>2429</v>
       </c>
       <c r="E69" s="76" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="F69" s="195" t="s">
         <v>2430</v>
@@ -37906,7 +37906,7 @@
         <v>2434</v>
       </c>
       <c r="E70" s="183" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="F70" s="193" t="s">
         <v>2430</v>
@@ -37932,7 +37932,7 @@
         <v>2278</v>
       </c>
       <c r="E71" s="183" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="F71" s="193" t="s">
         <v>2430</v>
@@ -37958,7 +37958,7 @@
         <v>2717</v>
       </c>
       <c r="E72" s="183" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="F72" s="183" t="s">
         <v>2430</v>
@@ -37985,7 +37985,7 @@
         <v>2049</v>
       </c>
       <c r="E73" s="183" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="F73" s="183" t="s">
         <v>2430</v>
@@ -38012,7 +38012,7 @@
         <v>2426</v>
       </c>
       <c r="E74" s="183" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="F74" s="183" t="s">
         <v>2430</v>
@@ -38039,7 +38039,7 @@
         <v>1720</v>
       </c>
       <c r="E76" s="76" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="F76" s="195" t="s">
         <v>2428</v>
@@ -38063,7 +38063,7 @@
         <v>2318</v>
       </c>
       <c r="E77" s="183" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="F77" s="193" t="s">
         <v>2428</v>
@@ -38087,7 +38087,7 @@
         <v>1235</v>
       </c>
       <c r="E78" s="183" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="F78" s="193" t="s">
         <v>2428</v>
@@ -38099,7 +38099,7 @@
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="183" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
       <c r="B79" s="183">
         <v>62820256</v>
@@ -38111,7 +38111,7 @@
         <v>2344</v>
       </c>
       <c r="E79" s="183" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="F79" s="193" t="s">
         <v>2428</v>
@@ -38123,19 +38123,19 @@
     </row>
     <row r="80" spans="1:9">
       <c r="A80" s="183" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="B80" s="183">
         <v>69563253</v>
       </c>
       <c r="C80" s="194" t="s">
-        <v>3451</v>
+        <v>3450</v>
       </c>
       <c r="D80" s="183" t="s">
         <v>1003</v>
       </c>
       <c r="E80" s="183" t="s">
-        <v>3452</v>
+        <v>3451</v>
       </c>
       <c r="F80" s="193" t="s">
         <v>2428</v>
@@ -38147,7 +38147,7 @@
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="183" t="s">
-        <v>3478</v>
+        <v>3477</v>
       </c>
       <c r="B81" s="183">
         <v>63233935</v>
@@ -38156,10 +38156,10 @@
         <v>2363</v>
       </c>
       <c r="D81" s="183" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="E81" s="183" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="F81" s="193" t="s">
         <v>2428</v>
@@ -38171,7 +38171,7 @@
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="76" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="B83" s="76">
         <v>63574980</v>
@@ -38186,7 +38186,7 @@
         <v>1341</v>
       </c>
       <c r="F83" s="195" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="G83" s="76" t="s">
         <v>1439</v>
@@ -38213,7 +38213,7 @@
         <v>1341</v>
       </c>
       <c r="F84" s="183" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="G84" s="183" t="s">
         <v>1439</v>
@@ -38240,7 +38240,7 @@
         <v>1341</v>
       </c>
       <c r="F85" s="183" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="G85" s="183" t="s">
         <v>1439</v>
@@ -38255,19 +38255,19 @@
         <v>2481</v>
       </c>
       <c r="B86" s="183" t="s">
-        <v>3082</v>
+        <v>3081</v>
       </c>
       <c r="C86" s="194" t="s">
         <v>2644</v>
       </c>
       <c r="D86" s="183" t="s">
-        <v>3081</v>
+        <v>3080</v>
       </c>
       <c r="E86" s="183" t="s">
         <v>1341</v>
       </c>
       <c r="F86" s="183" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="G86" s="183" t="s">
         <v>1439</v>
@@ -38279,7 +38279,7 @@
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="183" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="B87" s="183">
         <v>69904406</v>
@@ -38288,13 +38288,13 @@
         <v>2645</v>
       </c>
       <c r="D87" s="183" t="s">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="E87" s="183" t="s">
         <v>1341</v>
       </c>
       <c r="F87" s="183" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="G87" s="183" t="s">
         <v>1439</v>
@@ -38321,7 +38321,7 @@
         <v>1341</v>
       </c>
       <c r="F88" s="183" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="G88" s="183" t="s">
         <v>1439</v>
@@ -38348,7 +38348,7 @@
         <v>1650</v>
       </c>
       <c r="F90" s="195" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
       <c r="G90" s="76" t="s">
         <v>1439</v>
@@ -38372,7 +38372,7 @@
         <v>1650</v>
       </c>
       <c r="F91" s="193" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
       <c r="G91" s="183" t="s">
         <v>1439</v>
@@ -38396,7 +38396,7 @@
         <v>1650</v>
       </c>
       <c r="F92" s="193" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
       <c r="G92" s="183" t="s">
         <v>1439</v>
@@ -38405,7 +38405,7 @@
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="183" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="B93" s="183">
         <v>68259581</v>
@@ -38420,7 +38420,7 @@
         <v>1650</v>
       </c>
       <c r="F93" s="193" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
       <c r="G93" s="183" t="s">
         <v>1439</v>
@@ -38444,7 +38444,7 @@
         <v>1650</v>
       </c>
       <c r="F94" s="193" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
       <c r="G94" s="183" t="s">
         <v>1439</v>
@@ -38468,7 +38468,7 @@
         <v>1650</v>
       </c>
       <c r="F95" s="193" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
       <c r="G95" s="183" t="s">
         <v>1439</v>
@@ -38477,7 +38477,7 @@
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="195" t="s">
-        <v>3385</v>
+        <v>3384</v>
       </c>
       <c r="B97" s="195">
         <v>64476521</v>
@@ -38492,7 +38492,7 @@
         <v>2466</v>
       </c>
       <c r="F97" s="195" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="G97" s="76" t="s">
         <v>1439</v>
@@ -38503,7 +38503,7 @@
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="193" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="B98" s="193">
         <v>60389752</v>
@@ -38512,13 +38512,13 @@
         <v>2626</v>
       </c>
       <c r="D98" s="193" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="E98" s="183" t="s">
         <v>2466</v>
       </c>
       <c r="F98" s="193" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="G98" s="183" t="s">
         <v>1439</v>
@@ -38529,7 +38529,7 @@
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="183" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
       <c r="B99" s="183">
         <v>60389752</v>
@@ -38544,7 +38544,7 @@
         <v>2466</v>
       </c>
       <c r="F99" s="193" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="G99" s="183" t="s">
         <v>1439</v>
@@ -38570,7 +38570,7 @@
         <v>2466</v>
       </c>
       <c r="F100" s="193" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="G100" s="183" t="s">
         <v>1439</v>
@@ -38596,7 +38596,7 @@
         <v>2466</v>
       </c>
       <c r="F101" s="193" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="G101" s="183" t="s">
         <v>1439</v>
@@ -38607,7 +38607,7 @@
     </row>
     <row r="102" spans="1:9">
       <c r="A102" s="193" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="B102" s="193">
         <v>67381873</v>
@@ -38616,13 +38616,13 @@
         <v>2276</v>
       </c>
       <c r="D102" s="193" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="E102" s="183" t="s">
         <v>2466</v>
       </c>
       <c r="F102" s="193" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="G102" s="183" t="s">
         <v>1439</v>
@@ -38633,7 +38633,7 @@
     </row>
     <row r="104" spans="1:9">
       <c r="A104" s="195" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="B104" s="195">
         <v>66082581</v>
@@ -38645,7 +38645,7 @@
         <v>2286</v>
       </c>
       <c r="E104" s="76" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="F104" s="195" t="s">
         <v>422</v>
@@ -38671,7 +38671,7 @@
         <v>2291</v>
       </c>
       <c r="E105" s="183" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="F105" s="193" t="s">
         <v>422</v>
@@ -38685,7 +38685,7 @@
     </row>
     <row r="106" spans="1:9">
       <c r="A106" s="193" t="s">
-        <v>3221</v>
+        <v>3220</v>
       </c>
       <c r="B106" s="193">
         <v>62723048</v>
@@ -38694,10 +38694,10 @@
         <v>2292</v>
       </c>
       <c r="D106" s="193" t="s">
-        <v>3220</v>
+        <v>3219</v>
       </c>
       <c r="E106" s="183" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="F106" s="193" t="s">
         <v>422</v>
@@ -38723,7 +38723,7 @@
         <v>2440</v>
       </c>
       <c r="E107" s="183" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="F107" s="193" t="s">
         <v>422</v>
@@ -38749,7 +38749,7 @@
         <v>2295</v>
       </c>
       <c r="E108" s="183" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="F108" s="193" t="s">
         <v>422</v>
@@ -38775,7 +38775,7 @@
         <v>2892</v>
       </c>
       <c r="E109" s="183" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="F109" s="193" t="s">
         <v>422</v>
@@ -38789,22 +38789,22 @@
     </row>
     <row r="111" spans="1:9">
       <c r="A111" s="195" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="B111" s="195">
         <v>68310153</v>
       </c>
       <c r="C111" s="195" t="s">
+        <v>2939</v>
+      </c>
+      <c r="D111" s="195" t="s">
         <v>2940</v>
-      </c>
-      <c r="D111" s="195" t="s">
-        <v>2941</v>
       </c>
       <c r="E111" s="76" t="s">
         <v>362</v>
       </c>
       <c r="F111" s="195" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
       <c r="G111" s="76" t="s">
         <v>1341</v>
@@ -38818,7 +38818,7 @@
     </row>
     <row r="112" spans="1:9">
       <c r="A112" s="193" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="B112" s="193">
         <v>63910392</v>
@@ -38831,7 +38831,7 @@
         <v>362</v>
       </c>
       <c r="F112" s="193" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
       <c r="G112" s="183" t="s">
         <v>1341</v>
@@ -38860,7 +38860,7 @@
         <v>2466</v>
       </c>
       <c r="F113" s="193" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
       <c r="G113" s="183" t="s">
         <v>1341</v>
@@ -38880,16 +38880,16 @@
         <v>62360487</v>
       </c>
       <c r="C114" s="194" t="s">
+        <v>3231</v>
+      </c>
+      <c r="D114" s="183" t="s">
         <v>3232</v>
-      </c>
-      <c r="D114" s="183" t="s">
-        <v>3233</v>
       </c>
       <c r="E114" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F114" s="193" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
       <c r="G114" s="183" t="s">
         <v>1341</v>
@@ -38909,16 +38909,16 @@
         <v>62085821</v>
       </c>
       <c r="C115" s="193" t="s">
+        <v>3233</v>
+      </c>
+      <c r="D115" s="193" t="s">
         <v>3234</v>
-      </c>
-      <c r="D115" s="193" t="s">
-        <v>3235</v>
       </c>
       <c r="E115" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F115" s="193" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
       <c r="G115" s="183" t="s">
         <v>1341</v>
@@ -38932,22 +38932,22 @@
     </row>
     <row r="116" spans="1:9">
       <c r="A116" s="193" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="B116" s="193">
         <v>64403333</v>
       </c>
       <c r="C116" s="193" t="s">
+        <v>3235</v>
+      </c>
+      <c r="D116" s="193" t="s">
         <v>3236</v>
-      </c>
-      <c r="D116" s="193" t="s">
-        <v>3237</v>
       </c>
       <c r="E116" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F116" s="193" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
       <c r="G116" s="183" t="s">
         <v>1341</v>
@@ -38979,7 +38979,7 @@
         <v>2308</v>
       </c>
       <c r="E118" s="76" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="F118" s="76" t="s">
         <v>422</v>
@@ -39006,7 +39006,7 @@
         <v>2310</v>
       </c>
       <c r="E119" s="183" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="F119" s="193" t="s">
         <v>422</v>
@@ -39032,7 +39032,7 @@
         <v>2312</v>
       </c>
       <c r="E120" s="183" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="F120" s="193" t="s">
         <v>422</v>
@@ -39046,19 +39046,19 @@
     </row>
     <row r="121" spans="1:9">
       <c r="A121" s="183" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="B121" s="183">
         <v>64403333</v>
       </c>
       <c r="C121" s="183" t="s">
+        <v>3237</v>
+      </c>
+      <c r="D121" s="183" t="s">
         <v>3238</v>
       </c>
-      <c r="D121" s="183" t="s">
-        <v>3239</v>
-      </c>
       <c r="E121" s="183" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="F121" s="193" t="s">
         <v>422</v>
@@ -39072,7 +39072,7 @@
     </row>
     <row r="122" spans="1:9">
       <c r="A122" s="193" t="s">
-        <v>3586</v>
+        <v>3585</v>
       </c>
       <c r="B122" s="193" t="s">
         <v>2194</v>
@@ -39084,7 +39084,7 @@
         <v>377</v>
       </c>
       <c r="E122" s="183" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="F122" s="193" t="s">
         <v>422</v>
@@ -39110,7 +39110,7 @@
         <v>1646</v>
       </c>
       <c r="E123" s="183" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="F123" s="193" t="s">
         <v>422</v>
@@ -39139,7 +39139,7 @@
         <v>678</v>
       </c>
       <c r="F125" s="76" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="G125" s="76" t="s">
         <v>422</v>
@@ -39153,7 +39153,7 @@
     </row>
     <row r="126" spans="1:9">
       <c r="A126" s="183" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="B126" s="183">
         <v>64403333</v>
@@ -39168,7 +39168,7 @@
         <v>362</v>
       </c>
       <c r="F126" s="183" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="G126" s="183" t="s">
         <v>422</v>
@@ -39197,7 +39197,7 @@
         <v>362</v>
       </c>
       <c r="F127" s="183" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="G127" s="183" t="s">
         <v>422</v>
@@ -39224,7 +39224,7 @@
         <v>362</v>
       </c>
       <c r="F128" s="183" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="G128" s="183" t="s">
         <v>422</v>
@@ -39253,7 +39253,7 @@
         <v>362</v>
       </c>
       <c r="F129" s="183" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="G129" s="183" t="s">
         <v>422</v>
@@ -39282,7 +39282,7 @@
         <v>362</v>
       </c>
       <c r="F130" s="183" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="G130" s="183" t="s">
         <v>422</v>
@@ -39311,7 +39311,7 @@
         <v>2355</v>
       </c>
       <c r="F132" s="195" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="G132" s="76" t="s">
         <v>1439</v>
@@ -39328,7 +39328,7 @@
         <v>64226974</v>
       </c>
       <c r="C133" s="183" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="D133" s="193" t="s">
         <v>377</v>
@@ -39337,7 +39337,7 @@
         <v>2355</v>
       </c>
       <c r="F133" s="193" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="G133" s="183" t="s">
         <v>1439</v>
@@ -39363,7 +39363,7 @@
         <v>2355</v>
       </c>
       <c r="F134" s="193" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="G134" s="183" t="s">
         <v>1439</v>
@@ -39389,7 +39389,7 @@
         <v>2355</v>
       </c>
       <c r="F135" s="193" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="G135" s="183" t="s">
         <v>1439</v>
@@ -39415,7 +39415,7 @@
         <v>2355</v>
       </c>
       <c r="F136" s="193" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="G136" s="183" t="s">
         <v>1439</v>
@@ -39426,7 +39426,7 @@
     </row>
     <row r="137" spans="1:9">
       <c r="A137" s="193" t="s">
-        <v>3436</v>
+        <v>3435</v>
       </c>
       <c r="B137" s="193">
         <v>63811445</v>
@@ -39441,7 +39441,7 @@
         <v>2355</v>
       </c>
       <c r="F137" s="193" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="G137" s="183" t="s">
         <v>1439</v>
@@ -39452,22 +39452,22 @@
     </row>
     <row r="139" spans="1:9">
       <c r="A139" s="195" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B139" s="195" t="s">
         <v>2154</v>
       </c>
       <c r="C139" s="195" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="D139" s="195" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="E139" s="76" t="s">
         <v>2355</v>
       </c>
       <c r="F139" s="195" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="G139" s="76" t="s">
         <v>1439</v>
@@ -39484,16 +39484,16 @@
         <v>66319486</v>
       </c>
       <c r="C140" s="193" t="s">
-        <v>3240</v>
+        <v>3239</v>
       </c>
       <c r="D140" s="193" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="E140" s="183" t="s">
         <v>2355</v>
       </c>
       <c r="F140" s="193" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="G140" s="183" t="s">
         <v>1439</v>
@@ -39504,7 +39504,7 @@
     </row>
     <row r="141" spans="1:9">
       <c r="A141" s="183" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="B141" s="183">
         <v>60389752</v>
@@ -39519,7 +39519,7 @@
         <v>2355</v>
       </c>
       <c r="F141" s="193" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="G141" s="183" t="s">
         <v>1439</v>
@@ -39533,7 +39533,7 @@
         <v>2355</v>
       </c>
       <c r="F142" s="193" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="G142" s="183" t="s">
         <v>1439</v>
@@ -39559,7 +39559,7 @@
         <v>2355</v>
       </c>
       <c r="F143" s="193" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="G143" s="183" t="s">
         <v>1439</v>
@@ -39570,7 +39570,7 @@
     </row>
     <row r="144" spans="1:9">
       <c r="A144" s="193" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
       <c r="B144" s="193">
         <v>60389752</v>
@@ -39585,7 +39585,7 @@
         <v>2355</v>
       </c>
       <c r="F144" s="193" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="G144" s="183" t="s">
         <v>1439</v>
@@ -39611,7 +39611,7 @@
         <v>2466</v>
       </c>
       <c r="F146" s="195" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="G146" s="76" t="s">
         <v>1439</v>
@@ -39622,13 +39622,13 @@
     </row>
     <row r="147" spans="1:9">
       <c r="A147" s="193" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B147" s="193">
         <v>67697112</v>
       </c>
       <c r="C147" s="193" t="s">
-        <v>3265</v>
+        <v>3264</v>
       </c>
       <c r="D147" s="193" t="s">
         <v>1303</v>
@@ -39637,7 +39637,7 @@
         <v>2466</v>
       </c>
       <c r="F147" s="193" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="G147" s="183" t="s">
         <v>1439</v>
@@ -39648,7 +39648,7 @@
     </row>
     <row r="148" spans="1:9">
       <c r="A148" s="183" t="s">
-        <v>3306</v>
+        <v>3305</v>
       </c>
       <c r="B148" s="183">
         <v>62560788</v>
@@ -39663,7 +39663,7 @@
         <v>2466</v>
       </c>
       <c r="F148" s="193" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="G148" s="183" t="s">
         <v>1439</v>
@@ -39674,7 +39674,7 @@
     </row>
     <row r="149" spans="1:9">
       <c r="A149" s="193" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="B149" s="193">
         <v>64403333</v>
@@ -39689,7 +39689,7 @@
         <v>2466</v>
       </c>
       <c r="F149" s="193" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="G149" s="183" t="s">
         <v>1439</v>
@@ -39715,7 +39715,7 @@
         <v>2466</v>
       </c>
       <c r="F150" s="193" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="G150" s="183" t="s">
         <v>1439</v>
@@ -39741,7 +39741,7 @@
         <v>2466</v>
       </c>
       <c r="F151" s="193" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="G151" s="183" t="s">
         <v>1439</v>
@@ -39767,7 +39767,7 @@
         <v>362</v>
       </c>
       <c r="F153" s="195" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="G153" s="76" t="s">
         <v>2361</v>
@@ -39781,22 +39781,22 @@
     </row>
     <row r="154" spans="1:9">
       <c r="A154" s="193" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="B154" s="193">
         <v>65963732</v>
       </c>
       <c r="C154" s="194" t="s">
+        <v>3222</v>
+      </c>
+      <c r="D154" s="193" t="s">
         <v>3223</v>
-      </c>
-      <c r="D154" s="193" t="s">
-        <v>3224</v>
       </c>
       <c r="E154" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F154" s="193" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="G154" s="183" t="s">
         <v>2361</v>
@@ -39810,7 +39810,7 @@
     </row>
     <row r="155" spans="1:9">
       <c r="A155" s="183" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="B155" s="183">
         <v>60071688</v>
@@ -39819,13 +39819,13 @@
         <v>2345</v>
       </c>
       <c r="D155" s="183" t="s">
-        <v>3217</v>
+        <v>3216</v>
       </c>
       <c r="E155" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F155" s="193" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="G155" s="183" t="s">
         <v>2361</v>
@@ -39854,7 +39854,7 @@
         <v>362</v>
       </c>
       <c r="F156" s="193" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="G156" s="183" t="s">
         <v>2361</v>
@@ -39883,7 +39883,7 @@
         <v>362</v>
       </c>
       <c r="F157" s="193" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="G157" s="183" t="s">
         <v>2361</v>
@@ -39912,7 +39912,7 @@
         <v>362</v>
       </c>
       <c r="F158" s="193" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="G158" s="183" t="s">
         <v>2361</v>
@@ -39943,7 +39943,7 @@
       <c r="A183" s="221"/>
       <c r="B183" s="221"/>
       <c r="C183" s="221" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="D183" s="221"/>
       <c r="E183" s="221"/>
@@ -39957,19 +39957,19 @@
         <v>67836337</v>
       </c>
       <c r="C184" s="195" t="s">
+        <v>3423</v>
+      </c>
+      <c r="D184" s="195" t="s">
         <v>3424</v>
-      </c>
-      <c r="D184" s="195" t="s">
-        <v>3425</v>
       </c>
       <c r="E184" s="433">
         <v>46243</v>
       </c>
       <c r="F184" s="76" t="s">
-        <v>3313</v>
+        <v>3312</v>
       </c>
       <c r="G184" s="195" t="s">
-        <v>3476</v>
+        <v>3475</v>
       </c>
       <c r="H184" s="76" t="s">
         <v>1975</v>
@@ -39977,19 +39977,19 @@
     </row>
     <row r="185" spans="1:9">
       <c r="A185" s="193" t="s">
-        <v>3478</v>
+        <v>3477</v>
       </c>
       <c r="B185" s="193">
         <v>60196388</v>
       </c>
       <c r="C185" s="193" t="s">
-        <v>3477</v>
+        <v>3476</v>
       </c>
       <c r="D185" s="444" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
       <c r="E185" s="432" t="s">
-        <v>3473</v>
+        <v>3472</v>
       </c>
       <c r="F185" s="193"/>
       <c r="G185" s="183"/>
@@ -40003,13 +40003,13 @@
         <v>64403333</v>
       </c>
       <c r="C186" s="191" t="s">
-        <v>3494</v>
+        <v>3493</v>
       </c>
       <c r="D186" s="183" t="s">
-        <v>3484</v>
+        <v>3483</v>
       </c>
       <c r="E186" s="432" t="s">
-        <v>3473</v>
+        <v>3472</v>
       </c>
       <c r="F186" s="193"/>
       <c r="G186" s="183"/>
@@ -40017,19 +40017,19 @@
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="193" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
       <c r="B187" s="193">
         <v>68071614</v>
       </c>
       <c r="C187" s="193" t="s">
+        <v>3513</v>
+      </c>
+      <c r="D187" s="193" t="s">
         <v>3514</v>
       </c>
-      <c r="D187" s="193" t="s">
+      <c r="E187" s="432" t="s">
         <v>3515</v>
-      </c>
-      <c r="E187" s="432" t="s">
-        <v>3516</v>
       </c>
       <c r="F187" s="193"/>
       <c r="G187" s="183"/>
@@ -40043,13 +40043,13 @@
         <v>63950696</v>
       </c>
       <c r="C188" s="450" t="s">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D188" s="450" t="s">
         <v>2775</v>
       </c>
       <c r="E188" s="432" t="s">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="F188" s="451"/>
       <c r="G188" s="445"/>
@@ -40064,13 +40064,13 @@
         <v>65147336</v>
       </c>
       <c r="C189" s="183" t="s">
+        <v>3567</v>
+      </c>
+      <c r="D189" s="183" t="s">
         <v>3568</v>
       </c>
-      <c r="D189" s="183" t="s">
+      <c r="E189" s="432" t="s">
         <v>3569</v>
-      </c>
-      <c r="E189" s="432" t="s">
-        <v>3570</v>
       </c>
       <c r="F189" s="193"/>
       <c r="G189" s="183"/>
@@ -40111,7 +40111,7 @@
         <v>316</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="E194" s="30"/>
       <c r="F194"/>
@@ -40137,7 +40137,7 @@
         <v>439</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>3451</v>
+        <v>3450</v>
       </c>
       <c r="E196" s="30"/>
       <c r="F196"/>
@@ -40148,7 +40148,7 @@
         <v>26</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>3514</v>
+        <v>3513</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -40156,7 +40156,7 @@
         <v>1324</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>3544</v>
+        <v>3543</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -40164,7 +40164,7 @@
         <v>1657</v>
       </c>
       <c r="D199" s="428" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
       <c r="F199" s="394"/>
     </row>
@@ -40173,7 +40173,7 @@
         <v>1305</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>3240</v>
+        <v>3239</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -40181,7 +40181,7 @@
         <v>406</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>3342</v>
+        <v>3341</v>
       </c>
     </row>
     <row r="202" spans="1:9">
@@ -40189,7 +40189,7 @@
         <v>708</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>3345</v>
+        <v>3344</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -40197,7 +40197,7 @@
         <v>281</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>3361</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="204" spans="1:9">
@@ -40205,7 +40205,7 @@
         <v>2363</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>3362</v>
+        <v>3361</v>
       </c>
     </row>
     <row r="205" spans="1:9">
@@ -40215,7 +40215,7 @@
         <v>465</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>3365</v>
+        <v>3364</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -40223,7 +40223,7 @@
         <v>219</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>3369</v>
+        <v>3368</v>
       </c>
     </row>
     <row r="207" spans="1:9">
@@ -40231,7 +40231,7 @@
         <v>427</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
     </row>
     <row r="208" spans="1:9">
@@ -40239,7 +40239,7 @@
         <v>1050</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>3396</v>
+        <v>3395</v>
       </c>
     </row>
     <row r="223" spans="1:9">
@@ -41454,7 +41454,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B3">
         <v>62349088</v>
@@ -41475,10 +41475,10 @@
         <v>705</v>
       </c>
       <c r="H3" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>3618</v>
+        <v>3617</v>
       </c>
       <c r="J3"/>
     </row>
@@ -41505,10 +41505,10 @@
         <v>515</v>
       </c>
       <c r="H4" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="I4" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="J4"/>
     </row>
@@ -41526,7 +41526,7 @@
         <v>1519</v>
       </c>
       <c r="E5" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="F5" t="s">
         <v>2163</v>
@@ -41535,10 +41535,10 @@
         <v>515</v>
       </c>
       <c r="H5" s="220" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="I5" s="220" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="J5" t="s">
         <v>1394</v>
@@ -41546,19 +41546,19 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="B6" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>427</v>
       </c>
       <c r="D6" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>2853</v>
@@ -41567,10 +41567,10 @@
         <v>436</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="I6" t="s">
-        <v>3551</v>
+        <v>3550</v>
       </c>
       <c r="J6"/>
     </row>
@@ -41602,13 +41602,13 @@
         <v>1434</v>
       </c>
       <c r="B8" t="s">
-        <v>3620</v>
+        <v>3619</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>2060</v>
       </c>
       <c r="D8" t="s">
-        <v>3619</v>
+        <v>3618</v>
       </c>
       <c r="E8" t="s">
         <v>2320</v>
@@ -41620,10 +41620,10 @@
         <v>250</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
       <c r="I8" t="s">
-        <v>3625</v>
+        <v>3624</v>
       </c>
       <c r="J8"/>
     </row>
@@ -41658,31 +41658,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="278" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>3653</v>
+        <v>3652</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>3648</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>3649</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="E10" s="10" t="s">
         <v>3650</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="F10" s="10" t="s">
         <v>3651</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>3652</v>
       </c>
       <c r="G10" t="s">
         <v>250</v>
       </c>
       <c r="H10" s="278" t="s">
+        <v>3653</v>
+      </c>
+      <c r="I10" s="278" t="s">
         <v>3654</v>
-      </c>
-      <c r="I10" s="278" t="s">
-        <v>3655</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -41833,7 +41833,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="10" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="B5" s="10">
         <v>67992849</v>
@@ -41854,10 +41854,10 @@
         <v>517</v>
       </c>
       <c r="H5" s="220" t="s">
-        <v>3438</v>
+        <v>3437</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>3630</v>
+        <v>3629</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -41886,12 +41886,12 @@
         <v>2740</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="10" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>2398</v>
@@ -41900,7 +41900,7 @@
         <v>1722</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>3134</v>
+        <v>3133</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1695</v>
@@ -41912,10 +41912,10 @@
         <v>517</v>
       </c>
       <c r="H7" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>3135</v>
+        <v>3134</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -41931,7 +41931,7 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="10" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="B11" s="10">
         <v>64403333</v>
@@ -41963,7 +41963,7 @@
         <v>2144</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>959</v>
@@ -41975,10 +41975,10 @@
         <v>517</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>3149</v>
+        <v>3148</v>
       </c>
       <c r="I12" t="s">
-        <v>3296</v>
+        <v>3295</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -42003,7 +42003,7 @@
         <v>2202</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>2987</v>
+        <v>2986</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>959</v>
@@ -42015,10 +42015,10 @@
         <v>517</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -42044,7 +42044,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="10" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="B17" s="10">
         <v>64403333</v>
@@ -42067,7 +42067,7 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="10" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="B18" s="10">
         <v>60345107</v>
@@ -42076,7 +42076,7 @@
         <v>2327</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>3206</v>
+        <v>3205</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>959</v>
@@ -42088,10 +42088,10 @@
         <v>517</v>
       </c>
       <c r="H18" s="427" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>3275</v>
+        <v>3274</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -42105,7 +42105,7 @@
         <v>2378</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>3664</v>
+        <v>3663</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>959</v>
@@ -42117,10 +42117,10 @@
         <v>517</v>
       </c>
       <c r="H19" s="457" t="s">
-        <v>3665</v>
+        <v>3664</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>3386</v>
+        <v>3385</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="190" customFormat="1" ht="26">
@@ -42136,13 +42136,13 @@
         <v>2599</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>3351</v>
+        <v>3350</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>2403</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>3324</v>
+        <v>3323</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>959</v>
@@ -42154,15 +42154,15 @@
         <v>517</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>3439</v>
+        <v>3438</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="B23" s="10">
         <v>64720128</v>
@@ -42183,10 +42183,10 @@
         <v>517</v>
       </c>
       <c r="H23" s="10" t="s">
+        <v>3418</v>
+      </c>
+      <c r="I23" s="10" t="s">
         <v>3419</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>3420</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -42200,7 +42200,7 @@
         <v>2419</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>3084</v>
+        <v>3083</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>959</v>
@@ -42212,10 +42212,10 @@
         <v>517</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>3616</v>
+        <v>3615</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -42225,7 +42225,7 @@
         <v>2431</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>959</v>
@@ -42344,13 +42344,13 @@
         <v>2446</v>
       </c>
       <c r="B4" t="s">
-        <v>3053</v>
+        <v>3052</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1863</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="E4" t="s">
         <v>1864</v>
@@ -42362,13 +42362,13 @@
         <v>963</v>
       </c>
       <c r="H4" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="J4" t="s">
-        <v>3130</v>
+        <v>3129</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -42428,7 +42428,7 @@
         <v>2283</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>2284</v>
@@ -42440,13 +42440,13 @@
         <v>963</v>
       </c>
       <c r="H7" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>3171</v>
+        <v>3170</v>
       </c>
       <c r="J7" s="275" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -42454,16 +42454,16 @@
         <v>2500</v>
       </c>
       <c r="B8" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>3486</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>3487</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="10" t="s">
         <v>3488</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>3489</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>1738</v>
@@ -42472,30 +42472,30 @@
         <v>963</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="10" t="s">
+        <v>2999</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>3000</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>3001</v>
-      </c>
       <c r="C9" s="22" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>2877</v>
       </c>
       <c r="E9" s="447" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>2878</v>
@@ -42504,13 +42504,13 @@
         <v>963</v>
       </c>
       <c r="H9" s="10" t="s">
+        <v>3001</v>
+      </c>
+      <c r="I9" s="10" t="s">
         <v>3002</v>
       </c>
-      <c r="I9" s="10" t="s">
-        <v>3003</v>
-      </c>
       <c r="J9" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -42518,16 +42518,16 @@
         <v>1429</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>2285</v>
@@ -42536,30 +42536,30 @@
         <v>963</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="J10" t="s">
-        <v>3298</v>
+        <v>3297</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="457" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>3660</v>
+        <v>3659</v>
       </c>
       <c r="C11" s="10" t="s">
+        <v>3633</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>3636</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>3634</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>3637</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>3635</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>1738</v>
@@ -42579,7 +42579,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="C15" s="428" t="s">
-        <v>3634</v>
+        <v>3633</v>
       </c>
     </row>
   </sheetData>
@@ -42720,10 +42720,10 @@
         <v>60240509</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>3466</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>3467</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>3468</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>2597</v>
@@ -42744,7 +42744,7 @@
         <v>1786</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>2597</v>
@@ -42779,16 +42779,16 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="10" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="B12" s="10">
         <v>66466729</v>
       </c>
       <c r="C12" s="10" t="s">
+        <v>3595</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>3596</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>3597</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
@@ -42868,7 +42868,7 @@
       <c r="A19" s="10"/>
       <c r="B19" s="10"/>
       <c r="C19" s="428" t="s">
-        <v>3596</v>
+        <v>3595</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
@@ -42983,28 +42983,28 @@
         <v>147</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="E4" t="s">
         <v>2905</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="G4" s="275" t="s">
         <v>2915</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
   </sheetData>
@@ -44400,7 +44400,7 @@
         <v>51</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>1157</v>
@@ -44412,10 +44412,10 @@
         <v>159</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>3325</v>
+        <v>3324</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="N6" s="4" t="s">
         <v>26</v>
@@ -44423,7 +44423,7 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="456" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="B7" s="4">
         <v>69888391</v>
@@ -44447,13 +44447,13 @@
         <v>2261</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="L7" s="3"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
       <c r="B8" t="s">
         <v>452</v>
@@ -44477,7 +44477,7 @@
         <v>2715</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
     </row>
     <row r="9" spans="1:14" s="4" customFormat="1">
@@ -44489,19 +44489,19 @@
         <v>2153</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>3335</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>3336</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>3337</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>159</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>3300</v>
+        <v>3299</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>3258</v>
+        <v>3257</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>815</v>
@@ -44509,7 +44509,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="4" t="s">
-        <v>3504</v>
+        <v>3503</v>
       </c>
       <c r="B10" s="4">
         <v>67916500</v>
@@ -44530,10 +44530,10 @@
         <v>244</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>3188</v>
+        <v>3187</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -44550,7 +44550,7 @@
         <v>1510</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>2896</v>
@@ -44559,10 +44559,10 @@
         <v>244</v>
       </c>
       <c r="H11" t="s">
-        <v>3533</v>
+        <v>3532</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -44588,10 +44588,10 @@
         <v>244</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -44599,7 +44599,7 @@
         <v>2921</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="C13" s="22" t="s">
         <v>1218</v>
@@ -44617,10 +44617,10 @@
         <v>244</v>
       </c>
       <c r="H13" s="220" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>3621</v>
+        <v>3620</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="4" customFormat="1">
@@ -44646,10 +44646,10 @@
         <v>244</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="I14" s="220" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
       <c r="L14" s="3"/>
     </row>
@@ -44667,19 +44667,19 @@
         <v>2841</v>
       </c>
       <c r="E15" s="4" t="s">
+        <v>3590</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>3591</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>3592</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>887</v>
       </c>
       <c r="H15" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="I15" t="s">
-        <v>3617</v>
+        <v>3616</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>498</v>
@@ -44708,10 +44708,10 @@
         <v>159</v>
       </c>
       <c r="H16" t="s">
-        <v>3454</v>
+        <v>3453</v>
       </c>
       <c r="I16" t="s">
-        <v>3326</v>
+        <v>3325</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>805</v>
@@ -44719,7 +44719,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="B17">
         <v>65325884</v>
@@ -44742,7 +44742,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="4" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>2107</v>
@@ -44754,19 +44754,19 @@
         <v>2213</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>3337</v>
+        <v>3336</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>244</v>
       </c>
       <c r="H18" s="49" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="I18" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="4" customFormat="1">
@@ -44783,10 +44783,10 @@
         <v>2582</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>3353</v>
+        <v>3352</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>3337</v>
+        <v>3336</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>1227</v>
@@ -44796,7 +44796,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="4" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="B20">
         <v>64403333</v>
@@ -44857,7 +44857,7 @@
         <v>2204</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>2462</v>
@@ -44868,7 +44868,7 @@
     </row>
     <row r="23" spans="1:12" s="4" customFormat="1">
       <c r="A23" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="B23">
         <v>63247837</v>
@@ -44877,7 +44877,7 @@
         <v>2590</v>
       </c>
       <c r="D23" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="E23" t="s">
         <v>2593</v>
@@ -44889,16 +44889,16 @@
         <v>159</v>
       </c>
       <c r="H23" t="s">
-        <v>3212</v>
+        <v>3211</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
       <c r="L23" s="6"/>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
       <c r="B24">
         <v>69184177</v>
@@ -44907,10 +44907,10 @@
         <v>1630</v>
       </c>
       <c r="D24" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>3039</v>
+        <v>3038</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>2459</v>
@@ -44921,19 +44921,19 @@
     </row>
     <row r="25" spans="1:12" s="4" customFormat="1">
       <c r="A25" s="4" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>3381</v>
+        <v>3380</v>
       </c>
       <c r="C25" s="21" t="s">
         <v>1326</v>
       </c>
       <c r="D25" t="s">
-        <v>3380</v>
+        <v>3379</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>2955</v>
+        <v>2954</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>2462</v>
@@ -44942,10 +44942,10 @@
         <v>244</v>
       </c>
       <c r="H25" s="105" t="s">
-        <v>3645</v>
+        <v>3644</v>
       </c>
       <c r="I25" s="220" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="4" customFormat="1">
@@ -44971,10 +44971,10 @@
         <v>159</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="I27" t="s">
-        <v>3169</v>
+        <v>3168</v>
       </c>
       <c r="L27" s="4" t="s">
         <v>813</v>
@@ -44982,7 +44982,7 @@
     </row>
     <row r="28" spans="1:12" s="4" customFormat="1">
       <c r="A28" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>2453</v>
@@ -44994,7 +44994,7 @@
         <v>2028</v>
       </c>
       <c r="E28" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>2462</v>
@@ -45003,10 +45003,10 @@
         <v>325</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>3636</v>
+        <v>3635</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="K28"/>
     </row>
@@ -45024,7 +45024,7 @@
         <v>2865</v>
       </c>
       <c r="E29" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>2896</v>
@@ -45036,7 +45036,7 @@
         <v>2866</v>
       </c>
       <c r="I29" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="J29" s="4"/>
       <c r="L29" s="135"/>
@@ -45046,16 +45046,16 @@
         <v>2930</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="C30" s="22" t="s">
         <v>402</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="E30" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>1341</v>
@@ -45064,7 +45064,7 @@
         <v>159</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="I30" s="55" t="s">
         <v>2739</v>
@@ -45072,7 +45072,7 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="B31" s="4">
         <v>69409351</v>
@@ -45093,15 +45093,15 @@
         <v>159</v>
       </c>
       <c r="H31" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="97" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>2843</v>
@@ -45110,7 +45110,7 @@
         <v>2367</v>
       </c>
       <c r="D32" t="s">
-        <v>3669</v>
+        <v>3668</v>
       </c>
       <c r="E32" t="s">
         <v>2371</v>
@@ -45122,10 +45122,10 @@
         <v>159</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>3624</v>
+        <v>3623</v>
       </c>
       <c r="I32" s="455" t="s">
-        <v>3670</v>
+        <v>3669</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -45133,13 +45133,13 @@
         <v>2596</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>3481</v>
+        <v>3480</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>2580</v>
       </c>
       <c r="D33" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
       <c r="E33" t="s">
         <v>2583</v>
@@ -45151,7 +45151,7 @@
         <v>2584</v>
       </c>
       <c r="H33" s="455" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -45159,13 +45159,13 @@
         <v>1429</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>3432</v>
+        <v>3431</v>
       </c>
       <c r="C34" s="21" t="s">
         <v>2577</v>
       </c>
       <c r="D34" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="E34" t="s">
         <v>2583</v>
@@ -45177,10 +45177,10 @@
         <v>159</v>
       </c>
       <c r="H34" t="s">
-        <v>3127</v>
+        <v>3126</v>
       </c>
       <c r="I34" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="J34" s="4"/>
     </row>
@@ -45207,24 +45207,24 @@
         <v>2584</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>3640</v>
+        <v>3639</v>
       </c>
       <c r="I35" s="49" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="B36" t="s">
-        <v>3350</v>
+        <v>3349</v>
       </c>
       <c r="C36" s="22" t="s">
         <v>2579</v>
       </c>
       <c r="D36" t="s">
-        <v>3349</v>
+        <v>3348</v>
       </c>
       <c r="E36" t="s">
         <v>2583</v>
@@ -45236,10 +45236,10 @@
         <v>159</v>
       </c>
       <c r="H36" t="s">
-        <v>3352</v>
+        <v>3351</v>
       </c>
       <c r="I36" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -45247,7 +45247,7 @@
         <v>158</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>3656</v>
+        <v>3655</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>2591</v>
@@ -45265,7 +45265,7 @@
         <v>159</v>
       </c>
       <c r="H37" t="s">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="I37" t="s">
         <v>2919</v>
@@ -45276,7 +45276,7 @@
         <v>157</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>2592</v>
@@ -45294,10 +45294,10 @@
         <v>159</v>
       </c>
       <c r="H38" s="220" t="s">
-        <v>3530</v>
+        <v>3529</v>
       </c>
       <c r="I38" t="s">
-        <v>3205</v>
+        <v>3204</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="455" customFormat="1">
@@ -45310,10 +45310,10 @@
         <v>1351</v>
       </c>
       <c r="E41" s="97" t="s">
+        <v>3262</v>
+      </c>
+      <c r="F41" s="105" t="s">
         <v>3263</v>
-      </c>
-      <c r="F41" s="105" t="s">
-        <v>3264</v>
       </c>
       <c r="G41" s="105" t="s">
         <v>159</v>
@@ -45333,10 +45333,10 @@
         <v>2093</v>
       </c>
       <c r="E42" s="97" t="s">
+        <v>3262</v>
+      </c>
+      <c r="F42" s="105" t="s">
         <v>3263</v>
-      </c>
-      <c r="F42" s="105" t="s">
-        <v>3264</v>
       </c>
       <c r="G42" s="105" t="s">
         <v>159</v>
@@ -45356,10 +45356,10 @@
         <v>2324</v>
       </c>
       <c r="E43" s="105" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
       <c r="F43" s="105" t="s">
-        <v>3264</v>
+        <v>3263</v>
       </c>
       <c r="G43" s="97" t="s">
         <v>159</v>
@@ -45376,7 +45376,7 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="4" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="B45" t="s">
         <v>2495</v>
@@ -45406,7 +45406,7 @@
         <v>2799</v>
       </c>
       <c r="K45" t="s">
-        <v>3546</v>
+        <v>3545</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="4" customFormat="1">
@@ -45780,13 +45780,13 @@
         <v>157</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="C2" s="276" t="s">
         <v>254</v>
       </c>
       <c r="D2" s="106" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>1296</v>
@@ -45798,16 +45798,16 @@
         <v>62</v>
       </c>
       <c r="H2" s="300" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="I2" s="106" t="s">
-        <v>3036</v>
+        <v>3035</v>
       </c>
       <c r="J2" s="107" t="s">
-        <v>3522</v>
+        <v>3521</v>
       </c>
       <c r="K2" s="461" t="s">
-        <v>3668</v>
+        <v>3667</v>
       </c>
       <c r="M2" s="159"/>
     </row>
@@ -45822,7 +45822,7 @@
         <v>1179</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="E4" s="32" t="s">
         <v>2392</v>
@@ -45834,25 +45834,25 @@
         <v>270</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>3285</v>
+        <v>3284</v>
       </c>
       <c r="I4" s="30" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
       <c r="J4" s="139" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="K4" s="139" t="s">
-        <v>3354</v>
+        <v>3353</v>
       </c>
       <c r="M4" s="39"/>
     </row>
     <row r="5" spans="1:13" s="30" customFormat="1">
       <c r="A5" s="30" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>3207</v>
+        <v>3206</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>1112</v>
@@ -45870,22 +45870,22 @@
         <v>65</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="I5" s="306" t="s">
         <v>2931</v>
       </c>
       <c r="J5" s="30" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
       <c r="K5" s="30" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="M5" s="36"/>
     </row>
     <row r="6" spans="1:13" s="30" customFormat="1">
       <c r="A6" s="107" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B6" s="30" t="s">
         <v>2179</v>
@@ -45894,7 +45894,7 @@
         <v>2744</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>3423</v>
+        <v>3422</v>
       </c>
       <c r="E6" s="140" t="s">
         <v>2707</v>
@@ -45906,22 +45906,22 @@
         <v>65</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="K6" s="30" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="M6" s="36"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="107" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>1209</v>
@@ -45930,28 +45930,28 @@
         <v>1089</v>
       </c>
       <c r="D7" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
       <c r="E7" s="107" t="s">
+        <v>3265</v>
+      </c>
+      <c r="F7" s="30" t="s">
         <v>3266</v>
-      </c>
-      <c r="F7" s="30" t="s">
-        <v>3267</v>
       </c>
       <c r="G7" s="106" t="s">
         <v>720</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>3166</v>
+        <v>3165</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>3573</v>
+        <v>3572</v>
       </c>
       <c r="J7" s="30" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
       <c r="K7" s="30" t="s">
-        <v>3639</v>
+        <v>3638</v>
       </c>
       <c r="M7" s="36"/>
     </row>
@@ -45966,7 +45966,7 @@
         <v>983</v>
       </c>
       <c r="D8" s="139" t="s">
-        <v>3375</v>
+        <v>3374</v>
       </c>
       <c r="E8" s="107" t="s">
         <v>1154</v>
@@ -45978,22 +45978,22 @@
         <v>65</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="I8" s="32" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="J8" s="107" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
       <c r="K8" s="139" t="s">
-        <v>3331</v>
+        <v>3330</v>
       </c>
       <c r="M8" s="36"/>
     </row>
     <row r="9" spans="1:13" s="107" customFormat="1">
       <c r="A9" s="302" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="B9" s="32" t="s">
         <v>1672</v>
@@ -46014,22 +46014,22 @@
         <v>65</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>3617</v>
+        <v>3616</v>
       </c>
       <c r="I9" s="107" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>3216</v>
+        <v>3215</v>
       </c>
       <c r="K9" s="107" t="s">
-        <v>3647</v>
+        <v>3646</v>
       </c>
       <c r="M9" s="36"/>
     </row>
     <row r="10" spans="1:13" s="30" customFormat="1">
       <c r="A10" s="30" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="B10" s="30">
         <v>69575383</v>
@@ -46050,16 +46050,16 @@
         <v>65</v>
       </c>
       <c r="H10" s="107" t="s">
-        <v>3213</v>
+        <v>3212</v>
       </c>
       <c r="I10" t="s">
-        <v>3295</v>
+        <v>3294</v>
       </c>
       <c r="J10" s="219" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="K10" s="107" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="M10" s="34"/>
     </row>
@@ -46086,31 +46086,31 @@
         <v>605</v>
       </c>
       <c r="H11" s="139" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="I11" s="30" t="s">
-        <v>3505</v>
+        <v>3504</v>
       </c>
       <c r="J11" s="107" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
       <c r="K11" s="107" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="M11" s="36"/>
     </row>
     <row r="12" spans="1:13" s="106" customFormat="1">
       <c r="A12" s="319" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="B12" s="106" t="s">
-        <v>3644</v>
+        <v>3643</v>
       </c>
       <c r="C12" s="22" t="s">
         <v>72</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
       <c r="E12" s="106" t="s">
         <v>908</v>
@@ -46122,22 +46122,22 @@
         <v>245</v>
       </c>
       <c r="H12" s="30" t="s">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="I12" s="106" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
       <c r="J12" s="106" t="s">
-        <v>3642</v>
+        <v>3641</v>
       </c>
       <c r="K12" s="107" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="M12" s="151"/>
     </row>
     <row r="13" spans="1:13" s="107" customFormat="1">
       <c r="A13" s="140" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="B13" s="107" t="s">
         <v>2774</v>
@@ -46146,7 +46146,7 @@
         <v>919</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="E13" s="140" t="s">
         <v>2745</v>
@@ -46158,16 +46158,16 @@
         <v>65</v>
       </c>
       <c r="H13" s="30" t="s">
-        <v>3080</v>
+        <v>3079</v>
       </c>
       <c r="I13" s="30" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
       <c r="J13" s="107" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
       <c r="K13" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="M13" s="36"/>
     </row>
@@ -46194,13 +46194,13 @@
         <v>65</v>
       </c>
       <c r="H14" s="107" t="s">
-        <v>3301</v>
+        <v>3300</v>
       </c>
       <c r="I14" s="411" t="s">
         <v>2262</v>
       </c>
       <c r="J14" s="32" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="M14" s="36"/>
     </row>
@@ -46227,16 +46227,16 @@
         <v>66</v>
       </c>
       <c r="H15" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="I15" t="s">
-        <v>3453</v>
+        <v>3452</v>
       </c>
       <c r="J15" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="K15" s="454" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="M15" s="36"/>
     </row>
@@ -46288,16 +46288,16 @@
         <v>66</v>
       </c>
       <c r="H17" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="I17" s="30" t="s">
-        <v>3041</v>
+        <v>3040</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>3560</v>
+        <v>3559</v>
       </c>
       <c r="K17" s="220" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="M17" s="34"/>
     </row>
@@ -46324,16 +46324,16 @@
         <v>66</v>
       </c>
       <c r="H18" s="30" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="I18" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
       <c r="J18" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="K18" t="s">
-        <v>3629</v>
+        <v>3628</v>
       </c>
       <c r="M18" s="36"/>
     </row>
@@ -46348,7 +46348,7 @@
         <v>1689</v>
       </c>
       <c r="D19" s="134" t="s">
-        <v>3376</v>
+        <v>3375</v>
       </c>
       <c r="E19" t="s">
         <v>1692</v>
@@ -46360,16 +46360,16 @@
         <v>66</v>
       </c>
       <c r="H19" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="I19" s="49" t="s">
         <v>2903</v>
       </c>
       <c r="J19" s="220" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
       <c r="K19" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="M19" s="36"/>
     </row>
@@ -46384,7 +46384,7 @@
         <v>2476</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="E20" s="107" t="s">
         <v>2406</v>
@@ -46396,31 +46396,31 @@
         <v>65</v>
       </c>
       <c r="H20" s="436" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
       <c r="I20" t="s">
+        <v>2975</v>
+      </c>
+      <c r="J20" s="49" t="s">
         <v>2976</v>
       </c>
-      <c r="J20" s="49" t="s">
-        <v>2977</v>
-      </c>
       <c r="K20" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="M20" s="36"/>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>3306</v>
+        <v>3305</v>
       </c>
       <c r="B21" t="s">
-        <v>3311</v>
+        <v>3310</v>
       </c>
       <c r="C21" s="22" t="s">
         <v>1127</v>
       </c>
       <c r="D21" t="s">
-        <v>3310</v>
+        <v>3309</v>
       </c>
       <c r="E21" s="140" t="s">
         <v>1589</v>
@@ -46432,19 +46432,19 @@
         <v>65</v>
       </c>
       <c r="H21" t="s">
-        <v>3315</v>
+        <v>3314</v>
       </c>
       <c r="I21" t="s">
+        <v>3317</v>
+      </c>
+      <c r="J21" t="s">
         <v>3318</v>
-      </c>
-      <c r="J21" t="s">
-        <v>3319</v>
       </c>
       <c r="M21" s="36"/>
     </row>
     <row r="22" spans="1:13" s="30" customFormat="1">
       <c r="A22" s="30" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="B22" s="30" t="s">
         <v>2109</v>
@@ -46453,78 +46453,78 @@
         <v>2710</v>
       </c>
       <c r="D22" s="107" t="s">
-        <v>3360</v>
+        <v>3359</v>
       </c>
       <c r="E22" s="30" t="s">
+        <v>3332</v>
+      </c>
+      <c r="F22" s="30" t="s">
         <v>3333</v>
-      </c>
-      <c r="F22" s="30" t="s">
-        <v>3334</v>
       </c>
       <c r="G22" s="32" t="s">
         <v>65</v>
       </c>
       <c r="H22" s="30" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="I22" s="30" t="s">
+        <v>3339</v>
+      </c>
+      <c r="J22" s="30" t="s">
         <v>3340</v>
-      </c>
-      <c r="J22" s="30" t="s">
-        <v>3341</v>
       </c>
       <c r="M22" s="36"/>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="B23" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="C23" s="22" t="s">
         <v>1902</v>
       </c>
       <c r="D23" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="E23" s="30" t="s">
+        <v>3332</v>
+      </c>
+      <c r="F23" s="30" t="s">
         <v>3333</v>
-      </c>
-      <c r="F23" s="30" t="s">
-        <v>3334</v>
       </c>
       <c r="G23" t="s">
         <v>66</v>
       </c>
       <c r="H23" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="I23" t="s">
-        <v>3444</v>
+        <v>3443</v>
       </c>
       <c r="J23" t="s">
-        <v>3437</v>
+        <v>3436</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="30" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="B24" t="s">
-        <v>3667</v>
+        <v>3666</v>
       </c>
       <c r="C24" s="22" t="s">
         <v>1916</v>
       </c>
       <c r="D24" s="455" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="E24" s="107" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
       <c r="F24" s="30" t="s">
-        <v>3666</v>
+        <v>3665</v>
       </c>
       <c r="G24" s="32" t="s">
         <v>270</v>
@@ -46567,7 +46567,7 @@
     </row>
     <row r="31" spans="1:13" s="30" customFormat="1">
       <c r="A31" s="107" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="B31" s="107">
         <v>64403333</v>
@@ -46615,7 +46615,7 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="B33">
         <v>60389752</v>
@@ -46638,7 +46638,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="B34">
         <v>60389752</v>
@@ -46647,13 +46647,13 @@
         <v>2169</v>
       </c>
       <c r="D34" s="32" t="s">
-        <v>3211</v>
+        <v>3210</v>
       </c>
       <c r="E34" s="30" t="s">
+        <v>3332</v>
+      </c>
+      <c r="F34" s="30" t="s">
         <v>3333</v>
-      </c>
-      <c r="F34" s="30" t="s">
-        <v>3334</v>
       </c>
       <c r="G34" t="s">
         <v>3</v>
@@ -46662,7 +46662,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>3306</v>
+        <v>3305</v>
       </c>
       <c r="B35">
         <v>60389752</v>
@@ -46686,7 +46686,7 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B36">
         <v>60389752</v>
@@ -46710,7 +46710,7 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="30" t="s">
-        <v>3306</v>
+        <v>3305</v>
       </c>
       <c r="B37" s="30">
         <v>64403333</v>
@@ -46735,7 +46735,7 @@
     </row>
     <row r="38" spans="1:13" s="30" customFormat="1">
       <c r="A38" s="30" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="B38" s="30">
         <v>60389752</v>
@@ -46772,10 +46772,10 @@
         <v>2142</v>
       </c>
       <c r="E39" t="s">
+        <v>3332</v>
+      </c>
+      <c r="F39" t="s">
         <v>3333</v>
-      </c>
-      <c r="F39" t="s">
-        <v>3334</v>
       </c>
       <c r="G39" t="s">
         <v>3</v>
@@ -46844,7 +46844,7 @@
         <v>2502</v>
       </c>
       <c r="E45" t="s">
-        <v>3222</v>
+        <v>3221</v>
       </c>
       <c r="F45" s="30" t="s">
         <v>2503</v>
@@ -46853,10 +46853,10 @@
         <v>369</v>
       </c>
       <c r="H45" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="I45" s="30" t="s">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="J45" s="49" t="s">
         <v>2928</v>
@@ -46914,7 +46914,7 @@
         <v>1106</v>
       </c>
       <c r="D65" s="97" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="E65" s="107" t="s">
         <v>1123</v>
@@ -46932,10 +46932,10 @@
         <v>1122</v>
       </c>
       <c r="C66" s="97" t="s">
-        <v>3434</v>
+        <v>3433</v>
       </c>
       <c r="D66" s="97" t="s">
-        <v>3211</v>
+        <v>3210</v>
       </c>
       <c r="E66" s="97" t="s">
         <v>2404</v>
@@ -46955,24 +46955,24 @@
         <v>2164</v>
       </c>
       <c r="E67" s="107" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
       <c r="F67" s="30" t="s">
-        <v>3666</v>
+        <v>3665</v>
       </c>
     </row>
     <row r="68" spans="1:38">
       <c r="C68" s="459" t="s">
+        <v>3548</v>
+      </c>
+      <c r="D68" t="s">
         <v>3549</v>
       </c>
-      <c r="D68" t="s">
-        <v>3550</v>
-      </c>
       <c r="E68" s="107" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
       <c r="F68" s="30" t="s">
-        <v>3666</v>
+        <v>3665</v>
       </c>
       <c r="G68" s="106" t="s">
         <v>720</v>
@@ -46983,13 +46983,13 @@
         <v>1211</v>
       </c>
       <c r="D69" s="97" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="E69" s="107" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
       <c r="F69" s="30" t="s">
-        <v>3666</v>
+        <v>3665</v>
       </c>
       <c r="G69" s="106" t="s">
         <v>720</v>
@@ -47270,7 +47270,7 @@
         <v>1130</v>
       </c>
       <c r="D93" t="s">
-        <v>3329</v>
+        <v>3328</v>
       </c>
       <c r="E93" s="140" t="s">
         <v>1132</v>
@@ -47294,7 +47294,7 @@
         <v>1390</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>3330</v>
+        <v>3329</v>
       </c>
       <c r="E94" s="266" t="s">
         <v>1505</v>
@@ -47348,7 +47348,7 @@
         <v>358</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>3434</v>
+        <v>3433</v>
       </c>
     </row>
     <row r="105" spans="2:5">
@@ -47574,7 +47574,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="C12" s="236"/>
     </row>
@@ -47712,7 +47712,7 @@
       </c>
       <c r="B24" s="87"/>
       <c r="F24" s="2" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -47788,27 +47788,27 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="87" t="s">
-        <v>3388</v>
+        <v>3387</v>
       </c>
       <c r="C40" t="s">
-        <v>3391</v>
+        <v>3390</v>
       </c>
       <c r="F40" s="45"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="89" t="s">
-        <v>3389</v>
+        <v>3388</v>
       </c>
       <c r="C41" t="s">
-        <v>3392</v>
+        <v>3391</v>
       </c>
     </row>
     <row r="42" spans="2:6" ht="15" thickBot="1">
       <c r="B42" s="86" t="s">
-        <v>3390</v>
+        <v>3389</v>
       </c>
       <c r="C42" t="s">
-        <v>3393</v>
+        <v>3392</v>
       </c>
     </row>
     <row r="43" spans="2:6">
@@ -47971,22 +47971,22 @@
         <v>2033</v>
       </c>
       <c r="E6" s="247" t="s">
+        <v>3255</v>
+      </c>
+      <c r="F6" s="247" t="s">
         <v>3256</v>
-      </c>
-      <c r="F6" s="247" t="s">
-        <v>3257</v>
       </c>
       <c r="G6" s="247" t="s">
         <v>357</v>
       </c>
       <c r="H6" s="247" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="I6" s="244" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="J6" s="295" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="K6" s="247" t="s">
         <v>475</v>
@@ -48009,19 +48009,19 @@
         <v>1036</v>
       </c>
       <c r="F7" s="265" t="s">
-        <v>3259</v>
+        <v>3258</v>
       </c>
       <c r="G7" s="265" t="s">
         <v>690</v>
       </c>
       <c r="H7" s="295" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="I7" s="295" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="J7" s="295" t="s">
-        <v>3458</v>
+        <v>3457</v>
       </c>
       <c r="K7" s="265" t="s">
         <v>709</v>
@@ -48044,19 +48044,19 @@
         <v>1228</v>
       </c>
       <c r="F8" s="265" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="G8" s="265" t="s">
         <v>250</v>
       </c>
       <c r="H8" s="265" t="s">
-        <v>3605</v>
+        <v>3604</v>
       </c>
       <c r="I8" s="265" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="J8" s="265" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="K8" s="259"/>
       <c r="L8" s="259"/>
@@ -48078,7 +48078,7 @@
         <v>2695</v>
       </c>
       <c r="F9" s="263" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
       <c r="G9" s="263" t="s">
         <v>946</v>
@@ -48110,13 +48110,13 @@
         <v>690</v>
       </c>
       <c r="H10" s="264" t="s">
-        <v>3648</v>
+        <v>3647</v>
       </c>
       <c r="I10" s="448" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="J10" s="264" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="K10" s="245" t="s">
         <v>1203</v>
@@ -48127,7 +48127,7 @@
         <v>2500</v>
       </c>
       <c r="B11" s="262" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="C11" s="194" t="s">
         <v>491</v>
@@ -48145,13 +48145,13 @@
         <v>690</v>
       </c>
       <c r="H11" s="215" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="I11" s="424" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="J11" s="269" t="s">
-        <v>3554</v>
+        <v>3553</v>
       </c>
       <c r="K11" s="183" t="s">
         <v>1204</v>
@@ -48185,10 +48185,10 @@
     </row>
     <row r="13" spans="1:12" s="223" customFormat="1">
       <c r="A13" s="223" t="s">
-        <v>3306</v>
+        <v>3305</v>
       </c>
       <c r="B13" s="223" t="s">
-        <v>3328</v>
+        <v>3327</v>
       </c>
       <c r="C13" s="423" t="s">
         <v>335</v>
@@ -48197,22 +48197,22 @@
         <v>2390</v>
       </c>
       <c r="E13" s="223" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="F13" s="223" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="G13" s="223" t="s">
         <v>690</v>
       </c>
       <c r="H13" s="223" t="s">
+        <v>3026</v>
+      </c>
+      <c r="I13" s="215" t="s">
+        <v>3226</v>
+      </c>
+      <c r="J13" s="223" t="s">
         <v>3027</v>
-      </c>
-      <c r="I13" s="215" t="s">
-        <v>3227</v>
-      </c>
-      <c r="J13" s="223" t="s">
-        <v>3028</v>
       </c>
       <c r="K13" s="223" t="s">
         <v>1317</v>
@@ -48232,7 +48232,7 @@
         <v>1972</v>
       </c>
       <c r="E14" s="216" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="F14" s="216" t="s">
         <v>1433</v>
@@ -48241,13 +48241,13 @@
         <v>690</v>
       </c>
       <c r="H14" s="272" t="s">
-        <v>3459</v>
+        <v>3458</v>
       </c>
       <c r="I14" s="215" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
       <c r="J14" s="262" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="K14" s="183" t="s">
         <v>1205</v>
@@ -48258,7 +48258,7 @@
         <v>1416</v>
       </c>
       <c r="B15" s="264" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
       <c r="C15" s="270" t="s">
         <v>1305</v>
@@ -48276,13 +48276,13 @@
         <v>690</v>
       </c>
       <c r="H15" s="264" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="I15" s="271" t="s">
-        <v>3580</v>
+        <v>3579</v>
       </c>
       <c r="J15" s="264" t="s">
-        <v>3159</v>
+        <v>3158</v>
       </c>
       <c r="K15" s="259" t="s">
         <v>1438</v>
@@ -48340,7 +48340,7 @@
     </row>
     <row r="18" spans="1:11" s="259" customFormat="1">
       <c r="A18" s="271" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B18" s="259" t="s">
         <v>2332</v>
@@ -48349,7 +48349,7 @@
         <v>831</v>
       </c>
       <c r="D18" s="264" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="E18" s="264" t="s">
         <v>1788</v>
@@ -48361,13 +48361,13 @@
         <v>690</v>
       </c>
       <c r="H18" s="259" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="I18" s="298" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="J18" s="259" t="s">
-        <v>3523</v>
+        <v>3522</v>
       </c>
       <c r="K18" s="264" t="s">
         <v>1765</v>
@@ -48375,7 +48375,7 @@
     </row>
     <row r="19" spans="1:11" s="259" customFormat="1">
       <c r="A19" s="259" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="B19" s="259" t="s">
         <v>2377</v>
@@ -48396,13 +48396,13 @@
         <v>690</v>
       </c>
       <c r="H19" s="259" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="I19" s="259" t="s">
-        <v>3433</v>
+        <v>3432</v>
       </c>
       <c r="J19" s="259" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="K19" s="259" t="s">
         <v>1810</v>
@@ -48410,7 +48410,7 @@
     </row>
     <row r="20" spans="1:11" s="264" customFormat="1">
       <c r="A20" s="298" t="s">
-        <v>3504</v>
+        <v>3503</v>
       </c>
       <c r="B20" s="304">
         <v>63609244</v>
@@ -48434,10 +48434,10 @@
         <v>2761</v>
       </c>
       <c r="I20" s="264" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="J20" s="264" t="s">
-        <v>3348</v>
+        <v>3347</v>
       </c>
       <c r="K20" s="259" t="s">
         <v>1812</v>
@@ -48480,10 +48480,10 @@
         <v>637</v>
       </c>
       <c r="D22" s="255" t="s">
-        <v>3472</v>
+        <v>3471</v>
       </c>
       <c r="E22" s="271" t="s">
-        <v>3395</v>
+        <v>3394</v>
       </c>
       <c r="F22" s="271" t="s">
         <v>1710</v>
@@ -48492,13 +48492,13 @@
         <v>250</v>
       </c>
       <c r="H22" s="259" t="s">
-        <v>3483</v>
+        <v>3482</v>
       </c>
       <c r="I22" s="264" t="s">
-        <v>3228</v>
+        <v>3227</v>
       </c>
       <c r="J22" s="264" t="s">
-        <v>3128</v>
+        <v>3127</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="97" customFormat="1">
@@ -48719,7 +48719,7 @@
         <v>840</v>
       </c>
       <c r="D45" s="264" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
       <c r="E45" s="259" t="s">
         <v>1788</v>
@@ -48922,13 +48922,13 @@
         <v>2770</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
       <c r="I2" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="J2" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="L2" s="36" t="s">
         <v>1173</v>
@@ -48954,7 +48954,7 @@
         <v>298</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>707</v>
@@ -48983,19 +48983,19 @@
         <v>2917</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>323</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
       <c r="H4" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="J4" t="s">
         <v>2918</v>
@@ -49024,7 +49024,7 @@
         <v>424</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="H5" s="49" t="s">
         <v>2738</v>
@@ -49039,7 +49039,7 @@
     </row>
     <row r="6" spans="1:12" s="4" customFormat="1">
       <c r="A6" s="4" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
       <c r="B6" s="4">
         <v>65436260</v>
@@ -49057,13 +49057,13 @@
         <v>166</v>
       </c>
       <c r="G6" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
       <c r="I6" t="s">
-        <v>3287</v>
+        <v>3286</v>
       </c>
       <c r="J6" s="49" t="s">
         <v>2885</v>
@@ -49074,7 +49074,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="4" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="B7" s="4">
         <v>69561522</v>
@@ -49083,25 +49083,25 @@
         <v>434</v>
       </c>
       <c r="D7" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="E7" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="F7" t="s">
         <v>151</v>
       </c>
       <c r="G7" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="J7" t="s">
-        <v>3150</v>
+        <v>3149</v>
       </c>
       <c r="L7" s="83" t="s">
         <v>435</v>
@@ -49109,10 +49109,10 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="4" t="s">
-        <v>3504</v>
+        <v>3503</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>658</v>
@@ -49130,10 +49130,10 @@
         <v>2636</v>
       </c>
       <c r="H8" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="I8" s="49" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="J8" s="49" t="s">
         <v>2769</v>
@@ -49160,16 +49160,16 @@
         <v>151</v>
       </c>
       <c r="G9" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="H9" s="220" t="s">
-        <v>3085</v>
+        <v>3084</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>3532</v>
+        <v>3531</v>
       </c>
       <c r="J9" s="220" t="s">
-        <v>3073</v>
+        <v>3072</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -49183,7 +49183,7 @@
         <v>2196</v>
       </c>
       <c r="D10" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="E10" t="s">
         <v>2167</v>
@@ -49192,13 +49192,13 @@
         <v>1818</v>
       </c>
       <c r="G10" t="s">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="H10" s="49" t="s">
-        <v>3486</v>
+        <v>3485</v>
       </c>
       <c r="I10" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="J10" s="49" t="s">
         <v>2831</v>
@@ -49241,7 +49241,7 @@
         <v>1478</v>
       </c>
       <c r="E12" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="F12" t="s">
         <v>614</v>
@@ -49249,7 +49249,7 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="B13">
         <v>64403333</v>
@@ -49272,16 +49272,16 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>3221</v>
+        <v>3220</v>
       </c>
       <c r="B14" t="s">
-        <v>3230</v>
+        <v>3229</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>281</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
       <c r="E14" t="s">
         <v>2136</v>
@@ -49290,16 +49290,16 @@
         <v>1818</v>
       </c>
       <c r="G14" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="H14" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
       <c r="I14" t="s">
-        <v>3410</v>
+        <v>3409</v>
       </c>
       <c r="J14" t="s">
-        <v>3327</v>
+        <v>3326</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -49567,7 +49567,7 @@
     </row>
     <row r="2" spans="1:14" ht="43.15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>2990</v>
+        <v>2989</v>
       </c>
       <c r="C2" s="51"/>
       <c r="D2" s="52" t="s">
@@ -49591,7 +49591,7 @@
         <v>2667</v>
       </c>
       <c r="E4" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -49628,7 +49628,7 @@
         <v>1550</v>
       </c>
       <c r="E9" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="F9" t="s">
         <v>1732</v>
@@ -49636,7 +49636,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="B10">
         <v>63000545</v>
@@ -49648,7 +49648,7 @@
         <v>2211</v>
       </c>
       <c r="E10" t="s">
-        <v>3556</v>
+        <v>3555</v>
       </c>
       <c r="F10" t="s">
         <v>1681</v>
@@ -49668,7 +49668,7 @@
         <v>2054</v>
       </c>
       <c r="E11" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -49685,7 +49685,7 @@
         <v>2676</v>
       </c>
       <c r="E12" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="F12" t="s">
         <v>1681</v>
@@ -49693,7 +49693,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>3305</v>
+        <v>3304</v>
       </c>
       <c r="B13">
         <v>62271547</v>
@@ -49722,7 +49722,7 @@
         <v>1936</v>
       </c>
       <c r="D14" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="E14" t="s">
         <v>2637</v>
@@ -49733,7 +49733,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B15">
         <v>62806425</v>
@@ -49762,10 +49762,10 @@
         <v>2723</v>
       </c>
       <c r="D16" s="30" t="s">
+        <v>3015</v>
+      </c>
+      <c r="E16" t="s">
         <v>3016</v>
-      </c>
-      <c r="E16" t="s">
-        <v>3017</v>
       </c>
       <c r="F16" t="s">
         <v>2679</v>
@@ -49782,10 +49782,10 @@
         <v>2927</v>
       </c>
       <c r="D17" s="30" t="s">
+        <v>3029</v>
+      </c>
+      <c r="E17" t="s">
         <v>3030</v>
-      </c>
-      <c r="E17" t="s">
-        <v>3031</v>
       </c>
       <c r="F17" t="s">
         <v>2679</v>
@@ -49808,7 +49808,7 @@
         <v>2727</v>
       </c>
       <c r="E18" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="F18" t="s">
         <v>2679</v>
@@ -49828,7 +49828,7 @@
         <v>2767</v>
       </c>
       <c r="E19" t="s">
-        <v>3170</v>
+        <v>3169</v>
       </c>
       <c r="F19" t="s">
         <v>2907</v>
@@ -49851,7 +49851,7 @@
         <v>1512</v>
       </c>
       <c r="F21" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -49899,13 +49899,13 @@
         <v>2653</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>2990</v>
+      </c>
+      <c r="F26" t="s">
         <v>2991</v>
       </c>
-      <c r="F26" t="s">
-        <v>2992</v>
-      </c>
       <c r="G26" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -49922,13 +49922,13 @@
         <v>421</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="F27" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="G27" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -49939,16 +49939,16 @@
         <v>1461</v>
       </c>
       <c r="D29" t="s">
+        <v>3269</v>
+      </c>
+      <c r="E29" t="s">
+        <v>3217</v>
+      </c>
+      <c r="F29" t="s">
+        <v>3005</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>3270</v>
-      </c>
-      <c r="E29" t="s">
-        <v>3218</v>
-      </c>
-      <c r="F29" t="s">
-        <v>3006</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>3271</v>
       </c>
       <c r="H29" t="s">
         <v>407</v>
@@ -49968,10 +49968,10 @@
         <v>2678</v>
       </c>
       <c r="E30" t="s">
+        <v>3004</v>
+      </c>
+      <c r="F30" t="s">
         <v>3005</v>
-      </c>
-      <c r="F30" t="s">
-        <v>3006</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -49985,10 +49985,10 @@
         <v>1557</v>
       </c>
       <c r="D31" t="s">
+        <v>3241</v>
+      </c>
+      <c r="E31" t="s">
         <v>3242</v>
-      </c>
-      <c r="E31" t="s">
-        <v>3243</v>
       </c>
       <c r="F31" t="s">
         <v>1313</v>
@@ -52032,12 +52032,12 @@
     </row>
     <row r="252" spans="1:6" s="420" customFormat="1" ht="21">
       <c r="C252" s="420" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
     </row>
     <row r="253" spans="1:6">
       <c r="A253" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="B253">
         <v>64476521</v>
@@ -52049,10 +52049,10 @@
         <v>2241</v>
       </c>
       <c r="E253" t="s">
+        <v>2962</v>
+      </c>
+      <c r="F253" t="s">
         <v>2963</v>
-      </c>
-      <c r="F253" t="s">
-        <v>2964</v>
       </c>
     </row>
     <row r="254" spans="1:6">
@@ -52069,10 +52069,10 @@
         <v>2920</v>
       </c>
       <c r="E254" t="s">
+        <v>2962</v>
+      </c>
+      <c r="F254" t="s">
         <v>2963</v>
-      </c>
-      <c r="F254" t="s">
-        <v>2964</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -52089,15 +52089,15 @@
         <v>2622</v>
       </c>
       <c r="E255" t="s">
+        <v>2962</v>
+      </c>
+      <c r="F255" t="s">
         <v>2963</v>
-      </c>
-      <c r="F255" t="s">
-        <v>2964</v>
       </c>
     </row>
     <row r="256" spans="1:6">
       <c r="A256" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="B256">
         <v>61915064</v>
@@ -56846,7 +56846,7 @@
         <v>2667</v>
       </c>
       <c r="E537" s="76" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="F537" s="76"/>
       <c r="G537" s="76"/>

--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dc549f2659ed9bd7/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63137" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6EEF9C8-AE95-4A94-8615-A4672F96FF46}"/>
+  <xr:revisionPtr revIDLastSave="63140" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0407914E-EF9D-4C4D-85AB-FE4C9DBC1A2E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,7 +65,6 @@
     <author>tc={DA8DAF0D-B0F6-41A4-BEF1-65B0D0110B01}</author>
     <author>tc={63325648-98C5-43A5-B0A0-BE3F1931179F}</author>
     <author>tc={D74A6BC7-C936-4D18-B207-7662524F2FF1}</author>
-    <author>tc={A3C653E5-B008-4D78-A9B3-C292CBCE6481}</author>
     <author>tc={263CFA38-6940-48E3-8C6D-4FD90BA5C72C}</author>
     <author>tc={2DA6ACCC-7F6B-4F63-9F66-2022723D557F}</author>
     <author>tc={2C80CEB1-D520-47E4-8891-F2B7A2059B85}</author>
@@ -139,15 +138,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/64242340-marisol</t>
       </text>
     </comment>
-    <comment ref="K67" authorId="6" shapeId="0" xr:uid="{A3C653E5-B008-4D78-A9B3-C292CBCE6481}">
-      <text>
-        <t>[Comentario encadenado]
-Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
-Comentario:
-    https://netflix-server-a9i0.onrender.com/cliente/180826-2044</t>
-      </text>
-    </comment>
-    <comment ref="I76" authorId="7" shapeId="0" xr:uid="{263CFA38-6940-48E3-8C6D-4FD90BA5C72C}">
+    <comment ref="I76" authorId="6" shapeId="0" xr:uid="{263CFA38-6940-48E3-8C6D-4FD90BA5C72C}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -155,7 +146,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/150826-2208</t>
       </text>
     </comment>
-    <comment ref="J79" authorId="8" shapeId="0" xr:uid="{2DA6ACCC-7F6B-4F63-9F66-2022723D557F}">
+    <comment ref="J79" authorId="7" shapeId="0" xr:uid="{2DA6ACCC-7F6B-4F63-9F66-2022723D557F}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -163,7 +154,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/68582631-melanie</t>
       </text>
     </comment>
-    <comment ref="J88" authorId="9" shapeId="0" xr:uid="{2C80CEB1-D520-47E4-8891-F2B7A2059B85}">
+    <comment ref="J88" authorId="8" shapeId="0" xr:uid="{2C80CEB1-D520-47E4-8891-F2B7A2059B85}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -171,7 +162,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/200826-2043</t>
       </text>
     </comment>
-    <comment ref="K88" authorId="10" shapeId="0" xr:uid="{A1BAE17A-7373-4E96-9A79-0A588580086C}">
+    <comment ref="K88" authorId="9" shapeId="0" xr:uid="{A1BAE17A-7373-4E96-9A79-0A588580086C}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -179,7 +170,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/69645877-yimara</t>
       </text>
     </comment>
-    <comment ref="H91" authorId="11" shapeId="0" xr:uid="{6CB69787-04DC-427D-92C4-EA68685283A6}">
+    <comment ref="H91" authorId="10" shapeId="0" xr:uid="{6CB69787-04DC-427D-92C4-EA68685283A6}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -187,7 +178,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/68131498-melanie</t>
       </text>
     </comment>
-    <comment ref="J97" authorId="12" shapeId="0" xr:uid="{D6ECFDFD-E9B9-4F9B-B2EF-5C67AA00056B}">
+    <comment ref="J97" authorId="11" shapeId="0" xr:uid="{D6ECFDFD-E9B9-4F9B-B2EF-5C67AA00056B}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -195,7 +186,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/68259581-kenneth</t>
       </text>
     </comment>
-    <comment ref="H103" authorId="13" shapeId="0" xr:uid="{5775AADF-97AE-4D86-A7DF-2817E0EA08FF}">
+    <comment ref="H103" authorId="12" shapeId="0" xr:uid="{5775AADF-97AE-4D86-A7DF-2817E0EA08FF}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -10812,9 +10803,6 @@
     <t>Hfd010926</t>
   </si>
   <si>
-    <t>QUINCENAL 62140561b 1 pantalla hasta el 16 de septiembre (Itziar)</t>
-  </si>
-  <si>
     <t>65034102  280826-0400d</t>
   </si>
   <si>
@@ -12301,6 +12289,9 @@
   </si>
   <si>
     <t>N005 1 pantalla hasta el 23 de octubre 220926-2359f</t>
+  </si>
+  <si>
+    <t>N005 1 pantalla hasta el 23 de octubre 230926-0010r</t>
   </si>
 </sst>
 </file>
@@ -30116,15 +30107,6 @@
       </x:ext>
     </extLst>
   </threadedComment>
-  <threadedComment ref="K67" dT="2026-08-19T01:48:39.97" personId="{0912E1D7-9EEC-46AD-AFB7-0C0A7E0E5337}" id="{A3C653E5-B008-4D78-A9B3-C292CBCE6481}">
-    <text>https://netflix-server-a9i0.onrender.com/cliente/180826-2044</text>
-    <extLst>
-      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>856872094</xltc2:checksum>
-        <xltc2:hyperlink startIndex="0" length="49" url="https://netflix-server-a9i0.onrender.com/cliente/"/>
-      </x:ext>
-    </extLst>
-  </threadedComment>
   <threadedComment ref="I76" dT="2026-08-16T04:09:02.31" personId="{0912E1D7-9EEC-46AD-AFB7-0C0A7E0E5337}" id="{263CFA38-6940-48E3-8C6D-4FD90BA5C72C}">
     <text>https://netflix-server-a9i0.onrender.com/cliente/150826-2208</text>
     <extLst>
@@ -30280,7 +30262,7 @@
         <v>2007</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>3556</v>
+        <v>3555</v>
       </c>
       <c r="F1" s="30" t="s">
         <v>2073</v>
@@ -30331,7 +30313,7 @@
         <v>2005</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>3630</v>
+        <v>3629</v>
       </c>
       <c r="F4" s="30" t="s">
         <v>2073</v>
@@ -30402,12 +30384,12 @@
         <v>2234</v>
       </c>
       <c r="D8" s="148" t="s">
-        <v>3481</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="148" customFormat="1">
       <c r="A9" s="148" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="B9" s="148" t="s">
         <v>1200</v>
@@ -30449,7 +30431,7 @@
     <row r="12" spans="1:11" s="369" customFormat="1"/>
     <row r="13" spans="1:11" s="30" customFormat="1">
       <c r="A13" s="30" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="B13" s="30">
         <v>69184177</v>
@@ -30458,7 +30440,7 @@
         <v>1771</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>3582</v>
+        <v>3581</v>
       </c>
       <c r="E13" s="30" t="s">
         <v>3057</v>
@@ -30473,7 +30455,7 @@
     </row>
     <row r="14" spans="1:11" s="148" customFormat="1">
       <c r="A14" s="225" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="B14" s="225" t="s">
         <v>1671</v>
@@ -30487,7 +30469,7 @@
     </row>
     <row r="15" spans="1:11" s="148" customFormat="1">
       <c r="A15" s="225" t="s">
-        <v>3366</v>
+        <v>3365</v>
       </c>
       <c r="B15" s="416">
         <v>62439069</v>
@@ -30501,7 +30483,7 @@
     </row>
     <row r="16" spans="1:11" s="32" customFormat="1">
       <c r="A16" s="30" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="B16" s="284" t="s">
         <v>2190</v>
@@ -30525,7 +30507,7 @@
         <v>2973</v>
       </c>
       <c r="I16" s="32" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="J16" s="32" t="s">
         <v>3135</v>
@@ -30536,7 +30518,7 @@
     </row>
     <row r="17" spans="1:11" s="164" customFormat="1">
       <c r="A17" s="252" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="B17" s="252" t="s">
         <v>1391</v>
@@ -30553,7 +30535,7 @@
     </row>
     <row r="18" spans="1:11" s="164" customFormat="1">
       <c r="A18" s="252" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
       <c r="B18" s="252">
         <v>64341760</v>
@@ -30579,7 +30561,7 @@
         <v>1488</v>
       </c>
       <c r="D19" s="145" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="E19" s="145" t="s">
         <v>2960</v>
@@ -30614,7 +30596,7 @@
     </row>
     <row r="21" spans="1:11" s="297" customFormat="1">
       <c r="A21" s="252" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="B21" s="252">
         <v>62169673</v>
@@ -30623,7 +30605,7 @@
         <v>1682</v>
       </c>
       <c r="D21" s="164" t="s">
-        <v>3427</v>
+        <v>3426</v>
       </c>
       <c r="E21" s="164" t="s">
         <v>1683</v>
@@ -30643,7 +30625,7 @@
         <v>2116</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>3556</v>
+        <v>3555</v>
       </c>
       <c r="F22" s="30" t="s">
         <v>2072</v>
@@ -30677,7 +30659,7 @@
         <v>2112</v>
       </c>
       <c r="D24" s="148" t="s">
-        <v>3429</v>
+        <v>3428</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="30" customFormat="1">
@@ -30742,7 +30724,7 @@
     </row>
     <row r="28" spans="1:11" s="30" customFormat="1">
       <c r="A28" s="30" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="B28" s="30">
         <v>60389752</v>
@@ -30754,7 +30736,7 @@
         <v>2002</v>
       </c>
       <c r="E28" s="30" t="s">
-        <v>3180</v>
+        <v>3179</v>
       </c>
       <c r="F28" s="303" t="s">
         <v>2146</v>
@@ -30779,7 +30761,7 @@
     </row>
     <row r="30" spans="1:11" s="164" customFormat="1">
       <c r="A30" s="164" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="B30" s="164">
         <v>62782770</v>
@@ -30793,10 +30775,10 @@
     </row>
     <row r="31" spans="1:11" s="30" customFormat="1">
       <c r="A31" s="461" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="B31" s="461" t="s">
-        <v>3670</v>
+        <v>3669</v>
       </c>
       <c r="C31" s="251" t="s">
         <v>1896</v>
@@ -30805,7 +30787,7 @@
         <v>2950</v>
       </c>
       <c r="E31" s="30" t="s">
-        <v>3581</v>
+        <v>3580</v>
       </c>
       <c r="F31" s="30" t="s">
         <v>2023</v>
@@ -30814,7 +30796,7 @@
         <v>198</v>
       </c>
       <c r="H31" s="145" t="s">
-        <v>3672</v>
+        <v>3671</v>
       </c>
       <c r="I31" s="192" t="s">
         <v>3053</v>
@@ -30823,7 +30805,7 @@
         <v>2965</v>
       </c>
       <c r="K31" s="30" t="s">
-        <v>3459</v>
+        <v>3458</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="163" customFormat="1">
@@ -30869,7 +30851,7 @@
         <v>2085</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="F34" s="30" t="s">
         <v>2076</v>
@@ -30889,7 +30871,7 @@
         <v>1979</v>
       </c>
       <c r="D35" s="148" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="E35" s="148" t="s">
         <v>1981</v>
@@ -30911,7 +30893,7 @@
     </row>
     <row r="37" spans="1:11" s="30" customFormat="1">
       <c r="A37" s="30" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
       <c r="B37" s="30" t="s">
         <v>2704</v>
@@ -30923,7 +30905,7 @@
         <v>3077</v>
       </c>
       <c r="E37" s="30" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="F37" s="30" t="s">
         <v>2066</v>
@@ -30932,16 +30914,16 @@
         <v>198</v>
       </c>
       <c r="H37" s="145" t="s">
-        <v>3564</v>
+        <v>3563</v>
       </c>
       <c r="I37" s="30" t="s">
         <v>3109</v>
       </c>
       <c r="J37" s="30" t="s">
-        <v>3428</v>
+        <v>3427</v>
       </c>
       <c r="K37" s="30" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="147" customFormat="1">
@@ -30984,10 +30966,10 @@
         <v>1658</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>3404</v>
+        <v>3403</v>
       </c>
       <c r="E40" s="30" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="F40" s="30" t="s">
         <v>2081</v>
@@ -30996,7 +30978,7 @@
         <v>198</v>
       </c>
       <c r="H40" s="30" t="s">
-        <v>3554</v>
+        <v>3553</v>
       </c>
       <c r="I40" s="32" t="s">
         <v>3043</v>
@@ -31005,12 +30987,12 @@
         <v>3073</v>
       </c>
       <c r="K40" s="145" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="163" customFormat="1">
       <c r="A41" s="163" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="B41" s="163">
         <v>68381893</v>
@@ -31054,7 +31036,7 @@
         <v>2027</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>3631</v>
+        <v>3630</v>
       </c>
       <c r="F43" s="30" t="s">
         <v>2113</v>
@@ -31065,7 +31047,7 @@
     </row>
     <row r="44" spans="1:11" s="164" customFormat="1">
       <c r="A44" s="164" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="B44" s="164">
         <v>68381893</v>
@@ -31082,7 +31064,7 @@
     </row>
     <row r="45" spans="1:11" s="163" customFormat="1">
       <c r="A45" s="163" t="s">
-        <v>3305</v>
+        <v>3304</v>
       </c>
       <c r="B45" s="163">
         <v>64079861</v>
@@ -31111,7 +31093,7 @@
         <v>2822</v>
       </c>
       <c r="E46" s="30" t="s">
-        <v>3267</v>
+        <v>3266</v>
       </c>
       <c r="F46" s="30" t="s">
         <v>2097</v>
@@ -31157,16 +31139,16 @@
         <v>1495</v>
       </c>
       <c r="B49" s="30" t="s">
-        <v>3313</v>
+        <v>3312</v>
       </c>
       <c r="C49" s="134" t="s">
         <v>1991</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>3196</v>
+        <v>3195</v>
       </c>
       <c r="E49" s="30" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="F49" s="30" t="s">
         <v>2084</v>
@@ -31181,10 +31163,10 @@
         <v>3096</v>
       </c>
       <c r="J49" s="30" t="s">
-        <v>3510</v>
+        <v>3509</v>
       </c>
       <c r="K49" s="32" t="s">
-        <v>3195</v>
+        <v>3194</v>
       </c>
     </row>
     <row r="50" spans="1:12" s="164" customFormat="1">
@@ -31229,7 +31211,7 @@
         <v>2834</v>
       </c>
       <c r="E52" s="139" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="F52" s="139" t="s">
         <v>2082</v>
@@ -31238,16 +31220,16 @@
         <v>198</v>
       </c>
       <c r="H52" s="140" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
       <c r="I52" s="140" t="s">
-        <v>3287</v>
+        <v>3286</v>
       </c>
       <c r="J52" s="30" t="s">
         <v>3167</v>
       </c>
       <c r="K52" s="269" t="s">
-        <v>3621</v>
+        <v>3620</v>
       </c>
     </row>
     <row r="53" spans="1:12" s="164" customFormat="1">
@@ -31288,7 +31270,7 @@
     </row>
     <row r="55" spans="1:12" s="30" customFormat="1">
       <c r="A55" s="30" t="s">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="B55" s="30">
         <v>61130088</v>
@@ -31353,7 +31335,7 @@
         <v>2768</v>
       </c>
       <c r="E58" s="30" t="s">
-        <v>3608</v>
+        <v>3607</v>
       </c>
       <c r="F58" s="30" t="s">
         <v>2110</v>
@@ -31362,7 +31344,7 @@
         <v>198</v>
       </c>
       <c r="H58" s="30" t="s">
-        <v>3213</v>
+        <v>3212</v>
       </c>
       <c r="I58" s="30" t="s">
         <v>3085</v>
@@ -31371,21 +31353,21 @@
         <v>3171</v>
       </c>
       <c r="K58" s="30" t="s">
-        <v>3478</v>
+        <v>3477</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" s="147" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="B59" s="147">
         <v>67539485</v>
       </c>
       <c r="C59" s="399" t="s">
-        <v>3606</v>
+        <v>3605</v>
       </c>
       <c r="D59" s="371" t="s">
-        <v>3609</v>
+        <v>3608</v>
       </c>
       <c r="E59" s="148"/>
       <c r="F59" s="147"/>
@@ -31398,16 +31380,16 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" s="147" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="B60" s="147">
         <v>68853797</v>
       </c>
       <c r="C60" s="399" t="s">
-        <v>3607</v>
+        <v>3606</v>
       </c>
       <c r="D60" s="371" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
       <c r="E60" s="147"/>
       <c r="F60" s="147"/>
@@ -31441,16 +31423,16 @@
         <v>198</v>
       </c>
       <c r="H61" s="30" t="s">
-        <v>3331</v>
+        <v>3330</v>
       </c>
       <c r="I61" s="30" t="s">
         <v>3103</v>
       </c>
       <c r="J61" s="30" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="K61" s="30" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
     </row>
     <row r="62" spans="1:12" s="147" customFormat="1">
@@ -31496,10 +31478,10 @@
         <v>1657</v>
       </c>
       <c r="D64" s="30" t="s">
-        <v>3207</v>
+        <v>3206</v>
       </c>
       <c r="E64" s="30" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="F64" s="30" t="s">
         <v>2083</v>
@@ -31508,13 +31490,13 @@
         <v>198</v>
       </c>
       <c r="H64" s="32" t="s">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="I64" s="32" t="s">
-        <v>3369</v>
+        <v>3368</v>
       </c>
       <c r="J64" s="30" t="s">
-        <v>3257</v>
+        <v>3256</v>
       </c>
       <c r="K64" s="30" t="s">
         <v>3086</v>
@@ -31556,7 +31538,7 @@
     </row>
     <row r="67" spans="1:11" s="30" customFormat="1">
       <c r="A67" s="253" t="s">
-        <v>3377</v>
+        <v>3376</v>
       </c>
       <c r="B67" s="284" t="s">
         <v>1904</v>
@@ -31568,7 +31550,7 @@
         <v>2929</v>
       </c>
       <c r="E67" s="30" t="s">
-        <v>3511</v>
+        <v>3510</v>
       </c>
       <c r="F67" s="30" t="s">
         <v>2087</v>
@@ -31577,16 +31559,16 @@
         <v>198</v>
       </c>
       <c r="H67" s="30" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
       <c r="I67" s="30" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
       <c r="J67" s="30" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="K67" s="145" t="s">
-        <v>3673</v>
+        <v>3672</v>
       </c>
     </row>
     <row r="68" spans="1:11" s="147" customFormat="1">
@@ -31615,7 +31597,7 @@
         <v>2086</v>
       </c>
       <c r="D69" s="148" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
     </row>
     <row r="70" spans="1:11" s="30" customFormat="1">
@@ -31623,7 +31605,7 @@
         <v>467</v>
       </c>
       <c r="B70" s="32" t="s">
-        <v>3301</v>
+        <v>3300</v>
       </c>
       <c r="C70" s="251" t="s">
         <v>1660</v>
@@ -31641,13 +31623,13 @@
         <v>198</v>
       </c>
       <c r="H70" s="32" t="s">
-        <v>3509</v>
+        <v>3508</v>
       </c>
       <c r="I70" s="145" t="s">
-        <v>3565</v>
+        <v>3564</v>
       </c>
       <c r="J70" s="30" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
     </row>
     <row r="71" spans="1:11" s="164" customFormat="1">
@@ -31666,7 +31648,7 @@
     </row>
     <row r="72" spans="1:11" s="163" customFormat="1">
       <c r="A72" s="268" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="B72" s="268" t="s">
         <v>1449</v>
@@ -31681,7 +31663,7 @@
     </row>
     <row r="73" spans="1:11" s="30" customFormat="1">
       <c r="A73" s="30" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="B73" s="30">
         <v>60389752</v>
@@ -31693,7 +31675,7 @@
         <v>2779</v>
       </c>
       <c r="E73" s="30" t="s">
-        <v>3306</v>
+        <v>3305</v>
       </c>
       <c r="F73" s="30" t="s">
         <v>2022</v>
@@ -31704,7 +31686,7 @@
     </row>
     <row r="74" spans="1:11" s="147" customFormat="1">
       <c r="A74" s="147" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="B74" s="147">
         <v>64226974</v>
@@ -31755,16 +31737,16 @@
         <v>198</v>
       </c>
       <c r="H76" s="30" t="s">
-        <v>3462</v>
+        <v>3461</v>
       </c>
       <c r="I76" s="30" t="s">
-        <v>3508</v>
+        <v>3507</v>
       </c>
       <c r="J76" s="30" t="s">
         <v>3116</v>
       </c>
-      <c r="K76" s="217" t="s">
-        <v>3177</v>
+      <c r="K76" s="145" t="s">
+        <v>3673</v>
       </c>
     </row>
     <row r="77" spans="1:11" s="152" customFormat="1">
@@ -31789,7 +31771,7 @@
         <v>2914</v>
       </c>
       <c r="E79" s="30" t="s">
-        <v>3556</v>
+        <v>3555</v>
       </c>
       <c r="F79" s="30" t="s">
         <v>2077</v>
@@ -31804,7 +31786,7 @@
         <v>3082</v>
       </c>
       <c r="J79" s="30" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="K79" s="30" t="s">
         <v>3118</v>
@@ -31844,10 +31826,10 @@
     </row>
     <row r="82" spans="1:11" s="30" customFormat="1">
       <c r="A82" s="145" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="B82" s="30" t="s">
-        <v>3560</v>
+        <v>3559</v>
       </c>
       <c r="C82" s="22" t="s">
         <v>1897</v>
@@ -31865,16 +31847,16 @@
         <v>198</v>
       </c>
       <c r="H82" s="30" t="s">
-        <v>3376</v>
+        <v>3375</v>
       </c>
       <c r="I82" s="217" t="s">
-        <v>3224</v>
+        <v>3223</v>
       </c>
       <c r="J82" s="30" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
       <c r="K82" s="30" t="s">
-        <v>3439</v>
+        <v>3438</v>
       </c>
     </row>
     <row r="83" spans="1:11" s="148" customFormat="1">
@@ -31888,7 +31870,7 @@
         <v>1954</v>
       </c>
       <c r="D83" s="148" t="s">
-        <v>3558</v>
+        <v>3557</v>
       </c>
     </row>
     <row r="84" spans="1:11" s="280" customFormat="1">
@@ -31916,7 +31898,7 @@
         <v>693</v>
       </c>
       <c r="D85" s="30" t="s">
-        <v>3225</v>
+        <v>3224</v>
       </c>
       <c r="E85" s="30" t="s">
         <v>1787</v>
@@ -31928,16 +31910,16 @@
         <v>493</v>
       </c>
       <c r="H85" s="30" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="I85" s="32" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
       <c r="J85" s="30" t="s">
-        <v>3358</v>
+        <v>3357</v>
       </c>
       <c r="K85" s="215" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
     </row>
     <row r="86" spans="1:11" s="147" customFormat="1">
@@ -31978,10 +31960,10 @@
     </row>
     <row r="88" spans="1:11" s="30" customFormat="1">
       <c r="A88" s="30" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
       <c r="B88" s="30" t="s">
-        <v>3580</v>
+        <v>3579</v>
       </c>
       <c r="C88" s="153" t="s">
         <v>694</v>
@@ -31999,16 +31981,16 @@
         <v>1521</v>
       </c>
       <c r="H88" s="30" t="s">
-        <v>3601</v>
+        <v>3600</v>
       </c>
       <c r="I88" s="145" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
       <c r="J88" s="431" t="s">
         <v>2951</v>
       </c>
       <c r="K88" s="30" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
     </row>
     <row r="89" spans="1:11" s="147" customFormat="1">
@@ -32049,7 +32031,7 @@
     </row>
     <row r="91" spans="1:11" s="106" customFormat="1">
       <c r="A91" s="249" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="B91" s="32" t="s">
         <v>1397</v>
@@ -32073,13 +32055,13 @@
         <v>3090</v>
       </c>
       <c r="I91" s="31" t="s">
-        <v>3584</v>
+        <v>3583</v>
       </c>
       <c r="J91" s="431" t="s">
         <v>2947</v>
       </c>
       <c r="K91" s="30" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="406" customFormat="1">
@@ -32110,7 +32092,7 @@
         <v>1714</v>
       </c>
       <c r="D93" s="148" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="94" spans="1:11" s="32" customFormat="1">
@@ -32127,7 +32109,7 @@
         <v>1359</v>
       </c>
       <c r="E94" s="32" t="s">
-        <v>3343</v>
+        <v>3342</v>
       </c>
       <c r="F94" s="32" t="s">
         <v>1360</v>
@@ -32139,7 +32121,7 @@
     </row>
     <row r="95" spans="1:11" s="148" customFormat="1">
       <c r="A95" s="148" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="B95" s="148" t="s">
         <v>2623</v>
@@ -32156,7 +32138,7 @@
     </row>
     <row r="96" spans="1:11" s="148" customFormat="1">
       <c r="A96" s="148" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="B96" s="148">
         <v>65633205</v>
@@ -32165,7 +32147,7 @@
         <v>1376</v>
       </c>
       <c r="D96" s="148" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="E96" s="148" t="s">
         <v>1375</v>
@@ -32173,7 +32155,7 @@
     </row>
     <row r="97" spans="1:13" s="30" customFormat="1">
       <c r="A97" s="460" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="B97" s="30" t="s">
         <v>2881</v>
@@ -32194,16 +32176,16 @@
         <v>198</v>
       </c>
       <c r="H97" s="32" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="I97" s="30" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="J97" s="30" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="K97" s="429" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
     </row>
     <row r="98" spans="1:13" s="388" customFormat="1">
@@ -32219,13 +32201,13 @@
         <v>3157</v>
       </c>
       <c r="B100" s="30" t="s">
-        <v>3551</v>
+        <v>3550</v>
       </c>
       <c r="C100" s="251" t="s">
         <v>2807</v>
       </c>
       <c r="D100" s="30" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="E100" s="30" t="s">
         <v>3014</v>
@@ -32237,16 +32219,16 @@
         <v>198</v>
       </c>
       <c r="H100" s="30" t="s">
-        <v>3378</v>
+        <v>3377</v>
       </c>
       <c r="I100" s="30" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="J100" s="30" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="K100" s="30" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
     </row>
     <row r="101" spans="1:13" s="388" customFormat="1">
@@ -32262,7 +32244,7 @@
         <v>3064</v>
       </c>
       <c r="B103" s="30" t="s">
-        <v>3178</v>
+        <v>3177</v>
       </c>
       <c r="C103" s="251" t="s">
         <v>2847</v>
@@ -32283,7 +32265,7 @@
         <v>3106</v>
       </c>
       <c r="I103" s="30" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="J103" s="30" t="s">
         <v>3166</v>
@@ -32504,7 +32486,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="B139">
         <v>64720128</v>
@@ -32610,13 +32592,13 @@
         <v>1495</v>
       </c>
       <c r="B154" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
       <c r="C154" t="s">
         <v>2216</v>
       </c>
       <c r="D154" s="373" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="E154" s="30" t="s">
         <v>3034</v>
@@ -32641,7 +32623,7 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="B156">
         <v>63145336</v>
@@ -32650,7 +32632,7 @@
         <v>2225</v>
       </c>
       <c r="D156" s="373" t="s">
-        <v>3561</v>
+        <v>3560</v>
       </c>
       <c r="E156" s="30" t="s">
         <v>3144</v>
@@ -32675,7 +32657,7 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="B158">
         <v>64982293</v>
@@ -32684,7 +32666,7 @@
         <v>2227</v>
       </c>
       <c r="D158" s="373" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="E158" s="30" t="s">
         <v>3144</v>
@@ -32701,7 +32683,7 @@
         <v>2488</v>
       </c>
       <c r="D159" s="373" t="s">
-        <v>3275</v>
+        <v>3274</v>
       </c>
       <c r="E159" s="30" t="s">
         <v>3144</v>
@@ -32709,7 +32691,7 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="B160">
         <v>65133588</v>
@@ -32760,16 +32742,16 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="B163">
         <v>67570116</v>
       </c>
       <c r="C163" t="s">
-        <v>3563</v>
+        <v>3562</v>
       </c>
       <c r="D163" s="373" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
       <c r="E163" s="30" t="s">
         <v>3144</v>
@@ -32789,12 +32771,12 @@
         <v>2471</v>
       </c>
       <c r="E164" s="30" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="B165">
         <v>66315726</v>
@@ -32806,7 +32788,7 @@
         <v>2263</v>
       </c>
       <c r="E165" s="30" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -32823,24 +32805,24 @@
         <v>2263</v>
       </c>
       <c r="E166" s="30" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="B167">
         <v>68818154</v>
       </c>
       <c r="C167" t="s">
-        <v>3276</v>
+        <v>3275</v>
       </c>
       <c r="D167" s="373" t="s">
         <v>2576</v>
       </c>
       <c r="E167" s="30" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -32857,7 +32839,7 @@
         <v>3131</v>
       </c>
       <c r="E168" s="30" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -32874,7 +32856,7 @@
         <v>2728</v>
       </c>
       <c r="E169" s="30" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -32891,7 +32873,7 @@
         <v>2468</v>
       </c>
       <c r="E170" s="30" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -32908,7 +32890,7 @@
         <v>2301</v>
       </c>
       <c r="E171" s="30" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -32919,10 +32901,10 @@
         <v>2313</v>
       </c>
       <c r="D172" s="373" t="s">
-        <v>3660</v>
+        <v>3659</v>
       </c>
       <c r="E172" s="30" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -32939,7 +32921,7 @@
         <v>3112</v>
       </c>
       <c r="E173" s="30" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -32956,12 +32938,12 @@
         <v>3140</v>
       </c>
       <c r="E174" s="30" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="B175">
         <v>67178677</v>
@@ -32970,7 +32952,7 @@
         <v>2730</v>
       </c>
       <c r="D175" s="373" t="s">
-        <v>3562</v>
+        <v>3561</v>
       </c>
       <c r="E175" s="30" t="s">
         <v>3050</v>
@@ -32978,7 +32960,7 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="B176">
         <v>66935922</v>
@@ -32987,7 +32969,7 @@
         <v>2731</v>
       </c>
       <c r="D176" s="220" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="E176" s="30" t="s">
         <v>3050</v>
@@ -33004,7 +32986,7 @@
         <v>3099</v>
       </c>
       <c r="D177" s="220" t="s">
-        <v>3456</v>
+        <v>3455</v>
       </c>
       <c r="E177" s="30" t="s">
         <v>3050</v>
@@ -33038,7 +33020,7 @@
         <v>2733</v>
       </c>
       <c r="D179" s="220" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="E179" s="30" t="s">
         <v>3050</v>
@@ -33055,7 +33037,7 @@
         <v>2755</v>
       </c>
       <c r="D180" s="373" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
       <c r="E180" s="30" t="s">
         <v>3102</v>
@@ -33123,7 +33105,7 @@
         <v>2819</v>
       </c>
       <c r="D184" s="373" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="E184" s="30" t="s">
         <v>3102</v>
@@ -33131,7 +33113,7 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="B185">
         <v>61248427</v>
@@ -33140,7 +33122,7 @@
         <v>2789</v>
       </c>
       <c r="D185" s="373" t="s">
-        <v>3583</v>
+        <v>3582</v>
       </c>
       <c r="E185" s="30" t="s">
         <v>3174</v>
@@ -33148,7 +33130,7 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" t="s">
-        <v>3373</v>
+        <v>3372</v>
       </c>
       <c r="B186">
         <v>60240509</v>
@@ -33157,10 +33139,10 @@
         <v>2790</v>
       </c>
       <c r="D186" s="373" t="s">
+        <v>3370</v>
+      </c>
+      <c r="E186" s="30" t="s">
         <v>3371</v>
-      </c>
-      <c r="E186" s="30" t="s">
-        <v>3372</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -33174,7 +33156,7 @@
         <v>2791</v>
       </c>
       <c r="D187" s="373" t="s">
-        <v>3308</v>
+        <v>3307</v>
       </c>
       <c r="E187" s="30" t="s">
         <v>3174</v>
@@ -33259,7 +33241,7 @@
         <v>2830</v>
       </c>
       <c r="D192" s="373" t="s">
-        <v>3611</v>
+        <v>3610</v>
       </c>
       <c r="E192" s="30" t="s">
         <v>3174</v>
@@ -33276,7 +33258,7 @@
         <v>2796</v>
       </c>
       <c r="D193" s="373" t="s">
-        <v>3530</v>
+        <v>3529</v>
       </c>
       <c r="E193" s="30" t="s">
         <v>3174</v>
@@ -33304,7 +33286,7 @@
         <v>3125</v>
       </c>
       <c r="D195" t="s">
-        <v>3296</v>
+        <v>3295</v>
       </c>
       <c r="E195" s="30" t="s">
         <v>3034</v>
@@ -33329,7 +33311,7 @@
         <v>2820</v>
       </c>
       <c r="D198" s="373" t="s">
-        <v>3307</v>
+        <v>3306</v>
       </c>
       <c r="E198" s="30" t="s">
         <v>3161</v>
@@ -33337,16 +33319,16 @@
     </row>
     <row r="199" spans="1:5">
       <c r="A199" t="s">
+        <v>3365</v>
+      </c>
+      <c r="B199" t="s">
         <v>3366</v>
-      </c>
-      <c r="B199" t="s">
-        <v>3367</v>
       </c>
       <c r="C199" t="s">
         <v>2813</v>
       </c>
       <c r="D199" s="373" t="s">
-        <v>3365</v>
+        <v>3364</v>
       </c>
       <c r="E199" s="30" t="s">
         <v>3161</v>
@@ -33360,7 +33342,7 @@
         <v>63617941</v>
       </c>
       <c r="C200" s="22" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="D200" s="373" t="s">
         <v>2869</v>
@@ -33380,7 +33362,7 @@
         <v>2814</v>
       </c>
       <c r="D201" s="373" t="s">
-        <v>3605</v>
+        <v>3604</v>
       </c>
       <c r="E201" s="30" t="s">
         <v>3161</v>
@@ -33397,7 +33379,7 @@
         <v>2815</v>
       </c>
       <c r="D202" s="373" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="E202" s="30" t="s">
         <v>3161</v>
@@ -33414,7 +33396,7 @@
         <v>2868</v>
       </c>
       <c r="D203" s="373" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="E203" s="30" t="s">
         <v>3161</v>
@@ -33425,13 +33407,13 @@
         <v>3060</v>
       </c>
       <c r="B204" t="s">
-        <v>3455</v>
+        <v>3454</v>
       </c>
       <c r="C204" t="s">
         <v>2816</v>
       </c>
       <c r="D204" s="373" t="s">
-        <v>3454</v>
+        <v>3453</v>
       </c>
       <c r="E204" s="30" t="s">
         <v>3161</v>
@@ -33445,10 +33427,10 @@
         <v>64982293</v>
       </c>
       <c r="C205" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="D205" s="373" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="E205" s="30" t="s">
         <v>3161</v>
@@ -33502,12 +33484,12 @@
         <v>2889</v>
       </c>
       <c r="E208" s="30" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="105" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="B209" t="s">
         <v>1161</v>
@@ -33516,15 +33498,15 @@
         <v>2901</v>
       </c>
       <c r="D209" s="373" t="s">
-        <v>3661</v>
+        <v>3660</v>
       </c>
       <c r="E209" s="30" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="B210">
         <v>65574051</v>
@@ -33533,15 +33515,15 @@
         <v>2888</v>
       </c>
       <c r="D210" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
       <c r="E210" s="30" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="97" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="B211" t="s">
         <v>1161</v>
@@ -33550,10 +33532,10 @@
         <v>2902</v>
       </c>
       <c r="D211" s="373" t="s">
-        <v>3662</v>
+        <v>3661</v>
       </c>
       <c r="E211" s="30" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -33570,7 +33552,7 @@
         <v>3065</v>
       </c>
       <c r="E212" s="30" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -33587,21 +33569,21 @@
         <v>2934</v>
       </c>
       <c r="E213" s="30" t="s">
-        <v>3512</v>
+        <v>3511</v>
       </c>
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="97" t="s">
-        <v>3585</v>
+        <v>3584</v>
       </c>
       <c r="C214" s="22" t="s">
         <v>2941</v>
       </c>
       <c r="D214" t="s">
-        <v>3671</v>
+        <v>3670</v>
       </c>
       <c r="E214" s="30" t="s">
-        <v>3512</v>
+        <v>3511</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -33609,16 +33591,16 @@
         <v>1434</v>
       </c>
       <c r="B215" t="s">
-        <v>3603</v>
+        <v>3602</v>
       </c>
       <c r="C215" s="22" t="s">
         <v>2942</v>
       </c>
       <c r="D215" t="s">
-        <v>3602</v>
+        <v>3601</v>
       </c>
       <c r="E215" s="30" t="s">
-        <v>3512</v>
+        <v>3511</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -33635,7 +33617,7 @@
         <v>2937</v>
       </c>
       <c r="E216" s="30" t="s">
-        <v>3512</v>
+        <v>3511</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -33652,7 +33634,7 @@
         <v>2944</v>
       </c>
       <c r="E217" s="30" t="s">
-        <v>3512</v>
+        <v>3511</v>
       </c>
     </row>
     <row r="231" spans="3:4">
@@ -36528,7 +36510,7 @@
         <v>678</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="G6" s="363" t="s">
         <v>1439</v>
@@ -36549,13 +36531,13 @@
         <v>1841</v>
       </c>
       <c r="D7" s="183" t="s">
-        <v>3625</v>
+        <v>3624</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F7" s="183" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="G7" s="183" t="s">
         <v>1439</v>
@@ -36582,7 +36564,7 @@
         <v>362</v>
       </c>
       <c r="F8" s="183" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="G8" s="183" t="s">
         <v>1439</v>
@@ -36609,7 +36591,7 @@
         <v>362</v>
       </c>
       <c r="F9" s="183" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="G9" s="183" t="s">
         <v>1439</v>
@@ -36636,7 +36618,7 @@
         <v>362</v>
       </c>
       <c r="F10" s="183" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="G10" s="183" t="s">
         <v>1439</v>
@@ -36663,7 +36645,7 @@
         <v>362</v>
       </c>
       <c r="F11" s="183" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="G11" s="183" t="s">
         <v>1439</v>
@@ -36687,7 +36669,7 @@
         <v>2496</v>
       </c>
       <c r="E13" s="195" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="F13" s="195" t="s">
         <v>1426</v>
@@ -36713,7 +36695,7 @@
         <v>1842</v>
       </c>
       <c r="E14" s="193" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="F14" s="193" t="s">
         <v>1426</v>
@@ -36739,7 +36721,7 @@
         <v>2763</v>
       </c>
       <c r="E15" s="193" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="F15" s="193" t="s">
         <v>1426</v>
@@ -36765,7 +36747,7 @@
         <v>2304</v>
       </c>
       <c r="E16" s="193" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="F16" s="193" t="s">
         <v>1426</v>
@@ -36779,7 +36761,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="193" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="B17" s="193">
         <v>64403333</v>
@@ -36791,7 +36773,7 @@
         <v>1504</v>
       </c>
       <c r="E17" s="193" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="F17" s="193" t="s">
         <v>1426</v>
@@ -36817,7 +36799,7 @@
         <v>2150</v>
       </c>
       <c r="E18" s="193" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="F18" s="193" t="s">
         <v>1426</v>
@@ -36846,7 +36828,7 @@
         <v>362</v>
       </c>
       <c r="F20" s="195" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="G20" s="76" t="s">
         <v>422</v>
@@ -36875,7 +36857,7 @@
         <v>362</v>
       </c>
       <c r="F21" s="193" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="G21" s="183" t="s">
         <v>422</v>
@@ -36904,7 +36886,7 @@
         <v>362</v>
       </c>
       <c r="F22" s="193" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="G22" s="183" t="s">
         <v>422</v>
@@ -36933,7 +36915,7 @@
         <v>362</v>
       </c>
       <c r="F23" s="193" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="G23" s="183" t="s">
         <v>422</v>
@@ -36962,7 +36944,7 @@
         <v>362</v>
       </c>
       <c r="F24" s="193" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="G24" s="183" t="s">
         <v>422</v>
@@ -36991,7 +36973,7 @@
         <v>362</v>
       </c>
       <c r="F25" s="193" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="G25" s="183" t="s">
         <v>422</v>
@@ -37020,7 +37002,7 @@
         <v>362</v>
       </c>
       <c r="F27" s="76" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
       <c r="G27" s="76" t="s">
         <v>1440</v>
@@ -37047,7 +37029,7 @@
         <v>362</v>
       </c>
       <c r="F28" s="183" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
       <c r="G28" s="183" t="s">
         <v>378</v>
@@ -37061,22 +37043,22 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="183" t="s">
-        <v>3393</v>
+        <v>3392</v>
       </c>
       <c r="B29" s="183">
         <v>65234700</v>
       </c>
       <c r="C29" s="194" t="s">
+        <v>3314</v>
+      </c>
+      <c r="D29" s="183" t="s">
         <v>3315</v>
-      </c>
-      <c r="D29" s="183" t="s">
-        <v>3316</v>
       </c>
       <c r="E29" s="432">
         <v>46243</v>
       </c>
       <c r="F29" s="183" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
       <c r="G29" s="183" t="s">
         <v>378</v>
@@ -37105,7 +37087,7 @@
         <v>362</v>
       </c>
       <c r="F30" s="183" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
       <c r="G30" s="183" t="s">
         <v>378</v>
@@ -37134,7 +37116,7 @@
         <v>362</v>
       </c>
       <c r="F31" s="183" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
       <c r="G31" s="183" t="s">
         <v>378</v>
@@ -37163,7 +37145,7 @@
         <v>362</v>
       </c>
       <c r="F32" s="183" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
       <c r="G32" s="183" t="s">
         <v>378</v>
@@ -37177,7 +37159,7 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="195" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="B34" s="195">
         <v>66466729</v>
@@ -37186,13 +37168,13 @@
         <v>1661</v>
       </c>
       <c r="D34" s="195" t="s">
-        <v>3473</v>
+        <v>3472</v>
       </c>
       <c r="E34" s="76" t="s">
         <v>2466</v>
       </c>
       <c r="F34" s="195" t="s">
-        <v>3370</v>
+        <v>3369</v>
       </c>
       <c r="G34" s="76" t="s">
         <v>1439</v>
@@ -37218,7 +37200,7 @@
         <v>2466</v>
       </c>
       <c r="F35" s="193" t="s">
-        <v>3370</v>
+        <v>3369</v>
       </c>
       <c r="G35" s="183" t="s">
         <v>1439</v>
@@ -37244,7 +37226,7 @@
         <v>2466</v>
       </c>
       <c r="F36" s="193" t="s">
-        <v>3370</v>
+        <v>3369</v>
       </c>
       <c r="G36" s="183" t="s">
         <v>1439</v>
@@ -37255,7 +37237,7 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="193" t="s">
-        <v>3346</v>
+        <v>3345</v>
       </c>
       <c r="B37" s="193">
         <v>69111188</v>
@@ -37270,7 +37252,7 @@
         <v>2466</v>
       </c>
       <c r="F37" s="193" t="s">
-        <v>3370</v>
+        <v>3369</v>
       </c>
       <c r="G37" s="183" t="s">
         <v>1439</v>
@@ -37296,7 +37278,7 @@
         <v>2466</v>
       </c>
       <c r="F38" s="193" t="s">
-        <v>3370</v>
+        <v>3369</v>
       </c>
       <c r="G38" s="183" t="s">
         <v>1439</v>
@@ -37322,7 +37304,7 @@
         <v>2466</v>
       </c>
       <c r="F39" s="193" t="s">
-        <v>3370</v>
+        <v>3369</v>
       </c>
       <c r="G39" s="183" t="s">
         <v>1439</v>
@@ -37335,16 +37317,16 @@
       <c r="A41" s="195"/>
       <c r="B41" s="195"/>
       <c r="C41" s="195" t="s">
+        <v>3360</v>
+      </c>
+      <c r="D41" s="195" t="s">
         <v>3361</v>
-      </c>
-      <c r="D41" s="195" t="s">
-        <v>3362</v>
       </c>
       <c r="E41" s="76" t="s">
         <v>362</v>
       </c>
       <c r="F41" s="195" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="G41" s="76" t="s">
         <v>2361</v>
@@ -37364,7 +37346,7 @@
         <v>69563253</v>
       </c>
       <c r="C42" s="193" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="D42" s="193" t="s">
         <v>1673</v>
@@ -37384,10 +37366,10 @@
         <v>1938</v>
       </c>
       <c r="C43" s="194" t="s">
+        <v>3340</v>
+      </c>
+      <c r="D43" s="193" t="s">
         <v>3341</v>
-      </c>
-      <c r="D43" s="193" t="s">
-        <v>3342</v>
       </c>
       <c r="E43" s="432">
         <v>46304</v>
@@ -37404,7 +37386,7 @@
         <v>62751201</v>
       </c>
       <c r="C44" s="194" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
       <c r="D44" s="183" t="s">
         <v>1354</v>
@@ -37424,10 +37406,10 @@
         <v>68030850</v>
       </c>
       <c r="C45" s="193" t="s">
+        <v>3343</v>
+      </c>
+      <c r="D45" s="193" t="s">
         <v>3344</v>
-      </c>
-      <c r="D45" s="193" t="s">
-        <v>3345</v>
       </c>
       <c r="E45" s="432">
         <v>46243</v>
@@ -37460,16 +37442,16 @@
       <c r="A48" s="195"/>
       <c r="B48" s="195"/>
       <c r="C48" s="195" t="s">
+        <v>3394</v>
+      </c>
+      <c r="D48" s="195" t="s">
         <v>3395</v>
       </c>
-      <c r="D48" s="195" t="s">
+      <c r="E48" s="76" t="s">
         <v>3396</v>
       </c>
-      <c r="E48" s="76" t="s">
+      <c r="F48" s="195" t="s">
         <v>3397</v>
-      </c>
-      <c r="F48" s="195" t="s">
-        <v>3398</v>
       </c>
       <c r="G48" s="76" t="s">
         <v>1439</v>
@@ -37506,10 +37488,10 @@
         <v>61548403</v>
       </c>
       <c r="C50" s="194" t="s">
+        <v>3398</v>
+      </c>
+      <c r="D50" s="193" t="s">
         <v>3399</v>
-      </c>
-      <c r="D50" s="193" t="s">
-        <v>3400</v>
       </c>
       <c r="E50" s="432">
         <v>46304</v>
@@ -37522,7 +37504,7 @@
       <c r="C51" s="449"/>
       <c r="D51" s="449"/>
       <c r="E51" s="432" t="s">
-        <v>3472</v>
+        <v>3471</v>
       </c>
       <c r="F51" s="193"/>
       <c r="G51" s="183"/>
@@ -37532,7 +37514,7 @@
       <c r="C52" s="452"/>
       <c r="D52" s="183"/>
       <c r="E52" s="432" t="s">
-        <v>3472</v>
+        <v>3471</v>
       </c>
       <c r="F52" s="193"/>
       <c r="G52" s="183"/>
@@ -37552,7 +37534,7 @@
         <v>2908</v>
       </c>
       <c r="E53" s="432" t="s">
-        <v>3472</v>
+        <v>3471</v>
       </c>
       <c r="F53" s="193"/>
       <c r="G53" s="183"/>
@@ -37565,13 +37547,13 @@
         <v>1660</v>
       </c>
       <c r="D55" s="195" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
       <c r="E55" s="76" t="s">
         <v>2466</v>
       </c>
       <c r="F55" s="195" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="G55" s="76" t="s">
         <v>1439</v>
@@ -37597,7 +37579,7 @@
         <v>2466</v>
       </c>
       <c r="F56" s="193" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="G56" s="183" t="s">
         <v>1439</v>
@@ -37623,7 +37605,7 @@
         <v>2466</v>
       </c>
       <c r="F57" s="193" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="G57" s="183" t="s">
         <v>1439</v>
@@ -37649,7 +37631,7 @@
         <v>2466</v>
       </c>
       <c r="F58" s="193" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="G58" s="183" t="s">
         <v>1439</v>
@@ -37675,7 +37657,7 @@
         <v>2466</v>
       </c>
       <c r="F59" s="193" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="G59" s="183" t="s">
         <v>1439</v>
@@ -37686,22 +37668,22 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="183" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="B60" s="183">
         <v>63247837</v>
       </c>
       <c r="C60" s="193" t="s">
-        <v>3230</v>
+        <v>3229</v>
       </c>
       <c r="D60" s="193" t="s">
-        <v>3627</v>
+        <v>3626</v>
       </c>
       <c r="E60" s="183" t="s">
         <v>2466</v>
       </c>
       <c r="F60" s="193" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="G60" s="183" t="s">
         <v>1439</v>
@@ -37727,7 +37709,7 @@
         <v>2466</v>
       </c>
       <c r="F62" s="195" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="G62" s="76" t="s">
         <v>1439</v>
@@ -37753,7 +37735,7 @@
         <v>2466</v>
       </c>
       <c r="F63" s="193" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="G63" s="183" t="s">
         <v>1439</v>
@@ -37764,7 +37746,7 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="183" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="B64" s="183">
         <v>64403333</v>
@@ -37779,7 +37761,7 @@
         <v>2466</v>
       </c>
       <c r="F64" s="193" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="G64" s="183" t="s">
         <v>1439</v>
@@ -37790,7 +37772,7 @@
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="193" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="B65" s="193">
         <v>68030850</v>
@@ -37805,7 +37787,7 @@
         <v>2466</v>
       </c>
       <c r="F65" s="193" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="G65" s="183" t="s">
         <v>1439</v>
@@ -37816,7 +37798,7 @@
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="183" t="s">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="B66" s="183">
         <v>65003516</v>
@@ -37831,7 +37813,7 @@
         <v>2466</v>
       </c>
       <c r="F66" s="193" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="G66" s="183" t="s">
         <v>1439</v>
@@ -37857,7 +37839,7 @@
         <v>2466</v>
       </c>
       <c r="F67" s="193" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="G67" s="183" t="s">
         <v>1439</v>
@@ -37880,7 +37862,7 @@
         <v>2429</v>
       </c>
       <c r="E69" s="76" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="F69" s="195" t="s">
         <v>2430</v>
@@ -37906,7 +37888,7 @@
         <v>2434</v>
       </c>
       <c r="E70" s="183" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="F70" s="193" t="s">
         <v>2430</v>
@@ -37932,7 +37914,7 @@
         <v>2278</v>
       </c>
       <c r="E71" s="183" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="F71" s="193" t="s">
         <v>2430</v>
@@ -37958,7 +37940,7 @@
         <v>2717</v>
       </c>
       <c r="E72" s="183" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="F72" s="183" t="s">
         <v>2430</v>
@@ -37985,7 +37967,7 @@
         <v>2049</v>
       </c>
       <c r="E73" s="183" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="F73" s="183" t="s">
         <v>2430</v>
@@ -38012,7 +37994,7 @@
         <v>2426</v>
       </c>
       <c r="E74" s="183" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="F74" s="183" t="s">
         <v>2430</v>
@@ -38039,7 +38021,7 @@
         <v>1720</v>
       </c>
       <c r="E76" s="76" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="F76" s="195" t="s">
         <v>2428</v>
@@ -38063,7 +38045,7 @@
         <v>2318</v>
       </c>
       <c r="E77" s="183" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="F77" s="193" t="s">
         <v>2428</v>
@@ -38087,7 +38069,7 @@
         <v>1235</v>
       </c>
       <c r="E78" s="183" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="F78" s="193" t="s">
         <v>2428</v>
@@ -38099,7 +38081,7 @@
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="183" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
       <c r="B79" s="183">
         <v>62820256</v>
@@ -38111,7 +38093,7 @@
         <v>2344</v>
       </c>
       <c r="E79" s="183" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="F79" s="193" t="s">
         <v>2428</v>
@@ -38129,13 +38111,13 @@
         <v>69563253</v>
       </c>
       <c r="C80" s="194" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="D80" s="183" t="s">
         <v>1003</v>
       </c>
       <c r="E80" s="183" t="s">
-        <v>3451</v>
+        <v>3450</v>
       </c>
       <c r="F80" s="193" t="s">
         <v>2428</v>
@@ -38147,7 +38129,7 @@
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="183" t="s">
-        <v>3477</v>
+        <v>3476</v>
       </c>
       <c r="B81" s="183">
         <v>63233935</v>
@@ -38156,10 +38138,10 @@
         <v>2363</v>
       </c>
       <c r="D81" s="183" t="s">
-        <v>3474</v>
+        <v>3473</v>
       </c>
       <c r="E81" s="183" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="F81" s="193" t="s">
         <v>2428</v>
@@ -38171,7 +38153,7 @@
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="76" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="B83" s="76">
         <v>63574980</v>
@@ -38186,7 +38168,7 @@
         <v>1341</v>
       </c>
       <c r="F83" s="195" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="G83" s="76" t="s">
         <v>1439</v>
@@ -38213,7 +38195,7 @@
         <v>1341</v>
       </c>
       <c r="F84" s="183" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="G84" s="183" t="s">
         <v>1439</v>
@@ -38240,7 +38222,7 @@
         <v>1341</v>
       </c>
       <c r="F85" s="183" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="G85" s="183" t="s">
         <v>1439</v>
@@ -38267,7 +38249,7 @@
         <v>1341</v>
       </c>
       <c r="F86" s="183" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="G86" s="183" t="s">
         <v>1439</v>
@@ -38288,13 +38270,13 @@
         <v>2645</v>
       </c>
       <c r="D87" s="183" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="E87" s="183" t="s">
         <v>1341</v>
       </c>
       <c r="F87" s="183" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="G87" s="183" t="s">
         <v>1439</v>
@@ -38321,7 +38303,7 @@
         <v>1341</v>
       </c>
       <c r="F88" s="183" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="G88" s="183" t="s">
         <v>1439</v>
@@ -38348,7 +38330,7 @@
         <v>1650</v>
       </c>
       <c r="F90" s="195" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="G90" s="76" t="s">
         <v>1439</v>
@@ -38372,7 +38354,7 @@
         <v>1650</v>
       </c>
       <c r="F91" s="193" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="G91" s="183" t="s">
         <v>1439</v>
@@ -38396,7 +38378,7 @@
         <v>1650</v>
       </c>
       <c r="F92" s="193" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="G92" s="183" t="s">
         <v>1439</v>
@@ -38405,7 +38387,7 @@
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="183" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="B93" s="183">
         <v>68259581</v>
@@ -38420,7 +38402,7 @@
         <v>1650</v>
       </c>
       <c r="F93" s="193" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="G93" s="183" t="s">
         <v>1439</v>
@@ -38444,7 +38426,7 @@
         <v>1650</v>
       </c>
       <c r="F94" s="193" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="G94" s="183" t="s">
         <v>1439</v>
@@ -38468,7 +38450,7 @@
         <v>1650</v>
       </c>
       <c r="F95" s="193" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="G95" s="183" t="s">
         <v>1439</v>
@@ -38477,7 +38459,7 @@
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="195" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="B97" s="195">
         <v>64476521</v>
@@ -38492,7 +38474,7 @@
         <v>2466</v>
       </c>
       <c r="F97" s="195" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="G97" s="76" t="s">
         <v>1439</v>
@@ -38503,7 +38485,7 @@
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="193" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="B98" s="193">
         <v>60389752</v>
@@ -38512,13 +38494,13 @@
         <v>2626</v>
       </c>
       <c r="D98" s="193" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
       <c r="E98" s="183" t="s">
         <v>2466</v>
       </c>
       <c r="F98" s="193" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="G98" s="183" t="s">
         <v>1439</v>
@@ -38529,7 +38511,7 @@
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="183" t="s">
-        <v>3494</v>
+        <v>3493</v>
       </c>
       <c r="B99" s="183">
         <v>60389752</v>
@@ -38544,7 +38526,7 @@
         <v>2466</v>
       </c>
       <c r="F99" s="193" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="G99" s="183" t="s">
         <v>1439</v>
@@ -38570,7 +38552,7 @@
         <v>2466</v>
       </c>
       <c r="F100" s="193" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="G100" s="183" t="s">
         <v>1439</v>
@@ -38596,7 +38578,7 @@
         <v>2466</v>
       </c>
       <c r="F101" s="193" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="G101" s="183" t="s">
         <v>1439</v>
@@ -38616,13 +38598,13 @@
         <v>2276</v>
       </c>
       <c r="D102" s="193" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="E102" s="183" t="s">
         <v>2466</v>
       </c>
       <c r="F102" s="193" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="G102" s="183" t="s">
         <v>1439</v>
@@ -38645,7 +38627,7 @@
         <v>2286</v>
       </c>
       <c r="E104" s="76" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="F104" s="195" t="s">
         <v>422</v>
@@ -38671,7 +38653,7 @@
         <v>2291</v>
       </c>
       <c r="E105" s="183" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="F105" s="193" t="s">
         <v>422</v>
@@ -38685,7 +38667,7 @@
     </row>
     <row r="106" spans="1:9">
       <c r="A106" s="193" t="s">
-        <v>3220</v>
+        <v>3219</v>
       </c>
       <c r="B106" s="193">
         <v>62723048</v>
@@ -38694,10 +38676,10 @@
         <v>2292</v>
       </c>
       <c r="D106" s="193" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
       <c r="E106" s="183" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="F106" s="193" t="s">
         <v>422</v>
@@ -38723,7 +38705,7 @@
         <v>2440</v>
       </c>
       <c r="E107" s="183" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="F107" s="193" t="s">
         <v>422</v>
@@ -38749,7 +38731,7 @@
         <v>2295</v>
       </c>
       <c r="E108" s="183" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="F108" s="193" t="s">
         <v>422</v>
@@ -38775,7 +38757,7 @@
         <v>2892</v>
       </c>
       <c r="E109" s="183" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="F109" s="193" t="s">
         <v>422</v>
@@ -38789,7 +38771,7 @@
     </row>
     <row r="111" spans="1:9">
       <c r="A111" s="195" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="B111" s="195">
         <v>68310153</v>
@@ -38804,7 +38786,7 @@
         <v>362</v>
       </c>
       <c r="F111" s="195" t="s">
-        <v>3578</v>
+        <v>3577</v>
       </c>
       <c r="G111" s="76" t="s">
         <v>1341</v>
@@ -38831,7 +38813,7 @@
         <v>362</v>
       </c>
       <c r="F112" s="193" t="s">
-        <v>3578</v>
+        <v>3577</v>
       </c>
       <c r="G112" s="183" t="s">
         <v>1341</v>
@@ -38860,7 +38842,7 @@
         <v>2466</v>
       </c>
       <c r="F113" s="193" t="s">
-        <v>3578</v>
+        <v>3577</v>
       </c>
       <c r="G113" s="183" t="s">
         <v>1341</v>
@@ -38880,16 +38862,16 @@
         <v>62360487</v>
       </c>
       <c r="C114" s="194" t="s">
+        <v>3230</v>
+      </c>
+      <c r="D114" s="183" t="s">
         <v>3231</v>
-      </c>
-      <c r="D114" s="183" t="s">
-        <v>3232</v>
       </c>
       <c r="E114" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F114" s="193" t="s">
-        <v>3578</v>
+        <v>3577</v>
       </c>
       <c r="G114" s="183" t="s">
         <v>1341</v>
@@ -38909,16 +38891,16 @@
         <v>62085821</v>
       </c>
       <c r="C115" s="193" t="s">
+        <v>3232</v>
+      </c>
+      <c r="D115" s="193" t="s">
         <v>3233</v>
-      </c>
-      <c r="D115" s="193" t="s">
-        <v>3234</v>
       </c>
       <c r="E115" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F115" s="193" t="s">
-        <v>3578</v>
+        <v>3577</v>
       </c>
       <c r="G115" s="183" t="s">
         <v>1341</v>
@@ -38938,16 +38920,16 @@
         <v>64403333</v>
       </c>
       <c r="C116" s="193" t="s">
+        <v>3234</v>
+      </c>
+      <c r="D116" s="193" t="s">
         <v>3235</v>
-      </c>
-      <c r="D116" s="193" t="s">
-        <v>3236</v>
       </c>
       <c r="E116" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F116" s="193" t="s">
-        <v>3578</v>
+        <v>3577</v>
       </c>
       <c r="G116" s="183" t="s">
         <v>1341</v>
@@ -39046,16 +39028,16 @@
     </row>
     <row r="121" spans="1:9">
       <c r="A121" s="183" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="B121" s="183">
         <v>64403333</v>
       </c>
       <c r="C121" s="183" t="s">
+        <v>3236</v>
+      </c>
+      <c r="D121" s="183" t="s">
         <v>3237</v>
-      </c>
-      <c r="D121" s="183" t="s">
-        <v>3238</v>
       </c>
       <c r="E121" s="183" t="s">
         <v>2994</v>
@@ -39072,7 +39054,7 @@
     </row>
     <row r="122" spans="1:9">
       <c r="A122" s="193" t="s">
-        <v>3585</v>
+        <v>3584</v>
       </c>
       <c r="B122" s="193" t="s">
         <v>2194</v>
@@ -39328,7 +39310,7 @@
         <v>64226974</v>
       </c>
       <c r="C133" s="183" t="s">
-        <v>3381</v>
+        <v>3380</v>
       </c>
       <c r="D133" s="193" t="s">
         <v>377</v>
@@ -39426,7 +39408,7 @@
     </row>
     <row r="137" spans="1:9">
       <c r="A137" s="193" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="B137" s="193">
         <v>63811445</v>
@@ -39484,10 +39466,10 @@
         <v>66319486</v>
       </c>
       <c r="C140" s="193" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="D140" s="193" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="E140" s="183" t="s">
         <v>2355</v>
@@ -39570,7 +39552,7 @@
     </row>
     <row r="144" spans="1:9">
       <c r="A144" s="193" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
       <c r="B144" s="193">
         <v>60389752</v>
@@ -39628,7 +39610,7 @@
         <v>67697112</v>
       </c>
       <c r="C147" s="193" t="s">
-        <v>3264</v>
+        <v>3263</v>
       </c>
       <c r="D147" s="193" t="s">
         <v>1303</v>
@@ -39648,7 +39630,7 @@
     </row>
     <row r="148" spans="1:9">
       <c r="A148" s="183" t="s">
-        <v>3305</v>
+        <v>3304</v>
       </c>
       <c r="B148" s="183">
         <v>62560788</v>
@@ -39767,7 +39749,7 @@
         <v>362</v>
       </c>
       <c r="F153" s="195" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="G153" s="76" t="s">
         <v>2361</v>
@@ -39781,22 +39763,22 @@
     </row>
     <row r="154" spans="1:9">
       <c r="A154" s="193" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="B154" s="193">
         <v>65963732</v>
       </c>
       <c r="C154" s="194" t="s">
+        <v>3221</v>
+      </c>
+      <c r="D154" s="193" t="s">
         <v>3222</v>
-      </c>
-      <c r="D154" s="193" t="s">
-        <v>3223</v>
       </c>
       <c r="E154" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F154" s="193" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="G154" s="183" t="s">
         <v>2361</v>
@@ -39810,7 +39792,7 @@
     </row>
     <row r="155" spans="1:9">
       <c r="A155" s="183" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="B155" s="183">
         <v>60071688</v>
@@ -39819,13 +39801,13 @@
         <v>2345</v>
       </c>
       <c r="D155" s="183" t="s">
-        <v>3216</v>
+        <v>3215</v>
       </c>
       <c r="E155" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F155" s="193" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="G155" s="183" t="s">
         <v>2361</v>
@@ -39854,7 +39836,7 @@
         <v>362</v>
       </c>
       <c r="F156" s="193" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="G156" s="183" t="s">
         <v>2361</v>
@@ -39883,7 +39865,7 @@
         <v>362</v>
       </c>
       <c r="F157" s="193" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="G157" s="183" t="s">
         <v>2361</v>
@@ -39912,7 +39894,7 @@
         <v>362</v>
       </c>
       <c r="F158" s="193" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="G158" s="183" t="s">
         <v>2361</v>
@@ -39943,7 +39925,7 @@
       <c r="A183" s="221"/>
       <c r="B183" s="221"/>
       <c r="C183" s="221" t="s">
-        <v>3311</v>
+        <v>3310</v>
       </c>
       <c r="D183" s="221"/>
       <c r="E183" s="221"/>
@@ -39957,19 +39939,19 @@
         <v>67836337</v>
       </c>
       <c r="C184" s="195" t="s">
+        <v>3422</v>
+      </c>
+      <c r="D184" s="195" t="s">
         <v>3423</v>
-      </c>
-      <c r="D184" s="195" t="s">
-        <v>3424</v>
       </c>
       <c r="E184" s="433">
         <v>46243</v>
       </c>
       <c r="F184" s="76" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="G184" s="195" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="H184" s="76" t="s">
         <v>1975</v>
@@ -39977,19 +39959,19 @@
     </row>
     <row r="185" spans="1:9">
       <c r="A185" s="193" t="s">
-        <v>3477</v>
+        <v>3476</v>
       </c>
       <c r="B185" s="193">
         <v>60196388</v>
       </c>
       <c r="C185" s="193" t="s">
-        <v>3476</v>
+        <v>3475</v>
       </c>
       <c r="D185" s="444" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
       <c r="E185" s="432" t="s">
-        <v>3472</v>
+        <v>3471</v>
       </c>
       <c r="F185" s="193"/>
       <c r="G185" s="183"/>
@@ -40003,13 +39985,13 @@
         <v>64403333</v>
       </c>
       <c r="C186" s="191" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="D186" s="183" t="s">
-        <v>3483</v>
+        <v>3482</v>
       </c>
       <c r="E186" s="432" t="s">
-        <v>3472</v>
+        <v>3471</v>
       </c>
       <c r="F186" s="193"/>
       <c r="G186" s="183"/>
@@ -40017,19 +39999,19 @@
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="193" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="B187" s="193">
         <v>68071614</v>
       </c>
       <c r="C187" s="193" t="s">
+        <v>3512</v>
+      </c>
+      <c r="D187" s="193" t="s">
         <v>3513</v>
       </c>
-      <c r="D187" s="193" t="s">
+      <c r="E187" s="432" t="s">
         <v>3514</v>
-      </c>
-      <c r="E187" s="432" t="s">
-        <v>3515</v>
       </c>
       <c r="F187" s="193"/>
       <c r="G187" s="183"/>
@@ -40043,13 +40025,13 @@
         <v>63950696</v>
       </c>
       <c r="C188" s="450" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D188" s="450" t="s">
         <v>2775</v>
       </c>
       <c r="E188" s="432" t="s">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="F188" s="451"/>
       <c r="G188" s="445"/>
@@ -40064,13 +40046,13 @@
         <v>65147336</v>
       </c>
       <c r="C189" s="183" t="s">
+        <v>3566</v>
+      </c>
+      <c r="D189" s="183" t="s">
         <v>3567</v>
       </c>
-      <c r="D189" s="183" t="s">
+      <c r="E189" s="432" t="s">
         <v>3568</v>
-      </c>
-      <c r="E189" s="432" t="s">
-        <v>3569</v>
       </c>
       <c r="F189" s="193"/>
       <c r="G189" s="183"/>
@@ -40111,7 +40093,7 @@
         <v>316</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="E194" s="30"/>
       <c r="F194"/>
@@ -40137,7 +40119,7 @@
         <v>439</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="E196" s="30"/>
       <c r="F196"/>
@@ -40148,7 +40130,7 @@
         <v>26</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>3513</v>
+        <v>3512</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -40156,7 +40138,7 @@
         <v>1324</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -40164,7 +40146,7 @@
         <v>1657</v>
       </c>
       <c r="D199" s="428" t="s">
-        <v>3567</v>
+        <v>3566</v>
       </c>
       <c r="F199" s="394"/>
     </row>
@@ -40173,7 +40155,7 @@
         <v>1305</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -40181,7 +40163,7 @@
         <v>406</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
     </row>
     <row r="202" spans="1:9">
@@ -40189,7 +40171,7 @@
         <v>708</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>3344</v>
+        <v>3343</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -40197,7 +40179,7 @@
         <v>281</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>3360</v>
+        <v>3359</v>
       </c>
     </row>
     <row r="204" spans="1:9">
@@ -40205,7 +40187,7 @@
         <v>2363</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>3361</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="205" spans="1:9">
@@ -40215,7 +40197,7 @@
         <v>465</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -40223,7 +40205,7 @@
         <v>219</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
     </row>
     <row r="207" spans="1:9">
@@ -40231,7 +40213,7 @@
         <v>427</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>3381</v>
+        <v>3380</v>
       </c>
     </row>
     <row r="208" spans="1:9">
@@ -40239,7 +40221,7 @@
         <v>1050</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>3395</v>
+        <v>3394</v>
       </c>
     </row>
     <row r="223" spans="1:9">
@@ -41475,10 +41457,10 @@
         <v>705</v>
       </c>
       <c r="H3" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>3617</v>
+        <v>3616</v>
       </c>
       <c r="J3"/>
     </row>
@@ -41505,10 +41487,10 @@
         <v>515</v>
       </c>
       <c r="H4" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="I4" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="J4"/>
     </row>
@@ -41535,7 +41517,7 @@
         <v>515</v>
       </c>
       <c r="H5" s="220" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="I5" s="220" t="s">
         <v>3095</v>
@@ -41546,19 +41528,19 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="B6" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>427</v>
       </c>
       <c r="D6" t="s">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>3259</v>
+        <v>3258</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>2853</v>
@@ -41570,7 +41552,7 @@
         <v>3045</v>
       </c>
       <c r="I6" t="s">
-        <v>3550</v>
+        <v>3549</v>
       </c>
       <c r="J6"/>
     </row>
@@ -41602,13 +41584,13 @@
         <v>1434</v>
       </c>
       <c r="B8" t="s">
-        <v>3619</v>
+        <v>3618</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>2060</v>
       </c>
       <c r="D8" t="s">
-        <v>3618</v>
+        <v>3617</v>
       </c>
       <c r="E8" t="s">
         <v>2320</v>
@@ -41623,7 +41605,7 @@
         <v>3088</v>
       </c>
       <c r="I8" t="s">
-        <v>3624</v>
+        <v>3623</v>
       </c>
       <c r="J8"/>
     </row>
@@ -41658,31 +41640,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="278" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>3652</v>
+        <v>3651</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>3647</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>3648</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="E10" s="10" t="s">
         <v>3649</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="F10" s="10" t="s">
         <v>3650</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>3651</v>
       </c>
       <c r="G10" t="s">
         <v>250</v>
       </c>
       <c r="H10" s="278" t="s">
+        <v>3652</v>
+      </c>
+      <c r="I10" s="278" t="s">
         <v>3653</v>
-      </c>
-      <c r="I10" s="278" t="s">
-        <v>3654</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -41833,7 +41815,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="10" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="B5" s="10">
         <v>67992849</v>
@@ -41854,10 +41836,10 @@
         <v>517</v>
       </c>
       <c r="H5" s="220" t="s">
-        <v>3437</v>
+        <v>3436</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>3629</v>
+        <v>3628</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -41891,7 +41873,7 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="10" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>2398</v>
@@ -41931,7 +41913,7 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="10" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="B11" s="10">
         <v>64403333</v>
@@ -41978,7 +41960,7 @@
         <v>3148</v>
       </c>
       <c r="I12" t="s">
-        <v>3295</v>
+        <v>3294</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -42044,7 +42026,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="10" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="B17" s="10">
         <v>64403333</v>
@@ -42067,7 +42049,7 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="10" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="B18" s="10">
         <v>60345107</v>
@@ -42076,7 +42058,7 @@
         <v>2327</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>3205</v>
+        <v>3204</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>959</v>
@@ -42091,7 +42073,7 @@
         <v>3173</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>3274</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -42105,7 +42087,7 @@
         <v>2378</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>3663</v>
+        <v>3662</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>959</v>
@@ -42117,10 +42099,10 @@
         <v>517</v>
       </c>
       <c r="H19" s="457" t="s">
-        <v>3664</v>
+        <v>3663</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>3385</v>
+        <v>3384</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="190" customFormat="1" ht="26">
@@ -42136,13 +42118,13 @@
         <v>2599</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>3350</v>
+        <v>3349</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>2403</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>959</v>
@@ -42154,7 +42136,7 @@
         <v>517</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>3438</v>
+        <v>3437</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>3132</v>
@@ -42162,7 +42144,7 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="B23" s="10">
         <v>64720128</v>
@@ -42183,10 +42165,10 @@
         <v>517</v>
       </c>
       <c r="H23" s="10" t="s">
+        <v>3417</v>
+      </c>
+      <c r="I23" s="10" t="s">
         <v>3418</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>3419</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -42212,10 +42194,10 @@
         <v>517</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -42428,7 +42410,7 @@
         <v>2283</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>3410</v>
+        <v>3409</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>2284</v>
@@ -42454,16 +42436,16 @@
         <v>2500</v>
       </c>
       <c r="B8" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>3485</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>3486</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="10" t="s">
         <v>3487</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>3488</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>1738</v>
@@ -42524,7 +42506,7 @@
         <v>3145</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>3066</v>
@@ -42536,30 +42518,30 @@
         <v>963</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="J10" t="s">
-        <v>3297</v>
+        <v>3296</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="457" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>3659</v>
+        <v>3658</v>
       </c>
       <c r="C11" s="10" t="s">
+        <v>3632</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>3635</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>3633</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>3636</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>3634</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>1738</v>
@@ -42579,7 +42561,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="C15" s="428" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
     </row>
   </sheetData>
@@ -42720,10 +42702,10 @@
         <v>60240509</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>3465</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>3466</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>3467</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>2597</v>
@@ -42779,16 +42761,16 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="10" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="B12" s="10">
         <v>66466729</v>
       </c>
       <c r="C12" s="10" t="s">
+        <v>3594</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>3595</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>3596</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
@@ -42868,7 +42850,7 @@
       <c r="A19" s="10"/>
       <c r="B19" s="10"/>
       <c r="C19" s="428" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
@@ -44412,10 +44394,10 @@
         <v>159</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>3324</v>
+        <v>3323</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="N6" s="4" t="s">
         <v>26</v>
@@ -44423,7 +44405,7 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="456" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="B7" s="4">
         <v>69888391</v>
@@ -44453,7 +44435,7 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
       <c r="B8" t="s">
         <v>452</v>
@@ -44489,19 +44471,19 @@
         <v>2153</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>3334</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>3335</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>3336</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>159</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>3257</v>
+        <v>3256</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>815</v>
@@ -44509,7 +44491,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="4" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="B10" s="4">
         <v>67916500</v>
@@ -44530,10 +44512,10 @@
         <v>244</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>3187</v>
+        <v>3186</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -44550,7 +44532,7 @@
         <v>1510</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>2896</v>
@@ -44559,10 +44541,10 @@
         <v>244</v>
       </c>
       <c r="H11" t="s">
-        <v>3532</v>
+        <v>3531</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -44588,10 +44570,10 @@
         <v>244</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>3535</v>
+        <v>3534</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -44599,7 +44581,7 @@
         <v>2921</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>3552</v>
+        <v>3551</v>
       </c>
       <c r="C13" s="22" t="s">
         <v>1218</v>
@@ -44617,10 +44599,10 @@
         <v>244</v>
       </c>
       <c r="H13" s="220" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>3620</v>
+        <v>3619</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="4" customFormat="1">
@@ -44646,10 +44628,10 @@
         <v>244</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="I14" s="220" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="L14" s="3"/>
     </row>
@@ -44667,10 +44649,10 @@
         <v>2841</v>
       </c>
       <c r="E15" s="4" t="s">
+        <v>3589</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>3590</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>3591</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>887</v>
@@ -44679,7 +44661,7 @@
         <v>3164</v>
       </c>
       <c r="I15" t="s">
-        <v>3616</v>
+        <v>3615</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>498</v>
@@ -44708,10 +44690,10 @@
         <v>159</v>
       </c>
       <c r="H16" t="s">
-        <v>3453</v>
+        <v>3452</v>
       </c>
       <c r="I16" t="s">
-        <v>3325</v>
+        <v>3324</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>805</v>
@@ -44719,7 +44701,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="B17">
         <v>65325884</v>
@@ -44742,7 +44724,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="4" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>2107</v>
@@ -44754,10 +44736,10 @@
         <v>2213</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>3336</v>
+        <v>3335</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>244</v>
@@ -44766,7 +44748,7 @@
         <v>3013</v>
       </c>
       <c r="I18" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="4" customFormat="1">
@@ -44783,10 +44765,10 @@
         <v>2582</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>3352</v>
+        <v>3351</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>3336</v>
+        <v>3335</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>1227</v>
@@ -44796,7 +44778,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="4" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="B20">
         <v>64403333</v>
@@ -44857,7 +44839,7 @@
         <v>2204</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>3632</v>
+        <v>3631</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>2462</v>
@@ -44868,7 +44850,7 @@
     </row>
     <row r="23" spans="1:12" s="4" customFormat="1">
       <c r="A23" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="B23">
         <v>63247837</v>
@@ -44877,7 +44859,7 @@
         <v>2590</v>
       </c>
       <c r="D23" t="s">
-        <v>3271</v>
+        <v>3270</v>
       </c>
       <c r="E23" t="s">
         <v>2593</v>
@@ -44889,16 +44871,16 @@
         <v>159</v>
       </c>
       <c r="H23" t="s">
-        <v>3211</v>
+        <v>3210</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>3291</v>
+        <v>3290</v>
       </c>
       <c r="L23" s="6"/>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
       <c r="B24">
         <v>69184177</v>
@@ -44921,16 +44903,16 @@
     </row>
     <row r="25" spans="1:12" s="4" customFormat="1">
       <c r="A25" s="4" t="s">
-        <v>3366</v>
+        <v>3365</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>3380</v>
+        <v>3379</v>
       </c>
       <c r="C25" s="21" t="s">
         <v>1326</v>
       </c>
       <c r="D25" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>2954</v>
@@ -44942,10 +44924,10 @@
         <v>244</v>
       </c>
       <c r="H25" s="105" t="s">
-        <v>3644</v>
+        <v>3643</v>
       </c>
       <c r="I25" s="220" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="4" customFormat="1">
@@ -44971,7 +44953,7 @@
         <v>159</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>3463</v>
+        <v>3462</v>
       </c>
       <c r="I27" t="s">
         <v>3168</v>
@@ -44982,7 +44964,7 @@
     </row>
     <row r="28" spans="1:12" s="4" customFormat="1">
       <c r="A28" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>2453</v>
@@ -45003,10 +44985,10 @@
         <v>325</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>3635</v>
+        <v>3634</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="K28"/>
     </row>
@@ -45024,7 +45006,7 @@
         <v>2865</v>
       </c>
       <c r="E29" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>2896</v>
@@ -45036,7 +45018,7 @@
         <v>2866</v>
       </c>
       <c r="I29" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
       <c r="J29" s="4"/>
       <c r="L29" s="135"/>
@@ -45055,7 +45037,7 @@
         <v>3007</v>
       </c>
       <c r="E30" t="s">
-        <v>3188</v>
+        <v>3187</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>1341</v>
@@ -45072,7 +45054,7 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="B31" s="4">
         <v>69409351</v>
@@ -45101,7 +45083,7 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="97" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>2843</v>
@@ -45110,7 +45092,7 @@
         <v>2367</v>
       </c>
       <c r="D32" t="s">
-        <v>3668</v>
+        <v>3667</v>
       </c>
       <c r="E32" t="s">
         <v>2371</v>
@@ -45122,10 +45104,10 @@
         <v>159</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
       <c r="I32" s="455" t="s">
-        <v>3669</v>
+        <v>3668</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -45133,13 +45115,13 @@
         <v>2596</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>2580</v>
       </c>
       <c r="D33" t="s">
-        <v>3479</v>
+        <v>3478</v>
       </c>
       <c r="E33" t="s">
         <v>2583</v>
@@ -45151,7 +45133,7 @@
         <v>2584</v>
       </c>
       <c r="H33" s="455" t="s">
-        <v>3645</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -45159,7 +45141,7 @@
         <v>1429</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
       <c r="C34" s="21" t="s">
         <v>2577</v>
@@ -45180,7 +45162,7 @@
         <v>3126</v>
       </c>
       <c r="I34" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="J34" s="4"/>
     </row>
@@ -45207,7 +45189,7 @@
         <v>2584</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>3639</v>
+        <v>3638</v>
       </c>
       <c r="I35" s="49" t="s">
         <v>2952</v>
@@ -45215,16 +45197,16 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="B36" t="s">
-        <v>3349</v>
+        <v>3348</v>
       </c>
       <c r="C36" s="22" t="s">
         <v>2579</v>
       </c>
       <c r="D36" t="s">
-        <v>3348</v>
+        <v>3347</v>
       </c>
       <c r="E36" t="s">
         <v>2583</v>
@@ -45236,7 +45218,7 @@
         <v>159</v>
       </c>
       <c r="H36" t="s">
-        <v>3351</v>
+        <v>3350</v>
       </c>
       <c r="I36" t="s">
         <v>3151</v>
@@ -45247,7 +45229,7 @@
         <v>158</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>2591</v>
@@ -45265,7 +45247,7 @@
         <v>159</v>
       </c>
       <c r="H37" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
       <c r="I37" t="s">
         <v>2919</v>
@@ -45294,10 +45276,10 @@
         <v>159</v>
       </c>
       <c r="H38" s="220" t="s">
-        <v>3529</v>
+        <v>3528</v>
       </c>
       <c r="I38" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="455" customFormat="1">
@@ -45310,10 +45292,10 @@
         <v>1351</v>
       </c>
       <c r="E41" s="97" t="s">
+        <v>3261</v>
+      </c>
+      <c r="F41" s="105" t="s">
         <v>3262</v>
-      </c>
-      <c r="F41" s="105" t="s">
-        <v>3263</v>
       </c>
       <c r="G41" s="105" t="s">
         <v>159</v>
@@ -45333,10 +45315,10 @@
         <v>2093</v>
       </c>
       <c r="E42" s="97" t="s">
+        <v>3261</v>
+      </c>
+      <c r="F42" s="105" t="s">
         <v>3262</v>
-      </c>
-      <c r="F42" s="105" t="s">
-        <v>3263</v>
       </c>
       <c r="G42" s="105" t="s">
         <v>159</v>
@@ -45356,10 +45338,10 @@
         <v>2324</v>
       </c>
       <c r="E43" s="105" t="s">
-        <v>3656</v>
+        <v>3655</v>
       </c>
       <c r="F43" s="105" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
       <c r="G43" s="97" t="s">
         <v>159</v>
@@ -45376,7 +45358,7 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="4" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="B45" t="s">
         <v>2495</v>
@@ -45406,7 +45388,7 @@
         <v>2799</v>
       </c>
       <c r="K45" t="s">
-        <v>3545</v>
+        <v>3544</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="4" customFormat="1">
@@ -45804,10 +45786,10 @@
         <v>3035</v>
       </c>
       <c r="J2" s="107" t="s">
-        <v>3521</v>
+        <v>3520</v>
       </c>
       <c r="K2" s="461" t="s">
-        <v>3667</v>
+        <v>3666</v>
       </c>
       <c r="M2" s="159"/>
     </row>
@@ -45834,25 +45816,25 @@
         <v>270</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="I4" s="30" t="s">
         <v>3172</v>
       </c>
       <c r="J4" s="139" t="s">
-        <v>3533</v>
+        <v>3532</v>
       </c>
       <c r="K4" s="139" t="s">
-        <v>3353</v>
+        <v>3352</v>
       </c>
       <c r="M4" s="39"/>
     </row>
     <row r="5" spans="1:13" s="30" customFormat="1">
       <c r="A5" s="30" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>3206</v>
+        <v>3205</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>1112</v>
@@ -45870,16 +45852,16 @@
         <v>65</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
       <c r="I5" s="306" t="s">
         <v>2931</v>
       </c>
       <c r="J5" s="30" t="s">
-        <v>3277</v>
+        <v>3276</v>
       </c>
       <c r="K5" s="30" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="M5" s="36"/>
     </row>
@@ -45894,7 +45876,7 @@
         <v>2744</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
       <c r="E6" s="140" t="s">
         <v>2707</v>
@@ -45906,7 +45888,7 @@
         <v>65</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
       <c r="I6" s="32" t="s">
         <v>3028</v>
@@ -45930,13 +45912,13 @@
         <v>1089</v>
       </c>
       <c r="D7" t="s">
-        <v>3285</v>
+        <v>3284</v>
       </c>
       <c r="E7" s="107" t="s">
+        <v>3264</v>
+      </c>
+      <c r="F7" s="30" t="s">
         <v>3265</v>
-      </c>
-      <c r="F7" s="30" t="s">
-        <v>3266</v>
       </c>
       <c r="G7" s="106" t="s">
         <v>720</v>
@@ -45945,13 +45927,13 @@
         <v>3165</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
       <c r="J7" s="30" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
       <c r="K7" s="30" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="M7" s="36"/>
     </row>
@@ -45966,7 +45948,7 @@
         <v>983</v>
       </c>
       <c r="D8" s="139" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="E8" s="107" t="s">
         <v>1154</v>
@@ -45978,16 +45960,16 @@
         <v>65</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
       <c r="I8" s="32" t="s">
         <v>2993</v>
       </c>
       <c r="J8" s="107" t="s">
-        <v>3598</v>
+        <v>3597</v>
       </c>
       <c r="K8" s="139" t="s">
-        <v>3330</v>
+        <v>3329</v>
       </c>
       <c r="M8" s="36"/>
     </row>
@@ -46014,16 +45996,16 @@
         <v>65</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>3616</v>
+        <v>3615</v>
       </c>
       <c r="I9" s="107" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="K9" s="107" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
       <c r="M9" s="36"/>
     </row>
@@ -46050,13 +46032,13 @@
         <v>65</v>
       </c>
       <c r="H10" s="107" t="s">
-        <v>3212</v>
+        <v>3211</v>
       </c>
       <c r="I10" t="s">
-        <v>3294</v>
+        <v>3293</v>
       </c>
       <c r="J10" s="219" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="K10" s="107" t="s">
         <v>2981</v>
@@ -46089,28 +46071,28 @@
         <v>3093</v>
       </c>
       <c r="I11" s="30" t="s">
-        <v>3504</v>
+        <v>3503</v>
       </c>
       <c r="J11" s="107" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="K11" s="107" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="M11" s="36"/>
     </row>
     <row r="12" spans="1:13" s="106" customFormat="1">
       <c r="A12" s="319" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="B12" s="106" t="s">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="C12" s="22" t="s">
         <v>72</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>3640</v>
+        <v>3639</v>
       </c>
       <c r="E12" s="106" t="s">
         <v>908</v>
@@ -46122,22 +46104,22 @@
         <v>245</v>
       </c>
       <c r="H12" s="30" t="s">
-        <v>3642</v>
+        <v>3641</v>
       </c>
       <c r="I12" s="106" t="s">
-        <v>3484</v>
+        <v>3483</v>
       </c>
       <c r="J12" s="106" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
       <c r="K12" s="107" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="M12" s="151"/>
     </row>
     <row r="13" spans="1:13" s="107" customFormat="1">
       <c r="A13" s="140" t="s">
-        <v>3366</v>
+        <v>3365</v>
       </c>
       <c r="B13" s="107" t="s">
         <v>2774</v>
@@ -46164,10 +46146,10 @@
         <v>3175</v>
       </c>
       <c r="J13" s="107" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
       <c r="K13" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="M13" s="36"/>
     </row>
@@ -46194,7 +46176,7 @@
         <v>65</v>
       </c>
       <c r="H14" s="107" t="s">
-        <v>3300</v>
+        <v>3299</v>
       </c>
       <c r="I14" s="411" t="s">
         <v>2262</v>
@@ -46227,13 +46209,13 @@
         <v>66</v>
       </c>
       <c r="H15" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="I15" t="s">
-        <v>3452</v>
+        <v>3451</v>
       </c>
       <c r="J15" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="K15" s="454" t="s">
         <v>2953</v>
@@ -46288,16 +46270,16 @@
         <v>66</v>
       </c>
       <c r="H17" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="I17" s="30" t="s">
         <v>3040</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>3559</v>
+        <v>3558</v>
       </c>
       <c r="K17" s="220" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="M17" s="34"/>
     </row>
@@ -46333,7 +46315,7 @@
         <v>3164</v>
       </c>
       <c r="K18" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="M18" s="36"/>
     </row>
@@ -46348,7 +46330,7 @@
         <v>1689</v>
       </c>
       <c r="D19" s="134" t="s">
-        <v>3375</v>
+        <v>3374</v>
       </c>
       <c r="E19" t="s">
         <v>1692</v>
@@ -46396,7 +46378,7 @@
         <v>65</v>
       </c>
       <c r="H20" s="436" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="I20" t="s">
         <v>2975</v>
@@ -46411,16 +46393,16 @@
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>3305</v>
+        <v>3304</v>
       </c>
       <c r="B21" t="s">
-        <v>3310</v>
+        <v>3309</v>
       </c>
       <c r="C21" s="22" t="s">
         <v>1127</v>
       </c>
       <c r="D21" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="E21" s="140" t="s">
         <v>1589</v>
@@ -46432,19 +46414,19 @@
         <v>65</v>
       </c>
       <c r="H21" t="s">
-        <v>3314</v>
+        <v>3313</v>
       </c>
       <c r="I21" t="s">
+        <v>3316</v>
+      </c>
+      <c r="J21" t="s">
         <v>3317</v>
-      </c>
-      <c r="J21" t="s">
-        <v>3318</v>
       </c>
       <c r="M21" s="36"/>
     </row>
     <row r="22" spans="1:13" s="30" customFormat="1">
       <c r="A22" s="30" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="B22" s="30" t="s">
         <v>2109</v>
@@ -46453,78 +46435,78 @@
         <v>2710</v>
       </c>
       <c r="D22" s="107" t="s">
-        <v>3359</v>
+        <v>3358</v>
       </c>
       <c r="E22" s="30" t="s">
+        <v>3331</v>
+      </c>
+      <c r="F22" s="30" t="s">
         <v>3332</v>
-      </c>
-      <c r="F22" s="30" t="s">
-        <v>3333</v>
       </c>
       <c r="G22" s="32" t="s">
         <v>65</v>
       </c>
       <c r="H22" s="30" t="s">
-        <v>3337</v>
+        <v>3336</v>
       </c>
       <c r="I22" s="30" t="s">
+        <v>3338</v>
+      </c>
+      <c r="J22" s="30" t="s">
         <v>3339</v>
-      </c>
-      <c r="J22" s="30" t="s">
-        <v>3340</v>
       </c>
       <c r="M22" s="36"/>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="B23" t="s">
-        <v>3354</v>
+        <v>3353</v>
       </c>
       <c r="C23" s="22" t="s">
         <v>1902</v>
       </c>
       <c r="D23" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="E23" s="30" t="s">
+        <v>3331</v>
+      </c>
+      <c r="F23" s="30" t="s">
         <v>3332</v>
-      </c>
-      <c r="F23" s="30" t="s">
-        <v>3333</v>
       </c>
       <c r="G23" t="s">
         <v>66</v>
       </c>
       <c r="H23" t="s">
-        <v>3444</v>
+        <v>3443</v>
       </c>
       <c r="I23" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="J23" t="s">
-        <v>3436</v>
+        <v>3435</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="30" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="B24" t="s">
-        <v>3666</v>
+        <v>3665</v>
       </c>
       <c r="C24" s="22" t="s">
         <v>1916</v>
       </c>
       <c r="D24" s="455" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="E24" s="107" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
       <c r="F24" s="30" t="s">
-        <v>3665</v>
+        <v>3664</v>
       </c>
       <c r="G24" s="32" t="s">
         <v>270</v>
@@ -46615,7 +46597,7 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="B33">
         <v>60389752</v>
@@ -46638,7 +46620,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="B34">
         <v>60389752</v>
@@ -46647,13 +46629,13 @@
         <v>2169</v>
       </c>
       <c r="D34" s="32" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
       <c r="E34" s="30" t="s">
+        <v>3331</v>
+      </c>
+      <c r="F34" s="30" t="s">
         <v>3332</v>
-      </c>
-      <c r="F34" s="30" t="s">
-        <v>3333</v>
       </c>
       <c r="G34" t="s">
         <v>3</v>
@@ -46662,7 +46644,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>3305</v>
+        <v>3304</v>
       </c>
       <c r="B35">
         <v>60389752</v>
@@ -46710,7 +46692,7 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="30" t="s">
-        <v>3305</v>
+        <v>3304</v>
       </c>
       <c r="B37" s="30">
         <v>64403333</v>
@@ -46735,7 +46717,7 @@
     </row>
     <row r="38" spans="1:13" s="30" customFormat="1">
       <c r="A38" s="30" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="B38" s="30">
         <v>60389752</v>
@@ -46772,10 +46754,10 @@
         <v>2142</v>
       </c>
       <c r="E39" t="s">
+        <v>3331</v>
+      </c>
+      <c r="F39" t="s">
         <v>3332</v>
-      </c>
-      <c r="F39" t="s">
-        <v>3333</v>
       </c>
       <c r="G39" t="s">
         <v>3</v>
@@ -46844,7 +46826,7 @@
         <v>2502</v>
       </c>
       <c r="E45" t="s">
-        <v>3221</v>
+        <v>3220</v>
       </c>
       <c r="F45" s="30" t="s">
         <v>2503</v>
@@ -46856,7 +46838,7 @@
         <v>3114</v>
       </c>
       <c r="I45" s="30" t="s">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="J45" s="49" t="s">
         <v>2928</v>
@@ -46914,7 +46896,7 @@
         <v>1106</v>
       </c>
       <c r="D65" s="97" t="s">
-        <v>3586</v>
+        <v>3585</v>
       </c>
       <c r="E65" s="107" t="s">
         <v>1123</v>
@@ -46932,10 +46914,10 @@
         <v>1122</v>
       </c>
       <c r="C66" s="97" t="s">
-        <v>3433</v>
+        <v>3432</v>
       </c>
       <c r="D66" s="97" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
       <c r="E66" s="97" t="s">
         <v>2404</v>
@@ -46955,24 +46937,24 @@
         <v>2164</v>
       </c>
       <c r="E67" s="107" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
       <c r="F67" s="30" t="s">
-        <v>3665</v>
+        <v>3664</v>
       </c>
     </row>
     <row r="68" spans="1:38">
       <c r="C68" s="459" t="s">
+        <v>3547</v>
+      </c>
+      <c r="D68" t="s">
         <v>3548</v>
       </c>
-      <c r="D68" t="s">
-        <v>3549</v>
-      </c>
       <c r="E68" s="107" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
       <c r="F68" s="30" t="s">
-        <v>3665</v>
+        <v>3664</v>
       </c>
       <c r="G68" s="106" t="s">
         <v>720</v>
@@ -46983,13 +46965,13 @@
         <v>1211</v>
       </c>
       <c r="D69" s="97" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="E69" s="107" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
       <c r="F69" s="30" t="s">
-        <v>3665</v>
+        <v>3664</v>
       </c>
       <c r="G69" s="106" t="s">
         <v>720</v>
@@ -47270,7 +47252,7 @@
         <v>1130</v>
       </c>
       <c r="D93" t="s">
-        <v>3328</v>
+        <v>3327</v>
       </c>
       <c r="E93" s="140" t="s">
         <v>1132</v>
@@ -47294,7 +47276,7 @@
         <v>1390</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>3329</v>
+        <v>3328</v>
       </c>
       <c r="E94" s="266" t="s">
         <v>1505</v>
@@ -47348,7 +47330,7 @@
         <v>358</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>3433</v>
+        <v>3432</v>
       </c>
     </row>
     <row r="105" spans="2:5">
@@ -47574,7 +47556,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
       <c r="C12" s="236"/>
     </row>
@@ -47788,27 +47770,27 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="87" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="C40" t="s">
-        <v>3390</v>
+        <v>3389</v>
       </c>
       <c r="F40" s="45"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="89" t="s">
-        <v>3388</v>
+        <v>3387</v>
       </c>
       <c r="C41" t="s">
-        <v>3391</v>
+        <v>3390</v>
       </c>
     </row>
     <row r="42" spans="2:6" ht="15" thickBot="1">
       <c r="B42" s="86" t="s">
-        <v>3389</v>
+        <v>3388</v>
       </c>
       <c r="C42" t="s">
-        <v>3392</v>
+        <v>3391</v>
       </c>
     </row>
     <row r="43" spans="2:6">
@@ -47971,22 +47953,22 @@
         <v>2033</v>
       </c>
       <c r="E6" s="247" t="s">
+        <v>3254</v>
+      </c>
+      <c r="F6" s="247" t="s">
         <v>3255</v>
-      </c>
-      <c r="F6" s="247" t="s">
-        <v>3256</v>
       </c>
       <c r="G6" s="247" t="s">
         <v>357</v>
       </c>
       <c r="H6" s="247" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
       <c r="I6" s="244" t="s">
-        <v>3505</v>
+        <v>3504</v>
       </c>
       <c r="J6" s="295" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="K6" s="247" t="s">
         <v>475</v>
@@ -48009,19 +47991,19 @@
         <v>1036</v>
       </c>
       <c r="F7" s="265" t="s">
-        <v>3258</v>
+        <v>3257</v>
       </c>
       <c r="G7" s="265" t="s">
         <v>690</v>
       </c>
       <c r="H7" s="295" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="I7" s="295" t="s">
         <v>2988</v>
       </c>
       <c r="J7" s="295" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="K7" s="265" t="s">
         <v>709</v>
@@ -48050,13 +48032,13 @@
         <v>250</v>
       </c>
       <c r="H8" s="265" t="s">
-        <v>3604</v>
+        <v>3603</v>
       </c>
       <c r="I8" s="265" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="J8" s="265" t="s">
-        <v>3468</v>
+        <v>3467</v>
       </c>
       <c r="K8" s="259"/>
       <c r="L8" s="259"/>
@@ -48078,7 +48060,7 @@
         <v>2695</v>
       </c>
       <c r="F9" s="263" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="G9" s="263" t="s">
         <v>946</v>
@@ -48110,13 +48092,13 @@
         <v>690</v>
       </c>
       <c r="H10" s="264" t="s">
-        <v>3647</v>
+        <v>3646</v>
       </c>
       <c r="I10" s="448" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="J10" s="264" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="K10" s="245" t="s">
         <v>1203</v>
@@ -48127,7 +48109,7 @@
         <v>2500</v>
       </c>
       <c r="B11" s="262" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="C11" s="194" t="s">
         <v>491</v>
@@ -48145,13 +48127,13 @@
         <v>690</v>
       </c>
       <c r="H11" s="215" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
       <c r="I11" s="424" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="J11" s="269" t="s">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="K11" s="183" t="s">
         <v>1204</v>
@@ -48185,10 +48167,10 @@
     </row>
     <row r="13" spans="1:12" s="223" customFormat="1">
       <c r="A13" s="223" t="s">
-        <v>3305</v>
+        <v>3304</v>
       </c>
       <c r="B13" s="223" t="s">
-        <v>3327</v>
+        <v>3326</v>
       </c>
       <c r="C13" s="423" t="s">
         <v>335</v>
@@ -48209,7 +48191,7 @@
         <v>3026</v>
       </c>
       <c r="I13" s="215" t="s">
-        <v>3226</v>
+        <v>3225</v>
       </c>
       <c r="J13" s="223" t="s">
         <v>3027</v>
@@ -48232,7 +48214,7 @@
         <v>1972</v>
       </c>
       <c r="E14" s="216" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="F14" s="216" t="s">
         <v>1433</v>
@@ -48241,7 +48223,7 @@
         <v>690</v>
       </c>
       <c r="H14" s="272" t="s">
-        <v>3458</v>
+        <v>3457</v>
       </c>
       <c r="I14" s="215" t="s">
         <v>2948</v>
@@ -48276,10 +48258,10 @@
         <v>690</v>
       </c>
       <c r="H15" s="264" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="I15" s="271" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
       <c r="J15" s="264" t="s">
         <v>3158</v>
@@ -48349,7 +48331,7 @@
         <v>831</v>
       </c>
       <c r="D18" s="264" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="E18" s="264" t="s">
         <v>1788</v>
@@ -48361,13 +48343,13 @@
         <v>690</v>
       </c>
       <c r="H18" s="259" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="I18" s="298" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="J18" s="259" t="s">
-        <v>3522</v>
+        <v>3521</v>
       </c>
       <c r="K18" s="264" t="s">
         <v>1765</v>
@@ -48375,7 +48357,7 @@
     </row>
     <row r="19" spans="1:11" s="259" customFormat="1">
       <c r="A19" s="259" t="s">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="B19" s="259" t="s">
         <v>2377</v>
@@ -48399,7 +48381,7 @@
         <v>3107</v>
       </c>
       <c r="I19" s="259" t="s">
-        <v>3432</v>
+        <v>3431</v>
       </c>
       <c r="J19" s="259" t="s">
         <v>3042</v>
@@ -48410,7 +48392,7 @@
     </row>
     <row r="20" spans="1:11" s="264" customFormat="1">
       <c r="A20" s="298" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="B20" s="304">
         <v>63609244</v>
@@ -48434,10 +48416,10 @@
         <v>2761</v>
       </c>
       <c r="I20" s="264" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="J20" s="264" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="K20" s="259" t="s">
         <v>1812</v>
@@ -48480,10 +48462,10 @@
         <v>637</v>
       </c>
       <c r="D22" s="255" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="E22" s="271" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="F22" s="271" t="s">
         <v>1710</v>
@@ -48492,10 +48474,10 @@
         <v>250</v>
       </c>
       <c r="H22" s="259" t="s">
-        <v>3482</v>
+        <v>3481</v>
       </c>
       <c r="I22" s="264" t="s">
-        <v>3227</v>
+        <v>3226</v>
       </c>
       <c r="J22" s="264" t="s">
         <v>3127</v>
@@ -48922,13 +48904,13 @@
         <v>2770</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="I2" t="s">
-        <v>3434</v>
+        <v>3433</v>
       </c>
       <c r="J2" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
       <c r="L2" s="36" t="s">
         <v>1173</v>
@@ -48954,7 +48936,7 @@
         <v>298</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>707</v>
@@ -48989,13 +48971,13 @@
         <v>323</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="H4" t="s">
         <v>3017</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="J4" t="s">
         <v>2918</v>
@@ -49039,7 +49021,7 @@
     </row>
     <row r="6" spans="1:12" s="4" customFormat="1">
       <c r="A6" s="4" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="B6" s="4">
         <v>65436260</v>
@@ -49057,13 +49039,13 @@
         <v>166</v>
       </c>
       <c r="G6" t="s">
-        <v>3240</v>
+        <v>3239</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>3573</v>
+        <v>3572</v>
       </c>
       <c r="I6" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
       <c r="J6" s="49" t="s">
         <v>2885</v>
@@ -49074,7 +49056,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="4" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
       <c r="B7" s="4">
         <v>69561522</v>
@@ -49092,10 +49074,10 @@
         <v>151</v>
       </c>
       <c r="G7" t="s">
-        <v>3523</v>
+        <v>3522</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>3046</v>
@@ -49109,7 +49091,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="4" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2936</v>
@@ -49130,7 +49112,7 @@
         <v>2636</v>
       </c>
       <c r="H8" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="I8" s="49" t="s">
         <v>2953</v>
@@ -49166,7 +49148,7 @@
         <v>3084</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>3531</v>
+        <v>3530</v>
       </c>
       <c r="J9" s="220" t="s">
         <v>3072</v>
@@ -49192,13 +49174,13 @@
         <v>1818</v>
       </c>
       <c r="G10" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
       <c r="H10" s="49" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
       <c r="I10" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="J10" s="49" t="s">
         <v>2831</v>
@@ -49249,7 +49231,7 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="B13">
         <v>64403333</v>
@@ -49272,16 +49254,16 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>3220</v>
+        <v>3219</v>
       </c>
       <c r="B14" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>281</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>3228</v>
+        <v>3227</v>
       </c>
       <c r="E14" t="s">
         <v>2136</v>
@@ -49290,16 +49272,16 @@
         <v>1818</v>
       </c>
       <c r="G14" t="s">
-        <v>3637</v>
+        <v>3636</v>
       </c>
       <c r="H14" t="s">
-        <v>3546</v>
+        <v>3545</v>
       </c>
       <c r="I14" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="J14" t="s">
-        <v>3326</v>
+        <v>3325</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -49628,7 +49610,7 @@
         <v>1550</v>
       </c>
       <c r="E9" t="s">
-        <v>3570</v>
+        <v>3569</v>
       </c>
       <c r="F9" t="s">
         <v>1732</v>
@@ -49648,7 +49630,7 @@
         <v>2211</v>
       </c>
       <c r="E10" t="s">
-        <v>3555</v>
+        <v>3554</v>
       </c>
       <c r="F10" t="s">
         <v>1681</v>
@@ -49685,7 +49667,7 @@
         <v>2676</v>
       </c>
       <c r="E12" t="s">
-        <v>3386</v>
+        <v>3385</v>
       </c>
       <c r="F12" t="s">
         <v>1681</v>
@@ -49693,7 +49675,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>3304</v>
+        <v>3303</v>
       </c>
       <c r="B13">
         <v>62271547</v>
@@ -49851,7 +49833,7 @@
         <v>1512</v>
       </c>
       <c r="F21" t="s">
-        <v>3298</v>
+        <v>3297</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -49939,16 +49921,16 @@
         <v>1461</v>
       </c>
       <c r="D29" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="E29" t="s">
-        <v>3217</v>
+        <v>3216</v>
       </c>
       <c r="F29" t="s">
         <v>3005</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>3270</v>
+        <v>3269</v>
       </c>
       <c r="H29" t="s">
         <v>407</v>
@@ -49985,10 +49967,10 @@
         <v>1557</v>
       </c>
       <c r="D31" t="s">
+        <v>3240</v>
+      </c>
+      <c r="E31" t="s">
         <v>3241</v>
-      </c>
-      <c r="E31" t="s">
-        <v>3242</v>
       </c>
       <c r="F31" t="s">
         <v>1313</v>

--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dc549f2659ed9bd7/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63140" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0407914E-EF9D-4C4D-85AB-FE4C9DBC1A2E}"/>
+  <xr:revisionPtr revIDLastSave="63143" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F4ABD4E-9984-4D27-89C3-60C2287D511C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10941,9 +10941,6 @@
     <t>Pasf030926</t>
   </si>
   <si>
-    <t>QUINCENAL 66552711 1 pantalla hasta el 18 de septiembre (Dinora)</t>
-  </si>
-  <si>
     <t>Yrs030926</t>
   </si>
   <si>
@@ -12292,6 +12289,9 @@
   </si>
   <si>
     <t>N005 1 pantalla hasta el 23 de octubre 230926-0010r</t>
+  </si>
+  <si>
+    <t>N006 1 pantalla hasta el 23 de octubre 230926-0015d</t>
   </si>
 </sst>
 </file>
@@ -30262,7 +30262,7 @@
         <v>2007</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>3555</v>
+        <v>3554</v>
       </c>
       <c r="F1" s="30" t="s">
         <v>2073</v>
@@ -30313,7 +30313,7 @@
         <v>2005</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>3629</v>
+        <v>3628</v>
       </c>
       <c r="F4" s="30" t="s">
         <v>2073</v>
@@ -30384,7 +30384,7 @@
         <v>2234</v>
       </c>
       <c r="D8" s="148" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="148" customFormat="1">
@@ -30431,7 +30431,7 @@
     <row r="12" spans="1:11" s="369" customFormat="1"/>
     <row r="13" spans="1:11" s="30" customFormat="1">
       <c r="A13" s="30" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="B13" s="30">
         <v>69184177</v>
@@ -30440,7 +30440,7 @@
         <v>1771</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>3581</v>
+        <v>3580</v>
       </c>
       <c r="E13" s="30" t="s">
         <v>3057</v>
@@ -30455,7 +30455,7 @@
     </row>
     <row r="14" spans="1:11" s="148" customFormat="1">
       <c r="A14" s="225" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="B14" s="225" t="s">
         <v>1671</v>
@@ -30469,7 +30469,7 @@
     </row>
     <row r="15" spans="1:11" s="148" customFormat="1">
       <c r="A15" s="225" t="s">
-        <v>3365</v>
+        <v>3364</v>
       </c>
       <c r="B15" s="416">
         <v>62439069</v>
@@ -30483,7 +30483,7 @@
     </row>
     <row r="16" spans="1:11" s="32" customFormat="1">
       <c r="A16" s="30" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="B16" s="284" t="s">
         <v>2190</v>
@@ -30518,7 +30518,7 @@
     </row>
     <row r="17" spans="1:11" s="164" customFormat="1">
       <c r="A17" s="252" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="B17" s="252" t="s">
         <v>1391</v>
@@ -30535,7 +30535,7 @@
     </row>
     <row r="18" spans="1:11" s="164" customFormat="1">
       <c r="A18" s="252" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="B18" s="252">
         <v>64341760</v>
@@ -30561,7 +30561,7 @@
         <v>1488</v>
       </c>
       <c r="D19" s="145" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
       <c r="E19" s="145" t="s">
         <v>2960</v>
@@ -30596,7 +30596,7 @@
     </row>
     <row r="21" spans="1:11" s="297" customFormat="1">
       <c r="A21" s="252" t="s">
-        <v>3434</v>
+        <v>3433</v>
       </c>
       <c r="B21" s="252">
         <v>62169673</v>
@@ -30605,7 +30605,7 @@
         <v>1682</v>
       </c>
       <c r="D21" s="164" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="E21" s="164" t="s">
         <v>1683</v>
@@ -30625,7 +30625,7 @@
         <v>2116</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>3555</v>
+        <v>3554</v>
       </c>
       <c r="F22" s="30" t="s">
         <v>2072</v>
@@ -30659,7 +30659,7 @@
         <v>2112</v>
       </c>
       <c r="D24" s="148" t="s">
-        <v>3428</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="30" customFormat="1">
@@ -30761,7 +30761,7 @@
     </row>
     <row r="30" spans="1:11" s="164" customFormat="1">
       <c r="A30" s="164" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="B30" s="164">
         <v>62782770</v>
@@ -30775,10 +30775,10 @@
     </row>
     <row r="31" spans="1:11" s="30" customFormat="1">
       <c r="A31" s="461" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="B31" s="461" t="s">
-        <v>3669</v>
+        <v>3668</v>
       </c>
       <c r="C31" s="251" t="s">
         <v>1896</v>
@@ -30787,7 +30787,7 @@
         <v>2950</v>
       </c>
       <c r="E31" s="30" t="s">
-        <v>3580</v>
+        <v>3579</v>
       </c>
       <c r="F31" s="30" t="s">
         <v>2023</v>
@@ -30796,7 +30796,7 @@
         <v>198</v>
       </c>
       <c r="H31" s="145" t="s">
-        <v>3671</v>
+        <v>3670</v>
       </c>
       <c r="I31" s="192" t="s">
         <v>3053</v>
@@ -30805,7 +30805,7 @@
         <v>2965</v>
       </c>
       <c r="K31" s="30" t="s">
-        <v>3458</v>
+        <v>3457</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="163" customFormat="1">
@@ -30851,7 +30851,7 @@
         <v>2085</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>3459</v>
+        <v>3458</v>
       </c>
       <c r="F34" s="30" t="s">
         <v>2076</v>
@@ -30871,7 +30871,7 @@
         <v>1979</v>
       </c>
       <c r="D35" s="148" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="E35" s="148" t="s">
         <v>1981</v>
@@ -30893,7 +30893,7 @@
     </row>
     <row r="37" spans="1:11" s="30" customFormat="1">
       <c r="A37" s="30" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="B37" s="30" t="s">
         <v>2704</v>
@@ -30905,7 +30905,7 @@
         <v>3077</v>
       </c>
       <c r="E37" s="30" t="s">
-        <v>3556</v>
+        <v>3555</v>
       </c>
       <c r="F37" s="30" t="s">
         <v>2066</v>
@@ -30914,16 +30914,16 @@
         <v>198</v>
       </c>
       <c r="H37" s="145" t="s">
-        <v>3563</v>
+        <v>3562</v>
       </c>
       <c r="I37" s="30" t="s">
         <v>3109</v>
       </c>
       <c r="J37" s="30" t="s">
-        <v>3427</v>
+        <v>3426</v>
       </c>
       <c r="K37" s="30" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="147" customFormat="1">
@@ -30966,10 +30966,10 @@
         <v>1658</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="E40" s="30" t="s">
-        <v>3459</v>
+        <v>3458</v>
       </c>
       <c r="F40" s="30" t="s">
         <v>2081</v>
@@ -30978,7 +30978,7 @@
         <v>198</v>
       </c>
       <c r="H40" s="30" t="s">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="I40" s="32" t="s">
         <v>3043</v>
@@ -30987,12 +30987,12 @@
         <v>3073</v>
       </c>
       <c r="K40" s="145" t="s">
-        <v>3404</v>
+        <v>3403</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="163" customFormat="1">
       <c r="A41" s="163" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="B41" s="163">
         <v>68381893</v>
@@ -31036,7 +31036,7 @@
         <v>2027</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>3630</v>
+        <v>3629</v>
       </c>
       <c r="F43" s="30" t="s">
         <v>2113</v>
@@ -31047,7 +31047,7 @@
     </row>
     <row r="44" spans="1:11" s="164" customFormat="1">
       <c r="A44" s="164" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="B44" s="164">
         <v>68381893</v>
@@ -31064,7 +31064,7 @@
     </row>
     <row r="45" spans="1:11" s="163" customFormat="1">
       <c r="A45" s="163" t="s">
-        <v>3304</v>
+        <v>3303</v>
       </c>
       <c r="B45" s="163">
         <v>64079861</v>
@@ -31093,7 +31093,7 @@
         <v>2822</v>
       </c>
       <c r="E46" s="30" t="s">
-        <v>3266</v>
+        <v>3265</v>
       </c>
       <c r="F46" s="30" t="s">
         <v>2097</v>
@@ -31139,7 +31139,7 @@
         <v>1495</v>
       </c>
       <c r="B49" s="30" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="C49" s="134" t="s">
         <v>1991</v>
@@ -31148,7 +31148,7 @@
         <v>3195</v>
       </c>
       <c r="E49" s="30" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="F49" s="30" t="s">
         <v>2084</v>
@@ -31163,7 +31163,7 @@
         <v>3096</v>
       </c>
       <c r="J49" s="30" t="s">
-        <v>3509</v>
+        <v>3508</v>
       </c>
       <c r="K49" s="32" t="s">
         <v>3194</v>
@@ -31211,7 +31211,7 @@
         <v>2834</v>
       </c>
       <c r="E52" s="139" t="s">
-        <v>3459</v>
+        <v>3458</v>
       </c>
       <c r="F52" s="139" t="s">
         <v>2082</v>
@@ -31220,16 +31220,16 @@
         <v>198</v>
       </c>
       <c r="H52" s="140" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
       <c r="I52" s="140" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
       <c r="J52" s="30" t="s">
         <v>3167</v>
       </c>
       <c r="K52" s="269" t="s">
-        <v>3620</v>
+        <v>3619</v>
       </c>
     </row>
     <row r="53" spans="1:12" s="164" customFormat="1">
@@ -31270,7 +31270,7 @@
     </row>
     <row r="55" spans="1:12" s="30" customFormat="1">
       <c r="A55" s="30" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="B55" s="30">
         <v>61130088</v>
@@ -31335,7 +31335,7 @@
         <v>2768</v>
       </c>
       <c r="E58" s="30" t="s">
-        <v>3607</v>
+        <v>3606</v>
       </c>
       <c r="F58" s="30" t="s">
         <v>2110</v>
@@ -31353,21 +31353,21 @@
         <v>3171</v>
       </c>
       <c r="K58" s="30" t="s">
-        <v>3477</v>
+        <v>3476</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" s="147" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="B59" s="147">
         <v>67539485</v>
       </c>
       <c r="C59" s="399" t="s">
-        <v>3605</v>
+        <v>3604</v>
       </c>
       <c r="D59" s="371" t="s">
-        <v>3608</v>
+        <v>3607</v>
       </c>
       <c r="E59" s="148"/>
       <c r="F59" s="147"/>
@@ -31380,16 +31380,16 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" s="147" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="B60" s="147">
         <v>68853797</v>
       </c>
       <c r="C60" s="399" t="s">
-        <v>3606</v>
+        <v>3605</v>
       </c>
       <c r="D60" s="371" t="s">
-        <v>3609</v>
+        <v>3608</v>
       </c>
       <c r="E60" s="147"/>
       <c r="F60" s="147"/>
@@ -31423,7 +31423,7 @@
         <v>198</v>
       </c>
       <c r="H61" s="30" t="s">
-        <v>3330</v>
+        <v>3329</v>
       </c>
       <c r="I61" s="30" t="s">
         <v>3103</v>
@@ -31432,7 +31432,7 @@
         <v>3201</v>
       </c>
       <c r="K61" s="30" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
     </row>
     <row r="62" spans="1:12" s="147" customFormat="1">
@@ -31481,7 +31481,7 @@
         <v>3206</v>
       </c>
       <c r="E64" s="30" t="s">
-        <v>3459</v>
+        <v>3458</v>
       </c>
       <c r="F64" s="30" t="s">
         <v>2083</v>
@@ -31490,13 +31490,13 @@
         <v>198</v>
       </c>
       <c r="H64" s="32" t="s">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="I64" s="32" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
       <c r="J64" s="30" t="s">
-        <v>3256</v>
+        <v>3255</v>
       </c>
       <c r="K64" s="30" t="s">
         <v>3086</v>
@@ -31538,7 +31538,7 @@
     </row>
     <row r="67" spans="1:11" s="30" customFormat="1">
       <c r="A67" s="253" t="s">
-        <v>3376</v>
+        <v>3375</v>
       </c>
       <c r="B67" s="284" t="s">
         <v>1904</v>
@@ -31550,7 +31550,7 @@
         <v>2929</v>
       </c>
       <c r="E67" s="30" t="s">
-        <v>3510</v>
+        <v>3509</v>
       </c>
       <c r="F67" s="30" t="s">
         <v>2087</v>
@@ -31559,16 +31559,16 @@
         <v>198</v>
       </c>
       <c r="H67" s="30" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
       <c r="I67" s="30" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
       <c r="J67" s="30" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="K67" s="145" t="s">
-        <v>3672</v>
+        <v>3671</v>
       </c>
     </row>
     <row r="68" spans="1:11" s="147" customFormat="1">
@@ -31597,7 +31597,7 @@
         <v>2086</v>
       </c>
       <c r="D69" s="148" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
     </row>
     <row r="70" spans="1:11" s="30" customFormat="1">
@@ -31605,7 +31605,7 @@
         <v>467</v>
       </c>
       <c r="B70" s="32" t="s">
-        <v>3300</v>
+        <v>3299</v>
       </c>
       <c r="C70" s="251" t="s">
         <v>1660</v>
@@ -31623,13 +31623,13 @@
         <v>198</v>
       </c>
       <c r="H70" s="32" t="s">
-        <v>3508</v>
+        <v>3507</v>
       </c>
       <c r="I70" s="145" t="s">
-        <v>3564</v>
+        <v>3563</v>
       </c>
       <c r="J70" s="30" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
     </row>
     <row r="71" spans="1:11" s="164" customFormat="1">
@@ -31648,7 +31648,7 @@
     </row>
     <row r="72" spans="1:11" s="163" customFormat="1">
       <c r="A72" s="268" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="B72" s="268" t="s">
         <v>1449</v>
@@ -31675,7 +31675,7 @@
         <v>2779</v>
       </c>
       <c r="E73" s="30" t="s">
-        <v>3305</v>
+        <v>3304</v>
       </c>
       <c r="F73" s="30" t="s">
         <v>2022</v>
@@ -31686,7 +31686,7 @@
     </row>
     <row r="74" spans="1:11" s="147" customFormat="1">
       <c r="A74" s="147" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="B74" s="147">
         <v>64226974</v>
@@ -31737,16 +31737,16 @@
         <v>198</v>
       </c>
       <c r="H76" s="30" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="I76" s="30" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="J76" s="30" t="s">
         <v>3116</v>
       </c>
       <c r="K76" s="145" t="s">
-        <v>3673</v>
+        <v>3672</v>
       </c>
     </row>
     <row r="77" spans="1:11" s="152" customFormat="1">
@@ -31771,7 +31771,7 @@
         <v>2914</v>
       </c>
       <c r="E79" s="30" t="s">
-        <v>3555</v>
+        <v>3554</v>
       </c>
       <c r="F79" s="30" t="s">
         <v>2077</v>
@@ -31786,7 +31786,7 @@
         <v>3082</v>
       </c>
       <c r="J79" s="30" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="K79" s="30" t="s">
         <v>3118</v>
@@ -31826,10 +31826,10 @@
     </row>
     <row r="82" spans="1:11" s="30" customFormat="1">
       <c r="A82" s="145" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="B82" s="30" t="s">
-        <v>3559</v>
+        <v>3558</v>
       </c>
       <c r="C82" s="22" t="s">
         <v>1897</v>
@@ -31847,16 +31847,16 @@
         <v>198</v>
       </c>
       <c r="H82" s="30" t="s">
-        <v>3375</v>
-      </c>
-      <c r="I82" s="217" t="s">
-        <v>3223</v>
+        <v>3374</v>
+      </c>
+      <c r="I82" s="145" t="s">
+        <v>3673</v>
       </c>
       <c r="J82" s="30" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="K82" s="30" t="s">
-        <v>3438</v>
+        <v>3437</v>
       </c>
     </row>
     <row r="83" spans="1:11" s="148" customFormat="1">
@@ -31870,7 +31870,7 @@
         <v>1954</v>
       </c>
       <c r="D83" s="148" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
     </row>
     <row r="84" spans="1:11" s="280" customFormat="1">
@@ -31898,7 +31898,7 @@
         <v>693</v>
       </c>
       <c r="D85" s="30" t="s">
-        <v>3224</v>
+        <v>3223</v>
       </c>
       <c r="E85" s="30" t="s">
         <v>1787</v>
@@ -31910,16 +31910,16 @@
         <v>493</v>
       </c>
       <c r="H85" s="30" t="s">
-        <v>3337</v>
+        <v>3336</v>
       </c>
       <c r="I85" s="32" t="s">
-        <v>3573</v>
+        <v>3572</v>
       </c>
       <c r="J85" s="30" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
       <c r="K85" s="215" t="s">
-        <v>3533</v>
+        <v>3532</v>
       </c>
     </row>
     <row r="86" spans="1:11" s="147" customFormat="1">
@@ -31960,10 +31960,10 @@
     </row>
     <row r="88" spans="1:11" s="30" customFormat="1">
       <c r="A88" s="30" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
       <c r="B88" s="30" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
       <c r="C88" s="153" t="s">
         <v>694</v>
@@ -31981,16 +31981,16 @@
         <v>1521</v>
       </c>
       <c r="H88" s="30" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
       <c r="I88" s="145" t="s">
-        <v>3565</v>
+        <v>3564</v>
       </c>
       <c r="J88" s="431" t="s">
         <v>2951</v>
       </c>
       <c r="K88" s="30" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
     </row>
     <row r="89" spans="1:11" s="147" customFormat="1">
@@ -32031,7 +32031,7 @@
     </row>
     <row r="91" spans="1:11" s="106" customFormat="1">
       <c r="A91" s="249" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="B91" s="32" t="s">
         <v>1397</v>
@@ -32055,7 +32055,7 @@
         <v>3090</v>
       </c>
       <c r="I91" s="31" t="s">
-        <v>3583</v>
+        <v>3582</v>
       </c>
       <c r="J91" s="431" t="s">
         <v>2947</v>
@@ -32109,7 +32109,7 @@
         <v>1359</v>
       </c>
       <c r="E94" s="32" t="s">
-        <v>3342</v>
+        <v>3341</v>
       </c>
       <c r="F94" s="32" t="s">
         <v>1360</v>
@@ -32121,7 +32121,7 @@
     </row>
     <row r="95" spans="1:11" s="148" customFormat="1">
       <c r="A95" s="148" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="B95" s="148" t="s">
         <v>2623</v>
@@ -32138,7 +32138,7 @@
     </row>
     <row r="96" spans="1:11" s="148" customFormat="1">
       <c r="A96" s="148" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="B96" s="148">
         <v>65633205</v>
@@ -32147,7 +32147,7 @@
         <v>1376</v>
       </c>
       <c r="D96" s="148" t="s">
-        <v>3429</v>
+        <v>3428</v>
       </c>
       <c r="E96" s="148" t="s">
         <v>1375</v>
@@ -32155,7 +32155,7 @@
     </row>
     <row r="97" spans="1:13" s="30" customFormat="1">
       <c r="A97" s="460" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="B97" s="30" t="s">
         <v>2881</v>
@@ -32176,16 +32176,16 @@
         <v>198</v>
       </c>
       <c r="H97" s="32" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="I97" s="30" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="J97" s="30" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="K97" s="429" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
     </row>
     <row r="98" spans="1:13" s="388" customFormat="1">
@@ -32201,13 +32201,13 @@
         <v>3157</v>
       </c>
       <c r="B100" s="30" t="s">
-        <v>3550</v>
+        <v>3549</v>
       </c>
       <c r="C100" s="251" t="s">
         <v>2807</v>
       </c>
       <c r="D100" s="30" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="E100" s="30" t="s">
         <v>3014</v>
@@ -32219,16 +32219,16 @@
         <v>198</v>
       </c>
       <c r="H100" s="30" t="s">
-        <v>3377</v>
+        <v>3376</v>
       </c>
       <c r="I100" s="30" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
       <c r="J100" s="30" t="s">
-        <v>3410</v>
+        <v>3409</v>
       </c>
       <c r="K100" s="30" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
     </row>
     <row r="101" spans="1:13" s="388" customFormat="1">
@@ -32486,7 +32486,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="B139">
         <v>64720128</v>
@@ -32592,13 +32592,13 @@
         <v>1495</v>
       </c>
       <c r="B154" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="C154" t="s">
         <v>2216</v>
       </c>
       <c r="D154" s="373" t="s">
-        <v>3271</v>
+        <v>3270</v>
       </c>
       <c r="E154" s="30" t="s">
         <v>3034</v>
@@ -32623,7 +32623,7 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="B156">
         <v>63145336</v>
@@ -32632,7 +32632,7 @@
         <v>2225</v>
       </c>
       <c r="D156" s="373" t="s">
-        <v>3560</v>
+        <v>3559</v>
       </c>
       <c r="E156" s="30" t="s">
         <v>3144</v>
@@ -32657,7 +32657,7 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="B158">
         <v>64982293</v>
@@ -32666,7 +32666,7 @@
         <v>2227</v>
       </c>
       <c r="D158" s="373" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="E158" s="30" t="s">
         <v>3144</v>
@@ -32683,7 +32683,7 @@
         <v>2488</v>
       </c>
       <c r="D159" s="373" t="s">
-        <v>3274</v>
+        <v>3273</v>
       </c>
       <c r="E159" s="30" t="s">
         <v>3144</v>
@@ -32742,16 +32742,16 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="B163">
         <v>67570116</v>
       </c>
       <c r="C163" t="s">
-        <v>3562</v>
+        <v>3561</v>
       </c>
       <c r="D163" s="373" t="s">
-        <v>3596</v>
+        <v>3595</v>
       </c>
       <c r="E163" s="30" t="s">
         <v>3144</v>
@@ -32771,12 +32771,12 @@
         <v>2471</v>
       </c>
       <c r="E164" s="30" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="B165">
         <v>66315726</v>
@@ -32788,7 +32788,7 @@
         <v>2263</v>
       </c>
       <c r="E165" s="30" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -32805,24 +32805,24 @@
         <v>2263</v>
       </c>
       <c r="E166" s="30" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="B167">
         <v>68818154</v>
       </c>
       <c r="C167" t="s">
-        <v>3275</v>
+        <v>3274</v>
       </c>
       <c r="D167" s="373" t="s">
         <v>2576</v>
       </c>
       <c r="E167" s="30" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -32839,7 +32839,7 @@
         <v>3131</v>
       </c>
       <c r="E168" s="30" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -32856,7 +32856,7 @@
         <v>2728</v>
       </c>
       <c r="E169" s="30" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -32873,7 +32873,7 @@
         <v>2468</v>
       </c>
       <c r="E170" s="30" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -32890,7 +32890,7 @@
         <v>2301</v>
       </c>
       <c r="E171" s="30" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -32901,10 +32901,10 @@
         <v>2313</v>
       </c>
       <c r="D172" s="373" t="s">
-        <v>3659</v>
+        <v>3658</v>
       </c>
       <c r="E172" s="30" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -32921,7 +32921,7 @@
         <v>3112</v>
       </c>
       <c r="E173" s="30" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -32938,12 +32938,12 @@
         <v>3140</v>
       </c>
       <c r="E174" s="30" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="B175">
         <v>67178677</v>
@@ -32952,7 +32952,7 @@
         <v>2730</v>
       </c>
       <c r="D175" s="373" t="s">
-        <v>3561</v>
+        <v>3560</v>
       </c>
       <c r="E175" s="30" t="s">
         <v>3050</v>
@@ -32986,7 +32986,7 @@
         <v>3099</v>
       </c>
       <c r="D177" s="220" t="s">
-        <v>3455</v>
+        <v>3454</v>
       </c>
       <c r="E177" s="30" t="s">
         <v>3050</v>
@@ -33105,7 +33105,7 @@
         <v>2819</v>
       </c>
       <c r="D184" s="373" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="E184" s="30" t="s">
         <v>3102</v>
@@ -33113,7 +33113,7 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="B185">
         <v>61248427</v>
@@ -33122,7 +33122,7 @@
         <v>2789</v>
       </c>
       <c r="D185" s="373" t="s">
-        <v>3582</v>
+        <v>3581</v>
       </c>
       <c r="E185" s="30" t="s">
         <v>3174</v>
@@ -33130,7 +33130,7 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" t="s">
-        <v>3372</v>
+        <v>3371</v>
       </c>
       <c r="B186">
         <v>60240509</v>
@@ -33139,10 +33139,10 @@
         <v>2790</v>
       </c>
       <c r="D186" s="373" t="s">
+        <v>3369</v>
+      </c>
+      <c r="E186" s="30" t="s">
         <v>3370</v>
-      </c>
-      <c r="E186" s="30" t="s">
-        <v>3371</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -33156,7 +33156,7 @@
         <v>2791</v>
       </c>
       <c r="D187" s="373" t="s">
-        <v>3307</v>
+        <v>3306</v>
       </c>
       <c r="E187" s="30" t="s">
         <v>3174</v>
@@ -33241,7 +33241,7 @@
         <v>2830</v>
       </c>
       <c r="D192" s="373" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
       <c r="E192" s="30" t="s">
         <v>3174</v>
@@ -33258,7 +33258,7 @@
         <v>2796</v>
       </c>
       <c r="D193" s="373" t="s">
-        <v>3529</v>
+        <v>3528</v>
       </c>
       <c r="E193" s="30" t="s">
         <v>3174</v>
@@ -33286,7 +33286,7 @@
         <v>3125</v>
       </c>
       <c r="D195" t="s">
-        <v>3295</v>
+        <v>3294</v>
       </c>
       <c r="E195" s="30" t="s">
         <v>3034</v>
@@ -33311,7 +33311,7 @@
         <v>2820</v>
       </c>
       <c r="D198" s="373" t="s">
-        <v>3306</v>
+        <v>3305</v>
       </c>
       <c r="E198" s="30" t="s">
         <v>3161</v>
@@ -33319,16 +33319,16 @@
     </row>
     <row r="199" spans="1:5">
       <c r="A199" t="s">
+        <v>3364</v>
+      </c>
+      <c r="B199" t="s">
         <v>3365</v>
-      </c>
-      <c r="B199" t="s">
-        <v>3366</v>
       </c>
       <c r="C199" t="s">
         <v>2813</v>
       </c>
       <c r="D199" s="373" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="E199" s="30" t="s">
         <v>3161</v>
@@ -33362,7 +33362,7 @@
         <v>2814</v>
       </c>
       <c r="D201" s="373" t="s">
-        <v>3604</v>
+        <v>3603</v>
       </c>
       <c r="E201" s="30" t="s">
         <v>3161</v>
@@ -33379,7 +33379,7 @@
         <v>2815</v>
       </c>
       <c r="D202" s="373" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="E202" s="30" t="s">
         <v>3161</v>
@@ -33396,7 +33396,7 @@
         <v>2868</v>
       </c>
       <c r="D203" s="373" t="s">
-        <v>3468</v>
+        <v>3467</v>
       </c>
       <c r="E203" s="30" t="s">
         <v>3161</v>
@@ -33407,13 +33407,13 @@
         <v>3060</v>
       </c>
       <c r="B204" t="s">
-        <v>3454</v>
+        <v>3453</v>
       </c>
       <c r="C204" t="s">
         <v>2816</v>
       </c>
       <c r="D204" s="373" t="s">
-        <v>3453</v>
+        <v>3452</v>
       </c>
       <c r="E204" s="30" t="s">
         <v>3161</v>
@@ -33427,10 +33427,10 @@
         <v>64982293</v>
       </c>
       <c r="C205" t="s">
-        <v>3444</v>
+        <v>3443</v>
       </c>
       <c r="D205" s="373" t="s">
-        <v>3523</v>
+        <v>3522</v>
       </c>
       <c r="E205" s="30" t="s">
         <v>3161</v>
@@ -33484,12 +33484,12 @@
         <v>2889</v>
       </c>
       <c r="E208" s="30" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="105" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="B209" t="s">
         <v>1161</v>
@@ -33498,15 +33498,15 @@
         <v>2901</v>
       </c>
       <c r="D209" s="373" t="s">
-        <v>3660</v>
+        <v>3659</v>
       </c>
       <c r="E209" s="30" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="B210">
         <v>65574051</v>
@@ -33515,15 +33515,15 @@
         <v>2888</v>
       </c>
       <c r="D210" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
       <c r="E210" s="30" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="97" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="B211" t="s">
         <v>1161</v>
@@ -33532,10 +33532,10 @@
         <v>2902</v>
       </c>
       <c r="D211" s="373" t="s">
-        <v>3661</v>
+        <v>3660</v>
       </c>
       <c r="E211" s="30" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -33552,7 +33552,7 @@
         <v>3065</v>
       </c>
       <c r="E212" s="30" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -33569,21 +33569,21 @@
         <v>2934</v>
       </c>
       <c r="E213" s="30" t="s">
-        <v>3511</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="97" t="s">
-        <v>3584</v>
+        <v>3583</v>
       </c>
       <c r="C214" s="22" t="s">
         <v>2941</v>
       </c>
       <c r="D214" t="s">
-        <v>3670</v>
+        <v>3669</v>
       </c>
       <c r="E214" s="30" t="s">
-        <v>3511</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -33591,16 +33591,16 @@
         <v>1434</v>
       </c>
       <c r="B215" t="s">
-        <v>3602</v>
+        <v>3601</v>
       </c>
       <c r="C215" s="22" t="s">
         <v>2942</v>
       </c>
       <c r="D215" t="s">
-        <v>3601</v>
+        <v>3600</v>
       </c>
       <c r="E215" s="30" t="s">
-        <v>3511</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -33617,7 +33617,7 @@
         <v>2937</v>
       </c>
       <c r="E216" s="30" t="s">
-        <v>3511</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -33634,7 +33634,7 @@
         <v>2944</v>
       </c>
       <c r="E217" s="30" t="s">
-        <v>3511</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="231" spans="3:4">
@@ -36531,7 +36531,7 @@
         <v>1841</v>
       </c>
       <c r="D7" s="183" t="s">
-        <v>3624</v>
+        <v>3623</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>362</v>
@@ -36761,7 +36761,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="193" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="B17" s="193">
         <v>64403333</v>
@@ -37002,7 +37002,7 @@
         <v>362</v>
       </c>
       <c r="F27" s="76" t="s">
-        <v>3291</v>
+        <v>3290</v>
       </c>
       <c r="G27" s="76" t="s">
         <v>1440</v>
@@ -37029,7 +37029,7 @@
         <v>362</v>
       </c>
       <c r="F28" s="183" t="s">
-        <v>3291</v>
+        <v>3290</v>
       </c>
       <c r="G28" s="183" t="s">
         <v>378</v>
@@ -37043,22 +37043,22 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="183" t="s">
-        <v>3392</v>
+        <v>3391</v>
       </c>
       <c r="B29" s="183">
         <v>65234700</v>
       </c>
       <c r="C29" s="194" t="s">
+        <v>3313</v>
+      </c>
+      <c r="D29" s="183" t="s">
         <v>3314</v>
-      </c>
-      <c r="D29" s="183" t="s">
-        <v>3315</v>
       </c>
       <c r="E29" s="432">
         <v>46243</v>
       </c>
       <c r="F29" s="183" t="s">
-        <v>3291</v>
+        <v>3290</v>
       </c>
       <c r="G29" s="183" t="s">
         <v>378</v>
@@ -37087,7 +37087,7 @@
         <v>362</v>
       </c>
       <c r="F30" s="183" t="s">
-        <v>3291</v>
+        <v>3290</v>
       </c>
       <c r="G30" s="183" t="s">
         <v>378</v>
@@ -37116,7 +37116,7 @@
         <v>362</v>
       </c>
       <c r="F31" s="183" t="s">
-        <v>3291</v>
+        <v>3290</v>
       </c>
       <c r="G31" s="183" t="s">
         <v>378</v>
@@ -37145,7 +37145,7 @@
         <v>362</v>
       </c>
       <c r="F32" s="183" t="s">
-        <v>3291</v>
+        <v>3290</v>
       </c>
       <c r="G32" s="183" t="s">
         <v>378</v>
@@ -37159,7 +37159,7 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="195" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="B34" s="195">
         <v>66466729</v>
@@ -37168,13 +37168,13 @@
         <v>1661</v>
       </c>
       <c r="D34" s="195" t="s">
-        <v>3472</v>
+        <v>3471</v>
       </c>
       <c r="E34" s="76" t="s">
         <v>2466</v>
       </c>
       <c r="F34" s="195" t="s">
-        <v>3369</v>
+        <v>3368</v>
       </c>
       <c r="G34" s="76" t="s">
         <v>1439</v>
@@ -37200,7 +37200,7 @@
         <v>2466</v>
       </c>
       <c r="F35" s="193" t="s">
-        <v>3369</v>
+        <v>3368</v>
       </c>
       <c r="G35" s="183" t="s">
         <v>1439</v>
@@ -37226,7 +37226,7 @@
         <v>2466</v>
       </c>
       <c r="F36" s="193" t="s">
-        <v>3369</v>
+        <v>3368</v>
       </c>
       <c r="G36" s="183" t="s">
         <v>1439</v>
@@ -37237,7 +37237,7 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="193" t="s">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="B37" s="193">
         <v>69111188</v>
@@ -37252,7 +37252,7 @@
         <v>2466</v>
       </c>
       <c r="F37" s="193" t="s">
-        <v>3369</v>
+        <v>3368</v>
       </c>
       <c r="G37" s="183" t="s">
         <v>1439</v>
@@ -37278,7 +37278,7 @@
         <v>2466</v>
       </c>
       <c r="F38" s="193" t="s">
-        <v>3369</v>
+        <v>3368</v>
       </c>
       <c r="G38" s="183" t="s">
         <v>1439</v>
@@ -37304,7 +37304,7 @@
         <v>2466</v>
       </c>
       <c r="F39" s="193" t="s">
-        <v>3369</v>
+        <v>3368</v>
       </c>
       <c r="G39" s="183" t="s">
         <v>1439</v>
@@ -37317,16 +37317,16 @@
       <c r="A41" s="195"/>
       <c r="B41" s="195"/>
       <c r="C41" s="195" t="s">
+        <v>3359</v>
+      </c>
+      <c r="D41" s="195" t="s">
         <v>3360</v>
-      </c>
-      <c r="D41" s="195" t="s">
-        <v>3361</v>
       </c>
       <c r="E41" s="76" t="s">
         <v>362</v>
       </c>
       <c r="F41" s="195" t="s">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="G41" s="76" t="s">
         <v>2361</v>
@@ -37346,7 +37346,7 @@
         <v>69563253</v>
       </c>
       <c r="C42" s="193" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="D42" s="193" t="s">
         <v>1673</v>
@@ -37366,10 +37366,10 @@
         <v>1938</v>
       </c>
       <c r="C43" s="194" t="s">
+        <v>3339</v>
+      </c>
+      <c r="D43" s="193" t="s">
         <v>3340</v>
-      </c>
-      <c r="D43" s="193" t="s">
-        <v>3341</v>
       </c>
       <c r="E43" s="432">
         <v>46304</v>
@@ -37386,7 +37386,7 @@
         <v>62751201</v>
       </c>
       <c r="C44" s="194" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="D44" s="183" t="s">
         <v>1354</v>
@@ -37406,10 +37406,10 @@
         <v>68030850</v>
       </c>
       <c r="C45" s="193" t="s">
+        <v>3342</v>
+      </c>
+      <c r="D45" s="193" t="s">
         <v>3343</v>
-      </c>
-      <c r="D45" s="193" t="s">
-        <v>3344</v>
       </c>
       <c r="E45" s="432">
         <v>46243</v>
@@ -37442,16 +37442,16 @@
       <c r="A48" s="195"/>
       <c r="B48" s="195"/>
       <c r="C48" s="195" t="s">
+        <v>3393</v>
+      </c>
+      <c r="D48" s="195" t="s">
         <v>3394</v>
       </c>
-      <c r="D48" s="195" t="s">
+      <c r="E48" s="76" t="s">
         <v>3395</v>
       </c>
-      <c r="E48" s="76" t="s">
+      <c r="F48" s="195" t="s">
         <v>3396</v>
-      </c>
-      <c r="F48" s="195" t="s">
-        <v>3397</v>
       </c>
       <c r="G48" s="76" t="s">
         <v>1439</v>
@@ -37488,10 +37488,10 @@
         <v>61548403</v>
       </c>
       <c r="C50" s="194" t="s">
+        <v>3397</v>
+      </c>
+      <c r="D50" s="193" t="s">
         <v>3398</v>
-      </c>
-      <c r="D50" s="193" t="s">
-        <v>3399</v>
       </c>
       <c r="E50" s="432">
         <v>46304</v>
@@ -37504,7 +37504,7 @@
       <c r="C51" s="449"/>
       <c r="D51" s="449"/>
       <c r="E51" s="432" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="F51" s="193"/>
       <c r="G51" s="183"/>
@@ -37514,7 +37514,7 @@
       <c r="C52" s="452"/>
       <c r="D52" s="183"/>
       <c r="E52" s="432" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="F52" s="193"/>
       <c r="G52" s="183"/>
@@ -37534,7 +37534,7 @@
         <v>2908</v>
       </c>
       <c r="E53" s="432" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="F53" s="193"/>
       <c r="G53" s="183"/>
@@ -37547,13 +37547,13 @@
         <v>1660</v>
       </c>
       <c r="D55" s="195" t="s">
-        <v>3625</v>
+        <v>3624</v>
       </c>
       <c r="E55" s="76" t="s">
         <v>2466</v>
       </c>
       <c r="F55" s="195" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="G55" s="76" t="s">
         <v>1439</v>
@@ -37579,7 +37579,7 @@
         <v>2466</v>
       </c>
       <c r="F56" s="193" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="G56" s="183" t="s">
         <v>1439</v>
@@ -37605,7 +37605,7 @@
         <v>2466</v>
       </c>
       <c r="F57" s="193" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="G57" s="183" t="s">
         <v>1439</v>
@@ -37631,7 +37631,7 @@
         <v>2466</v>
       </c>
       <c r="F58" s="193" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="G58" s="183" t="s">
         <v>1439</v>
@@ -37657,7 +37657,7 @@
         <v>2466</v>
       </c>
       <c r="F59" s="193" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="G59" s="183" t="s">
         <v>1439</v>
@@ -37668,22 +37668,22 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="183" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="B60" s="183">
         <v>63247837</v>
       </c>
       <c r="C60" s="193" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
       <c r="D60" s="193" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
       <c r="E60" s="183" t="s">
         <v>2466</v>
       </c>
       <c r="F60" s="193" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="G60" s="183" t="s">
         <v>1439</v>
@@ -37709,7 +37709,7 @@
         <v>2466</v>
       </c>
       <c r="F62" s="195" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="G62" s="76" t="s">
         <v>1439</v>
@@ -37735,7 +37735,7 @@
         <v>2466</v>
       </c>
       <c r="F63" s="193" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="G63" s="183" t="s">
         <v>1439</v>
@@ -37746,7 +37746,7 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="183" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="B64" s="183">
         <v>64403333</v>
@@ -37761,7 +37761,7 @@
         <v>2466</v>
       </c>
       <c r="F64" s="193" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="G64" s="183" t="s">
         <v>1439</v>
@@ -37787,7 +37787,7 @@
         <v>2466</v>
       </c>
       <c r="F65" s="193" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="G65" s="183" t="s">
         <v>1439</v>
@@ -37798,7 +37798,7 @@
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="183" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="B66" s="183">
         <v>65003516</v>
@@ -37813,7 +37813,7 @@
         <v>2466</v>
       </c>
       <c r="F66" s="193" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="G66" s="183" t="s">
         <v>1439</v>
@@ -37839,7 +37839,7 @@
         <v>2466</v>
       </c>
       <c r="F67" s="193" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="G67" s="183" t="s">
         <v>1439</v>
@@ -37862,7 +37862,7 @@
         <v>2429</v>
       </c>
       <c r="E69" s="76" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="F69" s="195" t="s">
         <v>2430</v>
@@ -37888,7 +37888,7 @@
         <v>2434</v>
       </c>
       <c r="E70" s="183" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="F70" s="193" t="s">
         <v>2430</v>
@@ -37914,7 +37914,7 @@
         <v>2278</v>
       </c>
       <c r="E71" s="183" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="F71" s="193" t="s">
         <v>2430</v>
@@ -37940,7 +37940,7 @@
         <v>2717</v>
       </c>
       <c r="E72" s="183" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="F72" s="183" t="s">
         <v>2430</v>
@@ -37967,7 +37967,7 @@
         <v>2049</v>
       </c>
       <c r="E73" s="183" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="F73" s="183" t="s">
         <v>2430</v>
@@ -37994,7 +37994,7 @@
         <v>2426</v>
       </c>
       <c r="E74" s="183" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="F74" s="183" t="s">
         <v>2430</v>
@@ -38021,7 +38021,7 @@
         <v>1720</v>
       </c>
       <c r="E76" s="76" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="F76" s="195" t="s">
         <v>2428</v>
@@ -38045,7 +38045,7 @@
         <v>2318</v>
       </c>
       <c r="E77" s="183" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="F77" s="193" t="s">
         <v>2428</v>
@@ -38069,7 +38069,7 @@
         <v>1235</v>
       </c>
       <c r="E78" s="183" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="F78" s="193" t="s">
         <v>2428</v>
@@ -38081,7 +38081,7 @@
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="183" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="B79" s="183">
         <v>62820256</v>
@@ -38093,7 +38093,7 @@
         <v>2344</v>
       </c>
       <c r="E79" s="183" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="F79" s="193" t="s">
         <v>2428</v>
@@ -38111,13 +38111,13 @@
         <v>69563253</v>
       </c>
       <c r="C80" s="194" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="D80" s="183" t="s">
         <v>1003</v>
       </c>
       <c r="E80" s="183" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="F80" s="193" t="s">
         <v>2428</v>
@@ -38129,7 +38129,7 @@
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="183" t="s">
-        <v>3476</v>
+        <v>3475</v>
       </c>
       <c r="B81" s="183">
         <v>63233935</v>
@@ -38138,10 +38138,10 @@
         <v>2363</v>
       </c>
       <c r="D81" s="183" t="s">
-        <v>3473</v>
+        <v>3472</v>
       </c>
       <c r="E81" s="183" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="F81" s="193" t="s">
         <v>2428</v>
@@ -38168,7 +38168,7 @@
         <v>1341</v>
       </c>
       <c r="F83" s="195" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
       <c r="G83" s="76" t="s">
         <v>1439</v>
@@ -38195,7 +38195,7 @@
         <v>1341</v>
       </c>
       <c r="F84" s="183" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
       <c r="G84" s="183" t="s">
         <v>1439</v>
@@ -38222,7 +38222,7 @@
         <v>1341</v>
       </c>
       <c r="F85" s="183" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
       <c r="G85" s="183" t="s">
         <v>1439</v>
@@ -38249,7 +38249,7 @@
         <v>1341</v>
       </c>
       <c r="F86" s="183" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
       <c r="G86" s="183" t="s">
         <v>1439</v>
@@ -38276,7 +38276,7 @@
         <v>1341</v>
       </c>
       <c r="F87" s="183" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
       <c r="G87" s="183" t="s">
         <v>1439</v>
@@ -38303,7 +38303,7 @@
         <v>1341</v>
       </c>
       <c r="F88" s="183" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
       <c r="G88" s="183" t="s">
         <v>1439</v>
@@ -38330,7 +38330,7 @@
         <v>1650</v>
       </c>
       <c r="F90" s="195" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="G90" s="76" t="s">
         <v>1439</v>
@@ -38354,7 +38354,7 @@
         <v>1650</v>
       </c>
       <c r="F91" s="193" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="G91" s="183" t="s">
         <v>1439</v>
@@ -38378,7 +38378,7 @@
         <v>1650</v>
       </c>
       <c r="F92" s="193" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="G92" s="183" t="s">
         <v>1439</v>
@@ -38387,7 +38387,7 @@
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="183" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="B93" s="183">
         <v>68259581</v>
@@ -38402,7 +38402,7 @@
         <v>1650</v>
       </c>
       <c r="F93" s="193" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="G93" s="183" t="s">
         <v>1439</v>
@@ -38426,7 +38426,7 @@
         <v>1650</v>
       </c>
       <c r="F94" s="193" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="G94" s="183" t="s">
         <v>1439</v>
@@ -38450,7 +38450,7 @@
         <v>1650</v>
       </c>
       <c r="F95" s="193" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="G95" s="183" t="s">
         <v>1439</v>
@@ -38459,7 +38459,7 @@
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="195" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="B97" s="195">
         <v>64476521</v>
@@ -38474,7 +38474,7 @@
         <v>2466</v>
       </c>
       <c r="F97" s="195" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="G97" s="76" t="s">
         <v>1439</v>
@@ -38485,7 +38485,7 @@
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="193" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
       <c r="B98" s="193">
         <v>60389752</v>
@@ -38494,13 +38494,13 @@
         <v>2626</v>
       </c>
       <c r="D98" s="193" t="s">
-        <v>3277</v>
+        <v>3276</v>
       </c>
       <c r="E98" s="183" t="s">
         <v>2466</v>
       </c>
       <c r="F98" s="193" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="G98" s="183" t="s">
         <v>1439</v>
@@ -38511,7 +38511,7 @@
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="183" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="B99" s="183">
         <v>60389752</v>
@@ -38526,7 +38526,7 @@
         <v>2466</v>
       </c>
       <c r="F99" s="193" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="G99" s="183" t="s">
         <v>1439</v>
@@ -38552,7 +38552,7 @@
         <v>2466</v>
       </c>
       <c r="F100" s="193" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="G100" s="183" t="s">
         <v>1439</v>
@@ -38578,7 +38578,7 @@
         <v>2466</v>
       </c>
       <c r="F101" s="193" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="G101" s="183" t="s">
         <v>1439</v>
@@ -38604,7 +38604,7 @@
         <v>2466</v>
       </c>
       <c r="F102" s="193" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="G102" s="183" t="s">
         <v>1439</v>
@@ -38627,7 +38627,7 @@
         <v>2286</v>
       </c>
       <c r="E104" s="76" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="F104" s="195" t="s">
         <v>422</v>
@@ -38653,7 +38653,7 @@
         <v>2291</v>
       </c>
       <c r="E105" s="183" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="F105" s="193" t="s">
         <v>422</v>
@@ -38679,7 +38679,7 @@
         <v>3218</v>
       </c>
       <c r="E106" s="183" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="F106" s="193" t="s">
         <v>422</v>
@@ -38705,7 +38705,7 @@
         <v>2440</v>
       </c>
       <c r="E107" s="183" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="F107" s="193" t="s">
         <v>422</v>
@@ -38731,7 +38731,7 @@
         <v>2295</v>
       </c>
       <c r="E108" s="183" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="F108" s="193" t="s">
         <v>422</v>
@@ -38757,7 +38757,7 @@
         <v>2892</v>
       </c>
       <c r="E109" s="183" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="F109" s="193" t="s">
         <v>422</v>
@@ -38771,7 +38771,7 @@
     </row>
     <row r="111" spans="1:9">
       <c r="A111" s="195" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="B111" s="195">
         <v>68310153</v>
@@ -38786,7 +38786,7 @@
         <v>362</v>
       </c>
       <c r="F111" s="195" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
       <c r="G111" s="76" t="s">
         <v>1341</v>
@@ -38813,7 +38813,7 @@
         <v>362</v>
       </c>
       <c r="F112" s="193" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
       <c r="G112" s="183" t="s">
         <v>1341</v>
@@ -38842,7 +38842,7 @@
         <v>2466</v>
       </c>
       <c r="F113" s="193" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
       <c r="G113" s="183" t="s">
         <v>1341</v>
@@ -38862,16 +38862,16 @@
         <v>62360487</v>
       </c>
       <c r="C114" s="194" t="s">
+        <v>3229</v>
+      </c>
+      <c r="D114" s="183" t="s">
         <v>3230</v>
-      </c>
-      <c r="D114" s="183" t="s">
-        <v>3231</v>
       </c>
       <c r="E114" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F114" s="193" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
       <c r="G114" s="183" t="s">
         <v>1341</v>
@@ -38891,16 +38891,16 @@
         <v>62085821</v>
       </c>
       <c r="C115" s="193" t="s">
+        <v>3231</v>
+      </c>
+      <c r="D115" s="193" t="s">
         <v>3232</v>
-      </c>
-      <c r="D115" s="193" t="s">
-        <v>3233</v>
       </c>
       <c r="E115" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F115" s="193" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
       <c r="G115" s="183" t="s">
         <v>1341</v>
@@ -38920,16 +38920,16 @@
         <v>64403333</v>
       </c>
       <c r="C116" s="193" t="s">
+        <v>3233</v>
+      </c>
+      <c r="D116" s="193" t="s">
         <v>3234</v>
-      </c>
-      <c r="D116" s="193" t="s">
-        <v>3235</v>
       </c>
       <c r="E116" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F116" s="193" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
       <c r="G116" s="183" t="s">
         <v>1341</v>
@@ -39028,16 +39028,16 @@
     </row>
     <row r="121" spans="1:9">
       <c r="A121" s="183" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="B121" s="183">
         <v>64403333</v>
       </c>
       <c r="C121" s="183" t="s">
+        <v>3235</v>
+      </c>
+      <c r="D121" s="183" t="s">
         <v>3236</v>
-      </c>
-      <c r="D121" s="183" t="s">
-        <v>3237</v>
       </c>
       <c r="E121" s="183" t="s">
         <v>2994</v>
@@ -39054,7 +39054,7 @@
     </row>
     <row r="122" spans="1:9">
       <c r="A122" s="193" t="s">
-        <v>3584</v>
+        <v>3583</v>
       </c>
       <c r="B122" s="193" t="s">
         <v>2194</v>
@@ -39310,7 +39310,7 @@
         <v>64226974</v>
       </c>
       <c r="C133" s="183" t="s">
-        <v>3380</v>
+        <v>3379</v>
       </c>
       <c r="D133" s="193" t="s">
         <v>377</v>
@@ -39408,7 +39408,7 @@
     </row>
     <row r="137" spans="1:9">
       <c r="A137" s="193" t="s">
-        <v>3434</v>
+        <v>3433</v>
       </c>
       <c r="B137" s="193">
         <v>63811445</v>
@@ -39466,10 +39466,10 @@
         <v>66319486</v>
       </c>
       <c r="C140" s="193" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="D140" s="193" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="E140" s="183" t="s">
         <v>2355</v>
@@ -39552,7 +39552,7 @@
     </row>
     <row r="144" spans="1:9">
       <c r="A144" s="193" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="B144" s="193">
         <v>60389752</v>
@@ -39610,7 +39610,7 @@
         <v>67697112</v>
       </c>
       <c r="C147" s="193" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
       <c r="D147" s="193" t="s">
         <v>1303</v>
@@ -39630,7 +39630,7 @@
     </row>
     <row r="148" spans="1:9">
       <c r="A148" s="183" t="s">
-        <v>3304</v>
+        <v>3303</v>
       </c>
       <c r="B148" s="183">
         <v>62560788</v>
@@ -39925,7 +39925,7 @@
       <c r="A183" s="221"/>
       <c r="B183" s="221"/>
       <c r="C183" s="221" t="s">
-        <v>3310</v>
+        <v>3309</v>
       </c>
       <c r="D183" s="221"/>
       <c r="E183" s="221"/>
@@ -39939,19 +39939,19 @@
         <v>67836337</v>
       </c>
       <c r="C184" s="195" t="s">
+        <v>3421</v>
+      </c>
+      <c r="D184" s="195" t="s">
         <v>3422</v>
-      </c>
-      <c r="D184" s="195" t="s">
-        <v>3423</v>
       </c>
       <c r="E184" s="433">
         <v>46243</v>
       </c>
       <c r="F184" s="76" t="s">
-        <v>3311</v>
+        <v>3310</v>
       </c>
       <c r="G184" s="195" t="s">
-        <v>3474</v>
+        <v>3473</v>
       </c>
       <c r="H184" s="76" t="s">
         <v>1975</v>
@@ -39959,19 +39959,19 @@
     </row>
     <row r="185" spans="1:9">
       <c r="A185" s="193" t="s">
-        <v>3476</v>
+        <v>3475</v>
       </c>
       <c r="B185" s="193">
         <v>60196388</v>
       </c>
       <c r="C185" s="193" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="D185" s="444" t="s">
-        <v>3423</v>
+        <v>3422</v>
       </c>
       <c r="E185" s="432" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="F185" s="193"/>
       <c r="G185" s="183"/>
@@ -39985,13 +39985,13 @@
         <v>64403333</v>
       </c>
       <c r="C186" s="191" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
       <c r="D186" s="183" t="s">
-        <v>3482</v>
+        <v>3481</v>
       </c>
       <c r="E186" s="432" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="F186" s="193"/>
       <c r="G186" s="183"/>
@@ -39999,19 +39999,19 @@
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="193" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="B187" s="193">
         <v>68071614</v>
       </c>
       <c r="C187" s="193" t="s">
+        <v>3511</v>
+      </c>
+      <c r="D187" s="193" t="s">
         <v>3512</v>
       </c>
-      <c r="D187" s="193" t="s">
+      <c r="E187" s="432" t="s">
         <v>3513</v>
-      </c>
-      <c r="E187" s="432" t="s">
-        <v>3514</v>
       </c>
       <c r="F187" s="193"/>
       <c r="G187" s="183"/>
@@ -40025,13 +40025,13 @@
         <v>63950696</v>
       </c>
       <c r="C188" s="450" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="D188" s="450" t="s">
         <v>2775</v>
       </c>
       <c r="E188" s="432" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="F188" s="451"/>
       <c r="G188" s="445"/>
@@ -40046,13 +40046,13 @@
         <v>65147336</v>
       </c>
       <c r="C189" s="183" t="s">
+        <v>3565</v>
+      </c>
+      <c r="D189" s="183" t="s">
         <v>3566</v>
       </c>
-      <c r="D189" s="183" t="s">
+      <c r="E189" s="432" t="s">
         <v>3567</v>
-      </c>
-      <c r="E189" s="432" t="s">
-        <v>3568</v>
       </c>
       <c r="F189" s="193"/>
       <c r="G189" s="183"/>
@@ -40093,7 +40093,7 @@
         <v>316</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>3398</v>
+        <v>3397</v>
       </c>
       <c r="E194" s="30"/>
       <c r="F194"/>
@@ -40119,7 +40119,7 @@
         <v>439</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="E196" s="30"/>
       <c r="F196"/>
@@ -40130,7 +40130,7 @@
         <v>26</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>3512</v>
+        <v>3511</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -40138,7 +40138,7 @@
         <v>1324</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -40146,7 +40146,7 @@
         <v>1657</v>
       </c>
       <c r="D199" s="428" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
       <c r="F199" s="394"/>
     </row>
@@ -40155,7 +40155,7 @@
         <v>1305</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -40163,7 +40163,7 @@
         <v>406</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>3340</v>
+        <v>3339</v>
       </c>
     </row>
     <row r="202" spans="1:9">
@@ -40171,7 +40171,7 @@
         <v>708</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>3343</v>
+        <v>3342</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -40179,7 +40179,7 @@
         <v>281</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>3359</v>
+        <v>3358</v>
       </c>
     </row>
     <row r="204" spans="1:9">
@@ -40187,7 +40187,7 @@
         <v>2363</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>3360</v>
+        <v>3359</v>
       </c>
     </row>
     <row r="205" spans="1:9">
@@ -40197,7 +40197,7 @@
         <v>465</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -40205,7 +40205,7 @@
         <v>219</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
     </row>
     <row r="207" spans="1:9">
@@ -40213,7 +40213,7 @@
         <v>427</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>3380</v>
+        <v>3379</v>
       </c>
     </row>
     <row r="208" spans="1:9">
@@ -40221,7 +40221,7 @@
         <v>1050</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
     </row>
     <row r="223" spans="1:9">
@@ -41457,10 +41457,10 @@
         <v>705</v>
       </c>
       <c r="H3" t="s">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>3616</v>
+        <v>3615</v>
       </c>
       <c r="J3"/>
     </row>
@@ -41487,10 +41487,10 @@
         <v>515</v>
       </c>
       <c r="H4" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="I4" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="J4"/>
     </row>
@@ -41517,7 +41517,7 @@
         <v>515</v>
       </c>
       <c r="H5" s="220" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="I5" s="220" t="s">
         <v>3095</v>
@@ -41528,19 +41528,19 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="B6" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>427</v>
       </c>
       <c r="D6" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>3258</v>
+        <v>3257</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>2853</v>
@@ -41552,7 +41552,7 @@
         <v>3045</v>
       </c>
       <c r="I6" t="s">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="J6"/>
     </row>
@@ -41584,13 +41584,13 @@
         <v>1434</v>
       </c>
       <c r="B8" t="s">
-        <v>3618</v>
+        <v>3617</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>2060</v>
       </c>
       <c r="D8" t="s">
-        <v>3617</v>
+        <v>3616</v>
       </c>
       <c r="E8" t="s">
         <v>2320</v>
@@ -41605,7 +41605,7 @@
         <v>3088</v>
       </c>
       <c r="I8" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
       <c r="J8"/>
     </row>
@@ -41640,31 +41640,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="278" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>3651</v>
+        <v>3650</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>3646</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>3647</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="E10" s="10" t="s">
         <v>3648</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="F10" s="10" t="s">
         <v>3649</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>3650</v>
       </c>
       <c r="G10" t="s">
         <v>250</v>
       </c>
       <c r="H10" s="278" t="s">
+        <v>3651</v>
+      </c>
+      <c r="I10" s="278" t="s">
         <v>3652</v>
-      </c>
-      <c r="I10" s="278" t="s">
-        <v>3653</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -41815,7 +41815,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="10" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="B5" s="10">
         <v>67992849</v>
@@ -41836,10 +41836,10 @@
         <v>517</v>
       </c>
       <c r="H5" s="220" t="s">
-        <v>3436</v>
+        <v>3435</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -41873,7 +41873,7 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="10" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>2398</v>
@@ -41960,7 +41960,7 @@
         <v>3148</v>
       </c>
       <c r="I12" t="s">
-        <v>3294</v>
+        <v>3293</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -42026,7 +42026,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="10" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="B17" s="10">
         <v>64403333</v>
@@ -42073,7 +42073,7 @@
         <v>3173</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -42087,7 +42087,7 @@
         <v>2378</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>3662</v>
+        <v>3661</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>959</v>
@@ -42099,10 +42099,10 @@
         <v>517</v>
       </c>
       <c r="H19" s="457" t="s">
-        <v>3663</v>
+        <v>3662</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="190" customFormat="1" ht="26">
@@ -42118,13 +42118,13 @@
         <v>2599</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>3349</v>
+        <v>3348</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>2403</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>959</v>
@@ -42136,7 +42136,7 @@
         <v>517</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>3437</v>
+        <v>3436</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>3132</v>
@@ -42144,7 +42144,7 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="B23" s="10">
         <v>64720128</v>
@@ -42165,10 +42165,10 @@
         <v>517</v>
       </c>
       <c r="H23" s="10" t="s">
+        <v>3416</v>
+      </c>
+      <c r="I23" s="10" t="s">
         <v>3417</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>3418</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -42194,10 +42194,10 @@
         <v>517</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>3381</v>
+        <v>3380</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -42410,7 +42410,7 @@
         <v>2283</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>2284</v>
@@ -42436,16 +42436,16 @@
         <v>2500</v>
       </c>
       <c r="B8" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>3484</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>3485</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="10" t="s">
         <v>3486</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>3487</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>1738</v>
@@ -42506,7 +42506,7 @@
         <v>3145</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>3066</v>
@@ -42518,30 +42518,30 @@
         <v>963</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="J10" t="s">
-        <v>3296</v>
+        <v>3295</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="457" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="C11" s="10" t="s">
+        <v>3631</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>3634</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>3632</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>3635</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>3633</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>1738</v>
@@ -42561,7 +42561,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="C15" s="428" t="s">
-        <v>3632</v>
+        <v>3631</v>
       </c>
     </row>
   </sheetData>
@@ -42702,10 +42702,10 @@
         <v>60240509</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>3464</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>3465</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>3466</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>2597</v>
@@ -42761,16 +42761,16 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="10" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="B12" s="10">
         <v>66466729</v>
       </c>
       <c r="C12" s="10" t="s">
+        <v>3593</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>3594</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>3595</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
@@ -42850,7 +42850,7 @@
       <c r="A19" s="10"/>
       <c r="B19" s="10"/>
       <c r="C19" s="428" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
@@ -44394,10 +44394,10 @@
         <v>159</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>3333</v>
+        <v>3332</v>
       </c>
       <c r="N6" s="4" t="s">
         <v>26</v>
@@ -44405,7 +44405,7 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="456" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="B7" s="4">
         <v>69888391</v>
@@ -44435,7 +44435,7 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="B8" t="s">
         <v>452</v>
@@ -44471,19 +44471,19 @@
         <v>2153</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>3333</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>3334</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>3335</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>159</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>3298</v>
+        <v>3297</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>3256</v>
+        <v>3255</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>815</v>
@@ -44491,7 +44491,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="4" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="B10" s="4">
         <v>67916500</v>
@@ -44512,7 +44512,7 @@
         <v>244</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>3186</v>
@@ -44532,7 +44532,7 @@
         <v>1510</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>2896</v>
@@ -44541,10 +44541,10 @@
         <v>244</v>
       </c>
       <c r="H11" t="s">
-        <v>3531</v>
+        <v>3530</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -44570,10 +44570,10 @@
         <v>244</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>3570</v>
+        <v>3569</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -44581,7 +44581,7 @@
         <v>2921</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>3551</v>
+        <v>3550</v>
       </c>
       <c r="C13" s="22" t="s">
         <v>1218</v>
@@ -44599,10 +44599,10 @@
         <v>244</v>
       </c>
       <c r="H13" s="220" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>3619</v>
+        <v>3618</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="4" customFormat="1">
@@ -44628,10 +44628,10 @@
         <v>244</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="I14" s="220" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
       <c r="L14" s="3"/>
     </row>
@@ -44649,10 +44649,10 @@
         <v>2841</v>
       </c>
       <c r="E15" s="4" t="s">
+        <v>3588</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>3589</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>3590</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>887</v>
@@ -44661,7 +44661,7 @@
         <v>3164</v>
       </c>
       <c r="I15" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>498</v>
@@ -44690,10 +44690,10 @@
         <v>159</v>
       </c>
       <c r="H16" t="s">
-        <v>3452</v>
+        <v>3451</v>
       </c>
       <c r="I16" t="s">
-        <v>3324</v>
+        <v>3323</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>805</v>
@@ -44701,7 +44701,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="B17">
         <v>65325884</v>
@@ -44724,7 +44724,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="4" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>2107</v>
@@ -44736,10 +44736,10 @@
         <v>2213</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>244</v>
@@ -44748,7 +44748,7 @@
         <v>3013</v>
       </c>
       <c r="I18" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="4" customFormat="1">
@@ -44765,10 +44765,10 @@
         <v>2582</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>3351</v>
+        <v>3350</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>1227</v>
@@ -44778,7 +44778,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="4" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="B20">
         <v>64403333</v>
@@ -44839,7 +44839,7 @@
         <v>2204</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>3631</v>
+        <v>3630</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>2462</v>
@@ -44850,7 +44850,7 @@
     </row>
     <row r="23" spans="1:12" s="4" customFormat="1">
       <c r="A23" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="B23">
         <v>63247837</v>
@@ -44859,7 +44859,7 @@
         <v>2590</v>
       </c>
       <c r="D23" t="s">
-        <v>3270</v>
+        <v>3269</v>
       </c>
       <c r="E23" t="s">
         <v>2593</v>
@@ -44874,13 +44874,13 @@
         <v>3210</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="L23" s="6"/>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="B24">
         <v>69184177</v>
@@ -44903,16 +44903,16 @@
     </row>
     <row r="25" spans="1:12" s="4" customFormat="1">
       <c r="A25" s="4" t="s">
-        <v>3365</v>
+        <v>3364</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="C25" s="21" t="s">
         <v>1326</v>
       </c>
       <c r="D25" t="s">
-        <v>3378</v>
+        <v>3377</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>2954</v>
@@ -44924,10 +44924,10 @@
         <v>244</v>
       </c>
       <c r="H25" s="105" t="s">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="I25" s="220" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="4" customFormat="1">
@@ -44953,7 +44953,7 @@
         <v>159</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>3462</v>
+        <v>3461</v>
       </c>
       <c r="I27" t="s">
         <v>3168</v>
@@ -44964,7 +44964,7 @@
     </row>
     <row r="28" spans="1:12" s="4" customFormat="1">
       <c r="A28" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>2453</v>
@@ -44985,10 +44985,10 @@
         <v>325</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>3634</v>
+        <v>3633</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="K28"/>
     </row>
@@ -45006,7 +45006,7 @@
         <v>2865</v>
       </c>
       <c r="E29" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>2896</v>
@@ -45018,7 +45018,7 @@
         <v>2866</v>
       </c>
       <c r="I29" t="s">
-        <v>3267</v>
+        <v>3266</v>
       </c>
       <c r="J29" s="4"/>
       <c r="L29" s="135"/>
@@ -45054,7 +45054,7 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="B31" s="4">
         <v>69409351</v>
@@ -45083,7 +45083,7 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="97" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>2843</v>
@@ -45092,7 +45092,7 @@
         <v>2367</v>
       </c>
       <c r="D32" t="s">
-        <v>3667</v>
+        <v>3666</v>
       </c>
       <c r="E32" t="s">
         <v>2371</v>
@@ -45104,10 +45104,10 @@
         <v>159</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="I32" s="455" t="s">
-        <v>3668</v>
+        <v>3667</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -45115,13 +45115,13 @@
         <v>2596</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>3479</v>
+        <v>3478</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>2580</v>
       </c>
       <c r="D33" t="s">
-        <v>3478</v>
+        <v>3477</v>
       </c>
       <c r="E33" t="s">
         <v>2583</v>
@@ -45133,7 +45133,7 @@
         <v>2584</v>
       </c>
       <c r="H33" s="455" t="s">
-        <v>3644</v>
+        <v>3643</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -45141,7 +45141,7 @@
         <v>1429</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="C34" s="21" t="s">
         <v>2577</v>
@@ -45162,7 +45162,7 @@
         <v>3126</v>
       </c>
       <c r="I34" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="J34" s="4"/>
     </row>
@@ -45189,7 +45189,7 @@
         <v>2584</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="I35" s="49" t="s">
         <v>2952</v>
@@ -45197,16 +45197,16 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="B36" t="s">
-        <v>3348</v>
+        <v>3347</v>
       </c>
       <c r="C36" s="22" t="s">
         <v>2579</v>
       </c>
       <c r="D36" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="E36" t="s">
         <v>2583</v>
@@ -45218,7 +45218,7 @@
         <v>159</v>
       </c>
       <c r="H36" t="s">
-        <v>3350</v>
+        <v>3349</v>
       </c>
       <c r="I36" t="s">
         <v>3151</v>
@@ -45229,7 +45229,7 @@
         <v>158</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>3654</v>
+        <v>3653</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>2591</v>
@@ -45247,7 +45247,7 @@
         <v>159</v>
       </c>
       <c r="H37" t="s">
-        <v>3546</v>
+        <v>3545</v>
       </c>
       <c r="I37" t="s">
         <v>2919</v>
@@ -45276,7 +45276,7 @@
         <v>159</v>
       </c>
       <c r="H38" s="220" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="I38" t="s">
         <v>3203</v>
@@ -45292,10 +45292,10 @@
         <v>1351</v>
       </c>
       <c r="E41" s="97" t="s">
+        <v>3260</v>
+      </c>
+      <c r="F41" s="105" t="s">
         <v>3261</v>
-      </c>
-      <c r="F41" s="105" t="s">
-        <v>3262</v>
       </c>
       <c r="G41" s="105" t="s">
         <v>159</v>
@@ -45315,10 +45315,10 @@
         <v>2093</v>
       </c>
       <c r="E42" s="97" t="s">
+        <v>3260</v>
+      </c>
+      <c r="F42" s="105" t="s">
         <v>3261</v>
-      </c>
-      <c r="F42" s="105" t="s">
-        <v>3262</v>
       </c>
       <c r="G42" s="105" t="s">
         <v>159</v>
@@ -45338,10 +45338,10 @@
         <v>2324</v>
       </c>
       <c r="E43" s="105" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
       <c r="F43" s="105" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
       <c r="G43" s="97" t="s">
         <v>159</v>
@@ -45388,7 +45388,7 @@
         <v>2799</v>
       </c>
       <c r="K45" t="s">
-        <v>3544</v>
+        <v>3543</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="4" customFormat="1">
@@ -45786,10 +45786,10 @@
         <v>3035</v>
       </c>
       <c r="J2" s="107" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
       <c r="K2" s="461" t="s">
-        <v>3666</v>
+        <v>3665</v>
       </c>
       <c r="M2" s="159"/>
     </row>
@@ -45816,16 +45816,16 @@
         <v>270</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="I4" s="30" t="s">
         <v>3172</v>
       </c>
       <c r="J4" s="139" t="s">
-        <v>3532</v>
+        <v>3531</v>
       </c>
       <c r="K4" s="139" t="s">
-        <v>3352</v>
+        <v>3351</v>
       </c>
       <c r="M4" s="39"/>
     </row>
@@ -45852,13 +45852,13 @@
         <v>65</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>3494</v>
+        <v>3493</v>
       </c>
       <c r="I5" s="306" t="s">
         <v>2931</v>
       </c>
       <c r="J5" s="30" t="s">
-        <v>3276</v>
+        <v>3275</v>
       </c>
       <c r="K5" s="30" t="s">
         <v>3188</v>
@@ -45876,7 +45876,7 @@
         <v>2744</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="E6" s="140" t="s">
         <v>2707</v>
@@ -45888,7 +45888,7 @@
         <v>65</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>3488</v>
+        <v>3487</v>
       </c>
       <c r="I6" s="32" t="s">
         <v>3028</v>
@@ -45912,13 +45912,13 @@
         <v>1089</v>
       </c>
       <c r="D7" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="E7" s="107" t="s">
+        <v>3263</v>
+      </c>
+      <c r="F7" s="30" t="s">
         <v>3264</v>
-      </c>
-      <c r="F7" s="30" t="s">
-        <v>3265</v>
       </c>
       <c r="G7" s="106" t="s">
         <v>720</v>
@@ -45927,13 +45927,13 @@
         <v>3165</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="J7" s="30" t="s">
-        <v>3598</v>
+        <v>3597</v>
       </c>
       <c r="K7" s="30" t="s">
-        <v>3637</v>
+        <v>3636</v>
       </c>
       <c r="M7" s="36"/>
     </row>
@@ -45948,7 +45948,7 @@
         <v>983</v>
       </c>
       <c r="D8" s="139" t="s">
-        <v>3373</v>
+        <v>3372</v>
       </c>
       <c r="E8" s="107" t="s">
         <v>1154</v>
@@ -45960,16 +45960,16 @@
         <v>65</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="I8" s="32" t="s">
         <v>2993</v>
       </c>
       <c r="J8" s="107" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
       <c r="K8" s="139" t="s">
-        <v>3329</v>
+        <v>3328</v>
       </c>
       <c r="M8" s="36"/>
     </row>
@@ -45996,16 +45996,16 @@
         <v>65</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
       <c r="I9" s="107" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="J9" s="30" t="s">
         <v>3214</v>
       </c>
       <c r="K9" s="107" t="s">
-        <v>3645</v>
+        <v>3644</v>
       </c>
       <c r="M9" s="36"/>
     </row>
@@ -46035,10 +46035,10 @@
         <v>3211</v>
       </c>
       <c r="I10" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="J10" s="219" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="K10" s="107" t="s">
         <v>2981</v>
@@ -46071,10 +46071,10 @@
         <v>3093</v>
       </c>
       <c r="I11" s="30" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="J11" s="107" t="s">
-        <v>3621</v>
+        <v>3620</v>
       </c>
       <c r="K11" s="107" t="s">
         <v>3207</v>
@@ -46083,16 +46083,16 @@
     </row>
     <row r="12" spans="1:13" s="106" customFormat="1">
       <c r="A12" s="319" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="B12" s="106" t="s">
-        <v>3642</v>
+        <v>3641</v>
       </c>
       <c r="C12" s="22" t="s">
         <v>72</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>3639</v>
+        <v>3638</v>
       </c>
       <c r="E12" s="106" t="s">
         <v>908</v>
@@ -46104,13 +46104,13 @@
         <v>245</v>
       </c>
       <c r="H12" s="30" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
       <c r="I12" s="106" t="s">
-        <v>3483</v>
+        <v>3482</v>
       </c>
       <c r="J12" s="106" t="s">
-        <v>3640</v>
+        <v>3639</v>
       </c>
       <c r="K12" s="107" t="s">
         <v>3202</v>
@@ -46119,7 +46119,7 @@
     </row>
     <row r="13" spans="1:13" s="107" customFormat="1">
       <c r="A13" s="140" t="s">
-        <v>3365</v>
+        <v>3364</v>
       </c>
       <c r="B13" s="107" t="s">
         <v>2774</v>
@@ -46149,7 +46149,7 @@
         <v>3217</v>
       </c>
       <c r="K13" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="M13" s="36"/>
     </row>
@@ -46176,7 +46176,7 @@
         <v>65</v>
       </c>
       <c r="H14" s="107" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
       <c r="I14" s="411" t="s">
         <v>2262</v>
@@ -46209,10 +46209,10 @@
         <v>66</v>
       </c>
       <c r="H15" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="I15" t="s">
-        <v>3451</v>
+        <v>3450</v>
       </c>
       <c r="J15" t="s">
         <v>3189</v>
@@ -46270,16 +46270,16 @@
         <v>66</v>
       </c>
       <c r="H17" t="s">
-        <v>3505</v>
+        <v>3504</v>
       </c>
       <c r="I17" s="30" t="s">
         <v>3040</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>3558</v>
+        <v>3557</v>
       </c>
       <c r="K17" s="220" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="M17" s="34"/>
     </row>
@@ -46315,7 +46315,7 @@
         <v>3164</v>
       </c>
       <c r="K18" t="s">
-        <v>3627</v>
+        <v>3626</v>
       </c>
       <c r="M18" s="36"/>
     </row>
@@ -46330,7 +46330,7 @@
         <v>1689</v>
       </c>
       <c r="D19" s="134" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="E19" t="s">
         <v>1692</v>
@@ -46378,7 +46378,7 @@
         <v>65</v>
       </c>
       <c r="H20" s="436" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="I20" t="s">
         <v>2975</v>
@@ -46393,16 +46393,16 @@
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>3304</v>
+        <v>3303</v>
       </c>
       <c r="B21" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="C21" s="22" t="s">
         <v>1127</v>
       </c>
       <c r="D21" t="s">
-        <v>3308</v>
+        <v>3307</v>
       </c>
       <c r="E21" s="140" t="s">
         <v>1589</v>
@@ -46414,19 +46414,19 @@
         <v>65</v>
       </c>
       <c r="H21" t="s">
-        <v>3313</v>
+        <v>3312</v>
       </c>
       <c r="I21" t="s">
+        <v>3315</v>
+      </c>
+      <c r="J21" t="s">
         <v>3316</v>
-      </c>
-      <c r="J21" t="s">
-        <v>3317</v>
       </c>
       <c r="M21" s="36"/>
     </row>
     <row r="22" spans="1:13" s="30" customFormat="1">
       <c r="A22" s="30" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="B22" s="30" t="s">
         <v>2109</v>
@@ -46435,78 +46435,78 @@
         <v>2710</v>
       </c>
       <c r="D22" s="107" t="s">
-        <v>3358</v>
+        <v>3357</v>
       </c>
       <c r="E22" s="30" t="s">
+        <v>3330</v>
+      </c>
+      <c r="F22" s="30" t="s">
         <v>3331</v>
-      </c>
-      <c r="F22" s="30" t="s">
-        <v>3332</v>
       </c>
       <c r="G22" s="32" t="s">
         <v>65</v>
       </c>
       <c r="H22" s="30" t="s">
-        <v>3336</v>
+        <v>3335</v>
       </c>
       <c r="I22" s="30" t="s">
+        <v>3337</v>
+      </c>
+      <c r="J22" s="30" t="s">
         <v>3338</v>
-      </c>
-      <c r="J22" s="30" t="s">
-        <v>3339</v>
       </c>
       <c r="M22" s="36"/>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="B23" t="s">
-        <v>3353</v>
+        <v>3352</v>
       </c>
       <c r="C23" s="22" t="s">
         <v>1902</v>
       </c>
       <c r="D23" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="E23" s="30" t="s">
+        <v>3330</v>
+      </c>
+      <c r="F23" s="30" t="s">
         <v>3331</v>
-      </c>
-      <c r="F23" s="30" t="s">
-        <v>3332</v>
       </c>
       <c r="G23" t="s">
         <v>66</v>
       </c>
       <c r="H23" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="I23" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="J23" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="30" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="B24" t="s">
-        <v>3665</v>
+        <v>3664</v>
       </c>
       <c r="C24" s="22" t="s">
         <v>1916</v>
       </c>
       <c r="D24" s="455" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="E24" s="107" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="F24" s="30" t="s">
-        <v>3664</v>
+        <v>3663</v>
       </c>
       <c r="G24" s="32" t="s">
         <v>270</v>
@@ -46597,7 +46597,7 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="B33">
         <v>60389752</v>
@@ -46620,7 +46620,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="B34">
         <v>60389752</v>
@@ -46632,10 +46632,10 @@
         <v>3209</v>
       </c>
       <c r="E34" s="30" t="s">
+        <v>3330</v>
+      </c>
+      <c r="F34" s="30" t="s">
         <v>3331</v>
-      </c>
-      <c r="F34" s="30" t="s">
-        <v>3332</v>
       </c>
       <c r="G34" t="s">
         <v>3</v>
@@ -46644,7 +46644,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>3304</v>
+        <v>3303</v>
       </c>
       <c r="B35">
         <v>60389752</v>
@@ -46692,7 +46692,7 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="30" t="s">
-        <v>3304</v>
+        <v>3303</v>
       </c>
       <c r="B37" s="30">
         <v>64403333</v>
@@ -46717,7 +46717,7 @@
     </row>
     <row r="38" spans="1:13" s="30" customFormat="1">
       <c r="A38" s="30" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="B38" s="30">
         <v>60389752</v>
@@ -46754,10 +46754,10 @@
         <v>2142</v>
       </c>
       <c r="E39" t="s">
+        <v>3330</v>
+      </c>
+      <c r="F39" t="s">
         <v>3331</v>
-      </c>
-      <c r="F39" t="s">
-        <v>3332</v>
       </c>
       <c r="G39" t="s">
         <v>3</v>
@@ -46838,7 +46838,7 @@
         <v>3114</v>
       </c>
       <c r="I45" s="30" t="s">
-        <v>3301</v>
+        <v>3300</v>
       </c>
       <c r="J45" s="49" t="s">
         <v>2928</v>
@@ -46896,7 +46896,7 @@
         <v>1106</v>
       </c>
       <c r="D65" s="97" t="s">
-        <v>3585</v>
+        <v>3584</v>
       </c>
       <c r="E65" s="107" t="s">
         <v>1123</v>
@@ -46914,7 +46914,7 @@
         <v>1122</v>
       </c>
       <c r="C66" s="97" t="s">
-        <v>3432</v>
+        <v>3431</v>
       </c>
       <c r="D66" s="97" t="s">
         <v>3209</v>
@@ -46937,24 +46937,24 @@
         <v>2164</v>
       </c>
       <c r="E67" s="107" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="F67" s="30" t="s">
-        <v>3664</v>
+        <v>3663</v>
       </c>
     </row>
     <row r="68" spans="1:38">
       <c r="C68" s="459" t="s">
+        <v>3546</v>
+      </c>
+      <c r="D68" t="s">
         <v>3547</v>
       </c>
-      <c r="D68" t="s">
-        <v>3548</v>
-      </c>
       <c r="E68" s="107" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="F68" s="30" t="s">
-        <v>3664</v>
+        <v>3663</v>
       </c>
       <c r="G68" s="106" t="s">
         <v>720</v>
@@ -46965,13 +46965,13 @@
         <v>1211</v>
       </c>
       <c r="D69" s="97" t="s">
-        <v>3586</v>
+        <v>3585</v>
       </c>
       <c r="E69" s="107" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="F69" s="30" t="s">
-        <v>3664</v>
+        <v>3663</v>
       </c>
       <c r="G69" s="106" t="s">
         <v>720</v>
@@ -47252,7 +47252,7 @@
         <v>1130</v>
       </c>
       <c r="D93" t="s">
-        <v>3327</v>
+        <v>3326</v>
       </c>
       <c r="E93" s="140" t="s">
         <v>1132</v>
@@ -47276,7 +47276,7 @@
         <v>1390</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>3328</v>
+        <v>3327</v>
       </c>
       <c r="E94" s="266" t="s">
         <v>1505</v>
@@ -47330,7 +47330,7 @@
         <v>358</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>3432</v>
+        <v>3431</v>
       </c>
     </row>
     <row r="105" spans="2:5">
@@ -47556,7 +47556,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>3656</v>
+        <v>3655</v>
       </c>
       <c r="C12" s="236"/>
     </row>
@@ -47770,27 +47770,27 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="87" t="s">
-        <v>3386</v>
+        <v>3385</v>
       </c>
       <c r="C40" t="s">
-        <v>3389</v>
+        <v>3388</v>
       </c>
       <c r="F40" s="45"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="89" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="C41" t="s">
-        <v>3390</v>
+        <v>3389</v>
       </c>
     </row>
     <row r="42" spans="2:6" ht="15" thickBot="1">
       <c r="B42" s="86" t="s">
-        <v>3388</v>
+        <v>3387</v>
       </c>
       <c r="C42" t="s">
-        <v>3391</v>
+        <v>3390</v>
       </c>
     </row>
     <row r="43" spans="2:6">
@@ -47953,10 +47953,10 @@
         <v>2033</v>
       </c>
       <c r="E6" s="247" t="s">
+        <v>3253</v>
+      </c>
+      <c r="F6" s="247" t="s">
         <v>3254</v>
-      </c>
-      <c r="F6" s="247" t="s">
-        <v>3255</v>
       </c>
       <c r="G6" s="247" t="s">
         <v>357</v>
@@ -47965,10 +47965,10 @@
         <v>3213</v>
       </c>
       <c r="I6" s="244" t="s">
-        <v>3504</v>
+        <v>3503</v>
       </c>
       <c r="J6" s="295" t="s">
-        <v>3611</v>
+        <v>3610</v>
       </c>
       <c r="K6" s="247" t="s">
         <v>475</v>
@@ -47991,19 +47991,19 @@
         <v>1036</v>
       </c>
       <c r="F7" s="265" t="s">
-        <v>3257</v>
+        <v>3256</v>
       </c>
       <c r="G7" s="265" t="s">
         <v>690</v>
       </c>
       <c r="H7" s="295" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="I7" s="295" t="s">
         <v>2988</v>
       </c>
       <c r="J7" s="295" t="s">
-        <v>3456</v>
+        <v>3455</v>
       </c>
       <c r="K7" s="265" t="s">
         <v>709</v>
@@ -48032,13 +48032,13 @@
         <v>250</v>
       </c>
       <c r="H8" s="265" t="s">
-        <v>3603</v>
+        <v>3602</v>
       </c>
       <c r="I8" s="265" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="J8" s="265" t="s">
-        <v>3467</v>
+        <v>3466</v>
       </c>
       <c r="K8" s="259"/>
       <c r="L8" s="259"/>
@@ -48060,7 +48060,7 @@
         <v>2695</v>
       </c>
       <c r="F9" s="263" t="s">
-        <v>3354</v>
+        <v>3353</v>
       </c>
       <c r="G9" s="263" t="s">
         <v>946</v>
@@ -48092,13 +48092,13 @@
         <v>690</v>
       </c>
       <c r="H10" s="264" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
       <c r="I10" s="448" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="J10" s="264" t="s">
-        <v>3535</v>
+        <v>3534</v>
       </c>
       <c r="K10" s="245" t="s">
         <v>1203</v>
@@ -48109,7 +48109,7 @@
         <v>2500</v>
       </c>
       <c r="B11" s="262" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="C11" s="194" t="s">
         <v>491</v>
@@ -48127,13 +48127,13 @@
         <v>690</v>
       </c>
       <c r="H11" s="215" t="s">
-        <v>3439</v>
+        <v>3438</v>
       </c>
       <c r="I11" s="424" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="J11" s="269" t="s">
-        <v>3552</v>
+        <v>3551</v>
       </c>
       <c r="K11" s="183" t="s">
         <v>1204</v>
@@ -48167,10 +48167,10 @@
     </row>
     <row r="13" spans="1:12" s="223" customFormat="1">
       <c r="A13" s="223" t="s">
-        <v>3304</v>
+        <v>3303</v>
       </c>
       <c r="B13" s="223" t="s">
-        <v>3326</v>
+        <v>3325</v>
       </c>
       <c r="C13" s="423" t="s">
         <v>335</v>
@@ -48191,7 +48191,7 @@
         <v>3026</v>
       </c>
       <c r="I13" s="215" t="s">
-        <v>3225</v>
+        <v>3224</v>
       </c>
       <c r="J13" s="223" t="s">
         <v>3027</v>
@@ -48214,7 +48214,7 @@
         <v>1972</v>
       </c>
       <c r="E14" s="216" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
       <c r="F14" s="216" t="s">
         <v>1433</v>
@@ -48223,7 +48223,7 @@
         <v>690</v>
       </c>
       <c r="H14" s="272" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="I14" s="215" t="s">
         <v>2948</v>
@@ -48261,7 +48261,7 @@
         <v>3198</v>
       </c>
       <c r="I15" s="271" t="s">
-        <v>3578</v>
+        <v>3577</v>
       </c>
       <c r="J15" s="264" t="s">
         <v>3158</v>
@@ -48331,7 +48331,7 @@
         <v>831</v>
       </c>
       <c r="D18" s="264" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="E18" s="264" t="s">
         <v>1788</v>
@@ -48343,13 +48343,13 @@
         <v>690</v>
       </c>
       <c r="H18" s="259" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="I18" s="298" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="J18" s="259" t="s">
-        <v>3521</v>
+        <v>3520</v>
       </c>
       <c r="K18" s="264" t="s">
         <v>1765</v>
@@ -48357,7 +48357,7 @@
     </row>
     <row r="19" spans="1:11" s="259" customFormat="1">
       <c r="A19" s="259" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="B19" s="259" t="s">
         <v>2377</v>
@@ -48381,7 +48381,7 @@
         <v>3107</v>
       </c>
       <c r="I19" s="259" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
       <c r="J19" s="259" t="s">
         <v>3042</v>
@@ -48392,7 +48392,7 @@
     </row>
     <row r="20" spans="1:11" s="264" customFormat="1">
       <c r="A20" s="298" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="B20" s="304">
         <v>63609244</v>
@@ -48416,10 +48416,10 @@
         <v>2761</v>
       </c>
       <c r="I20" s="264" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
       <c r="J20" s="264" t="s">
-        <v>3346</v>
+        <v>3345</v>
       </c>
       <c r="K20" s="259" t="s">
         <v>1812</v>
@@ -48462,10 +48462,10 @@
         <v>637</v>
       </c>
       <c r="D22" s="255" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="E22" s="271" t="s">
-        <v>3393</v>
+        <v>3392</v>
       </c>
       <c r="F22" s="271" t="s">
         <v>1710</v>
@@ -48474,10 +48474,10 @@
         <v>250</v>
       </c>
       <c r="H22" s="259" t="s">
-        <v>3481</v>
+        <v>3480</v>
       </c>
       <c r="I22" s="264" t="s">
-        <v>3226</v>
+        <v>3225</v>
       </c>
       <c r="J22" s="264" t="s">
         <v>3127</v>
@@ -48904,13 +48904,13 @@
         <v>2770</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="I2" t="s">
-        <v>3433</v>
+        <v>3432</v>
       </c>
       <c r="J2" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
       <c r="L2" s="36" t="s">
         <v>1173</v>
@@ -48936,7 +48936,7 @@
         <v>298</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>707</v>
@@ -48971,13 +48971,13 @@
         <v>323</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>3463</v>
+        <v>3462</v>
       </c>
       <c r="H4" t="s">
         <v>3017</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="J4" t="s">
         <v>2918</v>
@@ -49021,7 +49021,7 @@
     </row>
     <row r="6" spans="1:12" s="4" customFormat="1">
       <c r="A6" s="4" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="B6" s="4">
         <v>65436260</v>
@@ -49039,13 +49039,13 @@
         <v>166</v>
       </c>
       <c r="G6" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
       <c r="I6" t="s">
-        <v>3285</v>
+        <v>3284</v>
       </c>
       <c r="J6" s="49" t="s">
         <v>2885</v>
@@ -49074,10 +49074,10 @@
         <v>151</v>
       </c>
       <c r="G7" t="s">
-        <v>3522</v>
+        <v>3521</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>3046</v>
@@ -49091,7 +49091,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="4" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2936</v>
@@ -49112,7 +49112,7 @@
         <v>2636</v>
       </c>
       <c r="H8" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
       <c r="I8" s="49" t="s">
         <v>2953</v>
@@ -49148,7 +49148,7 @@
         <v>3084</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>3530</v>
+        <v>3529</v>
       </c>
       <c r="J9" s="220" t="s">
         <v>3072</v>
@@ -49174,13 +49174,13 @@
         <v>1818</v>
       </c>
       <c r="G10" t="s">
-        <v>3259</v>
+        <v>3258</v>
       </c>
       <c r="H10" s="49" t="s">
-        <v>3484</v>
+        <v>3483</v>
       </c>
       <c r="I10" t="s">
-        <v>3287</v>
+        <v>3286</v>
       </c>
       <c r="J10" s="49" t="s">
         <v>2831</v>
@@ -49231,7 +49231,7 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="B13">
         <v>64403333</v>
@@ -49257,13 +49257,13 @@
         <v>3219</v>
       </c>
       <c r="B14" t="s">
-        <v>3228</v>
+        <v>3227</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>281</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>3227</v>
+        <v>3226</v>
       </c>
       <c r="E14" t="s">
         <v>2136</v>
@@ -49272,16 +49272,16 @@
         <v>1818</v>
       </c>
       <c r="G14" t="s">
-        <v>3636</v>
+        <v>3635</v>
       </c>
       <c r="H14" t="s">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="I14" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="J14" t="s">
-        <v>3325</v>
+        <v>3324</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -49610,7 +49610,7 @@
         <v>1550</v>
       </c>
       <c r="E9" t="s">
-        <v>3569</v>
+        <v>3568</v>
       </c>
       <c r="F9" t="s">
         <v>1732</v>
@@ -49630,7 +49630,7 @@
         <v>2211</v>
       </c>
       <c r="E10" t="s">
-        <v>3554</v>
+        <v>3553</v>
       </c>
       <c r="F10" t="s">
         <v>1681</v>
@@ -49667,7 +49667,7 @@
         <v>2676</v>
       </c>
       <c r="E12" t="s">
-        <v>3385</v>
+        <v>3384</v>
       </c>
       <c r="F12" t="s">
         <v>1681</v>
@@ -49675,7 +49675,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="B13">
         <v>62271547</v>
@@ -49833,7 +49833,7 @@
         <v>1512</v>
       </c>
       <c r="F21" t="s">
-        <v>3297</v>
+        <v>3296</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -49921,7 +49921,7 @@
         <v>1461</v>
       </c>
       <c r="D29" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
       <c r="E29" t="s">
         <v>3216</v>
@@ -49930,7 +49930,7 @@
         <v>3005</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="H29" t="s">
         <v>407</v>
@@ -49967,10 +49967,10 @@
         <v>1557</v>
       </c>
       <c r="D31" t="s">
+        <v>3239</v>
+      </c>
+      <c r="E31" t="s">
         <v>3240</v>
-      </c>
-      <c r="E31" t="s">
-        <v>3241</v>
       </c>
       <c r="F31" t="s">
         <v>1313</v>

--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dc549f2659ed9bd7/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63143" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F4ABD4E-9984-4D27-89C3-60C2287D511C}"/>
+  <xr:revisionPtr revIDLastSave="63146" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69BF60A1-19EB-4B87-A13A-86F449BEAA3E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,7 +67,6 @@
     <author>tc={D74A6BC7-C936-4D18-B207-7662524F2FF1}</author>
     <author>tc={263CFA38-6940-48E3-8C6D-4FD90BA5C72C}</author>
     <author>tc={2DA6ACCC-7F6B-4F63-9F66-2022723D557F}</author>
-    <author>tc={2C80CEB1-D520-47E4-8891-F2B7A2059B85}</author>
     <author>tc={A1BAE17A-7373-4E96-9A79-0A588580086C}</author>
     <author>tc={6CB69787-04DC-427D-92C4-EA68685283A6}</author>
     <author>tc={D6ECFDFD-E9B9-4F9B-B2EF-5C67AA00056B}</author>
@@ -154,15 +153,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/68582631-melanie</t>
       </text>
     </comment>
-    <comment ref="J88" authorId="8" shapeId="0" xr:uid="{2C80CEB1-D520-47E4-8891-F2B7A2059B85}">
-      <text>
-        <t>[Comentario encadenado]
-Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
-Comentario:
-    https://netflix-server-a9i0.onrender.com/cliente/200826-2043</t>
-      </text>
-    </comment>
-    <comment ref="K88" authorId="9" shapeId="0" xr:uid="{A1BAE17A-7373-4E96-9A79-0A588580086C}">
+    <comment ref="K88" authorId="8" shapeId="0" xr:uid="{A1BAE17A-7373-4E96-9A79-0A588580086C}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -170,7 +161,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/69645877-yimara</t>
       </text>
     </comment>
-    <comment ref="H91" authorId="10" shapeId="0" xr:uid="{6CB69787-04DC-427D-92C4-EA68685283A6}">
+    <comment ref="H91" authorId="9" shapeId="0" xr:uid="{6CB69787-04DC-427D-92C4-EA68685283A6}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -178,7 +169,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/68131498-melanie</t>
       </text>
     </comment>
-    <comment ref="J97" authorId="11" shapeId="0" xr:uid="{D6ECFDFD-E9B9-4F9B-B2EF-5C67AA00056B}">
+    <comment ref="J97" authorId="10" shapeId="0" xr:uid="{D6ECFDFD-E9B9-4F9B-B2EF-5C67AA00056B}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -186,7 +177,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/68259581-kenneth</t>
       </text>
     </comment>
-    <comment ref="H103" authorId="12" shapeId="0" xr:uid="{5775AADF-97AE-4D86-A7DF-2817E0EA08FF}">
+    <comment ref="H103" authorId="11" shapeId="0" xr:uid="{5775AADF-97AE-4D86-A7DF-2817E0EA08FF}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -10125,9 +10116,6 @@
     <t>Hds200826</t>
   </si>
   <si>
-    <t>62607975 1 pantalla hasta el 20 de septiembre 200826-2043</t>
-  </si>
-  <si>
     <t>65390170 (maicol) 1 pantalla hasta el 20 de septiembre</t>
   </si>
   <si>
@@ -12292,6 +12280,9 @@
   </si>
   <si>
     <t>N006 1 pantalla hasta el 23 de octubre 230926-0015d</t>
+  </si>
+  <si>
+    <t>N006 1 pantalla hasta el 23 de octubre 230926-0106f</t>
   </si>
 </sst>
 </file>
@@ -30125,15 +30116,6 @@
       </x:ext>
     </extLst>
   </threadedComment>
-  <threadedComment ref="J88" dT="2026-08-21T01:44:23.73" personId="{0912E1D7-9EEC-46AD-AFB7-0C0A7E0E5337}" id="{2C80CEB1-D520-47E4-8891-F2B7A2059B85}">
-    <text>https://netflix-server-a9i0.onrender.com/cliente/200826-2043</text>
-    <extLst>
-      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>992904583</xltc2:checksum>
-        <xltc2:hyperlink startIndex="0" length="60" url="https://netflix-server-a9i0.onrender.com/cliente/200826-2043"/>
-      </x:ext>
-    </extLst>
-  </threadedComment>
   <threadedComment ref="K88" dT="2026-08-21T01:47:31.10" personId="{0912E1D7-9EEC-46AD-AFB7-0C0A7E0E5337}" id="{A1BAE17A-7373-4E96-9A79-0A588580086C}">
     <text>https://netflix-server-a9i0.onrender.com/cliente/69645877-yimara</text>
     <extLst>
@@ -30250,7 +30232,7 @@
   <sheetData>
     <row r="1" spans="1:11" s="30" customFormat="1">
       <c r="A1" s="30" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="B1" s="30">
         <v>60389752</v>
@@ -30262,7 +30244,7 @@
         <v>2007</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>3554</v>
+        <v>3553</v>
       </c>
       <c r="F1" s="30" t="s">
         <v>2073</v>
@@ -30282,7 +30264,7 @@
         <v>2119</v>
       </c>
       <c r="D2" s="148" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="148" customFormat="1">
@@ -30301,7 +30283,7 @@
     </row>
     <row r="4" spans="1:11" s="30" customFormat="1">
       <c r="A4" s="30" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="B4" s="30">
         <v>60389752</v>
@@ -30313,7 +30295,7 @@
         <v>2005</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="F4" s="30" t="s">
         <v>2073</v>
@@ -30333,7 +30315,7 @@
         <v>2133</v>
       </c>
       <c r="D5" s="148" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="148" customFormat="1">
@@ -30364,7 +30346,7 @@
         <v>2828</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
       <c r="F7" s="30" t="s">
         <v>2078</v>
@@ -30384,12 +30366,12 @@
         <v>2234</v>
       </c>
       <c r="D8" s="148" t="s">
-        <v>3479</v>
+        <v>3478</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="148" customFormat="1">
       <c r="A9" s="148" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="B9" s="148" t="s">
         <v>1200</v>
@@ -30406,7 +30388,7 @@
     </row>
     <row r="10" spans="1:11" s="422" customFormat="1">
       <c r="A10" s="422" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="B10" s="422">
         <v>60389752</v>
@@ -30431,7 +30413,7 @@
     <row r="12" spans="1:11" s="369" customFormat="1"/>
     <row r="13" spans="1:11" s="30" customFormat="1">
       <c r="A13" s="30" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="B13" s="30">
         <v>69184177</v>
@@ -30440,10 +30422,10 @@
         <v>1771</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>3580</v>
+        <v>3579</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="F13" s="30" t="s">
         <v>2137</v>
@@ -30455,7 +30437,7 @@
     </row>
     <row r="14" spans="1:11" s="148" customFormat="1">
       <c r="A14" s="225" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
       <c r="B14" s="225" t="s">
         <v>1671</v>
@@ -30469,7 +30451,7 @@
     </row>
     <row r="15" spans="1:11" s="148" customFormat="1">
       <c r="A15" s="225" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="B15" s="416">
         <v>62439069</v>
@@ -30483,7 +30465,7 @@
     </row>
     <row r="16" spans="1:11" s="32" customFormat="1">
       <c r="A16" s="30" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="B16" s="284" t="s">
         <v>2190</v>
@@ -30492,10 +30474,10 @@
         <v>1523</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="F16" s="32" t="s">
         <v>1524</v>
@@ -30504,21 +30486,21 @@
         <v>198</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="I16" s="32" t="s">
-        <v>3207</v>
+        <v>3206</v>
       </c>
       <c r="J16" s="32" t="s">
+        <v>3134</v>
+      </c>
+      <c r="K16" s="30" t="s">
         <v>3135</v>
-      </c>
-      <c r="K16" s="30" t="s">
-        <v>3136</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="164" customFormat="1">
       <c r="A17" s="252" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="B17" s="252" t="s">
         <v>1391</v>
@@ -30535,7 +30517,7 @@
     </row>
     <row r="18" spans="1:11" s="164" customFormat="1">
       <c r="A18" s="252" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="B18" s="252">
         <v>64341760</v>
@@ -30561,10 +30543,10 @@
         <v>1488</v>
       </c>
       <c r="D19" s="145" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
       <c r="E19" s="145" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="F19" s="145" t="s">
         <v>1358</v>
@@ -30596,7 +30578,7 @@
     </row>
     <row r="21" spans="1:11" s="297" customFormat="1">
       <c r="A21" s="252" t="s">
-        <v>3433</v>
+        <v>3432</v>
       </c>
       <c r="B21" s="252">
         <v>62169673</v>
@@ -30605,7 +30587,7 @@
         <v>1682</v>
       </c>
       <c r="D21" s="164" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
       <c r="E21" s="164" t="s">
         <v>1683</v>
@@ -30625,7 +30607,7 @@
         <v>2116</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>3554</v>
+        <v>3553</v>
       </c>
       <c r="F22" s="30" t="s">
         <v>2072</v>
@@ -30636,7 +30618,7 @@
     </row>
     <row r="23" spans="1:11" s="148" customFormat="1">
       <c r="A23" s="225" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="B23" s="148">
         <v>64858241</v>
@@ -30650,7 +30632,7 @@
     </row>
     <row r="24" spans="1:11" s="148" customFormat="1">
       <c r="A24" s="149" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="B24" s="149">
         <v>68934853</v>
@@ -30659,7 +30641,7 @@
         <v>2112</v>
       </c>
       <c r="D24" s="148" t="s">
-        <v>3427</v>
+        <v>3426</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="30" customFormat="1">
@@ -30676,7 +30658,7 @@
         <v>1520</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="F25" s="30" t="s">
         <v>1358</v>
@@ -30724,7 +30706,7 @@
     </row>
     <row r="28" spans="1:11" s="30" customFormat="1">
       <c r="A28" s="30" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="B28" s="30">
         <v>60389752</v>
@@ -30736,7 +30718,7 @@
         <v>2002</v>
       </c>
       <c r="E28" s="30" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="F28" s="303" t="s">
         <v>2146</v>
@@ -30761,7 +30743,7 @@
     </row>
     <row r="30" spans="1:11" s="164" customFormat="1">
       <c r="A30" s="164" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="B30" s="164">
         <v>62782770</v>
@@ -30775,10 +30757,10 @@
     </row>
     <row r="31" spans="1:11" s="30" customFormat="1">
       <c r="A31" s="461" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="B31" s="461" t="s">
-        <v>3668</v>
+        <v>3667</v>
       </c>
       <c r="C31" s="251" t="s">
         <v>1896</v>
@@ -30787,7 +30769,7 @@
         <v>2950</v>
       </c>
       <c r="E31" s="30" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
       <c r="F31" s="30" t="s">
         <v>2023</v>
@@ -30796,16 +30778,16 @@
         <v>198</v>
       </c>
       <c r="H31" s="145" t="s">
-        <v>3670</v>
+        <v>3669</v>
       </c>
       <c r="I31" s="192" t="s">
-        <v>3053</v>
+        <v>3052</v>
       </c>
       <c r="J31" s="458" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
       <c r="K31" s="30" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="163" customFormat="1">
@@ -30851,7 +30833,7 @@
         <v>2085</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>3458</v>
+        <v>3457</v>
       </c>
       <c r="F34" s="30" t="s">
         <v>2076</v>
@@ -30871,7 +30853,7 @@
         <v>1979</v>
       </c>
       <c r="D35" s="148" t="s">
-        <v>3505</v>
+        <v>3504</v>
       </c>
       <c r="E35" s="148" t="s">
         <v>1981</v>
@@ -30893,7 +30875,7 @@
     </row>
     <row r="37" spans="1:11" s="30" customFormat="1">
       <c r="A37" s="30" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="B37" s="30" t="s">
         <v>2704</v>
@@ -30902,10 +30884,10 @@
         <v>2000</v>
       </c>
       <c r="D37" s="30" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="E37" s="30" t="s">
-        <v>3555</v>
+        <v>3554</v>
       </c>
       <c r="F37" s="30" t="s">
         <v>2066</v>
@@ -30914,16 +30896,16 @@
         <v>198</v>
       </c>
       <c r="H37" s="145" t="s">
-        <v>3562</v>
+        <v>3561</v>
       </c>
       <c r="I37" s="30" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="J37" s="30" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="K37" s="30" t="s">
-        <v>3291</v>
+        <v>3290</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="147" customFormat="1">
@@ -30960,16 +30942,16 @@
         <v>2469</v>
       </c>
       <c r="B40" s="32" t="s">
-        <v>3087</v>
+        <v>3086</v>
       </c>
       <c r="C40" s="251" t="s">
         <v>1658</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="E40" s="30" t="s">
-        <v>3458</v>
+        <v>3457</v>
       </c>
       <c r="F40" s="30" t="s">
         <v>2081</v>
@@ -30978,21 +30960,21 @@
         <v>198</v>
       </c>
       <c r="H40" s="30" t="s">
-        <v>3552</v>
+        <v>3551</v>
       </c>
       <c r="I40" s="32" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="J40" s="32" t="s">
-        <v>3073</v>
+        <v>3072</v>
       </c>
       <c r="K40" s="145" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="163" customFormat="1">
       <c r="A41" s="163" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="B41" s="163">
         <v>68381893</v>
@@ -31024,7 +31006,7 @@
     </row>
     <row r="43" spans="1:11" s="30" customFormat="1">
       <c r="A43" s="30" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="B43" s="30">
         <v>60389752</v>
@@ -31036,7 +31018,7 @@
         <v>2027</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>3629</v>
+        <v>3628</v>
       </c>
       <c r="F43" s="30" t="s">
         <v>2113</v>
@@ -31047,7 +31029,7 @@
     </row>
     <row r="44" spans="1:11" s="164" customFormat="1">
       <c r="A44" s="164" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="B44" s="164">
         <v>68381893</v>
@@ -31064,7 +31046,7 @@
     </row>
     <row r="45" spans="1:11" s="163" customFormat="1">
       <c r="A45" s="163" t="s">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="B45" s="163">
         <v>64079861</v>
@@ -31093,7 +31075,7 @@
         <v>2822</v>
       </c>
       <c r="E46" s="30" t="s">
-        <v>3265</v>
+        <v>3264</v>
       </c>
       <c r="F46" s="30" t="s">
         <v>2097</v>
@@ -31105,7 +31087,7 @@
     </row>
     <row r="47" spans="1:11" s="164" customFormat="1">
       <c r="A47" s="164" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="B47" s="164">
         <v>63183787</v>
@@ -31139,16 +31121,16 @@
         <v>1495</v>
       </c>
       <c r="B49" s="30" t="s">
-        <v>3311</v>
+        <v>3310</v>
       </c>
       <c r="C49" s="134" t="s">
         <v>1991</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="E49" s="30" t="s">
-        <v>3459</v>
+        <v>3458</v>
       </c>
       <c r="F49" s="30" t="s">
         <v>2084</v>
@@ -31157,16 +31139,16 @@
         <v>198</v>
       </c>
       <c r="H49" s="30" t="s">
-        <v>3041</v>
+        <v>3040</v>
       </c>
       <c r="I49" s="30" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="J49" s="30" t="s">
-        <v>3508</v>
+        <v>3507</v>
       </c>
       <c r="K49" s="32" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
     </row>
     <row r="50" spans="1:12" s="164" customFormat="1">
@@ -31194,7 +31176,7 @@
         <v>1999</v>
       </c>
       <c r="D51" s="164" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="52" spans="1:12" s="139" customFormat="1">
@@ -31211,7 +31193,7 @@
         <v>2834</v>
       </c>
       <c r="E52" s="139" t="s">
-        <v>3458</v>
+        <v>3457</v>
       </c>
       <c r="F52" s="139" t="s">
         <v>2082</v>
@@ -31220,16 +31202,16 @@
         <v>198</v>
       </c>
       <c r="H52" s="140" t="s">
-        <v>3488</v>
+        <v>3487</v>
       </c>
       <c r="I52" s="140" t="s">
-        <v>3285</v>
+        <v>3284</v>
       </c>
       <c r="J52" s="30" t="s">
-        <v>3167</v>
+        <v>3166</v>
       </c>
       <c r="K52" s="269" t="s">
-        <v>3619</v>
+        <v>3618</v>
       </c>
     </row>
     <row r="53" spans="1:12" s="164" customFormat="1">
@@ -31270,7 +31252,7 @@
     </row>
     <row r="55" spans="1:12" s="30" customFormat="1">
       <c r="A55" s="30" t="s">
-        <v>3410</v>
+        <v>3409</v>
       </c>
       <c r="B55" s="30">
         <v>61130088</v>
@@ -31282,7 +31264,7 @@
         <v>1995</v>
       </c>
       <c r="E55" s="30" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="F55" s="30" t="s">
         <v>2098</v>
@@ -31299,10 +31281,10 @@
         <v>60433915</v>
       </c>
       <c r="C56" s="400" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="D56" s="370" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="E56" s="164"/>
     </row>
@@ -31311,19 +31293,19 @@
         <v>2469</v>
       </c>
       <c r="B57" s="163" t="s">
-        <v>3074</v>
+        <v>3073</v>
       </c>
       <c r="C57" s="400" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="D57" s="370" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="E57" s="164"/>
     </row>
     <row r="58" spans="1:12" s="30" customFormat="1">
       <c r="A58" s="30" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="B58" s="412" t="s">
         <v>2064</v>
@@ -31335,7 +31317,7 @@
         <v>2768</v>
       </c>
       <c r="E58" s="30" t="s">
-        <v>3606</v>
+        <v>3605</v>
       </c>
       <c r="F58" s="30" t="s">
         <v>2110</v>
@@ -31344,30 +31326,30 @@
         <v>198</v>
       </c>
       <c r="H58" s="30" t="s">
-        <v>3212</v>
+        <v>3211</v>
       </c>
       <c r="I58" s="30" t="s">
-        <v>3085</v>
+        <v>3084</v>
       </c>
       <c r="J58" s="30" t="s">
-        <v>3171</v>
+        <v>3170</v>
       </c>
       <c r="K58" s="30" t="s">
-        <v>3476</v>
+        <v>3475</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" s="147" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="B59" s="147">
         <v>67539485</v>
       </c>
       <c r="C59" s="399" t="s">
-        <v>3604</v>
+        <v>3603</v>
       </c>
       <c r="D59" s="371" t="s">
-        <v>3607</v>
+        <v>3606</v>
       </c>
       <c r="E59" s="148"/>
       <c r="F59" s="147"/>
@@ -31380,16 +31362,16 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" s="147" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="B60" s="147">
         <v>68853797</v>
       </c>
       <c r="C60" s="399" t="s">
-        <v>3605</v>
+        <v>3604</v>
       </c>
       <c r="D60" s="371" t="s">
-        <v>3608</v>
+        <v>3607</v>
       </c>
       <c r="E60" s="147"/>
       <c r="F60" s="147"/>
@@ -31405,7 +31387,7 @@
         <v>158</v>
       </c>
       <c r="B61" s="30" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="C61" s="134" t="s">
         <v>2065</v>
@@ -31414,7 +31396,7 @@
         <v>2825</v>
       </c>
       <c r="E61" s="30" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="F61" s="30" t="s">
         <v>2066</v>
@@ -31423,21 +31405,21 @@
         <v>198</v>
       </c>
       <c r="H61" s="30" t="s">
-        <v>3329</v>
+        <v>3328</v>
       </c>
       <c r="I61" s="30" t="s">
-        <v>3103</v>
+        <v>3102</v>
       </c>
       <c r="J61" s="30" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="K61" s="30" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
     </row>
     <row r="62" spans="1:12" s="147" customFormat="1">
       <c r="A62" s="147" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B62" s="147">
         <v>60196388</v>
@@ -31446,7 +31428,7 @@
         <v>1467</v>
       </c>
       <c r="D62" s="371" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="E62" s="148" t="s">
         <v>1377</v>
@@ -31454,7 +31436,7 @@
     </row>
     <row r="63" spans="1:12" s="163" customFormat="1">
       <c r="A63" s="163" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="B63" s="163">
         <v>62960567</v>
@@ -31463,13 +31445,13 @@
         <v>2050</v>
       </c>
       <c r="D63" s="370" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="E63" s="164"/>
     </row>
     <row r="64" spans="1:12" s="30" customFormat="1">
       <c r="A64" s="32" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="B64" s="32" t="s">
         <v>2117</v>
@@ -31478,10 +31460,10 @@
         <v>1657</v>
       </c>
       <c r="D64" s="30" t="s">
-        <v>3206</v>
+        <v>3205</v>
       </c>
       <c r="E64" s="30" t="s">
-        <v>3458</v>
+        <v>3457</v>
       </c>
       <c r="F64" s="30" t="s">
         <v>2083</v>
@@ -31490,16 +31472,16 @@
         <v>198</v>
       </c>
       <c r="H64" s="32" t="s">
-        <v>3301</v>
+        <v>3300</v>
       </c>
       <c r="I64" s="32" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="J64" s="30" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="K64" s="30" t="s">
-        <v>3086</v>
+        <v>3085</v>
       </c>
     </row>
     <row r="65" spans="1:11" s="164" customFormat="1">
@@ -31538,7 +31520,7 @@
     </row>
     <row r="67" spans="1:11" s="30" customFormat="1">
       <c r="A67" s="253" t="s">
-        <v>3375</v>
+        <v>3374</v>
       </c>
       <c r="B67" s="284" t="s">
         <v>1904</v>
@@ -31550,7 +31532,7 @@
         <v>2929</v>
       </c>
       <c r="E67" s="30" t="s">
-        <v>3509</v>
+        <v>3508</v>
       </c>
       <c r="F67" s="30" t="s">
         <v>2087</v>
@@ -31559,21 +31541,21 @@
         <v>198</v>
       </c>
       <c r="H67" s="30" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
       <c r="I67" s="30" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="J67" s="30" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="K67" s="145" t="s">
-        <v>3671</v>
+        <v>3670</v>
       </c>
     </row>
     <row r="68" spans="1:11" s="147" customFormat="1">
       <c r="A68" s="147" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B68" s="147">
         <v>68741448</v>
@@ -31582,13 +31564,13 @@
         <v>1872</v>
       </c>
       <c r="D68" s="371" t="s">
-        <v>3039</v>
+        <v>3038</v>
       </c>
       <c r="E68" s="148"/>
     </row>
     <row r="69" spans="1:11" s="148" customFormat="1">
       <c r="A69" s="225" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="B69" s="148">
         <v>63018763</v>
@@ -31597,7 +31579,7 @@
         <v>2086</v>
       </c>
       <c r="D69" s="148" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
     </row>
     <row r="70" spans="1:11" s="30" customFormat="1">
@@ -31605,16 +31587,16 @@
         <v>467</v>
       </c>
       <c r="B70" s="32" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
       <c r="C70" s="251" t="s">
         <v>1660</v>
       </c>
       <c r="D70" s="30" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
       <c r="E70" s="30" t="s">
-        <v>3128</v>
+        <v>3127</v>
       </c>
       <c r="F70" s="30" t="s">
         <v>2124</v>
@@ -31623,13 +31605,13 @@
         <v>198</v>
       </c>
       <c r="H70" s="32" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="I70" s="145" t="s">
-        <v>3563</v>
+        <v>3562</v>
       </c>
       <c r="J70" s="30" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
     </row>
     <row r="71" spans="1:11" s="164" customFormat="1">
@@ -31648,7 +31630,7 @@
     </row>
     <row r="72" spans="1:11" s="163" customFormat="1">
       <c r="A72" s="268" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="B72" s="268" t="s">
         <v>1449</v>
@@ -31663,7 +31645,7 @@
     </row>
     <row r="73" spans="1:11" s="30" customFormat="1">
       <c r="A73" s="30" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="B73" s="30">
         <v>60389752</v>
@@ -31675,7 +31657,7 @@
         <v>2779</v>
       </c>
       <c r="E73" s="30" t="s">
-        <v>3304</v>
+        <v>3303</v>
       </c>
       <c r="F73" s="30" t="s">
         <v>2022</v>
@@ -31686,7 +31668,7 @@
     </row>
     <row r="74" spans="1:11" s="147" customFormat="1">
       <c r="A74" s="147" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
       <c r="B74" s="147">
         <v>64226974</v>
@@ -31710,7 +31692,7 @@
         <v>1941</v>
       </c>
       <c r="D75" s="148" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="E75" s="148"/>
     </row>
@@ -31728,7 +31710,7 @@
         <v>2900</v>
       </c>
       <c r="E76" s="30" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="F76" s="30" t="s">
         <v>2097</v>
@@ -31737,16 +31719,16 @@
         <v>198</v>
       </c>
       <c r="H76" s="30" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="I76" s="30" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="J76" s="30" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="K76" s="145" t="s">
-        <v>3672</v>
+        <v>3671</v>
       </c>
     </row>
     <row r="77" spans="1:11" s="152" customFormat="1">
@@ -31771,7 +31753,7 @@
         <v>2914</v>
       </c>
       <c r="E79" s="30" t="s">
-        <v>3554</v>
+        <v>3553</v>
       </c>
       <c r="F79" s="30" t="s">
         <v>2077</v>
@@ -31783,13 +31765,13 @@
         <v>2926</v>
       </c>
       <c r="I79" s="32" t="s">
-        <v>3082</v>
+        <v>3081</v>
       </c>
       <c r="J79" s="30" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="K79" s="30" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
     </row>
     <row r="80" spans="1:11" s="147" customFormat="1">
@@ -31809,7 +31791,7 @@
     </row>
     <row r="81" spans="1:11" s="147" customFormat="1">
       <c r="A81" s="149" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="B81" s="147">
         <v>64720128</v>
@@ -31826,10 +31808,10 @@
     </row>
     <row r="82" spans="1:11" s="30" customFormat="1">
       <c r="A82" s="145" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
       <c r="B82" s="30" t="s">
-        <v>3558</v>
+        <v>3557</v>
       </c>
       <c r="C82" s="22" t="s">
         <v>1897</v>
@@ -31847,16 +31829,16 @@
         <v>198</v>
       </c>
       <c r="H82" s="30" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="I82" s="145" t="s">
-        <v>3673</v>
+        <v>3672</v>
       </c>
       <c r="J82" s="30" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
       <c r="K82" s="30" t="s">
-        <v>3437</v>
+        <v>3436</v>
       </c>
     </row>
     <row r="83" spans="1:11" s="148" customFormat="1">
@@ -31864,13 +31846,13 @@
         <v>1513</v>
       </c>
       <c r="B83" s="225" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="C83" s="398" t="s">
         <v>1954</v>
       </c>
       <c r="D83" s="148" t="s">
-        <v>3556</v>
+        <v>3555</v>
       </c>
     </row>
     <row r="84" spans="1:11" s="280" customFormat="1">
@@ -31898,7 +31880,7 @@
         <v>693</v>
       </c>
       <c r="D85" s="30" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="E85" s="30" t="s">
         <v>1787</v>
@@ -31910,16 +31892,16 @@
         <v>493</v>
       </c>
       <c r="H85" s="30" t="s">
-        <v>3336</v>
+        <v>3335</v>
       </c>
       <c r="I85" s="32" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
       <c r="J85" s="30" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
       <c r="K85" s="215" t="s">
-        <v>3532</v>
+        <v>3531</v>
       </c>
     </row>
     <row r="86" spans="1:11" s="147" customFormat="1">
@@ -31942,7 +31924,7 @@
     </row>
     <row r="87" spans="1:11" s="147" customFormat="1">
       <c r="A87" s="147" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="B87" s="147" t="s">
         <v>909</v>
@@ -31960,10 +31942,10 @@
     </row>
     <row r="88" spans="1:11" s="30" customFormat="1">
       <c r="A88" s="30" t="s">
-        <v>3598</v>
+        <v>3597</v>
       </c>
       <c r="B88" s="30" t="s">
-        <v>3578</v>
+        <v>3577</v>
       </c>
       <c r="C88" s="153" t="s">
         <v>694</v>
@@ -31981,16 +31963,16 @@
         <v>1521</v>
       </c>
       <c r="H88" s="30" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
       <c r="I88" s="145" t="s">
-        <v>3564</v>
-      </c>
-      <c r="J88" s="431" t="s">
-        <v>2951</v>
+        <v>3563</v>
+      </c>
+      <c r="J88" s="437" t="s">
+        <v>3673</v>
       </c>
       <c r="K88" s="30" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
     </row>
     <row r="89" spans="1:11" s="147" customFormat="1">
@@ -32013,7 +31995,7 @@
     </row>
     <row r="90" spans="1:11" s="148" customFormat="1">
       <c r="A90" s="225" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="B90" s="148">
         <v>67381873</v>
@@ -32031,7 +32013,7 @@
     </row>
     <row r="91" spans="1:11" s="106" customFormat="1">
       <c r="A91" s="249" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="B91" s="32" t="s">
         <v>1397</v>
@@ -32040,7 +32022,7 @@
         <v>46</v>
       </c>
       <c r="D91" s="106" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
       <c r="E91" s="106" t="s">
         <v>1120</v>
@@ -32052,16 +32034,16 @@
         <v>66</v>
       </c>
       <c r="H91" s="30" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="I91" s="31" t="s">
-        <v>3582</v>
+        <v>3581</v>
       </c>
       <c r="J91" s="431" t="s">
         <v>2947</v>
       </c>
       <c r="K91" s="30" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="406" customFormat="1">
@@ -32092,7 +32074,7 @@
         <v>1714</v>
       </c>
       <c r="D93" s="148" t="s">
-        <v>3180</v>
+        <v>3179</v>
       </c>
     </row>
     <row r="94" spans="1:11" s="32" customFormat="1">
@@ -32109,7 +32091,7 @@
         <v>1359</v>
       </c>
       <c r="E94" s="32" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="F94" s="32" t="s">
         <v>1360</v>
@@ -32121,7 +32103,7 @@
     </row>
     <row r="95" spans="1:11" s="148" customFormat="1">
       <c r="A95" s="148" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="B95" s="148" t="s">
         <v>2623</v>
@@ -32138,7 +32120,7 @@
     </row>
     <row r="96" spans="1:11" s="148" customFormat="1">
       <c r="A96" s="148" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="B96" s="148">
         <v>65633205</v>
@@ -32147,7 +32129,7 @@
         <v>1376</v>
       </c>
       <c r="D96" s="148" t="s">
-        <v>3428</v>
+        <v>3427</v>
       </c>
       <c r="E96" s="148" t="s">
         <v>1375</v>
@@ -32155,7 +32137,7 @@
     </row>
     <row r="97" spans="1:13" s="30" customFormat="1">
       <c r="A97" s="460" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="B97" s="30" t="s">
         <v>2881</v>
@@ -32176,16 +32158,16 @@
         <v>198</v>
       </c>
       <c r="H97" s="32" t="s">
-        <v>3381</v>
+        <v>3380</v>
       </c>
       <c r="I97" s="30" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="J97" s="30" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="K97" s="429" t="s">
-        <v>3404</v>
+        <v>3403</v>
       </c>
     </row>
     <row r="98" spans="1:13" s="388" customFormat="1">
@@ -32198,19 +32180,19 @@
     </row>
     <row r="100" spans="1:13" s="30" customFormat="1">
       <c r="A100" s="30" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="B100" s="30" t="s">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="C100" s="251" t="s">
         <v>2807</v>
       </c>
       <c r="D100" s="30" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="E100" s="30" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="F100" s="30" t="s">
         <v>1898</v>
@@ -32219,16 +32201,16 @@
         <v>198</v>
       </c>
       <c r="H100" s="30" t="s">
-        <v>3376</v>
+        <v>3375</v>
       </c>
       <c r="I100" s="30" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
       <c r="J100" s="30" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="K100" s="30" t="s">
-        <v>3463</v>
+        <v>3462</v>
       </c>
     </row>
     <row r="101" spans="1:13" s="388" customFormat="1">
@@ -32241,19 +32223,19 @@
     </row>
     <row r="103" spans="1:13" s="30" customFormat="1">
       <c r="A103" s="30" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="B103" s="30" t="s">
-        <v>3177</v>
+        <v>3176</v>
       </c>
       <c r="C103" s="251" t="s">
         <v>2847</v>
       </c>
       <c r="D103" s="30" t="s">
+        <v>3103</v>
+      </c>
+      <c r="E103" s="30" t="s">
         <v>3104</v>
-      </c>
-      <c r="E103" s="30" t="s">
-        <v>3105</v>
       </c>
       <c r="F103" s="30" t="s">
         <v>1898</v>
@@ -32262,16 +32244,16 @@
         <v>198</v>
       </c>
       <c r="H103" s="30" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="I103" s="30" t="s">
-        <v>3178</v>
+        <v>3177</v>
       </c>
       <c r="J103" s="30" t="s">
-        <v>3166</v>
+        <v>3165</v>
       </c>
       <c r="K103" s="30" t="s">
-        <v>3130</v>
+        <v>3129</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -32315,13 +32297,13 @@
         <v>2846</v>
       </c>
       <c r="D106" s="30" t="s">
+        <v>2954</v>
+      </c>
+      <c r="E106" s="453" t="s">
+        <v>2956</v>
+      </c>
+      <c r="F106" s="30" t="s">
         <v>2955</v>
-      </c>
-      <c r="E106" s="453" t="s">
-        <v>2957</v>
-      </c>
-      <c r="F106" s="30" t="s">
-        <v>2956</v>
       </c>
       <c r="G106" s="30" t="s">
         <v>59</v>
@@ -32373,7 +32355,7 @@
         <v>1977</v>
       </c>
       <c r="E127" s="30" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="F127" t="s">
         <v>1975</v>
@@ -32393,7 +32375,7 @@
         <v>1947</v>
       </c>
       <c r="E128" s="30" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -32407,15 +32389,15 @@
         <v>2692</v>
       </c>
       <c r="D129" s="373" t="s">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="E129" s="30" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="4" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="B130">
         <v>67046608</v>
@@ -32427,7 +32409,7 @@
         <v>2573</v>
       </c>
       <c r="E130" s="30" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -32444,7 +32426,7 @@
         <v>1953</v>
       </c>
       <c r="E131" s="30" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
     </row>
     <row r="133" spans="1:6" s="121" customFormat="1" ht="23.5">
@@ -32466,7 +32448,7 @@
         <v>2334</v>
       </c>
       <c r="E134" s="30" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
       <c r="F134" t="s">
         <v>1336</v>
@@ -32486,7 +32468,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>3410</v>
+        <v>3409</v>
       </c>
       <c r="B139">
         <v>64720128</v>
@@ -32515,7 +32497,7 @@
         <v>1964</v>
       </c>
       <c r="D140" s="373" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
       <c r="E140" s="30" t="s">
         <v>1963</v>
@@ -32540,7 +32522,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="C143" s="1" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -32584,7 +32566,7 @@
         <v>2339</v>
       </c>
       <c r="E153" s="30" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -32592,21 +32574,21 @@
         <v>1495</v>
       </c>
       <c r="B154" t="s">
-        <v>3271</v>
+        <v>3270</v>
       </c>
       <c r="C154" t="s">
         <v>2216</v>
       </c>
       <c r="D154" s="373" t="s">
-        <v>3270</v>
+        <v>3269</v>
       </c>
       <c r="E154" s="30" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="B155">
         <v>60183566</v>
@@ -32618,12 +32600,12 @@
         <v>2574</v>
       </c>
       <c r="E155" s="30" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="B156">
         <v>63145336</v>
@@ -32632,10 +32614,10 @@
         <v>2225</v>
       </c>
       <c r="D156" s="373" t="s">
-        <v>3559</v>
+        <v>3558</v>
       </c>
       <c r="E156" s="30" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -32652,12 +32634,12 @@
         <v>2470</v>
       </c>
       <c r="E157" s="30" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="B158">
         <v>64982293</v>
@@ -32666,10 +32648,10 @@
         <v>2227</v>
       </c>
       <c r="D158" s="373" t="s">
-        <v>3611</v>
+        <v>3610</v>
       </c>
       <c r="E158" s="30" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -32683,15 +32665,15 @@
         <v>2488</v>
       </c>
       <c r="D159" s="373" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
       <c r="E159" s="30" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="B160">
         <v>65133588</v>
@@ -32703,12 +32685,12 @@
         <v>2489</v>
       </c>
       <c r="E160" s="30" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="4" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>1134</v>
@@ -32717,10 +32699,10 @@
         <v>2575</v>
       </c>
       <c r="D161" s="373" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="E161" s="30" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -32734,32 +32716,32 @@
         <v>2491</v>
       </c>
       <c r="D162" s="373" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="E162" s="30" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="B163">
         <v>67570116</v>
       </c>
       <c r="C163" t="s">
-        <v>3561</v>
+        <v>3560</v>
       </c>
       <c r="D163" s="373" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="E163" s="30" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="4" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>2160</v>
@@ -32771,12 +32753,12 @@
         <v>2471</v>
       </c>
       <c r="E164" s="30" t="s">
-        <v>3354</v>
+        <v>3353</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="B165">
         <v>66315726</v>
@@ -32788,12 +32770,12 @@
         <v>2263</v>
       </c>
       <c r="E165" s="30" t="s">
-        <v>3354</v>
+        <v>3353</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="B166">
         <v>64568369</v>
@@ -32805,24 +32787,24 @@
         <v>2263</v>
       </c>
       <c r="E166" s="30" t="s">
-        <v>3354</v>
+        <v>3353</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="B167">
         <v>68818154</v>
       </c>
       <c r="C167" t="s">
-        <v>3274</v>
+        <v>3273</v>
       </c>
       <c r="D167" s="373" t="s">
         <v>2576</v>
       </c>
       <c r="E167" s="30" t="s">
-        <v>3354</v>
+        <v>3353</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -32836,10 +32818,10 @@
         <v>2694</v>
       </c>
       <c r="D168" s="373" t="s">
-        <v>3131</v>
+        <v>3130</v>
       </c>
       <c r="E168" s="30" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -32856,7 +32838,7 @@
         <v>2728</v>
       </c>
       <c r="E169" s="30" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -32873,7 +32855,7 @@
         <v>2468</v>
       </c>
       <c r="E170" s="30" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -32890,7 +32872,7 @@
         <v>2301</v>
       </c>
       <c r="E171" s="30" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -32901,10 +32883,10 @@
         <v>2313</v>
       </c>
       <c r="D172" s="373" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="E172" s="30" t="s">
-        <v>3656</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -32918,10 +32900,10 @@
         <v>2314</v>
       </c>
       <c r="D173" s="373" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="E173" s="30" t="s">
-        <v>3656</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -32935,15 +32917,15 @@
         <v>2315</v>
       </c>
       <c r="D174" s="373" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="E174" s="30" t="s">
-        <v>3656</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
       <c r="B175">
         <v>67178677</v>
@@ -32952,15 +32934,15 @@
         <v>2730</v>
       </c>
       <c r="D175" s="373" t="s">
-        <v>3560</v>
+        <v>3559</v>
       </c>
       <c r="E175" s="30" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="B176">
         <v>66935922</v>
@@ -32969,27 +32951,27 @@
         <v>2731</v>
       </c>
       <c r="D176" s="220" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="E176" s="30" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="B177">
         <v>64455322</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
       <c r="D177" s="220" t="s">
-        <v>3454</v>
+        <v>3453</v>
       </c>
       <c r="E177" s="30" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -33006,12 +32988,12 @@
         <v>2750</v>
       </c>
       <c r="E178" s="30" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="B179">
         <v>68570552</v>
@@ -33020,15 +33002,15 @@
         <v>2733</v>
       </c>
       <c r="D179" s="220" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="E179" s="30" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="B180">
         <v>69964218</v>
@@ -33037,15 +33019,15 @@
         <v>2755</v>
       </c>
       <c r="D180" s="373" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="E180" s="30" t="s">
-        <v>3102</v>
+        <v>3101</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="B181">
         <v>63950696</v>
@@ -33057,12 +33039,12 @@
         <v>2756</v>
       </c>
       <c r="E181" s="30" t="s">
-        <v>3102</v>
+        <v>3101</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="4" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="B182" t="s">
         <v>2784</v>
@@ -33074,7 +33056,7 @@
         <v>2756</v>
       </c>
       <c r="E182" s="30" t="s">
-        <v>3102</v>
+        <v>3101</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -33091,12 +33073,12 @@
         <v>2829</v>
       </c>
       <c r="E183" s="30" t="s">
-        <v>3102</v>
+        <v>3101</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="B184">
         <v>63755362</v>
@@ -33105,15 +33087,15 @@
         <v>2819</v>
       </c>
       <c r="D184" s="373" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
       <c r="E184" s="30" t="s">
-        <v>3102</v>
+        <v>3101</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="B185">
         <v>61248427</v>
@@ -33122,15 +33104,15 @@
         <v>2789</v>
       </c>
       <c r="D185" s="373" t="s">
-        <v>3581</v>
+        <v>3580</v>
       </c>
       <c r="E185" s="30" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" t="s">
-        <v>3371</v>
+        <v>3370</v>
       </c>
       <c r="B186">
         <v>60240509</v>
@@ -33139,10 +33121,10 @@
         <v>2790</v>
       </c>
       <c r="D186" s="373" t="s">
+        <v>3368</v>
+      </c>
+      <c r="E186" s="30" t="s">
         <v>3369</v>
-      </c>
-      <c r="E186" s="30" t="s">
-        <v>3370</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -33156,10 +33138,10 @@
         <v>2791</v>
       </c>
       <c r="D187" s="373" t="s">
-        <v>3306</v>
+        <v>3305</v>
       </c>
       <c r="E187" s="30" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -33176,7 +33158,7 @@
         <v>2798</v>
       </c>
       <c r="E188" s="30" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -33193,7 +33175,7 @@
         <v>2798</v>
       </c>
       <c r="E189" s="30" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -33210,12 +33192,12 @@
         <v>2798</v>
       </c>
       <c r="E190" s="30" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="4" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>1853</v>
@@ -33227,7 +33209,7 @@
         <v>2798</v>
       </c>
       <c r="E191" s="30" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -33241,15 +33223,15 @@
         <v>2830</v>
       </c>
       <c r="D192" s="373" t="s">
-        <v>3609</v>
+        <v>3608</v>
       </c>
       <c r="E192" s="30" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="B193">
         <v>69575383</v>
@@ -33258,10 +33240,10 @@
         <v>2796</v>
       </c>
       <c r="D193" s="373" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="E193" s="30" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -33278,18 +33260,18 @@
         <v>2798</v>
       </c>
       <c r="E194" s="30" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="C195" s="56" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="D195" t="s">
-        <v>3294</v>
+        <v>3293</v>
       </c>
       <c r="E195" s="30" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
     </row>
     <row r="197" spans="1:5" s="391" customFormat="1" ht="23.5">
@@ -33311,44 +33293,44 @@
         <v>2820</v>
       </c>
       <c r="D198" s="373" t="s">
-        <v>3305</v>
+        <v>3304</v>
       </c>
       <c r="E198" s="30" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" t="s">
+        <v>3363</v>
+      </c>
+      <c r="B199" t="s">
         <v>3364</v>
-      </c>
-      <c r="B199" t="s">
-        <v>3365</v>
       </c>
       <c r="C199" t="s">
         <v>2813</v>
       </c>
       <c r="D199" s="373" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="E199" s="30" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="B200">
         <v>63617941</v>
       </c>
       <c r="C200" s="22" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
       <c r="D200" s="373" t="s">
         <v>2869</v>
       </c>
       <c r="E200" s="30" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -33362,15 +33344,15 @@
         <v>2814</v>
       </c>
       <c r="D201" s="373" t="s">
-        <v>3603</v>
+        <v>3602</v>
       </c>
       <c r="E201" s="30" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="202" spans="1:5">
       <c r="A202" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="B202">
         <v>62279384</v>
@@ -33379,10 +33361,10 @@
         <v>2815</v>
       </c>
       <c r="D202" s="373" t="s">
-        <v>3444</v>
+        <v>3443</v>
       </c>
       <c r="E202" s="30" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -33396,27 +33378,27 @@
         <v>2868</v>
       </c>
       <c r="D203" s="373" t="s">
-        <v>3467</v>
+        <v>3466</v>
       </c>
       <c r="E203" s="30" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="30" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="B204" t="s">
-        <v>3453</v>
+        <v>3452</v>
       </c>
       <c r="C204" t="s">
         <v>2816</v>
       </c>
       <c r="D204" s="373" t="s">
-        <v>3452</v>
+        <v>3451</v>
       </c>
       <c r="E204" s="30" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -33427,18 +33409,18 @@
         <v>64982293</v>
       </c>
       <c r="C205" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="D205" s="373" t="s">
-        <v>3522</v>
+        <v>3521</v>
       </c>
       <c r="E205" s="30" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="206" spans="1:5">
       <c r="A206" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="B206" t="s">
         <v>2876</v>
@@ -33450,7 +33432,7 @@
         <v>2874</v>
       </c>
       <c r="E206" s="30" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -33464,10 +33446,10 @@
         <v>2875</v>
       </c>
       <c r="D207" s="373" t="s">
+        <v>3159</v>
+      </c>
+      <c r="E207" s="30" t="s">
         <v>3160</v>
-      </c>
-      <c r="E207" s="30" t="s">
-        <v>3161</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -33484,12 +33466,12 @@
         <v>2889</v>
       </c>
       <c r="E208" s="30" t="s">
-        <v>3423</v>
+        <v>3422</v>
       </c>
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="105" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="B209" t="s">
         <v>1161</v>
@@ -33498,15 +33480,15 @@
         <v>2901</v>
       </c>
       <c r="D209" s="373" t="s">
-        <v>3659</v>
+        <v>3658</v>
       </c>
       <c r="E209" s="30" t="s">
-        <v>3423</v>
+        <v>3422</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="B210">
         <v>65574051</v>
@@ -33515,15 +33497,15 @@
         <v>2888</v>
       </c>
       <c r="D210" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
       <c r="E210" s="30" t="s">
-        <v>3423</v>
+        <v>3422</v>
       </c>
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="97" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="B211" t="s">
         <v>1161</v>
@@ -33532,10 +33514,10 @@
         <v>2902</v>
       </c>
       <c r="D211" s="373" t="s">
-        <v>3660</v>
+        <v>3659</v>
       </c>
       <c r="E211" s="30" t="s">
-        <v>3423</v>
+        <v>3422</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -33546,13 +33528,13 @@
         <v>64881871</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>3100</v>
+        <v>3099</v>
       </c>
       <c r="D212" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="E212" s="30" t="s">
-        <v>3423</v>
+        <v>3422</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -33569,21 +33551,21 @@
         <v>2934</v>
       </c>
       <c r="E213" s="30" t="s">
-        <v>3510</v>
+        <v>3509</v>
       </c>
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="97" t="s">
-        <v>3583</v>
+        <v>3582</v>
       </c>
       <c r="C214" s="22" t="s">
         <v>2941</v>
       </c>
       <c r="D214" t="s">
-        <v>3669</v>
+        <v>3668</v>
       </c>
       <c r="E214" s="30" t="s">
-        <v>3510</v>
+        <v>3509</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -33591,16 +33573,16 @@
         <v>1434</v>
       </c>
       <c r="B215" t="s">
-        <v>3601</v>
+        <v>3600</v>
       </c>
       <c r="C215" s="22" t="s">
         <v>2942</v>
       </c>
       <c r="D215" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
       <c r="E215" s="30" t="s">
-        <v>3510</v>
+        <v>3509</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -33617,7 +33599,7 @@
         <v>2937</v>
       </c>
       <c r="E216" s="30" t="s">
-        <v>3510</v>
+        <v>3509</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -33634,7 +33616,7 @@
         <v>2944</v>
       </c>
       <c r="E217" s="30" t="s">
-        <v>3510</v>
+        <v>3509</v>
       </c>
     </row>
     <row r="231" spans="3:4">
@@ -36510,7 +36492,7 @@
         <v>678</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="G6" s="363" t="s">
         <v>1439</v>
@@ -36531,13 +36513,13 @@
         <v>1841</v>
       </c>
       <c r="D7" s="183" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F7" s="183" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="G7" s="183" t="s">
         <v>1439</v>
@@ -36549,7 +36531,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="193" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="B8" s="193">
         <v>62747874</v>
@@ -36564,7 +36546,7 @@
         <v>362</v>
       </c>
       <c r="F8" s="183" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="G8" s="183" t="s">
         <v>1439</v>
@@ -36591,7 +36573,7 @@
         <v>362</v>
       </c>
       <c r="F9" s="183" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="G9" s="183" t="s">
         <v>1439</v>
@@ -36618,7 +36600,7 @@
         <v>362</v>
       </c>
       <c r="F10" s="183" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="G10" s="183" t="s">
         <v>1439</v>
@@ -36645,7 +36627,7 @@
         <v>362</v>
       </c>
       <c r="F11" s="183" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="G11" s="183" t="s">
         <v>1439</v>
@@ -36669,7 +36651,7 @@
         <v>2496</v>
       </c>
       <c r="E13" s="195" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="F13" s="195" t="s">
         <v>1426</v>
@@ -36695,7 +36677,7 @@
         <v>1842</v>
       </c>
       <c r="E14" s="193" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="F14" s="193" t="s">
         <v>1426</v>
@@ -36721,7 +36703,7 @@
         <v>2763</v>
       </c>
       <c r="E15" s="193" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="F15" s="193" t="s">
         <v>1426</v>
@@ -36747,7 +36729,7 @@
         <v>2304</v>
       </c>
       <c r="E16" s="193" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="F16" s="193" t="s">
         <v>1426</v>
@@ -36761,7 +36743,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="193" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="B17" s="193">
         <v>64403333</v>
@@ -36773,7 +36755,7 @@
         <v>1504</v>
       </c>
       <c r="E17" s="193" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="F17" s="193" t="s">
         <v>1426</v>
@@ -36799,7 +36781,7 @@
         <v>2150</v>
       </c>
       <c r="E18" s="193" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="F18" s="193" t="s">
         <v>1426</v>
@@ -36828,7 +36810,7 @@
         <v>362</v>
       </c>
       <c r="F20" s="195" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="G20" s="76" t="s">
         <v>422</v>
@@ -36857,7 +36839,7 @@
         <v>362</v>
       </c>
       <c r="F21" s="193" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="G21" s="183" t="s">
         <v>422</v>
@@ -36886,7 +36868,7 @@
         <v>362</v>
       </c>
       <c r="F22" s="193" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="G22" s="183" t="s">
         <v>422</v>
@@ -36900,7 +36882,7 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="183" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="B23" s="183">
         <v>60389752</v>
@@ -36915,7 +36897,7 @@
         <v>362</v>
       </c>
       <c r="F23" s="193" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="G23" s="183" t="s">
         <v>422</v>
@@ -36944,7 +36926,7 @@
         <v>362</v>
       </c>
       <c r="F24" s="193" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="G24" s="183" t="s">
         <v>422</v>
@@ -36973,7 +36955,7 @@
         <v>362</v>
       </c>
       <c r="F25" s="193" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="G25" s="183" t="s">
         <v>422</v>
@@ -36987,7 +36969,7 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="76" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="B27" s="76">
         <v>60389752</v>
@@ -37002,7 +36984,7 @@
         <v>362</v>
       </c>
       <c r="F27" s="76" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="G27" s="76" t="s">
         <v>1440</v>
@@ -37029,7 +37011,7 @@
         <v>362</v>
       </c>
       <c r="F28" s="183" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="G28" s="183" t="s">
         <v>378</v>
@@ -37043,22 +37025,22 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="183" t="s">
-        <v>3391</v>
+        <v>3390</v>
       </c>
       <c r="B29" s="183">
         <v>65234700</v>
       </c>
       <c r="C29" s="194" t="s">
+        <v>3312</v>
+      </c>
+      <c r="D29" s="183" t="s">
         <v>3313</v>
-      </c>
-      <c r="D29" s="183" t="s">
-        <v>3314</v>
       </c>
       <c r="E29" s="432">
         <v>46243</v>
       </c>
       <c r="F29" s="183" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="G29" s="183" t="s">
         <v>378</v>
@@ -37087,7 +37069,7 @@
         <v>362</v>
       </c>
       <c r="F30" s="183" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="G30" s="183" t="s">
         <v>378</v>
@@ -37116,7 +37098,7 @@
         <v>362</v>
       </c>
       <c r="F31" s="183" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="G31" s="183" t="s">
         <v>378</v>
@@ -37130,7 +37112,7 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="183" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="B32" s="183">
         <v>68241069</v>
@@ -37145,7 +37127,7 @@
         <v>362</v>
       </c>
       <c r="F32" s="183" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="G32" s="183" t="s">
         <v>378</v>
@@ -37159,7 +37141,7 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="195" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="B34" s="195">
         <v>66466729</v>
@@ -37168,13 +37150,13 @@
         <v>1661</v>
       </c>
       <c r="D34" s="195" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="E34" s="76" t="s">
         <v>2466</v>
       </c>
       <c r="F34" s="195" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
       <c r="G34" s="76" t="s">
         <v>1439</v>
@@ -37185,7 +37167,7 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="193" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="B35" s="193">
         <v>63465332</v>
@@ -37200,7 +37182,7 @@
         <v>2466</v>
       </c>
       <c r="F35" s="193" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
       <c r="G35" s="183" t="s">
         <v>1439</v>
@@ -37226,7 +37208,7 @@
         <v>2466</v>
       </c>
       <c r="F36" s="193" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
       <c r="G36" s="183" t="s">
         <v>1439</v>
@@ -37237,7 +37219,7 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="193" t="s">
-        <v>3344</v>
+        <v>3343</v>
       </c>
       <c r="B37" s="193">
         <v>69111188</v>
@@ -37252,7 +37234,7 @@
         <v>2466</v>
       </c>
       <c r="F37" s="193" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
       <c r="G37" s="183" t="s">
         <v>1439</v>
@@ -37278,7 +37260,7 @@
         <v>2466</v>
       </c>
       <c r="F38" s="193" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
       <c r="G38" s="183" t="s">
         <v>1439</v>
@@ -37304,7 +37286,7 @@
         <v>2466</v>
       </c>
       <c r="F39" s="193" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
       <c r="G39" s="183" t="s">
         <v>1439</v>
@@ -37317,16 +37299,16 @@
       <c r="A41" s="195"/>
       <c r="B41" s="195"/>
       <c r="C41" s="195" t="s">
+        <v>3358</v>
+      </c>
+      <c r="D41" s="195" t="s">
         <v>3359</v>
-      </c>
-      <c r="D41" s="195" t="s">
-        <v>3360</v>
       </c>
       <c r="E41" s="76" t="s">
         <v>362</v>
       </c>
       <c r="F41" s="195" t="s">
-        <v>3361</v>
+        <v>3360</v>
       </c>
       <c r="G41" s="76" t="s">
         <v>2361</v>
@@ -37346,7 +37328,7 @@
         <v>69563253</v>
       </c>
       <c r="C42" s="193" t="s">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="D42" s="193" t="s">
         <v>1673</v>
@@ -37366,10 +37348,10 @@
         <v>1938</v>
       </c>
       <c r="C43" s="194" t="s">
+        <v>3338</v>
+      </c>
+      <c r="D43" s="193" t="s">
         <v>3339</v>
-      </c>
-      <c r="D43" s="193" t="s">
-        <v>3340</v>
       </c>
       <c r="E43" s="432">
         <v>46304</v>
@@ -37386,7 +37368,7 @@
         <v>62751201</v>
       </c>
       <c r="C44" s="194" t="s">
-        <v>3366</v>
+        <v>3365</v>
       </c>
       <c r="D44" s="183" t="s">
         <v>1354</v>
@@ -37406,10 +37388,10 @@
         <v>68030850</v>
       </c>
       <c r="C45" s="193" t="s">
+        <v>3341</v>
+      </c>
+      <c r="D45" s="193" t="s">
         <v>3342</v>
-      </c>
-      <c r="D45" s="193" t="s">
-        <v>3343</v>
       </c>
       <c r="E45" s="432">
         <v>46243</v>
@@ -37442,16 +37424,16 @@
       <c r="A48" s="195"/>
       <c r="B48" s="195"/>
       <c r="C48" s="195" t="s">
+        <v>3392</v>
+      </c>
+      <c r="D48" s="195" t="s">
         <v>3393</v>
       </c>
-      <c r="D48" s="195" t="s">
+      <c r="E48" s="76" t="s">
         <v>3394</v>
       </c>
-      <c r="E48" s="76" t="s">
+      <c r="F48" s="195" t="s">
         <v>3395</v>
-      </c>
-      <c r="F48" s="195" t="s">
-        <v>3396</v>
       </c>
       <c r="G48" s="76" t="s">
         <v>1439</v>
@@ -37488,10 +37470,10 @@
         <v>61548403</v>
       </c>
       <c r="C50" s="194" t="s">
+        <v>3396</v>
+      </c>
+      <c r="D50" s="193" t="s">
         <v>3397</v>
-      </c>
-      <c r="D50" s="193" t="s">
-        <v>3398</v>
       </c>
       <c r="E50" s="432">
         <v>46304</v>
@@ -37504,7 +37486,7 @@
       <c r="C51" s="449"/>
       <c r="D51" s="449"/>
       <c r="E51" s="432" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="F51" s="193"/>
       <c r="G51" s="183"/>
@@ -37514,7 +37496,7 @@
       <c r="C52" s="452"/>
       <c r="D52" s="183"/>
       <c r="E52" s="432" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="F52" s="193"/>
       <c r="G52" s="183"/>
@@ -37534,7 +37516,7 @@
         <v>2908</v>
       </c>
       <c r="E53" s="432" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="F53" s="193"/>
       <c r="G53" s="183"/>
@@ -37547,13 +37529,13 @@
         <v>1660</v>
       </c>
       <c r="D55" s="195" t="s">
-        <v>3624</v>
+        <v>3623</v>
       </c>
       <c r="E55" s="76" t="s">
         <v>2466</v>
       </c>
       <c r="F55" s="195" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="G55" s="76" t="s">
         <v>1439</v>
@@ -37579,7 +37561,7 @@
         <v>2466</v>
       </c>
       <c r="F56" s="193" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="G56" s="183" t="s">
         <v>1439</v>
@@ -37599,13 +37581,13 @@
         <v>2587</v>
       </c>
       <c r="D57" s="193" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="E57" s="183" t="s">
         <v>2466</v>
       </c>
       <c r="F57" s="193" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="G57" s="183" t="s">
         <v>1439</v>
@@ -37631,7 +37613,7 @@
         <v>2466</v>
       </c>
       <c r="F58" s="193" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="G58" s="183" t="s">
         <v>1439</v>
@@ -37657,7 +37639,7 @@
         <v>2466</v>
       </c>
       <c r="F59" s="193" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="G59" s="183" t="s">
         <v>1439</v>
@@ -37668,22 +37650,22 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="183" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="B60" s="183">
         <v>63247837</v>
       </c>
       <c r="C60" s="193" t="s">
-        <v>3228</v>
+        <v>3227</v>
       </c>
       <c r="D60" s="193" t="s">
-        <v>3625</v>
+        <v>3624</v>
       </c>
       <c r="E60" s="183" t="s">
         <v>2466</v>
       </c>
       <c r="F60" s="193" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="G60" s="183" t="s">
         <v>1439</v>
@@ -37709,7 +37691,7 @@
         <v>2466</v>
       </c>
       <c r="F62" s="195" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="G62" s="76" t="s">
         <v>1439</v>
@@ -37735,7 +37717,7 @@
         <v>2466</v>
       </c>
       <c r="F63" s="193" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="G63" s="183" t="s">
         <v>1439</v>
@@ -37746,7 +37728,7 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="183" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="B64" s="183">
         <v>64403333</v>
@@ -37761,7 +37743,7 @@
         <v>2466</v>
       </c>
       <c r="F64" s="193" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="G64" s="183" t="s">
         <v>1439</v>
@@ -37772,7 +37754,7 @@
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="193" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="B65" s="193">
         <v>68030850</v>
@@ -37787,7 +37769,7 @@
         <v>2466</v>
       </c>
       <c r="F65" s="193" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="G65" s="183" t="s">
         <v>1439</v>
@@ -37798,7 +37780,7 @@
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="183" t="s">
-        <v>3410</v>
+        <v>3409</v>
       </c>
       <c r="B66" s="183">
         <v>65003516</v>
@@ -37813,7 +37795,7 @@
         <v>2466</v>
       </c>
       <c r="F66" s="193" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="G66" s="183" t="s">
         <v>1439</v>
@@ -37839,7 +37821,7 @@
         <v>2466</v>
       </c>
       <c r="F67" s="193" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="G67" s="183" t="s">
         <v>1439</v>
@@ -37862,7 +37844,7 @@
         <v>2429</v>
       </c>
       <c r="E69" s="76" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="F69" s="195" t="s">
         <v>2430</v>
@@ -37888,7 +37870,7 @@
         <v>2434</v>
       </c>
       <c r="E70" s="183" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="F70" s="193" t="s">
         <v>2430</v>
@@ -37914,7 +37896,7 @@
         <v>2278</v>
       </c>
       <c r="E71" s="183" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="F71" s="193" t="s">
         <v>2430</v>
@@ -37940,7 +37922,7 @@
         <v>2717</v>
       </c>
       <c r="E72" s="183" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="F72" s="183" t="s">
         <v>2430</v>
@@ -37967,7 +37949,7 @@
         <v>2049</v>
       </c>
       <c r="E73" s="183" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="F73" s="183" t="s">
         <v>2430</v>
@@ -37994,7 +37976,7 @@
         <v>2426</v>
       </c>
       <c r="E74" s="183" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="F74" s="183" t="s">
         <v>2430</v>
@@ -38021,7 +38003,7 @@
         <v>1720</v>
       </c>
       <c r="E76" s="76" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="F76" s="195" t="s">
         <v>2428</v>
@@ -38045,7 +38027,7 @@
         <v>2318</v>
       </c>
       <c r="E77" s="183" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="F77" s="193" t="s">
         <v>2428</v>
@@ -38069,7 +38051,7 @@
         <v>1235</v>
       </c>
       <c r="E78" s="183" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="F78" s="193" t="s">
         <v>2428</v>
@@ -38081,7 +38063,7 @@
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="183" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="B79" s="183">
         <v>62820256</v>
@@ -38093,7 +38075,7 @@
         <v>2344</v>
       </c>
       <c r="E79" s="183" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="F79" s="193" t="s">
         <v>2428</v>
@@ -38105,19 +38087,19 @@
     </row>
     <row r="80" spans="1:9">
       <c r="A80" s="183" t="s">
-        <v>2958</v>
+        <v>2957</v>
       </c>
       <c r="B80" s="183">
         <v>69563253</v>
       </c>
       <c r="C80" s="194" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="D80" s="183" t="s">
         <v>1003</v>
       </c>
       <c r="E80" s="183" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="F80" s="193" t="s">
         <v>2428</v>
@@ -38129,7 +38111,7 @@
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="183" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="B81" s="183">
         <v>63233935</v>
@@ -38138,10 +38120,10 @@
         <v>2363</v>
       </c>
       <c r="D81" s="183" t="s">
-        <v>3472</v>
+        <v>3471</v>
       </c>
       <c r="E81" s="183" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="F81" s="193" t="s">
         <v>2428</v>
@@ -38153,7 +38135,7 @@
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="76" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="B83" s="76">
         <v>63574980</v>
@@ -38168,7 +38150,7 @@
         <v>1341</v>
       </c>
       <c r="F83" s="195" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="G83" s="76" t="s">
         <v>1439</v>
@@ -38195,7 +38177,7 @@
         <v>1341</v>
       </c>
       <c r="F84" s="183" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="G84" s="183" t="s">
         <v>1439</v>
@@ -38222,7 +38204,7 @@
         <v>1341</v>
       </c>
       <c r="F85" s="183" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="G85" s="183" t="s">
         <v>1439</v>
@@ -38237,19 +38219,19 @@
         <v>2481</v>
       </c>
       <c r="B86" s="183" t="s">
-        <v>3081</v>
+        <v>3080</v>
       </c>
       <c r="C86" s="194" t="s">
         <v>2644</v>
       </c>
       <c r="D86" s="183" t="s">
-        <v>3080</v>
+        <v>3079</v>
       </c>
       <c r="E86" s="183" t="s">
         <v>1341</v>
       </c>
       <c r="F86" s="183" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="G86" s="183" t="s">
         <v>1439</v>
@@ -38261,7 +38243,7 @@
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="183" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="B87" s="183">
         <v>69904406</v>
@@ -38270,13 +38252,13 @@
         <v>2645</v>
       </c>
       <c r="D87" s="183" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="E87" s="183" t="s">
         <v>1341</v>
       </c>
       <c r="F87" s="183" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="G87" s="183" t="s">
         <v>1439</v>
@@ -38303,7 +38285,7 @@
         <v>1341</v>
       </c>
       <c r="F88" s="183" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="G88" s="183" t="s">
         <v>1439</v>
@@ -38330,7 +38312,7 @@
         <v>1650</v>
       </c>
       <c r="F90" s="195" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
       <c r="G90" s="76" t="s">
         <v>1439</v>
@@ -38354,7 +38336,7 @@
         <v>1650</v>
       </c>
       <c r="F91" s="193" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
       <c r="G91" s="183" t="s">
         <v>1439</v>
@@ -38378,7 +38360,7 @@
         <v>1650</v>
       </c>
       <c r="F92" s="193" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
       <c r="G92" s="183" t="s">
         <v>1439</v>
@@ -38387,7 +38369,7 @@
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="183" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="B93" s="183">
         <v>68259581</v>
@@ -38402,7 +38384,7 @@
         <v>1650</v>
       </c>
       <c r="F93" s="193" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
       <c r="G93" s="183" t="s">
         <v>1439</v>
@@ -38426,7 +38408,7 @@
         <v>1650</v>
       </c>
       <c r="F94" s="193" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
       <c r="G94" s="183" t="s">
         <v>1439</v>
@@ -38450,7 +38432,7 @@
         <v>1650</v>
       </c>
       <c r="F95" s="193" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
       <c r="G95" s="183" t="s">
         <v>1439</v>
@@ -38459,7 +38441,7 @@
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="195" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="B97" s="195">
         <v>64476521</v>
@@ -38474,7 +38456,7 @@
         <v>2466</v>
       </c>
       <c r="F97" s="195" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="G97" s="76" t="s">
         <v>1439</v>
@@ -38485,7 +38467,7 @@
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="193" t="s">
-        <v>3277</v>
+        <v>3276</v>
       </c>
       <c r="B98" s="193">
         <v>60389752</v>
@@ -38494,13 +38476,13 @@
         <v>2626</v>
       </c>
       <c r="D98" s="193" t="s">
-        <v>3276</v>
+        <v>3275</v>
       </c>
       <c r="E98" s="183" t="s">
         <v>2466</v>
       </c>
       <c r="F98" s="193" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="G98" s="183" t="s">
         <v>1439</v>
@@ -38511,7 +38493,7 @@
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="183" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
       <c r="B99" s="183">
         <v>60389752</v>
@@ -38526,7 +38508,7 @@
         <v>2466</v>
       </c>
       <c r="F99" s="193" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="G99" s="183" t="s">
         <v>1439</v>
@@ -38552,7 +38534,7 @@
         <v>2466</v>
       </c>
       <c r="F100" s="193" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="G100" s="183" t="s">
         <v>1439</v>
@@ -38578,7 +38560,7 @@
         <v>2466</v>
       </c>
       <c r="F101" s="193" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="G101" s="183" t="s">
         <v>1439</v>
@@ -38589,7 +38571,7 @@
     </row>
     <row r="102" spans="1:9">
       <c r="A102" s="193" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="B102" s="193">
         <v>67381873</v>
@@ -38598,13 +38580,13 @@
         <v>2276</v>
       </c>
       <c r="D102" s="193" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
       <c r="E102" s="183" t="s">
         <v>2466</v>
       </c>
       <c r="F102" s="193" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="G102" s="183" t="s">
         <v>1439</v>
@@ -38627,7 +38609,7 @@
         <v>2286</v>
       </c>
       <c r="E104" s="76" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="F104" s="195" t="s">
         <v>422</v>
@@ -38653,7 +38635,7 @@
         <v>2291</v>
       </c>
       <c r="E105" s="183" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="F105" s="193" t="s">
         <v>422</v>
@@ -38667,7 +38649,7 @@
     </row>
     <row r="106" spans="1:9">
       <c r="A106" s="193" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
       <c r="B106" s="193">
         <v>62723048</v>
@@ -38676,10 +38658,10 @@
         <v>2292</v>
       </c>
       <c r="D106" s="193" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
       <c r="E106" s="183" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="F106" s="193" t="s">
         <v>422</v>
@@ -38705,7 +38687,7 @@
         <v>2440</v>
       </c>
       <c r="E107" s="183" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="F107" s="193" t="s">
         <v>422</v>
@@ -38731,7 +38713,7 @@
         <v>2295</v>
       </c>
       <c r="E108" s="183" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="F108" s="193" t="s">
         <v>422</v>
@@ -38757,7 +38739,7 @@
         <v>2892</v>
       </c>
       <c r="E109" s="183" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="F109" s="193" t="s">
         <v>422</v>
@@ -38771,7 +38753,7 @@
     </row>
     <row r="111" spans="1:9">
       <c r="A111" s="195" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="B111" s="195">
         <v>68310153</v>
@@ -38786,7 +38768,7 @@
         <v>362</v>
       </c>
       <c r="F111" s="195" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
       <c r="G111" s="76" t="s">
         <v>1341</v>
@@ -38813,7 +38795,7 @@
         <v>362</v>
       </c>
       <c r="F112" s="193" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
       <c r="G112" s="183" t="s">
         <v>1341</v>
@@ -38842,7 +38824,7 @@
         <v>2466</v>
       </c>
       <c r="F113" s="193" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
       <c r="G113" s="183" t="s">
         <v>1341</v>
@@ -38862,16 +38844,16 @@
         <v>62360487</v>
       </c>
       <c r="C114" s="194" t="s">
+        <v>3228</v>
+      </c>
+      <c r="D114" s="183" t="s">
         <v>3229</v>
-      </c>
-      <c r="D114" s="183" t="s">
-        <v>3230</v>
       </c>
       <c r="E114" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F114" s="193" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
       <c r="G114" s="183" t="s">
         <v>1341</v>
@@ -38891,16 +38873,16 @@
         <v>62085821</v>
       </c>
       <c r="C115" s="193" t="s">
+        <v>3230</v>
+      </c>
+      <c r="D115" s="193" t="s">
         <v>3231</v>
-      </c>
-      <c r="D115" s="193" t="s">
-        <v>3232</v>
       </c>
       <c r="E115" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F115" s="193" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
       <c r="G115" s="183" t="s">
         <v>1341</v>
@@ -38914,22 +38896,22 @@
     </row>
     <row r="116" spans="1:9">
       <c r="A116" s="193" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="B116" s="193">
         <v>64403333</v>
       </c>
       <c r="C116" s="193" t="s">
+        <v>3232</v>
+      </c>
+      <c r="D116" s="193" t="s">
         <v>3233</v>
-      </c>
-      <c r="D116" s="193" t="s">
-        <v>3234</v>
       </c>
       <c r="E116" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F116" s="193" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
       <c r="G116" s="183" t="s">
         <v>1341</v>
@@ -38961,7 +38943,7 @@
         <v>2308</v>
       </c>
       <c r="E118" s="76" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="F118" s="76" t="s">
         <v>422</v>
@@ -38988,7 +38970,7 @@
         <v>2310</v>
       </c>
       <c r="E119" s="183" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="F119" s="193" t="s">
         <v>422</v>
@@ -39014,7 +38996,7 @@
         <v>2312</v>
       </c>
       <c r="E120" s="183" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="F120" s="193" t="s">
         <v>422</v>
@@ -39028,19 +39010,19 @@
     </row>
     <row r="121" spans="1:9">
       <c r="A121" s="183" t="s">
-        <v>3317</v>
+        <v>3316</v>
       </c>
       <c r="B121" s="183">
         <v>64403333</v>
       </c>
       <c r="C121" s="183" t="s">
+        <v>3234</v>
+      </c>
+      <c r="D121" s="183" t="s">
         <v>3235</v>
       </c>
-      <c r="D121" s="183" t="s">
-        <v>3236</v>
-      </c>
       <c r="E121" s="183" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="F121" s="193" t="s">
         <v>422</v>
@@ -39054,7 +39036,7 @@
     </row>
     <row r="122" spans="1:9">
       <c r="A122" s="193" t="s">
-        <v>3583</v>
+        <v>3582</v>
       </c>
       <c r="B122" s="193" t="s">
         <v>2194</v>
@@ -39066,7 +39048,7 @@
         <v>377</v>
       </c>
       <c r="E122" s="183" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="F122" s="193" t="s">
         <v>422</v>
@@ -39092,7 +39074,7 @@
         <v>1646</v>
       </c>
       <c r="E123" s="183" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="F123" s="193" t="s">
         <v>422</v>
@@ -39121,7 +39103,7 @@
         <v>678</v>
       </c>
       <c r="F125" s="76" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="G125" s="76" t="s">
         <v>422</v>
@@ -39135,7 +39117,7 @@
     </row>
     <row r="126" spans="1:9">
       <c r="A126" s="183" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="B126" s="183">
         <v>64403333</v>
@@ -39150,7 +39132,7 @@
         <v>362</v>
       </c>
       <c r="F126" s="183" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="G126" s="183" t="s">
         <v>422</v>
@@ -39179,7 +39161,7 @@
         <v>362</v>
       </c>
       <c r="F127" s="183" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="G127" s="183" t="s">
         <v>422</v>
@@ -39206,7 +39188,7 @@
         <v>362</v>
       </c>
       <c r="F128" s="183" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="G128" s="183" t="s">
         <v>422</v>
@@ -39235,7 +39217,7 @@
         <v>362</v>
       </c>
       <c r="F129" s="183" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="G129" s="183" t="s">
         <v>422</v>
@@ -39264,7 +39246,7 @@
         <v>362</v>
       </c>
       <c r="F130" s="183" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="G130" s="183" t="s">
         <v>422</v>
@@ -39293,7 +39275,7 @@
         <v>2355</v>
       </c>
       <c r="F132" s="195" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="G132" s="76" t="s">
         <v>1439</v>
@@ -39310,7 +39292,7 @@
         <v>64226974</v>
       </c>
       <c r="C133" s="183" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="D133" s="193" t="s">
         <v>377</v>
@@ -39319,7 +39301,7 @@
         <v>2355</v>
       </c>
       <c r="F133" s="193" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="G133" s="183" t="s">
         <v>1439</v>
@@ -39345,7 +39327,7 @@
         <v>2355</v>
       </c>
       <c r="F134" s="193" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="G134" s="183" t="s">
         <v>1439</v>
@@ -39371,7 +39353,7 @@
         <v>2355</v>
       </c>
       <c r="F135" s="193" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="G135" s="183" t="s">
         <v>1439</v>
@@ -39397,7 +39379,7 @@
         <v>2355</v>
       </c>
       <c r="F136" s="193" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="G136" s="183" t="s">
         <v>1439</v>
@@ -39408,7 +39390,7 @@
     </row>
     <row r="137" spans="1:9">
       <c r="A137" s="193" t="s">
-        <v>3433</v>
+        <v>3432</v>
       </c>
       <c r="B137" s="193">
         <v>63811445</v>
@@ -39423,7 +39405,7 @@
         <v>2355</v>
       </c>
       <c r="F137" s="193" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="G137" s="183" t="s">
         <v>1439</v>
@@ -39434,22 +39416,22 @@
     </row>
     <row r="139" spans="1:9">
       <c r="A139" s="195" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="B139" s="195" t="s">
         <v>2154</v>
       </c>
       <c r="C139" s="195" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="D139" s="195" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="E139" s="76" t="s">
         <v>2355</v>
       </c>
       <c r="F139" s="195" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="G139" s="76" t="s">
         <v>1439</v>
@@ -39466,16 +39448,16 @@
         <v>66319486</v>
       </c>
       <c r="C140" s="193" t="s">
-        <v>3237</v>
+        <v>3236</v>
       </c>
       <c r="D140" s="193" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
       <c r="E140" s="183" t="s">
         <v>2355</v>
       </c>
       <c r="F140" s="193" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="G140" s="183" t="s">
         <v>1439</v>
@@ -39486,7 +39468,7 @@
     </row>
     <row r="141" spans="1:9">
       <c r="A141" s="183" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="B141" s="183">
         <v>60389752</v>
@@ -39501,7 +39483,7 @@
         <v>2355</v>
       </c>
       <c r="F141" s="193" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="G141" s="183" t="s">
         <v>1439</v>
@@ -39515,7 +39497,7 @@
         <v>2355</v>
       </c>
       <c r="F142" s="193" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="G142" s="183" t="s">
         <v>1439</v>
@@ -39541,7 +39523,7 @@
         <v>2355</v>
       </c>
       <c r="F143" s="193" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="G143" s="183" t="s">
         <v>1439</v>
@@ -39552,7 +39534,7 @@
     </row>
     <row r="144" spans="1:9">
       <c r="A144" s="193" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="B144" s="193">
         <v>60389752</v>
@@ -39567,7 +39549,7 @@
         <v>2355</v>
       </c>
       <c r="F144" s="193" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="G144" s="183" t="s">
         <v>1439</v>
@@ -39593,7 +39575,7 @@
         <v>2466</v>
       </c>
       <c r="F146" s="195" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="G146" s="76" t="s">
         <v>1439</v>
@@ -39604,13 +39586,13 @@
     </row>
     <row r="147" spans="1:9">
       <c r="A147" s="193" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="B147" s="193">
         <v>67697112</v>
       </c>
       <c r="C147" s="193" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
       <c r="D147" s="193" t="s">
         <v>1303</v>
@@ -39619,7 +39601,7 @@
         <v>2466</v>
       </c>
       <c r="F147" s="193" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="G147" s="183" t="s">
         <v>1439</v>
@@ -39630,7 +39612,7 @@
     </row>
     <row r="148" spans="1:9">
       <c r="A148" s="183" t="s">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="B148" s="183">
         <v>62560788</v>
@@ -39645,7 +39627,7 @@
         <v>2466</v>
       </c>
       <c r="F148" s="193" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="G148" s="183" t="s">
         <v>1439</v>
@@ -39656,7 +39638,7 @@
     </row>
     <row r="149" spans="1:9">
       <c r="A149" s="193" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="B149" s="193">
         <v>64403333</v>
@@ -39671,7 +39653,7 @@
         <v>2466</v>
       </c>
       <c r="F149" s="193" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="G149" s="183" t="s">
         <v>1439</v>
@@ -39697,7 +39679,7 @@
         <v>2466</v>
       </c>
       <c r="F150" s="193" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="G150" s="183" t="s">
         <v>1439</v>
@@ -39723,7 +39705,7 @@
         <v>2466</v>
       </c>
       <c r="F151" s="193" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="G151" s="183" t="s">
         <v>1439</v>
@@ -39749,7 +39731,7 @@
         <v>362</v>
       </c>
       <c r="F153" s="195" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="G153" s="76" t="s">
         <v>2361</v>
@@ -39763,22 +39745,22 @@
     </row>
     <row r="154" spans="1:9">
       <c r="A154" s="193" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="B154" s="193">
         <v>65963732</v>
       </c>
       <c r="C154" s="194" t="s">
+        <v>3220</v>
+      </c>
+      <c r="D154" s="193" t="s">
         <v>3221</v>
-      </c>
-      <c r="D154" s="193" t="s">
-        <v>3222</v>
       </c>
       <c r="E154" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F154" s="193" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="G154" s="183" t="s">
         <v>2361</v>
@@ -39792,7 +39774,7 @@
     </row>
     <row r="155" spans="1:9">
       <c r="A155" s="183" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="B155" s="183">
         <v>60071688</v>
@@ -39801,13 +39783,13 @@
         <v>2345</v>
       </c>
       <c r="D155" s="183" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="E155" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F155" s="193" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="G155" s="183" t="s">
         <v>2361</v>
@@ -39836,7 +39818,7 @@
         <v>362</v>
       </c>
       <c r="F156" s="193" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="G156" s="183" t="s">
         <v>2361</v>
@@ -39865,7 +39847,7 @@
         <v>362</v>
       </c>
       <c r="F157" s="193" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="G157" s="183" t="s">
         <v>2361</v>
@@ -39894,7 +39876,7 @@
         <v>362</v>
       </c>
       <c r="F158" s="193" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="G158" s="183" t="s">
         <v>2361</v>
@@ -39925,7 +39907,7 @@
       <c r="A183" s="221"/>
       <c r="B183" s="221"/>
       <c r="C183" s="221" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="D183" s="221"/>
       <c r="E183" s="221"/>
@@ -39939,19 +39921,19 @@
         <v>67836337</v>
       </c>
       <c r="C184" s="195" t="s">
+        <v>3420</v>
+      </c>
+      <c r="D184" s="195" t="s">
         <v>3421</v>
-      </c>
-      <c r="D184" s="195" t="s">
-        <v>3422</v>
       </c>
       <c r="E184" s="433">
         <v>46243</v>
       </c>
       <c r="F184" s="76" t="s">
-        <v>3310</v>
+        <v>3309</v>
       </c>
       <c r="G184" s="195" t="s">
-        <v>3473</v>
+        <v>3472</v>
       </c>
       <c r="H184" s="76" t="s">
         <v>1975</v>
@@ -39959,19 +39941,19 @@
     </row>
     <row r="185" spans="1:9">
       <c r="A185" s="193" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="B185" s="193">
         <v>60196388</v>
       </c>
       <c r="C185" s="193" t="s">
-        <v>3474</v>
+        <v>3473</v>
       </c>
       <c r="D185" s="444" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
       <c r="E185" s="432" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="F185" s="193"/>
       <c r="G185" s="183"/>
@@ -39985,13 +39967,13 @@
         <v>64403333</v>
       </c>
       <c r="C186" s="191" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="D186" s="183" t="s">
-        <v>3481</v>
+        <v>3480</v>
       </c>
       <c r="E186" s="432" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="F186" s="193"/>
       <c r="G186" s="183"/>
@@ -39999,19 +39981,19 @@
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="193" t="s">
-        <v>3514</v>
+        <v>3513</v>
       </c>
       <c r="B187" s="193">
         <v>68071614</v>
       </c>
       <c r="C187" s="193" t="s">
+        <v>3510</v>
+      </c>
+      <c r="D187" s="193" t="s">
         <v>3511</v>
       </c>
-      <c r="D187" s="193" t="s">
+      <c r="E187" s="432" t="s">
         <v>3512</v>
-      </c>
-      <c r="E187" s="432" t="s">
-        <v>3513</v>
       </c>
       <c r="F187" s="193"/>
       <c r="G187" s="183"/>
@@ -40025,13 +40007,13 @@
         <v>63950696</v>
       </c>
       <c r="C188" s="450" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="D188" s="450" t="s">
         <v>2775</v>
       </c>
       <c r="E188" s="432" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="F188" s="451"/>
       <c r="G188" s="445"/>
@@ -40046,13 +40028,13 @@
         <v>65147336</v>
       </c>
       <c r="C189" s="183" t="s">
+        <v>3564</v>
+      </c>
+      <c r="D189" s="183" t="s">
         <v>3565</v>
       </c>
-      <c r="D189" s="183" t="s">
+      <c r="E189" s="432" t="s">
         <v>3566</v>
-      </c>
-      <c r="E189" s="432" t="s">
-        <v>3567</v>
       </c>
       <c r="F189" s="193"/>
       <c r="G189" s="183"/>
@@ -40093,7 +40075,7 @@
         <v>316</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>3397</v>
+        <v>3396</v>
       </c>
       <c r="E194" s="30"/>
       <c r="F194"/>
@@ -40119,7 +40101,7 @@
         <v>439</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="E196" s="30"/>
       <c r="F196"/>
@@ -40130,7 +40112,7 @@
         <v>26</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>3511</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -40138,7 +40120,7 @@
         <v>1324</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -40146,7 +40128,7 @@
         <v>1657</v>
       </c>
       <c r="D199" s="428" t="s">
-        <v>3565</v>
+        <v>3564</v>
       </c>
       <c r="F199" s="394"/>
     </row>
@@ -40155,7 +40137,7 @@
         <v>1305</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>3237</v>
+        <v>3236</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -40163,7 +40145,7 @@
         <v>406</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>3339</v>
+        <v>3338</v>
       </c>
     </row>
     <row r="202" spans="1:9">
@@ -40171,7 +40153,7 @@
         <v>708</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>3342</v>
+        <v>3341</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -40179,7 +40161,7 @@
         <v>281</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>3358</v>
+        <v>3357</v>
       </c>
     </row>
     <row r="204" spans="1:9">
@@ -40187,7 +40169,7 @@
         <v>2363</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>3359</v>
+        <v>3358</v>
       </c>
     </row>
     <row r="205" spans="1:9">
@@ -40197,7 +40179,7 @@
         <v>465</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>3362</v>
+        <v>3361</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -40205,7 +40187,7 @@
         <v>219</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>3366</v>
+        <v>3365</v>
       </c>
     </row>
     <row r="207" spans="1:9">
@@ -40213,7 +40195,7 @@
         <v>427</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
     </row>
     <row r="208" spans="1:9">
@@ -40221,7 +40203,7 @@
         <v>1050</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>3393</v>
+        <v>3392</v>
       </c>
     </row>
     <row r="223" spans="1:9">
@@ -41436,7 +41418,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="B3">
         <v>62349088</v>
@@ -41457,10 +41439,10 @@
         <v>705</v>
       </c>
       <c r="H3" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
       <c r="J3"/>
     </row>
@@ -41487,10 +41469,10 @@
         <v>515</v>
       </c>
       <c r="H4" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
       <c r="I4" t="s">
-        <v>3535</v>
+        <v>3534</v>
       </c>
       <c r="J4"/>
     </row>
@@ -41508,7 +41490,7 @@
         <v>1519</v>
       </c>
       <c r="E5" t="s">
-        <v>2983</v>
+        <v>2982</v>
       </c>
       <c r="F5" t="s">
         <v>2163</v>
@@ -41517,10 +41499,10 @@
         <v>515</v>
       </c>
       <c r="H5" s="220" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="I5" s="220" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="J5" t="s">
         <v>1394</v>
@@ -41528,19 +41510,19 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>3410</v>
+        <v>3409</v>
       </c>
       <c r="B6" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>427</v>
       </c>
       <c r="D6" t="s">
-        <v>3259</v>
+        <v>3258</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>3257</v>
+        <v>3256</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>2853</v>
@@ -41549,10 +41531,10 @@
         <v>436</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="I6" t="s">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="J6"/>
     </row>
@@ -41584,13 +41566,13 @@
         <v>1434</v>
       </c>
       <c r="B8" t="s">
-        <v>3617</v>
+        <v>3616</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>2060</v>
       </c>
       <c r="D8" t="s">
-        <v>3616</v>
+        <v>3615</v>
       </c>
       <c r="E8" t="s">
         <v>2320</v>
@@ -41602,10 +41584,10 @@
         <v>250</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>3088</v>
+        <v>3087</v>
       </c>
       <c r="I8" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="J8"/>
     </row>
@@ -41640,31 +41622,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="278" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>3650</v>
+        <v>3649</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>3645</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>3646</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="E10" s="10" t="s">
         <v>3647</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="F10" s="10" t="s">
         <v>3648</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>3649</v>
       </c>
       <c r="G10" t="s">
         <v>250</v>
       </c>
       <c r="H10" s="278" t="s">
+        <v>3650</v>
+      </c>
+      <c r="I10" s="278" t="s">
         <v>3651</v>
-      </c>
-      <c r="I10" s="278" t="s">
-        <v>3652</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -41815,7 +41797,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="10" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="B5" s="10">
         <v>67992849</v>
@@ -41836,10 +41818,10 @@
         <v>517</v>
       </c>
       <c r="H5" s="220" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>3627</v>
+        <v>3626</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -41868,12 +41850,12 @@
         <v>2740</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="10" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>2398</v>
@@ -41882,7 +41864,7 @@
         <v>1722</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1695</v>
@@ -41894,10 +41876,10 @@
         <v>517</v>
       </c>
       <c r="H7" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>3134</v>
+        <v>3133</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -41913,7 +41895,7 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="10" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="B11" s="10">
         <v>64403333</v>
@@ -41945,7 +41927,7 @@
         <v>2144</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>959</v>
@@ -41957,10 +41939,10 @@
         <v>517</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
       <c r="I12" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -41985,7 +41967,7 @@
         <v>2202</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>959</v>
@@ -41997,10 +41979,10 @@
         <v>517</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>2987</v>
+        <v>2986</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -42026,7 +42008,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="10" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="B17" s="10">
         <v>64403333</v>
@@ -42049,7 +42031,7 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="10" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="B18" s="10">
         <v>60345107</v>
@@ -42058,7 +42040,7 @@
         <v>2327</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>959</v>
@@ -42070,10 +42052,10 @@
         <v>517</v>
       </c>
       <c r="H18" s="427" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -42087,7 +42069,7 @@
         <v>2378</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>3661</v>
+        <v>3660</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>959</v>
@@ -42099,10 +42081,10 @@
         <v>517</v>
       </c>
       <c r="H19" s="457" t="s">
-        <v>3662</v>
+        <v>3661</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="190" customFormat="1" ht="26">
@@ -42118,13 +42100,13 @@
         <v>2599</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>3348</v>
+        <v>3347</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>2403</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>959</v>
@@ -42136,15 +42118,15 @@
         <v>517</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>3436</v>
+        <v>3435</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="B23" s="10">
         <v>64720128</v>
@@ -42165,10 +42147,10 @@
         <v>517</v>
       </c>
       <c r="H23" s="10" t="s">
+        <v>3415</v>
+      </c>
+      <c r="I23" s="10" t="s">
         <v>3416</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>3417</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -42182,7 +42164,7 @@
         <v>2419</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>3083</v>
+        <v>3082</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>959</v>
@@ -42194,10 +42176,10 @@
         <v>517</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>3380</v>
+        <v>3379</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -42207,7 +42189,7 @@
         <v>2431</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>959</v>
@@ -42326,13 +42308,13 @@
         <v>2446</v>
       </c>
       <c r="B4" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1863</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="E4" t="s">
         <v>1864</v>
@@ -42344,13 +42326,13 @@
         <v>963</v>
       </c>
       <c r="H4" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="J4" t="s">
-        <v>3129</v>
+        <v>3128</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -42410,7 +42392,7 @@
         <v>2283</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>2284</v>
@@ -42422,13 +42404,13 @@
         <v>963</v>
       </c>
       <c r="H7" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>3170</v>
+        <v>3169</v>
       </c>
       <c r="J7" s="275" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -42436,16 +42418,16 @@
         <v>2500</v>
       </c>
       <c r="B8" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>3483</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>3484</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="10" t="s">
         <v>3485</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>3486</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>1738</v>
@@ -42454,30 +42436,30 @@
         <v>963</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="10" t="s">
+        <v>2998</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>2999</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>3000</v>
-      </c>
       <c r="C9" s="22" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>2877</v>
       </c>
       <c r="E9" s="447" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>2878</v>
@@ -42486,13 +42468,13 @@
         <v>963</v>
       </c>
       <c r="H9" s="10" t="s">
+        <v>3000</v>
+      </c>
+      <c r="I9" s="10" t="s">
         <v>3001</v>
       </c>
-      <c r="I9" s="10" t="s">
-        <v>3002</v>
-      </c>
       <c r="J9" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -42500,16 +42482,16 @@
         <v>1429</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>2285</v>
@@ -42518,30 +42500,30 @@
         <v>963</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="J10" t="s">
-        <v>3295</v>
+        <v>3294</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="457" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
       <c r="C11" s="10" t="s">
+        <v>3630</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>3633</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>3631</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>3634</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>3632</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>1738</v>
@@ -42561,7 +42543,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="C15" s="428" t="s">
-        <v>3631</v>
+        <v>3630</v>
       </c>
     </row>
   </sheetData>
@@ -42702,10 +42684,10 @@
         <v>60240509</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>3463</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>3464</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>3465</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>2597</v>
@@ -42726,7 +42708,7 @@
         <v>1786</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>2597</v>
@@ -42761,16 +42743,16 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="10" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="B12" s="10">
         <v>66466729</v>
       </c>
       <c r="C12" s="10" t="s">
+        <v>3592</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>3593</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>3594</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
@@ -42850,7 +42832,7 @@
       <c r="A19" s="10"/>
       <c r="B19" s="10"/>
       <c r="C19" s="428" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
@@ -42968,25 +42950,25 @@
         <v>2938</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="E4" t="s">
         <v>2905</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="G4" s="275" t="s">
         <v>2915</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>3159</v>
+        <v>3158</v>
       </c>
     </row>
   </sheetData>
@@ -44382,7 +44364,7 @@
         <v>51</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>1157</v>
@@ -44394,10 +44376,10 @@
         <v>159</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>3332</v>
+        <v>3331</v>
       </c>
       <c r="N6" s="4" t="s">
         <v>26</v>
@@ -44405,7 +44387,7 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="456" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="B7" s="4">
         <v>69888391</v>
@@ -44429,13 +44411,13 @@
         <v>2261</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
       <c r="L7" s="3"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="B8" t="s">
         <v>452</v>
@@ -44459,7 +44441,7 @@
         <v>2715</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="9" spans="1:14" s="4" customFormat="1">
@@ -44471,19 +44453,19 @@
         <v>2153</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>3332</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>3333</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>3334</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>159</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>3297</v>
+        <v>3296</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>815</v>
@@ -44491,7 +44473,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="4" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
       <c r="B10" s="4">
         <v>67916500</v>
@@ -44512,10 +44494,10 @@
         <v>244</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -44532,7 +44514,7 @@
         <v>1510</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>2896</v>
@@ -44541,10 +44523,10 @@
         <v>244</v>
       </c>
       <c r="H11" t="s">
-        <v>3530</v>
+        <v>3529</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -44570,10 +44552,10 @@
         <v>244</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>3533</v>
+        <v>3532</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>3569</v>
+        <v>3568</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -44581,7 +44563,7 @@
         <v>2921</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>3550</v>
+        <v>3549</v>
       </c>
       <c r="C13" s="22" t="s">
         <v>1218</v>
@@ -44599,10 +44581,10 @@
         <v>244</v>
       </c>
       <c r="H13" s="220" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>3618</v>
+        <v>3617</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="4" customFormat="1">
@@ -44628,10 +44610,10 @@
         <v>244</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="I14" s="220" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
       <c r="L14" s="3"/>
     </row>
@@ -44649,19 +44631,19 @@
         <v>2841</v>
       </c>
       <c r="E15" s="4" t="s">
+        <v>3587</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>3588</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>3589</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>887</v>
       </c>
       <c r="H15" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="I15" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>498</v>
@@ -44690,10 +44672,10 @@
         <v>159</v>
       </c>
       <c r="H16" t="s">
-        <v>3451</v>
+        <v>3450</v>
       </c>
       <c r="I16" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>805</v>
@@ -44701,7 +44683,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="B17">
         <v>65325884</v>
@@ -44724,7 +44706,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="4" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>2107</v>
@@ -44736,19 +44718,19 @@
         <v>2213</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>3573</v>
+        <v>3572</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>244</v>
       </c>
       <c r="H18" s="49" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="I18" t="s">
-        <v>3523</v>
+        <v>3522</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="4" customFormat="1">
@@ -44765,10 +44747,10 @@
         <v>2582</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>3350</v>
+        <v>3349</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>1227</v>
@@ -44778,7 +44760,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="4" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="B20">
         <v>64403333</v>
@@ -44839,7 +44821,7 @@
         <v>2204</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>3630</v>
+        <v>3629</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>2462</v>
@@ -44850,7 +44832,7 @@
     </row>
     <row r="23" spans="1:12" s="4" customFormat="1">
       <c r="A23" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="B23">
         <v>63247837</v>
@@ -44859,7 +44841,7 @@
         <v>2590</v>
       </c>
       <c r="D23" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="E23" t="s">
         <v>2593</v>
@@ -44871,16 +44853,16 @@
         <v>159</v>
       </c>
       <c r="H23" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="L23" s="6"/>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="B24">
         <v>69184177</v>
@@ -44889,10 +44871,10 @@
         <v>1630</v>
       </c>
       <c r="D24" t="s">
-        <v>3036</v>
+        <v>3035</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>2459</v>
@@ -44903,19 +44885,19 @@
     </row>
     <row r="25" spans="1:12" s="4" customFormat="1">
       <c r="A25" s="4" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>3378</v>
+        <v>3377</v>
       </c>
       <c r="C25" s="21" t="s">
         <v>1326</v>
       </c>
       <c r="D25" t="s">
-        <v>3377</v>
+        <v>3376</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>2462</v>
@@ -44924,10 +44906,10 @@
         <v>244</v>
       </c>
       <c r="H25" s="105" t="s">
-        <v>3642</v>
+        <v>3641</v>
       </c>
       <c r="I25" s="220" t="s">
-        <v>3439</v>
+        <v>3438</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="4" customFormat="1">
@@ -44953,10 +44935,10 @@
         <v>159</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="I27" t="s">
-        <v>3168</v>
+        <v>3167</v>
       </c>
       <c r="L27" s="4" t="s">
         <v>813</v>
@@ -44964,7 +44946,7 @@
     </row>
     <row r="28" spans="1:12" s="4" customFormat="1">
       <c r="A28" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>2453</v>
@@ -44976,7 +44958,7 @@
         <v>2028</v>
       </c>
       <c r="E28" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>2462</v>
@@ -44985,10 +44967,10 @@
         <v>325</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="K28"/>
     </row>
@@ -45006,7 +44988,7 @@
         <v>2865</v>
       </c>
       <c r="E29" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>2896</v>
@@ -45018,7 +45000,7 @@
         <v>2866</v>
       </c>
       <c r="I29" t="s">
-        <v>3266</v>
+        <v>3265</v>
       </c>
       <c r="J29" s="4"/>
       <c r="L29" s="135"/>
@@ -45028,16 +45010,16 @@
         <v>2930</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="C30" s="22" t="s">
         <v>402</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="E30" t="s">
-        <v>3187</v>
+        <v>3186</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>1341</v>
@@ -45046,7 +45028,7 @@
         <v>159</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="I30" s="55" t="s">
         <v>2739</v>
@@ -45054,7 +45036,7 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>3317</v>
+        <v>3316</v>
       </c>
       <c r="B31" s="4">
         <v>69409351</v>
@@ -45075,15 +45057,15 @@
         <v>159</v>
       </c>
       <c r="H31" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="97" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>2843</v>
@@ -45092,7 +45074,7 @@
         <v>2367</v>
       </c>
       <c r="D32" t="s">
-        <v>3666</v>
+        <v>3665</v>
       </c>
       <c r="E32" t="s">
         <v>2371</v>
@@ -45104,10 +45086,10 @@
         <v>159</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>3621</v>
+        <v>3620</v>
       </c>
       <c r="I32" s="455" t="s">
-        <v>3667</v>
+        <v>3666</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -45115,13 +45097,13 @@
         <v>2596</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>3478</v>
+        <v>3477</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>2580</v>
       </c>
       <c r="D33" t="s">
-        <v>3477</v>
+        <v>3476</v>
       </c>
       <c r="E33" t="s">
         <v>2583</v>
@@ -45133,7 +45115,7 @@
         <v>2584</v>
       </c>
       <c r="H33" s="455" t="s">
-        <v>3643</v>
+        <v>3642</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -45141,13 +45123,13 @@
         <v>1429</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>3429</v>
+        <v>3428</v>
       </c>
       <c r="C34" s="21" t="s">
         <v>2577</v>
       </c>
       <c r="D34" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="E34" t="s">
         <v>2583</v>
@@ -45159,10 +45141,10 @@
         <v>159</v>
       </c>
       <c r="H34" t="s">
-        <v>3126</v>
+        <v>3125</v>
       </c>
       <c r="I34" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="J34" s="4"/>
     </row>
@@ -45189,24 +45171,24 @@
         <v>2584</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>3637</v>
+        <v>3636</v>
       </c>
       <c r="I35" s="49" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="B36" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="C36" s="22" t="s">
         <v>2579</v>
       </c>
       <c r="D36" t="s">
-        <v>3346</v>
+        <v>3345</v>
       </c>
       <c r="E36" t="s">
         <v>2583</v>
@@ -45218,10 +45200,10 @@
         <v>159</v>
       </c>
       <c r="H36" t="s">
-        <v>3349</v>
+        <v>3348</v>
       </c>
       <c r="I36" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -45229,7 +45211,7 @@
         <v>158</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>3653</v>
+        <v>3652</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>2591</v>
@@ -45247,7 +45229,7 @@
         <v>159</v>
       </c>
       <c r="H37" t="s">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="I37" t="s">
         <v>2919</v>
@@ -45258,7 +45240,7 @@
         <v>157</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>2592</v>
@@ -45276,10 +45258,10 @@
         <v>159</v>
       </c>
       <c r="H38" s="220" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
       <c r="I38" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="455" customFormat="1">
@@ -45292,10 +45274,10 @@
         <v>1351</v>
       </c>
       <c r="E41" s="97" t="s">
+        <v>3259</v>
+      </c>
+      <c r="F41" s="105" t="s">
         <v>3260</v>
-      </c>
-      <c r="F41" s="105" t="s">
-        <v>3261</v>
       </c>
       <c r="G41" s="105" t="s">
         <v>159</v>
@@ -45315,10 +45297,10 @@
         <v>2093</v>
       </c>
       <c r="E42" s="97" t="s">
+        <v>3259</v>
+      </c>
+      <c r="F42" s="105" t="s">
         <v>3260</v>
-      </c>
-      <c r="F42" s="105" t="s">
-        <v>3261</v>
       </c>
       <c r="G42" s="105" t="s">
         <v>159</v>
@@ -45338,10 +45320,10 @@
         <v>2324</v>
       </c>
       <c r="E43" s="105" t="s">
-        <v>3654</v>
+        <v>3653</v>
       </c>
       <c r="F43" s="105" t="s">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="G43" s="97" t="s">
         <v>159</v>
@@ -45358,7 +45340,7 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="4" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="B45" t="s">
         <v>2495</v>
@@ -45388,7 +45370,7 @@
         <v>2799</v>
       </c>
       <c r="K45" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="4" customFormat="1">
@@ -45762,13 +45744,13 @@
         <v>157</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="C2" s="276" t="s">
         <v>254</v>
       </c>
       <c r="D2" s="106" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>1296</v>
@@ -45780,16 +45762,16 @@
         <v>62</v>
       </c>
       <c r="H2" s="300" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="I2" s="106" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="J2" s="107" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="K2" s="461" t="s">
-        <v>3665</v>
+        <v>3664</v>
       </c>
       <c r="M2" s="159"/>
     </row>
@@ -45804,7 +45786,7 @@
         <v>1179</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="E4" s="32" t="s">
         <v>2392</v>
@@ -45816,25 +45798,25 @@
         <v>270</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
       <c r="I4" s="30" t="s">
-        <v>3172</v>
+        <v>3171</v>
       </c>
       <c r="J4" s="139" t="s">
-        <v>3531</v>
+        <v>3530</v>
       </c>
       <c r="K4" s="139" t="s">
-        <v>3351</v>
+        <v>3350</v>
       </c>
       <c r="M4" s="39"/>
     </row>
     <row r="5" spans="1:13" s="30" customFormat="1">
       <c r="A5" s="30" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>3205</v>
+        <v>3204</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>1112</v>
@@ -45852,22 +45834,22 @@
         <v>65</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="I5" s="306" t="s">
         <v>2931</v>
       </c>
       <c r="J5" s="30" t="s">
-        <v>3275</v>
+        <v>3274</v>
       </c>
       <c r="K5" s="30" t="s">
-        <v>3188</v>
+        <v>3187</v>
       </c>
       <c r="M5" s="36"/>
     </row>
     <row r="6" spans="1:13" s="30" customFormat="1">
       <c r="A6" s="107" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="B6" s="30" t="s">
         <v>2179</v>
@@ -45876,7 +45858,7 @@
         <v>2744</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="E6" s="140" t="s">
         <v>2707</v>
@@ -45888,22 +45870,22 @@
         <v>65</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>3028</v>
+        <v>3027</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="K6" s="30" t="s">
-        <v>3150</v>
+        <v>3149</v>
       </c>
       <c r="M6" s="36"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="107" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>1209</v>
@@ -45912,28 +45894,28 @@
         <v>1089</v>
       </c>
       <c r="D7" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="E7" s="107" t="s">
+        <v>3262</v>
+      </c>
+      <c r="F7" s="30" t="s">
         <v>3263</v>
-      </c>
-      <c r="F7" s="30" t="s">
-        <v>3264</v>
       </c>
       <c r="G7" s="106" t="s">
         <v>720</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>3570</v>
+        <v>3569</v>
       </c>
       <c r="J7" s="30" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
       <c r="K7" s="30" t="s">
-        <v>3636</v>
+        <v>3635</v>
       </c>
       <c r="M7" s="36"/>
     </row>
@@ -45948,7 +45930,7 @@
         <v>983</v>
       </c>
       <c r="D8" s="139" t="s">
-        <v>3372</v>
+        <v>3371</v>
       </c>
       <c r="E8" s="107" t="s">
         <v>1154</v>
@@ -45960,22 +45942,22 @@
         <v>65</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="I8" s="32" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="J8" s="107" t="s">
-        <v>3596</v>
+        <v>3595</v>
       </c>
       <c r="K8" s="139" t="s">
-        <v>3328</v>
+        <v>3327</v>
       </c>
       <c r="M8" s="36"/>
     </row>
     <row r="9" spans="1:13" s="107" customFormat="1">
       <c r="A9" s="302" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="B9" s="32" t="s">
         <v>1672</v>
@@ -45996,22 +45978,22 @@
         <v>65</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="I9" s="107" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
       <c r="K9" s="107" t="s">
-        <v>3644</v>
+        <v>3643</v>
       </c>
       <c r="M9" s="36"/>
     </row>
     <row r="10" spans="1:13" s="30" customFormat="1">
       <c r="A10" s="30" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="B10" s="30">
         <v>69575383</v>
@@ -46032,16 +46014,16 @@
         <v>65</v>
       </c>
       <c r="H10" s="107" t="s">
-        <v>3211</v>
+        <v>3210</v>
       </c>
       <c r="I10" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
       <c r="J10" s="219" t="s">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="K10" s="107" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="M10" s="34"/>
     </row>
@@ -46068,31 +46050,31 @@
         <v>605</v>
       </c>
       <c r="H11" s="139" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="I11" s="30" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="J11" s="107" t="s">
-        <v>3620</v>
+        <v>3619</v>
       </c>
       <c r="K11" s="107" t="s">
-        <v>3207</v>
+        <v>3206</v>
       </c>
       <c r="M11" s="36"/>
     </row>
     <row r="12" spans="1:13" s="106" customFormat="1">
       <c r="A12" s="319" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="B12" s="106" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
       <c r="C12" s="22" t="s">
         <v>72</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="E12" s="106" t="s">
         <v>908</v>
@@ -46104,22 +46086,22 @@
         <v>245</v>
       </c>
       <c r="H12" s="30" t="s">
-        <v>3640</v>
+        <v>3639</v>
       </c>
       <c r="I12" s="106" t="s">
-        <v>3482</v>
+        <v>3481</v>
       </c>
       <c r="J12" s="106" t="s">
-        <v>3639</v>
+        <v>3638</v>
       </c>
       <c r="K12" s="107" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="M12" s="151"/>
     </row>
     <row r="13" spans="1:13" s="107" customFormat="1">
       <c r="A13" s="140" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="B13" s="107" t="s">
         <v>2774</v>
@@ -46128,7 +46110,7 @@
         <v>919</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="E13" s="140" t="s">
         <v>2745</v>
@@ -46140,16 +46122,16 @@
         <v>65</v>
       </c>
       <c r="H13" s="30" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="I13" s="30" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
       <c r="J13" s="107" t="s">
-        <v>3217</v>
+        <v>3216</v>
       </c>
       <c r="K13" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="M13" s="36"/>
     </row>
@@ -46176,13 +46158,13 @@
         <v>65</v>
       </c>
       <c r="H14" s="107" t="s">
-        <v>3298</v>
+        <v>3297</v>
       </c>
       <c r="I14" s="411" t="s">
         <v>2262</v>
       </c>
       <c r="J14" s="32" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
       <c r="M14" s="36"/>
     </row>
@@ -46209,16 +46191,16 @@
         <v>66</v>
       </c>
       <c r="H15" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="I15" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="J15" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="K15" s="454" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="M15" s="36"/>
     </row>
@@ -46270,16 +46252,16 @@
         <v>66</v>
       </c>
       <c r="H17" t="s">
-        <v>3504</v>
+        <v>3503</v>
       </c>
       <c r="I17" s="30" t="s">
-        <v>3040</v>
+        <v>3039</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="K17" s="220" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="M17" s="34"/>
     </row>
@@ -46306,16 +46288,16 @@
         <v>66</v>
       </c>
       <c r="H18" s="30" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="I18" t="s">
-        <v>3137</v>
+        <v>3136</v>
       </c>
       <c r="J18" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="K18" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
       <c r="M18" s="36"/>
     </row>
@@ -46330,7 +46312,7 @@
         <v>1689</v>
       </c>
       <c r="D19" s="134" t="s">
-        <v>3373</v>
+        <v>3372</v>
       </c>
       <c r="E19" t="s">
         <v>1692</v>
@@ -46342,16 +46324,16 @@
         <v>66</v>
       </c>
       <c r="H19" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="I19" s="49" t="s">
         <v>2903</v>
       </c>
       <c r="J19" s="220" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="K19" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="M19" s="36"/>
     </row>
@@ -46366,7 +46348,7 @@
         <v>2476</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="E20" s="107" t="s">
         <v>2406</v>
@@ -46378,31 +46360,31 @@
         <v>65</v>
       </c>
       <c r="H20" s="436" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="I20" t="s">
+        <v>2974</v>
+      </c>
+      <c r="J20" s="49" t="s">
         <v>2975</v>
       </c>
-      <c r="J20" s="49" t="s">
-        <v>2976</v>
-      </c>
       <c r="K20" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="M20" s="36"/>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="B21" t="s">
-        <v>3308</v>
+        <v>3307</v>
       </c>
       <c r="C21" s="22" t="s">
         <v>1127</v>
       </c>
       <c r="D21" t="s">
-        <v>3307</v>
+        <v>3306</v>
       </c>
       <c r="E21" s="140" t="s">
         <v>1589</v>
@@ -46414,19 +46396,19 @@
         <v>65</v>
       </c>
       <c r="H21" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="I21" t="s">
+        <v>3314</v>
+      </c>
+      <c r="J21" t="s">
         <v>3315</v>
-      </c>
-      <c r="J21" t="s">
-        <v>3316</v>
       </c>
       <c r="M21" s="36"/>
     </row>
     <row r="22" spans="1:13" s="30" customFormat="1">
       <c r="A22" s="30" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="B22" s="30" t="s">
         <v>2109</v>
@@ -46435,78 +46417,78 @@
         <v>2710</v>
       </c>
       <c r="D22" s="107" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
       <c r="E22" s="30" t="s">
+        <v>3329</v>
+      </c>
+      <c r="F22" s="30" t="s">
         <v>3330</v>
-      </c>
-      <c r="F22" s="30" t="s">
-        <v>3331</v>
       </c>
       <c r="G22" s="32" t="s">
         <v>65</v>
       </c>
       <c r="H22" s="30" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="I22" s="30" t="s">
+        <v>3336</v>
+      </c>
+      <c r="J22" s="30" t="s">
         <v>3337</v>
-      </c>
-      <c r="J22" s="30" t="s">
-        <v>3338</v>
       </c>
       <c r="M22" s="36"/>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="B23" t="s">
-        <v>3352</v>
+        <v>3351</v>
       </c>
       <c r="C23" s="22" t="s">
         <v>1902</v>
       </c>
       <c r="D23" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="E23" s="30" t="s">
+        <v>3329</v>
+      </c>
+      <c r="F23" s="30" t="s">
         <v>3330</v>
-      </c>
-      <c r="F23" s="30" t="s">
-        <v>3331</v>
       </c>
       <c r="G23" t="s">
         <v>66</v>
       </c>
       <c r="H23" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="I23" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="J23" t="s">
-        <v>3434</v>
+        <v>3433</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="30" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="B24" t="s">
-        <v>3664</v>
+        <v>3663</v>
       </c>
       <c r="C24" s="22" t="s">
         <v>1916</v>
       </c>
       <c r="D24" s="455" t="s">
-        <v>3586</v>
+        <v>3585</v>
       </c>
       <c r="E24" s="107" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="F24" s="30" t="s">
-        <v>3663</v>
+        <v>3662</v>
       </c>
       <c r="G24" s="32" t="s">
         <v>270</v>
@@ -46549,7 +46531,7 @@
     </row>
     <row r="31" spans="1:13" s="30" customFormat="1">
       <c r="A31" s="107" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="B31" s="107">
         <v>64403333</v>
@@ -46597,7 +46579,7 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="B33">
         <v>60389752</v>
@@ -46620,7 +46602,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="B34">
         <v>60389752</v>
@@ -46629,13 +46611,13 @@
         <v>2169</v>
       </c>
       <c r="D34" s="32" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="E34" s="30" t="s">
+        <v>3329</v>
+      </c>
+      <c r="F34" s="30" t="s">
         <v>3330</v>
-      </c>
-      <c r="F34" s="30" t="s">
-        <v>3331</v>
       </c>
       <c r="G34" t="s">
         <v>3</v>
@@ -46644,7 +46626,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="B35">
         <v>60389752</v>
@@ -46668,7 +46650,7 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="B36">
         <v>60389752</v>
@@ -46692,7 +46674,7 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="30" t="s">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="B37" s="30">
         <v>64403333</v>
@@ -46717,7 +46699,7 @@
     </row>
     <row r="38" spans="1:13" s="30" customFormat="1">
       <c r="A38" s="30" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="B38" s="30">
         <v>60389752</v>
@@ -46754,10 +46736,10 @@
         <v>2142</v>
       </c>
       <c r="E39" t="s">
+        <v>3329</v>
+      </c>
+      <c r="F39" t="s">
         <v>3330</v>
-      </c>
-      <c r="F39" t="s">
-        <v>3331</v>
       </c>
       <c r="G39" t="s">
         <v>3</v>
@@ -46826,7 +46808,7 @@
         <v>2502</v>
       </c>
       <c r="E45" t="s">
-        <v>3220</v>
+        <v>3219</v>
       </c>
       <c r="F45" s="30" t="s">
         <v>2503</v>
@@ -46835,10 +46817,10 @@
         <v>369</v>
       </c>
       <c r="H45" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="I45" s="30" t="s">
-        <v>3300</v>
+        <v>3299</v>
       </c>
       <c r="J45" s="49" t="s">
         <v>2928</v>
@@ -46896,7 +46878,7 @@
         <v>1106</v>
       </c>
       <c r="D65" s="97" t="s">
-        <v>3584</v>
+        <v>3583</v>
       </c>
       <c r="E65" s="107" t="s">
         <v>1123</v>
@@ -46914,10 +46896,10 @@
         <v>1122</v>
       </c>
       <c r="C66" s="97" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
       <c r="D66" s="97" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="E66" s="97" t="s">
         <v>2404</v>
@@ -46937,24 +46919,24 @@
         <v>2164</v>
       </c>
       <c r="E67" s="107" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="F67" s="30" t="s">
-        <v>3663</v>
+        <v>3662</v>
       </c>
     </row>
     <row r="68" spans="1:38">
       <c r="C68" s="459" t="s">
+        <v>3545</v>
+      </c>
+      <c r="D68" t="s">
         <v>3546</v>
       </c>
-      <c r="D68" t="s">
-        <v>3547</v>
-      </c>
       <c r="E68" s="107" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="F68" s="30" t="s">
-        <v>3663</v>
+        <v>3662</v>
       </c>
       <c r="G68" s="106" t="s">
         <v>720</v>
@@ -46965,13 +46947,13 @@
         <v>1211</v>
       </c>
       <c r="D69" s="97" t="s">
-        <v>3585</v>
+        <v>3584</v>
       </c>
       <c r="E69" s="107" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="F69" s="30" t="s">
-        <v>3663</v>
+        <v>3662</v>
       </c>
       <c r="G69" s="106" t="s">
         <v>720</v>
@@ -47252,7 +47234,7 @@
         <v>1130</v>
       </c>
       <c r="D93" t="s">
-        <v>3326</v>
+        <v>3325</v>
       </c>
       <c r="E93" s="140" t="s">
         <v>1132</v>
@@ -47276,7 +47258,7 @@
         <v>1390</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>3327</v>
+        <v>3326</v>
       </c>
       <c r="E94" s="266" t="s">
         <v>1505</v>
@@ -47330,7 +47312,7 @@
         <v>358</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="105" spans="2:5">
@@ -47556,7 +47538,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
       <c r="C12" s="236"/>
     </row>
@@ -47694,7 +47676,7 @@
       </c>
       <c r="B24" s="87"/>
       <c r="F24" s="2" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -47770,27 +47752,27 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="87" t="s">
-        <v>3385</v>
+        <v>3384</v>
       </c>
       <c r="C40" t="s">
-        <v>3388</v>
+        <v>3387</v>
       </c>
       <c r="F40" s="45"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="89" t="s">
-        <v>3386</v>
+        <v>3385</v>
       </c>
       <c r="C41" t="s">
-        <v>3389</v>
+        <v>3388</v>
       </c>
     </row>
     <row r="42" spans="2:6" ht="15" thickBot="1">
       <c r="B42" s="86" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="C42" t="s">
-        <v>3390</v>
+        <v>3389</v>
       </c>
     </row>
     <row r="43" spans="2:6">
@@ -47953,22 +47935,22 @@
         <v>2033</v>
       </c>
       <c r="E6" s="247" t="s">
+        <v>3252</v>
+      </c>
+      <c r="F6" s="247" t="s">
         <v>3253</v>
-      </c>
-      <c r="F6" s="247" t="s">
-        <v>3254</v>
       </c>
       <c r="G6" s="247" t="s">
         <v>357</v>
       </c>
       <c r="H6" s="247" t="s">
-        <v>3213</v>
+        <v>3212</v>
       </c>
       <c r="I6" s="244" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="J6" s="295" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
       <c r="K6" s="247" t="s">
         <v>475</v>
@@ -47991,19 +47973,19 @@
         <v>1036</v>
       </c>
       <c r="F7" s="265" t="s">
-        <v>3256</v>
+        <v>3255</v>
       </c>
       <c r="G7" s="265" t="s">
         <v>690</v>
       </c>
       <c r="H7" s="295" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="I7" s="295" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="J7" s="295" t="s">
-        <v>3455</v>
+        <v>3454</v>
       </c>
       <c r="K7" s="265" t="s">
         <v>709</v>
@@ -48026,19 +48008,19 @@
         <v>1228</v>
       </c>
       <c r="F8" s="265" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="G8" s="265" t="s">
         <v>250</v>
       </c>
       <c r="H8" s="265" t="s">
-        <v>3602</v>
+        <v>3601</v>
       </c>
       <c r="I8" s="265" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="J8" s="265" t="s">
-        <v>3466</v>
+        <v>3465</v>
       </c>
       <c r="K8" s="259"/>
       <c r="L8" s="259"/>
@@ -48060,7 +48042,7 @@
         <v>2695</v>
       </c>
       <c r="F9" s="263" t="s">
-        <v>3353</v>
+        <v>3352</v>
       </c>
       <c r="G9" s="263" t="s">
         <v>946</v>
@@ -48092,13 +48074,13 @@
         <v>690</v>
       </c>
       <c r="H10" s="264" t="s">
-        <v>3645</v>
+        <v>3644</v>
       </c>
       <c r="I10" s="448" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="J10" s="264" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="K10" s="245" t="s">
         <v>1203</v>
@@ -48109,7 +48091,7 @@
         <v>2500</v>
       </c>
       <c r="B11" s="262" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="C11" s="194" t="s">
         <v>491</v>
@@ -48127,13 +48109,13 @@
         <v>690</v>
       </c>
       <c r="H11" s="215" t="s">
-        <v>3438</v>
+        <v>3437</v>
       </c>
       <c r="I11" s="424" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="J11" s="269" t="s">
-        <v>3551</v>
+        <v>3550</v>
       </c>
       <c r="K11" s="183" t="s">
         <v>1204</v>
@@ -48167,10 +48149,10 @@
     </row>
     <row r="13" spans="1:12" s="223" customFormat="1">
       <c r="A13" s="223" t="s">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="B13" s="223" t="s">
-        <v>3325</v>
+        <v>3324</v>
       </c>
       <c r="C13" s="423" t="s">
         <v>335</v>
@@ -48179,22 +48161,22 @@
         <v>2390</v>
       </c>
       <c r="E13" s="223" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="F13" s="223" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="G13" s="223" t="s">
         <v>690</v>
       </c>
       <c r="H13" s="223" t="s">
+        <v>3025</v>
+      </c>
+      <c r="I13" s="215" t="s">
+        <v>3223</v>
+      </c>
+      <c r="J13" s="223" t="s">
         <v>3026</v>
-      </c>
-      <c r="I13" s="215" t="s">
-        <v>3224</v>
-      </c>
-      <c r="J13" s="223" t="s">
-        <v>3027</v>
       </c>
       <c r="K13" s="223" t="s">
         <v>1317</v>
@@ -48214,7 +48196,7 @@
         <v>1972</v>
       </c>
       <c r="E14" s="216" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="F14" s="216" t="s">
         <v>1433</v>
@@ -48223,13 +48205,13 @@
         <v>690</v>
       </c>
       <c r="H14" s="272" t="s">
-        <v>3456</v>
+        <v>3455</v>
       </c>
       <c r="I14" s="215" t="s">
         <v>2948</v>
       </c>
       <c r="J14" s="262" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="K14" s="183" t="s">
         <v>1205</v>
@@ -48258,13 +48240,13 @@
         <v>690</v>
       </c>
       <c r="H15" s="264" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="I15" s="271" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
       <c r="J15" s="264" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="K15" s="259" t="s">
         <v>1438</v>
@@ -48322,7 +48304,7 @@
     </row>
     <row r="18" spans="1:11" s="259" customFormat="1">
       <c r="A18" s="271" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="B18" s="259" t="s">
         <v>2332</v>
@@ -48331,7 +48313,7 @@
         <v>831</v>
       </c>
       <c r="D18" s="264" t="s">
-        <v>3468</v>
+        <v>3467</v>
       </c>
       <c r="E18" s="264" t="s">
         <v>1788</v>
@@ -48343,13 +48325,13 @@
         <v>690</v>
       </c>
       <c r="H18" s="259" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="I18" s="298" t="s">
-        <v>3287</v>
+        <v>3286</v>
       </c>
       <c r="J18" s="259" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
       <c r="K18" s="264" t="s">
         <v>1765</v>
@@ -48357,7 +48339,7 @@
     </row>
     <row r="19" spans="1:11" s="259" customFormat="1">
       <c r="A19" s="259" t="s">
-        <v>3410</v>
+        <v>3409</v>
       </c>
       <c r="B19" s="259" t="s">
         <v>2377</v>
@@ -48378,13 +48360,13 @@
         <v>690</v>
       </c>
       <c r="H19" s="259" t="s">
-        <v>3107</v>
+        <v>3106</v>
       </c>
       <c r="I19" s="259" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="J19" s="259" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="K19" s="259" t="s">
         <v>1810</v>
@@ -48392,7 +48374,7 @@
     </row>
     <row r="20" spans="1:11" s="264" customFormat="1">
       <c r="A20" s="298" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
       <c r="B20" s="304">
         <v>63609244</v>
@@ -48416,10 +48398,10 @@
         <v>2761</v>
       </c>
       <c r="I20" s="264" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="J20" s="264" t="s">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="K20" s="259" t="s">
         <v>1812</v>
@@ -48462,10 +48444,10 @@
         <v>637</v>
       </c>
       <c r="D22" s="255" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="E22" s="271" t="s">
-        <v>3392</v>
+        <v>3391</v>
       </c>
       <c r="F22" s="271" t="s">
         <v>1710</v>
@@ -48474,13 +48456,13 @@
         <v>250</v>
       </c>
       <c r="H22" s="259" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
       <c r="I22" s="264" t="s">
-        <v>3225</v>
+        <v>3224</v>
       </c>
       <c r="J22" s="264" t="s">
-        <v>3127</v>
+        <v>3126</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="97" customFormat="1">
@@ -48701,7 +48683,7 @@
         <v>840</v>
       </c>
       <c r="D45" s="264" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="E45" s="259" t="s">
         <v>1788</v>
@@ -48904,13 +48886,13 @@
         <v>2770</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="I2" t="s">
-        <v>3432</v>
+        <v>3431</v>
       </c>
       <c r="J2" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="L2" s="36" t="s">
         <v>1173</v>
@@ -48936,7 +48918,7 @@
         <v>298</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>707</v>
@@ -48965,19 +48947,19 @@
         <v>2917</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>323</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>3462</v>
+        <v>3461</v>
       </c>
       <c r="H4" t="s">
-        <v>3017</v>
+        <v>3016</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="J4" t="s">
         <v>2918</v>
@@ -49006,7 +48988,7 @@
         <v>424</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="H5" s="49" t="s">
         <v>2738</v>
@@ -49021,7 +49003,7 @@
     </row>
     <row r="6" spans="1:12" s="4" customFormat="1">
       <c r="A6" s="4" t="s">
-        <v>3514</v>
+        <v>3513</v>
       </c>
       <c r="B6" s="4">
         <v>65436260</v>
@@ -49039,13 +49021,13 @@
         <v>166</v>
       </c>
       <c r="G6" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="I6" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="J6" s="49" t="s">
         <v>2885</v>
@@ -49056,7 +49038,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="4" t="s">
-        <v>3196</v>
+        <v>3195</v>
       </c>
       <c r="B7" s="4">
         <v>69561522</v>
@@ -49065,25 +49047,25 @@
         <v>434</v>
       </c>
       <c r="D7" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="E7" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="F7" t="s">
         <v>151</v>
       </c>
       <c r="G7" t="s">
-        <v>3521</v>
+        <v>3520</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="J7" t="s">
-        <v>3149</v>
+        <v>3148</v>
       </c>
       <c r="L7" s="83" t="s">
         <v>435</v>
@@ -49091,7 +49073,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="4" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2936</v>
@@ -49112,10 +49094,10 @@
         <v>2636</v>
       </c>
       <c r="H8" t="s">
-        <v>3494</v>
+        <v>3493</v>
       </c>
       <c r="I8" s="49" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="J8" s="49" t="s">
         <v>2769</v>
@@ -49142,16 +49124,16 @@
         <v>151</v>
       </c>
       <c r="G9" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="H9" s="220" t="s">
-        <v>3084</v>
+        <v>3083</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>3529</v>
+        <v>3528</v>
       </c>
       <c r="J9" s="220" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -49165,7 +49147,7 @@
         <v>2196</v>
       </c>
       <c r="D10" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="E10" t="s">
         <v>2167</v>
@@ -49174,13 +49156,13 @@
         <v>1818</v>
       </c>
       <c r="G10" t="s">
-        <v>3258</v>
+        <v>3257</v>
       </c>
       <c r="H10" s="49" t="s">
-        <v>3483</v>
+        <v>3482</v>
       </c>
       <c r="I10" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
       <c r="J10" s="49" t="s">
         <v>2831</v>
@@ -49223,7 +49205,7 @@
         <v>1478</v>
       </c>
       <c r="E12" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="F12" t="s">
         <v>614</v>
@@ -49231,7 +49213,7 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="B13">
         <v>64403333</v>
@@ -49254,16 +49236,16 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
       <c r="B14" t="s">
-        <v>3227</v>
+        <v>3226</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>281</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>3226</v>
+        <v>3225</v>
       </c>
       <c r="E14" t="s">
         <v>2136</v>
@@ -49272,16 +49254,16 @@
         <v>1818</v>
       </c>
       <c r="G14" t="s">
-        <v>3635</v>
+        <v>3634</v>
       </c>
       <c r="H14" t="s">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="I14" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="J14" t="s">
-        <v>3324</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -49549,7 +49531,7 @@
     </row>
     <row r="2" spans="1:14" ht="43.15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="C2" s="51"/>
       <c r="D2" s="52" t="s">
@@ -49573,7 +49555,7 @@
         <v>2667</v>
       </c>
       <c r="E4" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -49610,7 +49592,7 @@
         <v>1550</v>
       </c>
       <c r="E9" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
       <c r="F9" t="s">
         <v>1732</v>
@@ -49618,7 +49600,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="B10">
         <v>63000545</v>
@@ -49630,7 +49612,7 @@
         <v>2211</v>
       </c>
       <c r="E10" t="s">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="F10" t="s">
         <v>1681</v>
@@ -49650,7 +49632,7 @@
         <v>2054</v>
       </c>
       <c r="E11" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -49667,7 +49649,7 @@
         <v>2676</v>
       </c>
       <c r="E12" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="F12" t="s">
         <v>1681</v>
@@ -49675,7 +49657,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="B13">
         <v>62271547</v>
@@ -49704,7 +49686,7 @@
         <v>1936</v>
       </c>
       <c r="D14" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="E14" t="s">
         <v>2637</v>
@@ -49715,7 +49697,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="B15">
         <v>62806425</v>
@@ -49744,10 +49726,10 @@
         <v>2723</v>
       </c>
       <c r="D16" s="30" t="s">
+        <v>3014</v>
+      </c>
+      <c r="E16" t="s">
         <v>3015</v>
-      </c>
-      <c r="E16" t="s">
-        <v>3016</v>
       </c>
       <c r="F16" t="s">
         <v>2679</v>
@@ -49764,10 +49746,10 @@
         <v>2927</v>
       </c>
       <c r="D17" s="30" t="s">
+        <v>3028</v>
+      </c>
+      <c r="E17" t="s">
         <v>3029</v>
-      </c>
-      <c r="E17" t="s">
-        <v>3030</v>
       </c>
       <c r="F17" t="s">
         <v>2679</v>
@@ -49790,7 +49772,7 @@
         <v>2727</v>
       </c>
       <c r="E18" t="s">
-        <v>3030</v>
+        <v>3029</v>
       </c>
       <c r="F18" t="s">
         <v>2679</v>
@@ -49810,7 +49792,7 @@
         <v>2767</v>
       </c>
       <c r="E19" t="s">
-        <v>3169</v>
+        <v>3168</v>
       </c>
       <c r="F19" t="s">
         <v>2907</v>
@@ -49833,7 +49815,7 @@
         <v>1512</v>
       </c>
       <c r="F21" t="s">
-        <v>3296</v>
+        <v>3295</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -49881,13 +49863,13 @@
         <v>2653</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>2989</v>
+      </c>
+      <c r="F26" t="s">
         <v>2990</v>
       </c>
-      <c r="F26" t="s">
-        <v>2991</v>
-      </c>
       <c r="G26" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -49904,13 +49886,13 @@
         <v>421</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>2990</v>
+        <v>2989</v>
       </c>
       <c r="F27" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="G27" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -49921,16 +49903,16 @@
         <v>1461</v>
       </c>
       <c r="D29" t="s">
+        <v>3266</v>
+      </c>
+      <c r="E29" t="s">
+        <v>3215</v>
+      </c>
+      <c r="F29" t="s">
+        <v>3004</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>3267</v>
-      </c>
-      <c r="E29" t="s">
-        <v>3216</v>
-      </c>
-      <c r="F29" t="s">
-        <v>3005</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>3268</v>
       </c>
       <c r="H29" t="s">
         <v>407</v>
@@ -49950,10 +49932,10 @@
         <v>2678</v>
       </c>
       <c r="E30" t="s">
+        <v>3003</v>
+      </c>
+      <c r="F30" t="s">
         <v>3004</v>
-      </c>
-      <c r="F30" t="s">
-        <v>3005</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -49967,10 +49949,10 @@
         <v>1557</v>
       </c>
       <c r="D31" t="s">
+        <v>3238</v>
+      </c>
+      <c r="E31" t="s">
         <v>3239</v>
-      </c>
-      <c r="E31" t="s">
-        <v>3240</v>
       </c>
       <c r="F31" t="s">
         <v>1313</v>
@@ -52014,12 +51996,12 @@
     </row>
     <row r="252" spans="1:6" s="420" customFormat="1" ht="21">
       <c r="C252" s="420" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="253" spans="1:6">
       <c r="A253" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="B253">
         <v>64476521</v>
@@ -52031,10 +52013,10 @@
         <v>2241</v>
       </c>
       <c r="E253" t="s">
+        <v>2961</v>
+      </c>
+      <c r="F253" t="s">
         <v>2962</v>
-      </c>
-      <c r="F253" t="s">
-        <v>2963</v>
       </c>
     </row>
     <row r="254" spans="1:6">
@@ -52051,10 +52033,10 @@
         <v>2920</v>
       </c>
       <c r="E254" t="s">
+        <v>2961</v>
+      </c>
+      <c r="F254" t="s">
         <v>2962</v>
-      </c>
-      <c r="F254" t="s">
-        <v>2963</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -52071,15 +52053,15 @@
         <v>2622</v>
       </c>
       <c r="E255" t="s">
+        <v>2961</v>
+      </c>
+      <c r="F255" t="s">
         <v>2962</v>
-      </c>
-      <c r="F255" t="s">
-        <v>2963</v>
       </c>
     </row>
     <row r="256" spans="1:6">
       <c r="A256" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="B256">
         <v>61915064</v>
@@ -56828,7 +56810,7 @@
         <v>2667</v>
       </c>
       <c r="E537" s="76" t="s">
-        <v>3141</v>
+        <v>3140</v>
       </c>
       <c r="F537" s="76"/>
       <c r="G537" s="76"/>

--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dc549f2659ed9bd7/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63146" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69BF60A1-19EB-4B87-A13A-86F449BEAA3E}"/>
+  <xr:revisionPtr revIDLastSave="63148" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E7A2319-CC9D-474C-8595-6F1B9AD5DF3E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10104,9 +10104,6 @@
     <t>17 de noviembre</t>
   </si>
   <si>
-    <t>67376825 1 pantalla hasta el 18 de septiembre (Luis)</t>
-  </si>
-  <si>
     <t>66028988 1 pantalla hasta el 04 de octubre (koni)</t>
   </si>
   <si>
@@ -12283,6 +12280,9 @@
   </si>
   <si>
     <t>N006 1 pantalla hasta el 23 de octubre 230926-0106f</t>
+  </si>
+  <si>
+    <t>N005 1 pantalla hasta el 23 de octubre 230926-0129h</t>
   </si>
 </sst>
 </file>
@@ -30232,7 +30232,7 @@
   <sheetData>
     <row r="1" spans="1:11" s="30" customFormat="1">
       <c r="A1" s="30" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="B1" s="30">
         <v>60389752</v>
@@ -30244,7 +30244,7 @@
         <v>2007</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="F1" s="30" t="s">
         <v>2073</v>
@@ -30264,7 +30264,7 @@
         <v>2119</v>
       </c>
       <c r="D2" s="148" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="148" customFormat="1">
@@ -30283,7 +30283,7 @@
     </row>
     <row r="4" spans="1:11" s="30" customFormat="1">
       <c r="A4" s="30" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="B4" s="30">
         <v>60389752</v>
@@ -30295,7 +30295,7 @@
         <v>2005</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>3627</v>
+        <v>3626</v>
       </c>
       <c r="F4" s="30" t="s">
         <v>2073</v>
@@ -30315,7 +30315,7 @@
         <v>2133</v>
       </c>
       <c r="D5" s="148" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="148" customFormat="1">
@@ -30346,7 +30346,7 @@
         <v>2828</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="F7" s="30" t="s">
         <v>2078</v>
@@ -30366,12 +30366,12 @@
         <v>2234</v>
       </c>
       <c r="D8" s="148" t="s">
-        <v>3478</v>
+        <v>3477</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="148" customFormat="1">
       <c r="A9" s="148" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="B9" s="148" t="s">
         <v>1200</v>
@@ -30388,7 +30388,7 @@
     </row>
     <row r="10" spans="1:11" s="422" customFormat="1">
       <c r="A10" s="422" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B10" s="422">
         <v>60389752</v>
@@ -30413,7 +30413,7 @@
     <row r="12" spans="1:11" s="369" customFormat="1"/>
     <row r="13" spans="1:11" s="30" customFormat="1">
       <c r="A13" s="30" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="B13" s="30">
         <v>69184177</v>
@@ -30422,10 +30422,10 @@
         <v>1771</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="F13" s="30" t="s">
         <v>2137</v>
@@ -30437,7 +30437,7 @@
     </row>
     <row r="14" spans="1:11" s="148" customFormat="1">
       <c r="A14" s="225" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="B14" s="225" t="s">
         <v>1671</v>
@@ -30451,7 +30451,7 @@
     </row>
     <row r="15" spans="1:11" s="148" customFormat="1">
       <c r="A15" s="225" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="B15" s="416">
         <v>62439069</v>
@@ -30465,7 +30465,7 @@
     </row>
     <row r="16" spans="1:11" s="32" customFormat="1">
       <c r="A16" s="30" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="B16" s="284" t="s">
         <v>2190</v>
@@ -30474,10 +30474,10 @@
         <v>1523</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="F16" s="32" t="s">
         <v>1524</v>
@@ -30486,21 +30486,21 @@
         <v>198</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="I16" s="32" t="s">
-        <v>3206</v>
+        <v>3205</v>
       </c>
       <c r="J16" s="32" t="s">
+        <v>3133</v>
+      </c>
+      <c r="K16" s="30" t="s">
         <v>3134</v>
-      </c>
-      <c r="K16" s="30" t="s">
-        <v>3135</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="164" customFormat="1">
       <c r="A17" s="252" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="B17" s="252" t="s">
         <v>1391</v>
@@ -30517,7 +30517,7 @@
     </row>
     <row r="18" spans="1:11" s="164" customFormat="1">
       <c r="A18" s="252" t="s">
-        <v>3523</v>
+        <v>3522</v>
       </c>
       <c r="B18" s="252">
         <v>64341760</v>
@@ -30543,10 +30543,10 @@
         <v>1488</v>
       </c>
       <c r="D19" s="145" t="s">
-        <v>3423</v>
+        <v>3422</v>
       </c>
       <c r="E19" s="145" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="F19" s="145" t="s">
         <v>1358</v>
@@ -30578,7 +30578,7 @@
     </row>
     <row r="21" spans="1:11" s="297" customFormat="1">
       <c r="A21" s="252" t="s">
-        <v>3432</v>
+        <v>3431</v>
       </c>
       <c r="B21" s="252">
         <v>62169673</v>
@@ -30587,7 +30587,7 @@
         <v>1682</v>
       </c>
       <c r="D21" s="164" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
       <c r="E21" s="164" t="s">
         <v>1683</v>
@@ -30607,7 +30607,7 @@
         <v>2116</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="F22" s="30" t="s">
         <v>2072</v>
@@ -30618,7 +30618,7 @@
     </row>
     <row r="23" spans="1:11" s="148" customFormat="1">
       <c r="A23" s="225" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B23" s="148">
         <v>64858241</v>
@@ -30632,7 +30632,7 @@
     </row>
     <row r="24" spans="1:11" s="148" customFormat="1">
       <c r="A24" s="149" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B24" s="149">
         <v>68934853</v>
@@ -30641,7 +30641,7 @@
         <v>2112</v>
       </c>
       <c r="D24" s="148" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="30" customFormat="1">
@@ -30658,7 +30658,7 @@
         <v>1520</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>2958</v>
+        <v>2957</v>
       </c>
       <c r="F25" s="30" t="s">
         <v>1358</v>
@@ -30706,7 +30706,7 @@
     </row>
     <row r="28" spans="1:11" s="30" customFormat="1">
       <c r="A28" s="30" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="B28" s="30">
         <v>60389752</v>
@@ -30718,7 +30718,7 @@
         <v>2002</v>
       </c>
       <c r="E28" s="30" t="s">
-        <v>3178</v>
+        <v>3177</v>
       </c>
       <c r="F28" s="303" t="s">
         <v>2146</v>
@@ -30743,7 +30743,7 @@
     </row>
     <row r="30" spans="1:11" s="164" customFormat="1">
       <c r="A30" s="164" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="B30" s="164">
         <v>62782770</v>
@@ -30757,19 +30757,19 @@
     </row>
     <row r="31" spans="1:11" s="30" customFormat="1">
       <c r="A31" s="461" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="B31" s="461" t="s">
-        <v>3667</v>
+        <v>3666</v>
       </c>
       <c r="C31" s="251" t="s">
         <v>1896</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
       <c r="E31" s="30" t="s">
-        <v>3578</v>
+        <v>3577</v>
       </c>
       <c r="F31" s="30" t="s">
         <v>2023</v>
@@ -30778,16 +30778,16 @@
         <v>198</v>
       </c>
       <c r="H31" s="145" t="s">
-        <v>3669</v>
+        <v>3668</v>
       </c>
       <c r="I31" s="192" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="J31" s="458" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="K31" s="30" t="s">
-        <v>3456</v>
+        <v>3455</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="163" customFormat="1">
@@ -30833,7 +30833,7 @@
         <v>2085</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="F34" s="30" t="s">
         <v>2076</v>
@@ -30853,7 +30853,7 @@
         <v>1979</v>
       </c>
       <c r="D35" s="148" t="s">
-        <v>3504</v>
+        <v>3503</v>
       </c>
       <c r="E35" s="148" t="s">
         <v>1981</v>
@@ -30875,7 +30875,7 @@
     </row>
     <row r="37" spans="1:11" s="30" customFormat="1">
       <c r="A37" s="30" t="s">
-        <v>3523</v>
+        <v>3522</v>
       </c>
       <c r="B37" s="30" t="s">
         <v>2704</v>
@@ -30884,10 +30884,10 @@
         <v>2000</v>
       </c>
       <c r="D37" s="30" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="E37" s="30" t="s">
-        <v>3554</v>
+        <v>3553</v>
       </c>
       <c r="F37" s="30" t="s">
         <v>2066</v>
@@ -30896,16 +30896,16 @@
         <v>198</v>
       </c>
       <c r="H37" s="145" t="s">
-        <v>3561</v>
+        <v>3560</v>
       </c>
       <c r="I37" s="30" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="J37" s="30" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
       <c r="K37" s="30" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="147" customFormat="1">
@@ -30942,16 +30942,16 @@
         <v>2469</v>
       </c>
       <c r="B40" s="32" t="s">
-        <v>3086</v>
+        <v>3085</v>
       </c>
       <c r="C40" s="251" t="s">
         <v>1658</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="E40" s="30" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="F40" s="30" t="s">
         <v>2081</v>
@@ -30960,21 +30960,21 @@
         <v>198</v>
       </c>
       <c r="H40" s="30" t="s">
-        <v>3551</v>
+        <v>3550</v>
       </c>
       <c r="I40" s="32" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="J40" s="32" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="K40" s="145" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="163" customFormat="1">
       <c r="A41" s="163" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="B41" s="163">
         <v>68381893</v>
@@ -31006,7 +31006,7 @@
     </row>
     <row r="43" spans="1:11" s="30" customFormat="1">
       <c r="A43" s="30" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B43" s="30">
         <v>60389752</v>
@@ -31018,7 +31018,7 @@
         <v>2027</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="F43" s="30" t="s">
         <v>2113</v>
@@ -31029,7 +31029,7 @@
     </row>
     <row r="44" spans="1:11" s="164" customFormat="1">
       <c r="A44" s="164" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="B44" s="164">
         <v>68381893</v>
@@ -31046,7 +31046,7 @@
     </row>
     <row r="45" spans="1:11" s="163" customFormat="1">
       <c r="A45" s="163" t="s">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="B45" s="163">
         <v>64079861</v>
@@ -31075,7 +31075,7 @@
         <v>2822</v>
       </c>
       <c r="E46" s="30" t="s">
-        <v>3264</v>
+        <v>3263</v>
       </c>
       <c r="F46" s="30" t="s">
         <v>2097</v>
@@ -31087,7 +31087,7 @@
     </row>
     <row r="47" spans="1:11" s="164" customFormat="1">
       <c r="A47" s="164" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B47" s="164">
         <v>63183787</v>
@@ -31121,16 +31121,16 @@
         <v>1495</v>
       </c>
       <c r="B49" s="30" t="s">
-        <v>3310</v>
+        <v>3309</v>
       </c>
       <c r="C49" s="134" t="s">
         <v>1991</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="E49" s="30" t="s">
-        <v>3458</v>
+        <v>3457</v>
       </c>
       <c r="F49" s="30" t="s">
         <v>2084</v>
@@ -31139,16 +31139,16 @@
         <v>198</v>
       </c>
       <c r="H49" s="30" t="s">
-        <v>3040</v>
+        <v>3039</v>
       </c>
       <c r="I49" s="30" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="J49" s="30" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="K49" s="32" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
     </row>
     <row r="50" spans="1:12" s="164" customFormat="1">
@@ -31176,7 +31176,7 @@
         <v>1999</v>
       </c>
       <c r="D51" s="164" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
     </row>
     <row r="52" spans="1:12" s="139" customFormat="1">
@@ -31193,7 +31193,7 @@
         <v>2834</v>
       </c>
       <c r="E52" s="139" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="F52" s="139" t="s">
         <v>2082</v>
@@ -31202,16 +31202,16 @@
         <v>198</v>
       </c>
       <c r="H52" s="140" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="I52" s="140" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="J52" s="30" t="s">
-        <v>3166</v>
+        <v>3165</v>
       </c>
       <c r="K52" s="269" t="s">
-        <v>3618</v>
+        <v>3617</v>
       </c>
     </row>
     <row r="53" spans="1:12" s="164" customFormat="1">
@@ -31252,7 +31252,7 @@
     </row>
     <row r="55" spans="1:12" s="30" customFormat="1">
       <c r="A55" s="30" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="B55" s="30">
         <v>61130088</v>
@@ -31264,7 +31264,7 @@
         <v>1995</v>
       </c>
       <c r="E55" s="30" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="F55" s="30" t="s">
         <v>2098</v>
@@ -31281,10 +31281,10 @@
         <v>60433915</v>
       </c>
       <c r="C56" s="400" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
       <c r="D56" s="370" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="E56" s="164"/>
     </row>
@@ -31293,19 +31293,19 @@
         <v>2469</v>
       </c>
       <c r="B57" s="163" t="s">
-        <v>3073</v>
+        <v>3072</v>
       </c>
       <c r="C57" s="400" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="D57" s="370" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="E57" s="164"/>
     </row>
     <row r="58" spans="1:12" s="30" customFormat="1">
       <c r="A58" s="30" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B58" s="412" t="s">
         <v>2064</v>
@@ -31317,7 +31317,7 @@
         <v>2768</v>
       </c>
       <c r="E58" s="30" t="s">
-        <v>3605</v>
+        <v>3604</v>
       </c>
       <c r="F58" s="30" t="s">
         <v>2110</v>
@@ -31326,30 +31326,30 @@
         <v>198</v>
       </c>
       <c r="H58" s="30" t="s">
-        <v>3211</v>
+        <v>3210</v>
       </c>
       <c r="I58" s="30" t="s">
-        <v>3084</v>
+        <v>3083</v>
       </c>
       <c r="J58" s="30" t="s">
-        <v>3170</v>
+        <v>3169</v>
       </c>
       <c r="K58" s="30" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" s="147" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="B59" s="147">
         <v>67539485</v>
       </c>
       <c r="C59" s="399" t="s">
-        <v>3603</v>
+        <v>3602</v>
       </c>
       <c r="D59" s="371" t="s">
-        <v>3606</v>
+        <v>3605</v>
       </c>
       <c r="E59" s="148"/>
       <c r="F59" s="147"/>
@@ -31362,16 +31362,16 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" s="147" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="B60" s="147">
         <v>68853797</v>
       </c>
       <c r="C60" s="399" t="s">
-        <v>3604</v>
+        <v>3603</v>
       </c>
       <c r="D60" s="371" t="s">
-        <v>3607</v>
+        <v>3606</v>
       </c>
       <c r="E60" s="147"/>
       <c r="F60" s="147"/>
@@ -31387,7 +31387,7 @@
         <v>158</v>
       </c>
       <c r="B61" s="30" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="C61" s="134" t="s">
         <v>2065</v>
@@ -31396,7 +31396,7 @@
         <v>2825</v>
       </c>
       <c r="E61" s="30" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
       <c r="F61" s="30" t="s">
         <v>2066</v>
@@ -31405,21 +31405,21 @@
         <v>198</v>
       </c>
       <c r="H61" s="30" t="s">
-        <v>3328</v>
+        <v>3327</v>
       </c>
       <c r="I61" s="30" t="s">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="J61" s="30" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="K61" s="30" t="s">
-        <v>3287</v>
+        <v>3286</v>
       </c>
     </row>
     <row r="62" spans="1:12" s="147" customFormat="1">
       <c r="A62" s="147" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="B62" s="147">
         <v>60196388</v>
@@ -31428,7 +31428,7 @@
         <v>1467</v>
       </c>
       <c r="D62" s="371" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="E62" s="148" t="s">
         <v>1377</v>
@@ -31436,7 +31436,7 @@
     </row>
     <row r="63" spans="1:12" s="163" customFormat="1">
       <c r="A63" s="163" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="B63" s="163">
         <v>62960567</v>
@@ -31445,13 +31445,13 @@
         <v>2050</v>
       </c>
       <c r="D63" s="370" t="s">
-        <v>3017</v>
+        <v>3016</v>
       </c>
       <c r="E63" s="164"/>
     </row>
     <row r="64" spans="1:12" s="30" customFormat="1">
       <c r="A64" s="32" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B64" s="32" t="s">
         <v>2117</v>
@@ -31460,10 +31460,10 @@
         <v>1657</v>
       </c>
       <c r="D64" s="30" t="s">
-        <v>3205</v>
+        <v>3204</v>
       </c>
       <c r="E64" s="30" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="F64" s="30" t="s">
         <v>2083</v>
@@ -31472,16 +31472,16 @@
         <v>198</v>
       </c>
       <c r="H64" s="32" t="s">
-        <v>3300</v>
+        <v>3299</v>
       </c>
       <c r="I64" s="32" t="s">
-        <v>3366</v>
+        <v>3365</v>
       </c>
       <c r="J64" s="30" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="K64" s="30" t="s">
-        <v>3085</v>
+        <v>3084</v>
       </c>
     </row>
     <row r="65" spans="1:11" s="164" customFormat="1">
@@ -31520,7 +31520,7 @@
     </row>
     <row r="67" spans="1:11" s="30" customFormat="1">
       <c r="A67" s="253" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="B67" s="284" t="s">
         <v>1904</v>
@@ -31532,7 +31532,7 @@
         <v>2929</v>
       </c>
       <c r="E67" s="30" t="s">
-        <v>3508</v>
+        <v>3507</v>
       </c>
       <c r="F67" s="30" t="s">
         <v>2087</v>
@@ -31541,21 +31541,21 @@
         <v>198</v>
       </c>
       <c r="H67" s="30" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
       <c r="I67" s="30" t="s">
-        <v>3354</v>
+        <v>3353</v>
       </c>
       <c r="J67" s="30" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="K67" s="145" t="s">
-        <v>3670</v>
+        <v>3669</v>
       </c>
     </row>
     <row r="68" spans="1:11" s="147" customFormat="1">
       <c r="A68" s="147" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="B68" s="147">
         <v>68741448</v>
@@ -31564,13 +31564,13 @@
         <v>1872</v>
       </c>
       <c r="D68" s="371" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="E68" s="148"/>
     </row>
     <row r="69" spans="1:11" s="148" customFormat="1">
       <c r="A69" s="225" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="B69" s="148">
         <v>63018763</v>
@@ -31579,7 +31579,7 @@
         <v>2086</v>
       </c>
       <c r="D69" s="148" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="70" spans="1:11" s="30" customFormat="1">
@@ -31587,16 +31587,16 @@
         <v>467</v>
       </c>
       <c r="B70" s="32" t="s">
-        <v>3298</v>
+        <v>3297</v>
       </c>
       <c r="C70" s="251" t="s">
         <v>1660</v>
       </c>
       <c r="D70" s="30" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
       <c r="E70" s="30" t="s">
-        <v>3127</v>
+        <v>3126</v>
       </c>
       <c r="F70" s="30" t="s">
         <v>2124</v>
@@ -31605,13 +31605,13 @@
         <v>198</v>
       </c>
       <c r="H70" s="32" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="I70" s="145" t="s">
-        <v>3562</v>
+        <v>3561</v>
       </c>
       <c r="J70" s="30" t="s">
-        <v>3611</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="71" spans="1:11" s="164" customFormat="1">
@@ -31630,7 +31630,7 @@
     </row>
     <row r="72" spans="1:11" s="163" customFormat="1">
       <c r="A72" s="268" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="B72" s="268" t="s">
         <v>1449</v>
@@ -31645,7 +31645,7 @@
     </row>
     <row r="73" spans="1:11" s="30" customFormat="1">
       <c r="A73" s="30" t="s">
-        <v>3207</v>
+        <v>3206</v>
       </c>
       <c r="B73" s="30">
         <v>60389752</v>
@@ -31657,7 +31657,7 @@
         <v>2779</v>
       </c>
       <c r="E73" s="30" t="s">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="F73" s="30" t="s">
         <v>2022</v>
@@ -31668,7 +31668,7 @@
     </row>
     <row r="74" spans="1:11" s="147" customFormat="1">
       <c r="A74" s="147" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="B74" s="147">
         <v>64226974</v>
@@ -31692,7 +31692,7 @@
         <v>1941</v>
       </c>
       <c r="D75" s="148" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="E75" s="148"/>
     </row>
@@ -31710,7 +31710,7 @@
         <v>2900</v>
       </c>
       <c r="E76" s="30" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="F76" s="30" t="s">
         <v>2097</v>
@@ -31719,16 +31719,16 @@
         <v>198</v>
       </c>
       <c r="H76" s="30" t="s">
-        <v>3459</v>
+        <v>3458</v>
       </c>
       <c r="I76" s="30" t="s">
-        <v>3505</v>
+        <v>3504</v>
       </c>
       <c r="J76" s="30" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="K76" s="145" t="s">
-        <v>3671</v>
+        <v>3670</v>
       </c>
     </row>
     <row r="77" spans="1:11" s="152" customFormat="1">
@@ -31753,7 +31753,7 @@
         <v>2914</v>
       </c>
       <c r="E79" s="30" t="s">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="F79" s="30" t="s">
         <v>2077</v>
@@ -31765,13 +31765,13 @@
         <v>2926</v>
       </c>
       <c r="I79" s="32" t="s">
-        <v>3081</v>
+        <v>3080</v>
       </c>
       <c r="J79" s="30" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="K79" s="30" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="80" spans="1:11" s="147" customFormat="1">
@@ -31791,7 +31791,7 @@
     </row>
     <row r="81" spans="1:11" s="147" customFormat="1">
       <c r="A81" s="149" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B81" s="147">
         <v>64720128</v>
@@ -31808,10 +31808,10 @@
     </row>
     <row r="82" spans="1:11" s="30" customFormat="1">
       <c r="A82" s="145" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="B82" s="30" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="C82" s="22" t="s">
         <v>1897</v>
@@ -31829,16 +31829,16 @@
         <v>198</v>
       </c>
       <c r="H82" s="30" t="s">
-        <v>3373</v>
+        <v>3372</v>
       </c>
       <c r="I82" s="145" t="s">
-        <v>3672</v>
+        <v>3671</v>
       </c>
       <c r="J82" s="30" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
       <c r="K82" s="30" t="s">
-        <v>3436</v>
+        <v>3435</v>
       </c>
     </row>
     <row r="83" spans="1:11" s="148" customFormat="1">
@@ -31846,13 +31846,13 @@
         <v>1513</v>
       </c>
       <c r="B83" s="225" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="C83" s="398" t="s">
         <v>1954</v>
       </c>
       <c r="D83" s="148" t="s">
-        <v>3555</v>
+        <v>3554</v>
       </c>
     </row>
     <row r="84" spans="1:11" s="280" customFormat="1">
@@ -31880,7 +31880,7 @@
         <v>693</v>
       </c>
       <c r="D85" s="30" t="s">
-        <v>3222</v>
+        <v>3221</v>
       </c>
       <c r="E85" s="30" t="s">
         <v>1787</v>
@@ -31892,16 +31892,16 @@
         <v>493</v>
       </c>
       <c r="H85" s="30" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="I85" s="32" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="J85" s="30" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="K85" s="215" t="s">
-        <v>3531</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="86" spans="1:11" s="147" customFormat="1">
@@ -31924,7 +31924,7 @@
     </row>
     <row r="87" spans="1:11" s="147" customFormat="1">
       <c r="A87" s="147" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B87" s="147" t="s">
         <v>909</v>
@@ -31942,10 +31942,10 @@
     </row>
     <row r="88" spans="1:11" s="30" customFormat="1">
       <c r="A88" s="30" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
       <c r="B88" s="30" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
       <c r="C88" s="153" t="s">
         <v>694</v>
@@ -31963,16 +31963,16 @@
         <v>1521</v>
       </c>
       <c r="H88" s="30" t="s">
-        <v>3598</v>
+        <v>3597</v>
       </c>
       <c r="I88" s="145" t="s">
-        <v>3563</v>
+        <v>3562</v>
       </c>
       <c r="J88" s="437" t="s">
-        <v>3673</v>
+        <v>3672</v>
       </c>
       <c r="K88" s="30" t="s">
-        <v>3573</v>
+        <v>3572</v>
       </c>
     </row>
     <row r="89" spans="1:11" s="147" customFormat="1">
@@ -31995,7 +31995,7 @@
     </row>
     <row r="90" spans="1:11" s="148" customFormat="1">
       <c r="A90" s="225" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B90" s="148">
         <v>67381873</v>
@@ -32013,7 +32013,7 @@
     </row>
     <row r="91" spans="1:11" s="106" customFormat="1">
       <c r="A91" s="249" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="B91" s="32" t="s">
         <v>1397</v>
@@ -32022,7 +32022,7 @@
         <v>46</v>
       </c>
       <c r="D91" s="106" t="s">
-        <v>3088</v>
+        <v>3087</v>
       </c>
       <c r="E91" s="106" t="s">
         <v>1120</v>
@@ -32034,16 +32034,16 @@
         <v>66</v>
       </c>
       <c r="H91" s="30" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
       <c r="I91" s="31" t="s">
-        <v>3581</v>
-      </c>
-      <c r="J91" s="431" t="s">
-        <v>2947</v>
+        <v>3580</v>
+      </c>
+      <c r="J91" s="437" t="s">
+        <v>3673</v>
       </c>
       <c r="K91" s="30" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="406" customFormat="1">
@@ -32074,7 +32074,7 @@
         <v>1714</v>
       </c>
       <c r="D93" s="148" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
     </row>
     <row r="94" spans="1:11" s="32" customFormat="1">
@@ -32091,7 +32091,7 @@
         <v>1359</v>
       </c>
       <c r="E94" s="32" t="s">
-        <v>3340</v>
+        <v>3339</v>
       </c>
       <c r="F94" s="32" t="s">
         <v>1360</v>
@@ -32103,7 +32103,7 @@
     </row>
     <row r="95" spans="1:11" s="148" customFormat="1">
       <c r="A95" s="148" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="B95" s="148" t="s">
         <v>2623</v>
@@ -32120,7 +32120,7 @@
     </row>
     <row r="96" spans="1:11" s="148" customFormat="1">
       <c r="A96" s="148" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="B96" s="148">
         <v>65633205</v>
@@ -32129,7 +32129,7 @@
         <v>1376</v>
       </c>
       <c r="D96" s="148" t="s">
-        <v>3427</v>
+        <v>3426</v>
       </c>
       <c r="E96" s="148" t="s">
         <v>1375</v>
@@ -32137,7 +32137,7 @@
     </row>
     <row r="97" spans="1:13" s="30" customFormat="1">
       <c r="A97" s="460" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="B97" s="30" t="s">
         <v>2881</v>
@@ -32158,16 +32158,16 @@
         <v>198</v>
       </c>
       <c r="H97" s="32" t="s">
-        <v>3380</v>
+        <v>3379</v>
       </c>
       <c r="I97" s="30" t="s">
-        <v>3535</v>
+        <v>3534</v>
       </c>
       <c r="J97" s="30" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="K97" s="429" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
     </row>
     <row r="98" spans="1:13" s="388" customFormat="1">
@@ -32180,19 +32180,19 @@
     </row>
     <row r="100" spans="1:13" s="30" customFormat="1">
       <c r="A100" s="30" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="B100" s="30" t="s">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="C100" s="251" t="s">
         <v>2807</v>
       </c>
       <c r="D100" s="30" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="E100" s="30" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="F100" s="30" t="s">
         <v>1898</v>
@@ -32201,16 +32201,16 @@
         <v>198</v>
       </c>
       <c r="H100" s="30" t="s">
-        <v>3375</v>
+        <v>3374</v>
       </c>
       <c r="I100" s="30" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="J100" s="30" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="K100" s="30" t="s">
-        <v>3462</v>
+        <v>3461</v>
       </c>
     </row>
     <row r="101" spans="1:13" s="388" customFormat="1">
@@ -32223,19 +32223,19 @@
     </row>
     <row r="103" spans="1:13" s="30" customFormat="1">
       <c r="A103" s="30" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B103" s="30" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
       <c r="C103" s="251" t="s">
         <v>2847</v>
       </c>
       <c r="D103" s="30" t="s">
+        <v>3102</v>
+      </c>
+      <c r="E103" s="30" t="s">
         <v>3103</v>
-      </c>
-      <c r="E103" s="30" t="s">
-        <v>3104</v>
       </c>
       <c r="F103" s="30" t="s">
         <v>1898</v>
@@ -32244,16 +32244,16 @@
         <v>198</v>
       </c>
       <c r="H103" s="30" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="I103" s="30" t="s">
-        <v>3177</v>
+        <v>3176</v>
       </c>
       <c r="J103" s="30" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="K103" s="30" t="s">
-        <v>3129</v>
+        <v>3128</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -32297,13 +32297,13 @@
         <v>2846</v>
       </c>
       <c r="D106" s="30" t="s">
+        <v>2953</v>
+      </c>
+      <c r="E106" s="453" t="s">
+        <v>2955</v>
+      </c>
+      <c r="F106" s="30" t="s">
         <v>2954</v>
-      </c>
-      <c r="E106" s="453" t="s">
-        <v>2956</v>
-      </c>
-      <c r="F106" s="30" t="s">
-        <v>2955</v>
       </c>
       <c r="G106" s="30" t="s">
         <v>59</v>
@@ -32355,7 +32355,7 @@
         <v>1977</v>
       </c>
       <c r="E127" s="30" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="F127" t="s">
         <v>1975</v>
@@ -32375,7 +32375,7 @@
         <v>1947</v>
       </c>
       <c r="E128" s="30" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -32389,15 +32389,15 @@
         <v>2692</v>
       </c>
       <c r="D129" s="373" t="s">
-        <v>3100</v>
+        <v>3099</v>
       </c>
       <c r="E129" s="30" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="4" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B130">
         <v>67046608</v>
@@ -32409,7 +32409,7 @@
         <v>2573</v>
       </c>
       <c r="E130" s="30" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -32426,7 +32426,7 @@
         <v>1953</v>
       </c>
       <c r="E131" s="30" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
     </row>
     <row r="133" spans="1:6" s="121" customFormat="1" ht="23.5">
@@ -32448,7 +32448,7 @@
         <v>2334</v>
       </c>
       <c r="E134" s="30" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
       <c r="F134" t="s">
         <v>1336</v>
@@ -32468,7 +32468,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="B139">
         <v>64720128</v>
@@ -32497,7 +32497,7 @@
         <v>1964</v>
       </c>
       <c r="D140" s="373" t="s">
-        <v>3074</v>
+        <v>3073</v>
       </c>
       <c r="E140" s="30" t="s">
         <v>1963</v>
@@ -32522,7 +32522,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="C143" s="1" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -32566,7 +32566,7 @@
         <v>2339</v>
       </c>
       <c r="E153" s="30" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -32574,21 +32574,21 @@
         <v>1495</v>
       </c>
       <c r="B154" t="s">
-        <v>3270</v>
+        <v>3269</v>
       </c>
       <c r="C154" t="s">
         <v>2216</v>
       </c>
       <c r="D154" s="373" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="E154" s="30" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B155">
         <v>60183566</v>
@@ -32600,12 +32600,12 @@
         <v>2574</v>
       </c>
       <c r="E155" s="30" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="B156">
         <v>63145336</v>
@@ -32614,10 +32614,10 @@
         <v>2225</v>
       </c>
       <c r="D156" s="373" t="s">
-        <v>3558</v>
+        <v>3557</v>
       </c>
       <c r="E156" s="30" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -32634,12 +32634,12 @@
         <v>2470</v>
       </c>
       <c r="E157" s="30" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="B158">
         <v>64982293</v>
@@ -32648,10 +32648,10 @@
         <v>2227</v>
       </c>
       <c r="D158" s="373" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
       <c r="E158" s="30" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -32665,15 +32665,15 @@
         <v>2488</v>
       </c>
       <c r="D159" s="373" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="E159" s="30" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="B160">
         <v>65133588</v>
@@ -32685,12 +32685,12 @@
         <v>2489</v>
       </c>
       <c r="E160" s="30" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="4" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>1134</v>
@@ -32699,10 +32699,10 @@
         <v>2575</v>
       </c>
       <c r="D161" s="373" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="E161" s="30" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -32716,32 +32716,32 @@
         <v>2491</v>
       </c>
       <c r="D162" s="373" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="E162" s="30" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="B163">
         <v>67570116</v>
       </c>
       <c r="C163" t="s">
-        <v>3560</v>
+        <v>3559</v>
       </c>
       <c r="D163" s="373" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
       <c r="E163" s="30" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="4" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>2160</v>
@@ -32753,12 +32753,12 @@
         <v>2471</v>
       </c>
       <c r="E164" s="30" t="s">
-        <v>3353</v>
+        <v>3352</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="B165">
         <v>66315726</v>
@@ -32770,12 +32770,12 @@
         <v>2263</v>
       </c>
       <c r="E165" s="30" t="s">
-        <v>3353</v>
+        <v>3352</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="B166">
         <v>64568369</v>
@@ -32787,24 +32787,24 @@
         <v>2263</v>
       </c>
       <c r="E166" s="30" t="s">
-        <v>3353</v>
+        <v>3352</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="B167">
         <v>68818154</v>
       </c>
       <c r="C167" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
       <c r="D167" s="373" t="s">
         <v>2576</v>
       </c>
       <c r="E167" s="30" t="s">
-        <v>3353</v>
+        <v>3352</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -32818,10 +32818,10 @@
         <v>2694</v>
       </c>
       <c r="D168" s="373" t="s">
-        <v>3130</v>
+        <v>3129</v>
       </c>
       <c r="E168" s="30" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -32838,7 +32838,7 @@
         <v>2728</v>
       </c>
       <c r="E169" s="30" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -32855,7 +32855,7 @@
         <v>2468</v>
       </c>
       <c r="E170" s="30" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -32872,7 +32872,7 @@
         <v>2301</v>
       </c>
       <c r="E171" s="30" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -32883,10 +32883,10 @@
         <v>2313</v>
       </c>
       <c r="D172" s="373" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
       <c r="E172" s="30" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -32900,10 +32900,10 @@
         <v>2314</v>
       </c>
       <c r="D173" s="373" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="E173" s="30" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -32917,15 +32917,15 @@
         <v>2315</v>
       </c>
       <c r="D174" s="373" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="E174" s="30" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="B175">
         <v>67178677</v>
@@ -32934,15 +32934,15 @@
         <v>2730</v>
       </c>
       <c r="D175" s="373" t="s">
-        <v>3559</v>
+        <v>3558</v>
       </c>
       <c r="E175" s="30" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="B176">
         <v>66935922</v>
@@ -32951,27 +32951,27 @@
         <v>2731</v>
       </c>
       <c r="D176" s="220" t="s">
-        <v>3180</v>
+        <v>3179</v>
       </c>
       <c r="E176" s="30" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B177">
         <v>64455322</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="D177" s="220" t="s">
-        <v>3453</v>
+        <v>3452</v>
       </c>
       <c r="E177" s="30" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -32988,12 +32988,12 @@
         <v>2750</v>
       </c>
       <c r="E178" s="30" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="B179">
         <v>68570552</v>
@@ -33002,15 +33002,15 @@
         <v>2733</v>
       </c>
       <c r="D179" s="220" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="E179" s="30" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="B180">
         <v>69964218</v>
@@ -33019,15 +33019,15 @@
         <v>2755</v>
       </c>
       <c r="D180" s="373" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="E180" s="30" t="s">
-        <v>3101</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B181">
         <v>63950696</v>
@@ -33039,12 +33039,12 @@
         <v>2756</v>
       </c>
       <c r="E181" s="30" t="s">
-        <v>3101</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="4" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B182" t="s">
         <v>2784</v>
@@ -33056,7 +33056,7 @@
         <v>2756</v>
       </c>
       <c r="E182" s="30" t="s">
-        <v>3101</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -33073,12 +33073,12 @@
         <v>2829</v>
       </c>
       <c r="E183" s="30" t="s">
-        <v>3101</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B184">
         <v>63755362</v>
@@ -33087,15 +33087,15 @@
         <v>2819</v>
       </c>
       <c r="D184" s="373" t="s">
-        <v>3494</v>
+        <v>3493</v>
       </c>
       <c r="E184" s="30" t="s">
-        <v>3101</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="B185">
         <v>61248427</v>
@@ -33104,15 +33104,15 @@
         <v>2789</v>
       </c>
       <c r="D185" s="373" t="s">
-        <v>3580</v>
+        <v>3579</v>
       </c>
       <c r="E185" s="30" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" t="s">
-        <v>3370</v>
+        <v>3369</v>
       </c>
       <c r="B186">
         <v>60240509</v>
@@ -33121,10 +33121,10 @@
         <v>2790</v>
       </c>
       <c r="D186" s="373" t="s">
+        <v>3367</v>
+      </c>
+      <c r="E186" s="30" t="s">
         <v>3368</v>
-      </c>
-      <c r="E186" s="30" t="s">
-        <v>3369</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -33138,10 +33138,10 @@
         <v>2791</v>
       </c>
       <c r="D187" s="373" t="s">
-        <v>3305</v>
+        <v>3304</v>
       </c>
       <c r="E187" s="30" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -33158,7 +33158,7 @@
         <v>2798</v>
       </c>
       <c r="E188" s="30" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -33175,7 +33175,7 @@
         <v>2798</v>
       </c>
       <c r="E189" s="30" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -33192,12 +33192,12 @@
         <v>2798</v>
       </c>
       <c r="E190" s="30" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="4" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>1853</v>
@@ -33209,7 +33209,7 @@
         <v>2798</v>
       </c>
       <c r="E191" s="30" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -33223,15 +33223,15 @@
         <v>2830</v>
       </c>
       <c r="D192" s="373" t="s">
-        <v>3608</v>
+        <v>3607</v>
       </c>
       <c r="E192" s="30" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="B193">
         <v>69575383</v>
@@ -33240,10 +33240,10 @@
         <v>2796</v>
       </c>
       <c r="D193" s="373" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
       <c r="E193" s="30" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -33260,18 +33260,18 @@
         <v>2798</v>
       </c>
       <c r="E194" s="30" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="C195" s="56" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="D195" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="E195" s="30" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
     </row>
     <row r="197" spans="1:5" s="391" customFormat="1" ht="23.5">
@@ -33293,44 +33293,44 @@
         <v>2820</v>
       </c>
       <c r="D198" s="373" t="s">
-        <v>3304</v>
+        <v>3303</v>
       </c>
       <c r="E198" s="30" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" t="s">
+        <v>3362</v>
+      </c>
+      <c r="B199" t="s">
         <v>3363</v>
-      </c>
-      <c r="B199" t="s">
-        <v>3364</v>
       </c>
       <c r="C199" t="s">
         <v>2813</v>
       </c>
       <c r="D199" s="373" t="s">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="E199" s="30" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="B200">
         <v>63617941</v>
       </c>
       <c r="C200" s="22" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="D200" s="373" t="s">
         <v>2869</v>
       </c>
       <c r="E200" s="30" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -33344,15 +33344,15 @@
         <v>2814</v>
       </c>
       <c r="D201" s="373" t="s">
-        <v>3602</v>
+        <v>3601</v>
       </c>
       <c r="E201" s="30" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="202" spans="1:5">
       <c r="A202" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B202">
         <v>62279384</v>
@@ -33361,10 +33361,10 @@
         <v>2815</v>
       </c>
       <c r="D202" s="373" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="E202" s="30" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -33378,27 +33378,27 @@
         <v>2868</v>
       </c>
       <c r="D203" s="373" t="s">
-        <v>3466</v>
+        <v>3465</v>
       </c>
       <c r="E203" s="30" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="30" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B204" t="s">
-        <v>3452</v>
+        <v>3451</v>
       </c>
       <c r="C204" t="s">
         <v>2816</v>
       </c>
       <c r="D204" s="373" t="s">
-        <v>3451</v>
+        <v>3450</v>
       </c>
       <c r="E204" s="30" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -33409,18 +33409,18 @@
         <v>64982293</v>
       </c>
       <c r="C205" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="D205" s="373" t="s">
-        <v>3521</v>
+        <v>3520</v>
       </c>
       <c r="E205" s="30" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="206" spans="1:5">
       <c r="A206" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B206" t="s">
         <v>2876</v>
@@ -33432,7 +33432,7 @@
         <v>2874</v>
       </c>
       <c r="E206" s="30" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -33446,10 +33446,10 @@
         <v>2875</v>
       </c>
       <c r="D207" s="373" t="s">
+        <v>3158</v>
+      </c>
+      <c r="E207" s="30" t="s">
         <v>3159</v>
-      </c>
-      <c r="E207" s="30" t="s">
-        <v>3160</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -33466,12 +33466,12 @@
         <v>2889</v>
       </c>
       <c r="E208" s="30" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="105" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="B209" t="s">
         <v>1161</v>
@@ -33480,15 +33480,15 @@
         <v>2901</v>
       </c>
       <c r="D209" s="373" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="E209" s="30" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210" t="s">
-        <v>3317</v>
+        <v>3316</v>
       </c>
       <c r="B210">
         <v>65574051</v>
@@ -33497,15 +33497,15 @@
         <v>2888</v>
       </c>
       <c r="D210" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
       <c r="E210" s="30" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="97" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="B211" t="s">
         <v>1161</v>
@@ -33514,10 +33514,10 @@
         <v>2902</v>
       </c>
       <c r="D211" s="373" t="s">
-        <v>3659</v>
+        <v>3658</v>
       </c>
       <c r="E211" s="30" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -33528,13 +33528,13 @@
         <v>64881871</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
       <c r="D212" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="E212" s="30" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -33551,21 +33551,21 @@
         <v>2934</v>
       </c>
       <c r="E213" s="30" t="s">
-        <v>3509</v>
+        <v>3508</v>
       </c>
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="97" t="s">
-        <v>3582</v>
+        <v>3581</v>
       </c>
       <c r="C214" s="22" t="s">
         <v>2941</v>
       </c>
       <c r="D214" t="s">
-        <v>3668</v>
+        <v>3667</v>
       </c>
       <c r="E214" s="30" t="s">
-        <v>3509</v>
+        <v>3508</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -33573,16 +33573,16 @@
         <v>1434</v>
       </c>
       <c r="B215" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
       <c r="C215" s="22" t="s">
         <v>2942</v>
       </c>
       <c r="D215" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
       <c r="E215" s="30" t="s">
-        <v>3509</v>
+        <v>3508</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -33599,7 +33599,7 @@
         <v>2937</v>
       </c>
       <c r="E216" s="30" t="s">
-        <v>3509</v>
+        <v>3508</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -33616,7 +33616,7 @@
         <v>2944</v>
       </c>
       <c r="E217" s="30" t="s">
-        <v>3509</v>
+        <v>3508</v>
       </c>
     </row>
     <row r="231" spans="3:4">
@@ -36492,7 +36492,7 @@
         <v>678</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="G6" s="363" t="s">
         <v>1439</v>
@@ -36513,13 +36513,13 @@
         <v>1841</v>
       </c>
       <c r="D7" s="183" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F7" s="183" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="G7" s="183" t="s">
         <v>1439</v>
@@ -36531,7 +36531,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="193" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B8" s="193">
         <v>62747874</v>
@@ -36546,7 +36546,7 @@
         <v>362</v>
       </c>
       <c r="F8" s="183" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="G8" s="183" t="s">
         <v>1439</v>
@@ -36573,7 +36573,7 @@
         <v>362</v>
       </c>
       <c r="F9" s="183" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="G9" s="183" t="s">
         <v>1439</v>
@@ -36600,7 +36600,7 @@
         <v>362</v>
       </c>
       <c r="F10" s="183" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="G10" s="183" t="s">
         <v>1439</v>
@@ -36627,7 +36627,7 @@
         <v>362</v>
       </c>
       <c r="F11" s="183" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="G11" s="183" t="s">
         <v>1439</v>
@@ -36651,7 +36651,7 @@
         <v>2496</v>
       </c>
       <c r="E13" s="195" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="F13" s="195" t="s">
         <v>1426</v>
@@ -36677,7 +36677,7 @@
         <v>1842</v>
       </c>
       <c r="E14" s="193" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="F14" s="193" t="s">
         <v>1426</v>
@@ -36703,7 +36703,7 @@
         <v>2763</v>
       </c>
       <c r="E15" s="193" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="F15" s="193" t="s">
         <v>1426</v>
@@ -36729,7 +36729,7 @@
         <v>2304</v>
       </c>
       <c r="E16" s="193" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="F16" s="193" t="s">
         <v>1426</v>
@@ -36743,7 +36743,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="193" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="B17" s="193">
         <v>64403333</v>
@@ -36755,7 +36755,7 @@
         <v>1504</v>
       </c>
       <c r="E17" s="193" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="F17" s="193" t="s">
         <v>1426</v>
@@ -36781,7 +36781,7 @@
         <v>2150</v>
       </c>
       <c r="E18" s="193" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="F18" s="193" t="s">
         <v>1426</v>
@@ -36810,7 +36810,7 @@
         <v>362</v>
       </c>
       <c r="F20" s="195" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="G20" s="76" t="s">
         <v>422</v>
@@ -36839,7 +36839,7 @@
         <v>362</v>
       </c>
       <c r="F21" s="193" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="G21" s="183" t="s">
         <v>422</v>
@@ -36868,7 +36868,7 @@
         <v>362</v>
       </c>
       <c r="F22" s="193" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="G22" s="183" t="s">
         <v>422</v>
@@ -36882,7 +36882,7 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="183" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B23" s="183">
         <v>60389752</v>
@@ -36897,7 +36897,7 @@
         <v>362</v>
       </c>
       <c r="F23" s="193" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="G23" s="183" t="s">
         <v>422</v>
@@ -36926,7 +36926,7 @@
         <v>362</v>
       </c>
       <c r="F24" s="193" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="G24" s="183" t="s">
         <v>422</v>
@@ -36955,7 +36955,7 @@
         <v>362</v>
       </c>
       <c r="F25" s="193" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="G25" s="183" t="s">
         <v>422</v>
@@ -36969,7 +36969,7 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="76" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="B27" s="76">
         <v>60389752</v>
@@ -36984,7 +36984,7 @@
         <v>362</v>
       </c>
       <c r="F27" s="76" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="G27" s="76" t="s">
         <v>1440</v>
@@ -37011,7 +37011,7 @@
         <v>362</v>
       </c>
       <c r="F28" s="183" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="G28" s="183" t="s">
         <v>378</v>
@@ -37025,22 +37025,22 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="183" t="s">
-        <v>3390</v>
+        <v>3389</v>
       </c>
       <c r="B29" s="183">
         <v>65234700</v>
       </c>
       <c r="C29" s="194" t="s">
+        <v>3311</v>
+      </c>
+      <c r="D29" s="183" t="s">
         <v>3312</v>
-      </c>
-      <c r="D29" s="183" t="s">
-        <v>3313</v>
       </c>
       <c r="E29" s="432">
         <v>46243</v>
       </c>
       <c r="F29" s="183" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="G29" s="183" t="s">
         <v>378</v>
@@ -37069,7 +37069,7 @@
         <v>362</v>
       </c>
       <c r="F30" s="183" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="G30" s="183" t="s">
         <v>378</v>
@@ -37098,7 +37098,7 @@
         <v>362</v>
       </c>
       <c r="F31" s="183" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="G31" s="183" t="s">
         <v>378</v>
@@ -37112,7 +37112,7 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="183" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="B32" s="183">
         <v>68241069</v>
@@ -37127,7 +37127,7 @@
         <v>362</v>
       </c>
       <c r="F32" s="183" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="G32" s="183" t="s">
         <v>378</v>
@@ -37141,7 +37141,7 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="195" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="B34" s="195">
         <v>66466729</v>
@@ -37150,13 +37150,13 @@
         <v>1661</v>
       </c>
       <c r="D34" s="195" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="E34" s="76" t="s">
         <v>2466</v>
       </c>
       <c r="F34" s="195" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="G34" s="76" t="s">
         <v>1439</v>
@@ -37167,7 +37167,7 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="193" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B35" s="193">
         <v>63465332</v>
@@ -37182,7 +37182,7 @@
         <v>2466</v>
       </c>
       <c r="F35" s="193" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="G35" s="183" t="s">
         <v>1439</v>
@@ -37208,7 +37208,7 @@
         <v>2466</v>
       </c>
       <c r="F36" s="193" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="G36" s="183" t="s">
         <v>1439</v>
@@ -37219,7 +37219,7 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="193" t="s">
-        <v>3343</v>
+        <v>3342</v>
       </c>
       <c r="B37" s="193">
         <v>69111188</v>
@@ -37234,7 +37234,7 @@
         <v>2466</v>
       </c>
       <c r="F37" s="193" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="G37" s="183" t="s">
         <v>1439</v>
@@ -37260,7 +37260,7 @@
         <v>2466</v>
       </c>
       <c r="F38" s="193" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="G38" s="183" t="s">
         <v>1439</v>
@@ -37286,7 +37286,7 @@
         <v>2466</v>
       </c>
       <c r="F39" s="193" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="G39" s="183" t="s">
         <v>1439</v>
@@ -37299,16 +37299,16 @@
       <c r="A41" s="195"/>
       <c r="B41" s="195"/>
       <c r="C41" s="195" t="s">
+        <v>3357</v>
+      </c>
+      <c r="D41" s="195" t="s">
         <v>3358</v>
-      </c>
-      <c r="D41" s="195" t="s">
-        <v>3359</v>
       </c>
       <c r="E41" s="76" t="s">
         <v>362</v>
       </c>
       <c r="F41" s="195" t="s">
-        <v>3360</v>
+        <v>3359</v>
       </c>
       <c r="G41" s="76" t="s">
         <v>2361</v>
@@ -37328,7 +37328,7 @@
         <v>69563253</v>
       </c>
       <c r="C42" s="193" t="s">
-        <v>3361</v>
+        <v>3360</v>
       </c>
       <c r="D42" s="193" t="s">
         <v>1673</v>
@@ -37348,10 +37348,10 @@
         <v>1938</v>
       </c>
       <c r="C43" s="194" t="s">
+        <v>3337</v>
+      </c>
+      <c r="D43" s="193" t="s">
         <v>3338</v>
-      </c>
-      <c r="D43" s="193" t="s">
-        <v>3339</v>
       </c>
       <c r="E43" s="432">
         <v>46304</v>
@@ -37368,7 +37368,7 @@
         <v>62751201</v>
       </c>
       <c r="C44" s="194" t="s">
-        <v>3365</v>
+        <v>3364</v>
       </c>
       <c r="D44" s="183" t="s">
         <v>1354</v>
@@ -37388,10 +37388,10 @@
         <v>68030850</v>
       </c>
       <c r="C45" s="193" t="s">
+        <v>3340</v>
+      </c>
+      <c r="D45" s="193" t="s">
         <v>3341</v>
-      </c>
-      <c r="D45" s="193" t="s">
-        <v>3342</v>
       </c>
       <c r="E45" s="432">
         <v>46243</v>
@@ -37424,16 +37424,16 @@
       <c r="A48" s="195"/>
       <c r="B48" s="195"/>
       <c r="C48" s="195" t="s">
+        <v>3391</v>
+      </c>
+      <c r="D48" s="195" t="s">
         <v>3392</v>
       </c>
-      <c r="D48" s="195" t="s">
+      <c r="E48" s="76" t="s">
         <v>3393</v>
       </c>
-      <c r="E48" s="76" t="s">
+      <c r="F48" s="195" t="s">
         <v>3394</v>
-      </c>
-      <c r="F48" s="195" t="s">
-        <v>3395</v>
       </c>
       <c r="G48" s="76" t="s">
         <v>1439</v>
@@ -37470,10 +37470,10 @@
         <v>61548403</v>
       </c>
       <c r="C50" s="194" t="s">
+        <v>3395</v>
+      </c>
+      <c r="D50" s="193" t="s">
         <v>3396</v>
-      </c>
-      <c r="D50" s="193" t="s">
-        <v>3397</v>
       </c>
       <c r="E50" s="432">
         <v>46304</v>
@@ -37486,7 +37486,7 @@
       <c r="C51" s="449"/>
       <c r="D51" s="449"/>
       <c r="E51" s="432" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="F51" s="193"/>
       <c r="G51" s="183"/>
@@ -37496,7 +37496,7 @@
       <c r="C52" s="452"/>
       <c r="D52" s="183"/>
       <c r="E52" s="432" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="F52" s="193"/>
       <c r="G52" s="183"/>
@@ -37516,7 +37516,7 @@
         <v>2908</v>
       </c>
       <c r="E53" s="432" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="F53" s="193"/>
       <c r="G53" s="183"/>
@@ -37529,13 +37529,13 @@
         <v>1660</v>
       </c>
       <c r="D55" s="195" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
       <c r="E55" s="76" t="s">
         <v>2466</v>
       </c>
       <c r="F55" s="195" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="G55" s="76" t="s">
         <v>1439</v>
@@ -37561,7 +37561,7 @@
         <v>2466</v>
       </c>
       <c r="F56" s="193" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="G56" s="183" t="s">
         <v>1439</v>
@@ -37581,13 +37581,13 @@
         <v>2587</v>
       </c>
       <c r="D57" s="193" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="E57" s="183" t="s">
         <v>2466</v>
       </c>
       <c r="F57" s="193" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="G57" s="183" t="s">
         <v>1439</v>
@@ -37613,7 +37613,7 @@
         <v>2466</v>
       </c>
       <c r="F58" s="193" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="G58" s="183" t="s">
         <v>1439</v>
@@ -37639,7 +37639,7 @@
         <v>2466</v>
       </c>
       <c r="F59" s="193" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="G59" s="183" t="s">
         <v>1439</v>
@@ -37650,22 +37650,22 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="183" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="B60" s="183">
         <v>63247837</v>
       </c>
       <c r="C60" s="193" t="s">
-        <v>3227</v>
+        <v>3226</v>
       </c>
       <c r="D60" s="193" t="s">
-        <v>3624</v>
+        <v>3623</v>
       </c>
       <c r="E60" s="183" t="s">
         <v>2466</v>
       </c>
       <c r="F60" s="193" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="G60" s="183" t="s">
         <v>1439</v>
@@ -37691,7 +37691,7 @@
         <v>2466</v>
       </c>
       <c r="F62" s="195" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="G62" s="76" t="s">
         <v>1439</v>
@@ -37717,7 +37717,7 @@
         <v>2466</v>
       </c>
       <c r="F63" s="193" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="G63" s="183" t="s">
         <v>1439</v>
@@ -37728,7 +37728,7 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="183" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="B64" s="183">
         <v>64403333</v>
@@ -37743,7 +37743,7 @@
         <v>2466</v>
       </c>
       <c r="F64" s="193" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="G64" s="183" t="s">
         <v>1439</v>
@@ -37754,7 +37754,7 @@
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="193" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
       <c r="B65" s="193">
         <v>68030850</v>
@@ -37769,7 +37769,7 @@
         <v>2466</v>
       </c>
       <c r="F65" s="193" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="G65" s="183" t="s">
         <v>1439</v>
@@ -37780,7 +37780,7 @@
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="183" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="B66" s="183">
         <v>65003516</v>
@@ -37795,7 +37795,7 @@
         <v>2466</v>
       </c>
       <c r="F66" s="193" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="G66" s="183" t="s">
         <v>1439</v>
@@ -37821,7 +37821,7 @@
         <v>2466</v>
       </c>
       <c r="F67" s="193" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="G67" s="183" t="s">
         <v>1439</v>
@@ -37844,7 +37844,7 @@
         <v>2429</v>
       </c>
       <c r="E69" s="76" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="F69" s="195" t="s">
         <v>2430</v>
@@ -37870,7 +37870,7 @@
         <v>2434</v>
       </c>
       <c r="E70" s="183" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="F70" s="193" t="s">
         <v>2430</v>
@@ -37896,7 +37896,7 @@
         <v>2278</v>
       </c>
       <c r="E71" s="183" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="F71" s="193" t="s">
         <v>2430</v>
@@ -37922,7 +37922,7 @@
         <v>2717</v>
       </c>
       <c r="E72" s="183" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="F72" s="183" t="s">
         <v>2430</v>
@@ -37949,7 +37949,7 @@
         <v>2049</v>
       </c>
       <c r="E73" s="183" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="F73" s="183" t="s">
         <v>2430</v>
@@ -37976,7 +37976,7 @@
         <v>2426</v>
       </c>
       <c r="E74" s="183" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="F74" s="183" t="s">
         <v>2430</v>
@@ -38003,7 +38003,7 @@
         <v>1720</v>
       </c>
       <c r="E76" s="76" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="F76" s="195" t="s">
         <v>2428</v>
@@ -38027,7 +38027,7 @@
         <v>2318</v>
       </c>
       <c r="E77" s="183" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="F77" s="193" t="s">
         <v>2428</v>
@@ -38051,7 +38051,7 @@
         <v>1235</v>
       </c>
       <c r="E78" s="183" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="F78" s="193" t="s">
         <v>2428</v>
@@ -38063,7 +38063,7 @@
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="183" t="s">
-        <v>3523</v>
+        <v>3522</v>
       </c>
       <c r="B79" s="183">
         <v>62820256</v>
@@ -38075,7 +38075,7 @@
         <v>2344</v>
       </c>
       <c r="E79" s="183" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="F79" s="193" t="s">
         <v>2428</v>
@@ -38087,19 +38087,19 @@
     </row>
     <row r="80" spans="1:9">
       <c r="A80" s="183" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="B80" s="183">
         <v>69563253</v>
       </c>
       <c r="C80" s="194" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="D80" s="183" t="s">
         <v>1003</v>
       </c>
       <c r="E80" s="183" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="F80" s="193" t="s">
         <v>2428</v>
@@ -38111,7 +38111,7 @@
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="183" t="s">
-        <v>3474</v>
+        <v>3473</v>
       </c>
       <c r="B81" s="183">
         <v>63233935</v>
@@ -38120,10 +38120,10 @@
         <v>2363</v>
       </c>
       <c r="D81" s="183" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="E81" s="183" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="F81" s="193" t="s">
         <v>2428</v>
@@ -38135,7 +38135,7 @@
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="76" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="B83" s="76">
         <v>63574980</v>
@@ -38150,7 +38150,7 @@
         <v>1341</v>
       </c>
       <c r="F83" s="195" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="G83" s="76" t="s">
         <v>1439</v>
@@ -38177,7 +38177,7 @@
         <v>1341</v>
       </c>
       <c r="F84" s="183" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="G84" s="183" t="s">
         <v>1439</v>
@@ -38204,7 +38204,7 @@
         <v>1341</v>
       </c>
       <c r="F85" s="183" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="G85" s="183" t="s">
         <v>1439</v>
@@ -38219,19 +38219,19 @@
         <v>2481</v>
       </c>
       <c r="B86" s="183" t="s">
-        <v>3080</v>
+        <v>3079</v>
       </c>
       <c r="C86" s="194" t="s">
         <v>2644</v>
       </c>
       <c r="D86" s="183" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="E86" s="183" t="s">
         <v>1341</v>
       </c>
       <c r="F86" s="183" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="G86" s="183" t="s">
         <v>1439</v>
@@ -38243,7 +38243,7 @@
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="183" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B87" s="183">
         <v>69904406</v>
@@ -38252,13 +38252,13 @@
         <v>2645</v>
       </c>
       <c r="D87" s="183" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="E87" s="183" t="s">
         <v>1341</v>
       </c>
       <c r="F87" s="183" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="G87" s="183" t="s">
         <v>1439</v>
@@ -38285,7 +38285,7 @@
         <v>1341</v>
       </c>
       <c r="F88" s="183" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="G88" s="183" t="s">
         <v>1439</v>
@@ -38312,7 +38312,7 @@
         <v>1650</v>
       </c>
       <c r="F90" s="195" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="G90" s="76" t="s">
         <v>1439</v>
@@ -38336,7 +38336,7 @@
         <v>1650</v>
       </c>
       <c r="F91" s="193" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="G91" s="183" t="s">
         <v>1439</v>
@@ -38360,7 +38360,7 @@
         <v>1650</v>
       </c>
       <c r="F92" s="193" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="G92" s="183" t="s">
         <v>1439</v>
@@ -38369,7 +38369,7 @@
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="183" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="B93" s="183">
         <v>68259581</v>
@@ -38384,7 +38384,7 @@
         <v>1650</v>
       </c>
       <c r="F93" s="193" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="G93" s="183" t="s">
         <v>1439</v>
@@ -38408,7 +38408,7 @@
         <v>1650</v>
       </c>
       <c r="F94" s="193" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="G94" s="183" t="s">
         <v>1439</v>
@@ -38432,7 +38432,7 @@
         <v>1650</v>
       </c>
       <c r="F95" s="193" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="G95" s="183" t="s">
         <v>1439</v>
@@ -38441,7 +38441,7 @@
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="195" t="s">
-        <v>3381</v>
+        <v>3380</v>
       </c>
       <c r="B97" s="195">
         <v>64476521</v>
@@ -38456,7 +38456,7 @@
         <v>2466</v>
       </c>
       <c r="F97" s="195" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="G97" s="76" t="s">
         <v>1439</v>
@@ -38467,7 +38467,7 @@
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="193" t="s">
-        <v>3276</v>
+        <v>3275</v>
       </c>
       <c r="B98" s="193">
         <v>60389752</v>
@@ -38476,13 +38476,13 @@
         <v>2626</v>
       </c>
       <c r="D98" s="193" t="s">
-        <v>3275</v>
+        <v>3274</v>
       </c>
       <c r="E98" s="183" t="s">
         <v>2466</v>
       </c>
       <c r="F98" s="193" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="G98" s="183" t="s">
         <v>1439</v>
@@ -38493,7 +38493,7 @@
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="183" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="B99" s="183">
         <v>60389752</v>
@@ -38508,7 +38508,7 @@
         <v>2466</v>
       </c>
       <c r="F99" s="193" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="G99" s="183" t="s">
         <v>1439</v>
@@ -38534,7 +38534,7 @@
         <v>2466</v>
       </c>
       <c r="F100" s="193" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="G100" s="183" t="s">
         <v>1439</v>
@@ -38560,7 +38560,7 @@
         <v>2466</v>
       </c>
       <c r="F101" s="193" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="G101" s="183" t="s">
         <v>1439</v>
@@ -38571,7 +38571,7 @@
     </row>
     <row r="102" spans="1:9">
       <c r="A102" s="193" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B102" s="193">
         <v>67381873</v>
@@ -38580,13 +38580,13 @@
         <v>2276</v>
       </c>
       <c r="D102" s="193" t="s">
-        <v>3196</v>
+        <v>3195</v>
       </c>
       <c r="E102" s="183" t="s">
         <v>2466</v>
       </c>
       <c r="F102" s="193" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="G102" s="183" t="s">
         <v>1439</v>
@@ -38609,7 +38609,7 @@
         <v>2286</v>
       </c>
       <c r="E104" s="76" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="F104" s="195" t="s">
         <v>422</v>
@@ -38635,7 +38635,7 @@
         <v>2291</v>
       </c>
       <c r="E105" s="183" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="F105" s="193" t="s">
         <v>422</v>
@@ -38649,7 +38649,7 @@
     </row>
     <row r="106" spans="1:9">
       <c r="A106" s="193" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
       <c r="B106" s="193">
         <v>62723048</v>
@@ -38658,10 +38658,10 @@
         <v>2292</v>
       </c>
       <c r="D106" s="193" t="s">
-        <v>3217</v>
+        <v>3216</v>
       </c>
       <c r="E106" s="183" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="F106" s="193" t="s">
         <v>422</v>
@@ -38687,7 +38687,7 @@
         <v>2440</v>
       </c>
       <c r="E107" s="183" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="F107" s="193" t="s">
         <v>422</v>
@@ -38713,7 +38713,7 @@
         <v>2295</v>
       </c>
       <c r="E108" s="183" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="F108" s="193" t="s">
         <v>422</v>
@@ -38739,7 +38739,7 @@
         <v>2892</v>
       </c>
       <c r="E109" s="183" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="F109" s="193" t="s">
         <v>422</v>
@@ -38753,7 +38753,7 @@
     </row>
     <row r="111" spans="1:9">
       <c r="A111" s="195" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="B111" s="195">
         <v>68310153</v>
@@ -38768,7 +38768,7 @@
         <v>362</v>
       </c>
       <c r="F111" s="195" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
       <c r="G111" s="76" t="s">
         <v>1341</v>
@@ -38795,7 +38795,7 @@
         <v>362</v>
       </c>
       <c r="F112" s="193" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
       <c r="G112" s="183" t="s">
         <v>1341</v>
@@ -38824,7 +38824,7 @@
         <v>2466</v>
       </c>
       <c r="F113" s="193" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
       <c r="G113" s="183" t="s">
         <v>1341</v>
@@ -38844,16 +38844,16 @@
         <v>62360487</v>
       </c>
       <c r="C114" s="194" t="s">
+        <v>3227</v>
+      </c>
+      <c r="D114" s="183" t="s">
         <v>3228</v>
-      </c>
-      <c r="D114" s="183" t="s">
-        <v>3229</v>
       </c>
       <c r="E114" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F114" s="193" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
       <c r="G114" s="183" t="s">
         <v>1341</v>
@@ -38873,16 +38873,16 @@
         <v>62085821</v>
       </c>
       <c r="C115" s="193" t="s">
+        <v>3229</v>
+      </c>
+      <c r="D115" s="193" t="s">
         <v>3230</v>
-      </c>
-      <c r="D115" s="193" t="s">
-        <v>3231</v>
       </c>
       <c r="E115" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F115" s="193" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
       <c r="G115" s="183" t="s">
         <v>1341</v>
@@ -38896,22 +38896,22 @@
     </row>
     <row r="116" spans="1:9">
       <c r="A116" s="193" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="B116" s="193">
         <v>64403333</v>
       </c>
       <c r="C116" s="193" t="s">
+        <v>3231</v>
+      </c>
+      <c r="D116" s="193" t="s">
         <v>3232</v>
-      </c>
-      <c r="D116" s="193" t="s">
-        <v>3233</v>
       </c>
       <c r="E116" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F116" s="193" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
       <c r="G116" s="183" t="s">
         <v>1341</v>
@@ -38943,7 +38943,7 @@
         <v>2308</v>
       </c>
       <c r="E118" s="76" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="F118" s="76" t="s">
         <v>422</v>
@@ -38970,7 +38970,7 @@
         <v>2310</v>
       </c>
       <c r="E119" s="183" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="F119" s="193" t="s">
         <v>422</v>
@@ -38996,7 +38996,7 @@
         <v>2312</v>
       </c>
       <c r="E120" s="183" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="F120" s="193" t="s">
         <v>422</v>
@@ -39010,19 +39010,19 @@
     </row>
     <row r="121" spans="1:9">
       <c r="A121" s="183" t="s">
-        <v>3316</v>
+        <v>3315</v>
       </c>
       <c r="B121" s="183">
         <v>64403333</v>
       </c>
       <c r="C121" s="183" t="s">
+        <v>3233</v>
+      </c>
+      <c r="D121" s="183" t="s">
         <v>3234</v>
       </c>
-      <c r="D121" s="183" t="s">
-        <v>3235</v>
-      </c>
       <c r="E121" s="183" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="F121" s="193" t="s">
         <v>422</v>
@@ -39036,7 +39036,7 @@
     </row>
     <row r="122" spans="1:9">
       <c r="A122" s="193" t="s">
-        <v>3582</v>
+        <v>3581</v>
       </c>
       <c r="B122" s="193" t="s">
         <v>2194</v>
@@ -39048,7 +39048,7 @@
         <v>377</v>
       </c>
       <c r="E122" s="183" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="F122" s="193" t="s">
         <v>422</v>
@@ -39074,7 +39074,7 @@
         <v>1646</v>
       </c>
       <c r="E123" s="183" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="F123" s="193" t="s">
         <v>422</v>
@@ -39103,7 +39103,7 @@
         <v>678</v>
       </c>
       <c r="F125" s="76" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="G125" s="76" t="s">
         <v>422</v>
@@ -39117,7 +39117,7 @@
     </row>
     <row r="126" spans="1:9">
       <c r="A126" s="183" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="B126" s="183">
         <v>64403333</v>
@@ -39132,7 +39132,7 @@
         <v>362</v>
       </c>
       <c r="F126" s="183" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="G126" s="183" t="s">
         <v>422</v>
@@ -39161,7 +39161,7 @@
         <v>362</v>
       </c>
       <c r="F127" s="183" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="G127" s="183" t="s">
         <v>422</v>
@@ -39188,7 +39188,7 @@
         <v>362</v>
       </c>
       <c r="F128" s="183" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="G128" s="183" t="s">
         <v>422</v>
@@ -39217,7 +39217,7 @@
         <v>362</v>
       </c>
       <c r="F129" s="183" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="G129" s="183" t="s">
         <v>422</v>
@@ -39246,7 +39246,7 @@
         <v>362</v>
       </c>
       <c r="F130" s="183" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="G130" s="183" t="s">
         <v>422</v>
@@ -39275,7 +39275,7 @@
         <v>2355</v>
       </c>
       <c r="F132" s="195" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="G132" s="76" t="s">
         <v>1439</v>
@@ -39292,7 +39292,7 @@
         <v>64226974</v>
       </c>
       <c r="C133" s="183" t="s">
-        <v>3378</v>
+        <v>3377</v>
       </c>
       <c r="D133" s="193" t="s">
         <v>377</v>
@@ -39301,7 +39301,7 @@
         <v>2355</v>
       </c>
       <c r="F133" s="193" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="G133" s="183" t="s">
         <v>1439</v>
@@ -39327,7 +39327,7 @@
         <v>2355</v>
       </c>
       <c r="F134" s="193" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="G134" s="183" t="s">
         <v>1439</v>
@@ -39353,7 +39353,7 @@
         <v>2355</v>
       </c>
       <c r="F135" s="193" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="G135" s="183" t="s">
         <v>1439</v>
@@ -39379,7 +39379,7 @@
         <v>2355</v>
       </c>
       <c r="F136" s="193" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="G136" s="183" t="s">
         <v>1439</v>
@@ -39390,7 +39390,7 @@
     </row>
     <row r="137" spans="1:9">
       <c r="A137" s="193" t="s">
-        <v>3432</v>
+        <v>3431</v>
       </c>
       <c r="B137" s="193">
         <v>63811445</v>
@@ -39405,7 +39405,7 @@
         <v>2355</v>
       </c>
       <c r="F137" s="193" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="G137" s="183" t="s">
         <v>1439</v>
@@ -39416,22 +39416,22 @@
     </row>
     <row r="139" spans="1:9">
       <c r="A139" s="195" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B139" s="195" t="s">
         <v>2154</v>
       </c>
       <c r="C139" s="195" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="D139" s="195" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="E139" s="76" t="s">
         <v>2355</v>
       </c>
       <c r="F139" s="195" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="G139" s="76" t="s">
         <v>1439</v>
@@ -39448,16 +39448,16 @@
         <v>66319486</v>
       </c>
       <c r="C140" s="193" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="D140" s="193" t="s">
-        <v>3277</v>
+        <v>3276</v>
       </c>
       <c r="E140" s="183" t="s">
         <v>2355</v>
       </c>
       <c r="F140" s="193" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="G140" s="183" t="s">
         <v>1439</v>
@@ -39468,7 +39468,7 @@
     </row>
     <row r="141" spans="1:9">
       <c r="A141" s="183" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="B141" s="183">
         <v>60389752</v>
@@ -39483,7 +39483,7 @@
         <v>2355</v>
       </c>
       <c r="F141" s="193" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="G141" s="183" t="s">
         <v>1439</v>
@@ -39497,7 +39497,7 @@
         <v>2355</v>
       </c>
       <c r="F142" s="193" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="G142" s="183" t="s">
         <v>1439</v>
@@ -39523,7 +39523,7 @@
         <v>2355</v>
       </c>
       <c r="F143" s="193" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="G143" s="183" t="s">
         <v>1439</v>
@@ -39534,7 +39534,7 @@
     </row>
     <row r="144" spans="1:9">
       <c r="A144" s="193" t="s">
-        <v>3523</v>
+        <v>3522</v>
       </c>
       <c r="B144" s="193">
         <v>60389752</v>
@@ -39549,7 +39549,7 @@
         <v>2355</v>
       </c>
       <c r="F144" s="193" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="G144" s="183" t="s">
         <v>1439</v>
@@ -39575,7 +39575,7 @@
         <v>2466</v>
       </c>
       <c r="F146" s="195" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="G146" s="76" t="s">
         <v>1439</v>
@@ -39586,13 +39586,13 @@
     </row>
     <row r="147" spans="1:9">
       <c r="A147" s="193" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="B147" s="193">
         <v>67697112</v>
       </c>
       <c r="C147" s="193" t="s">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="D147" s="193" t="s">
         <v>1303</v>
@@ -39601,7 +39601,7 @@
         <v>2466</v>
       </c>
       <c r="F147" s="193" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="G147" s="183" t="s">
         <v>1439</v>
@@ -39612,7 +39612,7 @@
     </row>
     <row r="148" spans="1:9">
       <c r="A148" s="183" t="s">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="B148" s="183">
         <v>62560788</v>
@@ -39627,7 +39627,7 @@
         <v>2466</v>
       </c>
       <c r="F148" s="193" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="G148" s="183" t="s">
         <v>1439</v>
@@ -39638,7 +39638,7 @@
     </row>
     <row r="149" spans="1:9">
       <c r="A149" s="193" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B149" s="193">
         <v>64403333</v>
@@ -39653,7 +39653,7 @@
         <v>2466</v>
       </c>
       <c r="F149" s="193" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="G149" s="183" t="s">
         <v>1439</v>
@@ -39679,7 +39679,7 @@
         <v>2466</v>
       </c>
       <c r="F150" s="193" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="G150" s="183" t="s">
         <v>1439</v>
@@ -39705,7 +39705,7 @@
         <v>2466</v>
       </c>
       <c r="F151" s="193" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="G151" s="183" t="s">
         <v>1439</v>
@@ -39731,7 +39731,7 @@
         <v>362</v>
       </c>
       <c r="F153" s="195" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="G153" s="76" t="s">
         <v>2361</v>
@@ -39745,22 +39745,22 @@
     </row>
     <row r="154" spans="1:9">
       <c r="A154" s="193" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="B154" s="193">
         <v>65963732</v>
       </c>
       <c r="C154" s="194" t="s">
+        <v>3219</v>
+      </c>
+      <c r="D154" s="193" t="s">
         <v>3220</v>
-      </c>
-      <c r="D154" s="193" t="s">
-        <v>3221</v>
       </c>
       <c r="E154" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F154" s="193" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="G154" s="183" t="s">
         <v>2361</v>
@@ -39774,7 +39774,7 @@
     </row>
     <row r="155" spans="1:9">
       <c r="A155" s="183" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="B155" s="183">
         <v>60071688</v>
@@ -39783,13 +39783,13 @@
         <v>2345</v>
       </c>
       <c r="D155" s="183" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
       <c r="E155" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F155" s="193" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="G155" s="183" t="s">
         <v>2361</v>
@@ -39818,7 +39818,7 @@
         <v>362</v>
       </c>
       <c r="F156" s="193" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="G156" s="183" t="s">
         <v>2361</v>
@@ -39847,7 +39847,7 @@
         <v>362</v>
       </c>
       <c r="F157" s="193" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="G157" s="183" t="s">
         <v>2361</v>
@@ -39876,7 +39876,7 @@
         <v>362</v>
       </c>
       <c r="F158" s="193" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="G158" s="183" t="s">
         <v>2361</v>
@@ -39907,7 +39907,7 @@
       <c r="A183" s="221"/>
       <c r="B183" s="221"/>
       <c r="C183" s="221" t="s">
-        <v>3308</v>
+        <v>3307</v>
       </c>
       <c r="D183" s="221"/>
       <c r="E183" s="221"/>
@@ -39921,19 +39921,19 @@
         <v>67836337</v>
       </c>
       <c r="C184" s="195" t="s">
+        <v>3419</v>
+      </c>
+      <c r="D184" s="195" t="s">
         <v>3420</v>
-      </c>
-      <c r="D184" s="195" t="s">
-        <v>3421</v>
       </c>
       <c r="E184" s="433">
         <v>46243</v>
       </c>
       <c r="F184" s="76" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="G184" s="195" t="s">
-        <v>3472</v>
+        <v>3471</v>
       </c>
       <c r="H184" s="76" t="s">
         <v>1975</v>
@@ -39941,19 +39941,19 @@
     </row>
     <row r="185" spans="1:9">
       <c r="A185" s="193" t="s">
-        <v>3474</v>
+        <v>3473</v>
       </c>
       <c r="B185" s="193">
         <v>60196388</v>
       </c>
       <c r="C185" s="193" t="s">
-        <v>3473</v>
+        <v>3472</v>
       </c>
       <c r="D185" s="444" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="E185" s="432" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="F185" s="193"/>
       <c r="G185" s="183"/>
@@ -39967,13 +39967,13 @@
         <v>64403333</v>
       </c>
       <c r="C186" s="191" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
       <c r="D186" s="183" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
       <c r="E186" s="432" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="F186" s="193"/>
       <c r="G186" s="183"/>
@@ -39981,19 +39981,19 @@
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="193" t="s">
-        <v>3513</v>
+        <v>3512</v>
       </c>
       <c r="B187" s="193">
         <v>68071614</v>
       </c>
       <c r="C187" s="193" t="s">
+        <v>3509</v>
+      </c>
+      <c r="D187" s="193" t="s">
         <v>3510</v>
       </c>
-      <c r="D187" s="193" t="s">
+      <c r="E187" s="432" t="s">
         <v>3511</v>
-      </c>
-      <c r="E187" s="432" t="s">
-        <v>3512</v>
       </c>
       <c r="F187" s="193"/>
       <c r="G187" s="183"/>
@@ -40007,13 +40007,13 @@
         <v>63950696</v>
       </c>
       <c r="C188" s="450" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="D188" s="450" t="s">
         <v>2775</v>
       </c>
       <c r="E188" s="432" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="F188" s="451"/>
       <c r="G188" s="445"/>
@@ -40028,13 +40028,13 @@
         <v>65147336</v>
       </c>
       <c r="C189" s="183" t="s">
+        <v>3563</v>
+      </c>
+      <c r="D189" s="183" t="s">
         <v>3564</v>
       </c>
-      <c r="D189" s="183" t="s">
+      <c r="E189" s="432" t="s">
         <v>3565</v>
-      </c>
-      <c r="E189" s="432" t="s">
-        <v>3566</v>
       </c>
       <c r="F189" s="193"/>
       <c r="G189" s="183"/>
@@ -40075,7 +40075,7 @@
         <v>316</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>3396</v>
+        <v>3395</v>
       </c>
       <c r="E194" s="30"/>
       <c r="F194"/>
@@ -40101,7 +40101,7 @@
         <v>439</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="E196" s="30"/>
       <c r="F196"/>
@@ -40112,7 +40112,7 @@
         <v>26</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>3510</v>
+        <v>3509</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -40120,7 +40120,7 @@
         <v>1324</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -40128,7 +40128,7 @@
         <v>1657</v>
       </c>
       <c r="D199" s="428" t="s">
-        <v>3564</v>
+        <v>3563</v>
       </c>
       <c r="F199" s="394"/>
     </row>
@@ -40137,7 +40137,7 @@
         <v>1305</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -40145,7 +40145,7 @@
         <v>406</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
     </row>
     <row r="202" spans="1:9">
@@ -40153,7 +40153,7 @@
         <v>708</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -40161,7 +40161,7 @@
         <v>281</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
     </row>
     <row r="204" spans="1:9">
@@ -40169,7 +40169,7 @@
         <v>2363</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>3358</v>
+        <v>3357</v>
       </c>
     </row>
     <row r="205" spans="1:9">
@@ -40179,7 +40179,7 @@
         <v>465</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>3361</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -40187,7 +40187,7 @@
         <v>219</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>3365</v>
+        <v>3364</v>
       </c>
     </row>
     <row r="207" spans="1:9">
@@ -40195,7 +40195,7 @@
         <v>427</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>3378</v>
+        <v>3377</v>
       </c>
     </row>
     <row r="208" spans="1:9">
@@ -40203,7 +40203,7 @@
         <v>1050</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>3392</v>
+        <v>3391</v>
       </c>
     </row>
     <row r="223" spans="1:9">
@@ -41418,7 +41418,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B3">
         <v>62349088</v>
@@ -41439,10 +41439,10 @@
         <v>705</v>
       </c>
       <c r="H3" t="s">
-        <v>3410</v>
+        <v>3409</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="J3"/>
     </row>
@@ -41469,10 +41469,10 @@
         <v>515</v>
       </c>
       <c r="H4" t="s">
-        <v>3240</v>
+        <v>3239</v>
       </c>
       <c r="I4" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="J4"/>
     </row>
@@ -41490,7 +41490,7 @@
         <v>1519</v>
       </c>
       <c r="E5" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="F5" t="s">
         <v>2163</v>
@@ -41499,10 +41499,10 @@
         <v>515</v>
       </c>
       <c r="H5" s="220" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="I5" s="220" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="J5" t="s">
         <v>1394</v>
@@ -41510,19 +41510,19 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="B6" t="s">
-        <v>3439</v>
+        <v>3438</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>427</v>
       </c>
       <c r="D6" t="s">
-        <v>3258</v>
+        <v>3257</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>3256</v>
+        <v>3255</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>2853</v>
@@ -41531,10 +41531,10 @@
         <v>436</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="I6" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
       <c r="J6"/>
     </row>
@@ -41566,13 +41566,13 @@
         <v>1434</v>
       </c>
       <c r="B8" t="s">
-        <v>3616</v>
+        <v>3615</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>2060</v>
       </c>
       <c r="D8" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
       <c r="E8" t="s">
         <v>2320</v>
@@ -41584,10 +41584,10 @@
         <v>250</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>3087</v>
+        <v>3086</v>
       </c>
       <c r="I8" t="s">
-        <v>3621</v>
+        <v>3620</v>
       </c>
       <c r="J8"/>
     </row>
@@ -41622,31 +41622,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="278" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>3649</v>
+        <v>3648</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>3644</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>3645</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="E10" s="10" t="s">
         <v>3646</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="F10" s="10" t="s">
         <v>3647</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>3648</v>
       </c>
       <c r="G10" t="s">
         <v>250</v>
       </c>
       <c r="H10" s="278" t="s">
+        <v>3649</v>
+      </c>
+      <c r="I10" s="278" t="s">
         <v>3650</v>
-      </c>
-      <c r="I10" s="278" t="s">
-        <v>3651</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -41797,7 +41797,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="10" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="B5" s="10">
         <v>67992849</v>
@@ -41818,10 +41818,10 @@
         <v>517</v>
       </c>
       <c r="H5" s="220" t="s">
-        <v>3434</v>
+        <v>3433</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -41850,12 +41850,12 @@
         <v>2740</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="10" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>2398</v>
@@ -41864,7 +41864,7 @@
         <v>1722</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1695</v>
@@ -41876,10 +41876,10 @@
         <v>517</v>
       </c>
       <c r="H7" t="s">
-        <v>3107</v>
+        <v>3106</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -41895,7 +41895,7 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="10" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="B11" s="10">
         <v>64403333</v>
@@ -41927,7 +41927,7 @@
         <v>2144</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>959</v>
@@ -41939,10 +41939,10 @@
         <v>517</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="I12" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -41967,7 +41967,7 @@
         <v>2202</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>959</v>
@@ -41979,10 +41979,10 @@
         <v>517</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -42008,7 +42008,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="10" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="B17" s="10">
         <v>64403333</v>
@@ -42031,7 +42031,7 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="10" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="B18" s="10">
         <v>60345107</v>
@@ -42040,7 +42040,7 @@
         <v>2327</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>959</v>
@@ -42052,10 +42052,10 @@
         <v>517</v>
       </c>
       <c r="H18" s="427" t="s">
-        <v>3172</v>
+        <v>3171</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>3271</v>
+        <v>3270</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -42069,7 +42069,7 @@
         <v>2378</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>3660</v>
+        <v>3659</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>959</v>
@@ -42081,10 +42081,10 @@
         <v>517</v>
       </c>
       <c r="H19" s="457" t="s">
-        <v>3661</v>
+        <v>3660</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="190" customFormat="1" ht="26">
@@ -42100,13 +42100,13 @@
         <v>2599</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>2403</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>959</v>
@@ -42118,15 +42118,15 @@
         <v>517</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>3131</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="B23" s="10">
         <v>64720128</v>
@@ -42147,10 +42147,10 @@
         <v>517</v>
       </c>
       <c r="H23" s="10" t="s">
+        <v>3414</v>
+      </c>
+      <c r="I23" s="10" t="s">
         <v>3415</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>3416</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -42164,7 +42164,7 @@
         <v>2419</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>3082</v>
+        <v>3081</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>959</v>
@@ -42176,10 +42176,10 @@
         <v>517</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -42189,7 +42189,7 @@
         <v>2431</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>959</v>
@@ -42308,13 +42308,13 @@
         <v>2446</v>
       </c>
       <c r="B4" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1863</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
       <c r="E4" t="s">
         <v>1864</v>
@@ -42326,13 +42326,13 @@
         <v>963</v>
       </c>
       <c r="H4" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
       <c r="J4" t="s">
-        <v>3128</v>
+        <v>3127</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -42392,7 +42392,7 @@
         <v>2283</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>2284</v>
@@ -42404,13 +42404,13 @@
         <v>963</v>
       </c>
       <c r="H7" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>3169</v>
+        <v>3168</v>
       </c>
       <c r="J7" s="275" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -42418,16 +42418,16 @@
         <v>2500</v>
       </c>
       <c r="B8" t="s">
-        <v>3586</v>
+        <v>3585</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>3482</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>3483</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="10" t="s">
         <v>3484</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>3485</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>1738</v>
@@ -42436,30 +42436,30 @@
         <v>963</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>2983</v>
+        <v>2982</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>3141</v>
+        <v>3140</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="10" t="s">
+        <v>2997</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>2998</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>2999</v>
-      </c>
       <c r="C9" s="22" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>2877</v>
       </c>
       <c r="E9" s="447" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>2878</v>
@@ -42468,13 +42468,13 @@
         <v>963</v>
       </c>
       <c r="H9" s="10" t="s">
+        <v>2999</v>
+      </c>
+      <c r="I9" s="10" t="s">
         <v>3000</v>
       </c>
-      <c r="I9" s="10" t="s">
-        <v>3001</v>
-      </c>
       <c r="J9" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -42482,16 +42482,16 @@
         <v>1429</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>2285</v>
@@ -42500,30 +42500,30 @@
         <v>963</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="J10" t="s">
-        <v>3294</v>
+        <v>3293</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="457" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>3656</v>
+        <v>3655</v>
       </c>
       <c r="C11" s="10" t="s">
+        <v>3629</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>3632</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>3630</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>3633</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>3631</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>1738</v>
@@ -42543,7 +42543,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="C15" s="428" t="s">
-        <v>3630</v>
+        <v>3629</v>
       </c>
     </row>
   </sheetData>
@@ -42684,10 +42684,10 @@
         <v>60240509</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>3462</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>3463</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>3464</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>2597</v>
@@ -42708,7 +42708,7 @@
         <v>1786</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>2597</v>
@@ -42743,16 +42743,16 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="10" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="B12" s="10">
         <v>66466729</v>
       </c>
       <c r="C12" s="10" t="s">
+        <v>3591</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>3592</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>3593</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
@@ -42832,7 +42832,7 @@
       <c r="A19" s="10"/>
       <c r="B19" s="10"/>
       <c r="C19" s="428" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
@@ -42950,25 +42950,25 @@
         <v>2938</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="E4" t="s">
         <v>2905</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="G4" s="275" t="s">
         <v>2915</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>3036</v>
+        <v>3035</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
     </row>
   </sheetData>
@@ -44364,7 +44364,7 @@
         <v>51</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>1157</v>
@@ -44376,10 +44376,10 @@
         <v>159</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>3331</v>
+        <v>3330</v>
       </c>
       <c r="N6" s="4" t="s">
         <v>26</v>
@@ -44387,7 +44387,7 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="456" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="B7" s="4">
         <v>69888391</v>
@@ -44411,13 +44411,13 @@
         <v>2261</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>3137</v>
+        <v>3136</v>
       </c>
       <c r="L7" s="3"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>3523</v>
+        <v>3522</v>
       </c>
       <c r="B8" t="s">
         <v>452</v>
@@ -44441,7 +44441,7 @@
         <v>2715</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
     </row>
     <row r="9" spans="1:14" s="4" customFormat="1">
@@ -44453,19 +44453,19 @@
         <v>2153</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>3331</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>3332</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>3333</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>159</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>3296</v>
+        <v>3295</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>815</v>
@@ -44473,7 +44473,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="4" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="B10" s="4">
         <v>67916500</v>
@@ -44494,10 +44494,10 @@
         <v>244</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>3410</v>
+        <v>3409</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -44514,7 +44514,7 @@
         <v>1510</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>2896</v>
@@ -44523,10 +44523,10 @@
         <v>244</v>
       </c>
       <c r="H11" t="s">
-        <v>3529</v>
+        <v>3528</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -44552,10 +44552,10 @@
         <v>244</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>3532</v>
+        <v>3531</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -44563,7 +44563,7 @@
         <v>2921</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="C13" s="22" t="s">
         <v>1218</v>
@@ -44581,10 +44581,10 @@
         <v>244</v>
       </c>
       <c r="H13" s="220" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>3617</v>
+        <v>3616</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="4" customFormat="1">
@@ -44610,10 +44610,10 @@
         <v>244</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>3444</v>
+        <v>3443</v>
       </c>
       <c r="I14" s="220" t="s">
-        <v>3488</v>
+        <v>3487</v>
       </c>
       <c r="L14" s="3"/>
     </row>
@@ -44631,19 +44631,19 @@
         <v>2841</v>
       </c>
       <c r="E15" s="4" t="s">
+        <v>3586</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>3587</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>3588</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>887</v>
       </c>
       <c r="H15" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
       <c r="I15" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>498</v>
@@ -44672,10 +44672,10 @@
         <v>159</v>
       </c>
       <c r="H16" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="I16" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>805</v>
@@ -44683,7 +44683,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="B17">
         <v>65325884</v>
@@ -44706,7 +44706,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="4" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>2107</v>
@@ -44718,19 +44718,19 @@
         <v>2213</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>3333</v>
+        <v>3332</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>244</v>
       </c>
       <c r="H18" s="49" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="I18" t="s">
-        <v>3522</v>
+        <v>3521</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="4" customFormat="1">
@@ -44747,10 +44747,10 @@
         <v>2582</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>3349</v>
+        <v>3348</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>3333</v>
+        <v>3332</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>1227</v>
@@ -44760,7 +44760,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="4" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="B20">
         <v>64403333</v>
@@ -44821,7 +44821,7 @@
         <v>2204</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>3629</v>
+        <v>3628</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>2462</v>
@@ -44832,7 +44832,7 @@
     </row>
     <row r="23" spans="1:12" s="4" customFormat="1">
       <c r="A23" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="B23">
         <v>63247837</v>
@@ -44841,7 +44841,7 @@
         <v>2590</v>
       </c>
       <c r="D23" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
       <c r="E23" t="s">
         <v>2593</v>
@@ -44853,16 +44853,16 @@
         <v>159</v>
       </c>
       <c r="H23" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="L23" s="6"/>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>3523</v>
+        <v>3522</v>
       </c>
       <c r="B24">
         <v>69184177</v>
@@ -44871,10 +44871,10 @@
         <v>1630</v>
       </c>
       <c r="D24" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>2459</v>
@@ -44885,19 +44885,19 @@
     </row>
     <row r="25" spans="1:12" s="4" customFormat="1">
       <c r="A25" s="4" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>3377</v>
+        <v>3376</v>
       </c>
       <c r="C25" s="21" t="s">
         <v>1326</v>
       </c>
       <c r="D25" t="s">
-        <v>3376</v>
+        <v>3375</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>2462</v>
@@ -44906,10 +44906,10 @@
         <v>244</v>
       </c>
       <c r="H25" s="105" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
       <c r="I25" s="220" t="s">
-        <v>3438</v>
+        <v>3437</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="4" customFormat="1">
@@ -44935,10 +44935,10 @@
         <v>159</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="I27" t="s">
-        <v>3167</v>
+        <v>3166</v>
       </c>
       <c r="L27" s="4" t="s">
         <v>813</v>
@@ -44946,7 +44946,7 @@
     </row>
     <row r="28" spans="1:12" s="4" customFormat="1">
       <c r="A28" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>2453</v>
@@ -44958,7 +44958,7 @@
         <v>2028</v>
       </c>
       <c r="E28" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>2462</v>
@@ -44967,10 +44967,10 @@
         <v>325</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>3632</v>
+        <v>3631</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>3398</v>
+        <v>3397</v>
       </c>
       <c r="K28"/>
     </row>
@@ -44988,7 +44988,7 @@
         <v>2865</v>
       </c>
       <c r="E29" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>2896</v>
@@ -45000,7 +45000,7 @@
         <v>2866</v>
       </c>
       <c r="I29" t="s">
-        <v>3265</v>
+        <v>3264</v>
       </c>
       <c r="J29" s="4"/>
       <c r="L29" s="135"/>
@@ -45010,16 +45010,16 @@
         <v>2930</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="C30" s="22" t="s">
         <v>402</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="E30" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>1341</v>
@@ -45028,7 +45028,7 @@
         <v>159</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="I30" s="55" t="s">
         <v>2739</v>
@@ -45036,7 +45036,7 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>3316</v>
+        <v>3315</v>
       </c>
       <c r="B31" s="4">
         <v>69409351</v>
@@ -45057,15 +45057,15 @@
         <v>159</v>
       </c>
       <c r="H31" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="97" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>2843</v>
@@ -45074,7 +45074,7 @@
         <v>2367</v>
       </c>
       <c r="D32" t="s">
-        <v>3665</v>
+        <v>3664</v>
       </c>
       <c r="E32" t="s">
         <v>2371</v>
@@ -45086,10 +45086,10 @@
         <v>159</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>3620</v>
+        <v>3619</v>
       </c>
       <c r="I32" s="455" t="s">
-        <v>3666</v>
+        <v>3665</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -45097,13 +45097,13 @@
         <v>2596</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>3477</v>
+        <v>3476</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>2580</v>
       </c>
       <c r="D33" t="s">
-        <v>3476</v>
+        <v>3475</v>
       </c>
       <c r="E33" t="s">
         <v>2583</v>
@@ -45115,7 +45115,7 @@
         <v>2584</v>
       </c>
       <c r="H33" s="455" t="s">
-        <v>3642</v>
+        <v>3641</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -45123,13 +45123,13 @@
         <v>1429</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>3428</v>
+        <v>3427</v>
       </c>
       <c r="C34" s="21" t="s">
         <v>2577</v>
       </c>
       <c r="D34" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="E34" t="s">
         <v>2583</v>
@@ -45141,10 +45141,10 @@
         <v>159</v>
       </c>
       <c r="H34" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="I34" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="J34" s="4"/>
     </row>
@@ -45171,24 +45171,24 @@
         <v>2584</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>3636</v>
+        <v>3635</v>
       </c>
       <c r="I35" s="49" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="B36" t="s">
-        <v>3346</v>
+        <v>3345</v>
       </c>
       <c r="C36" s="22" t="s">
         <v>2579</v>
       </c>
       <c r="D36" t="s">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="E36" t="s">
         <v>2583</v>
@@ -45200,10 +45200,10 @@
         <v>159</v>
       </c>
       <c r="H36" t="s">
-        <v>3348</v>
+        <v>3347</v>
       </c>
       <c r="I36" t="s">
-        <v>3150</v>
+        <v>3149</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -45211,7 +45211,7 @@
         <v>158</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>3652</v>
+        <v>3651</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>2591</v>
@@ -45229,7 +45229,7 @@
         <v>159</v>
       </c>
       <c r="H37" t="s">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="I37" t="s">
         <v>2919</v>
@@ -45240,7 +45240,7 @@
         <v>157</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>2592</v>
@@ -45258,10 +45258,10 @@
         <v>159</v>
       </c>
       <c r="H38" s="220" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
       <c r="I38" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="455" customFormat="1">
@@ -45274,10 +45274,10 @@
         <v>1351</v>
       </c>
       <c r="E41" s="97" t="s">
+        <v>3258</v>
+      </c>
+      <c r="F41" s="105" t="s">
         <v>3259</v>
-      </c>
-      <c r="F41" s="105" t="s">
-        <v>3260</v>
       </c>
       <c r="G41" s="105" t="s">
         <v>159</v>
@@ -45297,10 +45297,10 @@
         <v>2093</v>
       </c>
       <c r="E42" s="97" t="s">
+        <v>3258</v>
+      </c>
+      <c r="F42" s="105" t="s">
         <v>3259</v>
-      </c>
-      <c r="F42" s="105" t="s">
-        <v>3260</v>
       </c>
       <c r="G42" s="105" t="s">
         <v>159</v>
@@ -45320,10 +45320,10 @@
         <v>2324</v>
       </c>
       <c r="E43" s="105" t="s">
-        <v>3653</v>
+        <v>3652</v>
       </c>
       <c r="F43" s="105" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
       <c r="G43" s="97" t="s">
         <v>159</v>
@@ -45340,7 +45340,7 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="4" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="B45" t="s">
         <v>2495</v>
@@ -45370,7 +45370,7 @@
         <v>2799</v>
       </c>
       <c r="K45" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="4" customFormat="1">
@@ -45744,13 +45744,13 @@
         <v>157</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="C2" s="276" t="s">
         <v>254</v>
       </c>
       <c r="D2" s="106" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>1296</v>
@@ -45762,16 +45762,16 @@
         <v>62</v>
       </c>
       <c r="H2" s="300" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="I2" s="106" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="J2" s="107" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="K2" s="461" t="s">
-        <v>3664</v>
+        <v>3663</v>
       </c>
       <c r="M2" s="159"/>
     </row>
@@ -45786,7 +45786,7 @@
         <v>1179</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="E4" s="32" t="s">
         <v>2392</v>
@@ -45798,25 +45798,25 @@
         <v>270</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="I4" s="30" t="s">
-        <v>3171</v>
+        <v>3170</v>
       </c>
       <c r="J4" s="139" t="s">
-        <v>3530</v>
+        <v>3529</v>
       </c>
       <c r="K4" s="139" t="s">
-        <v>3350</v>
+        <v>3349</v>
       </c>
       <c r="M4" s="39"/>
     </row>
     <row r="5" spans="1:13" s="30" customFormat="1">
       <c r="A5" s="30" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>1112</v>
@@ -45834,22 +45834,22 @@
         <v>65</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
       <c r="I5" s="306" t="s">
         <v>2931</v>
       </c>
       <c r="J5" s="30" t="s">
-        <v>3274</v>
+        <v>3273</v>
       </c>
       <c r="K5" s="30" t="s">
-        <v>3187</v>
+        <v>3186</v>
       </c>
       <c r="M5" s="36"/>
     </row>
     <row r="6" spans="1:13" s="30" customFormat="1">
       <c r="A6" s="107" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B6" s="30" t="s">
         <v>2179</v>
@@ -45858,7 +45858,7 @@
         <v>2744</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="E6" s="140" t="s">
         <v>2707</v>
@@ -45870,22 +45870,22 @@
         <v>65</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>3486</v>
+        <v>3485</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>3027</v>
+        <v>3026</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>3030</v>
+        <v>3029</v>
       </c>
       <c r="K6" s="30" t="s">
-        <v>3149</v>
+        <v>3148</v>
       </c>
       <c r="M6" s="36"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="107" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>1209</v>
@@ -45894,28 +45894,28 @@
         <v>1089</v>
       </c>
       <c r="D7" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
       <c r="E7" s="107" t="s">
+        <v>3261</v>
+      </c>
+      <c r="F7" s="30" t="s">
         <v>3262</v>
-      </c>
-      <c r="F7" s="30" t="s">
-        <v>3263</v>
       </c>
       <c r="G7" s="106" t="s">
         <v>720</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>3569</v>
+        <v>3568</v>
       </c>
       <c r="J7" s="30" t="s">
-        <v>3596</v>
+        <v>3595</v>
       </c>
       <c r="K7" s="30" t="s">
-        <v>3635</v>
+        <v>3634</v>
       </c>
       <c r="M7" s="36"/>
     </row>
@@ -45930,7 +45930,7 @@
         <v>983</v>
       </c>
       <c r="D8" s="139" t="s">
-        <v>3371</v>
+        <v>3370</v>
       </c>
       <c r="E8" s="107" t="s">
         <v>1154</v>
@@ -45942,22 +45942,22 @@
         <v>65</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="I8" s="32" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="J8" s="107" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="K8" s="139" t="s">
-        <v>3327</v>
+        <v>3326</v>
       </c>
       <c r="M8" s="36"/>
     </row>
     <row r="9" spans="1:13" s="107" customFormat="1">
       <c r="A9" s="302" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="B9" s="32" t="s">
         <v>1672</v>
@@ -45978,22 +45978,22 @@
         <v>65</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="I9" s="107" t="s">
-        <v>3514</v>
+        <v>3513</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>3213</v>
+        <v>3212</v>
       </c>
       <c r="K9" s="107" t="s">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="M9" s="36"/>
     </row>
     <row r="10" spans="1:13" s="30" customFormat="1">
       <c r="A10" s="30" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="B10" s="30">
         <v>69575383</v>
@@ -46014,16 +46014,16 @@
         <v>65</v>
       </c>
       <c r="H10" s="107" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
       <c r="I10" t="s">
-        <v>3291</v>
+        <v>3290</v>
       </c>
       <c r="J10" s="219" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="K10" s="107" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
       <c r="M10" s="34"/>
     </row>
@@ -46050,31 +46050,31 @@
         <v>605</v>
       </c>
       <c r="H11" s="139" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="I11" s="30" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
       <c r="J11" s="107" t="s">
-        <v>3619</v>
+        <v>3618</v>
       </c>
       <c r="K11" s="107" t="s">
-        <v>3206</v>
+        <v>3205</v>
       </c>
       <c r="M11" s="36"/>
     </row>
     <row r="12" spans="1:13" s="106" customFormat="1">
       <c r="A12" s="319" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="B12" s="106" t="s">
-        <v>3640</v>
+        <v>3639</v>
       </c>
       <c r="C12" s="22" t="s">
         <v>72</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>3637</v>
+        <v>3636</v>
       </c>
       <c r="E12" s="106" t="s">
         <v>908</v>
@@ -46086,22 +46086,22 @@
         <v>245</v>
       </c>
       <c r="H12" s="30" t="s">
-        <v>3639</v>
+        <v>3638</v>
       </c>
       <c r="I12" s="106" t="s">
-        <v>3481</v>
+        <v>3480</v>
       </c>
       <c r="J12" s="106" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="K12" s="107" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="M12" s="151"/>
     </row>
     <row r="13" spans="1:13" s="107" customFormat="1">
       <c r="A13" s="140" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="B13" s="107" t="s">
         <v>2774</v>
@@ -46110,7 +46110,7 @@
         <v>919</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="E13" s="140" t="s">
         <v>2745</v>
@@ -46122,16 +46122,16 @@
         <v>65</v>
       </c>
       <c r="H13" s="30" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="I13" s="30" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="J13" s="107" t="s">
-        <v>3216</v>
+        <v>3215</v>
       </c>
       <c r="K13" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
       <c r="M13" s="36"/>
     </row>
@@ -46158,13 +46158,13 @@
         <v>65</v>
       </c>
       <c r="H14" s="107" t="s">
-        <v>3297</v>
+        <v>3296</v>
       </c>
       <c r="I14" s="411" t="s">
         <v>2262</v>
       </c>
       <c r="J14" s="32" t="s">
-        <v>3137</v>
+        <v>3136</v>
       </c>
       <c r="M14" s="36"/>
     </row>
@@ -46191,16 +46191,16 @@
         <v>66</v>
       </c>
       <c r="H15" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="I15" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="J15" t="s">
-        <v>3188</v>
+        <v>3187</v>
       </c>
       <c r="K15" s="454" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
       <c r="M15" s="36"/>
     </row>
@@ -46252,16 +46252,16 @@
         <v>66</v>
       </c>
       <c r="H17" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="I17" s="30" t="s">
-        <v>3039</v>
+        <v>3038</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>3556</v>
+        <v>3555</v>
       </c>
       <c r="K17" s="220" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
       <c r="M17" s="34"/>
     </row>
@@ -46288,16 +46288,16 @@
         <v>66</v>
       </c>
       <c r="H18" s="30" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="I18" t="s">
-        <v>3136</v>
+        <v>3135</v>
       </c>
       <c r="J18" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
       <c r="K18" t="s">
-        <v>3625</v>
+        <v>3624</v>
       </c>
       <c r="M18" s="36"/>
     </row>
@@ -46312,7 +46312,7 @@
         <v>1689</v>
       </c>
       <c r="D19" s="134" t="s">
-        <v>3372</v>
+        <v>3371</v>
       </c>
       <c r="E19" t="s">
         <v>1692</v>
@@ -46324,16 +46324,16 @@
         <v>66</v>
       </c>
       <c r="H19" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="I19" s="49" t="s">
         <v>2903</v>
       </c>
       <c r="J19" s="220" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
       <c r="K19" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="M19" s="36"/>
     </row>
@@ -46348,7 +46348,7 @@
         <v>2476</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="E20" s="107" t="s">
         <v>2406</v>
@@ -46360,31 +46360,31 @@
         <v>65</v>
       </c>
       <c r="H20" s="436" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="I20" t="s">
+        <v>2973</v>
+      </c>
+      <c r="J20" s="49" t="s">
         <v>2974</v>
       </c>
-      <c r="J20" s="49" t="s">
-        <v>2975</v>
-      </c>
       <c r="K20" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="M20" s="36"/>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="B21" t="s">
-        <v>3307</v>
+        <v>3306</v>
       </c>
       <c r="C21" s="22" t="s">
         <v>1127</v>
       </c>
       <c r="D21" t="s">
-        <v>3306</v>
+        <v>3305</v>
       </c>
       <c r="E21" s="140" t="s">
         <v>1589</v>
@@ -46396,19 +46396,19 @@
         <v>65</v>
       </c>
       <c r="H21" t="s">
-        <v>3311</v>
+        <v>3310</v>
       </c>
       <c r="I21" t="s">
+        <v>3313</v>
+      </c>
+      <c r="J21" t="s">
         <v>3314</v>
-      </c>
-      <c r="J21" t="s">
-        <v>3315</v>
       </c>
       <c r="M21" s="36"/>
     </row>
     <row r="22" spans="1:13" s="30" customFormat="1">
       <c r="A22" s="30" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="B22" s="30" t="s">
         <v>2109</v>
@@ -46417,78 +46417,78 @@
         <v>2710</v>
       </c>
       <c r="D22" s="107" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
       <c r="E22" s="30" t="s">
+        <v>3328</v>
+      </c>
+      <c r="F22" s="30" t="s">
         <v>3329</v>
-      </c>
-      <c r="F22" s="30" t="s">
-        <v>3330</v>
       </c>
       <c r="G22" s="32" t="s">
         <v>65</v>
       </c>
       <c r="H22" s="30" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="I22" s="30" t="s">
+        <v>3335</v>
+      </c>
+      <c r="J22" s="30" t="s">
         <v>3336</v>
-      </c>
-      <c r="J22" s="30" t="s">
-        <v>3337</v>
       </c>
       <c r="M22" s="36"/>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="B23" t="s">
-        <v>3351</v>
+        <v>3350</v>
       </c>
       <c r="C23" s="22" t="s">
         <v>1902</v>
       </c>
       <c r="D23" t="s">
-        <v>3404</v>
+        <v>3403</v>
       </c>
       <c r="E23" s="30" t="s">
+        <v>3328</v>
+      </c>
+      <c r="F23" s="30" t="s">
         <v>3329</v>
-      </c>
-      <c r="F23" s="30" t="s">
-        <v>3330</v>
       </c>
       <c r="G23" t="s">
         <v>66</v>
       </c>
       <c r="H23" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="I23" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
       <c r="J23" t="s">
-        <v>3433</v>
+        <v>3432</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="30" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="B24" t="s">
-        <v>3663</v>
+        <v>3662</v>
       </c>
       <c r="C24" s="22" t="s">
         <v>1916</v>
       </c>
       <c r="D24" s="455" t="s">
-        <v>3585</v>
+        <v>3584</v>
       </c>
       <c r="E24" s="107" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="F24" s="30" t="s">
-        <v>3662</v>
+        <v>3661</v>
       </c>
       <c r="G24" s="32" t="s">
         <v>270</v>
@@ -46531,7 +46531,7 @@
     </row>
     <row r="31" spans="1:13" s="30" customFormat="1">
       <c r="A31" s="107" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="B31" s="107">
         <v>64403333</v>
@@ -46579,7 +46579,7 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="B33">
         <v>60389752</v>
@@ -46602,7 +46602,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="B34">
         <v>60389752</v>
@@ -46611,13 +46611,13 @@
         <v>2169</v>
       </c>
       <c r="D34" s="32" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="E34" s="30" t="s">
+        <v>3328</v>
+      </c>
+      <c r="F34" s="30" t="s">
         <v>3329</v>
-      </c>
-      <c r="F34" s="30" t="s">
-        <v>3330</v>
       </c>
       <c r="G34" t="s">
         <v>3</v>
@@ -46626,7 +46626,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="B35">
         <v>60389752</v>
@@ -46650,7 +46650,7 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B36">
         <v>60389752</v>
@@ -46674,7 +46674,7 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="30" t="s">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="B37" s="30">
         <v>64403333</v>
@@ -46699,7 +46699,7 @@
     </row>
     <row r="38" spans="1:13" s="30" customFormat="1">
       <c r="A38" s="30" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="B38" s="30">
         <v>60389752</v>
@@ -46736,10 +46736,10 @@
         <v>2142</v>
       </c>
       <c r="E39" t="s">
+        <v>3328</v>
+      </c>
+      <c r="F39" t="s">
         <v>3329</v>
-      </c>
-      <c r="F39" t="s">
-        <v>3330</v>
       </c>
       <c r="G39" t="s">
         <v>3</v>
@@ -46808,7 +46808,7 @@
         <v>2502</v>
       </c>
       <c r="E45" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
       <c r="F45" s="30" t="s">
         <v>2503</v>
@@ -46817,10 +46817,10 @@
         <v>369</v>
       </c>
       <c r="H45" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="I45" s="30" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
       <c r="J45" s="49" t="s">
         <v>2928</v>
@@ -46878,7 +46878,7 @@
         <v>1106</v>
       </c>
       <c r="D65" s="97" t="s">
-        <v>3583</v>
+        <v>3582</v>
       </c>
       <c r="E65" s="107" t="s">
         <v>1123</v>
@@ -46896,10 +46896,10 @@
         <v>1122</v>
       </c>
       <c r="C66" s="97" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="D66" s="97" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="E66" s="97" t="s">
         <v>2404</v>
@@ -46919,24 +46919,24 @@
         <v>2164</v>
       </c>
       <c r="E67" s="107" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="F67" s="30" t="s">
-        <v>3662</v>
+        <v>3661</v>
       </c>
     </row>
     <row r="68" spans="1:38">
       <c r="C68" s="459" t="s">
+        <v>3544</v>
+      </c>
+      <c r="D68" t="s">
         <v>3545</v>
       </c>
-      <c r="D68" t="s">
-        <v>3546</v>
-      </c>
       <c r="E68" s="107" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="F68" s="30" t="s">
-        <v>3662</v>
+        <v>3661</v>
       </c>
       <c r="G68" s="106" t="s">
         <v>720</v>
@@ -46947,13 +46947,13 @@
         <v>1211</v>
       </c>
       <c r="D69" s="97" t="s">
-        <v>3584</v>
+        <v>3583</v>
       </c>
       <c r="E69" s="107" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="F69" s="30" t="s">
-        <v>3662</v>
+        <v>3661</v>
       </c>
       <c r="G69" s="106" t="s">
         <v>720</v>
@@ -47234,7 +47234,7 @@
         <v>1130</v>
       </c>
       <c r="D93" t="s">
-        <v>3325</v>
+        <v>3324</v>
       </c>
       <c r="E93" s="140" t="s">
         <v>1132</v>
@@ -47258,7 +47258,7 @@
         <v>1390</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>3326</v>
+        <v>3325</v>
       </c>
       <c r="E94" s="266" t="s">
         <v>1505</v>
@@ -47312,7 +47312,7 @@
         <v>358</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
     </row>
     <row r="105" spans="2:5">
@@ -47538,7 +47538,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>3654</v>
+        <v>3653</v>
       </c>
       <c r="C12" s="236"/>
     </row>
@@ -47676,7 +47676,7 @@
       </c>
       <c r="B24" s="87"/>
       <c r="F24" s="2" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -47752,27 +47752,27 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="87" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="C40" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="F40" s="45"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="89" t="s">
-        <v>3385</v>
+        <v>3384</v>
       </c>
       <c r="C41" t="s">
-        <v>3388</v>
+        <v>3387</v>
       </c>
     </row>
     <row r="42" spans="2:6" ht="15" thickBot="1">
       <c r="B42" s="86" t="s">
-        <v>3386</v>
+        <v>3385</v>
       </c>
       <c r="C42" t="s">
-        <v>3389</v>
+        <v>3388</v>
       </c>
     </row>
     <row r="43" spans="2:6">
@@ -47935,22 +47935,22 @@
         <v>2033</v>
       </c>
       <c r="E6" s="247" t="s">
+        <v>3251</v>
+      </c>
+      <c r="F6" s="247" t="s">
         <v>3252</v>
-      </c>
-      <c r="F6" s="247" t="s">
-        <v>3253</v>
       </c>
       <c r="G6" s="247" t="s">
         <v>357</v>
       </c>
       <c r="H6" s="247" t="s">
-        <v>3212</v>
+        <v>3211</v>
       </c>
       <c r="I6" s="244" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="J6" s="295" t="s">
-        <v>3609</v>
+        <v>3608</v>
       </c>
       <c r="K6" s="247" t="s">
         <v>475</v>
@@ -47973,19 +47973,19 @@
         <v>1036</v>
       </c>
       <c r="F7" s="265" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="G7" s="265" t="s">
         <v>690</v>
       </c>
       <c r="H7" s="295" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="I7" s="295" t="s">
-        <v>2987</v>
+        <v>2986</v>
       </c>
       <c r="J7" s="295" t="s">
-        <v>3454</v>
+        <v>3453</v>
       </c>
       <c r="K7" s="265" t="s">
         <v>709</v>
@@ -48008,19 +48008,19 @@
         <v>1228</v>
       </c>
       <c r="F8" s="265" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
       <c r="G8" s="265" t="s">
         <v>250</v>
       </c>
       <c r="H8" s="265" t="s">
-        <v>3601</v>
+        <v>3600</v>
       </c>
       <c r="I8" s="265" t="s">
-        <v>3398</v>
+        <v>3397</v>
       </c>
       <c r="J8" s="265" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
       <c r="K8" s="259"/>
       <c r="L8" s="259"/>
@@ -48042,7 +48042,7 @@
         <v>2695</v>
       </c>
       <c r="F9" s="263" t="s">
-        <v>3352</v>
+        <v>3351</v>
       </c>
       <c r="G9" s="263" t="s">
         <v>946</v>
@@ -48074,13 +48074,13 @@
         <v>690</v>
       </c>
       <c r="H10" s="264" t="s">
-        <v>3644</v>
+        <v>3643</v>
       </c>
       <c r="I10" s="448" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="J10" s="264" t="s">
-        <v>3533</v>
+        <v>3532</v>
       </c>
       <c r="K10" s="245" t="s">
         <v>1203</v>
@@ -48091,7 +48091,7 @@
         <v>2500</v>
       </c>
       <c r="B11" s="262" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="C11" s="194" t="s">
         <v>491</v>
@@ -48109,13 +48109,13 @@
         <v>690</v>
       </c>
       <c r="H11" s="215" t="s">
-        <v>3437</v>
+        <v>3436</v>
       </c>
       <c r="I11" s="424" t="s">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="J11" s="269" t="s">
-        <v>3550</v>
+        <v>3549</v>
       </c>
       <c r="K11" s="183" t="s">
         <v>1204</v>
@@ -48149,10 +48149,10 @@
     </row>
     <row r="13" spans="1:12" s="223" customFormat="1">
       <c r="A13" s="223" t="s">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="B13" s="223" t="s">
-        <v>3324</v>
+        <v>3323</v>
       </c>
       <c r="C13" s="423" t="s">
         <v>335</v>
@@ -48161,22 +48161,22 @@
         <v>2390</v>
       </c>
       <c r="E13" s="223" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="F13" s="223" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="G13" s="223" t="s">
         <v>690</v>
       </c>
       <c r="H13" s="223" t="s">
+        <v>3024</v>
+      </c>
+      <c r="I13" s="215" t="s">
+        <v>3222</v>
+      </c>
+      <c r="J13" s="223" t="s">
         <v>3025</v>
-      </c>
-      <c r="I13" s="215" t="s">
-        <v>3223</v>
-      </c>
-      <c r="J13" s="223" t="s">
-        <v>3026</v>
       </c>
       <c r="K13" s="223" t="s">
         <v>1317</v>
@@ -48196,7 +48196,7 @@
         <v>1972</v>
       </c>
       <c r="E14" s="216" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="F14" s="216" t="s">
         <v>1433</v>
@@ -48205,13 +48205,13 @@
         <v>690</v>
       </c>
       <c r="H14" s="272" t="s">
-        <v>3455</v>
+        <v>3454</v>
       </c>
       <c r="I14" s="215" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="J14" s="262" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="K14" s="183" t="s">
         <v>1205</v>
@@ -48222,7 +48222,7 @@
         <v>1416</v>
       </c>
       <c r="B15" s="264" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
       <c r="C15" s="270" t="s">
         <v>1305</v>
@@ -48240,13 +48240,13 @@
         <v>690</v>
       </c>
       <c r="H15" s="264" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
       <c r="I15" s="271" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
       <c r="J15" s="264" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="K15" s="259" t="s">
         <v>1438</v>
@@ -48304,7 +48304,7 @@
     </row>
     <row r="18" spans="1:11" s="259" customFormat="1">
       <c r="A18" s="271" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B18" s="259" t="s">
         <v>2332</v>
@@ -48313,7 +48313,7 @@
         <v>831</v>
       </c>
       <c r="D18" s="264" t="s">
-        <v>3467</v>
+        <v>3466</v>
       </c>
       <c r="E18" s="264" t="s">
         <v>1788</v>
@@ -48325,13 +48325,13 @@
         <v>690</v>
       </c>
       <c r="H18" s="259" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="I18" s="298" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
       <c r="J18" s="259" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="K18" s="264" t="s">
         <v>1765</v>
@@ -48339,7 +48339,7 @@
     </row>
     <row r="19" spans="1:11" s="259" customFormat="1">
       <c r="A19" s="259" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="B19" s="259" t="s">
         <v>2377</v>
@@ -48360,13 +48360,13 @@
         <v>690</v>
       </c>
       <c r="H19" s="259" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="I19" s="259" t="s">
-        <v>3429</v>
+        <v>3428</v>
       </c>
       <c r="J19" s="259" t="s">
-        <v>3041</v>
+        <v>3040</v>
       </c>
       <c r="K19" s="259" t="s">
         <v>1810</v>
@@ -48374,7 +48374,7 @@
     </row>
     <row r="20" spans="1:11" s="264" customFormat="1">
       <c r="A20" s="298" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="B20" s="304">
         <v>63609244</v>
@@ -48398,10 +48398,10 @@
         <v>2761</v>
       </c>
       <c r="I20" s="264" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="J20" s="264" t="s">
-        <v>3344</v>
+        <v>3343</v>
       </c>
       <c r="K20" s="259" t="s">
         <v>1812</v>
@@ -48444,10 +48444,10 @@
         <v>637</v>
       </c>
       <c r="D22" s="255" t="s">
-        <v>3468</v>
+        <v>3467</v>
       </c>
       <c r="E22" s="271" t="s">
-        <v>3391</v>
+        <v>3390</v>
       </c>
       <c r="F22" s="271" t="s">
         <v>1710</v>
@@ -48456,13 +48456,13 @@
         <v>250</v>
       </c>
       <c r="H22" s="259" t="s">
-        <v>3479</v>
+        <v>3478</v>
       </c>
       <c r="I22" s="264" t="s">
-        <v>3224</v>
+        <v>3223</v>
       </c>
       <c r="J22" s="264" t="s">
-        <v>3126</v>
+        <v>3125</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="97" customFormat="1">
@@ -48683,7 +48683,7 @@
         <v>840</v>
       </c>
       <c r="D45" s="264" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
       <c r="E45" s="259" t="s">
         <v>1788</v>
@@ -48886,13 +48886,13 @@
         <v>2770</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
       <c r="I2" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
       <c r="J2" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="L2" s="36" t="s">
         <v>1173</v>
@@ -48918,7 +48918,7 @@
         <v>298</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>707</v>
@@ -48947,19 +48947,19 @@
         <v>2917</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>323</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="H4" t="s">
-        <v>3016</v>
+        <v>3015</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>3535</v>
+        <v>3534</v>
       </c>
       <c r="J4" t="s">
         <v>2918</v>
@@ -48988,7 +48988,7 @@
         <v>424</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="H5" s="49" t="s">
         <v>2738</v>
@@ -49003,7 +49003,7 @@
     </row>
     <row r="6" spans="1:12" s="4" customFormat="1">
       <c r="A6" s="4" t="s">
-        <v>3513</v>
+        <v>3512</v>
       </c>
       <c r="B6" s="4">
         <v>65436260</v>
@@ -49021,13 +49021,13 @@
         <v>166</v>
       </c>
       <c r="G6" t="s">
-        <v>3237</v>
+        <v>3236</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>3570</v>
+        <v>3569</v>
       </c>
       <c r="I6" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="J6" s="49" t="s">
         <v>2885</v>
@@ -49038,7 +49038,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="4" t="s">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="B7" s="4">
         <v>69561522</v>
@@ -49047,25 +49047,25 @@
         <v>434</v>
       </c>
       <c r="D7" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="E7" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="F7" t="s">
         <v>151</v>
       </c>
       <c r="G7" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="J7" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
       <c r="L7" s="83" t="s">
         <v>435</v>
@@ -49073,7 +49073,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="4" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2936</v>
@@ -49094,10 +49094,10 @@
         <v>2636</v>
       </c>
       <c r="H8" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="I8" s="49" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
       <c r="J8" s="49" t="s">
         <v>2769</v>
@@ -49124,16 +49124,16 @@
         <v>151</v>
       </c>
       <c r="G9" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="H9" s="220" t="s">
-        <v>3083</v>
+        <v>3082</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="J9" s="220" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -49147,7 +49147,7 @@
         <v>2196</v>
       </c>
       <c r="D10" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="E10" t="s">
         <v>2167</v>
@@ -49156,13 +49156,13 @@
         <v>1818</v>
       </c>
       <c r="G10" t="s">
-        <v>3257</v>
+        <v>3256</v>
       </c>
       <c r="H10" s="49" t="s">
-        <v>3482</v>
+        <v>3481</v>
       </c>
       <c r="I10" t="s">
-        <v>3285</v>
+        <v>3284</v>
       </c>
       <c r="J10" s="49" t="s">
         <v>2831</v>
@@ -49205,7 +49205,7 @@
         <v>1478</v>
       </c>
       <c r="E12" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="F12" t="s">
         <v>614</v>
@@ -49213,7 +49213,7 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="B13">
         <v>64403333</v>
@@ -49236,16 +49236,16 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
       <c r="B14" t="s">
-        <v>3226</v>
+        <v>3225</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>281</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>3225</v>
+        <v>3224</v>
       </c>
       <c r="E14" t="s">
         <v>2136</v>
@@ -49254,16 +49254,16 @@
         <v>1818</v>
       </c>
       <c r="G14" t="s">
-        <v>3634</v>
+        <v>3633</v>
       </c>
       <c r="H14" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="I14" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="J14" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -49531,7 +49531,7 @@
     </row>
     <row r="2" spans="1:14" ht="43.15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="C2" s="51"/>
       <c r="D2" s="52" t="s">
@@ -49555,7 +49555,7 @@
         <v>2667</v>
       </c>
       <c r="E4" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -49592,7 +49592,7 @@
         <v>1550</v>
       </c>
       <c r="E9" t="s">
-        <v>3567</v>
+        <v>3566</v>
       </c>
       <c r="F9" t="s">
         <v>1732</v>
@@ -49600,7 +49600,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="B10">
         <v>63000545</v>
@@ -49612,7 +49612,7 @@
         <v>2211</v>
       </c>
       <c r="E10" t="s">
-        <v>3552</v>
+        <v>3551</v>
       </c>
       <c r="F10" t="s">
         <v>1681</v>
@@ -49632,7 +49632,7 @@
         <v>2054</v>
       </c>
       <c r="E11" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -49649,7 +49649,7 @@
         <v>2676</v>
       </c>
       <c r="E12" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="F12" t="s">
         <v>1681</v>
@@ -49657,7 +49657,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>3301</v>
+        <v>3300</v>
       </c>
       <c r="B13">
         <v>62271547</v>
@@ -49686,7 +49686,7 @@
         <v>1936</v>
       </c>
       <c r="D14" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="E14" t="s">
         <v>2637</v>
@@ -49697,7 +49697,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="B15">
         <v>62806425</v>
@@ -49726,10 +49726,10 @@
         <v>2723</v>
       </c>
       <c r="D16" s="30" t="s">
+        <v>3013</v>
+      </c>
+      <c r="E16" t="s">
         <v>3014</v>
-      </c>
-      <c r="E16" t="s">
-        <v>3015</v>
       </c>
       <c r="F16" t="s">
         <v>2679</v>
@@ -49746,10 +49746,10 @@
         <v>2927</v>
       </c>
       <c r="D17" s="30" t="s">
+        <v>3027</v>
+      </c>
+      <c r="E17" t="s">
         <v>3028</v>
-      </c>
-      <c r="E17" t="s">
-        <v>3029</v>
       </c>
       <c r="F17" t="s">
         <v>2679</v>
@@ -49772,7 +49772,7 @@
         <v>2727</v>
       </c>
       <c r="E18" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="F18" t="s">
         <v>2679</v>
@@ -49792,7 +49792,7 @@
         <v>2767</v>
       </c>
       <c r="E19" t="s">
-        <v>3168</v>
+        <v>3167</v>
       </c>
       <c r="F19" t="s">
         <v>2907</v>
@@ -49815,7 +49815,7 @@
         <v>1512</v>
       </c>
       <c r="F21" t="s">
-        <v>3295</v>
+        <v>3294</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -49863,13 +49863,13 @@
         <v>2653</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>2988</v>
+      </c>
+      <c r="F26" t="s">
         <v>2989</v>
       </c>
-      <c r="F26" t="s">
-        <v>2990</v>
-      </c>
       <c r="G26" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -49886,13 +49886,13 @@
         <v>421</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="F27" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="G27" t="s">
-        <v>3053</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -49903,16 +49903,16 @@
         <v>1461</v>
       </c>
       <c r="D29" t="s">
+        <v>3265</v>
+      </c>
+      <c r="E29" t="s">
+        <v>3214</v>
+      </c>
+      <c r="F29" t="s">
+        <v>3003</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>3266</v>
-      </c>
-      <c r="E29" t="s">
-        <v>3215</v>
-      </c>
-      <c r="F29" t="s">
-        <v>3004</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>3267</v>
       </c>
       <c r="H29" t="s">
         <v>407</v>
@@ -49932,10 +49932,10 @@
         <v>2678</v>
       </c>
       <c r="E30" t="s">
+        <v>3002</v>
+      </c>
+      <c r="F30" t="s">
         <v>3003</v>
-      </c>
-      <c r="F30" t="s">
-        <v>3004</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -49949,10 +49949,10 @@
         <v>1557</v>
       </c>
       <c r="D31" t="s">
+        <v>3237</v>
+      </c>
+      <c r="E31" t="s">
         <v>3238</v>
-      </c>
-      <c r="E31" t="s">
-        <v>3239</v>
       </c>
       <c r="F31" t="s">
         <v>1313</v>
@@ -51996,12 +51996,12 @@
     </row>
     <row r="252" spans="1:6" s="420" customFormat="1" ht="21">
       <c r="C252" s="420" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="253" spans="1:6">
       <c r="A253" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="B253">
         <v>64476521</v>
@@ -52013,10 +52013,10 @@
         <v>2241</v>
       </c>
       <c r="E253" t="s">
+        <v>2960</v>
+      </c>
+      <c r="F253" t="s">
         <v>2961</v>
-      </c>
-      <c r="F253" t="s">
-        <v>2962</v>
       </c>
     </row>
     <row r="254" spans="1:6">
@@ -52033,10 +52033,10 @@
         <v>2920</v>
       </c>
       <c r="E254" t="s">
+        <v>2960</v>
+      </c>
+      <c r="F254" t="s">
         <v>2961</v>
-      </c>
-      <c r="F254" t="s">
-        <v>2962</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -52053,15 +52053,15 @@
         <v>2622</v>
       </c>
       <c r="E255" t="s">
+        <v>2960</v>
+      </c>
+      <c r="F255" t="s">
         <v>2961</v>
-      </c>
-      <c r="F255" t="s">
-        <v>2962</v>
       </c>
     </row>
     <row r="256" spans="1:6">
       <c r="A256" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="B256">
         <v>61915064</v>
@@ -56810,7 +56810,7 @@
         <v>2667</v>
       </c>
       <c r="E537" s="76" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="F537" s="76"/>
       <c r="G537" s="76"/>

--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dc549f2659ed9bd7/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63991" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74A4DC3A-CCB9-463D-A0CC-9E3C4578F40A}"/>
+  <xr:revisionPtr revIDLastSave="63993" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C92A05E3-D526-47A8-A329-6041457288ED}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12223,13 +12223,13 @@
     <t>65208339 1 pantalla hasta el 29 de octubre (Yaribel)</t>
   </si>
   <si>
-    <t>N004 1 pantalla hasta el 30 de octubre</t>
-  </si>
-  <si>
-    <t>N005 1 pantalla hasta el 30 de octubre</t>
-  </si>
-  <si>
     <t xml:space="preserve">65014102-fran 1 pantalla hasta el 30 de octubre </t>
+  </si>
+  <si>
+    <t>N004 1 pantalla hasta el 30 de octubre 290826-2000y</t>
+  </si>
+  <si>
+    <t>N005 1 pantalla hasta el 30 de octubre 290926-1940h</t>
   </si>
 </sst>
 </file>
@@ -31495,16 +31495,16 @@
         <v>198</v>
       </c>
       <c r="H49" s="145" t="s">
-        <v>3677</v>
+        <v>3678</v>
       </c>
       <c r="I49" s="145" t="s">
-        <v>3678</v>
+        <v>3679</v>
       </c>
       <c r="J49" s="30" t="s">
         <v>3382</v>
       </c>
       <c r="K49" s="453" t="s">
-        <v>3679</v>
+        <v>3677</v>
       </c>
     </row>
     <row r="50" spans="1:12" s="164" customFormat="1">

--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dc549f2659ed9bd7/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64649" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02066CA7-3DB2-456F-82B5-DC44A7807522}"/>
+  <xr:revisionPtr revIDLastSave="64661" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76148D05-9666-4021-892D-1FB1103C5582}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9439,9 +9439,6 @@
     <t>Luisjorge14170+net01@gmail.com</t>
   </si>
   <si>
-    <t>Hss050826</t>
-  </si>
-  <si>
     <t>63104189 1 pantalla ahsta el 04 de noviembre (Yuli)</t>
   </si>
   <si>
@@ -10066,9 +10063,6 @@
     <t>15,66 hasta 25 de octubre</t>
   </si>
   <si>
-    <t>60526532 1 pantalla hasta el 30 de septiembre (Edwin) 280826-0431l</t>
-  </si>
-  <si>
     <t>Hya310826</t>
   </si>
   <si>
@@ -11983,12 +11977,6 @@
     <t>64183562 1 pantalla hasta el 01 de noviembre 220926-2350e</t>
   </si>
   <si>
-    <t>63325272  280826-0400d</t>
-  </si>
-  <si>
-    <t>65014102 1 pantalla hasta el 01 de octubre 280826-0427c</t>
-  </si>
-  <si>
     <t>https://www.spotify.com/ng/family/join/invite/XY87Acy72z560B3/</t>
   </si>
   <si>
@@ -12103,9 +12091,6 @@
     <t>63164544 1 pantalla hasta el 01 de noviembre</t>
   </si>
   <si>
-    <t>67620550 1 pantalla hasta el 01 de noviembre 280826-0430z</t>
-  </si>
-  <si>
     <t>64284799 1 pantalla hasta el 01 de noviembre (Cesar)</t>
   </si>
   <si>
@@ -12254,6 +12239,21 @@
   </si>
   <si>
     <t>N004 1 pantalla hasta el 05 de noviembre 051026-0002f</t>
+  </si>
+  <si>
+    <t>Yts051026</t>
+  </si>
+  <si>
+    <t>67620550 1 pantalla hasta el 01 de noviembre (N) 280826-0430z</t>
+  </si>
+  <si>
+    <t>N003 051026-0005f</t>
+  </si>
+  <si>
+    <t>N004 1 pantalla hasta el 05 de noviembre 051026-0010r</t>
+  </si>
+  <si>
+    <t>N005 1 pantalla hasta el 05 de noviembre 051026-0015d</t>
   </si>
 </sst>
 </file>
@@ -18372,53 +18372,6 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1416050</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="155474" cy="114073"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="56" name="Imagen 38">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5794DD7-886B-4D7F-98F3-144B84F2E6CF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-            <a:ext uri="{837473B0-CC2E-450A-ABE3-18F120FF3D39}">
-              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId10"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect l="29804" t="7200" r="26959" b="6400"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1416050" y="11468100"/>
-          <a:ext cx="155474" cy="114073"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
       <xdr:colOff>1320800</xdr:colOff>
       <xdr:row>62</xdr:row>
       <xdr:rowOff>88900</xdr:rowOff>
@@ -30699,7 +30652,7 @@
   <sheetData>
     <row r="1" spans="1:11" s="30" customFormat="1">
       <c r="A1" s="30" t="s">
-        <v>3535</v>
+        <v>3533</v>
       </c>
       <c r="B1" s="30">
         <v>60389752</v>
@@ -30711,7 +30664,7 @@
         <v>1987</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>3320</v>
+        <v>3318</v>
       </c>
       <c r="F1" s="30" t="s">
         <v>2052</v>
@@ -30722,7 +30675,7 @@
     </row>
     <row r="2" spans="1:11" s="148" customFormat="1">
       <c r="A2" s="148" t="s">
-        <v>3451</v>
+        <v>3449</v>
       </c>
       <c r="B2" s="148">
         <v>62360487</v>
@@ -30731,7 +30684,7 @@
         <v>2097</v>
       </c>
       <c r="D2" s="148" t="s">
-        <v>3477</v>
+        <v>3475</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="148" customFormat="1">
@@ -30750,7 +30703,7 @@
     </row>
     <row r="4" spans="1:11" s="30" customFormat="1">
       <c r="A4" s="30" t="s">
-        <v>3535</v>
+        <v>3533</v>
       </c>
       <c r="B4" s="30">
         <v>60389752</v>
@@ -30762,7 +30715,7 @@
         <v>1985</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>3389</v>
+        <v>3387</v>
       </c>
       <c r="F4" s="30" t="s">
         <v>2052</v>
@@ -30773,7 +30726,7 @@
     </row>
     <row r="5" spans="1:11" s="148" customFormat="1">
       <c r="A5" s="148" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
       <c r="B5" s="148">
         <v>60240509</v>
@@ -30782,12 +30735,12 @@
         <v>2111</v>
       </c>
       <c r="D5" s="148" t="s">
-        <v>3565</v>
+        <v>3563</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="148" customFormat="1">
       <c r="A6" s="225" t="s">
-        <v>2763</v>
+        <v>2762</v>
       </c>
       <c r="B6" s="148">
         <v>68241069</v>
@@ -30801,7 +30754,7 @@
     </row>
     <row r="7" spans="1:11" s="30" customFormat="1">
       <c r="A7" s="30" t="s">
-        <v>3539</v>
+        <v>3537</v>
       </c>
       <c r="B7" s="30">
         <v>60389752</v>
@@ -30810,10 +30763,10 @@
         <v>1988</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>2754</v>
+        <v>2753</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>3471</v>
+        <v>3469</v>
       </c>
       <c r="F7" s="30" t="s">
         <v>2057</v>
@@ -30824,7 +30777,7 @@
     </row>
     <row r="8" spans="1:11" s="148" customFormat="1">
       <c r="A8" s="225" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
       <c r="B8" s="148">
         <v>66003234</v>
@@ -30833,7 +30786,7 @@
         <v>2210</v>
       </c>
       <c r="D8" s="148" t="s">
-        <v>3250</v>
+        <v>3248</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="148" customFormat="1">
@@ -30855,7 +30808,7 @@
     </row>
     <row r="10" spans="1:11" s="421" customFormat="1">
       <c r="A10" s="421" t="s">
-        <v>3488</v>
+        <v>3486</v>
       </c>
       <c r="B10" s="421">
         <v>60389752</v>
@@ -30867,7 +30820,7 @@
         <v>2069</v>
       </c>
       <c r="E10" s="421" t="s">
-        <v>3519</v>
+        <v>3517</v>
       </c>
       <c r="F10" s="421" t="s">
         <v>2715</v>
@@ -30880,7 +30833,7 @@
     <row r="12" spans="1:11" s="367" customFormat="1"/>
     <row r="13" spans="1:11" s="30" customFormat="1">
       <c r="A13" s="30" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B13" s="30">
         <v>69184177</v>
@@ -30889,10 +30842,10 @@
         <v>1754</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>3343</v>
+        <v>3341</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>3559</v>
+        <v>3557</v>
       </c>
       <c r="F13" s="30" t="s">
         <v>2115</v>
@@ -30904,7 +30857,7 @@
     </row>
     <row r="14" spans="1:11" s="148" customFormat="1">
       <c r="A14" s="225" t="s">
-        <v>3270</v>
+        <v>3268</v>
       </c>
       <c r="B14" s="225" t="s">
         <v>1655</v>
@@ -30918,7 +30871,7 @@
     </row>
     <row r="15" spans="1:11" s="148" customFormat="1">
       <c r="A15" s="225" t="s">
-        <v>3136</v>
+        <v>3134</v>
       </c>
       <c r="B15" s="414">
         <v>62439069</v>
@@ -30932,7 +30885,7 @@
     </row>
     <row r="16" spans="1:11" s="32" customFormat="1">
       <c r="A16" s="30" t="s">
-        <v>3178</v>
+        <v>3176</v>
       </c>
       <c r="B16" s="282" t="s">
         <v>2167</v>
@@ -30941,10 +30894,10 @@
         <v>1509</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>2874</v>
+        <v>2873</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>3593</v>
+        <v>3591</v>
       </c>
       <c r="F16" s="32" t="s">
         <v>1510</v>
@@ -30953,21 +30906,21 @@
         <v>198</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>3483</v>
+        <v>3481</v>
       </c>
       <c r="I16" s="32" t="s">
-        <v>3383</v>
+        <v>3381</v>
       </c>
       <c r="J16" s="32" t="s">
-        <v>3454</v>
+        <v>3452</v>
       </c>
       <c r="K16" s="30" t="s">
-        <v>3643</v>
+        <v>3638</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="164" customFormat="1">
       <c r="A17" s="250" t="s">
-        <v>3093</v>
+        <v>3091</v>
       </c>
       <c r="B17" s="250" t="s">
         <v>1385</v>
@@ -30984,7 +30937,7 @@
     </row>
     <row r="18" spans="1:11" s="164" customFormat="1">
       <c r="A18" s="250" t="s">
-        <v>3292</v>
+        <v>3290</v>
       </c>
       <c r="B18" s="250">
         <v>64341760</v>
@@ -31006,10 +30959,10 @@
         <v>1474</v>
       </c>
       <c r="D19" s="145" t="s">
-        <v>3196</v>
+        <v>3194</v>
       </c>
       <c r="E19" s="145" t="s">
-        <v>3472</v>
+        <v>3470</v>
       </c>
       <c r="F19" s="145" t="s">
         <v>1352</v>
@@ -31024,7 +30977,7 @@
     </row>
     <row r="20" spans="1:11" s="295" customFormat="1">
       <c r="A20" s="164" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
       <c r="B20" s="164">
         <v>68444421</v>
@@ -31033,7 +30986,7 @@
         <v>1661</v>
       </c>
       <c r="D20" s="250" t="s">
-        <v>2834</v>
+        <v>2833</v>
       </c>
       <c r="E20" s="250" t="s">
         <v>1662</v>
@@ -31041,7 +30994,7 @@
     </row>
     <row r="21" spans="1:11" s="295" customFormat="1">
       <c r="A21" s="250" t="s">
-        <v>3204</v>
+        <v>3202</v>
       </c>
       <c r="B21" s="250">
         <v>62169673</v>
@@ -31050,7 +31003,7 @@
         <v>1666</v>
       </c>
       <c r="D21" s="164" t="s">
-        <v>3197</v>
+        <v>3195</v>
       </c>
       <c r="E21" s="164" t="s">
         <v>1667</v>
@@ -31058,7 +31011,7 @@
     </row>
     <row r="22" spans="1:11" s="30" customFormat="1">
       <c r="A22" s="32" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="B22" s="32">
         <v>60389752</v>
@@ -31070,7 +31023,7 @@
         <v>2094</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>3320</v>
+        <v>3318</v>
       </c>
       <c r="F22" s="30" t="s">
         <v>2051</v>
@@ -31081,7 +31034,7 @@
     </row>
     <row r="23" spans="1:11" s="148" customFormat="1">
       <c r="A23" s="225" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="B23" s="148">
         <v>64858241</v>
@@ -31095,7 +31048,7 @@
     </row>
     <row r="24" spans="1:11" s="148" customFormat="1">
       <c r="A24" s="149" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="B24" s="149">
         <v>68934853</v>
@@ -31104,12 +31057,12 @@
         <v>2090</v>
       </c>
       <c r="D24" s="148" t="s">
-        <v>3199</v>
+        <v>3197</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="30" customFormat="1">
       <c r="A25" s="30" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
       <c r="B25" s="30">
         <v>63166786</v>
@@ -31121,7 +31074,7 @@
         <v>1506</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>3443</v>
+        <v>3441</v>
       </c>
       <c r="F25" s="30" t="s">
         <v>1352</v>
@@ -31135,7 +31088,7 @@
     </row>
     <row r="26" spans="1:11" s="225" customFormat="1">
       <c r="A26" s="225" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="B26" s="225" t="s">
         <v>1902</v>
@@ -31181,7 +31134,7 @@
         <v>1982</v>
       </c>
       <c r="E28" s="456" t="s">
-        <v>2983</v>
+        <v>2981</v>
       </c>
       <c r="F28" s="301" t="s">
         <v>2124</v>
@@ -31206,7 +31159,7 @@
     </row>
     <row r="30" spans="1:11" s="164" customFormat="1">
       <c r="A30" s="164" t="s">
-        <v>3178</v>
+        <v>3176</v>
       </c>
       <c r="B30" s="164">
         <v>62782770</v>
@@ -31215,24 +31168,24 @@
         <v>2314</v>
       </c>
       <c r="D30" s="164" t="s">
-        <v>2768</v>
+        <v>2767</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="30" customFormat="1">
       <c r="A31" s="30" t="s">
-        <v>3306</v>
+        <v>3304</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>3418</v>
+        <v>3416</v>
       </c>
       <c r="C31" s="249" t="s">
         <v>1878</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
       <c r="E31" s="30" t="s">
-        <v>3342</v>
+        <v>3340</v>
       </c>
       <c r="F31" s="30" t="s">
         <v>2002</v>
@@ -31241,21 +31194,21 @@
         <v>198</v>
       </c>
       <c r="H31" s="30" t="s">
-        <v>3599</v>
+        <v>3597</v>
       </c>
       <c r="I31" s="192" t="s">
-        <v>3486</v>
+        <v>3484</v>
       </c>
       <c r="J31" s="419" t="s">
-        <v>3423</v>
+        <v>3421</v>
       </c>
       <c r="K31" s="30" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="163" customFormat="1">
       <c r="A32" s="163" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
       <c r="B32" s="163">
         <v>63487773</v>
@@ -31296,7 +31249,7 @@
         <v>2064</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>3229</v>
+        <v>3227</v>
       </c>
       <c r="F34" s="30" t="s">
         <v>2055</v>
@@ -31307,7 +31260,7 @@
     </row>
     <row r="35" spans="1:11" s="148" customFormat="1">
       <c r="A35" s="148" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="B35" s="148">
         <v>69692470</v>
@@ -31316,7 +31269,7 @@
         <v>1959</v>
       </c>
       <c r="D35" s="148" t="s">
-        <v>3274</v>
+        <v>3272</v>
       </c>
       <c r="E35" s="148" t="s">
         <v>1961</v>
@@ -31338,7 +31291,7 @@
     </row>
     <row r="37" spans="1:11" s="30" customFormat="1">
       <c r="A37" s="30" t="s">
-        <v>3292</v>
+        <v>3290</v>
       </c>
       <c r="B37" s="30" t="s">
         <v>2646</v>
@@ -31347,10 +31300,10 @@
         <v>1980</v>
       </c>
       <c r="D37" s="30" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="E37" s="30" t="s">
-        <v>3321</v>
+        <v>3319</v>
       </c>
       <c r="F37" s="30" t="s">
         <v>2045</v>
@@ -31359,16 +31312,16 @@
         <v>198</v>
       </c>
       <c r="H37" s="458" t="s">
-        <v>3684</v>
+        <v>3679</v>
       </c>
       <c r="I37" s="217" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="J37" s="217" t="s">
-        <v>3198</v>
+        <v>3196</v>
       </c>
       <c r="K37" s="30" t="s">
-        <v>3066</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="147" customFormat="1">
@@ -31397,24 +31350,24 @@
         <v>2031</v>
       </c>
       <c r="D39" s="148" t="s">
-        <v>3491</v>
+        <v>3489</v>
       </c>
     </row>
     <row r="40" spans="1:11" s="30" customFormat="1">
       <c r="A40" s="30" t="s">
-        <v>3262</v>
+        <v>3260</v>
       </c>
       <c r="B40" s="32" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="C40" s="249" t="s">
         <v>1642</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>3174</v>
+        <v>3172</v>
       </c>
       <c r="E40" s="30" t="s">
-        <v>3229</v>
+        <v>3227</v>
       </c>
       <c r="F40" s="30" t="s">
         <v>2060</v>
@@ -31423,21 +31376,21 @@
         <v>198</v>
       </c>
       <c r="H40" s="30" t="s">
-        <v>3318</v>
+        <v>3316</v>
       </c>
       <c r="I40" s="32" t="s">
-        <v>3545</v>
+        <v>3543</v>
       </c>
       <c r="J40" s="32" t="s">
-        <v>3529</v>
+        <v>3527</v>
       </c>
       <c r="K40" s="145" t="s">
-        <v>3175</v>
+        <v>3173</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="163" customFormat="1">
       <c r="A41" s="163" t="s">
-        <v>3306</v>
+        <v>3304</v>
       </c>
       <c r="B41" s="163">
         <v>68381893</v>
@@ -31454,7 +31407,7 @@
     </row>
     <row r="42" spans="1:11" s="252" customFormat="1">
       <c r="A42" s="266" t="s">
-        <v>3451</v>
+        <v>3449</v>
       </c>
       <c r="B42" s="266">
         <v>62360487</v>
@@ -31469,7 +31422,7 @@
     </row>
     <row r="43" spans="1:11" s="30" customFormat="1">
       <c r="A43" s="30" t="s">
-        <v>3597</v>
+        <v>3595</v>
       </c>
       <c r="B43" s="30">
         <v>60389752</v>
@@ -31481,7 +31434,7 @@
         <v>2006</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="F43" s="30" t="s">
         <v>2091</v>
@@ -31492,7 +31445,7 @@
     </row>
     <row r="44" spans="1:11" s="164" customFormat="1">
       <c r="A44" s="164" t="s">
-        <v>3306</v>
+        <v>3304</v>
       </c>
       <c r="B44" s="164">
         <v>68381893</v>
@@ -31509,7 +31462,7 @@
     </row>
     <row r="45" spans="1:11" s="163" customFormat="1">
       <c r="A45" s="163" t="s">
-        <v>3077</v>
+        <v>3075</v>
       </c>
       <c r="B45" s="163">
         <v>64079861</v>
@@ -31538,7 +31491,7 @@
         <v>2749</v>
       </c>
       <c r="E46" s="30" t="s">
-        <v>3043</v>
+        <v>3041</v>
       </c>
       <c r="F46" s="30" t="s">
         <v>2075</v>
@@ -31550,7 +31503,7 @@
     </row>
     <row r="47" spans="1:11" s="164" customFormat="1">
       <c r="A47" s="164" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="B47" s="164">
         <v>63183787</v>
@@ -31584,16 +31537,16 @@
         <v>1481</v>
       </c>
       <c r="B49" s="30" t="s">
-        <v>3085</v>
+        <v>3083</v>
       </c>
       <c r="C49" s="134" t="s">
         <v>1971</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>2990</v>
+        <v>2988</v>
       </c>
       <c r="E49" s="30" t="s">
-        <v>3230</v>
+        <v>3228</v>
       </c>
       <c r="F49" s="30" t="s">
         <v>2063</v>
@@ -31602,16 +31555,16 @@
         <v>198</v>
       </c>
       <c r="H49" s="30" t="s">
-        <v>3590</v>
+        <v>3588</v>
       </c>
       <c r="I49" s="30" t="s">
-        <v>3556</v>
+        <v>3554</v>
       </c>
       <c r="J49" s="30" t="s">
-        <v>3656</v>
+        <v>3651</v>
       </c>
       <c r="K49" s="30" t="s">
-        <v>3555</v>
+        <v>3553</v>
       </c>
     </row>
     <row r="50" spans="1:12" s="164" customFormat="1">
@@ -31630,7 +31583,7 @@
     </row>
     <row r="51" spans="1:12" s="164" customFormat="1">
       <c r="A51" s="164" t="s">
-        <v>3292</v>
+        <v>3290</v>
       </c>
       <c r="B51" s="164">
         <v>62455811</v>
@@ -31639,12 +31592,12 @@
         <v>1979</v>
       </c>
       <c r="D51" s="164" t="s">
-        <v>3444</v>
+        <v>3442</v>
       </c>
     </row>
     <row r="52" spans="1:12" s="139" customFormat="1">
       <c r="A52" s="140" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
       <c r="B52" s="411" t="s">
         <v>1424</v>
@@ -31653,10 +31606,10 @@
         <v>1355</v>
       </c>
       <c r="D52" s="139" t="s">
-        <v>2760</v>
+        <v>2759</v>
       </c>
       <c r="E52" s="139" t="s">
-        <v>3229</v>
+        <v>3227</v>
       </c>
       <c r="F52" s="139" t="s">
         <v>2061</v>
@@ -31665,21 +31618,21 @@
         <v>198</v>
       </c>
       <c r="H52" s="459" t="s">
-        <v>3687</v>
+        <v>3682</v>
       </c>
       <c r="I52" s="140" t="s">
-        <v>3061</v>
+        <v>3059</v>
       </c>
       <c r="J52" s="30" t="s">
-        <v>3623</v>
+        <v>3619</v>
       </c>
       <c r="K52" s="267" t="s">
-        <v>3380</v>
+        <v>3378</v>
       </c>
     </row>
     <row r="53" spans="1:12" s="164" customFormat="1">
       <c r="A53" s="164" t="s">
-        <v>3585</v>
+        <v>3583</v>
       </c>
       <c r="B53" s="164" t="s">
         <v>1140</v>
@@ -31715,7 +31668,7 @@
     </row>
     <row r="55" spans="1:12" s="30" customFormat="1">
       <c r="A55" s="30" t="s">
-        <v>3182</v>
+        <v>3180</v>
       </c>
       <c r="B55" s="30">
         <v>61130088</v>
@@ -31727,7 +31680,7 @@
         <v>1975</v>
       </c>
       <c r="E55" s="30" t="s">
-        <v>3558</v>
+        <v>3556</v>
       </c>
       <c r="F55" s="30" t="s">
         <v>2076</v>
@@ -31744,31 +31697,31 @@
         <v>60196388</v>
       </c>
       <c r="C56" s="398" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="D56" s="368" t="s">
-        <v>3550</v>
+        <v>3548</v>
       </c>
       <c r="E56" s="164"/>
     </row>
     <row r="57" spans="1:12" s="163" customFormat="1">
       <c r="A57" s="163" t="s">
-        <v>3262</v>
+        <v>3260</v>
       </c>
       <c r="B57" s="163" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="C57" s="398" t="s">
+        <v>2925</v>
+      </c>
+      <c r="D57" s="368" t="s">
         <v>2926</v>
-      </c>
-      <c r="D57" s="368" t="s">
-        <v>2927</v>
       </c>
       <c r="E57" s="164"/>
     </row>
     <row r="58" spans="1:12" s="30" customFormat="1">
       <c r="A58" s="30" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="B58" s="410" t="s">
         <v>2043</v>
@@ -31780,7 +31733,7 @@
         <v>2703</v>
       </c>
       <c r="E58" s="30" t="s">
-        <v>3367</v>
+        <v>3365</v>
       </c>
       <c r="F58" s="30" t="s">
         <v>2088</v>
@@ -31789,30 +31742,30 @@
         <v>198</v>
       </c>
       <c r="H58" s="217" t="s">
-        <v>3001</v>
+        <v>2999</v>
       </c>
       <c r="I58" s="217" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
       <c r="J58" s="30" t="s">
-        <v>3639</v>
+        <v>3635</v>
       </c>
       <c r="K58" s="30" t="s">
-        <v>3247</v>
+        <v>3245</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" s="147" t="s">
-        <v>3266</v>
+        <v>3264</v>
       </c>
       <c r="B59" s="147">
         <v>67539485</v>
       </c>
       <c r="C59" s="397" t="s">
-        <v>3365</v>
+        <v>3363</v>
       </c>
       <c r="D59" s="369" t="s">
-        <v>3368</v>
+        <v>3366</v>
       </c>
       <c r="E59" s="148"/>
       <c r="F59" s="147"/>
@@ -31825,16 +31778,16 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" s="147" t="s">
-        <v>3266</v>
+        <v>3264</v>
       </c>
       <c r="B60" s="147">
         <v>68853797</v>
       </c>
       <c r="C60" s="397" t="s">
-        <v>3366</v>
+        <v>3364</v>
       </c>
       <c r="D60" s="369" t="s">
-        <v>3369</v>
+        <v>3367</v>
       </c>
       <c r="E60" s="147"/>
       <c r="F60" s="147"/>
@@ -31847,19 +31800,19 @@
     </row>
     <row r="61" spans="1:12" s="30" customFormat="1">
       <c r="A61" s="145" t="s">
-        <v>3585</v>
+        <v>3583</v>
       </c>
       <c r="B61" s="30" t="s">
-        <v>3689</v>
+        <v>3684</v>
       </c>
       <c r="C61" s="134" t="s">
         <v>2044</v>
       </c>
       <c r="D61" s="30" t="s">
-        <v>2752</v>
+        <v>3686</v>
       </c>
       <c r="E61" s="30" t="s">
-        <v>3473</v>
+        <v>3471</v>
       </c>
       <c r="F61" s="30" t="s">
         <v>2045</v>
@@ -31868,16 +31821,16 @@
         <v>198</v>
       </c>
       <c r="H61" s="30" t="s">
-        <v>3103</v>
+        <v>3101</v>
       </c>
       <c r="I61" s="145" t="s">
-        <v>3690</v>
+        <v>3685</v>
       </c>
       <c r="J61" s="30" t="s">
-        <v>2994</v>
+        <v>2992</v>
       </c>
       <c r="K61" s="30" t="s">
-        <v>3063</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="62" spans="1:12" s="147" customFormat="1">
@@ -31891,7 +31844,7 @@
         <v>1453</v>
       </c>
       <c r="D62" s="369" t="s">
-        <v>3551</v>
+        <v>3549</v>
       </c>
       <c r="E62" s="148" t="s">
         <v>1371</v>
@@ -31899,7 +31852,7 @@
     </row>
     <row r="63" spans="1:12" s="163" customFormat="1">
       <c r="A63" s="49" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="B63" s="163">
         <v>62960567</v>
@@ -31908,13 +31861,13 @@
         <v>2029</v>
       </c>
       <c r="D63" s="368" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="E63" s="164"/>
     </row>
     <row r="64" spans="1:12" s="30" customFormat="1">
       <c r="A64" s="32" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="B64" s="32" t="s">
         <v>2095</v>
@@ -31923,10 +31876,10 @@
         <v>1641</v>
       </c>
       <c r="D64" s="30" t="s">
-        <v>2999</v>
+        <v>2997</v>
       </c>
       <c r="E64" s="30" t="s">
-        <v>3229</v>
+        <v>3227</v>
       </c>
       <c r="F64" s="30" t="s">
         <v>2062</v>
@@ -31935,16 +31888,16 @@
         <v>198</v>
       </c>
       <c r="H64" s="32" t="s">
-        <v>3075</v>
+        <v>3073</v>
       </c>
       <c r="I64" s="32" t="s">
-        <v>3139</v>
+        <v>3137</v>
       </c>
       <c r="J64" s="30" t="s">
-        <v>3676</v>
+        <v>3671</v>
       </c>
       <c r="K64" s="30" t="s">
-        <v>3524</v>
+        <v>3522</v>
       </c>
     </row>
     <row r="65" spans="1:11" s="164" customFormat="1">
@@ -31966,7 +31919,7 @@
     </row>
     <row r="66" spans="1:11" s="164" customFormat="1">
       <c r="A66" s="250" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="B66" s="164">
         <v>62090364</v>
@@ -31983,7 +31936,7 @@
     </row>
     <row r="67" spans="1:11" s="30" customFormat="1">
       <c r="A67" s="251" t="s">
-        <v>3147</v>
+        <v>3145</v>
       </c>
       <c r="B67" s="282" t="s">
         <v>1886</v>
@@ -31992,10 +31945,10 @@
         <v>1645</v>
       </c>
       <c r="D67" s="30" t="s">
-        <v>2846</v>
+        <v>2845</v>
       </c>
       <c r="E67" s="30" t="s">
-        <v>3277</v>
+        <v>3275</v>
       </c>
       <c r="F67" s="30" t="s">
         <v>2066</v>
@@ -32004,21 +31957,21 @@
         <v>198</v>
       </c>
       <c r="H67" s="30" t="s">
-        <v>3338</v>
+        <v>3336</v>
       </c>
       <c r="I67" s="30" t="s">
-        <v>3128</v>
+        <v>3126</v>
       </c>
       <c r="J67" s="30" t="s">
-        <v>3173</v>
+        <v>3171</v>
       </c>
       <c r="K67" s="30" t="s">
-        <v>3542</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="68" spans="1:11" s="147" customFormat="1">
       <c r="A68" s="147" t="s">
-        <v>3539</v>
+        <v>3537</v>
       </c>
       <c r="B68" s="147">
         <v>60432412</v>
@@ -32027,13 +31980,13 @@
         <v>1854</v>
       </c>
       <c r="D68" s="369" t="s">
-        <v>3649</v>
+        <v>3644</v>
       </c>
       <c r="E68" s="148"/>
     </row>
     <row r="69" spans="1:11" s="148" customFormat="1">
       <c r="A69" s="225" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
       <c r="B69" s="148">
         <v>63018763</v>
@@ -32042,24 +31995,24 @@
         <v>2065</v>
       </c>
       <c r="D69" s="148" t="s">
-        <v>3286</v>
+        <v>3284</v>
       </c>
     </row>
     <row r="70" spans="1:11" s="30" customFormat="1">
       <c r="A70" s="30" t="s">
-        <v>2763</v>
+        <v>2762</v>
       </c>
       <c r="B70" s="32" t="s">
-        <v>3073</v>
+        <v>3071</v>
       </c>
       <c r="C70" s="249" t="s">
         <v>1644</v>
       </c>
       <c r="D70" s="30" t="s">
-        <v>2982</v>
+        <v>2980</v>
       </c>
       <c r="E70" s="30" t="s">
-        <v>3657</v>
+        <v>3652</v>
       </c>
       <c r="F70" s="30" t="s">
         <v>2102</v>
@@ -32068,13 +32021,13 @@
         <v>198</v>
       </c>
       <c r="H70" s="32" t="s">
-        <v>3276</v>
+        <v>3274</v>
       </c>
       <c r="I70" s="30" t="s">
-        <v>3663</v>
+        <v>3658</v>
       </c>
       <c r="J70" s="30" t="s">
-        <v>3373</v>
+        <v>3371</v>
       </c>
     </row>
     <row r="71" spans="1:11" s="164" customFormat="1">
@@ -32088,12 +32041,12 @@
         <v>1938</v>
       </c>
       <c r="D71" s="164" t="s">
-        <v>2786</v>
+        <v>2785</v>
       </c>
     </row>
     <row r="72" spans="1:11" s="163" customFormat="1">
       <c r="A72" s="266" t="s">
-        <v>3266</v>
+        <v>3264</v>
       </c>
       <c r="B72" s="266" t="s">
         <v>1436</v>
@@ -32108,7 +32061,7 @@
     </row>
     <row r="73" spans="1:11" s="30" customFormat="1">
       <c r="A73" s="30" t="s">
-        <v>3597</v>
+        <v>3595</v>
       </c>
       <c r="B73" s="30">
         <v>60389752</v>
@@ -32120,7 +32073,7 @@
         <v>2713</v>
       </c>
       <c r="E73" s="30" t="s">
-        <v>3078</v>
+        <v>3076</v>
       </c>
       <c r="F73" s="30" t="s">
         <v>2001</v>
@@ -32131,7 +32084,7 @@
     </row>
     <row r="74" spans="1:11" s="147" customFormat="1">
       <c r="A74" s="147" t="s">
-        <v>3270</v>
+        <v>3268</v>
       </c>
       <c r="B74" s="147">
         <v>64226974</v>
@@ -32155,7 +32108,7 @@
         <v>1922</v>
       </c>
       <c r="D75" s="148" t="s">
-        <v>3566</v>
+        <v>3564</v>
       </c>
       <c r="E75" s="148"/>
     </row>
@@ -32170,10 +32123,10 @@
         <v>1853</v>
       </c>
       <c r="D76" s="30" t="s">
-        <v>2822</v>
+        <v>2821</v>
       </c>
       <c r="E76" s="30" t="s">
-        <v>2896</v>
+        <v>2895</v>
       </c>
       <c r="F76" s="30" t="s">
         <v>2075</v>
@@ -32182,16 +32135,16 @@
         <v>198</v>
       </c>
       <c r="H76" s="30" t="s">
-        <v>3231</v>
+        <v>3229</v>
       </c>
       <c r="I76" s="30" t="s">
-        <v>3275</v>
+        <v>3273</v>
       </c>
       <c r="J76" s="30" t="s">
-        <v>3596</v>
+        <v>3594</v>
       </c>
       <c r="K76" s="30" t="s">
-        <v>3531</v>
+        <v>3529</v>
       </c>
     </row>
     <row r="77" spans="1:11" s="152" customFormat="1">
@@ -32204,19 +32157,19 @@
     </row>
     <row r="79" spans="1:11" s="30" customFormat="1">
       <c r="A79" s="30" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
       <c r="B79" s="30" t="s">
-        <v>2805</v>
+        <v>2804</v>
       </c>
       <c r="C79" s="134" t="s">
         <v>1978</v>
       </c>
       <c r="D79" s="30" t="s">
-        <v>2833</v>
+        <v>2832</v>
       </c>
       <c r="E79" s="30" t="s">
-        <v>3320</v>
+        <v>3318</v>
       </c>
       <c r="F79" s="30" t="s">
         <v>2056</v>
@@ -32225,21 +32178,21 @@
         <v>198</v>
       </c>
       <c r="H79" s="428" t="s">
-        <v>2844</v>
+        <v>2843</v>
       </c>
       <c r="I79" s="428" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
       <c r="J79" s="30" t="s">
-        <v>3190</v>
+        <v>3188</v>
       </c>
       <c r="K79" s="217" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
     </row>
     <row r="80" spans="1:11" s="147" customFormat="1">
       <c r="A80" s="149" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
       <c r="B80" s="147">
         <v>60533053</v>
@@ -32254,7 +32207,7 @@
     </row>
     <row r="81" spans="1:11" s="147" customFormat="1">
       <c r="A81" s="149" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="B81" s="147">
         <v>64720128</v>
@@ -32271,10 +32224,10 @@
     </row>
     <row r="82" spans="1:11" s="30" customFormat="1">
       <c r="A82" s="145" t="s">
-        <v>3270</v>
+        <v>3268</v>
       </c>
       <c r="B82" s="30" t="s">
-        <v>3324</v>
+        <v>3322</v>
       </c>
       <c r="C82" s="22" t="s">
         <v>1879</v>
@@ -32283,7 +32236,7 @@
         <v>2735</v>
       </c>
       <c r="E82" s="30" t="s">
-        <v>2821</v>
+        <v>2820</v>
       </c>
       <c r="F82" s="30" t="s">
         <v>1880</v>
@@ -32292,16 +32245,16 @@
         <v>198</v>
       </c>
       <c r="H82" s="30" t="s">
-        <v>3146</v>
+        <v>3144</v>
       </c>
       <c r="I82" s="30" t="s">
-        <v>3474</v>
+        <v>3472</v>
       </c>
       <c r="J82" s="30" t="s">
-        <v>3260</v>
+        <v>3258</v>
       </c>
       <c r="K82" s="30" t="s">
-        <v>3208</v>
+        <v>3206</v>
       </c>
     </row>
     <row r="83" spans="1:11" s="148" customFormat="1">
@@ -32309,13 +32262,13 @@
         <v>1499</v>
       </c>
       <c r="B83" s="225" t="s">
-        <v>2871</v>
+        <v>2870</v>
       </c>
       <c r="C83" s="396" t="s">
         <v>1935</v>
       </c>
       <c r="D83" s="148" t="s">
-        <v>3322</v>
+        <v>3320</v>
       </c>
     </row>
     <row r="84" spans="1:11" s="278" customFormat="1">
@@ -32343,7 +32296,7 @@
         <v>692</v>
       </c>
       <c r="D85" s="30" t="s">
-        <v>3009</v>
+        <v>3007</v>
       </c>
       <c r="E85" s="30" t="s">
         <v>1770</v>
@@ -32355,21 +32308,21 @@
         <v>493</v>
       </c>
       <c r="H85" s="217" t="s">
-        <v>3110</v>
+        <v>3108</v>
       </c>
       <c r="I85" s="32" t="s">
-        <v>3335</v>
+        <v>3333</v>
       </c>
       <c r="J85" s="30" t="s">
-        <v>3129</v>
+        <v>3127</v>
       </c>
       <c r="K85" s="215" t="s">
-        <v>3300</v>
+        <v>3298</v>
       </c>
     </row>
     <row r="86" spans="1:11" s="147" customFormat="1">
       <c r="A86" s="147" t="s">
-        <v>3292</v>
+        <v>3290</v>
       </c>
       <c r="B86" s="147">
         <v>65509692</v>
@@ -32387,7 +32340,7 @@
     </row>
     <row r="87" spans="1:11" s="147" customFormat="1">
       <c r="A87" s="147" t="s">
-        <v>3488</v>
+        <v>3486</v>
       </c>
       <c r="B87" s="147" t="s">
         <v>908</v>
@@ -32408,16 +32361,16 @@
         <v>1499</v>
       </c>
       <c r="B88" s="30" t="s">
-        <v>3200</v>
+        <v>3198</v>
       </c>
       <c r="C88" s="153" t="s">
         <v>693</v>
       </c>
       <c r="D88" s="30" t="s">
-        <v>2818</v>
+        <v>2817</v>
       </c>
       <c r="E88" s="30" t="s">
-        <v>3658</v>
+        <v>3653</v>
       </c>
       <c r="F88" s="30" t="s">
         <v>1074</v>
@@ -32426,21 +32379,21 @@
         <v>1507</v>
       </c>
       <c r="H88" s="30" t="s">
-        <v>3360</v>
+        <v>3358</v>
       </c>
       <c r="I88" s="30" t="s">
-        <v>3456</v>
+        <v>3454</v>
       </c>
       <c r="J88" s="32" t="s">
-        <v>3455</v>
+        <v>3453</v>
       </c>
       <c r="K88" s="30" t="s">
-        <v>3337</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="89" spans="1:11" s="147" customFormat="1">
       <c r="A89" s="149" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="B89" s="147">
         <v>64844119</v>
@@ -32458,7 +32411,7 @@
     </row>
     <row r="90" spans="1:11" s="148" customFormat="1">
       <c r="A90" s="225" t="s">
-        <v>3539</v>
+        <v>3537</v>
       </c>
       <c r="B90" s="148">
         <v>69645877</v>
@@ -32467,7 +32420,7 @@
         <v>2716</v>
       </c>
       <c r="D90" s="148" t="s">
-        <v>3662</v>
+        <v>3657</v>
       </c>
       <c r="E90" s="148" t="s">
         <v>865</v>
@@ -32476,7 +32429,7 @@
     </row>
     <row r="91" spans="1:11" s="106" customFormat="1">
       <c r="A91" s="247" t="s">
-        <v>3266</v>
+        <v>3264</v>
       </c>
       <c r="B91" s="32" t="s">
         <v>1389</v>
@@ -32485,7 +32438,7 @@
         <v>46</v>
       </c>
       <c r="D91" s="106" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="E91" s="106" t="s">
         <v>1118</v>
@@ -32497,16 +32450,16 @@
         <v>66</v>
       </c>
       <c r="H91" s="217" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
       <c r="I91" s="31" t="s">
-        <v>3345</v>
+        <v>3343</v>
       </c>
       <c r="J91" s="32" t="s">
-        <v>3424</v>
+        <v>3422</v>
       </c>
       <c r="K91" s="30" t="s">
-        <v>3625</v>
+        <v>3621</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="404" customFormat="1">
@@ -32528,7 +32481,7 @@
     </row>
     <row r="93" spans="1:11" s="148" customFormat="1">
       <c r="A93" s="148" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="B93" s="148">
         <v>63465332</v>
@@ -32537,12 +32490,12 @@
         <v>1698</v>
       </c>
       <c r="D93" s="148" t="s">
-        <v>3686</v>
+        <v>3681</v>
       </c>
     </row>
     <row r="94" spans="1:11" s="32" customFormat="1">
       <c r="A94" s="30" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
       <c r="B94" s="32" t="s">
         <v>1183</v>
@@ -32554,7 +32507,7 @@
         <v>1353</v>
       </c>
       <c r="E94" s="32" t="s">
-        <v>3115</v>
+        <v>3113</v>
       </c>
       <c r="F94" s="32" t="s">
         <v>1354</v>
@@ -32566,7 +32519,7 @@
     </row>
     <row r="95" spans="1:11" s="148" customFormat="1">
       <c r="A95" s="148" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B95" s="148" t="s">
         <v>2567</v>
@@ -32583,7 +32536,7 @@
     </row>
     <row r="96" spans="1:11" s="148" customFormat="1">
       <c r="A96" s="148" t="s">
-        <v>3178</v>
+        <v>3176</v>
       </c>
       <c r="B96" s="148">
         <v>65633205</v>
@@ -32592,7 +32545,7 @@
         <v>1370</v>
       </c>
       <c r="D96" s="148" t="s">
-        <v>3201</v>
+        <v>3199</v>
       </c>
       <c r="E96" s="148" t="s">
         <v>1369</v>
@@ -32600,19 +32553,19 @@
     </row>
     <row r="97" spans="1:13" s="30" customFormat="1">
       <c r="A97" s="32" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B97" s="30" t="s">
-        <v>2804</v>
+        <v>2803</v>
       </c>
       <c r="C97" s="153" t="s">
         <v>1968</v>
       </c>
       <c r="D97" s="30" t="s">
-        <v>2803</v>
+        <v>2802</v>
       </c>
       <c r="E97" s="30" t="s">
-        <v>2821</v>
+        <v>2820</v>
       </c>
       <c r="F97" s="30" t="s">
         <v>1880</v>
@@ -32621,16 +32574,16 @@
         <v>198</v>
       </c>
       <c r="H97" s="32" t="s">
-        <v>3153</v>
+        <v>3151</v>
       </c>
       <c r="I97" s="30" t="s">
-        <v>3304</v>
+        <v>3302</v>
       </c>
       <c r="J97" s="30" t="s">
-        <v>3677</v>
+        <v>3672</v>
       </c>
       <c r="K97" s="427" t="s">
-        <v>3176</v>
+        <v>3174</v>
       </c>
     </row>
     <row r="98" spans="1:13" s="386" customFormat="1">
@@ -32643,19 +32596,19 @@
     </row>
     <row r="100" spans="1:13" s="30" customFormat="1">
       <c r="A100" s="30" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
       <c r="B100" s="30" t="s">
-        <v>3315</v>
+        <v>3313</v>
       </c>
       <c r="C100" s="249" t="s">
         <v>2734</v>
       </c>
       <c r="D100" s="30" t="s">
-        <v>3028</v>
+        <v>3026</v>
       </c>
       <c r="E100" s="30" t="s">
-        <v>2897</v>
+        <v>2896</v>
       </c>
       <c r="F100" s="30" t="s">
         <v>1880</v>
@@ -32664,16 +32617,16 @@
         <v>198</v>
       </c>
       <c r="H100" s="30" t="s">
-        <v>3148</v>
+        <v>3146</v>
       </c>
       <c r="I100" s="30" t="s">
-        <v>3294</v>
+        <v>3292</v>
       </c>
       <c r="J100" s="30" t="s">
-        <v>3181</v>
+        <v>3179</v>
       </c>
       <c r="K100" s="30" t="s">
-        <v>3234</v>
+        <v>3232</v>
       </c>
     </row>
     <row r="101" spans="1:13" s="386" customFormat="1">
@@ -32685,20 +32638,20 @@
       <c r="E102" s="367"/>
     </row>
     <row r="103" spans="1:13" s="30" customFormat="1">
-      <c r="A103" s="217" t="s">
-        <v>2922</v>
+      <c r="A103" s="145" t="s">
+        <v>3583</v>
       </c>
       <c r="B103" s="30" t="s">
-        <v>3600</v>
+        <v>3688</v>
       </c>
       <c r="C103" s="249" t="s">
-        <v>2771</v>
+        <v>2770</v>
       </c>
       <c r="D103" s="30" t="s">
+        <v>2944</v>
+      </c>
+      <c r="E103" s="30" t="s">
         <v>2945</v>
-      </c>
-      <c r="E103" s="30" t="s">
-        <v>2946</v>
       </c>
       <c r="F103" s="30" t="s">
         <v>1880</v>
@@ -32707,16 +32660,16 @@
         <v>198</v>
       </c>
       <c r="H103" s="30" t="s">
-        <v>3582</v>
-      </c>
-      <c r="I103" s="217" t="s">
-        <v>3601</v>
+        <v>3580</v>
+      </c>
+      <c r="I103" s="145" t="s">
+        <v>3689</v>
       </c>
       <c r="J103" s="30" t="s">
-        <v>3640</v>
-      </c>
-      <c r="K103" s="217" t="s">
-        <v>2961</v>
+        <v>3687</v>
+      </c>
+      <c r="K103" s="145" t="s">
+        <v>3690</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -32751,22 +32704,22 @@
     </row>
     <row r="106" spans="1:13" s="30" customFormat="1">
       <c r="A106" s="217" t="s">
-        <v>2794</v>
+        <v>2793</v>
       </c>
       <c r="B106" s="30">
         <v>62724019</v>
       </c>
       <c r="C106" s="249" t="s">
-        <v>2770</v>
+        <v>2769</v>
       </c>
       <c r="D106" s="30" t="s">
+        <v>2863</v>
+      </c>
+      <c r="E106" s="30" t="s">
+        <v>3439</v>
+      </c>
+      <c r="F106" s="30" t="s">
         <v>2864</v>
-      </c>
-      <c r="E106" s="30" t="s">
-        <v>3441</v>
-      </c>
-      <c r="F106" s="30" t="s">
-        <v>2865</v>
       </c>
       <c r="G106" s="30" t="s">
         <v>59</v>
@@ -32818,7 +32771,7 @@
         <v>1957</v>
       </c>
       <c r="E127" s="30" t="s">
-        <v>3462</v>
+        <v>3460</v>
       </c>
       <c r="F127" t="s">
         <v>1955</v>
@@ -32838,7 +32791,7 @@
         <v>1928</v>
       </c>
       <c r="E128" s="30" t="s">
-        <v>3462</v>
+        <v>3460</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -32852,15 +32805,15 @@
         <v>2635</v>
       </c>
       <c r="D129" s="371" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
       <c r="E129" s="30" t="s">
-        <v>3462</v>
+        <v>3460</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="4" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="B130">
         <v>67046608</v>
@@ -32872,7 +32825,7 @@
         <v>2520</v>
       </c>
       <c r="E130" s="30" t="s">
-        <v>3462</v>
+        <v>3460</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -32889,7 +32842,7 @@
         <v>1934</v>
       </c>
       <c r="E131" s="30" t="s">
-        <v>3462</v>
+        <v>3460</v>
       </c>
     </row>
     <row r="133" spans="1:6" s="121" customFormat="1" ht="23.5">
@@ -32911,7 +32864,7 @@
         <v>2301</v>
       </c>
       <c r="E134" s="30" t="s">
-        <v>3530</v>
+        <v>3528</v>
       </c>
       <c r="F134" t="s">
         <v>1331</v>
@@ -32931,7 +32884,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>3182</v>
+        <v>3180</v>
       </c>
       <c r="B139">
         <v>64720128</v>
@@ -32951,7 +32904,7 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>3292</v>
+        <v>3290</v>
       </c>
       <c r="B140">
         <v>66175393</v>
@@ -32960,7 +32913,7 @@
         <v>1945</v>
       </c>
       <c r="D140" s="371" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="E140" s="30" t="s">
         <v>1944</v>
@@ -32985,7 +32938,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="C143" s="1" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -33029,7 +32982,7 @@
         <v>2306</v>
       </c>
       <c r="E153" s="30" t="s">
-        <v>3517</v>
+        <v>3515</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -33037,21 +32990,21 @@
         <v>1481</v>
       </c>
       <c r="B154" t="s">
-        <v>3049</v>
+        <v>3047</v>
       </c>
       <c r="C154" t="s">
         <v>2193</v>
       </c>
       <c r="D154" s="371" t="s">
-        <v>3048</v>
+        <v>3046</v>
       </c>
       <c r="E154" s="30" t="s">
-        <v>3517</v>
+        <v>3515</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="B155">
         <v>60183566</v>
@@ -33063,12 +33016,12 @@
         <v>2521</v>
       </c>
       <c r="E155" s="30" t="s">
-        <v>3594</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B156">
         <v>63145336</v>
@@ -33077,15 +33030,15 @@
         <v>2202</v>
       </c>
       <c r="D156" s="371" t="s">
-        <v>3325</v>
+        <v>3323</v>
       </c>
       <c r="E156" s="30" t="s">
-        <v>3594</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
       <c r="B157" t="s">
         <v>2437</v>
@@ -33097,12 +33050,12 @@
         <v>2430</v>
       </c>
       <c r="E157" s="30" t="s">
-        <v>3594</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" t="s">
-        <v>3266</v>
+        <v>3264</v>
       </c>
       <c r="B158">
         <v>64982293</v>
@@ -33111,10 +33064,10 @@
         <v>2204</v>
       </c>
       <c r="D158" s="371" t="s">
-        <v>3372</v>
+        <v>3370</v>
       </c>
       <c r="E158" s="30" t="s">
-        <v>3594</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -33128,10 +33081,10 @@
         <v>2447</v>
       </c>
       <c r="D159" s="371" t="s">
-        <v>3051</v>
+        <v>3049</v>
       </c>
       <c r="E159" s="30" t="s">
-        <v>3594</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -33148,12 +33101,12 @@
         <v>2448</v>
       </c>
       <c r="E160" s="30" t="s">
-        <v>3594</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="4" t="s">
-        <v>3535</v>
+        <v>3533</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>1132</v>
@@ -33162,10 +33115,10 @@
         <v>2522</v>
       </c>
       <c r="D161" s="371" t="s">
-        <v>2877</v>
+        <v>2876</v>
       </c>
       <c r="E161" s="30" t="s">
-        <v>3594</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -33179,32 +33132,32 @@
         <v>2450</v>
       </c>
       <c r="D162" s="371" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="E162" s="30" t="s">
-        <v>3594</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B163">
         <v>67570116</v>
       </c>
       <c r="C163" t="s">
-        <v>3327</v>
+        <v>3325</v>
       </c>
       <c r="D163" s="371" t="s">
-        <v>3357</v>
+        <v>3355</v>
       </c>
       <c r="E163" s="30" t="s">
-        <v>3594</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="4" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>2138</v>
@@ -33216,12 +33169,12 @@
         <v>2431</v>
       </c>
       <c r="E164" s="30" t="s">
-        <v>3127</v>
+        <v>3125</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>3093</v>
+        <v>3091</v>
       </c>
       <c r="B165">
         <v>66315726</v>
@@ -33233,12 +33186,12 @@
         <v>2239</v>
       </c>
       <c r="E165" s="30" t="s">
-        <v>3127</v>
+        <v>3125</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
       <c r="B166">
         <v>64568369</v>
@@ -33250,24 +33203,24 @@
         <v>2239</v>
       </c>
       <c r="E166" s="30" t="s">
-        <v>3127</v>
+        <v>3125</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>3093</v>
+        <v>3091</v>
       </c>
       <c r="B167">
         <v>68818154</v>
       </c>
       <c r="C167" t="s">
-        <v>3052</v>
+        <v>3050</v>
       </c>
       <c r="D167" s="371" t="s">
         <v>2523</v>
       </c>
       <c r="E167" s="30" t="s">
-        <v>3127</v>
+        <v>3125</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -33275,16 +33228,16 @@
         <v>1417</v>
       </c>
       <c r="B168" t="s">
-        <v>3561</v>
+        <v>3559</v>
       </c>
       <c r="C168" s="21" t="s">
         <v>2637</v>
       </c>
       <c r="D168" s="371" t="s">
-        <v>3560</v>
+        <v>3558</v>
       </c>
       <c r="E168" s="30" t="s">
-        <v>3354</v>
+        <v>3352</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -33301,7 +33254,7 @@
         <v>2669</v>
       </c>
       <c r="E169" s="30" t="s">
-        <v>3354</v>
+        <v>3352</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -33318,12 +33271,12 @@
         <v>2428</v>
       </c>
       <c r="E170" s="30" t="s">
-        <v>3354</v>
+        <v>3352</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" t="s">
-        <v>3539</v>
+        <v>3537</v>
       </c>
       <c r="B171">
         <v>69355525</v>
@@ -33335,7 +33288,7 @@
         <v>2273</v>
       </c>
       <c r="E171" s="30" t="s">
-        <v>3354</v>
+        <v>3352</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -33349,15 +33302,15 @@
         <v>2285</v>
       </c>
       <c r="D172" s="371" t="s">
-        <v>3495</v>
+        <v>3493</v>
       </c>
       <c r="E172" s="30" t="s">
-        <v>3410</v>
+        <v>3408</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" t="s">
-        <v>3292</v>
+        <v>3290</v>
       </c>
       <c r="B173">
         <v>64982293</v>
@@ -33366,10 +33319,10 @@
         <v>2286</v>
       </c>
       <c r="D173" s="371" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="E173" s="30" t="s">
-        <v>3410</v>
+        <v>3408</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -33383,15 +33336,15 @@
         <v>2287</v>
       </c>
       <c r="D174" s="371" t="s">
-        <v>2962</v>
+        <v>2960</v>
       </c>
       <c r="E174" s="30" t="s">
-        <v>3410</v>
+        <v>3408</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" t="s">
-        <v>3270</v>
+        <v>3268</v>
       </c>
       <c r="B175">
         <v>67178677</v>
@@ -33400,15 +33353,15 @@
         <v>2671</v>
       </c>
       <c r="D175" s="371" t="s">
-        <v>3326</v>
+        <v>3324</v>
       </c>
       <c r="E175" s="30" t="s">
-        <v>3518</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" t="s">
-        <v>3535</v>
+        <v>3533</v>
       </c>
       <c r="B176">
         <v>64881871</v>
@@ -33417,32 +33370,32 @@
         <v>2672</v>
       </c>
       <c r="D176" s="220" t="s">
-        <v>3680</v>
+        <v>3675</v>
       </c>
       <c r="E176" s="30" t="s">
-        <v>3518</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="B177">
         <v>64455322</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="D177" s="220" t="s">
-        <v>3225</v>
+        <v>3223</v>
       </c>
       <c r="E177" s="30" t="s">
-        <v>3518</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="4" t="s">
-        <v>3488</v>
+        <v>3486</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>1836</v>
@@ -33451,15 +33404,15 @@
         <v>2673</v>
       </c>
       <c r="D178" s="220" t="s">
-        <v>3664</v>
+        <v>3659</v>
       </c>
       <c r="E178" s="30" t="s">
-        <v>3518</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="49" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="B179">
         <v>68570552</v>
@@ -33468,15 +33421,15 @@
         <v>2674</v>
       </c>
       <c r="D179" s="220" t="s">
-        <v>2984</v>
+        <v>2982</v>
       </c>
       <c r="E179" s="30" t="s">
-        <v>3518</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="49" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="B180">
         <v>69964218</v>
@@ -33485,15 +33438,15 @@
         <v>2692</v>
       </c>
       <c r="D180" s="371" t="s">
-        <v>2985</v>
+        <v>2983</v>
       </c>
       <c r="E180" s="30" t="s">
-        <v>3530</v>
+        <v>3528</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" t="s">
-        <v>3488</v>
+        <v>3486</v>
       </c>
       <c r="B181">
         <v>63950696</v>
@@ -33505,12 +33458,12 @@
         <v>2693</v>
       </c>
       <c r="E181" s="30" t="s">
-        <v>3530</v>
+        <v>3528</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="4" t="s">
-        <v>3488</v>
+        <v>3486</v>
       </c>
       <c r="B182" t="s">
         <v>2717</v>
@@ -33522,7 +33475,7 @@
         <v>2693</v>
       </c>
       <c r="E182" s="30" t="s">
-        <v>3530</v>
+        <v>3528</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -33536,15 +33489,15 @@
         <v>2696</v>
       </c>
       <c r="D183" s="371" t="s">
-        <v>2755</v>
+        <v>2754</v>
       </c>
       <c r="E183" s="30" t="s">
-        <v>3530</v>
+        <v>3528</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="B184">
         <v>63755362</v>
@@ -33553,10 +33506,10 @@
         <v>2746</v>
       </c>
       <c r="D184" s="371" t="s">
-        <v>3264</v>
+        <v>3262</v>
       </c>
       <c r="E184" s="30" t="s">
-        <v>3530</v>
+        <v>3528</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -33564,15 +33517,15 @@
         <v>53</v>
       </c>
       <c r="D185" s="371" t="s">
-        <v>3344</v>
+        <v>3342</v>
       </c>
       <c r="E185" s="30" t="s">
-        <v>3634</v>
+        <v>3630</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" t="s">
-        <v>3143</v>
+        <v>3141</v>
       </c>
       <c r="B186">
         <v>60240509</v>
@@ -33581,15 +33534,15 @@
         <v>2719</v>
       </c>
       <c r="D186" s="371" t="s">
-        <v>3141</v>
+        <v>3139</v>
       </c>
       <c r="E186" s="30" t="s">
-        <v>3142</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="A187" t="s">
-        <v>3585</v>
+        <v>3583</v>
       </c>
       <c r="B187">
         <v>64730396</v>
@@ -33598,10 +33551,10 @@
         <v>2720</v>
       </c>
       <c r="D187" s="371" t="s">
-        <v>3080</v>
+        <v>3078</v>
       </c>
       <c r="E187" s="30" t="s">
-        <v>3634</v>
+        <v>3630</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -33618,7 +33571,7 @@
         <v>2727</v>
       </c>
       <c r="E188" s="30" t="s">
-        <v>3634</v>
+        <v>3630</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -33635,12 +33588,12 @@
         <v>2727</v>
       </c>
       <c r="E189" s="30" t="s">
-        <v>3634</v>
+        <v>3630</v>
       </c>
     </row>
     <row r="190" spans="1:5">
       <c r="A190" t="s">
-        <v>3539</v>
+        <v>3537</v>
       </c>
       <c r="B190">
         <v>68726473</v>
@@ -33652,7 +33605,7 @@
         <v>2727</v>
       </c>
       <c r="E190" s="30" t="s">
-        <v>3634</v>
+        <v>3630</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -33663,7 +33616,7 @@
         <v>2727</v>
       </c>
       <c r="E191" s="30" t="s">
-        <v>3634</v>
+        <v>3630</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -33674,18 +33627,18 @@
         <v>62646973</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="D192" s="371" t="s">
-        <v>3370</v>
+        <v>3368</v>
       </c>
       <c r="E192" s="30" t="s">
-        <v>3634</v>
+        <v>3630</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
       <c r="B193">
         <v>69575383</v>
@@ -33694,10 +33647,10 @@
         <v>2725</v>
       </c>
       <c r="D193" s="371" t="s">
-        <v>3296</v>
+        <v>3294</v>
       </c>
       <c r="E193" s="30" t="s">
-        <v>3634</v>
+        <v>3630</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -33711,10 +33664,10 @@
         <v>2726</v>
       </c>
       <c r="D194" s="371" t="s">
-        <v>3685</v>
+        <v>3680</v>
       </c>
       <c r="E194" s="30" t="s">
-        <v>3634</v>
+        <v>3630</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -33740,44 +33693,44 @@
         <v>2747</v>
       </c>
       <c r="D198" s="371" t="s">
-        <v>3079</v>
+        <v>3077</v>
       </c>
       <c r="E198" s="30" t="s">
-        <v>3635</v>
+        <v>3631</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" t="s">
-        <v>3136</v>
+        <v>3134</v>
       </c>
       <c r="B199" t="s">
-        <v>3137</v>
+        <v>3135</v>
       </c>
       <c r="C199" t="s">
         <v>2740</v>
       </c>
       <c r="D199" s="371" t="s">
-        <v>3135</v>
+        <v>3133</v>
       </c>
       <c r="E199" s="30" t="s">
-        <v>3635</v>
+        <v>3631</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" t="s">
-        <v>3535</v>
+        <v>3533</v>
       </c>
       <c r="B200">
         <v>63617941</v>
       </c>
       <c r="C200" s="22" t="s">
-        <v>2986</v>
+        <v>2984</v>
       </c>
       <c r="D200" s="371" t="s">
-        <v>2792</v>
+        <v>2791</v>
       </c>
       <c r="E200" s="30" t="s">
-        <v>3635</v>
+        <v>3631</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -33791,15 +33744,15 @@
         <v>2741</v>
       </c>
       <c r="D201" s="371" t="s">
-        <v>3364</v>
+        <v>3362</v>
       </c>
       <c r="E201" s="30" t="s">
-        <v>3635</v>
+        <v>3631</v>
       </c>
     </row>
     <row r="202" spans="1:5">
       <c r="A202" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="B202">
         <v>62279384</v>
@@ -33808,78 +33761,78 @@
         <v>2742</v>
       </c>
       <c r="D202" s="371" t="s">
-        <v>3215</v>
+        <v>3213</v>
       </c>
       <c r="E202" s="30" t="s">
-        <v>3635</v>
+        <v>3631</v>
       </c>
     </row>
     <row r="203" spans="1:5">
       <c r="A203" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
       <c r="B203">
         <v>67911756</v>
       </c>
       <c r="C203" t="s">
-        <v>2791</v>
+        <v>2790</v>
       </c>
       <c r="D203" s="371" t="s">
-        <v>3238</v>
+        <v>3236</v>
       </c>
       <c r="E203" s="30" t="s">
-        <v>3635</v>
+        <v>3631</v>
       </c>
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="30" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="B204" t="s">
-        <v>3224</v>
+        <v>3222</v>
       </c>
       <c r="C204" t="s">
         <v>2743</v>
       </c>
       <c r="D204" s="371" t="s">
-        <v>3223</v>
+        <v>3221</v>
       </c>
       <c r="E204" s="30" t="s">
-        <v>3635</v>
+        <v>3631</v>
       </c>
     </row>
     <row r="205" spans="1:5">
       <c r="A205" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
       <c r="B205">
         <v>64982293</v>
       </c>
       <c r="C205" t="s">
-        <v>3214</v>
+        <v>3212</v>
       </c>
       <c r="D205" s="371" t="s">
-        <v>3290</v>
+        <v>3288</v>
       </c>
       <c r="E205" s="30" t="s">
-        <v>3635</v>
+        <v>3631</v>
       </c>
     </row>
     <row r="206" spans="1:5">
       <c r="A206" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="B206" t="s">
-        <v>2799</v>
+        <v>2798</v>
       </c>
       <c r="C206" t="s">
+        <v>2795</v>
+      </c>
+      <c r="D206" s="371" t="s">
         <v>2796</v>
       </c>
-      <c r="D206" s="371" t="s">
-        <v>2797</v>
-      </c>
       <c r="E206" s="30" t="s">
-        <v>3635</v>
+        <v>3631</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -33890,30 +33843,30 @@
         <v>65344753</v>
       </c>
       <c r="C207" t="s">
-        <v>2798</v>
+        <v>2797</v>
       </c>
       <c r="D207" s="371" t="s">
-        <v>2977</v>
+        <v>2975</v>
       </c>
       <c r="E207" s="30" t="s">
-        <v>3635</v>
+        <v>3631</v>
       </c>
     </row>
     <row r="208" spans="1:5">
       <c r="A208" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
       <c r="B208">
         <v>66496809</v>
       </c>
       <c r="C208" t="s">
-        <v>2810</v>
+        <v>2809</v>
       </c>
       <c r="D208" t="s">
-        <v>2812</v>
+        <v>2811</v>
       </c>
       <c r="E208" s="30" t="s">
-        <v>3195</v>
+        <v>3193</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -33921,84 +33874,84 @@
         <v>2662</v>
       </c>
       <c r="B209" t="s">
-        <v>3504</v>
+        <v>3502</v>
       </c>
       <c r="C209" t="s">
-        <v>2823</v>
+        <v>2822</v>
       </c>
       <c r="D209" s="371" t="s">
-        <v>3412</v>
+        <v>3410</v>
       </c>
       <c r="E209" s="30" t="s">
-        <v>3195</v>
+        <v>3193</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210" t="s">
-        <v>3092</v>
+        <v>3090</v>
       </c>
       <c r="B210">
         <v>65574051</v>
       </c>
       <c r="C210" t="s">
-        <v>2811</v>
+        <v>2810</v>
       </c>
       <c r="D210" t="s">
-        <v>3353</v>
+        <v>3351</v>
       </c>
       <c r="E210" s="30" t="s">
-        <v>3195</v>
+        <v>3193</v>
       </c>
     </row>
     <row r="211" spans="1:5">
       <c r="A211" t="s">
-        <v>3262</v>
+        <v>3260</v>
       </c>
       <c r="B211">
         <v>64403333</v>
       </c>
       <c r="C211" t="s">
-        <v>2824</v>
+        <v>2823</v>
       </c>
       <c r="D211" s="371" t="s">
-        <v>3547</v>
+        <v>3545</v>
       </c>
       <c r="E211" s="30" t="s">
-        <v>3195</v>
+        <v>3193</v>
       </c>
     </row>
     <row r="212" spans="1:5">
       <c r="A212" t="s">
-        <v>3539</v>
+        <v>3537</v>
       </c>
       <c r="B212">
         <v>64957521</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
       <c r="D212" t="s">
-        <v>3667</v>
+        <v>3662</v>
       </c>
       <c r="E212" s="30" t="s">
-        <v>3195</v>
+        <v>3193</v>
       </c>
     </row>
     <row r="213" spans="1:5">
       <c r="A213" t="s">
-        <v>3535</v>
+        <v>3533</v>
       </c>
       <c r="B213">
         <v>68069608</v>
       </c>
       <c r="C213" s="22" t="s">
-        <v>2848</v>
+        <v>2847</v>
       </c>
       <c r="D213" s="371" t="s">
-        <v>3673</v>
+        <v>3668</v>
       </c>
       <c r="E213" s="30" t="s">
-        <v>3278</v>
+        <v>3276</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -34009,13 +33962,13 @@
         <v>62361908</v>
       </c>
       <c r="C214" s="22" t="s">
-        <v>2855</v>
+        <v>2854</v>
       </c>
       <c r="D214" t="s">
-        <v>3419</v>
+        <v>3417</v>
       </c>
       <c r="E214" s="30" t="s">
-        <v>3278</v>
+        <v>3276</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -34023,16 +33976,16 @@
         <v>1421</v>
       </c>
       <c r="B215" t="s">
-        <v>3362</v>
+        <v>3360</v>
       </c>
       <c r="C215" s="22" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="D215" t="s">
-        <v>3361</v>
+        <v>3359</v>
       </c>
       <c r="E215" s="30" t="s">
-        <v>3278</v>
+        <v>3276</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -34043,30 +33996,30 @@
         <v>67752170</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
       <c r="D216" t="s">
-        <v>2852</v>
+        <v>2851</v>
       </c>
       <c r="E216" s="30" t="s">
-        <v>3278</v>
+        <v>3276</v>
       </c>
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="4" t="s">
-        <v>3539</v>
+        <v>3537</v>
       </c>
       <c r="B217">
         <v>64457890</v>
       </c>
       <c r="C217" t="s">
+        <v>2856</v>
+      </c>
+      <c r="D217" s="371" t="s">
         <v>2857</v>
       </c>
-      <c r="D217" s="371" t="s">
-        <v>2858</v>
-      </c>
       <c r="E217" s="30" t="s">
-        <v>3278</v>
+        <v>3276</v>
       </c>
     </row>
     <row r="231" spans="3:4">
@@ -34197,10 +34150,10 @@
     </row>
     <row r="259" spans="1:6">
       <c r="C259" s="1" t="s">
+        <v>2768</v>
+      </c>
+      <c r="D259" s="1" t="s">
         <v>2769</v>
-      </c>
-      <c r="D259" s="1" t="s">
-        <v>2770</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -34208,7 +34161,7 @@
         <v>1643</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>2771</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="261" spans="1:6">
@@ -36859,7 +36812,7 @@
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>2845</v>
+        <v>2844</v>
       </c>
     </row>
   </sheetData>
@@ -36932,7 +36885,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="76" t="s">
-        <v>3306</v>
+        <v>3304</v>
       </c>
       <c r="B6" s="76">
         <v>64957521</v>
@@ -36947,7 +36900,7 @@
         <v>678</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>3644</v>
+        <v>3639</v>
       </c>
       <c r="G6" s="361" t="s">
         <v>1426</v>
@@ -36968,13 +36921,13 @@
         <v>1824</v>
       </c>
       <c r="D7" s="183" t="s">
-        <v>3384</v>
+        <v>3382</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F7" s="183" t="s">
-        <v>3644</v>
+        <v>3639</v>
       </c>
       <c r="G7" s="183" t="s">
         <v>1426</v>
@@ -36986,7 +36939,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="193" t="s">
-        <v>3488</v>
+        <v>3486</v>
       </c>
       <c r="B8" s="193">
         <v>62747874</v>
@@ -37001,7 +36954,7 @@
         <v>362</v>
       </c>
       <c r="F8" s="183" t="s">
-        <v>3644</v>
+        <v>3639</v>
       </c>
       <c r="G8" s="183" t="s">
         <v>1426</v>
@@ -37020,7 +36973,7 @@
         <v>362</v>
       </c>
       <c r="F9" s="183" t="s">
-        <v>3644</v>
+        <v>3639</v>
       </c>
       <c r="G9" s="183" t="s">
         <v>1426</v>
@@ -37047,7 +37000,7 @@
         <v>362</v>
       </c>
       <c r="F10" s="183" t="s">
-        <v>3644</v>
+        <v>3639</v>
       </c>
       <c r="G10" s="183" t="s">
         <v>1426</v>
@@ -37074,7 +37027,7 @@
         <v>362</v>
       </c>
       <c r="F11" s="183" t="s">
-        <v>3644</v>
+        <v>3639</v>
       </c>
       <c r="G11" s="183" t="s">
         <v>1426</v>
@@ -37098,7 +37051,7 @@
         <v>2455</v>
       </c>
       <c r="E13" s="195" t="s">
-        <v>3645</v>
+        <v>3640</v>
       </c>
       <c r="F13" s="195" t="s">
         <v>1415</v>
@@ -37124,7 +37077,7 @@
         <v>1825</v>
       </c>
       <c r="E14" s="193" t="s">
-        <v>3645</v>
+        <v>3640</v>
       </c>
       <c r="F14" s="193" t="s">
         <v>1415</v>
@@ -37150,7 +37103,7 @@
         <v>2699</v>
       </c>
       <c r="E15" s="193" t="s">
-        <v>3645</v>
+        <v>3640</v>
       </c>
       <c r="F15" s="193" t="s">
         <v>1415</v>
@@ -37176,7 +37129,7 @@
         <v>2276</v>
       </c>
       <c r="E16" s="193" t="s">
-        <v>3645</v>
+        <v>3640</v>
       </c>
       <c r="F16" s="193" t="s">
         <v>1415</v>
@@ -37190,7 +37143,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="193" t="s">
-        <v>3178</v>
+        <v>3176</v>
       </c>
       <c r="B17" s="193">
         <v>64403333</v>
@@ -37202,7 +37155,7 @@
         <v>1490</v>
       </c>
       <c r="E17" s="193" t="s">
-        <v>3645</v>
+        <v>3640</v>
       </c>
       <c r="F17" s="193" t="s">
         <v>1415</v>
@@ -37216,7 +37169,7 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="193" t="s">
-        <v>2763</v>
+        <v>2762</v>
       </c>
       <c r="B18" s="193">
         <v>60389752</v>
@@ -37228,7 +37181,7 @@
         <v>2128</v>
       </c>
       <c r="E18" s="193" t="s">
-        <v>3645</v>
+        <v>3640</v>
       </c>
       <c r="F18" s="193" t="s">
         <v>1415</v>
@@ -37242,7 +37195,7 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="195" t="s">
-        <v>3306</v>
+        <v>3304</v>
       </c>
       <c r="B20" s="195">
         <v>67539485</v>
@@ -37257,7 +37210,7 @@
         <v>362</v>
       </c>
       <c r="F20" s="195" t="s">
-        <v>3645</v>
+        <v>3640</v>
       </c>
       <c r="G20" s="76" t="s">
         <v>422</v>
@@ -37271,7 +37224,7 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="183" t="s">
-        <v>2763</v>
+        <v>2762</v>
       </c>
       <c r="B21" s="183">
         <v>62723048</v>
@@ -37286,7 +37239,7 @@
         <v>362</v>
       </c>
       <c r="F21" s="193" t="s">
-        <v>3645</v>
+        <v>3640</v>
       </c>
       <c r="G21" s="183" t="s">
         <v>422</v>
@@ -37315,7 +37268,7 @@
         <v>362</v>
       </c>
       <c r="F22" s="193" t="s">
-        <v>3645</v>
+        <v>3640</v>
       </c>
       <c r="G22" s="183" t="s">
         <v>422</v>
@@ -37329,7 +37282,7 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="183" t="s">
-        <v>3521</v>
+        <v>3519</v>
       </c>
       <c r="B23" s="183">
         <v>60389752</v>
@@ -37344,7 +37297,7 @@
         <v>362</v>
       </c>
       <c r="F23" s="193" t="s">
-        <v>3645</v>
+        <v>3640</v>
       </c>
       <c r="G23" s="183" t="s">
         <v>422</v>
@@ -37358,7 +37311,7 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="193" t="s">
-        <v>3292</v>
+        <v>3290</v>
       </c>
       <c r="B24" s="193">
         <v>69291416</v>
@@ -37373,7 +37326,7 @@
         <v>362</v>
       </c>
       <c r="F24" s="193" t="s">
-        <v>3645</v>
+        <v>3640</v>
       </c>
       <c r="G24" s="183" t="s">
         <v>422</v>
@@ -37402,7 +37355,7 @@
         <v>362</v>
       </c>
       <c r="F25" s="193" t="s">
-        <v>3645</v>
+        <v>3640</v>
       </c>
       <c r="G25" s="183" t="s">
         <v>422</v>
@@ -37416,7 +37369,7 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="76" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
       <c r="B27" s="76">
         <v>60389752</v>
@@ -37431,7 +37384,7 @@
         <v>362</v>
       </c>
       <c r="F27" s="76" t="s">
-        <v>3065</v>
+        <v>3063</v>
       </c>
       <c r="G27" s="76" t="s">
         <v>1427</v>
@@ -37458,7 +37411,7 @@
         <v>362</v>
       </c>
       <c r="F28" s="183" t="s">
-        <v>3065</v>
+        <v>3063</v>
       </c>
       <c r="G28" s="183" t="s">
         <v>378</v>
@@ -37472,22 +37425,22 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="183" t="s">
-        <v>3163</v>
+        <v>3161</v>
       </c>
       <c r="B29" s="183">
         <v>65234700</v>
       </c>
       <c r="C29" s="194" t="s">
-        <v>3087</v>
+        <v>3085</v>
       </c>
       <c r="D29" s="183" t="s">
-        <v>3088</v>
+        <v>3086</v>
       </c>
       <c r="E29" s="429">
         <v>46243</v>
       </c>
       <c r="F29" s="183" t="s">
-        <v>3065</v>
+        <v>3063</v>
       </c>
       <c r="G29" s="183" t="s">
         <v>378</v>
@@ -37501,7 +37454,7 @@
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="183" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="B30" s="183">
         <v>68241069</v>
@@ -37516,7 +37469,7 @@
         <v>362</v>
       </c>
       <c r="F30" s="183" t="s">
-        <v>3065</v>
+        <v>3063</v>
       </c>
       <c r="G30" s="183" t="s">
         <v>378</v>
@@ -37530,7 +37483,7 @@
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="193" t="s">
-        <v>3262</v>
+        <v>3260</v>
       </c>
       <c r="B31" s="193" t="s">
         <v>2422</v>
@@ -37545,7 +37498,7 @@
         <v>362</v>
       </c>
       <c r="F31" s="183" t="s">
-        <v>3065</v>
+        <v>3063</v>
       </c>
       <c r="G31" s="183" t="s">
         <v>378</v>
@@ -37559,7 +37512,7 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="183" t="s">
-        <v>3535</v>
+        <v>3533</v>
       </c>
       <c r="B32" s="183">
         <v>68241069</v>
@@ -37574,7 +37527,7 @@
         <v>362</v>
       </c>
       <c r="F32" s="183" t="s">
-        <v>3065</v>
+        <v>3063</v>
       </c>
       <c r="G32" s="183" t="s">
         <v>378</v>
@@ -37588,7 +37541,7 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="195" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B34" s="195">
         <v>66466729</v>
@@ -37597,13 +37550,13 @@
         <v>1645</v>
       </c>
       <c r="D34" s="195" t="s">
-        <v>3242</v>
+        <v>3240</v>
       </c>
       <c r="E34" s="76" t="s">
         <v>2426</v>
       </c>
       <c r="F34" s="195" t="s">
-        <v>3140</v>
+        <v>3138</v>
       </c>
       <c r="G34" s="76" t="s">
         <v>1426</v>
@@ -37614,7 +37567,7 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="193" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="B35" s="193">
         <v>63465332</v>
@@ -37629,7 +37582,7 @@
         <v>2426</v>
       </c>
       <c r="F35" s="193" t="s">
-        <v>3140</v>
+        <v>3138</v>
       </c>
       <c r="G35" s="183" t="s">
         <v>1426</v>
@@ -37655,7 +37608,7 @@
         <v>2426</v>
       </c>
       <c r="F36" s="193" t="s">
-        <v>3140</v>
+        <v>3138</v>
       </c>
       <c r="G36" s="183" t="s">
         <v>1426</v>
@@ -37666,7 +37619,7 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="193" t="s">
-        <v>3118</v>
+        <v>3116</v>
       </c>
       <c r="B37" s="193">
         <v>69111188</v>
@@ -37681,7 +37634,7 @@
         <v>2426</v>
       </c>
       <c r="F37" s="193" t="s">
-        <v>3140</v>
+        <v>3138</v>
       </c>
       <c r="G37" s="183" t="s">
         <v>1426</v>
@@ -37701,13 +37654,13 @@
         <v>1313</v>
       </c>
       <c r="D38" s="193" t="s">
-        <v>3665</v>
+        <v>3660</v>
       </c>
       <c r="E38" s="183" t="s">
         <v>2426</v>
       </c>
       <c r="F38" s="193" t="s">
-        <v>3140</v>
+        <v>3138</v>
       </c>
       <c r="G38" s="183" t="s">
         <v>1426</v>
@@ -37733,7 +37686,7 @@
         <v>2426</v>
       </c>
       <c r="F39" s="193" t="s">
-        <v>3140</v>
+        <v>3138</v>
       </c>
       <c r="G39" s="183" t="s">
         <v>1426</v>
@@ -37746,16 +37699,16 @@
       <c r="A41" s="195"/>
       <c r="B41" s="195"/>
       <c r="C41" s="195" t="s">
-        <v>3131</v>
+        <v>3129</v>
       </c>
       <c r="D41" s="195" t="s">
-        <v>3132</v>
+        <v>3130</v>
       </c>
       <c r="E41" s="76" t="s">
         <v>362</v>
       </c>
       <c r="F41" s="195" t="s">
-        <v>3133</v>
+        <v>3131</v>
       </c>
       <c r="G41" s="76" t="s">
         <v>2328</v>
@@ -37775,7 +37728,7 @@
         <v>69563253</v>
       </c>
       <c r="C42" s="193" t="s">
-        <v>3134</v>
+        <v>3132</v>
       </c>
       <c r="D42" s="193" t="s">
         <v>1657</v>
@@ -37789,16 +37742,16 @@
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="234" t="s">
-        <v>2830</v>
+        <v>2829</v>
       </c>
       <c r="B43" s="193" t="s">
         <v>1919</v>
       </c>
       <c r="C43" s="194" t="s">
-        <v>3113</v>
+        <v>3111</v>
       </c>
       <c r="D43" s="193" t="s">
-        <v>3114</v>
+        <v>3112</v>
       </c>
       <c r="E43" s="429">
         <v>46304</v>
@@ -37815,7 +37768,7 @@
         <v>62751201</v>
       </c>
       <c r="C44" s="194" t="s">
-        <v>3138</v>
+        <v>3136</v>
       </c>
       <c r="D44" s="183" t="s">
         <v>1348</v>
@@ -37835,10 +37788,10 @@
         <v>68030850</v>
       </c>
       <c r="C45" s="193" t="s">
-        <v>3116</v>
+        <v>3114</v>
       </c>
       <c r="D45" s="193" t="s">
-        <v>3117</v>
+        <v>3115</v>
       </c>
       <c r="E45" s="429">
         <v>46243</v>
@@ -37871,16 +37824,16 @@
       <c r="A48" s="195"/>
       <c r="B48" s="195"/>
       <c r="C48" s="195" t="s">
+        <v>3163</v>
+      </c>
+      <c r="D48" s="195" t="s">
+        <v>3164</v>
+      </c>
+      <c r="E48" s="76" t="s">
         <v>3165</v>
       </c>
-      <c r="D48" s="195" t="s">
+      <c r="F48" s="195" t="s">
         <v>3166</v>
-      </c>
-      <c r="E48" s="76" t="s">
-        <v>3167</v>
-      </c>
-      <c r="F48" s="195" t="s">
-        <v>3168</v>
       </c>
       <c r="G48" s="76" t="s">
         <v>1426</v>
@@ -37891,7 +37844,7 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="183" t="s">
-        <v>3585</v>
+        <v>3583</v>
       </c>
       <c r="B49" s="183">
         <v>68361109</v>
@@ -37917,10 +37870,10 @@
         <v>61548403</v>
       </c>
       <c r="C50" s="194" t="s">
-        <v>3169</v>
+        <v>3167</v>
       </c>
       <c r="D50" s="193" t="s">
-        <v>3170</v>
+        <v>3168</v>
       </c>
       <c r="E50" s="429">
         <v>46304</v>
@@ -37951,13 +37904,13 @@
         <v>1644</v>
       </c>
       <c r="D55" s="195" t="s">
-        <v>3385</v>
+        <v>3383</v>
       </c>
       <c r="E55" s="76" t="s">
         <v>2426</v>
       </c>
       <c r="F55" s="195" t="s">
-        <v>3172</v>
+        <v>3170</v>
       </c>
       <c r="G55" s="76" t="s">
         <v>1426</v>
@@ -37968,7 +37921,7 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="193" t="s">
-        <v>3262</v>
+        <v>3260</v>
       </c>
       <c r="B56" s="193">
         <v>69624389</v>
@@ -37983,7 +37936,7 @@
         <v>2426</v>
       </c>
       <c r="F56" s="193" t="s">
-        <v>3172</v>
+        <v>3170</v>
       </c>
       <c r="G56" s="183" t="s">
         <v>1426</v>
@@ -37994,7 +37947,7 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="193" t="s">
-        <v>3539</v>
+        <v>3537</v>
       </c>
       <c r="B57" s="193">
         <v>68658411</v>
@@ -38003,13 +37956,13 @@
         <v>2534</v>
       </c>
       <c r="D57" s="193" t="s">
-        <v>3668</v>
+        <v>3663</v>
       </c>
       <c r="E57" s="183" t="s">
         <v>2426</v>
       </c>
       <c r="F57" s="193" t="s">
-        <v>3172</v>
+        <v>3170</v>
       </c>
       <c r="G57" s="183" t="s">
         <v>1426</v>
@@ -38035,7 +37988,7 @@
         <v>2426</v>
       </c>
       <c r="F58" s="193" t="s">
-        <v>3172</v>
+        <v>3170</v>
       </c>
       <c r="G58" s="183" t="s">
         <v>1426</v>
@@ -38046,7 +37999,7 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="193" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="B59" s="193">
         <v>65174343</v>
@@ -38061,7 +38014,7 @@
         <v>2426</v>
       </c>
       <c r="F59" s="193" t="s">
-        <v>3172</v>
+        <v>3170</v>
       </c>
       <c r="G59" s="183" t="s">
         <v>1426</v>
@@ -38072,22 +38025,22 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="183" t="s">
-        <v>3266</v>
+        <v>3264</v>
       </c>
       <c r="B60" s="183">
         <v>63247837</v>
       </c>
       <c r="C60" s="193" t="s">
-        <v>3013</v>
+        <v>3011</v>
       </c>
       <c r="D60" s="193" t="s">
-        <v>3386</v>
+        <v>3384</v>
       </c>
       <c r="E60" s="183" t="s">
         <v>2426</v>
       </c>
       <c r="F60" s="193" t="s">
-        <v>3172</v>
+        <v>3170</v>
       </c>
       <c r="G60" s="183" t="s">
         <v>1426</v>
@@ -38098,7 +38051,7 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="195" t="s">
-        <v>3262</v>
+        <v>3260</v>
       </c>
       <c r="B62" s="195">
         <v>68259581</v>
@@ -38107,13 +38060,13 @@
         <v>1641</v>
       </c>
       <c r="D62" s="195" t="s">
-        <v>3534</v>
+        <v>3532</v>
       </c>
       <c r="E62" s="76" t="s">
         <v>2426</v>
       </c>
       <c r="F62" s="195" t="s">
-        <v>3172</v>
+        <v>3170</v>
       </c>
       <c r="G62" s="76" t="s">
         <v>1426</v>
@@ -38139,7 +38092,7 @@
         <v>2426</v>
       </c>
       <c r="F63" s="193" t="s">
-        <v>3172</v>
+        <v>3170</v>
       </c>
       <c r="G63" s="183" t="s">
         <v>1426</v>
@@ -38150,7 +38103,7 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="183" t="s">
-        <v>3093</v>
+        <v>3091</v>
       </c>
       <c r="B64" s="183">
         <v>64403333</v>
@@ -38165,7 +38118,7 @@
         <v>2426</v>
       </c>
       <c r="F64" s="193" t="s">
-        <v>3172</v>
+        <v>3170</v>
       </c>
       <c r="G64" s="183" t="s">
         <v>1426</v>
@@ -38176,7 +38129,7 @@
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="193" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="B65" s="193">
         <v>68030850</v>
@@ -38191,7 +38144,7 @@
         <v>2426</v>
       </c>
       <c r="F65" s="193" t="s">
-        <v>3172</v>
+        <v>3170</v>
       </c>
       <c r="G65" s="183" t="s">
         <v>1426</v>
@@ -38202,7 +38155,7 @@
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="183" t="s">
-        <v>3182</v>
+        <v>3180</v>
       </c>
       <c r="B66" s="183">
         <v>65003516</v>
@@ -38217,7 +38170,7 @@
         <v>2426</v>
       </c>
       <c r="F66" s="193" t="s">
-        <v>3172</v>
+        <v>3170</v>
       </c>
       <c r="G66" s="183" t="s">
         <v>1426</v>
@@ -38243,7 +38196,7 @@
         <v>2426</v>
       </c>
       <c r="F67" s="193" t="s">
-        <v>3172</v>
+        <v>3170</v>
       </c>
       <c r="G67" s="183" t="s">
         <v>1426</v>
@@ -38263,10 +38216,10 @@
         <v>2584</v>
       </c>
       <c r="D69" s="195" t="s">
-        <v>3463</v>
+        <v>3461</v>
       </c>
       <c r="E69" s="76" t="s">
-        <v>3218</v>
+        <v>3216</v>
       </c>
       <c r="F69" s="195" t="s">
         <v>2393</v>
@@ -38280,7 +38233,7 @@
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="193" t="s">
-        <v>2790</v>
+        <v>2789</v>
       </c>
       <c r="B70" s="193">
         <v>62646186</v>
@@ -38292,7 +38245,7 @@
         <v>2397</v>
       </c>
       <c r="E70" s="183" t="s">
-        <v>3218</v>
+        <v>3216</v>
       </c>
       <c r="F70" s="193" t="s">
         <v>2393</v>
@@ -38318,7 +38271,7 @@
         <v>2252</v>
       </c>
       <c r="E71" s="183" t="s">
-        <v>3218</v>
+        <v>3216</v>
       </c>
       <c r="F71" s="193" t="s">
         <v>2393</v>
@@ -38344,7 +38297,7 @@
         <v>2658</v>
       </c>
       <c r="E72" s="183" t="s">
-        <v>3218</v>
+        <v>3216</v>
       </c>
       <c r="F72" s="183" t="s">
         <v>2393</v>
@@ -38371,7 +38324,7 @@
         <v>2028</v>
       </c>
       <c r="E73" s="183" t="s">
-        <v>3218</v>
+        <v>3216</v>
       </c>
       <c r="F73" s="183" t="s">
         <v>2393</v>
@@ -38395,10 +38348,10 @@
         <v>732</v>
       </c>
       <c r="D74" s="183" t="s">
-        <v>3549</v>
+        <v>3547</v>
       </c>
       <c r="E74" s="183" t="s">
-        <v>3218</v>
+        <v>3216</v>
       </c>
       <c r="F74" s="183" t="s">
         <v>2393</v>
@@ -38425,7 +38378,7 @@
         <v>1704</v>
       </c>
       <c r="E76" s="76" t="s">
-        <v>3218</v>
+        <v>3216</v>
       </c>
       <c r="F76" s="195" t="s">
         <v>2392</v>
@@ -38437,7 +38390,7 @@
     </row>
     <row r="77" spans="1:9">
       <c r="A77" s="193" t="s">
-        <v>2763</v>
+        <v>2762</v>
       </c>
       <c r="B77" s="193">
         <v>66082581</v>
@@ -38449,7 +38402,7 @@
         <v>2289</v>
       </c>
       <c r="E77" s="183" t="s">
-        <v>3218</v>
+        <v>3216</v>
       </c>
       <c r="F77" s="193" t="s">
         <v>2392</v>
@@ -38461,7 +38414,7 @@
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="183" t="s">
-        <v>3292</v>
+        <v>3290</v>
       </c>
       <c r="B78" s="183">
         <v>62874575</v>
@@ -38473,7 +38426,7 @@
         <v>1230</v>
       </c>
       <c r="E78" s="183" t="s">
-        <v>3218</v>
+        <v>3216</v>
       </c>
       <c r="F78" s="193" t="s">
         <v>2392</v>
@@ -38485,7 +38438,7 @@
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="183" t="s">
-        <v>3292</v>
+        <v>3290</v>
       </c>
       <c r="B79" s="183">
         <v>62820256</v>
@@ -38497,7 +38450,7 @@
         <v>2311</v>
       </c>
       <c r="E79" s="183" t="s">
-        <v>3218</v>
+        <v>3216</v>
       </c>
       <c r="F79" s="193" t="s">
         <v>2392</v>
@@ -38509,19 +38462,19 @@
     </row>
     <row r="80" spans="1:9">
       <c r="A80" s="183" t="s">
-        <v>2866</v>
+        <v>2865</v>
       </c>
       <c r="B80" s="183">
         <v>69563253</v>
       </c>
       <c r="C80" s="194" t="s">
-        <v>3219</v>
+        <v>3217</v>
       </c>
       <c r="D80" s="183" t="s">
         <v>1002</v>
       </c>
       <c r="E80" s="183" t="s">
-        <v>3220</v>
+        <v>3218</v>
       </c>
       <c r="F80" s="193" t="s">
         <v>2392</v>
@@ -38533,7 +38486,7 @@
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="183" t="s">
-        <v>3246</v>
+        <v>3244</v>
       </c>
       <c r="B81" s="183">
         <v>63233935</v>
@@ -38542,10 +38495,10 @@
         <v>2330</v>
       </c>
       <c r="D81" s="183" t="s">
-        <v>3243</v>
+        <v>3241</v>
       </c>
       <c r="E81" s="183" t="s">
-        <v>3218</v>
+        <v>3216</v>
       </c>
       <c r="F81" s="193" t="s">
         <v>2392</v>
@@ -38557,7 +38510,7 @@
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="49" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
       <c r="B83" s="76">
         <v>63574980</v>
@@ -38572,7 +38525,7 @@
         <v>1336</v>
       </c>
       <c r="F83" s="195" t="s">
-        <v>3284</v>
+        <v>3282</v>
       </c>
       <c r="G83" s="76" t="s">
         <v>1426</v>
@@ -38599,7 +38552,7 @@
         <v>1336</v>
       </c>
       <c r="F84" s="183" t="s">
-        <v>3284</v>
+        <v>3282</v>
       </c>
       <c r="G84" s="183" t="s">
         <v>1426</v>
@@ -38617,7 +38570,7 @@
         <v>68483411</v>
       </c>
       <c r="C85" s="183" t="s">
-        <v>2793</v>
+        <v>2792</v>
       </c>
       <c r="D85" s="183" t="s">
         <v>2126</v>
@@ -38626,7 +38579,7 @@
         <v>1336</v>
       </c>
       <c r="F85" s="183" t="s">
-        <v>3284</v>
+        <v>3282</v>
       </c>
       <c r="G85" s="183" t="s">
         <v>1426</v>
@@ -38641,19 +38594,19 @@
         <v>2662</v>
       </c>
       <c r="B86" s="183" t="s">
-        <v>2933</v>
+        <v>2932</v>
       </c>
       <c r="C86" s="194" t="s">
         <v>2588</v>
       </c>
       <c r="D86" s="183" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="E86" s="183" t="s">
         <v>1336</v>
       </c>
       <c r="F86" s="183" t="s">
-        <v>3284</v>
+        <v>3282</v>
       </c>
       <c r="G86" s="183" t="s">
         <v>1426</v>
@@ -38665,7 +38618,7 @@
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="183" t="s">
-        <v>3488</v>
+        <v>3486</v>
       </c>
       <c r="B87" s="183">
         <v>69904406</v>
@@ -38674,13 +38627,13 @@
         <v>2589</v>
       </c>
       <c r="D87" s="183" t="s">
-        <v>2989</v>
+        <v>2987</v>
       </c>
       <c r="E87" s="183" t="s">
         <v>1336</v>
       </c>
       <c r="F87" s="183" t="s">
-        <v>3284</v>
+        <v>3282</v>
       </c>
       <c r="G87" s="183" t="s">
         <v>1426</v>
@@ -38692,7 +38645,7 @@
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="183" t="s">
-        <v>3266</v>
+        <v>3264</v>
       </c>
       <c r="B88" s="183" t="s">
         <v>2606</v>
@@ -38707,7 +38660,7 @@
         <v>1336</v>
       </c>
       <c r="F88" s="183" t="s">
-        <v>3284</v>
+        <v>3282</v>
       </c>
       <c r="G88" s="183" t="s">
         <v>1426</v>
@@ -38734,7 +38687,7 @@
         <v>1634</v>
       </c>
       <c r="F90" s="195" t="s">
-        <v>3285</v>
+        <v>3283</v>
       </c>
       <c r="G90" s="76" t="s">
         <v>1426</v>
@@ -38743,7 +38696,7 @@
     </row>
     <row r="91" spans="1:9">
       <c r="A91" s="183" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
       <c r="B91" s="183">
         <v>68865112</v>
@@ -38758,7 +38711,7 @@
         <v>1634</v>
       </c>
       <c r="F91" s="193" t="s">
-        <v>3285</v>
+        <v>3283</v>
       </c>
       <c r="G91" s="183" t="s">
         <v>1426</v>
@@ -38767,7 +38720,7 @@
     </row>
     <row r="92" spans="1:9">
       <c r="A92" s="183" t="s">
-        <v>3346</v>
+        <v>3344</v>
       </c>
       <c r="B92" s="183">
         <v>65014102</v>
@@ -38782,7 +38735,7 @@
         <v>1634</v>
       </c>
       <c r="F92" s="193" t="s">
-        <v>3285</v>
+        <v>3283</v>
       </c>
       <c r="G92" s="183" t="s">
         <v>1426</v>
@@ -38791,7 +38744,7 @@
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="183" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B93" s="183">
         <v>68259581</v>
@@ -38806,7 +38759,7 @@
         <v>1634</v>
       </c>
       <c r="F93" s="193" t="s">
-        <v>3285</v>
+        <v>3283</v>
       </c>
       <c r="G93" s="183" t="s">
         <v>1426</v>
@@ -38815,7 +38768,7 @@
     </row>
     <row r="94" spans="1:9">
       <c r="A94" s="183" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="B94" s="183">
         <v>64403333</v>
@@ -38830,7 +38783,7 @@
         <v>1634</v>
       </c>
       <c r="F94" s="193" t="s">
-        <v>3285</v>
+        <v>3283</v>
       </c>
       <c r="G94" s="183" t="s">
         <v>1426</v>
@@ -38854,7 +38807,7 @@
         <v>1634</v>
       </c>
       <c r="F95" s="193" t="s">
-        <v>3285</v>
+        <v>3283</v>
       </c>
       <c r="G95" s="183" t="s">
         <v>1426</v>
@@ -38863,7 +38816,7 @@
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="195" t="s">
-        <v>3154</v>
+        <v>3152</v>
       </c>
       <c r="B97" s="195">
         <v>64476521</v>
@@ -38878,7 +38831,7 @@
         <v>2426</v>
       </c>
       <c r="F97" s="195" t="s">
-        <v>3307</v>
+        <v>3305</v>
       </c>
       <c r="G97" s="76" t="s">
         <v>1426</v>
@@ -38889,7 +38842,7 @@
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="193" t="s">
-        <v>3055</v>
+        <v>3053</v>
       </c>
       <c r="B98" s="193">
         <v>60389752</v>
@@ -38898,13 +38851,13 @@
         <v>2570</v>
       </c>
       <c r="D98" s="193" t="s">
-        <v>3054</v>
+        <v>3052</v>
       </c>
       <c r="E98" s="183" t="s">
         <v>2426</v>
       </c>
       <c r="F98" s="193" t="s">
-        <v>3307</v>
+        <v>3305</v>
       </c>
       <c r="G98" s="183" t="s">
         <v>1426</v>
@@ -38915,7 +38868,7 @@
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="183" t="s">
-        <v>3262</v>
+        <v>3260</v>
       </c>
       <c r="B99" s="183">
         <v>60389752</v>
@@ -38930,7 +38883,7 @@
         <v>2426</v>
       </c>
       <c r="F99" s="193" t="s">
-        <v>3307</v>
+        <v>3305</v>
       </c>
       <c r="G99" s="183" t="s">
         <v>1426</v>
@@ -38956,7 +38909,7 @@
         <v>2426</v>
       </c>
       <c r="F100" s="193" t="s">
-        <v>3307</v>
+        <v>3305</v>
       </c>
       <c r="G100" s="183" t="s">
         <v>1426</v>
@@ -38967,7 +38920,7 @@
     </row>
     <row r="101" spans="1:9">
       <c r="A101" s="183" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
       <c r="B101" s="183">
         <v>60533053</v>
@@ -38982,7 +38935,7 @@
         <v>2426</v>
       </c>
       <c r="F101" s="193" t="s">
-        <v>3307</v>
+        <v>3305</v>
       </c>
       <c r="G101" s="183" t="s">
         <v>1426</v>
@@ -38993,7 +38946,7 @@
     </row>
     <row r="102" spans="1:9">
       <c r="A102" s="273" t="s">
-        <v>2922</v>
+        <v>2921</v>
       </c>
       <c r="B102" s="193">
         <v>67381873</v>
@@ -39002,13 +38955,13 @@
         <v>2250</v>
       </c>
       <c r="D102" s="193" t="s">
-        <v>2992</v>
+        <v>2990</v>
       </c>
       <c r="E102" s="183" t="s">
         <v>2426</v>
       </c>
       <c r="F102" s="193" t="s">
-        <v>3307</v>
+        <v>3305</v>
       </c>
       <c r="G102" s="183" t="s">
         <v>1426</v>
@@ -39019,7 +38972,7 @@
     </row>
     <row r="104" spans="1:9">
       <c r="A104" s="195" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
       <c r="B104" s="195">
         <v>66082581</v>
@@ -39031,7 +38984,7 @@
         <v>2258</v>
       </c>
       <c r="E104" s="76" t="s">
-        <v>3307</v>
+        <v>3305</v>
       </c>
       <c r="F104" s="195" t="s">
         <v>422</v>
@@ -39045,7 +38998,7 @@
     </row>
     <row r="105" spans="1:9">
       <c r="A105" s="193" t="s">
-        <v>3306</v>
+        <v>3304</v>
       </c>
       <c r="B105" s="193" t="s">
         <v>2626</v>
@@ -39057,7 +39010,7 @@
         <v>2263</v>
       </c>
       <c r="E105" s="183" t="s">
-        <v>3307</v>
+        <v>3305</v>
       </c>
       <c r="F105" s="193" t="s">
         <v>422</v>
@@ -39071,7 +39024,7 @@
     </row>
     <row r="106" spans="1:9">
       <c r="A106" s="193" t="s">
-        <v>3005</v>
+        <v>3003</v>
       </c>
       <c r="B106" s="193">
         <v>62723048</v>
@@ -39080,10 +39033,10 @@
         <v>2264</v>
       </c>
       <c r="D106" s="193" t="s">
-        <v>3004</v>
+        <v>3002</v>
       </c>
       <c r="E106" s="183" t="s">
-        <v>3307</v>
+        <v>3305</v>
       </c>
       <c r="F106" s="193" t="s">
         <v>422</v>
@@ -39103,13 +39056,13 @@
         <v>60196388</v>
       </c>
       <c r="C107" s="194" t="s">
-        <v>2809</v>
+        <v>2808</v>
       </c>
       <c r="D107" s="193" t="s">
-        <v>3548</v>
+        <v>3546</v>
       </c>
       <c r="E107" s="183" t="s">
-        <v>3307</v>
+        <v>3305</v>
       </c>
       <c r="F107" s="193" t="s">
         <v>422</v>
@@ -39123,7 +39076,7 @@
     </row>
     <row r="108" spans="1:9">
       <c r="A108" s="193" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B108" s="193">
         <v>65353736</v>
@@ -39135,7 +39088,7 @@
         <v>2267</v>
       </c>
       <c r="E108" s="183" t="s">
-        <v>3307</v>
+        <v>3305</v>
       </c>
       <c r="F108" s="193" t="s">
         <v>422</v>
@@ -39155,13 +39108,13 @@
         <v>62723048</v>
       </c>
       <c r="C109" s="194" t="s">
-        <v>2816</v>
+        <v>2815</v>
       </c>
       <c r="D109" s="193" t="s">
-        <v>2815</v>
+        <v>2814</v>
       </c>
       <c r="E109" s="183" t="s">
-        <v>3307</v>
+        <v>3305</v>
       </c>
       <c r="F109" s="193" t="s">
         <v>422</v>
@@ -39175,22 +39128,22 @@
     </row>
     <row r="111" spans="1:9">
       <c r="A111" s="195" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B111" s="195">
         <v>68310153</v>
       </c>
       <c r="C111" s="195" t="s">
+        <v>2852</v>
+      </c>
+      <c r="D111" s="195" t="s">
         <v>2853</v>
-      </c>
-      <c r="D111" s="195" t="s">
-        <v>2854</v>
       </c>
       <c r="E111" s="76" t="s">
         <v>362</v>
       </c>
       <c r="F111" s="195" t="s">
-        <v>3339</v>
+        <v>3337</v>
       </c>
       <c r="G111" s="76" t="s">
         <v>1336</v>
@@ -39204,7 +39157,7 @@
     </row>
     <row r="112" spans="1:9">
       <c r="A112" s="193" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
       <c r="B112" s="193">
         <v>63910392</v>
@@ -39217,7 +39170,7 @@
         <v>362</v>
       </c>
       <c r="F112" s="193" t="s">
-        <v>3339</v>
+        <v>3337</v>
       </c>
       <c r="G112" s="183" t="s">
         <v>1336</v>
@@ -39246,7 +39199,7 @@
         <v>2426</v>
       </c>
       <c r="F113" s="193" t="s">
-        <v>3339</v>
+        <v>3337</v>
       </c>
       <c r="G113" s="183" t="s">
         <v>1336</v>
@@ -39266,16 +39219,16 @@
         <v>62360487</v>
       </c>
       <c r="C114" s="194" t="s">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="D114" s="183" t="s">
-        <v>3015</v>
+        <v>3013</v>
       </c>
       <c r="E114" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F114" s="193" t="s">
-        <v>3339</v>
+        <v>3337</v>
       </c>
       <c r="G114" s="183" t="s">
         <v>1336</v>
@@ -39295,16 +39248,16 @@
         <v>62085821</v>
       </c>
       <c r="C115" s="193" t="s">
-        <v>3016</v>
+        <v>3014</v>
       </c>
       <c r="D115" s="193" t="s">
-        <v>3017</v>
+        <v>3015</v>
       </c>
       <c r="E115" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F115" s="193" t="s">
-        <v>3339</v>
+        <v>3337</v>
       </c>
       <c r="G115" s="183" t="s">
         <v>1336</v>
@@ -39318,22 +39271,22 @@
     </row>
     <row r="116" spans="1:9">
       <c r="A116" s="193" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
       <c r="B116" s="193">
         <v>64403333</v>
       </c>
       <c r="C116" s="193" t="s">
-        <v>3018</v>
+        <v>3016</v>
       </c>
       <c r="D116" s="193" t="s">
-        <v>3019</v>
+        <v>3017</v>
       </c>
       <c r="E116" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F116" s="193" t="s">
-        <v>3339</v>
+        <v>3337</v>
       </c>
       <c r="G116" s="183" t="s">
         <v>1336</v>
@@ -39353,7 +39306,7 @@
     </row>
     <row r="118" spans="1:9">
       <c r="A118" s="195" t="s">
-        <v>3346</v>
+        <v>3344</v>
       </c>
       <c r="B118" s="76">
         <v>60389752</v>
@@ -39365,7 +39318,7 @@
         <v>2280</v>
       </c>
       <c r="E118" s="76" t="s">
-        <v>3427</v>
+        <v>3425</v>
       </c>
       <c r="F118" s="76" t="s">
         <v>422</v>
@@ -39392,7 +39345,7 @@
         <v>2282</v>
       </c>
       <c r="E119" s="183" t="s">
-        <v>3427</v>
+        <v>3425</v>
       </c>
       <c r="F119" s="193" t="s">
         <v>422</v>
@@ -39406,7 +39359,7 @@
     </row>
     <row r="120" spans="1:9">
       <c r="A120" s="193" t="s">
-        <v>3346</v>
+        <v>3344</v>
       </c>
       <c r="B120" s="193">
         <v>60389752</v>
@@ -39418,7 +39371,7 @@
         <v>2284</v>
       </c>
       <c r="E120" s="183" t="s">
-        <v>3427</v>
+        <v>3425</v>
       </c>
       <c r="F120" s="193" t="s">
         <v>422</v>
@@ -39432,19 +39385,19 @@
     </row>
     <row r="121" spans="1:9">
       <c r="A121" s="183" t="s">
-        <v>3091</v>
+        <v>3089</v>
       </c>
       <c r="B121" s="183">
         <v>64403333</v>
       </c>
       <c r="C121" s="183" t="s">
-        <v>3020</v>
+        <v>3018</v>
       </c>
       <c r="D121" s="183" t="s">
-        <v>3021</v>
+        <v>3019</v>
       </c>
       <c r="E121" s="183" t="s">
-        <v>3427</v>
+        <v>3425</v>
       </c>
       <c r="F121" s="193" t="s">
         <v>422</v>
@@ -39458,7 +39411,7 @@
     </row>
     <row r="122" spans="1:9">
       <c r="A122" s="193" t="s">
-        <v>3346</v>
+        <v>3344</v>
       </c>
       <c r="B122" s="193" t="s">
         <v>2171</v>
@@ -39470,7 +39423,7 @@
         <v>377</v>
       </c>
       <c r="E122" s="183" t="s">
-        <v>3427</v>
+        <v>3425</v>
       </c>
       <c r="F122" s="193" t="s">
         <v>422</v>
@@ -39496,7 +39449,7 @@
         <v>1630</v>
       </c>
       <c r="E123" s="183" t="s">
-        <v>3427</v>
+        <v>3425</v>
       </c>
       <c r="F123" s="193" t="s">
         <v>422</v>
@@ -39510,16 +39463,16 @@
     </row>
     <row r="125" spans="1:9">
       <c r="C125" s="449" t="s">
-        <v>3543</v>
+        <v>3541</v>
       </c>
       <c r="D125" s="76" t="s">
-        <v>3666</v>
+        <v>3661</v>
       </c>
       <c r="E125" s="76" t="s">
         <v>678</v>
       </c>
       <c r="F125" s="76" t="s">
-        <v>3544</v>
+        <v>3542</v>
       </c>
       <c r="G125" s="76" t="s">
         <v>422</v>
@@ -39536,7 +39489,7 @@
         <v>362</v>
       </c>
       <c r="F126" s="183" t="s">
-        <v>3544</v>
+        <v>3542</v>
       </c>
       <c r="G126" s="183" t="s">
         <v>422</v>
@@ -39550,20 +39503,20 @@
     </row>
     <row r="127" spans="1:9">
       <c r="A127" s="451" t="s">
-        <v>3608</v>
+        <v>3604</v>
       </c>
       <c r="B127" s="451"/>
       <c r="C127" s="453" t="s">
-        <v>3610</v>
+        <v>3606</v>
       </c>
       <c r="D127" s="451" t="s">
-        <v>3611</v>
+        <v>3607</v>
       </c>
       <c r="E127" s="386" t="s">
         <v>362</v>
       </c>
       <c r="F127" s="386" t="s">
-        <v>3544</v>
+        <v>3542</v>
       </c>
       <c r="G127" s="386" t="s">
         <v>422</v>
@@ -39590,7 +39543,7 @@
         <v>362</v>
       </c>
       <c r="F128" s="183" t="s">
-        <v>3544</v>
+        <v>3542</v>
       </c>
       <c r="G128" s="183" t="s">
         <v>422</v>
@@ -39604,7 +39557,7 @@
     </row>
     <row r="129" spans="1:9">
       <c r="A129" s="451" t="s">
-        <v>3608</v>
+        <v>3604</v>
       </c>
       <c r="B129" s="451"/>
       <c r="C129" s="453" t="s">
@@ -39617,7 +39570,7 @@
         <v>362</v>
       </c>
       <c r="F129" s="386" t="s">
-        <v>3544</v>
+        <v>3542</v>
       </c>
       <c r="G129" s="386" t="s">
         <v>422</v>
@@ -39631,20 +39584,20 @@
     </row>
     <row r="130" spans="1:9">
       <c r="A130" s="451" t="s">
-        <v>3608</v>
+        <v>3604</v>
       </c>
       <c r="B130" s="451"/>
       <c r="C130" s="452" t="s">
         <v>1163</v>
       </c>
       <c r="D130" s="386" t="s">
-        <v>3609</v>
+        <v>3605</v>
       </c>
       <c r="E130" s="386" t="s">
         <v>362</v>
       </c>
       <c r="F130" s="386" t="s">
-        <v>3544</v>
+        <v>3542</v>
       </c>
       <c r="G130" s="386" t="s">
         <v>422</v>
@@ -39673,7 +39626,7 @@
         <v>2322</v>
       </c>
       <c r="F132" s="195" t="s">
-        <v>3563</v>
+        <v>3561</v>
       </c>
       <c r="G132" s="76" t="s">
         <v>1426</v>
@@ -39690,7 +39643,7 @@
         <v>64226974</v>
       </c>
       <c r="C133" s="183" t="s">
-        <v>3151</v>
+        <v>3149</v>
       </c>
       <c r="D133" s="193" t="s">
         <v>377</v>
@@ -39699,7 +39652,7 @@
         <v>2322</v>
       </c>
       <c r="F133" s="193" t="s">
-        <v>3563</v>
+        <v>3561</v>
       </c>
       <c r="G133" s="183" t="s">
         <v>1426</v>
@@ -39725,7 +39678,7 @@
         <v>2322</v>
       </c>
       <c r="F134" s="193" t="s">
-        <v>3563</v>
+        <v>3561</v>
       </c>
       <c r="G134" s="183" t="s">
         <v>1426</v>
@@ -39751,7 +39704,7 @@
         <v>2322</v>
       </c>
       <c r="F135" s="193" t="s">
-        <v>3563</v>
+        <v>3561</v>
       </c>
       <c r="G135" s="183" t="s">
         <v>1426</v>
@@ -39777,7 +39730,7 @@
         <v>2322</v>
       </c>
       <c r="F136" s="193" t="s">
-        <v>3563</v>
+        <v>3561</v>
       </c>
       <c r="G136" s="183" t="s">
         <v>1426</v>
@@ -39788,7 +39741,7 @@
     </row>
     <row r="137" spans="1:9">
       <c r="A137" s="193" t="s">
-        <v>3204</v>
+        <v>3202</v>
       </c>
       <c r="B137" s="193">
         <v>63811445</v>
@@ -39803,7 +39756,7 @@
         <v>2322</v>
       </c>
       <c r="F137" s="193" t="s">
-        <v>3563</v>
+        <v>3561</v>
       </c>
       <c r="G137" s="183" t="s">
         <v>1426</v>
@@ -39814,22 +39767,22 @@
     </row>
     <row r="139" spans="1:9">
       <c r="A139" s="195" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="B139" s="195" t="s">
         <v>2132</v>
       </c>
       <c r="C139" s="195" t="s">
-        <v>2973</v>
+        <v>2971</v>
       </c>
       <c r="D139" s="195" t="s">
-        <v>2972</v>
+        <v>2970</v>
       </c>
       <c r="E139" s="76" t="s">
         <v>2322</v>
       </c>
       <c r="F139" s="195" t="s">
-        <v>3563</v>
+        <v>3561</v>
       </c>
       <c r="G139" s="76" t="s">
         <v>1426</v>
@@ -39846,16 +39799,16 @@
         <v>66319486</v>
       </c>
       <c r="C140" s="193" t="s">
-        <v>3022</v>
+        <v>3020</v>
       </c>
       <c r="D140" s="193" t="s">
-        <v>3056</v>
+        <v>3054</v>
       </c>
       <c r="E140" s="183" t="s">
         <v>2322</v>
       </c>
       <c r="F140" s="193" t="s">
-        <v>3563</v>
+        <v>3561</v>
       </c>
       <c r="G140" s="183" t="s">
         <v>1426</v>
@@ -39866,7 +39819,7 @@
     </row>
     <row r="141" spans="1:9">
       <c r="A141" s="183" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
       <c r="B141" s="183">
         <v>60389752</v>
@@ -39881,7 +39834,7 @@
         <v>2322</v>
       </c>
       <c r="F141" s="193" t="s">
-        <v>3563</v>
+        <v>3561</v>
       </c>
       <c r="G141" s="183" t="s">
         <v>1426</v>
@@ -39895,7 +39848,7 @@
         <v>2322</v>
       </c>
       <c r="F142" s="193" t="s">
-        <v>3563</v>
+        <v>3561</v>
       </c>
       <c r="G142" s="183" t="s">
         <v>1426</v>
@@ -39921,7 +39874,7 @@
         <v>2322</v>
       </c>
       <c r="F143" s="193" t="s">
-        <v>3563</v>
+        <v>3561</v>
       </c>
       <c r="G143" s="183" t="s">
         <v>1426</v>
@@ -39932,7 +39885,7 @@
     </row>
     <row r="144" spans="1:9">
       <c r="A144" s="193" t="s">
-        <v>3292</v>
+        <v>3290</v>
       </c>
       <c r="B144" s="193">
         <v>60389752</v>
@@ -39947,7 +39900,7 @@
         <v>2322</v>
       </c>
       <c r="F144" s="193" t="s">
-        <v>3563</v>
+        <v>3561</v>
       </c>
       <c r="G144" s="183" t="s">
         <v>1426</v>
@@ -39973,7 +39926,7 @@
         <v>2426</v>
       </c>
       <c r="F146" s="195" t="s">
-        <v>3564</v>
+        <v>3562</v>
       </c>
       <c r="G146" s="76" t="s">
         <v>1426</v>
@@ -39984,13 +39937,13 @@
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="193" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="B147" s="193">
         <v>67697112</v>
       </c>
       <c r="C147" s="193" t="s">
-        <v>3040</v>
+        <v>3038</v>
       </c>
       <c r="D147" s="193" t="s">
         <v>1298</v>
@@ -39999,7 +39952,7 @@
         <v>2426</v>
       </c>
       <c r="F147" s="193" t="s">
-        <v>3564</v>
+        <v>3562</v>
       </c>
       <c r="G147" s="183" t="s">
         <v>1426</v>
@@ -40010,7 +39963,7 @@
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="183" t="s">
-        <v>3077</v>
+        <v>3075</v>
       </c>
       <c r="B148" s="183">
         <v>62560788</v>
@@ -40025,7 +39978,7 @@
         <v>2426</v>
       </c>
       <c r="F148" s="193" t="s">
-        <v>3564</v>
+        <v>3562</v>
       </c>
       <c r="G148" s="183" t="s">
         <v>1426</v>
@@ -40036,7 +39989,7 @@
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="273" t="s">
-        <v>2922</v>
+        <v>2921</v>
       </c>
       <c r="B149" s="193">
         <v>64403333</v>
@@ -40051,7 +40004,7 @@
         <v>2426</v>
       </c>
       <c r="F149" s="193" t="s">
-        <v>3564</v>
+        <v>3562</v>
       </c>
       <c r="G149" s="183" t="s">
         <v>1426</v>
@@ -40062,22 +40015,22 @@
     </row>
     <row r="150" spans="1:8">
       <c r="A150" s="193" t="s">
-        <v>2830</v>
+        <v>2829</v>
       </c>
       <c r="B150" s="193">
         <v>60125401</v>
       </c>
       <c r="C150" s="194" t="s">
-        <v>2829</v>
+        <v>2828</v>
       </c>
       <c r="D150" s="193" t="s">
-        <v>2831</v>
+        <v>2830</v>
       </c>
       <c r="E150" s="183" t="s">
         <v>2426</v>
       </c>
       <c r="F150" s="193" t="s">
-        <v>3564</v>
+        <v>3562</v>
       </c>
       <c r="G150" s="183" t="s">
         <v>1426</v>
@@ -40103,7 +40056,7 @@
         <v>2426</v>
       </c>
       <c r="F151" s="193" t="s">
-        <v>3564</v>
+        <v>3562</v>
       </c>
       <c r="G151" s="183" t="s">
         <v>1426</v>
@@ -40116,45 +40069,45 @@
       <c r="A160" s="195"/>
       <c r="B160" s="195"/>
       <c r="C160" s="195" t="s">
-        <v>3602</v>
+        <v>3598</v>
       </c>
       <c r="D160" s="195" t="s">
-        <v>3603</v>
+        <v>3599</v>
       </c>
       <c r="E160" s="195" t="s">
-        <v>3604</v>
+        <v>3600</v>
       </c>
       <c r="F160" s="76" t="s">
-        <v>3605</v>
+        <v>3601</v>
       </c>
       <c r="G160" s="76"/>
       <c r="H160" s="76"/>
     </row>
     <row r="161" spans="1:9">
       <c r="A161" s="183" t="s">
-        <v>3346</v>
+        <v>3344</v>
       </c>
       <c r="B161" s="183">
         <v>69888391</v>
       </c>
       <c r="C161" s="193" t="s">
-        <v>3606</v>
+        <v>3602</v>
       </c>
       <c r="D161" s="183" t="s">
-        <v>3607</v>
+        <v>3603</v>
       </c>
       <c r="E161" s="193" t="s">
-        <v>3604</v>
+        <v>3600</v>
       </c>
       <c r="F161" s="183" t="s">
-        <v>3605</v>
+        <v>3601</v>
       </c>
       <c r="G161" s="183"/>
       <c r="H161" s="183"/>
     </row>
     <row r="162" spans="1:9">
       <c r="A162" s="183" t="s">
-        <v>3612</v>
+        <v>3608</v>
       </c>
       <c r="B162" s="183">
         <v>68030850</v>
@@ -40163,62 +40116,62 @@
         <v>1739</v>
       </c>
       <c r="D162" s="183" t="s">
-        <v>3611</v>
+        <v>3607</v>
       </c>
       <c r="E162" s="193" t="s">
-        <v>3604</v>
+        <v>3600</v>
       </c>
       <c r="F162" s="183" t="s">
-        <v>3605</v>
+        <v>3601</v>
       </c>
       <c r="G162" s="183"/>
       <c r="H162" s="183"/>
     </row>
     <row r="163" spans="1:9">
       <c r="A163" s="183" t="s">
-        <v>3147</v>
+        <v>3145</v>
       </c>
       <c r="B163" s="183">
         <v>66230961</v>
       </c>
       <c r="C163" s="193" t="s">
-        <v>3614</v>
+        <v>3610</v>
       </c>
       <c r="D163" s="193" t="s">
-        <v>3615</v>
+        <v>3611</v>
       </c>
       <c r="E163" s="193" t="s">
-        <v>3604</v>
+        <v>3600</v>
       </c>
       <c r="F163" s="183" t="s">
-        <v>3605</v>
+        <v>3601</v>
       </c>
       <c r="G163" s="183"/>
       <c r="H163" s="183"/>
     </row>
     <row r="164" spans="1:9">
       <c r="A164" s="193" t="s">
-        <v>3488</v>
+        <v>3486</v>
       </c>
       <c r="B164" s="193">
         <v>69566600</v>
       </c>
       <c r="C164" s="193" t="s">
-        <v>3630</v>
+        <v>3626</v>
       </c>
       <c r="D164" s="193"/>
       <c r="E164" s="193" t="s">
-        <v>3604</v>
+        <v>3600</v>
       </c>
       <c r="F164" s="183" t="s">
-        <v>3605</v>
+        <v>3601</v>
       </c>
       <c r="G164" s="183"/>
       <c r="H164" s="183"/>
     </row>
     <row r="165" spans="1:9">
       <c r="A165" s="183" t="s">
-        <v>3270</v>
+        <v>3268</v>
       </c>
       <c r="B165" s="183">
         <v>64403333</v>
@@ -40230,10 +40183,10 @@
         <v>1818</v>
       </c>
       <c r="E165" s="193" t="s">
-        <v>3604</v>
+        <v>3600</v>
       </c>
       <c r="F165" s="183" t="s">
-        <v>3605</v>
+        <v>3601</v>
       </c>
       <c r="G165" s="183"/>
       <c r="H165" s="183"/>
@@ -40242,7 +40195,7 @@
       <c r="A167" s="221"/>
       <c r="B167" s="221"/>
       <c r="C167" s="221" t="s">
-        <v>3626</v>
+        <v>3622</v>
       </c>
       <c r="D167" s="221"/>
       <c r="E167" s="221"/>
@@ -40267,42 +40220,42 @@
         <v>362</v>
       </c>
       <c r="F169" s="195" t="s">
-        <v>3651</v>
+        <v>3646</v>
       </c>
       <c r="G169" s="76" t="s">
-        <v>3653</v>
+        <v>3648</v>
       </c>
       <c r="H169" s="76" t="s">
-        <v>3652</v>
+        <v>3647</v>
       </c>
       <c r="I169" t="s">
-        <v>3650</v>
+        <v>3645</v>
       </c>
     </row>
     <row r="170" spans="1:9">
       <c r="A170" s="273" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
       <c r="B170" s="193">
         <v>65963732</v>
       </c>
       <c r="C170" s="194" t="s">
-        <v>3007</v>
+        <v>3005</v>
       </c>
       <c r="D170" s="193" t="s">
-        <v>3008</v>
+        <v>3006</v>
       </c>
       <c r="E170" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F170" s="193" t="s">
-        <v>3651</v>
+        <v>3646</v>
       </c>
       <c r="G170" s="183" t="s">
-        <v>3653</v>
+        <v>3648</v>
       </c>
       <c r="H170" s="183" t="s">
-        <v>3652</v>
+        <v>3647</v>
       </c>
       <c r="I170" s="10" t="s">
         <v>407</v>
@@ -40319,19 +40272,19 @@
         <v>2312</v>
       </c>
       <c r="D171" s="183" t="s">
-        <v>3002</v>
+        <v>3000</v>
       </c>
       <c r="E171" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F171" s="193" t="s">
-        <v>3651</v>
+        <v>3646</v>
       </c>
       <c r="G171" s="183" t="s">
-        <v>3653</v>
+        <v>3648</v>
       </c>
       <c r="H171" s="183" t="s">
-        <v>3652</v>
+        <v>3647</v>
       </c>
       <c r="I171" s="10" t="s">
         <v>407</v>
@@ -40354,13 +40307,13 @@
         <v>362</v>
       </c>
       <c r="F172" s="193" t="s">
-        <v>3651</v>
+        <v>3646</v>
       </c>
       <c r="G172" s="183" t="s">
-        <v>3653</v>
+        <v>3648</v>
       </c>
       <c r="H172" s="183" t="s">
-        <v>3652</v>
+        <v>3647</v>
       </c>
       <c r="I172" s="10" t="s">
         <v>407</v>
@@ -40368,7 +40321,7 @@
     </row>
     <row r="173" spans="1:9">
       <c r="A173" s="183" t="s">
-        <v>3292</v>
+        <v>3290</v>
       </c>
       <c r="B173" s="183">
         <v>64403333</v>
@@ -40383,13 +40336,13 @@
         <v>362</v>
       </c>
       <c r="F173" s="193" t="s">
-        <v>3651</v>
+        <v>3646</v>
       </c>
       <c r="G173" s="183" t="s">
-        <v>3653</v>
+        <v>3648</v>
       </c>
       <c r="H173" s="183" t="s">
-        <v>3652</v>
+        <v>3647</v>
       </c>
       <c r="I173" s="10" t="s">
         <v>407</v>
@@ -40403,22 +40356,22 @@
         <v>64403333</v>
       </c>
       <c r="C174" s="194" t="s">
-        <v>2832</v>
+        <v>2831</v>
       </c>
       <c r="D174" s="436" t="s">
-        <v>2831</v>
+        <v>2830</v>
       </c>
       <c r="E174" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F174" s="193" t="s">
-        <v>3651</v>
+        <v>3646</v>
       </c>
       <c r="G174" s="183" t="s">
-        <v>3653</v>
+        <v>3648</v>
       </c>
       <c r="H174" s="183" t="s">
-        <v>3652</v>
+        <v>3647</v>
       </c>
       <c r="I174" s="10" t="s">
         <v>407</v>
@@ -40426,13 +40379,13 @@
     </row>
     <row r="178" spans="1:9">
       <c r="A178" s="10" t="s">
-        <v>3629</v>
+        <v>3625</v>
       </c>
       <c r="C178" s="10" t="s">
-        <v>3627</v>
+        <v>3623</v>
       </c>
       <c r="D178" s="10" t="s">
-        <v>3628</v>
+        <v>3624</v>
       </c>
     </row>
     <row r="180" spans="1:9">
@@ -40454,7 +40407,7 @@
       <c r="A183" s="221"/>
       <c r="B183" s="221"/>
       <c r="C183" s="221" t="s">
-        <v>3083</v>
+        <v>3081</v>
       </c>
       <c r="D183" s="221"/>
       <c r="E183" s="221"/>
@@ -40462,25 +40415,25 @@
     </row>
     <row r="184" spans="1:9">
       <c r="A184" s="76" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="B184" s="76">
         <v>67836337</v>
       </c>
       <c r="C184" s="116" t="s">
-        <v>3193</v>
+        <v>3191</v>
       </c>
       <c r="D184" s="195" t="s">
-        <v>3194</v>
+        <v>3192</v>
       </c>
       <c r="E184" s="430">
         <v>46243</v>
       </c>
       <c r="F184" s="76" t="s">
-        <v>3084</v>
+        <v>3082</v>
       </c>
       <c r="G184" s="195" t="s">
-        <v>3244</v>
+        <v>3242</v>
       </c>
       <c r="H184" s="76" t="s">
         <v>1955</v>
@@ -40488,19 +40441,19 @@
     </row>
     <row r="185" spans="1:9">
       <c r="A185" s="193" t="s">
-        <v>3246</v>
+        <v>3244</v>
       </c>
       <c r="B185" s="193">
         <v>60196388</v>
       </c>
       <c r="C185" s="193" t="s">
-        <v>3245</v>
+        <v>3243</v>
       </c>
       <c r="D185" s="439" t="s">
-        <v>3194</v>
+        <v>3192</v>
       </c>
       <c r="E185" s="429" t="s">
-        <v>3241</v>
+        <v>3239</v>
       </c>
       <c r="F185" s="193"/>
       <c r="G185" s="183"/>
@@ -40508,19 +40461,19 @@
     </row>
     <row r="186" spans="1:9">
       <c r="A186" s="183" t="s">
-        <v>3306</v>
+        <v>3304</v>
       </c>
       <c r="B186" s="183">
         <v>64403333</v>
       </c>
       <c r="C186" s="191" t="s">
-        <v>3261</v>
+        <v>3259</v>
       </c>
       <c r="D186" s="183" t="s">
-        <v>3252</v>
+        <v>3250</v>
       </c>
       <c r="E186" s="429" t="s">
-        <v>3241</v>
+        <v>3239</v>
       </c>
       <c r="F186" s="193"/>
       <c r="G186" s="183"/>
@@ -40528,19 +40481,19 @@
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="193" t="s">
-        <v>3282</v>
+        <v>3280</v>
       </c>
       <c r="B187" s="193">
         <v>68071614</v>
       </c>
       <c r="C187" s="193" t="s">
+        <v>3277</v>
+      </c>
+      <c r="D187" s="193" t="s">
+        <v>3278</v>
+      </c>
+      <c r="E187" s="429" t="s">
         <v>3279</v>
-      </c>
-      <c r="D187" s="193" t="s">
-        <v>3280</v>
-      </c>
-      <c r="E187" s="429" t="s">
-        <v>3281</v>
       </c>
       <c r="F187" s="193"/>
       <c r="G187" s="183"/>
@@ -40548,19 +40501,19 @@
     </row>
     <row r="188" spans="1:9" s="226" customFormat="1" ht="15.5">
       <c r="A188" s="183" t="s">
-        <v>3539</v>
+        <v>3537</v>
       </c>
       <c r="B188" s="183">
         <v>63950696</v>
       </c>
       <c r="C188" s="445" t="s">
-        <v>3308</v>
+        <v>3306</v>
       </c>
       <c r="D188" s="445" t="s">
         <v>2709</v>
       </c>
       <c r="E188" s="429" t="s">
-        <v>3309</v>
+        <v>3307</v>
       </c>
       <c r="F188" s="446"/>
       <c r="G188" s="440"/>
@@ -40575,13 +40528,13 @@
         <v>65147336</v>
       </c>
       <c r="C189" s="183" t="s">
+        <v>3326</v>
+      </c>
+      <c r="D189" s="183" t="s">
+        <v>3327</v>
+      </c>
+      <c r="E189" s="429" t="s">
         <v>3328</v>
-      </c>
-      <c r="D189" s="183" t="s">
-        <v>3329</v>
-      </c>
-      <c r="E189" s="429" t="s">
-        <v>3330</v>
       </c>
       <c r="F189" s="193"/>
       <c r="G189" s="183"/>
@@ -40622,7 +40575,7 @@
         <v>316</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>3169</v>
+        <v>3167</v>
       </c>
       <c r="E194" s="30"/>
       <c r="F194"/>
@@ -40648,7 +40601,7 @@
         <v>439</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>3219</v>
+        <v>3217</v>
       </c>
       <c r="E196" s="30"/>
       <c r="F196"/>
@@ -40659,7 +40612,7 @@
         <v>26</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>3279</v>
+        <v>3277</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -40667,7 +40620,7 @@
         <v>1319</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>3308</v>
+        <v>3306</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -40675,7 +40628,7 @@
         <v>1641</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>3328</v>
+        <v>3326</v>
       </c>
       <c r="F199" s="392"/>
     </row>
@@ -40684,7 +40637,7 @@
         <v>1300</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>3543</v>
+        <v>3541</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -40692,7 +40645,7 @@
         <v>406</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>3606</v>
+        <v>3602</v>
       </c>
     </row>
     <row r="202" spans="1:9">
@@ -40700,7 +40653,7 @@
         <v>707</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>3610</v>
+        <v>3606</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -40708,7 +40661,7 @@
         <v>281</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>3614</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="204" spans="1:9">
@@ -40716,7 +40669,7 @@
         <v>2330</v>
       </c>
       <c r="D204" s="426" t="s">
-        <v>3627</v>
+        <v>3623</v>
       </c>
     </row>
     <row r="205" spans="1:9">
@@ -40726,7 +40679,7 @@
         <v>465</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>3134</v>
+        <v>3132</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -40734,7 +40687,7 @@
         <v>219</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>3138</v>
+        <v>3136</v>
       </c>
     </row>
     <row r="207" spans="1:9">
@@ -40742,7 +40695,7 @@
         <v>427</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>3151</v>
+        <v>3149</v>
       </c>
     </row>
     <row r="208" spans="1:9">
@@ -40750,7 +40703,7 @@
         <v>1049</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>3165</v>
+        <v>3163</v>
       </c>
     </row>
     <row r="223" spans="1:9">
@@ -41976,19 +41929,19 @@
         <v>1383</v>
       </c>
       <c r="E3" t="s">
-        <v>3552</v>
+        <v>3550</v>
       </c>
       <c r="F3" t="s">
-        <v>3553</v>
+        <v>3551</v>
       </c>
       <c r="G3" t="s">
         <v>704</v>
       </c>
       <c r="H3" t="s">
-        <v>3183</v>
+        <v>3181</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>3376</v>
+        <v>3374</v>
       </c>
       <c r="J3"/>
     </row>
@@ -42015,10 +41968,10 @@
         <v>515</v>
       </c>
       <c r="H4" s="49" t="s">
-        <v>3025</v>
+        <v>3023</v>
       </c>
       <c r="I4" t="s">
-        <v>3303</v>
+        <v>3301</v>
       </c>
       <c r="J4"/>
     </row>
@@ -42027,7 +41980,7 @@
         <v>1421</v>
       </c>
       <c r="B5" t="s">
-        <v>3378</v>
+        <v>3376</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>480</v>
@@ -42036,7 +41989,7 @@
         <v>1505</v>
       </c>
       <c r="E5" t="s">
-        <v>3487</v>
+        <v>3485</v>
       </c>
       <c r="F5" t="s">
         <v>2141</v>
@@ -42045,10 +41998,10 @@
         <v>515</v>
       </c>
       <c r="H5" s="220" t="s">
-        <v>3470</v>
+        <v>3468</v>
       </c>
       <c r="I5" s="220" t="s">
-        <v>3540</v>
+        <v>3538</v>
       </c>
       <c r="J5" t="s">
         <v>1388</v>
@@ -42056,31 +42009,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>3182</v>
+        <v>3180</v>
       </c>
       <c r="B6" t="s">
-        <v>3211</v>
+        <v>3209</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>427</v>
       </c>
       <c r="D6" t="s">
-        <v>3037</v>
+        <v>3035</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>3035</v>
+        <v>3033</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>2777</v>
+        <v>2776</v>
       </c>
       <c r="G6" t="s">
         <v>436</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>3481</v>
+        <v>3479</v>
       </c>
       <c r="I6" t="s">
-        <v>3314</v>
+        <v>3312</v>
       </c>
       <c r="J6"/>
     </row>
@@ -42112,7 +42065,7 @@
         <v>2039</v>
       </c>
       <c r="D8" t="s">
-        <v>3377</v>
+        <v>3375</v>
       </c>
       <c r="E8" t="s">
         <v>2290</v>
@@ -42124,10 +42077,10 @@
         <v>250</v>
       </c>
       <c r="H8" s="304" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
       <c r="I8" t="s">
-        <v>3672</v>
+        <v>3667</v>
       </c>
       <c r="J8"/>
     </row>
@@ -42157,36 +42110,36 @@
         <v>2670</v>
       </c>
       <c r="I9" s="273" t="s">
-        <v>2759</v>
+        <v>2758</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="B10">
         <v>62349088</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>3402</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>3403</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>3404</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="F10" s="10" t="s">
         <v>3405</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>3406</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>3407</v>
       </c>
       <c r="G10" t="s">
         <v>250</v>
       </c>
       <c r="H10" s="276" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>3453</v>
+        <v>3451</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -42247,16 +42200,16 @@
     </row>
     <row r="16" spans="1:10">
       <c r="C16" s="8" t="s">
-        <v>2762</v>
+        <v>2761</v>
       </c>
       <c r="D16" t="s">
-        <v>2761</v>
+        <v>2760</v>
       </c>
       <c r="E16" t="s">
+        <v>2786</v>
+      </c>
+      <c r="F16" t="s">
         <v>2787</v>
-      </c>
-      <c r="F16" t="s">
-        <v>2788</v>
       </c>
       <c r="G16" t="s">
         <v>121</v>
@@ -42323,7 +42276,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="10" t="s">
-        <v>3093</v>
+        <v>3091</v>
       </c>
       <c r="B5" s="10">
         <v>67992849</v>
@@ -42344,15 +42297,15 @@
         <v>517</v>
       </c>
       <c r="H5" s="220" t="s">
-        <v>3206</v>
+        <v>3204</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>3388</v>
+        <v>3386</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="457" t="s">
-        <v>3539</v>
+        <v>3537</v>
       </c>
       <c r="B6" s="10">
         <v>62140561</v>
@@ -42361,7 +42314,7 @@
         <v>1695</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>3682</v>
+        <v>3677</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>1679</v>
@@ -42373,15 +42326,15 @@
         <v>517</v>
       </c>
       <c r="H6" s="457" t="s">
-        <v>3683</v>
+        <v>3678</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>3431</v>
+        <v>3429</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="10" t="s">
-        <v>3178</v>
+        <v>3176</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>2364</v>
@@ -42390,7 +42343,7 @@
         <v>1706</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>3567</v>
+        <v>3565</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1679</v>
@@ -42402,10 +42355,10 @@
         <v>517</v>
       </c>
       <c r="H7" t="s">
-        <v>3568</v>
+        <v>3566</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>3631</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -42453,7 +42406,7 @@
         <v>2122</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>2968</v>
+        <v>2966</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>958</v>
@@ -42465,10 +42418,10 @@
         <v>517</v>
       </c>
       <c r="H12" s="273" t="s">
-        <v>2969</v>
+        <v>2967</v>
       </c>
       <c r="I12" t="s">
-        <v>3068</v>
+        <v>3066</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -42484,7 +42437,7 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="10" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="B15" s="10">
         <v>68543713</v>
@@ -42493,7 +42446,7 @@
         <v>2179</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>2881</v>
+        <v>2880</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>958</v>
@@ -42505,10 +42458,10 @@
         <v>517</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>3439</v>
+        <v>3437</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>3429</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -42534,7 +42487,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="10" t="s">
-        <v>3178</v>
+        <v>3176</v>
       </c>
       <c r="B17" s="10">
         <v>64403333</v>
@@ -42566,7 +42519,7 @@
         <v>2294</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>2997</v>
+        <v>2995</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>958</v>
@@ -42578,10 +42531,10 @@
         <v>517</v>
       </c>
       <c r="H18" s="454" t="s">
-        <v>2981</v>
+        <v>2979</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>3050</v>
+        <v>3048</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -42595,7 +42548,7 @@
         <v>2345</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>3413</v>
+        <v>3411</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>958</v>
@@ -42607,10 +42560,10 @@
         <v>517</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>3414</v>
+        <v>3412</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>3155</v>
+        <v>3153</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="190" customFormat="1" ht="26">
@@ -42626,13 +42579,13 @@
         <v>2546</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>3121</v>
+        <v>3119</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>2369</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>3095</v>
+        <v>3093</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>958</v>
@@ -42644,15 +42597,15 @@
         <v>517</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>3207</v>
+        <v>3205</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>3526</v>
+        <v>3524</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B23" s="10">
         <v>64720128</v>
@@ -42673,15 +42626,15 @@
         <v>517</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>3188</v>
+        <v>3186</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>3189</v>
+        <v>3187</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="10" t="s">
-        <v>3306</v>
+        <v>3304</v>
       </c>
       <c r="B24" s="10">
         <v>63844875</v>
@@ -42690,7 +42643,7 @@
         <v>2385</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>3438</v>
+        <v>3436</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>958</v>
@@ -42702,10 +42655,10 @@
         <v>517</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>3152</v>
+        <v>3150</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>3374</v>
+        <v>3372</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -42715,7 +42668,7 @@
         <v>2394</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>2880</v>
+        <v>2879</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>958</v>
@@ -42834,13 +42787,13 @@
         <v>2407</v>
       </c>
       <c r="B4" t="s">
-        <v>2917</v>
+        <v>2916</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1845</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="E4" t="s">
         <v>1846</v>
@@ -42852,13 +42805,13 @@
         <v>962</v>
       </c>
       <c r="H4" s="49" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>3525</v>
+        <v>3523</v>
       </c>
       <c r="J4" t="s">
-        <v>3569</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -42912,13 +42865,13 @@
         <v>2543</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>2802</v>
+        <v>2801</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>2255</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>3180</v>
+        <v>3178</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>2256</v>
@@ -42930,30 +42883,30 @@
         <v>962</v>
       </c>
       <c r="H7" s="49" t="s">
-        <v>2908</v>
+        <v>2907</v>
       </c>
       <c r="I7" s="273" t="s">
-        <v>2979</v>
+        <v>2977</v>
       </c>
       <c r="J7" s="273" t="s">
-        <v>2878</v>
+        <v>2877</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="10" t="s">
-        <v>3539</v>
+        <v>3537</v>
       </c>
       <c r="B8" t="s">
-        <v>3349</v>
+        <v>3347</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>3253</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>3254</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>3255</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>3256</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>3257</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>1722</v>
@@ -42962,45 +42915,45 @@
         <v>962</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>3428</v>
+        <v>3426</v>
       </c>
       <c r="I8" s="273" t="s">
-        <v>2964</v>
+        <v>2962</v>
       </c>
       <c r="J8" s="273" t="s">
-        <v>2885</v>
+        <v>2884</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="273" t="s">
+        <v>2887</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>2888</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>2889</v>
-      </c>
       <c r="C9" s="22" t="s">
+        <v>2885</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>2799</v>
+      </c>
+      <c r="E9" s="444" t="s">
         <v>2886</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="F9" s="10" t="s">
         <v>2800</v>
-      </c>
-      <c r="E9" s="444" t="s">
-        <v>2887</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>2801</v>
       </c>
       <c r="G9" t="s">
         <v>962</v>
       </c>
       <c r="H9" s="273" t="s">
+        <v>2889</v>
+      </c>
+      <c r="I9" s="273" t="s">
         <v>2890</v>
       </c>
-      <c r="I9" s="273" t="s">
-        <v>2891</v>
-      </c>
       <c r="J9" t="s">
-        <v>3516</v>
+        <v>3514</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -43008,16 +42961,16 @@
         <v>1418</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2967</v>
+        <v>2965</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>2966</v>
+        <v>2964</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>3352</v>
+        <v>3350</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>2257</v>
@@ -43026,30 +42979,30 @@
         <v>962</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>3678</v>
+        <v>3673</v>
       </c>
       <c r="I10" s="273" t="s">
-        <v>3027</v>
+        <v>3025</v>
       </c>
       <c r="J10" t="s">
-        <v>3069</v>
+        <v>3067</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="10" t="s">
-        <v>3266</v>
+        <v>3264</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>3411</v>
+        <v>3409</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>3391</v>
+        <v>3389</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>3394</v>
+        <v>3392</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>3392</v>
+        <v>3390</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>1722</v>
@@ -43069,7 +43022,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="C15" s="426" t="s">
-        <v>3391</v>
+        <v>3389</v>
       </c>
     </row>
   </sheetData>
@@ -43210,10 +43163,10 @@
         <v>60240509</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>3235</v>
+        <v>3233</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>3236</v>
+        <v>3234</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>2544</v>
@@ -43225,7 +43178,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="273" t="s">
-        <v>2794</v>
+        <v>2793</v>
       </c>
       <c r="B10" s="10">
         <v>64676716</v>
@@ -43234,7 +43187,7 @@
         <v>1769</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>2872</v>
+        <v>2871</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>2544</v>
@@ -43269,16 +43222,16 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="10" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B12" s="10">
         <v>66466729</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>3355</v>
+        <v>3353</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>3356</v>
+        <v>3354</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
@@ -43358,7 +43311,7 @@
       <c r="A19" s="10"/>
       <c r="B19" s="10"/>
       <c r="C19" s="426" t="s">
-        <v>3355</v>
+        <v>3353</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
@@ -43464,30 +43417,30 @@
     <row r="1" spans="1:10" s="408" customFormat="1" ht="42.65" customHeight="1">
       <c r="A1" s="407"/>
       <c r="B1" s="407" t="s">
-        <v>2825</v>
+        <v>2824</v>
       </c>
       <c r="C1" s="407"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="276"/>
       <c r="C4" s="1" t="s">
+        <v>2918</v>
+      </c>
+      <c r="E4" t="s">
+        <v>2825</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>2919</v>
-      </c>
-      <c r="E4" t="s">
-        <v>2826</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>2920</v>
       </c>
       <c r="G4" s="276"/>
       <c r="H4" s="273" t="s">
-        <v>2911</v>
+        <v>2910</v>
       </c>
       <c r="I4" s="273" t="s">
-        <v>2915</v>
+        <v>2914</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>2976</v>
+        <v>2974</v>
       </c>
     </row>
   </sheetData>
@@ -43832,7 +43785,7 @@
         <v>2493</v>
       </c>
       <c r="C5" s="323" t="s">
-        <v>2777</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="323" customFormat="1">
@@ -43840,10 +43793,10 @@
         <v>2472</v>
       </c>
       <c r="B6" s="323" t="s">
-        <v>2776</v>
+        <v>2775</v>
       </c>
       <c r="C6" s="323" t="s">
-        <v>2776</v>
+        <v>2775</v>
       </c>
     </row>
     <row r="7" spans="1:13" s="323" customFormat="1">
@@ -43918,10 +43871,10 @@
         <v>2501</v>
       </c>
       <c r="H14" s="329" t="s">
-        <v>2779</v>
+        <v>2778</v>
       </c>
       <c r="I14" s="329" t="s">
-        <v>2782</v>
+        <v>2781</v>
       </c>
       <c r="L14" s="329"/>
       <c r="M14" s="329"/>
@@ -43949,10 +43902,10 @@
         <v>2502</v>
       </c>
       <c r="H15" s="330" t="s">
-        <v>2780</v>
+        <v>2779</v>
       </c>
       <c r="I15" s="330" t="s">
-        <v>2783</v>
+        <v>2782</v>
       </c>
       <c r="L15" s="330"/>
       <c r="M15" s="330"/>
@@ -43980,7 +43933,7 @@
         <v>2503</v>
       </c>
       <c r="H16" s="330" t="s">
-        <v>2781</v>
+        <v>2780</v>
       </c>
       <c r="I16" s="330" t="s">
         <v>1336</v>
@@ -43993,7 +43946,7 @@
         <v>2477</v>
       </c>
       <c r="B17" s="394" t="s">
-        <v>2773</v>
+        <v>2772</v>
       </c>
       <c r="C17" s="394"/>
       <c r="D17" s="394"/>
@@ -44010,7 +43963,7 @@
         <v>2472</v>
       </c>
       <c r="B18" s="394" t="s">
-        <v>2774</v>
+        <v>2773</v>
       </c>
       <c r="C18" s="394"/>
       <c r="D18" s="394"/>
@@ -44027,7 +43980,7 @@
         <v>2473</v>
       </c>
       <c r="B19" s="394" t="s">
-        <v>2775</v>
+        <v>2774</v>
       </c>
       <c r="C19" s="394"/>
       <c r="D19" s="394"/>
@@ -44882,7 +44835,7 @@
         <v>51</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>1155</v>
@@ -44894,10 +44847,10 @@
         <v>159</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>3096</v>
+        <v>3094</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>3106</v>
+        <v>3104</v>
       </c>
       <c r="N6" s="4" t="s">
         <v>26</v>
@@ -44905,7 +44858,7 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="4" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B7" s="4">
         <v>69888391</v>
@@ -44929,13 +44882,13 @@
         <v>2237</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>3581</v>
+        <v>3579</v>
       </c>
       <c r="L7" s="3"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>3292</v>
+        <v>3290</v>
       </c>
       <c r="B8" t="s">
         <v>452</v>
@@ -44959,15 +44912,15 @@
         <v>2656</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>3676</v>
+        <v>3671</v>
       </c>
     </row>
     <row r="9" spans="1:14" s="4" customFormat="1">
       <c r="A9" t="s">
-        <v>3488</v>
+        <v>3486</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>3633</v>
+        <v>3629</v>
       </c>
       <c r="C9" s="22" t="s">
         <v>642</v>
@@ -44976,16 +44929,16 @@
         <v>2131</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>3107</v>
+        <v>3105</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>3108</v>
+        <v>3106</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>159</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>3071</v>
+        <v>3069</v>
       </c>
       <c r="I9" s="105"/>
       <c r="L9" s="4" t="s">
@@ -44994,7 +44947,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="4" t="s">
-        <v>3270</v>
+        <v>3268</v>
       </c>
       <c r="B10" s="4">
         <v>67916500</v>
@@ -45015,10 +44968,10 @@
         <v>244</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>3183</v>
+        <v>3181</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>3616</v>
+        <v>3612</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -45035,19 +44988,19 @@
         <v>1496</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>3031</v>
+        <v>3029</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>2819</v>
+        <v>2818</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>244</v>
       </c>
       <c r="H11" t="s">
-        <v>3298</v>
+        <v>3296</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>3267</v>
+        <v>3265</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -45067,18 +45020,18 @@
         <v>244</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>3301</v>
+        <v>3299</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>3332</v>
+        <v>3330</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="4" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>3316</v>
+        <v>3314</v>
       </c>
       <c r="C13" s="22" t="s">
         <v>1215</v>
@@ -45096,10 +45049,10 @@
         <v>244</v>
       </c>
       <c r="H13" s="447" t="s">
-        <v>3029</v>
+        <v>3027</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>3379</v>
+        <v>3377</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="4" customFormat="1">
@@ -45125,40 +45078,40 @@
         <v>244</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>3216</v>
+        <v>3214</v>
       </c>
       <c r="I14" s="220" t="s">
-        <v>3259</v>
+        <v>3257</v>
       </c>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="4" t="s">
-        <v>3539</v>
+        <v>3537</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>3681</v>
+        <v>3676</v>
       </c>
       <c r="C15" s="22" t="s">
         <v>340</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>2767</v>
+        <v>2766</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>3350</v>
+        <v>3348</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>3351</v>
+        <v>3349</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>886</v>
       </c>
       <c r="H15" t="s">
-        <v>3654</v>
+        <v>3649</v>
       </c>
       <c r="I15" t="s">
-        <v>3375</v>
+        <v>3373</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>498</v>
@@ -45175,7 +45128,7 @@
         <v>2528</v>
       </c>
       <c r="D16" t="s">
-        <v>2758</v>
+        <v>2757</v>
       </c>
       <c r="E16" t="s">
         <v>2530</v>
@@ -45187,10 +45140,10 @@
         <v>159</v>
       </c>
       <c r="H16" t="s">
-        <v>3222</v>
+        <v>3220</v>
       </c>
       <c r="I16" t="s">
-        <v>3097</v>
+        <v>3095</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>804</v>
@@ -45198,7 +45151,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>3093</v>
+        <v>3091</v>
       </c>
       <c r="B17">
         <v>65325884</v>
@@ -45221,7 +45174,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="4" t="s">
-        <v>3178</v>
+        <v>3176</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>2085</v>
@@ -45233,24 +45186,24 @@
         <v>2190</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>3336</v>
+        <v>3334</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>3108</v>
+        <v>3106</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>244</v>
       </c>
       <c r="H18" t="s">
-        <v>3420</v>
+        <v>3418</v>
       </c>
       <c r="I18" t="s">
-        <v>3291</v>
+        <v>3289</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="4" customFormat="1">
       <c r="A19" s="4" t="s">
-        <v>3306</v>
+        <v>3304</v>
       </c>
       <c r="B19" s="4">
         <v>64403333</v>
@@ -45262,10 +45215,10 @@
         <v>2529</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>3108</v>
+        <v>3106</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>1223</v>
@@ -45275,7 +45228,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="4" t="s">
-        <v>3093</v>
+        <v>3091</v>
       </c>
       <c r="B20">
         <v>64403333</v>
@@ -45301,7 +45254,7 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="4" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
       <c r="B21" s="4">
         <v>64403333</v>
@@ -45336,7 +45289,7 @@
         <v>2181</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>3390</v>
+        <v>3388</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>2423</v>
@@ -45347,7 +45300,7 @@
     </row>
     <row r="23" spans="1:12" s="4" customFormat="1">
       <c r="A23" t="s">
-        <v>3093</v>
+        <v>3091</v>
       </c>
       <c r="B23">
         <v>63247837</v>
@@ -45356,7 +45309,7 @@
         <v>2537</v>
       </c>
       <c r="D23" t="s">
-        <v>3047</v>
+        <v>3045</v>
       </c>
       <c r="E23" t="s">
         <v>2540</v>
@@ -45368,16 +45321,16 @@
         <v>159</v>
       </c>
       <c r="H23" t="s">
-        <v>3641</v>
+        <v>3636</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>3064</v>
+        <v>3062</v>
       </c>
       <c r="L23" s="6"/>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>3292</v>
+        <v>3290</v>
       </c>
       <c r="B24">
         <v>69184177</v>
@@ -45386,10 +45339,10 @@
         <v>1614</v>
       </c>
       <c r="D24" t="s">
-        <v>2910</v>
+        <v>2909</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>2420</v>
@@ -45400,19 +45353,19 @@
     </row>
     <row r="25" spans="1:12" s="4" customFormat="1">
       <c r="A25" s="4" t="s">
-        <v>3136</v>
+        <v>3134</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>3150</v>
+        <v>3148</v>
       </c>
       <c r="C25" s="21" t="s">
         <v>1321</v>
       </c>
       <c r="D25" t="s">
-        <v>3149</v>
+        <v>3147</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>2863</v>
+        <v>2862</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>2423</v>
@@ -45421,10 +45374,10 @@
         <v>244</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>3446</v>
+        <v>3444</v>
       </c>
       <c r="I25" s="220" t="s">
-        <v>3210</v>
+        <v>3208</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="4" customFormat="1">
@@ -45450,10 +45403,10 @@
         <v>159</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>3232</v>
+        <v>3230</v>
       </c>
       <c r="I27" t="s">
-        <v>3624</v>
+        <v>3620</v>
       </c>
       <c r="L27" s="4" t="s">
         <v>812</v>
@@ -45461,7 +45414,7 @@
     </row>
     <row r="28" spans="1:12" s="4" customFormat="1">
       <c r="A28" t="s">
-        <v>3266</v>
+        <v>3264</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>2414</v>
@@ -45473,7 +45426,7 @@
         <v>2007</v>
       </c>
       <c r="E28" t="s">
-        <v>2914</v>
+        <v>2913</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>2423</v>
@@ -45482,16 +45435,16 @@
         <v>325</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>3393</v>
+        <v>3391</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>3171</v>
+        <v>3169</v>
       </c>
       <c r="K28"/>
     </row>
     <row r="29" spans="1:12" s="75" customFormat="1">
       <c r="A29" t="s">
-        <v>3585</v>
+        <v>3583</v>
       </c>
       <c r="B29" t="s">
         <v>1206</v>
@@ -45500,22 +45453,22 @@
         <v>350</v>
       </c>
       <c r="D29" s="75" t="s">
-        <v>2789</v>
+        <v>2788</v>
       </c>
       <c r="E29" t="s">
-        <v>3094</v>
+        <v>3092</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>2819</v>
+        <v>2818</v>
       </c>
       <c r="G29" s="75" t="s">
         <v>250</v>
       </c>
       <c r="H29" t="s">
-        <v>3430</v>
+        <v>3428</v>
       </c>
       <c r="I29" t="s">
-        <v>3044</v>
+        <v>3042</v>
       </c>
       <c r="J29" s="4"/>
       <c r="L29" s="135"/>
@@ -45525,16 +45478,16 @@
         <v>2662</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>3504</v>
+        <v>3502</v>
       </c>
       <c r="C30" s="22" t="s">
         <v>402</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>2895</v>
+        <v>2894</v>
       </c>
       <c r="E30" t="s">
-        <v>2988</v>
+        <v>2986</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>1336</v>
@@ -45543,15 +45496,15 @@
         <v>159</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>3532</v>
+        <v>3530</v>
       </c>
       <c r="I30" t="s">
-        <v>3426</v>
+        <v>3424</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>3091</v>
+        <v>3089</v>
       </c>
       <c r="B31" s="4">
         <v>69409351</v>
@@ -45572,10 +45525,10 @@
         <v>159</v>
       </c>
       <c r="H31" t="s">
-        <v>3618</v>
+        <v>3614</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>3536</v>
+        <v>3534</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -45589,7 +45542,7 @@
         <v>2334</v>
       </c>
       <c r="D32" t="s">
-        <v>3416</v>
+        <v>3414</v>
       </c>
       <c r="E32" t="s">
         <v>2338</v>
@@ -45601,10 +45554,10 @@
         <v>159</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>3382</v>
+        <v>3380</v>
       </c>
       <c r="I32" t="s">
-        <v>3417</v>
+        <v>3415</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -45612,13 +45565,13 @@
         <v>2543</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>3249</v>
+        <v>3247</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>2527</v>
       </c>
       <c r="D33" t="s">
-        <v>3248</v>
+        <v>3246</v>
       </c>
       <c r="E33" t="s">
         <v>2530</v>
@@ -45630,21 +45583,21 @@
         <v>2531</v>
       </c>
       <c r="H33" t="s">
-        <v>3401</v>
+        <v>3399</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>3632</v>
+        <v>3628</v>
       </c>
       <c r="C34" s="21" t="s">
         <v>2524</v>
       </c>
       <c r="D34" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
       <c r="E34" t="s">
         <v>2530</v>
@@ -45656,25 +45609,25 @@
         <v>159</v>
       </c>
       <c r="H34" t="s">
-        <v>2958</v>
+        <v>2957</v>
       </c>
       <c r="I34" t="s">
-        <v>3679</v>
+        <v>3674</v>
       </c>
       <c r="J34" s="4"/>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>2843</v>
+        <v>2842</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>2525</v>
       </c>
       <c r="D35" t="s">
-        <v>2842</v>
+        <v>2841</v>
       </c>
       <c r="E35" t="s">
         <v>2530</v>
@@ -45686,24 +45639,24 @@
         <v>2531</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>3397</v>
+        <v>3395</v>
       </c>
       <c r="I35" t="s">
-        <v>3432</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>3093</v>
+        <v>3091</v>
       </c>
       <c r="B36" t="s">
-        <v>3121</v>
+        <v>3119</v>
       </c>
       <c r="C36" s="22" t="s">
         <v>2526</v>
       </c>
       <c r="D36" t="s">
-        <v>3120</v>
+        <v>3118</v>
       </c>
       <c r="E36" t="s">
         <v>2530</v>
@@ -45715,10 +45668,10 @@
         <v>159</v>
       </c>
       <c r="H36" t="s">
-        <v>3122</v>
+        <v>3120</v>
       </c>
       <c r="I36" t="s">
-        <v>3587</v>
+        <v>3585</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -45726,13 +45679,13 @@
         <v>1417</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>3408</v>
+        <v>3406</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>2538</v>
       </c>
       <c r="D37" t="s">
-        <v>2814</v>
+        <v>2813</v>
       </c>
       <c r="E37" t="s">
         <v>2540</v>
@@ -45744,10 +45697,10 @@
         <v>159</v>
       </c>
       <c r="H37" t="s">
-        <v>3312</v>
+        <v>3310</v>
       </c>
       <c r="I37" t="s">
-        <v>2837</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -45773,39 +45726,39 @@
         <v>159</v>
       </c>
       <c r="H38" s="220" t="s">
-        <v>3295</v>
+        <v>3293</v>
       </c>
       <c r="I38" s="49" t="s">
-        <v>2996</v>
+        <v>2994</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>3451</v>
+        <v>3449</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>3452</v>
+        <v>3450</v>
       </c>
       <c r="C39" s="22" t="s">
         <v>1345</v>
       </c>
       <c r="D39" s="22" t="s">
-        <v>3450</v>
+        <v>3448</v>
       </c>
       <c r="E39" t="s">
-        <v>3038</v>
+        <v>3036</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>159</v>
       </c>
       <c r="H39" t="s">
-        <v>3475</v>
+        <v>3473</v>
       </c>
       <c r="I39" t="s">
-        <v>3485</v>
+        <v>3483</v>
       </c>
     </row>
     <row r="40" spans="1:11" s="4" customFormat="1">
@@ -45819,22 +45772,22 @@
         <v>429</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>3490</v>
+        <v>3488</v>
       </c>
       <c r="E40" t="s">
-        <v>3038</v>
+        <v>3036</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>159</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>3523</v>
+        <v>3521</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>3510</v>
+        <v>3508</v>
       </c>
       <c r="K40"/>
     </row>
@@ -45849,22 +45802,22 @@
         <v>1243</v>
       </c>
       <c r="D41" t="s">
-        <v>3492</v>
+        <v>3490</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>3409</v>
+        <v>3407</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="G41" t="s">
         <v>159</v>
       </c>
       <c r="H41" t="s">
-        <v>3496</v>
+        <v>3494</v>
       </c>
       <c r="I41" t="s">
-        <v>3503</v>
+        <v>3501</v>
       </c>
     </row>
     <row r="44" spans="1:11" s="259" customFormat="1" ht="15.5">
@@ -45895,7 +45848,7 @@
         <v>244</v>
       </c>
       <c r="H45" t="s">
-        <v>3310</v>
+        <v>3308</v>
       </c>
     </row>
     <row r="49" spans="1:12" s="4" customFormat="1">
@@ -46269,13 +46222,13 @@
         <v>2429</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="C2" s="274" t="s">
         <v>254</v>
       </c>
       <c r="D2" s="106" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>1291</v>
@@ -46287,16 +46240,16 @@
         <v>62</v>
       </c>
       <c r="H2" s="298" t="s">
-        <v>3489</v>
+        <v>3487</v>
       </c>
       <c r="I2" s="442" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
       <c r="J2" s="107" t="s">
-        <v>3287</v>
+        <v>3285</v>
       </c>
       <c r="K2" s="30" t="s">
-        <v>3415</v>
+        <v>3413</v>
       </c>
       <c r="M2" s="159"/>
     </row>
@@ -46311,7 +46264,7 @@
         <v>1176</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
       <c r="E4" s="32" t="s">
         <v>2358</v>
@@ -46323,25 +46276,25 @@
         <v>270</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>3479</v>
+        <v>3477</v>
       </c>
       <c r="I4" s="217" t="s">
-        <v>2980</v>
+        <v>2978</v>
       </c>
       <c r="J4" s="139" t="s">
-        <v>3299</v>
+        <v>3297</v>
       </c>
       <c r="K4" s="139" t="s">
-        <v>3124</v>
+        <v>3122</v>
       </c>
       <c r="M4" s="39"/>
     </row>
     <row r="5" spans="1:13" s="30" customFormat="1">
       <c r="A5" s="217" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>2998</v>
+        <v>2996</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>1110</v>
@@ -46359,19 +46312,19 @@
         <v>65</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>3263</v>
+        <v>3261</v>
       </c>
       <c r="I5" s="30" t="s">
-        <v>3669</v>
+        <v>3664</v>
       </c>
       <c r="J5" s="30" t="s">
-        <v>3053</v>
+        <v>3051</v>
       </c>
       <c r="M5" s="36"/>
     </row>
     <row r="6" spans="1:13" s="30" customFormat="1">
       <c r="A6" s="107" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="B6" s="30" t="s">
         <v>2156</v>
@@ -46380,7 +46333,7 @@
         <v>2682</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>3192</v>
+        <v>3190</v>
       </c>
       <c r="E6" s="140" t="s">
         <v>2648</v>
@@ -46392,22 +46345,22 @@
         <v>65</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>3258</v>
+        <v>3256</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="J6" s="217" t="s">
-        <v>2907</v>
+        <v>2906</v>
       </c>
       <c r="K6" s="30" t="s">
-        <v>3584</v>
+        <v>3582</v>
       </c>
       <c r="M6" s="36"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="107" t="s">
-        <v>3535</v>
+        <v>3533</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>1206</v>
@@ -46416,28 +46369,28 @@
         <v>1087</v>
       </c>
       <c r="D7" t="s">
-        <v>3059</v>
+        <v>3057</v>
       </c>
       <c r="E7" s="107" t="s">
-        <v>3041</v>
+        <v>3039</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>3042</v>
+        <v>3040</v>
       </c>
       <c r="G7" s="106" t="s">
         <v>719</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>3619</v>
+        <v>3615</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>3333</v>
+        <v>3331</v>
       </c>
       <c r="J7" s="30" t="s">
-        <v>3359</v>
+        <v>3357</v>
       </c>
       <c r="K7" s="30" t="s">
-        <v>3396</v>
+        <v>3394</v>
       </c>
       <c r="M7" s="36"/>
     </row>
@@ -46452,7 +46405,7 @@
         <v>982</v>
       </c>
       <c r="D8" s="139" t="s">
-        <v>3144</v>
+        <v>3142</v>
       </c>
       <c r="E8" s="107" t="s">
         <v>1152</v>
@@ -46464,22 +46417,22 @@
         <v>65</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>3268</v>
+        <v>3266</v>
       </c>
       <c r="I8" s="32" t="s">
-        <v>3437</v>
+        <v>3435</v>
       </c>
       <c r="J8" s="107" t="s">
-        <v>3358</v>
+        <v>3356</v>
       </c>
       <c r="K8" s="139" t="s">
-        <v>3102</v>
+        <v>3100</v>
       </c>
       <c r="M8" s="36"/>
     </row>
     <row r="9" spans="1:13" s="107" customFormat="1">
       <c r="A9" s="300" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
       <c r="B9" s="32" t="s">
         <v>1656</v>
@@ -46500,22 +46453,22 @@
         <v>65</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>3375</v>
+        <v>3373</v>
       </c>
       <c r="I9" s="107" t="s">
-        <v>3283</v>
+        <v>3281</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>3670</v>
+        <v>3665</v>
       </c>
       <c r="K9" s="107" t="s">
-        <v>3402</v>
+        <v>3400</v>
       </c>
       <c r="M9" s="36"/>
     </row>
     <row r="10" spans="1:13" s="30" customFormat="1">
       <c r="A10" s="30" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
       <c r="B10" s="30">
         <v>69575383</v>
@@ -46536,16 +46489,16 @@
         <v>65</v>
       </c>
       <c r="H10" s="107" t="s">
-        <v>3642</v>
+        <v>3637</v>
       </c>
       <c r="I10" t="s">
-        <v>3067</v>
+        <v>3065</v>
       </c>
       <c r="J10" s="219" t="s">
-        <v>3184</v>
+        <v>3182</v>
       </c>
       <c r="K10" s="441" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="M10" s="34"/>
     </row>
@@ -46572,22 +46525,22 @@
         <v>605</v>
       </c>
       <c r="H11" s="139" t="s">
-        <v>3537</v>
+        <v>3535</v>
       </c>
       <c r="I11" s="30" t="s">
-        <v>3271</v>
+        <v>3269</v>
       </c>
       <c r="J11" s="107" t="s">
+        <v>3379</v>
+      </c>
+      <c r="K11" s="107" t="s">
         <v>3381</v>
-      </c>
-      <c r="K11" s="107" t="s">
-        <v>3383</v>
       </c>
       <c r="M11" s="36"/>
     </row>
     <row r="12" spans="1:13" s="106" customFormat="1">
       <c r="A12" s="106" t="s">
-        <v>3292</v>
+        <v>3290</v>
       </c>
       <c r="B12" s="106">
         <v>69581554</v>
@@ -46596,7 +46549,7 @@
         <v>72</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>3398</v>
+        <v>3396</v>
       </c>
       <c r="E12" s="106" t="s">
         <v>907</v>
@@ -46608,31 +46561,31 @@
         <v>245</v>
       </c>
       <c r="H12" s="30" t="s">
-        <v>3400</v>
+        <v>3398</v>
       </c>
       <c r="I12" s="106" t="s">
-        <v>3253</v>
+        <v>3251</v>
       </c>
       <c r="J12" s="106" t="s">
-        <v>3399</v>
+        <v>3397</v>
       </c>
       <c r="K12" s="107" t="s">
-        <v>2995</v>
+        <v>2993</v>
       </c>
       <c r="M12" s="151"/>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="140" t="s">
-        <v>3136</v>
+        <v>3134</v>
       </c>
       <c r="B13" s="107" t="s">
         <v>2708</v>
       </c>
       <c r="C13" t="s">
-        <v>3202</v>
+        <v>3200</v>
       </c>
       <c r="D13" t="s">
-        <v>3659</v>
+        <v>3654</v>
       </c>
       <c r="E13" t="s">
         <v>2370</v>
@@ -46644,14 +46597,14 @@
         <v>270</v>
       </c>
       <c r="H13" s="30" t="s">
-        <v>3661</v>
+        <v>3656</v>
       </c>
       <c r="I13" s="145"/>
       <c r="J13" s="107" t="s">
-        <v>3675</v>
+        <v>3670</v>
       </c>
       <c r="K13" t="s">
-        <v>3660</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="14" spans="1:13" s="107" customFormat="1">
@@ -46677,13 +46630,13 @@
         <v>65</v>
       </c>
       <c r="H14" s="107" t="s">
-        <v>3072</v>
+        <v>3070</v>
       </c>
       <c r="I14" s="409" t="s">
         <v>2238</v>
       </c>
       <c r="J14" s="32" t="s">
-        <v>3581</v>
+        <v>3579</v>
       </c>
       <c r="M14" s="36"/>
     </row>
@@ -46710,16 +46663,16 @@
         <v>66</v>
       </c>
       <c r="H15" t="s">
-        <v>3217</v>
+        <v>3215</v>
       </c>
       <c r="I15" t="s">
-        <v>3221</v>
+        <v>3219</v>
       </c>
       <c r="J15" t="s">
-        <v>3655</v>
+        <v>3650</v>
       </c>
       <c r="K15" s="107" t="s">
-        <v>3433</v>
+        <v>3431</v>
       </c>
       <c r="M15" s="36"/>
     </row>
@@ -46750,7 +46703,7 @@
     </row>
     <row r="17" spans="1:13" s="30" customFormat="1">
       <c r="A17" s="30" t="s">
-        <v>3469</v>
+        <v>3467</v>
       </c>
       <c r="B17" s="30" t="s">
         <v>1827</v>
@@ -46759,7 +46712,7 @@
         <v>1611</v>
       </c>
       <c r="D17" s="249" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="E17" s="140" t="s">
         <v>1612</v>
@@ -46771,16 +46724,16 @@
         <v>66</v>
       </c>
       <c r="H17" t="s">
-        <v>3273</v>
+        <v>3271</v>
       </c>
       <c r="I17" s="30" t="s">
-        <v>3508</v>
+        <v>3506</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>3323</v>
+        <v>3321</v>
       </c>
       <c r="K17" s="220" t="s">
-        <v>3265</v>
+        <v>3263</v>
       </c>
       <c r="M17" s="34"/>
     </row>
@@ -46807,22 +46760,22 @@
         <v>66</v>
       </c>
       <c r="H18" s="30" t="s">
-        <v>3583</v>
+        <v>3581</v>
       </c>
       <c r="I18" t="s">
-        <v>3589</v>
+        <v>3587</v>
       </c>
       <c r="J18" t="s">
-        <v>3654</v>
+        <v>3649</v>
       </c>
       <c r="K18" t="s">
-        <v>3387</v>
+        <v>3385</v>
       </c>
       <c r="M18" s="36"/>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="4" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>1515</v>
@@ -46831,7 +46784,7 @@
         <v>1673</v>
       </c>
       <c r="D19" s="134" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="E19" t="s">
         <v>1676</v>
@@ -46843,19 +46796,19 @@
         <v>66</v>
       </c>
       <c r="H19" t="s">
-        <v>3546</v>
+        <v>3544</v>
       </c>
       <c r="I19" t="s">
-        <v>3482</v>
+        <v>3480</v>
       </c>
       <c r="J19" s="220" t="s">
-        <v>3586</v>
+        <v>3584</v>
       </c>
       <c r="M19" s="36"/>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="300" t="s">
-        <v>3585</v>
+        <v>3583</v>
       </c>
       <c r="B20" t="s">
         <v>2441</v>
@@ -46864,7 +46817,7 @@
         <v>2436</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>2875</v>
+        <v>2874</v>
       </c>
       <c r="E20" s="107" t="s">
         <v>2372</v>
@@ -46876,31 +46829,31 @@
         <v>65</v>
       </c>
       <c r="H20" s="432" t="s">
-        <v>3191</v>
+        <v>3189</v>
       </c>
       <c r="I20" t="s">
-        <v>3476</v>
+        <v>3474</v>
       </c>
       <c r="J20" t="s">
-        <v>3509</v>
+        <v>3507</v>
       </c>
       <c r="K20" t="s">
-        <v>3425</v>
+        <v>3423</v>
       </c>
       <c r="M20" s="36"/>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>3077</v>
+        <v>3075</v>
       </c>
       <c r="B21" t="s">
-        <v>3082</v>
+        <v>3080</v>
       </c>
       <c r="C21" s="22" t="s">
         <v>1125</v>
       </c>
       <c r="D21" t="s">
-        <v>3081</v>
+        <v>3079</v>
       </c>
       <c r="E21" s="140" t="s">
         <v>1573</v>
@@ -46912,19 +46865,19 @@
         <v>65</v>
       </c>
       <c r="H21" t="s">
-        <v>3086</v>
+        <v>3084</v>
       </c>
       <c r="I21" t="s">
-        <v>3089</v>
+        <v>3087</v>
       </c>
       <c r="J21" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="M21" s="36"/>
     </row>
     <row r="22" spans="1:13" s="30" customFormat="1">
       <c r="A22" s="30" t="s">
-        <v>3093</v>
+        <v>3091</v>
       </c>
       <c r="B22" s="30" t="s">
         <v>2087</v>
@@ -46933,104 +46886,104 @@
         <v>2651</v>
       </c>
       <c r="D22" s="107" t="s">
-        <v>3130</v>
+        <v>3128</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>3104</v>
+        <v>3102</v>
       </c>
       <c r="F22" s="30" t="s">
-        <v>3105</v>
+        <v>3103</v>
       </c>
       <c r="G22" s="32" t="s">
         <v>65</v>
       </c>
       <c r="H22" s="30" t="s">
+        <v>3107</v>
+      </c>
+      <c r="I22" s="30" t="s">
         <v>3109</v>
       </c>
-      <c r="I22" s="30" t="s">
-        <v>3111</v>
-      </c>
       <c r="J22" s="30" t="s">
-        <v>3112</v>
+        <v>3110</v>
       </c>
       <c r="M22" s="36"/>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>3093</v>
+        <v>3091</v>
       </c>
       <c r="B23" t="s">
-        <v>3125</v>
+        <v>3123</v>
       </c>
       <c r="C23" s="22" t="s">
         <v>1884</v>
       </c>
       <c r="D23" t="s">
-        <v>3177</v>
+        <v>3175</v>
       </c>
       <c r="E23" s="30" t="s">
-        <v>3104</v>
+        <v>3102</v>
       </c>
       <c r="F23" s="30" t="s">
-        <v>3105</v>
+        <v>3103</v>
       </c>
       <c r="G23" t="s">
         <v>66</v>
       </c>
       <c r="H23" t="s">
-        <v>3213</v>
+        <v>3211</v>
       </c>
       <c r="I23" t="s">
-        <v>3212</v>
+        <v>3210</v>
       </c>
       <c r="J23" t="s">
-        <v>3205</v>
+        <v>3203</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="30" t="s">
-        <v>3488</v>
+        <v>3486</v>
       </c>
       <c r="B24" t="s">
-        <v>3613</v>
+        <v>3609</v>
       </c>
       <c r="C24" s="22" t="s">
         <v>1898</v>
       </c>
       <c r="D24" t="s">
+        <v>3346</v>
+      </c>
+      <c r="E24" s="107" t="s">
         <v>3348</v>
       </c>
-      <c r="E24" s="107" t="s">
-        <v>3350</v>
-      </c>
       <c r="F24" s="30" t="s">
-        <v>3340</v>
+        <v>3338</v>
       </c>
       <c r="G24" s="32" t="s">
         <v>270</v>
       </c>
       <c r="H24" t="s">
-        <v>3595</v>
+        <v>3593</v>
       </c>
       <c r="I24" t="s">
-        <v>3591</v>
+        <v>3589</v>
       </c>
       <c r="J24" t="s">
-        <v>3620</v>
+        <v>3616</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" t="s">
-        <v>3292</v>
+        <v>3290</v>
       </c>
       <c r="B25" t="s">
-        <v>2772</v>
+        <v>2771</v>
       </c>
       <c r="C25" s="22" t="s">
         <v>1104</v>
       </c>
       <c r="D25" t="s">
-        <v>3505</v>
+        <v>3503</v>
       </c>
       <c r="E25" s="107" t="s">
         <v>1121</v>
@@ -47042,13 +46995,13 @@
         <v>65</v>
       </c>
       <c r="H25" t="s">
-        <v>3494</v>
+        <v>3492</v>
       </c>
       <c r="I25" t="s">
-        <v>3501</v>
+        <v>3499</v>
       </c>
       <c r="J25" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="M25" s="36"/>
     </row>
@@ -47057,13 +47010,13 @@
         <v>2662</v>
       </c>
       <c r="B26" s="107" t="s">
-        <v>3514</v>
+        <v>3512</v>
       </c>
       <c r="C26" s="22" t="s">
         <v>918</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>3513</v>
+        <v>3511</v>
       </c>
       <c r="E26" s="140" t="s">
         <v>2683</v>
@@ -47075,13 +47028,13 @@
         <v>65</v>
       </c>
       <c r="H26" s="30" t="s">
-        <v>3515</v>
+        <v>3513</v>
       </c>
       <c r="I26" s="30" t="s">
-        <v>3562</v>
+        <v>3560</v>
       </c>
       <c r="J26" s="107" t="s">
-        <v>3598</v>
+        <v>3596</v>
       </c>
       <c r="K26"/>
       <c r="M26" s="36"/>
@@ -47120,7 +47073,7 @@
     </row>
     <row r="31" spans="1:13" s="30" customFormat="1">
       <c r="A31" s="107" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
       <c r="B31" s="107">
         <v>64403333</v>
@@ -47144,7 +47097,7 @@
     </row>
     <row r="32" spans="1:13" s="107" customFormat="1">
       <c r="A32" s="32" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
       <c r="B32" s="32">
         <v>64403333</v>
@@ -47168,7 +47121,7 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" t="s">
-        <v>3266</v>
+        <v>3264</v>
       </c>
       <c r="B33">
         <v>60389752</v>
@@ -47191,7 +47144,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" t="s">
-        <v>3178</v>
+        <v>3176</v>
       </c>
       <c r="B34">
         <v>60389752</v>
@@ -47200,13 +47153,13 @@
         <v>2146</v>
       </c>
       <c r="D34" s="32" t="s">
-        <v>3000</v>
+        <v>2998</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>3104</v>
+        <v>3102</v>
       </c>
       <c r="F34" s="30" t="s">
-        <v>3105</v>
+        <v>3103</v>
       </c>
       <c r="G34" t="s">
         <v>3</v>
@@ -47215,7 +47168,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>3077</v>
+        <v>3075</v>
       </c>
       <c r="B35">
         <v>60389752</v>
@@ -47239,7 +47192,7 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="B36">
         <v>60389752</v>
@@ -47272,13 +47225,13 @@
         <v>1208</v>
       </c>
       <c r="D37" t="s">
-        <v>3347</v>
+        <v>3345</v>
       </c>
       <c r="E37" s="107" t="s">
-        <v>3350</v>
+        <v>3348</v>
       </c>
       <c r="F37" s="30" t="s">
-        <v>3340</v>
+        <v>3338</v>
       </c>
       <c r="G37" s="106" t="s">
         <v>719</v>
@@ -47288,7 +47241,7 @@
     </row>
     <row r="38" spans="1:13" s="30" customFormat="1">
       <c r="A38" s="30" t="s">
-        <v>3178</v>
+        <v>3176</v>
       </c>
       <c r="B38" s="30">
         <v>60389752</v>
@@ -47325,10 +47278,10 @@
         <v>2120</v>
       </c>
       <c r="E39" t="s">
-        <v>3104</v>
+        <v>3102</v>
       </c>
       <c r="F39" t="s">
-        <v>3105</v>
+        <v>3103</v>
       </c>
       <c r="G39" t="s">
         <v>3</v>
@@ -47392,7 +47345,7 @@
         <v>2461</v>
       </c>
       <c r="E45" s="281" t="s">
-        <v>3006</v>
+        <v>3004</v>
       </c>
       <c r="F45" s="30" t="s">
         <v>2462</v>
@@ -47401,10 +47354,10 @@
         <v>369</v>
       </c>
       <c r="H45" s="49" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
       <c r="I45" s="30" t="s">
-        <v>3074</v>
+        <v>3072</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -47456,16 +47409,16 @@
     </row>
     <row r="68" spans="1:38">
       <c r="C68" s="138" t="s">
-        <v>3313</v>
+        <v>3311</v>
       </c>
       <c r="D68" t="s">
-        <v>3512</v>
+        <v>3510</v>
       </c>
       <c r="E68" s="107" t="s">
-        <v>3350</v>
+        <v>3348</v>
       </c>
       <c r="F68" s="30" t="s">
-        <v>3340</v>
+        <v>3338</v>
       </c>
       <c r="G68" s="106" t="s">
         <v>719</v>
@@ -47479,13 +47432,13 @@
         <v>2147</v>
       </c>
       <c r="D70" t="s">
-        <v>3511</v>
+        <v>3509</v>
       </c>
       <c r="E70" s="107" t="s">
-        <v>3350</v>
+        <v>3348</v>
       </c>
       <c r="F70" s="30" t="s">
-        <v>3340</v>
+        <v>3338</v>
       </c>
       <c r="M70" s="36"/>
     </row>
@@ -47545,7 +47498,7 @@
         <v>916</v>
       </c>
       <c r="D79" s="30" t="s">
-        <v>3570</v>
+        <v>3568</v>
       </c>
       <c r="E79" s="107" t="s">
         <v>1088</v>
@@ -47570,7 +47523,7 @@
         <v>1429</v>
       </c>
       <c r="D81" t="s">
-        <v>3571</v>
+        <v>3569</v>
       </c>
       <c r="M81" s="36"/>
     </row>
@@ -47596,7 +47549,7 @@
         <v>915</v>
       </c>
       <c r="D83" s="30" t="s">
-        <v>3572</v>
+        <v>3570</v>
       </c>
       <c r="E83" s="30" t="s">
         <v>1095</v>
@@ -47616,7 +47569,7 @@
         <v>997</v>
       </c>
       <c r="D84" s="139" t="s">
-        <v>3573</v>
+        <v>3571</v>
       </c>
       <c r="E84" s="107" t="s">
         <v>1073</v>
@@ -47636,7 +47589,7 @@
         <v>936</v>
       </c>
       <c r="D85" s="107" t="s">
-        <v>3574</v>
+        <v>3572</v>
       </c>
       <c r="E85" s="139" t="s">
         <v>998</v>
@@ -47655,7 +47608,7 @@
         <v>946</v>
       </c>
       <c r="D86" s="30" t="s">
-        <v>3575</v>
+        <v>3573</v>
       </c>
       <c r="E86" s="107" t="s">
         <v>1004</v>
@@ -47677,7 +47630,7 @@
         <v>1006</v>
       </c>
       <c r="D87" t="s">
-        <v>3576</v>
+        <v>3574</v>
       </c>
       <c r="E87" s="107" t="s">
         <v>1253</v>
@@ -47695,7 +47648,7 @@
         <v>1043</v>
       </c>
       <c r="D88" s="30" t="s">
-        <v>3577</v>
+        <v>3575</v>
       </c>
       <c r="E88" s="107" t="s">
         <v>1044</v>
@@ -47715,7 +47668,7 @@
         <v>1054</v>
       </c>
       <c r="D89" s="30" t="s">
-        <v>3578</v>
+        <v>3576</v>
       </c>
       <c r="E89" s="107" t="s">
         <v>1055</v>
@@ -47739,7 +47692,7 @@
         <v>1126</v>
       </c>
       <c r="D91" t="s">
-        <v>3579</v>
+        <v>3577</v>
       </c>
       <c r="E91" s="140" t="s">
         <v>1131</v>
@@ -47758,7 +47711,7 @@
         <v>1127</v>
       </c>
       <c r="D92" t="s">
-        <v>3580</v>
+        <v>3578</v>
       </c>
       <c r="E92" s="140" t="s">
         <v>1131</v>
@@ -47780,7 +47733,7 @@
         <v>1128</v>
       </c>
       <c r="D93" t="s">
-        <v>3100</v>
+        <v>3098</v>
       </c>
       <c r="E93" s="140" t="s">
         <v>1130</v>
@@ -47804,7 +47757,7 @@
         <v>1384</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>3101</v>
+        <v>3099</v>
       </c>
       <c r="E94" s="264" t="s">
         <v>1491</v>
@@ -47858,7 +47811,7 @@
         <v>358</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>3202</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="105" spans="2:5">
@@ -48210,7 +48163,7 @@
         <v>6.83</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>2795</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -48219,7 +48172,7 @@
       </c>
       <c r="B24" s="87"/>
       <c r="F24" s="2" t="s">
-        <v>2879</v>
+        <v>2878</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -48295,27 +48248,27 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="87" t="s">
-        <v>3157</v>
+        <v>3155</v>
       </c>
       <c r="C40" t="s">
-        <v>3160</v>
+        <v>3158</v>
       </c>
       <c r="F40" s="45"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="89" t="s">
-        <v>3158</v>
+        <v>3156</v>
       </c>
       <c r="C41" t="s">
-        <v>3161</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="42" spans="2:6" ht="15" thickBot="1">
       <c r="B42" s="86" t="s">
-        <v>3159</v>
+        <v>3157</v>
       </c>
       <c r="C42" t="s">
-        <v>3162</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="43" spans="2:6">
@@ -48466,10 +48419,10 @@
     </row>
     <row r="6" spans="1:12" s="246" customFormat="1" ht="16.5" customHeight="1">
       <c r="A6" s="296" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
       <c r="B6" s="246" t="s">
-        <v>2817</v>
+        <v>2816</v>
       </c>
       <c r="C6" s="245" t="s">
         <v>1283</v>
@@ -48478,22 +48431,22 @@
         <v>2012</v>
       </c>
       <c r="E6" s="246" t="s">
-        <v>3032</v>
+        <v>3030</v>
       </c>
       <c r="F6" s="246" t="s">
-        <v>3033</v>
+        <v>3031</v>
       </c>
       <c r="G6" s="246" t="s">
         <v>357</v>
       </c>
       <c r="H6" s="246" t="s">
-        <v>3671</v>
+        <v>3666</v>
       </c>
       <c r="I6" s="243" t="s">
-        <v>3272</v>
+        <v>3270</v>
       </c>
       <c r="J6" s="293" t="s">
-        <v>3371</v>
+        <v>3369</v>
       </c>
       <c r="K6" s="246" t="s">
         <v>475</v>
@@ -48501,7 +48454,7 @@
     </row>
     <row r="7" spans="1:12" s="106" customFormat="1">
       <c r="A7" s="30" t="s">
-        <v>3451</v>
+        <v>3449</v>
       </c>
       <c r="B7" t="s">
         <v>1827</v>
@@ -48516,19 +48469,19 @@
         <v>1035</v>
       </c>
       <c r="F7" s="106" t="s">
-        <v>3034</v>
+        <v>3032</v>
       </c>
       <c r="G7" s="106" t="s">
         <v>689</v>
       </c>
       <c r="H7" s="219" t="s">
-        <v>3030</v>
+        <v>3028</v>
       </c>
       <c r="I7" s="219" t="s">
-        <v>3448</v>
+        <v>3446</v>
       </c>
       <c r="J7" s="219" t="s">
-        <v>3226</v>
+        <v>3224</v>
       </c>
       <c r="K7" s="106" t="s">
         <v>708</v>
@@ -48548,29 +48501,29 @@
         <v>868</v>
       </c>
       <c r="E8" s="263" t="s">
-        <v>3621</v>
+        <v>3617</v>
       </c>
       <c r="F8" s="263" t="s">
-        <v>3622</v>
+        <v>3618</v>
       </c>
       <c r="G8" s="263" t="s">
         <v>250</v>
       </c>
       <c r="H8" s="263" t="s">
-        <v>3363</v>
+        <v>3361</v>
       </c>
       <c r="I8" s="263" t="s">
-        <v>3171</v>
+        <v>3169</v>
       </c>
       <c r="J8" s="263" t="s">
-        <v>3237</v>
+        <v>3235</v>
       </c>
       <c r="K8" s="257"/>
       <c r="L8" s="257"/>
     </row>
     <row r="9" spans="1:12" s="257" customFormat="1">
       <c r="A9" s="424" t="s">
-        <v>3346</v>
+        <v>3344</v>
       </c>
       <c r="B9" s="262">
         <v>64403333</v>
@@ -48585,7 +48538,7 @@
         <v>2638</v>
       </c>
       <c r="F9" s="261" t="s">
-        <v>3126</v>
+        <v>3124</v>
       </c>
       <c r="G9" s="261" t="s">
         <v>945</v>
@@ -48596,7 +48549,7 @@
     </row>
     <row r="10" spans="1:12" s="244" customFormat="1">
       <c r="A10" s="296" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
       <c r="B10" s="241" t="s">
         <v>2551</v>
@@ -48617,13 +48570,13 @@
         <v>689</v>
       </c>
       <c r="H10" s="262" t="s">
-        <v>3403</v>
+        <v>3401</v>
       </c>
       <c r="I10" s="262" t="s">
-        <v>3421</v>
+        <v>3419</v>
       </c>
       <c r="J10" s="262" t="s">
-        <v>3302</v>
+        <v>3300</v>
       </c>
       <c r="K10" s="244" t="s">
         <v>1200</v>
@@ -48631,10 +48584,10 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="260" t="s">
-        <v>3539</v>
+        <v>3537</v>
       </c>
       <c r="B11" s="260" t="s">
-        <v>3026</v>
+        <v>3024</v>
       </c>
       <c r="C11" s="194" t="s">
         <v>491</v>
@@ -48646,19 +48599,19 @@
         <v>2638</v>
       </c>
       <c r="F11" s="216" t="s">
-        <v>3435</v>
+        <v>3433</v>
       </c>
       <c r="G11" s="216" t="s">
         <v>689</v>
       </c>
       <c r="H11" s="215" t="s">
-        <v>3209</v>
+        <v>3207</v>
       </c>
       <c r="I11" s="423" t="s">
-        <v>3185</v>
+        <v>3183</v>
       </c>
       <c r="J11" s="267" t="s">
-        <v>3317</v>
+        <v>3315</v>
       </c>
       <c r="K11" s="183" t="s">
         <v>1201</v>
@@ -48692,10 +48645,10 @@
     </row>
     <row r="13" spans="1:12" s="223" customFormat="1">
       <c r="A13" s="223" t="s">
-        <v>3077</v>
+        <v>3075</v>
       </c>
       <c r="B13" s="223" t="s">
-        <v>3099</v>
+        <v>3097</v>
       </c>
       <c r="C13" s="422" t="s">
         <v>335</v>
@@ -48707,19 +48660,19 @@
         <v>2638</v>
       </c>
       <c r="F13" s="223" t="s">
-        <v>3638</v>
+        <v>3634</v>
       </c>
       <c r="G13" s="223" t="s">
         <v>689</v>
       </c>
       <c r="H13" s="223" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="I13" s="223" t="s">
-        <v>3679</v>
+        <v>3674</v>
       </c>
       <c r="J13" s="455" t="s">
-        <v>3648</v>
+        <v>3643</v>
       </c>
       <c r="K13" s="223" t="s">
         <v>1312</v>
@@ -48742,19 +48695,19 @@
         <v>2638</v>
       </c>
       <c r="F14" s="216" t="s">
-        <v>3638</v>
+        <v>3634</v>
       </c>
       <c r="G14" s="216" t="s">
         <v>689</v>
       </c>
       <c r="H14" s="270" t="s">
-        <v>3227</v>
+        <v>3225</v>
       </c>
       <c r="I14" s="215" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="J14" s="260" t="s">
-        <v>3538</v>
+        <v>3536</v>
       </c>
       <c r="K14" s="183" t="s">
         <v>1202</v>
@@ -48762,16 +48715,16 @@
     </row>
     <row r="15" spans="1:12" s="257" customFormat="1">
       <c r="A15" s="262" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="B15" s="262" t="s">
-        <v>3461</v>
+        <v>3459</v>
       </c>
       <c r="C15" s="268" t="s">
         <v>1300</v>
       </c>
       <c r="D15" s="257" t="s">
-        <v>2850</v>
+        <v>2849</v>
       </c>
       <c r="E15" s="257" t="s">
         <v>2690</v>
@@ -48783,13 +48736,13 @@
         <v>689</v>
       </c>
       <c r="H15" s="262" t="s">
-        <v>3647</v>
+        <v>3642</v>
       </c>
       <c r="I15" s="269" t="s">
-        <v>3341</v>
+        <v>3339</v>
       </c>
       <c r="J15" s="217" t="s">
-        <v>2975</v>
+        <v>2973</v>
       </c>
       <c r="K15" s="257" t="s">
         <v>1425</v>
@@ -48797,7 +48750,7 @@
     </row>
     <row r="16" spans="1:12" s="262" customFormat="1">
       <c r="A16" s="269" t="s">
-        <v>3539</v>
+        <v>3537</v>
       </c>
       <c r="B16" s="269">
         <v>64403333</v>
@@ -48847,7 +48800,7 @@
     </row>
     <row r="18" spans="1:11" s="257" customFormat="1">
       <c r="A18" s="269" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="B18" s="257" t="s">
         <v>2299</v>
@@ -48856,7 +48809,7 @@
         <v>830</v>
       </c>
       <c r="D18" s="262" t="s">
-        <v>3239</v>
+        <v>3237</v>
       </c>
       <c r="E18" s="262" t="s">
         <v>1771</v>
@@ -48868,13 +48821,13 @@
         <v>689</v>
       </c>
       <c r="H18" s="257" t="s">
-        <v>3305</v>
+        <v>3303</v>
       </c>
       <c r="I18" s="296" t="s">
-        <v>3480</v>
+        <v>3478</v>
       </c>
       <c r="J18" s="257" t="s">
-        <v>3288</v>
+        <v>3286</v>
       </c>
       <c r="K18" s="262" t="s">
         <v>1748</v>
@@ -48882,7 +48835,7 @@
     </row>
     <row r="19" spans="1:11" s="257" customFormat="1">
       <c r="A19" s="257" t="s">
-        <v>3182</v>
+        <v>3180</v>
       </c>
       <c r="B19" s="257" t="s">
         <v>2344</v>
@@ -48903,11 +48856,11 @@
         <v>689</v>
       </c>
       <c r="H19" s="257" t="s">
-        <v>3554</v>
+        <v>3552</v>
       </c>
       <c r="I19" s="97"/>
       <c r="J19" s="257" t="s">
-        <v>3493</v>
+        <v>3491</v>
       </c>
       <c r="K19" s="257" t="s">
         <v>1793</v>
@@ -48915,7 +48868,7 @@
     </row>
     <row r="20" spans="1:11" s="262" customFormat="1">
       <c r="A20" s="296" t="s">
-        <v>3270</v>
+        <v>3268</v>
       </c>
       <c r="B20" s="302">
         <v>63609244</v>
@@ -48939,10 +48892,10 @@
         <v>2697</v>
       </c>
       <c r="I20" s="262" t="s">
-        <v>3269</v>
+        <v>3267</v>
       </c>
       <c r="J20" s="262" t="s">
-        <v>3119</v>
+        <v>3117</v>
       </c>
       <c r="K20" s="257" t="s">
         <v>1795</v>
@@ -48985,10 +48938,10 @@
         <v>637</v>
       </c>
       <c r="D22" s="253" t="s">
-        <v>3240</v>
+        <v>3238</v>
       </c>
       <c r="E22" s="269" t="s">
-        <v>3164</v>
+        <v>3162</v>
       </c>
       <c r="F22" s="269" t="s">
         <v>1694</v>
@@ -48997,18 +48950,18 @@
         <v>250</v>
       </c>
       <c r="H22" s="257" t="s">
-        <v>3251</v>
+        <v>3249</v>
       </c>
       <c r="I22" s="217" t="s">
-        <v>3010</v>
+        <v>3008</v>
       </c>
       <c r="J22" s="217" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="30" t="s">
-        <v>3346</v>
+        <v>3344</v>
       </c>
       <c r="B23">
         <v>62560788</v>
@@ -49029,13 +48982,13 @@
         <v>689</v>
       </c>
       <c r="H23" s="30" t="s">
-        <v>3449</v>
+        <v>3447</v>
       </c>
       <c r="I23" s="30" t="s">
-        <v>3447</v>
+        <v>3445</v>
       </c>
       <c r="J23" s="30" t="s">
-        <v>3436</v>
+        <v>3434</v>
       </c>
       <c r="K23" t="s">
         <v>1203</v>
@@ -49043,34 +48996,34 @@
     </row>
     <row r="24" spans="1:11" s="30" customFormat="1">
       <c r="A24" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="B24" t="s">
-        <v>3468</v>
+        <v>3466</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>499</v>
       </c>
       <c r="D24" s="30" t="s">
-        <v>3467</v>
+        <v>3465</v>
       </c>
       <c r="E24" s="173" t="s">
         <v>2554</v>
       </c>
       <c r="F24" s="173" t="s">
-        <v>3638</v>
+        <v>3634</v>
       </c>
       <c r="G24" s="30" t="s">
         <v>945</v>
       </c>
       <c r="H24" s="30" t="s">
-        <v>3484</v>
+        <v>3482</v>
       </c>
       <c r="I24" s="30" t="s">
-        <v>3478</v>
+        <v>3476</v>
       </c>
       <c r="J24" s="30" t="s">
-        <v>3476</v>
+        <v>3474</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="30" customFormat="1">
@@ -49078,31 +49031,31 @@
         <v>2662</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>3498</v>
+        <v>3496</v>
       </c>
       <c r="C25" s="30" t="s">
         <v>449</v>
       </c>
       <c r="D25" s="30" t="s">
-        <v>3497</v>
+        <v>3495</v>
       </c>
       <c r="E25" s="173" t="s">
         <v>2554</v>
       </c>
       <c r="F25" s="173" t="s">
-        <v>3638</v>
+        <v>3634</v>
       </c>
       <c r="G25" s="106" t="s">
         <v>262</v>
       </c>
       <c r="H25" s="30" t="s">
-        <v>3528</v>
+        <v>3526</v>
       </c>
       <c r="I25" s="30" t="s">
-        <v>3520</v>
+        <v>3518</v>
       </c>
       <c r="J25" s="30" t="s">
-        <v>3507</v>
+        <v>3505</v>
       </c>
       <c r="K25" s="30" t="s">
         <v>1438</v>
@@ -49113,28 +49066,28 @@
         <v>1852</v>
       </c>
       <c r="B26" t="s">
-        <v>3533</v>
+        <v>3531</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>555</v>
       </c>
       <c r="D26" t="s">
-        <v>3466</v>
+        <v>3464</v>
       </c>
       <c r="E26" s="173" t="s">
         <v>2554</v>
       </c>
       <c r="F26" s="173" t="s">
-        <v>3638</v>
+        <v>3634</v>
       </c>
       <c r="G26" s="30" t="s">
         <v>945</v>
       </c>
       <c r="H26" s="55" t="s">
-        <v>3674</v>
+        <v>3669</v>
       </c>
       <c r="I26" t="s">
-        <v>3557</v>
+        <v>3555</v>
       </c>
       <c r="J26" s="97"/>
       <c r="K26" t="s">
@@ -49155,10 +49108,10 @@
         <v>1284</v>
       </c>
       <c r="E30" s="106" t="s">
-        <v>3465</v>
+        <v>3463</v>
       </c>
       <c r="F30" s="106" t="s">
-        <v>3464</v>
+        <v>3462</v>
       </c>
       <c r="G30" s="173" t="s">
         <v>945</v>
@@ -49262,7 +49215,7 @@
         <v>839</v>
       </c>
       <c r="D45" s="262" t="s">
-        <v>2873</v>
+        <v>2872</v>
       </c>
       <c r="E45" s="257" t="s">
         <v>1771</v>
@@ -49453,7 +49406,7 @@
         <v>578</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>3457</v>
+        <v>3455</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>1169</v>
@@ -49462,16 +49415,16 @@
         <v>570</v>
       </c>
       <c r="G2" t="s">
-        <v>3458</v>
+        <v>3456</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>3057</v>
+        <v>3055</v>
       </c>
       <c r="I2" t="s">
-        <v>3203</v>
+        <v>3201</v>
       </c>
       <c r="J2" t="s">
-        <v>3293</v>
+        <v>3291</v>
       </c>
       <c r="L2" s="36" t="s">
         <v>1170</v>
@@ -49488,7 +49441,7 @@
         <v>225</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>3434</v>
+        <v>3432</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>1187</v>
@@ -49497,13 +49450,13 @@
         <v>298</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>3058</v>
+        <v>3056</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>706</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>3440</v>
+        <v>3438</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>2349</v>
@@ -49514,7 +49467,7 @@
     </row>
     <row r="4" spans="1:12" s="4" customFormat="1">
       <c r="A4" s="4" t="s">
-        <v>3592</v>
+        <v>3590</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>1775</v>
@@ -49523,25 +49476,25 @@
         <v>313</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>2835</v>
+        <v>2834</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>2870</v>
+        <v>2869</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>323</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>3233</v>
+        <v>3231</v>
       </c>
       <c r="H4" s="49" t="s">
-        <v>2900</v>
+        <v>2899</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>3304</v>
+        <v>3302</v>
       </c>
       <c r="J4" t="s">
-        <v>2836</v>
+        <v>2835</v>
       </c>
       <c r="L4" s="127" t="s">
         <v>322</v>
@@ -49558,7 +49511,7 @@
         <v>118</v>
       </c>
       <c r="D5" s="57" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>1466</v>
@@ -49567,13 +49520,13 @@
         <v>424</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>3442</v>
+        <v>3440</v>
       </c>
       <c r="H5" t="s">
-        <v>3617</v>
+        <v>3613</v>
       </c>
       <c r="I5" s="75" t="s">
-        <v>2753</v>
+        <v>2752</v>
       </c>
       <c r="J5" s="220" t="s">
         <v>2547</v>
@@ -49582,7 +49535,7 @@
     </row>
     <row r="6" spans="1:12" s="4" customFormat="1">
       <c r="A6" s="4" t="s">
-        <v>3282</v>
+        <v>3280</v>
       </c>
       <c r="B6" s="4">
         <v>65436260</v>
@@ -49591,25 +49544,25 @@
         <v>327</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>2807</v>
+        <v>2806</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>2806</v>
+        <v>2805</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>166</v>
       </c>
       <c r="G6" t="s">
-        <v>3646</v>
+        <v>3641</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>3334</v>
+        <v>3332</v>
       </c>
       <c r="I6" t="s">
-        <v>3060</v>
+        <v>3058</v>
       </c>
       <c r="J6" s="49" t="s">
-        <v>2808</v>
+        <v>2807</v>
       </c>
       <c r="L6" s="67" t="s">
         <v>423</v>
@@ -49617,7 +49570,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="4" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
       <c r="B7" s="4">
         <v>69561522</v>
@@ -49626,25 +49579,25 @@
         <v>434</v>
       </c>
       <c r="D7" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="E7" t="s">
-        <v>2971</v>
+        <v>2969</v>
       </c>
       <c r="F7" t="s">
         <v>151</v>
       </c>
       <c r="G7" t="s">
-        <v>3289</v>
+        <v>3287</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>3186</v>
+        <v>3184</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
       <c r="J7" s="49" t="s">
-        <v>2970</v>
+        <v>2968</v>
       </c>
       <c r="L7" s="83" t="s">
         <v>435</v>
@@ -49652,10 +49605,10 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="4" t="s">
-        <v>3270</v>
+        <v>3268</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>658</v>
@@ -49673,10 +49626,10 @@
         <v>2580</v>
       </c>
       <c r="H8" t="s">
-        <v>3588</v>
+        <v>3586</v>
       </c>
       <c r="I8" t="s">
-        <v>3433</v>
+        <v>3431</v>
       </c>
       <c r="J8" s="49" t="s">
         <v>2704</v>
@@ -49703,16 +49656,16 @@
         <v>151</v>
       </c>
       <c r="G9" t="s">
-        <v>3537</v>
+        <v>3535</v>
       </c>
       <c r="H9" s="220" t="s">
-        <v>3522</v>
+        <v>3520</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>3297</v>
+        <v>3295</v>
       </c>
       <c r="J9" s="447" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -49726,7 +49679,7 @@
         <v>2173</v>
       </c>
       <c r="D10" t="s">
-        <v>2876</v>
+        <v>2875</v>
       </c>
       <c r="E10" t="s">
         <v>2144</v>
@@ -49735,16 +49688,16 @@
         <v>1801</v>
       </c>
       <c r="G10" t="s">
-        <v>3036</v>
+        <v>3034</v>
       </c>
       <c r="H10" s="49" t="s">
-        <v>3254</v>
+        <v>3252</v>
       </c>
       <c r="I10" t="s">
-        <v>3062</v>
+        <v>3060</v>
       </c>
       <c r="J10" s="49" t="s">
-        <v>2757</v>
+        <v>2756</v>
       </c>
       <c r="L10" s="36" t="s">
         <v>2174</v>
@@ -49772,7 +49725,7 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>3346</v>
+        <v>3344</v>
       </c>
       <c r="B12">
         <v>64403333</v>
@@ -49784,7 +49737,7 @@
         <v>1464</v>
       </c>
       <c r="E12" t="s">
-        <v>2955</v>
+        <v>2954</v>
       </c>
       <c r="F12" t="s">
         <v>614</v>
@@ -49792,7 +49745,7 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B13">
         <v>64403333</v>
@@ -49815,16 +49768,16 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>3005</v>
+        <v>3003</v>
       </c>
       <c r="B14" t="s">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>281</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>3011</v>
+        <v>3009</v>
       </c>
       <c r="E14" t="s">
         <v>2114</v>
@@ -49833,16 +49786,16 @@
         <v>1801</v>
       </c>
       <c r="G14" t="s">
-        <v>3395</v>
+        <v>3393</v>
       </c>
       <c r="H14" t="s">
-        <v>3311</v>
+        <v>3309</v>
       </c>
       <c r="I14" t="s">
-        <v>3179</v>
+        <v>3177</v>
       </c>
       <c r="J14" t="s">
-        <v>3098</v>
+        <v>3096</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -49856,7 +49809,7 @@
         <v>707</v>
       </c>
       <c r="D15" t="s">
-        <v>3499</v>
+        <v>3497</v>
       </c>
       <c r="E15" t="s">
         <v>2706</v>
@@ -49865,16 +49818,16 @@
         <v>151</v>
       </c>
       <c r="G15" s="97" t="s">
-        <v>3500</v>
+        <v>3498</v>
       </c>
       <c r="H15" s="460" t="s">
-        <v>3688</v>
+        <v>3683</v>
       </c>
       <c r="I15" t="s">
-        <v>3637</v>
+        <v>3633</v>
       </c>
       <c r="J15" t="s">
-        <v>3636</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="17" spans="2:12">
@@ -50110,7 +50063,7 @@
     </row>
     <row r="2" spans="1:14" ht="43.15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="C2" s="51"/>
       <c r="D2" s="52" t="s">
@@ -50134,7 +50087,7 @@
         <v>2611</v>
       </c>
       <c r="E4" t="s">
-        <v>2965</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -50159,7 +50112,7 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="49" t="s">
-        <v>2820</v>
+        <v>2819</v>
       </c>
       <c r="B9" t="s">
         <v>1537</v>
@@ -50171,7 +50124,7 @@
         <v>1536</v>
       </c>
       <c r="E9" t="s">
-        <v>3331</v>
+        <v>3329</v>
       </c>
       <c r="F9" t="s">
         <v>1716</v>
@@ -50179,7 +50132,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
       <c r="B10">
         <v>63000545</v>
@@ -50191,7 +50144,7 @@
         <v>2188</v>
       </c>
       <c r="E10" t="s">
-        <v>3319</v>
+        <v>3317</v>
       </c>
       <c r="F10" t="s">
         <v>1665</v>
@@ -50199,7 +50152,7 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="30" t="s">
-        <v>3092</v>
+        <v>3090</v>
       </c>
       <c r="B11" s="178">
         <v>68241069</v>
@@ -50211,10 +50164,10 @@
         <v>2033</v>
       </c>
       <c r="E11" t="s">
-        <v>3422</v>
+        <v>3420</v>
       </c>
       <c r="F11" t="s">
-        <v>2828</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -50231,7 +50184,7 @@
         <v>2620</v>
       </c>
       <c r="E12" t="s">
-        <v>3156</v>
+        <v>3154</v>
       </c>
       <c r="F12" t="s">
         <v>1665</v>
@@ -50239,7 +50192,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>3076</v>
+        <v>3074</v>
       </c>
       <c r="B13">
         <v>62271547</v>
@@ -50251,10 +50204,10 @@
         <v>2350</v>
       </c>
       <c r="E13" t="s">
+        <v>2826</v>
+      </c>
+      <c r="F13" t="s">
         <v>2827</v>
-      </c>
-      <c r="F13" t="s">
-        <v>2828</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -50268,7 +50221,7 @@
         <v>1917</v>
       </c>
       <c r="D14" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="E14" t="s">
         <v>2581</v>
@@ -50279,7 +50232,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="B15">
         <v>62806425</v>
@@ -50291,7 +50244,7 @@
         <v>1719</v>
       </c>
       <c r="E15" t="s">
-        <v>2764</v>
+        <v>2763</v>
       </c>
       <c r="F15" t="s">
         <v>2623</v>
@@ -50308,10 +50261,10 @@
         <v>2664</v>
       </c>
       <c r="D16" s="30" t="s">
+        <v>2897</v>
+      </c>
+      <c r="E16" t="s">
         <v>2898</v>
-      </c>
-      <c r="E16" t="s">
-        <v>2899</v>
       </c>
       <c r="F16" t="s">
         <v>2623</v>
@@ -50325,13 +50278,13 @@
         <v>68927207</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>2845</v>
+        <v>2844</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>3459</v>
+        <v>3457</v>
       </c>
       <c r="E17" t="s">
-        <v>2906</v>
+        <v>2905</v>
       </c>
       <c r="F17" t="s">
         <v>2623</v>
@@ -50354,7 +50307,7 @@
         <v>2668</v>
       </c>
       <c r="E18" t="s">
-        <v>2906</v>
+        <v>2905</v>
       </c>
       <c r="F18" t="s">
         <v>2623</v>
@@ -50374,10 +50327,10 @@
         <v>2702</v>
       </c>
       <c r="E19" t="s">
-        <v>2978</v>
+        <v>2976</v>
       </c>
       <c r="F19" t="s">
-        <v>2828</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -50394,13 +50347,13 @@
         <v>421</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>3541</v>
+        <v>3539</v>
       </c>
       <c r="F20" t="s">
-        <v>2828</v>
+        <v>2827</v>
       </c>
       <c r="G20" t="s">
-        <v>2918</v>
+        <v>2917</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -50420,7 +50373,7 @@
         <v>1498</v>
       </c>
       <c r="F21" t="s">
-        <v>3070</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -50456,7 +50409,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="49" t="s">
-        <v>2847</v>
+        <v>2846</v>
       </c>
       <c r="B26">
         <v>68927207</v>
@@ -50468,13 +50421,13 @@
         <v>2597</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>2882</v>
+      </c>
+      <c r="F26" t="s">
         <v>2883</v>
       </c>
-      <c r="F26" t="s">
-        <v>2884</v>
-      </c>
       <c r="G26" t="s">
-        <v>2892</v>
+        <v>2891</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -50488,16 +50441,16 @@
         <v>1447</v>
       </c>
       <c r="D29" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="E29" s="49" t="s">
-        <v>3003</v>
+        <v>3001</v>
       </c>
       <c r="F29" t="s">
-        <v>2894</v>
+        <v>2893</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="H29" t="s">
         <v>407</v>
@@ -50505,7 +50458,7 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="49" t="s">
-        <v>2847</v>
+        <v>2846</v>
       </c>
       <c r="B30">
         <v>63926844</v>
@@ -50517,10 +50470,10 @@
         <v>2622</v>
       </c>
       <c r="E30" t="s">
+        <v>2892</v>
+      </c>
+      <c r="F30" t="s">
         <v>2893</v>
-      </c>
-      <c r="F30" t="s">
-        <v>2894</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -50534,10 +50487,10 @@
         <v>1543</v>
       </c>
       <c r="D31" t="s">
-        <v>3023</v>
+        <v>3021</v>
       </c>
       <c r="E31" t="s">
-        <v>3024</v>
+        <v>3022</v>
       </c>
       <c r="F31" t="s">
         <v>1308</v>
@@ -50646,10 +50599,10 @@
         <v>2453</v>
       </c>
       <c r="D47" s="30" t="s">
+        <v>2783</v>
+      </c>
+      <c r="F47" s="395" t="s">
         <v>2784</v>
-      </c>
-      <c r="F47" s="395" t="s">
-        <v>2785</v>
       </c>
       <c r="G47" s="30" t="s">
         <v>407</v>
@@ -50745,7 +50698,7 @@
     </row>
     <row r="60" spans="1:5" s="390" customFormat="1" ht="18">
       <c r="C60" s="390" t="s">
-        <v>2765</v>
+        <v>2764</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -50762,7 +50715,7 @@
         <v>2457</v>
       </c>
       <c r="E61" s="30" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
     </row>
     <row r="69" spans="1:12" s="76" customFormat="1">
@@ -52581,12 +52534,12 @@
     </row>
     <row r="252" spans="1:6" s="418" customFormat="1" ht="21">
       <c r="C252" s="418" t="s">
-        <v>2869</v>
+        <v>2868</v>
       </c>
     </row>
     <row r="253" spans="1:6">
       <c r="A253" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
       <c r="B253">
         <v>64476521</v>
@@ -52598,55 +52551,55 @@
         <v>2217</v>
       </c>
       <c r="E253" t="s">
+        <v>2866</v>
+      </c>
+      <c r="F253" t="s">
         <v>2867</v>
-      </c>
-      <c r="F253" t="s">
-        <v>2868</v>
       </c>
     </row>
     <row r="254" spans="1:6">
       <c r="A254" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="B254">
         <v>64738222</v>
       </c>
       <c r="C254" s="22" t="s">
-        <v>2841</v>
+        <v>2840</v>
       </c>
       <c r="D254" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="E254" t="s">
+        <v>2866</v>
+      </c>
+      <c r="F254" t="s">
         <v>2867</v>
-      </c>
-      <c r="F254" t="s">
-        <v>2868</v>
       </c>
     </row>
     <row r="255" spans="1:6">
       <c r="A255" s="30" t="s">
-        <v>3346</v>
+        <v>3344</v>
       </c>
       <c r="B255" s="30">
         <v>60433915</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>2840</v>
+        <v>2839</v>
       </c>
       <c r="D255" s="249" t="s">
         <v>2566</v>
       </c>
       <c r="E255" t="s">
+        <v>2866</v>
+      </c>
+      <c r="F255" t="s">
         <v>2867</v>
-      </c>
-      <c r="F255" t="s">
-        <v>2868</v>
       </c>
     </row>
     <row r="256" spans="1:6">
       <c r="A256" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
       <c r="B256">
         <v>61915064</v>
@@ -57395,7 +57348,7 @@
         <v>2611</v>
       </c>
       <c r="E537" s="76" t="s">
-        <v>2963</v>
+        <v>2961</v>
       </c>
       <c r="F537" s="76"/>
       <c r="G537" s="76"/>

--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dc549f2659ed9bd7/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64661" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76148D05-9666-4021-892D-1FB1103C5582}"/>
+  <xr:revisionPtr revIDLastSave="64672" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCE9F61B-E13D-4007-9065-7B66752D1370}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1181,7 +1181,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6206" uniqueCount="3691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6208" uniqueCount="3691">
   <si>
     <t>shopfreefire.1.21.2@gmail.com</t>
   </si>
@@ -10021,9 +10021,6 @@
     <t>14.60 USD BELICE hasta 23 de octubre</t>
   </si>
   <si>
-    <t>66838623 1 pantalla hasta el 27 de septiembre (Naychell)</t>
-  </si>
-  <si>
     <t>Rwa280626</t>
   </si>
   <si>
@@ -10129,12 +10126,6 @@
     <t>15,66 hasta 04 de octubre</t>
   </si>
   <si>
-    <t>Tre020926</t>
-  </si>
-  <si>
-    <t>Tra020926</t>
-  </si>
-  <si>
     <t>swansondonald4462+loknet.br@outlook.com</t>
   </si>
   <si>
@@ -10771,9 +10762,6 @@
     <t>Trs120926</t>
   </si>
   <si>
-    <t>QUINCENAL 63000428 1 pantalla hasta el 27 de septiembre (Yuri  270826-0413d</t>
-  </si>
-  <si>
     <t>Ydd120926</t>
   </si>
   <si>
@@ -12254,6 +12242,18 @@
   </si>
   <si>
     <t>N005 1 pantalla hasta el 05 de noviembre 051026-0015d</t>
+  </si>
+  <si>
+    <t>Nhs051026</t>
+  </si>
+  <si>
+    <t>Nsd050926</t>
+  </si>
+  <si>
+    <t>N004 1 pantalla hasta el 05 de noviembre 051026-0100d</t>
+  </si>
+  <si>
+    <t>N005 1 pantalla hasta el 05 de noviembre 051026-0105s</t>
   </si>
 </sst>
 </file>
@@ -30652,7 +30652,7 @@
   <sheetData>
     <row r="1" spans="1:11" s="30" customFormat="1">
       <c r="A1" s="30" t="s">
-        <v>3533</v>
+        <v>3529</v>
       </c>
       <c r="B1" s="30">
         <v>60389752</v>
@@ -30664,7 +30664,7 @@
         <v>1987</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>3318</v>
+        <v>3314</v>
       </c>
       <c r="F1" s="30" t="s">
         <v>2052</v>
@@ -30675,7 +30675,7 @@
     </row>
     <row r="2" spans="1:11" s="148" customFormat="1">
       <c r="A2" s="148" t="s">
-        <v>3449</v>
+        <v>3445</v>
       </c>
       <c r="B2" s="148">
         <v>62360487</v>
@@ -30684,7 +30684,7 @@
         <v>2097</v>
       </c>
       <c r="D2" s="148" t="s">
-        <v>3475</v>
+        <v>3471</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="148" customFormat="1">
@@ -30703,7 +30703,7 @@
     </row>
     <row r="4" spans="1:11" s="30" customFormat="1">
       <c r="A4" s="30" t="s">
-        <v>3533</v>
+        <v>3529</v>
       </c>
       <c r="B4" s="30">
         <v>60389752</v>
@@ -30715,7 +30715,7 @@
         <v>1985</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>3387</v>
+        <v>3383</v>
       </c>
       <c r="F4" s="30" t="s">
         <v>2052</v>
@@ -30735,7 +30735,7 @@
         <v>2111</v>
       </c>
       <c r="D5" s="148" t="s">
-        <v>3563</v>
+        <v>3559</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="148" customFormat="1">
@@ -30754,7 +30754,7 @@
     </row>
     <row r="7" spans="1:11" s="30" customFormat="1">
       <c r="A7" s="30" t="s">
-        <v>3537</v>
+        <v>3533</v>
       </c>
       <c r="B7" s="30">
         <v>60389752</v>
@@ -30766,7 +30766,7 @@
         <v>2753</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>3469</v>
+        <v>3465</v>
       </c>
       <c r="F7" s="30" t="s">
         <v>2057</v>
@@ -30786,7 +30786,7 @@
         <v>2210</v>
       </c>
       <c r="D8" s="148" t="s">
-        <v>3248</v>
+        <v>3244</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="148" customFormat="1">
@@ -30808,7 +30808,7 @@
     </row>
     <row r="10" spans="1:11" s="421" customFormat="1">
       <c r="A10" s="421" t="s">
-        <v>3486</v>
+        <v>3482</v>
       </c>
       <c r="B10" s="421">
         <v>60389752</v>
@@ -30820,7 +30820,7 @@
         <v>2069</v>
       </c>
       <c r="E10" s="421" t="s">
-        <v>3517</v>
+        <v>3513</v>
       </c>
       <c r="F10" s="421" t="s">
         <v>2715</v>
@@ -30833,7 +30833,7 @@
     <row r="12" spans="1:11" s="367" customFormat="1"/>
     <row r="13" spans="1:11" s="30" customFormat="1">
       <c r="A13" s="30" t="s">
-        <v>3185</v>
+        <v>3182</v>
       </c>
       <c r="B13" s="30">
         <v>69184177</v>
@@ -30842,10 +30842,10 @@
         <v>1754</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>3341</v>
+        <v>3337</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>3557</v>
+        <v>3553</v>
       </c>
       <c r="F13" s="30" t="s">
         <v>2115</v>
@@ -30857,7 +30857,7 @@
     </row>
     <row r="14" spans="1:11" s="148" customFormat="1">
       <c r="A14" s="225" t="s">
-        <v>3268</v>
+        <v>3264</v>
       </c>
       <c r="B14" s="225" t="s">
         <v>1655</v>
@@ -30871,7 +30871,7 @@
     </row>
     <row r="15" spans="1:11" s="148" customFormat="1">
       <c r="A15" s="225" t="s">
-        <v>3134</v>
+        <v>3131</v>
       </c>
       <c r="B15" s="414">
         <v>62439069</v>
@@ -30885,7 +30885,7 @@
     </row>
     <row r="16" spans="1:11" s="32" customFormat="1">
       <c r="A16" s="30" t="s">
-        <v>3176</v>
+        <v>3173</v>
       </c>
       <c r="B16" s="282" t="s">
         <v>2167</v>
@@ -30897,7 +30897,7 @@
         <v>2873</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>3591</v>
+        <v>3587</v>
       </c>
       <c r="F16" s="32" t="s">
         <v>1510</v>
@@ -30906,21 +30906,21 @@
         <v>198</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>3481</v>
+        <v>3477</v>
       </c>
       <c r="I16" s="32" t="s">
-        <v>3381</v>
+        <v>3377</v>
       </c>
       <c r="J16" s="32" t="s">
-        <v>3452</v>
+        <v>3448</v>
       </c>
       <c r="K16" s="30" t="s">
-        <v>3638</v>
+        <v>3634</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="164" customFormat="1">
       <c r="A17" s="250" t="s">
-        <v>3091</v>
+        <v>3088</v>
       </c>
       <c r="B17" s="250" t="s">
         <v>1385</v>
@@ -30937,7 +30937,7 @@
     </row>
     <row r="18" spans="1:11" s="164" customFormat="1">
       <c r="A18" s="250" t="s">
-        <v>3290</v>
+        <v>3286</v>
       </c>
       <c r="B18" s="250">
         <v>64341760</v>
@@ -30959,10 +30959,10 @@
         <v>1474</v>
       </c>
       <c r="D19" s="145" t="s">
-        <v>3194</v>
+        <v>3191</v>
       </c>
       <c r="E19" s="145" t="s">
-        <v>3470</v>
+        <v>3466</v>
       </c>
       <c r="F19" s="145" t="s">
         <v>1352</v>
@@ -30994,7 +30994,7 @@
     </row>
     <row r="21" spans="1:11" s="295" customFormat="1">
       <c r="A21" s="250" t="s">
-        <v>3202</v>
+        <v>3198</v>
       </c>
       <c r="B21" s="250">
         <v>62169673</v>
@@ -31003,7 +31003,7 @@
         <v>1666</v>
       </c>
       <c r="D21" s="164" t="s">
-        <v>3195</v>
+        <v>3192</v>
       </c>
       <c r="E21" s="164" t="s">
         <v>1667</v>
@@ -31023,7 +31023,7 @@
         <v>2094</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>3318</v>
+        <v>3314</v>
       </c>
       <c r="F22" s="30" t="s">
         <v>2051</v>
@@ -31057,7 +31057,7 @@
         <v>2090</v>
       </c>
       <c r="D24" s="148" t="s">
-        <v>3197</v>
+        <v>3193</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="30" customFormat="1">
@@ -31074,7 +31074,7 @@
         <v>1506</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>3441</v>
+        <v>3437</v>
       </c>
       <c r="F25" s="30" t="s">
         <v>1352</v>
@@ -31134,7 +31134,7 @@
         <v>1982</v>
       </c>
       <c r="E28" s="456" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="F28" s="301" t="s">
         <v>2124</v>
@@ -31159,7 +31159,7 @@
     </row>
     <row r="30" spans="1:11" s="164" customFormat="1">
       <c r="A30" s="164" t="s">
-        <v>3176</v>
+        <v>3173</v>
       </c>
       <c r="B30" s="164">
         <v>62782770</v>
@@ -31173,10 +31173,10 @@
     </row>
     <row r="31" spans="1:11" s="30" customFormat="1">
       <c r="A31" s="30" t="s">
-        <v>3304</v>
+        <v>3300</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>3416</v>
+        <v>3412</v>
       </c>
       <c r="C31" s="249" t="s">
         <v>1878</v>
@@ -31185,7 +31185,7 @@
         <v>2861</v>
       </c>
       <c r="E31" s="30" t="s">
-        <v>3340</v>
+        <v>3336</v>
       </c>
       <c r="F31" s="30" t="s">
         <v>2002</v>
@@ -31194,16 +31194,16 @@
         <v>198</v>
       </c>
       <c r="H31" s="30" t="s">
-        <v>3597</v>
+        <v>3593</v>
       </c>
       <c r="I31" s="192" t="s">
-        <v>3484</v>
+        <v>3480</v>
       </c>
       <c r="J31" s="419" t="s">
-        <v>3421</v>
+        <v>3417</v>
       </c>
       <c r="K31" s="30" t="s">
-        <v>3226</v>
+        <v>3222</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="163" customFormat="1">
@@ -31249,7 +31249,7 @@
         <v>2064</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>3227</v>
+        <v>3223</v>
       </c>
       <c r="F34" s="30" t="s">
         <v>2055</v>
@@ -31269,7 +31269,7 @@
         <v>1959</v>
       </c>
       <c r="D35" s="148" t="s">
-        <v>3272</v>
+        <v>3268</v>
       </c>
       <c r="E35" s="148" t="s">
         <v>1961</v>
@@ -31291,7 +31291,7 @@
     </row>
     <row r="37" spans="1:11" s="30" customFormat="1">
       <c r="A37" s="30" t="s">
-        <v>3290</v>
+        <v>3286</v>
       </c>
       <c r="B37" s="30" t="s">
         <v>2646</v>
@@ -31303,7 +31303,7 @@
         <v>2930</v>
       </c>
       <c r="E37" s="30" t="s">
-        <v>3319</v>
+        <v>3315</v>
       </c>
       <c r="F37" s="30" t="s">
         <v>2045</v>
@@ -31312,16 +31312,16 @@
         <v>198</v>
       </c>
       <c r="H37" s="458" t="s">
-        <v>3679</v>
-      </c>
-      <c r="I37" s="217" t="s">
-        <v>2946</v>
-      </c>
-      <c r="J37" s="217" t="s">
-        <v>3196</v>
+        <v>3675</v>
+      </c>
+      <c r="I37" s="145" t="s">
+        <v>3689</v>
+      </c>
+      <c r="J37" s="145" t="s">
+        <v>3690</v>
       </c>
       <c r="K37" s="30" t="s">
-        <v>3064</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="147" customFormat="1">
@@ -31350,12 +31350,12 @@
         <v>2031</v>
       </c>
       <c r="D39" s="148" t="s">
-        <v>3489</v>
+        <v>3485</v>
       </c>
     </row>
     <row r="40" spans="1:11" s="30" customFormat="1">
       <c r="A40" s="30" t="s">
-        <v>3260</v>
+        <v>3256</v>
       </c>
       <c r="B40" s="32" t="s">
         <v>2935</v>
@@ -31364,10 +31364,10 @@
         <v>1642</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>3172</v>
+        <v>3169</v>
       </c>
       <c r="E40" s="30" t="s">
-        <v>3227</v>
+        <v>3223</v>
       </c>
       <c r="F40" s="30" t="s">
         <v>2060</v>
@@ -31376,21 +31376,21 @@
         <v>198</v>
       </c>
       <c r="H40" s="30" t="s">
-        <v>3316</v>
+        <v>3312</v>
       </c>
       <c r="I40" s="32" t="s">
-        <v>3543</v>
+        <v>3539</v>
       </c>
       <c r="J40" s="32" t="s">
-        <v>3527</v>
+        <v>3523</v>
       </c>
       <c r="K40" s="145" t="s">
-        <v>3173</v>
+        <v>3170</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="163" customFormat="1">
       <c r="A41" s="163" t="s">
-        <v>3304</v>
+        <v>3300</v>
       </c>
       <c r="B41" s="163">
         <v>68381893</v>
@@ -31407,7 +31407,7 @@
     </row>
     <row r="42" spans="1:11" s="252" customFormat="1">
       <c r="A42" s="266" t="s">
-        <v>3449</v>
+        <v>3445</v>
       </c>
       <c r="B42" s="266">
         <v>62360487</v>
@@ -31422,7 +31422,7 @@
     </row>
     <row r="43" spans="1:11" s="30" customFormat="1">
       <c r="A43" s="30" t="s">
-        <v>3595</v>
+        <v>3591</v>
       </c>
       <c r="B43" s="30">
         <v>60389752</v>
@@ -31434,7 +31434,7 @@
         <v>2006</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="F43" s="30" t="s">
         <v>2091</v>
@@ -31445,7 +31445,7 @@
     </row>
     <row r="44" spans="1:11" s="164" customFormat="1">
       <c r="A44" s="164" t="s">
-        <v>3304</v>
+        <v>3300</v>
       </c>
       <c r="B44" s="164">
         <v>68381893</v>
@@ -31462,7 +31462,7 @@
     </row>
     <row r="45" spans="1:11" s="163" customFormat="1">
       <c r="A45" s="163" t="s">
-        <v>3075</v>
+        <v>3072</v>
       </c>
       <c r="B45" s="163">
         <v>64079861</v>
@@ -31491,7 +31491,7 @@
         <v>2749</v>
       </c>
       <c r="E46" s="30" t="s">
-        <v>3041</v>
+        <v>3038</v>
       </c>
       <c r="F46" s="30" t="s">
         <v>2075</v>
@@ -31537,16 +31537,16 @@
         <v>1481</v>
       </c>
       <c r="B49" s="30" t="s">
-        <v>3083</v>
+        <v>3080</v>
       </c>
       <c r="C49" s="134" t="s">
         <v>1971</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>2988</v>
+        <v>2985</v>
       </c>
       <c r="E49" s="30" t="s">
-        <v>3228</v>
+        <v>3224</v>
       </c>
       <c r="F49" s="30" t="s">
         <v>2063</v>
@@ -31555,16 +31555,16 @@
         <v>198</v>
       </c>
       <c r="H49" s="30" t="s">
-        <v>3588</v>
+        <v>3584</v>
       </c>
       <c r="I49" s="30" t="s">
-        <v>3554</v>
+        <v>3550</v>
       </c>
       <c r="J49" s="30" t="s">
-        <v>3651</v>
+        <v>3647</v>
       </c>
       <c r="K49" s="30" t="s">
-        <v>3553</v>
+        <v>3549</v>
       </c>
     </row>
     <row r="50" spans="1:12" s="164" customFormat="1">
@@ -31583,7 +31583,7 @@
     </row>
     <row r="51" spans="1:12" s="164" customFormat="1">
       <c r="A51" s="164" t="s">
-        <v>3290</v>
+        <v>3286</v>
       </c>
       <c r="B51" s="164">
         <v>62455811</v>
@@ -31592,7 +31592,7 @@
         <v>1979</v>
       </c>
       <c r="D51" s="164" t="s">
-        <v>3442</v>
+        <v>3438</v>
       </c>
     </row>
     <row r="52" spans="1:12" s="139" customFormat="1">
@@ -31609,7 +31609,7 @@
         <v>2759</v>
       </c>
       <c r="E52" s="139" t="s">
-        <v>3227</v>
+        <v>3223</v>
       </c>
       <c r="F52" s="139" t="s">
         <v>2061</v>
@@ -31618,21 +31618,21 @@
         <v>198</v>
       </c>
       <c r="H52" s="459" t="s">
-        <v>3682</v>
+        <v>3678</v>
       </c>
       <c r="I52" s="140" t="s">
-        <v>3059</v>
+        <v>3056</v>
       </c>
       <c r="J52" s="30" t="s">
-        <v>3619</v>
+        <v>3615</v>
       </c>
       <c r="K52" s="267" t="s">
-        <v>3378</v>
+        <v>3374</v>
       </c>
     </row>
     <row r="53" spans="1:12" s="164" customFormat="1">
       <c r="A53" s="164" t="s">
-        <v>3583</v>
+        <v>3579</v>
       </c>
       <c r="B53" s="164" t="s">
         <v>1140</v>
@@ -31668,7 +31668,7 @@
     </row>
     <row r="55" spans="1:12" s="30" customFormat="1">
       <c r="A55" s="30" t="s">
-        <v>3180</v>
+        <v>3177</v>
       </c>
       <c r="B55" s="30">
         <v>61130088</v>
@@ -31680,7 +31680,7 @@
         <v>1975</v>
       </c>
       <c r="E55" s="30" t="s">
-        <v>3556</v>
+        <v>3552</v>
       </c>
       <c r="F55" s="30" t="s">
         <v>2076</v>
@@ -31700,13 +31700,13 @@
         <v>2924</v>
       </c>
       <c r="D56" s="368" t="s">
-        <v>3548</v>
+        <v>3544</v>
       </c>
       <c r="E56" s="164"/>
     </row>
     <row r="57" spans="1:12" s="163" customFormat="1">
       <c r="A57" s="163" t="s">
-        <v>3260</v>
+        <v>3256</v>
       </c>
       <c r="B57" s="163" t="s">
         <v>2928</v>
@@ -31733,7 +31733,7 @@
         <v>2703</v>
       </c>
       <c r="E58" s="30" t="s">
-        <v>3365</v>
+        <v>3361</v>
       </c>
       <c r="F58" s="30" t="s">
         <v>2088</v>
@@ -31742,30 +31742,30 @@
         <v>198</v>
       </c>
       <c r="H58" s="217" t="s">
-        <v>2999</v>
+        <v>2996</v>
       </c>
       <c r="I58" s="217" t="s">
         <v>2934</v>
       </c>
       <c r="J58" s="30" t="s">
-        <v>3635</v>
+        <v>3631</v>
       </c>
       <c r="K58" s="30" t="s">
-        <v>3245</v>
+        <v>3241</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" s="147" t="s">
-        <v>3264</v>
+        <v>3260</v>
       </c>
       <c r="B59" s="147">
         <v>67539485</v>
       </c>
       <c r="C59" s="397" t="s">
-        <v>3363</v>
+        <v>3359</v>
       </c>
       <c r="D59" s="369" t="s">
-        <v>3366</v>
+        <v>3362</v>
       </c>
       <c r="E59" s="148"/>
       <c r="F59" s="147"/>
@@ -31778,16 +31778,16 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" s="147" t="s">
-        <v>3264</v>
+        <v>3260</v>
       </c>
       <c r="B60" s="147">
         <v>68853797</v>
       </c>
       <c r="C60" s="397" t="s">
-        <v>3364</v>
+        <v>3360</v>
       </c>
       <c r="D60" s="369" t="s">
-        <v>3367</v>
+        <v>3363</v>
       </c>
       <c r="E60" s="147"/>
       <c r="F60" s="147"/>
@@ -31800,19 +31800,19 @@
     </row>
     <row r="61" spans="1:12" s="30" customFormat="1">
       <c r="A61" s="145" t="s">
-        <v>3583</v>
+        <v>3579</v>
       </c>
       <c r="B61" s="30" t="s">
-        <v>3684</v>
+        <v>3680</v>
       </c>
       <c r="C61" s="134" t="s">
         <v>2044</v>
       </c>
       <c r="D61" s="30" t="s">
-        <v>3686</v>
+        <v>3682</v>
       </c>
       <c r="E61" s="30" t="s">
-        <v>3471</v>
+        <v>3467</v>
       </c>
       <c r="F61" s="30" t="s">
         <v>2045</v>
@@ -31821,16 +31821,16 @@
         <v>198</v>
       </c>
       <c r="H61" s="30" t="s">
-        <v>3101</v>
+        <v>3098</v>
       </c>
       <c r="I61" s="145" t="s">
-        <v>3685</v>
+        <v>3681</v>
       </c>
       <c r="J61" s="30" t="s">
-        <v>2992</v>
+        <v>2989</v>
       </c>
       <c r="K61" s="30" t="s">
-        <v>3061</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="62" spans="1:12" s="147" customFormat="1">
@@ -31844,7 +31844,7 @@
         <v>1453</v>
       </c>
       <c r="D62" s="369" t="s">
-        <v>3549</v>
+        <v>3545</v>
       </c>
       <c r="E62" s="148" t="s">
         <v>1371</v>
@@ -31876,10 +31876,10 @@
         <v>1641</v>
       </c>
       <c r="D64" s="30" t="s">
-        <v>2997</v>
+        <v>2994</v>
       </c>
       <c r="E64" s="30" t="s">
-        <v>3227</v>
+        <v>3223</v>
       </c>
       <c r="F64" s="30" t="s">
         <v>2062</v>
@@ -31888,16 +31888,16 @@
         <v>198</v>
       </c>
       <c r="H64" s="32" t="s">
-        <v>3073</v>
+        <v>3070</v>
       </c>
       <c r="I64" s="32" t="s">
-        <v>3137</v>
+        <v>3134</v>
       </c>
       <c r="J64" s="30" t="s">
-        <v>3671</v>
+        <v>3667</v>
       </c>
       <c r="K64" s="30" t="s">
-        <v>3522</v>
+        <v>3518</v>
       </c>
     </row>
     <row r="65" spans="1:11" s="164" customFormat="1">
@@ -31936,7 +31936,7 @@
     </row>
     <row r="67" spans="1:11" s="30" customFormat="1">
       <c r="A67" s="251" t="s">
-        <v>3145</v>
+        <v>3142</v>
       </c>
       <c r="B67" s="282" t="s">
         <v>1886</v>
@@ -31948,7 +31948,7 @@
         <v>2845</v>
       </c>
       <c r="E67" s="30" t="s">
-        <v>3275</v>
+        <v>3271</v>
       </c>
       <c r="F67" s="30" t="s">
         <v>2066</v>
@@ -31957,21 +31957,21 @@
         <v>198</v>
       </c>
       <c r="H67" s="30" t="s">
-        <v>3336</v>
+        <v>3332</v>
       </c>
       <c r="I67" s="30" t="s">
-        <v>3126</v>
+        <v>3123</v>
       </c>
       <c r="J67" s="30" t="s">
-        <v>3171</v>
+        <v>3168</v>
       </c>
       <c r="K67" s="30" t="s">
-        <v>3540</v>
+        <v>3536</v>
       </c>
     </row>
     <row r="68" spans="1:11" s="147" customFormat="1">
       <c r="A68" s="147" t="s">
-        <v>3537</v>
+        <v>3533</v>
       </c>
       <c r="B68" s="147">
         <v>60432412</v>
@@ -31980,13 +31980,13 @@
         <v>1854</v>
       </c>
       <c r="D68" s="369" t="s">
-        <v>3644</v>
+        <v>3640</v>
       </c>
       <c r="E68" s="148"/>
     </row>
     <row r="69" spans="1:11" s="148" customFormat="1">
       <c r="A69" s="225" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="B69" s="148">
         <v>63018763</v>
@@ -31995,7 +31995,7 @@
         <v>2065</v>
       </c>
       <c r="D69" s="148" t="s">
-        <v>3284</v>
+        <v>3280</v>
       </c>
     </row>
     <row r="70" spans="1:11" s="30" customFormat="1">
@@ -32003,16 +32003,16 @@
         <v>2762</v>
       </c>
       <c r="B70" s="32" t="s">
-        <v>3071</v>
+        <v>3068</v>
       </c>
       <c r="C70" s="249" t="s">
         <v>1644</v>
       </c>
       <c r="D70" s="30" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
       <c r="E70" s="30" t="s">
-        <v>3652</v>
+        <v>3648</v>
       </c>
       <c r="F70" s="30" t="s">
         <v>2102</v>
@@ -32021,13 +32021,13 @@
         <v>198</v>
       </c>
       <c r="H70" s="32" t="s">
-        <v>3274</v>
+        <v>3270</v>
       </c>
       <c r="I70" s="30" t="s">
-        <v>3658</v>
+        <v>3654</v>
       </c>
       <c r="J70" s="30" t="s">
-        <v>3371</v>
+        <v>3367</v>
       </c>
     </row>
     <row r="71" spans="1:11" s="164" customFormat="1">
@@ -32046,7 +32046,7 @@
     </row>
     <row r="72" spans="1:11" s="163" customFormat="1">
       <c r="A72" s="266" t="s">
-        <v>3264</v>
+        <v>3260</v>
       </c>
       <c r="B72" s="266" t="s">
         <v>1436</v>
@@ -32061,7 +32061,7 @@
     </row>
     <row r="73" spans="1:11" s="30" customFormat="1">
       <c r="A73" s="30" t="s">
-        <v>3595</v>
+        <v>3591</v>
       </c>
       <c r="B73" s="30">
         <v>60389752</v>
@@ -32073,7 +32073,7 @@
         <v>2713</v>
       </c>
       <c r="E73" s="30" t="s">
-        <v>3076</v>
+        <v>3073</v>
       </c>
       <c r="F73" s="30" t="s">
         <v>2001</v>
@@ -32084,7 +32084,7 @@
     </row>
     <row r="74" spans="1:11" s="147" customFormat="1">
       <c r="A74" s="147" t="s">
-        <v>3268</v>
+        <v>3264</v>
       </c>
       <c r="B74" s="147">
         <v>64226974</v>
@@ -32108,7 +32108,7 @@
         <v>1922</v>
       </c>
       <c r="D75" s="148" t="s">
-        <v>3564</v>
+        <v>3560</v>
       </c>
       <c r="E75" s="148"/>
     </row>
@@ -32135,16 +32135,16 @@
         <v>198</v>
       </c>
       <c r="H76" s="30" t="s">
-        <v>3229</v>
+        <v>3225</v>
       </c>
       <c r="I76" s="30" t="s">
-        <v>3273</v>
+        <v>3269</v>
       </c>
       <c r="J76" s="30" t="s">
-        <v>3594</v>
+        <v>3590</v>
       </c>
       <c r="K76" s="30" t="s">
-        <v>3529</v>
+        <v>3525</v>
       </c>
     </row>
     <row r="77" spans="1:11" s="152" customFormat="1">
@@ -32169,7 +32169,7 @@
         <v>2832</v>
       </c>
       <c r="E79" s="30" t="s">
-        <v>3318</v>
+        <v>3314</v>
       </c>
       <c r="F79" s="30" t="s">
         <v>2056</v>
@@ -32184,10 +32184,10 @@
         <v>2933</v>
       </c>
       <c r="J79" s="30" t="s">
-        <v>3188</v>
+        <v>3185</v>
       </c>
       <c r="K79" s="217" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="80" spans="1:11" s="147" customFormat="1">
@@ -32224,10 +32224,10 @@
     </row>
     <row r="82" spans="1:11" s="30" customFormat="1">
       <c r="A82" s="145" t="s">
-        <v>3268</v>
+        <v>3264</v>
       </c>
       <c r="B82" s="30" t="s">
-        <v>3322</v>
+        <v>3318</v>
       </c>
       <c r="C82" s="22" t="s">
         <v>1879</v>
@@ -32245,16 +32245,16 @@
         <v>198</v>
       </c>
       <c r="H82" s="30" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="I82" s="30" t="s">
-        <v>3472</v>
+        <v>3468</v>
       </c>
       <c r="J82" s="30" t="s">
-        <v>3258</v>
+        <v>3254</v>
       </c>
       <c r="K82" s="30" t="s">
-        <v>3206</v>
+        <v>3202</v>
       </c>
     </row>
     <row r="83" spans="1:11" s="148" customFormat="1">
@@ -32268,7 +32268,7 @@
         <v>1935</v>
       </c>
       <c r="D83" s="148" t="s">
-        <v>3320</v>
+        <v>3316</v>
       </c>
     </row>
     <row r="84" spans="1:11" s="278" customFormat="1">
@@ -32296,7 +32296,7 @@
         <v>692</v>
       </c>
       <c r="D85" s="30" t="s">
-        <v>3007</v>
+        <v>3004</v>
       </c>
       <c r="E85" s="30" t="s">
         <v>1770</v>
@@ -32308,21 +32308,21 @@
         <v>493</v>
       </c>
       <c r="H85" s="217" t="s">
-        <v>3108</v>
+        <v>3105</v>
       </c>
       <c r="I85" s="32" t="s">
-        <v>3333</v>
+        <v>3329</v>
       </c>
       <c r="J85" s="30" t="s">
-        <v>3127</v>
+        <v>3124</v>
       </c>
       <c r="K85" s="215" t="s">
-        <v>3298</v>
+        <v>3294</v>
       </c>
     </row>
     <row r="86" spans="1:11" s="147" customFormat="1">
       <c r="A86" s="147" t="s">
-        <v>3290</v>
+        <v>3286</v>
       </c>
       <c r="B86" s="147">
         <v>65509692</v>
@@ -32340,7 +32340,7 @@
     </row>
     <row r="87" spans="1:11" s="147" customFormat="1">
       <c r="A87" s="147" t="s">
-        <v>3486</v>
+        <v>3482</v>
       </c>
       <c r="B87" s="147" t="s">
         <v>908</v>
@@ -32361,7 +32361,7 @@
         <v>1499</v>
       </c>
       <c r="B88" s="30" t="s">
-        <v>3198</v>
+        <v>3194</v>
       </c>
       <c r="C88" s="153" t="s">
         <v>693</v>
@@ -32370,7 +32370,7 @@
         <v>2817</v>
       </c>
       <c r="E88" s="30" t="s">
-        <v>3653</v>
+        <v>3649</v>
       </c>
       <c r="F88" s="30" t="s">
         <v>1074</v>
@@ -32379,16 +32379,16 @@
         <v>1507</v>
       </c>
       <c r="H88" s="30" t="s">
-        <v>3358</v>
+        <v>3354</v>
       </c>
       <c r="I88" s="30" t="s">
-        <v>3454</v>
+        <v>3450</v>
       </c>
       <c r="J88" s="32" t="s">
-        <v>3453</v>
+        <v>3449</v>
       </c>
       <c r="K88" s="30" t="s">
-        <v>3335</v>
+        <v>3331</v>
       </c>
     </row>
     <row r="89" spans="1:11" s="147" customFormat="1">
@@ -32411,7 +32411,7 @@
     </row>
     <row r="90" spans="1:11" s="148" customFormat="1">
       <c r="A90" s="225" t="s">
-        <v>3537</v>
+        <v>3533</v>
       </c>
       <c r="B90" s="148">
         <v>69645877</v>
@@ -32420,7 +32420,7 @@
         <v>2716</v>
       </c>
       <c r="D90" s="148" t="s">
-        <v>3657</v>
+        <v>3653</v>
       </c>
       <c r="E90" s="148" t="s">
         <v>865</v>
@@ -32429,7 +32429,7 @@
     </row>
     <row r="91" spans="1:11" s="106" customFormat="1">
       <c r="A91" s="247" t="s">
-        <v>3264</v>
+        <v>3260</v>
       </c>
       <c r="B91" s="32" t="s">
         <v>1389</v>
@@ -32453,13 +32453,13 @@
         <v>2938</v>
       </c>
       <c r="I91" s="31" t="s">
-        <v>3343</v>
+        <v>3339</v>
       </c>
       <c r="J91" s="32" t="s">
-        <v>3422</v>
+        <v>3418</v>
       </c>
       <c r="K91" s="30" t="s">
-        <v>3621</v>
+        <v>3617</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="404" customFormat="1">
@@ -32490,7 +32490,7 @@
         <v>1698</v>
       </c>
       <c r="D93" s="148" t="s">
-        <v>3681</v>
+        <v>3677</v>
       </c>
     </row>
     <row r="94" spans="1:11" s="32" customFormat="1">
@@ -32507,7 +32507,7 @@
         <v>1353</v>
       </c>
       <c r="E94" s="32" t="s">
-        <v>3113</v>
+        <v>3110</v>
       </c>
       <c r="F94" s="32" t="s">
         <v>1354</v>
@@ -32519,7 +32519,7 @@
     </row>
     <row r="95" spans="1:11" s="148" customFormat="1">
       <c r="A95" s="148" t="s">
-        <v>3185</v>
+        <v>3182</v>
       </c>
       <c r="B95" s="148" t="s">
         <v>2567</v>
@@ -32536,7 +32536,7 @@
     </row>
     <row r="96" spans="1:11" s="148" customFormat="1">
       <c r="A96" s="148" t="s">
-        <v>3176</v>
+        <v>3173</v>
       </c>
       <c r="B96" s="148">
         <v>65633205</v>
@@ -32545,7 +32545,7 @@
         <v>1370</v>
       </c>
       <c r="D96" s="148" t="s">
-        <v>3199</v>
+        <v>3195</v>
       </c>
       <c r="E96" s="148" t="s">
         <v>1369</v>
@@ -32553,7 +32553,7 @@
     </row>
     <row r="97" spans="1:13" s="30" customFormat="1">
       <c r="A97" s="32" t="s">
-        <v>3185</v>
+        <v>3182</v>
       </c>
       <c r="B97" s="30" t="s">
         <v>2803</v>
@@ -32574,16 +32574,16 @@
         <v>198</v>
       </c>
       <c r="H97" s="32" t="s">
-        <v>3151</v>
+        <v>3148</v>
       </c>
       <c r="I97" s="30" t="s">
-        <v>3302</v>
+        <v>3298</v>
       </c>
       <c r="J97" s="30" t="s">
-        <v>3672</v>
+        <v>3668</v>
       </c>
       <c r="K97" s="427" t="s">
-        <v>3174</v>
+        <v>3171</v>
       </c>
     </row>
     <row r="98" spans="1:13" s="386" customFormat="1">
@@ -32596,16 +32596,16 @@
     </row>
     <row r="100" spans="1:13" s="30" customFormat="1">
       <c r="A100" s="30" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="B100" s="30" t="s">
-        <v>3313</v>
+        <v>3309</v>
       </c>
       <c r="C100" s="249" t="s">
         <v>2734</v>
       </c>
       <c r="D100" s="30" t="s">
-        <v>3026</v>
+        <v>3023</v>
       </c>
       <c r="E100" s="30" t="s">
         <v>2896</v>
@@ -32617,16 +32617,16 @@
         <v>198</v>
       </c>
       <c r="H100" s="30" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="I100" s="30" t="s">
-        <v>3292</v>
+        <v>3288</v>
       </c>
       <c r="J100" s="30" t="s">
-        <v>3179</v>
+        <v>3176</v>
       </c>
       <c r="K100" s="30" t="s">
-        <v>3232</v>
+        <v>3228</v>
       </c>
     </row>
     <row r="101" spans="1:13" s="386" customFormat="1">
@@ -32639,10 +32639,10 @@
     </row>
     <row r="103" spans="1:13" s="30" customFormat="1">
       <c r="A103" s="145" t="s">
-        <v>3583</v>
+        <v>3579</v>
       </c>
       <c r="B103" s="30" t="s">
-        <v>3688</v>
+        <v>3684</v>
       </c>
       <c r="C103" s="249" t="s">
         <v>2770</v>
@@ -32660,16 +32660,16 @@
         <v>198</v>
       </c>
       <c r="H103" s="30" t="s">
-        <v>3580</v>
+        <v>3576</v>
       </c>
       <c r="I103" s="145" t="s">
-        <v>3689</v>
+        <v>3685</v>
       </c>
       <c r="J103" s="30" t="s">
-        <v>3687</v>
+        <v>3683</v>
       </c>
       <c r="K103" s="145" t="s">
-        <v>3690</v>
+        <v>3686</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -32716,7 +32716,7 @@
         <v>2863</v>
       </c>
       <c r="E106" s="30" t="s">
-        <v>3439</v>
+        <v>3435</v>
       </c>
       <c r="F106" s="30" t="s">
         <v>2864</v>
@@ -32771,7 +32771,7 @@
         <v>1957</v>
       </c>
       <c r="E127" s="30" t="s">
-        <v>3460</v>
+        <v>3456</v>
       </c>
       <c r="F127" t="s">
         <v>1955</v>
@@ -32791,7 +32791,7 @@
         <v>1928</v>
       </c>
       <c r="E128" s="30" t="s">
-        <v>3460</v>
+        <v>3456</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -32808,7 +32808,7 @@
         <v>2943</v>
       </c>
       <c r="E129" s="30" t="s">
-        <v>3460</v>
+        <v>3456</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -32825,7 +32825,7 @@
         <v>2520</v>
       </c>
       <c r="E130" s="30" t="s">
-        <v>3460</v>
+        <v>3456</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -32842,7 +32842,7 @@
         <v>1934</v>
       </c>
       <c r="E131" s="30" t="s">
-        <v>3460</v>
+        <v>3456</v>
       </c>
     </row>
     <row r="133" spans="1:6" s="121" customFormat="1" ht="23.5">
@@ -32864,7 +32864,7 @@
         <v>2301</v>
       </c>
       <c r="E134" s="30" t="s">
-        <v>3528</v>
+        <v>3524</v>
       </c>
       <c r="F134" t="s">
         <v>1331</v>
@@ -32884,7 +32884,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>3180</v>
+        <v>3177</v>
       </c>
       <c r="B139">
         <v>64720128</v>
@@ -32904,7 +32904,7 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>3290</v>
+        <v>3286</v>
       </c>
       <c r="B140">
         <v>66175393</v>
@@ -32938,7 +32938,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="C143" s="1" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -32982,7 +32982,7 @@
         <v>2306</v>
       </c>
       <c r="E153" s="30" t="s">
-        <v>3515</v>
+        <v>3511</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -32990,16 +32990,16 @@
         <v>1481</v>
       </c>
       <c r="B154" t="s">
-        <v>3047</v>
+        <v>3044</v>
       </c>
       <c r="C154" t="s">
         <v>2193</v>
       </c>
       <c r="D154" s="371" t="s">
-        <v>3046</v>
+        <v>3043</v>
       </c>
       <c r="E154" s="30" t="s">
-        <v>3515</v>
+        <v>3511</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -33016,12 +33016,12 @@
         <v>2521</v>
       </c>
       <c r="E155" s="30" t="s">
-        <v>3592</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" t="s">
-        <v>3185</v>
+        <v>3182</v>
       </c>
       <c r="B156">
         <v>63145336</v>
@@ -33030,10 +33030,10 @@
         <v>2202</v>
       </c>
       <c r="D156" s="371" t="s">
-        <v>3323</v>
+        <v>3319</v>
       </c>
       <c r="E156" s="30" t="s">
-        <v>3592</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -33050,12 +33050,12 @@
         <v>2430</v>
       </c>
       <c r="E157" s="30" t="s">
-        <v>3592</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" t="s">
-        <v>3264</v>
+        <v>3260</v>
       </c>
       <c r="B158">
         <v>64982293</v>
@@ -33064,10 +33064,10 @@
         <v>2204</v>
       </c>
       <c r="D158" s="371" t="s">
-        <v>3370</v>
+        <v>3366</v>
       </c>
       <c r="E158" s="30" t="s">
-        <v>3592</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -33081,10 +33081,10 @@
         <v>2447</v>
       </c>
       <c r="D159" s="371" t="s">
-        <v>3049</v>
+        <v>3046</v>
       </c>
       <c r="E159" s="30" t="s">
-        <v>3592</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -33101,12 +33101,12 @@
         <v>2448</v>
       </c>
       <c r="E160" s="30" t="s">
-        <v>3592</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="4" t="s">
-        <v>3533</v>
+        <v>3529</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>1132</v>
@@ -33118,7 +33118,7 @@
         <v>2876</v>
       </c>
       <c r="E161" s="30" t="s">
-        <v>3592</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -33135,24 +33135,24 @@
         <v>2940</v>
       </c>
       <c r="E162" s="30" t="s">
-        <v>3592</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" t="s">
-        <v>3185</v>
+        <v>3182</v>
       </c>
       <c r="B163">
         <v>67570116</v>
       </c>
       <c r="C163" t="s">
-        <v>3325</v>
+        <v>3321</v>
       </c>
       <c r="D163" s="371" t="s">
-        <v>3355</v>
+        <v>3351</v>
       </c>
       <c r="E163" s="30" t="s">
-        <v>3592</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -33169,12 +33169,12 @@
         <v>2431</v>
       </c>
       <c r="E164" s="30" t="s">
-        <v>3125</v>
+        <v>3122</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>3091</v>
+        <v>3088</v>
       </c>
       <c r="B165">
         <v>66315726</v>
@@ -33186,12 +33186,12 @@
         <v>2239</v>
       </c>
       <c r="E165" s="30" t="s">
-        <v>3125</v>
+        <v>3122</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="B166">
         <v>64568369</v>
@@ -33203,24 +33203,24 @@
         <v>2239</v>
       </c>
       <c r="E166" s="30" t="s">
-        <v>3125</v>
+        <v>3122</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>3091</v>
+        <v>3088</v>
       </c>
       <c r="B167">
         <v>68818154</v>
       </c>
       <c r="C167" t="s">
-        <v>3050</v>
+        <v>3047</v>
       </c>
       <c r="D167" s="371" t="s">
         <v>2523</v>
       </c>
       <c r="E167" s="30" t="s">
-        <v>3125</v>
+        <v>3122</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -33228,16 +33228,16 @@
         <v>1417</v>
       </c>
       <c r="B168" t="s">
-        <v>3559</v>
+        <v>3555</v>
       </c>
       <c r="C168" s="21" t="s">
         <v>2637</v>
       </c>
       <c r="D168" s="371" t="s">
-        <v>3558</v>
+        <v>3554</v>
       </c>
       <c r="E168" s="30" t="s">
-        <v>3352</v>
+        <v>3348</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -33254,7 +33254,7 @@
         <v>2669</v>
       </c>
       <c r="E169" s="30" t="s">
-        <v>3352</v>
+        <v>3348</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -33271,12 +33271,12 @@
         <v>2428</v>
       </c>
       <c r="E170" s="30" t="s">
-        <v>3352</v>
+        <v>3348</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" t="s">
-        <v>3537</v>
+        <v>3533</v>
       </c>
       <c r="B171">
         <v>69355525</v>
@@ -33288,7 +33288,7 @@
         <v>2273</v>
       </c>
       <c r="E171" s="30" t="s">
-        <v>3352</v>
+        <v>3348</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -33302,15 +33302,15 @@
         <v>2285</v>
       </c>
       <c r="D172" s="371" t="s">
-        <v>3493</v>
+        <v>3489</v>
       </c>
       <c r="E172" s="30" t="s">
-        <v>3408</v>
+        <v>3404</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" t="s">
-        <v>3290</v>
+        <v>3286</v>
       </c>
       <c r="B173">
         <v>64982293</v>
@@ -33319,10 +33319,10 @@
         <v>2286</v>
       </c>
       <c r="D173" s="371" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="E173" s="30" t="s">
-        <v>3408</v>
+        <v>3404</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -33336,15 +33336,15 @@
         <v>2287</v>
       </c>
       <c r="D174" s="371" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="E174" s="30" t="s">
-        <v>3408</v>
+        <v>3404</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" t="s">
-        <v>3268</v>
+        <v>3264</v>
       </c>
       <c r="B175">
         <v>67178677</v>
@@ -33353,15 +33353,15 @@
         <v>2671</v>
       </c>
       <c r="D175" s="371" t="s">
-        <v>3324</v>
+        <v>3320</v>
       </c>
       <c r="E175" s="30" t="s">
-        <v>3516</v>
+        <v>3512</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" t="s">
-        <v>3533</v>
+        <v>3529</v>
       </c>
       <c r="B176">
         <v>64881871</v>
@@ -33370,10 +33370,10 @@
         <v>2672</v>
       </c>
       <c r="D176" s="220" t="s">
-        <v>3675</v>
+        <v>3671</v>
       </c>
       <c r="E176" s="30" t="s">
-        <v>3516</v>
+        <v>3512</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -33387,15 +33387,15 @@
         <v>2941</v>
       </c>
       <c r="D177" s="220" t="s">
-        <v>3223</v>
+        <v>3219</v>
       </c>
       <c r="E177" s="30" t="s">
-        <v>3516</v>
+        <v>3512</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="4" t="s">
-        <v>3486</v>
+        <v>3482</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>1836</v>
@@ -33404,49 +33404,49 @@
         <v>2673</v>
       </c>
       <c r="D178" s="220" t="s">
-        <v>3659</v>
+        <v>3655</v>
       </c>
       <c r="E178" s="30" t="s">
-        <v>3516</v>
+        <v>3512</v>
       </c>
     </row>
     <row r="179" spans="1:5">
-      <c r="A179" s="49" t="s">
-        <v>2939</v>
-      </c>
-      <c r="B179">
-        <v>68570552</v>
+      <c r="A179" s="97" t="s">
+        <v>3579</v>
+      </c>
+      <c r="B179" t="s">
+        <v>1159</v>
       </c>
       <c r="C179" s="22" t="s">
         <v>2674</v>
       </c>
       <c r="D179" s="220" t="s">
-        <v>2982</v>
+        <v>3687</v>
       </c>
       <c r="E179" s="30" t="s">
-        <v>3516</v>
+        <v>3512</v>
       </c>
     </row>
     <row r="180" spans="1:5">
-      <c r="A180" s="49" t="s">
-        <v>2939</v>
-      </c>
-      <c r="B180">
-        <v>69964218</v>
+      <c r="A180" s="97" t="s">
+        <v>3579</v>
+      </c>
+      <c r="B180" t="s">
+        <v>1159</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>2692</v>
       </c>
       <c r="D180" s="371" t="s">
-        <v>2983</v>
+        <v>3688</v>
       </c>
       <c r="E180" s="30" t="s">
-        <v>3528</v>
+        <v>3524</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" t="s">
-        <v>3486</v>
+        <v>3482</v>
       </c>
       <c r="B181">
         <v>63950696</v>
@@ -33458,12 +33458,12 @@
         <v>2693</v>
       </c>
       <c r="E181" s="30" t="s">
-        <v>3528</v>
+        <v>3524</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="4" t="s">
-        <v>3486</v>
+        <v>3482</v>
       </c>
       <c r="B182" t="s">
         <v>2717</v>
@@ -33475,7 +33475,7 @@
         <v>2693</v>
       </c>
       <c r="E182" s="30" t="s">
-        <v>3528</v>
+        <v>3524</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -33492,7 +33492,7 @@
         <v>2754</v>
       </c>
       <c r="E183" s="30" t="s">
-        <v>3528</v>
+        <v>3524</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -33506,10 +33506,10 @@
         <v>2746</v>
       </c>
       <c r="D184" s="371" t="s">
-        <v>3262</v>
+        <v>3258</v>
       </c>
       <c r="E184" s="30" t="s">
-        <v>3528</v>
+        <v>3524</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -33517,15 +33517,15 @@
         <v>53</v>
       </c>
       <c r="D185" s="371" t="s">
-        <v>3342</v>
+        <v>3338</v>
       </c>
       <c r="E185" s="30" t="s">
-        <v>3630</v>
+        <v>3626</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" t="s">
-        <v>3141</v>
+        <v>3138</v>
       </c>
       <c r="B186">
         <v>60240509</v>
@@ -33534,15 +33534,15 @@
         <v>2719</v>
       </c>
       <c r="D186" s="371" t="s">
-        <v>3139</v>
+        <v>3136</v>
       </c>
       <c r="E186" s="30" t="s">
-        <v>3140</v>
+        <v>3137</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="A187" t="s">
-        <v>3583</v>
+        <v>3579</v>
       </c>
       <c r="B187">
         <v>64730396</v>
@@ -33551,10 +33551,10 @@
         <v>2720</v>
       </c>
       <c r="D187" s="371" t="s">
-        <v>3078</v>
+        <v>3075</v>
       </c>
       <c r="E187" s="30" t="s">
-        <v>3630</v>
+        <v>3626</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -33571,7 +33571,7 @@
         <v>2727</v>
       </c>
       <c r="E188" s="30" t="s">
-        <v>3630</v>
+        <v>3626</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -33588,12 +33588,12 @@
         <v>2727</v>
       </c>
       <c r="E189" s="30" t="s">
-        <v>3630</v>
+        <v>3626</v>
       </c>
     </row>
     <row r="190" spans="1:5">
       <c r="A190" t="s">
-        <v>3537</v>
+        <v>3533</v>
       </c>
       <c r="B190">
         <v>68726473</v>
@@ -33605,7 +33605,7 @@
         <v>2727</v>
       </c>
       <c r="E190" s="30" t="s">
-        <v>3630</v>
+        <v>3626</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -33616,7 +33616,7 @@
         <v>2727</v>
       </c>
       <c r="E191" s="30" t="s">
-        <v>3630</v>
+        <v>3626</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -33630,15 +33630,15 @@
         <v>2755</v>
       </c>
       <c r="D192" s="371" t="s">
-        <v>3368</v>
+        <v>3364</v>
       </c>
       <c r="E192" s="30" t="s">
-        <v>3630</v>
+        <v>3626</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="B193">
         <v>69575383</v>
@@ -33647,10 +33647,10 @@
         <v>2725</v>
       </c>
       <c r="D193" s="371" t="s">
-        <v>3294</v>
+        <v>3290</v>
       </c>
       <c r="E193" s="30" t="s">
-        <v>3630</v>
+        <v>3626</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -33664,10 +33664,10 @@
         <v>2726</v>
       </c>
       <c r="D194" s="371" t="s">
-        <v>3680</v>
+        <v>3676</v>
       </c>
       <c r="E194" s="30" t="s">
-        <v>3630</v>
+        <v>3626</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -33693,44 +33693,44 @@
         <v>2747</v>
       </c>
       <c r="D198" s="371" t="s">
-        <v>3077</v>
+        <v>3074</v>
       </c>
       <c r="E198" s="30" t="s">
-        <v>3631</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" t="s">
-        <v>3134</v>
+        <v>3131</v>
       </c>
       <c r="B199" t="s">
-        <v>3135</v>
+        <v>3132</v>
       </c>
       <c r="C199" t="s">
         <v>2740</v>
       </c>
       <c r="D199" s="371" t="s">
-        <v>3133</v>
+        <v>3130</v>
       </c>
       <c r="E199" s="30" t="s">
-        <v>3631</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" t="s">
-        <v>3533</v>
+        <v>3529</v>
       </c>
       <c r="B200">
         <v>63617941</v>
       </c>
       <c r="C200" s="22" t="s">
-        <v>2984</v>
+        <v>2981</v>
       </c>
       <c r="D200" s="371" t="s">
         <v>2791</v>
       </c>
       <c r="E200" s="30" t="s">
-        <v>3631</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -33744,10 +33744,10 @@
         <v>2741</v>
       </c>
       <c r="D201" s="371" t="s">
-        <v>3362</v>
+        <v>3358</v>
       </c>
       <c r="E201" s="30" t="s">
-        <v>3631</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -33761,10 +33761,10 @@
         <v>2742</v>
       </c>
       <c r="D202" s="371" t="s">
-        <v>3213</v>
+        <v>3209</v>
       </c>
       <c r="E202" s="30" t="s">
-        <v>3631</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -33778,10 +33778,10 @@
         <v>2790</v>
       </c>
       <c r="D203" s="371" t="s">
-        <v>3236</v>
+        <v>3232</v>
       </c>
       <c r="E203" s="30" t="s">
-        <v>3631</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -33789,16 +33789,16 @@
         <v>2920</v>
       </c>
       <c r="B204" t="s">
-        <v>3222</v>
+        <v>3218</v>
       </c>
       <c r="C204" t="s">
         <v>2743</v>
       </c>
       <c r="D204" s="371" t="s">
-        <v>3221</v>
+        <v>3217</v>
       </c>
       <c r="E204" s="30" t="s">
-        <v>3631</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -33809,13 +33809,13 @@
         <v>64982293</v>
       </c>
       <c r="C205" t="s">
-        <v>3212</v>
+        <v>3208</v>
       </c>
       <c r="D205" s="371" t="s">
-        <v>3288</v>
+        <v>3284</v>
       </c>
       <c r="E205" s="30" t="s">
-        <v>3631</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -33832,7 +33832,7 @@
         <v>2796</v>
       </c>
       <c r="E206" s="30" t="s">
-        <v>3631</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -33846,10 +33846,10 @@
         <v>2797</v>
       </c>
       <c r="D207" s="371" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="E207" s="30" t="s">
-        <v>3631</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -33866,7 +33866,7 @@
         <v>2811</v>
       </c>
       <c r="E208" s="30" t="s">
-        <v>3193</v>
+        <v>3190</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -33874,21 +33874,21 @@
         <v>2662</v>
       </c>
       <c r="B209" t="s">
-        <v>3502</v>
+        <v>3498</v>
       </c>
       <c r="C209" t="s">
         <v>2822</v>
       </c>
       <c r="D209" s="371" t="s">
-        <v>3410</v>
+        <v>3406</v>
       </c>
       <c r="E209" s="30" t="s">
-        <v>3193</v>
+        <v>3190</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210" t="s">
-        <v>3090</v>
+        <v>3087</v>
       </c>
       <c r="B210">
         <v>65574051</v>
@@ -33897,15 +33897,15 @@
         <v>2810</v>
       </c>
       <c r="D210" t="s">
-        <v>3351</v>
+        <v>3347</v>
       </c>
       <c r="E210" s="30" t="s">
-        <v>3193</v>
+        <v>3190</v>
       </c>
     </row>
     <row r="211" spans="1:5">
       <c r="A211" t="s">
-        <v>3260</v>
+        <v>3256</v>
       </c>
       <c r="B211">
         <v>64403333</v>
@@ -33914,15 +33914,15 @@
         <v>2823</v>
       </c>
       <c r="D211" s="371" t="s">
-        <v>3545</v>
+        <v>3541</v>
       </c>
       <c r="E211" s="30" t="s">
-        <v>3193</v>
+        <v>3190</v>
       </c>
     </row>
     <row r="212" spans="1:5">
       <c r="A212" t="s">
-        <v>3537</v>
+        <v>3533</v>
       </c>
       <c r="B212">
         <v>64957521</v>
@@ -33931,15 +33931,15 @@
         <v>2942</v>
       </c>
       <c r="D212" t="s">
-        <v>3662</v>
+        <v>3658</v>
       </c>
       <c r="E212" s="30" t="s">
-        <v>3193</v>
+        <v>3190</v>
       </c>
     </row>
     <row r="213" spans="1:5">
       <c r="A213" t="s">
-        <v>3533</v>
+        <v>3529</v>
       </c>
       <c r="B213">
         <v>68069608</v>
@@ -33948,10 +33948,10 @@
         <v>2847</v>
       </c>
       <c r="D213" s="371" t="s">
-        <v>3668</v>
+        <v>3664</v>
       </c>
       <c r="E213" s="30" t="s">
-        <v>3276</v>
+        <v>3272</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -33965,10 +33965,10 @@
         <v>2854</v>
       </c>
       <c r="D214" t="s">
-        <v>3417</v>
+        <v>3413</v>
       </c>
       <c r="E214" s="30" t="s">
-        <v>3276</v>
+        <v>3272</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -33976,16 +33976,16 @@
         <v>1421</v>
       </c>
       <c r="B215" t="s">
-        <v>3360</v>
+        <v>3356</v>
       </c>
       <c r="C215" s="22" t="s">
         <v>2855</v>
       </c>
       <c r="D215" t="s">
-        <v>3359</v>
+        <v>3355</v>
       </c>
       <c r="E215" s="30" t="s">
-        <v>3276</v>
+        <v>3272</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -34002,12 +34002,12 @@
         <v>2851</v>
       </c>
       <c r="E216" s="30" t="s">
-        <v>3276</v>
+        <v>3272</v>
       </c>
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="4" t="s">
-        <v>3537</v>
+        <v>3533</v>
       </c>
       <c r="B217">
         <v>64457890</v>
@@ -34019,7 +34019,7 @@
         <v>2857</v>
       </c>
       <c r="E217" s="30" t="s">
-        <v>3276</v>
+        <v>3272</v>
       </c>
     </row>
     <row r="231" spans="3:4">
@@ -36885,7 +36885,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="76" t="s">
-        <v>3304</v>
+        <v>3300</v>
       </c>
       <c r="B6" s="76">
         <v>64957521</v>
@@ -36900,7 +36900,7 @@
         <v>678</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>3639</v>
+        <v>3635</v>
       </c>
       <c r="G6" s="361" t="s">
         <v>1426</v>
@@ -36921,13 +36921,13 @@
         <v>1824</v>
       </c>
       <c r="D7" s="183" t="s">
-        <v>3382</v>
+        <v>3378</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F7" s="183" t="s">
-        <v>3639</v>
+        <v>3635</v>
       </c>
       <c r="G7" s="183" t="s">
         <v>1426</v>
@@ -36939,7 +36939,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="193" t="s">
-        <v>3486</v>
+        <v>3482</v>
       </c>
       <c r="B8" s="193">
         <v>62747874</v>
@@ -36954,7 +36954,7 @@
         <v>362</v>
       </c>
       <c r="F8" s="183" t="s">
-        <v>3639</v>
+        <v>3635</v>
       </c>
       <c r="G8" s="183" t="s">
         <v>1426</v>
@@ -36973,7 +36973,7 @@
         <v>362</v>
       </c>
       <c r="F9" s="183" t="s">
-        <v>3639</v>
+        <v>3635</v>
       </c>
       <c r="G9" s="183" t="s">
         <v>1426</v>
@@ -37000,7 +37000,7 @@
         <v>362</v>
       </c>
       <c r="F10" s="183" t="s">
-        <v>3639</v>
+        <v>3635</v>
       </c>
       <c r="G10" s="183" t="s">
         <v>1426</v>
@@ -37027,7 +37027,7 @@
         <v>362</v>
       </c>
       <c r="F11" s="183" t="s">
-        <v>3639</v>
+        <v>3635</v>
       </c>
       <c r="G11" s="183" t="s">
         <v>1426</v>
@@ -37051,7 +37051,7 @@
         <v>2455</v>
       </c>
       <c r="E13" s="195" t="s">
-        <v>3640</v>
+        <v>3636</v>
       </c>
       <c r="F13" s="195" t="s">
         <v>1415</v>
@@ -37077,7 +37077,7 @@
         <v>1825</v>
       </c>
       <c r="E14" s="193" t="s">
-        <v>3640</v>
+        <v>3636</v>
       </c>
       <c r="F14" s="193" t="s">
         <v>1415</v>
@@ -37103,7 +37103,7 @@
         <v>2699</v>
       </c>
       <c r="E15" s="193" t="s">
-        <v>3640</v>
+        <v>3636</v>
       </c>
       <c r="F15" s="193" t="s">
         <v>1415</v>
@@ -37129,7 +37129,7 @@
         <v>2276</v>
       </c>
       <c r="E16" s="193" t="s">
-        <v>3640</v>
+        <v>3636</v>
       </c>
       <c r="F16" s="193" t="s">
         <v>1415</v>
@@ -37143,7 +37143,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="193" t="s">
-        <v>3176</v>
+        <v>3173</v>
       </c>
       <c r="B17" s="193">
         <v>64403333</v>
@@ -37155,7 +37155,7 @@
         <v>1490</v>
       </c>
       <c r="E17" s="193" t="s">
-        <v>3640</v>
+        <v>3636</v>
       </c>
       <c r="F17" s="193" t="s">
         <v>1415</v>
@@ -37181,7 +37181,7 @@
         <v>2128</v>
       </c>
       <c r="E18" s="193" t="s">
-        <v>3640</v>
+        <v>3636</v>
       </c>
       <c r="F18" s="193" t="s">
         <v>1415</v>
@@ -37195,7 +37195,7 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="195" t="s">
-        <v>3304</v>
+        <v>3300</v>
       </c>
       <c r="B20" s="195">
         <v>67539485</v>
@@ -37210,7 +37210,7 @@
         <v>362</v>
       </c>
       <c r="F20" s="195" t="s">
-        <v>3640</v>
+        <v>3636</v>
       </c>
       <c r="G20" s="76" t="s">
         <v>422</v>
@@ -37239,7 +37239,7 @@
         <v>362</v>
       </c>
       <c r="F21" s="193" t="s">
-        <v>3640</v>
+        <v>3636</v>
       </c>
       <c r="G21" s="183" t="s">
         <v>422</v>
@@ -37268,7 +37268,7 @@
         <v>362</v>
       </c>
       <c r="F22" s="193" t="s">
-        <v>3640</v>
+        <v>3636</v>
       </c>
       <c r="G22" s="183" t="s">
         <v>422</v>
@@ -37282,7 +37282,7 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="183" t="s">
-        <v>3519</v>
+        <v>3515</v>
       </c>
       <c r="B23" s="183">
         <v>60389752</v>
@@ -37297,7 +37297,7 @@
         <v>362</v>
       </c>
       <c r="F23" s="193" t="s">
-        <v>3640</v>
+        <v>3636</v>
       </c>
       <c r="G23" s="183" t="s">
         <v>422</v>
@@ -37311,7 +37311,7 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="193" t="s">
-        <v>3290</v>
+        <v>3286</v>
       </c>
       <c r="B24" s="193">
         <v>69291416</v>
@@ -37326,7 +37326,7 @@
         <v>362</v>
       </c>
       <c r="F24" s="193" t="s">
-        <v>3640</v>
+        <v>3636</v>
       </c>
       <c r="G24" s="183" t="s">
         <v>422</v>
@@ -37355,7 +37355,7 @@
         <v>362</v>
       </c>
       <c r="F25" s="193" t="s">
-        <v>3640</v>
+        <v>3636</v>
       </c>
       <c r="G25" s="183" t="s">
         <v>422</v>
@@ -37384,7 +37384,7 @@
         <v>362</v>
       </c>
       <c r="F27" s="76" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="G27" s="76" t="s">
         <v>1427</v>
@@ -37411,7 +37411,7 @@
         <v>362</v>
       </c>
       <c r="F28" s="183" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="G28" s="183" t="s">
         <v>378</v>
@@ -37425,22 +37425,22 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="183" t="s">
-        <v>3161</v>
+        <v>3158</v>
       </c>
       <c r="B29" s="183">
         <v>65234700</v>
       </c>
       <c r="C29" s="194" t="s">
-        <v>3085</v>
+        <v>3082</v>
       </c>
       <c r="D29" s="183" t="s">
-        <v>3086</v>
+        <v>3083</v>
       </c>
       <c r="E29" s="429">
         <v>46243</v>
       </c>
       <c r="F29" s="183" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="G29" s="183" t="s">
         <v>378</v>
@@ -37454,7 +37454,7 @@
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="183" t="s">
-        <v>2985</v>
+        <v>2982</v>
       </c>
       <c r="B30" s="183">
         <v>68241069</v>
@@ -37469,7 +37469,7 @@
         <v>362</v>
       </c>
       <c r="F30" s="183" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="G30" s="183" t="s">
         <v>378</v>
@@ -37483,7 +37483,7 @@
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="193" t="s">
-        <v>3260</v>
+        <v>3256</v>
       </c>
       <c r="B31" s="193" t="s">
         <v>2422</v>
@@ -37498,7 +37498,7 @@
         <v>362</v>
       </c>
       <c r="F31" s="183" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="G31" s="183" t="s">
         <v>378</v>
@@ -37512,7 +37512,7 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="183" t="s">
-        <v>3533</v>
+        <v>3529</v>
       </c>
       <c r="B32" s="183">
         <v>68241069</v>
@@ -37527,7 +37527,7 @@
         <v>362</v>
       </c>
       <c r="F32" s="183" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="G32" s="183" t="s">
         <v>378</v>
@@ -37541,7 +37541,7 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="195" t="s">
-        <v>3185</v>
+        <v>3182</v>
       </c>
       <c r="B34" s="195">
         <v>66466729</v>
@@ -37550,13 +37550,13 @@
         <v>1645</v>
       </c>
       <c r="D34" s="195" t="s">
-        <v>3240</v>
+        <v>3236</v>
       </c>
       <c r="E34" s="76" t="s">
         <v>2426</v>
       </c>
       <c r="F34" s="195" t="s">
-        <v>3138</v>
+        <v>3135</v>
       </c>
       <c r="G34" s="76" t="s">
         <v>1426</v>
@@ -37582,7 +37582,7 @@
         <v>2426</v>
       </c>
       <c r="F35" s="193" t="s">
-        <v>3138</v>
+        <v>3135</v>
       </c>
       <c r="G35" s="183" t="s">
         <v>1426</v>
@@ -37608,7 +37608,7 @@
         <v>2426</v>
       </c>
       <c r="F36" s="193" t="s">
-        <v>3138</v>
+        <v>3135</v>
       </c>
       <c r="G36" s="183" t="s">
         <v>1426</v>
@@ -37619,7 +37619,7 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="193" t="s">
-        <v>3116</v>
+        <v>3113</v>
       </c>
       <c r="B37" s="193">
         <v>69111188</v>
@@ -37634,7 +37634,7 @@
         <v>2426</v>
       </c>
       <c r="F37" s="193" t="s">
-        <v>3138</v>
+        <v>3135</v>
       </c>
       <c r="G37" s="183" t="s">
         <v>1426</v>
@@ -37654,13 +37654,13 @@
         <v>1313</v>
       </c>
       <c r="D38" s="193" t="s">
-        <v>3660</v>
+        <v>3656</v>
       </c>
       <c r="E38" s="183" t="s">
         <v>2426</v>
       </c>
       <c r="F38" s="193" t="s">
-        <v>3138</v>
+        <v>3135</v>
       </c>
       <c r="G38" s="183" t="s">
         <v>1426</v>
@@ -37686,7 +37686,7 @@
         <v>2426</v>
       </c>
       <c r="F39" s="193" t="s">
-        <v>3138</v>
+        <v>3135</v>
       </c>
       <c r="G39" s="183" t="s">
         <v>1426</v>
@@ -37699,16 +37699,16 @@
       <c r="A41" s="195"/>
       <c r="B41" s="195"/>
       <c r="C41" s="195" t="s">
-        <v>3129</v>
+        <v>3126</v>
       </c>
       <c r="D41" s="195" t="s">
-        <v>3130</v>
+        <v>3127</v>
       </c>
       <c r="E41" s="76" t="s">
         <v>362</v>
       </c>
       <c r="F41" s="195" t="s">
-        <v>3131</v>
+        <v>3128</v>
       </c>
       <c r="G41" s="76" t="s">
         <v>2328</v>
@@ -37728,7 +37728,7 @@
         <v>69563253</v>
       </c>
       <c r="C42" s="193" t="s">
-        <v>3132</v>
+        <v>3129</v>
       </c>
       <c r="D42" s="193" t="s">
         <v>1657</v>
@@ -37748,10 +37748,10 @@
         <v>1919</v>
       </c>
       <c r="C43" s="194" t="s">
-        <v>3111</v>
+        <v>3108</v>
       </c>
       <c r="D43" s="193" t="s">
-        <v>3112</v>
+        <v>3109</v>
       </c>
       <c r="E43" s="429">
         <v>46304</v>
@@ -37768,7 +37768,7 @@
         <v>62751201</v>
       </c>
       <c r="C44" s="194" t="s">
-        <v>3136</v>
+        <v>3133</v>
       </c>
       <c r="D44" s="183" t="s">
         <v>1348</v>
@@ -37788,10 +37788,10 @@
         <v>68030850</v>
       </c>
       <c r="C45" s="193" t="s">
-        <v>3114</v>
+        <v>3111</v>
       </c>
       <c r="D45" s="193" t="s">
-        <v>3115</v>
+        <v>3112</v>
       </c>
       <c r="E45" s="429">
         <v>46243</v>
@@ -37824,16 +37824,16 @@
       <c r="A48" s="195"/>
       <c r="B48" s="195"/>
       <c r="C48" s="195" t="s">
+        <v>3160</v>
+      </c>
+      <c r="D48" s="195" t="s">
+        <v>3161</v>
+      </c>
+      <c r="E48" s="76" t="s">
+        <v>3162</v>
+      </c>
+      <c r="F48" s="195" t="s">
         <v>3163</v>
-      </c>
-      <c r="D48" s="195" t="s">
-        <v>3164</v>
-      </c>
-      <c r="E48" s="76" t="s">
-        <v>3165</v>
-      </c>
-      <c r="F48" s="195" t="s">
-        <v>3166</v>
       </c>
       <c r="G48" s="76" t="s">
         <v>1426</v>
@@ -37844,7 +37844,7 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="183" t="s">
-        <v>3583</v>
+        <v>3579</v>
       </c>
       <c r="B49" s="183">
         <v>68361109</v>
@@ -37870,10 +37870,10 @@
         <v>61548403</v>
       </c>
       <c r="C50" s="194" t="s">
-        <v>3167</v>
+        <v>3164</v>
       </c>
       <c r="D50" s="193" t="s">
-        <v>3168</v>
+        <v>3165</v>
       </c>
       <c r="E50" s="429">
         <v>46304</v>
@@ -37904,13 +37904,13 @@
         <v>1644</v>
       </c>
       <c r="D55" s="195" t="s">
-        <v>3383</v>
+        <v>3379</v>
       </c>
       <c r="E55" s="76" t="s">
         <v>2426</v>
       </c>
       <c r="F55" s="195" t="s">
-        <v>3170</v>
+        <v>3167</v>
       </c>
       <c r="G55" s="76" t="s">
         <v>1426</v>
@@ -37921,7 +37921,7 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="193" t="s">
-        <v>3260</v>
+        <v>3256</v>
       </c>
       <c r="B56" s="193">
         <v>69624389</v>
@@ -37936,7 +37936,7 @@
         <v>2426</v>
       </c>
       <c r="F56" s="193" t="s">
-        <v>3170</v>
+        <v>3167</v>
       </c>
       <c r="G56" s="183" t="s">
         <v>1426</v>
@@ -37947,7 +37947,7 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="193" t="s">
-        <v>3537</v>
+        <v>3533</v>
       </c>
       <c r="B57" s="193">
         <v>68658411</v>
@@ -37956,13 +37956,13 @@
         <v>2534</v>
       </c>
       <c r="D57" s="193" t="s">
-        <v>3663</v>
+        <v>3659</v>
       </c>
       <c r="E57" s="183" t="s">
         <v>2426</v>
       </c>
       <c r="F57" s="193" t="s">
-        <v>3170</v>
+        <v>3167</v>
       </c>
       <c r="G57" s="183" t="s">
         <v>1426</v>
@@ -37988,7 +37988,7 @@
         <v>2426</v>
       </c>
       <c r="F58" s="193" t="s">
-        <v>3170</v>
+        <v>3167</v>
       </c>
       <c r="G58" s="183" t="s">
         <v>1426</v>
@@ -38014,7 +38014,7 @@
         <v>2426</v>
       </c>
       <c r="F59" s="193" t="s">
-        <v>3170</v>
+        <v>3167</v>
       </c>
       <c r="G59" s="183" t="s">
         <v>1426</v>
@@ -38025,22 +38025,22 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="183" t="s">
-        <v>3264</v>
+        <v>3260</v>
       </c>
       <c r="B60" s="183">
         <v>63247837</v>
       </c>
       <c r="C60" s="193" t="s">
-        <v>3011</v>
+        <v>3008</v>
       </c>
       <c r="D60" s="193" t="s">
-        <v>3384</v>
+        <v>3380</v>
       </c>
       <c r="E60" s="183" t="s">
         <v>2426</v>
       </c>
       <c r="F60" s="193" t="s">
-        <v>3170</v>
+        <v>3167</v>
       </c>
       <c r="G60" s="183" t="s">
         <v>1426</v>
@@ -38051,7 +38051,7 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="195" t="s">
-        <v>3260</v>
+        <v>3256</v>
       </c>
       <c r="B62" s="195">
         <v>68259581</v>
@@ -38060,13 +38060,13 @@
         <v>1641</v>
       </c>
       <c r="D62" s="195" t="s">
-        <v>3532</v>
+        <v>3528</v>
       </c>
       <c r="E62" s="76" t="s">
         <v>2426</v>
       </c>
       <c r="F62" s="195" t="s">
-        <v>3170</v>
+        <v>3167</v>
       </c>
       <c r="G62" s="76" t="s">
         <v>1426</v>
@@ -38092,7 +38092,7 @@
         <v>2426</v>
       </c>
       <c r="F63" s="193" t="s">
-        <v>3170</v>
+        <v>3167</v>
       </c>
       <c r="G63" s="183" t="s">
         <v>1426</v>
@@ -38103,7 +38103,7 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="183" t="s">
-        <v>3091</v>
+        <v>3088</v>
       </c>
       <c r="B64" s="183">
         <v>64403333</v>
@@ -38118,7 +38118,7 @@
         <v>2426</v>
       </c>
       <c r="F64" s="193" t="s">
-        <v>3170</v>
+        <v>3167</v>
       </c>
       <c r="G64" s="183" t="s">
         <v>1426</v>
@@ -38129,7 +38129,7 @@
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="193" t="s">
-        <v>2985</v>
+        <v>2982</v>
       </c>
       <c r="B65" s="193">
         <v>68030850</v>
@@ -38144,7 +38144,7 @@
         <v>2426</v>
       </c>
       <c r="F65" s="193" t="s">
-        <v>3170</v>
+        <v>3167</v>
       </c>
       <c r="G65" s="183" t="s">
         <v>1426</v>
@@ -38155,7 +38155,7 @@
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="183" t="s">
-        <v>3180</v>
+        <v>3177</v>
       </c>
       <c r="B66" s="183">
         <v>65003516</v>
@@ -38170,7 +38170,7 @@
         <v>2426</v>
       </c>
       <c r="F66" s="193" t="s">
-        <v>3170</v>
+        <v>3167</v>
       </c>
       <c r="G66" s="183" t="s">
         <v>1426</v>
@@ -38196,7 +38196,7 @@
         <v>2426</v>
       </c>
       <c r="F67" s="193" t="s">
-        <v>3170</v>
+        <v>3167</v>
       </c>
       <c r="G67" s="183" t="s">
         <v>1426</v>
@@ -38216,10 +38216,10 @@
         <v>2584</v>
       </c>
       <c r="D69" s="195" t="s">
-        <v>3461</v>
+        <v>3457</v>
       </c>
       <c r="E69" s="76" t="s">
-        <v>3216</v>
+        <v>3212</v>
       </c>
       <c r="F69" s="195" t="s">
         <v>2393</v>
@@ -38245,7 +38245,7 @@
         <v>2397</v>
       </c>
       <c r="E70" s="183" t="s">
-        <v>3216</v>
+        <v>3212</v>
       </c>
       <c r="F70" s="193" t="s">
         <v>2393</v>
@@ -38271,7 +38271,7 @@
         <v>2252</v>
       </c>
       <c r="E71" s="183" t="s">
-        <v>3216</v>
+        <v>3212</v>
       </c>
       <c r="F71" s="193" t="s">
         <v>2393</v>
@@ -38297,7 +38297,7 @@
         <v>2658</v>
       </c>
       <c r="E72" s="183" t="s">
-        <v>3216</v>
+        <v>3212</v>
       </c>
       <c r="F72" s="183" t="s">
         <v>2393</v>
@@ -38324,7 +38324,7 @@
         <v>2028</v>
       </c>
       <c r="E73" s="183" t="s">
-        <v>3216</v>
+        <v>3212</v>
       </c>
       <c r="F73" s="183" t="s">
         <v>2393</v>
@@ -38348,10 +38348,10 @@
         <v>732</v>
       </c>
       <c r="D74" s="183" t="s">
-        <v>3547</v>
+        <v>3543</v>
       </c>
       <c r="E74" s="183" t="s">
-        <v>3216</v>
+        <v>3212</v>
       </c>
       <c r="F74" s="183" t="s">
         <v>2393</v>
@@ -38378,7 +38378,7 @@
         <v>1704</v>
       </c>
       <c r="E76" s="76" t="s">
-        <v>3216</v>
+        <v>3212</v>
       </c>
       <c r="F76" s="195" t="s">
         <v>2392</v>
@@ -38402,7 +38402,7 @@
         <v>2289</v>
       </c>
       <c r="E77" s="183" t="s">
-        <v>3216</v>
+        <v>3212</v>
       </c>
       <c r="F77" s="193" t="s">
         <v>2392</v>
@@ -38414,7 +38414,7 @@
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="183" t="s">
-        <v>3290</v>
+        <v>3286</v>
       </c>
       <c r="B78" s="183">
         <v>62874575</v>
@@ -38426,7 +38426,7 @@
         <v>1230</v>
       </c>
       <c r="E78" s="183" t="s">
-        <v>3216</v>
+        <v>3212</v>
       </c>
       <c r="F78" s="193" t="s">
         <v>2392</v>
@@ -38438,7 +38438,7 @@
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="183" t="s">
-        <v>3290</v>
+        <v>3286</v>
       </c>
       <c r="B79" s="183">
         <v>62820256</v>
@@ -38450,7 +38450,7 @@
         <v>2311</v>
       </c>
       <c r="E79" s="183" t="s">
-        <v>3216</v>
+        <v>3212</v>
       </c>
       <c r="F79" s="193" t="s">
         <v>2392</v>
@@ -38468,13 +38468,13 @@
         <v>69563253</v>
       </c>
       <c r="C80" s="194" t="s">
-        <v>3217</v>
+        <v>3213</v>
       </c>
       <c r="D80" s="183" t="s">
         <v>1002</v>
       </c>
       <c r="E80" s="183" t="s">
-        <v>3218</v>
+        <v>3214</v>
       </c>
       <c r="F80" s="193" t="s">
         <v>2392</v>
@@ -38486,7 +38486,7 @@
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="183" t="s">
-        <v>3244</v>
+        <v>3240</v>
       </c>
       <c r="B81" s="183">
         <v>63233935</v>
@@ -38495,10 +38495,10 @@
         <v>2330</v>
       </c>
       <c r="D81" s="183" t="s">
-        <v>3241</v>
+        <v>3237</v>
       </c>
       <c r="E81" s="183" t="s">
-        <v>3216</v>
+        <v>3212</v>
       </c>
       <c r="F81" s="193" t="s">
         <v>2392</v>
@@ -38510,7 +38510,7 @@
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="49" t="s">
-        <v>2991</v>
+        <v>2988</v>
       </c>
       <c r="B83" s="76">
         <v>63574980</v>
@@ -38525,7 +38525,7 @@
         <v>1336</v>
       </c>
       <c r="F83" s="195" t="s">
-        <v>3282</v>
+        <v>3278</v>
       </c>
       <c r="G83" s="76" t="s">
         <v>1426</v>
@@ -38552,7 +38552,7 @@
         <v>1336</v>
       </c>
       <c r="F84" s="183" t="s">
-        <v>3282</v>
+        <v>3278</v>
       </c>
       <c r="G84" s="183" t="s">
         <v>1426</v>
@@ -38579,7 +38579,7 @@
         <v>1336</v>
       </c>
       <c r="F85" s="183" t="s">
-        <v>3282</v>
+        <v>3278</v>
       </c>
       <c r="G85" s="183" t="s">
         <v>1426</v>
@@ -38606,7 +38606,7 @@
         <v>1336</v>
       </c>
       <c r="F86" s="183" t="s">
-        <v>3282</v>
+        <v>3278</v>
       </c>
       <c r="G86" s="183" t="s">
         <v>1426</v>
@@ -38618,7 +38618,7 @@
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="183" t="s">
-        <v>3486</v>
+        <v>3482</v>
       </c>
       <c r="B87" s="183">
         <v>69904406</v>
@@ -38627,13 +38627,13 @@
         <v>2589</v>
       </c>
       <c r="D87" s="183" t="s">
-        <v>2987</v>
+        <v>2984</v>
       </c>
       <c r="E87" s="183" t="s">
         <v>1336</v>
       </c>
       <c r="F87" s="183" t="s">
-        <v>3282</v>
+        <v>3278</v>
       </c>
       <c r="G87" s="183" t="s">
         <v>1426</v>
@@ -38645,7 +38645,7 @@
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="183" t="s">
-        <v>3264</v>
+        <v>3260</v>
       </c>
       <c r="B88" s="183" t="s">
         <v>2606</v>
@@ -38660,7 +38660,7 @@
         <v>1336</v>
       </c>
       <c r="F88" s="183" t="s">
-        <v>3282</v>
+        <v>3278</v>
       </c>
       <c r="G88" s="183" t="s">
         <v>1426</v>
@@ -38687,7 +38687,7 @@
         <v>1634</v>
       </c>
       <c r="F90" s="195" t="s">
-        <v>3283</v>
+        <v>3279</v>
       </c>
       <c r="G90" s="76" t="s">
         <v>1426</v>
@@ -38711,7 +38711,7 @@
         <v>1634</v>
       </c>
       <c r="F91" s="193" t="s">
-        <v>3283</v>
+        <v>3279</v>
       </c>
       <c r="G91" s="183" t="s">
         <v>1426</v>
@@ -38720,7 +38720,7 @@
     </row>
     <row r="92" spans="1:9">
       <c r="A92" s="183" t="s">
-        <v>3344</v>
+        <v>3340</v>
       </c>
       <c r="B92" s="183">
         <v>65014102</v>
@@ -38735,7 +38735,7 @@
         <v>1634</v>
       </c>
       <c r="F92" s="193" t="s">
-        <v>3283</v>
+        <v>3279</v>
       </c>
       <c r="G92" s="183" t="s">
         <v>1426</v>
@@ -38744,7 +38744,7 @@
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="183" t="s">
-        <v>3185</v>
+        <v>3182</v>
       </c>
       <c r="B93" s="183">
         <v>68259581</v>
@@ -38759,7 +38759,7 @@
         <v>1634</v>
       </c>
       <c r="F93" s="193" t="s">
-        <v>3283</v>
+        <v>3279</v>
       </c>
       <c r="G93" s="183" t="s">
         <v>1426</v>
@@ -38783,7 +38783,7 @@
         <v>1634</v>
       </c>
       <c r="F94" s="193" t="s">
-        <v>3283</v>
+        <v>3279</v>
       </c>
       <c r="G94" s="183" t="s">
         <v>1426</v>
@@ -38807,7 +38807,7 @@
         <v>1634</v>
       </c>
       <c r="F95" s="193" t="s">
-        <v>3283</v>
+        <v>3279</v>
       </c>
       <c r="G95" s="183" t="s">
         <v>1426</v>
@@ -38816,7 +38816,7 @@
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="195" t="s">
-        <v>3152</v>
+        <v>3149</v>
       </c>
       <c r="B97" s="195">
         <v>64476521</v>
@@ -38831,7 +38831,7 @@
         <v>2426</v>
       </c>
       <c r="F97" s="195" t="s">
-        <v>3305</v>
+        <v>3301</v>
       </c>
       <c r="G97" s="76" t="s">
         <v>1426</v>
@@ -38842,7 +38842,7 @@
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="193" t="s">
-        <v>3053</v>
+        <v>3050</v>
       </c>
       <c r="B98" s="193">
         <v>60389752</v>
@@ -38851,13 +38851,13 @@
         <v>2570</v>
       </c>
       <c r="D98" s="193" t="s">
-        <v>3052</v>
+        <v>3049</v>
       </c>
       <c r="E98" s="183" t="s">
         <v>2426</v>
       </c>
       <c r="F98" s="193" t="s">
-        <v>3305</v>
+        <v>3301</v>
       </c>
       <c r="G98" s="183" t="s">
         <v>1426</v>
@@ -38868,7 +38868,7 @@
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="183" t="s">
-        <v>3260</v>
+        <v>3256</v>
       </c>
       <c r="B99" s="183">
         <v>60389752</v>
@@ -38883,7 +38883,7 @@
         <v>2426</v>
       </c>
       <c r="F99" s="193" t="s">
-        <v>3305</v>
+        <v>3301</v>
       </c>
       <c r="G99" s="183" t="s">
         <v>1426</v>
@@ -38909,7 +38909,7 @@
         <v>2426</v>
       </c>
       <c r="F100" s="193" t="s">
-        <v>3305</v>
+        <v>3301</v>
       </c>
       <c r="G100" s="183" t="s">
         <v>1426</v>
@@ -38935,7 +38935,7 @@
         <v>2426</v>
       </c>
       <c r="F101" s="193" t="s">
-        <v>3305</v>
+        <v>3301</v>
       </c>
       <c r="G101" s="183" t="s">
         <v>1426</v>
@@ -38955,13 +38955,13 @@
         <v>2250</v>
       </c>
       <c r="D102" s="193" t="s">
-        <v>2990</v>
+        <v>2987</v>
       </c>
       <c r="E102" s="183" t="s">
         <v>2426</v>
       </c>
       <c r="F102" s="193" t="s">
-        <v>3305</v>
+        <v>3301</v>
       </c>
       <c r="G102" s="183" t="s">
         <v>1426</v>
@@ -38984,7 +38984,7 @@
         <v>2258</v>
       </c>
       <c r="E104" s="76" t="s">
-        <v>3305</v>
+        <v>3301</v>
       </c>
       <c r="F104" s="195" t="s">
         <v>422</v>
@@ -38998,7 +38998,7 @@
     </row>
     <row r="105" spans="1:9">
       <c r="A105" s="193" t="s">
-        <v>3304</v>
+        <v>3300</v>
       </c>
       <c r="B105" s="193" t="s">
         <v>2626</v>
@@ -39010,7 +39010,7 @@
         <v>2263</v>
       </c>
       <c r="E105" s="183" t="s">
-        <v>3305</v>
+        <v>3301</v>
       </c>
       <c r="F105" s="193" t="s">
         <v>422</v>
@@ -39024,7 +39024,7 @@
     </row>
     <row r="106" spans="1:9">
       <c r="A106" s="193" t="s">
-        <v>3003</v>
+        <v>3000</v>
       </c>
       <c r="B106" s="193">
         <v>62723048</v>
@@ -39033,10 +39033,10 @@
         <v>2264</v>
       </c>
       <c r="D106" s="193" t="s">
-        <v>3002</v>
+        <v>2999</v>
       </c>
       <c r="E106" s="183" t="s">
-        <v>3305</v>
+        <v>3301</v>
       </c>
       <c r="F106" s="193" t="s">
         <v>422</v>
@@ -39059,10 +39059,10 @@
         <v>2808</v>
       </c>
       <c r="D107" s="193" t="s">
-        <v>3546</v>
+        <v>3542</v>
       </c>
       <c r="E107" s="183" t="s">
-        <v>3305</v>
+        <v>3301</v>
       </c>
       <c r="F107" s="193" t="s">
         <v>422</v>
@@ -39076,7 +39076,7 @@
     </row>
     <row r="108" spans="1:9">
       <c r="A108" s="193" t="s">
-        <v>3185</v>
+        <v>3182</v>
       </c>
       <c r="B108" s="193">
         <v>65353736</v>
@@ -39088,7 +39088,7 @@
         <v>2267</v>
       </c>
       <c r="E108" s="183" t="s">
-        <v>3305</v>
+        <v>3301</v>
       </c>
       <c r="F108" s="193" t="s">
         <v>422</v>
@@ -39114,7 +39114,7 @@
         <v>2814</v>
       </c>
       <c r="E109" s="183" t="s">
-        <v>3305</v>
+        <v>3301</v>
       </c>
       <c r="F109" s="193" t="s">
         <v>422</v>
@@ -39128,7 +39128,7 @@
     </row>
     <row r="111" spans="1:9">
       <c r="A111" s="195" t="s">
-        <v>3185</v>
+        <v>3182</v>
       </c>
       <c r="B111" s="195">
         <v>68310153</v>
@@ -39143,7 +39143,7 @@
         <v>362</v>
       </c>
       <c r="F111" s="195" t="s">
-        <v>3337</v>
+        <v>3333</v>
       </c>
       <c r="G111" s="76" t="s">
         <v>1336</v>
@@ -39170,7 +39170,7 @@
         <v>362</v>
       </c>
       <c r="F112" s="193" t="s">
-        <v>3337</v>
+        <v>3333</v>
       </c>
       <c r="G112" s="183" t="s">
         <v>1336</v>
@@ -39199,7 +39199,7 @@
         <v>2426</v>
       </c>
       <c r="F113" s="193" t="s">
-        <v>3337</v>
+        <v>3333</v>
       </c>
       <c r="G113" s="183" t="s">
         <v>1336</v>
@@ -39219,16 +39219,16 @@
         <v>62360487</v>
       </c>
       <c r="C114" s="194" t="s">
-        <v>3012</v>
+        <v>3009</v>
       </c>
       <c r="D114" s="183" t="s">
-        <v>3013</v>
+        <v>3010</v>
       </c>
       <c r="E114" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F114" s="193" t="s">
-        <v>3337</v>
+        <v>3333</v>
       </c>
       <c r="G114" s="183" t="s">
         <v>1336</v>
@@ -39248,16 +39248,16 @@
         <v>62085821</v>
       </c>
       <c r="C115" s="193" t="s">
-        <v>3014</v>
+        <v>3011</v>
       </c>
       <c r="D115" s="193" t="s">
-        <v>3015</v>
+        <v>3012</v>
       </c>
       <c r="E115" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F115" s="193" t="s">
-        <v>3337</v>
+        <v>3333</v>
       </c>
       <c r="G115" s="183" t="s">
         <v>1336</v>
@@ -39271,22 +39271,22 @@
     </row>
     <row r="116" spans="1:9">
       <c r="A116" s="193" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="B116" s="193">
         <v>64403333</v>
       </c>
       <c r="C116" s="193" t="s">
-        <v>3016</v>
+        <v>3013</v>
       </c>
       <c r="D116" s="193" t="s">
-        <v>3017</v>
+        <v>3014</v>
       </c>
       <c r="E116" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F116" s="193" t="s">
-        <v>3337</v>
+        <v>3333</v>
       </c>
       <c r="G116" s="183" t="s">
         <v>1336</v>
@@ -39306,7 +39306,7 @@
     </row>
     <row r="118" spans="1:9">
       <c r="A118" s="195" t="s">
-        <v>3344</v>
+        <v>3340</v>
       </c>
       <c r="B118" s="76">
         <v>60389752</v>
@@ -39318,7 +39318,7 @@
         <v>2280</v>
       </c>
       <c r="E118" s="76" t="s">
-        <v>3425</v>
+        <v>3421</v>
       </c>
       <c r="F118" s="76" t="s">
         <v>422</v>
@@ -39345,7 +39345,7 @@
         <v>2282</v>
       </c>
       <c r="E119" s="183" t="s">
-        <v>3425</v>
+        <v>3421</v>
       </c>
       <c r="F119" s="193" t="s">
         <v>422</v>
@@ -39359,7 +39359,7 @@
     </row>
     <row r="120" spans="1:9">
       <c r="A120" s="193" t="s">
-        <v>3344</v>
+        <v>3340</v>
       </c>
       <c r="B120" s="193">
         <v>60389752</v>
@@ -39371,7 +39371,7 @@
         <v>2284</v>
       </c>
       <c r="E120" s="183" t="s">
-        <v>3425</v>
+        <v>3421</v>
       </c>
       <c r="F120" s="193" t="s">
         <v>422</v>
@@ -39385,19 +39385,19 @@
     </row>
     <row r="121" spans="1:9">
       <c r="A121" s="183" t="s">
-        <v>3089</v>
+        <v>3086</v>
       </c>
       <c r="B121" s="183">
         <v>64403333</v>
       </c>
       <c r="C121" s="183" t="s">
-        <v>3018</v>
+        <v>3015</v>
       </c>
       <c r="D121" s="183" t="s">
-        <v>3019</v>
+        <v>3016</v>
       </c>
       <c r="E121" s="183" t="s">
-        <v>3425</v>
+        <v>3421</v>
       </c>
       <c r="F121" s="193" t="s">
         <v>422</v>
@@ -39411,7 +39411,7 @@
     </row>
     <row r="122" spans="1:9">
       <c r="A122" s="193" t="s">
-        <v>3344</v>
+        <v>3340</v>
       </c>
       <c r="B122" s="193" t="s">
         <v>2171</v>
@@ -39423,7 +39423,7 @@
         <v>377</v>
       </c>
       <c r="E122" s="183" t="s">
-        <v>3425</v>
+        <v>3421</v>
       </c>
       <c r="F122" s="193" t="s">
         <v>422</v>
@@ -39449,7 +39449,7 @@
         <v>1630</v>
       </c>
       <c r="E123" s="183" t="s">
-        <v>3425</v>
+        <v>3421</v>
       </c>
       <c r="F123" s="193" t="s">
         <v>422</v>
@@ -39463,16 +39463,16 @@
     </row>
     <row r="125" spans="1:9">
       <c r="C125" s="449" t="s">
-        <v>3541</v>
+        <v>3537</v>
       </c>
       <c r="D125" s="76" t="s">
-        <v>3661</v>
+        <v>3657</v>
       </c>
       <c r="E125" s="76" t="s">
         <v>678</v>
       </c>
       <c r="F125" s="76" t="s">
-        <v>3542</v>
+        <v>3538</v>
       </c>
       <c r="G125" s="76" t="s">
         <v>422</v>
@@ -39489,7 +39489,7 @@
         <v>362</v>
       </c>
       <c r="F126" s="183" t="s">
-        <v>3542</v>
+        <v>3538</v>
       </c>
       <c r="G126" s="183" t="s">
         <v>422</v>
@@ -39503,20 +39503,20 @@
     </row>
     <row r="127" spans="1:9">
       <c r="A127" s="451" t="s">
-        <v>3604</v>
+        <v>3600</v>
       </c>
       <c r="B127" s="451"/>
       <c r="C127" s="453" t="s">
-        <v>3606</v>
+        <v>3602</v>
       </c>
       <c r="D127" s="451" t="s">
-        <v>3607</v>
+        <v>3603</v>
       </c>
       <c r="E127" s="386" t="s">
         <v>362</v>
       </c>
       <c r="F127" s="386" t="s">
-        <v>3542</v>
+        <v>3538</v>
       </c>
       <c r="G127" s="386" t="s">
         <v>422</v>
@@ -39543,7 +39543,7 @@
         <v>362</v>
       </c>
       <c r="F128" s="183" t="s">
-        <v>3542</v>
+        <v>3538</v>
       </c>
       <c r="G128" s="183" t="s">
         <v>422</v>
@@ -39557,7 +39557,7 @@
     </row>
     <row r="129" spans="1:9">
       <c r="A129" s="451" t="s">
-        <v>3604</v>
+        <v>3600</v>
       </c>
       <c r="B129" s="451"/>
       <c r="C129" s="453" t="s">
@@ -39570,7 +39570,7 @@
         <v>362</v>
       </c>
       <c r="F129" s="386" t="s">
-        <v>3542</v>
+        <v>3538</v>
       </c>
       <c r="G129" s="386" t="s">
         <v>422</v>
@@ -39584,20 +39584,20 @@
     </row>
     <row r="130" spans="1:9">
       <c r="A130" s="451" t="s">
-        <v>3604</v>
+        <v>3600</v>
       </c>
       <c r="B130" s="451"/>
       <c r="C130" s="452" t="s">
         <v>1163</v>
       </c>
       <c r="D130" s="386" t="s">
-        <v>3605</v>
+        <v>3601</v>
       </c>
       <c r="E130" s="386" t="s">
         <v>362</v>
       </c>
       <c r="F130" s="386" t="s">
-        <v>3542</v>
+        <v>3538</v>
       </c>
       <c r="G130" s="386" t="s">
         <v>422</v>
@@ -39626,7 +39626,7 @@
         <v>2322</v>
       </c>
       <c r="F132" s="195" t="s">
-        <v>3561</v>
+        <v>3557</v>
       </c>
       <c r="G132" s="76" t="s">
         <v>1426</v>
@@ -39643,7 +39643,7 @@
         <v>64226974</v>
       </c>
       <c r="C133" s="183" t="s">
-        <v>3149</v>
+        <v>3146</v>
       </c>
       <c r="D133" s="193" t="s">
         <v>377</v>
@@ -39652,7 +39652,7 @@
         <v>2322</v>
       </c>
       <c r="F133" s="193" t="s">
-        <v>3561</v>
+        <v>3557</v>
       </c>
       <c r="G133" s="183" t="s">
         <v>1426</v>
@@ -39678,7 +39678,7 @@
         <v>2322</v>
       </c>
       <c r="F134" s="193" t="s">
-        <v>3561</v>
+        <v>3557</v>
       </c>
       <c r="G134" s="183" t="s">
         <v>1426</v>
@@ -39704,7 +39704,7 @@
         <v>2322</v>
       </c>
       <c r="F135" s="193" t="s">
-        <v>3561</v>
+        <v>3557</v>
       </c>
       <c r="G135" s="183" t="s">
         <v>1426</v>
@@ -39730,7 +39730,7 @@
         <v>2322</v>
       </c>
       <c r="F136" s="193" t="s">
-        <v>3561</v>
+        <v>3557</v>
       </c>
       <c r="G136" s="183" t="s">
         <v>1426</v>
@@ -39741,7 +39741,7 @@
     </row>
     <row r="137" spans="1:9">
       <c r="A137" s="193" t="s">
-        <v>3202</v>
+        <v>3198</v>
       </c>
       <c r="B137" s="193">
         <v>63811445</v>
@@ -39756,7 +39756,7 @@
         <v>2322</v>
       </c>
       <c r="F137" s="193" t="s">
-        <v>3561</v>
+        <v>3557</v>
       </c>
       <c r="G137" s="183" t="s">
         <v>1426</v>
@@ -39773,16 +39773,16 @@
         <v>2132</v>
       </c>
       <c r="C139" s="195" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="D139" s="195" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
       <c r="E139" s="76" t="s">
         <v>2322</v>
       </c>
       <c r="F139" s="195" t="s">
-        <v>3561</v>
+        <v>3557</v>
       </c>
       <c r="G139" s="76" t="s">
         <v>1426</v>
@@ -39799,16 +39799,16 @@
         <v>66319486</v>
       </c>
       <c r="C140" s="193" t="s">
-        <v>3020</v>
+        <v>3017</v>
       </c>
       <c r="D140" s="193" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="E140" s="183" t="s">
         <v>2322</v>
       </c>
       <c r="F140" s="193" t="s">
-        <v>3561</v>
+        <v>3557</v>
       </c>
       <c r="G140" s="183" t="s">
         <v>1426</v>
@@ -39819,7 +39819,7 @@
     </row>
     <row r="141" spans="1:9">
       <c r="A141" s="183" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="B141" s="183">
         <v>60389752</v>
@@ -39834,7 +39834,7 @@
         <v>2322</v>
       </c>
       <c r="F141" s="193" t="s">
-        <v>3561</v>
+        <v>3557</v>
       </c>
       <c r="G141" s="183" t="s">
         <v>1426</v>
@@ -39848,7 +39848,7 @@
         <v>2322</v>
       </c>
       <c r="F142" s="193" t="s">
-        <v>3561</v>
+        <v>3557</v>
       </c>
       <c r="G142" s="183" t="s">
         <v>1426</v>
@@ -39874,7 +39874,7 @@
         <v>2322</v>
       </c>
       <c r="F143" s="193" t="s">
-        <v>3561</v>
+        <v>3557</v>
       </c>
       <c r="G143" s="183" t="s">
         <v>1426</v>
@@ -39885,7 +39885,7 @@
     </row>
     <row r="144" spans="1:9">
       <c r="A144" s="193" t="s">
-        <v>3290</v>
+        <v>3286</v>
       </c>
       <c r="B144" s="193">
         <v>60389752</v>
@@ -39900,7 +39900,7 @@
         <v>2322</v>
       </c>
       <c r="F144" s="193" t="s">
-        <v>3561</v>
+        <v>3557</v>
       </c>
       <c r="G144" s="183" t="s">
         <v>1426</v>
@@ -39926,7 +39926,7 @@
         <v>2426</v>
       </c>
       <c r="F146" s="195" t="s">
-        <v>3562</v>
+        <v>3558</v>
       </c>
       <c r="G146" s="76" t="s">
         <v>1426</v>
@@ -39943,7 +39943,7 @@
         <v>67697112</v>
       </c>
       <c r="C147" s="193" t="s">
-        <v>3038</v>
+        <v>3035</v>
       </c>
       <c r="D147" s="193" t="s">
         <v>1298</v>
@@ -39952,7 +39952,7 @@
         <v>2426</v>
       </c>
       <c r="F147" s="193" t="s">
-        <v>3562</v>
+        <v>3558</v>
       </c>
       <c r="G147" s="183" t="s">
         <v>1426</v>
@@ -39963,7 +39963,7 @@
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="183" t="s">
-        <v>3075</v>
+        <v>3072</v>
       </c>
       <c r="B148" s="183">
         <v>62560788</v>
@@ -39978,7 +39978,7 @@
         <v>2426</v>
       </c>
       <c r="F148" s="193" t="s">
-        <v>3562</v>
+        <v>3558</v>
       </c>
       <c r="G148" s="183" t="s">
         <v>1426</v>
@@ -40004,7 +40004,7 @@
         <v>2426</v>
       </c>
       <c r="F149" s="193" t="s">
-        <v>3562</v>
+        <v>3558</v>
       </c>
       <c r="G149" s="183" t="s">
         <v>1426</v>
@@ -40030,7 +40030,7 @@
         <v>2426</v>
       </c>
       <c r="F150" s="193" t="s">
-        <v>3562</v>
+        <v>3558</v>
       </c>
       <c r="G150" s="183" t="s">
         <v>1426</v>
@@ -40056,7 +40056,7 @@
         <v>2426</v>
       </c>
       <c r="F151" s="193" t="s">
-        <v>3562</v>
+        <v>3558</v>
       </c>
       <c r="G151" s="183" t="s">
         <v>1426</v>
@@ -40069,45 +40069,45 @@
       <c r="A160" s="195"/>
       <c r="B160" s="195"/>
       <c r="C160" s="195" t="s">
-        <v>3598</v>
+        <v>3594</v>
       </c>
       <c r="D160" s="195" t="s">
-        <v>3599</v>
+        <v>3595</v>
       </c>
       <c r="E160" s="195" t="s">
-        <v>3600</v>
+        <v>3596</v>
       </c>
       <c r="F160" s="76" t="s">
-        <v>3601</v>
+        <v>3597</v>
       </c>
       <c r="G160" s="76"/>
       <c r="H160" s="76"/>
     </row>
     <row r="161" spans="1:9">
       <c r="A161" s="183" t="s">
-        <v>3344</v>
+        <v>3340</v>
       </c>
       <c r="B161" s="183">
         <v>69888391</v>
       </c>
       <c r="C161" s="193" t="s">
-        <v>3602</v>
+        <v>3598</v>
       </c>
       <c r="D161" s="183" t="s">
-        <v>3603</v>
+        <v>3599</v>
       </c>
       <c r="E161" s="193" t="s">
-        <v>3600</v>
+        <v>3596</v>
       </c>
       <c r="F161" s="183" t="s">
-        <v>3601</v>
+        <v>3597</v>
       </c>
       <c r="G161" s="183"/>
       <c r="H161" s="183"/>
     </row>
     <row r="162" spans="1:9">
       <c r="A162" s="183" t="s">
-        <v>3608</v>
+        <v>3604</v>
       </c>
       <c r="B162" s="183">
         <v>68030850</v>
@@ -40116,62 +40116,62 @@
         <v>1739</v>
       </c>
       <c r="D162" s="183" t="s">
-        <v>3607</v>
+        <v>3603</v>
       </c>
       <c r="E162" s="193" t="s">
-        <v>3600</v>
+        <v>3596</v>
       </c>
       <c r="F162" s="183" t="s">
-        <v>3601</v>
+        <v>3597</v>
       </c>
       <c r="G162" s="183"/>
       <c r="H162" s="183"/>
     </row>
     <row r="163" spans="1:9">
       <c r="A163" s="183" t="s">
-        <v>3145</v>
+        <v>3142</v>
       </c>
       <c r="B163" s="183">
         <v>66230961</v>
       </c>
       <c r="C163" s="193" t="s">
-        <v>3610</v>
+        <v>3606</v>
       </c>
       <c r="D163" s="193" t="s">
-        <v>3611</v>
+        <v>3607</v>
       </c>
       <c r="E163" s="193" t="s">
-        <v>3600</v>
+        <v>3596</v>
       </c>
       <c r="F163" s="183" t="s">
-        <v>3601</v>
+        <v>3597</v>
       </c>
       <c r="G163" s="183"/>
       <c r="H163" s="183"/>
     </row>
     <row r="164" spans="1:9">
       <c r="A164" s="193" t="s">
-        <v>3486</v>
+        <v>3482</v>
       </c>
       <c r="B164" s="193">
         <v>69566600</v>
       </c>
       <c r="C164" s="193" t="s">
-        <v>3626</v>
+        <v>3622</v>
       </c>
       <c r="D164" s="193"/>
       <c r="E164" s="193" t="s">
-        <v>3600</v>
+        <v>3596</v>
       </c>
       <c r="F164" s="183" t="s">
-        <v>3601</v>
+        <v>3597</v>
       </c>
       <c r="G164" s="183"/>
       <c r="H164" s="183"/>
     </row>
     <row r="165" spans="1:9">
       <c r="A165" s="183" t="s">
-        <v>3268</v>
+        <v>3264</v>
       </c>
       <c r="B165" s="183">
         <v>64403333</v>
@@ -40183,10 +40183,10 @@
         <v>1818</v>
       </c>
       <c r="E165" s="193" t="s">
-        <v>3600</v>
+        <v>3596</v>
       </c>
       <c r="F165" s="183" t="s">
-        <v>3601</v>
+        <v>3597</v>
       </c>
       <c r="G165" s="183"/>
       <c r="H165" s="183"/>
@@ -40195,7 +40195,7 @@
       <c r="A167" s="221"/>
       <c r="B167" s="221"/>
       <c r="C167" s="221" t="s">
-        <v>3622</v>
+        <v>3618</v>
       </c>
       <c r="D167" s="221"/>
       <c r="E167" s="221"/>
@@ -40220,42 +40220,42 @@
         <v>362</v>
       </c>
       <c r="F169" s="195" t="s">
-        <v>3646</v>
+        <v>3642</v>
       </c>
       <c r="G169" s="76" t="s">
-        <v>3648</v>
+        <v>3644</v>
       </c>
       <c r="H169" s="76" t="s">
-        <v>3647</v>
+        <v>3643</v>
       </c>
       <c r="I169" t="s">
-        <v>3645</v>
+        <v>3641</v>
       </c>
     </row>
     <row r="170" spans="1:9">
       <c r="A170" s="273" t="s">
-        <v>2991</v>
+        <v>2988</v>
       </c>
       <c r="B170" s="193">
         <v>65963732</v>
       </c>
       <c r="C170" s="194" t="s">
-        <v>3005</v>
+        <v>3002</v>
       </c>
       <c r="D170" s="193" t="s">
-        <v>3006</v>
+        <v>3003</v>
       </c>
       <c r="E170" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F170" s="193" t="s">
-        <v>3646</v>
+        <v>3642</v>
       </c>
       <c r="G170" s="183" t="s">
-        <v>3648</v>
+        <v>3644</v>
       </c>
       <c r="H170" s="183" t="s">
-        <v>3647</v>
+        <v>3643</v>
       </c>
       <c r="I170" s="10" t="s">
         <v>407</v>
@@ -40272,19 +40272,19 @@
         <v>2312</v>
       </c>
       <c r="D171" s="183" t="s">
-        <v>3000</v>
+        <v>2997</v>
       </c>
       <c r="E171" s="183" t="s">
         <v>362</v>
       </c>
       <c r="F171" s="193" t="s">
-        <v>3646</v>
+        <v>3642</v>
       </c>
       <c r="G171" s="183" t="s">
-        <v>3648</v>
+        <v>3644</v>
       </c>
       <c r="H171" s="183" t="s">
-        <v>3647</v>
+        <v>3643</v>
       </c>
       <c r="I171" s="10" t="s">
         <v>407</v>
@@ -40307,13 +40307,13 @@
         <v>362</v>
       </c>
       <c r="F172" s="193" t="s">
-        <v>3646</v>
+        <v>3642</v>
       </c>
       <c r="G172" s="183" t="s">
-        <v>3648</v>
+        <v>3644</v>
       </c>
       <c r="H172" s="183" t="s">
-        <v>3647</v>
+        <v>3643</v>
       </c>
       <c r="I172" s="10" t="s">
         <v>407</v>
@@ -40321,7 +40321,7 @@
     </row>
     <row r="173" spans="1:9">
       <c r="A173" s="183" t="s">
-        <v>3290</v>
+        <v>3286</v>
       </c>
       <c r="B173" s="183">
         <v>64403333</v>
@@ -40336,13 +40336,13 @@
         <v>362</v>
       </c>
       <c r="F173" s="193" t="s">
-        <v>3646</v>
+        <v>3642</v>
       </c>
       <c r="G173" s="183" t="s">
-        <v>3648</v>
+        <v>3644</v>
       </c>
       <c r="H173" s="183" t="s">
-        <v>3647</v>
+        <v>3643</v>
       </c>
       <c r="I173" s="10" t="s">
         <v>407</v>
@@ -40365,13 +40365,13 @@
         <v>362</v>
       </c>
       <c r="F174" s="193" t="s">
-        <v>3646</v>
+        <v>3642</v>
       </c>
       <c r="G174" s="183" t="s">
-        <v>3648</v>
+        <v>3644</v>
       </c>
       <c r="H174" s="183" t="s">
-        <v>3647</v>
+        <v>3643</v>
       </c>
       <c r="I174" s="10" t="s">
         <v>407</v>
@@ -40379,13 +40379,13 @@
     </row>
     <row r="178" spans="1:9">
       <c r="A178" s="10" t="s">
-        <v>3625</v>
+        <v>3621</v>
       </c>
       <c r="C178" s="10" t="s">
-        <v>3623</v>
+        <v>3619</v>
       </c>
       <c r="D178" s="10" t="s">
-        <v>3624</v>
+        <v>3620</v>
       </c>
     </row>
     <row r="180" spans="1:9">
@@ -40407,7 +40407,7 @@
       <c r="A183" s="221"/>
       <c r="B183" s="221"/>
       <c r="C183" s="221" t="s">
-        <v>3081</v>
+        <v>3078</v>
       </c>
       <c r="D183" s="221"/>
       <c r="E183" s="221"/>
@@ -40421,19 +40421,19 @@
         <v>67836337</v>
       </c>
       <c r="C184" s="116" t="s">
-        <v>3191</v>
+        <v>3188</v>
       </c>
       <c r="D184" s="195" t="s">
-        <v>3192</v>
+        <v>3189</v>
       </c>
       <c r="E184" s="430">
         <v>46243</v>
       </c>
       <c r="F184" s="76" t="s">
-        <v>3082</v>
+        <v>3079</v>
       </c>
       <c r="G184" s="195" t="s">
-        <v>3242</v>
+        <v>3238</v>
       </c>
       <c r="H184" s="76" t="s">
         <v>1955</v>
@@ -40441,19 +40441,19 @@
     </row>
     <row r="185" spans="1:9">
       <c r="A185" s="193" t="s">
-        <v>3244</v>
+        <v>3240</v>
       </c>
       <c r="B185" s="193">
         <v>60196388</v>
       </c>
       <c r="C185" s="193" t="s">
-        <v>3243</v>
+        <v>3239</v>
       </c>
       <c r="D185" s="439" t="s">
-        <v>3192</v>
+        <v>3189</v>
       </c>
       <c r="E185" s="429" t="s">
-        <v>3239</v>
+        <v>3235</v>
       </c>
       <c r="F185" s="193"/>
       <c r="G185" s="183"/>
@@ -40461,19 +40461,19 @@
     </row>
     <row r="186" spans="1:9">
       <c r="A186" s="183" t="s">
-        <v>3304</v>
+        <v>3300</v>
       </c>
       <c r="B186" s="183">
         <v>64403333</v>
       </c>
       <c r="C186" s="191" t="s">
-        <v>3259</v>
+        <v>3255</v>
       </c>
       <c r="D186" s="183" t="s">
-        <v>3250</v>
+        <v>3246</v>
       </c>
       <c r="E186" s="429" t="s">
-        <v>3239</v>
+        <v>3235</v>
       </c>
       <c r="F186" s="193"/>
       <c r="G186" s="183"/>
@@ -40481,19 +40481,19 @@
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="193" t="s">
-        <v>3280</v>
+        <v>3276</v>
       </c>
       <c r="B187" s="193">
         <v>68071614</v>
       </c>
       <c r="C187" s="193" t="s">
-        <v>3277</v>
+        <v>3273</v>
       </c>
       <c r="D187" s="193" t="s">
-        <v>3278</v>
+        <v>3274</v>
       </c>
       <c r="E187" s="429" t="s">
-        <v>3279</v>
+        <v>3275</v>
       </c>
       <c r="F187" s="193"/>
       <c r="G187" s="183"/>
@@ -40501,19 +40501,19 @@
     </row>
     <row r="188" spans="1:9" s="226" customFormat="1" ht="15.5">
       <c r="A188" s="183" t="s">
-        <v>3537</v>
+        <v>3533</v>
       </c>
       <c r="B188" s="183">
         <v>63950696</v>
       </c>
       <c r="C188" s="445" t="s">
-        <v>3306</v>
+        <v>3302</v>
       </c>
       <c r="D188" s="445" t="s">
         <v>2709</v>
       </c>
       <c r="E188" s="429" t="s">
-        <v>3307</v>
+        <v>3303</v>
       </c>
       <c r="F188" s="446"/>
       <c r="G188" s="440"/>
@@ -40528,13 +40528,13 @@
         <v>65147336</v>
       </c>
       <c r="C189" s="183" t="s">
-        <v>3326</v>
+        <v>3322</v>
       </c>
       <c r="D189" s="183" t="s">
-        <v>3327</v>
+        <v>3323</v>
       </c>
       <c r="E189" s="429" t="s">
-        <v>3328</v>
+        <v>3324</v>
       </c>
       <c r="F189" s="193"/>
       <c r="G189" s="183"/>
@@ -40575,7 +40575,7 @@
         <v>316</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>3167</v>
+        <v>3164</v>
       </c>
       <c r="E194" s="30"/>
       <c r="F194"/>
@@ -40601,7 +40601,7 @@
         <v>439</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>3217</v>
+        <v>3213</v>
       </c>
       <c r="E196" s="30"/>
       <c r="F196"/>
@@ -40612,7 +40612,7 @@
         <v>26</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>3277</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -40620,7 +40620,7 @@
         <v>1319</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>3306</v>
+        <v>3302</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -40628,7 +40628,7 @@
         <v>1641</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>3326</v>
+        <v>3322</v>
       </c>
       <c r="F199" s="392"/>
     </row>
@@ -40637,7 +40637,7 @@
         <v>1300</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>3541</v>
+        <v>3537</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -40645,7 +40645,7 @@
         <v>406</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>3602</v>
+        <v>3598</v>
       </c>
     </row>
     <row r="202" spans="1:9">
@@ -40653,7 +40653,7 @@
         <v>707</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>3606</v>
+        <v>3602</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -40661,7 +40661,7 @@
         <v>281</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>3610</v>
+        <v>3606</v>
       </c>
     </row>
     <row r="204" spans="1:9">
@@ -40669,7 +40669,7 @@
         <v>2330</v>
       </c>
       <c r="D204" s="426" t="s">
-        <v>3623</v>
+        <v>3619</v>
       </c>
     </row>
     <row r="205" spans="1:9">
@@ -40679,7 +40679,7 @@
         <v>465</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>3132</v>
+        <v>3129</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -40687,7 +40687,7 @@
         <v>219</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>3136</v>
+        <v>3133</v>
       </c>
     </row>
     <row r="207" spans="1:9">
@@ -40695,7 +40695,7 @@
         <v>427</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>3149</v>
+        <v>3146</v>
       </c>
     </row>
     <row r="208" spans="1:9">
@@ -40703,7 +40703,7 @@
         <v>1049</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>3163</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="223" spans="1:9">
@@ -41929,19 +41929,19 @@
         <v>1383</v>
       </c>
       <c r="E3" t="s">
-        <v>3550</v>
+        <v>3546</v>
       </c>
       <c r="F3" t="s">
-        <v>3551</v>
+        <v>3547</v>
       </c>
       <c r="G3" t="s">
         <v>704</v>
       </c>
       <c r="H3" t="s">
-        <v>3181</v>
+        <v>3178</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>3374</v>
+        <v>3370</v>
       </c>
       <c r="J3"/>
     </row>
@@ -41968,10 +41968,10 @@
         <v>515</v>
       </c>
       <c r="H4" s="49" t="s">
-        <v>3023</v>
+        <v>3020</v>
       </c>
       <c r="I4" t="s">
-        <v>3301</v>
+        <v>3297</v>
       </c>
       <c r="J4"/>
     </row>
@@ -41980,7 +41980,7 @@
         <v>1421</v>
       </c>
       <c r="B5" t="s">
-        <v>3376</v>
+        <v>3372</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>480</v>
@@ -41989,7 +41989,7 @@
         <v>1505</v>
       </c>
       <c r="E5" t="s">
-        <v>3485</v>
+        <v>3481</v>
       </c>
       <c r="F5" t="s">
         <v>2141</v>
@@ -41998,10 +41998,10 @@
         <v>515</v>
       </c>
       <c r="H5" s="220" t="s">
-        <v>3468</v>
+        <v>3464</v>
       </c>
       <c r="I5" s="220" t="s">
-        <v>3538</v>
+        <v>3534</v>
       </c>
       <c r="J5" t="s">
         <v>1388</v>
@@ -42009,19 +42009,19 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>3180</v>
+        <v>3177</v>
       </c>
       <c r="B6" t="s">
-        <v>3209</v>
+        <v>3205</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>427</v>
       </c>
       <c r="D6" t="s">
-        <v>3035</v>
+        <v>3032</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>3033</v>
+        <v>3030</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>2776</v>
@@ -42030,10 +42030,10 @@
         <v>436</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>3479</v>
+        <v>3475</v>
       </c>
       <c r="I6" t="s">
-        <v>3312</v>
+        <v>3308</v>
       </c>
       <c r="J6"/>
     </row>
@@ -42065,7 +42065,7 @@
         <v>2039</v>
       </c>
       <c r="D8" t="s">
-        <v>3375</v>
+        <v>3371</v>
       </c>
       <c r="E8" t="s">
         <v>2290</v>
@@ -42080,7 +42080,7 @@
         <v>2936</v>
       </c>
       <c r="I8" t="s">
-        <v>3667</v>
+        <v>3663</v>
       </c>
       <c r="J8"/>
     </row>
@@ -42121,25 +42121,25 @@
         <v>62349088</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>3402</v>
+        <v>3398</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>3403</v>
+        <v>3399</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>3404</v>
+        <v>3400</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>3405</v>
+        <v>3401</v>
       </c>
       <c r="G10" t="s">
         <v>250</v>
       </c>
       <c r="H10" s="276" t="s">
-        <v>3525</v>
+        <v>3521</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>3451</v>
+        <v>3447</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -42276,7 +42276,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="10" t="s">
-        <v>3091</v>
+        <v>3088</v>
       </c>
       <c r="B5" s="10">
         <v>67992849</v>
@@ -42297,15 +42297,15 @@
         <v>517</v>
       </c>
       <c r="H5" s="220" t="s">
-        <v>3204</v>
+        <v>3200</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>3386</v>
+        <v>3382</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="457" t="s">
-        <v>3537</v>
+        <v>3533</v>
       </c>
       <c r="B6" s="10">
         <v>62140561</v>
@@ -42314,7 +42314,7 @@
         <v>1695</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>3677</v>
+        <v>3673</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>1679</v>
@@ -42326,15 +42326,15 @@
         <v>517</v>
       </c>
       <c r="H6" s="457" t="s">
-        <v>3678</v>
+        <v>3674</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>3429</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="10" t="s">
-        <v>3176</v>
+        <v>3173</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>2364</v>
@@ -42343,7 +42343,7 @@
         <v>1706</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>3565</v>
+        <v>3561</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1679</v>
@@ -42355,10 +42355,10 @@
         <v>517</v>
       </c>
       <c r="H7" t="s">
-        <v>3566</v>
+        <v>3562</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>3627</v>
+        <v>3623</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -42406,7 +42406,7 @@
         <v>2122</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>958</v>
@@ -42418,10 +42418,10 @@
         <v>517</v>
       </c>
       <c r="H12" s="273" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="I12" t="s">
-        <v>3066</v>
+        <v>3063</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -42458,10 +42458,10 @@
         <v>517</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>3437</v>
+        <v>3433</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>3427</v>
+        <v>3423</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -42487,7 +42487,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="10" t="s">
-        <v>3176</v>
+        <v>3173</v>
       </c>
       <c r="B17" s="10">
         <v>64403333</v>
@@ -42519,7 +42519,7 @@
         <v>2294</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>2995</v>
+        <v>2992</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>958</v>
@@ -42531,10 +42531,10 @@
         <v>517</v>
       </c>
       <c r="H18" s="454" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>3048</v>
+        <v>3045</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -42548,7 +42548,7 @@
         <v>2345</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>3411</v>
+        <v>3407</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>958</v>
@@ -42560,10 +42560,10 @@
         <v>517</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>3412</v>
+        <v>3408</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>3153</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="190" customFormat="1" ht="26">
@@ -42579,13 +42579,13 @@
         <v>2546</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>3119</v>
+        <v>3116</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>2369</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>3093</v>
+        <v>3090</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>958</v>
@@ -42597,15 +42597,15 @@
         <v>517</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>3205</v>
+        <v>3201</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>3524</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>3185</v>
+        <v>3182</v>
       </c>
       <c r="B23" s="10">
         <v>64720128</v>
@@ -42626,15 +42626,15 @@
         <v>517</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>3186</v>
+        <v>3183</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>3187</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="10" t="s">
-        <v>3304</v>
+        <v>3300</v>
       </c>
       <c r="B24" s="10">
         <v>63844875</v>
@@ -42643,7 +42643,7 @@
         <v>2385</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>3436</v>
+        <v>3432</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>958</v>
@@ -42655,10 +42655,10 @@
         <v>517</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>3150</v>
+        <v>3147</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>3372</v>
+        <v>3368</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -42808,10 +42808,10 @@
         <v>2923</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>3523</v>
+        <v>3519</v>
       </c>
       <c r="J4" t="s">
-        <v>3567</v>
+        <v>3563</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -42871,7 +42871,7 @@
         <v>2255</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>3178</v>
+        <v>3175</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>2256</v>
@@ -42886,7 +42886,7 @@
         <v>2907</v>
       </c>
       <c r="I7" s="273" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="J7" s="273" t="s">
         <v>2877</v>
@@ -42894,19 +42894,19 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="10" t="s">
-        <v>3537</v>
+        <v>3533</v>
       </c>
       <c r="B8" t="s">
-        <v>3347</v>
+        <v>3343</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>3253</v>
+        <v>3249</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>3254</v>
+        <v>3250</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>3255</v>
+        <v>3251</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>1722</v>
@@ -42915,10 +42915,10 @@
         <v>962</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>3426</v>
+        <v>3422</v>
       </c>
       <c r="I8" s="273" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
       <c r="J8" s="273" t="s">
         <v>2884</v>
@@ -42953,7 +42953,7 @@
         <v>2890</v>
       </c>
       <c r="J9" t="s">
-        <v>3514</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -42961,13 +42961,13 @@
         <v>1418</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>3350</v>
+        <v>3346</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>2922</v>
@@ -42979,30 +42979,30 @@
         <v>962</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>3673</v>
+        <v>3669</v>
       </c>
       <c r="I10" s="273" t="s">
-        <v>3025</v>
+        <v>3022</v>
       </c>
       <c r="J10" t="s">
-        <v>3067</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="10" t="s">
-        <v>3264</v>
+        <v>3260</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>3409</v>
+        <v>3405</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>3389</v>
+        <v>3385</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>3392</v>
+        <v>3388</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>3390</v>
+        <v>3386</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>1722</v>
@@ -43022,7 +43022,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="C15" s="426" t="s">
-        <v>3389</v>
+        <v>3385</v>
       </c>
     </row>
   </sheetData>
@@ -43163,10 +43163,10 @@
         <v>60240509</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>3233</v>
+        <v>3229</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>3234</v>
+        <v>3230</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>2544</v>
@@ -43222,16 +43222,16 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="10" t="s">
-        <v>3185</v>
+        <v>3182</v>
       </c>
       <c r="B12" s="10">
         <v>66466729</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>3353</v>
+        <v>3349</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>3354</v>
+        <v>3350</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
@@ -43311,7 +43311,7 @@
       <c r="A19" s="10"/>
       <c r="B19" s="10"/>
       <c r="C19" s="426" t="s">
-        <v>3353</v>
+        <v>3349</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
@@ -43440,7 +43440,7 @@
         <v>2914</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
     </row>
   </sheetData>
@@ -44835,7 +44835,7 @@
         <v>51</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>1155</v>
@@ -44847,10 +44847,10 @@
         <v>159</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>3094</v>
+        <v>3091</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>3104</v>
+        <v>3101</v>
       </c>
       <c r="N6" s="4" t="s">
         <v>26</v>
@@ -44858,7 +44858,7 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="4" t="s">
-        <v>3185</v>
+        <v>3182</v>
       </c>
       <c r="B7" s="4">
         <v>69888391</v>
@@ -44882,13 +44882,13 @@
         <v>2237</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>3579</v>
+        <v>3575</v>
       </c>
       <c r="L7" s="3"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>3290</v>
+        <v>3286</v>
       </c>
       <c r="B8" t="s">
         <v>452</v>
@@ -44912,15 +44912,15 @@
         <v>2656</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>3671</v>
+        <v>3667</v>
       </c>
     </row>
     <row r="9" spans="1:14" s="4" customFormat="1">
       <c r="A9" t="s">
-        <v>3486</v>
+        <v>3482</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>3629</v>
+        <v>3625</v>
       </c>
       <c r="C9" s="22" t="s">
         <v>642</v>
@@ -44929,16 +44929,16 @@
         <v>2131</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>3105</v>
+        <v>3102</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>3106</v>
+        <v>3103</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>159</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>3069</v>
+        <v>3066</v>
       </c>
       <c r="I9" s="105"/>
       <c r="L9" s="4" t="s">
@@ -44947,7 +44947,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="4" t="s">
-        <v>3268</v>
+        <v>3264</v>
       </c>
       <c r="B10" s="4">
         <v>67916500</v>
@@ -44968,10 +44968,10 @@
         <v>244</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>3181</v>
+        <v>3178</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>3612</v>
+        <v>3608</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -44988,7 +44988,7 @@
         <v>1496</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>3029</v>
+        <v>3026</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>2818</v>
@@ -44997,10 +44997,10 @@
         <v>244</v>
       </c>
       <c r="H11" t="s">
-        <v>3296</v>
+        <v>3292</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>3265</v>
+        <v>3261</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -45020,10 +45020,10 @@
         <v>244</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>3299</v>
+        <v>3295</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>3330</v>
+        <v>3326</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -45031,7 +45031,7 @@
         <v>2838</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>3314</v>
+        <v>3310</v>
       </c>
       <c r="C13" s="22" t="s">
         <v>1215</v>
@@ -45049,10 +45049,10 @@
         <v>244</v>
       </c>
       <c r="H13" s="447" t="s">
-        <v>3027</v>
+        <v>3024</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>3377</v>
+        <v>3373</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="4" customFormat="1">
@@ -45078,19 +45078,19 @@
         <v>244</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>3214</v>
+        <v>3210</v>
       </c>
       <c r="I14" s="220" t="s">
-        <v>3257</v>
+        <v>3253</v>
       </c>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="4" t="s">
-        <v>3537</v>
+        <v>3533</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>3676</v>
+        <v>3672</v>
       </c>
       <c r="C15" s="22" t="s">
         <v>340</v>
@@ -45099,19 +45099,19 @@
         <v>2766</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>3348</v>
+        <v>3344</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>3349</v>
+        <v>3345</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>886</v>
       </c>
       <c r="H15" t="s">
-        <v>3649</v>
+        <v>3645</v>
       </c>
       <c r="I15" t="s">
-        <v>3373</v>
+        <v>3369</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>498</v>
@@ -45140,10 +45140,10 @@
         <v>159</v>
       </c>
       <c r="H16" t="s">
-        <v>3220</v>
+        <v>3216</v>
       </c>
       <c r="I16" t="s">
-        <v>3095</v>
+        <v>3092</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>804</v>
@@ -45151,7 +45151,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>3091</v>
+        <v>3088</v>
       </c>
       <c r="B17">
         <v>65325884</v>
@@ -45174,7 +45174,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="4" t="s">
-        <v>3176</v>
+        <v>3173</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>2085</v>
@@ -45186,24 +45186,24 @@
         <v>2190</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>3334</v>
+        <v>3330</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>3106</v>
+        <v>3103</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>244</v>
       </c>
       <c r="H18" t="s">
-        <v>3418</v>
+        <v>3414</v>
       </c>
       <c r="I18" t="s">
-        <v>3289</v>
+        <v>3285</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="4" customFormat="1">
       <c r="A19" s="4" t="s">
-        <v>3304</v>
+        <v>3300</v>
       </c>
       <c r="B19" s="4">
         <v>64403333</v>
@@ -45215,10 +45215,10 @@
         <v>2529</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>3121</v>
+        <v>3118</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>3106</v>
+        <v>3103</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>1223</v>
@@ -45228,7 +45228,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="4" t="s">
-        <v>3091</v>
+        <v>3088</v>
       </c>
       <c r="B20">
         <v>64403333</v>
@@ -45289,7 +45289,7 @@
         <v>2181</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>3388</v>
+        <v>3384</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>2423</v>
@@ -45300,7 +45300,7 @@
     </row>
     <row r="23" spans="1:12" s="4" customFormat="1">
       <c r="A23" t="s">
-        <v>3091</v>
+        <v>3088</v>
       </c>
       <c r="B23">
         <v>63247837</v>
@@ -45309,7 +45309,7 @@
         <v>2537</v>
       </c>
       <c r="D23" t="s">
-        <v>3045</v>
+        <v>3042</v>
       </c>
       <c r="E23" t="s">
         <v>2540</v>
@@ -45321,16 +45321,16 @@
         <v>159</v>
       </c>
       <c r="H23" t="s">
-        <v>3636</v>
+        <v>3632</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>3062</v>
+        <v>3059</v>
       </c>
       <c r="L23" s="6"/>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>3290</v>
+        <v>3286</v>
       </c>
       <c r="B24">
         <v>69184177</v>
@@ -45353,16 +45353,16 @@
     </row>
     <row r="25" spans="1:12" s="4" customFormat="1">
       <c r="A25" s="4" t="s">
-        <v>3134</v>
+        <v>3131</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>3148</v>
+        <v>3145</v>
       </c>
       <c r="C25" s="21" t="s">
         <v>1321</v>
       </c>
       <c r="D25" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>2862</v>
@@ -45374,10 +45374,10 @@
         <v>244</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>3444</v>
+        <v>3440</v>
       </c>
       <c r="I25" s="220" t="s">
-        <v>3208</v>
+        <v>3204</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="4" customFormat="1">
@@ -45403,10 +45403,10 @@
         <v>159</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>3230</v>
+        <v>3226</v>
       </c>
       <c r="I27" t="s">
-        <v>3620</v>
+        <v>3616</v>
       </c>
       <c r="L27" s="4" t="s">
         <v>812</v>
@@ -45414,7 +45414,7 @@
     </row>
     <row r="28" spans="1:12" s="4" customFormat="1">
       <c r="A28" t="s">
-        <v>3264</v>
+        <v>3260</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>2414</v>
@@ -45435,16 +45435,16 @@
         <v>325</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>3391</v>
+        <v>3387</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>3169</v>
+        <v>3166</v>
       </c>
       <c r="K28"/>
     </row>
     <row r="29" spans="1:12" s="75" customFormat="1">
       <c r="A29" t="s">
-        <v>3583</v>
+        <v>3579</v>
       </c>
       <c r="B29" t="s">
         <v>1206</v>
@@ -45456,7 +45456,7 @@
         <v>2788</v>
       </c>
       <c r="E29" t="s">
-        <v>3092</v>
+        <v>3089</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>2818</v>
@@ -45465,10 +45465,10 @@
         <v>250</v>
       </c>
       <c r="H29" t="s">
-        <v>3428</v>
+        <v>3424</v>
       </c>
       <c r="I29" t="s">
-        <v>3042</v>
+        <v>3039</v>
       </c>
       <c r="J29" s="4"/>
       <c r="L29" s="135"/>
@@ -45478,7 +45478,7 @@
         <v>2662</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>3502</v>
+        <v>3498</v>
       </c>
       <c r="C30" s="22" t="s">
         <v>402</v>
@@ -45487,7 +45487,7 @@
         <v>2894</v>
       </c>
       <c r="E30" t="s">
-        <v>2986</v>
+        <v>2983</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>1336</v>
@@ -45496,15 +45496,15 @@
         <v>159</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>3530</v>
+        <v>3526</v>
       </c>
       <c r="I30" t="s">
-        <v>3424</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>3089</v>
+        <v>3086</v>
       </c>
       <c r="B31" s="4">
         <v>69409351</v>
@@ -45525,10 +45525,10 @@
         <v>159</v>
       </c>
       <c r="H31" t="s">
-        <v>3614</v>
+        <v>3610</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>3534</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -45542,7 +45542,7 @@
         <v>2334</v>
       </c>
       <c r="D32" t="s">
-        <v>3414</v>
+        <v>3410</v>
       </c>
       <c r="E32" t="s">
         <v>2338</v>
@@ -45554,10 +45554,10 @@
         <v>159</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>3380</v>
+        <v>3376</v>
       </c>
       <c r="I32" t="s">
-        <v>3415</v>
+        <v>3411</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -45565,13 +45565,13 @@
         <v>2543</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>3247</v>
+        <v>3243</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>2527</v>
       </c>
       <c r="D33" t="s">
-        <v>3246</v>
+        <v>3242</v>
       </c>
       <c r="E33" t="s">
         <v>2530</v>
@@ -45583,21 +45583,21 @@
         <v>2531</v>
       </c>
       <c r="H33" t="s">
-        <v>3399</v>
+        <v>3395</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>3628</v>
+        <v>3624</v>
       </c>
       <c r="C34" s="21" t="s">
         <v>2524</v>
       </c>
       <c r="D34" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
       <c r="E34" t="s">
         <v>2530</v>
@@ -45609,10 +45609,10 @@
         <v>159</v>
       </c>
       <c r="H34" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I34" t="s">
-        <v>3674</v>
+        <v>3670</v>
       </c>
       <c r="J34" s="4"/>
     </row>
@@ -45639,24 +45639,24 @@
         <v>2531</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>3395</v>
+        <v>3391</v>
       </c>
       <c r="I35" t="s">
-        <v>3430</v>
+        <v>3426</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>3091</v>
+        <v>3088</v>
       </c>
       <c r="B36" t="s">
-        <v>3119</v>
+        <v>3116</v>
       </c>
       <c r="C36" s="22" t="s">
         <v>2526</v>
       </c>
       <c r="D36" t="s">
-        <v>3118</v>
+        <v>3115</v>
       </c>
       <c r="E36" t="s">
         <v>2530</v>
@@ -45668,10 +45668,10 @@
         <v>159</v>
       </c>
       <c r="H36" t="s">
-        <v>3120</v>
+        <v>3117</v>
       </c>
       <c r="I36" t="s">
-        <v>3585</v>
+        <v>3581</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -45679,7 +45679,7 @@
         <v>1417</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>3406</v>
+        <v>3402</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>2538</v>
@@ -45697,7 +45697,7 @@
         <v>159</v>
       </c>
       <c r="H37" t="s">
-        <v>3310</v>
+        <v>3306</v>
       </c>
       <c r="I37" t="s">
         <v>2836</v>
@@ -45726,39 +45726,39 @@
         <v>159</v>
       </c>
       <c r="H38" s="220" t="s">
-        <v>3293</v>
+        <v>3289</v>
       </c>
       <c r="I38" s="49" t="s">
-        <v>2994</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>3449</v>
+        <v>3445</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>3450</v>
+        <v>3446</v>
       </c>
       <c r="C39" s="22" t="s">
         <v>1345</v>
       </c>
       <c r="D39" s="22" t="s">
-        <v>3448</v>
+        <v>3444</v>
       </c>
       <c r="E39" t="s">
-        <v>3036</v>
+        <v>3033</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>3037</v>
+        <v>3034</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>159</v>
       </c>
       <c r="H39" t="s">
-        <v>3473</v>
+        <v>3469</v>
       </c>
       <c r="I39" t="s">
-        <v>3483</v>
+        <v>3479</v>
       </c>
     </row>
     <row r="40" spans="1:11" s="4" customFormat="1">
@@ -45772,22 +45772,22 @@
         <v>429</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>3488</v>
+        <v>3484</v>
       </c>
       <c r="E40" t="s">
-        <v>3036</v>
+        <v>3033</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>3037</v>
+        <v>3034</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>159</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>3521</v>
+        <v>3517</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>3508</v>
+        <v>3504</v>
       </c>
       <c r="K40"/>
     </row>
@@ -45802,22 +45802,22 @@
         <v>1243</v>
       </c>
       <c r="D41" t="s">
-        <v>3490</v>
+        <v>3486</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>3407</v>
+        <v>3403</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>3037</v>
+        <v>3034</v>
       </c>
       <c r="G41" t="s">
         <v>159</v>
       </c>
       <c r="H41" t="s">
-        <v>3494</v>
+        <v>3490</v>
       </c>
       <c r="I41" t="s">
-        <v>3501</v>
+        <v>3497</v>
       </c>
     </row>
     <row r="44" spans="1:11" s="259" customFormat="1" ht="15.5">
@@ -45848,7 +45848,7 @@
         <v>244</v>
       </c>
       <c r="H45" t="s">
-        <v>3308</v>
+        <v>3304</v>
       </c>
     </row>
     <row r="49" spans="1:12" s="4" customFormat="1">
@@ -46240,16 +46240,16 @@
         <v>62</v>
       </c>
       <c r="H2" s="298" t="s">
-        <v>3487</v>
+        <v>3483</v>
       </c>
       <c r="I2" s="442" t="s">
         <v>2908</v>
       </c>
       <c r="J2" s="107" t="s">
-        <v>3285</v>
+        <v>3281</v>
       </c>
       <c r="K2" s="30" t="s">
-        <v>3413</v>
+        <v>3409</v>
       </c>
       <c r="M2" s="159"/>
     </row>
@@ -46264,7 +46264,7 @@
         <v>1176</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
       <c r="E4" s="32" t="s">
         <v>2358</v>
@@ -46276,25 +46276,25 @@
         <v>270</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>3477</v>
+        <v>3473</v>
       </c>
       <c r="I4" s="217" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="J4" s="139" t="s">
-        <v>3297</v>
+        <v>3293</v>
       </c>
       <c r="K4" s="139" t="s">
-        <v>3122</v>
+        <v>3119</v>
       </c>
       <c r="M4" s="39"/>
     </row>
     <row r="5" spans="1:13" s="30" customFormat="1">
       <c r="A5" s="217" t="s">
-        <v>2991</v>
+        <v>2988</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>2996</v>
+        <v>2993</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>1110</v>
@@ -46312,13 +46312,13 @@
         <v>65</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>3261</v>
+        <v>3257</v>
       </c>
       <c r="I5" s="30" t="s">
-        <v>3664</v>
+        <v>3660</v>
       </c>
       <c r="J5" s="30" t="s">
-        <v>3051</v>
+        <v>3048</v>
       </c>
       <c r="M5" s="36"/>
     </row>
@@ -46333,7 +46333,7 @@
         <v>2682</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>3190</v>
+        <v>3187</v>
       </c>
       <c r="E6" s="140" t="s">
         <v>2648</v>
@@ -46345,7 +46345,7 @@
         <v>65</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>3256</v>
+        <v>3252</v>
       </c>
       <c r="I6" s="32" t="s">
         <v>2904</v>
@@ -46354,13 +46354,13 @@
         <v>2906</v>
       </c>
       <c r="K6" s="30" t="s">
-        <v>3582</v>
+        <v>3578</v>
       </c>
       <c r="M6" s="36"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="107" t="s">
-        <v>3533</v>
+        <v>3529</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>1206</v>
@@ -46369,28 +46369,28 @@
         <v>1087</v>
       </c>
       <c r="D7" t="s">
-        <v>3057</v>
+        <v>3054</v>
       </c>
       <c r="E7" s="107" t="s">
-        <v>3039</v>
+        <v>3036</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>3040</v>
+        <v>3037</v>
       </c>
       <c r="G7" s="106" t="s">
         <v>719</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>3615</v>
+        <v>3611</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>3331</v>
+        <v>3327</v>
       </c>
       <c r="J7" s="30" t="s">
-        <v>3357</v>
+        <v>3353</v>
       </c>
       <c r="K7" s="30" t="s">
-        <v>3394</v>
+        <v>3390</v>
       </c>
       <c r="M7" s="36"/>
     </row>
@@ -46405,7 +46405,7 @@
         <v>982</v>
       </c>
       <c r="D8" s="139" t="s">
-        <v>3142</v>
+        <v>3139</v>
       </c>
       <c r="E8" s="107" t="s">
         <v>1152</v>
@@ -46417,22 +46417,22 @@
         <v>65</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>3266</v>
+        <v>3262</v>
       </c>
       <c r="I8" s="32" t="s">
-        <v>3435</v>
+        <v>3431</v>
       </c>
       <c r="J8" s="107" t="s">
-        <v>3356</v>
+        <v>3352</v>
       </c>
       <c r="K8" s="139" t="s">
-        <v>3100</v>
+        <v>3097</v>
       </c>
       <c r="M8" s="36"/>
     </row>
     <row r="9" spans="1:13" s="107" customFormat="1">
       <c r="A9" s="300" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="B9" s="32" t="s">
         <v>1656</v>
@@ -46453,22 +46453,22 @@
         <v>65</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>3373</v>
+        <v>3369</v>
       </c>
       <c r="I9" s="107" t="s">
-        <v>3281</v>
+        <v>3277</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>3665</v>
+        <v>3661</v>
       </c>
       <c r="K9" s="107" t="s">
-        <v>3400</v>
+        <v>3396</v>
       </c>
       <c r="M9" s="36"/>
     </row>
     <row r="10" spans="1:13" s="30" customFormat="1">
       <c r="A10" s="30" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="B10" s="30">
         <v>69575383</v>
@@ -46489,16 +46489,16 @@
         <v>65</v>
       </c>
       <c r="H10" s="107" t="s">
-        <v>3637</v>
+        <v>3633</v>
       </c>
       <c r="I10" t="s">
-        <v>3065</v>
+        <v>3062</v>
       </c>
       <c r="J10" s="219" t="s">
-        <v>3182</v>
+        <v>3179</v>
       </c>
       <c r="K10" s="441" t="s">
-        <v>3443</v>
+        <v>3439</v>
       </c>
       <c r="M10" s="34"/>
     </row>
@@ -46525,22 +46525,22 @@
         <v>605</v>
       </c>
       <c r="H11" s="139" t="s">
-        <v>3535</v>
+        <v>3531</v>
       </c>
       <c r="I11" s="30" t="s">
-        <v>3269</v>
+        <v>3265</v>
       </c>
       <c r="J11" s="107" t="s">
-        <v>3379</v>
+        <v>3375</v>
       </c>
       <c r="K11" s="107" t="s">
-        <v>3381</v>
+        <v>3377</v>
       </c>
       <c r="M11" s="36"/>
     </row>
     <row r="12" spans="1:13" s="106" customFormat="1">
       <c r="A12" s="106" t="s">
-        <v>3290</v>
+        <v>3286</v>
       </c>
       <c r="B12" s="106">
         <v>69581554</v>
@@ -46549,7 +46549,7 @@
         <v>72</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>3396</v>
+        <v>3392</v>
       </c>
       <c r="E12" s="106" t="s">
         <v>907</v>
@@ -46561,31 +46561,31 @@
         <v>245</v>
       </c>
       <c r="H12" s="30" t="s">
-        <v>3398</v>
+        <v>3394</v>
       </c>
       <c r="I12" s="106" t="s">
-        <v>3251</v>
+        <v>3247</v>
       </c>
       <c r="J12" s="106" t="s">
-        <v>3397</v>
+        <v>3393</v>
       </c>
       <c r="K12" s="107" t="s">
-        <v>2993</v>
+        <v>2990</v>
       </c>
       <c r="M12" s="151"/>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="140" t="s">
-        <v>3134</v>
+        <v>3131</v>
       </c>
       <c r="B13" s="107" t="s">
         <v>2708</v>
       </c>
       <c r="C13" t="s">
-        <v>3200</v>
+        <v>3196</v>
       </c>
       <c r="D13" t="s">
-        <v>3654</v>
+        <v>3650</v>
       </c>
       <c r="E13" t="s">
         <v>2370</v>
@@ -46597,14 +46597,14 @@
         <v>270</v>
       </c>
       <c r="H13" s="30" t="s">
-        <v>3656</v>
+        <v>3652</v>
       </c>
       <c r="I13" s="145"/>
       <c r="J13" s="107" t="s">
-        <v>3670</v>
+        <v>3666</v>
       </c>
       <c r="K13" t="s">
-        <v>3655</v>
+        <v>3651</v>
       </c>
     </row>
     <row r="14" spans="1:13" s="107" customFormat="1">
@@ -46630,13 +46630,13 @@
         <v>65</v>
       </c>
       <c r="H14" s="107" t="s">
-        <v>3070</v>
+        <v>3067</v>
       </c>
       <c r="I14" s="409" t="s">
         <v>2238</v>
       </c>
       <c r="J14" s="32" t="s">
-        <v>3579</v>
+        <v>3575</v>
       </c>
       <c r="M14" s="36"/>
     </row>
@@ -46663,16 +46663,16 @@
         <v>66</v>
       </c>
       <c r="H15" t="s">
+        <v>3211</v>
+      </c>
+      <c r="I15" t="s">
         <v>3215</v>
       </c>
-      <c r="I15" t="s">
-        <v>3219</v>
-      </c>
       <c r="J15" t="s">
-        <v>3650</v>
+        <v>3646</v>
       </c>
       <c r="K15" s="107" t="s">
-        <v>3431</v>
+        <v>3427</v>
       </c>
       <c r="M15" s="36"/>
     </row>
@@ -46703,7 +46703,7 @@
     </row>
     <row r="17" spans="1:13" s="30" customFormat="1">
       <c r="A17" s="30" t="s">
-        <v>3467</v>
+        <v>3463</v>
       </c>
       <c r="B17" s="30" t="s">
         <v>1827</v>
@@ -46712,7 +46712,7 @@
         <v>1611</v>
       </c>
       <c r="D17" s="249" t="s">
-        <v>3500</v>
+        <v>3496</v>
       </c>
       <c r="E17" s="140" t="s">
         <v>1612</v>
@@ -46724,16 +46724,16 @@
         <v>66</v>
       </c>
       <c r="H17" t="s">
-        <v>3271</v>
+        <v>3267</v>
       </c>
       <c r="I17" s="30" t="s">
-        <v>3506</v>
+        <v>3502</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>3321</v>
+        <v>3317</v>
       </c>
       <c r="K17" s="220" t="s">
-        <v>3263</v>
+        <v>3259</v>
       </c>
       <c r="M17" s="34"/>
     </row>
@@ -46760,16 +46760,16 @@
         <v>66</v>
       </c>
       <c r="H18" s="30" t="s">
-        <v>3581</v>
+        <v>3577</v>
       </c>
       <c r="I18" t="s">
-        <v>3587</v>
+        <v>3583</v>
       </c>
       <c r="J18" t="s">
-        <v>3649</v>
+        <v>3645</v>
       </c>
       <c r="K18" t="s">
-        <v>3385</v>
+        <v>3381</v>
       </c>
       <c r="M18" s="36"/>
     </row>
@@ -46784,7 +46784,7 @@
         <v>1673</v>
       </c>
       <c r="D19" s="134" t="s">
-        <v>3143</v>
+        <v>3140</v>
       </c>
       <c r="E19" t="s">
         <v>1676</v>
@@ -46796,19 +46796,19 @@
         <v>66</v>
       </c>
       <c r="H19" t="s">
-        <v>3544</v>
+        <v>3540</v>
       </c>
       <c r="I19" t="s">
-        <v>3480</v>
+        <v>3476</v>
       </c>
       <c r="J19" s="220" t="s">
-        <v>3584</v>
+        <v>3580</v>
       </c>
       <c r="M19" s="36"/>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="300" t="s">
-        <v>3583</v>
+        <v>3579</v>
       </c>
       <c r="B20" t="s">
         <v>2441</v>
@@ -46829,31 +46829,31 @@
         <v>65</v>
       </c>
       <c r="H20" s="432" t="s">
-        <v>3189</v>
+        <v>3186</v>
       </c>
       <c r="I20" t="s">
-        <v>3474</v>
+        <v>3470</v>
       </c>
       <c r="J20" t="s">
-        <v>3507</v>
+        <v>3503</v>
       </c>
       <c r="K20" t="s">
-        <v>3423</v>
+        <v>3419</v>
       </c>
       <c r="M20" s="36"/>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>3075</v>
+        <v>3072</v>
       </c>
       <c r="B21" t="s">
-        <v>3080</v>
+        <v>3077</v>
       </c>
       <c r="C21" s="22" t="s">
         <v>1125</v>
       </c>
       <c r="D21" t="s">
-        <v>3079</v>
+        <v>3076</v>
       </c>
       <c r="E21" s="140" t="s">
         <v>1573</v>
@@ -46865,19 +46865,19 @@
         <v>65</v>
       </c>
       <c r="H21" t="s">
+        <v>3081</v>
+      </c>
+      <c r="I21" t="s">
         <v>3084</v>
       </c>
-      <c r="I21" t="s">
-        <v>3087</v>
-      </c>
       <c r="J21" t="s">
-        <v>3088</v>
+        <v>3085</v>
       </c>
       <c r="M21" s="36"/>
     </row>
     <row r="22" spans="1:13" s="30" customFormat="1">
       <c r="A22" s="30" t="s">
-        <v>3091</v>
+        <v>3088</v>
       </c>
       <c r="B22" s="30" t="s">
         <v>2087</v>
@@ -46886,95 +46886,95 @@
         <v>2651</v>
       </c>
       <c r="D22" s="107" t="s">
-        <v>3128</v>
+        <v>3125</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>3102</v>
+        <v>3099</v>
       </c>
       <c r="F22" s="30" t="s">
-        <v>3103</v>
+        <v>3100</v>
       </c>
       <c r="G22" s="32" t="s">
         <v>65</v>
       </c>
       <c r="H22" s="30" t="s">
+        <v>3104</v>
+      </c>
+      <c r="I22" s="30" t="s">
+        <v>3106</v>
+      </c>
+      <c r="J22" s="30" t="s">
         <v>3107</v>
-      </c>
-      <c r="I22" s="30" t="s">
-        <v>3109</v>
-      </c>
-      <c r="J22" s="30" t="s">
-        <v>3110</v>
       </c>
       <c r="M22" s="36"/>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>3091</v>
+        <v>3088</v>
       </c>
       <c r="B23" t="s">
-        <v>3123</v>
+        <v>3120</v>
       </c>
       <c r="C23" s="22" t="s">
         <v>1884</v>
       </c>
       <c r="D23" t="s">
-        <v>3175</v>
+        <v>3172</v>
       </c>
       <c r="E23" s="30" t="s">
-        <v>3102</v>
+        <v>3099</v>
       </c>
       <c r="F23" s="30" t="s">
-        <v>3103</v>
+        <v>3100</v>
       </c>
       <c r="G23" t="s">
         <v>66</v>
       </c>
       <c r="H23" t="s">
-        <v>3211</v>
+        <v>3207</v>
       </c>
       <c r="I23" t="s">
-        <v>3210</v>
+        <v>3206</v>
       </c>
       <c r="J23" t="s">
-        <v>3203</v>
+        <v>3199</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="30" t="s">
-        <v>3486</v>
+        <v>3482</v>
       </c>
       <c r="B24" t="s">
-        <v>3609</v>
+        <v>3605</v>
       </c>
       <c r="C24" s="22" t="s">
         <v>1898</v>
       </c>
       <c r="D24" t="s">
-        <v>3346</v>
+        <v>3342</v>
       </c>
       <c r="E24" s="107" t="s">
-        <v>3348</v>
+        <v>3344</v>
       </c>
       <c r="F24" s="30" t="s">
-        <v>3338</v>
+        <v>3334</v>
       </c>
       <c r="G24" s="32" t="s">
         <v>270</v>
       </c>
       <c r="H24" t="s">
-        <v>3593</v>
+        <v>3589</v>
       </c>
       <c r="I24" t="s">
-        <v>3589</v>
+        <v>3585</v>
       </c>
       <c r="J24" t="s">
-        <v>3616</v>
+        <v>3612</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" t="s">
-        <v>3290</v>
+        <v>3286</v>
       </c>
       <c r="B25" t="s">
         <v>2771</v>
@@ -46983,7 +46983,7 @@
         <v>1104</v>
       </c>
       <c r="D25" t="s">
-        <v>3503</v>
+        <v>3499</v>
       </c>
       <c r="E25" s="107" t="s">
         <v>1121</v>
@@ -46995,13 +46995,13 @@
         <v>65</v>
       </c>
       <c r="H25" t="s">
-        <v>3492</v>
+        <v>3488</v>
       </c>
       <c r="I25" t="s">
-        <v>3499</v>
+        <v>3495</v>
       </c>
       <c r="J25" t="s">
-        <v>3504</v>
+        <v>3500</v>
       </c>
       <c r="M25" s="36"/>
     </row>
@@ -47010,13 +47010,13 @@
         <v>2662</v>
       </c>
       <c r="B26" s="107" t="s">
-        <v>3512</v>
+        <v>3508</v>
       </c>
       <c r="C26" s="22" t="s">
         <v>918</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>3511</v>
+        <v>3507</v>
       </c>
       <c r="E26" s="140" t="s">
         <v>2683</v>
@@ -47028,13 +47028,13 @@
         <v>65</v>
       </c>
       <c r="H26" s="30" t="s">
-        <v>3513</v>
+        <v>3509</v>
       </c>
       <c r="I26" s="30" t="s">
-        <v>3560</v>
+        <v>3556</v>
       </c>
       <c r="J26" s="107" t="s">
-        <v>3596</v>
+        <v>3592</v>
       </c>
       <c r="K26"/>
       <c r="M26" s="36"/>
@@ -47073,7 +47073,7 @@
     </row>
     <row r="31" spans="1:13" s="30" customFormat="1">
       <c r="A31" s="107" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="B31" s="107">
         <v>64403333</v>
@@ -47121,7 +47121,7 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" t="s">
-        <v>3264</v>
+        <v>3260</v>
       </c>
       <c r="B33">
         <v>60389752</v>
@@ -47144,7 +47144,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" t="s">
-        <v>3176</v>
+        <v>3173</v>
       </c>
       <c r="B34">
         <v>60389752</v>
@@ -47153,13 +47153,13 @@
         <v>2146</v>
       </c>
       <c r="D34" s="32" t="s">
-        <v>2998</v>
+        <v>2995</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>3102</v>
+        <v>3099</v>
       </c>
       <c r="F34" s="30" t="s">
-        <v>3103</v>
+        <v>3100</v>
       </c>
       <c r="G34" t="s">
         <v>3</v>
@@ -47168,7 +47168,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>3075</v>
+        <v>3072</v>
       </c>
       <c r="B35">
         <v>60389752</v>
@@ -47225,13 +47225,13 @@
         <v>1208</v>
       </c>
       <c r="D37" t="s">
-        <v>3345</v>
+        <v>3341</v>
       </c>
       <c r="E37" s="107" t="s">
-        <v>3348</v>
+        <v>3344</v>
       </c>
       <c r="F37" s="30" t="s">
-        <v>3338</v>
+        <v>3334</v>
       </c>
       <c r="G37" s="106" t="s">
         <v>719</v>
@@ -47241,7 +47241,7 @@
     </row>
     <row r="38" spans="1:13" s="30" customFormat="1">
       <c r="A38" s="30" t="s">
-        <v>3176</v>
+        <v>3173</v>
       </c>
       <c r="B38" s="30">
         <v>60389752</v>
@@ -47278,10 +47278,10 @@
         <v>2120</v>
       </c>
       <c r="E39" t="s">
-        <v>3102</v>
+        <v>3099</v>
       </c>
       <c r="F39" t="s">
-        <v>3103</v>
+        <v>3100</v>
       </c>
       <c r="G39" t="s">
         <v>3</v>
@@ -47345,7 +47345,7 @@
         <v>2461</v>
       </c>
       <c r="E45" s="281" t="s">
-        <v>3004</v>
+        <v>3001</v>
       </c>
       <c r="F45" s="30" t="s">
         <v>2462</v>
@@ -47354,10 +47354,10 @@
         <v>369</v>
       </c>
       <c r="H45" s="49" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
       <c r="I45" s="30" t="s">
-        <v>3072</v>
+        <v>3069</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -47409,16 +47409,16 @@
     </row>
     <row r="68" spans="1:38">
       <c r="C68" s="138" t="s">
-        <v>3311</v>
+        <v>3307</v>
       </c>
       <c r="D68" t="s">
-        <v>3510</v>
+        <v>3506</v>
       </c>
       <c r="E68" s="107" t="s">
-        <v>3348</v>
+        <v>3344</v>
       </c>
       <c r="F68" s="30" t="s">
-        <v>3338</v>
+        <v>3334</v>
       </c>
       <c r="G68" s="106" t="s">
         <v>719</v>
@@ -47432,13 +47432,13 @@
         <v>2147</v>
       </c>
       <c r="D70" t="s">
-        <v>3509</v>
+        <v>3505</v>
       </c>
       <c r="E70" s="107" t="s">
-        <v>3348</v>
+        <v>3344</v>
       </c>
       <c r="F70" s="30" t="s">
-        <v>3338</v>
+        <v>3334</v>
       </c>
       <c r="M70" s="36"/>
     </row>
@@ -47498,7 +47498,7 @@
         <v>916</v>
       </c>
       <c r="D79" s="30" t="s">
-        <v>3568</v>
+        <v>3564</v>
       </c>
       <c r="E79" s="107" t="s">
         <v>1088</v>
@@ -47523,7 +47523,7 @@
         <v>1429</v>
       </c>
       <c r="D81" t="s">
-        <v>3569</v>
+        <v>3565</v>
       </c>
       <c r="M81" s="36"/>
     </row>
@@ -47549,7 +47549,7 @@
         <v>915</v>
       </c>
       <c r="D83" s="30" t="s">
-        <v>3570</v>
+        <v>3566</v>
       </c>
       <c r="E83" s="30" t="s">
         <v>1095</v>
@@ -47569,7 +47569,7 @@
         <v>997</v>
       </c>
       <c r="D84" s="139" t="s">
-        <v>3571</v>
+        <v>3567</v>
       </c>
       <c r="E84" s="107" t="s">
         <v>1073</v>
@@ -47589,7 +47589,7 @@
         <v>936</v>
       </c>
       <c r="D85" s="107" t="s">
-        <v>3572</v>
+        <v>3568</v>
       </c>
       <c r="E85" s="139" t="s">
         <v>998</v>
@@ -47608,7 +47608,7 @@
         <v>946</v>
       </c>
       <c r="D86" s="30" t="s">
-        <v>3573</v>
+        <v>3569</v>
       </c>
       <c r="E86" s="107" t="s">
         <v>1004</v>
@@ -47630,7 +47630,7 @@
         <v>1006</v>
       </c>
       <c r="D87" t="s">
-        <v>3574</v>
+        <v>3570</v>
       </c>
       <c r="E87" s="107" t="s">
         <v>1253</v>
@@ -47648,7 +47648,7 @@
         <v>1043</v>
       </c>
       <c r="D88" s="30" t="s">
-        <v>3575</v>
+        <v>3571</v>
       </c>
       <c r="E88" s="107" t="s">
         <v>1044</v>
@@ -47668,7 +47668,7 @@
         <v>1054</v>
       </c>
       <c r="D89" s="30" t="s">
-        <v>3576</v>
+        <v>3572</v>
       </c>
       <c r="E89" s="107" t="s">
         <v>1055</v>
@@ -47692,7 +47692,7 @@
         <v>1126</v>
       </c>
       <c r="D91" t="s">
-        <v>3577</v>
+        <v>3573</v>
       </c>
       <c r="E91" s="140" t="s">
         <v>1131</v>
@@ -47711,7 +47711,7 @@
         <v>1127</v>
       </c>
       <c r="D92" t="s">
-        <v>3578</v>
+        <v>3574</v>
       </c>
       <c r="E92" s="140" t="s">
         <v>1131</v>
@@ -47733,7 +47733,7 @@
         <v>1128</v>
       </c>
       <c r="D93" t="s">
-        <v>3098</v>
+        <v>3095</v>
       </c>
       <c r="E93" s="140" t="s">
         <v>1130</v>
@@ -47757,7 +47757,7 @@
         <v>1384</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>3099</v>
+        <v>3096</v>
       </c>
       <c r="E94" s="264" t="s">
         <v>1491</v>
@@ -47811,7 +47811,7 @@
         <v>358</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>3200</v>
+        <v>3196</v>
       </c>
     </row>
     <row r="105" spans="2:5">
@@ -48248,27 +48248,27 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="87" t="s">
+        <v>3152</v>
+      </c>
+      <c r="C40" t="s">
         <v>3155</v>
-      </c>
-      <c r="C40" t="s">
-        <v>3158</v>
       </c>
       <c r="F40" s="45"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="89" t="s">
+        <v>3153</v>
+      </c>
+      <c r="C41" t="s">
         <v>3156</v>
-      </c>
-      <c r="C41" t="s">
-        <v>3159</v>
       </c>
     </row>
     <row r="42" spans="2:6" ht="15" thickBot="1">
       <c r="B42" s="86" t="s">
+        <v>3154</v>
+      </c>
+      <c r="C42" t="s">
         <v>3157</v>
-      </c>
-      <c r="C42" t="s">
-        <v>3160</v>
       </c>
     </row>
     <row r="43" spans="2:6">
@@ -48431,22 +48431,22 @@
         <v>2012</v>
       </c>
       <c r="E6" s="246" t="s">
-        <v>3030</v>
+        <v>3027</v>
       </c>
       <c r="F6" s="246" t="s">
-        <v>3031</v>
+        <v>3028</v>
       </c>
       <c r="G6" s="246" t="s">
         <v>357</v>
       </c>
       <c r="H6" s="246" t="s">
-        <v>3666</v>
+        <v>3662</v>
       </c>
       <c r="I6" s="243" t="s">
-        <v>3270</v>
+        <v>3266</v>
       </c>
       <c r="J6" s="293" t="s">
-        <v>3369</v>
+        <v>3365</v>
       </c>
       <c r="K6" s="246" t="s">
         <v>475</v>
@@ -48454,7 +48454,7 @@
     </row>
     <row r="7" spans="1:12" s="106" customFormat="1">
       <c r="A7" s="30" t="s">
-        <v>3449</v>
+        <v>3445</v>
       </c>
       <c r="B7" t="s">
         <v>1827</v>
@@ -48469,19 +48469,19 @@
         <v>1035</v>
       </c>
       <c r="F7" s="106" t="s">
-        <v>3032</v>
+        <v>3029</v>
       </c>
       <c r="G7" s="106" t="s">
         <v>689</v>
       </c>
       <c r="H7" s="219" t="s">
-        <v>3028</v>
+        <v>3025</v>
       </c>
       <c r="I7" s="219" t="s">
-        <v>3446</v>
+        <v>3442</v>
       </c>
       <c r="J7" s="219" t="s">
-        <v>3224</v>
+        <v>3220</v>
       </c>
       <c r="K7" s="106" t="s">
         <v>708</v>
@@ -48501,29 +48501,29 @@
         <v>868</v>
       </c>
       <c r="E8" s="263" t="s">
-        <v>3617</v>
+        <v>3613</v>
       </c>
       <c r="F8" s="263" t="s">
-        <v>3618</v>
+        <v>3614</v>
       </c>
       <c r="G8" s="263" t="s">
         <v>250</v>
       </c>
       <c r="H8" s="263" t="s">
-        <v>3361</v>
+        <v>3357</v>
       </c>
       <c r="I8" s="263" t="s">
-        <v>3169</v>
+        <v>3166</v>
       </c>
       <c r="J8" s="263" t="s">
-        <v>3235</v>
+        <v>3231</v>
       </c>
       <c r="K8" s="257"/>
       <c r="L8" s="257"/>
     </row>
     <row r="9" spans="1:12" s="257" customFormat="1">
       <c r="A9" s="424" t="s">
-        <v>3344</v>
+        <v>3340</v>
       </c>
       <c r="B9" s="262">
         <v>64403333</v>
@@ -48538,7 +48538,7 @@
         <v>2638</v>
       </c>
       <c r="F9" s="261" t="s">
-        <v>3124</v>
+        <v>3121</v>
       </c>
       <c r="G9" s="261" t="s">
         <v>945</v>
@@ -48570,13 +48570,13 @@
         <v>689</v>
       </c>
       <c r="H10" s="262" t="s">
-        <v>3401</v>
+        <v>3397</v>
       </c>
       <c r="I10" s="262" t="s">
-        <v>3419</v>
+        <v>3415</v>
       </c>
       <c r="J10" s="262" t="s">
-        <v>3300</v>
+        <v>3296</v>
       </c>
       <c r="K10" s="244" t="s">
         <v>1200</v>
@@ -48584,10 +48584,10 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="260" t="s">
-        <v>3537</v>
+        <v>3533</v>
       </c>
       <c r="B11" s="260" t="s">
-        <v>3024</v>
+        <v>3021</v>
       </c>
       <c r="C11" s="194" t="s">
         <v>491</v>
@@ -48599,19 +48599,19 @@
         <v>2638</v>
       </c>
       <c r="F11" s="216" t="s">
-        <v>3433</v>
+        <v>3429</v>
       </c>
       <c r="G11" s="216" t="s">
         <v>689</v>
       </c>
       <c r="H11" s="215" t="s">
-        <v>3207</v>
+        <v>3203</v>
       </c>
       <c r="I11" s="423" t="s">
-        <v>3183</v>
+        <v>3180</v>
       </c>
       <c r="J11" s="267" t="s">
-        <v>3315</v>
+        <v>3311</v>
       </c>
       <c r="K11" s="183" t="s">
         <v>1201</v>
@@ -48645,10 +48645,10 @@
     </row>
     <row r="13" spans="1:12" s="223" customFormat="1">
       <c r="A13" s="223" t="s">
-        <v>3075</v>
+        <v>3072</v>
       </c>
       <c r="B13" s="223" t="s">
-        <v>3097</v>
+        <v>3094</v>
       </c>
       <c r="C13" s="422" t="s">
         <v>335</v>
@@ -48660,7 +48660,7 @@
         <v>2638</v>
       </c>
       <c r="F13" s="223" t="s">
-        <v>3634</v>
+        <v>3630</v>
       </c>
       <c r="G13" s="223" t="s">
         <v>689</v>
@@ -48669,10 +48669,10 @@
         <v>2903</v>
       </c>
       <c r="I13" s="223" t="s">
-        <v>3674</v>
+        <v>3670</v>
       </c>
       <c r="J13" s="455" t="s">
-        <v>3643</v>
+        <v>3639</v>
       </c>
       <c r="K13" s="223" t="s">
         <v>1312</v>
@@ -48695,19 +48695,19 @@
         <v>2638</v>
       </c>
       <c r="F14" s="216" t="s">
-        <v>3634</v>
+        <v>3630</v>
       </c>
       <c r="G14" s="216" t="s">
         <v>689</v>
       </c>
       <c r="H14" s="270" t="s">
-        <v>3225</v>
+        <v>3221</v>
       </c>
       <c r="I14" s="215" t="s">
         <v>2860</v>
       </c>
       <c r="J14" s="260" t="s">
-        <v>3536</v>
+        <v>3532</v>
       </c>
       <c r="K14" s="183" t="s">
         <v>1202</v>
@@ -48715,10 +48715,10 @@
     </row>
     <row r="15" spans="1:12" s="257" customFormat="1">
       <c r="A15" s="262" t="s">
-        <v>3458</v>
+        <v>3454</v>
       </c>
       <c r="B15" s="262" t="s">
-        <v>3459</v>
+        <v>3455</v>
       </c>
       <c r="C15" s="268" t="s">
         <v>1300</v>
@@ -48736,13 +48736,13 @@
         <v>689</v>
       </c>
       <c r="H15" s="262" t="s">
-        <v>3642</v>
+        <v>3638</v>
       </c>
       <c r="I15" s="269" t="s">
-        <v>3339</v>
+        <v>3335</v>
       </c>
       <c r="J15" s="217" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="K15" s="257" t="s">
         <v>1425</v>
@@ -48750,7 +48750,7 @@
     </row>
     <row r="16" spans="1:12" s="262" customFormat="1">
       <c r="A16" s="269" t="s">
-        <v>3537</v>
+        <v>3533</v>
       </c>
       <c r="B16" s="269">
         <v>64403333</v>
@@ -48809,7 +48809,7 @@
         <v>830</v>
       </c>
       <c r="D18" s="262" t="s">
-        <v>3237</v